--- a/DSA Master Sheet.xlsx
+++ b/DSA Master Sheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2d5460abf00c5a51/Desktop/DSA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\OneDrive\Desktop\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{943D0165-5182-41A4-97BF-F526F8BAFB59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C875588-5F5E-4C3C-99B6-C778E82AB4BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="714">
   <si>
     <t>DSA Master Sheet</t>
   </si>
@@ -2319,16 +2319,282 @@
     }</t>
     </r>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Right-to-Left Traversal with Running Maximum :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> think from right of array to find max element 
+        ArrayList&lt;Integer&gt; al = new ArrayList&lt;&gt;();
+        int max = arr[arr.length-1];
+        al.add(max);
+        for(int i = arr.length-2 ; i&gt;=0 ; i--){
+            if(arr[i]&gt;=max){
+                al.add(arr[i]);
+                max = arr[i];
+            }
+        }
+        Collections.reverse(al);
+        return al;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Optimized Trial Division using √n  :
+         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>static boolean isPrime(int n) {
+if (n &lt; 2) return false;
+        for (int i = 2; i * i &lt;= n; i++) {
+            if (n % i == 0)
+                return false;
+        }
+        return true;
+    }</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>for 20 : factors 1 2, 4, 5, 10 ,20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> approach : 1*20 = 20 , 2*10 = 20 , 4*5 = 20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+        ArrayList&lt;Integer&gt; getDivisors(int n) {   ArrayList&lt;Integer&gt; al = new ArrayList&lt;&gt;();
+        for(int num = 1 ; num*num&lt;=n ; num++){
+            if(n%num==0){
+                al.add(num);
+                if(n/num!=num){
+                    al.add(n/num);
+                }
+            }
+        }
+        Collections.sort(al);
+        return al;</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">        while((a%b)!=0){
+            temp = b;
+            b= a%b;
+            a = temp;
+        }</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Boyer–Moore Majority Vote Algorithm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>same element → +1
+different element → -1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+When two different elements meet, they cancel each other.
+  int candidate = 0 , count = 0;
+        for (int num : nums) {
+            if (count == 0) 
+                candidate = num;
+            if (num == candidate) {
+                count++;
+            } else {
+                count--;
+            }
+        }
+        return candidate;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Optimal approach: Reversal Algorithm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+You can rotate the array using three reversals without creating another array.
+Example:
+[1, 2, 3, 4, 5, 6, 7]
+k = 3
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Step 1: Reverse entire array</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+[7, 6, 5, 4, 3, 2, 1]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Step 2: Reverse first k elements</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+[5, 6, 7, 4, 3, 2, 1]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Step 3: Reverse remaining elements</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+[5, 6, 7, 1, 2, 3, 4]</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="86">
+  <fonts count="92">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2842,6 +3108,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="55">
     <fill>
@@ -3349,45 +3636,34 @@
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="81" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="82" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="83" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="84" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="85" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="86" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="163">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3397,361 +3673,342 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="23" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="23" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="23" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="23" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="24" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="26" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="27" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="27" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="27" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="27" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="28" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="29" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="30" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="30" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="30" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="30" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="31" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="32" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="32" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="27" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="27" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="27" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="27" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="34" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="34" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="34" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="34" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="35" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="35" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="36" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="36" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="36" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="36" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="37" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="37" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="38" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="38" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="38" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="38" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="39" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="39" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="40" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="40" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="41" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="41" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="42" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="42" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="42" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="42" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="43" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="43" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="44" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="67" fillId="44" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="44" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="68" fillId="44" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="45" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="45" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="46" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="46" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="46" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="46" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="47" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="47" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="71" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="48" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="48" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="49" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="49" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="49" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="49" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="50" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="50" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="51" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="51" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="51" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="51" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="77" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="78" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="81" fillId="52" borderId="8" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="82" fillId="53" borderId="8" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="83" fillId="54" borderId="8" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="84" fillId="52" borderId="8" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="85" fillId="53" borderId="8" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="86" fillId="54" borderId="8" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3759,22 +4016,61 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4014,18 +4310,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="30.75" customHeight="1">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="154" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="134"/>
+      <c r="B1" s="155"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="155"/>
+      <c r="G1" s="155"/>
+      <c r="H1" s="155"/>
+      <c r="I1" s="155"/>
+      <c r="J1" s="156"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -4080,18 +4376,18 @@
       <c r="T2" s="5"/>
     </row>
     <row r="3" spans="1:20" ht="13.8">
-      <c r="A3" s="135" t="s">
+      <c r="A3" s="153" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="136"/>
-      <c r="C3" s="136"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="136"/>
-      <c r="F3" s="136"/>
-      <c r="G3" s="136"/>
-      <c r="H3" s="136"/>
-      <c r="I3" s="136"/>
-      <c r="J3" s="137"/>
+      <c r="B3" s="146"/>
+      <c r="C3" s="146"/>
+      <c r="D3" s="146"/>
+      <c r="E3" s="146"/>
+      <c r="F3" s="146"/>
+      <c r="G3" s="146"/>
+      <c r="H3" s="146"/>
+      <c r="I3" s="146"/>
+      <c r="J3" s="147"/>
     </row>
     <row r="4" spans="1:20" ht="13.8">
       <c r="A4" s="6">
@@ -4103,7 +4399,7 @@
       <c r="C4" s="138" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="129" t="s">
+      <c r="D4" s="143" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -4133,8 +4429,8 @@
       <c r="B5" s="7">
         <v>2</v>
       </c>
-      <c r="C5" s="130"/>
-      <c r="D5" s="130"/>
+      <c r="C5" s="135"/>
+      <c r="D5" s="135"/>
       <c r="E5" s="8" t="s">
         <v>16</v>
       </c>
@@ -4162,8 +4458,8 @@
       <c r="B6" s="7">
         <v>3</v>
       </c>
-      <c r="C6" s="130"/>
-      <c r="D6" s="130"/>
+      <c r="C6" s="135"/>
+      <c r="D6" s="135"/>
       <c r="E6" s="8" t="s">
         <v>19</v>
       </c>
@@ -4191,8 +4487,8 @@
       <c r="B7" s="7">
         <v>4</v>
       </c>
-      <c r="C7" s="130"/>
-      <c r="D7" s="130"/>
+      <c r="C7" s="135"/>
+      <c r="D7" s="135"/>
       <c r="E7" s="8" t="s">
         <v>23</v>
       </c>
@@ -4220,8 +4516,8 @@
       <c r="B8" s="7">
         <v>5</v>
       </c>
-      <c r="C8" s="130"/>
-      <c r="D8" s="130"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="135"/>
       <c r="E8" s="8" t="s">
         <v>26</v>
       </c>
@@ -4249,8 +4545,8 @@
       <c r="B9" s="7">
         <v>6</v>
       </c>
-      <c r="C9" s="130"/>
-      <c r="D9" s="131"/>
+      <c r="C9" s="135"/>
+      <c r="D9" s="136"/>
       <c r="E9" s="8" t="s">
         <v>29</v>
       </c>
@@ -4275,8 +4571,8 @@
       <c r="B10" s="7">
         <v>7</v>
       </c>
-      <c r="C10" s="130"/>
-      <c r="D10" s="129" t="s">
+      <c r="C10" s="135"/>
+      <c r="D10" s="143" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="8" t="s">
@@ -4303,8 +4599,8 @@
       <c r="B11" s="7">
         <v>8</v>
       </c>
-      <c r="C11" s="130"/>
-      <c r="D11" s="130"/>
+      <c r="C11" s="135"/>
+      <c r="D11" s="135"/>
       <c r="E11" s="13" t="s">
         <v>32</v>
       </c>
@@ -4329,8 +4625,8 @@
       <c r="B12" s="7">
         <v>9</v>
       </c>
-      <c r="C12" s="130"/>
-      <c r="D12" s="130"/>
+      <c r="C12" s="135"/>
+      <c r="D12" s="135"/>
       <c r="E12" s="8" t="s">
         <v>33</v>
       </c>
@@ -4355,8 +4651,8 @@
       <c r="B13" s="7">
         <v>10</v>
       </c>
-      <c r="C13" s="130"/>
-      <c r="D13" s="130"/>
+      <c r="C13" s="135"/>
+      <c r="D13" s="135"/>
       <c r="E13" s="8" t="s">
         <v>34</v>
       </c>
@@ -4383,8 +4679,8 @@
       <c r="B14" s="7">
         <v>11</v>
       </c>
-      <c r="C14" s="130"/>
-      <c r="D14" s="130"/>
+      <c r="C14" s="135"/>
+      <c r="D14" s="135"/>
       <c r="E14" s="8" t="s">
         <v>35</v>
       </c>
@@ -4409,8 +4705,8 @@
       <c r="B15" s="7">
         <v>12</v>
       </c>
-      <c r="C15" s="130"/>
-      <c r="D15" s="130"/>
+      <c r="C15" s="135"/>
+      <c r="D15" s="135"/>
       <c r="E15" s="8" t="s">
         <v>36</v>
       </c>
@@ -4423,7 +4719,7 @@
       <c r="H15" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I15" s="158" t="s">
+      <c r="I15" s="130" t="s">
         <v>703</v>
       </c>
       <c r="J15" s="11" t="s">
@@ -4437,8 +4733,8 @@
       <c r="B16" s="7">
         <v>13</v>
       </c>
-      <c r="C16" s="130"/>
-      <c r="D16" s="130"/>
+      <c r="C16" s="135"/>
+      <c r="D16" s="135"/>
       <c r="E16" s="8" t="s">
         <v>37</v>
       </c>
@@ -4463,8 +4759,8 @@
       <c r="B17" s="7">
         <v>14</v>
       </c>
-      <c r="C17" s="130"/>
-      <c r="D17" s="130"/>
+      <c r="C17" s="135"/>
+      <c r="D17" s="135"/>
       <c r="E17" s="8" t="s">
         <v>38</v>
       </c>
@@ -4491,8 +4787,8 @@
       <c r="B18" s="7">
         <v>15</v>
       </c>
-      <c r="C18" s="130"/>
-      <c r="D18" s="131"/>
+      <c r="C18" s="135"/>
+      <c r="D18" s="136"/>
       <c r="E18" s="13" t="s">
         <v>39</v>
       </c>
@@ -4505,7 +4801,7 @@
       <c r="H18" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I18" s="157" t="s">
+      <c r="I18" s="129" t="s">
         <v>705</v>
       </c>
       <c r="J18" s="126" t="s">
@@ -4519,8 +4815,8 @@
       <c r="B19" s="7">
         <v>16</v>
       </c>
-      <c r="C19" s="130"/>
-      <c r="D19" s="129" t="s">
+      <c r="C19" s="135"/>
+      <c r="D19" s="143" t="s">
         <v>40</v>
       </c>
       <c r="E19" s="8" t="s">
@@ -4535,7 +4831,7 @@
       <c r="H19" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="I19" s="159" t="s">
+      <c r="I19" s="131" t="s">
         <v>706</v>
       </c>
       <c r="J19" s="126" t="s">
@@ -4549,8 +4845,8 @@
       <c r="B20" s="7">
         <v>17</v>
       </c>
-      <c r="C20" s="130"/>
-      <c r="D20" s="130"/>
+      <c r="C20" s="135"/>
+      <c r="D20" s="135"/>
       <c r="E20" s="8" t="s">
         <v>42</v>
       </c>
@@ -4563,22 +4859,22 @@
       <c r="H20" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="I20" s="157" t="s">
+      <c r="I20" s="129" t="s">
         <v>707</v>
       </c>
       <c r="J20" s="126" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="13.8">
+    <row r="21" spans="1:10" ht="207">
       <c r="A21" s="6">
         <v>18</v>
       </c>
       <c r="B21" s="7">
         <v>18</v>
       </c>
-      <c r="C21" s="130"/>
-      <c r="D21" s="130"/>
+      <c r="C21" s="135"/>
+      <c r="D21" s="135"/>
       <c r="E21" s="8" t="s">
         <v>43</v>
       </c>
@@ -4588,9 +4884,15 @@
       <c r="G21" s="10">
         <v>3</v>
       </c>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
+      <c r="H21" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" s="132" t="s">
+        <v>708</v>
+      </c>
+      <c r="J21" s="128" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="22" spans="1:10" ht="13.8">
       <c r="A22" s="6">
@@ -4599,8 +4901,8 @@
       <c r="B22" s="7">
         <v>19</v>
       </c>
-      <c r="C22" s="130"/>
-      <c r="D22" s="130"/>
+      <c r="C22" s="135"/>
+      <c r="D22" s="135"/>
       <c r="E22" s="8" t="s">
         <v>44</v>
       </c>
@@ -4621,8 +4923,8 @@
       <c r="B23" s="7">
         <v>20</v>
       </c>
-      <c r="C23" s="130"/>
-      <c r="D23" s="130"/>
+      <c r="C23" s="135"/>
+      <c r="D23" s="135"/>
       <c r="E23" s="8" t="s">
         <v>45</v>
       </c>
@@ -4643,8 +4945,8 @@
       <c r="B24" s="7">
         <v>21</v>
       </c>
-      <c r="C24" s="130"/>
-      <c r="D24" s="130"/>
+      <c r="C24" s="135"/>
+      <c r="D24" s="135"/>
       <c r="E24" s="13" t="s">
         <v>46</v>
       </c>
@@ -4654,19 +4956,23 @@
       <c r="G24" s="15">
         <v>3</v>
       </c>
-      <c r="H24" s="11"/>
+      <c r="H24" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-    </row>
-    <row r="25" spans="1:10" ht="13.8">
+      <c r="J24" s="11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="262.2">
       <c r="A25" s="6">
         <v>22</v>
       </c>
       <c r="B25" s="7">
         <v>22</v>
       </c>
-      <c r="C25" s="130"/>
-      <c r="D25" s="131"/>
+      <c r="C25" s="135"/>
+      <c r="D25" s="136"/>
       <c r="E25" s="8" t="s">
         <v>47</v>
       </c>
@@ -4676,19 +4982,25 @@
       <c r="G25" s="10">
         <v>3</v>
       </c>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-    </row>
-    <row r="26" spans="1:10" ht="13.8">
+      <c r="H25" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="162" t="s">
+        <v>712</v>
+      </c>
+      <c r="J25" s="126" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="165.6">
       <c r="A26" s="6">
         <v>23</v>
       </c>
       <c r="B26" s="7">
         <v>23</v>
       </c>
-      <c r="C26" s="130"/>
-      <c r="D26" s="129" t="s">
+      <c r="C26" s="135"/>
+      <c r="D26" s="143" t="s">
         <v>48</v>
       </c>
       <c r="E26" s="13" t="s">
@@ -4700,9 +5012,15 @@
       <c r="G26" s="15">
         <v>4</v>
       </c>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
+      <c r="H26" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="162" t="s">
+        <v>713</v>
+      </c>
+      <c r="J26" s="126" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="27" spans="1:10" ht="13.8">
       <c r="A27" s="6">
@@ -4711,8 +5029,8 @@
       <c r="B27" s="7">
         <v>24</v>
       </c>
-      <c r="C27" s="130"/>
-      <c r="D27" s="130"/>
+      <c r="C27" s="135"/>
+      <c r="D27" s="135"/>
       <c r="E27" s="8" t="s">
         <v>50</v>
       </c>
@@ -4733,8 +5051,8 @@
       <c r="B28" s="7">
         <v>25</v>
       </c>
-      <c r="C28" s="130"/>
-      <c r="D28" s="130"/>
+      <c r="C28" s="135"/>
+      <c r="D28" s="135"/>
       <c r="E28" s="8" t="s">
         <v>51</v>
       </c>
@@ -4755,8 +5073,8 @@
       <c r="B29" s="7">
         <v>26</v>
       </c>
-      <c r="C29" s="130"/>
-      <c r="D29" s="130"/>
+      <c r="C29" s="135"/>
+      <c r="D29" s="135"/>
       <c r="E29" s="8" t="s">
         <v>52</v>
       </c>
@@ -4777,8 +5095,8 @@
       <c r="B30" s="7">
         <v>27</v>
       </c>
-      <c r="C30" s="130"/>
-      <c r="D30" s="130"/>
+      <c r="C30" s="135"/>
+      <c r="D30" s="135"/>
       <c r="E30" s="8" t="s">
         <v>53</v>
       </c>
@@ -4799,8 +5117,8 @@
       <c r="B31" s="7">
         <v>28</v>
       </c>
-      <c r="C31" s="130"/>
-      <c r="D31" s="130"/>
+      <c r="C31" s="135"/>
+      <c r="D31" s="135"/>
       <c r="E31" s="8" t="s">
         <v>54</v>
       </c>
@@ -4821,8 +5139,8 @@
       <c r="B32" s="7">
         <v>29</v>
       </c>
-      <c r="C32" s="131"/>
-      <c r="D32" s="131"/>
+      <c r="C32" s="136"/>
+      <c r="D32" s="136"/>
       <c r="E32" s="17" t="s">
         <v>55</v>
       </c>
@@ -4846,7 +5164,7 @@
       <c r="C33" s="139" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="129" t="s">
+      <c r="D33" s="143" t="s">
         <v>57</v>
       </c>
       <c r="E33" s="8" t="s">
@@ -4869,8 +5187,8 @@
       <c r="B34" s="7">
         <v>2</v>
       </c>
-      <c r="C34" s="130"/>
-      <c r="D34" s="130"/>
+      <c r="C34" s="135"/>
+      <c r="D34" s="135"/>
       <c r="E34" s="8" t="s">
         <v>59</v>
       </c>
@@ -4891,8 +5209,8 @@
       <c r="B35" s="7">
         <v>3</v>
       </c>
-      <c r="C35" s="130"/>
-      <c r="D35" s="130"/>
+      <c r="C35" s="135"/>
+      <c r="D35" s="135"/>
       <c r="E35" s="8" t="s">
         <v>60</v>
       </c>
@@ -4913,8 +5231,8 @@
       <c r="B36" s="7">
         <v>4</v>
       </c>
-      <c r="C36" s="130"/>
-      <c r="D36" s="131"/>
+      <c r="C36" s="135"/>
+      <c r="D36" s="136"/>
       <c r="E36" s="8" t="s">
         <v>61</v>
       </c>
@@ -4935,8 +5253,8 @@
       <c r="B37" s="7">
         <v>5</v>
       </c>
-      <c r="C37" s="130"/>
-      <c r="D37" s="129" t="s">
+      <c r="C37" s="135"/>
+      <c r="D37" s="143" t="s">
         <v>62</v>
       </c>
       <c r="E37" s="8" t="s">
@@ -4959,8 +5277,8 @@
       <c r="B38" s="7">
         <v>6</v>
       </c>
-      <c r="C38" s="130"/>
-      <c r="D38" s="130"/>
+      <c r="C38" s="135"/>
+      <c r="D38" s="135"/>
       <c r="E38" s="8" t="s">
         <v>64</v>
       </c>
@@ -4981,8 +5299,8 @@
       <c r="B39" s="7">
         <v>7</v>
       </c>
-      <c r="C39" s="130"/>
-      <c r="D39" s="131"/>
+      <c r="C39" s="135"/>
+      <c r="D39" s="136"/>
       <c r="E39" s="8" t="s">
         <v>65</v>
       </c>
@@ -5003,8 +5321,8 @@
       <c r="B40" s="7">
         <v>8</v>
       </c>
-      <c r="C40" s="130"/>
-      <c r="D40" s="129" t="s">
+      <c r="C40" s="135"/>
+      <c r="D40" s="143" t="s">
         <v>66</v>
       </c>
       <c r="E40" s="8" t="s">
@@ -5027,8 +5345,8 @@
       <c r="B41" s="7">
         <v>9</v>
       </c>
-      <c r="C41" s="130"/>
-      <c r="D41" s="130"/>
+      <c r="C41" s="135"/>
+      <c r="D41" s="135"/>
       <c r="E41" s="8" t="s">
         <v>68</v>
       </c>
@@ -5049,8 +5367,8 @@
       <c r="B42" s="7">
         <v>10</v>
       </c>
-      <c r="C42" s="130"/>
-      <c r="D42" s="130"/>
+      <c r="C42" s="135"/>
+      <c r="D42" s="135"/>
       <c r="E42" s="8" t="s">
         <v>69</v>
       </c>
@@ -5071,8 +5389,8 @@
       <c r="B43" s="7">
         <v>11</v>
       </c>
-      <c r="C43" s="130"/>
-      <c r="D43" s="130"/>
+      <c r="C43" s="135"/>
+      <c r="D43" s="135"/>
       <c r="E43" s="8" t="s">
         <v>70</v>
       </c>
@@ -5093,8 +5411,8 @@
       <c r="B44" s="24">
         <v>12</v>
       </c>
-      <c r="C44" s="131"/>
-      <c r="D44" s="131"/>
+      <c r="C44" s="136"/>
+      <c r="D44" s="136"/>
       <c r="E44" s="17" t="s">
         <v>71</v>
       </c>
@@ -5115,10 +5433,10 @@
       <c r="B45" s="22">
         <v>1</v>
       </c>
-      <c r="C45" s="144" t="s">
+      <c r="C45" s="140" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="145" t="s">
+      <c r="D45" s="144" t="s">
         <v>73</v>
       </c>
       <c r="E45" s="13" t="s">
@@ -5130,19 +5448,23 @@
       <c r="G45" s="10">
         <v>1</v>
       </c>
-      <c r="H45" s="11"/>
+      <c r="H45" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="I45" s="11"/>
-      <c r="J45" s="11"/>
-    </row>
-    <row r="46" spans="1:10" ht="13.8">
+      <c r="J45" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="262.2">
       <c r="A46" s="6">
         <v>43</v>
       </c>
       <c r="B46" s="7">
         <v>2</v>
       </c>
-      <c r="C46" s="130"/>
-      <c r="D46" s="130"/>
+      <c r="C46" s="135"/>
+      <c r="D46" s="135"/>
       <c r="E46" s="8" t="s">
         <v>75</v>
       </c>
@@ -5152,19 +5474,25 @@
       <c r="G46" s="10">
         <v>1</v>
       </c>
-      <c r="H46" s="11"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="11"/>
-    </row>
-    <row r="47" spans="1:10" ht="13.8">
+      <c r="H46" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I46" s="133" t="s">
+        <v>710</v>
+      </c>
+      <c r="J46" s="126" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="138">
       <c r="A47" s="6">
         <v>44</v>
       </c>
       <c r="B47" s="7">
         <v>3</v>
       </c>
-      <c r="C47" s="130"/>
-      <c r="D47" s="130"/>
+      <c r="C47" s="135"/>
+      <c r="D47" s="135"/>
       <c r="E47" s="13" t="s">
         <v>76</v>
       </c>
@@ -5174,19 +5502,25 @@
       <c r="G47" s="10">
         <v>1</v>
       </c>
-      <c r="H47" s="11"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="11"/>
-    </row>
-    <row r="48" spans="1:10" ht="13.8">
+      <c r="H47" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I47" s="131" t="s">
+        <v>709</v>
+      </c>
+      <c r="J47" s="126" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="69">
       <c r="A48" s="6">
         <v>45</v>
       </c>
       <c r="B48" s="7">
         <v>4</v>
       </c>
-      <c r="C48" s="130"/>
-      <c r="D48" s="130"/>
+      <c r="C48" s="135"/>
+      <c r="D48" s="135"/>
       <c r="E48" s="13" t="s">
         <v>77</v>
       </c>
@@ -5196,9 +5530,15 @@
       <c r="G48" s="10">
         <v>1</v>
       </c>
-      <c r="H48" s="11"/>
-      <c r="I48" s="11"/>
-      <c r="J48" s="11"/>
+      <c r="H48" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I48" s="133" t="s">
+        <v>711</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="49" spans="1:10" ht="13.8">
       <c r="A49" s="6">
@@ -5207,8 +5547,8 @@
       <c r="B49" s="7">
         <v>5</v>
       </c>
-      <c r="C49" s="130"/>
-      <c r="D49" s="130"/>
+      <c r="C49" s="135"/>
+      <c r="D49" s="135"/>
       <c r="E49" s="13" t="s">
         <v>78</v>
       </c>
@@ -5218,9 +5558,13 @@
       <c r="G49" s="10">
         <v>2</v>
       </c>
-      <c r="H49" s="11"/>
+      <c r="H49" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="I49" s="11"/>
-      <c r="J49" s="11"/>
+      <c r="J49" s="11" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="50" spans="1:10" ht="13.8">
       <c r="A50" s="23">
@@ -5229,8 +5573,8 @@
       <c r="B50" s="24">
         <v>6</v>
       </c>
-      <c r="C50" s="131"/>
-      <c r="D50" s="131"/>
+      <c r="C50" s="136"/>
+      <c r="D50" s="136"/>
       <c r="E50" s="25" t="s">
         <v>79</v>
       </c>
@@ -5240,9 +5584,13 @@
       <c r="G50" s="19">
         <v>3</v>
       </c>
-      <c r="H50" s="20"/>
+      <c r="H50" s="20" t="s">
+        <v>27</v>
+      </c>
       <c r="I50" s="20"/>
-      <c r="J50" s="20"/>
+      <c r="J50" s="20" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="51" spans="1:10" ht="13.8">
       <c r="A51" s="6">
@@ -5251,10 +5599,10 @@
       <c r="B51" s="7">
         <v>1</v>
       </c>
-      <c r="C51" s="141" t="s">
+      <c r="C51" s="137" t="s">
         <v>80</v>
       </c>
-      <c r="D51" s="129" t="s">
+      <c r="D51" s="143" t="s">
         <v>81</v>
       </c>
       <c r="E51" s="13" t="s">
@@ -5277,8 +5625,8 @@
       <c r="B52" s="7">
         <v>2</v>
       </c>
-      <c r="C52" s="130"/>
-      <c r="D52" s="130"/>
+      <c r="C52" s="135"/>
+      <c r="D52" s="135"/>
       <c r="E52" s="8" t="s">
         <v>83</v>
       </c>
@@ -5299,8 +5647,8 @@
       <c r="B53" s="7">
         <v>3</v>
       </c>
-      <c r="C53" s="130"/>
-      <c r="D53" s="130"/>
+      <c r="C53" s="135"/>
+      <c r="D53" s="135"/>
       <c r="E53" s="27" t="s">
         <v>84</v>
       </c>
@@ -5321,8 +5669,8 @@
       <c r="B54" s="7">
         <v>4</v>
       </c>
-      <c r="C54" s="130"/>
-      <c r="D54" s="130"/>
+      <c r="C54" s="135"/>
+      <c r="D54" s="135"/>
       <c r="E54" s="13" t="s">
         <v>85</v>
       </c>
@@ -5343,8 +5691,8 @@
       <c r="B55" s="7">
         <v>5</v>
       </c>
-      <c r="C55" s="130"/>
-      <c r="D55" s="130"/>
+      <c r="C55" s="135"/>
+      <c r="D55" s="135"/>
       <c r="E55" s="13" t="s">
         <v>86</v>
       </c>
@@ -5365,8 +5713,8 @@
       <c r="B56" s="7">
         <v>6</v>
       </c>
-      <c r="C56" s="130"/>
-      <c r="D56" s="130"/>
+      <c r="C56" s="135"/>
+      <c r="D56" s="135"/>
       <c r="E56" s="13" t="s">
         <v>87</v>
       </c>
@@ -5387,8 +5735,8 @@
       <c r="B57" s="7">
         <v>7</v>
       </c>
-      <c r="C57" s="130"/>
-      <c r="D57" s="131"/>
+      <c r="C57" s="135"/>
+      <c r="D57" s="136"/>
       <c r="E57" s="13" t="s">
         <v>88</v>
       </c>
@@ -5409,8 +5757,8 @@
       <c r="B58" s="7">
         <v>8</v>
       </c>
-      <c r="C58" s="130"/>
-      <c r="D58" s="129" t="s">
+      <c r="C58" s="135"/>
+      <c r="D58" s="143" t="s">
         <v>89</v>
       </c>
       <c r="E58" s="13" t="s">
@@ -5433,8 +5781,8 @@
       <c r="B59" s="7">
         <v>9</v>
       </c>
-      <c r="C59" s="130"/>
-      <c r="D59" s="130"/>
+      <c r="C59" s="135"/>
+      <c r="D59" s="135"/>
       <c r="E59" s="8" t="s">
         <v>91</v>
       </c>
@@ -5455,8 +5803,8 @@
       <c r="B60" s="7">
         <v>10</v>
       </c>
-      <c r="C60" s="130"/>
-      <c r="D60" s="130"/>
+      <c r="C60" s="135"/>
+      <c r="D60" s="135"/>
       <c r="E60" s="8" t="s">
         <v>92</v>
       </c>
@@ -5477,8 +5825,8 @@
       <c r="B61" s="7">
         <v>11</v>
       </c>
-      <c r="C61" s="130"/>
-      <c r="D61" s="130"/>
+      <c r="C61" s="135"/>
+      <c r="D61" s="135"/>
       <c r="E61" s="8" t="s">
         <v>93</v>
       </c>
@@ -5499,8 +5847,8 @@
       <c r="B62" s="7">
         <v>12</v>
       </c>
-      <c r="C62" s="130"/>
-      <c r="D62" s="130"/>
+      <c r="C62" s="135"/>
+      <c r="D62" s="135"/>
       <c r="E62" s="8" t="s">
         <v>94</v>
       </c>
@@ -5521,8 +5869,8 @@
       <c r="B63" s="7">
         <v>13</v>
       </c>
-      <c r="C63" s="130"/>
-      <c r="D63" s="131"/>
+      <c r="C63" s="135"/>
+      <c r="D63" s="136"/>
       <c r="E63" s="8" t="s">
         <v>95</v>
       </c>
@@ -5543,8 +5891,8 @@
       <c r="B64" s="7">
         <v>14</v>
       </c>
-      <c r="C64" s="130"/>
-      <c r="D64" s="129" t="s">
+      <c r="C64" s="135"/>
+      <c r="D64" s="143" t="s">
         <v>48</v>
       </c>
       <c r="E64" s="8" t="s">
@@ -5567,8 +5915,8 @@
       <c r="B65" s="7">
         <v>15</v>
       </c>
-      <c r="C65" s="130"/>
-      <c r="D65" s="130"/>
+      <c r="C65" s="135"/>
+      <c r="D65" s="135"/>
       <c r="E65" s="8" t="s">
         <v>97</v>
       </c>
@@ -5589,8 +5937,8 @@
       <c r="B66" s="7">
         <v>16</v>
       </c>
-      <c r="C66" s="130"/>
-      <c r="D66" s="130"/>
+      <c r="C66" s="135"/>
+      <c r="D66" s="135"/>
       <c r="E66" s="8" t="s">
         <v>98</v>
       </c>
@@ -5611,8 +5959,8 @@
       <c r="B67" s="7">
         <v>17</v>
       </c>
-      <c r="C67" s="131"/>
-      <c r="D67" s="131"/>
+      <c r="C67" s="136"/>
+      <c r="D67" s="136"/>
       <c r="E67" s="8" t="s">
         <v>99</v>
       </c>
@@ -5627,18 +5975,18 @@
       <c r="J67" s="11"/>
     </row>
     <row r="68" spans="1:10" ht="13.8">
-      <c r="A68" s="146" t="s">
+      <c r="A68" s="149" t="s">
         <v>100</v>
       </c>
-      <c r="B68" s="136"/>
-      <c r="C68" s="136"/>
-      <c r="D68" s="136"/>
-      <c r="E68" s="136"/>
-      <c r="F68" s="136"/>
-      <c r="G68" s="136"/>
-      <c r="H68" s="136"/>
-      <c r="I68" s="136"/>
-      <c r="J68" s="137"/>
+      <c r="B68" s="146"/>
+      <c r="C68" s="146"/>
+      <c r="D68" s="146"/>
+      <c r="E68" s="146"/>
+      <c r="F68" s="146"/>
+      <c r="G68" s="146"/>
+      <c r="H68" s="146"/>
+      <c r="I68" s="146"/>
+      <c r="J68" s="147"/>
     </row>
     <row r="69" spans="1:10" ht="13.8">
       <c r="A69" s="6">
@@ -5650,7 +5998,7 @@
       <c r="C69" s="138" t="s">
         <v>101</v>
       </c>
-      <c r="D69" s="129" t="s">
+      <c r="D69" s="143" t="s">
         <v>102</v>
       </c>
       <c r="E69" s="8" t="s">
@@ -5673,8 +6021,8 @@
       <c r="B70" s="7">
         <v>2</v>
       </c>
-      <c r="C70" s="130"/>
-      <c r="D70" s="130"/>
+      <c r="C70" s="135"/>
+      <c r="D70" s="135"/>
       <c r="E70" s="28" t="s">
         <v>104</v>
       </c>
@@ -5695,8 +6043,8 @@
       <c r="B71" s="7">
         <v>3</v>
       </c>
-      <c r="C71" s="130"/>
-      <c r="D71" s="130"/>
+      <c r="C71" s="135"/>
+      <c r="D71" s="135"/>
       <c r="E71" s="8" t="s">
         <v>105</v>
       </c>
@@ -5717,8 +6065,8 @@
       <c r="B72" s="7">
         <v>4</v>
       </c>
-      <c r="C72" s="130"/>
-      <c r="D72" s="130"/>
+      <c r="C72" s="135"/>
+      <c r="D72" s="135"/>
       <c r="E72" s="8" t="s">
         <v>106</v>
       </c>
@@ -5739,8 +6087,8 @@
       <c r="B73" s="7">
         <v>5</v>
       </c>
-      <c r="C73" s="130"/>
-      <c r="D73" s="130"/>
+      <c r="C73" s="135"/>
+      <c r="D73" s="135"/>
       <c r="E73" s="28" t="s">
         <v>107</v>
       </c>
@@ -5761,8 +6109,8 @@
       <c r="B74" s="7">
         <v>6</v>
       </c>
-      <c r="C74" s="130"/>
-      <c r="D74" s="130"/>
+      <c r="C74" s="135"/>
+      <c r="D74" s="135"/>
       <c r="E74" s="28" t="s">
         <v>108</v>
       </c>
@@ -5783,8 +6131,8 @@
       <c r="B75" s="7">
         <v>7</v>
       </c>
-      <c r="C75" s="130"/>
-      <c r="D75" s="130"/>
+      <c r="C75" s="135"/>
+      <c r="D75" s="135"/>
       <c r="E75" s="28" t="s">
         <v>109</v>
       </c>
@@ -5805,8 +6153,8 @@
       <c r="B76" s="7">
         <v>8</v>
       </c>
-      <c r="C76" s="130"/>
-      <c r="D76" s="130"/>
+      <c r="C76" s="135"/>
+      <c r="D76" s="135"/>
       <c r="E76" s="8" t="s">
         <v>110</v>
       </c>
@@ -5827,8 +6175,8 @@
       <c r="B77" s="7">
         <v>9</v>
       </c>
-      <c r="C77" s="130"/>
-      <c r="D77" s="130"/>
+      <c r="C77" s="135"/>
+      <c r="D77" s="135"/>
       <c r="E77" s="8" t="s">
         <v>111</v>
       </c>
@@ -5849,8 +6197,8 @@
       <c r="B78" s="7">
         <v>10</v>
       </c>
-      <c r="C78" s="130"/>
-      <c r="D78" s="131"/>
+      <c r="C78" s="135"/>
+      <c r="D78" s="136"/>
       <c r="E78" s="8" t="s">
         <v>112</v>
       </c>
@@ -5871,8 +6219,8 @@
       <c r="B79" s="7">
         <v>11</v>
       </c>
-      <c r="C79" s="130"/>
-      <c r="D79" s="129" t="s">
+      <c r="C79" s="135"/>
+      <c r="D79" s="143" t="s">
         <v>113</v>
       </c>
       <c r="E79" s="8" t="s">
@@ -5895,8 +6243,8 @@
       <c r="B80" s="7">
         <v>12</v>
       </c>
-      <c r="C80" s="130"/>
-      <c r="D80" s="130"/>
+      <c r="C80" s="135"/>
+      <c r="D80" s="135"/>
       <c r="E80" s="8" t="s">
         <v>115</v>
       </c>
@@ -5917,8 +6265,8 @@
       <c r="B81" s="7">
         <v>13</v>
       </c>
-      <c r="C81" s="130"/>
-      <c r="D81" s="130"/>
+      <c r="C81" s="135"/>
+      <c r="D81" s="135"/>
       <c r="E81" s="8" t="s">
         <v>116</v>
       </c>
@@ -5939,8 +6287,8 @@
       <c r="B82" s="7">
         <v>14</v>
       </c>
-      <c r="C82" s="130"/>
-      <c r="D82" s="130"/>
+      <c r="C82" s="135"/>
+      <c r="D82" s="135"/>
       <c r="E82" s="8" t="s">
         <v>117</v>
       </c>
@@ -5961,8 +6309,8 @@
       <c r="B83" s="7">
         <v>15</v>
       </c>
-      <c r="C83" s="130"/>
-      <c r="D83" s="130"/>
+      <c r="C83" s="135"/>
+      <c r="D83" s="135"/>
       <c r="E83" s="8" t="s">
         <v>118</v>
       </c>
@@ -5983,8 +6331,8 @@
       <c r="B84" s="7">
         <v>16</v>
       </c>
-      <c r="C84" s="130"/>
-      <c r="D84" s="131"/>
+      <c r="C84" s="135"/>
+      <c r="D84" s="136"/>
       <c r="E84" s="8" t="s">
         <v>119</v>
       </c>
@@ -6005,8 +6353,8 @@
       <c r="B85" s="7">
         <v>17</v>
       </c>
-      <c r="C85" s="130"/>
-      <c r="D85" s="129" t="s">
+      <c r="C85" s="135"/>
+      <c r="D85" s="143" t="s">
         <v>120</v>
       </c>
       <c r="E85" s="8" t="s">
@@ -6029,8 +6377,8 @@
       <c r="B86" s="7">
         <v>18</v>
       </c>
-      <c r="C86" s="130"/>
-      <c r="D86" s="130"/>
+      <c r="C86" s="135"/>
+      <c r="D86" s="135"/>
       <c r="E86" s="8" t="s">
         <v>122</v>
       </c>
@@ -6051,8 +6399,8 @@
       <c r="B87" s="7">
         <v>19</v>
       </c>
-      <c r="C87" s="130"/>
-      <c r="D87" s="130"/>
+      <c r="C87" s="135"/>
+      <c r="D87" s="135"/>
       <c r="E87" s="29" t="s">
         <v>123</v>
       </c>
@@ -6073,8 +6421,8 @@
       <c r="B88" s="7">
         <v>20</v>
       </c>
-      <c r="C88" s="130"/>
-      <c r="D88" s="130"/>
+      <c r="C88" s="135"/>
+      <c r="D88" s="135"/>
       <c r="E88" s="8" t="s">
         <v>124</v>
       </c>
@@ -6095,8 +6443,8 @@
       <c r="B89" s="7">
         <v>21</v>
       </c>
-      <c r="C89" s="130"/>
-      <c r="D89" s="130"/>
+      <c r="C89" s="135"/>
+      <c r="D89" s="135"/>
       <c r="E89" s="8" t="s">
         <v>125</v>
       </c>
@@ -6117,8 +6465,8 @@
       <c r="B90" s="7">
         <v>22</v>
       </c>
-      <c r="C90" s="130"/>
-      <c r="D90" s="131"/>
+      <c r="C90" s="135"/>
+      <c r="D90" s="136"/>
       <c r="E90" s="8" t="s">
         <v>126</v>
       </c>
@@ -6139,8 +6487,8 @@
       <c r="B91" s="7">
         <v>23</v>
       </c>
-      <c r="C91" s="130"/>
-      <c r="D91" s="129" t="s">
+      <c r="C91" s="135"/>
+      <c r="D91" s="143" t="s">
         <v>127</v>
       </c>
       <c r="E91" s="8" t="s">
@@ -6163,8 +6511,8 @@
       <c r="B92" s="7">
         <v>24</v>
       </c>
-      <c r="C92" s="130"/>
-      <c r="D92" s="130"/>
+      <c r="C92" s="135"/>
+      <c r="D92" s="135"/>
       <c r="E92" s="8" t="s">
         <v>129</v>
       </c>
@@ -6185,8 +6533,8 @@
       <c r="B93" s="7">
         <v>25</v>
       </c>
-      <c r="C93" s="130"/>
-      <c r="D93" s="130"/>
+      <c r="C93" s="135"/>
+      <c r="D93" s="135"/>
       <c r="E93" s="8" t="s">
         <v>130</v>
       </c>
@@ -6207,8 +6555,8 @@
       <c r="B94" s="7">
         <v>26</v>
       </c>
-      <c r="C94" s="130"/>
-      <c r="D94" s="130"/>
+      <c r="C94" s="135"/>
+      <c r="D94" s="135"/>
       <c r="E94" s="8" t="s">
         <v>131</v>
       </c>
@@ -6229,8 +6577,8 @@
       <c r="B95" s="7">
         <v>27</v>
       </c>
-      <c r="C95" s="130"/>
-      <c r="D95" s="130"/>
+      <c r="C95" s="135"/>
+      <c r="D95" s="135"/>
       <c r="E95" s="8" t="s">
         <v>132</v>
       </c>
@@ -6251,8 +6599,8 @@
       <c r="B96" s="7">
         <v>28</v>
       </c>
-      <c r="C96" s="130"/>
-      <c r="D96" s="130"/>
+      <c r="C96" s="135"/>
+      <c r="D96" s="135"/>
       <c r="E96" s="8" t="s">
         <v>133</v>
       </c>
@@ -6273,8 +6621,8 @@
       <c r="B97" s="7">
         <v>29</v>
       </c>
-      <c r="C97" s="130"/>
-      <c r="D97" s="130"/>
+      <c r="C97" s="135"/>
+      <c r="D97" s="135"/>
       <c r="E97" s="8" t="s">
         <v>134</v>
       </c>
@@ -6295,8 +6643,8 @@
       <c r="B98" s="7">
         <v>30</v>
       </c>
-      <c r="C98" s="130"/>
-      <c r="D98" s="130"/>
+      <c r="C98" s="135"/>
+      <c r="D98" s="135"/>
       <c r="E98" s="8" t="s">
         <v>135</v>
       </c>
@@ -6317,8 +6665,8 @@
       <c r="B99" s="7">
         <v>31</v>
       </c>
-      <c r="C99" s="130"/>
-      <c r="D99" s="130"/>
+      <c r="C99" s="135"/>
+      <c r="D99" s="135"/>
       <c r="E99" s="30" t="s">
         <v>136</v>
       </c>
@@ -6339,8 +6687,8 @@
       <c r="B100" s="7">
         <v>32</v>
       </c>
-      <c r="C100" s="130"/>
-      <c r="D100" s="130"/>
+      <c r="C100" s="135"/>
+      <c r="D100" s="135"/>
       <c r="E100" s="8" t="s">
         <v>137</v>
       </c>
@@ -6361,8 +6709,8 @@
       <c r="B101" s="7">
         <v>33</v>
       </c>
-      <c r="C101" s="130"/>
-      <c r="D101" s="130"/>
+      <c r="C101" s="135"/>
+      <c r="D101" s="135"/>
       <c r="E101" s="8" t="s">
         <v>138</v>
       </c>
@@ -6383,8 +6731,8 @@
       <c r="B102" s="7">
         <v>34</v>
       </c>
-      <c r="C102" s="130"/>
-      <c r="D102" s="130"/>
+      <c r="C102" s="135"/>
+      <c r="D102" s="135"/>
       <c r="E102" s="8" t="s">
         <v>139</v>
       </c>
@@ -6405,8 +6753,8 @@
       <c r="B103" s="7">
         <v>35</v>
       </c>
-      <c r="C103" s="130"/>
-      <c r="D103" s="130"/>
+      <c r="C103" s="135"/>
+      <c r="D103" s="135"/>
       <c r="E103" s="8" t="s">
         <v>140</v>
       </c>
@@ -6427,8 +6775,8 @@
       <c r="B104" s="7">
         <v>36</v>
       </c>
-      <c r="C104" s="130"/>
-      <c r="D104" s="130"/>
+      <c r="C104" s="135"/>
+      <c r="D104" s="135"/>
       <c r="E104" s="8" t="s">
         <v>141</v>
       </c>
@@ -6449,8 +6797,8 @@
       <c r="B105" s="7">
         <v>37</v>
       </c>
-      <c r="C105" s="131"/>
-      <c r="D105" s="131"/>
+      <c r="C105" s="136"/>
+      <c r="D105" s="136"/>
       <c r="E105" s="8" t="s">
         <v>142</v>
       </c>
@@ -6465,18 +6813,18 @@
       <c r="J105" s="11"/>
     </row>
     <row r="106" spans="1:10" ht="13.8">
-      <c r="A106" s="142" t="s">
+      <c r="A106" s="151" t="s">
         <v>143</v>
       </c>
-      <c r="B106" s="136"/>
-      <c r="C106" s="136"/>
-      <c r="D106" s="136"/>
-      <c r="E106" s="136"/>
-      <c r="F106" s="136"/>
-      <c r="G106" s="136"/>
-      <c r="H106" s="136"/>
-      <c r="I106" s="136"/>
-      <c r="J106" s="137"/>
+      <c r="B106" s="146"/>
+      <c r="C106" s="146"/>
+      <c r="D106" s="146"/>
+      <c r="E106" s="146"/>
+      <c r="F106" s="146"/>
+      <c r="G106" s="146"/>
+      <c r="H106" s="146"/>
+      <c r="I106" s="146"/>
+      <c r="J106" s="147"/>
     </row>
     <row r="107" spans="1:10" ht="13.8">
       <c r="A107" s="6">
@@ -6488,7 +6836,7 @@
       <c r="C107" s="139" t="s">
         <v>144</v>
       </c>
-      <c r="D107" s="129" t="s">
+      <c r="D107" s="143" t="s">
         <v>145</v>
       </c>
       <c r="E107" s="8" t="s">
@@ -6511,8 +6859,8 @@
       <c r="B108" s="7">
         <v>2</v>
       </c>
-      <c r="C108" s="130"/>
-      <c r="D108" s="130"/>
+      <c r="C108" s="135"/>
+      <c r="D108" s="135"/>
       <c r="E108" s="8" t="s">
         <v>147</v>
       </c>
@@ -6533,8 +6881,8 @@
       <c r="B109" s="7">
         <v>3</v>
       </c>
-      <c r="C109" s="130"/>
-      <c r="D109" s="130"/>
+      <c r="C109" s="135"/>
+      <c r="D109" s="135"/>
       <c r="E109" s="8" t="s">
         <v>148</v>
       </c>
@@ -6555,8 +6903,8 @@
       <c r="B110" s="7">
         <v>4</v>
       </c>
-      <c r="C110" s="130"/>
-      <c r="D110" s="130"/>
+      <c r="C110" s="135"/>
+      <c r="D110" s="135"/>
       <c r="E110" s="8" t="s">
         <v>149</v>
       </c>
@@ -6577,8 +6925,8 @@
       <c r="B111" s="7">
         <v>5</v>
       </c>
-      <c r="C111" s="130"/>
-      <c r="D111" s="131"/>
+      <c r="C111" s="135"/>
+      <c r="D111" s="136"/>
       <c r="E111" s="8" t="s">
         <v>150</v>
       </c>
@@ -6599,8 +6947,8 @@
       <c r="B112" s="7">
         <v>6</v>
       </c>
-      <c r="C112" s="130"/>
-      <c r="D112" s="129" t="s">
+      <c r="C112" s="135"/>
+      <c r="D112" s="143" t="s">
         <v>151</v>
       </c>
       <c r="E112" s="8" t="s">
@@ -6623,8 +6971,8 @@
       <c r="B113" s="7">
         <v>7</v>
       </c>
-      <c r="C113" s="130"/>
-      <c r="D113" s="130"/>
+      <c r="C113" s="135"/>
+      <c r="D113" s="135"/>
       <c r="E113" s="8" t="s">
         <v>153</v>
       </c>
@@ -6645,8 +6993,8 @@
       <c r="B114" s="7">
         <v>8</v>
       </c>
-      <c r="C114" s="130"/>
-      <c r="D114" s="130"/>
+      <c r="C114" s="135"/>
+      <c r="D114" s="135"/>
       <c r="E114" s="8" t="s">
         <v>154</v>
       </c>
@@ -6667,8 +7015,8 @@
       <c r="B115" s="7">
         <v>9</v>
       </c>
-      <c r="C115" s="130"/>
-      <c r="D115" s="131"/>
+      <c r="C115" s="135"/>
+      <c r="D115" s="136"/>
       <c r="E115" s="8" t="s">
         <v>155</v>
       </c>
@@ -6689,7 +7037,7 @@
       <c r="B116" s="24">
         <v>10</v>
       </c>
-      <c r="C116" s="131"/>
+      <c r="C116" s="136"/>
       <c r="D116" s="31" t="s">
         <v>156</v>
       </c>
@@ -6713,10 +7061,10 @@
       <c r="B117" s="7">
         <v>1</v>
       </c>
-      <c r="C117" s="140" t="s">
+      <c r="C117" s="134" t="s">
         <v>158</v>
       </c>
-      <c r="D117" s="129" t="s">
+      <c r="D117" s="143" t="s">
         <v>159</v>
       </c>
       <c r="E117" s="8" t="s">
@@ -6739,8 +7087,8 @@
       <c r="B118" s="7">
         <v>2</v>
       </c>
-      <c r="C118" s="130"/>
-      <c r="D118" s="130"/>
+      <c r="C118" s="135"/>
+      <c r="D118" s="135"/>
       <c r="E118" s="8" t="s">
         <v>161</v>
       </c>
@@ -6761,8 +7109,8 @@
       <c r="B119" s="7">
         <v>3</v>
       </c>
-      <c r="C119" s="130"/>
-      <c r="D119" s="130"/>
+      <c r="C119" s="135"/>
+      <c r="D119" s="135"/>
       <c r="E119" s="8" t="s">
         <v>162</v>
       </c>
@@ -6783,8 +7131,8 @@
       <c r="B120" s="7">
         <v>4</v>
       </c>
-      <c r="C120" s="130"/>
-      <c r="D120" s="131"/>
+      <c r="C120" s="135"/>
+      <c r="D120" s="136"/>
       <c r="E120" s="8" t="s">
         <v>163</v>
       </c>
@@ -6805,8 +7153,8 @@
       <c r="B121" s="7">
         <v>5</v>
       </c>
-      <c r="C121" s="130"/>
-      <c r="D121" s="129" t="s">
+      <c r="C121" s="135"/>
+      <c r="D121" s="143" t="s">
         <v>164</v>
       </c>
       <c r="E121" s="8" t="s">
@@ -6829,8 +7177,8 @@
       <c r="B122" s="7">
         <v>6</v>
       </c>
-      <c r="C122" s="130"/>
-      <c r="D122" s="131"/>
+      <c r="C122" s="135"/>
+      <c r="D122" s="136"/>
       <c r="E122" s="8" t="s">
         <v>166</v>
       </c>
@@ -6851,8 +7199,8 @@
       <c r="B123" s="7">
         <v>7</v>
       </c>
-      <c r="C123" s="130"/>
-      <c r="D123" s="129" t="s">
+      <c r="C123" s="135"/>
+      <c r="D123" s="143" t="s">
         <v>167</v>
       </c>
       <c r="E123" s="8" t="s">
@@ -6875,8 +7223,8 @@
       <c r="B124" s="7">
         <v>8</v>
       </c>
-      <c r="C124" s="130"/>
-      <c r="D124" s="130"/>
+      <c r="C124" s="135"/>
+      <c r="D124" s="135"/>
       <c r="E124" s="28" t="s">
         <v>169</v>
       </c>
@@ -6897,8 +7245,8 @@
       <c r="B125" s="7">
         <v>9</v>
       </c>
-      <c r="C125" s="131"/>
-      <c r="D125" s="131"/>
+      <c r="C125" s="136"/>
+      <c r="D125" s="136"/>
       <c r="E125" s="8" t="s">
         <v>170</v>
       </c>
@@ -6913,18 +7261,18 @@
       <c r="J125" s="11"/>
     </row>
     <row r="126" spans="1:10" ht="13.8">
-      <c r="A126" s="143" t="s">
+      <c r="A126" s="152" t="s">
         <v>171</v>
       </c>
-      <c r="B126" s="136"/>
-      <c r="C126" s="136"/>
-      <c r="D126" s="136"/>
-      <c r="E126" s="136"/>
-      <c r="F126" s="136"/>
-      <c r="G126" s="136"/>
-      <c r="H126" s="136"/>
-      <c r="I126" s="136"/>
-      <c r="J126" s="137"/>
+      <c r="B126" s="146"/>
+      <c r="C126" s="146"/>
+      <c r="D126" s="146"/>
+      <c r="E126" s="146"/>
+      <c r="F126" s="146"/>
+      <c r="G126" s="146"/>
+      <c r="H126" s="146"/>
+      <c r="I126" s="146"/>
+      <c r="J126" s="147"/>
     </row>
     <row r="127" spans="1:10" ht="13.8">
       <c r="A127" s="6">
@@ -6933,10 +7281,10 @@
       <c r="B127" s="7">
         <v>1</v>
       </c>
-      <c r="C127" s="141" t="s">
+      <c r="C127" s="137" t="s">
         <v>172</v>
       </c>
-      <c r="D127" s="129" t="s">
+      <c r="D127" s="143" t="s">
         <v>173</v>
       </c>
       <c r="E127" s="32" t="s">
@@ -6957,8 +7305,8 @@
       <c r="B128" s="7">
         <v>2</v>
       </c>
-      <c r="C128" s="130"/>
-      <c r="D128" s="130"/>
+      <c r="C128" s="135"/>
+      <c r="D128" s="135"/>
       <c r="E128" s="32" t="s">
         <v>175</v>
       </c>
@@ -6977,8 +7325,8 @@
       <c r="B129" s="7">
         <v>3</v>
       </c>
-      <c r="C129" s="130"/>
-      <c r="D129" s="130"/>
+      <c r="C129" s="135"/>
+      <c r="D129" s="135"/>
       <c r="E129" s="32" t="s">
         <v>176</v>
       </c>
@@ -6997,8 +7345,8 @@
       <c r="B130" s="7">
         <v>4</v>
       </c>
-      <c r="C130" s="130"/>
-      <c r="D130" s="131"/>
+      <c r="C130" s="135"/>
+      <c r="D130" s="136"/>
       <c r="E130" s="32" t="s">
         <v>177</v>
       </c>
@@ -7017,8 +7365,8 @@
       <c r="B131" s="7">
         <v>5</v>
       </c>
-      <c r="C131" s="130"/>
-      <c r="D131" s="129" t="s">
+      <c r="C131" s="135"/>
+      <c r="D131" s="143" t="s">
         <v>178</v>
       </c>
       <c r="E131" s="32" t="s">
@@ -7039,8 +7387,8 @@
       <c r="B132" s="7">
         <v>6</v>
       </c>
-      <c r="C132" s="131"/>
-      <c r="D132" s="131"/>
+      <c r="C132" s="136"/>
+      <c r="D132" s="136"/>
       <c r="E132" s="32" t="s">
         <v>180</v>
       </c>
@@ -7053,18 +7401,18 @@
       <c r="J132" s="11"/>
     </row>
     <row r="133" spans="1:10" ht="13.8">
-      <c r="A133" s="135" t="s">
+      <c r="A133" s="153" t="s">
         <v>181</v>
       </c>
-      <c r="B133" s="136"/>
-      <c r="C133" s="136"/>
-      <c r="D133" s="136"/>
-      <c r="E133" s="136"/>
-      <c r="F133" s="136"/>
-      <c r="G133" s="136"/>
-      <c r="H133" s="136"/>
-      <c r="I133" s="136"/>
-      <c r="J133" s="137"/>
+      <c r="B133" s="146"/>
+      <c r="C133" s="146"/>
+      <c r="D133" s="146"/>
+      <c r="E133" s="146"/>
+      <c r="F133" s="146"/>
+      <c r="G133" s="146"/>
+      <c r="H133" s="146"/>
+      <c r="I133" s="146"/>
+      <c r="J133" s="147"/>
     </row>
     <row r="134" spans="1:10" ht="13.8">
       <c r="A134" s="6">
@@ -7076,7 +7424,7 @@
       <c r="C134" s="138" t="s">
         <v>182</v>
       </c>
-      <c r="D134" s="129" t="s">
+      <c r="D134" s="143" t="s">
         <v>183</v>
       </c>
       <c r="E134" s="8" t="s">
@@ -7099,8 +7447,8 @@
       <c r="B135" s="7">
         <v>2</v>
       </c>
-      <c r="C135" s="130"/>
-      <c r="D135" s="130"/>
+      <c r="C135" s="135"/>
+      <c r="D135" s="135"/>
       <c r="E135" s="8" t="s">
         <v>185</v>
       </c>
@@ -7121,8 +7469,8 @@
       <c r="B136" s="7">
         <v>3</v>
       </c>
-      <c r="C136" s="130"/>
-      <c r="D136" s="131"/>
+      <c r="C136" s="135"/>
+      <c r="D136" s="136"/>
       <c r="E136" s="8" t="s">
         <v>186</v>
       </c>
@@ -7143,8 +7491,8 @@
       <c r="B137" s="7">
         <v>4</v>
       </c>
-      <c r="C137" s="130"/>
-      <c r="D137" s="129" t="s">
+      <c r="C137" s="135"/>
+      <c r="D137" s="143" t="s">
         <v>187</v>
       </c>
       <c r="E137" s="8" t="s">
@@ -7167,8 +7515,8 @@
       <c r="B138" s="7">
         <v>5</v>
       </c>
-      <c r="C138" s="130"/>
-      <c r="D138" s="130"/>
+      <c r="C138" s="135"/>
+      <c r="D138" s="135"/>
       <c r="E138" s="8" t="s">
         <v>189</v>
       </c>
@@ -7189,8 +7537,8 @@
       <c r="B139" s="7">
         <v>6</v>
       </c>
-      <c r="C139" s="130"/>
-      <c r="D139" s="130"/>
+      <c r="C139" s="135"/>
+      <c r="D139" s="135"/>
       <c r="E139" s="8" t="s">
         <v>190</v>
       </c>
@@ -7211,8 +7559,8 @@
       <c r="B140" s="7">
         <v>7</v>
       </c>
-      <c r="C140" s="130"/>
-      <c r="D140" s="130"/>
+      <c r="C140" s="135"/>
+      <c r="D140" s="135"/>
       <c r="E140" s="8" t="s">
         <v>191</v>
       </c>
@@ -7233,8 +7581,8 @@
       <c r="B141" s="7">
         <v>8</v>
       </c>
-      <c r="C141" s="130"/>
-      <c r="D141" s="130"/>
+      <c r="C141" s="135"/>
+      <c r="D141" s="135"/>
       <c r="E141" s="8" t="s">
         <v>192</v>
       </c>
@@ -7255,8 +7603,8 @@
       <c r="B142" s="7">
         <v>9</v>
       </c>
-      <c r="C142" s="130"/>
-      <c r="D142" s="130"/>
+      <c r="C142" s="135"/>
+      <c r="D142" s="135"/>
       <c r="E142" s="8" t="s">
         <v>193</v>
       </c>
@@ -7277,8 +7625,8 @@
       <c r="B143" s="7">
         <v>10</v>
       </c>
-      <c r="C143" s="130"/>
-      <c r="D143" s="131"/>
+      <c r="C143" s="135"/>
+      <c r="D143" s="136"/>
       <c r="E143" s="8" t="s">
         <v>194</v>
       </c>
@@ -7299,8 +7647,8 @@
       <c r="B144" s="7">
         <v>11</v>
       </c>
-      <c r="C144" s="130"/>
-      <c r="D144" s="129" t="s">
+      <c r="C144" s="135"/>
+      <c r="D144" s="143" t="s">
         <v>195</v>
       </c>
       <c r="E144" s="8" t="s">
@@ -7323,8 +7671,8 @@
       <c r="B145" s="7">
         <v>12</v>
       </c>
-      <c r="C145" s="130"/>
-      <c r="D145" s="130"/>
+      <c r="C145" s="135"/>
+      <c r="D145" s="135"/>
       <c r="E145" s="8" t="s">
         <v>197</v>
       </c>
@@ -7345,8 +7693,8 @@
       <c r="B146" s="7">
         <v>13</v>
       </c>
-      <c r="C146" s="130"/>
-      <c r="D146" s="130"/>
+      <c r="C146" s="135"/>
+      <c r="D146" s="135"/>
       <c r="E146" s="8" t="s">
         <v>198</v>
       </c>
@@ -7367,8 +7715,8 @@
       <c r="B147" s="7">
         <v>14</v>
       </c>
-      <c r="C147" s="130"/>
-      <c r="D147" s="130"/>
+      <c r="C147" s="135"/>
+      <c r="D147" s="135"/>
       <c r="E147" s="8" t="s">
         <v>199</v>
       </c>
@@ -7389,8 +7737,8 @@
       <c r="B148" s="7">
         <v>15</v>
       </c>
-      <c r="C148" s="130"/>
-      <c r="D148" s="130"/>
+      <c r="C148" s="135"/>
+      <c r="D148" s="135"/>
       <c r="E148" s="8" t="s">
         <v>200</v>
       </c>
@@ -7411,8 +7759,8 @@
       <c r="B149" s="7">
         <v>16</v>
       </c>
-      <c r="C149" s="130"/>
-      <c r="D149" s="130"/>
+      <c r="C149" s="135"/>
+      <c r="D149" s="135"/>
       <c r="E149" s="8" t="s">
         <v>201</v>
       </c>
@@ -7433,8 +7781,8 @@
       <c r="B150" s="7">
         <v>17</v>
       </c>
-      <c r="C150" s="130"/>
-      <c r="D150" s="131"/>
+      <c r="C150" s="135"/>
+      <c r="D150" s="136"/>
       <c r="E150" s="8" t="s">
         <v>202</v>
       </c>
@@ -7455,8 +7803,8 @@
       <c r="B151" s="7">
         <v>18</v>
       </c>
-      <c r="C151" s="130"/>
-      <c r="D151" s="129" t="s">
+      <c r="C151" s="135"/>
+      <c r="D151" s="143" t="s">
         <v>203</v>
       </c>
       <c r="E151" s="8" t="s">
@@ -7479,8 +7827,8 @@
       <c r="B152" s="7">
         <v>19</v>
       </c>
-      <c r="C152" s="130"/>
-      <c r="D152" s="130"/>
+      <c r="C152" s="135"/>
+      <c r="D152" s="135"/>
       <c r="E152" s="8" t="s">
         <v>205</v>
       </c>
@@ -7501,8 +7849,8 @@
       <c r="B153" s="7">
         <v>20</v>
       </c>
-      <c r="C153" s="130"/>
-      <c r="D153" s="130"/>
+      <c r="C153" s="135"/>
+      <c r="D153" s="135"/>
       <c r="E153" s="8" t="s">
         <v>206</v>
       </c>
@@ -7523,8 +7871,8 @@
       <c r="B154" s="7">
         <v>21</v>
       </c>
-      <c r="C154" s="130"/>
-      <c r="D154" s="130"/>
+      <c r="C154" s="135"/>
+      <c r="D154" s="135"/>
       <c r="E154" s="8" t="s">
         <v>207</v>
       </c>
@@ -7545,8 +7893,8 @@
       <c r="B155" s="7">
         <v>22</v>
       </c>
-      <c r="C155" s="130"/>
-      <c r="D155" s="130"/>
+      <c r="C155" s="135"/>
+      <c r="D155" s="135"/>
       <c r="E155" s="8" t="s">
         <v>208</v>
       </c>
@@ -7567,8 +7915,8 @@
       <c r="B156" s="7">
         <v>23</v>
       </c>
-      <c r="C156" s="130"/>
-      <c r="D156" s="131"/>
+      <c r="C156" s="135"/>
+      <c r="D156" s="136"/>
       <c r="E156" s="8" t="s">
         <v>209</v>
       </c>
@@ -7589,8 +7937,8 @@
       <c r="B157" s="7">
         <v>24</v>
       </c>
-      <c r="C157" s="130"/>
-      <c r="D157" s="129" t="s">
+      <c r="C157" s="135"/>
+      <c r="D157" s="143" t="s">
         <v>210</v>
       </c>
       <c r="E157" s="8" t="s">
@@ -7613,8 +7961,8 @@
       <c r="B158" s="7">
         <v>25</v>
       </c>
-      <c r="C158" s="130"/>
-      <c r="D158" s="130"/>
+      <c r="C158" s="135"/>
+      <c r="D158" s="135"/>
       <c r="E158" s="8" t="s">
         <v>212</v>
       </c>
@@ -7635,8 +7983,8 @@
       <c r="B159" s="7">
         <v>26</v>
       </c>
-      <c r="C159" s="130"/>
-      <c r="D159" s="131"/>
+      <c r="C159" s="135"/>
+      <c r="D159" s="136"/>
       <c r="E159" s="8" t="s">
         <v>213</v>
       </c>
@@ -7657,8 +8005,8 @@
       <c r="B160" s="7">
         <v>27</v>
       </c>
-      <c r="C160" s="130"/>
-      <c r="D160" s="129" t="s">
+      <c r="C160" s="135"/>
+      <c r="D160" s="143" t="s">
         <v>214</v>
       </c>
       <c r="E160" s="8" t="s">
@@ -7681,8 +8029,8 @@
       <c r="B161" s="7">
         <v>28</v>
       </c>
-      <c r="C161" s="130"/>
-      <c r="D161" s="130"/>
+      <c r="C161" s="135"/>
+      <c r="D161" s="135"/>
       <c r="E161" s="8" t="s">
         <v>216</v>
       </c>
@@ -7703,8 +8051,8 @@
       <c r="B162" s="7">
         <v>29</v>
       </c>
-      <c r="C162" s="130"/>
-      <c r="D162" s="130"/>
+      <c r="C162" s="135"/>
+      <c r="D162" s="135"/>
       <c r="E162" s="8" t="s">
         <v>217</v>
       </c>
@@ -7725,8 +8073,8 @@
       <c r="B163" s="7">
         <v>30</v>
       </c>
-      <c r="C163" s="130"/>
-      <c r="D163" s="130"/>
+      <c r="C163" s="135"/>
+      <c r="D163" s="135"/>
       <c r="E163" s="8" t="s">
         <v>218</v>
       </c>
@@ -7747,8 +8095,8 @@
       <c r="B164" s="7">
         <v>31</v>
       </c>
-      <c r="C164" s="130"/>
-      <c r="D164" s="130"/>
+      <c r="C164" s="135"/>
+      <c r="D164" s="135"/>
       <c r="E164" s="8" t="s">
         <v>219</v>
       </c>
@@ -7769,8 +8117,8 @@
       <c r="B165" s="7">
         <v>32</v>
       </c>
-      <c r="C165" s="130"/>
-      <c r="D165" s="131"/>
+      <c r="C165" s="135"/>
+      <c r="D165" s="136"/>
       <c r="E165" s="8" t="s">
         <v>220</v>
       </c>
@@ -7791,8 +8139,8 @@
       <c r="B166" s="7">
         <v>33</v>
       </c>
-      <c r="C166" s="130"/>
-      <c r="D166" s="129" t="s">
+      <c r="C166" s="135"/>
+      <c r="D166" s="143" t="s">
         <v>221</v>
       </c>
       <c r="E166" s="8" t="s">
@@ -7815,8 +8163,8 @@
       <c r="B167" s="7">
         <v>34</v>
       </c>
-      <c r="C167" s="130"/>
-      <c r="D167" s="130"/>
+      <c r="C167" s="135"/>
+      <c r="D167" s="135"/>
       <c r="E167" s="8" t="s">
         <v>223</v>
       </c>
@@ -7835,8 +8183,8 @@
       <c r="B168" s="7">
         <v>35</v>
       </c>
-      <c r="C168" s="130"/>
-      <c r="D168" s="130"/>
+      <c r="C168" s="135"/>
+      <c r="D168" s="135"/>
       <c r="E168" s="8" t="s">
         <v>224</v>
       </c>
@@ -7857,8 +8205,8 @@
       <c r="B169" s="7">
         <v>36</v>
       </c>
-      <c r="C169" s="130"/>
-      <c r="D169" s="130"/>
+      <c r="C169" s="135"/>
+      <c r="D169" s="135"/>
       <c r="E169" s="8" t="s">
         <v>225</v>
       </c>
@@ -7879,8 +8227,8 @@
       <c r="B170" s="7">
         <v>37</v>
       </c>
-      <c r="C170" s="130"/>
-      <c r="D170" s="130"/>
+      <c r="C170" s="135"/>
+      <c r="D170" s="135"/>
       <c r="E170" s="8" t="s">
         <v>226</v>
       </c>
@@ -7901,8 +8249,8 @@
       <c r="B171" s="7">
         <v>38</v>
       </c>
-      <c r="C171" s="130"/>
-      <c r="D171" s="130"/>
+      <c r="C171" s="135"/>
+      <c r="D171" s="135"/>
       <c r="E171" s="8" t="s">
         <v>227</v>
       </c>
@@ -7923,8 +8271,8 @@
       <c r="B172" s="7">
         <v>39</v>
       </c>
-      <c r="C172" s="130"/>
-      <c r="D172" s="131"/>
+      <c r="C172" s="135"/>
+      <c r="D172" s="136"/>
       <c r="E172" s="8" t="s">
         <v>228</v>
       </c>
@@ -7945,8 +8293,8 @@
       <c r="B173" s="7">
         <v>40</v>
       </c>
-      <c r="C173" s="130"/>
-      <c r="D173" s="129" t="s">
+      <c r="C173" s="135"/>
+      <c r="D173" s="143" t="s">
         <v>48</v>
       </c>
       <c r="E173" s="11" t="s">
@@ -7969,8 +8317,8 @@
       <c r="B174" s="7">
         <v>41</v>
       </c>
-      <c r="C174" s="130"/>
-      <c r="D174" s="130"/>
+      <c r="C174" s="135"/>
+      <c r="D174" s="135"/>
       <c r="E174" s="8" t="s">
         <v>230</v>
       </c>
@@ -7991,8 +8339,8 @@
       <c r="B175" s="7">
         <v>42</v>
       </c>
-      <c r="C175" s="130"/>
-      <c r="D175" s="130"/>
+      <c r="C175" s="135"/>
+      <c r="D175" s="135"/>
       <c r="E175" s="8" t="s">
         <v>231</v>
       </c>
@@ -8013,8 +8361,8 @@
       <c r="B176" s="24">
         <v>43</v>
       </c>
-      <c r="C176" s="131"/>
-      <c r="D176" s="131"/>
+      <c r="C176" s="136"/>
+      <c r="D176" s="136"/>
       <c r="E176" s="17" t="s">
         <v>232</v>
       </c>
@@ -8038,7 +8386,7 @@
       <c r="C177" s="139" t="s">
         <v>233</v>
       </c>
-      <c r="D177" s="129" t="s">
+      <c r="D177" s="143" t="s">
         <v>234</v>
       </c>
       <c r="E177" s="8" t="s">
@@ -8061,8 +8409,8 @@
       <c r="B178" s="7">
         <v>2</v>
       </c>
-      <c r="C178" s="130"/>
-      <c r="D178" s="131"/>
+      <c r="C178" s="135"/>
+      <c r="D178" s="136"/>
       <c r="E178" s="8" t="s">
         <v>236</v>
       </c>
@@ -8083,8 +8431,8 @@
       <c r="B179" s="7">
         <v>3</v>
       </c>
-      <c r="C179" s="130"/>
-      <c r="D179" s="129" t="s">
+      <c r="C179" s="135"/>
+      <c r="D179" s="143" t="s">
         <v>237</v>
       </c>
       <c r="E179" s="8" t="s">
@@ -8107,8 +8455,8 @@
       <c r="B180" s="7">
         <v>4</v>
       </c>
-      <c r="C180" s="130"/>
-      <c r="D180" s="130"/>
+      <c r="C180" s="135"/>
+      <c r="D180" s="135"/>
       <c r="E180" s="8" t="s">
         <v>239</v>
       </c>
@@ -8129,8 +8477,8 @@
       <c r="B181" s="7">
         <v>5</v>
       </c>
-      <c r="C181" s="130"/>
-      <c r="D181" s="130"/>
+      <c r="C181" s="135"/>
+      <c r="D181" s="135"/>
       <c r="E181" s="8" t="s">
         <v>240</v>
       </c>
@@ -8151,8 +8499,8 @@
       <c r="B182" s="7">
         <v>6</v>
       </c>
-      <c r="C182" s="130"/>
-      <c r="D182" s="130"/>
+      <c r="C182" s="135"/>
+      <c r="D182" s="135"/>
       <c r="E182" s="8" t="s">
         <v>241</v>
       </c>
@@ -8173,8 +8521,8 @@
       <c r="B183" s="7">
         <v>7</v>
       </c>
-      <c r="C183" s="130"/>
-      <c r="D183" s="130"/>
+      <c r="C183" s="135"/>
+      <c r="D183" s="135"/>
       <c r="E183" s="8" t="s">
         <v>242</v>
       </c>
@@ -8195,8 +8543,8 @@
       <c r="B184" s="7">
         <v>8</v>
       </c>
-      <c r="C184" s="130"/>
-      <c r="D184" s="131"/>
+      <c r="C184" s="135"/>
+      <c r="D184" s="136"/>
       <c r="E184" s="8" t="s">
         <v>243</v>
       </c>
@@ -8217,8 +8565,8 @@
       <c r="B185" s="7">
         <v>9</v>
       </c>
-      <c r="C185" s="130"/>
-      <c r="D185" s="129" t="s">
+      <c r="C185" s="135"/>
+      <c r="D185" s="143" t="s">
         <v>244</v>
       </c>
       <c r="E185" s="8" t="s">
@@ -8241,8 +8589,8 @@
       <c r="B186" s="7">
         <v>10</v>
       </c>
-      <c r="C186" s="130"/>
-      <c r="D186" s="131"/>
+      <c r="C186" s="135"/>
+      <c r="D186" s="136"/>
       <c r="E186" s="8" t="s">
         <v>246</v>
       </c>
@@ -8263,8 +8611,8 @@
       <c r="B187" s="7">
         <v>11</v>
       </c>
-      <c r="C187" s="130"/>
-      <c r="D187" s="129" t="s">
+      <c r="C187" s="135"/>
+      <c r="D187" s="143" t="s">
         <v>247</v>
       </c>
       <c r="E187" s="8" t="s">
@@ -8287,8 +8635,8 @@
       <c r="B188" s="7">
         <v>12</v>
       </c>
-      <c r="C188" s="130"/>
-      <c r="D188" s="130"/>
+      <c r="C188" s="135"/>
+      <c r="D188" s="135"/>
       <c r="E188" s="8" t="s">
         <v>249</v>
       </c>
@@ -8309,8 +8657,8 @@
       <c r="B189" s="7">
         <v>13</v>
       </c>
-      <c r="C189" s="130"/>
-      <c r="D189" s="130"/>
+      <c r="C189" s="135"/>
+      <c r="D189" s="135"/>
       <c r="E189" s="11" t="s">
         <v>250</v>
       </c>
@@ -8331,8 +8679,8 @@
       <c r="B190" s="7">
         <v>14</v>
       </c>
-      <c r="C190" s="130"/>
-      <c r="D190" s="131"/>
+      <c r="C190" s="135"/>
+      <c r="D190" s="136"/>
       <c r="E190" s="8" t="s">
         <v>251</v>
       </c>
@@ -8353,8 +8701,8 @@
       <c r="B191" s="7">
         <v>15</v>
       </c>
-      <c r="C191" s="130"/>
-      <c r="D191" s="129" t="s">
+      <c r="C191" s="135"/>
+      <c r="D191" s="143" t="s">
         <v>252</v>
       </c>
       <c r="E191" s="8" t="s">
@@ -8377,8 +8725,8 @@
       <c r="B192" s="7">
         <v>16</v>
       </c>
-      <c r="C192" s="130"/>
-      <c r="D192" s="130"/>
+      <c r="C192" s="135"/>
+      <c r="D192" s="135"/>
       <c r="E192" s="8" t="s">
         <v>254</v>
       </c>
@@ -8399,8 +8747,8 @@
       <c r="B193" s="7">
         <v>17</v>
       </c>
-      <c r="C193" s="130"/>
-      <c r="D193" s="130"/>
+      <c r="C193" s="135"/>
+      <c r="D193" s="135"/>
       <c r="E193" s="8" t="s">
         <v>255</v>
       </c>
@@ -8421,8 +8769,8 @@
       <c r="B194" s="7">
         <v>18</v>
       </c>
-      <c r="C194" s="130"/>
-      <c r="D194" s="130"/>
+      <c r="C194" s="135"/>
+      <c r="D194" s="135"/>
       <c r="E194" s="8" t="s">
         <v>256</v>
       </c>
@@ -8443,8 +8791,8 @@
       <c r="B195" s="7">
         <v>19</v>
       </c>
-      <c r="C195" s="130"/>
-      <c r="D195" s="130"/>
+      <c r="C195" s="135"/>
+      <c r="D195" s="135"/>
       <c r="E195" s="8" t="s">
         <v>257</v>
       </c>
@@ -8465,8 +8813,8 @@
       <c r="B196" s="7">
         <v>20</v>
       </c>
-      <c r="C196" s="130"/>
-      <c r="D196" s="130"/>
+      <c r="C196" s="135"/>
+      <c r="D196" s="135"/>
       <c r="E196" s="8" t="s">
         <v>258</v>
       </c>
@@ -8487,8 +8835,8 @@
       <c r="B197" s="7">
         <v>21</v>
       </c>
-      <c r="C197" s="130"/>
-      <c r="D197" s="130"/>
+      <c r="C197" s="135"/>
+      <c r="D197" s="135"/>
       <c r="E197" s="8" t="s">
         <v>259</v>
       </c>
@@ -8509,8 +8857,8 @@
       <c r="B198" s="7">
         <v>22</v>
       </c>
-      <c r="C198" s="130"/>
-      <c r="D198" s="131"/>
+      <c r="C198" s="135"/>
+      <c r="D198" s="136"/>
       <c r="E198" s="8" t="s">
         <v>260</v>
       </c>
@@ -8531,8 +8879,8 @@
       <c r="B199" s="7">
         <v>23</v>
       </c>
-      <c r="C199" s="130"/>
-      <c r="D199" s="129" t="s">
+      <c r="C199" s="135"/>
+      <c r="D199" s="143" t="s">
         <v>261</v>
       </c>
       <c r="E199" s="8" t="s">
@@ -8555,8 +8903,8 @@
       <c r="B200" s="7">
         <v>24</v>
       </c>
-      <c r="C200" s="130"/>
-      <c r="D200" s="130"/>
+      <c r="C200" s="135"/>
+      <c r="D200" s="135"/>
       <c r="E200" s="8" t="s">
         <v>263</v>
       </c>
@@ -8577,8 +8925,8 @@
       <c r="B201" s="7">
         <v>25</v>
       </c>
-      <c r="C201" s="130"/>
-      <c r="D201" s="130"/>
+      <c r="C201" s="135"/>
+      <c r="D201" s="135"/>
       <c r="E201" s="8" t="s">
         <v>264</v>
       </c>
@@ -8599,8 +8947,8 @@
       <c r="B202" s="7">
         <v>26</v>
       </c>
-      <c r="C202" s="130"/>
-      <c r="D202" s="131"/>
+      <c r="C202" s="135"/>
+      <c r="D202" s="136"/>
       <c r="E202" s="8" t="s">
         <v>265</v>
       </c>
@@ -8621,8 +8969,8 @@
       <c r="B203" s="7">
         <v>27</v>
       </c>
-      <c r="C203" s="130"/>
-      <c r="D203" s="129" t="s">
+      <c r="C203" s="135"/>
+      <c r="D203" s="143" t="s">
         <v>266</v>
       </c>
       <c r="E203" s="8" t="s">
@@ -8645,8 +8993,8 @@
       <c r="B204" s="24">
         <v>28</v>
       </c>
-      <c r="C204" s="131"/>
-      <c r="D204" s="131"/>
+      <c r="C204" s="136"/>
+      <c r="D204" s="136"/>
       <c r="E204" s="17" t="s">
         <v>268</v>
       </c>
@@ -8667,10 +9015,10 @@
       <c r="B205" s="7">
         <v>1</v>
       </c>
-      <c r="C205" s="140" t="s">
+      <c r="C205" s="134" t="s">
         <v>269</v>
       </c>
-      <c r="D205" s="129" t="s">
+      <c r="D205" s="143" t="s">
         <v>270</v>
       </c>
       <c r="E205" s="8" t="s">
@@ -8693,8 +9041,8 @@
       <c r="B206" s="7">
         <v>2</v>
       </c>
-      <c r="C206" s="130"/>
-      <c r="D206" s="130"/>
+      <c r="C206" s="135"/>
+      <c r="D206" s="135"/>
       <c r="E206" s="8" t="s">
         <v>272</v>
       </c>
@@ -8715,8 +9063,8 @@
       <c r="B207" s="7">
         <v>3</v>
       </c>
-      <c r="C207" s="130"/>
-      <c r="D207" s="130"/>
+      <c r="C207" s="135"/>
+      <c r="D207" s="135"/>
       <c r="E207" s="8" t="s">
         <v>273</v>
       </c>
@@ -8737,8 +9085,8 @@
       <c r="B208" s="7">
         <v>4</v>
       </c>
-      <c r="C208" s="130"/>
-      <c r="D208" s="130"/>
+      <c r="C208" s="135"/>
+      <c r="D208" s="135"/>
       <c r="E208" s="8" t="s">
         <v>274</v>
       </c>
@@ -8759,8 +9107,8 @@
       <c r="B209" s="7">
         <v>5</v>
       </c>
-      <c r="C209" s="130"/>
-      <c r="D209" s="131"/>
+      <c r="C209" s="135"/>
+      <c r="D209" s="136"/>
       <c r="E209" s="8" t="s">
         <v>275</v>
       </c>
@@ -8781,8 +9129,8 @@
       <c r="B210" s="7">
         <v>6</v>
       </c>
-      <c r="C210" s="130"/>
-      <c r="D210" s="129" t="s">
+      <c r="C210" s="135"/>
+      <c r="D210" s="143" t="s">
         <v>276</v>
       </c>
       <c r="E210" s="8" t="s">
@@ -8805,8 +9153,8 @@
       <c r="B211" s="7">
         <v>7</v>
       </c>
-      <c r="C211" s="130"/>
-      <c r="D211" s="131"/>
+      <c r="C211" s="135"/>
+      <c r="D211" s="136"/>
       <c r="E211" s="8" t="s">
         <v>278</v>
       </c>
@@ -8827,8 +9175,8 @@
       <c r="B212" s="7">
         <v>8</v>
       </c>
-      <c r="C212" s="130"/>
-      <c r="D212" s="129" t="s">
+      <c r="C212" s="135"/>
+      <c r="D212" s="143" t="s">
         <v>279</v>
       </c>
       <c r="E212" s="8" t="s">
@@ -8851,8 +9199,8 @@
       <c r="B213" s="7">
         <v>9</v>
       </c>
-      <c r="C213" s="130"/>
-      <c r="D213" s="130"/>
+      <c r="C213" s="135"/>
+      <c r="D213" s="135"/>
       <c r="E213" s="8" t="s">
         <v>281</v>
       </c>
@@ -8873,8 +9221,8 @@
       <c r="B214" s="7">
         <v>10</v>
       </c>
-      <c r="C214" s="131"/>
-      <c r="D214" s="131"/>
+      <c r="C214" s="136"/>
+      <c r="D214" s="136"/>
       <c r="E214" s="8" t="s">
         <v>282</v>
       </c>
@@ -8889,18 +9237,18 @@
       <c r="J214" s="11"/>
     </row>
     <row r="215" spans="1:10" ht="13.8">
-      <c r="A215" s="147" t="s">
+      <c r="A215" s="148" t="s">
         <v>283</v>
       </c>
-      <c r="B215" s="136"/>
-      <c r="C215" s="136"/>
-      <c r="D215" s="136"/>
-      <c r="E215" s="136"/>
-      <c r="F215" s="136"/>
-      <c r="G215" s="136"/>
-      <c r="H215" s="136"/>
-      <c r="I215" s="136"/>
-      <c r="J215" s="137"/>
+      <c r="B215" s="146"/>
+      <c r="C215" s="146"/>
+      <c r="D215" s="146"/>
+      <c r="E215" s="146"/>
+      <c r="F215" s="146"/>
+      <c r="G215" s="146"/>
+      <c r="H215" s="146"/>
+      <c r="I215" s="146"/>
+      <c r="J215" s="147"/>
     </row>
     <row r="216" spans="1:10" ht="13.8">
       <c r="A216" s="6">
@@ -8909,10 +9257,10 @@
       <c r="B216" s="7">
         <v>1</v>
       </c>
-      <c r="C216" s="141" t="s">
+      <c r="C216" s="137" t="s">
         <v>284</v>
       </c>
-      <c r="D216" s="129" t="s">
+      <c r="D216" s="143" t="s">
         <v>285</v>
       </c>
       <c r="E216" s="8" t="s">
@@ -8935,8 +9283,8 @@
       <c r="B217" s="7">
         <v>2</v>
       </c>
-      <c r="C217" s="130"/>
-      <c r="D217" s="130"/>
+      <c r="C217" s="135"/>
+      <c r="D217" s="135"/>
       <c r="E217" s="8" t="s">
         <v>287</v>
       </c>
@@ -8957,8 +9305,8 @@
       <c r="B218" s="7">
         <v>3</v>
       </c>
-      <c r="C218" s="130"/>
-      <c r="D218" s="130"/>
+      <c r="C218" s="135"/>
+      <c r="D218" s="135"/>
       <c r="E218" s="8" t="s">
         <v>288</v>
       </c>
@@ -8979,8 +9327,8 @@
       <c r="B219" s="7">
         <v>4</v>
       </c>
-      <c r="C219" s="130"/>
-      <c r="D219" s="130"/>
+      <c r="C219" s="135"/>
+      <c r="D219" s="135"/>
       <c r="E219" s="8" t="s">
         <v>289</v>
       </c>
@@ -9001,8 +9349,8 @@
       <c r="B220" s="7">
         <v>5</v>
       </c>
-      <c r="C220" s="130"/>
-      <c r="D220" s="130"/>
+      <c r="C220" s="135"/>
+      <c r="D220" s="135"/>
       <c r="E220" s="8" t="s">
         <v>290</v>
       </c>
@@ -9023,8 +9371,8 @@
       <c r="B221" s="7">
         <v>6</v>
       </c>
-      <c r="C221" s="130"/>
-      <c r="D221" s="130"/>
+      <c r="C221" s="135"/>
+      <c r="D221" s="135"/>
       <c r="E221" s="8" t="s">
         <v>291</v>
       </c>
@@ -9045,8 +9393,8 @@
       <c r="B222" s="7">
         <v>7</v>
       </c>
-      <c r="C222" s="130"/>
-      <c r="D222" s="130"/>
+      <c r="C222" s="135"/>
+      <c r="D222" s="135"/>
       <c r="E222" s="8" t="s">
         <v>292</v>
       </c>
@@ -9067,8 +9415,8 @@
       <c r="B223" s="7">
         <v>8</v>
       </c>
-      <c r="C223" s="130"/>
-      <c r="D223" s="130"/>
+      <c r="C223" s="135"/>
+      <c r="D223" s="135"/>
       <c r="E223" s="8" t="s">
         <v>293</v>
       </c>
@@ -9089,8 +9437,8 @@
       <c r="B224" s="7">
         <v>9</v>
       </c>
-      <c r="C224" s="130"/>
-      <c r="D224" s="130"/>
+      <c r="C224" s="135"/>
+      <c r="D224" s="135"/>
       <c r="E224" s="8" t="s">
         <v>294</v>
       </c>
@@ -9111,8 +9459,8 @@
       <c r="B225" s="7">
         <v>10</v>
       </c>
-      <c r="C225" s="130"/>
-      <c r="D225" s="131"/>
+      <c r="C225" s="135"/>
+      <c r="D225" s="136"/>
       <c r="E225" s="8" t="s">
         <v>295</v>
       </c>
@@ -9133,8 +9481,8 @@
       <c r="B226" s="7">
         <v>11</v>
       </c>
-      <c r="C226" s="130"/>
-      <c r="D226" s="129" t="s">
+      <c r="C226" s="135"/>
+      <c r="D226" s="143" t="s">
         <v>296</v>
       </c>
       <c r="E226" s="8" t="s">
@@ -9157,8 +9505,8 @@
       <c r="B227" s="7">
         <v>12</v>
       </c>
-      <c r="C227" s="130"/>
-      <c r="D227" s="130"/>
+      <c r="C227" s="135"/>
+      <c r="D227" s="135"/>
       <c r="E227" s="8" t="s">
         <v>298</v>
       </c>
@@ -9179,8 +9527,8 @@
       <c r="B228" s="7">
         <v>13</v>
       </c>
-      <c r="C228" s="130"/>
-      <c r="D228" s="130"/>
+      <c r="C228" s="135"/>
+      <c r="D228" s="135"/>
       <c r="E228" s="8" t="s">
         <v>299</v>
       </c>
@@ -9201,8 +9549,8 @@
       <c r="B229" s="7">
         <v>14</v>
       </c>
-      <c r="C229" s="130"/>
-      <c r="D229" s="130"/>
+      <c r="C229" s="135"/>
+      <c r="D229" s="135"/>
       <c r="E229" s="8" t="s">
         <v>300</v>
       </c>
@@ -9223,8 +9571,8 @@
       <c r="B230" s="7">
         <v>15</v>
       </c>
-      <c r="C230" s="130"/>
-      <c r="D230" s="130"/>
+      <c r="C230" s="135"/>
+      <c r="D230" s="135"/>
       <c r="E230" s="8" t="s">
         <v>301</v>
       </c>
@@ -9245,8 +9593,8 @@
       <c r="B231" s="7">
         <v>16</v>
       </c>
-      <c r="C231" s="130"/>
-      <c r="D231" s="130"/>
+      <c r="C231" s="135"/>
+      <c r="D231" s="135"/>
       <c r="E231" s="8" t="s">
         <v>302</v>
       </c>
@@ -9267,8 +9615,8 @@
       <c r="B232" s="7">
         <v>17</v>
       </c>
-      <c r="C232" s="130"/>
-      <c r="D232" s="130"/>
+      <c r="C232" s="135"/>
+      <c r="D232" s="135"/>
       <c r="E232" s="8" t="s">
         <v>303</v>
       </c>
@@ -9289,8 +9637,8 @@
       <c r="B233" s="7">
         <v>18</v>
       </c>
-      <c r="C233" s="130"/>
-      <c r="D233" s="131"/>
+      <c r="C233" s="135"/>
+      <c r="D233" s="136"/>
       <c r="E233" s="8" t="s">
         <v>304</v>
       </c>
@@ -9311,8 +9659,8 @@
       <c r="B234" s="7">
         <v>19</v>
       </c>
-      <c r="C234" s="130"/>
-      <c r="D234" s="129" t="s">
+      <c r="C234" s="135"/>
+      <c r="D234" s="143" t="s">
         <v>305</v>
       </c>
       <c r="E234" s="8" t="s">
@@ -9335,8 +9683,8 @@
       <c r="B235" s="7">
         <v>20</v>
       </c>
-      <c r="C235" s="130"/>
-      <c r="D235" s="130"/>
+      <c r="C235" s="135"/>
+      <c r="D235" s="135"/>
       <c r="E235" s="8" t="s">
         <v>307</v>
       </c>
@@ -9357,8 +9705,8 @@
       <c r="B236" s="7">
         <v>21</v>
       </c>
-      <c r="C236" s="130"/>
-      <c r="D236" s="130"/>
+      <c r="C236" s="135"/>
+      <c r="D236" s="135"/>
       <c r="E236" s="8" t="s">
         <v>308</v>
       </c>
@@ -9379,8 +9727,8 @@
       <c r="B237" s="7">
         <v>22</v>
       </c>
-      <c r="C237" s="130"/>
-      <c r="D237" s="130"/>
+      <c r="C237" s="135"/>
+      <c r="D237" s="135"/>
       <c r="E237" s="8" t="s">
         <v>309</v>
       </c>
@@ -9401,8 +9749,8 @@
       <c r="B238" s="7">
         <v>23</v>
       </c>
-      <c r="C238" s="130"/>
-      <c r="D238" s="130"/>
+      <c r="C238" s="135"/>
+      <c r="D238" s="135"/>
       <c r="E238" s="8" t="s">
         <v>310</v>
       </c>
@@ -9423,8 +9771,8 @@
       <c r="B239" s="7">
         <v>24</v>
       </c>
-      <c r="C239" s="130"/>
-      <c r="D239" s="130"/>
+      <c r="C239" s="135"/>
+      <c r="D239" s="135"/>
       <c r="E239" s="8" t="s">
         <v>311</v>
       </c>
@@ -9445,8 +9793,8 @@
       <c r="B240" s="7">
         <v>25</v>
       </c>
-      <c r="C240" s="130"/>
-      <c r="D240" s="131"/>
+      <c r="C240" s="135"/>
+      <c r="D240" s="136"/>
       <c r="E240" s="8" t="s">
         <v>312</v>
       </c>
@@ -9467,8 +9815,8 @@
       <c r="B241" s="7">
         <v>26</v>
       </c>
-      <c r="C241" s="130"/>
-      <c r="D241" s="129" t="s">
+      <c r="C241" s="135"/>
+      <c r="D241" s="143" t="s">
         <v>313</v>
       </c>
       <c r="E241" s="8" t="s">
@@ -9491,8 +9839,8 @@
       <c r="B242" s="7">
         <v>27</v>
       </c>
-      <c r="C242" s="130"/>
-      <c r="D242" s="130"/>
+      <c r="C242" s="135"/>
+      <c r="D242" s="135"/>
       <c r="E242" s="8" t="s">
         <v>315</v>
       </c>
@@ -9513,8 +9861,8 @@
       <c r="B243" s="7">
         <v>28</v>
       </c>
-      <c r="C243" s="130"/>
-      <c r="D243" s="131"/>
+      <c r="C243" s="135"/>
+      <c r="D243" s="136"/>
       <c r="E243" s="8" t="s">
         <v>316</v>
       </c>
@@ -9535,8 +9883,8 @@
       <c r="B244" s="7">
         <v>29</v>
       </c>
-      <c r="C244" s="130"/>
-      <c r="D244" s="129" t="s">
+      <c r="C244" s="135"/>
+      <c r="D244" s="143" t="s">
         <v>317</v>
       </c>
       <c r="E244" s="8" t="s">
@@ -9559,8 +9907,8 @@
       <c r="B245" s="7">
         <v>30</v>
       </c>
-      <c r="C245" s="130"/>
-      <c r="D245" s="130"/>
+      <c r="C245" s="135"/>
+      <c r="D245" s="135"/>
       <c r="E245" s="8" t="s">
         <v>319</v>
       </c>
@@ -9581,8 +9929,8 @@
       <c r="B246" s="7">
         <v>31</v>
       </c>
-      <c r="C246" s="130"/>
-      <c r="D246" s="130"/>
+      <c r="C246" s="135"/>
+      <c r="D246" s="135"/>
       <c r="E246" s="8" t="s">
         <v>320</v>
       </c>
@@ -9603,8 +9951,8 @@
       <c r="B247" s="7">
         <v>32</v>
       </c>
-      <c r="C247" s="130"/>
-      <c r="D247" s="130"/>
+      <c r="C247" s="135"/>
+      <c r="D247" s="135"/>
       <c r="E247" s="8" t="s">
         <v>321</v>
       </c>
@@ -9625,8 +9973,8 @@
       <c r="B248" s="7">
         <v>33</v>
       </c>
-      <c r="C248" s="130"/>
-      <c r="D248" s="130"/>
+      <c r="C248" s="135"/>
+      <c r="D248" s="135"/>
       <c r="E248" s="8" t="s">
         <v>322</v>
       </c>
@@ -9647,8 +9995,8 @@
       <c r="B249" s="24">
         <v>34</v>
       </c>
-      <c r="C249" s="131"/>
-      <c r="D249" s="131"/>
+      <c r="C249" s="136"/>
+      <c r="D249" s="136"/>
       <c r="E249" s="17" t="s">
         <v>323</v>
       </c>
@@ -9672,7 +10020,7 @@
       <c r="C250" s="138" t="s">
         <v>324</v>
       </c>
-      <c r="D250" s="129" t="s">
+      <c r="D250" s="143" t="s">
         <v>325</v>
       </c>
       <c r="E250" s="8" t="s">
@@ -9695,8 +10043,8 @@
       <c r="B251" s="7">
         <v>2</v>
       </c>
-      <c r="C251" s="130"/>
-      <c r="D251" s="130"/>
+      <c r="C251" s="135"/>
+      <c r="D251" s="135"/>
       <c r="E251" s="8" t="s">
         <v>327</v>
       </c>
@@ -9717,8 +10065,8 @@
       <c r="B252" s="7">
         <v>3</v>
       </c>
-      <c r="C252" s="130"/>
-      <c r="D252" s="130"/>
+      <c r="C252" s="135"/>
+      <c r="D252" s="135"/>
       <c r="E252" s="8" t="s">
         <v>328</v>
       </c>
@@ -9739,8 +10087,8 @@
       <c r="B253" s="7">
         <v>4</v>
       </c>
-      <c r="C253" s="130"/>
-      <c r="D253" s="130"/>
+      <c r="C253" s="135"/>
+      <c r="D253" s="135"/>
       <c r="E253" s="8" t="s">
         <v>329</v>
       </c>
@@ -9761,8 +10109,8 @@
       <c r="B254" s="7">
         <v>5</v>
       </c>
-      <c r="C254" s="130"/>
-      <c r="D254" s="130"/>
+      <c r="C254" s="135"/>
+      <c r="D254" s="135"/>
       <c r="E254" s="8" t="s">
         <v>330</v>
       </c>
@@ -9783,8 +10131,8 @@
       <c r="B255" s="7">
         <v>6</v>
       </c>
-      <c r="C255" s="130"/>
-      <c r="D255" s="130"/>
+      <c r="C255" s="135"/>
+      <c r="D255" s="135"/>
       <c r="E255" s="8" t="s">
         <v>331</v>
       </c>
@@ -9805,8 +10153,8 @@
       <c r="B256" s="7">
         <v>7</v>
       </c>
-      <c r="C256" s="130"/>
-      <c r="D256" s="130"/>
+      <c r="C256" s="135"/>
+      <c r="D256" s="135"/>
       <c r="E256" s="8" t="s">
         <v>332</v>
       </c>
@@ -9827,8 +10175,8 @@
       <c r="B257" s="7">
         <v>8</v>
       </c>
-      <c r="C257" s="130"/>
-      <c r="D257" s="131"/>
+      <c r="C257" s="135"/>
+      <c r="D257" s="136"/>
       <c r="E257" s="8" t="s">
         <v>333</v>
       </c>
@@ -9849,8 +10197,8 @@
       <c r="B258" s="7">
         <v>9</v>
       </c>
-      <c r="C258" s="130"/>
-      <c r="D258" s="129" t="s">
+      <c r="C258" s="135"/>
+      <c r="D258" s="143" t="s">
         <v>334</v>
       </c>
       <c r="E258" s="8" t="s">
@@ -9873,8 +10221,8 @@
       <c r="B259" s="7">
         <v>10</v>
       </c>
-      <c r="C259" s="130"/>
-      <c r="D259" s="131"/>
+      <c r="C259" s="135"/>
+      <c r="D259" s="136"/>
       <c r="E259" s="8" t="s">
         <v>336</v>
       </c>
@@ -9895,8 +10243,8 @@
       <c r="B260" s="7">
         <v>11</v>
       </c>
-      <c r="C260" s="130"/>
-      <c r="D260" s="129" t="s">
+      <c r="C260" s="135"/>
+      <c r="D260" s="143" t="s">
         <v>337</v>
       </c>
       <c r="E260" s="8" t="s">
@@ -9919,8 +10267,8 @@
       <c r="B261" s="7">
         <v>12</v>
       </c>
-      <c r="C261" s="130"/>
-      <c r="D261" s="130"/>
+      <c r="C261" s="135"/>
+      <c r="D261" s="135"/>
       <c r="E261" s="8" t="s">
         <v>339</v>
       </c>
@@ -9941,8 +10289,8 @@
       <c r="B262" s="7">
         <v>13</v>
       </c>
-      <c r="C262" s="130"/>
-      <c r="D262" s="130"/>
+      <c r="C262" s="135"/>
+      <c r="D262" s="135"/>
       <c r="E262" s="8" t="s">
         <v>340</v>
       </c>
@@ -9963,8 +10311,8 @@
       <c r="B263" s="7">
         <v>14</v>
       </c>
-      <c r="C263" s="130"/>
-      <c r="D263" s="130"/>
+      <c r="C263" s="135"/>
+      <c r="D263" s="135"/>
       <c r="E263" s="8" t="s">
         <v>341</v>
       </c>
@@ -9985,8 +10333,8 @@
       <c r="B264" s="7">
         <v>15</v>
       </c>
-      <c r="C264" s="130"/>
-      <c r="D264" s="130"/>
+      <c r="C264" s="135"/>
+      <c r="D264" s="135"/>
       <c r="E264" s="8" t="s">
         <v>342</v>
       </c>
@@ -10007,8 +10355,8 @@
       <c r="B265" s="24">
         <v>16</v>
       </c>
-      <c r="C265" s="131"/>
-      <c r="D265" s="131"/>
+      <c r="C265" s="136"/>
+      <c r="D265" s="136"/>
       <c r="E265" s="17" t="s">
         <v>343</v>
       </c>
@@ -10032,7 +10380,7 @@
       <c r="C266" s="139" t="s">
         <v>344</v>
       </c>
-      <c r="D266" s="129" t="s">
+      <c r="D266" s="143" t="s">
         <v>345</v>
       </c>
       <c r="E266" s="8" t="s">
@@ -10055,8 +10403,8 @@
       <c r="B267" s="7">
         <v>2</v>
       </c>
-      <c r="C267" s="130"/>
-      <c r="D267" s="130"/>
+      <c r="C267" s="135"/>
+      <c r="D267" s="135"/>
       <c r="E267" s="8" t="s">
         <v>347</v>
       </c>
@@ -10077,8 +10425,8 @@
       <c r="B268" s="7">
         <v>3</v>
       </c>
-      <c r="C268" s="130"/>
-      <c r="D268" s="130"/>
+      <c r="C268" s="135"/>
+      <c r="D268" s="135"/>
       <c r="E268" s="8" t="s">
         <v>348</v>
       </c>
@@ -10099,8 +10447,8 @@
       <c r="B269" s="7">
         <v>4</v>
       </c>
-      <c r="C269" s="130"/>
-      <c r="D269" s="130"/>
+      <c r="C269" s="135"/>
+      <c r="D269" s="135"/>
       <c r="E269" s="8" t="s">
         <v>349</v>
       </c>
@@ -10121,8 +10469,8 @@
       <c r="B270" s="7">
         <v>5</v>
       </c>
-      <c r="C270" s="130"/>
-      <c r="D270" s="131"/>
+      <c r="C270" s="135"/>
+      <c r="D270" s="136"/>
       <c r="E270" s="8" t="s">
         <v>350</v>
       </c>
@@ -10143,8 +10491,8 @@
       <c r="B271" s="7">
         <v>6</v>
       </c>
-      <c r="C271" s="130"/>
-      <c r="D271" s="129" t="s">
+      <c r="C271" s="135"/>
+      <c r="D271" s="143" t="s">
         <v>351</v>
       </c>
       <c r="E271" s="8" t="s">
@@ -10167,8 +10515,8 @@
       <c r="B272" s="7">
         <v>7</v>
       </c>
-      <c r="C272" s="131"/>
-      <c r="D272" s="131"/>
+      <c r="C272" s="136"/>
+      <c r="D272" s="136"/>
       <c r="E272" s="8" t="s">
         <v>353</v>
       </c>
@@ -10183,18 +10531,18 @@
       <c r="J272" s="11"/>
     </row>
     <row r="273" spans="1:10" ht="13.8">
-      <c r="A273" s="146" t="s">
+      <c r="A273" s="149" t="s">
         <v>354</v>
       </c>
-      <c r="B273" s="136"/>
-      <c r="C273" s="136"/>
-      <c r="D273" s="136"/>
-      <c r="E273" s="136"/>
-      <c r="F273" s="136"/>
-      <c r="G273" s="136"/>
-      <c r="H273" s="136"/>
-      <c r="I273" s="136"/>
-      <c r="J273" s="137"/>
+      <c r="B273" s="146"/>
+      <c r="C273" s="146"/>
+      <c r="D273" s="146"/>
+      <c r="E273" s="146"/>
+      <c r="F273" s="146"/>
+      <c r="G273" s="146"/>
+      <c r="H273" s="146"/>
+      <c r="I273" s="146"/>
+      <c r="J273" s="147"/>
     </row>
     <row r="274" spans="1:10" ht="13.8">
       <c r="A274" s="33">
@@ -10203,10 +10551,10 @@
       <c r="B274" s="7">
         <v>1</v>
       </c>
-      <c r="C274" s="144" t="s">
+      <c r="C274" s="140" t="s">
         <v>355</v>
       </c>
-      <c r="D274" s="145" t="s">
+      <c r="D274" s="144" t="s">
         <v>356</v>
       </c>
       <c r="E274" s="13" t="s">
@@ -10229,8 +10577,8 @@
       <c r="B275" s="7">
         <v>2</v>
       </c>
-      <c r="C275" s="130"/>
-      <c r="D275" s="130"/>
+      <c r="C275" s="135"/>
+      <c r="D275" s="135"/>
       <c r="E275" s="13" t="s">
         <v>358</v>
       </c>
@@ -10251,8 +10599,8 @@
       <c r="B276" s="7">
         <v>3</v>
       </c>
-      <c r="C276" s="130"/>
-      <c r="D276" s="130"/>
+      <c r="C276" s="135"/>
+      <c r="D276" s="135"/>
       <c r="E276" s="8" t="s">
         <v>359</v>
       </c>
@@ -10273,8 +10621,8 @@
       <c r="B277" s="7">
         <v>4</v>
       </c>
-      <c r="C277" s="130"/>
-      <c r="D277" s="130"/>
+      <c r="C277" s="135"/>
+      <c r="D277" s="135"/>
       <c r="E277" s="8" t="s">
         <v>360</v>
       </c>
@@ -10295,8 +10643,8 @@
       <c r="B278" s="7">
         <v>5</v>
       </c>
-      <c r="C278" s="130"/>
-      <c r="D278" s="130"/>
+      <c r="C278" s="135"/>
+      <c r="D278" s="135"/>
       <c r="E278" s="8" t="s">
         <v>361</v>
       </c>
@@ -10317,8 +10665,8 @@
       <c r="B279" s="7">
         <v>6</v>
       </c>
-      <c r="C279" s="130"/>
-      <c r="D279" s="130"/>
+      <c r="C279" s="135"/>
+      <c r="D279" s="135"/>
       <c r="E279" s="8" t="s">
         <v>362</v>
       </c>
@@ -10339,8 +10687,8 @@
       <c r="B280" s="7">
         <v>7</v>
       </c>
-      <c r="C280" s="130"/>
-      <c r="D280" s="130"/>
+      <c r="C280" s="135"/>
+      <c r="D280" s="135"/>
       <c r="E280" s="8" t="s">
         <v>363</v>
       </c>
@@ -10361,8 +10709,8 @@
       <c r="B281" s="7">
         <v>8</v>
       </c>
-      <c r="C281" s="130"/>
-      <c r="D281" s="131"/>
+      <c r="C281" s="135"/>
+      <c r="D281" s="136"/>
       <c r="E281" s="13" t="s">
         <v>364</v>
       </c>
@@ -10383,8 +10731,8 @@
       <c r="B282" s="7">
         <v>9</v>
       </c>
-      <c r="C282" s="130"/>
-      <c r="D282" s="145" t="s">
+      <c r="C282" s="135"/>
+      <c r="D282" s="144" t="s">
         <v>365</v>
       </c>
       <c r="E282" s="8" t="s">
@@ -10407,8 +10755,8 @@
       <c r="B283" s="7">
         <v>10</v>
       </c>
-      <c r="C283" s="130"/>
-      <c r="D283" s="130"/>
+      <c r="C283" s="135"/>
+      <c r="D283" s="135"/>
       <c r="E283" s="13" t="s">
         <v>367</v>
       </c>
@@ -10429,8 +10777,8 @@
       <c r="B284" s="7">
         <v>11</v>
       </c>
-      <c r="C284" s="130"/>
-      <c r="D284" s="130"/>
+      <c r="C284" s="135"/>
+      <c r="D284" s="135"/>
       <c r="E284" s="13" t="s">
         <v>368</v>
       </c>
@@ -10451,8 +10799,8 @@
       <c r="B285" s="7">
         <v>12</v>
       </c>
-      <c r="C285" s="130"/>
-      <c r="D285" s="130"/>
+      <c r="C285" s="135"/>
+      <c r="D285" s="135"/>
       <c r="E285" s="13" t="s">
         <v>369</v>
       </c>
@@ -10473,8 +10821,8 @@
       <c r="B286" s="7">
         <v>13</v>
       </c>
-      <c r="C286" s="130"/>
-      <c r="D286" s="130"/>
+      <c r="C286" s="135"/>
+      <c r="D286" s="135"/>
       <c r="E286" s="13" t="s">
         <v>370</v>
       </c>
@@ -10495,8 +10843,8 @@
       <c r="B287" s="7">
         <v>14</v>
       </c>
-      <c r="C287" s="130"/>
-      <c r="D287" s="130"/>
+      <c r="C287" s="135"/>
+      <c r="D287" s="135"/>
       <c r="E287" s="13" t="s">
         <v>371</v>
       </c>
@@ -10517,8 +10865,8 @@
       <c r="B288" s="7">
         <v>15</v>
       </c>
-      <c r="C288" s="130"/>
-      <c r="D288" s="131"/>
+      <c r="C288" s="135"/>
+      <c r="D288" s="136"/>
       <c r="E288" s="13" t="s">
         <v>372</v>
       </c>
@@ -10539,8 +10887,8 @@
       <c r="B289" s="7">
         <v>16</v>
       </c>
-      <c r="C289" s="130"/>
-      <c r="D289" s="145" t="s">
+      <c r="C289" s="135"/>
+      <c r="D289" s="144" t="s">
         <v>373</v>
       </c>
       <c r="E289" s="13" t="s">
@@ -10563,8 +10911,8 @@
       <c r="B290" s="7">
         <v>17</v>
       </c>
-      <c r="C290" s="130"/>
-      <c r="D290" s="130"/>
+      <c r="C290" s="135"/>
+      <c r="D290" s="135"/>
       <c r="E290" s="8" t="s">
         <v>375</v>
       </c>
@@ -10585,8 +10933,8 @@
       <c r="B291" s="7">
         <v>18</v>
       </c>
-      <c r="C291" s="130"/>
-      <c r="D291" s="130"/>
+      <c r="C291" s="135"/>
+      <c r="D291" s="135"/>
       <c r="E291" s="11" t="s">
         <v>376</v>
       </c>
@@ -10607,8 +10955,8 @@
       <c r="B292" s="24">
         <v>19</v>
       </c>
-      <c r="C292" s="131"/>
-      <c r="D292" s="131"/>
+      <c r="C292" s="136"/>
+      <c r="D292" s="136"/>
       <c r="E292" s="20" t="s">
         <v>377</v>
       </c>
@@ -10629,10 +10977,10 @@
       <c r="B293" s="7">
         <v>1</v>
       </c>
-      <c r="C293" s="141" t="s">
+      <c r="C293" s="137" t="s">
         <v>378</v>
       </c>
-      <c r="D293" s="129" t="s">
+      <c r="D293" s="143" t="s">
         <v>379</v>
       </c>
       <c r="E293" s="8" t="s">
@@ -10655,8 +11003,8 @@
       <c r="B294" s="7">
         <v>2</v>
       </c>
-      <c r="C294" s="130"/>
-      <c r="D294" s="130"/>
+      <c r="C294" s="135"/>
+      <c r="D294" s="135"/>
       <c r="E294" s="8" t="s">
         <v>381</v>
       </c>
@@ -10677,8 +11025,8 @@
       <c r="B295" s="7">
         <v>3</v>
       </c>
-      <c r="C295" s="130"/>
-      <c r="D295" s="131"/>
+      <c r="C295" s="135"/>
+      <c r="D295" s="136"/>
       <c r="E295" s="8" t="s">
         <v>382</v>
       </c>
@@ -10697,8 +11045,8 @@
       <c r="B296" s="7">
         <v>4</v>
       </c>
-      <c r="C296" s="130"/>
-      <c r="D296" s="129" t="s">
+      <c r="C296" s="135"/>
+      <c r="D296" s="143" t="s">
         <v>383</v>
       </c>
       <c r="E296" s="37" t="s">
@@ -10721,8 +11069,8 @@
       <c r="B297" s="7">
         <v>5</v>
       </c>
-      <c r="C297" s="130"/>
-      <c r="D297" s="130"/>
+      <c r="C297" s="135"/>
+      <c r="D297" s="135"/>
       <c r="E297" s="8" t="s">
         <v>385</v>
       </c>
@@ -10743,8 +11091,8 @@
       <c r="B298" s="7">
         <v>6</v>
       </c>
-      <c r="C298" s="130"/>
-      <c r="D298" s="130"/>
+      <c r="C298" s="135"/>
+      <c r="D298" s="135"/>
       <c r="E298" s="8" t="s">
         <v>386</v>
       </c>
@@ -10765,8 +11113,8 @@
       <c r="B299" s="7">
         <v>7</v>
       </c>
-      <c r="C299" s="130"/>
-      <c r="D299" s="130"/>
+      <c r="C299" s="135"/>
+      <c r="D299" s="135"/>
       <c r="E299" s="8" t="s">
         <v>387</v>
       </c>
@@ -10787,8 +11135,8 @@
       <c r="B300" s="7">
         <v>8</v>
       </c>
-      <c r="C300" s="130"/>
-      <c r="D300" s="131"/>
+      <c r="C300" s="135"/>
+      <c r="D300" s="136"/>
       <c r="E300" s="8" t="s">
         <v>388</v>
       </c>
@@ -10809,8 +11157,8 @@
       <c r="B301" s="7">
         <v>9</v>
       </c>
-      <c r="C301" s="130"/>
-      <c r="D301" s="129" t="s">
+      <c r="C301" s="135"/>
+      <c r="D301" s="143" t="s">
         <v>389</v>
       </c>
       <c r="E301" s="8" t="s">
@@ -10833,8 +11181,8 @@
       <c r="B302" s="7">
         <v>10</v>
       </c>
-      <c r="C302" s="130"/>
-      <c r="D302" s="130"/>
+      <c r="C302" s="135"/>
+      <c r="D302" s="135"/>
       <c r="E302" s="8" t="s">
         <v>391</v>
       </c>
@@ -10855,8 +11203,8 @@
       <c r="B303" s="7">
         <v>11</v>
       </c>
-      <c r="C303" s="130"/>
-      <c r="D303" s="131"/>
+      <c r="C303" s="135"/>
+      <c r="D303" s="136"/>
       <c r="E303" s="8" t="s">
         <v>392</v>
       </c>
@@ -10877,8 +11225,8 @@
       <c r="B304" s="7">
         <v>12</v>
       </c>
-      <c r="C304" s="130"/>
-      <c r="D304" s="129" t="s">
+      <c r="C304" s="135"/>
+      <c r="D304" s="143" t="s">
         <v>393</v>
       </c>
       <c r="E304" s="8" t="s">
@@ -10901,8 +11249,8 @@
       <c r="B305" s="7">
         <v>13</v>
       </c>
-      <c r="C305" s="130"/>
-      <c r="D305" s="130"/>
+      <c r="C305" s="135"/>
+      <c r="D305" s="135"/>
       <c r="E305" s="8" t="s">
         <v>395</v>
       </c>
@@ -10923,8 +11271,8 @@
       <c r="B306" s="7">
         <v>14</v>
       </c>
-      <c r="C306" s="130"/>
-      <c r="D306" s="130"/>
+      <c r="C306" s="135"/>
+      <c r="D306" s="135"/>
       <c r="E306" s="8" t="s">
         <v>396</v>
       </c>
@@ -10945,8 +11293,8 @@
       <c r="B307" s="24">
         <v>15</v>
       </c>
-      <c r="C307" s="131"/>
-      <c r="D307" s="131"/>
+      <c r="C307" s="136"/>
+      <c r="D307" s="136"/>
       <c r="E307" s="17" t="s">
         <v>397</v>
       </c>
@@ -10967,10 +11315,10 @@
       <c r="B308" s="7">
         <v>1</v>
       </c>
-      <c r="C308" s="150" t="s">
+      <c r="C308" s="141" t="s">
         <v>398</v>
       </c>
-      <c r="D308" s="145" t="s">
+      <c r="D308" s="144" t="s">
         <v>399</v>
       </c>
       <c r="E308" s="13" t="s">
@@ -10993,8 +11341,8 @@
       <c r="B309" s="7">
         <v>2</v>
       </c>
-      <c r="C309" s="130"/>
-      <c r="D309" s="130"/>
+      <c r="C309" s="135"/>
+      <c r="D309" s="135"/>
       <c r="E309" s="8" t="s">
         <v>401</v>
       </c>
@@ -11015,8 +11363,8 @@
       <c r="B310" s="7">
         <v>3</v>
       </c>
-      <c r="C310" s="130"/>
-      <c r="D310" s="130"/>
+      <c r="C310" s="135"/>
+      <c r="D310" s="135"/>
       <c r="E310" s="13" t="s">
         <v>402</v>
       </c>
@@ -11037,8 +11385,8 @@
       <c r="B311" s="7">
         <v>4</v>
       </c>
-      <c r="C311" s="130"/>
-      <c r="D311" s="130"/>
+      <c r="C311" s="135"/>
+      <c r="D311" s="135"/>
       <c r="E311" s="8" t="s">
         <v>403</v>
       </c>
@@ -11059,8 +11407,8 @@
       <c r="B312" s="7">
         <v>5</v>
       </c>
-      <c r="C312" s="130"/>
-      <c r="D312" s="130"/>
+      <c r="C312" s="135"/>
+      <c r="D312" s="135"/>
       <c r="E312" s="13" t="s">
         <v>404</v>
       </c>
@@ -11081,8 +11429,8 @@
       <c r="B313" s="7">
         <v>6</v>
       </c>
-      <c r="C313" s="130"/>
-      <c r="D313" s="130"/>
+      <c r="C313" s="135"/>
+      <c r="D313" s="135"/>
       <c r="E313" s="13" t="s">
         <v>405</v>
       </c>
@@ -11103,8 +11451,8 @@
       <c r="B314" s="7">
         <v>7</v>
       </c>
-      <c r="C314" s="130"/>
-      <c r="D314" s="131"/>
+      <c r="C314" s="135"/>
+      <c r="D314" s="136"/>
       <c r="E314" s="8" t="s">
         <v>406</v>
       </c>
@@ -11125,8 +11473,8 @@
       <c r="B315" s="7">
         <v>8</v>
       </c>
-      <c r="C315" s="130"/>
-      <c r="D315" s="145" t="s">
+      <c r="C315" s="135"/>
+      <c r="D315" s="144" t="s">
         <v>407</v>
       </c>
       <c r="E315" s="13" t="s">
@@ -11149,8 +11497,8 @@
       <c r="B316" s="7">
         <v>9</v>
       </c>
-      <c r="C316" s="130"/>
-      <c r="D316" s="130"/>
+      <c r="C316" s="135"/>
+      <c r="D316" s="135"/>
       <c r="E316" s="8" t="s">
         <v>409</v>
       </c>
@@ -11171,8 +11519,8 @@
       <c r="B317" s="24">
         <v>10</v>
       </c>
-      <c r="C317" s="131"/>
-      <c r="D317" s="131"/>
+      <c r="C317" s="136"/>
+      <c r="D317" s="136"/>
       <c r="E317" s="17" t="s">
         <v>410</v>
       </c>
@@ -11193,10 +11541,10 @@
       <c r="B318" s="7">
         <v>1</v>
       </c>
-      <c r="C318" s="151" t="s">
+      <c r="C318" s="142" t="s">
         <v>411</v>
       </c>
-      <c r="D318" s="145" t="s">
+      <c r="D318" s="144" t="s">
         <v>412</v>
       </c>
       <c r="E318" s="8" t="s">
@@ -11219,8 +11567,8 @@
       <c r="B319" s="7">
         <v>2</v>
       </c>
-      <c r="C319" s="130"/>
-      <c r="D319" s="130"/>
+      <c r="C319" s="135"/>
+      <c r="D319" s="135"/>
       <c r="E319" s="13" t="s">
         <v>414</v>
       </c>
@@ -11241,8 +11589,8 @@
       <c r="B320" s="7">
         <v>3</v>
       </c>
-      <c r="C320" s="130"/>
-      <c r="D320" s="130"/>
+      <c r="C320" s="135"/>
+      <c r="D320" s="135"/>
       <c r="E320" s="8" t="s">
         <v>415</v>
       </c>
@@ -11263,8 +11611,8 @@
       <c r="B321" s="7">
         <v>4</v>
       </c>
-      <c r="C321" s="130"/>
-      <c r="D321" s="130"/>
+      <c r="C321" s="135"/>
+      <c r="D321" s="135"/>
       <c r="E321" s="8" t="s">
         <v>416</v>
       </c>
@@ -11285,8 +11633,8 @@
       <c r="B322" s="7">
         <v>5</v>
       </c>
-      <c r="C322" s="130"/>
-      <c r="D322" s="130"/>
+      <c r="C322" s="135"/>
+      <c r="D322" s="135"/>
       <c r="E322" s="8" t="s">
         <v>417</v>
       </c>
@@ -11307,8 +11655,8 @@
       <c r="B323" s="7">
         <v>6</v>
       </c>
-      <c r="C323" s="130"/>
-      <c r="D323" s="131"/>
+      <c r="C323" s="135"/>
+      <c r="D323" s="136"/>
       <c r="E323" s="29" t="s">
         <v>418</v>
       </c>
@@ -11329,8 +11677,8 @@
       <c r="B324" s="7">
         <v>7</v>
       </c>
-      <c r="C324" s="130"/>
-      <c r="D324" s="145" t="s">
+      <c r="C324" s="135"/>
+      <c r="D324" s="144" t="s">
         <v>419</v>
       </c>
       <c r="E324" s="13" t="s">
@@ -11353,8 +11701,8 @@
       <c r="B325" s="7">
         <v>8</v>
       </c>
-      <c r="C325" s="130"/>
-      <c r="D325" s="130"/>
+      <c r="C325" s="135"/>
+      <c r="D325" s="135"/>
       <c r="E325" s="8" t="s">
         <v>421</v>
       </c>
@@ -11375,8 +11723,8 @@
       <c r="B326" s="7">
         <v>9</v>
       </c>
-      <c r="C326" s="130"/>
-      <c r="D326" s="130"/>
+      <c r="C326" s="135"/>
+      <c r="D326" s="135"/>
       <c r="E326" s="8" t="s">
         <v>422</v>
       </c>
@@ -11397,8 +11745,8 @@
       <c r="B327" s="7">
         <v>10</v>
       </c>
-      <c r="C327" s="130"/>
-      <c r="D327" s="130"/>
+      <c r="C327" s="135"/>
+      <c r="D327" s="135"/>
       <c r="E327" s="8" t="s">
         <v>423</v>
       </c>
@@ -11419,8 +11767,8 @@
       <c r="B328" s="7">
         <v>11</v>
       </c>
-      <c r="C328" s="130"/>
-      <c r="D328" s="131"/>
+      <c r="C328" s="135"/>
+      <c r="D328" s="136"/>
       <c r="E328" s="13" t="s">
         <v>424</v>
       </c>
@@ -11441,8 +11789,8 @@
       <c r="B329" s="7">
         <v>12</v>
       </c>
-      <c r="C329" s="130"/>
-      <c r="D329" s="145" t="s">
+      <c r="C329" s="135"/>
+      <c r="D329" s="144" t="s">
         <v>425</v>
       </c>
       <c r="E329" s="8" t="s">
@@ -11465,8 +11813,8 @@
       <c r="B330" s="7">
         <v>13</v>
       </c>
-      <c r="C330" s="130"/>
-      <c r="D330" s="130"/>
+      <c r="C330" s="135"/>
+      <c r="D330" s="135"/>
       <c r="E330" s="8" t="s">
         <v>427</v>
       </c>
@@ -11487,8 +11835,8 @@
       <c r="B331" s="7">
         <v>14</v>
       </c>
-      <c r="C331" s="130"/>
-      <c r="D331" s="130"/>
+      <c r="C331" s="135"/>
+      <c r="D331" s="135"/>
       <c r="E331" s="8" t="s">
         <v>428</v>
       </c>
@@ -11509,8 +11857,8 @@
       <c r="B332" s="7">
         <v>15</v>
       </c>
-      <c r="C332" s="130"/>
-      <c r="D332" s="130"/>
+      <c r="C332" s="135"/>
+      <c r="D332" s="135"/>
       <c r="E332" s="8" t="s">
         <v>429</v>
       </c>
@@ -11531,8 +11879,8 @@
       <c r="B333" s="7">
         <v>16</v>
       </c>
-      <c r="C333" s="130"/>
-      <c r="D333" s="130"/>
+      <c r="C333" s="135"/>
+      <c r="D333" s="135"/>
       <c r="E333" s="8" t="s">
         <v>430</v>
       </c>
@@ -11553,8 +11901,8 @@
       <c r="B334" s="7">
         <v>17</v>
       </c>
-      <c r="C334" s="130"/>
-      <c r="D334" s="130"/>
+      <c r="C334" s="135"/>
+      <c r="D334" s="135"/>
       <c r="E334" s="8" t="s">
         <v>431</v>
       </c>
@@ -11575,8 +11923,8 @@
       <c r="B335" s="7">
         <v>18</v>
       </c>
-      <c r="C335" s="130"/>
-      <c r="D335" s="130"/>
+      <c r="C335" s="135"/>
+      <c r="D335" s="135"/>
       <c r="E335" s="8" t="s">
         <v>432</v>
       </c>
@@ -11597,8 +11945,8 @@
       <c r="B336" s="7">
         <v>19</v>
       </c>
-      <c r="C336" s="130"/>
-      <c r="D336" s="130"/>
+      <c r="C336" s="135"/>
+      <c r="D336" s="135"/>
       <c r="E336" s="8" t="s">
         <v>433</v>
       </c>
@@ -11619,8 +11967,8 @@
       <c r="B337" s="7">
         <v>20</v>
       </c>
-      <c r="C337" s="130"/>
-      <c r="D337" s="131"/>
+      <c r="C337" s="135"/>
+      <c r="D337" s="136"/>
       <c r="E337" s="13" t="s">
         <v>434</v>
       </c>
@@ -11641,8 +11989,8 @@
       <c r="B338" s="7">
         <v>21</v>
       </c>
-      <c r="C338" s="130"/>
-      <c r="D338" s="145" t="s">
+      <c r="C338" s="135"/>
+      <c r="D338" s="144" t="s">
         <v>435</v>
       </c>
       <c r="E338" s="13" t="s">
@@ -11665,8 +12013,8 @@
       <c r="B339" s="7">
         <v>22</v>
       </c>
-      <c r="C339" s="130"/>
-      <c r="D339" s="130"/>
+      <c r="C339" s="135"/>
+      <c r="D339" s="135"/>
       <c r="E339" s="13" t="s">
         <v>437</v>
       </c>
@@ -11687,8 +12035,8 @@
       <c r="B340" s="7">
         <v>23</v>
       </c>
-      <c r="C340" s="130"/>
-      <c r="D340" s="130"/>
+      <c r="C340" s="135"/>
+      <c r="D340" s="135"/>
       <c r="E340" s="13" t="s">
         <v>438</v>
       </c>
@@ -11709,8 +12057,8 @@
       <c r="B341" s="7">
         <v>24</v>
       </c>
-      <c r="C341" s="130"/>
-      <c r="D341" s="130"/>
+      <c r="C341" s="135"/>
+      <c r="D341" s="135"/>
       <c r="E341" s="13" t="s">
         <v>439</v>
       </c>
@@ -11731,8 +12079,8 @@
       <c r="B342" s="24">
         <v>25</v>
       </c>
-      <c r="C342" s="131"/>
-      <c r="D342" s="131"/>
+      <c r="C342" s="136"/>
+      <c r="D342" s="136"/>
       <c r="E342" s="25" t="s">
         <v>440</v>
       </c>
@@ -11753,10 +12101,10 @@
       <c r="B343" s="7">
         <v>1</v>
       </c>
-      <c r="C343" s="140" t="s">
+      <c r="C343" s="134" t="s">
         <v>441</v>
       </c>
-      <c r="D343" s="129" t="s">
+      <c r="D343" s="143" t="s">
         <v>442</v>
       </c>
       <c r="E343" s="8" t="s">
@@ -11785,8 +12133,8 @@
       <c r="B344" s="7">
         <v>2</v>
       </c>
-      <c r="C344" s="130"/>
-      <c r="D344" s="130"/>
+      <c r="C344" s="135"/>
+      <c r="D344" s="135"/>
       <c r="E344" s="8" t="s">
         <v>444</v>
       </c>
@@ -11813,8 +12161,8 @@
       <c r="B345" s="7">
         <v>3</v>
       </c>
-      <c r="C345" s="130"/>
-      <c r="D345" s="130"/>
+      <c r="C345" s="135"/>
+      <c r="D345" s="135"/>
       <c r="E345" s="8" t="s">
         <v>445</v>
       </c>
@@ -11841,8 +12189,8 @@
       <c r="B346" s="7">
         <v>4</v>
       </c>
-      <c r="C346" s="130"/>
-      <c r="D346" s="130"/>
+      <c r="C346" s="135"/>
+      <c r="D346" s="135"/>
       <c r="E346" s="8" t="s">
         <v>446</v>
       </c>
@@ -11869,8 +12217,8 @@
       <c r="B347" s="7">
         <v>5</v>
       </c>
-      <c r="C347" s="130"/>
-      <c r="D347" s="131"/>
+      <c r="C347" s="135"/>
+      <c r="D347" s="136"/>
       <c r="E347" s="8" t="s">
         <v>447</v>
       </c>
@@ -11897,8 +12245,8 @@
       <c r="B348" s="7">
         <v>6</v>
       </c>
-      <c r="C348" s="130"/>
-      <c r="D348" s="129" t="s">
+      <c r="C348" s="135"/>
+      <c r="D348" s="143" t="s">
         <v>448</v>
       </c>
       <c r="E348" s="8" t="s">
@@ -11925,8 +12273,8 @@
       <c r="B349" s="7">
         <v>7</v>
       </c>
-      <c r="C349" s="130"/>
-      <c r="D349" s="130"/>
+      <c r="C349" s="135"/>
+      <c r="D349" s="135"/>
       <c r="E349" s="8" t="s">
         <v>450</v>
       </c>
@@ -11953,8 +12301,8 @@
       <c r="B350" s="7">
         <v>8</v>
       </c>
-      <c r="C350" s="130"/>
-      <c r="D350" s="130"/>
+      <c r="C350" s="135"/>
+      <c r="D350" s="135"/>
       <c r="E350" s="8" t="s">
         <v>451</v>
       </c>
@@ -11981,8 +12329,8 @@
       <c r="B351" s="7">
         <v>9</v>
       </c>
-      <c r="C351" s="130"/>
-      <c r="D351" s="130"/>
+      <c r="C351" s="135"/>
+      <c r="D351" s="135"/>
       <c r="E351" s="8" t="s">
         <v>452</v>
       </c>
@@ -12005,8 +12353,8 @@
       <c r="B352" s="7">
         <v>10</v>
       </c>
-      <c r="C352" s="130"/>
-      <c r="D352" s="130"/>
+      <c r="C352" s="135"/>
+      <c r="D352" s="135"/>
       <c r="E352" s="8" t="s">
         <v>453</v>
       </c>
@@ -12033,8 +12381,8 @@
       <c r="B353" s="7">
         <v>11</v>
       </c>
-      <c r="C353" s="130"/>
-      <c r="D353" s="131"/>
+      <c r="C353" s="135"/>
+      <c r="D353" s="136"/>
       <c r="E353" s="8" t="s">
         <v>454</v>
       </c>
@@ -12055,8 +12403,8 @@
       <c r="B354" s="7">
         <v>12</v>
       </c>
-      <c r="C354" s="130"/>
-      <c r="D354" s="129" t="s">
+      <c r="C354" s="135"/>
+      <c r="D354" s="143" t="s">
         <v>455</v>
       </c>
       <c r="E354" s="8" t="s">
@@ -12083,8 +12431,8 @@
       <c r="B355" s="7">
         <v>13</v>
       </c>
-      <c r="C355" s="130"/>
-      <c r="D355" s="130"/>
+      <c r="C355" s="135"/>
+      <c r="D355" s="135"/>
       <c r="E355" s="8" t="s">
         <v>457</v>
       </c>
@@ -12111,8 +12459,8 @@
       <c r="B356" s="7">
         <v>14</v>
       </c>
-      <c r="C356" s="130"/>
-      <c r="D356" s="130"/>
+      <c r="C356" s="135"/>
+      <c r="D356" s="135"/>
       <c r="E356" s="8" t="s">
         <v>458</v>
       </c>
@@ -12133,8 +12481,8 @@
       <c r="B357" s="7">
         <v>15</v>
       </c>
-      <c r="C357" s="131"/>
-      <c r="D357" s="131"/>
+      <c r="C357" s="136"/>
+      <c r="D357" s="136"/>
       <c r="E357" s="8" t="s">
         <v>459</v>
       </c>
@@ -12149,18 +12497,18 @@
       <c r="J357" s="11"/>
     </row>
     <row r="358" spans="1:10" ht="13.8">
-      <c r="A358" s="148" t="s">
+      <c r="A358" s="150" t="s">
         <v>460</v>
       </c>
-      <c r="B358" s="136"/>
-      <c r="C358" s="136"/>
-      <c r="D358" s="136"/>
-      <c r="E358" s="136"/>
-      <c r="F358" s="136"/>
-      <c r="G358" s="136"/>
-      <c r="H358" s="136"/>
-      <c r="I358" s="136"/>
-      <c r="J358" s="137"/>
+      <c r="B358" s="146"/>
+      <c r="C358" s="146"/>
+      <c r="D358" s="146"/>
+      <c r="E358" s="146"/>
+      <c r="F358" s="146"/>
+      <c r="G358" s="146"/>
+      <c r="H358" s="146"/>
+      <c r="I358" s="146"/>
+      <c r="J358" s="147"/>
     </row>
     <row r="359" spans="1:10" ht="13.8">
       <c r="A359" s="6">
@@ -12169,10 +12517,10 @@
       <c r="B359" s="7">
         <v>1</v>
       </c>
-      <c r="C359" s="141" t="s">
+      <c r="C359" s="137" t="s">
         <v>461</v>
       </c>
-      <c r="D359" s="129" t="s">
+      <c r="D359" s="143" t="s">
         <v>462</v>
       </c>
       <c r="E359" s="8" t="s">
@@ -12195,8 +12543,8 @@
       <c r="B360" s="7">
         <v>2</v>
       </c>
-      <c r="C360" s="130"/>
-      <c r="D360" s="130"/>
+      <c r="C360" s="135"/>
+      <c r="D360" s="135"/>
       <c r="E360" s="8" t="s">
         <v>464</v>
       </c>
@@ -12217,8 +12565,8 @@
       <c r="B361" s="7">
         <v>3</v>
       </c>
-      <c r="C361" s="130"/>
-      <c r="D361" s="130"/>
+      <c r="C361" s="135"/>
+      <c r="D361" s="135"/>
       <c r="E361" s="8" t="s">
         <v>465</v>
       </c>
@@ -12239,8 +12587,8 @@
       <c r="B362" s="7">
         <v>4</v>
       </c>
-      <c r="C362" s="130"/>
-      <c r="D362" s="130"/>
+      <c r="C362" s="135"/>
+      <c r="D362" s="135"/>
       <c r="E362" s="8" t="s">
         <v>466</v>
       </c>
@@ -12261,8 +12609,8 @@
       <c r="B363" s="7">
         <v>5</v>
       </c>
-      <c r="C363" s="130"/>
-      <c r="D363" s="131"/>
+      <c r="C363" s="135"/>
+      <c r="D363" s="136"/>
       <c r="E363" s="8" t="s">
         <v>467</v>
       </c>
@@ -12283,8 +12631,8 @@
       <c r="B364" s="7">
         <v>6</v>
       </c>
-      <c r="C364" s="130"/>
-      <c r="D364" s="129" t="s">
+      <c r="C364" s="135"/>
+      <c r="D364" s="143" t="s">
         <v>468</v>
       </c>
       <c r="E364" s="8" t="s">
@@ -12307,8 +12655,8 @@
       <c r="B365" s="7">
         <v>7</v>
       </c>
-      <c r="C365" s="130"/>
-      <c r="D365" s="130"/>
+      <c r="C365" s="135"/>
+      <c r="D365" s="135"/>
       <c r="E365" s="8" t="s">
         <v>470</v>
       </c>
@@ -12329,8 +12677,8 @@
       <c r="B366" s="7">
         <v>8</v>
       </c>
-      <c r="C366" s="130"/>
-      <c r="D366" s="130"/>
+      <c r="C366" s="135"/>
+      <c r="D366" s="135"/>
       <c r="E366" s="8" t="s">
         <v>471</v>
       </c>
@@ -12351,8 +12699,8 @@
       <c r="B367" s="7">
         <v>9</v>
       </c>
-      <c r="C367" s="130"/>
-      <c r="D367" s="130"/>
+      <c r="C367" s="135"/>
+      <c r="D367" s="135"/>
       <c r="E367" s="8" t="s">
         <v>472</v>
       </c>
@@ -12373,8 +12721,8 @@
       <c r="B368" s="7">
         <v>10</v>
       </c>
-      <c r="C368" s="130"/>
-      <c r="D368" s="130"/>
+      <c r="C368" s="135"/>
+      <c r="D368" s="135"/>
       <c r="E368" s="8" t="s">
         <v>473</v>
       </c>
@@ -12395,8 +12743,8 @@
       <c r="B369" s="7">
         <v>11</v>
       </c>
-      <c r="C369" s="130"/>
-      <c r="D369" s="130"/>
+      <c r="C369" s="135"/>
+      <c r="D369" s="135"/>
       <c r="E369" s="8" t="s">
         <v>474</v>
       </c>
@@ -12417,8 +12765,8 @@
       <c r="B370" s="7">
         <v>12</v>
       </c>
-      <c r="C370" s="130"/>
-      <c r="D370" s="130"/>
+      <c r="C370" s="135"/>
+      <c r="D370" s="135"/>
       <c r="E370" s="8" t="s">
         <v>475</v>
       </c>
@@ -12439,8 +12787,8 @@
       <c r="B371" s="7">
         <v>13</v>
       </c>
-      <c r="C371" s="130"/>
-      <c r="D371" s="131"/>
+      <c r="C371" s="135"/>
+      <c r="D371" s="136"/>
       <c r="E371" s="8" t="s">
         <v>476</v>
       </c>
@@ -12461,8 +12809,8 @@
       <c r="B372" s="7">
         <v>14</v>
       </c>
-      <c r="C372" s="130"/>
-      <c r="D372" s="129" t="s">
+      <c r="C372" s="135"/>
+      <c r="D372" s="143" t="s">
         <v>477</v>
       </c>
       <c r="E372" s="8" t="s">
@@ -12485,8 +12833,8 @@
       <c r="B373" s="7">
         <v>15</v>
       </c>
-      <c r="C373" s="130"/>
-      <c r="D373" s="130"/>
+      <c r="C373" s="135"/>
+      <c r="D373" s="135"/>
       <c r="E373" s="11" t="s">
         <v>479</v>
       </c>
@@ -12507,8 +12855,8 @@
       <c r="B374" s="7">
         <v>16</v>
       </c>
-      <c r="C374" s="130"/>
-      <c r="D374" s="130"/>
+      <c r="C374" s="135"/>
+      <c r="D374" s="135"/>
       <c r="E374" s="8" t="s">
         <v>480</v>
       </c>
@@ -12529,8 +12877,8 @@
       <c r="B375" s="7">
         <v>17</v>
       </c>
-      <c r="C375" s="130"/>
-      <c r="D375" s="131"/>
+      <c r="C375" s="135"/>
+      <c r="D375" s="136"/>
       <c r="E375" s="8" t="s">
         <v>481</v>
       </c>
@@ -12551,8 +12899,8 @@
       <c r="B376" s="7">
         <v>18</v>
       </c>
-      <c r="C376" s="130"/>
-      <c r="D376" s="129" t="s">
+      <c r="C376" s="135"/>
+      <c r="D376" s="143" t="s">
         <v>482</v>
       </c>
       <c r="E376" s="8" t="s">
@@ -12575,8 +12923,8 @@
       <c r="B377" s="7">
         <v>19</v>
       </c>
-      <c r="C377" s="130"/>
-      <c r="D377" s="130"/>
+      <c r="C377" s="135"/>
+      <c r="D377" s="135"/>
       <c r="E377" s="8" t="s">
         <v>484</v>
       </c>
@@ -12597,8 +12945,8 @@
       <c r="B378" s="7">
         <v>20</v>
       </c>
-      <c r="C378" s="130"/>
-      <c r="D378" s="130"/>
+      <c r="C378" s="135"/>
+      <c r="D378" s="135"/>
       <c r="E378" s="8" t="s">
         <v>485</v>
       </c>
@@ -12619,8 +12967,8 @@
       <c r="B379" s="7">
         <v>21</v>
       </c>
-      <c r="C379" s="130"/>
-      <c r="D379" s="130"/>
+      <c r="C379" s="135"/>
+      <c r="D379" s="135"/>
       <c r="E379" s="8" t="s">
         <v>486</v>
       </c>
@@ -12641,8 +12989,8 @@
       <c r="B380" s="24">
         <v>22</v>
       </c>
-      <c r="C380" s="131"/>
-      <c r="D380" s="131"/>
+      <c r="C380" s="136"/>
+      <c r="D380" s="136"/>
       <c r="E380" s="17" t="s">
         <v>487</v>
       </c>
@@ -12666,7 +13014,7 @@
       <c r="C381" s="138" t="s">
         <v>488</v>
       </c>
-      <c r="D381" s="129" t="s">
+      <c r="D381" s="143" t="s">
         <v>489</v>
       </c>
       <c r="E381" s="8" t="s">
@@ -12689,8 +13037,8 @@
       <c r="B382" s="7">
         <v>2</v>
       </c>
-      <c r="C382" s="130"/>
-      <c r="D382" s="130"/>
+      <c r="C382" s="135"/>
+      <c r="D382" s="135"/>
       <c r="E382" s="8" t="s">
         <v>491</v>
       </c>
@@ -12711,8 +13059,8 @@
       <c r="B383" s="7">
         <v>3</v>
       </c>
-      <c r="C383" s="130"/>
-      <c r="D383" s="130"/>
+      <c r="C383" s="135"/>
+      <c r="D383" s="135"/>
       <c r="E383" s="8" t="s">
         <v>492</v>
       </c>
@@ -12733,8 +13081,8 @@
       <c r="B384" s="7">
         <v>4</v>
       </c>
-      <c r="C384" s="130"/>
-      <c r="D384" s="130"/>
+      <c r="C384" s="135"/>
+      <c r="D384" s="135"/>
       <c r="E384" s="8" t="s">
         <v>493</v>
       </c>
@@ -12755,8 +13103,8 @@
       <c r="B385" s="7">
         <v>5</v>
       </c>
-      <c r="C385" s="130"/>
-      <c r="D385" s="130"/>
+      <c r="C385" s="135"/>
+      <c r="D385" s="135"/>
       <c r="E385" s="8" t="s">
         <v>494</v>
       </c>
@@ -12777,8 +13125,8 @@
       <c r="B386" s="7">
         <v>6</v>
       </c>
-      <c r="C386" s="130"/>
-      <c r="D386" s="131"/>
+      <c r="C386" s="135"/>
+      <c r="D386" s="136"/>
       <c r="E386" s="8" t="s">
         <v>495</v>
       </c>
@@ -12799,8 +13147,8 @@
       <c r="B387" s="7">
         <v>7</v>
       </c>
-      <c r="C387" s="130"/>
-      <c r="D387" s="129" t="s">
+      <c r="C387" s="135"/>
+      <c r="D387" s="143" t="s">
         <v>496</v>
       </c>
       <c r="E387" s="8" t="s">
@@ -12823,8 +13171,8 @@
       <c r="B388" s="7">
         <v>8</v>
       </c>
-      <c r="C388" s="130"/>
-      <c r="D388" s="130"/>
+      <c r="C388" s="135"/>
+      <c r="D388" s="135"/>
       <c r="E388" s="8" t="s">
         <v>498</v>
       </c>
@@ -12845,8 +13193,8 @@
       <c r="B389" s="7">
         <v>9</v>
       </c>
-      <c r="C389" s="130"/>
-      <c r="D389" s="130"/>
+      <c r="C389" s="135"/>
+      <c r="D389" s="135"/>
       <c r="E389" s="8" t="s">
         <v>499</v>
       </c>
@@ -12867,8 +13215,8 @@
       <c r="B390" s="7">
         <v>10</v>
       </c>
-      <c r="C390" s="130"/>
-      <c r="D390" s="130"/>
+      <c r="C390" s="135"/>
+      <c r="D390" s="135"/>
       <c r="E390" s="8" t="s">
         <v>500</v>
       </c>
@@ -12889,8 +13237,8 @@
       <c r="B391" s="7">
         <v>11</v>
       </c>
-      <c r="C391" s="130"/>
-      <c r="D391" s="130"/>
+      <c r="C391" s="135"/>
+      <c r="D391" s="135"/>
       <c r="E391" s="8" t="s">
         <v>501</v>
       </c>
@@ -12911,8 +13259,8 @@
       <c r="B392" s="7">
         <v>12</v>
       </c>
-      <c r="C392" s="130"/>
-      <c r="D392" s="130"/>
+      <c r="C392" s="135"/>
+      <c r="D392" s="135"/>
       <c r="E392" s="8" t="s">
         <v>502</v>
       </c>
@@ -12933,8 +13281,8 @@
       <c r="B393" s="7">
         <v>13</v>
       </c>
-      <c r="C393" s="130"/>
-      <c r="D393" s="130"/>
+      <c r="C393" s="135"/>
+      <c r="D393" s="135"/>
       <c r="E393" s="8" t="s">
         <v>503</v>
       </c>
@@ -12955,8 +13303,8 @@
       <c r="B394" s="7">
         <v>14</v>
       </c>
-      <c r="C394" s="130"/>
-      <c r="D394" s="130"/>
+      <c r="C394" s="135"/>
+      <c r="D394" s="135"/>
       <c r="E394" s="8" t="s">
         <v>504</v>
       </c>
@@ -12977,8 +13325,8 @@
       <c r="B395" s="7">
         <v>15</v>
       </c>
-      <c r="C395" s="130"/>
-      <c r="D395" s="130"/>
+      <c r="C395" s="135"/>
+      <c r="D395" s="135"/>
       <c r="E395" s="8" t="s">
         <v>505</v>
       </c>
@@ -12999,8 +13347,8 @@
       <c r="B396" s="7">
         <v>16</v>
       </c>
-      <c r="C396" s="130"/>
-      <c r="D396" s="131"/>
+      <c r="C396" s="135"/>
+      <c r="D396" s="136"/>
       <c r="E396" s="8" t="s">
         <v>506</v>
       </c>
@@ -13021,8 +13369,8 @@
       <c r="B397" s="7">
         <v>17</v>
       </c>
-      <c r="C397" s="130"/>
-      <c r="D397" s="129" t="s">
+      <c r="C397" s="135"/>
+      <c r="D397" s="143" t="s">
         <v>507</v>
       </c>
       <c r="E397" s="8" t="s">
@@ -13045,8 +13393,8 @@
       <c r="B398" s="7">
         <v>18</v>
       </c>
-      <c r="C398" s="130"/>
-      <c r="D398" s="130"/>
+      <c r="C398" s="135"/>
+      <c r="D398" s="135"/>
       <c r="E398" s="8" t="s">
         <v>509</v>
       </c>
@@ -13067,8 +13415,8 @@
       <c r="B399" s="7">
         <v>19</v>
       </c>
-      <c r="C399" s="130"/>
-      <c r="D399" s="131"/>
+      <c r="C399" s="135"/>
+      <c r="D399" s="136"/>
       <c r="E399" s="8" t="s">
         <v>510</v>
       </c>
@@ -13089,8 +13437,8 @@
       <c r="B400" s="7">
         <v>20</v>
       </c>
-      <c r="C400" s="130"/>
-      <c r="D400" s="129" t="s">
+      <c r="C400" s="135"/>
+      <c r="D400" s="143" t="s">
         <v>511</v>
       </c>
       <c r="E400" s="8" t="s">
@@ -13113,8 +13461,8 @@
       <c r="B401" s="7">
         <v>21</v>
       </c>
-      <c r="C401" s="130"/>
-      <c r="D401" s="130"/>
+      <c r="C401" s="135"/>
+      <c r="D401" s="135"/>
       <c r="E401" s="8" t="s">
         <v>513</v>
       </c>
@@ -13135,8 +13483,8 @@
       <c r="B402" s="7">
         <v>22</v>
       </c>
-      <c r="C402" s="130"/>
-      <c r="D402" s="130"/>
+      <c r="C402" s="135"/>
+      <c r="D402" s="135"/>
       <c r="E402" s="8" t="s">
         <v>514</v>
       </c>
@@ -13157,8 +13505,8 @@
       <c r="B403" s="7">
         <v>23</v>
       </c>
-      <c r="C403" s="130"/>
-      <c r="D403" s="130"/>
+      <c r="C403" s="135"/>
+      <c r="D403" s="135"/>
       <c r="E403" s="8" t="s">
         <v>515</v>
       </c>
@@ -13179,8 +13527,8 @@
       <c r="B404" s="7">
         <v>24</v>
       </c>
-      <c r="C404" s="130"/>
-      <c r="D404" s="131"/>
+      <c r="C404" s="135"/>
+      <c r="D404" s="136"/>
       <c r="E404" s="8" t="s">
         <v>516</v>
       </c>
@@ -13201,8 +13549,8 @@
       <c r="B405" s="7">
         <v>25</v>
       </c>
-      <c r="C405" s="130"/>
-      <c r="D405" s="129" t="s">
+      <c r="C405" s="135"/>
+      <c r="D405" s="143" t="s">
         <v>517</v>
       </c>
       <c r="E405" s="8" t="s">
@@ -13225,8 +13573,8 @@
       <c r="B406" s="7">
         <v>26</v>
       </c>
-      <c r="C406" s="130"/>
-      <c r="D406" s="130"/>
+      <c r="C406" s="135"/>
+      <c r="D406" s="135"/>
       <c r="E406" s="8" t="s">
         <v>519</v>
       </c>
@@ -13247,8 +13595,8 @@
       <c r="B407" s="7">
         <v>27</v>
       </c>
-      <c r="C407" s="130"/>
-      <c r="D407" s="130"/>
+      <c r="C407" s="135"/>
+      <c r="D407" s="135"/>
       <c r="E407" s="8" t="s">
         <v>520</v>
       </c>
@@ -13269,8 +13617,8 @@
       <c r="B408" s="7">
         <v>28</v>
       </c>
-      <c r="C408" s="130"/>
-      <c r="D408" s="130"/>
+      <c r="C408" s="135"/>
+      <c r="D408" s="135"/>
       <c r="E408" s="8" t="s">
         <v>521</v>
       </c>
@@ -13291,8 +13639,8 @@
       <c r="B409" s="7">
         <v>29</v>
       </c>
-      <c r="C409" s="130"/>
-      <c r="D409" s="130"/>
+      <c r="C409" s="135"/>
+      <c r="D409" s="135"/>
       <c r="E409" s="8" t="s">
         <v>522</v>
       </c>
@@ -13313,8 +13661,8 @@
       <c r="B410" s="7">
         <v>30</v>
       </c>
-      <c r="C410" s="130"/>
-      <c r="D410" s="130"/>
+      <c r="C410" s="135"/>
+      <c r="D410" s="135"/>
       <c r="E410" s="8" t="s">
         <v>523</v>
       </c>
@@ -13335,8 +13683,8 @@
       <c r="B411" s="7">
         <v>31</v>
       </c>
-      <c r="C411" s="130"/>
-      <c r="D411" s="130"/>
+      <c r="C411" s="135"/>
+      <c r="D411" s="135"/>
       <c r="E411" s="8" t="s">
         <v>524</v>
       </c>
@@ -13357,8 +13705,8 @@
       <c r="B412" s="7">
         <v>32</v>
       </c>
-      <c r="C412" s="130"/>
-      <c r="D412" s="130"/>
+      <c r="C412" s="135"/>
+      <c r="D412" s="135"/>
       <c r="E412" s="8" t="s">
         <v>525</v>
       </c>
@@ -13379,8 +13727,8 @@
       <c r="B413" s="7">
         <v>33</v>
       </c>
-      <c r="C413" s="130"/>
-      <c r="D413" s="130"/>
+      <c r="C413" s="135"/>
+      <c r="D413" s="135"/>
       <c r="E413" s="8" t="s">
         <v>526</v>
       </c>
@@ -13401,8 +13749,8 @@
       <c r="B414" s="7">
         <v>34</v>
       </c>
-      <c r="C414" s="130"/>
-      <c r="D414" s="130"/>
+      <c r="C414" s="135"/>
+      <c r="D414" s="135"/>
       <c r="E414" s="8" t="s">
         <v>527</v>
       </c>
@@ -13423,8 +13771,8 @@
       <c r="B415" s="7">
         <v>35</v>
       </c>
-      <c r="C415" s="130"/>
-      <c r="D415" s="130"/>
+      <c r="C415" s="135"/>
+      <c r="D415" s="135"/>
       <c r="E415" s="8" t="s">
         <v>528</v>
       </c>
@@ -13445,8 +13793,8 @@
       <c r="B416" s="7">
         <v>36</v>
       </c>
-      <c r="C416" s="130"/>
-      <c r="D416" s="131"/>
+      <c r="C416" s="135"/>
+      <c r="D416" s="136"/>
       <c r="E416" s="8" t="s">
         <v>529</v>
       </c>
@@ -13467,8 +13815,8 @@
       <c r="B417" s="7">
         <v>37</v>
       </c>
-      <c r="C417" s="130"/>
-      <c r="D417" s="129" t="s">
+      <c r="C417" s="135"/>
+      <c r="D417" s="143" t="s">
         <v>530</v>
       </c>
       <c r="E417" s="8" t="s">
@@ -13491,8 +13839,8 @@
       <c r="B418" s="7">
         <v>38</v>
       </c>
-      <c r="C418" s="130"/>
-      <c r="D418" s="130"/>
+      <c r="C418" s="135"/>
+      <c r="D418" s="135"/>
       <c r="E418" s="8" t="s">
         <v>532</v>
       </c>
@@ -13513,8 +13861,8 @@
       <c r="B419" s="7">
         <v>39</v>
       </c>
-      <c r="C419" s="130"/>
-      <c r="D419" s="131"/>
+      <c r="C419" s="135"/>
+      <c r="D419" s="136"/>
       <c r="E419" s="8" t="s">
         <v>533</v>
       </c>
@@ -13535,8 +13883,8 @@
       <c r="B420" s="7">
         <v>40</v>
       </c>
-      <c r="C420" s="130"/>
-      <c r="D420" s="129" t="s">
+      <c r="C420" s="135"/>
+      <c r="D420" s="143" t="s">
         <v>534</v>
       </c>
       <c r="E420" s="8" t="s">
@@ -13559,8 +13907,8 @@
       <c r="B421" s="7">
         <v>41</v>
       </c>
-      <c r="C421" s="130"/>
-      <c r="D421" s="130"/>
+      <c r="C421" s="135"/>
+      <c r="D421" s="135"/>
       <c r="E421" s="8" t="s">
         <v>536</v>
       </c>
@@ -13581,8 +13929,8 @@
       <c r="B422" s="7">
         <v>42</v>
       </c>
-      <c r="C422" s="130"/>
-      <c r="D422" s="130"/>
+      <c r="C422" s="135"/>
+      <c r="D422" s="135"/>
       <c r="E422" s="8" t="s">
         <v>537</v>
       </c>
@@ -13603,8 +13951,8 @@
       <c r="B423" s="7">
         <v>43</v>
       </c>
-      <c r="C423" s="130"/>
-      <c r="D423" s="130"/>
+      <c r="C423" s="135"/>
+      <c r="D423" s="135"/>
       <c r="E423" s="8" t="s">
         <v>538</v>
       </c>
@@ -13625,8 +13973,8 @@
       <c r="B424" s="7">
         <v>44</v>
       </c>
-      <c r="C424" s="130"/>
-      <c r="D424" s="130"/>
+      <c r="C424" s="135"/>
+      <c r="D424" s="135"/>
       <c r="E424" s="8" t="s">
         <v>539</v>
       </c>
@@ -13647,8 +13995,8 @@
       <c r="B425" s="7">
         <v>45</v>
       </c>
-      <c r="C425" s="130"/>
-      <c r="D425" s="130"/>
+      <c r="C425" s="135"/>
+      <c r="D425" s="135"/>
       <c r="E425" s="8" t="s">
         <v>540</v>
       </c>
@@ -13669,8 +14017,8 @@
       <c r="B426" s="7">
         <v>46</v>
       </c>
-      <c r="C426" s="130"/>
-      <c r="D426" s="131"/>
+      <c r="C426" s="135"/>
+      <c r="D426" s="136"/>
       <c r="E426" s="8" t="s">
         <v>541</v>
       </c>
@@ -13691,8 +14039,8 @@
       <c r="B427" s="7">
         <v>47</v>
       </c>
-      <c r="C427" s="130"/>
-      <c r="D427" s="129" t="s">
+      <c r="C427" s="135"/>
+      <c r="D427" s="143" t="s">
         <v>542</v>
       </c>
       <c r="E427" s="8" t="s">
@@ -13713,8 +14061,8 @@
       <c r="B428" s="7">
         <v>48</v>
       </c>
-      <c r="C428" s="130"/>
-      <c r="D428" s="130"/>
+      <c r="C428" s="135"/>
+      <c r="D428" s="135"/>
       <c r="E428" s="8" t="s">
         <v>544</v>
       </c>
@@ -13735,8 +14083,8 @@
       <c r="B429" s="7">
         <v>49</v>
       </c>
-      <c r="C429" s="130"/>
-      <c r="D429" s="130"/>
+      <c r="C429" s="135"/>
+      <c r="D429" s="135"/>
       <c r="E429" s="8" t="s">
         <v>545</v>
       </c>
@@ -13757,8 +14105,8 @@
       <c r="B430" s="7">
         <v>50</v>
       </c>
-      <c r="C430" s="130"/>
-      <c r="D430" s="131"/>
+      <c r="C430" s="135"/>
+      <c r="D430" s="136"/>
       <c r="E430" s="8" t="s">
         <v>546</v>
       </c>
@@ -13779,8 +14127,8 @@
       <c r="B431" s="7">
         <v>51</v>
       </c>
-      <c r="C431" s="130"/>
-      <c r="D431" s="129" t="s">
+      <c r="C431" s="135"/>
+      <c r="D431" s="143" t="s">
         <v>547</v>
       </c>
       <c r="E431" s="8" t="s">
@@ -13803,8 +14151,8 @@
       <c r="B432" s="7">
         <v>52</v>
       </c>
-      <c r="C432" s="130"/>
-      <c r="D432" s="130"/>
+      <c r="C432" s="135"/>
+      <c r="D432" s="135"/>
       <c r="E432" s="8" t="s">
         <v>549</v>
       </c>
@@ -13825,8 +14173,8 @@
       <c r="B433" s="7">
         <v>53</v>
       </c>
-      <c r="C433" s="130"/>
-      <c r="D433" s="130"/>
+      <c r="C433" s="135"/>
+      <c r="D433" s="135"/>
       <c r="E433" s="8" t="s">
         <v>550</v>
       </c>
@@ -13847,8 +14195,8 @@
       <c r="B434" s="7">
         <v>54</v>
       </c>
-      <c r="C434" s="130"/>
-      <c r="D434" s="130"/>
+      <c r="C434" s="135"/>
+      <c r="D434" s="135"/>
       <c r="E434" s="8" t="s">
         <v>551</v>
       </c>
@@ -13869,8 +14217,8 @@
       <c r="B435" s="7">
         <v>55</v>
       </c>
-      <c r="C435" s="131"/>
-      <c r="D435" s="131"/>
+      <c r="C435" s="136"/>
+      <c r="D435" s="136"/>
       <c r="E435" s="8" t="s">
         <v>552</v>
       </c>
@@ -13885,18 +14233,18 @@
       <c r="J435" s="11"/>
     </row>
     <row r="436" spans="1:10" ht="13.8">
-      <c r="A436" s="149" t="s">
+      <c r="A436" s="145" t="s">
         <v>553</v>
       </c>
-      <c r="B436" s="136"/>
-      <c r="C436" s="136"/>
-      <c r="D436" s="136"/>
-      <c r="E436" s="136"/>
-      <c r="F436" s="136"/>
-      <c r="G436" s="136"/>
-      <c r="H436" s="136"/>
-      <c r="I436" s="136"/>
-      <c r="J436" s="137"/>
+      <c r="B436" s="146"/>
+      <c r="C436" s="146"/>
+      <c r="D436" s="146"/>
+      <c r="E436" s="146"/>
+      <c r="F436" s="146"/>
+      <c r="G436" s="146"/>
+      <c r="H436" s="146"/>
+      <c r="I436" s="146"/>
+      <c r="J436" s="147"/>
     </row>
     <row r="437" spans="1:10" ht="13.8">
       <c r="A437" s="6">
@@ -13908,7 +14256,7 @@
       <c r="C437" s="139" t="s">
         <v>554</v>
       </c>
-      <c r="D437" s="129" t="s">
+      <c r="D437" s="143" t="s">
         <v>555</v>
       </c>
       <c r="E437" s="29" t="s">
@@ -13931,8 +14279,8 @@
       <c r="B438" s="7">
         <v>2</v>
       </c>
-      <c r="C438" s="130"/>
-      <c r="D438" s="130"/>
+      <c r="C438" s="135"/>
+      <c r="D438" s="135"/>
       <c r="E438" s="8" t="s">
         <v>557</v>
       </c>
@@ -13951,8 +14299,8 @@
       <c r="B439" s="7">
         <v>3</v>
       </c>
-      <c r="C439" s="130"/>
-      <c r="D439" s="130"/>
+      <c r="C439" s="135"/>
+      <c r="D439" s="135"/>
       <c r="E439" s="8" t="s">
         <v>558</v>
       </c>
@@ -13973,8 +14321,8 @@
       <c r="B440" s="7">
         <v>4</v>
       </c>
-      <c r="C440" s="130"/>
-      <c r="D440" s="130"/>
+      <c r="C440" s="135"/>
+      <c r="D440" s="135"/>
       <c r="E440" s="29" t="s">
         <v>559</v>
       </c>
@@ -13995,8 +14343,8 @@
       <c r="B441" s="7">
         <v>5</v>
       </c>
-      <c r="C441" s="130"/>
-      <c r="D441" s="131"/>
+      <c r="C441" s="135"/>
+      <c r="D441" s="136"/>
       <c r="E441" s="8" t="s">
         <v>560</v>
       </c>
@@ -14017,8 +14365,8 @@
       <c r="B442" s="7">
         <v>6</v>
       </c>
-      <c r="C442" s="130"/>
-      <c r="D442" s="129" t="s">
+      <c r="C442" s="135"/>
+      <c r="D442" s="143" t="s">
         <v>561</v>
       </c>
       <c r="E442" s="29" t="s">
@@ -14041,8 +14389,8 @@
       <c r="B443" s="7">
         <v>7</v>
       </c>
-      <c r="C443" s="130"/>
-      <c r="D443" s="130"/>
+      <c r="C443" s="135"/>
+      <c r="D443" s="135"/>
       <c r="E443" s="8" t="s">
         <v>563</v>
       </c>
@@ -14063,8 +14411,8 @@
       <c r="B444" s="7">
         <v>8</v>
       </c>
-      <c r="C444" s="130"/>
-      <c r="D444" s="130"/>
+      <c r="C444" s="135"/>
+      <c r="D444" s="135"/>
       <c r="E444" s="29" t="s">
         <v>564</v>
       </c>
@@ -14085,8 +14433,8 @@
       <c r="B445" s="7">
         <v>9</v>
       </c>
-      <c r="C445" s="130"/>
-      <c r="D445" s="131"/>
+      <c r="C445" s="135"/>
+      <c r="D445" s="136"/>
       <c r="E445" s="8" t="s">
         <v>565</v>
       </c>
@@ -14107,8 +14455,8 @@
       <c r="B446" s="7">
         <v>10</v>
       </c>
-      <c r="C446" s="130"/>
-      <c r="D446" s="129" t="s">
+      <c r="C446" s="135"/>
+      <c r="D446" s="143" t="s">
         <v>566</v>
       </c>
       <c r="E446" s="8" t="s">
@@ -14131,8 +14479,8 @@
       <c r="B447" s="7">
         <v>11</v>
       </c>
-      <c r="C447" s="130"/>
-      <c r="D447" s="130"/>
+      <c r="C447" s="135"/>
+      <c r="D447" s="135"/>
       <c r="E447" s="8" t="s">
         <v>568</v>
       </c>
@@ -14153,8 +14501,8 @@
       <c r="B448" s="7">
         <v>12</v>
       </c>
-      <c r="C448" s="130"/>
-      <c r="D448" s="131"/>
+      <c r="C448" s="135"/>
+      <c r="D448" s="136"/>
       <c r="E448" s="8" t="s">
         <v>569</v>
       </c>
@@ -14175,8 +14523,8 @@
       <c r="B449" s="7">
         <v>13</v>
       </c>
-      <c r="C449" s="130"/>
-      <c r="D449" s="129" t="s">
+      <c r="C449" s="135"/>
+      <c r="D449" s="143" t="s">
         <v>570</v>
       </c>
       <c r="E449" s="8" t="s">
@@ -14199,8 +14547,8 @@
       <c r="B450" s="7">
         <v>14</v>
       </c>
-      <c r="C450" s="130"/>
-      <c r="D450" s="130"/>
+      <c r="C450" s="135"/>
+      <c r="D450" s="135"/>
       <c r="E450" s="29" t="s">
         <v>572</v>
       </c>
@@ -14221,8 +14569,8 @@
       <c r="B451" s="7">
         <v>15</v>
       </c>
-      <c r="C451" s="130"/>
-      <c r="D451" s="130"/>
+      <c r="C451" s="135"/>
+      <c r="D451" s="135"/>
       <c r="E451" s="8" t="s">
         <v>573</v>
       </c>
@@ -14243,8 +14591,8 @@
       <c r="B452" s="7">
         <v>16</v>
       </c>
-      <c r="C452" s="130"/>
-      <c r="D452" s="131"/>
+      <c r="C452" s="135"/>
+      <c r="D452" s="136"/>
       <c r="E452" s="8" t="s">
         <v>574</v>
       </c>
@@ -14265,8 +14613,8 @@
       <c r="B453" s="7">
         <v>17</v>
       </c>
-      <c r="C453" s="130"/>
-      <c r="D453" s="129" t="s">
+      <c r="C453" s="135"/>
+      <c r="D453" s="143" t="s">
         <v>575</v>
       </c>
       <c r="E453" s="8" t="s">
@@ -14289,8 +14637,8 @@
       <c r="B454" s="7">
         <v>18</v>
       </c>
-      <c r="C454" s="130"/>
-      <c r="D454" s="130"/>
+      <c r="C454" s="135"/>
+      <c r="D454" s="135"/>
       <c r="E454" s="8" t="s">
         <v>577</v>
       </c>
@@ -14311,8 +14659,8 @@
       <c r="B455" s="7">
         <v>19</v>
       </c>
-      <c r="C455" s="130"/>
-      <c r="D455" s="130"/>
+      <c r="C455" s="135"/>
+      <c r="D455" s="135"/>
       <c r="E455" s="8" t="s">
         <v>578</v>
       </c>
@@ -14333,8 +14681,8 @@
       <c r="B456" s="7">
         <v>20</v>
       </c>
-      <c r="C456" s="130"/>
-      <c r="D456" s="130"/>
+      <c r="C456" s="135"/>
+      <c r="D456" s="135"/>
       <c r="E456" s="39" t="s">
         <v>579</v>
       </c>
@@ -14355,8 +14703,8 @@
       <c r="B457" s="7">
         <v>21</v>
       </c>
-      <c r="C457" s="130"/>
-      <c r="D457" s="130"/>
+      <c r="C457" s="135"/>
+      <c r="D457" s="135"/>
       <c r="E457" s="8" t="s">
         <v>580</v>
       </c>
@@ -14377,8 +14725,8 @@
       <c r="B458" s="24">
         <v>22</v>
       </c>
-      <c r="C458" s="131"/>
-      <c r="D458" s="131"/>
+      <c r="C458" s="136"/>
+      <c r="D458" s="136"/>
       <c r="E458" s="17" t="s">
         <v>581</v>
       </c>
@@ -14400,10 +14748,10 @@
       <c r="B459" s="7">
         <v>1</v>
       </c>
-      <c r="C459" s="140" t="s">
+      <c r="C459" s="134" t="s">
         <v>582</v>
       </c>
-      <c r="D459" s="129" t="s">
+      <c r="D459" s="143" t="s">
         <v>583</v>
       </c>
       <c r="E459" s="8" t="s">
@@ -14426,8 +14774,8 @@
       <c r="B460" s="7">
         <v>2</v>
       </c>
-      <c r="C460" s="130"/>
-      <c r="D460" s="130"/>
+      <c r="C460" s="135"/>
+      <c r="D460" s="135"/>
       <c r="E460" s="8" t="s">
         <v>584</v>
       </c>
@@ -14448,8 +14796,8 @@
       <c r="B461" s="7">
         <v>3</v>
       </c>
-      <c r="C461" s="130"/>
-      <c r="D461" s="130"/>
+      <c r="C461" s="135"/>
+      <c r="D461" s="135"/>
       <c r="E461" s="8" t="s">
         <v>585</v>
       </c>
@@ -14470,8 +14818,8 @@
       <c r="B462" s="7">
         <v>4</v>
       </c>
-      <c r="C462" s="130"/>
-      <c r="D462" s="130"/>
+      <c r="C462" s="135"/>
+      <c r="D462" s="135"/>
       <c r="E462" s="8" t="s">
         <v>586</v>
       </c>
@@ -14492,8 +14840,8 @@
       <c r="B463" s="7">
         <v>5</v>
       </c>
-      <c r="C463" s="130"/>
-      <c r="D463" s="130"/>
+      <c r="C463" s="135"/>
+      <c r="D463" s="135"/>
       <c r="E463" s="8" t="s">
         <v>587</v>
       </c>
@@ -14514,8 +14862,8 @@
       <c r="B464" s="7">
         <v>6</v>
       </c>
-      <c r="C464" s="130"/>
-      <c r="D464" s="130"/>
+      <c r="C464" s="135"/>
+      <c r="D464" s="135"/>
       <c r="E464" s="8" t="s">
         <v>588</v>
       </c>
@@ -14536,8 +14884,8 @@
       <c r="B465" s="7">
         <v>7</v>
       </c>
-      <c r="C465" s="130"/>
-      <c r="D465" s="130"/>
+      <c r="C465" s="135"/>
+      <c r="D465" s="135"/>
       <c r="E465" s="8" t="s">
         <v>589</v>
       </c>
@@ -14558,8 +14906,8 @@
       <c r="B466" s="7">
         <v>8</v>
       </c>
-      <c r="C466" s="130"/>
-      <c r="D466" s="131"/>
+      <c r="C466" s="135"/>
+      <c r="D466" s="136"/>
       <c r="E466" s="8" t="s">
         <v>590</v>
       </c>
@@ -14580,8 +14928,8 @@
       <c r="B467" s="7">
         <v>9</v>
       </c>
-      <c r="C467" s="130"/>
-      <c r="D467" s="129" t="s">
+      <c r="C467" s="135"/>
+      <c r="D467" s="143" t="s">
         <v>591</v>
       </c>
       <c r="E467" s="8" t="s">
@@ -14604,8 +14952,8 @@
       <c r="B468" s="7">
         <v>10</v>
       </c>
-      <c r="C468" s="130"/>
-      <c r="D468" s="130"/>
+      <c r="C468" s="135"/>
+      <c r="D468" s="135"/>
       <c r="E468" s="8" t="s">
         <v>593</v>
       </c>
@@ -14626,8 +14974,8 @@
       <c r="B469" s="7">
         <v>11</v>
       </c>
-      <c r="C469" s="130"/>
-      <c r="D469" s="130"/>
+      <c r="C469" s="135"/>
+      <c r="D469" s="135"/>
       <c r="E469" s="8" t="s">
         <v>594</v>
       </c>
@@ -14648,8 +14996,8 @@
       <c r="B470" s="7">
         <v>12</v>
       </c>
-      <c r="C470" s="130"/>
-      <c r="D470" s="130"/>
+      <c r="C470" s="135"/>
+      <c r="D470" s="135"/>
       <c r="E470" s="8" t="s">
         <v>595</v>
       </c>
@@ -14670,8 +15018,8 @@
       <c r="B471" s="7">
         <v>13</v>
       </c>
-      <c r="C471" s="130"/>
-      <c r="D471" s="130"/>
+      <c r="C471" s="135"/>
+      <c r="D471" s="135"/>
       <c r="E471" s="8" t="s">
         <v>596</v>
       </c>
@@ -14692,8 +15040,8 @@
       <c r="B472" s="7">
         <v>14</v>
       </c>
-      <c r="C472" s="130"/>
-      <c r="D472" s="130"/>
+      <c r="C472" s="135"/>
+      <c r="D472" s="135"/>
       <c r="E472" s="8" t="s">
         <v>597</v>
       </c>
@@ -14714,8 +15062,8 @@
       <c r="B473" s="7">
         <v>15</v>
       </c>
-      <c r="C473" s="130"/>
-      <c r="D473" s="131"/>
+      <c r="C473" s="135"/>
+      <c r="D473" s="136"/>
       <c r="E473" s="8" t="s">
         <v>598</v>
       </c>
@@ -14736,8 +15084,8 @@
       <c r="B474" s="7">
         <v>16</v>
       </c>
-      <c r="C474" s="130"/>
-      <c r="D474" s="129" t="s">
+      <c r="C474" s="135"/>
+      <c r="D474" s="143" t="s">
         <v>599</v>
       </c>
       <c r="E474" s="8" t="s">
@@ -14760,8 +15108,8 @@
       <c r="B475" s="7">
         <v>17</v>
       </c>
-      <c r="C475" s="130"/>
-      <c r="D475" s="130"/>
+      <c r="C475" s="135"/>
+      <c r="D475" s="135"/>
       <c r="E475" s="8" t="s">
         <v>601</v>
       </c>
@@ -14782,8 +15130,8 @@
       <c r="B476" s="7">
         <v>18</v>
       </c>
-      <c r="C476" s="130"/>
-      <c r="D476" s="130"/>
+      <c r="C476" s="135"/>
+      <c r="D476" s="135"/>
       <c r="E476" s="8" t="s">
         <v>602</v>
       </c>
@@ -14804,8 +15152,8 @@
       <c r="B477" s="7">
         <v>19</v>
       </c>
-      <c r="C477" s="130"/>
-      <c r="D477" s="130"/>
+      <c r="C477" s="135"/>
+      <c r="D477" s="135"/>
       <c r="E477" s="8" t="s">
         <v>603</v>
       </c>
@@ -14826,8 +15174,8 @@
       <c r="B478" s="7">
         <v>20</v>
       </c>
-      <c r="C478" s="130"/>
-      <c r="D478" s="130"/>
+      <c r="C478" s="135"/>
+      <c r="D478" s="135"/>
       <c r="E478" s="8" t="s">
         <v>604</v>
       </c>
@@ -14848,8 +15196,8 @@
       <c r="B479" s="7">
         <v>21</v>
       </c>
-      <c r="C479" s="130"/>
-      <c r="D479" s="130"/>
+      <c r="C479" s="135"/>
+      <c r="D479" s="135"/>
       <c r="E479" s="8" t="s">
         <v>605</v>
       </c>
@@ -14870,8 +15218,8 @@
       <c r="B480" s="7">
         <v>22</v>
       </c>
-      <c r="C480" s="130"/>
-      <c r="D480" s="130"/>
+      <c r="C480" s="135"/>
+      <c r="D480" s="135"/>
       <c r="E480" s="8" t="s">
         <v>606</v>
       </c>
@@ -14892,8 +15240,8 @@
       <c r="B481" s="7">
         <v>23</v>
       </c>
-      <c r="C481" s="130"/>
-      <c r="D481" s="131"/>
+      <c r="C481" s="135"/>
+      <c r="D481" s="136"/>
       <c r="E481" s="8" t="s">
         <v>607</v>
       </c>
@@ -14914,8 +15262,8 @@
       <c r="B482" s="7">
         <v>24</v>
       </c>
-      <c r="C482" s="130"/>
-      <c r="D482" s="129" t="s">
+      <c r="C482" s="135"/>
+      <c r="D482" s="143" t="s">
         <v>608</v>
       </c>
       <c r="E482" s="8" t="s">
@@ -14938,8 +15286,8 @@
       <c r="B483" s="7">
         <v>25</v>
       </c>
-      <c r="C483" s="130"/>
-      <c r="D483" s="130"/>
+      <c r="C483" s="135"/>
+      <c r="D483" s="135"/>
       <c r="E483" s="8" t="s">
         <v>610</v>
       </c>
@@ -14960,8 +15308,8 @@
       <c r="B484" s="7">
         <v>26</v>
       </c>
-      <c r="C484" s="130"/>
-      <c r="D484" s="130"/>
+      <c r="C484" s="135"/>
+      <c r="D484" s="135"/>
       <c r="E484" s="8" t="s">
         <v>611</v>
       </c>
@@ -14982,8 +15330,8 @@
       <c r="B485" s="7">
         <v>27</v>
       </c>
-      <c r="C485" s="130"/>
-      <c r="D485" s="131"/>
+      <c r="C485" s="135"/>
+      <c r="D485" s="136"/>
       <c r="E485" s="8" t="s">
         <v>612</v>
       </c>
@@ -15004,8 +15352,8 @@
       <c r="B486" s="7">
         <v>28</v>
       </c>
-      <c r="C486" s="130"/>
-      <c r="D486" s="129" t="s">
+      <c r="C486" s="135"/>
+      <c r="D486" s="143" t="s">
         <v>613</v>
       </c>
       <c r="E486" s="8" t="s">
@@ -15028,8 +15376,8 @@
       <c r="B487" s="7">
         <v>29</v>
       </c>
-      <c r="C487" s="130"/>
-      <c r="D487" s="130"/>
+      <c r="C487" s="135"/>
+      <c r="D487" s="135"/>
       <c r="E487" s="8" t="s">
         <v>615</v>
       </c>
@@ -15050,8 +15398,8 @@
       <c r="B488" s="7">
         <v>30</v>
       </c>
-      <c r="C488" s="130"/>
-      <c r="D488" s="130"/>
+      <c r="C488" s="135"/>
+      <c r="D488" s="135"/>
       <c r="E488" s="8" t="s">
         <v>616</v>
       </c>
@@ -15072,8 +15420,8 @@
       <c r="B489" s="7">
         <v>31</v>
       </c>
-      <c r="C489" s="130"/>
-      <c r="D489" s="130"/>
+      <c r="C489" s="135"/>
+      <c r="D489" s="135"/>
       <c r="E489" s="8" t="s">
         <v>617</v>
       </c>
@@ -15094,8 +15442,8 @@
       <c r="B490" s="7">
         <v>32</v>
       </c>
-      <c r="C490" s="130"/>
-      <c r="D490" s="130"/>
+      <c r="C490" s="135"/>
+      <c r="D490" s="135"/>
       <c r="E490" s="8" t="s">
         <v>618</v>
       </c>
@@ -15116,8 +15464,8 @@
       <c r="B491" s="7">
         <v>33</v>
       </c>
-      <c r="C491" s="130"/>
-      <c r="D491" s="130"/>
+      <c r="C491" s="135"/>
+      <c r="D491" s="135"/>
       <c r="E491" s="8" t="s">
         <v>619</v>
       </c>
@@ -15138,8 +15486,8 @@
       <c r="B492" s="7">
         <v>34</v>
       </c>
-      <c r="C492" s="130"/>
-      <c r="D492" s="130"/>
+      <c r="C492" s="135"/>
+      <c r="D492" s="135"/>
       <c r="E492" s="8" t="s">
         <v>620</v>
       </c>
@@ -15160,8 +15508,8 @@
       <c r="B493" s="7">
         <v>35</v>
       </c>
-      <c r="C493" s="130"/>
-      <c r="D493" s="130"/>
+      <c r="C493" s="135"/>
+      <c r="D493" s="135"/>
       <c r="E493" s="8" t="s">
         <v>621</v>
       </c>
@@ -15182,8 +15530,8 @@
       <c r="B494" s="7">
         <v>36</v>
       </c>
-      <c r="C494" s="130"/>
-      <c r="D494" s="130"/>
+      <c r="C494" s="135"/>
+      <c r="D494" s="135"/>
       <c r="E494" s="8" t="s">
         <v>622</v>
       </c>
@@ -15204,8 +15552,8 @@
       <c r="B495" s="7">
         <v>37</v>
       </c>
-      <c r="C495" s="130"/>
-      <c r="D495" s="130"/>
+      <c r="C495" s="135"/>
+      <c r="D495" s="135"/>
       <c r="E495" s="8" t="s">
         <v>623</v>
       </c>
@@ -15226,8 +15574,8 @@
       <c r="B496" s="7">
         <v>38</v>
       </c>
-      <c r="C496" s="130"/>
-      <c r="D496" s="131"/>
+      <c r="C496" s="135"/>
+      <c r="D496" s="136"/>
       <c r="E496" s="8" t="s">
         <v>624</v>
       </c>
@@ -15248,8 +15596,8 @@
       <c r="B497" s="7">
         <v>39</v>
       </c>
-      <c r="C497" s="130"/>
-      <c r="D497" s="129" t="s">
+      <c r="C497" s="135"/>
+      <c r="D497" s="143" t="s">
         <v>625</v>
       </c>
       <c r="E497" s="8" t="s">
@@ -15272,8 +15620,8 @@
       <c r="B498" s="7">
         <v>40</v>
       </c>
-      <c r="C498" s="130"/>
-      <c r="D498" s="130"/>
+      <c r="C498" s="135"/>
+      <c r="D498" s="135"/>
       <c r="E498" s="8" t="s">
         <v>626</v>
       </c>
@@ -15294,8 +15642,8 @@
       <c r="B499" s="7">
         <v>41</v>
       </c>
-      <c r="C499" s="130"/>
-      <c r="D499" s="130"/>
+      <c r="C499" s="135"/>
+      <c r="D499" s="135"/>
       <c r="E499" s="8" t="s">
         <v>627</v>
       </c>
@@ -15316,8 +15664,8 @@
       <c r="B500" s="7">
         <v>42</v>
       </c>
-      <c r="C500" s="130"/>
-      <c r="D500" s="130"/>
+      <c r="C500" s="135"/>
+      <c r="D500" s="135"/>
       <c r="E500" s="8" t="s">
         <v>628</v>
       </c>
@@ -15338,8 +15686,8 @@
       <c r="B501" s="7">
         <v>43</v>
       </c>
-      <c r="C501" s="130"/>
-      <c r="D501" s="130"/>
+      <c r="C501" s="135"/>
+      <c r="D501" s="135"/>
       <c r="E501" s="8" t="s">
         <v>629</v>
       </c>
@@ -15360,8 +15708,8 @@
       <c r="B502" s="7">
         <v>44</v>
       </c>
-      <c r="C502" s="130"/>
-      <c r="D502" s="131"/>
+      <c r="C502" s="135"/>
+      <c r="D502" s="136"/>
       <c r="E502" s="8" t="s">
         <v>630</v>
       </c>
@@ -15382,8 +15730,8 @@
       <c r="B503" s="7">
         <v>45</v>
       </c>
-      <c r="C503" s="130"/>
-      <c r="D503" s="129" t="s">
+      <c r="C503" s="135"/>
+      <c r="D503" s="143" t="s">
         <v>631</v>
       </c>
       <c r="E503" s="8" t="s">
@@ -15406,8 +15754,8 @@
       <c r="B504" s="7">
         <v>46</v>
       </c>
-      <c r="C504" s="130"/>
-      <c r="D504" s="130"/>
+      <c r="C504" s="135"/>
+      <c r="D504" s="135"/>
       <c r="E504" s="8" t="s">
         <v>633</v>
       </c>
@@ -15428,8 +15776,8 @@
       <c r="B505" s="7">
         <v>47</v>
       </c>
-      <c r="C505" s="130"/>
-      <c r="D505" s="130"/>
+      <c r="C505" s="135"/>
+      <c r="D505" s="135"/>
       <c r="E505" s="8" t="s">
         <v>634</v>
       </c>
@@ -15450,8 +15798,8 @@
       <c r="B506" s="7">
         <v>48</v>
       </c>
-      <c r="C506" s="130"/>
-      <c r="D506" s="130"/>
+      <c r="C506" s="135"/>
+      <c r="D506" s="135"/>
       <c r="E506" s="8" t="s">
         <v>635</v>
       </c>
@@ -15472,8 +15820,8 @@
       <c r="B507" s="7">
         <v>49</v>
       </c>
-      <c r="C507" s="130"/>
-      <c r="D507" s="130"/>
+      <c r="C507" s="135"/>
+      <c r="D507" s="135"/>
       <c r="E507" s="8" t="s">
         <v>636</v>
       </c>
@@ -15494,8 +15842,8 @@
       <c r="B508" s="7">
         <v>50</v>
       </c>
-      <c r="C508" s="130"/>
-      <c r="D508" s="130"/>
+      <c r="C508" s="135"/>
+      <c r="D508" s="135"/>
       <c r="E508" s="8" t="s">
         <v>637</v>
       </c>
@@ -15516,8 +15864,8 @@
       <c r="B509" s="7">
         <v>51</v>
       </c>
-      <c r="C509" s="130"/>
-      <c r="D509" s="131"/>
+      <c r="C509" s="135"/>
+      <c r="D509" s="136"/>
       <c r="E509" s="8" t="s">
         <v>638</v>
       </c>
@@ -15538,8 +15886,8 @@
       <c r="B510" s="7">
         <v>52</v>
       </c>
-      <c r="C510" s="130"/>
-      <c r="D510" s="129" t="s">
+      <c r="C510" s="135"/>
+      <c r="D510" s="143" t="s">
         <v>639</v>
       </c>
       <c r="E510" s="8" t="s">
@@ -15562,8 +15910,8 @@
       <c r="B511" s="7">
         <v>53</v>
       </c>
-      <c r="C511" s="130"/>
-      <c r="D511" s="130"/>
+      <c r="C511" s="135"/>
+      <c r="D511" s="135"/>
       <c r="E511" s="8" t="s">
         <v>641</v>
       </c>
@@ -15584,8 +15932,8 @@
       <c r="B512" s="7">
         <v>54</v>
       </c>
-      <c r="C512" s="130"/>
-      <c r="D512" s="130"/>
+      <c r="C512" s="135"/>
+      <c r="D512" s="135"/>
       <c r="E512" s="8" t="s">
         <v>642</v>
       </c>
@@ -15606,8 +15954,8 @@
       <c r="B513" s="24">
         <v>55</v>
       </c>
-      <c r="C513" s="131"/>
-      <c r="D513" s="131"/>
+      <c r="C513" s="136"/>
+      <c r="D513" s="136"/>
       <c r="E513" s="17" t="s">
         <v>643</v>
       </c>
@@ -22541,6 +22889,107 @@
     </row>
   </sheetData>
   <mergeCells count="125">
+    <mergeCell ref="D26:D32"/>
+    <mergeCell ref="D33:D36"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="C4:C32"/>
+    <mergeCell ref="D4:D9"/>
+    <mergeCell ref="D10:D18"/>
+    <mergeCell ref="D19:D25"/>
+    <mergeCell ref="C33:C44"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="D40:D44"/>
+    <mergeCell ref="C107:C116"/>
+    <mergeCell ref="C117:C125"/>
+    <mergeCell ref="C127:C132"/>
+    <mergeCell ref="C134:C176"/>
+    <mergeCell ref="C177:C204"/>
+    <mergeCell ref="C205:C214"/>
+    <mergeCell ref="A106:J106"/>
+    <mergeCell ref="D107:D111"/>
+    <mergeCell ref="D112:D115"/>
+    <mergeCell ref="D117:D120"/>
+    <mergeCell ref="D121:D122"/>
+    <mergeCell ref="D123:D125"/>
+    <mergeCell ref="A126:J126"/>
+    <mergeCell ref="D127:D130"/>
+    <mergeCell ref="D131:D132"/>
+    <mergeCell ref="A133:J133"/>
+    <mergeCell ref="D210:D211"/>
+    <mergeCell ref="D212:D214"/>
+    <mergeCell ref="C45:C50"/>
+    <mergeCell ref="D45:D50"/>
+    <mergeCell ref="D51:D57"/>
+    <mergeCell ref="D58:D63"/>
+    <mergeCell ref="D64:D67"/>
+    <mergeCell ref="D69:D78"/>
+    <mergeCell ref="D79:D84"/>
+    <mergeCell ref="D85:D90"/>
+    <mergeCell ref="D91:D105"/>
+    <mergeCell ref="A68:J68"/>
+    <mergeCell ref="C51:C67"/>
+    <mergeCell ref="C69:C105"/>
+    <mergeCell ref="A215:J215"/>
+    <mergeCell ref="A273:J273"/>
+    <mergeCell ref="A358:J358"/>
+    <mergeCell ref="D134:D136"/>
+    <mergeCell ref="D137:D143"/>
+    <mergeCell ref="D144:D150"/>
+    <mergeCell ref="D151:D156"/>
+    <mergeCell ref="D157:D159"/>
+    <mergeCell ref="D160:D165"/>
+    <mergeCell ref="D166:D172"/>
+    <mergeCell ref="D173:D176"/>
+    <mergeCell ref="D177:D178"/>
+    <mergeCell ref="D179:D184"/>
+    <mergeCell ref="D185:D186"/>
+    <mergeCell ref="D187:D190"/>
+    <mergeCell ref="D191:D198"/>
+    <mergeCell ref="D199:D202"/>
+    <mergeCell ref="D203:D204"/>
+    <mergeCell ref="D205:D209"/>
+    <mergeCell ref="D216:D225"/>
+    <mergeCell ref="D226:D233"/>
+    <mergeCell ref="D234:D240"/>
+    <mergeCell ref="D241:D243"/>
+    <mergeCell ref="D244:D249"/>
+    <mergeCell ref="D442:D445"/>
+    <mergeCell ref="D446:D448"/>
+    <mergeCell ref="D400:D404"/>
+    <mergeCell ref="D405:D416"/>
+    <mergeCell ref="A436:J436"/>
+    <mergeCell ref="D359:D363"/>
+    <mergeCell ref="D364:D371"/>
+    <mergeCell ref="D372:D375"/>
+    <mergeCell ref="D376:D380"/>
+    <mergeCell ref="D381:D386"/>
+    <mergeCell ref="D387:D396"/>
+    <mergeCell ref="D397:D399"/>
+    <mergeCell ref="D301:D303"/>
+    <mergeCell ref="D304:D307"/>
+    <mergeCell ref="D308:D314"/>
+    <mergeCell ref="D315:D317"/>
+    <mergeCell ref="C343:C357"/>
+    <mergeCell ref="C359:C380"/>
+    <mergeCell ref="C381:C435"/>
+    <mergeCell ref="C437:C458"/>
+    <mergeCell ref="D250:D257"/>
+    <mergeCell ref="D258:D259"/>
+    <mergeCell ref="D260:D265"/>
+    <mergeCell ref="D266:D270"/>
+    <mergeCell ref="D271:D272"/>
+    <mergeCell ref="D274:D281"/>
+    <mergeCell ref="D282:D288"/>
+    <mergeCell ref="D289:D292"/>
+    <mergeCell ref="D293:D295"/>
+    <mergeCell ref="D449:D452"/>
+    <mergeCell ref="D453:D458"/>
+    <mergeCell ref="D417:D419"/>
+    <mergeCell ref="D420:D426"/>
+    <mergeCell ref="D427:D430"/>
+    <mergeCell ref="D431:D435"/>
+    <mergeCell ref="D437:D441"/>
     <mergeCell ref="C459:C513"/>
     <mergeCell ref="C216:C249"/>
     <mergeCell ref="C250:C265"/>
@@ -22565,107 +23014,6 @@
     <mergeCell ref="D348:D353"/>
     <mergeCell ref="D354:D357"/>
     <mergeCell ref="D296:D300"/>
-    <mergeCell ref="D301:D303"/>
-    <mergeCell ref="D304:D307"/>
-    <mergeCell ref="D308:D314"/>
-    <mergeCell ref="D315:D317"/>
-    <mergeCell ref="C343:C357"/>
-    <mergeCell ref="C359:C380"/>
-    <mergeCell ref="C381:C435"/>
-    <mergeCell ref="C437:C458"/>
-    <mergeCell ref="D250:D257"/>
-    <mergeCell ref="D258:D259"/>
-    <mergeCell ref="D260:D265"/>
-    <mergeCell ref="D266:D270"/>
-    <mergeCell ref="D271:D272"/>
-    <mergeCell ref="D274:D281"/>
-    <mergeCell ref="D282:D288"/>
-    <mergeCell ref="D289:D292"/>
-    <mergeCell ref="D293:D295"/>
-    <mergeCell ref="D449:D452"/>
-    <mergeCell ref="D453:D458"/>
-    <mergeCell ref="D417:D419"/>
-    <mergeCell ref="D420:D426"/>
-    <mergeCell ref="D427:D430"/>
-    <mergeCell ref="D431:D435"/>
-    <mergeCell ref="D437:D441"/>
-    <mergeCell ref="D442:D445"/>
-    <mergeCell ref="D446:D448"/>
-    <mergeCell ref="D400:D404"/>
-    <mergeCell ref="D405:D416"/>
-    <mergeCell ref="A436:J436"/>
-    <mergeCell ref="D359:D363"/>
-    <mergeCell ref="D364:D371"/>
-    <mergeCell ref="D372:D375"/>
-    <mergeCell ref="D376:D380"/>
-    <mergeCell ref="D381:D386"/>
-    <mergeCell ref="D387:D396"/>
-    <mergeCell ref="D397:D399"/>
-    <mergeCell ref="A215:J215"/>
-    <mergeCell ref="A273:J273"/>
-    <mergeCell ref="A358:J358"/>
-    <mergeCell ref="D134:D136"/>
-    <mergeCell ref="D137:D143"/>
-    <mergeCell ref="D144:D150"/>
-    <mergeCell ref="D151:D156"/>
-    <mergeCell ref="D157:D159"/>
-    <mergeCell ref="D160:D165"/>
-    <mergeCell ref="D166:D172"/>
-    <mergeCell ref="D173:D176"/>
-    <mergeCell ref="D177:D178"/>
-    <mergeCell ref="D179:D184"/>
-    <mergeCell ref="D185:D186"/>
-    <mergeCell ref="D187:D190"/>
-    <mergeCell ref="D191:D198"/>
-    <mergeCell ref="D199:D202"/>
-    <mergeCell ref="D203:D204"/>
-    <mergeCell ref="D205:D209"/>
-    <mergeCell ref="D216:D225"/>
-    <mergeCell ref="D226:D233"/>
-    <mergeCell ref="D234:D240"/>
-    <mergeCell ref="D241:D243"/>
-    <mergeCell ref="D244:D249"/>
-    <mergeCell ref="C45:C50"/>
-    <mergeCell ref="D45:D50"/>
-    <mergeCell ref="D51:D57"/>
-    <mergeCell ref="D58:D63"/>
-    <mergeCell ref="D64:D67"/>
-    <mergeCell ref="D69:D78"/>
-    <mergeCell ref="D79:D84"/>
-    <mergeCell ref="D85:D90"/>
-    <mergeCell ref="D91:D105"/>
-    <mergeCell ref="A68:J68"/>
-    <mergeCell ref="C51:C67"/>
-    <mergeCell ref="C69:C105"/>
-    <mergeCell ref="C107:C116"/>
-    <mergeCell ref="C117:C125"/>
-    <mergeCell ref="C127:C132"/>
-    <mergeCell ref="C134:C176"/>
-    <mergeCell ref="C177:C204"/>
-    <mergeCell ref="C205:C214"/>
-    <mergeCell ref="A106:J106"/>
-    <mergeCell ref="D107:D111"/>
-    <mergeCell ref="D112:D115"/>
-    <mergeCell ref="D117:D120"/>
-    <mergeCell ref="D121:D122"/>
-    <mergeCell ref="D123:D125"/>
-    <mergeCell ref="A126:J126"/>
-    <mergeCell ref="D127:D130"/>
-    <mergeCell ref="D131:D132"/>
-    <mergeCell ref="A133:J133"/>
-    <mergeCell ref="D210:D211"/>
-    <mergeCell ref="D212:D214"/>
-    <mergeCell ref="D26:D32"/>
-    <mergeCell ref="D33:D36"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="C4:C32"/>
-    <mergeCell ref="D4:D9"/>
-    <mergeCell ref="D10:D18"/>
-    <mergeCell ref="D19:D25"/>
-    <mergeCell ref="C33:C44"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="D40:D44"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H67 H69:H105 H107:H125 H127:H132 H134:H214 H216:H272 H274:H357 H359:H435 H437:H513" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -23194,16 +23542,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="31.5" customHeight="1">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="157" t="s">
         <v>644</v>
       </c>
-      <c r="B1" s="153"/>
+      <c r="B1" s="158"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1">
-      <c r="A2" s="154" t="s">
+      <c r="A2" s="159" t="s">
         <v>645</v>
       </c>
-      <c r="B2" s="153"/>
+      <c r="B2" s="158"/>
     </row>
     <row r="3" spans="1:2" ht="18" customHeight="1">
       <c r="A3" s="46" t="s">
@@ -23250,10 +23598,10 @@
       <c r="B8" s="47"/>
     </row>
     <row r="9" spans="1:2" ht="18" customHeight="1">
-      <c r="A9" s="154" t="s">
+      <c r="A9" s="159" t="s">
         <v>656</v>
       </c>
-      <c r="B9" s="153"/>
+      <c r="B9" s="158"/>
     </row>
     <row r="10" spans="1:2" ht="18" customHeight="1">
       <c r="A10" s="52" t="s">
@@ -23332,10 +23680,10 @@
       <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:2" ht="18" customHeight="1">
-      <c r="A20" s="154" t="s">
+      <c r="A20" s="159" t="s">
         <v>675</v>
       </c>
-      <c r="B20" s="153"/>
+      <c r="B20" s="158"/>
     </row>
     <row r="21" spans="1:2" ht="18" customHeight="1">
       <c r="A21" s="52" t="s">
@@ -24332,15 +24680,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="160" t="s">
         <v>678</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="153"/>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="158"/>
     </row>
     <row r="2" spans="1:8" ht="13.2">
       <c r="A2" s="53" t="s">

--- a/DSA Master Sheet.xlsx
+++ b/DSA Master Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\OneDrive\Desktop\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C875588-5F5E-4C3C-99B6-C778E82AB4BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB0EA0F3-D3B6-4A65-AE82-ED864364DFF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="719">
   <si>
     <t>DSA Master Sheet</t>
   </si>
@@ -2564,16 +2564,161 @@
 [5, 6, 7, 1, 2, 3, 4]</t>
     </r>
   </si>
+  <si>
+    <t>1. Count the frequency of each character using a 26-element array — O(n) time.
+2. Find the character with maximum frequency** by scanning the array — **O(26) = O(1) time.
+Overall Time Complexity: O(n)
+Space Complexity: O(1)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>We use StringBuilder (or StringBuffer) instead of String concatenation because String is immutable, so repeated += creates a new String object each time, which can make the operation O(n²). StringBuilder allows efficient modification using append(), giving O(n) time.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>For this problem, prefer StringBuilder because it is faster than StringBuffer and thread-safety is not required.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Must Learn </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Charcter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Class Methods</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>26-Character Frequency Array Technique</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Approach: Use an integer array of size 26 to store the frequency of lowercase English letters (a-z).
+Mapping: index = character - 'a'
+Process: Traverse the string and increment/decrement arr[c - 'a'] as required.
+Complexity: Time: O(n) | Space: O(26) = O(1)
+Used for: Anagrams, character frequency, duplicates, maximum/minimum occurring character, etc.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Technique: Two-Array Last Seen Position Mapping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+s = "egg"
+t = "add"
+e → 1    a → 1
+g → 2    d → 2
+g → 3    d → 3
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Maintain two arrays to store the last seen position of each character in s and t.
+For every pair of characters, compare their previous positions. If they differ, return false; otherwise, update both positions to i + 1.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="3"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">        int[] map1 = new int[200];
+        int[] map2 = new int[200];
+        for(int i = 0 ; i&lt;s.length() ; i++){
+            if(map1[s.charAt(i)] != map2[t.charAt(i)])return false;
+            map1[s.charAt(i)] = i+1;
+            map2[t.charAt(i)] = i+1;
+        }
+        return true;</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="92">
+  <fonts count="96">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3129,6 +3274,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="55">
     <fill>
@@ -3453,7 +3619,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -3462,30 +3628,8 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -3636,441 +3780,544 @@
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="84" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="85" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="86" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="85" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="86" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="87" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="163">
+  <cellXfs count="194">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="22" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="29" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="31" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="32" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="37" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="38" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="38" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="39" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="40" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="41" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="42" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="42" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="43" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="44" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="44" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="45" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="46" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="46" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="47" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="48" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="49" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="49" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="50" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="51" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="51" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="52" borderId="6" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="86" fillId="53" borderId="6" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="87" fillId="54" borderId="6" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="23" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="23" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="24" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="26" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="27" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="27" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="28" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="29" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="30" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="30" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="31" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="32" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="27" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="27" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="34" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="34" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="35" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="36" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="36" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="37" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="38" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="38" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="39" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="40" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="41" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="42" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="42" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="43" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="44" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="44" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="45" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="46" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="46" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="47" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="48" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="49" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="49" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="50" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="51" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="51" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="84" fillId="52" borderId="8" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="85" fillId="53" borderId="8" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="86" fillId="54" borderId="8" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4310,18 +4557,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="30.75" customHeight="1">
-      <c r="A1" s="154" t="s">
+      <c r="A1" s="188" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="155"/>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
-      <c r="J1" s="156"/>
+      <c r="B1" s="189"/>
+      <c r="C1" s="189"/>
+      <c r="D1" s="189"/>
+      <c r="E1" s="189"/>
+      <c r="F1" s="189"/>
+      <c r="G1" s="189"/>
+      <c r="H1" s="189"/>
+      <c r="I1" s="189"/>
+      <c r="J1" s="190"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -4376,18 +4623,18 @@
       <c r="T2" s="5"/>
     </row>
     <row r="3" spans="1:20" ht="13.8">
-      <c r="A3" s="153" t="s">
+      <c r="A3" s="136" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="146"/>
-      <c r="C3" s="146"/>
-      <c r="D3" s="146"/>
-      <c r="E3" s="146"/>
-      <c r="F3" s="146"/>
-      <c r="G3" s="146"/>
-      <c r="H3" s="146"/>
-      <c r="I3" s="146"/>
-      <c r="J3" s="147"/>
+      <c r="B3" s="182"/>
+      <c r="C3" s="182"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="182"/>
+      <c r="F3" s="182"/>
+      <c r="G3" s="182"/>
+      <c r="H3" s="182"/>
+      <c r="I3" s="182"/>
+      <c r="J3" s="183"/>
     </row>
     <row r="4" spans="1:20" ht="13.8">
       <c r="A4" s="6">
@@ -4396,10 +4643,10 @@
       <c r="B4" s="7">
         <v>1</v>
       </c>
-      <c r="C4" s="138" t="s">
+      <c r="C4" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="143" t="s">
+      <c r="D4" s="135" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -4429,8 +4676,8 @@
       <c r="B5" s="7">
         <v>2</v>
       </c>
-      <c r="C5" s="135"/>
-      <c r="D5" s="135"/>
+      <c r="C5" s="164"/>
+      <c r="D5" s="156"/>
       <c r="E5" s="8" t="s">
         <v>16</v>
       </c>
@@ -4458,8 +4705,8 @@
       <c r="B6" s="7">
         <v>3</v>
       </c>
-      <c r="C6" s="135"/>
-      <c r="D6" s="135"/>
+      <c r="C6" s="164"/>
+      <c r="D6" s="156"/>
       <c r="E6" s="8" t="s">
         <v>19</v>
       </c>
@@ -4487,8 +4734,8 @@
       <c r="B7" s="7">
         <v>4</v>
       </c>
-      <c r="C7" s="135"/>
-      <c r="D7" s="135"/>
+      <c r="C7" s="164"/>
+      <c r="D7" s="156"/>
       <c r="E7" s="8" t="s">
         <v>23</v>
       </c>
@@ -4516,8 +4763,8 @@
       <c r="B8" s="7">
         <v>5</v>
       </c>
-      <c r="C8" s="135"/>
-      <c r="D8" s="135"/>
+      <c r="C8" s="164"/>
+      <c r="D8" s="156"/>
       <c r="E8" s="8" t="s">
         <v>26</v>
       </c>
@@ -4545,8 +4792,8 @@
       <c r="B9" s="7">
         <v>6</v>
       </c>
-      <c r="C9" s="135"/>
-      <c r="D9" s="136"/>
+      <c r="C9" s="164"/>
+      <c r="D9" s="157"/>
       <c r="E9" s="8" t="s">
         <v>29</v>
       </c>
@@ -4571,8 +4818,8 @@
       <c r="B10" s="7">
         <v>7</v>
       </c>
-      <c r="C10" s="135"/>
-      <c r="D10" s="143" t="s">
+      <c r="C10" s="164"/>
+      <c r="D10" s="135" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="8" t="s">
@@ -4599,8 +4846,8 @@
       <c r="B11" s="7">
         <v>8</v>
       </c>
-      <c r="C11" s="135"/>
-      <c r="D11" s="135"/>
+      <c r="C11" s="164"/>
+      <c r="D11" s="156"/>
       <c r="E11" s="13" t="s">
         <v>32</v>
       </c>
@@ -4625,8 +4872,8 @@
       <c r="B12" s="7">
         <v>9</v>
       </c>
-      <c r="C12" s="135"/>
-      <c r="D12" s="135"/>
+      <c r="C12" s="164"/>
+      <c r="D12" s="156"/>
       <c r="E12" s="8" t="s">
         <v>33</v>
       </c>
@@ -4651,8 +4898,8 @@
       <c r="B13" s="7">
         <v>10</v>
       </c>
-      <c r="C13" s="135"/>
-      <c r="D13" s="135"/>
+      <c r="C13" s="164"/>
+      <c r="D13" s="156"/>
       <c r="E13" s="8" t="s">
         <v>34</v>
       </c>
@@ -4679,8 +4926,8 @@
       <c r="B14" s="7">
         <v>11</v>
       </c>
-      <c r="C14" s="135"/>
-      <c r="D14" s="135"/>
+      <c r="C14" s="164"/>
+      <c r="D14" s="156"/>
       <c r="E14" s="8" t="s">
         <v>35</v>
       </c>
@@ -4705,8 +4952,8 @@
       <c r="B15" s="7">
         <v>12</v>
       </c>
-      <c r="C15" s="135"/>
-      <c r="D15" s="135"/>
+      <c r="C15" s="164"/>
+      <c r="D15" s="156"/>
       <c r="E15" s="8" t="s">
         <v>36</v>
       </c>
@@ -4733,8 +4980,8 @@
       <c r="B16" s="7">
         <v>13</v>
       </c>
-      <c r="C16" s="135"/>
-      <c r="D16" s="135"/>
+      <c r="C16" s="164"/>
+      <c r="D16" s="156"/>
       <c r="E16" s="8" t="s">
         <v>37</v>
       </c>
@@ -4759,8 +5006,8 @@
       <c r="B17" s="7">
         <v>14</v>
       </c>
-      <c r="C17" s="135"/>
-      <c r="D17" s="135"/>
+      <c r="C17" s="164"/>
+      <c r="D17" s="156"/>
       <c r="E17" s="8" t="s">
         <v>38</v>
       </c>
@@ -4787,8 +5034,8 @@
       <c r="B18" s="7">
         <v>15</v>
       </c>
-      <c r="C18" s="135"/>
-      <c r="D18" s="136"/>
+      <c r="C18" s="164"/>
+      <c r="D18" s="157"/>
       <c r="E18" s="13" t="s">
         <v>39</v>
       </c>
@@ -4815,8 +5062,8 @@
       <c r="B19" s="7">
         <v>16</v>
       </c>
-      <c r="C19" s="135"/>
-      <c r="D19" s="143" t="s">
+      <c r="C19" s="164"/>
+      <c r="D19" s="135" t="s">
         <v>40</v>
       </c>
       <c r="E19" s="8" t="s">
@@ -4845,8 +5092,8 @@
       <c r="B20" s="7">
         <v>17</v>
       </c>
-      <c r="C20" s="135"/>
-      <c r="D20" s="135"/>
+      <c r="C20" s="164"/>
+      <c r="D20" s="156"/>
       <c r="E20" s="8" t="s">
         <v>42</v>
       </c>
@@ -4873,8 +5120,8 @@
       <c r="B21" s="7">
         <v>18</v>
       </c>
-      <c r="C21" s="135"/>
-      <c r="D21" s="135"/>
+      <c r="C21" s="164"/>
+      <c r="D21" s="156"/>
       <c r="E21" s="8" t="s">
         <v>43</v>
       </c>
@@ -4901,8 +5148,8 @@
       <c r="B22" s="7">
         <v>19</v>
       </c>
-      <c r="C22" s="135"/>
-      <c r="D22" s="135"/>
+      <c r="C22" s="164"/>
+      <c r="D22" s="156"/>
       <c r="E22" s="8" t="s">
         <v>44</v>
       </c>
@@ -4923,8 +5170,8 @@
       <c r="B23" s="7">
         <v>20</v>
       </c>
-      <c r="C23" s="135"/>
-      <c r="D23" s="135"/>
+      <c r="C23" s="164"/>
+      <c r="D23" s="156"/>
       <c r="E23" s="8" t="s">
         <v>45</v>
       </c>
@@ -4945,8 +5192,8 @@
       <c r="B24" s="7">
         <v>21</v>
       </c>
-      <c r="C24" s="135"/>
-      <c r="D24" s="135"/>
+      <c r="C24" s="164"/>
+      <c r="D24" s="156"/>
       <c r="E24" s="13" t="s">
         <v>46</v>
       </c>
@@ -4971,8 +5218,8 @@
       <c r="B25" s="7">
         <v>22</v>
       </c>
-      <c r="C25" s="135"/>
-      <c r="D25" s="136"/>
+      <c r="C25" s="164"/>
+      <c r="D25" s="157"/>
       <c r="E25" s="8" t="s">
         <v>47</v>
       </c>
@@ -4985,7 +5232,7 @@
       <c r="H25" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="I25" s="162" t="s">
+      <c r="I25" s="134" t="s">
         <v>712</v>
       </c>
       <c r="J25" s="126" t="s">
@@ -4999,8 +5246,8 @@
       <c r="B26" s="7">
         <v>23</v>
       </c>
-      <c r="C26" s="135"/>
-      <c r="D26" s="143" t="s">
+      <c r="C26" s="164"/>
+      <c r="D26" s="135" t="s">
         <v>48</v>
       </c>
       <c r="E26" s="13" t="s">
@@ -5015,7 +5262,7 @@
       <c r="H26" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="I26" s="162" t="s">
+      <c r="I26" s="134" t="s">
         <v>713</v>
       </c>
       <c r="J26" s="126" t="s">
@@ -5029,8 +5276,8 @@
       <c r="B27" s="7">
         <v>24</v>
       </c>
-      <c r="C27" s="135"/>
-      <c r="D27" s="135"/>
+      <c r="C27" s="164"/>
+      <c r="D27" s="156"/>
       <c r="E27" s="8" t="s">
         <v>50</v>
       </c>
@@ -5051,8 +5298,8 @@
       <c r="B28" s="7">
         <v>25</v>
       </c>
-      <c r="C28" s="135"/>
-      <c r="D28" s="135"/>
+      <c r="C28" s="164"/>
+      <c r="D28" s="156"/>
       <c r="E28" s="8" t="s">
         <v>51</v>
       </c>
@@ -5073,8 +5320,8 @@
       <c r="B29" s="7">
         <v>26</v>
       </c>
-      <c r="C29" s="135"/>
-      <c r="D29" s="135"/>
+      <c r="C29" s="164"/>
+      <c r="D29" s="156"/>
       <c r="E29" s="8" t="s">
         <v>52</v>
       </c>
@@ -5095,8 +5342,8 @@
       <c r="B30" s="7">
         <v>27</v>
       </c>
-      <c r="C30" s="135"/>
-      <c r="D30" s="135"/>
+      <c r="C30" s="164"/>
+      <c r="D30" s="156"/>
       <c r="E30" s="8" t="s">
         <v>53</v>
       </c>
@@ -5117,8 +5364,8 @@
       <c r="B31" s="7">
         <v>28</v>
       </c>
-      <c r="C31" s="135"/>
-      <c r="D31" s="135"/>
+      <c r="C31" s="164"/>
+      <c r="D31" s="156"/>
       <c r="E31" s="8" t="s">
         <v>54</v>
       </c>
@@ -5139,8 +5386,8 @@
       <c r="B32" s="7">
         <v>29</v>
       </c>
-      <c r="C32" s="136"/>
-      <c r="D32" s="136"/>
+      <c r="C32" s="165"/>
+      <c r="D32" s="157"/>
       <c r="E32" s="17" t="s">
         <v>55</v>
       </c>
@@ -5161,10 +5408,10 @@
       <c r="B33" s="22">
         <v>1</v>
       </c>
-      <c r="C33" s="139" t="s">
+      <c r="C33" s="138" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="143" t="s">
+      <c r="D33" s="135" t="s">
         <v>57</v>
       </c>
       <c r="E33" s="8" t="s">
@@ -5187,8 +5434,8 @@
       <c r="B34" s="7">
         <v>2</v>
       </c>
-      <c r="C34" s="135"/>
-      <c r="D34" s="135"/>
+      <c r="C34" s="158"/>
+      <c r="D34" s="156"/>
       <c r="E34" s="8" t="s">
         <v>59</v>
       </c>
@@ -5209,8 +5456,8 @@
       <c r="B35" s="7">
         <v>3</v>
       </c>
-      <c r="C35" s="135"/>
-      <c r="D35" s="135"/>
+      <c r="C35" s="158"/>
+      <c r="D35" s="156"/>
       <c r="E35" s="8" t="s">
         <v>60</v>
       </c>
@@ -5231,8 +5478,8 @@
       <c r="B36" s="7">
         <v>4</v>
       </c>
-      <c r="C36" s="135"/>
-      <c r="D36" s="136"/>
+      <c r="C36" s="158"/>
+      <c r="D36" s="157"/>
       <c r="E36" s="8" t="s">
         <v>61</v>
       </c>
@@ -5253,8 +5500,8 @@
       <c r="B37" s="7">
         <v>5</v>
       </c>
-      <c r="C37" s="135"/>
-      <c r="D37" s="143" t="s">
+      <c r="C37" s="158"/>
+      <c r="D37" s="135" t="s">
         <v>62</v>
       </c>
       <c r="E37" s="8" t="s">
@@ -5277,8 +5524,8 @@
       <c r="B38" s="7">
         <v>6</v>
       </c>
-      <c r="C38" s="135"/>
-      <c r="D38" s="135"/>
+      <c r="C38" s="158"/>
+      <c r="D38" s="156"/>
       <c r="E38" s="8" t="s">
         <v>64</v>
       </c>
@@ -5299,8 +5546,8 @@
       <c r="B39" s="7">
         <v>7</v>
       </c>
-      <c r="C39" s="135"/>
-      <c r="D39" s="136"/>
+      <c r="C39" s="158"/>
+      <c r="D39" s="157"/>
       <c r="E39" s="8" t="s">
         <v>65</v>
       </c>
@@ -5321,8 +5568,8 @@
       <c r="B40" s="7">
         <v>8</v>
       </c>
-      <c r="C40" s="135"/>
-      <c r="D40" s="143" t="s">
+      <c r="C40" s="158"/>
+      <c r="D40" s="135" t="s">
         <v>66</v>
       </c>
       <c r="E40" s="8" t="s">
@@ -5345,8 +5592,8 @@
       <c r="B41" s="7">
         <v>9</v>
       </c>
-      <c r="C41" s="135"/>
-      <c r="D41" s="135"/>
+      <c r="C41" s="158"/>
+      <c r="D41" s="156"/>
       <c r="E41" s="8" t="s">
         <v>68</v>
       </c>
@@ -5367,8 +5614,8 @@
       <c r="B42" s="7">
         <v>10</v>
       </c>
-      <c r="C42" s="135"/>
-      <c r="D42" s="135"/>
+      <c r="C42" s="158"/>
+      <c r="D42" s="156"/>
       <c r="E42" s="8" t="s">
         <v>69</v>
       </c>
@@ -5389,8 +5636,8 @@
       <c r="B43" s="7">
         <v>11</v>
       </c>
-      <c r="C43" s="135"/>
-      <c r="D43" s="135"/>
+      <c r="C43" s="158"/>
+      <c r="D43" s="156"/>
       <c r="E43" s="8" t="s">
         <v>70</v>
       </c>
@@ -5411,8 +5658,8 @@
       <c r="B44" s="24">
         <v>12</v>
       </c>
-      <c r="C44" s="136"/>
-      <c r="D44" s="136"/>
+      <c r="C44" s="159"/>
+      <c r="D44" s="157"/>
       <c r="E44" s="17" t="s">
         <v>71</v>
       </c>
@@ -5433,7 +5680,7 @@
       <c r="B45" s="22">
         <v>1</v>
       </c>
-      <c r="C45" s="140" t="s">
+      <c r="C45" s="143" t="s">
         <v>72</v>
       </c>
       <c r="D45" s="144" t="s">
@@ -5463,8 +5710,8 @@
       <c r="B46" s="7">
         <v>2</v>
       </c>
-      <c r="C46" s="135"/>
-      <c r="D46" s="135"/>
+      <c r="C46" s="176"/>
+      <c r="D46" s="170"/>
       <c r="E46" s="8" t="s">
         <v>75</v>
       </c>
@@ -5491,8 +5738,8 @@
       <c r="B47" s="7">
         <v>3</v>
       </c>
-      <c r="C47" s="135"/>
-      <c r="D47" s="135"/>
+      <c r="C47" s="176"/>
+      <c r="D47" s="170"/>
       <c r="E47" s="13" t="s">
         <v>76</v>
       </c>
@@ -5519,8 +5766,8 @@
       <c r="B48" s="7">
         <v>4</v>
       </c>
-      <c r="C48" s="135"/>
-      <c r="D48" s="135"/>
+      <c r="C48" s="176"/>
+      <c r="D48" s="170"/>
       <c r="E48" s="13" t="s">
         <v>77</v>
       </c>
@@ -5547,8 +5794,8 @@
       <c r="B49" s="7">
         <v>5</v>
       </c>
-      <c r="C49" s="135"/>
-      <c r="D49" s="135"/>
+      <c r="C49" s="176"/>
+      <c r="D49" s="170"/>
       <c r="E49" s="13" t="s">
         <v>78</v>
       </c>
@@ -5573,8 +5820,8 @@
       <c r="B50" s="24">
         <v>6</v>
       </c>
-      <c r="C50" s="136"/>
-      <c r="D50" s="136"/>
+      <c r="C50" s="177"/>
+      <c r="D50" s="171"/>
       <c r="E50" s="25" t="s">
         <v>79</v>
       </c>
@@ -5592,17 +5839,17 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="13.8">
+    <row r="51" spans="1:10" ht="96.6">
       <c r="A51" s="6">
         <v>48</v>
       </c>
       <c r="B51" s="7">
         <v>1</v>
       </c>
-      <c r="C51" s="137" t="s">
+      <c r="C51" s="140" t="s">
         <v>80</v>
       </c>
-      <c r="D51" s="143" t="s">
+      <c r="D51" s="135" t="s">
         <v>81</v>
       </c>
       <c r="E51" s="13" t="s">
@@ -5614,19 +5861,25 @@
       <c r="G51" s="10">
         <v>1</v>
       </c>
-      <c r="H51" s="11"/>
-      <c r="I51" s="11"/>
-      <c r="J51" s="11"/>
-    </row>
-    <row r="52" spans="1:10" ht="13.8">
+      <c r="H51" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I51" s="125" t="s">
+        <v>714</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="132">
       <c r="A52" s="6">
         <v>49</v>
       </c>
       <c r="B52" s="7">
         <v>2</v>
       </c>
-      <c r="C52" s="135"/>
-      <c r="D52" s="135"/>
+      <c r="C52" s="166"/>
+      <c r="D52" s="156"/>
       <c r="E52" s="8" t="s">
         <v>83</v>
       </c>
@@ -5636,9 +5889,15 @@
       <c r="G52" s="10">
         <v>1</v>
       </c>
-      <c r="H52" s="11"/>
-      <c r="I52" s="26"/>
-      <c r="J52" s="11"/>
+      <c r="H52" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I52" s="191" t="s">
+        <v>715</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="53" spans="1:10" ht="13.8">
       <c r="A53" s="6">
@@ -5647,8 +5906,8 @@
       <c r="B53" s="7">
         <v>3</v>
       </c>
-      <c r="C53" s="135"/>
-      <c r="D53" s="135"/>
+      <c r="C53" s="166"/>
+      <c r="D53" s="156"/>
       <c r="E53" s="27" t="s">
         <v>84</v>
       </c>
@@ -5658,9 +5917,13 @@
       <c r="G53" s="10">
         <v>2</v>
       </c>
-      <c r="H53" s="11"/>
+      <c r="H53" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="I53" s="26"/>
-      <c r="J53" s="11"/>
+      <c r="J53" s="11" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="54" spans="1:10" ht="13.8">
       <c r="A54" s="6">
@@ -5669,8 +5932,8 @@
       <c r="B54" s="7">
         <v>4</v>
       </c>
-      <c r="C54" s="135"/>
-      <c r="D54" s="135"/>
+      <c r="C54" s="166"/>
+      <c r="D54" s="156"/>
       <c r="E54" s="13" t="s">
         <v>85</v>
       </c>
@@ -5680,9 +5943,13 @@
       <c r="G54" s="10">
         <v>2</v>
       </c>
-      <c r="H54" s="11"/>
+      <c r="H54" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="I54" s="26"/>
-      <c r="J54" s="11"/>
+      <c r="J54" s="11" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="55" spans="1:10" ht="13.8">
       <c r="A55" s="6">
@@ -5691,8 +5958,8 @@
       <c r="B55" s="7">
         <v>5</v>
       </c>
-      <c r="C55" s="135"/>
-      <c r="D55" s="135"/>
+      <c r="C55" s="166"/>
+      <c r="D55" s="156"/>
       <c r="E55" s="13" t="s">
         <v>86</v>
       </c>
@@ -5702,19 +5969,25 @@
       <c r="G55" s="10">
         <v>2</v>
       </c>
-      <c r="H55" s="11"/>
-      <c r="I55" s="26"/>
-      <c r="J55" s="11"/>
-    </row>
-    <row r="56" spans="1:10" ht="13.8">
+      <c r="H55" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I55" s="192" t="s">
+        <v>716</v>
+      </c>
+      <c r="J55" s="126" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="207">
       <c r="A56" s="6">
         <v>53</v>
       </c>
       <c r="B56" s="7">
         <v>6</v>
       </c>
-      <c r="C56" s="135"/>
-      <c r="D56" s="135"/>
+      <c r="C56" s="166"/>
+      <c r="D56" s="156"/>
       <c r="E56" s="13" t="s">
         <v>87</v>
       </c>
@@ -5724,19 +5997,25 @@
       <c r="G56" s="10">
         <v>2</v>
       </c>
-      <c r="H56" s="11"/>
-      <c r="I56" s="11"/>
-      <c r="J56" s="11"/>
-    </row>
-    <row r="57" spans="1:10" ht="13.8">
+      <c r="H56" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I56" s="193" t="s">
+        <v>717</v>
+      </c>
+      <c r="J56" s="126" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="345">
       <c r="A57" s="6">
         <v>54</v>
       </c>
       <c r="B57" s="7">
         <v>7</v>
       </c>
-      <c r="C57" s="135"/>
-      <c r="D57" s="136"/>
+      <c r="C57" s="166"/>
+      <c r="D57" s="157"/>
       <c r="E57" s="13" t="s">
         <v>88</v>
       </c>
@@ -5746,9 +6025,15 @@
       <c r="G57" s="10">
         <v>2</v>
       </c>
-      <c r="H57" s="11"/>
-      <c r="I57" s="11"/>
-      <c r="J57" s="11"/>
+      <c r="H57" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I57" s="131" t="s">
+        <v>718</v>
+      </c>
+      <c r="J57" s="128" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="58" spans="1:10" ht="13.8">
       <c r="A58" s="6">
@@ -5757,8 +6042,8 @@
       <c r="B58" s="7">
         <v>8</v>
       </c>
-      <c r="C58" s="135"/>
-      <c r="D58" s="143" t="s">
+      <c r="C58" s="166"/>
+      <c r="D58" s="135" t="s">
         <v>89</v>
       </c>
       <c r="E58" s="13" t="s">
@@ -5781,8 +6066,8 @@
       <c r="B59" s="7">
         <v>9</v>
       </c>
-      <c r="C59" s="135"/>
-      <c r="D59" s="135"/>
+      <c r="C59" s="166"/>
+      <c r="D59" s="156"/>
       <c r="E59" s="8" t="s">
         <v>91</v>
       </c>
@@ -5803,8 +6088,8 @@
       <c r="B60" s="7">
         <v>10</v>
       </c>
-      <c r="C60" s="135"/>
-      <c r="D60" s="135"/>
+      <c r="C60" s="166"/>
+      <c r="D60" s="156"/>
       <c r="E60" s="8" t="s">
         <v>92</v>
       </c>
@@ -5825,8 +6110,8 @@
       <c r="B61" s="7">
         <v>11</v>
       </c>
-      <c r="C61" s="135"/>
-      <c r="D61" s="135"/>
+      <c r="C61" s="166"/>
+      <c r="D61" s="156"/>
       <c r="E61" s="8" t="s">
         <v>93</v>
       </c>
@@ -5847,8 +6132,8 @@
       <c r="B62" s="7">
         <v>12</v>
       </c>
-      <c r="C62" s="135"/>
-      <c r="D62" s="135"/>
+      <c r="C62" s="166"/>
+      <c r="D62" s="156"/>
       <c r="E62" s="8" t="s">
         <v>94</v>
       </c>
@@ -5869,8 +6154,8 @@
       <c r="B63" s="7">
         <v>13</v>
       </c>
-      <c r="C63" s="135"/>
-      <c r="D63" s="136"/>
+      <c r="C63" s="166"/>
+      <c r="D63" s="157"/>
       <c r="E63" s="8" t="s">
         <v>95</v>
       </c>
@@ -5891,8 +6176,8 @@
       <c r="B64" s="7">
         <v>14</v>
       </c>
-      <c r="C64" s="135"/>
-      <c r="D64" s="143" t="s">
+      <c r="C64" s="166"/>
+      <c r="D64" s="135" t="s">
         <v>48</v>
       </c>
       <c r="E64" s="8" t="s">
@@ -5915,8 +6200,8 @@
       <c r="B65" s="7">
         <v>15</v>
       </c>
-      <c r="C65" s="135"/>
-      <c r="D65" s="135"/>
+      <c r="C65" s="166"/>
+      <c r="D65" s="156"/>
       <c r="E65" s="8" t="s">
         <v>97</v>
       </c>
@@ -5937,8 +6222,8 @@
       <c r="B66" s="7">
         <v>16</v>
       </c>
-      <c r="C66" s="135"/>
-      <c r="D66" s="135"/>
+      <c r="C66" s="166"/>
+      <c r="D66" s="156"/>
       <c r="E66" s="8" t="s">
         <v>98</v>
       </c>
@@ -5959,8 +6244,8 @@
       <c r="B67" s="7">
         <v>17</v>
       </c>
-      <c r="C67" s="136"/>
-      <c r="D67" s="136"/>
+      <c r="C67" s="167"/>
+      <c r="D67" s="157"/>
       <c r="E67" s="8" t="s">
         <v>99</v>
       </c>
@@ -5975,18 +6260,18 @@
       <c r="J67" s="11"/>
     </row>
     <row r="68" spans="1:10" ht="13.8">
-      <c r="A68" s="149" t="s">
+      <c r="A68" s="145" t="s">
         <v>100</v>
       </c>
-      <c r="B68" s="146"/>
-      <c r="C68" s="146"/>
-      <c r="D68" s="146"/>
-      <c r="E68" s="146"/>
-      <c r="F68" s="146"/>
-      <c r="G68" s="146"/>
-      <c r="H68" s="146"/>
-      <c r="I68" s="146"/>
-      <c r="J68" s="147"/>
+      <c r="B68" s="178"/>
+      <c r="C68" s="178"/>
+      <c r="D68" s="178"/>
+      <c r="E68" s="178"/>
+      <c r="F68" s="178"/>
+      <c r="G68" s="178"/>
+      <c r="H68" s="178"/>
+      <c r="I68" s="178"/>
+      <c r="J68" s="179"/>
     </row>
     <row r="69" spans="1:10" ht="13.8">
       <c r="A69" s="6">
@@ -5995,10 +6280,10 @@
       <c r="B69" s="7">
         <v>1</v>
       </c>
-      <c r="C69" s="138" t="s">
+      <c r="C69" s="137" t="s">
         <v>101</v>
       </c>
-      <c r="D69" s="143" t="s">
+      <c r="D69" s="135" t="s">
         <v>102</v>
       </c>
       <c r="E69" s="8" t="s">
@@ -6021,8 +6306,8 @@
       <c r="B70" s="7">
         <v>2</v>
       </c>
-      <c r="C70" s="135"/>
-      <c r="D70" s="135"/>
+      <c r="C70" s="164"/>
+      <c r="D70" s="156"/>
       <c r="E70" s="28" t="s">
         <v>104</v>
       </c>
@@ -6043,8 +6328,8 @@
       <c r="B71" s="7">
         <v>3</v>
       </c>
-      <c r="C71" s="135"/>
-      <c r="D71" s="135"/>
+      <c r="C71" s="164"/>
+      <c r="D71" s="156"/>
       <c r="E71" s="8" t="s">
         <v>105</v>
       </c>
@@ -6065,8 +6350,8 @@
       <c r="B72" s="7">
         <v>4</v>
       </c>
-      <c r="C72" s="135"/>
-      <c r="D72" s="135"/>
+      <c r="C72" s="164"/>
+      <c r="D72" s="156"/>
       <c r="E72" s="8" t="s">
         <v>106</v>
       </c>
@@ -6087,8 +6372,8 @@
       <c r="B73" s="7">
         <v>5</v>
       </c>
-      <c r="C73" s="135"/>
-      <c r="D73" s="135"/>
+      <c r="C73" s="164"/>
+      <c r="D73" s="156"/>
       <c r="E73" s="28" t="s">
         <v>107</v>
       </c>
@@ -6109,8 +6394,8 @@
       <c r="B74" s="7">
         <v>6</v>
       </c>
-      <c r="C74" s="135"/>
-      <c r="D74" s="135"/>
+      <c r="C74" s="164"/>
+      <c r="D74" s="156"/>
       <c r="E74" s="28" t="s">
         <v>108</v>
       </c>
@@ -6131,8 +6416,8 @@
       <c r="B75" s="7">
         <v>7</v>
       </c>
-      <c r="C75" s="135"/>
-      <c r="D75" s="135"/>
+      <c r="C75" s="164"/>
+      <c r="D75" s="156"/>
       <c r="E75" s="28" t="s">
         <v>109</v>
       </c>
@@ -6153,8 +6438,8 @@
       <c r="B76" s="7">
         <v>8</v>
       </c>
-      <c r="C76" s="135"/>
-      <c r="D76" s="135"/>
+      <c r="C76" s="164"/>
+      <c r="D76" s="156"/>
       <c r="E76" s="8" t="s">
         <v>110</v>
       </c>
@@ -6175,8 +6460,8 @@
       <c r="B77" s="7">
         <v>9</v>
       </c>
-      <c r="C77" s="135"/>
-      <c r="D77" s="135"/>
+      <c r="C77" s="164"/>
+      <c r="D77" s="156"/>
       <c r="E77" s="8" t="s">
         <v>111</v>
       </c>
@@ -6197,8 +6482,8 @@
       <c r="B78" s="7">
         <v>10</v>
       </c>
-      <c r="C78" s="135"/>
-      <c r="D78" s="136"/>
+      <c r="C78" s="164"/>
+      <c r="D78" s="157"/>
       <c r="E78" s="8" t="s">
         <v>112</v>
       </c>
@@ -6219,8 +6504,8 @@
       <c r="B79" s="7">
         <v>11</v>
       </c>
-      <c r="C79" s="135"/>
-      <c r="D79" s="143" t="s">
+      <c r="C79" s="164"/>
+      <c r="D79" s="135" t="s">
         <v>113</v>
       </c>
       <c r="E79" s="8" t="s">
@@ -6243,8 +6528,8 @@
       <c r="B80" s="7">
         <v>12</v>
       </c>
-      <c r="C80" s="135"/>
-      <c r="D80" s="135"/>
+      <c r="C80" s="164"/>
+      <c r="D80" s="156"/>
       <c r="E80" s="8" t="s">
         <v>115</v>
       </c>
@@ -6265,8 +6550,8 @@
       <c r="B81" s="7">
         <v>13</v>
       </c>
-      <c r="C81" s="135"/>
-      <c r="D81" s="135"/>
+      <c r="C81" s="164"/>
+      <c r="D81" s="156"/>
       <c r="E81" s="8" t="s">
         <v>116</v>
       </c>
@@ -6287,8 +6572,8 @@
       <c r="B82" s="7">
         <v>14</v>
       </c>
-      <c r="C82" s="135"/>
-      <c r="D82" s="135"/>
+      <c r="C82" s="164"/>
+      <c r="D82" s="156"/>
       <c r="E82" s="8" t="s">
         <v>117</v>
       </c>
@@ -6309,8 +6594,8 @@
       <c r="B83" s="7">
         <v>15</v>
       </c>
-      <c r="C83" s="135"/>
-      <c r="D83" s="135"/>
+      <c r="C83" s="164"/>
+      <c r="D83" s="156"/>
       <c r="E83" s="8" t="s">
         <v>118</v>
       </c>
@@ -6331,8 +6616,8 @@
       <c r="B84" s="7">
         <v>16</v>
       </c>
-      <c r="C84" s="135"/>
-      <c r="D84" s="136"/>
+      <c r="C84" s="164"/>
+      <c r="D84" s="157"/>
       <c r="E84" s="8" t="s">
         <v>119</v>
       </c>
@@ -6353,8 +6638,8 @@
       <c r="B85" s="7">
         <v>17</v>
       </c>
-      <c r="C85" s="135"/>
-      <c r="D85" s="143" t="s">
+      <c r="C85" s="164"/>
+      <c r="D85" s="135" t="s">
         <v>120</v>
       </c>
       <c r="E85" s="8" t="s">
@@ -6377,8 +6662,8 @@
       <c r="B86" s="7">
         <v>18</v>
       </c>
-      <c r="C86" s="135"/>
-      <c r="D86" s="135"/>
+      <c r="C86" s="164"/>
+      <c r="D86" s="156"/>
       <c r="E86" s="8" t="s">
         <v>122</v>
       </c>
@@ -6399,8 +6684,8 @@
       <c r="B87" s="7">
         <v>19</v>
       </c>
-      <c r="C87" s="135"/>
-      <c r="D87" s="135"/>
+      <c r="C87" s="164"/>
+      <c r="D87" s="156"/>
       <c r="E87" s="29" t="s">
         <v>123</v>
       </c>
@@ -6421,8 +6706,8 @@
       <c r="B88" s="7">
         <v>20</v>
       </c>
-      <c r="C88" s="135"/>
-      <c r="D88" s="135"/>
+      <c r="C88" s="164"/>
+      <c r="D88" s="156"/>
       <c r="E88" s="8" t="s">
         <v>124</v>
       </c>
@@ -6443,8 +6728,8 @@
       <c r="B89" s="7">
         <v>21</v>
       </c>
-      <c r="C89" s="135"/>
-      <c r="D89" s="135"/>
+      <c r="C89" s="164"/>
+      <c r="D89" s="156"/>
       <c r="E89" s="8" t="s">
         <v>125</v>
       </c>
@@ -6465,8 +6750,8 @@
       <c r="B90" s="7">
         <v>22</v>
       </c>
-      <c r="C90" s="135"/>
-      <c r="D90" s="136"/>
+      <c r="C90" s="164"/>
+      <c r="D90" s="157"/>
       <c r="E90" s="8" t="s">
         <v>126</v>
       </c>
@@ -6487,8 +6772,8 @@
       <c r="B91" s="7">
         <v>23</v>
       </c>
-      <c r="C91" s="135"/>
-      <c r="D91" s="143" t="s">
+      <c r="C91" s="164"/>
+      <c r="D91" s="135" t="s">
         <v>127</v>
       </c>
       <c r="E91" s="8" t="s">
@@ -6511,8 +6796,8 @@
       <c r="B92" s="7">
         <v>24</v>
       </c>
-      <c r="C92" s="135"/>
-      <c r="D92" s="135"/>
+      <c r="C92" s="164"/>
+      <c r="D92" s="156"/>
       <c r="E92" s="8" t="s">
         <v>129</v>
       </c>
@@ -6533,8 +6818,8 @@
       <c r="B93" s="7">
         <v>25</v>
       </c>
-      <c r="C93" s="135"/>
-      <c r="D93" s="135"/>
+      <c r="C93" s="164"/>
+      <c r="D93" s="156"/>
       <c r="E93" s="8" t="s">
         <v>130</v>
       </c>
@@ -6555,8 +6840,8 @@
       <c r="B94" s="7">
         <v>26</v>
       </c>
-      <c r="C94" s="135"/>
-      <c r="D94" s="135"/>
+      <c r="C94" s="164"/>
+      <c r="D94" s="156"/>
       <c r="E94" s="8" t="s">
         <v>131</v>
       </c>
@@ -6577,8 +6862,8 @@
       <c r="B95" s="7">
         <v>27</v>
       </c>
-      <c r="C95" s="135"/>
-      <c r="D95" s="135"/>
+      <c r="C95" s="164"/>
+      <c r="D95" s="156"/>
       <c r="E95" s="8" t="s">
         <v>132</v>
       </c>
@@ -6599,8 +6884,8 @@
       <c r="B96" s="7">
         <v>28</v>
       </c>
-      <c r="C96" s="135"/>
-      <c r="D96" s="135"/>
+      <c r="C96" s="164"/>
+      <c r="D96" s="156"/>
       <c r="E96" s="8" t="s">
         <v>133</v>
       </c>
@@ -6621,8 +6906,8 @@
       <c r="B97" s="7">
         <v>29</v>
       </c>
-      <c r="C97" s="135"/>
-      <c r="D97" s="135"/>
+      <c r="C97" s="164"/>
+      <c r="D97" s="156"/>
       <c r="E97" s="8" t="s">
         <v>134</v>
       </c>
@@ -6643,8 +6928,8 @@
       <c r="B98" s="7">
         <v>30</v>
       </c>
-      <c r="C98" s="135"/>
-      <c r="D98" s="135"/>
+      <c r="C98" s="164"/>
+      <c r="D98" s="156"/>
       <c r="E98" s="8" t="s">
         <v>135</v>
       </c>
@@ -6665,8 +6950,8 @@
       <c r="B99" s="7">
         <v>31</v>
       </c>
-      <c r="C99" s="135"/>
-      <c r="D99" s="135"/>
+      <c r="C99" s="164"/>
+      <c r="D99" s="156"/>
       <c r="E99" s="30" t="s">
         <v>136</v>
       </c>
@@ -6687,8 +6972,8 @@
       <c r="B100" s="7">
         <v>32</v>
       </c>
-      <c r="C100" s="135"/>
-      <c r="D100" s="135"/>
+      <c r="C100" s="164"/>
+      <c r="D100" s="156"/>
       <c r="E100" s="8" t="s">
         <v>137</v>
       </c>
@@ -6709,8 +6994,8 @@
       <c r="B101" s="7">
         <v>33</v>
       </c>
-      <c r="C101" s="135"/>
-      <c r="D101" s="135"/>
+      <c r="C101" s="164"/>
+      <c r="D101" s="156"/>
       <c r="E101" s="8" t="s">
         <v>138</v>
       </c>
@@ -6731,8 +7016,8 @@
       <c r="B102" s="7">
         <v>34</v>
       </c>
-      <c r="C102" s="135"/>
-      <c r="D102" s="135"/>
+      <c r="C102" s="164"/>
+      <c r="D102" s="156"/>
       <c r="E102" s="8" t="s">
         <v>139</v>
       </c>
@@ -6753,8 +7038,8 @@
       <c r="B103" s="7">
         <v>35</v>
       </c>
-      <c r="C103" s="135"/>
-      <c r="D103" s="135"/>
+      <c r="C103" s="164"/>
+      <c r="D103" s="156"/>
       <c r="E103" s="8" t="s">
         <v>140</v>
       </c>
@@ -6775,8 +7060,8 @@
       <c r="B104" s="7">
         <v>36</v>
       </c>
-      <c r="C104" s="135"/>
-      <c r="D104" s="135"/>
+      <c r="C104" s="164"/>
+      <c r="D104" s="156"/>
       <c r="E104" s="8" t="s">
         <v>141</v>
       </c>
@@ -6797,8 +7082,8 @@
       <c r="B105" s="7">
         <v>37</v>
       </c>
-      <c r="C105" s="136"/>
-      <c r="D105" s="136"/>
+      <c r="C105" s="165"/>
+      <c r="D105" s="157"/>
       <c r="E105" s="8" t="s">
         <v>142</v>
       </c>
@@ -6813,18 +7098,18 @@
       <c r="J105" s="11"/>
     </row>
     <row r="106" spans="1:10" ht="13.8">
-      <c r="A106" s="151" t="s">
+      <c r="A106" s="141" t="s">
         <v>143</v>
       </c>
-      <c r="B106" s="146"/>
-      <c r="C106" s="146"/>
-      <c r="D106" s="146"/>
-      <c r="E106" s="146"/>
-      <c r="F106" s="146"/>
-      <c r="G106" s="146"/>
-      <c r="H106" s="146"/>
-      <c r="I106" s="146"/>
-      <c r="J106" s="147"/>
+      <c r="B106" s="186"/>
+      <c r="C106" s="186"/>
+      <c r="D106" s="186"/>
+      <c r="E106" s="186"/>
+      <c r="F106" s="186"/>
+      <c r="G106" s="186"/>
+      <c r="H106" s="186"/>
+      <c r="I106" s="186"/>
+      <c r="J106" s="187"/>
     </row>
     <row r="107" spans="1:10" ht="13.8">
       <c r="A107" s="6">
@@ -6833,10 +7118,10 @@
       <c r="B107" s="7">
         <v>1</v>
       </c>
-      <c r="C107" s="139" t="s">
+      <c r="C107" s="138" t="s">
         <v>144</v>
       </c>
-      <c r="D107" s="143" t="s">
+      <c r="D107" s="135" t="s">
         <v>145</v>
       </c>
       <c r="E107" s="8" t="s">
@@ -6859,8 +7144,8 @@
       <c r="B108" s="7">
         <v>2</v>
       </c>
-      <c r="C108" s="135"/>
-      <c r="D108" s="135"/>
+      <c r="C108" s="158"/>
+      <c r="D108" s="156"/>
       <c r="E108" s="8" t="s">
         <v>147</v>
       </c>
@@ -6881,8 +7166,8 @@
       <c r="B109" s="7">
         <v>3</v>
       </c>
-      <c r="C109" s="135"/>
-      <c r="D109" s="135"/>
+      <c r="C109" s="158"/>
+      <c r="D109" s="156"/>
       <c r="E109" s="8" t="s">
         <v>148</v>
       </c>
@@ -6903,8 +7188,8 @@
       <c r="B110" s="7">
         <v>4</v>
       </c>
-      <c r="C110" s="135"/>
-      <c r="D110" s="135"/>
+      <c r="C110" s="158"/>
+      <c r="D110" s="156"/>
       <c r="E110" s="8" t="s">
         <v>149</v>
       </c>
@@ -6925,8 +7210,8 @@
       <c r="B111" s="7">
         <v>5</v>
       </c>
-      <c r="C111" s="135"/>
-      <c r="D111" s="136"/>
+      <c r="C111" s="158"/>
+      <c r="D111" s="157"/>
       <c r="E111" s="8" t="s">
         <v>150</v>
       </c>
@@ -6947,8 +7232,8 @@
       <c r="B112" s="7">
         <v>6</v>
       </c>
-      <c r="C112" s="135"/>
-      <c r="D112" s="143" t="s">
+      <c r="C112" s="158"/>
+      <c r="D112" s="135" t="s">
         <v>151</v>
       </c>
       <c r="E112" s="8" t="s">
@@ -6971,8 +7256,8 @@
       <c r="B113" s="7">
         <v>7</v>
       </c>
-      <c r="C113" s="135"/>
-      <c r="D113" s="135"/>
+      <c r="C113" s="158"/>
+      <c r="D113" s="156"/>
       <c r="E113" s="8" t="s">
         <v>153</v>
       </c>
@@ -6993,8 +7278,8 @@
       <c r="B114" s="7">
         <v>8</v>
       </c>
-      <c r="C114" s="135"/>
-      <c r="D114" s="135"/>
+      <c r="C114" s="158"/>
+      <c r="D114" s="156"/>
       <c r="E114" s="8" t="s">
         <v>154</v>
       </c>
@@ -7015,8 +7300,8 @@
       <c r="B115" s="7">
         <v>9</v>
       </c>
-      <c r="C115" s="135"/>
-      <c r="D115" s="136"/>
+      <c r="C115" s="158"/>
+      <c r="D115" s="157"/>
       <c r="E115" s="8" t="s">
         <v>155</v>
       </c>
@@ -7037,7 +7322,7 @@
       <c r="B116" s="24">
         <v>10</v>
       </c>
-      <c r="C116" s="136"/>
+      <c r="C116" s="159"/>
       <c r="D116" s="31" t="s">
         <v>156</v>
       </c>
@@ -7061,10 +7346,10 @@
       <c r="B117" s="7">
         <v>1</v>
       </c>
-      <c r="C117" s="134" t="s">
+      <c r="C117" s="139" t="s">
         <v>158</v>
       </c>
-      <c r="D117" s="143" t="s">
+      <c r="D117" s="135" t="s">
         <v>159</v>
       </c>
       <c r="E117" s="8" t="s">
@@ -7087,8 +7372,8 @@
       <c r="B118" s="7">
         <v>2</v>
       </c>
-      <c r="C118" s="135"/>
-      <c r="D118" s="135"/>
+      <c r="C118" s="160"/>
+      <c r="D118" s="156"/>
       <c r="E118" s="8" t="s">
         <v>161</v>
       </c>
@@ -7109,8 +7394,8 @@
       <c r="B119" s="7">
         <v>3</v>
       </c>
-      <c r="C119" s="135"/>
-      <c r="D119" s="135"/>
+      <c r="C119" s="160"/>
+      <c r="D119" s="156"/>
       <c r="E119" s="8" t="s">
         <v>162</v>
       </c>
@@ -7131,8 +7416,8 @@
       <c r="B120" s="7">
         <v>4</v>
       </c>
-      <c r="C120" s="135"/>
-      <c r="D120" s="136"/>
+      <c r="C120" s="160"/>
+      <c r="D120" s="157"/>
       <c r="E120" s="8" t="s">
         <v>163</v>
       </c>
@@ -7153,8 +7438,8 @@
       <c r="B121" s="7">
         <v>5</v>
       </c>
-      <c r="C121" s="135"/>
-      <c r="D121" s="143" t="s">
+      <c r="C121" s="160"/>
+      <c r="D121" s="135" t="s">
         <v>164</v>
       </c>
       <c r="E121" s="8" t="s">
@@ -7177,8 +7462,8 @@
       <c r="B122" s="7">
         <v>6</v>
       </c>
-      <c r="C122" s="135"/>
-      <c r="D122" s="136"/>
+      <c r="C122" s="160"/>
+      <c r="D122" s="157"/>
       <c r="E122" s="8" t="s">
         <v>166</v>
       </c>
@@ -7199,8 +7484,8 @@
       <c r="B123" s="7">
         <v>7</v>
       </c>
-      <c r="C123" s="135"/>
-      <c r="D123" s="143" t="s">
+      <c r="C123" s="160"/>
+      <c r="D123" s="135" t="s">
         <v>167</v>
       </c>
       <c r="E123" s="8" t="s">
@@ -7223,8 +7508,8 @@
       <c r="B124" s="7">
         <v>8</v>
       </c>
-      <c r="C124" s="135"/>
-      <c r="D124" s="135"/>
+      <c r="C124" s="160"/>
+      <c r="D124" s="156"/>
       <c r="E124" s="28" t="s">
         <v>169</v>
       </c>
@@ -7245,8 +7530,8 @@
       <c r="B125" s="7">
         <v>9</v>
       </c>
-      <c r="C125" s="136"/>
-      <c r="D125" s="136"/>
+      <c r="C125" s="161"/>
+      <c r="D125" s="157"/>
       <c r="E125" s="8" t="s">
         <v>170</v>
       </c>
@@ -7261,18 +7546,18 @@
       <c r="J125" s="11"/>
     </row>
     <row r="126" spans="1:10" ht="13.8">
-      <c r="A126" s="152" t="s">
+      <c r="A126" s="142" t="s">
         <v>171</v>
       </c>
-      <c r="B126" s="146"/>
-      <c r="C126" s="146"/>
-      <c r="D126" s="146"/>
-      <c r="E126" s="146"/>
-      <c r="F126" s="146"/>
-      <c r="G126" s="146"/>
-      <c r="H126" s="146"/>
-      <c r="I126" s="146"/>
-      <c r="J126" s="147"/>
+      <c r="B126" s="184"/>
+      <c r="C126" s="184"/>
+      <c r="D126" s="184"/>
+      <c r="E126" s="184"/>
+      <c r="F126" s="184"/>
+      <c r="G126" s="184"/>
+      <c r="H126" s="184"/>
+      <c r="I126" s="184"/>
+      <c r="J126" s="185"/>
     </row>
     <row r="127" spans="1:10" ht="13.8">
       <c r="A127" s="6">
@@ -7281,10 +7566,10 @@
       <c r="B127" s="7">
         <v>1</v>
       </c>
-      <c r="C127" s="137" t="s">
+      <c r="C127" s="140" t="s">
         <v>172</v>
       </c>
-      <c r="D127" s="143" t="s">
+      <c r="D127" s="135" t="s">
         <v>173</v>
       </c>
       <c r="E127" s="32" t="s">
@@ -7305,8 +7590,8 @@
       <c r="B128" s="7">
         <v>2</v>
       </c>
-      <c r="C128" s="135"/>
-      <c r="D128" s="135"/>
+      <c r="C128" s="166"/>
+      <c r="D128" s="156"/>
       <c r="E128" s="32" t="s">
         <v>175</v>
       </c>
@@ -7325,8 +7610,8 @@
       <c r="B129" s="7">
         <v>3</v>
       </c>
-      <c r="C129" s="135"/>
-      <c r="D129" s="135"/>
+      <c r="C129" s="166"/>
+      <c r="D129" s="156"/>
       <c r="E129" s="32" t="s">
         <v>176</v>
       </c>
@@ -7345,8 +7630,8 @@
       <c r="B130" s="7">
         <v>4</v>
       </c>
-      <c r="C130" s="135"/>
-      <c r="D130" s="136"/>
+      <c r="C130" s="166"/>
+      <c r="D130" s="157"/>
       <c r="E130" s="32" t="s">
         <v>177</v>
       </c>
@@ -7365,8 +7650,8 @@
       <c r="B131" s="7">
         <v>5</v>
       </c>
-      <c r="C131" s="135"/>
-      <c r="D131" s="143" t="s">
+      <c r="C131" s="166"/>
+      <c r="D131" s="135" t="s">
         <v>178</v>
       </c>
       <c r="E131" s="32" t="s">
@@ -7387,8 +7672,8 @@
       <c r="B132" s="7">
         <v>6</v>
       </c>
-      <c r="C132" s="136"/>
-      <c r="D132" s="136"/>
+      <c r="C132" s="167"/>
+      <c r="D132" s="157"/>
       <c r="E132" s="32" t="s">
         <v>180</v>
       </c>
@@ -7401,18 +7686,18 @@
       <c r="J132" s="11"/>
     </row>
     <row r="133" spans="1:10" ht="13.8">
-      <c r="A133" s="153" t="s">
+      <c r="A133" s="136" t="s">
         <v>181</v>
       </c>
-      <c r="B133" s="146"/>
-      <c r="C133" s="146"/>
-      <c r="D133" s="146"/>
-      <c r="E133" s="146"/>
-      <c r="F133" s="146"/>
-      <c r="G133" s="146"/>
-      <c r="H133" s="146"/>
-      <c r="I133" s="146"/>
-      <c r="J133" s="147"/>
+      <c r="B133" s="182"/>
+      <c r="C133" s="182"/>
+      <c r="D133" s="182"/>
+      <c r="E133" s="182"/>
+      <c r="F133" s="182"/>
+      <c r="G133" s="182"/>
+      <c r="H133" s="182"/>
+      <c r="I133" s="182"/>
+      <c r="J133" s="183"/>
     </row>
     <row r="134" spans="1:10" ht="13.8">
       <c r="A134" s="6">
@@ -7421,10 +7706,10 @@
       <c r="B134" s="7">
         <v>1</v>
       </c>
-      <c r="C134" s="138" t="s">
+      <c r="C134" s="137" t="s">
         <v>182</v>
       </c>
-      <c r="D134" s="143" t="s">
+      <c r="D134" s="135" t="s">
         <v>183</v>
       </c>
       <c r="E134" s="8" t="s">
@@ -7447,8 +7732,8 @@
       <c r="B135" s="7">
         <v>2</v>
       </c>
-      <c r="C135" s="135"/>
-      <c r="D135" s="135"/>
+      <c r="C135" s="164"/>
+      <c r="D135" s="156"/>
       <c r="E135" s="8" t="s">
         <v>185</v>
       </c>
@@ -7469,8 +7754,8 @@
       <c r="B136" s="7">
         <v>3</v>
       </c>
-      <c r="C136" s="135"/>
-      <c r="D136" s="136"/>
+      <c r="C136" s="164"/>
+      <c r="D136" s="157"/>
       <c r="E136" s="8" t="s">
         <v>186</v>
       </c>
@@ -7491,8 +7776,8 @@
       <c r="B137" s="7">
         <v>4</v>
       </c>
-      <c r="C137" s="135"/>
-      <c r="D137" s="143" t="s">
+      <c r="C137" s="164"/>
+      <c r="D137" s="135" t="s">
         <v>187</v>
       </c>
       <c r="E137" s="8" t="s">
@@ -7515,8 +7800,8 @@
       <c r="B138" s="7">
         <v>5</v>
       </c>
-      <c r="C138" s="135"/>
-      <c r="D138" s="135"/>
+      <c r="C138" s="164"/>
+      <c r="D138" s="156"/>
       <c r="E138" s="8" t="s">
         <v>189</v>
       </c>
@@ -7537,8 +7822,8 @@
       <c r="B139" s="7">
         <v>6</v>
       </c>
-      <c r="C139" s="135"/>
-      <c r="D139" s="135"/>
+      <c r="C139" s="164"/>
+      <c r="D139" s="156"/>
       <c r="E139" s="8" t="s">
         <v>190</v>
       </c>
@@ -7559,8 +7844,8 @@
       <c r="B140" s="7">
         <v>7</v>
       </c>
-      <c r="C140" s="135"/>
-      <c r="D140" s="135"/>
+      <c r="C140" s="164"/>
+      <c r="D140" s="156"/>
       <c r="E140" s="8" t="s">
         <v>191</v>
       </c>
@@ -7581,8 +7866,8 @@
       <c r="B141" s="7">
         <v>8</v>
       </c>
-      <c r="C141" s="135"/>
-      <c r="D141" s="135"/>
+      <c r="C141" s="164"/>
+      <c r="D141" s="156"/>
       <c r="E141" s="8" t="s">
         <v>192</v>
       </c>
@@ -7603,8 +7888,8 @@
       <c r="B142" s="7">
         <v>9</v>
       </c>
-      <c r="C142" s="135"/>
-      <c r="D142" s="135"/>
+      <c r="C142" s="164"/>
+      <c r="D142" s="156"/>
       <c r="E142" s="8" t="s">
         <v>193</v>
       </c>
@@ -7625,8 +7910,8 @@
       <c r="B143" s="7">
         <v>10</v>
       </c>
-      <c r="C143" s="135"/>
-      <c r="D143" s="136"/>
+      <c r="C143" s="164"/>
+      <c r="D143" s="157"/>
       <c r="E143" s="8" t="s">
         <v>194</v>
       </c>
@@ -7647,8 +7932,8 @@
       <c r="B144" s="7">
         <v>11</v>
       </c>
-      <c r="C144" s="135"/>
-      <c r="D144" s="143" t="s">
+      <c r="C144" s="164"/>
+      <c r="D144" s="135" t="s">
         <v>195</v>
       </c>
       <c r="E144" s="8" t="s">
@@ -7671,8 +7956,8 @@
       <c r="B145" s="7">
         <v>12</v>
       </c>
-      <c r="C145" s="135"/>
-      <c r="D145" s="135"/>
+      <c r="C145" s="164"/>
+      <c r="D145" s="156"/>
       <c r="E145" s="8" t="s">
         <v>197</v>
       </c>
@@ -7693,8 +7978,8 @@
       <c r="B146" s="7">
         <v>13</v>
       </c>
-      <c r="C146" s="135"/>
-      <c r="D146" s="135"/>
+      <c r="C146" s="164"/>
+      <c r="D146" s="156"/>
       <c r="E146" s="8" t="s">
         <v>198</v>
       </c>
@@ -7715,8 +8000,8 @@
       <c r="B147" s="7">
         <v>14</v>
       </c>
-      <c r="C147" s="135"/>
-      <c r="D147" s="135"/>
+      <c r="C147" s="164"/>
+      <c r="D147" s="156"/>
       <c r="E147" s="8" t="s">
         <v>199</v>
       </c>
@@ -7737,8 +8022,8 @@
       <c r="B148" s="7">
         <v>15</v>
       </c>
-      <c r="C148" s="135"/>
-      <c r="D148" s="135"/>
+      <c r="C148" s="164"/>
+      <c r="D148" s="156"/>
       <c r="E148" s="8" t="s">
         <v>200</v>
       </c>
@@ -7759,8 +8044,8 @@
       <c r="B149" s="7">
         <v>16</v>
       </c>
-      <c r="C149" s="135"/>
-      <c r="D149" s="135"/>
+      <c r="C149" s="164"/>
+      <c r="D149" s="156"/>
       <c r="E149" s="8" t="s">
         <v>201</v>
       </c>
@@ -7781,8 +8066,8 @@
       <c r="B150" s="7">
         <v>17</v>
       </c>
-      <c r="C150" s="135"/>
-      <c r="D150" s="136"/>
+      <c r="C150" s="164"/>
+      <c r="D150" s="157"/>
       <c r="E150" s="8" t="s">
         <v>202</v>
       </c>
@@ -7803,8 +8088,8 @@
       <c r="B151" s="7">
         <v>18</v>
       </c>
-      <c r="C151" s="135"/>
-      <c r="D151" s="143" t="s">
+      <c r="C151" s="164"/>
+      <c r="D151" s="135" t="s">
         <v>203</v>
       </c>
       <c r="E151" s="8" t="s">
@@ -7827,8 +8112,8 @@
       <c r="B152" s="7">
         <v>19</v>
       </c>
-      <c r="C152" s="135"/>
-      <c r="D152" s="135"/>
+      <c r="C152" s="164"/>
+      <c r="D152" s="156"/>
       <c r="E152" s="8" t="s">
         <v>205</v>
       </c>
@@ -7849,8 +8134,8 @@
       <c r="B153" s="7">
         <v>20</v>
       </c>
-      <c r="C153" s="135"/>
-      <c r="D153" s="135"/>
+      <c r="C153" s="164"/>
+      <c r="D153" s="156"/>
       <c r="E153" s="8" t="s">
         <v>206</v>
       </c>
@@ -7871,8 +8156,8 @@
       <c r="B154" s="7">
         <v>21</v>
       </c>
-      <c r="C154" s="135"/>
-      <c r="D154" s="135"/>
+      <c r="C154" s="164"/>
+      <c r="D154" s="156"/>
       <c r="E154" s="8" t="s">
         <v>207</v>
       </c>
@@ -7893,8 +8178,8 @@
       <c r="B155" s="7">
         <v>22</v>
       </c>
-      <c r="C155" s="135"/>
-      <c r="D155" s="135"/>
+      <c r="C155" s="164"/>
+      <c r="D155" s="156"/>
       <c r="E155" s="8" t="s">
         <v>208</v>
       </c>
@@ -7915,8 +8200,8 @@
       <c r="B156" s="7">
         <v>23</v>
       </c>
-      <c r="C156" s="135"/>
-      <c r="D156" s="136"/>
+      <c r="C156" s="164"/>
+      <c r="D156" s="157"/>
       <c r="E156" s="8" t="s">
         <v>209</v>
       </c>
@@ -7937,8 +8222,8 @@
       <c r="B157" s="7">
         <v>24</v>
       </c>
-      <c r="C157" s="135"/>
-      <c r="D157" s="143" t="s">
+      <c r="C157" s="164"/>
+      <c r="D157" s="135" t="s">
         <v>210</v>
       </c>
       <c r="E157" s="8" t="s">
@@ -7961,8 +8246,8 @@
       <c r="B158" s="7">
         <v>25</v>
       </c>
-      <c r="C158" s="135"/>
-      <c r="D158" s="135"/>
+      <c r="C158" s="164"/>
+      <c r="D158" s="156"/>
       <c r="E158" s="8" t="s">
         <v>212</v>
       </c>
@@ -7983,8 +8268,8 @@
       <c r="B159" s="7">
         <v>26</v>
       </c>
-      <c r="C159" s="135"/>
-      <c r="D159" s="136"/>
+      <c r="C159" s="164"/>
+      <c r="D159" s="157"/>
       <c r="E159" s="8" t="s">
         <v>213</v>
       </c>
@@ -8005,8 +8290,8 @@
       <c r="B160" s="7">
         <v>27</v>
       </c>
-      <c r="C160" s="135"/>
-      <c r="D160" s="143" t="s">
+      <c r="C160" s="164"/>
+      <c r="D160" s="135" t="s">
         <v>214</v>
       </c>
       <c r="E160" s="8" t="s">
@@ -8029,8 +8314,8 @@
       <c r="B161" s="7">
         <v>28</v>
       </c>
-      <c r="C161" s="135"/>
-      <c r="D161" s="135"/>
+      <c r="C161" s="164"/>
+      <c r="D161" s="156"/>
       <c r="E161" s="8" t="s">
         <v>216</v>
       </c>
@@ -8051,8 +8336,8 @@
       <c r="B162" s="7">
         <v>29</v>
       </c>
-      <c r="C162" s="135"/>
-      <c r="D162" s="135"/>
+      <c r="C162" s="164"/>
+      <c r="D162" s="156"/>
       <c r="E162" s="8" t="s">
         <v>217</v>
       </c>
@@ -8073,8 +8358,8 @@
       <c r="B163" s="7">
         <v>30</v>
       </c>
-      <c r="C163" s="135"/>
-      <c r="D163" s="135"/>
+      <c r="C163" s="164"/>
+      <c r="D163" s="156"/>
       <c r="E163" s="8" t="s">
         <v>218</v>
       </c>
@@ -8095,8 +8380,8 @@
       <c r="B164" s="7">
         <v>31</v>
       </c>
-      <c r="C164" s="135"/>
-      <c r="D164" s="135"/>
+      <c r="C164" s="164"/>
+      <c r="D164" s="156"/>
       <c r="E164" s="8" t="s">
         <v>219</v>
       </c>
@@ -8117,8 +8402,8 @@
       <c r="B165" s="7">
         <v>32</v>
       </c>
-      <c r="C165" s="135"/>
-      <c r="D165" s="136"/>
+      <c r="C165" s="164"/>
+      <c r="D165" s="157"/>
       <c r="E165" s="8" t="s">
         <v>220</v>
       </c>
@@ -8139,8 +8424,8 @@
       <c r="B166" s="7">
         <v>33</v>
       </c>
-      <c r="C166" s="135"/>
-      <c r="D166" s="143" t="s">
+      <c r="C166" s="164"/>
+      <c r="D166" s="135" t="s">
         <v>221</v>
       </c>
       <c r="E166" s="8" t="s">
@@ -8163,8 +8448,8 @@
       <c r="B167" s="7">
         <v>34</v>
       </c>
-      <c r="C167" s="135"/>
-      <c r="D167" s="135"/>
+      <c r="C167" s="164"/>
+      <c r="D167" s="156"/>
       <c r="E167" s="8" t="s">
         <v>223</v>
       </c>
@@ -8183,8 +8468,8 @@
       <c r="B168" s="7">
         <v>35</v>
       </c>
-      <c r="C168" s="135"/>
-      <c r="D168" s="135"/>
+      <c r="C168" s="164"/>
+      <c r="D168" s="156"/>
       <c r="E168" s="8" t="s">
         <v>224</v>
       </c>
@@ -8205,8 +8490,8 @@
       <c r="B169" s="7">
         <v>36</v>
       </c>
-      <c r="C169" s="135"/>
-      <c r="D169" s="135"/>
+      <c r="C169" s="164"/>
+      <c r="D169" s="156"/>
       <c r="E169" s="8" t="s">
         <v>225</v>
       </c>
@@ -8227,8 +8512,8 @@
       <c r="B170" s="7">
         <v>37</v>
       </c>
-      <c r="C170" s="135"/>
-      <c r="D170" s="135"/>
+      <c r="C170" s="164"/>
+      <c r="D170" s="156"/>
       <c r="E170" s="8" t="s">
         <v>226</v>
       </c>
@@ -8249,8 +8534,8 @@
       <c r="B171" s="7">
         <v>38</v>
       </c>
-      <c r="C171" s="135"/>
-      <c r="D171" s="135"/>
+      <c r="C171" s="164"/>
+      <c r="D171" s="156"/>
       <c r="E171" s="8" t="s">
         <v>227</v>
       </c>
@@ -8271,8 +8556,8 @@
       <c r="B172" s="7">
         <v>39</v>
       </c>
-      <c r="C172" s="135"/>
-      <c r="D172" s="136"/>
+      <c r="C172" s="164"/>
+      <c r="D172" s="157"/>
       <c r="E172" s="8" t="s">
         <v>228</v>
       </c>
@@ -8293,8 +8578,8 @@
       <c r="B173" s="7">
         <v>40</v>
       </c>
-      <c r="C173" s="135"/>
-      <c r="D173" s="143" t="s">
+      <c r="C173" s="164"/>
+      <c r="D173" s="135" t="s">
         <v>48</v>
       </c>
       <c r="E173" s="11" t="s">
@@ -8317,8 +8602,8 @@
       <c r="B174" s="7">
         <v>41</v>
       </c>
-      <c r="C174" s="135"/>
-      <c r="D174" s="135"/>
+      <c r="C174" s="164"/>
+      <c r="D174" s="156"/>
       <c r="E174" s="8" t="s">
         <v>230</v>
       </c>
@@ -8339,8 +8624,8 @@
       <c r="B175" s="7">
         <v>42</v>
       </c>
-      <c r="C175" s="135"/>
-      <c r="D175" s="135"/>
+      <c r="C175" s="164"/>
+      <c r="D175" s="156"/>
       <c r="E175" s="8" t="s">
         <v>231</v>
       </c>
@@ -8361,8 +8646,8 @@
       <c r="B176" s="24">
         <v>43</v>
       </c>
-      <c r="C176" s="136"/>
-      <c r="D176" s="136"/>
+      <c r="C176" s="165"/>
+      <c r="D176" s="157"/>
       <c r="E176" s="17" t="s">
         <v>232</v>
       </c>
@@ -8383,10 +8668,10 @@
       <c r="B177" s="7">
         <v>1</v>
       </c>
-      <c r="C177" s="139" t="s">
+      <c r="C177" s="138" t="s">
         <v>233</v>
       </c>
-      <c r="D177" s="143" t="s">
+      <c r="D177" s="135" t="s">
         <v>234</v>
       </c>
       <c r="E177" s="8" t="s">
@@ -8409,8 +8694,8 @@
       <c r="B178" s="7">
         <v>2</v>
       </c>
-      <c r="C178" s="135"/>
-      <c r="D178" s="136"/>
+      <c r="C178" s="158"/>
+      <c r="D178" s="157"/>
       <c r="E178" s="8" t="s">
         <v>236</v>
       </c>
@@ -8431,8 +8716,8 @@
       <c r="B179" s="7">
         <v>3</v>
       </c>
-      <c r="C179" s="135"/>
-      <c r="D179" s="143" t="s">
+      <c r="C179" s="158"/>
+      <c r="D179" s="135" t="s">
         <v>237</v>
       </c>
       <c r="E179" s="8" t="s">
@@ -8455,8 +8740,8 @@
       <c r="B180" s="7">
         <v>4</v>
       </c>
-      <c r="C180" s="135"/>
-      <c r="D180" s="135"/>
+      <c r="C180" s="158"/>
+      <c r="D180" s="156"/>
       <c r="E180" s="8" t="s">
         <v>239</v>
       </c>
@@ -8477,8 +8762,8 @@
       <c r="B181" s="7">
         <v>5</v>
       </c>
-      <c r="C181" s="135"/>
-      <c r="D181" s="135"/>
+      <c r="C181" s="158"/>
+      <c r="D181" s="156"/>
       <c r="E181" s="8" t="s">
         <v>240</v>
       </c>
@@ -8499,8 +8784,8 @@
       <c r="B182" s="7">
         <v>6</v>
       </c>
-      <c r="C182" s="135"/>
-      <c r="D182" s="135"/>
+      <c r="C182" s="158"/>
+      <c r="D182" s="156"/>
       <c r="E182" s="8" t="s">
         <v>241</v>
       </c>
@@ -8521,8 +8806,8 @@
       <c r="B183" s="7">
         <v>7</v>
       </c>
-      <c r="C183" s="135"/>
-      <c r="D183" s="135"/>
+      <c r="C183" s="158"/>
+      <c r="D183" s="156"/>
       <c r="E183" s="8" t="s">
         <v>242</v>
       </c>
@@ -8543,8 +8828,8 @@
       <c r="B184" s="7">
         <v>8</v>
       </c>
-      <c r="C184" s="135"/>
-      <c r="D184" s="136"/>
+      <c r="C184" s="158"/>
+      <c r="D184" s="157"/>
       <c r="E184" s="8" t="s">
         <v>243</v>
       </c>
@@ -8565,8 +8850,8 @@
       <c r="B185" s="7">
         <v>9</v>
       </c>
-      <c r="C185" s="135"/>
-      <c r="D185" s="143" t="s">
+      <c r="C185" s="158"/>
+      <c r="D185" s="135" t="s">
         <v>244</v>
       </c>
       <c r="E185" s="8" t="s">
@@ -8589,8 +8874,8 @@
       <c r="B186" s="7">
         <v>10</v>
       </c>
-      <c r="C186" s="135"/>
-      <c r="D186" s="136"/>
+      <c r="C186" s="158"/>
+      <c r="D186" s="157"/>
       <c r="E186" s="8" t="s">
         <v>246</v>
       </c>
@@ -8611,8 +8896,8 @@
       <c r="B187" s="7">
         <v>11</v>
       </c>
-      <c r="C187" s="135"/>
-      <c r="D187" s="143" t="s">
+      <c r="C187" s="158"/>
+      <c r="D187" s="135" t="s">
         <v>247</v>
       </c>
       <c r="E187" s="8" t="s">
@@ -8635,8 +8920,8 @@
       <c r="B188" s="7">
         <v>12</v>
       </c>
-      <c r="C188" s="135"/>
-      <c r="D188" s="135"/>
+      <c r="C188" s="158"/>
+      <c r="D188" s="156"/>
       <c r="E188" s="8" t="s">
         <v>249</v>
       </c>
@@ -8657,8 +8942,8 @@
       <c r="B189" s="7">
         <v>13</v>
       </c>
-      <c r="C189" s="135"/>
-      <c r="D189" s="135"/>
+      <c r="C189" s="158"/>
+      <c r="D189" s="156"/>
       <c r="E189" s="11" t="s">
         <v>250</v>
       </c>
@@ -8679,8 +8964,8 @@
       <c r="B190" s="7">
         <v>14</v>
       </c>
-      <c r="C190" s="135"/>
-      <c r="D190" s="136"/>
+      <c r="C190" s="158"/>
+      <c r="D190" s="157"/>
       <c r="E190" s="8" t="s">
         <v>251</v>
       </c>
@@ -8701,8 +8986,8 @@
       <c r="B191" s="7">
         <v>15</v>
       </c>
-      <c r="C191" s="135"/>
-      <c r="D191" s="143" t="s">
+      <c r="C191" s="158"/>
+      <c r="D191" s="135" t="s">
         <v>252</v>
       </c>
       <c r="E191" s="8" t="s">
@@ -8725,8 +9010,8 @@
       <c r="B192" s="7">
         <v>16</v>
       </c>
-      <c r="C192" s="135"/>
-      <c r="D192" s="135"/>
+      <c r="C192" s="158"/>
+      <c r="D192" s="156"/>
       <c r="E192" s="8" t="s">
         <v>254</v>
       </c>
@@ -8747,8 +9032,8 @@
       <c r="B193" s="7">
         <v>17</v>
       </c>
-      <c r="C193" s="135"/>
-      <c r="D193" s="135"/>
+      <c r="C193" s="158"/>
+      <c r="D193" s="156"/>
       <c r="E193" s="8" t="s">
         <v>255</v>
       </c>
@@ -8769,8 +9054,8 @@
       <c r="B194" s="7">
         <v>18</v>
       </c>
-      <c r="C194" s="135"/>
-      <c r="D194" s="135"/>
+      <c r="C194" s="158"/>
+      <c r="D194" s="156"/>
       <c r="E194" s="8" t="s">
         <v>256</v>
       </c>
@@ -8791,8 +9076,8 @@
       <c r="B195" s="7">
         <v>19</v>
       </c>
-      <c r="C195" s="135"/>
-      <c r="D195" s="135"/>
+      <c r="C195" s="158"/>
+      <c r="D195" s="156"/>
       <c r="E195" s="8" t="s">
         <v>257</v>
       </c>
@@ -8813,8 +9098,8 @@
       <c r="B196" s="7">
         <v>20</v>
       </c>
-      <c r="C196" s="135"/>
-      <c r="D196" s="135"/>
+      <c r="C196" s="158"/>
+      <c r="D196" s="156"/>
       <c r="E196" s="8" t="s">
         <v>258</v>
       </c>
@@ -8835,8 +9120,8 @@
       <c r="B197" s="7">
         <v>21</v>
       </c>
-      <c r="C197" s="135"/>
-      <c r="D197" s="135"/>
+      <c r="C197" s="158"/>
+      <c r="D197" s="156"/>
       <c r="E197" s="8" t="s">
         <v>259</v>
       </c>
@@ -8857,8 +9142,8 @@
       <c r="B198" s="7">
         <v>22</v>
       </c>
-      <c r="C198" s="135"/>
-      <c r="D198" s="136"/>
+      <c r="C198" s="158"/>
+      <c r="D198" s="157"/>
       <c r="E198" s="8" t="s">
         <v>260</v>
       </c>
@@ -8879,8 +9164,8 @@
       <c r="B199" s="7">
         <v>23</v>
       </c>
-      <c r="C199" s="135"/>
-      <c r="D199" s="143" t="s">
+      <c r="C199" s="158"/>
+      <c r="D199" s="135" t="s">
         <v>261</v>
       </c>
       <c r="E199" s="8" t="s">
@@ -8903,8 +9188,8 @@
       <c r="B200" s="7">
         <v>24</v>
       </c>
-      <c r="C200" s="135"/>
-      <c r="D200" s="135"/>
+      <c r="C200" s="158"/>
+      <c r="D200" s="156"/>
       <c r="E200" s="8" t="s">
         <v>263</v>
       </c>
@@ -8925,8 +9210,8 @@
       <c r="B201" s="7">
         <v>25</v>
       </c>
-      <c r="C201" s="135"/>
-      <c r="D201" s="135"/>
+      <c r="C201" s="158"/>
+      <c r="D201" s="156"/>
       <c r="E201" s="8" t="s">
         <v>264</v>
       </c>
@@ -8947,8 +9232,8 @@
       <c r="B202" s="7">
         <v>26</v>
       </c>
-      <c r="C202" s="135"/>
-      <c r="D202" s="136"/>
+      <c r="C202" s="158"/>
+      <c r="D202" s="157"/>
       <c r="E202" s="8" t="s">
         <v>265</v>
       </c>
@@ -8969,8 +9254,8 @@
       <c r="B203" s="7">
         <v>27</v>
       </c>
-      <c r="C203" s="135"/>
-      <c r="D203" s="143" t="s">
+      <c r="C203" s="158"/>
+      <c r="D203" s="135" t="s">
         <v>266</v>
       </c>
       <c r="E203" s="8" t="s">
@@ -8993,8 +9278,8 @@
       <c r="B204" s="24">
         <v>28</v>
       </c>
-      <c r="C204" s="136"/>
-      <c r="D204" s="136"/>
+      <c r="C204" s="159"/>
+      <c r="D204" s="157"/>
       <c r="E204" s="17" t="s">
         <v>268</v>
       </c>
@@ -9015,10 +9300,10 @@
       <c r="B205" s="7">
         <v>1</v>
       </c>
-      <c r="C205" s="134" t="s">
+      <c r="C205" s="139" t="s">
         <v>269</v>
       </c>
-      <c r="D205" s="143" t="s">
+      <c r="D205" s="135" t="s">
         <v>270</v>
       </c>
       <c r="E205" s="8" t="s">
@@ -9041,8 +9326,8 @@
       <c r="B206" s="7">
         <v>2</v>
       </c>
-      <c r="C206" s="135"/>
-      <c r="D206" s="135"/>
+      <c r="C206" s="160"/>
+      <c r="D206" s="156"/>
       <c r="E206" s="8" t="s">
         <v>272</v>
       </c>
@@ -9063,8 +9348,8 @@
       <c r="B207" s="7">
         <v>3</v>
       </c>
-      <c r="C207" s="135"/>
-      <c r="D207" s="135"/>
+      <c r="C207" s="160"/>
+      <c r="D207" s="156"/>
       <c r="E207" s="8" t="s">
         <v>273</v>
       </c>
@@ -9085,8 +9370,8 @@
       <c r="B208" s="7">
         <v>4</v>
       </c>
-      <c r="C208" s="135"/>
-      <c r="D208" s="135"/>
+      <c r="C208" s="160"/>
+      <c r="D208" s="156"/>
       <c r="E208" s="8" t="s">
         <v>274</v>
       </c>
@@ -9107,8 +9392,8 @@
       <c r="B209" s="7">
         <v>5</v>
       </c>
-      <c r="C209" s="135"/>
-      <c r="D209" s="136"/>
+      <c r="C209" s="160"/>
+      <c r="D209" s="157"/>
       <c r="E209" s="8" t="s">
         <v>275</v>
       </c>
@@ -9129,8 +9414,8 @@
       <c r="B210" s="7">
         <v>6</v>
       </c>
-      <c r="C210" s="135"/>
-      <c r="D210" s="143" t="s">
+      <c r="C210" s="160"/>
+      <c r="D210" s="135" t="s">
         <v>276</v>
       </c>
       <c r="E210" s="8" t="s">
@@ -9153,8 +9438,8 @@
       <c r="B211" s="7">
         <v>7</v>
       </c>
-      <c r="C211" s="135"/>
-      <c r="D211" s="136"/>
+      <c r="C211" s="160"/>
+      <c r="D211" s="157"/>
       <c r="E211" s="8" t="s">
         <v>278</v>
       </c>
@@ -9175,8 +9460,8 @@
       <c r="B212" s="7">
         <v>8</v>
       </c>
-      <c r="C212" s="135"/>
-      <c r="D212" s="143" t="s">
+      <c r="C212" s="160"/>
+      <c r="D212" s="135" t="s">
         <v>279</v>
       </c>
       <c r="E212" s="8" t="s">
@@ -9199,8 +9484,8 @@
       <c r="B213" s="7">
         <v>9</v>
       </c>
-      <c r="C213" s="135"/>
-      <c r="D213" s="135"/>
+      <c r="C213" s="160"/>
+      <c r="D213" s="156"/>
       <c r="E213" s="8" t="s">
         <v>281</v>
       </c>
@@ -9221,8 +9506,8 @@
       <c r="B214" s="7">
         <v>10</v>
       </c>
-      <c r="C214" s="136"/>
-      <c r="D214" s="136"/>
+      <c r="C214" s="161"/>
+      <c r="D214" s="157"/>
       <c r="E214" s="8" t="s">
         <v>282</v>
       </c>
@@ -9237,18 +9522,18 @@
       <c r="J214" s="11"/>
     </row>
     <row r="215" spans="1:10" ht="13.8">
-      <c r="A215" s="148" t="s">
+      <c r="A215" s="146" t="s">
         <v>283</v>
       </c>
-      <c r="B215" s="146"/>
-      <c r="C215" s="146"/>
-      <c r="D215" s="146"/>
-      <c r="E215" s="146"/>
-      <c r="F215" s="146"/>
-      <c r="G215" s="146"/>
-      <c r="H215" s="146"/>
-      <c r="I215" s="146"/>
-      <c r="J215" s="147"/>
+      <c r="B215" s="180"/>
+      <c r="C215" s="180"/>
+      <c r="D215" s="180"/>
+      <c r="E215" s="180"/>
+      <c r="F215" s="180"/>
+      <c r="G215" s="180"/>
+      <c r="H215" s="180"/>
+      <c r="I215" s="180"/>
+      <c r="J215" s="181"/>
     </row>
     <row r="216" spans="1:10" ht="13.8">
       <c r="A216" s="6">
@@ -9257,10 +9542,10 @@
       <c r="B216" s="7">
         <v>1</v>
       </c>
-      <c r="C216" s="137" t="s">
+      <c r="C216" s="140" t="s">
         <v>284</v>
       </c>
-      <c r="D216" s="143" t="s">
+      <c r="D216" s="135" t="s">
         <v>285</v>
       </c>
       <c r="E216" s="8" t="s">
@@ -9283,8 +9568,8 @@
       <c r="B217" s="7">
         <v>2</v>
       </c>
-      <c r="C217" s="135"/>
-      <c r="D217" s="135"/>
+      <c r="C217" s="166"/>
+      <c r="D217" s="156"/>
       <c r="E217" s="8" t="s">
         <v>287</v>
       </c>
@@ -9305,8 +9590,8 @@
       <c r="B218" s="7">
         <v>3</v>
       </c>
-      <c r="C218" s="135"/>
-      <c r="D218" s="135"/>
+      <c r="C218" s="166"/>
+      <c r="D218" s="156"/>
       <c r="E218" s="8" t="s">
         <v>288</v>
       </c>
@@ -9327,8 +9612,8 @@
       <c r="B219" s="7">
         <v>4</v>
       </c>
-      <c r="C219" s="135"/>
-      <c r="D219" s="135"/>
+      <c r="C219" s="166"/>
+      <c r="D219" s="156"/>
       <c r="E219" s="8" t="s">
         <v>289</v>
       </c>
@@ -9349,8 +9634,8 @@
       <c r="B220" s="7">
         <v>5</v>
       </c>
-      <c r="C220" s="135"/>
-      <c r="D220" s="135"/>
+      <c r="C220" s="166"/>
+      <c r="D220" s="156"/>
       <c r="E220" s="8" t="s">
         <v>290</v>
       </c>
@@ -9371,8 +9656,8 @@
       <c r="B221" s="7">
         <v>6</v>
       </c>
-      <c r="C221" s="135"/>
-      <c r="D221" s="135"/>
+      <c r="C221" s="166"/>
+      <c r="D221" s="156"/>
       <c r="E221" s="8" t="s">
         <v>291</v>
       </c>
@@ -9393,8 +9678,8 @@
       <c r="B222" s="7">
         <v>7</v>
       </c>
-      <c r="C222" s="135"/>
-      <c r="D222" s="135"/>
+      <c r="C222" s="166"/>
+      <c r="D222" s="156"/>
       <c r="E222" s="8" t="s">
         <v>292</v>
       </c>
@@ -9415,8 +9700,8 @@
       <c r="B223" s="7">
         <v>8</v>
       </c>
-      <c r="C223" s="135"/>
-      <c r="D223" s="135"/>
+      <c r="C223" s="166"/>
+      <c r="D223" s="156"/>
       <c r="E223" s="8" t="s">
         <v>293</v>
       </c>
@@ -9437,8 +9722,8 @@
       <c r="B224" s="7">
         <v>9</v>
       </c>
-      <c r="C224" s="135"/>
-      <c r="D224" s="135"/>
+      <c r="C224" s="166"/>
+      <c r="D224" s="156"/>
       <c r="E224" s="8" t="s">
         <v>294</v>
       </c>
@@ -9459,8 +9744,8 @@
       <c r="B225" s="7">
         <v>10</v>
       </c>
-      <c r="C225" s="135"/>
-      <c r="D225" s="136"/>
+      <c r="C225" s="166"/>
+      <c r="D225" s="157"/>
       <c r="E225" s="8" t="s">
         <v>295</v>
       </c>
@@ -9481,8 +9766,8 @@
       <c r="B226" s="7">
         <v>11</v>
       </c>
-      <c r="C226" s="135"/>
-      <c r="D226" s="143" t="s">
+      <c r="C226" s="166"/>
+      <c r="D226" s="135" t="s">
         <v>296</v>
       </c>
       <c r="E226" s="8" t="s">
@@ -9505,8 +9790,8 @@
       <c r="B227" s="7">
         <v>12</v>
       </c>
-      <c r="C227" s="135"/>
-      <c r="D227" s="135"/>
+      <c r="C227" s="166"/>
+      <c r="D227" s="156"/>
       <c r="E227" s="8" t="s">
         <v>298</v>
       </c>
@@ -9527,8 +9812,8 @@
       <c r="B228" s="7">
         <v>13</v>
       </c>
-      <c r="C228" s="135"/>
-      <c r="D228" s="135"/>
+      <c r="C228" s="166"/>
+      <c r="D228" s="156"/>
       <c r="E228" s="8" t="s">
         <v>299</v>
       </c>
@@ -9549,8 +9834,8 @@
       <c r="B229" s="7">
         <v>14</v>
       </c>
-      <c r="C229" s="135"/>
-      <c r="D229" s="135"/>
+      <c r="C229" s="166"/>
+      <c r="D229" s="156"/>
       <c r="E229" s="8" t="s">
         <v>300</v>
       </c>
@@ -9571,8 +9856,8 @@
       <c r="B230" s="7">
         <v>15</v>
       </c>
-      <c r="C230" s="135"/>
-      <c r="D230" s="135"/>
+      <c r="C230" s="166"/>
+      <c r="D230" s="156"/>
       <c r="E230" s="8" t="s">
         <v>301</v>
       </c>
@@ -9593,8 +9878,8 @@
       <c r="B231" s="7">
         <v>16</v>
       </c>
-      <c r="C231" s="135"/>
-      <c r="D231" s="135"/>
+      <c r="C231" s="166"/>
+      <c r="D231" s="156"/>
       <c r="E231" s="8" t="s">
         <v>302</v>
       </c>
@@ -9615,8 +9900,8 @@
       <c r="B232" s="7">
         <v>17</v>
       </c>
-      <c r="C232" s="135"/>
-      <c r="D232" s="135"/>
+      <c r="C232" s="166"/>
+      <c r="D232" s="156"/>
       <c r="E232" s="8" t="s">
         <v>303</v>
       </c>
@@ -9637,8 +9922,8 @@
       <c r="B233" s="7">
         <v>18</v>
       </c>
-      <c r="C233" s="135"/>
-      <c r="D233" s="136"/>
+      <c r="C233" s="166"/>
+      <c r="D233" s="157"/>
       <c r="E233" s="8" t="s">
         <v>304</v>
       </c>
@@ -9659,8 +9944,8 @@
       <c r="B234" s="7">
         <v>19</v>
       </c>
-      <c r="C234" s="135"/>
-      <c r="D234" s="143" t="s">
+      <c r="C234" s="166"/>
+      <c r="D234" s="135" t="s">
         <v>305</v>
       </c>
       <c r="E234" s="8" t="s">
@@ -9683,8 +9968,8 @@
       <c r="B235" s="7">
         <v>20</v>
       </c>
-      <c r="C235" s="135"/>
-      <c r="D235" s="135"/>
+      <c r="C235" s="166"/>
+      <c r="D235" s="156"/>
       <c r="E235" s="8" t="s">
         <v>307</v>
       </c>
@@ -9705,8 +9990,8 @@
       <c r="B236" s="7">
         <v>21</v>
       </c>
-      <c r="C236" s="135"/>
-      <c r="D236" s="135"/>
+      <c r="C236" s="166"/>
+      <c r="D236" s="156"/>
       <c r="E236" s="8" t="s">
         <v>308</v>
       </c>
@@ -9727,8 +10012,8 @@
       <c r="B237" s="7">
         <v>22</v>
       </c>
-      <c r="C237" s="135"/>
-      <c r="D237" s="135"/>
+      <c r="C237" s="166"/>
+      <c r="D237" s="156"/>
       <c r="E237" s="8" t="s">
         <v>309</v>
       </c>
@@ -9749,8 +10034,8 @@
       <c r="B238" s="7">
         <v>23</v>
       </c>
-      <c r="C238" s="135"/>
-      <c r="D238" s="135"/>
+      <c r="C238" s="166"/>
+      <c r="D238" s="156"/>
       <c r="E238" s="8" t="s">
         <v>310</v>
       </c>
@@ -9771,8 +10056,8 @@
       <c r="B239" s="7">
         <v>24</v>
       </c>
-      <c r="C239" s="135"/>
-      <c r="D239" s="135"/>
+      <c r="C239" s="166"/>
+      <c r="D239" s="156"/>
       <c r="E239" s="8" t="s">
         <v>311</v>
       </c>
@@ -9793,8 +10078,8 @@
       <c r="B240" s="7">
         <v>25</v>
       </c>
-      <c r="C240" s="135"/>
-      <c r="D240" s="136"/>
+      <c r="C240" s="166"/>
+      <c r="D240" s="157"/>
       <c r="E240" s="8" t="s">
         <v>312</v>
       </c>
@@ -9815,8 +10100,8 @@
       <c r="B241" s="7">
         <v>26</v>
       </c>
-      <c r="C241" s="135"/>
-      <c r="D241" s="143" t="s">
+      <c r="C241" s="166"/>
+      <c r="D241" s="135" t="s">
         <v>313</v>
       </c>
       <c r="E241" s="8" t="s">
@@ -9839,8 +10124,8 @@
       <c r="B242" s="7">
         <v>27</v>
       </c>
-      <c r="C242" s="135"/>
-      <c r="D242" s="135"/>
+      <c r="C242" s="166"/>
+      <c r="D242" s="156"/>
       <c r="E242" s="8" t="s">
         <v>315</v>
       </c>
@@ -9861,8 +10146,8 @@
       <c r="B243" s="7">
         <v>28</v>
       </c>
-      <c r="C243" s="135"/>
-      <c r="D243" s="136"/>
+      <c r="C243" s="166"/>
+      <c r="D243" s="157"/>
       <c r="E243" s="8" t="s">
         <v>316</v>
       </c>
@@ -9883,8 +10168,8 @@
       <c r="B244" s="7">
         <v>29</v>
       </c>
-      <c r="C244" s="135"/>
-      <c r="D244" s="143" t="s">
+      <c r="C244" s="166"/>
+      <c r="D244" s="135" t="s">
         <v>317</v>
       </c>
       <c r="E244" s="8" t="s">
@@ -9907,8 +10192,8 @@
       <c r="B245" s="7">
         <v>30</v>
       </c>
-      <c r="C245" s="135"/>
-      <c r="D245" s="135"/>
+      <c r="C245" s="166"/>
+      <c r="D245" s="156"/>
       <c r="E245" s="8" t="s">
         <v>319</v>
       </c>
@@ -9929,8 +10214,8 @@
       <c r="B246" s="7">
         <v>31</v>
       </c>
-      <c r="C246" s="135"/>
-      <c r="D246" s="135"/>
+      <c r="C246" s="166"/>
+      <c r="D246" s="156"/>
       <c r="E246" s="8" t="s">
         <v>320</v>
       </c>
@@ -9951,8 +10236,8 @@
       <c r="B247" s="7">
         <v>32</v>
       </c>
-      <c r="C247" s="135"/>
-      <c r="D247" s="135"/>
+      <c r="C247" s="166"/>
+      <c r="D247" s="156"/>
       <c r="E247" s="8" t="s">
         <v>321</v>
       </c>
@@ -9973,8 +10258,8 @@
       <c r="B248" s="7">
         <v>33</v>
       </c>
-      <c r="C248" s="135"/>
-      <c r="D248" s="135"/>
+      <c r="C248" s="166"/>
+      <c r="D248" s="156"/>
       <c r="E248" s="8" t="s">
         <v>322</v>
       </c>
@@ -9995,8 +10280,8 @@
       <c r="B249" s="24">
         <v>34</v>
       </c>
-      <c r="C249" s="136"/>
-      <c r="D249" s="136"/>
+      <c r="C249" s="167"/>
+      <c r="D249" s="157"/>
       <c r="E249" s="17" t="s">
         <v>323</v>
       </c>
@@ -10017,10 +10302,10 @@
       <c r="B250" s="7">
         <v>1</v>
       </c>
-      <c r="C250" s="138" t="s">
+      <c r="C250" s="137" t="s">
         <v>324</v>
       </c>
-      <c r="D250" s="143" t="s">
+      <c r="D250" s="135" t="s">
         <v>325</v>
       </c>
       <c r="E250" s="8" t="s">
@@ -10043,8 +10328,8 @@
       <c r="B251" s="7">
         <v>2</v>
       </c>
-      <c r="C251" s="135"/>
-      <c r="D251" s="135"/>
+      <c r="C251" s="164"/>
+      <c r="D251" s="156"/>
       <c r="E251" s="8" t="s">
         <v>327</v>
       </c>
@@ -10065,8 +10350,8 @@
       <c r="B252" s="7">
         <v>3</v>
       </c>
-      <c r="C252" s="135"/>
-      <c r="D252" s="135"/>
+      <c r="C252" s="164"/>
+      <c r="D252" s="156"/>
       <c r="E252" s="8" t="s">
         <v>328</v>
       </c>
@@ -10087,8 +10372,8 @@
       <c r="B253" s="7">
         <v>4</v>
       </c>
-      <c r="C253" s="135"/>
-      <c r="D253" s="135"/>
+      <c r="C253" s="164"/>
+      <c r="D253" s="156"/>
       <c r="E253" s="8" t="s">
         <v>329</v>
       </c>
@@ -10109,8 +10394,8 @@
       <c r="B254" s="7">
         <v>5</v>
       </c>
-      <c r="C254" s="135"/>
-      <c r="D254" s="135"/>
+      <c r="C254" s="164"/>
+      <c r="D254" s="156"/>
       <c r="E254" s="8" t="s">
         <v>330</v>
       </c>
@@ -10131,8 +10416,8 @@
       <c r="B255" s="7">
         <v>6</v>
       </c>
-      <c r="C255" s="135"/>
-      <c r="D255" s="135"/>
+      <c r="C255" s="164"/>
+      <c r="D255" s="156"/>
       <c r="E255" s="8" t="s">
         <v>331</v>
       </c>
@@ -10153,8 +10438,8 @@
       <c r="B256" s="7">
         <v>7</v>
       </c>
-      <c r="C256" s="135"/>
-      <c r="D256" s="135"/>
+      <c r="C256" s="164"/>
+      <c r="D256" s="156"/>
       <c r="E256" s="8" t="s">
         <v>332</v>
       </c>
@@ -10175,8 +10460,8 @@
       <c r="B257" s="7">
         <v>8</v>
       </c>
-      <c r="C257" s="135"/>
-      <c r="D257" s="136"/>
+      <c r="C257" s="164"/>
+      <c r="D257" s="157"/>
       <c r="E257" s="8" t="s">
         <v>333</v>
       </c>
@@ -10197,8 +10482,8 @@
       <c r="B258" s="7">
         <v>9</v>
       </c>
-      <c r="C258" s="135"/>
-      <c r="D258" s="143" t="s">
+      <c r="C258" s="164"/>
+      <c r="D258" s="135" t="s">
         <v>334</v>
       </c>
       <c r="E258" s="8" t="s">
@@ -10221,8 +10506,8 @@
       <c r="B259" s="7">
         <v>10</v>
       </c>
-      <c r="C259" s="135"/>
-      <c r="D259" s="136"/>
+      <c r="C259" s="164"/>
+      <c r="D259" s="157"/>
       <c r="E259" s="8" t="s">
         <v>336</v>
       </c>
@@ -10243,8 +10528,8 @@
       <c r="B260" s="7">
         <v>11</v>
       </c>
-      <c r="C260" s="135"/>
-      <c r="D260" s="143" t="s">
+      <c r="C260" s="164"/>
+      <c r="D260" s="135" t="s">
         <v>337</v>
       </c>
       <c r="E260" s="8" t="s">
@@ -10267,8 +10552,8 @@
       <c r="B261" s="7">
         <v>12</v>
       </c>
-      <c r="C261" s="135"/>
-      <c r="D261" s="135"/>
+      <c r="C261" s="164"/>
+      <c r="D261" s="156"/>
       <c r="E261" s="8" t="s">
         <v>339</v>
       </c>
@@ -10289,8 +10574,8 @@
       <c r="B262" s="7">
         <v>13</v>
       </c>
-      <c r="C262" s="135"/>
-      <c r="D262" s="135"/>
+      <c r="C262" s="164"/>
+      <c r="D262" s="156"/>
       <c r="E262" s="8" t="s">
         <v>340</v>
       </c>
@@ -10311,8 +10596,8 @@
       <c r="B263" s="7">
         <v>14</v>
       </c>
-      <c r="C263" s="135"/>
-      <c r="D263" s="135"/>
+      <c r="C263" s="164"/>
+      <c r="D263" s="156"/>
       <c r="E263" s="8" t="s">
         <v>341</v>
       </c>
@@ -10333,8 +10618,8 @@
       <c r="B264" s="7">
         <v>15</v>
       </c>
-      <c r="C264" s="135"/>
-      <c r="D264" s="135"/>
+      <c r="C264" s="164"/>
+      <c r="D264" s="156"/>
       <c r="E264" s="8" t="s">
         <v>342</v>
       </c>
@@ -10355,8 +10640,8 @@
       <c r="B265" s="24">
         <v>16</v>
       </c>
-      <c r="C265" s="136"/>
-      <c r="D265" s="136"/>
+      <c r="C265" s="165"/>
+      <c r="D265" s="157"/>
       <c r="E265" s="17" t="s">
         <v>343</v>
       </c>
@@ -10377,10 +10662,10 @@
       <c r="B266" s="7">
         <v>1</v>
       </c>
-      <c r="C266" s="139" t="s">
+      <c r="C266" s="138" t="s">
         <v>344</v>
       </c>
-      <c r="D266" s="143" t="s">
+      <c r="D266" s="135" t="s">
         <v>345</v>
       </c>
       <c r="E266" s="8" t="s">
@@ -10403,8 +10688,8 @@
       <c r="B267" s="7">
         <v>2</v>
       </c>
-      <c r="C267" s="135"/>
-      <c r="D267" s="135"/>
+      <c r="C267" s="158"/>
+      <c r="D267" s="156"/>
       <c r="E267" s="8" t="s">
         <v>347</v>
       </c>
@@ -10425,8 +10710,8 @@
       <c r="B268" s="7">
         <v>3</v>
       </c>
-      <c r="C268" s="135"/>
-      <c r="D268" s="135"/>
+      <c r="C268" s="158"/>
+      <c r="D268" s="156"/>
       <c r="E268" s="8" t="s">
         <v>348</v>
       </c>
@@ -10447,8 +10732,8 @@
       <c r="B269" s="7">
         <v>4</v>
       </c>
-      <c r="C269" s="135"/>
-      <c r="D269" s="135"/>
+      <c r="C269" s="158"/>
+      <c r="D269" s="156"/>
       <c r="E269" s="8" t="s">
         <v>349</v>
       </c>
@@ -10469,8 +10754,8 @@
       <c r="B270" s="7">
         <v>5</v>
       </c>
-      <c r="C270" s="135"/>
-      <c r="D270" s="136"/>
+      <c r="C270" s="158"/>
+      <c r="D270" s="157"/>
       <c r="E270" s="8" t="s">
         <v>350</v>
       </c>
@@ -10491,8 +10776,8 @@
       <c r="B271" s="7">
         <v>6</v>
       </c>
-      <c r="C271" s="135"/>
-      <c r="D271" s="143" t="s">
+      <c r="C271" s="158"/>
+      <c r="D271" s="135" t="s">
         <v>351</v>
       </c>
       <c r="E271" s="8" t="s">
@@ -10515,8 +10800,8 @@
       <c r="B272" s="7">
         <v>7</v>
       </c>
-      <c r="C272" s="136"/>
-      <c r="D272" s="136"/>
+      <c r="C272" s="159"/>
+      <c r="D272" s="157"/>
       <c r="E272" s="8" t="s">
         <v>353</v>
       </c>
@@ -10531,18 +10816,18 @@
       <c r="J272" s="11"/>
     </row>
     <row r="273" spans="1:10" ht="13.8">
-      <c r="A273" s="149" t="s">
+      <c r="A273" s="145" t="s">
         <v>354</v>
       </c>
-      <c r="B273" s="146"/>
-      <c r="C273" s="146"/>
-      <c r="D273" s="146"/>
-      <c r="E273" s="146"/>
-      <c r="F273" s="146"/>
-      <c r="G273" s="146"/>
-      <c r="H273" s="146"/>
-      <c r="I273" s="146"/>
-      <c r="J273" s="147"/>
+      <c r="B273" s="178"/>
+      <c r="C273" s="178"/>
+      <c r="D273" s="178"/>
+      <c r="E273" s="178"/>
+      <c r="F273" s="178"/>
+      <c r="G273" s="178"/>
+      <c r="H273" s="178"/>
+      <c r="I273" s="178"/>
+      <c r="J273" s="179"/>
     </row>
     <row r="274" spans="1:10" ht="13.8">
       <c r="A274" s="33">
@@ -10551,7 +10836,7 @@
       <c r="B274" s="7">
         <v>1</v>
       </c>
-      <c r="C274" s="140" t="s">
+      <c r="C274" s="143" t="s">
         <v>355</v>
       </c>
       <c r="D274" s="144" t="s">
@@ -10577,8 +10862,8 @@
       <c r="B275" s="7">
         <v>2</v>
       </c>
-      <c r="C275" s="135"/>
-      <c r="D275" s="135"/>
+      <c r="C275" s="176"/>
+      <c r="D275" s="170"/>
       <c r="E275" s="13" t="s">
         <v>358</v>
       </c>
@@ -10599,8 +10884,8 @@
       <c r="B276" s="7">
         <v>3</v>
       </c>
-      <c r="C276" s="135"/>
-      <c r="D276" s="135"/>
+      <c r="C276" s="176"/>
+      <c r="D276" s="170"/>
       <c r="E276" s="8" t="s">
         <v>359</v>
       </c>
@@ -10621,8 +10906,8 @@
       <c r="B277" s="7">
         <v>4</v>
       </c>
-      <c r="C277" s="135"/>
-      <c r="D277" s="135"/>
+      <c r="C277" s="176"/>
+      <c r="D277" s="170"/>
       <c r="E277" s="8" t="s">
         <v>360</v>
       </c>
@@ -10643,8 +10928,8 @@
       <c r="B278" s="7">
         <v>5</v>
       </c>
-      <c r="C278" s="135"/>
-      <c r="D278" s="135"/>
+      <c r="C278" s="176"/>
+      <c r="D278" s="170"/>
       <c r="E278" s="8" t="s">
         <v>361</v>
       </c>
@@ -10665,8 +10950,8 @@
       <c r="B279" s="7">
         <v>6</v>
       </c>
-      <c r="C279" s="135"/>
-      <c r="D279" s="135"/>
+      <c r="C279" s="176"/>
+      <c r="D279" s="170"/>
       <c r="E279" s="8" t="s">
         <v>362</v>
       </c>
@@ -10687,8 +10972,8 @@
       <c r="B280" s="7">
         <v>7</v>
       </c>
-      <c r="C280" s="135"/>
-      <c r="D280" s="135"/>
+      <c r="C280" s="176"/>
+      <c r="D280" s="170"/>
       <c r="E280" s="8" t="s">
         <v>363</v>
       </c>
@@ -10709,8 +10994,8 @@
       <c r="B281" s="7">
         <v>8</v>
       </c>
-      <c r="C281" s="135"/>
-      <c r="D281" s="136"/>
+      <c r="C281" s="176"/>
+      <c r="D281" s="171"/>
       <c r="E281" s="13" t="s">
         <v>364</v>
       </c>
@@ -10731,7 +11016,7 @@
       <c r="B282" s="7">
         <v>9</v>
       </c>
-      <c r="C282" s="135"/>
+      <c r="C282" s="176"/>
       <c r="D282" s="144" t="s">
         <v>365</v>
       </c>
@@ -10755,8 +11040,8 @@
       <c r="B283" s="7">
         <v>10</v>
       </c>
-      <c r="C283" s="135"/>
-      <c r="D283" s="135"/>
+      <c r="C283" s="176"/>
+      <c r="D283" s="170"/>
       <c r="E283" s="13" t="s">
         <v>367</v>
       </c>
@@ -10777,8 +11062,8 @@
       <c r="B284" s="7">
         <v>11</v>
       </c>
-      <c r="C284" s="135"/>
-      <c r="D284" s="135"/>
+      <c r="C284" s="176"/>
+      <c r="D284" s="170"/>
       <c r="E284" s="13" t="s">
         <v>368</v>
       </c>
@@ -10799,8 +11084,8 @@
       <c r="B285" s="7">
         <v>12</v>
       </c>
-      <c r="C285" s="135"/>
-      <c r="D285" s="135"/>
+      <c r="C285" s="176"/>
+      <c r="D285" s="170"/>
       <c r="E285" s="13" t="s">
         <v>369</v>
       </c>
@@ -10821,8 +11106,8 @@
       <c r="B286" s="7">
         <v>13</v>
       </c>
-      <c r="C286" s="135"/>
-      <c r="D286" s="135"/>
+      <c r="C286" s="176"/>
+      <c r="D286" s="170"/>
       <c r="E286" s="13" t="s">
         <v>370</v>
       </c>
@@ -10843,8 +11128,8 @@
       <c r="B287" s="7">
         <v>14</v>
       </c>
-      <c r="C287" s="135"/>
-      <c r="D287" s="135"/>
+      <c r="C287" s="176"/>
+      <c r="D287" s="170"/>
       <c r="E287" s="13" t="s">
         <v>371</v>
       </c>
@@ -10865,8 +11150,8 @@
       <c r="B288" s="7">
         <v>15</v>
       </c>
-      <c r="C288" s="135"/>
-      <c r="D288" s="136"/>
+      <c r="C288" s="176"/>
+      <c r="D288" s="171"/>
       <c r="E288" s="13" t="s">
         <v>372</v>
       </c>
@@ -10887,7 +11172,7 @@
       <c r="B289" s="7">
         <v>16</v>
       </c>
-      <c r="C289" s="135"/>
+      <c r="C289" s="176"/>
       <c r="D289" s="144" t="s">
         <v>373</v>
       </c>
@@ -10911,8 +11196,8 @@
       <c r="B290" s="7">
         <v>17</v>
       </c>
-      <c r="C290" s="135"/>
-      <c r="D290" s="135"/>
+      <c r="C290" s="176"/>
+      <c r="D290" s="170"/>
       <c r="E290" s="8" t="s">
         <v>375</v>
       </c>
@@ -10933,8 +11218,8 @@
       <c r="B291" s="7">
         <v>18</v>
       </c>
-      <c r="C291" s="135"/>
-      <c r="D291" s="135"/>
+      <c r="C291" s="176"/>
+      <c r="D291" s="170"/>
       <c r="E291" s="11" t="s">
         <v>376</v>
       </c>
@@ -10955,8 +11240,8 @@
       <c r="B292" s="24">
         <v>19</v>
       </c>
-      <c r="C292" s="136"/>
-      <c r="D292" s="136"/>
+      <c r="C292" s="177"/>
+      <c r="D292" s="171"/>
       <c r="E292" s="20" t="s">
         <v>377</v>
       </c>
@@ -10977,10 +11262,10 @@
       <c r="B293" s="7">
         <v>1</v>
       </c>
-      <c r="C293" s="137" t="s">
+      <c r="C293" s="140" t="s">
         <v>378</v>
       </c>
-      <c r="D293" s="143" t="s">
+      <c r="D293" s="135" t="s">
         <v>379</v>
       </c>
       <c r="E293" s="8" t="s">
@@ -11003,8 +11288,8 @@
       <c r="B294" s="7">
         <v>2</v>
       </c>
-      <c r="C294" s="135"/>
-      <c r="D294" s="135"/>
+      <c r="C294" s="166"/>
+      <c r="D294" s="156"/>
       <c r="E294" s="8" t="s">
         <v>381</v>
       </c>
@@ -11025,8 +11310,8 @@
       <c r="B295" s="7">
         <v>3</v>
       </c>
-      <c r="C295" s="135"/>
-      <c r="D295" s="136"/>
+      <c r="C295" s="166"/>
+      <c r="D295" s="157"/>
       <c r="E295" s="8" t="s">
         <v>382</v>
       </c>
@@ -11045,8 +11330,8 @@
       <c r="B296" s="7">
         <v>4</v>
       </c>
-      <c r="C296" s="135"/>
-      <c r="D296" s="143" t="s">
+      <c r="C296" s="166"/>
+      <c r="D296" s="135" t="s">
         <v>383</v>
       </c>
       <c r="E296" s="37" t="s">
@@ -11069,8 +11354,8 @@
       <c r="B297" s="7">
         <v>5</v>
       </c>
-      <c r="C297" s="135"/>
-      <c r="D297" s="135"/>
+      <c r="C297" s="166"/>
+      <c r="D297" s="156"/>
       <c r="E297" s="8" t="s">
         <v>385</v>
       </c>
@@ -11091,8 +11376,8 @@
       <c r="B298" s="7">
         <v>6</v>
       </c>
-      <c r="C298" s="135"/>
-      <c r="D298" s="135"/>
+      <c r="C298" s="166"/>
+      <c r="D298" s="156"/>
       <c r="E298" s="8" t="s">
         <v>386</v>
       </c>
@@ -11113,8 +11398,8 @@
       <c r="B299" s="7">
         <v>7</v>
       </c>
-      <c r="C299" s="135"/>
-      <c r="D299" s="135"/>
+      <c r="C299" s="166"/>
+      <c r="D299" s="156"/>
       <c r="E299" s="8" t="s">
         <v>387</v>
       </c>
@@ -11135,8 +11420,8 @@
       <c r="B300" s="7">
         <v>8</v>
       </c>
-      <c r="C300" s="135"/>
-      <c r="D300" s="136"/>
+      <c r="C300" s="166"/>
+      <c r="D300" s="157"/>
       <c r="E300" s="8" t="s">
         <v>388</v>
       </c>
@@ -11157,8 +11442,8 @@
       <c r="B301" s="7">
         <v>9</v>
       </c>
-      <c r="C301" s="135"/>
-      <c r="D301" s="143" t="s">
+      <c r="C301" s="166"/>
+      <c r="D301" s="135" t="s">
         <v>389</v>
       </c>
       <c r="E301" s="8" t="s">
@@ -11181,8 +11466,8 @@
       <c r="B302" s="7">
         <v>10</v>
       </c>
-      <c r="C302" s="135"/>
-      <c r="D302" s="135"/>
+      <c r="C302" s="166"/>
+      <c r="D302" s="156"/>
       <c r="E302" s="8" t="s">
         <v>391</v>
       </c>
@@ -11203,8 +11488,8 @@
       <c r="B303" s="7">
         <v>11</v>
       </c>
-      <c r="C303" s="135"/>
-      <c r="D303" s="136"/>
+      <c r="C303" s="166"/>
+      <c r="D303" s="157"/>
       <c r="E303" s="8" t="s">
         <v>392</v>
       </c>
@@ -11225,8 +11510,8 @@
       <c r="B304" s="7">
         <v>12</v>
       </c>
-      <c r="C304" s="135"/>
-      <c r="D304" s="143" t="s">
+      <c r="C304" s="166"/>
+      <c r="D304" s="135" t="s">
         <v>393</v>
       </c>
       <c r="E304" s="8" t="s">
@@ -11249,8 +11534,8 @@
       <c r="B305" s="7">
         <v>13</v>
       </c>
-      <c r="C305" s="135"/>
-      <c r="D305" s="135"/>
+      <c r="C305" s="166"/>
+      <c r="D305" s="156"/>
       <c r="E305" s="8" t="s">
         <v>395</v>
       </c>
@@ -11271,8 +11556,8 @@
       <c r="B306" s="7">
         <v>14</v>
       </c>
-      <c r="C306" s="135"/>
-      <c r="D306" s="135"/>
+      <c r="C306" s="166"/>
+      <c r="D306" s="156"/>
       <c r="E306" s="8" t="s">
         <v>396</v>
       </c>
@@ -11293,8 +11578,8 @@
       <c r="B307" s="24">
         <v>15</v>
       </c>
-      <c r="C307" s="136"/>
-      <c r="D307" s="136"/>
+      <c r="C307" s="167"/>
+      <c r="D307" s="157"/>
       <c r="E307" s="17" t="s">
         <v>397</v>
       </c>
@@ -11315,7 +11600,7 @@
       <c r="B308" s="7">
         <v>1</v>
       </c>
-      <c r="C308" s="141" t="s">
+      <c r="C308" s="149" t="s">
         <v>398</v>
       </c>
       <c r="D308" s="144" t="s">
@@ -11341,8 +11626,8 @@
       <c r="B309" s="7">
         <v>2</v>
       </c>
-      <c r="C309" s="135"/>
-      <c r="D309" s="135"/>
+      <c r="C309" s="174"/>
+      <c r="D309" s="170"/>
       <c r="E309" s="8" t="s">
         <v>401</v>
       </c>
@@ -11363,8 +11648,8 @@
       <c r="B310" s="7">
         <v>3</v>
       </c>
-      <c r="C310" s="135"/>
-      <c r="D310" s="135"/>
+      <c r="C310" s="174"/>
+      <c r="D310" s="170"/>
       <c r="E310" s="13" t="s">
         <v>402</v>
       </c>
@@ -11385,8 +11670,8 @@
       <c r="B311" s="7">
         <v>4</v>
       </c>
-      <c r="C311" s="135"/>
-      <c r="D311" s="135"/>
+      <c r="C311" s="174"/>
+      <c r="D311" s="170"/>
       <c r="E311" s="8" t="s">
         <v>403</v>
       </c>
@@ -11407,8 +11692,8 @@
       <c r="B312" s="7">
         <v>5</v>
       </c>
-      <c r="C312" s="135"/>
-      <c r="D312" s="135"/>
+      <c r="C312" s="174"/>
+      <c r="D312" s="170"/>
       <c r="E312" s="13" t="s">
         <v>404</v>
       </c>
@@ -11429,8 +11714,8 @@
       <c r="B313" s="7">
         <v>6</v>
       </c>
-      <c r="C313" s="135"/>
-      <c r="D313" s="135"/>
+      <c r="C313" s="174"/>
+      <c r="D313" s="170"/>
       <c r="E313" s="13" t="s">
         <v>405</v>
       </c>
@@ -11451,8 +11736,8 @@
       <c r="B314" s="7">
         <v>7</v>
       </c>
-      <c r="C314" s="135"/>
-      <c r="D314" s="136"/>
+      <c r="C314" s="174"/>
+      <c r="D314" s="171"/>
       <c r="E314" s="8" t="s">
         <v>406</v>
       </c>
@@ -11473,7 +11758,7 @@
       <c r="B315" s="7">
         <v>8</v>
       </c>
-      <c r="C315" s="135"/>
+      <c r="C315" s="174"/>
       <c r="D315" s="144" t="s">
         <v>407</v>
       </c>
@@ -11497,8 +11782,8 @@
       <c r="B316" s="7">
         <v>9</v>
       </c>
-      <c r="C316" s="135"/>
-      <c r="D316" s="135"/>
+      <c r="C316" s="174"/>
+      <c r="D316" s="170"/>
       <c r="E316" s="8" t="s">
         <v>409</v>
       </c>
@@ -11519,8 +11804,8 @@
       <c r="B317" s="24">
         <v>10</v>
       </c>
-      <c r="C317" s="136"/>
-      <c r="D317" s="136"/>
+      <c r="C317" s="175"/>
+      <c r="D317" s="171"/>
       <c r="E317" s="17" t="s">
         <v>410</v>
       </c>
@@ -11541,7 +11826,7 @@
       <c r="B318" s="7">
         <v>1</v>
       </c>
-      <c r="C318" s="142" t="s">
+      <c r="C318" s="150" t="s">
         <v>411</v>
       </c>
       <c r="D318" s="144" t="s">
@@ -11567,8 +11852,8 @@
       <c r="B319" s="7">
         <v>2</v>
       </c>
-      <c r="C319" s="135"/>
-      <c r="D319" s="135"/>
+      <c r="C319" s="172"/>
+      <c r="D319" s="170"/>
       <c r="E319" s="13" t="s">
         <v>414</v>
       </c>
@@ -11589,8 +11874,8 @@
       <c r="B320" s="7">
         <v>3</v>
       </c>
-      <c r="C320" s="135"/>
-      <c r="D320" s="135"/>
+      <c r="C320" s="172"/>
+      <c r="D320" s="170"/>
       <c r="E320" s="8" t="s">
         <v>415</v>
       </c>
@@ -11611,8 +11896,8 @@
       <c r="B321" s="7">
         <v>4</v>
       </c>
-      <c r="C321" s="135"/>
-      <c r="D321" s="135"/>
+      <c r="C321" s="172"/>
+      <c r="D321" s="170"/>
       <c r="E321" s="8" t="s">
         <v>416</v>
       </c>
@@ -11633,8 +11918,8 @@
       <c r="B322" s="7">
         <v>5</v>
       </c>
-      <c r="C322" s="135"/>
-      <c r="D322" s="135"/>
+      <c r="C322" s="172"/>
+      <c r="D322" s="170"/>
       <c r="E322" s="8" t="s">
         <v>417</v>
       </c>
@@ -11655,8 +11940,8 @@
       <c r="B323" s="7">
         <v>6</v>
       </c>
-      <c r="C323" s="135"/>
-      <c r="D323" s="136"/>
+      <c r="C323" s="172"/>
+      <c r="D323" s="171"/>
       <c r="E323" s="29" t="s">
         <v>418</v>
       </c>
@@ -11677,7 +11962,7 @@
       <c r="B324" s="7">
         <v>7</v>
       </c>
-      <c r="C324" s="135"/>
+      <c r="C324" s="172"/>
       <c r="D324" s="144" t="s">
         <v>419</v>
       </c>
@@ -11701,8 +11986,8 @@
       <c r="B325" s="7">
         <v>8</v>
       </c>
-      <c r="C325" s="135"/>
-      <c r="D325" s="135"/>
+      <c r="C325" s="172"/>
+      <c r="D325" s="170"/>
       <c r="E325" s="8" t="s">
         <v>421</v>
       </c>
@@ -11723,8 +12008,8 @@
       <c r="B326" s="7">
         <v>9</v>
       </c>
-      <c r="C326" s="135"/>
-      <c r="D326" s="135"/>
+      <c r="C326" s="172"/>
+      <c r="D326" s="170"/>
       <c r="E326" s="8" t="s">
         <v>422</v>
       </c>
@@ -11745,8 +12030,8 @@
       <c r="B327" s="7">
         <v>10</v>
       </c>
-      <c r="C327" s="135"/>
-      <c r="D327" s="135"/>
+      <c r="C327" s="172"/>
+      <c r="D327" s="170"/>
       <c r="E327" s="8" t="s">
         <v>423</v>
       </c>
@@ -11767,8 +12052,8 @@
       <c r="B328" s="7">
         <v>11</v>
       </c>
-      <c r="C328" s="135"/>
-      <c r="D328" s="136"/>
+      <c r="C328" s="172"/>
+      <c r="D328" s="171"/>
       <c r="E328" s="13" t="s">
         <v>424</v>
       </c>
@@ -11789,7 +12074,7 @@
       <c r="B329" s="7">
         <v>12</v>
       </c>
-      <c r="C329" s="135"/>
+      <c r="C329" s="172"/>
       <c r="D329" s="144" t="s">
         <v>425</v>
       </c>
@@ -11813,8 +12098,8 @@
       <c r="B330" s="7">
         <v>13</v>
       </c>
-      <c r="C330" s="135"/>
-      <c r="D330" s="135"/>
+      <c r="C330" s="172"/>
+      <c r="D330" s="170"/>
       <c r="E330" s="8" t="s">
         <v>427</v>
       </c>
@@ -11835,8 +12120,8 @@
       <c r="B331" s="7">
         <v>14</v>
       </c>
-      <c r="C331" s="135"/>
-      <c r="D331" s="135"/>
+      <c r="C331" s="172"/>
+      <c r="D331" s="170"/>
       <c r="E331" s="8" t="s">
         <v>428</v>
       </c>
@@ -11857,8 +12142,8 @@
       <c r="B332" s="7">
         <v>15</v>
       </c>
-      <c r="C332" s="135"/>
-      <c r="D332" s="135"/>
+      <c r="C332" s="172"/>
+      <c r="D332" s="170"/>
       <c r="E332" s="8" t="s">
         <v>429</v>
       </c>
@@ -11879,8 +12164,8 @@
       <c r="B333" s="7">
         <v>16</v>
       </c>
-      <c r="C333" s="135"/>
-      <c r="D333" s="135"/>
+      <c r="C333" s="172"/>
+      <c r="D333" s="170"/>
       <c r="E333" s="8" t="s">
         <v>430</v>
       </c>
@@ -11901,8 +12186,8 @@
       <c r="B334" s="7">
         <v>17</v>
       </c>
-      <c r="C334" s="135"/>
-      <c r="D334" s="135"/>
+      <c r="C334" s="172"/>
+      <c r="D334" s="170"/>
       <c r="E334" s="8" t="s">
         <v>431</v>
       </c>
@@ -11923,8 +12208,8 @@
       <c r="B335" s="7">
         <v>18</v>
       </c>
-      <c r="C335" s="135"/>
-      <c r="D335" s="135"/>
+      <c r="C335" s="172"/>
+      <c r="D335" s="170"/>
       <c r="E335" s="8" t="s">
         <v>432</v>
       </c>
@@ -11945,8 +12230,8 @@
       <c r="B336" s="7">
         <v>19</v>
       </c>
-      <c r="C336" s="135"/>
-      <c r="D336" s="135"/>
+      <c r="C336" s="172"/>
+      <c r="D336" s="170"/>
       <c r="E336" s="8" t="s">
         <v>433</v>
       </c>
@@ -11967,8 +12252,8 @@
       <c r="B337" s="7">
         <v>20</v>
       </c>
-      <c r="C337" s="135"/>
-      <c r="D337" s="136"/>
+      <c r="C337" s="172"/>
+      <c r="D337" s="171"/>
       <c r="E337" s="13" t="s">
         <v>434</v>
       </c>
@@ -11989,7 +12274,7 @@
       <c r="B338" s="7">
         <v>21</v>
       </c>
-      <c r="C338" s="135"/>
+      <c r="C338" s="172"/>
       <c r="D338" s="144" t="s">
         <v>435</v>
       </c>
@@ -12013,8 +12298,8 @@
       <c r="B339" s="7">
         <v>22</v>
       </c>
-      <c r="C339" s="135"/>
-      <c r="D339" s="135"/>
+      <c r="C339" s="172"/>
+      <c r="D339" s="170"/>
       <c r="E339" s="13" t="s">
         <v>437</v>
       </c>
@@ -12035,8 +12320,8 @@
       <c r="B340" s="7">
         <v>23</v>
       </c>
-      <c r="C340" s="135"/>
-      <c r="D340" s="135"/>
+      <c r="C340" s="172"/>
+      <c r="D340" s="170"/>
       <c r="E340" s="13" t="s">
         <v>438</v>
       </c>
@@ -12057,8 +12342,8 @@
       <c r="B341" s="7">
         <v>24</v>
       </c>
-      <c r="C341" s="135"/>
-      <c r="D341" s="135"/>
+      <c r="C341" s="172"/>
+      <c r="D341" s="170"/>
       <c r="E341" s="13" t="s">
         <v>439</v>
       </c>
@@ -12079,8 +12364,8 @@
       <c r="B342" s="24">
         <v>25</v>
       </c>
-      <c r="C342" s="136"/>
-      <c r="D342" s="136"/>
+      <c r="C342" s="173"/>
+      <c r="D342" s="171"/>
       <c r="E342" s="25" t="s">
         <v>440</v>
       </c>
@@ -12101,10 +12386,10 @@
       <c r="B343" s="7">
         <v>1</v>
       </c>
-      <c r="C343" s="134" t="s">
+      <c r="C343" s="139" t="s">
         <v>441</v>
       </c>
-      <c r="D343" s="143" t="s">
+      <c r="D343" s="135" t="s">
         <v>442</v>
       </c>
       <c r="E343" s="8" t="s">
@@ -12133,8 +12418,8 @@
       <c r="B344" s="7">
         <v>2</v>
       </c>
-      <c r="C344" s="135"/>
-      <c r="D344" s="135"/>
+      <c r="C344" s="160"/>
+      <c r="D344" s="156"/>
       <c r="E344" s="8" t="s">
         <v>444</v>
       </c>
@@ -12161,8 +12446,8 @@
       <c r="B345" s="7">
         <v>3</v>
       </c>
-      <c r="C345" s="135"/>
-      <c r="D345" s="135"/>
+      <c r="C345" s="160"/>
+      <c r="D345" s="156"/>
       <c r="E345" s="8" t="s">
         <v>445</v>
       </c>
@@ -12189,8 +12474,8 @@
       <c r="B346" s="7">
         <v>4</v>
       </c>
-      <c r="C346" s="135"/>
-      <c r="D346" s="135"/>
+      <c r="C346" s="160"/>
+      <c r="D346" s="156"/>
       <c r="E346" s="8" t="s">
         <v>446</v>
       </c>
@@ -12217,8 +12502,8 @@
       <c r="B347" s="7">
         <v>5</v>
       </c>
-      <c r="C347" s="135"/>
-      <c r="D347" s="136"/>
+      <c r="C347" s="160"/>
+      <c r="D347" s="157"/>
       <c r="E347" s="8" t="s">
         <v>447</v>
       </c>
@@ -12245,8 +12530,8 @@
       <c r="B348" s="7">
         <v>6</v>
       </c>
-      <c r="C348" s="135"/>
-      <c r="D348" s="143" t="s">
+      <c r="C348" s="160"/>
+      <c r="D348" s="135" t="s">
         <v>448</v>
       </c>
       <c r="E348" s="8" t="s">
@@ -12273,8 +12558,8 @@
       <c r="B349" s="7">
         <v>7</v>
       </c>
-      <c r="C349" s="135"/>
-      <c r="D349" s="135"/>
+      <c r="C349" s="160"/>
+      <c r="D349" s="156"/>
       <c r="E349" s="8" t="s">
         <v>450</v>
       </c>
@@ -12301,8 +12586,8 @@
       <c r="B350" s="7">
         <v>8</v>
       </c>
-      <c r="C350" s="135"/>
-      <c r="D350" s="135"/>
+      <c r="C350" s="160"/>
+      <c r="D350" s="156"/>
       <c r="E350" s="8" t="s">
         <v>451</v>
       </c>
@@ -12329,8 +12614,8 @@
       <c r="B351" s="7">
         <v>9</v>
       </c>
-      <c r="C351" s="135"/>
-      <c r="D351" s="135"/>
+      <c r="C351" s="160"/>
+      <c r="D351" s="156"/>
       <c r="E351" s="8" t="s">
         <v>452</v>
       </c>
@@ -12353,8 +12638,8 @@
       <c r="B352" s="7">
         <v>10</v>
       </c>
-      <c r="C352" s="135"/>
-      <c r="D352" s="135"/>
+      <c r="C352" s="160"/>
+      <c r="D352" s="156"/>
       <c r="E352" s="8" t="s">
         <v>453</v>
       </c>
@@ -12381,8 +12666,8 @@
       <c r="B353" s="7">
         <v>11</v>
       </c>
-      <c r="C353" s="135"/>
-      <c r="D353" s="136"/>
+      <c r="C353" s="160"/>
+      <c r="D353" s="157"/>
       <c r="E353" s="8" t="s">
         <v>454</v>
       </c>
@@ -12403,8 +12688,8 @@
       <c r="B354" s="7">
         <v>12</v>
       </c>
-      <c r="C354" s="135"/>
-      <c r="D354" s="143" t="s">
+      <c r="C354" s="160"/>
+      <c r="D354" s="135" t="s">
         <v>455</v>
       </c>
       <c r="E354" s="8" t="s">
@@ -12431,8 +12716,8 @@
       <c r="B355" s="7">
         <v>13</v>
       </c>
-      <c r="C355" s="135"/>
-      <c r="D355" s="135"/>
+      <c r="C355" s="160"/>
+      <c r="D355" s="156"/>
       <c r="E355" s="8" t="s">
         <v>457</v>
       </c>
@@ -12459,8 +12744,8 @@
       <c r="B356" s="7">
         <v>14</v>
       </c>
-      <c r="C356" s="135"/>
-      <c r="D356" s="135"/>
+      <c r="C356" s="160"/>
+      <c r="D356" s="156"/>
       <c r="E356" s="8" t="s">
         <v>458</v>
       </c>
@@ -12481,8 +12766,8 @@
       <c r="B357" s="7">
         <v>15</v>
       </c>
-      <c r="C357" s="136"/>
-      <c r="D357" s="136"/>
+      <c r="C357" s="161"/>
+      <c r="D357" s="157"/>
       <c r="E357" s="8" t="s">
         <v>459</v>
       </c>
@@ -12497,18 +12782,18 @@
       <c r="J357" s="11"/>
     </row>
     <row r="358" spans="1:10" ht="13.8">
-      <c r="A358" s="150" t="s">
+      <c r="A358" s="147" t="s">
         <v>460</v>
       </c>
-      <c r="B358" s="146"/>
-      <c r="C358" s="146"/>
-      <c r="D358" s="146"/>
-      <c r="E358" s="146"/>
-      <c r="F358" s="146"/>
-      <c r="G358" s="146"/>
-      <c r="H358" s="146"/>
-      <c r="I358" s="146"/>
-      <c r="J358" s="147"/>
+      <c r="B358" s="168"/>
+      <c r="C358" s="168"/>
+      <c r="D358" s="168"/>
+      <c r="E358" s="168"/>
+      <c r="F358" s="168"/>
+      <c r="G358" s="168"/>
+      <c r="H358" s="168"/>
+      <c r="I358" s="168"/>
+      <c r="J358" s="169"/>
     </row>
     <row r="359" spans="1:10" ht="13.8">
       <c r="A359" s="6">
@@ -12517,10 +12802,10 @@
       <c r="B359" s="7">
         <v>1</v>
       </c>
-      <c r="C359" s="137" t="s">
+      <c r="C359" s="140" t="s">
         <v>461</v>
       </c>
-      <c r="D359" s="143" t="s">
+      <c r="D359" s="135" t="s">
         <v>462</v>
       </c>
       <c r="E359" s="8" t="s">
@@ -12543,8 +12828,8 @@
       <c r="B360" s="7">
         <v>2</v>
       </c>
-      <c r="C360" s="135"/>
-      <c r="D360" s="135"/>
+      <c r="C360" s="166"/>
+      <c r="D360" s="156"/>
       <c r="E360" s="8" t="s">
         <v>464</v>
       </c>
@@ -12565,8 +12850,8 @@
       <c r="B361" s="7">
         <v>3</v>
       </c>
-      <c r="C361" s="135"/>
-      <c r="D361" s="135"/>
+      <c r="C361" s="166"/>
+      <c r="D361" s="156"/>
       <c r="E361" s="8" t="s">
         <v>465</v>
       </c>
@@ -12587,8 +12872,8 @@
       <c r="B362" s="7">
         <v>4</v>
       </c>
-      <c r="C362" s="135"/>
-      <c r="D362" s="135"/>
+      <c r="C362" s="166"/>
+      <c r="D362" s="156"/>
       <c r="E362" s="8" t="s">
         <v>466</v>
       </c>
@@ -12609,8 +12894,8 @@
       <c r="B363" s="7">
         <v>5</v>
       </c>
-      <c r="C363" s="135"/>
-      <c r="D363" s="136"/>
+      <c r="C363" s="166"/>
+      <c r="D363" s="157"/>
       <c r="E363" s="8" t="s">
         <v>467</v>
       </c>
@@ -12631,8 +12916,8 @@
       <c r="B364" s="7">
         <v>6</v>
       </c>
-      <c r="C364" s="135"/>
-      <c r="D364" s="143" t="s">
+      <c r="C364" s="166"/>
+      <c r="D364" s="135" t="s">
         <v>468</v>
       </c>
       <c r="E364" s="8" t="s">
@@ -12655,8 +12940,8 @@
       <c r="B365" s="7">
         <v>7</v>
       </c>
-      <c r="C365" s="135"/>
-      <c r="D365" s="135"/>
+      <c r="C365" s="166"/>
+      <c r="D365" s="156"/>
       <c r="E365" s="8" t="s">
         <v>470</v>
       </c>
@@ -12677,8 +12962,8 @@
       <c r="B366" s="7">
         <v>8</v>
       </c>
-      <c r="C366" s="135"/>
-      <c r="D366" s="135"/>
+      <c r="C366" s="166"/>
+      <c r="D366" s="156"/>
       <c r="E366" s="8" t="s">
         <v>471</v>
       </c>
@@ -12699,8 +12984,8 @@
       <c r="B367" s="7">
         <v>9</v>
       </c>
-      <c r="C367" s="135"/>
-      <c r="D367" s="135"/>
+      <c r="C367" s="166"/>
+      <c r="D367" s="156"/>
       <c r="E367" s="8" t="s">
         <v>472</v>
       </c>
@@ -12721,8 +13006,8 @@
       <c r="B368" s="7">
         <v>10</v>
       </c>
-      <c r="C368" s="135"/>
-      <c r="D368" s="135"/>
+      <c r="C368" s="166"/>
+      <c r="D368" s="156"/>
       <c r="E368" s="8" t="s">
         <v>473</v>
       </c>
@@ -12743,8 +13028,8 @@
       <c r="B369" s="7">
         <v>11</v>
       </c>
-      <c r="C369" s="135"/>
-      <c r="D369" s="135"/>
+      <c r="C369" s="166"/>
+      <c r="D369" s="156"/>
       <c r="E369" s="8" t="s">
         <v>474</v>
       </c>
@@ -12765,8 +13050,8 @@
       <c r="B370" s="7">
         <v>12</v>
       </c>
-      <c r="C370" s="135"/>
-      <c r="D370" s="135"/>
+      <c r="C370" s="166"/>
+      <c r="D370" s="156"/>
       <c r="E370" s="8" t="s">
         <v>475</v>
       </c>
@@ -12787,8 +13072,8 @@
       <c r="B371" s="7">
         <v>13</v>
       </c>
-      <c r="C371" s="135"/>
-      <c r="D371" s="136"/>
+      <c r="C371" s="166"/>
+      <c r="D371" s="157"/>
       <c r="E371" s="8" t="s">
         <v>476</v>
       </c>
@@ -12809,8 +13094,8 @@
       <c r="B372" s="7">
         <v>14</v>
       </c>
-      <c r="C372" s="135"/>
-      <c r="D372" s="143" t="s">
+      <c r="C372" s="166"/>
+      <c r="D372" s="135" t="s">
         <v>477</v>
       </c>
       <c r="E372" s="8" t="s">
@@ -12833,8 +13118,8 @@
       <c r="B373" s="7">
         <v>15</v>
       </c>
-      <c r="C373" s="135"/>
-      <c r="D373" s="135"/>
+      <c r="C373" s="166"/>
+      <c r="D373" s="156"/>
       <c r="E373" s="11" t="s">
         <v>479</v>
       </c>
@@ -12855,8 +13140,8 @@
       <c r="B374" s="7">
         <v>16</v>
       </c>
-      <c r="C374" s="135"/>
-      <c r="D374" s="135"/>
+      <c r="C374" s="166"/>
+      <c r="D374" s="156"/>
       <c r="E374" s="8" t="s">
         <v>480</v>
       </c>
@@ -12877,8 +13162,8 @@
       <c r="B375" s="7">
         <v>17</v>
       </c>
-      <c r="C375" s="135"/>
-      <c r="D375" s="136"/>
+      <c r="C375" s="166"/>
+      <c r="D375" s="157"/>
       <c r="E375" s="8" t="s">
         <v>481</v>
       </c>
@@ -12899,8 +13184,8 @@
       <c r="B376" s="7">
         <v>18</v>
       </c>
-      <c r="C376" s="135"/>
-      <c r="D376" s="143" t="s">
+      <c r="C376" s="166"/>
+      <c r="D376" s="135" t="s">
         <v>482</v>
       </c>
       <c r="E376" s="8" t="s">
@@ -12923,8 +13208,8 @@
       <c r="B377" s="7">
         <v>19</v>
       </c>
-      <c r="C377" s="135"/>
-      <c r="D377" s="135"/>
+      <c r="C377" s="166"/>
+      <c r="D377" s="156"/>
       <c r="E377" s="8" t="s">
         <v>484</v>
       </c>
@@ -12945,8 +13230,8 @@
       <c r="B378" s="7">
         <v>20</v>
       </c>
-      <c r="C378" s="135"/>
-      <c r="D378" s="135"/>
+      <c r="C378" s="166"/>
+      <c r="D378" s="156"/>
       <c r="E378" s="8" t="s">
         <v>485</v>
       </c>
@@ -12967,8 +13252,8 @@
       <c r="B379" s="7">
         <v>21</v>
       </c>
-      <c r="C379" s="135"/>
-      <c r="D379" s="135"/>
+      <c r="C379" s="166"/>
+      <c r="D379" s="156"/>
       <c r="E379" s="8" t="s">
         <v>486</v>
       </c>
@@ -12989,8 +13274,8 @@
       <c r="B380" s="24">
         <v>22</v>
       </c>
-      <c r="C380" s="136"/>
-      <c r="D380" s="136"/>
+      <c r="C380" s="167"/>
+      <c r="D380" s="157"/>
       <c r="E380" s="17" t="s">
         <v>487</v>
       </c>
@@ -13011,10 +13296,10 @@
       <c r="B381" s="7">
         <v>1</v>
       </c>
-      <c r="C381" s="138" t="s">
+      <c r="C381" s="137" t="s">
         <v>488</v>
       </c>
-      <c r="D381" s="143" t="s">
+      <c r="D381" s="135" t="s">
         <v>489</v>
       </c>
       <c r="E381" s="8" t="s">
@@ -13037,8 +13322,8 @@
       <c r="B382" s="7">
         <v>2</v>
       </c>
-      <c r="C382" s="135"/>
-      <c r="D382" s="135"/>
+      <c r="C382" s="164"/>
+      <c r="D382" s="156"/>
       <c r="E382" s="8" t="s">
         <v>491</v>
       </c>
@@ -13059,8 +13344,8 @@
       <c r="B383" s="7">
         <v>3</v>
       </c>
-      <c r="C383" s="135"/>
-      <c r="D383" s="135"/>
+      <c r="C383" s="164"/>
+      <c r="D383" s="156"/>
       <c r="E383" s="8" t="s">
         <v>492</v>
       </c>
@@ -13081,8 +13366,8 @@
       <c r="B384" s="7">
         <v>4</v>
       </c>
-      <c r="C384" s="135"/>
-      <c r="D384" s="135"/>
+      <c r="C384" s="164"/>
+      <c r="D384" s="156"/>
       <c r="E384" s="8" t="s">
         <v>493</v>
       </c>
@@ -13103,8 +13388,8 @@
       <c r="B385" s="7">
         <v>5</v>
       </c>
-      <c r="C385" s="135"/>
-      <c r="D385" s="135"/>
+      <c r="C385" s="164"/>
+      <c r="D385" s="156"/>
       <c r="E385" s="8" t="s">
         <v>494</v>
       </c>
@@ -13125,8 +13410,8 @@
       <c r="B386" s="7">
         <v>6</v>
       </c>
-      <c r="C386" s="135"/>
-      <c r="D386" s="136"/>
+      <c r="C386" s="164"/>
+      <c r="D386" s="157"/>
       <c r="E386" s="8" t="s">
         <v>495</v>
       </c>
@@ -13147,8 +13432,8 @@
       <c r="B387" s="7">
         <v>7</v>
       </c>
-      <c r="C387" s="135"/>
-      <c r="D387" s="143" t="s">
+      <c r="C387" s="164"/>
+      <c r="D387" s="135" t="s">
         <v>496</v>
       </c>
       <c r="E387" s="8" t="s">
@@ -13171,8 +13456,8 @@
       <c r="B388" s="7">
         <v>8</v>
       </c>
-      <c r="C388" s="135"/>
-      <c r="D388" s="135"/>
+      <c r="C388" s="164"/>
+      <c r="D388" s="156"/>
       <c r="E388" s="8" t="s">
         <v>498</v>
       </c>
@@ -13193,8 +13478,8 @@
       <c r="B389" s="7">
         <v>9</v>
       </c>
-      <c r="C389" s="135"/>
-      <c r="D389" s="135"/>
+      <c r="C389" s="164"/>
+      <c r="D389" s="156"/>
       <c r="E389" s="8" t="s">
         <v>499</v>
       </c>
@@ -13215,8 +13500,8 @@
       <c r="B390" s="7">
         <v>10</v>
       </c>
-      <c r="C390" s="135"/>
-      <c r="D390" s="135"/>
+      <c r="C390" s="164"/>
+      <c r="D390" s="156"/>
       <c r="E390" s="8" t="s">
         <v>500</v>
       </c>
@@ -13237,8 +13522,8 @@
       <c r="B391" s="7">
         <v>11</v>
       </c>
-      <c r="C391" s="135"/>
-      <c r="D391" s="135"/>
+      <c r="C391" s="164"/>
+      <c r="D391" s="156"/>
       <c r="E391" s="8" t="s">
         <v>501</v>
       </c>
@@ -13259,8 +13544,8 @@
       <c r="B392" s="7">
         <v>12</v>
       </c>
-      <c r="C392" s="135"/>
-      <c r="D392" s="135"/>
+      <c r="C392" s="164"/>
+      <c r="D392" s="156"/>
       <c r="E392" s="8" t="s">
         <v>502</v>
       </c>
@@ -13281,8 +13566,8 @@
       <c r="B393" s="7">
         <v>13</v>
       </c>
-      <c r="C393" s="135"/>
-      <c r="D393" s="135"/>
+      <c r="C393" s="164"/>
+      <c r="D393" s="156"/>
       <c r="E393" s="8" t="s">
         <v>503</v>
       </c>
@@ -13303,8 +13588,8 @@
       <c r="B394" s="7">
         <v>14</v>
       </c>
-      <c r="C394" s="135"/>
-      <c r="D394" s="135"/>
+      <c r="C394" s="164"/>
+      <c r="D394" s="156"/>
       <c r="E394" s="8" t="s">
         <v>504</v>
       </c>
@@ -13325,8 +13610,8 @@
       <c r="B395" s="7">
         <v>15</v>
       </c>
-      <c r="C395" s="135"/>
-      <c r="D395" s="135"/>
+      <c r="C395" s="164"/>
+      <c r="D395" s="156"/>
       <c r="E395" s="8" t="s">
         <v>505</v>
       </c>
@@ -13347,8 +13632,8 @@
       <c r="B396" s="7">
         <v>16</v>
       </c>
-      <c r="C396" s="135"/>
-      <c r="D396" s="136"/>
+      <c r="C396" s="164"/>
+      <c r="D396" s="157"/>
       <c r="E396" s="8" t="s">
         <v>506</v>
       </c>
@@ -13369,8 +13654,8 @@
       <c r="B397" s="7">
         <v>17</v>
       </c>
-      <c r="C397" s="135"/>
-      <c r="D397" s="143" t="s">
+      <c r="C397" s="164"/>
+      <c r="D397" s="135" t="s">
         <v>507</v>
       </c>
       <c r="E397" s="8" t="s">
@@ -13393,8 +13678,8 @@
       <c r="B398" s="7">
         <v>18</v>
       </c>
-      <c r="C398" s="135"/>
-      <c r="D398" s="135"/>
+      <c r="C398" s="164"/>
+      <c r="D398" s="156"/>
       <c r="E398" s="8" t="s">
         <v>509</v>
       </c>
@@ -13415,8 +13700,8 @@
       <c r="B399" s="7">
         <v>19</v>
       </c>
-      <c r="C399" s="135"/>
-      <c r="D399" s="136"/>
+      <c r="C399" s="164"/>
+      <c r="D399" s="157"/>
       <c r="E399" s="8" t="s">
         <v>510</v>
       </c>
@@ -13437,8 +13722,8 @@
       <c r="B400" s="7">
         <v>20</v>
       </c>
-      <c r="C400" s="135"/>
-      <c r="D400" s="143" t="s">
+      <c r="C400" s="164"/>
+      <c r="D400" s="135" t="s">
         <v>511</v>
       </c>
       <c r="E400" s="8" t="s">
@@ -13461,8 +13746,8 @@
       <c r="B401" s="7">
         <v>21</v>
       </c>
-      <c r="C401" s="135"/>
-      <c r="D401" s="135"/>
+      <c r="C401" s="164"/>
+      <c r="D401" s="156"/>
       <c r="E401" s="8" t="s">
         <v>513</v>
       </c>
@@ -13483,8 +13768,8 @@
       <c r="B402" s="7">
         <v>22</v>
       </c>
-      <c r="C402" s="135"/>
-      <c r="D402" s="135"/>
+      <c r="C402" s="164"/>
+      <c r="D402" s="156"/>
       <c r="E402" s="8" t="s">
         <v>514</v>
       </c>
@@ -13505,8 +13790,8 @@
       <c r="B403" s="7">
         <v>23</v>
       </c>
-      <c r="C403" s="135"/>
-      <c r="D403" s="135"/>
+      <c r="C403" s="164"/>
+      <c r="D403" s="156"/>
       <c r="E403" s="8" t="s">
         <v>515</v>
       </c>
@@ -13527,8 +13812,8 @@
       <c r="B404" s="7">
         <v>24</v>
       </c>
-      <c r="C404" s="135"/>
-      <c r="D404" s="136"/>
+      <c r="C404" s="164"/>
+      <c r="D404" s="157"/>
       <c r="E404" s="8" t="s">
         <v>516</v>
       </c>
@@ -13549,8 +13834,8 @@
       <c r="B405" s="7">
         <v>25</v>
       </c>
-      <c r="C405" s="135"/>
-      <c r="D405" s="143" t="s">
+      <c r="C405" s="164"/>
+      <c r="D405" s="135" t="s">
         <v>517</v>
       </c>
       <c r="E405" s="8" t="s">
@@ -13573,8 +13858,8 @@
       <c r="B406" s="7">
         <v>26</v>
       </c>
-      <c r="C406" s="135"/>
-      <c r="D406" s="135"/>
+      <c r="C406" s="164"/>
+      <c r="D406" s="156"/>
       <c r="E406" s="8" t="s">
         <v>519</v>
       </c>
@@ -13595,8 +13880,8 @@
       <c r="B407" s="7">
         <v>27</v>
       </c>
-      <c r="C407" s="135"/>
-      <c r="D407" s="135"/>
+      <c r="C407" s="164"/>
+      <c r="D407" s="156"/>
       <c r="E407" s="8" t="s">
         <v>520</v>
       </c>
@@ -13617,8 +13902,8 @@
       <c r="B408" s="7">
         <v>28</v>
       </c>
-      <c r="C408" s="135"/>
-      <c r="D408" s="135"/>
+      <c r="C408" s="164"/>
+      <c r="D408" s="156"/>
       <c r="E408" s="8" t="s">
         <v>521</v>
       </c>
@@ -13639,8 +13924,8 @@
       <c r="B409" s="7">
         <v>29</v>
       </c>
-      <c r="C409" s="135"/>
-      <c r="D409" s="135"/>
+      <c r="C409" s="164"/>
+      <c r="D409" s="156"/>
       <c r="E409" s="8" t="s">
         <v>522</v>
       </c>
@@ -13661,8 +13946,8 @@
       <c r="B410" s="7">
         <v>30</v>
       </c>
-      <c r="C410" s="135"/>
-      <c r="D410" s="135"/>
+      <c r="C410" s="164"/>
+      <c r="D410" s="156"/>
       <c r="E410" s="8" t="s">
         <v>523</v>
       </c>
@@ -13683,8 +13968,8 @@
       <c r="B411" s="7">
         <v>31</v>
       </c>
-      <c r="C411" s="135"/>
-      <c r="D411" s="135"/>
+      <c r="C411" s="164"/>
+      <c r="D411" s="156"/>
       <c r="E411" s="8" t="s">
         <v>524</v>
       </c>
@@ -13705,8 +13990,8 @@
       <c r="B412" s="7">
         <v>32</v>
       </c>
-      <c r="C412" s="135"/>
-      <c r="D412" s="135"/>
+      <c r="C412" s="164"/>
+      <c r="D412" s="156"/>
       <c r="E412" s="8" t="s">
         <v>525</v>
       </c>
@@ -13727,8 +14012,8 @@
       <c r="B413" s="7">
         <v>33</v>
       </c>
-      <c r="C413" s="135"/>
-      <c r="D413" s="135"/>
+      <c r="C413" s="164"/>
+      <c r="D413" s="156"/>
       <c r="E413" s="8" t="s">
         <v>526</v>
       </c>
@@ -13749,8 +14034,8 @@
       <c r="B414" s="7">
         <v>34</v>
       </c>
-      <c r="C414" s="135"/>
-      <c r="D414" s="135"/>
+      <c r="C414" s="164"/>
+      <c r="D414" s="156"/>
       <c r="E414" s="8" t="s">
         <v>527</v>
       </c>
@@ -13771,8 +14056,8 @@
       <c r="B415" s="7">
         <v>35</v>
       </c>
-      <c r="C415" s="135"/>
-      <c r="D415" s="135"/>
+      <c r="C415" s="164"/>
+      <c r="D415" s="156"/>
       <c r="E415" s="8" t="s">
         <v>528</v>
       </c>
@@ -13793,8 +14078,8 @@
       <c r="B416" s="7">
         <v>36</v>
       </c>
-      <c r="C416" s="135"/>
-      <c r="D416" s="136"/>
+      <c r="C416" s="164"/>
+      <c r="D416" s="157"/>
       <c r="E416" s="8" t="s">
         <v>529</v>
       </c>
@@ -13815,8 +14100,8 @@
       <c r="B417" s="7">
         <v>37</v>
       </c>
-      <c r="C417" s="135"/>
-      <c r="D417" s="143" t="s">
+      <c r="C417" s="164"/>
+      <c r="D417" s="135" t="s">
         <v>530</v>
       </c>
       <c r="E417" s="8" t="s">
@@ -13839,8 +14124,8 @@
       <c r="B418" s="7">
         <v>38</v>
       </c>
-      <c r="C418" s="135"/>
-      <c r="D418" s="135"/>
+      <c r="C418" s="164"/>
+      <c r="D418" s="156"/>
       <c r="E418" s="8" t="s">
         <v>532</v>
       </c>
@@ -13861,8 +14146,8 @@
       <c r="B419" s="7">
         <v>39</v>
       </c>
-      <c r="C419" s="135"/>
-      <c r="D419" s="136"/>
+      <c r="C419" s="164"/>
+      <c r="D419" s="157"/>
       <c r="E419" s="8" t="s">
         <v>533</v>
       </c>
@@ -13883,8 +14168,8 @@
       <c r="B420" s="7">
         <v>40</v>
       </c>
-      <c r="C420" s="135"/>
-      <c r="D420" s="143" t="s">
+      <c r="C420" s="164"/>
+      <c r="D420" s="135" t="s">
         <v>534</v>
       </c>
       <c r="E420" s="8" t="s">
@@ -13907,8 +14192,8 @@
       <c r="B421" s="7">
         <v>41</v>
       </c>
-      <c r="C421" s="135"/>
-      <c r="D421" s="135"/>
+      <c r="C421" s="164"/>
+      <c r="D421" s="156"/>
       <c r="E421" s="8" t="s">
         <v>536</v>
       </c>
@@ -13929,8 +14214,8 @@
       <c r="B422" s="7">
         <v>42</v>
       </c>
-      <c r="C422" s="135"/>
-      <c r="D422" s="135"/>
+      <c r="C422" s="164"/>
+      <c r="D422" s="156"/>
       <c r="E422" s="8" t="s">
         <v>537</v>
       </c>
@@ -13951,8 +14236,8 @@
       <c r="B423" s="7">
         <v>43</v>
       </c>
-      <c r="C423" s="135"/>
-      <c r="D423" s="135"/>
+      <c r="C423" s="164"/>
+      <c r="D423" s="156"/>
       <c r="E423" s="8" t="s">
         <v>538</v>
       </c>
@@ -13973,8 +14258,8 @@
       <c r="B424" s="7">
         <v>44</v>
       </c>
-      <c r="C424" s="135"/>
-      <c r="D424" s="135"/>
+      <c r="C424" s="164"/>
+      <c r="D424" s="156"/>
       <c r="E424" s="8" t="s">
         <v>539</v>
       </c>
@@ -13995,8 +14280,8 @@
       <c r="B425" s="7">
         <v>45</v>
       </c>
-      <c r="C425" s="135"/>
-      <c r="D425" s="135"/>
+      <c r="C425" s="164"/>
+      <c r="D425" s="156"/>
       <c r="E425" s="8" t="s">
         <v>540</v>
       </c>
@@ -14017,8 +14302,8 @@
       <c r="B426" s="7">
         <v>46</v>
       </c>
-      <c r="C426" s="135"/>
-      <c r="D426" s="136"/>
+      <c r="C426" s="164"/>
+      <c r="D426" s="157"/>
       <c r="E426" s="8" t="s">
         <v>541</v>
       </c>
@@ -14039,8 +14324,8 @@
       <c r="B427" s="7">
         <v>47</v>
       </c>
-      <c r="C427" s="135"/>
-      <c r="D427" s="143" t="s">
+      <c r="C427" s="164"/>
+      <c r="D427" s="135" t="s">
         <v>542</v>
       </c>
       <c r="E427" s="8" t="s">
@@ -14061,8 +14346,8 @@
       <c r="B428" s="7">
         <v>48</v>
       </c>
-      <c r="C428" s="135"/>
-      <c r="D428" s="135"/>
+      <c r="C428" s="164"/>
+      <c r="D428" s="156"/>
       <c r="E428" s="8" t="s">
         <v>544</v>
       </c>
@@ -14083,8 +14368,8 @@
       <c r="B429" s="7">
         <v>49</v>
       </c>
-      <c r="C429" s="135"/>
-      <c r="D429" s="135"/>
+      <c r="C429" s="164"/>
+      <c r="D429" s="156"/>
       <c r="E429" s="8" t="s">
         <v>545</v>
       </c>
@@ -14105,8 +14390,8 @@
       <c r="B430" s="7">
         <v>50</v>
       </c>
-      <c r="C430" s="135"/>
-      <c r="D430" s="136"/>
+      <c r="C430" s="164"/>
+      <c r="D430" s="157"/>
       <c r="E430" s="8" t="s">
         <v>546</v>
       </c>
@@ -14127,8 +14412,8 @@
       <c r="B431" s="7">
         <v>51</v>
       </c>
-      <c r="C431" s="135"/>
-      <c r="D431" s="143" t="s">
+      <c r="C431" s="164"/>
+      <c r="D431" s="135" t="s">
         <v>547</v>
       </c>
       <c r="E431" s="8" t="s">
@@ -14151,8 +14436,8 @@
       <c r="B432" s="7">
         <v>52</v>
       </c>
-      <c r="C432" s="135"/>
-      <c r="D432" s="135"/>
+      <c r="C432" s="164"/>
+      <c r="D432" s="156"/>
       <c r="E432" s="8" t="s">
         <v>549</v>
       </c>
@@ -14173,8 +14458,8 @@
       <c r="B433" s="7">
         <v>53</v>
       </c>
-      <c r="C433" s="135"/>
-      <c r="D433" s="135"/>
+      <c r="C433" s="164"/>
+      <c r="D433" s="156"/>
       <c r="E433" s="8" t="s">
         <v>550</v>
       </c>
@@ -14195,8 +14480,8 @@
       <c r="B434" s="7">
         <v>54</v>
       </c>
-      <c r="C434" s="135"/>
-      <c r="D434" s="135"/>
+      <c r="C434" s="164"/>
+      <c r="D434" s="156"/>
       <c r="E434" s="8" t="s">
         <v>551</v>
       </c>
@@ -14217,8 +14502,8 @@
       <c r="B435" s="7">
         <v>55</v>
       </c>
-      <c r="C435" s="136"/>
-      <c r="D435" s="136"/>
+      <c r="C435" s="165"/>
+      <c r="D435" s="157"/>
       <c r="E435" s="8" t="s">
         <v>552</v>
       </c>
@@ -14233,18 +14518,18 @@
       <c r="J435" s="11"/>
     </row>
     <row r="436" spans="1:10" ht="13.8">
-      <c r="A436" s="145" t="s">
+      <c r="A436" s="148" t="s">
         <v>553</v>
       </c>
-      <c r="B436" s="146"/>
-      <c r="C436" s="146"/>
-      <c r="D436" s="146"/>
-      <c r="E436" s="146"/>
-      <c r="F436" s="146"/>
-      <c r="G436" s="146"/>
-      <c r="H436" s="146"/>
-      <c r="I436" s="146"/>
-      <c r="J436" s="147"/>
+      <c r="B436" s="162"/>
+      <c r="C436" s="162"/>
+      <c r="D436" s="162"/>
+      <c r="E436" s="162"/>
+      <c r="F436" s="162"/>
+      <c r="G436" s="162"/>
+      <c r="H436" s="162"/>
+      <c r="I436" s="162"/>
+      <c r="J436" s="163"/>
     </row>
     <row r="437" spans="1:10" ht="13.8">
       <c r="A437" s="6">
@@ -14253,10 +14538,10 @@
       <c r="B437" s="7">
         <v>1</v>
       </c>
-      <c r="C437" s="139" t="s">
+      <c r="C437" s="138" t="s">
         <v>554</v>
       </c>
-      <c r="D437" s="143" t="s">
+      <c r="D437" s="135" t="s">
         <v>555</v>
       </c>
       <c r="E437" s="29" t="s">
@@ -14279,8 +14564,8 @@
       <c r="B438" s="7">
         <v>2</v>
       </c>
-      <c r="C438" s="135"/>
-      <c r="D438" s="135"/>
+      <c r="C438" s="158"/>
+      <c r="D438" s="156"/>
       <c r="E438" s="8" t="s">
         <v>557</v>
       </c>
@@ -14299,8 +14584,8 @@
       <c r="B439" s="7">
         <v>3</v>
       </c>
-      <c r="C439" s="135"/>
-      <c r="D439" s="135"/>
+      <c r="C439" s="158"/>
+      <c r="D439" s="156"/>
       <c r="E439" s="8" t="s">
         <v>558</v>
       </c>
@@ -14321,8 +14606,8 @@
       <c r="B440" s="7">
         <v>4</v>
       </c>
-      <c r="C440" s="135"/>
-      <c r="D440" s="135"/>
+      <c r="C440" s="158"/>
+      <c r="D440" s="156"/>
       <c r="E440" s="29" t="s">
         <v>559</v>
       </c>
@@ -14343,8 +14628,8 @@
       <c r="B441" s="7">
         <v>5</v>
       </c>
-      <c r="C441" s="135"/>
-      <c r="D441" s="136"/>
+      <c r="C441" s="158"/>
+      <c r="D441" s="157"/>
       <c r="E441" s="8" t="s">
         <v>560</v>
       </c>
@@ -14365,8 +14650,8 @@
       <c r="B442" s="7">
         <v>6</v>
       </c>
-      <c r="C442" s="135"/>
-      <c r="D442" s="143" t="s">
+      <c r="C442" s="158"/>
+      <c r="D442" s="135" t="s">
         <v>561</v>
       </c>
       <c r="E442" s="29" t="s">
@@ -14389,8 +14674,8 @@
       <c r="B443" s="7">
         <v>7</v>
       </c>
-      <c r="C443" s="135"/>
-      <c r="D443" s="135"/>
+      <c r="C443" s="158"/>
+      <c r="D443" s="156"/>
       <c r="E443" s="8" t="s">
         <v>563</v>
       </c>
@@ -14411,8 +14696,8 @@
       <c r="B444" s="7">
         <v>8</v>
       </c>
-      <c r="C444" s="135"/>
-      <c r="D444" s="135"/>
+      <c r="C444" s="158"/>
+      <c r="D444" s="156"/>
       <c r="E444" s="29" t="s">
         <v>564</v>
       </c>
@@ -14433,8 +14718,8 @@
       <c r="B445" s="7">
         <v>9</v>
       </c>
-      <c r="C445" s="135"/>
-      <c r="D445" s="136"/>
+      <c r="C445" s="158"/>
+      <c r="D445" s="157"/>
       <c r="E445" s="8" t="s">
         <v>565</v>
       </c>
@@ -14455,8 +14740,8 @@
       <c r="B446" s="7">
         <v>10</v>
       </c>
-      <c r="C446" s="135"/>
-      <c r="D446" s="143" t="s">
+      <c r="C446" s="158"/>
+      <c r="D446" s="135" t="s">
         <v>566</v>
       </c>
       <c r="E446" s="8" t="s">
@@ -14479,8 +14764,8 @@
       <c r="B447" s="7">
         <v>11</v>
       </c>
-      <c r="C447" s="135"/>
-      <c r="D447" s="135"/>
+      <c r="C447" s="158"/>
+      <c r="D447" s="156"/>
       <c r="E447" s="8" t="s">
         <v>568</v>
       </c>
@@ -14501,8 +14786,8 @@
       <c r="B448" s="7">
         <v>12</v>
       </c>
-      <c r="C448" s="135"/>
-      <c r="D448" s="136"/>
+      <c r="C448" s="158"/>
+      <c r="D448" s="157"/>
       <c r="E448" s="8" t="s">
         <v>569</v>
       </c>
@@ -14523,8 +14808,8 @@
       <c r="B449" s="7">
         <v>13</v>
       </c>
-      <c r="C449" s="135"/>
-      <c r="D449" s="143" t="s">
+      <c r="C449" s="158"/>
+      <c r="D449" s="135" t="s">
         <v>570</v>
       </c>
       <c r="E449" s="8" t="s">
@@ -14547,8 +14832,8 @@
       <c r="B450" s="7">
         <v>14</v>
       </c>
-      <c r="C450" s="135"/>
-      <c r="D450" s="135"/>
+      <c r="C450" s="158"/>
+      <c r="D450" s="156"/>
       <c r="E450" s="29" t="s">
         <v>572</v>
       </c>
@@ -14569,8 +14854,8 @@
       <c r="B451" s="7">
         <v>15</v>
       </c>
-      <c r="C451" s="135"/>
-      <c r="D451" s="135"/>
+      <c r="C451" s="158"/>
+      <c r="D451" s="156"/>
       <c r="E451" s="8" t="s">
         <v>573</v>
       </c>
@@ -14591,8 +14876,8 @@
       <c r="B452" s="7">
         <v>16</v>
       </c>
-      <c r="C452" s="135"/>
-      <c r="D452" s="136"/>
+      <c r="C452" s="158"/>
+      <c r="D452" s="157"/>
       <c r="E452" s="8" t="s">
         <v>574</v>
       </c>
@@ -14613,8 +14898,8 @@
       <c r="B453" s="7">
         <v>17</v>
       </c>
-      <c r="C453" s="135"/>
-      <c r="D453" s="143" t="s">
+      <c r="C453" s="158"/>
+      <c r="D453" s="135" t="s">
         <v>575</v>
       </c>
       <c r="E453" s="8" t="s">
@@ -14637,8 +14922,8 @@
       <c r="B454" s="7">
         <v>18</v>
       </c>
-      <c r="C454" s="135"/>
-      <c r="D454" s="135"/>
+      <c r="C454" s="158"/>
+      <c r="D454" s="156"/>
       <c r="E454" s="8" t="s">
         <v>577</v>
       </c>
@@ -14659,8 +14944,8 @@
       <c r="B455" s="7">
         <v>19</v>
       </c>
-      <c r="C455" s="135"/>
-      <c r="D455" s="135"/>
+      <c r="C455" s="158"/>
+      <c r="D455" s="156"/>
       <c r="E455" s="8" t="s">
         <v>578</v>
       </c>
@@ -14681,8 +14966,8 @@
       <c r="B456" s="7">
         <v>20</v>
       </c>
-      <c r="C456" s="135"/>
-      <c r="D456" s="135"/>
+      <c r="C456" s="158"/>
+      <c r="D456" s="156"/>
       <c r="E456" s="39" t="s">
         <v>579</v>
       </c>
@@ -14703,8 +14988,8 @@
       <c r="B457" s="7">
         <v>21</v>
       </c>
-      <c r="C457" s="135"/>
-      <c r="D457" s="135"/>
+      <c r="C457" s="158"/>
+      <c r="D457" s="156"/>
       <c r="E457" s="8" t="s">
         <v>580</v>
       </c>
@@ -14725,8 +15010,8 @@
       <c r="B458" s="24">
         <v>22</v>
       </c>
-      <c r="C458" s="136"/>
-      <c r="D458" s="136"/>
+      <c r="C458" s="159"/>
+      <c r="D458" s="157"/>
       <c r="E458" s="17" t="s">
         <v>581</v>
       </c>
@@ -14748,10 +15033,10 @@
       <c r="B459" s="7">
         <v>1</v>
       </c>
-      <c r="C459" s="134" t="s">
+      <c r="C459" s="139" t="s">
         <v>582</v>
       </c>
-      <c r="D459" s="143" t="s">
+      <c r="D459" s="135" t="s">
         <v>583</v>
       </c>
       <c r="E459" s="8" t="s">
@@ -14774,8 +15059,8 @@
       <c r="B460" s="7">
         <v>2</v>
       </c>
-      <c r="C460" s="135"/>
-      <c r="D460" s="135"/>
+      <c r="C460" s="160"/>
+      <c r="D460" s="156"/>
       <c r="E460" s="8" t="s">
         <v>584</v>
       </c>
@@ -14796,8 +15081,8 @@
       <c r="B461" s="7">
         <v>3</v>
       </c>
-      <c r="C461" s="135"/>
-      <c r="D461" s="135"/>
+      <c r="C461" s="160"/>
+      <c r="D461" s="156"/>
       <c r="E461" s="8" t="s">
         <v>585</v>
       </c>
@@ -14818,8 +15103,8 @@
       <c r="B462" s="7">
         <v>4</v>
       </c>
-      <c r="C462" s="135"/>
-      <c r="D462" s="135"/>
+      <c r="C462" s="160"/>
+      <c r="D462" s="156"/>
       <c r="E462" s="8" t="s">
         <v>586</v>
       </c>
@@ -14840,8 +15125,8 @@
       <c r="B463" s="7">
         <v>5</v>
       </c>
-      <c r="C463" s="135"/>
-      <c r="D463" s="135"/>
+      <c r="C463" s="160"/>
+      <c r="D463" s="156"/>
       <c r="E463" s="8" t="s">
         <v>587</v>
       </c>
@@ -14862,8 +15147,8 @@
       <c r="B464" s="7">
         <v>6</v>
       </c>
-      <c r="C464" s="135"/>
-      <c r="D464" s="135"/>
+      <c r="C464" s="160"/>
+      <c r="D464" s="156"/>
       <c r="E464" s="8" t="s">
         <v>588</v>
       </c>
@@ -14884,8 +15169,8 @@
       <c r="B465" s="7">
         <v>7</v>
       </c>
-      <c r="C465" s="135"/>
-      <c r="D465" s="135"/>
+      <c r="C465" s="160"/>
+      <c r="D465" s="156"/>
       <c r="E465" s="8" t="s">
         <v>589</v>
       </c>
@@ -14906,8 +15191,8 @@
       <c r="B466" s="7">
         <v>8</v>
       </c>
-      <c r="C466" s="135"/>
-      <c r="D466" s="136"/>
+      <c r="C466" s="160"/>
+      <c r="D466" s="157"/>
       <c r="E466" s="8" t="s">
         <v>590</v>
       </c>
@@ -14928,8 +15213,8 @@
       <c r="B467" s="7">
         <v>9</v>
       </c>
-      <c r="C467" s="135"/>
-      <c r="D467" s="143" t="s">
+      <c r="C467" s="160"/>
+      <c r="D467" s="135" t="s">
         <v>591</v>
       </c>
       <c r="E467" s="8" t="s">
@@ -14952,8 +15237,8 @@
       <c r="B468" s="7">
         <v>10</v>
       </c>
-      <c r="C468" s="135"/>
-      <c r="D468" s="135"/>
+      <c r="C468" s="160"/>
+      <c r="D468" s="156"/>
       <c r="E468" s="8" t="s">
         <v>593</v>
       </c>
@@ -14974,8 +15259,8 @@
       <c r="B469" s="7">
         <v>11</v>
       </c>
-      <c r="C469" s="135"/>
-      <c r="D469" s="135"/>
+      <c r="C469" s="160"/>
+      <c r="D469" s="156"/>
       <c r="E469" s="8" t="s">
         <v>594</v>
       </c>
@@ -14996,8 +15281,8 @@
       <c r="B470" s="7">
         <v>12</v>
       </c>
-      <c r="C470" s="135"/>
-      <c r="D470" s="135"/>
+      <c r="C470" s="160"/>
+      <c r="D470" s="156"/>
       <c r="E470" s="8" t="s">
         <v>595</v>
       </c>
@@ -15018,8 +15303,8 @@
       <c r="B471" s="7">
         <v>13</v>
       </c>
-      <c r="C471" s="135"/>
-      <c r="D471" s="135"/>
+      <c r="C471" s="160"/>
+      <c r="D471" s="156"/>
       <c r="E471" s="8" t="s">
         <v>596</v>
       </c>
@@ -15040,8 +15325,8 @@
       <c r="B472" s="7">
         <v>14</v>
       </c>
-      <c r="C472" s="135"/>
-      <c r="D472" s="135"/>
+      <c r="C472" s="160"/>
+      <c r="D472" s="156"/>
       <c r="E472" s="8" t="s">
         <v>597</v>
       </c>
@@ -15062,8 +15347,8 @@
       <c r="B473" s="7">
         <v>15</v>
       </c>
-      <c r="C473" s="135"/>
-      <c r="D473" s="136"/>
+      <c r="C473" s="160"/>
+      <c r="D473" s="157"/>
       <c r="E473" s="8" t="s">
         <v>598</v>
       </c>
@@ -15084,8 +15369,8 @@
       <c r="B474" s="7">
         <v>16</v>
       </c>
-      <c r="C474" s="135"/>
-      <c r="D474" s="143" t="s">
+      <c r="C474" s="160"/>
+      <c r="D474" s="135" t="s">
         <v>599</v>
       </c>
       <c r="E474" s="8" t="s">
@@ -15108,8 +15393,8 @@
       <c r="B475" s="7">
         <v>17</v>
       </c>
-      <c r="C475" s="135"/>
-      <c r="D475" s="135"/>
+      <c r="C475" s="160"/>
+      <c r="D475" s="156"/>
       <c r="E475" s="8" t="s">
         <v>601</v>
       </c>
@@ -15130,8 +15415,8 @@
       <c r="B476" s="7">
         <v>18</v>
       </c>
-      <c r="C476" s="135"/>
-      <c r="D476" s="135"/>
+      <c r="C476" s="160"/>
+      <c r="D476" s="156"/>
       <c r="E476" s="8" t="s">
         <v>602</v>
       </c>
@@ -15152,8 +15437,8 @@
       <c r="B477" s="7">
         <v>19</v>
       </c>
-      <c r="C477" s="135"/>
-      <c r="D477" s="135"/>
+      <c r="C477" s="160"/>
+      <c r="D477" s="156"/>
       <c r="E477" s="8" t="s">
         <v>603</v>
       </c>
@@ -15174,8 +15459,8 @@
       <c r="B478" s="7">
         <v>20</v>
       </c>
-      <c r="C478" s="135"/>
-      <c r="D478" s="135"/>
+      <c r="C478" s="160"/>
+      <c r="D478" s="156"/>
       <c r="E478" s="8" t="s">
         <v>604</v>
       </c>
@@ -15196,8 +15481,8 @@
       <c r="B479" s="7">
         <v>21</v>
       </c>
-      <c r="C479" s="135"/>
-      <c r="D479" s="135"/>
+      <c r="C479" s="160"/>
+      <c r="D479" s="156"/>
       <c r="E479" s="8" t="s">
         <v>605</v>
       </c>
@@ -15218,8 +15503,8 @@
       <c r="B480" s="7">
         <v>22</v>
       </c>
-      <c r="C480" s="135"/>
-      <c r="D480" s="135"/>
+      <c r="C480" s="160"/>
+      <c r="D480" s="156"/>
       <c r="E480" s="8" t="s">
         <v>606</v>
       </c>
@@ -15240,8 +15525,8 @@
       <c r="B481" s="7">
         <v>23</v>
       </c>
-      <c r="C481" s="135"/>
-      <c r="D481" s="136"/>
+      <c r="C481" s="160"/>
+      <c r="D481" s="157"/>
       <c r="E481" s="8" t="s">
         <v>607</v>
       </c>
@@ -15262,8 +15547,8 @@
       <c r="B482" s="7">
         <v>24</v>
       </c>
-      <c r="C482" s="135"/>
-      <c r="D482" s="143" t="s">
+      <c r="C482" s="160"/>
+      <c r="D482" s="135" t="s">
         <v>608</v>
       </c>
       <c r="E482" s="8" t="s">
@@ -15286,8 +15571,8 @@
       <c r="B483" s="7">
         <v>25</v>
       </c>
-      <c r="C483" s="135"/>
-      <c r="D483" s="135"/>
+      <c r="C483" s="160"/>
+      <c r="D483" s="156"/>
       <c r="E483" s="8" t="s">
         <v>610</v>
       </c>
@@ -15308,8 +15593,8 @@
       <c r="B484" s="7">
         <v>26</v>
       </c>
-      <c r="C484" s="135"/>
-      <c r="D484" s="135"/>
+      <c r="C484" s="160"/>
+      <c r="D484" s="156"/>
       <c r="E484" s="8" t="s">
         <v>611</v>
       </c>
@@ -15330,8 +15615,8 @@
       <c r="B485" s="7">
         <v>27</v>
       </c>
-      <c r="C485" s="135"/>
-      <c r="D485" s="136"/>
+      <c r="C485" s="160"/>
+      <c r="D485" s="157"/>
       <c r="E485" s="8" t="s">
         <v>612</v>
       </c>
@@ -15352,8 +15637,8 @@
       <c r="B486" s="7">
         <v>28</v>
       </c>
-      <c r="C486" s="135"/>
-      <c r="D486" s="143" t="s">
+      <c r="C486" s="160"/>
+      <c r="D486" s="135" t="s">
         <v>613</v>
       </c>
       <c r="E486" s="8" t="s">
@@ -15376,8 +15661,8 @@
       <c r="B487" s="7">
         <v>29</v>
       </c>
-      <c r="C487" s="135"/>
-      <c r="D487" s="135"/>
+      <c r="C487" s="160"/>
+      <c r="D487" s="156"/>
       <c r="E487" s="8" t="s">
         <v>615</v>
       </c>
@@ -15398,8 +15683,8 @@
       <c r="B488" s="7">
         <v>30</v>
       </c>
-      <c r="C488" s="135"/>
-      <c r="D488" s="135"/>
+      <c r="C488" s="160"/>
+      <c r="D488" s="156"/>
       <c r="E488" s="8" t="s">
         <v>616</v>
       </c>
@@ -15420,8 +15705,8 @@
       <c r="B489" s="7">
         <v>31</v>
       </c>
-      <c r="C489" s="135"/>
-      <c r="D489" s="135"/>
+      <c r="C489" s="160"/>
+      <c r="D489" s="156"/>
       <c r="E489" s="8" t="s">
         <v>617</v>
       </c>
@@ -15442,8 +15727,8 @@
       <c r="B490" s="7">
         <v>32</v>
       </c>
-      <c r="C490" s="135"/>
-      <c r="D490" s="135"/>
+      <c r="C490" s="160"/>
+      <c r="D490" s="156"/>
       <c r="E490" s="8" t="s">
         <v>618</v>
       </c>
@@ -15464,8 +15749,8 @@
       <c r="B491" s="7">
         <v>33</v>
       </c>
-      <c r="C491" s="135"/>
-      <c r="D491" s="135"/>
+      <c r="C491" s="160"/>
+      <c r="D491" s="156"/>
       <c r="E491" s="8" t="s">
         <v>619</v>
       </c>
@@ -15486,8 +15771,8 @@
       <c r="B492" s="7">
         <v>34</v>
       </c>
-      <c r="C492" s="135"/>
-      <c r="D492" s="135"/>
+      <c r="C492" s="160"/>
+      <c r="D492" s="156"/>
       <c r="E492" s="8" t="s">
         <v>620</v>
       </c>
@@ -15508,8 +15793,8 @@
       <c r="B493" s="7">
         <v>35</v>
       </c>
-      <c r="C493" s="135"/>
-      <c r="D493" s="135"/>
+      <c r="C493" s="160"/>
+      <c r="D493" s="156"/>
       <c r="E493" s="8" t="s">
         <v>621</v>
       </c>
@@ -15530,8 +15815,8 @@
       <c r="B494" s="7">
         <v>36</v>
       </c>
-      <c r="C494" s="135"/>
-      <c r="D494" s="135"/>
+      <c r="C494" s="160"/>
+      <c r="D494" s="156"/>
       <c r="E494" s="8" t="s">
         <v>622</v>
       </c>
@@ -15552,8 +15837,8 @@
       <c r="B495" s="7">
         <v>37</v>
       </c>
-      <c r="C495" s="135"/>
-      <c r="D495" s="135"/>
+      <c r="C495" s="160"/>
+      <c r="D495" s="156"/>
       <c r="E495" s="8" t="s">
         <v>623</v>
       </c>
@@ -15574,8 +15859,8 @@
       <c r="B496" s="7">
         <v>38</v>
       </c>
-      <c r="C496" s="135"/>
-      <c r="D496" s="136"/>
+      <c r="C496" s="160"/>
+      <c r="D496" s="157"/>
       <c r="E496" s="8" t="s">
         <v>624</v>
       </c>
@@ -15596,8 +15881,8 @@
       <c r="B497" s="7">
         <v>39</v>
       </c>
-      <c r="C497" s="135"/>
-      <c r="D497" s="143" t="s">
+      <c r="C497" s="160"/>
+      <c r="D497" s="135" t="s">
         <v>625</v>
       </c>
       <c r="E497" s="8" t="s">
@@ -15620,8 +15905,8 @@
       <c r="B498" s="7">
         <v>40</v>
       </c>
-      <c r="C498" s="135"/>
-      <c r="D498" s="135"/>
+      <c r="C498" s="160"/>
+      <c r="D498" s="156"/>
       <c r="E498" s="8" t="s">
         <v>626</v>
       </c>
@@ -15642,8 +15927,8 @@
       <c r="B499" s="7">
         <v>41</v>
       </c>
-      <c r="C499" s="135"/>
-      <c r="D499" s="135"/>
+      <c r="C499" s="160"/>
+      <c r="D499" s="156"/>
       <c r="E499" s="8" t="s">
         <v>627</v>
       </c>
@@ -15664,8 +15949,8 @@
       <c r="B500" s="7">
         <v>42</v>
       </c>
-      <c r="C500" s="135"/>
-      <c r="D500" s="135"/>
+      <c r="C500" s="160"/>
+      <c r="D500" s="156"/>
       <c r="E500" s="8" t="s">
         <v>628</v>
       </c>
@@ -15686,8 +15971,8 @@
       <c r="B501" s="7">
         <v>43</v>
       </c>
-      <c r="C501" s="135"/>
-      <c r="D501" s="135"/>
+      <c r="C501" s="160"/>
+      <c r="D501" s="156"/>
       <c r="E501" s="8" t="s">
         <v>629</v>
       </c>
@@ -15708,8 +15993,8 @@
       <c r="B502" s="7">
         <v>44</v>
       </c>
-      <c r="C502" s="135"/>
-      <c r="D502" s="136"/>
+      <c r="C502" s="160"/>
+      <c r="D502" s="157"/>
       <c r="E502" s="8" t="s">
         <v>630</v>
       </c>
@@ -15730,8 +16015,8 @@
       <c r="B503" s="7">
         <v>45</v>
       </c>
-      <c r="C503" s="135"/>
-      <c r="D503" s="143" t="s">
+      <c r="C503" s="160"/>
+      <c r="D503" s="135" t="s">
         <v>631</v>
       </c>
       <c r="E503" s="8" t="s">
@@ -15754,8 +16039,8 @@
       <c r="B504" s="7">
         <v>46</v>
       </c>
-      <c r="C504" s="135"/>
-      <c r="D504" s="135"/>
+      <c r="C504" s="160"/>
+      <c r="D504" s="156"/>
       <c r="E504" s="8" t="s">
         <v>633</v>
       </c>
@@ -15776,8 +16061,8 @@
       <c r="B505" s="7">
         <v>47</v>
       </c>
-      <c r="C505" s="135"/>
-      <c r="D505" s="135"/>
+      <c r="C505" s="160"/>
+      <c r="D505" s="156"/>
       <c r="E505" s="8" t="s">
         <v>634</v>
       </c>
@@ -15798,8 +16083,8 @@
       <c r="B506" s="7">
         <v>48</v>
       </c>
-      <c r="C506" s="135"/>
-      <c r="D506" s="135"/>
+      <c r="C506" s="160"/>
+      <c r="D506" s="156"/>
       <c r="E506" s="8" t="s">
         <v>635</v>
       </c>
@@ -15820,8 +16105,8 @@
       <c r="B507" s="7">
         <v>49</v>
       </c>
-      <c r="C507" s="135"/>
-      <c r="D507" s="135"/>
+      <c r="C507" s="160"/>
+      <c r="D507" s="156"/>
       <c r="E507" s="8" t="s">
         <v>636</v>
       </c>
@@ -15842,8 +16127,8 @@
       <c r="B508" s="7">
         <v>50</v>
       </c>
-      <c r="C508" s="135"/>
-      <c r="D508" s="135"/>
+      <c r="C508" s="160"/>
+      <c r="D508" s="156"/>
       <c r="E508" s="8" t="s">
         <v>637</v>
       </c>
@@ -15864,8 +16149,8 @@
       <c r="B509" s="7">
         <v>51</v>
       </c>
-      <c r="C509" s="135"/>
-      <c r="D509" s="136"/>
+      <c r="C509" s="160"/>
+      <c r="D509" s="157"/>
       <c r="E509" s="8" t="s">
         <v>638</v>
       </c>
@@ -15886,8 +16171,8 @@
       <c r="B510" s="7">
         <v>52</v>
       </c>
-      <c r="C510" s="135"/>
-      <c r="D510" s="143" t="s">
+      <c r="C510" s="160"/>
+      <c r="D510" s="135" t="s">
         <v>639</v>
       </c>
       <c r="E510" s="8" t="s">
@@ -15910,8 +16195,8 @@
       <c r="B511" s="7">
         <v>53</v>
       </c>
-      <c r="C511" s="135"/>
-      <c r="D511" s="135"/>
+      <c r="C511" s="160"/>
+      <c r="D511" s="156"/>
       <c r="E511" s="8" t="s">
         <v>641</v>
       </c>
@@ -15932,8 +16217,8 @@
       <c r="B512" s="7">
         <v>54</v>
       </c>
-      <c r="C512" s="135"/>
-      <c r="D512" s="135"/>
+      <c r="C512" s="160"/>
+      <c r="D512" s="156"/>
       <c r="E512" s="8" t="s">
         <v>642</v>
       </c>
@@ -15954,8 +16239,8 @@
       <c r="B513" s="24">
         <v>55</v>
       </c>
-      <c r="C513" s="136"/>
-      <c r="D513" s="136"/>
+      <c r="C513" s="161"/>
+      <c r="D513" s="157"/>
       <c r="E513" s="17" t="s">
         <v>643</v>
       </c>
@@ -22889,47 +23174,66 @@
     </row>
   </sheetData>
   <mergeCells count="125">
-    <mergeCell ref="D26:D32"/>
-    <mergeCell ref="D33:D36"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="C4:C32"/>
-    <mergeCell ref="D4:D9"/>
-    <mergeCell ref="D10:D18"/>
-    <mergeCell ref="D19:D25"/>
-    <mergeCell ref="C33:C44"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="D40:D44"/>
-    <mergeCell ref="C107:C116"/>
-    <mergeCell ref="C117:C125"/>
-    <mergeCell ref="C127:C132"/>
-    <mergeCell ref="C134:C176"/>
-    <mergeCell ref="C177:C204"/>
-    <mergeCell ref="C205:C214"/>
-    <mergeCell ref="A106:J106"/>
-    <mergeCell ref="D107:D111"/>
-    <mergeCell ref="D112:D115"/>
-    <mergeCell ref="D117:D120"/>
-    <mergeCell ref="D121:D122"/>
-    <mergeCell ref="D123:D125"/>
-    <mergeCell ref="A126:J126"/>
-    <mergeCell ref="D127:D130"/>
-    <mergeCell ref="D131:D132"/>
-    <mergeCell ref="A133:J133"/>
-    <mergeCell ref="D210:D211"/>
-    <mergeCell ref="D212:D214"/>
-    <mergeCell ref="C45:C50"/>
-    <mergeCell ref="D45:D50"/>
-    <mergeCell ref="D51:D57"/>
-    <mergeCell ref="D58:D63"/>
-    <mergeCell ref="D64:D67"/>
-    <mergeCell ref="D69:D78"/>
-    <mergeCell ref="D79:D84"/>
-    <mergeCell ref="D85:D90"/>
-    <mergeCell ref="D91:D105"/>
-    <mergeCell ref="A68:J68"/>
-    <mergeCell ref="C51:C67"/>
-    <mergeCell ref="C69:C105"/>
+    <mergeCell ref="C459:C513"/>
+    <mergeCell ref="C216:C249"/>
+    <mergeCell ref="C250:C265"/>
+    <mergeCell ref="C266:C272"/>
+    <mergeCell ref="C274:C292"/>
+    <mergeCell ref="C293:C307"/>
+    <mergeCell ref="C308:C317"/>
+    <mergeCell ref="C318:C342"/>
+    <mergeCell ref="D459:D466"/>
+    <mergeCell ref="D467:D473"/>
+    <mergeCell ref="D474:D481"/>
+    <mergeCell ref="D482:D485"/>
+    <mergeCell ref="D486:D496"/>
+    <mergeCell ref="D497:D502"/>
+    <mergeCell ref="D503:D509"/>
+    <mergeCell ref="D510:D513"/>
+    <mergeCell ref="D318:D323"/>
+    <mergeCell ref="D324:D328"/>
+    <mergeCell ref="D329:D337"/>
+    <mergeCell ref="D338:D342"/>
+    <mergeCell ref="D343:D347"/>
+    <mergeCell ref="D348:D353"/>
+    <mergeCell ref="D354:D357"/>
+    <mergeCell ref="D296:D300"/>
+    <mergeCell ref="D301:D303"/>
+    <mergeCell ref="D304:D307"/>
+    <mergeCell ref="D308:D314"/>
+    <mergeCell ref="D315:D317"/>
+    <mergeCell ref="C343:C357"/>
+    <mergeCell ref="C359:C380"/>
+    <mergeCell ref="C381:C435"/>
+    <mergeCell ref="C437:C458"/>
+    <mergeCell ref="D250:D257"/>
+    <mergeCell ref="D258:D259"/>
+    <mergeCell ref="D260:D265"/>
+    <mergeCell ref="D266:D270"/>
+    <mergeCell ref="D271:D272"/>
+    <mergeCell ref="D274:D281"/>
+    <mergeCell ref="D282:D288"/>
+    <mergeCell ref="D289:D292"/>
+    <mergeCell ref="D293:D295"/>
+    <mergeCell ref="D449:D452"/>
+    <mergeCell ref="D453:D458"/>
+    <mergeCell ref="D417:D419"/>
+    <mergeCell ref="D420:D426"/>
+    <mergeCell ref="D427:D430"/>
+    <mergeCell ref="D431:D435"/>
+    <mergeCell ref="D437:D441"/>
+    <mergeCell ref="D442:D445"/>
+    <mergeCell ref="D446:D448"/>
+    <mergeCell ref="D400:D404"/>
+    <mergeCell ref="D405:D416"/>
+    <mergeCell ref="A436:J436"/>
+    <mergeCell ref="D359:D363"/>
+    <mergeCell ref="D364:D371"/>
+    <mergeCell ref="D372:D375"/>
+    <mergeCell ref="D376:D380"/>
+    <mergeCell ref="D381:D386"/>
+    <mergeCell ref="D387:D396"/>
+    <mergeCell ref="D397:D399"/>
     <mergeCell ref="A215:J215"/>
     <mergeCell ref="A273:J273"/>
     <mergeCell ref="A358:J358"/>
@@ -22954,66 +23258,47 @@
     <mergeCell ref="D234:D240"/>
     <mergeCell ref="D241:D243"/>
     <mergeCell ref="D244:D249"/>
-    <mergeCell ref="D442:D445"/>
-    <mergeCell ref="D446:D448"/>
-    <mergeCell ref="D400:D404"/>
-    <mergeCell ref="D405:D416"/>
-    <mergeCell ref="A436:J436"/>
-    <mergeCell ref="D359:D363"/>
-    <mergeCell ref="D364:D371"/>
-    <mergeCell ref="D372:D375"/>
-    <mergeCell ref="D376:D380"/>
-    <mergeCell ref="D381:D386"/>
-    <mergeCell ref="D387:D396"/>
-    <mergeCell ref="D397:D399"/>
-    <mergeCell ref="D301:D303"/>
-    <mergeCell ref="D304:D307"/>
-    <mergeCell ref="D308:D314"/>
-    <mergeCell ref="D315:D317"/>
-    <mergeCell ref="C343:C357"/>
-    <mergeCell ref="C359:C380"/>
-    <mergeCell ref="C381:C435"/>
-    <mergeCell ref="C437:C458"/>
-    <mergeCell ref="D250:D257"/>
-    <mergeCell ref="D258:D259"/>
-    <mergeCell ref="D260:D265"/>
-    <mergeCell ref="D266:D270"/>
-    <mergeCell ref="D271:D272"/>
-    <mergeCell ref="D274:D281"/>
-    <mergeCell ref="D282:D288"/>
-    <mergeCell ref="D289:D292"/>
-    <mergeCell ref="D293:D295"/>
-    <mergeCell ref="D449:D452"/>
-    <mergeCell ref="D453:D458"/>
-    <mergeCell ref="D417:D419"/>
-    <mergeCell ref="D420:D426"/>
-    <mergeCell ref="D427:D430"/>
-    <mergeCell ref="D431:D435"/>
-    <mergeCell ref="D437:D441"/>
-    <mergeCell ref="C459:C513"/>
-    <mergeCell ref="C216:C249"/>
-    <mergeCell ref="C250:C265"/>
-    <mergeCell ref="C266:C272"/>
-    <mergeCell ref="C274:C292"/>
-    <mergeCell ref="C293:C307"/>
-    <mergeCell ref="C308:C317"/>
-    <mergeCell ref="C318:C342"/>
-    <mergeCell ref="D459:D466"/>
-    <mergeCell ref="D467:D473"/>
-    <mergeCell ref="D474:D481"/>
-    <mergeCell ref="D482:D485"/>
-    <mergeCell ref="D486:D496"/>
-    <mergeCell ref="D497:D502"/>
-    <mergeCell ref="D503:D509"/>
-    <mergeCell ref="D510:D513"/>
-    <mergeCell ref="D318:D323"/>
-    <mergeCell ref="D324:D328"/>
-    <mergeCell ref="D329:D337"/>
-    <mergeCell ref="D338:D342"/>
-    <mergeCell ref="D343:D347"/>
-    <mergeCell ref="D348:D353"/>
-    <mergeCell ref="D354:D357"/>
-    <mergeCell ref="D296:D300"/>
+    <mergeCell ref="C45:C50"/>
+    <mergeCell ref="D45:D50"/>
+    <mergeCell ref="D51:D57"/>
+    <mergeCell ref="D58:D63"/>
+    <mergeCell ref="D64:D67"/>
+    <mergeCell ref="D69:D78"/>
+    <mergeCell ref="D79:D84"/>
+    <mergeCell ref="D85:D90"/>
+    <mergeCell ref="D91:D105"/>
+    <mergeCell ref="A68:J68"/>
+    <mergeCell ref="C51:C67"/>
+    <mergeCell ref="C69:C105"/>
+    <mergeCell ref="C107:C116"/>
+    <mergeCell ref="C117:C125"/>
+    <mergeCell ref="C127:C132"/>
+    <mergeCell ref="C134:C176"/>
+    <mergeCell ref="C177:C204"/>
+    <mergeCell ref="C205:C214"/>
+    <mergeCell ref="A106:J106"/>
+    <mergeCell ref="D107:D111"/>
+    <mergeCell ref="D112:D115"/>
+    <mergeCell ref="D117:D120"/>
+    <mergeCell ref="D121:D122"/>
+    <mergeCell ref="D123:D125"/>
+    <mergeCell ref="A126:J126"/>
+    <mergeCell ref="D127:D130"/>
+    <mergeCell ref="D131:D132"/>
+    <mergeCell ref="A133:J133"/>
+    <mergeCell ref="D210:D211"/>
+    <mergeCell ref="D212:D214"/>
+    <mergeCell ref="D26:D32"/>
+    <mergeCell ref="D33:D36"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="C4:C32"/>
+    <mergeCell ref="D4:D9"/>
+    <mergeCell ref="D10:D18"/>
+    <mergeCell ref="D19:D25"/>
+    <mergeCell ref="C33:C44"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="D40:D44"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H67 H69:H105 H107:H125 H127:H132 H134:H214 H216:H272 H274:H357 H359:H435 H437:H513" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -23030,501 +23315,501 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="F4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="F5" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="F6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="F7" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="F8" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="F9" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="F10" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="F11" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="F12" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="F13" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="F14" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="F15" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="F16" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="F17" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="F18" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="F19" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="F20" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="F21" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="F22" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="F23" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="F24" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="F25" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="F26" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="F27" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="F28" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="F29" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="F30" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="F31" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="F32" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="F33" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="F34" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="F35" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="F36" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="F37" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="F38" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="F39" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="F40" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="F41" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="F42" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="F43" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="F44" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="F45" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="F46" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="F47" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="F48" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="F49" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="F50" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="F51" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="F52" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="F53" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="F54" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="F55" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="F56" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="F57" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="F58" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="F59" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="F60" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="F61" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="F62" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="F63" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="F64" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="F65" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="F66" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="F67" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="F69" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="F70" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="F71" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="F72" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="F73" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="F74" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="F75" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="F76" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="F77" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="F78" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="F79" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="F80" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="F81" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="F82" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="F83" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="F84" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="F85" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="F86" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="F87" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="F88" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="F89" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="F90" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="F91" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="F92" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="F93" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="F94" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="F95" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="F96" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="F97" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="F98" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="F99" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="F100" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="F101" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="F102" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="F103" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="F104" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="F105" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="F107" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="I355" r:id="rId1" display="https://www.geeksforgeeks.org/problems/bleak-numbers1552/1?page=6&amp;category=Bit%20Magic&amp;sortBy=difficulty" xr:uid="{B278AF57-6FD5-47BA-B637-A66848ECE515}"/>
+    <hyperlink ref="I354" r:id="rId2" display="https://www.geeksforgeeks.org/problems/count-total-set-bits-1587115620/1?page=1&amp;category=Bit%20Magic&amp;sortBy=submissions" xr:uid="{39FD791E-2FA5-4251-A8B8-D37477C8188C}"/>
+    <hyperlink ref="I346" r:id="rId3" display="https://leetcode.com/problems/number-of-even-and-odd-bits/" xr:uid="{F5BACACB-0735-4CF8-A9F9-EEB3416037CD}"/>
+    <hyperlink ref="F513" r:id="rId4" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
+    <hyperlink ref="F512" r:id="rId5" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
+    <hyperlink ref="F511" r:id="rId6" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
+    <hyperlink ref="F510" r:id="rId7" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
+    <hyperlink ref="F509" r:id="rId8" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
+    <hyperlink ref="F508" r:id="rId9" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
+    <hyperlink ref="F507" r:id="rId10" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
+    <hyperlink ref="F506" r:id="rId11" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
+    <hyperlink ref="F505" r:id="rId12" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
+    <hyperlink ref="F504" r:id="rId13" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
+    <hyperlink ref="F503" r:id="rId14" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
+    <hyperlink ref="F502" r:id="rId15" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
+    <hyperlink ref="F501" r:id="rId16" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
+    <hyperlink ref="F500" r:id="rId17" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
+    <hyperlink ref="F499" r:id="rId18" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
+    <hyperlink ref="F498" r:id="rId19" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
+    <hyperlink ref="F497" r:id="rId20" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
+    <hyperlink ref="F496" r:id="rId21" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
+    <hyperlink ref="F495" r:id="rId22" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
+    <hyperlink ref="F494" r:id="rId23" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
+    <hyperlink ref="F493" r:id="rId24" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
+    <hyperlink ref="F492" r:id="rId25" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
+    <hyperlink ref="F491" r:id="rId26" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
+    <hyperlink ref="F490" r:id="rId27" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
+    <hyperlink ref="F489" r:id="rId28" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
+    <hyperlink ref="F488" r:id="rId29" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
+    <hyperlink ref="F487" r:id="rId30" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
+    <hyperlink ref="F486" r:id="rId31" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
+    <hyperlink ref="F485" r:id="rId32" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
+    <hyperlink ref="F484" r:id="rId33" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
+    <hyperlink ref="F483" r:id="rId34" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
+    <hyperlink ref="F482" r:id="rId35" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
+    <hyperlink ref="F481" r:id="rId36" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
+    <hyperlink ref="F480" r:id="rId37" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
+    <hyperlink ref="F479" r:id="rId38" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
+    <hyperlink ref="F478" r:id="rId39" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
+    <hyperlink ref="F477" r:id="rId40" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
+    <hyperlink ref="F476" r:id="rId41" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
+    <hyperlink ref="F475" r:id="rId42" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
+    <hyperlink ref="F474" r:id="rId43" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
+    <hyperlink ref="F473" r:id="rId44" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
+    <hyperlink ref="F472" r:id="rId45" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
+    <hyperlink ref="F471" r:id="rId46" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
+    <hyperlink ref="F470" r:id="rId47" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
+    <hyperlink ref="F469" r:id="rId48" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
+    <hyperlink ref="F468" r:id="rId49" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
+    <hyperlink ref="F467" r:id="rId50" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
+    <hyperlink ref="F466" r:id="rId51" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
+    <hyperlink ref="F465" r:id="rId52" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
+    <hyperlink ref="F464" r:id="rId53" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
+    <hyperlink ref="F463" r:id="rId54" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
+    <hyperlink ref="F462" r:id="rId55" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
+    <hyperlink ref="F461" r:id="rId56" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
+    <hyperlink ref="F460" r:id="rId57" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
+    <hyperlink ref="F459" r:id="rId58" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
+    <hyperlink ref="F458" r:id="rId59" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
+    <hyperlink ref="F457" r:id="rId60" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
+    <hyperlink ref="F456" r:id="rId61" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
+    <hyperlink ref="F455" r:id="rId62" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
+    <hyperlink ref="F454" r:id="rId63" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
+    <hyperlink ref="F453" r:id="rId64" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
+    <hyperlink ref="F452" r:id="rId65" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
+    <hyperlink ref="F451" r:id="rId66" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
+    <hyperlink ref="F450" r:id="rId67" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
+    <hyperlink ref="F449" r:id="rId68" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
+    <hyperlink ref="F448" r:id="rId69" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
+    <hyperlink ref="F447" r:id="rId70" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
+    <hyperlink ref="F446" r:id="rId71" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
+    <hyperlink ref="F445" r:id="rId72" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
+    <hyperlink ref="F444" r:id="rId73" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
+    <hyperlink ref="F443" r:id="rId74" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
+    <hyperlink ref="F442" r:id="rId75" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
+    <hyperlink ref="F441" r:id="rId76" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
+    <hyperlink ref="F440" r:id="rId77" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
+    <hyperlink ref="F439" r:id="rId78" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
+    <hyperlink ref="F437" r:id="rId79" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
+    <hyperlink ref="F435" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
+    <hyperlink ref="F434" r:id="rId81" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
+    <hyperlink ref="F433" r:id="rId82" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
+    <hyperlink ref="F432" r:id="rId83" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
+    <hyperlink ref="F431" r:id="rId84" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
+    <hyperlink ref="F430" r:id="rId85" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
+    <hyperlink ref="F429" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
+    <hyperlink ref="F428" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
+    <hyperlink ref="F426" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
+    <hyperlink ref="F425" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
+    <hyperlink ref="F424" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
+    <hyperlink ref="F423" r:id="rId91" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
+    <hyperlink ref="F422" r:id="rId92" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
+    <hyperlink ref="F421" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
+    <hyperlink ref="F420" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
+    <hyperlink ref="F419" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
+    <hyperlink ref="F418" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
+    <hyperlink ref="F417" r:id="rId97" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
+    <hyperlink ref="F416" r:id="rId98" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
+    <hyperlink ref="F415" r:id="rId99" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
+    <hyperlink ref="F414" r:id="rId100" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
+    <hyperlink ref="F413" r:id="rId101" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
+    <hyperlink ref="F412" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
+    <hyperlink ref="F411" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
+    <hyperlink ref="F410" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
+    <hyperlink ref="F409" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
+    <hyperlink ref="F408" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
+    <hyperlink ref="F407" r:id="rId107" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
+    <hyperlink ref="F406" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
+    <hyperlink ref="F405" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
+    <hyperlink ref="F404" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
+    <hyperlink ref="F403" r:id="rId111" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
+    <hyperlink ref="F402" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
+    <hyperlink ref="F401" r:id="rId113" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="F400" r:id="rId114" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="F399" r:id="rId115" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="F398" r:id="rId116" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="F397" r:id="rId117" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="F396" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="F395" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="F394" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="F393" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="F392" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="F391" r:id="rId123" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="F390" r:id="rId124" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
+    <hyperlink ref="F389" r:id="rId125" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
+    <hyperlink ref="F388" r:id="rId126" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
+    <hyperlink ref="F387" r:id="rId127" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
+    <hyperlink ref="F386" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="F385" r:id="rId129" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="F384" r:id="rId130" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="F383" r:id="rId131" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="F382" r:id="rId132" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="F381" r:id="rId133" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="F380" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="F379" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="F378" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="F377" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="F376" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="F375" r:id="rId139" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="F374" r:id="rId140" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="F373" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="F372" r:id="rId142" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="F371" r:id="rId143" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="F370" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="F369" r:id="rId145" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="F368" r:id="rId146" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="F367" r:id="rId147" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="F366" r:id="rId148" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="F365" r:id="rId149" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="F364" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="F363" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="F362" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="F361" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="F360" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="F359" r:id="rId155" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="F357" r:id="rId156" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="F356" r:id="rId157" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="F355" r:id="rId158" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="F354" r:id="rId159" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
+    <hyperlink ref="F353" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="F352" r:id="rId161" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="F351" r:id="rId162" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="F350" r:id="rId163" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="F349" r:id="rId164" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="F348" r:id="rId165" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="F347" r:id="rId166" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="F346" r:id="rId167" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="F345" r:id="rId168" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="F344" r:id="rId169" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="F343" r:id="rId170" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="F342" r:id="rId171" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="F341" r:id="rId172" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="F340" r:id="rId173" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="F339" r:id="rId174" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="F338" r:id="rId175" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
+    <hyperlink ref="F337" r:id="rId176" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="F336" r:id="rId177" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="F335" r:id="rId178" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="F334" r:id="rId179" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="F333" r:id="rId180" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="F332" r:id="rId181" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="F331" r:id="rId182" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
+    <hyperlink ref="F330" r:id="rId183" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
+    <hyperlink ref="F329" r:id="rId184" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
+    <hyperlink ref="F328" r:id="rId185" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
+    <hyperlink ref="F327" r:id="rId186" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="F326" r:id="rId187" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="F325" r:id="rId188" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
+    <hyperlink ref="F324" r:id="rId189" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
+    <hyperlink ref="F323" r:id="rId190" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
+    <hyperlink ref="F322" r:id="rId191" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
+    <hyperlink ref="F321" r:id="rId192" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
+    <hyperlink ref="F320" r:id="rId193" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
+    <hyperlink ref="F319" r:id="rId194" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
+    <hyperlink ref="F318" r:id="rId195" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
+    <hyperlink ref="F317" r:id="rId196" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
+    <hyperlink ref="F316" r:id="rId197" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
+    <hyperlink ref="F315" r:id="rId198" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
+    <hyperlink ref="F314" r:id="rId199" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
+    <hyperlink ref="F313" r:id="rId200" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
+    <hyperlink ref="F312" r:id="rId201" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
+    <hyperlink ref="F311" r:id="rId202" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
+    <hyperlink ref="F310" r:id="rId203" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
+    <hyperlink ref="F309" r:id="rId204" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
+    <hyperlink ref="F308" r:id="rId205" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
+    <hyperlink ref="F307" r:id="rId206" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
+    <hyperlink ref="F306" r:id="rId207" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
+    <hyperlink ref="F305" r:id="rId208" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
+    <hyperlink ref="F304" r:id="rId209" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="F303" r:id="rId210" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
+    <hyperlink ref="F302" r:id="rId211" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
+    <hyperlink ref="F301" r:id="rId212" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="F300" r:id="rId213" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
+    <hyperlink ref="F299" r:id="rId214" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
+    <hyperlink ref="F298" r:id="rId215" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
+    <hyperlink ref="F297" r:id="rId216" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
+    <hyperlink ref="F296" r:id="rId217" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
+    <hyperlink ref="F294" r:id="rId218" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
+    <hyperlink ref="F293" r:id="rId219" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
+    <hyperlink ref="F292" r:id="rId220" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
+    <hyperlink ref="F291" r:id="rId221" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
+    <hyperlink ref="F290" r:id="rId222" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
+    <hyperlink ref="F289" r:id="rId223" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
+    <hyperlink ref="F288" r:id="rId224" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
+    <hyperlink ref="F287" r:id="rId225" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
+    <hyperlink ref="F286" r:id="rId226" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
+    <hyperlink ref="F285" r:id="rId227" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
+    <hyperlink ref="F284" r:id="rId228" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
+    <hyperlink ref="F283" r:id="rId229" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
+    <hyperlink ref="F282" r:id="rId230" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
+    <hyperlink ref="F281" r:id="rId231" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
+    <hyperlink ref="F280" r:id="rId232" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
+    <hyperlink ref="F279" r:id="rId233" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="F278" r:id="rId234" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="F277" r:id="rId235" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="F276" r:id="rId236" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="F275" r:id="rId237" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="F274" r:id="rId238" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="F272" r:id="rId239" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="F271" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="F270" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="F269" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="F268" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="F267" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="F266" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="F265" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="F264" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="F263" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="F262" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="F261" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="F260" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
+    <hyperlink ref="F259" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
+    <hyperlink ref="F258" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
+    <hyperlink ref="F257" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
+    <hyperlink ref="F256" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="F255" r:id="rId256" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
+    <hyperlink ref="F254" r:id="rId257" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
+    <hyperlink ref="F253" r:id="rId258" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
+    <hyperlink ref="F252" r:id="rId259" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
+    <hyperlink ref="F251" r:id="rId260" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
+    <hyperlink ref="F250" r:id="rId261" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="F249" r:id="rId262" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="F248" r:id="rId263" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="F247" r:id="rId264" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="F246" r:id="rId265" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="F245" r:id="rId266" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="F244" r:id="rId267" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="F243" r:id="rId268" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="F242" r:id="rId269" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="F241" r:id="rId270" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="F240" r:id="rId271" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="F239" r:id="rId272" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="F238" r:id="rId273" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="F237" r:id="rId274" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="F236" r:id="rId275" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="F235" r:id="rId276" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="F234" r:id="rId277" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="F233" r:id="rId278" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="F232" r:id="rId279" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="F231" r:id="rId280" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="F230" r:id="rId281" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="F229" r:id="rId282" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="F228" r:id="rId283" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="F227" r:id="rId284" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="F226" r:id="rId285" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="F225" r:id="rId286" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="F224" r:id="rId287" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="F223" r:id="rId288" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="F222" r:id="rId289" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="F221" r:id="rId290" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="F220" r:id="rId291" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="F219" r:id="rId292" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="F218" r:id="rId293" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="F217" r:id="rId294" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="F216" r:id="rId295" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="F214" r:id="rId296" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="F213" r:id="rId297" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="F212" r:id="rId298" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="F211" r:id="rId299" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="F210" r:id="rId300" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="F209" r:id="rId301" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="F208" r:id="rId302" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="F207" r:id="rId303" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="F206" r:id="rId304" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="F205" r:id="rId305" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="F204" r:id="rId306" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="F203" r:id="rId307" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="F202" r:id="rId308" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="F201" r:id="rId309" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="F200" r:id="rId310" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="F199" r:id="rId311" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="F198" r:id="rId312" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="F197" r:id="rId313" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="F196" r:id="rId314" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="F195" r:id="rId315" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="F194" r:id="rId316" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="F193" r:id="rId317" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="F192" r:id="rId318" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="F191" r:id="rId319" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="F190" r:id="rId320" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="F189" r:id="rId321" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="F188" r:id="rId322" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="F187" r:id="rId323" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="F186" r:id="rId324" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="F185" r:id="rId325" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="F184" r:id="rId326" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="F183" r:id="rId327" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="F182" r:id="rId328" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="F181" r:id="rId329" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="F180" r:id="rId330" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="F179" r:id="rId331" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="F178" r:id="rId332" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="F177" r:id="rId333" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="F176" r:id="rId334" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="F175" r:id="rId335" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="F174" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="F173" r:id="rId337" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="F172" r:id="rId338" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="F171" r:id="rId339" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="F170" r:id="rId340" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="F169" r:id="rId341" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="F168" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="F166" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="F165" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="F164" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="F163" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="F162" r:id="rId347" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="F161" r:id="rId348" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="F160" r:id="rId349" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="F159" r:id="rId350" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="F158" r:id="rId351" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="F157" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="F156" r:id="rId353" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="F155" r:id="rId354" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="F154" r:id="rId355" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="F153" r:id="rId356" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="F152" r:id="rId357" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="F151" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="F150" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="F149" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="F148" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="F147" r:id="rId362" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="F146" r:id="rId363" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="F145" r:id="rId364" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="F144" r:id="rId365" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="F143" r:id="rId366" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="F142" r:id="rId367" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="F141" r:id="rId368" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="F140" r:id="rId369" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="F139" r:id="rId370" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="F138" r:id="rId371" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="F137" r:id="rId372" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="F136" r:id="rId373" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="F135" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="F134" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="F125" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="F124" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="F123" r:id="rId378" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="F122" r:id="rId379" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="F121" r:id="rId380" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="F120" r:id="rId381" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="F119" r:id="rId382" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="F118" r:id="rId383" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="F117" r:id="rId384" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="F116" r:id="rId385" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="F115" r:id="rId386" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="F114" r:id="rId387" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="F113" r:id="rId388" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="F112" r:id="rId389" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="F111" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="F110" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="F109" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
     <hyperlink ref="F108" location="'DSA Sheet Final'!A1" display="Link" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="F109" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="F110" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="F111" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="F112" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="F113" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="F114" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="F115" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="F116" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="F117" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="F118" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="F119" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="F120" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="F121" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="F122" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="F123" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="F124" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="F125" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="F134" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="F135" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="F136" r:id="rId122" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="F137" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="F138" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="F139" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="F140" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="F141" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="F142" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="F143" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="F144" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="F145" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="F146" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="F147" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="F148" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="F149" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="F150" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="F151" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="F152" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="F153" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="F154" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="F155" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="F156" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="F157" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="F158" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="F159" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="F160" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="F161" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="F162" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="F163" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="F164" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="F165" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="F166" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="F168" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="F169" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="F170" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="F171" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="F172" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="F173" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="F174" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="F175" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="F176" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="F177" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="F178" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="F179" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="F180" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="F181" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="F182" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="F183" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="F184" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="F185" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="F186" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="F187" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="F188" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="F189" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="F190" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="F191" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="F192" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="F193" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="F194" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="F195" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="F196" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="F197" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="F198" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="F199" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="F200" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="F201" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="F202" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="F203" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="F204" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="F205" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="F206" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="F207" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="F208" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="F209" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="F210" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="F211" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="F212" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="F213" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="F214" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="F216" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="F217" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="F218" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="F219" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="F220" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="F221" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="F222" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="F223" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="F224" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="F225" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="F226" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="F227" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="F228" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="F229" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="F230" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="F231" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="F232" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="F233" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
-    <hyperlink ref="F234" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="F235" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="F236" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="F237" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="F238" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="F239" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="F240" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="F241" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="F242" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="F243" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="F244" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="F245" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
-    <hyperlink ref="F246" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="F247" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="F248" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
-    <hyperlink ref="F249" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="F250" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
-    <hyperlink ref="F251" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
-    <hyperlink ref="F252" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
-    <hyperlink ref="F253" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
-    <hyperlink ref="F254" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
-    <hyperlink ref="F255" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
-    <hyperlink ref="F256" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
-    <hyperlink ref="F257" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
-    <hyperlink ref="F258" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000F2000000}"/>
-    <hyperlink ref="F259" r:id="rId243" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="F260" r:id="rId244" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
-    <hyperlink ref="F261" r:id="rId245" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="F262" r:id="rId246" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="F263" r:id="rId247" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="F264" r:id="rId248" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="F265" r:id="rId249" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="F266" r:id="rId250" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="F267" r:id="rId251" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="F268" r:id="rId252" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="F269" r:id="rId253" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="F270" r:id="rId254" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="F271" r:id="rId255" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="F272" r:id="rId256" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="F274" r:id="rId257" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="F275" r:id="rId258" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="F276" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="F277" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="F278" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
-    <hyperlink ref="F279" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
-    <hyperlink ref="F280" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
-    <hyperlink ref="F281" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
-    <hyperlink ref="F282" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
-    <hyperlink ref="F283" r:id="rId266" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
-    <hyperlink ref="F284" r:id="rId267" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
-    <hyperlink ref="F285" r:id="rId268" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
-    <hyperlink ref="F286" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
-    <hyperlink ref="F287" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
-    <hyperlink ref="F288" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
-    <hyperlink ref="F289" r:id="rId272" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
-    <hyperlink ref="F290" r:id="rId273" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
-    <hyperlink ref="F291" r:id="rId274" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
-    <hyperlink ref="F292" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
-    <hyperlink ref="F293" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
-    <hyperlink ref="F294" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
-    <hyperlink ref="F296" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
-    <hyperlink ref="F297" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
-    <hyperlink ref="F298" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
-    <hyperlink ref="F299" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
-    <hyperlink ref="F300" r:id="rId282" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
-    <hyperlink ref="F301" r:id="rId283" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
-    <hyperlink ref="F302" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
-    <hyperlink ref="F303" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
-    <hyperlink ref="F304" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
-    <hyperlink ref="F305" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
-    <hyperlink ref="F306" r:id="rId288" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
-    <hyperlink ref="F307" r:id="rId289" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
-    <hyperlink ref="F308" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
-    <hyperlink ref="F309" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
-    <hyperlink ref="F310" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
-    <hyperlink ref="F311" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
-    <hyperlink ref="F312" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
-    <hyperlink ref="F313" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
-    <hyperlink ref="F314" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000028010000}"/>
-    <hyperlink ref="F315" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
-    <hyperlink ref="F316" r:id="rId298" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
-    <hyperlink ref="F317" r:id="rId299" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
-    <hyperlink ref="F318" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
-    <hyperlink ref="F319" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
-    <hyperlink ref="F320" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
-    <hyperlink ref="F321" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
-    <hyperlink ref="F322" r:id="rId304" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
-    <hyperlink ref="F323" r:id="rId305" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
-    <hyperlink ref="F324" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
-    <hyperlink ref="F325" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
-    <hyperlink ref="F326" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
-    <hyperlink ref="F327" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
-    <hyperlink ref="F328" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
-    <hyperlink ref="F329" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
-    <hyperlink ref="F330" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
-    <hyperlink ref="F331" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
-    <hyperlink ref="F332" r:id="rId314" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
-    <hyperlink ref="F333" r:id="rId315" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
-    <hyperlink ref="F334" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
-    <hyperlink ref="F335" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
-    <hyperlink ref="F336" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
-    <hyperlink ref="F337" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
-    <hyperlink ref="F338" r:id="rId320" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
-    <hyperlink ref="F339" r:id="rId321" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="F340" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="F341" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="F342" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="F343" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="F344" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="F345" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="F346" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="F347" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="F348" r:id="rId330" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="F349" r:id="rId331" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="F350" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="F351" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="F352" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="F353" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="F354" r:id="rId336" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
-    <hyperlink ref="F355" r:id="rId337" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="F356" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="F357" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="F359" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="F360" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="F361" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="F362" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="F363" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="F364" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="F365" r:id="rId346" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="F366" r:id="rId347" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="F367" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="F368" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="F369" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
-    <hyperlink ref="F370" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
-    <hyperlink ref="F371" r:id="rId352" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="F372" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="F373" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="F374" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="F375" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="F376" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
-    <hyperlink ref="F377" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="F378" r:id="rId359" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="F379" r:id="rId360" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="F380" r:id="rId361" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="F381" r:id="rId362" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="F382" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="F383" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="F384" r:id="rId365" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="F385" r:id="rId366" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="F386" r:id="rId367" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
-    <hyperlink ref="F387" r:id="rId368" xr:uid="{00000000-0004-0000-0000-000070010000}"/>
-    <hyperlink ref="F388" r:id="rId369" xr:uid="{00000000-0004-0000-0000-000071010000}"/>
-    <hyperlink ref="F389" r:id="rId370" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
-    <hyperlink ref="F390" r:id="rId371" xr:uid="{00000000-0004-0000-0000-000073010000}"/>
-    <hyperlink ref="F391" r:id="rId372" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="F392" r:id="rId373" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="F393" r:id="rId374" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="F394" r:id="rId375" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="F395" r:id="rId376" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
-    <hyperlink ref="F396" r:id="rId377" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="F397" r:id="rId378" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
-    <hyperlink ref="F398" r:id="rId379" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="F399" r:id="rId380" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
-    <hyperlink ref="F400" r:id="rId381" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
-    <hyperlink ref="F401" r:id="rId382" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="F402" r:id="rId383" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
-    <hyperlink ref="F403" r:id="rId384" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
-    <hyperlink ref="F404" r:id="rId385" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
-    <hyperlink ref="F405" r:id="rId386" xr:uid="{00000000-0004-0000-0000-000082010000}"/>
-    <hyperlink ref="F406" r:id="rId387" xr:uid="{00000000-0004-0000-0000-000083010000}"/>
-    <hyperlink ref="F407" r:id="rId388" xr:uid="{00000000-0004-0000-0000-000084010000}"/>
-    <hyperlink ref="F408" r:id="rId389" xr:uid="{00000000-0004-0000-0000-000085010000}"/>
-    <hyperlink ref="F409" r:id="rId390" xr:uid="{00000000-0004-0000-0000-000086010000}"/>
-    <hyperlink ref="F410" r:id="rId391" xr:uid="{00000000-0004-0000-0000-000087010000}"/>
-    <hyperlink ref="F411" r:id="rId392" xr:uid="{00000000-0004-0000-0000-000088010000}"/>
-    <hyperlink ref="F412" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000089010000}"/>
-    <hyperlink ref="F413" r:id="rId394" xr:uid="{00000000-0004-0000-0000-00008A010000}"/>
-    <hyperlink ref="F414" r:id="rId395" xr:uid="{00000000-0004-0000-0000-00008B010000}"/>
-    <hyperlink ref="F415" r:id="rId396" xr:uid="{00000000-0004-0000-0000-00008C010000}"/>
-    <hyperlink ref="F416" r:id="rId397" xr:uid="{00000000-0004-0000-0000-00008D010000}"/>
-    <hyperlink ref="F417" r:id="rId398" xr:uid="{00000000-0004-0000-0000-00008E010000}"/>
-    <hyperlink ref="F418" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00008F010000}"/>
-    <hyperlink ref="F419" r:id="rId400" xr:uid="{00000000-0004-0000-0000-000090010000}"/>
-    <hyperlink ref="F420" r:id="rId401" xr:uid="{00000000-0004-0000-0000-000091010000}"/>
-    <hyperlink ref="F421" r:id="rId402" xr:uid="{00000000-0004-0000-0000-000092010000}"/>
-    <hyperlink ref="F422" r:id="rId403" xr:uid="{00000000-0004-0000-0000-000093010000}"/>
-    <hyperlink ref="F423" r:id="rId404" xr:uid="{00000000-0004-0000-0000-000094010000}"/>
-    <hyperlink ref="F424" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000095010000}"/>
-    <hyperlink ref="F425" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000096010000}"/>
-    <hyperlink ref="F426" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000097010000}"/>
-    <hyperlink ref="F428" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000098010000}"/>
-    <hyperlink ref="F429" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000099010000}"/>
-    <hyperlink ref="F430" r:id="rId410" xr:uid="{00000000-0004-0000-0000-00009A010000}"/>
-    <hyperlink ref="F431" r:id="rId411" xr:uid="{00000000-0004-0000-0000-00009B010000}"/>
-    <hyperlink ref="F432" r:id="rId412" xr:uid="{00000000-0004-0000-0000-00009C010000}"/>
-    <hyperlink ref="F433" r:id="rId413" xr:uid="{00000000-0004-0000-0000-00009D010000}"/>
-    <hyperlink ref="F434" r:id="rId414" xr:uid="{00000000-0004-0000-0000-00009E010000}"/>
-    <hyperlink ref="F435" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00009F010000}"/>
-    <hyperlink ref="F437" r:id="rId416" xr:uid="{00000000-0004-0000-0000-0000A0010000}"/>
-    <hyperlink ref="F439" r:id="rId417" xr:uid="{00000000-0004-0000-0000-0000A1010000}"/>
-    <hyperlink ref="F440" r:id="rId418" xr:uid="{00000000-0004-0000-0000-0000A2010000}"/>
-    <hyperlink ref="F441" r:id="rId419" xr:uid="{00000000-0004-0000-0000-0000A3010000}"/>
-    <hyperlink ref="F442" r:id="rId420" xr:uid="{00000000-0004-0000-0000-0000A4010000}"/>
-    <hyperlink ref="F443" r:id="rId421" xr:uid="{00000000-0004-0000-0000-0000A5010000}"/>
-    <hyperlink ref="F444" r:id="rId422" xr:uid="{00000000-0004-0000-0000-0000A6010000}"/>
-    <hyperlink ref="F445" r:id="rId423" xr:uid="{00000000-0004-0000-0000-0000A7010000}"/>
-    <hyperlink ref="F446" r:id="rId424" xr:uid="{00000000-0004-0000-0000-0000A8010000}"/>
-    <hyperlink ref="F447" r:id="rId425" xr:uid="{00000000-0004-0000-0000-0000A9010000}"/>
-    <hyperlink ref="F448" r:id="rId426" xr:uid="{00000000-0004-0000-0000-0000AA010000}"/>
-    <hyperlink ref="F449" r:id="rId427" xr:uid="{00000000-0004-0000-0000-0000AB010000}"/>
-    <hyperlink ref="F450" r:id="rId428" xr:uid="{00000000-0004-0000-0000-0000AC010000}"/>
-    <hyperlink ref="F451" r:id="rId429" xr:uid="{00000000-0004-0000-0000-0000AD010000}"/>
-    <hyperlink ref="F452" r:id="rId430" xr:uid="{00000000-0004-0000-0000-0000AE010000}"/>
-    <hyperlink ref="F453" r:id="rId431" xr:uid="{00000000-0004-0000-0000-0000AF010000}"/>
-    <hyperlink ref="F454" r:id="rId432" xr:uid="{00000000-0004-0000-0000-0000B0010000}"/>
-    <hyperlink ref="F455" r:id="rId433" xr:uid="{00000000-0004-0000-0000-0000B1010000}"/>
-    <hyperlink ref="F456" r:id="rId434" xr:uid="{00000000-0004-0000-0000-0000B2010000}"/>
-    <hyperlink ref="F457" r:id="rId435" xr:uid="{00000000-0004-0000-0000-0000B3010000}"/>
-    <hyperlink ref="F458" r:id="rId436" xr:uid="{00000000-0004-0000-0000-0000B4010000}"/>
-    <hyperlink ref="F459" r:id="rId437" xr:uid="{00000000-0004-0000-0000-0000B5010000}"/>
-    <hyperlink ref="F460" r:id="rId438" xr:uid="{00000000-0004-0000-0000-0000B6010000}"/>
-    <hyperlink ref="F461" r:id="rId439" xr:uid="{00000000-0004-0000-0000-0000B7010000}"/>
-    <hyperlink ref="F462" r:id="rId440" xr:uid="{00000000-0004-0000-0000-0000B8010000}"/>
-    <hyperlink ref="F463" r:id="rId441" xr:uid="{00000000-0004-0000-0000-0000B9010000}"/>
-    <hyperlink ref="F464" r:id="rId442" xr:uid="{00000000-0004-0000-0000-0000BA010000}"/>
-    <hyperlink ref="F465" r:id="rId443" xr:uid="{00000000-0004-0000-0000-0000BB010000}"/>
-    <hyperlink ref="F466" r:id="rId444" xr:uid="{00000000-0004-0000-0000-0000BC010000}"/>
-    <hyperlink ref="F467" r:id="rId445" xr:uid="{00000000-0004-0000-0000-0000BD010000}"/>
-    <hyperlink ref="F468" r:id="rId446" xr:uid="{00000000-0004-0000-0000-0000BE010000}"/>
-    <hyperlink ref="F469" r:id="rId447" xr:uid="{00000000-0004-0000-0000-0000BF010000}"/>
-    <hyperlink ref="F470" r:id="rId448" xr:uid="{00000000-0004-0000-0000-0000C0010000}"/>
-    <hyperlink ref="F471" r:id="rId449" xr:uid="{00000000-0004-0000-0000-0000C1010000}"/>
-    <hyperlink ref="F472" r:id="rId450" xr:uid="{00000000-0004-0000-0000-0000C2010000}"/>
-    <hyperlink ref="F473" r:id="rId451" xr:uid="{00000000-0004-0000-0000-0000C3010000}"/>
-    <hyperlink ref="F474" r:id="rId452" xr:uid="{00000000-0004-0000-0000-0000C4010000}"/>
-    <hyperlink ref="F475" r:id="rId453" xr:uid="{00000000-0004-0000-0000-0000C5010000}"/>
-    <hyperlink ref="F476" r:id="rId454" xr:uid="{00000000-0004-0000-0000-0000C6010000}"/>
-    <hyperlink ref="F477" r:id="rId455" xr:uid="{00000000-0004-0000-0000-0000C7010000}"/>
-    <hyperlink ref="F478" r:id="rId456" xr:uid="{00000000-0004-0000-0000-0000C8010000}"/>
-    <hyperlink ref="F479" r:id="rId457" xr:uid="{00000000-0004-0000-0000-0000C9010000}"/>
-    <hyperlink ref="F480" r:id="rId458" xr:uid="{00000000-0004-0000-0000-0000CA010000}"/>
-    <hyperlink ref="F481" r:id="rId459" xr:uid="{00000000-0004-0000-0000-0000CB010000}"/>
-    <hyperlink ref="F482" r:id="rId460" xr:uid="{00000000-0004-0000-0000-0000CC010000}"/>
-    <hyperlink ref="F483" r:id="rId461" xr:uid="{00000000-0004-0000-0000-0000CD010000}"/>
-    <hyperlink ref="F484" r:id="rId462" xr:uid="{00000000-0004-0000-0000-0000CE010000}"/>
-    <hyperlink ref="F485" r:id="rId463" xr:uid="{00000000-0004-0000-0000-0000CF010000}"/>
-    <hyperlink ref="F486" r:id="rId464" xr:uid="{00000000-0004-0000-0000-0000D0010000}"/>
-    <hyperlink ref="F487" r:id="rId465" xr:uid="{00000000-0004-0000-0000-0000D1010000}"/>
-    <hyperlink ref="F488" r:id="rId466" xr:uid="{00000000-0004-0000-0000-0000D2010000}"/>
-    <hyperlink ref="F489" r:id="rId467" xr:uid="{00000000-0004-0000-0000-0000D3010000}"/>
-    <hyperlink ref="F490" r:id="rId468" xr:uid="{00000000-0004-0000-0000-0000D4010000}"/>
-    <hyperlink ref="F491" r:id="rId469" xr:uid="{00000000-0004-0000-0000-0000D5010000}"/>
-    <hyperlink ref="F492" r:id="rId470" xr:uid="{00000000-0004-0000-0000-0000D6010000}"/>
-    <hyperlink ref="F493" r:id="rId471" xr:uid="{00000000-0004-0000-0000-0000D7010000}"/>
-    <hyperlink ref="F494" r:id="rId472" xr:uid="{00000000-0004-0000-0000-0000D8010000}"/>
-    <hyperlink ref="F495" r:id="rId473" xr:uid="{00000000-0004-0000-0000-0000D9010000}"/>
-    <hyperlink ref="F496" r:id="rId474" xr:uid="{00000000-0004-0000-0000-0000DA010000}"/>
-    <hyperlink ref="F497" r:id="rId475" xr:uid="{00000000-0004-0000-0000-0000DB010000}"/>
-    <hyperlink ref="F498" r:id="rId476" xr:uid="{00000000-0004-0000-0000-0000DC010000}"/>
-    <hyperlink ref="F499" r:id="rId477" xr:uid="{00000000-0004-0000-0000-0000DD010000}"/>
-    <hyperlink ref="F500" r:id="rId478" xr:uid="{00000000-0004-0000-0000-0000DE010000}"/>
-    <hyperlink ref="F501" r:id="rId479" xr:uid="{00000000-0004-0000-0000-0000DF010000}"/>
-    <hyperlink ref="F502" r:id="rId480" xr:uid="{00000000-0004-0000-0000-0000E0010000}"/>
-    <hyperlink ref="F503" r:id="rId481" xr:uid="{00000000-0004-0000-0000-0000E1010000}"/>
-    <hyperlink ref="F504" r:id="rId482" xr:uid="{00000000-0004-0000-0000-0000E2010000}"/>
-    <hyperlink ref="F505" r:id="rId483" xr:uid="{00000000-0004-0000-0000-0000E3010000}"/>
-    <hyperlink ref="F506" r:id="rId484" xr:uid="{00000000-0004-0000-0000-0000E4010000}"/>
-    <hyperlink ref="F507" r:id="rId485" xr:uid="{00000000-0004-0000-0000-0000E5010000}"/>
-    <hyperlink ref="F508" r:id="rId486" xr:uid="{00000000-0004-0000-0000-0000E6010000}"/>
-    <hyperlink ref="F509" r:id="rId487" xr:uid="{00000000-0004-0000-0000-0000E7010000}"/>
-    <hyperlink ref="F510" r:id="rId488" xr:uid="{00000000-0004-0000-0000-0000E8010000}"/>
-    <hyperlink ref="F511" r:id="rId489" xr:uid="{00000000-0004-0000-0000-0000E9010000}"/>
-    <hyperlink ref="F512" r:id="rId490" xr:uid="{00000000-0004-0000-0000-0000EA010000}"/>
-    <hyperlink ref="F513" r:id="rId491" xr:uid="{00000000-0004-0000-0000-0000EB010000}"/>
-    <hyperlink ref="I346" r:id="rId492" display="https://leetcode.com/problems/number-of-even-and-odd-bits/" xr:uid="{F5BACACB-0735-4CF8-A9F9-EEB3416037CD}"/>
-    <hyperlink ref="I354" r:id="rId493" display="https://www.geeksforgeeks.org/problems/count-total-set-bits-1587115620/1?page=1&amp;category=Bit%20Magic&amp;sortBy=submissions" xr:uid="{39FD791E-2FA5-4251-A8B8-D37477C8188C}"/>
-    <hyperlink ref="I355" r:id="rId494" display="https://www.geeksforgeeks.org/problems/bleak-numbers1552/1?page=6&amp;category=Bit%20Magic&amp;sortBy=difficulty" xr:uid="{B278AF57-6FD5-47BA-B637-A66848ECE515}"/>
+    <hyperlink ref="F107" r:id="rId393" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="F105" r:id="rId394" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="F104" r:id="rId395" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="F103" r:id="rId396" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="F102" r:id="rId397" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="F101" r:id="rId398" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="F100" r:id="rId399" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="F99" r:id="rId400" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="F98" r:id="rId401" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="F97" r:id="rId402" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="F96" r:id="rId403" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="F95" r:id="rId404" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="F94" r:id="rId405" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="F93" r:id="rId406" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="F92" r:id="rId407" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="F91" r:id="rId408" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="F90" r:id="rId409" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="F89" r:id="rId410" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="F88" r:id="rId411" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="F87" r:id="rId412" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="F86" r:id="rId413" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="F85" r:id="rId414" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="F84" r:id="rId415" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="F83" r:id="rId416" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="F82" r:id="rId417" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="F81" r:id="rId418" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="F80" r:id="rId419" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="F79" r:id="rId420" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="F78" r:id="rId421" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="F77" r:id="rId422" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="F76" r:id="rId423" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="F75" r:id="rId424" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="F74" r:id="rId425" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="F73" r:id="rId426" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="F72" r:id="rId427" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="F71" r:id="rId428" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="F70" r:id="rId429" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="F69" r:id="rId430" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="F67" r:id="rId431" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="F66" r:id="rId432" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="F65" r:id="rId433" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="F64" r:id="rId434" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="F63" r:id="rId435" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="F62" r:id="rId436" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="F61" r:id="rId437" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="F60" r:id="rId438" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="F59" r:id="rId439" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="F58" r:id="rId440" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="F57" r:id="rId441" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="F56" r:id="rId442" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="F55" r:id="rId443" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="F54" r:id="rId444" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="F53" r:id="rId445" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="F52" r:id="rId446" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="F51" r:id="rId447" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="F50" r:id="rId448" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="F49" r:id="rId449" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="F48" r:id="rId450" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="F47" r:id="rId451" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="F46" r:id="rId452" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="F45" r:id="rId453" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="F44" r:id="rId454" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="F43" r:id="rId455" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="F42" r:id="rId456" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="F41" r:id="rId457" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="F40" r:id="rId458" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="F39" r:id="rId459" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="F38" r:id="rId460" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="F37" r:id="rId461" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="F36" r:id="rId462" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="F35" r:id="rId463" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="F34" r:id="rId464" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="F33" r:id="rId465" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="F32" r:id="rId466" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="F31" r:id="rId467" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="F30" r:id="rId468" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="F29" r:id="rId469" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="F28" r:id="rId470" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="F27" r:id="rId471" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="F26" r:id="rId472" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="F25" r:id="rId473" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="F24" r:id="rId474" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="F23" r:id="rId475" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="F22" r:id="rId476" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="F21" r:id="rId477" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="F20" r:id="rId478" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="F19" r:id="rId479" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="F18" r:id="rId480" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="F17" r:id="rId481" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="F16" r:id="rId482" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="F15" r:id="rId483" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="F14" r:id="rId484" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="F13" r:id="rId485" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="F12" r:id="rId486" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="F11" r:id="rId487" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="F10" r:id="rId488" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="F9" r:id="rId489" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="F8" r:id="rId490" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="F7" r:id="rId491" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="F6" r:id="rId492" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="F5" r:id="rId493" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F4" r:id="rId494" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId495"/>
@@ -23542,16 +23827,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="31.5" customHeight="1">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="151" t="s">
         <v>644</v>
       </c>
-      <c r="B1" s="158"/>
+      <c r="B1" s="152"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1">
-      <c r="A2" s="159" t="s">
+      <c r="A2" s="153" t="s">
         <v>645</v>
       </c>
-      <c r="B2" s="158"/>
+      <c r="B2" s="152"/>
     </row>
     <row r="3" spans="1:2" ht="18" customHeight="1">
       <c r="A3" s="46" t="s">
@@ -23598,10 +23883,10 @@
       <c r="B8" s="47"/>
     </row>
     <row r="9" spans="1:2" ht="18" customHeight="1">
-      <c r="A9" s="159" t="s">
+      <c r="A9" s="153" t="s">
         <v>656</v>
       </c>
-      <c r="B9" s="158"/>
+      <c r="B9" s="152"/>
     </row>
     <row r="10" spans="1:2" ht="18" customHeight="1">
       <c r="A10" s="52" t="s">
@@ -23680,10 +23965,10 @@
       <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:2" ht="18" customHeight="1">
-      <c r="A20" s="159" t="s">
+      <c r="A20" s="153" t="s">
         <v>675</v>
       </c>
-      <c r="B20" s="158"/>
+      <c r="B20" s="152"/>
     </row>
     <row r="21" spans="1:2" ht="18" customHeight="1">
       <c r="A21" s="52" t="s">
@@ -24680,15 +24965,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="154" t="s">
         <v>678</v>
       </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="E1" s="161"/>
-      <c r="F1" s="161"/>
-      <c r="G1" s="158"/>
+      <c r="B1" s="155"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="155"/>
+      <c r="G1" s="152"/>
     </row>
     <row r="2" spans="1:8" ht="13.2">
       <c r="A2" s="53" t="s">

--- a/DSA Master Sheet.xlsx
+++ b/DSA Master Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\OneDrive\Desktop\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB0EA0F3-D3B6-4A65-AE82-ED864364DFF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B7707A-2786-47BF-B3A4-7825A85D6518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="723">
   <si>
     <t>DSA Master Sheet</t>
   </si>
@@ -2702,16 +2702,117 @@
         return true;</t>
     </r>
   </si>
+  <si>
+    <t xml:space="preserve">1) number of element greate than n/3 is atmost 2 (either 1 or 2 elements) because if there are three element then  n/3*3(is three) but we need n/3+1
+2) use boyer moore with candidate1 and candidate2 </t>
+  </si>
+  <si>
+    <t>Not Attempted</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1) Matrix is sorted in decreasing order → use the sorted property.
+2) Start from bottom-left.
+3) If negative → all elements to the right are negative → count n-col and move up.
+4) If non-negative → move right.
+5) Each step moves either up or right → O(m+n)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Time  : O(m + n)
+Space : O(1)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    public int countNegatives(int[][] grid) {
+        int m = grid.length;
+        int n = grid[0].length;
+        int row = m-1;
+        int col = 0;
+        int count = 0;
+        while(col&lt;n &amp;&amp; row&gt;=0){
+            if(grid[row][col]&lt;0){
+                count+=n-col;
+                row--;
+            }
+            else{
+                col++;
+            }
+        }
+        return count;
+    }
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>For every row i:
+Primary diagonal → mat[i][i]
+Secondary diagonal → mat[i][n - 1 - i]
+If both are the same element (middle of odd-sized matrix), don't add it twice.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                                      int n = mat.length;
+        int sum = 0;
+        for (int i = 0; i &lt; n; i++) {
+            sum += mat[i][i];
+            if (i != n - 1 - i) {
+                sum += mat[i][n - 1 - i];
+            }
+        }
+        return sum;</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="96">
+  <fonts count="98">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3295,6 +3396,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="55">
     <fill>
@@ -3780,364 +3888,367 @@
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="85" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="86" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="87" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="86" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="87" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="194">
+  <cellXfs count="196">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="31" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="33" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="20" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="20" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="22" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="22" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="24" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="24" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="28" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="28" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="29" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="29" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="31" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="31" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="32" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="32" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="37" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="37" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="38" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="38" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="38" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="38" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="39" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="39" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="40" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="40" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="41" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="41" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="42" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="67" fillId="42" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="42" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="68" fillId="42" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="43" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="43" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="44" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="44" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="44" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="44" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="45" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="45" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="46" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="71" fillId="46" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="46" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="46" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="47" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="47" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="48" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="48" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="49" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="49" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="49" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="49" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="50" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="50" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="51" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="77" fillId="51" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="51" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="78" fillId="51" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="79" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="80" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="85" fillId="52" borderId="6" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="86" fillId="53" borderId="6" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="87" fillId="54" borderId="6" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="86" fillId="52" borderId="6" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="87" fillId="53" borderId="6" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="88" fillId="54" borderId="6" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4146,177 +4257,178 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -4557,18 +4669,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="30.75" customHeight="1">
-      <c r="A1" s="188" t="s">
+      <c r="A1" s="186" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="189"/>
-      <c r="C1" s="189"/>
-      <c r="D1" s="189"/>
-      <c r="E1" s="189"/>
-      <c r="F1" s="189"/>
-      <c r="G1" s="189"/>
-      <c r="H1" s="189"/>
-      <c r="I1" s="189"/>
-      <c r="J1" s="190"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+      <c r="I1" s="187"/>
+      <c r="J1" s="188"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -4623,18 +4735,18 @@
       <c r="T2" s="5"/>
     </row>
     <row r="3" spans="1:20" ht="13.8">
-      <c r="A3" s="136" t="s">
+      <c r="A3" s="183" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="182"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="182"/>
-      <c r="F3" s="182"/>
-      <c r="G3" s="182"/>
-      <c r="H3" s="182"/>
-      <c r="I3" s="182"/>
-      <c r="J3" s="183"/>
+      <c r="B3" s="184"/>
+      <c r="C3" s="184"/>
+      <c r="D3" s="184"/>
+      <c r="E3" s="184"/>
+      <c r="F3" s="184"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="184"/>
+      <c r="I3" s="184"/>
+      <c r="J3" s="185"/>
     </row>
     <row r="4" spans="1:20" ht="13.8">
       <c r="A4" s="6">
@@ -4643,10 +4755,10 @@
       <c r="B4" s="7">
         <v>1</v>
       </c>
-      <c r="C4" s="137" t="s">
+      <c r="C4" s="144" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="135" t="s">
+      <c r="D4" s="159" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -4676,8 +4788,8 @@
       <c r="B5" s="7">
         <v>2</v>
       </c>
-      <c r="C5" s="164"/>
-      <c r="D5" s="156"/>
+      <c r="C5" s="145"/>
+      <c r="D5" s="160"/>
       <c r="E5" s="8" t="s">
         <v>16</v>
       </c>
@@ -4705,8 +4817,8 @@
       <c r="B6" s="7">
         <v>3</v>
       </c>
-      <c r="C6" s="164"/>
-      <c r="D6" s="156"/>
+      <c r="C6" s="145"/>
+      <c r="D6" s="160"/>
       <c r="E6" s="8" t="s">
         <v>19</v>
       </c>
@@ -4734,8 +4846,8 @@
       <c r="B7" s="7">
         <v>4</v>
       </c>
-      <c r="C7" s="164"/>
-      <c r="D7" s="156"/>
+      <c r="C7" s="145"/>
+      <c r="D7" s="160"/>
       <c r="E7" s="8" t="s">
         <v>23</v>
       </c>
@@ -4763,8 +4875,8 @@
       <c r="B8" s="7">
         <v>5</v>
       </c>
-      <c r="C8" s="164"/>
-      <c r="D8" s="156"/>
+      <c r="C8" s="145"/>
+      <c r="D8" s="160"/>
       <c r="E8" s="8" t="s">
         <v>26</v>
       </c>
@@ -4792,8 +4904,8 @@
       <c r="B9" s="7">
         <v>6</v>
       </c>
-      <c r="C9" s="164"/>
-      <c r="D9" s="157"/>
+      <c r="C9" s="145"/>
+      <c r="D9" s="161"/>
       <c r="E9" s="8" t="s">
         <v>29</v>
       </c>
@@ -4818,8 +4930,8 @@
       <c r="B10" s="7">
         <v>7</v>
       </c>
-      <c r="C10" s="164"/>
-      <c r="D10" s="135" t="s">
+      <c r="C10" s="145"/>
+      <c r="D10" s="159" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="8" t="s">
@@ -4846,8 +4958,8 @@
       <c r="B11" s="7">
         <v>8</v>
       </c>
-      <c r="C11" s="164"/>
-      <c r="D11" s="156"/>
+      <c r="C11" s="145"/>
+      <c r="D11" s="160"/>
       <c r="E11" s="13" t="s">
         <v>32</v>
       </c>
@@ -4872,8 +4984,8 @@
       <c r="B12" s="7">
         <v>9</v>
       </c>
-      <c r="C12" s="164"/>
-      <c r="D12" s="156"/>
+      <c r="C12" s="145"/>
+      <c r="D12" s="160"/>
       <c r="E12" s="8" t="s">
         <v>33</v>
       </c>
@@ -4898,8 +5010,8 @@
       <c r="B13" s="7">
         <v>10</v>
       </c>
-      <c r="C13" s="164"/>
-      <c r="D13" s="156"/>
+      <c r="C13" s="145"/>
+      <c r="D13" s="160"/>
       <c r="E13" s="8" t="s">
         <v>34</v>
       </c>
@@ -4926,8 +5038,8 @@
       <c r="B14" s="7">
         <v>11</v>
       </c>
-      <c r="C14" s="164"/>
-      <c r="D14" s="156"/>
+      <c r="C14" s="145"/>
+      <c r="D14" s="160"/>
       <c r="E14" s="8" t="s">
         <v>35</v>
       </c>
@@ -4952,8 +5064,8 @@
       <c r="B15" s="7">
         <v>12</v>
       </c>
-      <c r="C15" s="164"/>
-      <c r="D15" s="156"/>
+      <c r="C15" s="145"/>
+      <c r="D15" s="160"/>
       <c r="E15" s="8" t="s">
         <v>36</v>
       </c>
@@ -4980,8 +5092,8 @@
       <c r="B16" s="7">
         <v>13</v>
       </c>
-      <c r="C16" s="164"/>
-      <c r="D16" s="156"/>
+      <c r="C16" s="145"/>
+      <c r="D16" s="160"/>
       <c r="E16" s="8" t="s">
         <v>37</v>
       </c>
@@ -5006,8 +5118,8 @@
       <c r="B17" s="7">
         <v>14</v>
       </c>
-      <c r="C17" s="164"/>
-      <c r="D17" s="156"/>
+      <c r="C17" s="145"/>
+      <c r="D17" s="160"/>
       <c r="E17" s="8" t="s">
         <v>38</v>
       </c>
@@ -5034,8 +5146,8 @@
       <c r="B18" s="7">
         <v>15</v>
       </c>
-      <c r="C18" s="164"/>
-      <c r="D18" s="157"/>
+      <c r="C18" s="145"/>
+      <c r="D18" s="161"/>
       <c r="E18" s="13" t="s">
         <v>39</v>
       </c>
@@ -5062,8 +5174,8 @@
       <c r="B19" s="7">
         <v>16</v>
       </c>
-      <c r="C19" s="164"/>
-      <c r="D19" s="135" t="s">
+      <c r="C19" s="145"/>
+      <c r="D19" s="159" t="s">
         <v>40</v>
       </c>
       <c r="E19" s="8" t="s">
@@ -5092,8 +5204,8 @@
       <c r="B20" s="7">
         <v>17</v>
       </c>
-      <c r="C20" s="164"/>
-      <c r="D20" s="156"/>
+      <c r="C20" s="145"/>
+      <c r="D20" s="160"/>
       <c r="E20" s="8" t="s">
         <v>42</v>
       </c>
@@ -5120,8 +5232,8 @@
       <c r="B21" s="7">
         <v>18</v>
       </c>
-      <c r="C21" s="164"/>
-      <c r="D21" s="156"/>
+      <c r="C21" s="145"/>
+      <c r="D21" s="160"/>
       <c r="E21" s="8" t="s">
         <v>43</v>
       </c>
@@ -5148,8 +5260,8 @@
       <c r="B22" s="7">
         <v>19</v>
       </c>
-      <c r="C22" s="164"/>
-      <c r="D22" s="156"/>
+      <c r="C22" s="145"/>
+      <c r="D22" s="160"/>
       <c r="E22" s="8" t="s">
         <v>44</v>
       </c>
@@ -5170,8 +5282,8 @@
       <c r="B23" s="7">
         <v>20</v>
       </c>
-      <c r="C23" s="164"/>
-      <c r="D23" s="156"/>
+      <c r="C23" s="145"/>
+      <c r="D23" s="160"/>
       <c r="E23" s="8" t="s">
         <v>45</v>
       </c>
@@ -5192,8 +5304,8 @@
       <c r="B24" s="7">
         <v>21</v>
       </c>
-      <c r="C24" s="164"/>
-      <c r="D24" s="156"/>
+      <c r="C24" s="145"/>
+      <c r="D24" s="160"/>
       <c r="E24" s="13" t="s">
         <v>46</v>
       </c>
@@ -5218,8 +5330,8 @@
       <c r="B25" s="7">
         <v>22</v>
       </c>
-      <c r="C25" s="164"/>
-      <c r="D25" s="157"/>
+      <c r="C25" s="145"/>
+      <c r="D25" s="161"/>
       <c r="E25" s="8" t="s">
         <v>47</v>
       </c>
@@ -5246,8 +5358,8 @@
       <c r="B26" s="7">
         <v>23</v>
       </c>
-      <c r="C26" s="164"/>
-      <c r="D26" s="135" t="s">
+      <c r="C26" s="145"/>
+      <c r="D26" s="159" t="s">
         <v>48</v>
       </c>
       <c r="E26" s="13" t="s">
@@ -5276,8 +5388,8 @@
       <c r="B27" s="7">
         <v>24</v>
       </c>
-      <c r="C27" s="164"/>
-      <c r="D27" s="156"/>
+      <c r="C27" s="145"/>
+      <c r="D27" s="160"/>
       <c r="E27" s="8" t="s">
         <v>50</v>
       </c>
@@ -5287,19 +5399,23 @@
       <c r="G27" s="10">
         <v>4</v>
       </c>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-    </row>
-    <row r="28" spans="1:10" ht="13.8">
+      <c r="H27" s="194" t="s">
+        <v>720</v>
+      </c>
+      <c r="I27" s="131"/>
+      <c r="J27" s="126" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="82.8">
       <c r="A28" s="6">
         <v>25</v>
       </c>
       <c r="B28" s="7">
         <v>25</v>
       </c>
-      <c r="C28" s="164"/>
-      <c r="D28" s="156"/>
+      <c r="C28" s="145"/>
+      <c r="D28" s="160"/>
       <c r="E28" s="8" t="s">
         <v>51</v>
       </c>
@@ -5309,9 +5425,15 @@
       <c r="G28" s="10">
         <v>4</v>
       </c>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
+      <c r="H28" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" s="131" t="s">
+        <v>719</v>
+      </c>
+      <c r="J28" s="126" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="29" spans="1:10" ht="13.8">
       <c r="A29" s="6">
@@ -5320,8 +5442,8 @@
       <c r="B29" s="7">
         <v>26</v>
       </c>
-      <c r="C29" s="164"/>
-      <c r="D29" s="156"/>
+      <c r="C29" s="145"/>
+      <c r="D29" s="160"/>
       <c r="E29" s="8" t="s">
         <v>52</v>
       </c>
@@ -5342,8 +5464,8 @@
       <c r="B30" s="7">
         <v>27</v>
       </c>
-      <c r="C30" s="164"/>
-      <c r="D30" s="156"/>
+      <c r="C30" s="145"/>
+      <c r="D30" s="160"/>
       <c r="E30" s="8" t="s">
         <v>53</v>
       </c>
@@ -5364,8 +5486,8 @@
       <c r="B31" s="7">
         <v>28</v>
       </c>
-      <c r="C31" s="164"/>
-      <c r="D31" s="156"/>
+      <c r="C31" s="145"/>
+      <c r="D31" s="160"/>
       <c r="E31" s="8" t="s">
         <v>54</v>
       </c>
@@ -5386,8 +5508,8 @@
       <c r="B32" s="7">
         <v>29</v>
       </c>
-      <c r="C32" s="165"/>
-      <c r="D32" s="157"/>
+      <c r="C32" s="146"/>
+      <c r="D32" s="161"/>
       <c r="E32" s="17" t="s">
         <v>55</v>
       </c>
@@ -5408,10 +5530,10 @@
       <c r="B33" s="22">
         <v>1</v>
       </c>
-      <c r="C33" s="138" t="s">
+      <c r="C33" s="147" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="135" t="s">
+      <c r="D33" s="159" t="s">
         <v>57</v>
       </c>
       <c r="E33" s="8" t="s">
@@ -5423,9 +5545,13 @@
       <c r="G33" s="10">
         <v>2</v>
       </c>
-      <c r="H33" s="11"/>
+      <c r="H33" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
+      <c r="J33" s="11" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="34" spans="1:10" ht="13.8">
       <c r="A34" s="6">
@@ -5434,8 +5560,8 @@
       <c r="B34" s="7">
         <v>2</v>
       </c>
-      <c r="C34" s="158"/>
-      <c r="D34" s="156"/>
+      <c r="C34" s="148"/>
+      <c r="D34" s="160"/>
       <c r="E34" s="8" t="s">
         <v>59</v>
       </c>
@@ -5445,19 +5571,23 @@
       <c r="G34" s="10">
         <v>2</v>
       </c>
-      <c r="H34" s="11"/>
+      <c r="H34" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-    </row>
-    <row r="35" spans="1:10" ht="13.8">
+      <c r="J34" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="386.4">
       <c r="A35" s="6">
         <v>32</v>
       </c>
       <c r="B35" s="7">
         <v>3</v>
       </c>
-      <c r="C35" s="158"/>
-      <c r="D35" s="156"/>
+      <c r="C35" s="148"/>
+      <c r="D35" s="160"/>
       <c r="E35" s="8" t="s">
         <v>60</v>
       </c>
@@ -5467,19 +5597,25 @@
       <c r="G35" s="10">
         <v>2</v>
       </c>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-    </row>
-    <row r="36" spans="1:10" ht="13.8">
+      <c r="H35" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="195" t="s">
+        <v>721</v>
+      </c>
+      <c r="J35" s="126" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="262.2">
       <c r="A36" s="6">
         <v>33</v>
       </c>
       <c r="B36" s="7">
         <v>4</v>
       </c>
-      <c r="C36" s="158"/>
-      <c r="D36" s="157"/>
+      <c r="C36" s="148"/>
+      <c r="D36" s="161"/>
       <c r="E36" s="8" t="s">
         <v>61</v>
       </c>
@@ -5489,9 +5625,15 @@
       <c r="G36" s="10">
         <v>2</v>
       </c>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
+      <c r="H36" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I36" s="195" t="s">
+        <v>722</v>
+      </c>
+      <c r="J36" s="126" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="37" spans="1:10" ht="13.8">
       <c r="A37" s="6">
@@ -5500,8 +5642,8 @@
       <c r="B37" s="7">
         <v>5</v>
       </c>
-      <c r="C37" s="158"/>
-      <c r="D37" s="135" t="s">
+      <c r="C37" s="148"/>
+      <c r="D37" s="159" t="s">
         <v>62</v>
       </c>
       <c r="E37" s="8" t="s">
@@ -5513,9 +5655,13 @@
       <c r="G37" s="10">
         <v>3</v>
       </c>
-      <c r="H37" s="11"/>
+      <c r="H37" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
+      <c r="J37" s="11" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="38" spans="1:10" ht="13.8">
       <c r="A38" s="6">
@@ -5524,8 +5670,8 @@
       <c r="B38" s="7">
         <v>6</v>
       </c>
-      <c r="C38" s="158"/>
-      <c r="D38" s="156"/>
+      <c r="C38" s="148"/>
+      <c r="D38" s="160"/>
       <c r="E38" s="8" t="s">
         <v>64</v>
       </c>
@@ -5546,8 +5692,8 @@
       <c r="B39" s="7">
         <v>7</v>
       </c>
-      <c r="C39" s="158"/>
-      <c r="D39" s="157"/>
+      <c r="C39" s="148"/>
+      <c r="D39" s="161"/>
       <c r="E39" s="8" t="s">
         <v>65</v>
       </c>
@@ -5568,8 +5714,8 @@
       <c r="B40" s="7">
         <v>8</v>
       </c>
-      <c r="C40" s="158"/>
-      <c r="D40" s="135" t="s">
+      <c r="C40" s="148"/>
+      <c r="D40" s="159" t="s">
         <v>66</v>
       </c>
       <c r="E40" s="8" t="s">
@@ -5592,8 +5738,8 @@
       <c r="B41" s="7">
         <v>9</v>
       </c>
-      <c r="C41" s="158"/>
-      <c r="D41" s="156"/>
+      <c r="C41" s="148"/>
+      <c r="D41" s="160"/>
       <c r="E41" s="8" t="s">
         <v>68</v>
       </c>
@@ -5614,8 +5760,8 @@
       <c r="B42" s="7">
         <v>10</v>
       </c>
-      <c r="C42" s="158"/>
-      <c r="D42" s="156"/>
+      <c r="C42" s="148"/>
+      <c r="D42" s="160"/>
       <c r="E42" s="8" t="s">
         <v>69</v>
       </c>
@@ -5636,8 +5782,8 @@
       <c r="B43" s="7">
         <v>11</v>
       </c>
-      <c r="C43" s="158"/>
-      <c r="D43" s="156"/>
+      <c r="C43" s="148"/>
+      <c r="D43" s="160"/>
       <c r="E43" s="8" t="s">
         <v>70</v>
       </c>
@@ -5658,8 +5804,8 @@
       <c r="B44" s="24">
         <v>12</v>
       </c>
-      <c r="C44" s="159"/>
-      <c r="D44" s="157"/>
+      <c r="C44" s="149"/>
+      <c r="D44" s="161"/>
       <c r="E44" s="17" t="s">
         <v>71</v>
       </c>
@@ -5680,10 +5826,10 @@
       <c r="B45" s="22">
         <v>1</v>
       </c>
-      <c r="C45" s="143" t="s">
+      <c r="C45" s="150" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="144" t="s">
+      <c r="D45" s="162" t="s">
         <v>73</v>
       </c>
       <c r="E45" s="13" t="s">
@@ -5710,8 +5856,8 @@
       <c r="B46" s="7">
         <v>2</v>
       </c>
-      <c r="C46" s="176"/>
-      <c r="D46" s="170"/>
+      <c r="C46" s="151"/>
+      <c r="D46" s="163"/>
       <c r="E46" s="8" t="s">
         <v>75</v>
       </c>
@@ -5738,8 +5884,8 @@
       <c r="B47" s="7">
         <v>3</v>
       </c>
-      <c r="C47" s="176"/>
-      <c r="D47" s="170"/>
+      <c r="C47" s="151"/>
+      <c r="D47" s="163"/>
       <c r="E47" s="13" t="s">
         <v>76</v>
       </c>
@@ -5766,8 +5912,8 @@
       <c r="B48" s="7">
         <v>4</v>
       </c>
-      <c r="C48" s="176"/>
-      <c r="D48" s="170"/>
+      <c r="C48" s="151"/>
+      <c r="D48" s="163"/>
       <c r="E48" s="13" t="s">
         <v>77</v>
       </c>
@@ -5794,8 +5940,8 @@
       <c r="B49" s="7">
         <v>5</v>
       </c>
-      <c r="C49" s="176"/>
-      <c r="D49" s="170"/>
+      <c r="C49" s="151"/>
+      <c r="D49" s="163"/>
       <c r="E49" s="13" t="s">
         <v>78</v>
       </c>
@@ -5820,8 +5966,8 @@
       <c r="B50" s="24">
         <v>6</v>
       </c>
-      <c r="C50" s="177"/>
-      <c r="D50" s="171"/>
+      <c r="C50" s="152"/>
+      <c r="D50" s="164"/>
       <c r="E50" s="25" t="s">
         <v>79</v>
       </c>
@@ -5846,10 +5992,10 @@
       <c r="B51" s="7">
         <v>1</v>
       </c>
-      <c r="C51" s="140" t="s">
+      <c r="C51" s="141" t="s">
         <v>80</v>
       </c>
-      <c r="D51" s="135" t="s">
+      <c r="D51" s="159" t="s">
         <v>81</v>
       </c>
       <c r="E51" s="13" t="s">
@@ -5878,8 +6024,8 @@
       <c r="B52" s="7">
         <v>2</v>
       </c>
-      <c r="C52" s="166"/>
-      <c r="D52" s="156"/>
+      <c r="C52" s="142"/>
+      <c r="D52" s="160"/>
       <c r="E52" s="8" t="s">
         <v>83</v>
       </c>
@@ -5892,7 +6038,7 @@
       <c r="H52" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I52" s="191" t="s">
+      <c r="I52" s="135" t="s">
         <v>715</v>
       </c>
       <c r="J52" s="11" t="s">
@@ -5906,8 +6052,8 @@
       <c r="B53" s="7">
         <v>3</v>
       </c>
-      <c r="C53" s="166"/>
-      <c r="D53" s="156"/>
+      <c r="C53" s="142"/>
+      <c r="D53" s="160"/>
       <c r="E53" s="27" t="s">
         <v>84</v>
       </c>
@@ -5932,8 +6078,8 @@
       <c r="B54" s="7">
         <v>4</v>
       </c>
-      <c r="C54" s="166"/>
-      <c r="D54" s="156"/>
+      <c r="C54" s="142"/>
+      <c r="D54" s="160"/>
       <c r="E54" s="13" t="s">
         <v>85</v>
       </c>
@@ -5958,8 +6104,8 @@
       <c r="B55" s="7">
         <v>5</v>
       </c>
-      <c r="C55" s="166"/>
-      <c r="D55" s="156"/>
+      <c r="C55" s="142"/>
+      <c r="D55" s="160"/>
       <c r="E55" s="13" t="s">
         <v>86</v>
       </c>
@@ -5972,7 +6118,7 @@
       <c r="H55" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I55" s="192" t="s">
+      <c r="I55" s="136" t="s">
         <v>716</v>
       </c>
       <c r="J55" s="126" t="s">
@@ -5986,8 +6132,8 @@
       <c r="B56" s="7">
         <v>6</v>
       </c>
-      <c r="C56" s="166"/>
-      <c r="D56" s="156"/>
+      <c r="C56" s="142"/>
+      <c r="D56" s="160"/>
       <c r="E56" s="13" t="s">
         <v>87</v>
       </c>
@@ -6000,7 +6146,7 @@
       <c r="H56" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I56" s="193" t="s">
+      <c r="I56" s="137" t="s">
         <v>717</v>
       </c>
       <c r="J56" s="126" t="s">
@@ -6014,8 +6160,8 @@
       <c r="B57" s="7">
         <v>7</v>
       </c>
-      <c r="C57" s="166"/>
-      <c r="D57" s="157"/>
+      <c r="C57" s="142"/>
+      <c r="D57" s="161"/>
       <c r="E57" s="13" t="s">
         <v>88</v>
       </c>
@@ -6042,8 +6188,8 @@
       <c r="B58" s="7">
         <v>8</v>
       </c>
-      <c r="C58" s="166"/>
-      <c r="D58" s="135" t="s">
+      <c r="C58" s="142"/>
+      <c r="D58" s="159" t="s">
         <v>89</v>
       </c>
       <c r="E58" s="13" t="s">
@@ -6066,8 +6212,8 @@
       <c r="B59" s="7">
         <v>9</v>
       </c>
-      <c r="C59" s="166"/>
-      <c r="D59" s="156"/>
+      <c r="C59" s="142"/>
+      <c r="D59" s="160"/>
       <c r="E59" s="8" t="s">
         <v>91</v>
       </c>
@@ -6088,8 +6234,8 @@
       <c r="B60" s="7">
         <v>10</v>
       </c>
-      <c r="C60" s="166"/>
-      <c r="D60" s="156"/>
+      <c r="C60" s="142"/>
+      <c r="D60" s="160"/>
       <c r="E60" s="8" t="s">
         <v>92</v>
       </c>
@@ -6110,8 +6256,8 @@
       <c r="B61" s="7">
         <v>11</v>
       </c>
-      <c r="C61" s="166"/>
-      <c r="D61" s="156"/>
+      <c r="C61" s="142"/>
+      <c r="D61" s="160"/>
       <c r="E61" s="8" t="s">
         <v>93</v>
       </c>
@@ -6132,8 +6278,8 @@
       <c r="B62" s="7">
         <v>12</v>
       </c>
-      <c r="C62" s="166"/>
-      <c r="D62" s="156"/>
+      <c r="C62" s="142"/>
+      <c r="D62" s="160"/>
       <c r="E62" s="8" t="s">
         <v>94</v>
       </c>
@@ -6154,8 +6300,8 @@
       <c r="B63" s="7">
         <v>13</v>
       </c>
-      <c r="C63" s="166"/>
-      <c r="D63" s="157"/>
+      <c r="C63" s="142"/>
+      <c r="D63" s="161"/>
       <c r="E63" s="8" t="s">
         <v>95</v>
       </c>
@@ -6176,8 +6322,8 @@
       <c r="B64" s="7">
         <v>14</v>
       </c>
-      <c r="C64" s="166"/>
-      <c r="D64" s="135" t="s">
+      <c r="C64" s="142"/>
+      <c r="D64" s="159" t="s">
         <v>48</v>
       </c>
       <c r="E64" s="8" t="s">
@@ -6200,8 +6346,8 @@
       <c r="B65" s="7">
         <v>15</v>
       </c>
-      <c r="C65" s="166"/>
-      <c r="D65" s="156"/>
+      <c r="C65" s="142"/>
+      <c r="D65" s="160"/>
       <c r="E65" s="8" t="s">
         <v>97</v>
       </c>
@@ -6222,8 +6368,8 @@
       <c r="B66" s="7">
         <v>16</v>
       </c>
-      <c r="C66" s="166"/>
-      <c r="D66" s="156"/>
+      <c r="C66" s="142"/>
+      <c r="D66" s="160"/>
       <c r="E66" s="8" t="s">
         <v>98</v>
       </c>
@@ -6244,8 +6390,8 @@
       <c r="B67" s="7">
         <v>17</v>
       </c>
-      <c r="C67" s="167"/>
-      <c r="D67" s="157"/>
+      <c r="C67" s="143"/>
+      <c r="D67" s="161"/>
       <c r="E67" s="8" t="s">
         <v>99</v>
       </c>
@@ -6260,18 +6406,18 @@
       <c r="J67" s="11"/>
     </row>
     <row r="68" spans="1:10" ht="13.8">
-      <c r="A68" s="145" t="s">
+      <c r="A68" s="171" t="s">
         <v>100</v>
       </c>
-      <c r="B68" s="178"/>
-      <c r="C68" s="178"/>
-      <c r="D68" s="178"/>
-      <c r="E68" s="178"/>
-      <c r="F68" s="178"/>
-      <c r="G68" s="178"/>
-      <c r="H68" s="178"/>
-      <c r="I68" s="178"/>
-      <c r="J68" s="179"/>
+      <c r="B68" s="172"/>
+      <c r="C68" s="172"/>
+      <c r="D68" s="172"/>
+      <c r="E68" s="172"/>
+      <c r="F68" s="172"/>
+      <c r="G68" s="172"/>
+      <c r="H68" s="172"/>
+      <c r="I68" s="172"/>
+      <c r="J68" s="173"/>
     </row>
     <row r="69" spans="1:10" ht="13.8">
       <c r="A69" s="6">
@@ -6280,10 +6426,10 @@
       <c r="B69" s="7">
         <v>1</v>
       </c>
-      <c r="C69" s="137" t="s">
+      <c r="C69" s="144" t="s">
         <v>101</v>
       </c>
-      <c r="D69" s="135" t="s">
+      <c r="D69" s="159" t="s">
         <v>102</v>
       </c>
       <c r="E69" s="8" t="s">
@@ -6306,8 +6452,8 @@
       <c r="B70" s="7">
         <v>2</v>
       </c>
-      <c r="C70" s="164"/>
-      <c r="D70" s="156"/>
+      <c r="C70" s="145"/>
+      <c r="D70" s="160"/>
       <c r="E70" s="28" t="s">
         <v>104</v>
       </c>
@@ -6328,8 +6474,8 @@
       <c r="B71" s="7">
         <v>3</v>
       </c>
-      <c r="C71" s="164"/>
-      <c r="D71" s="156"/>
+      <c r="C71" s="145"/>
+      <c r="D71" s="160"/>
       <c r="E71" s="8" t="s">
         <v>105</v>
       </c>
@@ -6350,8 +6496,8 @@
       <c r="B72" s="7">
         <v>4</v>
       </c>
-      <c r="C72" s="164"/>
-      <c r="D72" s="156"/>
+      <c r="C72" s="145"/>
+      <c r="D72" s="160"/>
       <c r="E72" s="8" t="s">
         <v>106</v>
       </c>
@@ -6372,8 +6518,8 @@
       <c r="B73" s="7">
         <v>5</v>
       </c>
-      <c r="C73" s="164"/>
-      <c r="D73" s="156"/>
+      <c r="C73" s="145"/>
+      <c r="D73" s="160"/>
       <c r="E73" s="28" t="s">
         <v>107</v>
       </c>
@@ -6394,8 +6540,8 @@
       <c r="B74" s="7">
         <v>6</v>
       </c>
-      <c r="C74" s="164"/>
-      <c r="D74" s="156"/>
+      <c r="C74" s="145"/>
+      <c r="D74" s="160"/>
       <c r="E74" s="28" t="s">
         <v>108</v>
       </c>
@@ -6416,8 +6562,8 @@
       <c r="B75" s="7">
         <v>7</v>
       </c>
-      <c r="C75" s="164"/>
-      <c r="D75" s="156"/>
+      <c r="C75" s="145"/>
+      <c r="D75" s="160"/>
       <c r="E75" s="28" t="s">
         <v>109</v>
       </c>
@@ -6438,8 +6584,8 @@
       <c r="B76" s="7">
         <v>8</v>
       </c>
-      <c r="C76" s="164"/>
-      <c r="D76" s="156"/>
+      <c r="C76" s="145"/>
+      <c r="D76" s="160"/>
       <c r="E76" s="8" t="s">
         <v>110</v>
       </c>
@@ -6460,8 +6606,8 @@
       <c r="B77" s="7">
         <v>9</v>
       </c>
-      <c r="C77" s="164"/>
-      <c r="D77" s="156"/>
+      <c r="C77" s="145"/>
+      <c r="D77" s="160"/>
       <c r="E77" s="8" t="s">
         <v>111</v>
       </c>
@@ -6482,8 +6628,8 @@
       <c r="B78" s="7">
         <v>10</v>
       </c>
-      <c r="C78" s="164"/>
-      <c r="D78" s="157"/>
+      <c r="C78" s="145"/>
+      <c r="D78" s="161"/>
       <c r="E78" s="8" t="s">
         <v>112</v>
       </c>
@@ -6504,8 +6650,8 @@
       <c r="B79" s="7">
         <v>11</v>
       </c>
-      <c r="C79" s="164"/>
-      <c r="D79" s="135" t="s">
+      <c r="C79" s="145"/>
+      <c r="D79" s="159" t="s">
         <v>113</v>
       </c>
       <c r="E79" s="8" t="s">
@@ -6528,8 +6674,8 @@
       <c r="B80" s="7">
         <v>12</v>
       </c>
-      <c r="C80" s="164"/>
-      <c r="D80" s="156"/>
+      <c r="C80" s="145"/>
+      <c r="D80" s="160"/>
       <c r="E80" s="8" t="s">
         <v>115</v>
       </c>
@@ -6550,8 +6696,8 @@
       <c r="B81" s="7">
         <v>13</v>
       </c>
-      <c r="C81" s="164"/>
-      <c r="D81" s="156"/>
+      <c r="C81" s="145"/>
+      <c r="D81" s="160"/>
       <c r="E81" s="8" t="s">
         <v>116</v>
       </c>
@@ -6572,8 +6718,8 @@
       <c r="B82" s="7">
         <v>14</v>
       </c>
-      <c r="C82" s="164"/>
-      <c r="D82" s="156"/>
+      <c r="C82" s="145"/>
+      <c r="D82" s="160"/>
       <c r="E82" s="8" t="s">
         <v>117</v>
       </c>
@@ -6594,8 +6740,8 @@
       <c r="B83" s="7">
         <v>15</v>
       </c>
-      <c r="C83" s="164"/>
-      <c r="D83" s="156"/>
+      <c r="C83" s="145"/>
+      <c r="D83" s="160"/>
       <c r="E83" s="8" t="s">
         <v>118</v>
       </c>
@@ -6616,8 +6762,8 @@
       <c r="B84" s="7">
         <v>16</v>
       </c>
-      <c r="C84" s="164"/>
-      <c r="D84" s="157"/>
+      <c r="C84" s="145"/>
+      <c r="D84" s="161"/>
       <c r="E84" s="8" t="s">
         <v>119</v>
       </c>
@@ -6638,8 +6784,8 @@
       <c r="B85" s="7">
         <v>17</v>
       </c>
-      <c r="C85" s="164"/>
-      <c r="D85" s="135" t="s">
+      <c r="C85" s="145"/>
+      <c r="D85" s="159" t="s">
         <v>120</v>
       </c>
       <c r="E85" s="8" t="s">
@@ -6662,8 +6808,8 @@
       <c r="B86" s="7">
         <v>18</v>
       </c>
-      <c r="C86" s="164"/>
-      <c r="D86" s="156"/>
+      <c r="C86" s="145"/>
+      <c r="D86" s="160"/>
       <c r="E86" s="8" t="s">
         <v>122</v>
       </c>
@@ -6684,8 +6830,8 @@
       <c r="B87" s="7">
         <v>19</v>
       </c>
-      <c r="C87" s="164"/>
-      <c r="D87" s="156"/>
+      <c r="C87" s="145"/>
+      <c r="D87" s="160"/>
       <c r="E87" s="29" t="s">
         <v>123</v>
       </c>
@@ -6706,8 +6852,8 @@
       <c r="B88" s="7">
         <v>20</v>
       </c>
-      <c r="C88" s="164"/>
-      <c r="D88" s="156"/>
+      <c r="C88" s="145"/>
+      <c r="D88" s="160"/>
       <c r="E88" s="8" t="s">
         <v>124</v>
       </c>
@@ -6728,8 +6874,8 @@
       <c r="B89" s="7">
         <v>21</v>
       </c>
-      <c r="C89" s="164"/>
-      <c r="D89" s="156"/>
+      <c r="C89" s="145"/>
+      <c r="D89" s="160"/>
       <c r="E89" s="8" t="s">
         <v>125</v>
       </c>
@@ -6750,8 +6896,8 @@
       <c r="B90" s="7">
         <v>22</v>
       </c>
-      <c r="C90" s="164"/>
-      <c r="D90" s="157"/>
+      <c r="C90" s="145"/>
+      <c r="D90" s="161"/>
       <c r="E90" s="8" t="s">
         <v>126</v>
       </c>
@@ -6772,8 +6918,8 @@
       <c r="B91" s="7">
         <v>23</v>
       </c>
-      <c r="C91" s="164"/>
-      <c r="D91" s="135" t="s">
+      <c r="C91" s="145"/>
+      <c r="D91" s="159" t="s">
         <v>127</v>
       </c>
       <c r="E91" s="8" t="s">
@@ -6796,8 +6942,8 @@
       <c r="B92" s="7">
         <v>24</v>
       </c>
-      <c r="C92" s="164"/>
-      <c r="D92" s="156"/>
+      <c r="C92" s="145"/>
+      <c r="D92" s="160"/>
       <c r="E92" s="8" t="s">
         <v>129</v>
       </c>
@@ -6818,8 +6964,8 @@
       <c r="B93" s="7">
         <v>25</v>
       </c>
-      <c r="C93" s="164"/>
-      <c r="D93" s="156"/>
+      <c r="C93" s="145"/>
+      <c r="D93" s="160"/>
       <c r="E93" s="8" t="s">
         <v>130</v>
       </c>
@@ -6840,8 +6986,8 @@
       <c r="B94" s="7">
         <v>26</v>
       </c>
-      <c r="C94" s="164"/>
-      <c r="D94" s="156"/>
+      <c r="C94" s="145"/>
+      <c r="D94" s="160"/>
       <c r="E94" s="8" t="s">
         <v>131</v>
       </c>
@@ -6862,8 +7008,8 @@
       <c r="B95" s="7">
         <v>27</v>
       </c>
-      <c r="C95" s="164"/>
-      <c r="D95" s="156"/>
+      <c r="C95" s="145"/>
+      <c r="D95" s="160"/>
       <c r="E95" s="8" t="s">
         <v>132</v>
       </c>
@@ -6884,8 +7030,8 @@
       <c r="B96" s="7">
         <v>28</v>
       </c>
-      <c r="C96" s="164"/>
-      <c r="D96" s="156"/>
+      <c r="C96" s="145"/>
+      <c r="D96" s="160"/>
       <c r="E96" s="8" t="s">
         <v>133</v>
       </c>
@@ -6906,8 +7052,8 @@
       <c r="B97" s="7">
         <v>29</v>
       </c>
-      <c r="C97" s="164"/>
-      <c r="D97" s="156"/>
+      <c r="C97" s="145"/>
+      <c r="D97" s="160"/>
       <c r="E97" s="8" t="s">
         <v>134</v>
       </c>
@@ -6928,8 +7074,8 @@
       <c r="B98" s="7">
         <v>30</v>
       </c>
-      <c r="C98" s="164"/>
-      <c r="D98" s="156"/>
+      <c r="C98" s="145"/>
+      <c r="D98" s="160"/>
       <c r="E98" s="8" t="s">
         <v>135</v>
       </c>
@@ -6950,8 +7096,8 @@
       <c r="B99" s="7">
         <v>31</v>
       </c>
-      <c r="C99" s="164"/>
-      <c r="D99" s="156"/>
+      <c r="C99" s="145"/>
+      <c r="D99" s="160"/>
       <c r="E99" s="30" t="s">
         <v>136</v>
       </c>
@@ -6972,8 +7118,8 @@
       <c r="B100" s="7">
         <v>32</v>
       </c>
-      <c r="C100" s="164"/>
-      <c r="D100" s="156"/>
+      <c r="C100" s="145"/>
+      <c r="D100" s="160"/>
       <c r="E100" s="8" t="s">
         <v>137</v>
       </c>
@@ -6994,8 +7140,8 @@
       <c r="B101" s="7">
         <v>33</v>
       </c>
-      <c r="C101" s="164"/>
-      <c r="D101" s="156"/>
+      <c r="C101" s="145"/>
+      <c r="D101" s="160"/>
       <c r="E101" s="8" t="s">
         <v>138</v>
       </c>
@@ -7016,8 +7162,8 @@
       <c r="B102" s="7">
         <v>34</v>
       </c>
-      <c r="C102" s="164"/>
-      <c r="D102" s="156"/>
+      <c r="C102" s="145"/>
+      <c r="D102" s="160"/>
       <c r="E102" s="8" t="s">
         <v>139</v>
       </c>
@@ -7038,8 +7184,8 @@
       <c r="B103" s="7">
         <v>35</v>
       </c>
-      <c r="C103" s="164"/>
-      <c r="D103" s="156"/>
+      <c r="C103" s="145"/>
+      <c r="D103" s="160"/>
       <c r="E103" s="8" t="s">
         <v>140</v>
       </c>
@@ -7060,8 +7206,8 @@
       <c r="B104" s="7">
         <v>36</v>
       </c>
-      <c r="C104" s="164"/>
-      <c r="D104" s="156"/>
+      <c r="C104" s="145"/>
+      <c r="D104" s="160"/>
       <c r="E104" s="8" t="s">
         <v>141</v>
       </c>
@@ -7082,8 +7228,8 @@
       <c r="B105" s="7">
         <v>37</v>
       </c>
-      <c r="C105" s="165"/>
-      <c r="D105" s="157"/>
+      <c r="C105" s="146"/>
+      <c r="D105" s="161"/>
       <c r="E105" s="8" t="s">
         <v>142</v>
       </c>
@@ -7098,18 +7244,18 @@
       <c r="J105" s="11"/>
     </row>
     <row r="106" spans="1:10" ht="13.8">
-      <c r="A106" s="141" t="s">
+      <c r="A106" s="177" t="s">
         <v>143</v>
       </c>
-      <c r="B106" s="186"/>
-      <c r="C106" s="186"/>
-      <c r="D106" s="186"/>
-      <c r="E106" s="186"/>
-      <c r="F106" s="186"/>
-      <c r="G106" s="186"/>
-      <c r="H106" s="186"/>
-      <c r="I106" s="186"/>
-      <c r="J106" s="187"/>
+      <c r="B106" s="178"/>
+      <c r="C106" s="178"/>
+      <c r="D106" s="178"/>
+      <c r="E106" s="178"/>
+      <c r="F106" s="178"/>
+      <c r="G106" s="178"/>
+      <c r="H106" s="178"/>
+      <c r="I106" s="178"/>
+      <c r="J106" s="179"/>
     </row>
     <row r="107" spans="1:10" ht="13.8">
       <c r="A107" s="6">
@@ -7118,10 +7264,10 @@
       <c r="B107" s="7">
         <v>1</v>
       </c>
-      <c r="C107" s="138" t="s">
+      <c r="C107" s="147" t="s">
         <v>144</v>
       </c>
-      <c r="D107" s="135" t="s">
+      <c r="D107" s="159" t="s">
         <v>145</v>
       </c>
       <c r="E107" s="8" t="s">
@@ -7144,8 +7290,8 @@
       <c r="B108" s="7">
         <v>2</v>
       </c>
-      <c r="C108" s="158"/>
-      <c r="D108" s="156"/>
+      <c r="C108" s="148"/>
+      <c r="D108" s="160"/>
       <c r="E108" s="8" t="s">
         <v>147</v>
       </c>
@@ -7166,8 +7312,8 @@
       <c r="B109" s="7">
         <v>3</v>
       </c>
-      <c r="C109" s="158"/>
-      <c r="D109" s="156"/>
+      <c r="C109" s="148"/>
+      <c r="D109" s="160"/>
       <c r="E109" s="8" t="s">
         <v>148</v>
       </c>
@@ -7188,8 +7334,8 @@
       <c r="B110" s="7">
         <v>4</v>
       </c>
-      <c r="C110" s="158"/>
-      <c r="D110" s="156"/>
+      <c r="C110" s="148"/>
+      <c r="D110" s="160"/>
       <c r="E110" s="8" t="s">
         <v>149</v>
       </c>
@@ -7210,8 +7356,8 @@
       <c r="B111" s="7">
         <v>5</v>
       </c>
-      <c r="C111" s="158"/>
-      <c r="D111" s="157"/>
+      <c r="C111" s="148"/>
+      <c r="D111" s="161"/>
       <c r="E111" s="8" t="s">
         <v>150</v>
       </c>
@@ -7232,8 +7378,8 @@
       <c r="B112" s="7">
         <v>6</v>
       </c>
-      <c r="C112" s="158"/>
-      <c r="D112" s="135" t="s">
+      <c r="C112" s="148"/>
+      <c r="D112" s="159" t="s">
         <v>151</v>
       </c>
       <c r="E112" s="8" t="s">
@@ -7256,8 +7402,8 @@
       <c r="B113" s="7">
         <v>7</v>
       </c>
-      <c r="C113" s="158"/>
-      <c r="D113" s="156"/>
+      <c r="C113" s="148"/>
+      <c r="D113" s="160"/>
       <c r="E113" s="8" t="s">
         <v>153</v>
       </c>
@@ -7278,8 +7424,8 @@
       <c r="B114" s="7">
         <v>8</v>
       </c>
-      <c r="C114" s="158"/>
-      <c r="D114" s="156"/>
+      <c r="C114" s="148"/>
+      <c r="D114" s="160"/>
       <c r="E114" s="8" t="s">
         <v>154</v>
       </c>
@@ -7300,8 +7446,8 @@
       <c r="B115" s="7">
         <v>9</v>
       </c>
-      <c r="C115" s="158"/>
-      <c r="D115" s="157"/>
+      <c r="C115" s="148"/>
+      <c r="D115" s="161"/>
       <c r="E115" s="8" t="s">
         <v>155</v>
       </c>
@@ -7322,7 +7468,7 @@
       <c r="B116" s="24">
         <v>10</v>
       </c>
-      <c r="C116" s="159"/>
+      <c r="C116" s="149"/>
       <c r="D116" s="31" t="s">
         <v>156</v>
       </c>
@@ -7346,10 +7492,10 @@
       <c r="B117" s="7">
         <v>1</v>
       </c>
-      <c r="C117" s="139" t="s">
+      <c r="C117" s="138" t="s">
         <v>158</v>
       </c>
-      <c r="D117" s="135" t="s">
+      <c r="D117" s="159" t="s">
         <v>159</v>
       </c>
       <c r="E117" s="8" t="s">
@@ -7372,8 +7518,8 @@
       <c r="B118" s="7">
         <v>2</v>
       </c>
-      <c r="C118" s="160"/>
-      <c r="D118" s="156"/>
+      <c r="C118" s="139"/>
+      <c r="D118" s="160"/>
       <c r="E118" s="8" t="s">
         <v>161</v>
       </c>
@@ -7394,8 +7540,8 @@
       <c r="B119" s="7">
         <v>3</v>
       </c>
-      <c r="C119" s="160"/>
-      <c r="D119" s="156"/>
+      <c r="C119" s="139"/>
+      <c r="D119" s="160"/>
       <c r="E119" s="8" t="s">
         <v>162</v>
       </c>
@@ -7416,8 +7562,8 @@
       <c r="B120" s="7">
         <v>4</v>
       </c>
-      <c r="C120" s="160"/>
-      <c r="D120" s="157"/>
+      <c r="C120" s="139"/>
+      <c r="D120" s="161"/>
       <c r="E120" s="8" t="s">
         <v>163</v>
       </c>
@@ -7438,8 +7584,8 @@
       <c r="B121" s="7">
         <v>5</v>
       </c>
-      <c r="C121" s="160"/>
-      <c r="D121" s="135" t="s">
+      <c r="C121" s="139"/>
+      <c r="D121" s="159" t="s">
         <v>164</v>
       </c>
       <c r="E121" s="8" t="s">
@@ -7462,8 +7608,8 @@
       <c r="B122" s="7">
         <v>6</v>
       </c>
-      <c r="C122" s="160"/>
-      <c r="D122" s="157"/>
+      <c r="C122" s="139"/>
+      <c r="D122" s="161"/>
       <c r="E122" s="8" t="s">
         <v>166</v>
       </c>
@@ -7484,8 +7630,8 @@
       <c r="B123" s="7">
         <v>7</v>
       </c>
-      <c r="C123" s="160"/>
-      <c r="D123" s="135" t="s">
+      <c r="C123" s="139"/>
+      <c r="D123" s="159" t="s">
         <v>167</v>
       </c>
       <c r="E123" s="8" t="s">
@@ -7508,8 +7654,8 @@
       <c r="B124" s="7">
         <v>8</v>
       </c>
-      <c r="C124" s="160"/>
-      <c r="D124" s="156"/>
+      <c r="C124" s="139"/>
+      <c r="D124" s="160"/>
       <c r="E124" s="28" t="s">
         <v>169</v>
       </c>
@@ -7530,8 +7676,8 @@
       <c r="B125" s="7">
         <v>9</v>
       </c>
-      <c r="C125" s="161"/>
-      <c r="D125" s="157"/>
+      <c r="C125" s="140"/>
+      <c r="D125" s="161"/>
       <c r="E125" s="8" t="s">
         <v>170</v>
       </c>
@@ -7546,18 +7692,18 @@
       <c r="J125" s="11"/>
     </row>
     <row r="126" spans="1:10" ht="13.8">
-      <c r="A126" s="142" t="s">
+      <c r="A126" s="180" t="s">
         <v>171</v>
       </c>
-      <c r="B126" s="184"/>
-      <c r="C126" s="184"/>
-      <c r="D126" s="184"/>
-      <c r="E126" s="184"/>
-      <c r="F126" s="184"/>
-      <c r="G126" s="184"/>
-      <c r="H126" s="184"/>
-      <c r="I126" s="184"/>
-      <c r="J126" s="185"/>
+      <c r="B126" s="181"/>
+      <c r="C126" s="181"/>
+      <c r="D126" s="181"/>
+      <c r="E126" s="181"/>
+      <c r="F126" s="181"/>
+      <c r="G126" s="181"/>
+      <c r="H126" s="181"/>
+      <c r="I126" s="181"/>
+      <c r="J126" s="182"/>
     </row>
     <row r="127" spans="1:10" ht="13.8">
       <c r="A127" s="6">
@@ -7566,10 +7712,10 @@
       <c r="B127" s="7">
         <v>1</v>
       </c>
-      <c r="C127" s="140" t="s">
+      <c r="C127" s="141" t="s">
         <v>172</v>
       </c>
-      <c r="D127" s="135" t="s">
+      <c r="D127" s="159" t="s">
         <v>173</v>
       </c>
       <c r="E127" s="32" t="s">
@@ -7590,8 +7736,8 @@
       <c r="B128" s="7">
         <v>2</v>
       </c>
-      <c r="C128" s="166"/>
-      <c r="D128" s="156"/>
+      <c r="C128" s="142"/>
+      <c r="D128" s="160"/>
       <c r="E128" s="32" t="s">
         <v>175</v>
       </c>
@@ -7610,8 +7756,8 @@
       <c r="B129" s="7">
         <v>3</v>
       </c>
-      <c r="C129" s="166"/>
-      <c r="D129" s="156"/>
+      <c r="C129" s="142"/>
+      <c r="D129" s="160"/>
       <c r="E129" s="32" t="s">
         <v>176</v>
       </c>
@@ -7630,8 +7776,8 @@
       <c r="B130" s="7">
         <v>4</v>
       </c>
-      <c r="C130" s="166"/>
-      <c r="D130" s="157"/>
+      <c r="C130" s="142"/>
+      <c r="D130" s="161"/>
       <c r="E130" s="32" t="s">
         <v>177</v>
       </c>
@@ -7650,8 +7796,8 @@
       <c r="B131" s="7">
         <v>5</v>
       </c>
-      <c r="C131" s="166"/>
-      <c r="D131" s="135" t="s">
+      <c r="C131" s="142"/>
+      <c r="D131" s="159" t="s">
         <v>178</v>
       </c>
       <c r="E131" s="32" t="s">
@@ -7672,8 +7818,8 @@
       <c r="B132" s="7">
         <v>6</v>
       </c>
-      <c r="C132" s="167"/>
-      <c r="D132" s="157"/>
+      <c r="C132" s="143"/>
+      <c r="D132" s="161"/>
       <c r="E132" s="32" t="s">
         <v>180</v>
       </c>
@@ -7686,18 +7832,18 @@
       <c r="J132" s="11"/>
     </row>
     <row r="133" spans="1:10" ht="13.8">
-      <c r="A133" s="136" t="s">
+      <c r="A133" s="183" t="s">
         <v>181</v>
       </c>
-      <c r="B133" s="182"/>
-      <c r="C133" s="182"/>
-      <c r="D133" s="182"/>
-      <c r="E133" s="182"/>
-      <c r="F133" s="182"/>
-      <c r="G133" s="182"/>
-      <c r="H133" s="182"/>
-      <c r="I133" s="182"/>
-      <c r="J133" s="183"/>
+      <c r="B133" s="184"/>
+      <c r="C133" s="184"/>
+      <c r="D133" s="184"/>
+      <c r="E133" s="184"/>
+      <c r="F133" s="184"/>
+      <c r="G133" s="184"/>
+      <c r="H133" s="184"/>
+      <c r="I133" s="184"/>
+      <c r="J133" s="185"/>
     </row>
     <row r="134" spans="1:10" ht="13.8">
       <c r="A134" s="6">
@@ -7706,10 +7852,10 @@
       <c r="B134" s="7">
         <v>1</v>
       </c>
-      <c r="C134" s="137" t="s">
+      <c r="C134" s="144" t="s">
         <v>182</v>
       </c>
-      <c r="D134" s="135" t="s">
+      <c r="D134" s="159" t="s">
         <v>183</v>
       </c>
       <c r="E134" s="8" t="s">
@@ -7732,8 +7878,8 @@
       <c r="B135" s="7">
         <v>2</v>
       </c>
-      <c r="C135" s="164"/>
-      <c r="D135" s="156"/>
+      <c r="C135" s="145"/>
+      <c r="D135" s="160"/>
       <c r="E135" s="8" t="s">
         <v>185</v>
       </c>
@@ -7754,8 +7900,8 @@
       <c r="B136" s="7">
         <v>3</v>
       </c>
-      <c r="C136" s="164"/>
-      <c r="D136" s="157"/>
+      <c r="C136" s="145"/>
+      <c r="D136" s="161"/>
       <c r="E136" s="8" t="s">
         <v>186</v>
       </c>
@@ -7776,8 +7922,8 @@
       <c r="B137" s="7">
         <v>4</v>
       </c>
-      <c r="C137" s="164"/>
-      <c r="D137" s="135" t="s">
+      <c r="C137" s="145"/>
+      <c r="D137" s="159" t="s">
         <v>187</v>
       </c>
       <c r="E137" s="8" t="s">
@@ -7800,8 +7946,8 @@
       <c r="B138" s="7">
         <v>5</v>
       </c>
-      <c r="C138" s="164"/>
-      <c r="D138" s="156"/>
+      <c r="C138" s="145"/>
+      <c r="D138" s="160"/>
       <c r="E138" s="8" t="s">
         <v>189</v>
       </c>
@@ -7822,8 +7968,8 @@
       <c r="B139" s="7">
         <v>6</v>
       </c>
-      <c r="C139" s="164"/>
-      <c r="D139" s="156"/>
+      <c r="C139" s="145"/>
+      <c r="D139" s="160"/>
       <c r="E139" s="8" t="s">
         <v>190</v>
       </c>
@@ -7844,8 +7990,8 @@
       <c r="B140" s="7">
         <v>7</v>
       </c>
-      <c r="C140" s="164"/>
-      <c r="D140" s="156"/>
+      <c r="C140" s="145"/>
+      <c r="D140" s="160"/>
       <c r="E140" s="8" t="s">
         <v>191</v>
       </c>
@@ -7866,8 +8012,8 @@
       <c r="B141" s="7">
         <v>8</v>
       </c>
-      <c r="C141" s="164"/>
-      <c r="D141" s="156"/>
+      <c r="C141" s="145"/>
+      <c r="D141" s="160"/>
       <c r="E141" s="8" t="s">
         <v>192</v>
       </c>
@@ -7888,8 +8034,8 @@
       <c r="B142" s="7">
         <v>9</v>
       </c>
-      <c r="C142" s="164"/>
-      <c r="D142" s="156"/>
+      <c r="C142" s="145"/>
+      <c r="D142" s="160"/>
       <c r="E142" s="8" t="s">
         <v>193</v>
       </c>
@@ -7910,8 +8056,8 @@
       <c r="B143" s="7">
         <v>10</v>
       </c>
-      <c r="C143" s="164"/>
-      <c r="D143" s="157"/>
+      <c r="C143" s="145"/>
+      <c r="D143" s="161"/>
       <c r="E143" s="8" t="s">
         <v>194</v>
       </c>
@@ -7932,8 +8078,8 @@
       <c r="B144" s="7">
         <v>11</v>
       </c>
-      <c r="C144" s="164"/>
-      <c r="D144" s="135" t="s">
+      <c r="C144" s="145"/>
+      <c r="D144" s="159" t="s">
         <v>195</v>
       </c>
       <c r="E144" s="8" t="s">
@@ -7956,8 +8102,8 @@
       <c r="B145" s="7">
         <v>12</v>
       </c>
-      <c r="C145" s="164"/>
-      <c r="D145" s="156"/>
+      <c r="C145" s="145"/>
+      <c r="D145" s="160"/>
       <c r="E145" s="8" t="s">
         <v>197</v>
       </c>
@@ -7978,8 +8124,8 @@
       <c r="B146" s="7">
         <v>13</v>
       </c>
-      <c r="C146" s="164"/>
-      <c r="D146" s="156"/>
+      <c r="C146" s="145"/>
+      <c r="D146" s="160"/>
       <c r="E146" s="8" t="s">
         <v>198</v>
       </c>
@@ -8000,8 +8146,8 @@
       <c r="B147" s="7">
         <v>14</v>
       </c>
-      <c r="C147" s="164"/>
-      <c r="D147" s="156"/>
+      <c r="C147" s="145"/>
+      <c r="D147" s="160"/>
       <c r="E147" s="8" t="s">
         <v>199</v>
       </c>
@@ -8022,8 +8168,8 @@
       <c r="B148" s="7">
         <v>15</v>
       </c>
-      <c r="C148" s="164"/>
-      <c r="D148" s="156"/>
+      <c r="C148" s="145"/>
+      <c r="D148" s="160"/>
       <c r="E148" s="8" t="s">
         <v>200</v>
       </c>
@@ -8044,8 +8190,8 @@
       <c r="B149" s="7">
         <v>16</v>
       </c>
-      <c r="C149" s="164"/>
-      <c r="D149" s="156"/>
+      <c r="C149" s="145"/>
+      <c r="D149" s="160"/>
       <c r="E149" s="8" t="s">
         <v>201</v>
       </c>
@@ -8066,8 +8212,8 @@
       <c r="B150" s="7">
         <v>17</v>
       </c>
-      <c r="C150" s="164"/>
-      <c r="D150" s="157"/>
+      <c r="C150" s="145"/>
+      <c r="D150" s="161"/>
       <c r="E150" s="8" t="s">
         <v>202</v>
       </c>
@@ -8088,8 +8234,8 @@
       <c r="B151" s="7">
         <v>18</v>
       </c>
-      <c r="C151" s="164"/>
-      <c r="D151" s="135" t="s">
+      <c r="C151" s="145"/>
+      <c r="D151" s="159" t="s">
         <v>203</v>
       </c>
       <c r="E151" s="8" t="s">
@@ -8112,8 +8258,8 @@
       <c r="B152" s="7">
         <v>19</v>
       </c>
-      <c r="C152" s="164"/>
-      <c r="D152" s="156"/>
+      <c r="C152" s="145"/>
+      <c r="D152" s="160"/>
       <c r="E152" s="8" t="s">
         <v>205</v>
       </c>
@@ -8134,8 +8280,8 @@
       <c r="B153" s="7">
         <v>20</v>
       </c>
-      <c r="C153" s="164"/>
-      <c r="D153" s="156"/>
+      <c r="C153" s="145"/>
+      <c r="D153" s="160"/>
       <c r="E153" s="8" t="s">
         <v>206</v>
       </c>
@@ -8156,8 +8302,8 @@
       <c r="B154" s="7">
         <v>21</v>
       </c>
-      <c r="C154" s="164"/>
-      <c r="D154" s="156"/>
+      <c r="C154" s="145"/>
+      <c r="D154" s="160"/>
       <c r="E154" s="8" t="s">
         <v>207</v>
       </c>
@@ -8178,8 +8324,8 @@
       <c r="B155" s="7">
         <v>22</v>
       </c>
-      <c r="C155" s="164"/>
-      <c r="D155" s="156"/>
+      <c r="C155" s="145"/>
+      <c r="D155" s="160"/>
       <c r="E155" s="8" t="s">
         <v>208</v>
       </c>
@@ -8200,8 +8346,8 @@
       <c r="B156" s="7">
         <v>23</v>
       </c>
-      <c r="C156" s="164"/>
-      <c r="D156" s="157"/>
+      <c r="C156" s="145"/>
+      <c r="D156" s="161"/>
       <c r="E156" s="8" t="s">
         <v>209</v>
       </c>
@@ -8222,8 +8368,8 @@
       <c r="B157" s="7">
         <v>24</v>
       </c>
-      <c r="C157" s="164"/>
-      <c r="D157" s="135" t="s">
+      <c r="C157" s="145"/>
+      <c r="D157" s="159" t="s">
         <v>210</v>
       </c>
       <c r="E157" s="8" t="s">
@@ -8246,8 +8392,8 @@
       <c r="B158" s="7">
         <v>25</v>
       </c>
-      <c r="C158" s="164"/>
-      <c r="D158" s="156"/>
+      <c r="C158" s="145"/>
+      <c r="D158" s="160"/>
       <c r="E158" s="8" t="s">
         <v>212</v>
       </c>
@@ -8268,8 +8414,8 @@
       <c r="B159" s="7">
         <v>26</v>
       </c>
-      <c r="C159" s="164"/>
-      <c r="D159" s="157"/>
+      <c r="C159" s="145"/>
+      <c r="D159" s="161"/>
       <c r="E159" s="8" t="s">
         <v>213</v>
       </c>
@@ -8290,8 +8436,8 @@
       <c r="B160" s="7">
         <v>27</v>
       </c>
-      <c r="C160" s="164"/>
-      <c r="D160" s="135" t="s">
+      <c r="C160" s="145"/>
+      <c r="D160" s="159" t="s">
         <v>214</v>
       </c>
       <c r="E160" s="8" t="s">
@@ -8314,8 +8460,8 @@
       <c r="B161" s="7">
         <v>28</v>
       </c>
-      <c r="C161" s="164"/>
-      <c r="D161" s="156"/>
+      <c r="C161" s="145"/>
+      <c r="D161" s="160"/>
       <c r="E161" s="8" t="s">
         <v>216</v>
       </c>
@@ -8336,8 +8482,8 @@
       <c r="B162" s="7">
         <v>29</v>
       </c>
-      <c r="C162" s="164"/>
-      <c r="D162" s="156"/>
+      <c r="C162" s="145"/>
+      <c r="D162" s="160"/>
       <c r="E162" s="8" t="s">
         <v>217</v>
       </c>
@@ -8358,8 +8504,8 @@
       <c r="B163" s="7">
         <v>30</v>
       </c>
-      <c r="C163" s="164"/>
-      <c r="D163" s="156"/>
+      <c r="C163" s="145"/>
+      <c r="D163" s="160"/>
       <c r="E163" s="8" t="s">
         <v>218</v>
       </c>
@@ -8380,8 +8526,8 @@
       <c r="B164" s="7">
         <v>31</v>
       </c>
-      <c r="C164" s="164"/>
-      <c r="D164" s="156"/>
+      <c r="C164" s="145"/>
+      <c r="D164" s="160"/>
       <c r="E164" s="8" t="s">
         <v>219</v>
       </c>
@@ -8402,8 +8548,8 @@
       <c r="B165" s="7">
         <v>32</v>
       </c>
-      <c r="C165" s="164"/>
-      <c r="D165" s="157"/>
+      <c r="C165" s="145"/>
+      <c r="D165" s="161"/>
       <c r="E165" s="8" t="s">
         <v>220</v>
       </c>
@@ -8424,8 +8570,8 @@
       <c r="B166" s="7">
         <v>33</v>
       </c>
-      <c r="C166" s="164"/>
-      <c r="D166" s="135" t="s">
+      <c r="C166" s="145"/>
+      <c r="D166" s="159" t="s">
         <v>221</v>
       </c>
       <c r="E166" s="8" t="s">
@@ -8448,8 +8594,8 @@
       <c r="B167" s="7">
         <v>34</v>
       </c>
-      <c r="C167" s="164"/>
-      <c r="D167" s="156"/>
+      <c r="C167" s="145"/>
+      <c r="D167" s="160"/>
       <c r="E167" s="8" t="s">
         <v>223</v>
       </c>
@@ -8468,8 +8614,8 @@
       <c r="B168" s="7">
         <v>35</v>
       </c>
-      <c r="C168" s="164"/>
-      <c r="D168" s="156"/>
+      <c r="C168" s="145"/>
+      <c r="D168" s="160"/>
       <c r="E168" s="8" t="s">
         <v>224</v>
       </c>
@@ -8490,8 +8636,8 @@
       <c r="B169" s="7">
         <v>36</v>
       </c>
-      <c r="C169" s="164"/>
-      <c r="D169" s="156"/>
+      <c r="C169" s="145"/>
+      <c r="D169" s="160"/>
       <c r="E169" s="8" t="s">
         <v>225</v>
       </c>
@@ -8512,8 +8658,8 @@
       <c r="B170" s="7">
         <v>37</v>
       </c>
-      <c r="C170" s="164"/>
-      <c r="D170" s="156"/>
+      <c r="C170" s="145"/>
+      <c r="D170" s="160"/>
       <c r="E170" s="8" t="s">
         <v>226</v>
       </c>
@@ -8534,8 +8680,8 @@
       <c r="B171" s="7">
         <v>38</v>
       </c>
-      <c r="C171" s="164"/>
-      <c r="D171" s="156"/>
+      <c r="C171" s="145"/>
+      <c r="D171" s="160"/>
       <c r="E171" s="8" t="s">
         <v>227</v>
       </c>
@@ -8556,8 +8702,8 @@
       <c r="B172" s="7">
         <v>39</v>
       </c>
-      <c r="C172" s="164"/>
-      <c r="D172" s="157"/>
+      <c r="C172" s="145"/>
+      <c r="D172" s="161"/>
       <c r="E172" s="8" t="s">
         <v>228</v>
       </c>
@@ -8578,8 +8724,8 @@
       <c r="B173" s="7">
         <v>40</v>
       </c>
-      <c r="C173" s="164"/>
-      <c r="D173" s="135" t="s">
+      <c r="C173" s="145"/>
+      <c r="D173" s="159" t="s">
         <v>48</v>
       </c>
       <c r="E173" s="11" t="s">
@@ -8602,8 +8748,8 @@
       <c r="B174" s="7">
         <v>41</v>
       </c>
-      <c r="C174" s="164"/>
-      <c r="D174" s="156"/>
+      <c r="C174" s="145"/>
+      <c r="D174" s="160"/>
       <c r="E174" s="8" t="s">
         <v>230</v>
       </c>
@@ -8624,8 +8770,8 @@
       <c r="B175" s="7">
         <v>42</v>
       </c>
-      <c r="C175" s="164"/>
-      <c r="D175" s="156"/>
+      <c r="C175" s="145"/>
+      <c r="D175" s="160"/>
       <c r="E175" s="8" t="s">
         <v>231</v>
       </c>
@@ -8646,8 +8792,8 @@
       <c r="B176" s="24">
         <v>43</v>
       </c>
-      <c r="C176" s="165"/>
-      <c r="D176" s="157"/>
+      <c r="C176" s="146"/>
+      <c r="D176" s="161"/>
       <c r="E176" s="17" t="s">
         <v>232</v>
       </c>
@@ -8668,10 +8814,10 @@
       <c r="B177" s="7">
         <v>1</v>
       </c>
-      <c r="C177" s="138" t="s">
+      <c r="C177" s="147" t="s">
         <v>233</v>
       </c>
-      <c r="D177" s="135" t="s">
+      <c r="D177" s="159" t="s">
         <v>234</v>
       </c>
       <c r="E177" s="8" t="s">
@@ -8694,8 +8840,8 @@
       <c r="B178" s="7">
         <v>2</v>
       </c>
-      <c r="C178" s="158"/>
-      <c r="D178" s="157"/>
+      <c r="C178" s="148"/>
+      <c r="D178" s="161"/>
       <c r="E178" s="8" t="s">
         <v>236</v>
       </c>
@@ -8716,8 +8862,8 @@
       <c r="B179" s="7">
         <v>3</v>
       </c>
-      <c r="C179" s="158"/>
-      <c r="D179" s="135" t="s">
+      <c r="C179" s="148"/>
+      <c r="D179" s="159" t="s">
         <v>237</v>
       </c>
       <c r="E179" s="8" t="s">
@@ -8740,8 +8886,8 @@
       <c r="B180" s="7">
         <v>4</v>
       </c>
-      <c r="C180" s="158"/>
-      <c r="D180" s="156"/>
+      <c r="C180" s="148"/>
+      <c r="D180" s="160"/>
       <c r="E180" s="8" t="s">
         <v>239</v>
       </c>
@@ -8762,8 +8908,8 @@
       <c r="B181" s="7">
         <v>5</v>
       </c>
-      <c r="C181" s="158"/>
-      <c r="D181" s="156"/>
+      <c r="C181" s="148"/>
+      <c r="D181" s="160"/>
       <c r="E181" s="8" t="s">
         <v>240</v>
       </c>
@@ -8784,8 +8930,8 @@
       <c r="B182" s="7">
         <v>6</v>
       </c>
-      <c r="C182" s="158"/>
-      <c r="D182" s="156"/>
+      <c r="C182" s="148"/>
+      <c r="D182" s="160"/>
       <c r="E182" s="8" t="s">
         <v>241</v>
       </c>
@@ -8806,8 +8952,8 @@
       <c r="B183" s="7">
         <v>7</v>
       </c>
-      <c r="C183" s="158"/>
-      <c r="D183" s="156"/>
+      <c r="C183" s="148"/>
+      <c r="D183" s="160"/>
       <c r="E183" s="8" t="s">
         <v>242</v>
       </c>
@@ -8828,8 +8974,8 @@
       <c r="B184" s="7">
         <v>8</v>
       </c>
-      <c r="C184" s="158"/>
-      <c r="D184" s="157"/>
+      <c r="C184" s="148"/>
+      <c r="D184" s="161"/>
       <c r="E184" s="8" t="s">
         <v>243</v>
       </c>
@@ -8850,8 +8996,8 @@
       <c r="B185" s="7">
         <v>9</v>
       </c>
-      <c r="C185" s="158"/>
-      <c r="D185" s="135" t="s">
+      <c r="C185" s="148"/>
+      <c r="D185" s="159" t="s">
         <v>244</v>
       </c>
       <c r="E185" s="8" t="s">
@@ -8874,8 +9020,8 @@
       <c r="B186" s="7">
         <v>10</v>
       </c>
-      <c r="C186" s="158"/>
-      <c r="D186" s="157"/>
+      <c r="C186" s="148"/>
+      <c r="D186" s="161"/>
       <c r="E186" s="8" t="s">
         <v>246</v>
       </c>
@@ -8896,8 +9042,8 @@
       <c r="B187" s="7">
         <v>11</v>
       </c>
-      <c r="C187" s="158"/>
-      <c r="D187" s="135" t="s">
+      <c r="C187" s="148"/>
+      <c r="D187" s="159" t="s">
         <v>247</v>
       </c>
       <c r="E187" s="8" t="s">
@@ -8920,8 +9066,8 @@
       <c r="B188" s="7">
         <v>12</v>
       </c>
-      <c r="C188" s="158"/>
-      <c r="D188" s="156"/>
+      <c r="C188" s="148"/>
+      <c r="D188" s="160"/>
       <c r="E188" s="8" t="s">
         <v>249</v>
       </c>
@@ -8942,8 +9088,8 @@
       <c r="B189" s="7">
         <v>13</v>
       </c>
-      <c r="C189" s="158"/>
-      <c r="D189" s="156"/>
+      <c r="C189" s="148"/>
+      <c r="D189" s="160"/>
       <c r="E189" s="11" t="s">
         <v>250</v>
       </c>
@@ -8964,8 +9110,8 @@
       <c r="B190" s="7">
         <v>14</v>
       </c>
-      <c r="C190" s="158"/>
-      <c r="D190" s="157"/>
+      <c r="C190" s="148"/>
+      <c r="D190" s="161"/>
       <c r="E190" s="8" t="s">
         <v>251</v>
       </c>
@@ -8986,8 +9132,8 @@
       <c r="B191" s="7">
         <v>15</v>
       </c>
-      <c r="C191" s="158"/>
-      <c r="D191" s="135" t="s">
+      <c r="C191" s="148"/>
+      <c r="D191" s="159" t="s">
         <v>252</v>
       </c>
       <c r="E191" s="8" t="s">
@@ -9010,8 +9156,8 @@
       <c r="B192" s="7">
         <v>16</v>
       </c>
-      <c r="C192" s="158"/>
-      <c r="D192" s="156"/>
+      <c r="C192" s="148"/>
+      <c r="D192" s="160"/>
       <c r="E192" s="8" t="s">
         <v>254</v>
       </c>
@@ -9032,8 +9178,8 @@
       <c r="B193" s="7">
         <v>17</v>
       </c>
-      <c r="C193" s="158"/>
-      <c r="D193" s="156"/>
+      <c r="C193" s="148"/>
+      <c r="D193" s="160"/>
       <c r="E193" s="8" t="s">
         <v>255</v>
       </c>
@@ -9054,8 +9200,8 @@
       <c r="B194" s="7">
         <v>18</v>
       </c>
-      <c r="C194" s="158"/>
-      <c r="D194" s="156"/>
+      <c r="C194" s="148"/>
+      <c r="D194" s="160"/>
       <c r="E194" s="8" t="s">
         <v>256</v>
       </c>
@@ -9076,8 +9222,8 @@
       <c r="B195" s="7">
         <v>19</v>
       </c>
-      <c r="C195" s="158"/>
-      <c r="D195" s="156"/>
+      <c r="C195" s="148"/>
+      <c r="D195" s="160"/>
       <c r="E195" s="8" t="s">
         <v>257</v>
       </c>
@@ -9098,8 +9244,8 @@
       <c r="B196" s="7">
         <v>20</v>
       </c>
-      <c r="C196" s="158"/>
-      <c r="D196" s="156"/>
+      <c r="C196" s="148"/>
+      <c r="D196" s="160"/>
       <c r="E196" s="8" t="s">
         <v>258</v>
       </c>
@@ -9120,8 +9266,8 @@
       <c r="B197" s="7">
         <v>21</v>
       </c>
-      <c r="C197" s="158"/>
-      <c r="D197" s="156"/>
+      <c r="C197" s="148"/>
+      <c r="D197" s="160"/>
       <c r="E197" s="8" t="s">
         <v>259</v>
       </c>
@@ -9142,8 +9288,8 @@
       <c r="B198" s="7">
         <v>22</v>
       </c>
-      <c r="C198" s="158"/>
-      <c r="D198" s="157"/>
+      <c r="C198" s="148"/>
+      <c r="D198" s="161"/>
       <c r="E198" s="8" t="s">
         <v>260</v>
       </c>
@@ -9164,8 +9310,8 @@
       <c r="B199" s="7">
         <v>23</v>
       </c>
-      <c r="C199" s="158"/>
-      <c r="D199" s="135" t="s">
+      <c r="C199" s="148"/>
+      <c r="D199" s="159" t="s">
         <v>261</v>
       </c>
       <c r="E199" s="8" t="s">
@@ -9188,8 +9334,8 @@
       <c r="B200" s="7">
         <v>24</v>
       </c>
-      <c r="C200" s="158"/>
-      <c r="D200" s="156"/>
+      <c r="C200" s="148"/>
+      <c r="D200" s="160"/>
       <c r="E200" s="8" t="s">
         <v>263</v>
       </c>
@@ -9210,8 +9356,8 @@
       <c r="B201" s="7">
         <v>25</v>
       </c>
-      <c r="C201" s="158"/>
-      <c r="D201" s="156"/>
+      <c r="C201" s="148"/>
+      <c r="D201" s="160"/>
       <c r="E201" s="8" t="s">
         <v>264</v>
       </c>
@@ -9232,8 +9378,8 @@
       <c r="B202" s="7">
         <v>26</v>
       </c>
-      <c r="C202" s="158"/>
-      <c r="D202" s="157"/>
+      <c r="C202" s="148"/>
+      <c r="D202" s="161"/>
       <c r="E202" s="8" t="s">
         <v>265</v>
       </c>
@@ -9254,8 +9400,8 @@
       <c r="B203" s="7">
         <v>27</v>
       </c>
-      <c r="C203" s="158"/>
-      <c r="D203" s="135" t="s">
+      <c r="C203" s="148"/>
+      <c r="D203" s="159" t="s">
         <v>266</v>
       </c>
       <c r="E203" s="8" t="s">
@@ -9278,8 +9424,8 @@
       <c r="B204" s="24">
         <v>28</v>
       </c>
-      <c r="C204" s="159"/>
-      <c r="D204" s="157"/>
+      <c r="C204" s="149"/>
+      <c r="D204" s="161"/>
       <c r="E204" s="17" t="s">
         <v>268</v>
       </c>
@@ -9300,10 +9446,10 @@
       <c r="B205" s="7">
         <v>1</v>
       </c>
-      <c r="C205" s="139" t="s">
+      <c r="C205" s="138" t="s">
         <v>269</v>
       </c>
-      <c r="D205" s="135" t="s">
+      <c r="D205" s="159" t="s">
         <v>270</v>
       </c>
       <c r="E205" s="8" t="s">
@@ -9326,8 +9472,8 @@
       <c r="B206" s="7">
         <v>2</v>
       </c>
-      <c r="C206" s="160"/>
-      <c r="D206" s="156"/>
+      <c r="C206" s="139"/>
+      <c r="D206" s="160"/>
       <c r="E206" s="8" t="s">
         <v>272</v>
       </c>
@@ -9348,8 +9494,8 @@
       <c r="B207" s="7">
         <v>3</v>
       </c>
-      <c r="C207" s="160"/>
-      <c r="D207" s="156"/>
+      <c r="C207" s="139"/>
+      <c r="D207" s="160"/>
       <c r="E207" s="8" t="s">
         <v>273</v>
       </c>
@@ -9370,8 +9516,8 @@
       <c r="B208" s="7">
         <v>4</v>
       </c>
-      <c r="C208" s="160"/>
-      <c r="D208" s="156"/>
+      <c r="C208" s="139"/>
+      <c r="D208" s="160"/>
       <c r="E208" s="8" t="s">
         <v>274</v>
       </c>
@@ -9392,8 +9538,8 @@
       <c r="B209" s="7">
         <v>5</v>
       </c>
-      <c r="C209" s="160"/>
-      <c r="D209" s="157"/>
+      <c r="C209" s="139"/>
+      <c r="D209" s="161"/>
       <c r="E209" s="8" t="s">
         <v>275</v>
       </c>
@@ -9414,8 +9560,8 @@
       <c r="B210" s="7">
         <v>6</v>
       </c>
-      <c r="C210" s="160"/>
-      <c r="D210" s="135" t="s">
+      <c r="C210" s="139"/>
+      <c r="D210" s="159" t="s">
         <v>276</v>
       </c>
       <c r="E210" s="8" t="s">
@@ -9438,8 +9584,8 @@
       <c r="B211" s="7">
         <v>7</v>
       </c>
-      <c r="C211" s="160"/>
-      <c r="D211" s="157"/>
+      <c r="C211" s="139"/>
+      <c r="D211" s="161"/>
       <c r="E211" s="8" t="s">
         <v>278</v>
       </c>
@@ -9460,8 +9606,8 @@
       <c r="B212" s="7">
         <v>8</v>
       </c>
-      <c r="C212" s="160"/>
-      <c r="D212" s="135" t="s">
+      <c r="C212" s="139"/>
+      <c r="D212" s="159" t="s">
         <v>279</v>
       </c>
       <c r="E212" s="8" t="s">
@@ -9484,8 +9630,8 @@
       <c r="B213" s="7">
         <v>9</v>
       </c>
-      <c r="C213" s="160"/>
-      <c r="D213" s="156"/>
+      <c r="C213" s="139"/>
+      <c r="D213" s="160"/>
       <c r="E213" s="8" t="s">
         <v>281</v>
       </c>
@@ -9506,8 +9652,8 @@
       <c r="B214" s="7">
         <v>10</v>
       </c>
-      <c r="C214" s="161"/>
-      <c r="D214" s="157"/>
+      <c r="C214" s="140"/>
+      <c r="D214" s="161"/>
       <c r="E214" s="8" t="s">
         <v>282</v>
       </c>
@@ -9522,18 +9668,18 @@
       <c r="J214" s="11"/>
     </row>
     <row r="215" spans="1:10" ht="13.8">
-      <c r="A215" s="146" t="s">
+      <c r="A215" s="168" t="s">
         <v>283</v>
       </c>
-      <c r="B215" s="180"/>
-      <c r="C215" s="180"/>
-      <c r="D215" s="180"/>
-      <c r="E215" s="180"/>
-      <c r="F215" s="180"/>
-      <c r="G215" s="180"/>
-      <c r="H215" s="180"/>
-      <c r="I215" s="180"/>
-      <c r="J215" s="181"/>
+      <c r="B215" s="169"/>
+      <c r="C215" s="169"/>
+      <c r="D215" s="169"/>
+      <c r="E215" s="169"/>
+      <c r="F215" s="169"/>
+      <c r="G215" s="169"/>
+      <c r="H215" s="169"/>
+      <c r="I215" s="169"/>
+      <c r="J215" s="170"/>
     </row>
     <row r="216" spans="1:10" ht="13.8">
       <c r="A216" s="6">
@@ -9542,10 +9688,10 @@
       <c r="B216" s="7">
         <v>1</v>
       </c>
-      <c r="C216" s="140" t="s">
+      <c r="C216" s="141" t="s">
         <v>284</v>
       </c>
-      <c r="D216" s="135" t="s">
+      <c r="D216" s="159" t="s">
         <v>285</v>
       </c>
       <c r="E216" s="8" t="s">
@@ -9568,8 +9714,8 @@
       <c r="B217" s="7">
         <v>2</v>
       </c>
-      <c r="C217" s="166"/>
-      <c r="D217" s="156"/>
+      <c r="C217" s="142"/>
+      <c r="D217" s="160"/>
       <c r="E217" s="8" t="s">
         <v>287</v>
       </c>
@@ -9590,8 +9736,8 @@
       <c r="B218" s="7">
         <v>3</v>
       </c>
-      <c r="C218" s="166"/>
-      <c r="D218" s="156"/>
+      <c r="C218" s="142"/>
+      <c r="D218" s="160"/>
       <c r="E218" s="8" t="s">
         <v>288</v>
       </c>
@@ -9612,8 +9758,8 @@
       <c r="B219" s="7">
         <v>4</v>
       </c>
-      <c r="C219" s="166"/>
-      <c r="D219" s="156"/>
+      <c r="C219" s="142"/>
+      <c r="D219" s="160"/>
       <c r="E219" s="8" t="s">
         <v>289</v>
       </c>
@@ -9634,8 +9780,8 @@
       <c r="B220" s="7">
         <v>5</v>
       </c>
-      <c r="C220" s="166"/>
-      <c r="D220" s="156"/>
+      <c r="C220" s="142"/>
+      <c r="D220" s="160"/>
       <c r="E220" s="8" t="s">
         <v>290</v>
       </c>
@@ -9656,8 +9802,8 @@
       <c r="B221" s="7">
         <v>6</v>
       </c>
-      <c r="C221" s="166"/>
-      <c r="D221" s="156"/>
+      <c r="C221" s="142"/>
+      <c r="D221" s="160"/>
       <c r="E221" s="8" t="s">
         <v>291</v>
       </c>
@@ -9678,8 +9824,8 @@
       <c r="B222" s="7">
         <v>7</v>
       </c>
-      <c r="C222" s="166"/>
-      <c r="D222" s="156"/>
+      <c r="C222" s="142"/>
+      <c r="D222" s="160"/>
       <c r="E222" s="8" t="s">
         <v>292</v>
       </c>
@@ -9700,8 +9846,8 @@
       <c r="B223" s="7">
         <v>8</v>
       </c>
-      <c r="C223" s="166"/>
-      <c r="D223" s="156"/>
+      <c r="C223" s="142"/>
+      <c r="D223" s="160"/>
       <c r="E223" s="8" t="s">
         <v>293</v>
       </c>
@@ -9722,8 +9868,8 @@
       <c r="B224" s="7">
         <v>9</v>
       </c>
-      <c r="C224" s="166"/>
-      <c r="D224" s="156"/>
+      <c r="C224" s="142"/>
+      <c r="D224" s="160"/>
       <c r="E224" s="8" t="s">
         <v>294</v>
       </c>
@@ -9744,8 +9890,8 @@
       <c r="B225" s="7">
         <v>10</v>
       </c>
-      <c r="C225" s="166"/>
-      <c r="D225" s="157"/>
+      <c r="C225" s="142"/>
+      <c r="D225" s="161"/>
       <c r="E225" s="8" t="s">
         <v>295</v>
       </c>
@@ -9766,8 +9912,8 @@
       <c r="B226" s="7">
         <v>11</v>
       </c>
-      <c r="C226" s="166"/>
-      <c r="D226" s="135" t="s">
+      <c r="C226" s="142"/>
+      <c r="D226" s="159" t="s">
         <v>296</v>
       </c>
       <c r="E226" s="8" t="s">
@@ -9790,8 +9936,8 @@
       <c r="B227" s="7">
         <v>12</v>
       </c>
-      <c r="C227" s="166"/>
-      <c r="D227" s="156"/>
+      <c r="C227" s="142"/>
+      <c r="D227" s="160"/>
       <c r="E227" s="8" t="s">
         <v>298</v>
       </c>
@@ -9812,8 +9958,8 @@
       <c r="B228" s="7">
         <v>13</v>
       </c>
-      <c r="C228" s="166"/>
-      <c r="D228" s="156"/>
+      <c r="C228" s="142"/>
+      <c r="D228" s="160"/>
       <c r="E228" s="8" t="s">
         <v>299</v>
       </c>
@@ -9834,8 +9980,8 @@
       <c r="B229" s="7">
         <v>14</v>
       </c>
-      <c r="C229" s="166"/>
-      <c r="D229" s="156"/>
+      <c r="C229" s="142"/>
+      <c r="D229" s="160"/>
       <c r="E229" s="8" t="s">
         <v>300</v>
       </c>
@@ -9856,8 +10002,8 @@
       <c r="B230" s="7">
         <v>15</v>
       </c>
-      <c r="C230" s="166"/>
-      <c r="D230" s="156"/>
+      <c r="C230" s="142"/>
+      <c r="D230" s="160"/>
       <c r="E230" s="8" t="s">
         <v>301</v>
       </c>
@@ -9878,8 +10024,8 @@
       <c r="B231" s="7">
         <v>16</v>
       </c>
-      <c r="C231" s="166"/>
-      <c r="D231" s="156"/>
+      <c r="C231" s="142"/>
+      <c r="D231" s="160"/>
       <c r="E231" s="8" t="s">
         <v>302</v>
       </c>
@@ -9900,8 +10046,8 @@
       <c r="B232" s="7">
         <v>17</v>
       </c>
-      <c r="C232" s="166"/>
-      <c r="D232" s="156"/>
+      <c r="C232" s="142"/>
+      <c r="D232" s="160"/>
       <c r="E232" s="8" t="s">
         <v>303</v>
       </c>
@@ -9922,8 +10068,8 @@
       <c r="B233" s="7">
         <v>18</v>
       </c>
-      <c r="C233" s="166"/>
-      <c r="D233" s="157"/>
+      <c r="C233" s="142"/>
+      <c r="D233" s="161"/>
       <c r="E233" s="8" t="s">
         <v>304</v>
       </c>
@@ -9944,8 +10090,8 @@
       <c r="B234" s="7">
         <v>19</v>
       </c>
-      <c r="C234" s="166"/>
-      <c r="D234" s="135" t="s">
+      <c r="C234" s="142"/>
+      <c r="D234" s="159" t="s">
         <v>305</v>
       </c>
       <c r="E234" s="8" t="s">
@@ -9968,8 +10114,8 @@
       <c r="B235" s="7">
         <v>20</v>
       </c>
-      <c r="C235" s="166"/>
-      <c r="D235" s="156"/>
+      <c r="C235" s="142"/>
+      <c r="D235" s="160"/>
       <c r="E235" s="8" t="s">
         <v>307</v>
       </c>
@@ -9990,8 +10136,8 @@
       <c r="B236" s="7">
         <v>21</v>
       </c>
-      <c r="C236" s="166"/>
-      <c r="D236" s="156"/>
+      <c r="C236" s="142"/>
+      <c r="D236" s="160"/>
       <c r="E236" s="8" t="s">
         <v>308</v>
       </c>
@@ -10012,8 +10158,8 @@
       <c r="B237" s="7">
         <v>22</v>
       </c>
-      <c r="C237" s="166"/>
-      <c r="D237" s="156"/>
+      <c r="C237" s="142"/>
+      <c r="D237" s="160"/>
       <c r="E237" s="8" t="s">
         <v>309</v>
       </c>
@@ -10034,8 +10180,8 @@
       <c r="B238" s="7">
         <v>23</v>
       </c>
-      <c r="C238" s="166"/>
-      <c r="D238" s="156"/>
+      <c r="C238" s="142"/>
+      <c r="D238" s="160"/>
       <c r="E238" s="8" t="s">
         <v>310</v>
       </c>
@@ -10056,8 +10202,8 @@
       <c r="B239" s="7">
         <v>24</v>
       </c>
-      <c r="C239" s="166"/>
-      <c r="D239" s="156"/>
+      <c r="C239" s="142"/>
+      <c r="D239" s="160"/>
       <c r="E239" s="8" t="s">
         <v>311</v>
       </c>
@@ -10078,8 +10224,8 @@
       <c r="B240" s="7">
         <v>25</v>
       </c>
-      <c r="C240" s="166"/>
-      <c r="D240" s="157"/>
+      <c r="C240" s="142"/>
+      <c r="D240" s="161"/>
       <c r="E240" s="8" t="s">
         <v>312</v>
       </c>
@@ -10100,8 +10246,8 @@
       <c r="B241" s="7">
         <v>26</v>
       </c>
-      <c r="C241" s="166"/>
-      <c r="D241" s="135" t="s">
+      <c r="C241" s="142"/>
+      <c r="D241" s="159" t="s">
         <v>313</v>
       </c>
       <c r="E241" s="8" t="s">
@@ -10124,8 +10270,8 @@
       <c r="B242" s="7">
         <v>27</v>
       </c>
-      <c r="C242" s="166"/>
-      <c r="D242" s="156"/>
+      <c r="C242" s="142"/>
+      <c r="D242" s="160"/>
       <c r="E242" s="8" t="s">
         <v>315</v>
       </c>
@@ -10146,8 +10292,8 @@
       <c r="B243" s="7">
         <v>28</v>
       </c>
-      <c r="C243" s="166"/>
-      <c r="D243" s="157"/>
+      <c r="C243" s="142"/>
+      <c r="D243" s="161"/>
       <c r="E243" s="8" t="s">
         <v>316</v>
       </c>
@@ -10168,8 +10314,8 @@
       <c r="B244" s="7">
         <v>29</v>
       </c>
-      <c r="C244" s="166"/>
-      <c r="D244" s="135" t="s">
+      <c r="C244" s="142"/>
+      <c r="D244" s="159" t="s">
         <v>317</v>
       </c>
       <c r="E244" s="8" t="s">
@@ -10192,8 +10338,8 @@
       <c r="B245" s="7">
         <v>30</v>
       </c>
-      <c r="C245" s="166"/>
-      <c r="D245" s="156"/>
+      <c r="C245" s="142"/>
+      <c r="D245" s="160"/>
       <c r="E245" s="8" t="s">
         <v>319</v>
       </c>
@@ -10214,8 +10360,8 @@
       <c r="B246" s="7">
         <v>31</v>
       </c>
-      <c r="C246" s="166"/>
-      <c r="D246" s="156"/>
+      <c r="C246" s="142"/>
+      <c r="D246" s="160"/>
       <c r="E246" s="8" t="s">
         <v>320</v>
       </c>
@@ -10236,8 +10382,8 @@
       <c r="B247" s="7">
         <v>32</v>
       </c>
-      <c r="C247" s="166"/>
-      <c r="D247" s="156"/>
+      <c r="C247" s="142"/>
+      <c r="D247" s="160"/>
       <c r="E247" s="8" t="s">
         <v>321</v>
       </c>
@@ -10258,8 +10404,8 @@
       <c r="B248" s="7">
         <v>33</v>
       </c>
-      <c r="C248" s="166"/>
-      <c r="D248" s="156"/>
+      <c r="C248" s="142"/>
+      <c r="D248" s="160"/>
       <c r="E248" s="8" t="s">
         <v>322</v>
       </c>
@@ -10280,8 +10426,8 @@
       <c r="B249" s="24">
         <v>34</v>
       </c>
-      <c r="C249" s="167"/>
-      <c r="D249" s="157"/>
+      <c r="C249" s="143"/>
+      <c r="D249" s="161"/>
       <c r="E249" s="17" t="s">
         <v>323</v>
       </c>
@@ -10302,10 +10448,10 @@
       <c r="B250" s="7">
         <v>1</v>
       </c>
-      <c r="C250" s="137" t="s">
+      <c r="C250" s="144" t="s">
         <v>324</v>
       </c>
-      <c r="D250" s="135" t="s">
+      <c r="D250" s="159" t="s">
         <v>325</v>
       </c>
       <c r="E250" s="8" t="s">
@@ -10328,8 +10474,8 @@
       <c r="B251" s="7">
         <v>2</v>
       </c>
-      <c r="C251" s="164"/>
-      <c r="D251" s="156"/>
+      <c r="C251" s="145"/>
+      <c r="D251" s="160"/>
       <c r="E251" s="8" t="s">
         <v>327</v>
       </c>
@@ -10350,8 +10496,8 @@
       <c r="B252" s="7">
         <v>3</v>
       </c>
-      <c r="C252" s="164"/>
-      <c r="D252" s="156"/>
+      <c r="C252" s="145"/>
+      <c r="D252" s="160"/>
       <c r="E252" s="8" t="s">
         <v>328</v>
       </c>
@@ -10372,8 +10518,8 @@
       <c r="B253" s="7">
         <v>4</v>
       </c>
-      <c r="C253" s="164"/>
-      <c r="D253" s="156"/>
+      <c r="C253" s="145"/>
+      <c r="D253" s="160"/>
       <c r="E253" s="8" t="s">
         <v>329</v>
       </c>
@@ -10394,8 +10540,8 @@
       <c r="B254" s="7">
         <v>5</v>
       </c>
-      <c r="C254" s="164"/>
-      <c r="D254" s="156"/>
+      <c r="C254" s="145"/>
+      <c r="D254" s="160"/>
       <c r="E254" s="8" t="s">
         <v>330</v>
       </c>
@@ -10416,8 +10562,8 @@
       <c r="B255" s="7">
         <v>6</v>
       </c>
-      <c r="C255" s="164"/>
-      <c r="D255" s="156"/>
+      <c r="C255" s="145"/>
+      <c r="D255" s="160"/>
       <c r="E255" s="8" t="s">
         <v>331</v>
       </c>
@@ -10438,8 +10584,8 @@
       <c r="B256" s="7">
         <v>7</v>
       </c>
-      <c r="C256" s="164"/>
-      <c r="D256" s="156"/>
+      <c r="C256" s="145"/>
+      <c r="D256" s="160"/>
       <c r="E256" s="8" t="s">
         <v>332</v>
       </c>
@@ -10460,8 +10606,8 @@
       <c r="B257" s="7">
         <v>8</v>
       </c>
-      <c r="C257" s="164"/>
-      <c r="D257" s="157"/>
+      <c r="C257" s="145"/>
+      <c r="D257" s="161"/>
       <c r="E257" s="8" t="s">
         <v>333</v>
       </c>
@@ -10482,8 +10628,8 @@
       <c r="B258" s="7">
         <v>9</v>
       </c>
-      <c r="C258" s="164"/>
-      <c r="D258" s="135" t="s">
+      <c r="C258" s="145"/>
+      <c r="D258" s="159" t="s">
         <v>334</v>
       </c>
       <c r="E258" s="8" t="s">
@@ -10506,8 +10652,8 @@
       <c r="B259" s="7">
         <v>10</v>
       </c>
-      <c r="C259" s="164"/>
-      <c r="D259" s="157"/>
+      <c r="C259" s="145"/>
+      <c r="D259" s="161"/>
       <c r="E259" s="8" t="s">
         <v>336</v>
       </c>
@@ -10528,8 +10674,8 @@
       <c r="B260" s="7">
         <v>11</v>
       </c>
-      <c r="C260" s="164"/>
-      <c r="D260" s="135" t="s">
+      <c r="C260" s="145"/>
+      <c r="D260" s="159" t="s">
         <v>337</v>
       </c>
       <c r="E260" s="8" t="s">
@@ -10552,8 +10698,8 @@
       <c r="B261" s="7">
         <v>12</v>
       </c>
-      <c r="C261" s="164"/>
-      <c r="D261" s="156"/>
+      <c r="C261" s="145"/>
+      <c r="D261" s="160"/>
       <c r="E261" s="8" t="s">
         <v>339</v>
       </c>
@@ -10574,8 +10720,8 @@
       <c r="B262" s="7">
         <v>13</v>
       </c>
-      <c r="C262" s="164"/>
-      <c r="D262" s="156"/>
+      <c r="C262" s="145"/>
+      <c r="D262" s="160"/>
       <c r="E262" s="8" t="s">
         <v>340</v>
       </c>
@@ -10596,8 +10742,8 @@
       <c r="B263" s="7">
         <v>14</v>
       </c>
-      <c r="C263" s="164"/>
-      <c r="D263" s="156"/>
+      <c r="C263" s="145"/>
+      <c r="D263" s="160"/>
       <c r="E263" s="8" t="s">
         <v>341</v>
       </c>
@@ -10618,8 +10764,8 @@
       <c r="B264" s="7">
         <v>15</v>
       </c>
-      <c r="C264" s="164"/>
-      <c r="D264" s="156"/>
+      <c r="C264" s="145"/>
+      <c r="D264" s="160"/>
       <c r="E264" s="8" t="s">
         <v>342</v>
       </c>
@@ -10640,8 +10786,8 @@
       <c r="B265" s="24">
         <v>16</v>
       </c>
-      <c r="C265" s="165"/>
-      <c r="D265" s="157"/>
+      <c r="C265" s="146"/>
+      <c r="D265" s="161"/>
       <c r="E265" s="17" t="s">
         <v>343</v>
       </c>
@@ -10662,10 +10808,10 @@
       <c r="B266" s="7">
         <v>1</v>
       </c>
-      <c r="C266" s="138" t="s">
+      <c r="C266" s="147" t="s">
         <v>344</v>
       </c>
-      <c r="D266" s="135" t="s">
+      <c r="D266" s="159" t="s">
         <v>345</v>
       </c>
       <c r="E266" s="8" t="s">
@@ -10688,8 +10834,8 @@
       <c r="B267" s="7">
         <v>2</v>
       </c>
-      <c r="C267" s="158"/>
-      <c r="D267" s="156"/>
+      <c r="C267" s="148"/>
+      <c r="D267" s="160"/>
       <c r="E267" s="8" t="s">
         <v>347</v>
       </c>
@@ -10710,8 +10856,8 @@
       <c r="B268" s="7">
         <v>3</v>
       </c>
-      <c r="C268" s="158"/>
-      <c r="D268" s="156"/>
+      <c r="C268" s="148"/>
+      <c r="D268" s="160"/>
       <c r="E268" s="8" t="s">
         <v>348</v>
       </c>
@@ -10732,8 +10878,8 @@
       <c r="B269" s="7">
         <v>4</v>
       </c>
-      <c r="C269" s="158"/>
-      <c r="D269" s="156"/>
+      <c r="C269" s="148"/>
+      <c r="D269" s="160"/>
       <c r="E269" s="8" t="s">
         <v>349</v>
       </c>
@@ -10754,8 +10900,8 @@
       <c r="B270" s="7">
         <v>5</v>
       </c>
-      <c r="C270" s="158"/>
-      <c r="D270" s="157"/>
+      <c r="C270" s="148"/>
+      <c r="D270" s="161"/>
       <c r="E270" s="8" t="s">
         <v>350</v>
       </c>
@@ -10776,8 +10922,8 @@
       <c r="B271" s="7">
         <v>6</v>
       </c>
-      <c r="C271" s="158"/>
-      <c r="D271" s="135" t="s">
+      <c r="C271" s="148"/>
+      <c r="D271" s="159" t="s">
         <v>351</v>
       </c>
       <c r="E271" s="8" t="s">
@@ -10800,8 +10946,8 @@
       <c r="B272" s="7">
         <v>7</v>
       </c>
-      <c r="C272" s="159"/>
-      <c r="D272" s="157"/>
+      <c r="C272" s="149"/>
+      <c r="D272" s="161"/>
       <c r="E272" s="8" t="s">
         <v>353</v>
       </c>
@@ -10816,18 +10962,18 @@
       <c r="J272" s="11"/>
     </row>
     <row r="273" spans="1:10" ht="13.8">
-      <c r="A273" s="145" t="s">
+      <c r="A273" s="171" t="s">
         <v>354</v>
       </c>
-      <c r="B273" s="178"/>
-      <c r="C273" s="178"/>
-      <c r="D273" s="178"/>
-      <c r="E273" s="178"/>
-      <c r="F273" s="178"/>
-      <c r="G273" s="178"/>
-      <c r="H273" s="178"/>
-      <c r="I273" s="178"/>
-      <c r="J273" s="179"/>
+      <c r="B273" s="172"/>
+      <c r="C273" s="172"/>
+      <c r="D273" s="172"/>
+      <c r="E273" s="172"/>
+      <c r="F273" s="172"/>
+      <c r="G273" s="172"/>
+      <c r="H273" s="172"/>
+      <c r="I273" s="172"/>
+      <c r="J273" s="173"/>
     </row>
     <row r="274" spans="1:10" ht="13.8">
       <c r="A274" s="33">
@@ -10836,10 +10982,10 @@
       <c r="B274" s="7">
         <v>1</v>
       </c>
-      <c r="C274" s="143" t="s">
+      <c r="C274" s="150" t="s">
         <v>355</v>
       </c>
-      <c r="D274" s="144" t="s">
+      <c r="D274" s="162" t="s">
         <v>356</v>
       </c>
       <c r="E274" s="13" t="s">
@@ -10862,8 +11008,8 @@
       <c r="B275" s="7">
         <v>2</v>
       </c>
-      <c r="C275" s="176"/>
-      <c r="D275" s="170"/>
+      <c r="C275" s="151"/>
+      <c r="D275" s="163"/>
       <c r="E275" s="13" t="s">
         <v>358</v>
       </c>
@@ -10884,8 +11030,8 @@
       <c r="B276" s="7">
         <v>3</v>
       </c>
-      <c r="C276" s="176"/>
-      <c r="D276" s="170"/>
+      <c r="C276" s="151"/>
+      <c r="D276" s="163"/>
       <c r="E276" s="8" t="s">
         <v>359</v>
       </c>
@@ -10906,8 +11052,8 @@
       <c r="B277" s="7">
         <v>4</v>
       </c>
-      <c r="C277" s="176"/>
-      <c r="D277" s="170"/>
+      <c r="C277" s="151"/>
+      <c r="D277" s="163"/>
       <c r="E277" s="8" t="s">
         <v>360</v>
       </c>
@@ -10928,8 +11074,8 @@
       <c r="B278" s="7">
         <v>5</v>
       </c>
-      <c r="C278" s="176"/>
-      <c r="D278" s="170"/>
+      <c r="C278" s="151"/>
+      <c r="D278" s="163"/>
       <c r="E278" s="8" t="s">
         <v>361</v>
       </c>
@@ -10950,8 +11096,8 @@
       <c r="B279" s="7">
         <v>6</v>
       </c>
-      <c r="C279" s="176"/>
-      <c r="D279" s="170"/>
+      <c r="C279" s="151"/>
+      <c r="D279" s="163"/>
       <c r="E279" s="8" t="s">
         <v>362</v>
       </c>
@@ -10972,8 +11118,8 @@
       <c r="B280" s="7">
         <v>7</v>
       </c>
-      <c r="C280" s="176"/>
-      <c r="D280" s="170"/>
+      <c r="C280" s="151"/>
+      <c r="D280" s="163"/>
       <c r="E280" s="8" t="s">
         <v>363</v>
       </c>
@@ -10994,8 +11140,8 @@
       <c r="B281" s="7">
         <v>8</v>
       </c>
-      <c r="C281" s="176"/>
-      <c r="D281" s="171"/>
+      <c r="C281" s="151"/>
+      <c r="D281" s="164"/>
       <c r="E281" s="13" t="s">
         <v>364</v>
       </c>
@@ -11016,8 +11162,8 @@
       <c r="B282" s="7">
         <v>9</v>
       </c>
-      <c r="C282" s="176"/>
-      <c r="D282" s="144" t="s">
+      <c r="C282" s="151"/>
+      <c r="D282" s="162" t="s">
         <v>365</v>
       </c>
       <c r="E282" s="8" t="s">
@@ -11040,8 +11186,8 @@
       <c r="B283" s="7">
         <v>10</v>
       </c>
-      <c r="C283" s="176"/>
-      <c r="D283" s="170"/>
+      <c r="C283" s="151"/>
+      <c r="D283" s="163"/>
       <c r="E283" s="13" t="s">
         <v>367</v>
       </c>
@@ -11062,8 +11208,8 @@
       <c r="B284" s="7">
         <v>11</v>
       </c>
-      <c r="C284" s="176"/>
-      <c r="D284" s="170"/>
+      <c r="C284" s="151"/>
+      <c r="D284" s="163"/>
       <c r="E284" s="13" t="s">
         <v>368</v>
       </c>
@@ -11084,8 +11230,8 @@
       <c r="B285" s="7">
         <v>12</v>
       </c>
-      <c r="C285" s="176"/>
-      <c r="D285" s="170"/>
+      <c r="C285" s="151"/>
+      <c r="D285" s="163"/>
       <c r="E285" s="13" t="s">
         <v>369</v>
       </c>
@@ -11106,8 +11252,8 @@
       <c r="B286" s="7">
         <v>13</v>
       </c>
-      <c r="C286" s="176"/>
-      <c r="D286" s="170"/>
+      <c r="C286" s="151"/>
+      <c r="D286" s="163"/>
       <c r="E286" s="13" t="s">
         <v>370</v>
       </c>
@@ -11128,8 +11274,8 @@
       <c r="B287" s="7">
         <v>14</v>
       </c>
-      <c r="C287" s="176"/>
-      <c r="D287" s="170"/>
+      <c r="C287" s="151"/>
+      <c r="D287" s="163"/>
       <c r="E287" s="13" t="s">
         <v>371</v>
       </c>
@@ -11150,8 +11296,8 @@
       <c r="B288" s="7">
         <v>15</v>
       </c>
-      <c r="C288" s="176"/>
-      <c r="D288" s="171"/>
+      <c r="C288" s="151"/>
+      <c r="D288" s="164"/>
       <c r="E288" s="13" t="s">
         <v>372</v>
       </c>
@@ -11172,8 +11318,8 @@
       <c r="B289" s="7">
         <v>16</v>
       </c>
-      <c r="C289" s="176"/>
-      <c r="D289" s="144" t="s">
+      <c r="C289" s="151"/>
+      <c r="D289" s="162" t="s">
         <v>373</v>
       </c>
       <c r="E289" s="13" t="s">
@@ -11196,8 +11342,8 @@
       <c r="B290" s="7">
         <v>17</v>
       </c>
-      <c r="C290" s="176"/>
-      <c r="D290" s="170"/>
+      <c r="C290" s="151"/>
+      <c r="D290" s="163"/>
       <c r="E290" s="8" t="s">
         <v>375</v>
       </c>
@@ -11218,8 +11364,8 @@
       <c r="B291" s="7">
         <v>18</v>
       </c>
-      <c r="C291" s="176"/>
-      <c r="D291" s="170"/>
+      <c r="C291" s="151"/>
+      <c r="D291" s="163"/>
       <c r="E291" s="11" t="s">
         <v>376</v>
       </c>
@@ -11240,8 +11386,8 @@
       <c r="B292" s="24">
         <v>19</v>
       </c>
-      <c r="C292" s="177"/>
-      <c r="D292" s="171"/>
+      <c r="C292" s="152"/>
+      <c r="D292" s="164"/>
       <c r="E292" s="20" t="s">
         <v>377</v>
       </c>
@@ -11262,10 +11408,10 @@
       <c r="B293" s="7">
         <v>1</v>
       </c>
-      <c r="C293" s="140" t="s">
+      <c r="C293" s="141" t="s">
         <v>378</v>
       </c>
-      <c r="D293" s="135" t="s">
+      <c r="D293" s="159" t="s">
         <v>379</v>
       </c>
       <c r="E293" s="8" t="s">
@@ -11288,8 +11434,8 @@
       <c r="B294" s="7">
         <v>2</v>
       </c>
-      <c r="C294" s="166"/>
-      <c r="D294" s="156"/>
+      <c r="C294" s="142"/>
+      <c r="D294" s="160"/>
       <c r="E294" s="8" t="s">
         <v>381</v>
       </c>
@@ -11310,8 +11456,8 @@
       <c r="B295" s="7">
         <v>3</v>
       </c>
-      <c r="C295" s="166"/>
-      <c r="D295" s="157"/>
+      <c r="C295" s="142"/>
+      <c r="D295" s="161"/>
       <c r="E295" s="8" t="s">
         <v>382</v>
       </c>
@@ -11330,8 +11476,8 @@
       <c r="B296" s="7">
         <v>4</v>
       </c>
-      <c r="C296" s="166"/>
-      <c r="D296" s="135" t="s">
+      <c r="C296" s="142"/>
+      <c r="D296" s="159" t="s">
         <v>383</v>
       </c>
       <c r="E296" s="37" t="s">
@@ -11354,8 +11500,8 @@
       <c r="B297" s="7">
         <v>5</v>
       </c>
-      <c r="C297" s="166"/>
-      <c r="D297" s="156"/>
+      <c r="C297" s="142"/>
+      <c r="D297" s="160"/>
       <c r="E297" s="8" t="s">
         <v>385</v>
       </c>
@@ -11376,8 +11522,8 @@
       <c r="B298" s="7">
         <v>6</v>
       </c>
-      <c r="C298" s="166"/>
-      <c r="D298" s="156"/>
+      <c r="C298" s="142"/>
+      <c r="D298" s="160"/>
       <c r="E298" s="8" t="s">
         <v>386</v>
       </c>
@@ -11398,8 +11544,8 @@
       <c r="B299" s="7">
         <v>7</v>
       </c>
-      <c r="C299" s="166"/>
-      <c r="D299" s="156"/>
+      <c r="C299" s="142"/>
+      <c r="D299" s="160"/>
       <c r="E299" s="8" t="s">
         <v>387</v>
       </c>
@@ -11420,8 +11566,8 @@
       <c r="B300" s="7">
         <v>8</v>
       </c>
-      <c r="C300" s="166"/>
-      <c r="D300" s="157"/>
+      <c r="C300" s="142"/>
+      <c r="D300" s="161"/>
       <c r="E300" s="8" t="s">
         <v>388</v>
       </c>
@@ -11442,8 +11588,8 @@
       <c r="B301" s="7">
         <v>9</v>
       </c>
-      <c r="C301" s="166"/>
-      <c r="D301" s="135" t="s">
+      <c r="C301" s="142"/>
+      <c r="D301" s="159" t="s">
         <v>389</v>
       </c>
       <c r="E301" s="8" t="s">
@@ -11466,8 +11612,8 @@
       <c r="B302" s="7">
         <v>10</v>
       </c>
-      <c r="C302" s="166"/>
-      <c r="D302" s="156"/>
+      <c r="C302" s="142"/>
+      <c r="D302" s="160"/>
       <c r="E302" s="8" t="s">
         <v>391</v>
       </c>
@@ -11488,8 +11634,8 @@
       <c r="B303" s="7">
         <v>11</v>
       </c>
-      <c r="C303" s="166"/>
-      <c r="D303" s="157"/>
+      <c r="C303" s="142"/>
+      <c r="D303" s="161"/>
       <c r="E303" s="8" t="s">
         <v>392</v>
       </c>
@@ -11510,8 +11656,8 @@
       <c r="B304" s="7">
         <v>12</v>
       </c>
-      <c r="C304" s="166"/>
-      <c r="D304" s="135" t="s">
+      <c r="C304" s="142"/>
+      <c r="D304" s="159" t="s">
         <v>393</v>
       </c>
       <c r="E304" s="8" t="s">
@@ -11534,8 +11680,8 @@
       <c r="B305" s="7">
         <v>13</v>
       </c>
-      <c r="C305" s="166"/>
-      <c r="D305" s="156"/>
+      <c r="C305" s="142"/>
+      <c r="D305" s="160"/>
       <c r="E305" s="8" t="s">
         <v>395</v>
       </c>
@@ -11556,8 +11702,8 @@
       <c r="B306" s="7">
         <v>14</v>
       </c>
-      <c r="C306" s="166"/>
-      <c r="D306" s="156"/>
+      <c r="C306" s="142"/>
+      <c r="D306" s="160"/>
       <c r="E306" s="8" t="s">
         <v>396</v>
       </c>
@@ -11578,8 +11724,8 @@
       <c r="B307" s="24">
         <v>15</v>
       </c>
-      <c r="C307" s="167"/>
-      <c r="D307" s="157"/>
+      <c r="C307" s="143"/>
+      <c r="D307" s="161"/>
       <c r="E307" s="17" t="s">
         <v>397</v>
       </c>
@@ -11600,10 +11746,10 @@
       <c r="B308" s="7">
         <v>1</v>
       </c>
-      <c r="C308" s="149" t="s">
+      <c r="C308" s="153" t="s">
         <v>398</v>
       </c>
-      <c r="D308" s="144" t="s">
+      <c r="D308" s="162" t="s">
         <v>399</v>
       </c>
       <c r="E308" s="13" t="s">
@@ -11626,8 +11772,8 @@
       <c r="B309" s="7">
         <v>2</v>
       </c>
-      <c r="C309" s="174"/>
-      <c r="D309" s="170"/>
+      <c r="C309" s="154"/>
+      <c r="D309" s="163"/>
       <c r="E309" s="8" t="s">
         <v>401</v>
       </c>
@@ -11648,8 +11794,8 @@
       <c r="B310" s="7">
         <v>3</v>
       </c>
-      <c r="C310" s="174"/>
-      <c r="D310" s="170"/>
+      <c r="C310" s="154"/>
+      <c r="D310" s="163"/>
       <c r="E310" s="13" t="s">
         <v>402</v>
       </c>
@@ -11670,8 +11816,8 @@
       <c r="B311" s="7">
         <v>4</v>
       </c>
-      <c r="C311" s="174"/>
-      <c r="D311" s="170"/>
+      <c r="C311" s="154"/>
+      <c r="D311" s="163"/>
       <c r="E311" s="8" t="s">
         <v>403</v>
       </c>
@@ -11692,8 +11838,8 @@
       <c r="B312" s="7">
         <v>5</v>
       </c>
-      <c r="C312" s="174"/>
-      <c r="D312" s="170"/>
+      <c r="C312" s="154"/>
+      <c r="D312" s="163"/>
       <c r="E312" s="13" t="s">
         <v>404</v>
       </c>
@@ -11714,8 +11860,8 @@
       <c r="B313" s="7">
         <v>6</v>
       </c>
-      <c r="C313" s="174"/>
-      <c r="D313" s="170"/>
+      <c r="C313" s="154"/>
+      <c r="D313" s="163"/>
       <c r="E313" s="13" t="s">
         <v>405</v>
       </c>
@@ -11736,8 +11882,8 @@
       <c r="B314" s="7">
         <v>7</v>
       </c>
-      <c r="C314" s="174"/>
-      <c r="D314" s="171"/>
+      <c r="C314" s="154"/>
+      <c r="D314" s="164"/>
       <c r="E314" s="8" t="s">
         <v>406</v>
       </c>
@@ -11758,8 +11904,8 @@
       <c r="B315" s="7">
         <v>8</v>
       </c>
-      <c r="C315" s="174"/>
-      <c r="D315" s="144" t="s">
+      <c r="C315" s="154"/>
+      <c r="D315" s="162" t="s">
         <v>407</v>
       </c>
       <c r="E315" s="13" t="s">
@@ -11782,8 +11928,8 @@
       <c r="B316" s="7">
         <v>9</v>
       </c>
-      <c r="C316" s="174"/>
-      <c r="D316" s="170"/>
+      <c r="C316" s="154"/>
+      <c r="D316" s="163"/>
       <c r="E316" s="8" t="s">
         <v>409</v>
       </c>
@@ -11804,8 +11950,8 @@
       <c r="B317" s="24">
         <v>10</v>
       </c>
-      <c r="C317" s="175"/>
-      <c r="D317" s="171"/>
+      <c r="C317" s="155"/>
+      <c r="D317" s="164"/>
       <c r="E317" s="17" t="s">
         <v>410</v>
       </c>
@@ -11826,10 +11972,10 @@
       <c r="B318" s="7">
         <v>1</v>
       </c>
-      <c r="C318" s="150" t="s">
+      <c r="C318" s="156" t="s">
         <v>411</v>
       </c>
-      <c r="D318" s="144" t="s">
+      <c r="D318" s="162" t="s">
         <v>412</v>
       </c>
       <c r="E318" s="8" t="s">
@@ -11852,8 +11998,8 @@
       <c r="B319" s="7">
         <v>2</v>
       </c>
-      <c r="C319" s="172"/>
-      <c r="D319" s="170"/>
+      <c r="C319" s="157"/>
+      <c r="D319" s="163"/>
       <c r="E319" s="13" t="s">
         <v>414</v>
       </c>
@@ -11874,8 +12020,8 @@
       <c r="B320" s="7">
         <v>3</v>
       </c>
-      <c r="C320" s="172"/>
-      <c r="D320" s="170"/>
+      <c r="C320" s="157"/>
+      <c r="D320" s="163"/>
       <c r="E320" s="8" t="s">
         <v>415</v>
       </c>
@@ -11896,8 +12042,8 @@
       <c r="B321" s="7">
         <v>4</v>
       </c>
-      <c r="C321" s="172"/>
-      <c r="D321" s="170"/>
+      <c r="C321" s="157"/>
+      <c r="D321" s="163"/>
       <c r="E321" s="8" t="s">
         <v>416</v>
       </c>
@@ -11918,8 +12064,8 @@
       <c r="B322" s="7">
         <v>5</v>
       </c>
-      <c r="C322" s="172"/>
-      <c r="D322" s="170"/>
+      <c r="C322" s="157"/>
+      <c r="D322" s="163"/>
       <c r="E322" s="8" t="s">
         <v>417</v>
       </c>
@@ -11940,8 +12086,8 @@
       <c r="B323" s="7">
         <v>6</v>
       </c>
-      <c r="C323" s="172"/>
-      <c r="D323" s="171"/>
+      <c r="C323" s="157"/>
+      <c r="D323" s="164"/>
       <c r="E323" s="29" t="s">
         <v>418</v>
       </c>
@@ -11962,8 +12108,8 @@
       <c r="B324" s="7">
         <v>7</v>
       </c>
-      <c r="C324" s="172"/>
-      <c r="D324" s="144" t="s">
+      <c r="C324" s="157"/>
+      <c r="D324" s="162" t="s">
         <v>419</v>
       </c>
       <c r="E324" s="13" t="s">
@@ -11986,8 +12132,8 @@
       <c r="B325" s="7">
         <v>8</v>
       </c>
-      <c r="C325" s="172"/>
-      <c r="D325" s="170"/>
+      <c r="C325" s="157"/>
+      <c r="D325" s="163"/>
       <c r="E325" s="8" t="s">
         <v>421</v>
       </c>
@@ -12008,8 +12154,8 @@
       <c r="B326" s="7">
         <v>9</v>
       </c>
-      <c r="C326" s="172"/>
-      <c r="D326" s="170"/>
+      <c r="C326" s="157"/>
+      <c r="D326" s="163"/>
       <c r="E326" s="8" t="s">
         <v>422</v>
       </c>
@@ -12030,8 +12176,8 @@
       <c r="B327" s="7">
         <v>10</v>
       </c>
-      <c r="C327" s="172"/>
-      <c r="D327" s="170"/>
+      <c r="C327" s="157"/>
+      <c r="D327" s="163"/>
       <c r="E327" s="8" t="s">
         <v>423</v>
       </c>
@@ -12052,8 +12198,8 @@
       <c r="B328" s="7">
         <v>11</v>
       </c>
-      <c r="C328" s="172"/>
-      <c r="D328" s="171"/>
+      <c r="C328" s="157"/>
+      <c r="D328" s="164"/>
       <c r="E328" s="13" t="s">
         <v>424</v>
       </c>
@@ -12074,8 +12220,8 @@
       <c r="B329" s="7">
         <v>12</v>
       </c>
-      <c r="C329" s="172"/>
-      <c r="D329" s="144" t="s">
+      <c r="C329" s="157"/>
+      <c r="D329" s="162" t="s">
         <v>425</v>
       </c>
       <c r="E329" s="8" t="s">
@@ -12098,8 +12244,8 @@
       <c r="B330" s="7">
         <v>13</v>
       </c>
-      <c r="C330" s="172"/>
-      <c r="D330" s="170"/>
+      <c r="C330" s="157"/>
+      <c r="D330" s="163"/>
       <c r="E330" s="8" t="s">
         <v>427</v>
       </c>
@@ -12120,8 +12266,8 @@
       <c r="B331" s="7">
         <v>14</v>
       </c>
-      <c r="C331" s="172"/>
-      <c r="D331" s="170"/>
+      <c r="C331" s="157"/>
+      <c r="D331" s="163"/>
       <c r="E331" s="8" t="s">
         <v>428</v>
       </c>
@@ -12142,8 +12288,8 @@
       <c r="B332" s="7">
         <v>15</v>
       </c>
-      <c r="C332" s="172"/>
-      <c r="D332" s="170"/>
+      <c r="C332" s="157"/>
+      <c r="D332" s="163"/>
       <c r="E332" s="8" t="s">
         <v>429</v>
       </c>
@@ -12164,8 +12310,8 @@
       <c r="B333" s="7">
         <v>16</v>
       </c>
-      <c r="C333" s="172"/>
-      <c r="D333" s="170"/>
+      <c r="C333" s="157"/>
+      <c r="D333" s="163"/>
       <c r="E333" s="8" t="s">
         <v>430</v>
       </c>
@@ -12186,8 +12332,8 @@
       <c r="B334" s="7">
         <v>17</v>
       </c>
-      <c r="C334" s="172"/>
-      <c r="D334" s="170"/>
+      <c r="C334" s="157"/>
+      <c r="D334" s="163"/>
       <c r="E334" s="8" t="s">
         <v>431</v>
       </c>
@@ -12208,8 +12354,8 @@
       <c r="B335" s="7">
         <v>18</v>
       </c>
-      <c r="C335" s="172"/>
-      <c r="D335" s="170"/>
+      <c r="C335" s="157"/>
+      <c r="D335" s="163"/>
       <c r="E335" s="8" t="s">
         <v>432</v>
       </c>
@@ -12230,8 +12376,8 @@
       <c r="B336" s="7">
         <v>19</v>
       </c>
-      <c r="C336" s="172"/>
-      <c r="D336" s="170"/>
+      <c r="C336" s="157"/>
+      <c r="D336" s="163"/>
       <c r="E336" s="8" t="s">
         <v>433</v>
       </c>
@@ -12252,8 +12398,8 @@
       <c r="B337" s="7">
         <v>20</v>
       </c>
-      <c r="C337" s="172"/>
-      <c r="D337" s="171"/>
+      <c r="C337" s="157"/>
+      <c r="D337" s="164"/>
       <c r="E337" s="13" t="s">
         <v>434</v>
       </c>
@@ -12274,8 +12420,8 @@
       <c r="B338" s="7">
         <v>21</v>
       </c>
-      <c r="C338" s="172"/>
-      <c r="D338" s="144" t="s">
+      <c r="C338" s="157"/>
+      <c r="D338" s="162" t="s">
         <v>435</v>
       </c>
       <c r="E338" s="13" t="s">
@@ -12298,8 +12444,8 @@
       <c r="B339" s="7">
         <v>22</v>
       </c>
-      <c r="C339" s="172"/>
-      <c r="D339" s="170"/>
+      <c r="C339" s="157"/>
+      <c r="D339" s="163"/>
       <c r="E339" s="13" t="s">
         <v>437</v>
       </c>
@@ -12320,8 +12466,8 @@
       <c r="B340" s="7">
         <v>23</v>
       </c>
-      <c r="C340" s="172"/>
-      <c r="D340" s="170"/>
+      <c r="C340" s="157"/>
+      <c r="D340" s="163"/>
       <c r="E340" s="13" t="s">
         <v>438</v>
       </c>
@@ -12342,8 +12488,8 @@
       <c r="B341" s="7">
         <v>24</v>
       </c>
-      <c r="C341" s="172"/>
-      <c r="D341" s="170"/>
+      <c r="C341" s="157"/>
+      <c r="D341" s="163"/>
       <c r="E341" s="13" t="s">
         <v>439</v>
       </c>
@@ -12364,8 +12510,8 @@
       <c r="B342" s="24">
         <v>25</v>
       </c>
-      <c r="C342" s="173"/>
-      <c r="D342" s="171"/>
+      <c r="C342" s="158"/>
+      <c r="D342" s="164"/>
       <c r="E342" s="25" t="s">
         <v>440</v>
       </c>
@@ -12386,10 +12532,10 @@
       <c r="B343" s="7">
         <v>1</v>
       </c>
-      <c r="C343" s="139" t="s">
+      <c r="C343" s="138" t="s">
         <v>441</v>
       </c>
-      <c r="D343" s="135" t="s">
+      <c r="D343" s="159" t="s">
         <v>442</v>
       </c>
       <c r="E343" s="8" t="s">
@@ -12418,8 +12564,8 @@
       <c r="B344" s="7">
         <v>2</v>
       </c>
-      <c r="C344" s="160"/>
-      <c r="D344" s="156"/>
+      <c r="C344" s="139"/>
+      <c r="D344" s="160"/>
       <c r="E344" s="8" t="s">
         <v>444</v>
       </c>
@@ -12446,8 +12592,8 @@
       <c r="B345" s="7">
         <v>3</v>
       </c>
-      <c r="C345" s="160"/>
-      <c r="D345" s="156"/>
+      <c r="C345" s="139"/>
+      <c r="D345" s="160"/>
       <c r="E345" s="8" t="s">
         <v>445</v>
       </c>
@@ -12474,8 +12620,8 @@
       <c r="B346" s="7">
         <v>4</v>
       </c>
-      <c r="C346" s="160"/>
-      <c r="D346" s="156"/>
+      <c r="C346" s="139"/>
+      <c r="D346" s="160"/>
       <c r="E346" s="8" t="s">
         <v>446</v>
       </c>
@@ -12502,8 +12648,8 @@
       <c r="B347" s="7">
         <v>5</v>
       </c>
-      <c r="C347" s="160"/>
-      <c r="D347" s="157"/>
+      <c r="C347" s="139"/>
+      <c r="D347" s="161"/>
       <c r="E347" s="8" t="s">
         <v>447</v>
       </c>
@@ -12530,8 +12676,8 @@
       <c r="B348" s="7">
         <v>6</v>
       </c>
-      <c r="C348" s="160"/>
-      <c r="D348" s="135" t="s">
+      <c r="C348" s="139"/>
+      <c r="D348" s="159" t="s">
         <v>448</v>
       </c>
       <c r="E348" s="8" t="s">
@@ -12558,8 +12704,8 @@
       <c r="B349" s="7">
         <v>7</v>
       </c>
-      <c r="C349" s="160"/>
-      <c r="D349" s="156"/>
+      <c r="C349" s="139"/>
+      <c r="D349" s="160"/>
       <c r="E349" s="8" t="s">
         <v>450</v>
       </c>
@@ -12586,8 +12732,8 @@
       <c r="B350" s="7">
         <v>8</v>
       </c>
-      <c r="C350" s="160"/>
-      <c r="D350" s="156"/>
+      <c r="C350" s="139"/>
+      <c r="D350" s="160"/>
       <c r="E350" s="8" t="s">
         <v>451</v>
       </c>
@@ -12614,8 +12760,8 @@
       <c r="B351" s="7">
         <v>9</v>
       </c>
-      <c r="C351" s="160"/>
-      <c r="D351" s="156"/>
+      <c r="C351" s="139"/>
+      <c r="D351" s="160"/>
       <c r="E351" s="8" t="s">
         <v>452</v>
       </c>
@@ -12638,8 +12784,8 @@
       <c r="B352" s="7">
         <v>10</v>
       </c>
-      <c r="C352" s="160"/>
-      <c r="D352" s="156"/>
+      <c r="C352" s="139"/>
+      <c r="D352" s="160"/>
       <c r="E352" s="8" t="s">
         <v>453</v>
       </c>
@@ -12666,8 +12812,8 @@
       <c r="B353" s="7">
         <v>11</v>
       </c>
-      <c r="C353" s="160"/>
-      <c r="D353" s="157"/>
+      <c r="C353" s="139"/>
+      <c r="D353" s="161"/>
       <c r="E353" s="8" t="s">
         <v>454</v>
       </c>
@@ -12688,8 +12834,8 @@
       <c r="B354" s="7">
         <v>12</v>
       </c>
-      <c r="C354" s="160"/>
-      <c r="D354" s="135" t="s">
+      <c r="C354" s="139"/>
+      <c r="D354" s="159" t="s">
         <v>455</v>
       </c>
       <c r="E354" s="8" t="s">
@@ -12716,8 +12862,8 @@
       <c r="B355" s="7">
         <v>13</v>
       </c>
-      <c r="C355" s="160"/>
-      <c r="D355" s="156"/>
+      <c r="C355" s="139"/>
+      <c r="D355" s="160"/>
       <c r="E355" s="8" t="s">
         <v>457</v>
       </c>
@@ -12744,8 +12890,8 @@
       <c r="B356" s="7">
         <v>14</v>
       </c>
-      <c r="C356" s="160"/>
-      <c r="D356" s="156"/>
+      <c r="C356" s="139"/>
+      <c r="D356" s="160"/>
       <c r="E356" s="8" t="s">
         <v>458</v>
       </c>
@@ -12766,8 +12912,8 @@
       <c r="B357" s="7">
         <v>15</v>
       </c>
-      <c r="C357" s="161"/>
-      <c r="D357" s="157"/>
+      <c r="C357" s="140"/>
+      <c r="D357" s="161"/>
       <c r="E357" s="8" t="s">
         <v>459</v>
       </c>
@@ -12782,18 +12928,18 @@
       <c r="J357" s="11"/>
     </row>
     <row r="358" spans="1:10" ht="13.8">
-      <c r="A358" s="147" t="s">
+      <c r="A358" s="174" t="s">
         <v>460</v>
       </c>
-      <c r="B358" s="168"/>
-      <c r="C358" s="168"/>
-      <c r="D358" s="168"/>
-      <c r="E358" s="168"/>
-      <c r="F358" s="168"/>
-      <c r="G358" s="168"/>
-      <c r="H358" s="168"/>
-      <c r="I358" s="168"/>
-      <c r="J358" s="169"/>
+      <c r="B358" s="175"/>
+      <c r="C358" s="175"/>
+      <c r="D358" s="175"/>
+      <c r="E358" s="175"/>
+      <c r="F358" s="175"/>
+      <c r="G358" s="175"/>
+      <c r="H358" s="175"/>
+      <c r="I358" s="175"/>
+      <c r="J358" s="176"/>
     </row>
     <row r="359" spans="1:10" ht="13.8">
       <c r="A359" s="6">
@@ -12802,10 +12948,10 @@
       <c r="B359" s="7">
         <v>1</v>
       </c>
-      <c r="C359" s="140" t="s">
+      <c r="C359" s="141" t="s">
         <v>461</v>
       </c>
-      <c r="D359" s="135" t="s">
+      <c r="D359" s="159" t="s">
         <v>462</v>
       </c>
       <c r="E359" s="8" t="s">
@@ -12828,8 +12974,8 @@
       <c r="B360" s="7">
         <v>2</v>
       </c>
-      <c r="C360" s="166"/>
-      <c r="D360" s="156"/>
+      <c r="C360" s="142"/>
+      <c r="D360" s="160"/>
       <c r="E360" s="8" t="s">
         <v>464</v>
       </c>
@@ -12850,8 +12996,8 @@
       <c r="B361" s="7">
         <v>3</v>
       </c>
-      <c r="C361" s="166"/>
-      <c r="D361" s="156"/>
+      <c r="C361" s="142"/>
+      <c r="D361" s="160"/>
       <c r="E361" s="8" t="s">
         <v>465</v>
       </c>
@@ -12872,8 +13018,8 @@
       <c r="B362" s="7">
         <v>4</v>
       </c>
-      <c r="C362" s="166"/>
-      <c r="D362" s="156"/>
+      <c r="C362" s="142"/>
+      <c r="D362" s="160"/>
       <c r="E362" s="8" t="s">
         <v>466</v>
       </c>
@@ -12894,8 +13040,8 @@
       <c r="B363" s="7">
         <v>5</v>
       </c>
-      <c r="C363" s="166"/>
-      <c r="D363" s="157"/>
+      <c r="C363" s="142"/>
+      <c r="D363" s="161"/>
       <c r="E363" s="8" t="s">
         <v>467</v>
       </c>
@@ -12916,8 +13062,8 @@
       <c r="B364" s="7">
         <v>6</v>
       </c>
-      <c r="C364" s="166"/>
-      <c r="D364" s="135" t="s">
+      <c r="C364" s="142"/>
+      <c r="D364" s="159" t="s">
         <v>468</v>
       </c>
       <c r="E364" s="8" t="s">
@@ -12940,8 +13086,8 @@
       <c r="B365" s="7">
         <v>7</v>
       </c>
-      <c r="C365" s="166"/>
-      <c r="D365" s="156"/>
+      <c r="C365" s="142"/>
+      <c r="D365" s="160"/>
       <c r="E365" s="8" t="s">
         <v>470</v>
       </c>
@@ -12962,8 +13108,8 @@
       <c r="B366" s="7">
         <v>8</v>
       </c>
-      <c r="C366" s="166"/>
-      <c r="D366" s="156"/>
+      <c r="C366" s="142"/>
+      <c r="D366" s="160"/>
       <c r="E366" s="8" t="s">
         <v>471</v>
       </c>
@@ -12984,8 +13130,8 @@
       <c r="B367" s="7">
         <v>9</v>
       </c>
-      <c r="C367" s="166"/>
-      <c r="D367" s="156"/>
+      <c r="C367" s="142"/>
+      <c r="D367" s="160"/>
       <c r="E367" s="8" t="s">
         <v>472</v>
       </c>
@@ -13006,8 +13152,8 @@
       <c r="B368" s="7">
         <v>10</v>
       </c>
-      <c r="C368" s="166"/>
-      <c r="D368" s="156"/>
+      <c r="C368" s="142"/>
+      <c r="D368" s="160"/>
       <c r="E368" s="8" t="s">
         <v>473</v>
       </c>
@@ -13028,8 +13174,8 @@
       <c r="B369" s="7">
         <v>11</v>
       </c>
-      <c r="C369" s="166"/>
-      <c r="D369" s="156"/>
+      <c r="C369" s="142"/>
+      <c r="D369" s="160"/>
       <c r="E369" s="8" t="s">
         <v>474</v>
       </c>
@@ -13050,8 +13196,8 @@
       <c r="B370" s="7">
         <v>12</v>
       </c>
-      <c r="C370" s="166"/>
-      <c r="D370" s="156"/>
+      <c r="C370" s="142"/>
+      <c r="D370" s="160"/>
       <c r="E370" s="8" t="s">
         <v>475</v>
       </c>
@@ -13072,8 +13218,8 @@
       <c r="B371" s="7">
         <v>13</v>
       </c>
-      <c r="C371" s="166"/>
-      <c r="D371" s="157"/>
+      <c r="C371" s="142"/>
+      <c r="D371" s="161"/>
       <c r="E371" s="8" t="s">
         <v>476</v>
       </c>
@@ -13094,8 +13240,8 @@
       <c r="B372" s="7">
         <v>14</v>
       </c>
-      <c r="C372" s="166"/>
-      <c r="D372" s="135" t="s">
+      <c r="C372" s="142"/>
+      <c r="D372" s="159" t="s">
         <v>477</v>
       </c>
       <c r="E372" s="8" t="s">
@@ -13118,8 +13264,8 @@
       <c r="B373" s="7">
         <v>15</v>
       </c>
-      <c r="C373" s="166"/>
-      <c r="D373" s="156"/>
+      <c r="C373" s="142"/>
+      <c r="D373" s="160"/>
       <c r="E373" s="11" t="s">
         <v>479</v>
       </c>
@@ -13140,8 +13286,8 @@
       <c r="B374" s="7">
         <v>16</v>
       </c>
-      <c r="C374" s="166"/>
-      <c r="D374" s="156"/>
+      <c r="C374" s="142"/>
+      <c r="D374" s="160"/>
       <c r="E374" s="8" t="s">
         <v>480</v>
       </c>
@@ -13162,8 +13308,8 @@
       <c r="B375" s="7">
         <v>17</v>
       </c>
-      <c r="C375" s="166"/>
-      <c r="D375" s="157"/>
+      <c r="C375" s="142"/>
+      <c r="D375" s="161"/>
       <c r="E375" s="8" t="s">
         <v>481</v>
       </c>
@@ -13184,8 +13330,8 @@
       <c r="B376" s="7">
         <v>18</v>
       </c>
-      <c r="C376" s="166"/>
-      <c r="D376" s="135" t="s">
+      <c r="C376" s="142"/>
+      <c r="D376" s="159" t="s">
         <v>482</v>
       </c>
       <c r="E376" s="8" t="s">
@@ -13208,8 +13354,8 @@
       <c r="B377" s="7">
         <v>19</v>
       </c>
-      <c r="C377" s="166"/>
-      <c r="D377" s="156"/>
+      <c r="C377" s="142"/>
+      <c r="D377" s="160"/>
       <c r="E377" s="8" t="s">
         <v>484</v>
       </c>
@@ -13230,8 +13376,8 @@
       <c r="B378" s="7">
         <v>20</v>
       </c>
-      <c r="C378" s="166"/>
-      <c r="D378" s="156"/>
+      <c r="C378" s="142"/>
+      <c r="D378" s="160"/>
       <c r="E378" s="8" t="s">
         <v>485</v>
       </c>
@@ -13252,8 +13398,8 @@
       <c r="B379" s="7">
         <v>21</v>
       </c>
-      <c r="C379" s="166"/>
-      <c r="D379" s="156"/>
+      <c r="C379" s="142"/>
+      <c r="D379" s="160"/>
       <c r="E379" s="8" t="s">
         <v>486</v>
       </c>
@@ -13274,8 +13420,8 @@
       <c r="B380" s="24">
         <v>22</v>
       </c>
-      <c r="C380" s="167"/>
-      <c r="D380" s="157"/>
+      <c r="C380" s="143"/>
+      <c r="D380" s="161"/>
       <c r="E380" s="17" t="s">
         <v>487</v>
       </c>
@@ -13296,10 +13442,10 @@
       <c r="B381" s="7">
         <v>1</v>
       </c>
-      <c r="C381" s="137" t="s">
+      <c r="C381" s="144" t="s">
         <v>488</v>
       </c>
-      <c r="D381" s="135" t="s">
+      <c r="D381" s="159" t="s">
         <v>489</v>
       </c>
       <c r="E381" s="8" t="s">
@@ -13322,8 +13468,8 @@
       <c r="B382" s="7">
         <v>2</v>
       </c>
-      <c r="C382" s="164"/>
-      <c r="D382" s="156"/>
+      <c r="C382" s="145"/>
+      <c r="D382" s="160"/>
       <c r="E382" s="8" t="s">
         <v>491</v>
       </c>
@@ -13344,8 +13490,8 @@
       <c r="B383" s="7">
         <v>3</v>
       </c>
-      <c r="C383" s="164"/>
-      <c r="D383" s="156"/>
+      <c r="C383" s="145"/>
+      <c r="D383" s="160"/>
       <c r="E383" s="8" t="s">
         <v>492</v>
       </c>
@@ -13366,8 +13512,8 @@
       <c r="B384" s="7">
         <v>4</v>
       </c>
-      <c r="C384" s="164"/>
-      <c r="D384" s="156"/>
+      <c r="C384" s="145"/>
+      <c r="D384" s="160"/>
       <c r="E384" s="8" t="s">
         <v>493</v>
       </c>
@@ -13388,8 +13534,8 @@
       <c r="B385" s="7">
         <v>5</v>
       </c>
-      <c r="C385" s="164"/>
-      <c r="D385" s="156"/>
+      <c r="C385" s="145"/>
+      <c r="D385" s="160"/>
       <c r="E385" s="8" t="s">
         <v>494</v>
       </c>
@@ -13410,8 +13556,8 @@
       <c r="B386" s="7">
         <v>6</v>
       </c>
-      <c r="C386" s="164"/>
-      <c r="D386" s="157"/>
+      <c r="C386" s="145"/>
+      <c r="D386" s="161"/>
       <c r="E386" s="8" t="s">
         <v>495</v>
       </c>
@@ -13432,8 +13578,8 @@
       <c r="B387" s="7">
         <v>7</v>
       </c>
-      <c r="C387" s="164"/>
-      <c r="D387" s="135" t="s">
+      <c r="C387" s="145"/>
+      <c r="D387" s="159" t="s">
         <v>496</v>
       </c>
       <c r="E387" s="8" t="s">
@@ -13456,8 +13602,8 @@
       <c r="B388" s="7">
         <v>8</v>
       </c>
-      <c r="C388" s="164"/>
-      <c r="D388" s="156"/>
+      <c r="C388" s="145"/>
+      <c r="D388" s="160"/>
       <c r="E388" s="8" t="s">
         <v>498</v>
       </c>
@@ -13478,8 +13624,8 @@
       <c r="B389" s="7">
         <v>9</v>
       </c>
-      <c r="C389" s="164"/>
-      <c r="D389" s="156"/>
+      <c r="C389" s="145"/>
+      <c r="D389" s="160"/>
       <c r="E389" s="8" t="s">
         <v>499</v>
       </c>
@@ -13500,8 +13646,8 @@
       <c r="B390" s="7">
         <v>10</v>
       </c>
-      <c r="C390" s="164"/>
-      <c r="D390" s="156"/>
+      <c r="C390" s="145"/>
+      <c r="D390" s="160"/>
       <c r="E390" s="8" t="s">
         <v>500</v>
       </c>
@@ -13522,8 +13668,8 @@
       <c r="B391" s="7">
         <v>11</v>
       </c>
-      <c r="C391" s="164"/>
-      <c r="D391" s="156"/>
+      <c r="C391" s="145"/>
+      <c r="D391" s="160"/>
       <c r="E391" s="8" t="s">
         <v>501</v>
       </c>
@@ -13544,8 +13690,8 @@
       <c r="B392" s="7">
         <v>12</v>
       </c>
-      <c r="C392" s="164"/>
-      <c r="D392" s="156"/>
+      <c r="C392" s="145"/>
+      <c r="D392" s="160"/>
       <c r="E392" s="8" t="s">
         <v>502</v>
       </c>
@@ -13566,8 +13712,8 @@
       <c r="B393" s="7">
         <v>13</v>
       </c>
-      <c r="C393" s="164"/>
-      <c r="D393" s="156"/>
+      <c r="C393" s="145"/>
+      <c r="D393" s="160"/>
       <c r="E393" s="8" t="s">
         <v>503</v>
       </c>
@@ -13588,8 +13734,8 @@
       <c r="B394" s="7">
         <v>14</v>
       </c>
-      <c r="C394" s="164"/>
-      <c r="D394" s="156"/>
+      <c r="C394" s="145"/>
+      <c r="D394" s="160"/>
       <c r="E394" s="8" t="s">
         <v>504</v>
       </c>
@@ -13610,8 +13756,8 @@
       <c r="B395" s="7">
         <v>15</v>
       </c>
-      <c r="C395" s="164"/>
-      <c r="D395" s="156"/>
+      <c r="C395" s="145"/>
+      <c r="D395" s="160"/>
       <c r="E395" s="8" t="s">
         <v>505</v>
       </c>
@@ -13632,8 +13778,8 @@
       <c r="B396" s="7">
         <v>16</v>
       </c>
-      <c r="C396" s="164"/>
-      <c r="D396" s="157"/>
+      <c r="C396" s="145"/>
+      <c r="D396" s="161"/>
       <c r="E396" s="8" t="s">
         <v>506</v>
       </c>
@@ -13654,8 +13800,8 @@
       <c r="B397" s="7">
         <v>17</v>
       </c>
-      <c r="C397" s="164"/>
-      <c r="D397" s="135" t="s">
+      <c r="C397" s="145"/>
+      <c r="D397" s="159" t="s">
         <v>507</v>
       </c>
       <c r="E397" s="8" t="s">
@@ -13678,8 +13824,8 @@
       <c r="B398" s="7">
         <v>18</v>
       </c>
-      <c r="C398" s="164"/>
-      <c r="D398" s="156"/>
+      <c r="C398" s="145"/>
+      <c r="D398" s="160"/>
       <c r="E398" s="8" t="s">
         <v>509</v>
       </c>
@@ -13700,8 +13846,8 @@
       <c r="B399" s="7">
         <v>19</v>
       </c>
-      <c r="C399" s="164"/>
-      <c r="D399" s="157"/>
+      <c r="C399" s="145"/>
+      <c r="D399" s="161"/>
       <c r="E399" s="8" t="s">
         <v>510</v>
       </c>
@@ -13722,8 +13868,8 @@
       <c r="B400" s="7">
         <v>20</v>
       </c>
-      <c r="C400" s="164"/>
-      <c r="D400" s="135" t="s">
+      <c r="C400" s="145"/>
+      <c r="D400" s="159" t="s">
         <v>511</v>
       </c>
       <c r="E400" s="8" t="s">
@@ -13746,8 +13892,8 @@
       <c r="B401" s="7">
         <v>21</v>
       </c>
-      <c r="C401" s="164"/>
-      <c r="D401" s="156"/>
+      <c r="C401" s="145"/>
+      <c r="D401" s="160"/>
       <c r="E401" s="8" t="s">
         <v>513</v>
       </c>
@@ -13768,8 +13914,8 @@
       <c r="B402" s="7">
         <v>22</v>
       </c>
-      <c r="C402" s="164"/>
-      <c r="D402" s="156"/>
+      <c r="C402" s="145"/>
+      <c r="D402" s="160"/>
       <c r="E402" s="8" t="s">
         <v>514</v>
       </c>
@@ -13790,8 +13936,8 @@
       <c r="B403" s="7">
         <v>23</v>
       </c>
-      <c r="C403" s="164"/>
-      <c r="D403" s="156"/>
+      <c r="C403" s="145"/>
+      <c r="D403" s="160"/>
       <c r="E403" s="8" t="s">
         <v>515</v>
       </c>
@@ -13812,8 +13958,8 @@
       <c r="B404" s="7">
         <v>24</v>
       </c>
-      <c r="C404" s="164"/>
-      <c r="D404" s="157"/>
+      <c r="C404" s="145"/>
+      <c r="D404" s="161"/>
       <c r="E404" s="8" t="s">
         <v>516</v>
       </c>
@@ -13834,8 +13980,8 @@
       <c r="B405" s="7">
         <v>25</v>
       </c>
-      <c r="C405" s="164"/>
-      <c r="D405" s="135" t="s">
+      <c r="C405" s="145"/>
+      <c r="D405" s="159" t="s">
         <v>517</v>
       </c>
       <c r="E405" s="8" t="s">
@@ -13858,8 +14004,8 @@
       <c r="B406" s="7">
         <v>26</v>
       </c>
-      <c r="C406" s="164"/>
-      <c r="D406" s="156"/>
+      <c r="C406" s="145"/>
+      <c r="D406" s="160"/>
       <c r="E406" s="8" t="s">
         <v>519</v>
       </c>
@@ -13880,8 +14026,8 @@
       <c r="B407" s="7">
         <v>27</v>
       </c>
-      <c r="C407" s="164"/>
-      <c r="D407" s="156"/>
+      <c r="C407" s="145"/>
+      <c r="D407" s="160"/>
       <c r="E407" s="8" t="s">
         <v>520</v>
       </c>
@@ -13902,8 +14048,8 @@
       <c r="B408" s="7">
         <v>28</v>
       </c>
-      <c r="C408" s="164"/>
-      <c r="D408" s="156"/>
+      <c r="C408" s="145"/>
+      <c r="D408" s="160"/>
       <c r="E408" s="8" t="s">
         <v>521</v>
       </c>
@@ -13924,8 +14070,8 @@
       <c r="B409" s="7">
         <v>29</v>
       </c>
-      <c r="C409" s="164"/>
-      <c r="D409" s="156"/>
+      <c r="C409" s="145"/>
+      <c r="D409" s="160"/>
       <c r="E409" s="8" t="s">
         <v>522</v>
       </c>
@@ -13946,8 +14092,8 @@
       <c r="B410" s="7">
         <v>30</v>
       </c>
-      <c r="C410" s="164"/>
-      <c r="D410" s="156"/>
+      <c r="C410" s="145"/>
+      <c r="D410" s="160"/>
       <c r="E410" s="8" t="s">
         <v>523</v>
       </c>
@@ -13968,8 +14114,8 @@
       <c r="B411" s="7">
         <v>31</v>
       </c>
-      <c r="C411" s="164"/>
-      <c r="D411" s="156"/>
+      <c r="C411" s="145"/>
+      <c r="D411" s="160"/>
       <c r="E411" s="8" t="s">
         <v>524</v>
       </c>
@@ -13990,8 +14136,8 @@
       <c r="B412" s="7">
         <v>32</v>
       </c>
-      <c r="C412" s="164"/>
-      <c r="D412" s="156"/>
+      <c r="C412" s="145"/>
+      <c r="D412" s="160"/>
       <c r="E412" s="8" t="s">
         <v>525</v>
       </c>
@@ -14012,8 +14158,8 @@
       <c r="B413" s="7">
         <v>33</v>
       </c>
-      <c r="C413" s="164"/>
-      <c r="D413" s="156"/>
+      <c r="C413" s="145"/>
+      <c r="D413" s="160"/>
       <c r="E413" s="8" t="s">
         <v>526</v>
       </c>
@@ -14034,8 +14180,8 @@
       <c r="B414" s="7">
         <v>34</v>
       </c>
-      <c r="C414" s="164"/>
-      <c r="D414" s="156"/>
+      <c r="C414" s="145"/>
+      <c r="D414" s="160"/>
       <c r="E414" s="8" t="s">
         <v>527</v>
       </c>
@@ -14056,8 +14202,8 @@
       <c r="B415" s="7">
         <v>35</v>
       </c>
-      <c r="C415" s="164"/>
-      <c r="D415" s="156"/>
+      <c r="C415" s="145"/>
+      <c r="D415" s="160"/>
       <c r="E415" s="8" t="s">
         <v>528</v>
       </c>
@@ -14078,8 +14224,8 @@
       <c r="B416" s="7">
         <v>36</v>
       </c>
-      <c r="C416" s="164"/>
-      <c r="D416" s="157"/>
+      <c r="C416" s="145"/>
+      <c r="D416" s="161"/>
       <c r="E416" s="8" t="s">
         <v>529</v>
       </c>
@@ -14100,8 +14246,8 @@
       <c r="B417" s="7">
         <v>37</v>
       </c>
-      <c r="C417" s="164"/>
-      <c r="D417" s="135" t="s">
+      <c r="C417" s="145"/>
+      <c r="D417" s="159" t="s">
         <v>530</v>
       </c>
       <c r="E417" s="8" t="s">
@@ -14124,8 +14270,8 @@
       <c r="B418" s="7">
         <v>38</v>
       </c>
-      <c r="C418" s="164"/>
-      <c r="D418" s="156"/>
+      <c r="C418" s="145"/>
+      <c r="D418" s="160"/>
       <c r="E418" s="8" t="s">
         <v>532</v>
       </c>
@@ -14146,8 +14292,8 @@
       <c r="B419" s="7">
         <v>39</v>
       </c>
-      <c r="C419" s="164"/>
-      <c r="D419" s="157"/>
+      <c r="C419" s="145"/>
+      <c r="D419" s="161"/>
       <c r="E419" s="8" t="s">
         <v>533</v>
       </c>
@@ -14168,8 +14314,8 @@
       <c r="B420" s="7">
         <v>40</v>
       </c>
-      <c r="C420" s="164"/>
-      <c r="D420" s="135" t="s">
+      <c r="C420" s="145"/>
+      <c r="D420" s="159" t="s">
         <v>534</v>
       </c>
       <c r="E420" s="8" t="s">
@@ -14192,8 +14338,8 @@
       <c r="B421" s="7">
         <v>41</v>
       </c>
-      <c r="C421" s="164"/>
-      <c r="D421" s="156"/>
+      <c r="C421" s="145"/>
+      <c r="D421" s="160"/>
       <c r="E421" s="8" t="s">
         <v>536</v>
       </c>
@@ -14214,8 +14360,8 @@
       <c r="B422" s="7">
         <v>42</v>
       </c>
-      <c r="C422" s="164"/>
-      <c r="D422" s="156"/>
+      <c r="C422" s="145"/>
+      <c r="D422" s="160"/>
       <c r="E422" s="8" t="s">
         <v>537</v>
       </c>
@@ -14236,8 +14382,8 @@
       <c r="B423" s="7">
         <v>43</v>
       </c>
-      <c r="C423" s="164"/>
-      <c r="D423" s="156"/>
+      <c r="C423" s="145"/>
+      <c r="D423" s="160"/>
       <c r="E423" s="8" t="s">
         <v>538</v>
       </c>
@@ -14258,8 +14404,8 @@
       <c r="B424" s="7">
         <v>44</v>
       </c>
-      <c r="C424" s="164"/>
-      <c r="D424" s="156"/>
+      <c r="C424" s="145"/>
+      <c r="D424" s="160"/>
       <c r="E424" s="8" t="s">
         <v>539</v>
       </c>
@@ -14280,8 +14426,8 @@
       <c r="B425" s="7">
         <v>45</v>
       </c>
-      <c r="C425" s="164"/>
-      <c r="D425" s="156"/>
+      <c r="C425" s="145"/>
+      <c r="D425" s="160"/>
       <c r="E425" s="8" t="s">
         <v>540</v>
       </c>
@@ -14302,8 +14448,8 @@
       <c r="B426" s="7">
         <v>46</v>
       </c>
-      <c r="C426" s="164"/>
-      <c r="D426" s="157"/>
+      <c r="C426" s="145"/>
+      <c r="D426" s="161"/>
       <c r="E426" s="8" t="s">
         <v>541</v>
       </c>
@@ -14324,8 +14470,8 @@
       <c r="B427" s="7">
         <v>47</v>
       </c>
-      <c r="C427" s="164"/>
-      <c r="D427" s="135" t="s">
+      <c r="C427" s="145"/>
+      <c r="D427" s="159" t="s">
         <v>542</v>
       </c>
       <c r="E427" s="8" t="s">
@@ -14346,8 +14492,8 @@
       <c r="B428" s="7">
         <v>48</v>
       </c>
-      <c r="C428" s="164"/>
-      <c r="D428" s="156"/>
+      <c r="C428" s="145"/>
+      <c r="D428" s="160"/>
       <c r="E428" s="8" t="s">
         <v>544</v>
       </c>
@@ -14368,8 +14514,8 @@
       <c r="B429" s="7">
         <v>49</v>
       </c>
-      <c r="C429" s="164"/>
-      <c r="D429" s="156"/>
+      <c r="C429" s="145"/>
+      <c r="D429" s="160"/>
       <c r="E429" s="8" t="s">
         <v>545</v>
       </c>
@@ -14390,8 +14536,8 @@
       <c r="B430" s="7">
         <v>50</v>
       </c>
-      <c r="C430" s="164"/>
-      <c r="D430" s="157"/>
+      <c r="C430" s="145"/>
+      <c r="D430" s="161"/>
       <c r="E430" s="8" t="s">
         <v>546</v>
       </c>
@@ -14412,8 +14558,8 @@
       <c r="B431" s="7">
         <v>51</v>
       </c>
-      <c r="C431" s="164"/>
-      <c r="D431" s="135" t="s">
+      <c r="C431" s="145"/>
+      <c r="D431" s="159" t="s">
         <v>547</v>
       </c>
       <c r="E431" s="8" t="s">
@@ -14436,8 +14582,8 @@
       <c r="B432" s="7">
         <v>52</v>
       </c>
-      <c r="C432" s="164"/>
-      <c r="D432" s="156"/>
+      <c r="C432" s="145"/>
+      <c r="D432" s="160"/>
       <c r="E432" s="8" t="s">
         <v>549</v>
       </c>
@@ -14458,8 +14604,8 @@
       <c r="B433" s="7">
         <v>53</v>
       </c>
-      <c r="C433" s="164"/>
-      <c r="D433" s="156"/>
+      <c r="C433" s="145"/>
+      <c r="D433" s="160"/>
       <c r="E433" s="8" t="s">
         <v>550</v>
       </c>
@@ -14480,8 +14626,8 @@
       <c r="B434" s="7">
         <v>54</v>
       </c>
-      <c r="C434" s="164"/>
-      <c r="D434" s="156"/>
+      <c r="C434" s="145"/>
+      <c r="D434" s="160"/>
       <c r="E434" s="8" t="s">
         <v>551</v>
       </c>
@@ -14502,8 +14648,8 @@
       <c r="B435" s="7">
         <v>55</v>
       </c>
-      <c r="C435" s="165"/>
-      <c r="D435" s="157"/>
+      <c r="C435" s="146"/>
+      <c r="D435" s="161"/>
       <c r="E435" s="8" t="s">
         <v>552</v>
       </c>
@@ -14518,18 +14664,18 @@
       <c r="J435" s="11"/>
     </row>
     <row r="436" spans="1:10" ht="13.8">
-      <c r="A436" s="148" t="s">
+      <c r="A436" s="165" t="s">
         <v>553</v>
       </c>
-      <c r="B436" s="162"/>
-      <c r="C436" s="162"/>
-      <c r="D436" s="162"/>
-      <c r="E436" s="162"/>
-      <c r="F436" s="162"/>
-      <c r="G436" s="162"/>
-      <c r="H436" s="162"/>
-      <c r="I436" s="162"/>
-      <c r="J436" s="163"/>
+      <c r="B436" s="166"/>
+      <c r="C436" s="166"/>
+      <c r="D436" s="166"/>
+      <c r="E436" s="166"/>
+      <c r="F436" s="166"/>
+      <c r="G436" s="166"/>
+      <c r="H436" s="166"/>
+      <c r="I436" s="166"/>
+      <c r="J436" s="167"/>
     </row>
     <row r="437" spans="1:10" ht="13.8">
       <c r="A437" s="6">
@@ -14538,10 +14684,10 @@
       <c r="B437" s="7">
         <v>1</v>
       </c>
-      <c r="C437" s="138" t="s">
+      <c r="C437" s="147" t="s">
         <v>554</v>
       </c>
-      <c r="D437" s="135" t="s">
+      <c r="D437" s="159" t="s">
         <v>555</v>
       </c>
       <c r="E437" s="29" t="s">
@@ -14564,8 +14710,8 @@
       <c r="B438" s="7">
         <v>2</v>
       </c>
-      <c r="C438" s="158"/>
-      <c r="D438" s="156"/>
+      <c r="C438" s="148"/>
+      <c r="D438" s="160"/>
       <c r="E438" s="8" t="s">
         <v>557</v>
       </c>
@@ -14584,8 +14730,8 @@
       <c r="B439" s="7">
         <v>3</v>
       </c>
-      <c r="C439" s="158"/>
-      <c r="D439" s="156"/>
+      <c r="C439" s="148"/>
+      <c r="D439" s="160"/>
       <c r="E439" s="8" t="s">
         <v>558</v>
       </c>
@@ -14606,8 +14752,8 @@
       <c r="B440" s="7">
         <v>4</v>
       </c>
-      <c r="C440" s="158"/>
-      <c r="D440" s="156"/>
+      <c r="C440" s="148"/>
+      <c r="D440" s="160"/>
       <c r="E440" s="29" t="s">
         <v>559</v>
       </c>
@@ -14628,8 +14774,8 @@
       <c r="B441" s="7">
         <v>5</v>
       </c>
-      <c r="C441" s="158"/>
-      <c r="D441" s="157"/>
+      <c r="C441" s="148"/>
+      <c r="D441" s="161"/>
       <c r="E441" s="8" t="s">
         <v>560</v>
       </c>
@@ -14650,8 +14796,8 @@
       <c r="B442" s="7">
         <v>6</v>
       </c>
-      <c r="C442" s="158"/>
-      <c r="D442" s="135" t="s">
+      <c r="C442" s="148"/>
+      <c r="D442" s="159" t="s">
         <v>561</v>
       </c>
       <c r="E442" s="29" t="s">
@@ -14674,8 +14820,8 @@
       <c r="B443" s="7">
         <v>7</v>
       </c>
-      <c r="C443" s="158"/>
-      <c r="D443" s="156"/>
+      <c r="C443" s="148"/>
+      <c r="D443" s="160"/>
       <c r="E443" s="8" t="s">
         <v>563</v>
       </c>
@@ -14696,8 +14842,8 @@
       <c r="B444" s="7">
         <v>8</v>
       </c>
-      <c r="C444" s="158"/>
-      <c r="D444" s="156"/>
+      <c r="C444" s="148"/>
+      <c r="D444" s="160"/>
       <c r="E444" s="29" t="s">
         <v>564</v>
       </c>
@@ -14718,8 +14864,8 @@
       <c r="B445" s="7">
         <v>9</v>
       </c>
-      <c r="C445" s="158"/>
-      <c r="D445" s="157"/>
+      <c r="C445" s="148"/>
+      <c r="D445" s="161"/>
       <c r="E445" s="8" t="s">
         <v>565</v>
       </c>
@@ -14740,8 +14886,8 @@
       <c r="B446" s="7">
         <v>10</v>
       </c>
-      <c r="C446" s="158"/>
-      <c r="D446" s="135" t="s">
+      <c r="C446" s="148"/>
+      <c r="D446" s="159" t="s">
         <v>566</v>
       </c>
       <c r="E446" s="8" t="s">
@@ -14764,8 +14910,8 @@
       <c r="B447" s="7">
         <v>11</v>
       </c>
-      <c r="C447" s="158"/>
-      <c r="D447" s="156"/>
+      <c r="C447" s="148"/>
+      <c r="D447" s="160"/>
       <c r="E447" s="8" t="s">
         <v>568</v>
       </c>
@@ -14786,8 +14932,8 @@
       <c r="B448" s="7">
         <v>12</v>
       </c>
-      <c r="C448" s="158"/>
-      <c r="D448" s="157"/>
+      <c r="C448" s="148"/>
+      <c r="D448" s="161"/>
       <c r="E448" s="8" t="s">
         <v>569</v>
       </c>
@@ -14808,8 +14954,8 @@
       <c r="B449" s="7">
         <v>13</v>
       </c>
-      <c r="C449" s="158"/>
-      <c r="D449" s="135" t="s">
+      <c r="C449" s="148"/>
+      <c r="D449" s="159" t="s">
         <v>570</v>
       </c>
       <c r="E449" s="8" t="s">
@@ -14832,8 +14978,8 @@
       <c r="B450" s="7">
         <v>14</v>
       </c>
-      <c r="C450" s="158"/>
-      <c r="D450" s="156"/>
+      <c r="C450" s="148"/>
+      <c r="D450" s="160"/>
       <c r="E450" s="29" t="s">
         <v>572</v>
       </c>
@@ -14854,8 +15000,8 @@
       <c r="B451" s="7">
         <v>15</v>
       </c>
-      <c r="C451" s="158"/>
-      <c r="D451" s="156"/>
+      <c r="C451" s="148"/>
+      <c r="D451" s="160"/>
       <c r="E451" s="8" t="s">
         <v>573</v>
       </c>
@@ -14876,8 +15022,8 @@
       <c r="B452" s="7">
         <v>16</v>
       </c>
-      <c r="C452" s="158"/>
-      <c r="D452" s="157"/>
+      <c r="C452" s="148"/>
+      <c r="D452" s="161"/>
       <c r="E452" s="8" t="s">
         <v>574</v>
       </c>
@@ -14898,8 +15044,8 @@
       <c r="B453" s="7">
         <v>17</v>
       </c>
-      <c r="C453" s="158"/>
-      <c r="D453" s="135" t="s">
+      <c r="C453" s="148"/>
+      <c r="D453" s="159" t="s">
         <v>575</v>
       </c>
       <c r="E453" s="8" t="s">
@@ -14922,8 +15068,8 @@
       <c r="B454" s="7">
         <v>18</v>
       </c>
-      <c r="C454" s="158"/>
-      <c r="D454" s="156"/>
+      <c r="C454" s="148"/>
+      <c r="D454" s="160"/>
       <c r="E454" s="8" t="s">
         <v>577</v>
       </c>
@@ -14944,8 +15090,8 @@
       <c r="B455" s="7">
         <v>19</v>
       </c>
-      <c r="C455" s="158"/>
-      <c r="D455" s="156"/>
+      <c r="C455" s="148"/>
+      <c r="D455" s="160"/>
       <c r="E455" s="8" t="s">
         <v>578</v>
       </c>
@@ -14966,8 +15112,8 @@
       <c r="B456" s="7">
         <v>20</v>
       </c>
-      <c r="C456" s="158"/>
-      <c r="D456" s="156"/>
+      <c r="C456" s="148"/>
+      <c r="D456" s="160"/>
       <c r="E456" s="39" t="s">
         <v>579</v>
       </c>
@@ -14988,8 +15134,8 @@
       <c r="B457" s="7">
         <v>21</v>
       </c>
-      <c r="C457" s="158"/>
-      <c r="D457" s="156"/>
+      <c r="C457" s="148"/>
+      <c r="D457" s="160"/>
       <c r="E457" s="8" t="s">
         <v>580</v>
       </c>
@@ -15010,8 +15156,8 @@
       <c r="B458" s="24">
         <v>22</v>
       </c>
-      <c r="C458" s="159"/>
-      <c r="D458" s="157"/>
+      <c r="C458" s="149"/>
+      <c r="D458" s="161"/>
       <c r="E458" s="17" t="s">
         <v>581</v>
       </c>
@@ -15033,10 +15179,10 @@
       <c r="B459" s="7">
         <v>1</v>
       </c>
-      <c r="C459" s="139" t="s">
+      <c r="C459" s="138" t="s">
         <v>582</v>
       </c>
-      <c r="D459" s="135" t="s">
+      <c r="D459" s="159" t="s">
         <v>583</v>
       </c>
       <c r="E459" s="8" t="s">
@@ -15059,8 +15205,8 @@
       <c r="B460" s="7">
         <v>2</v>
       </c>
-      <c r="C460" s="160"/>
-      <c r="D460" s="156"/>
+      <c r="C460" s="139"/>
+      <c r="D460" s="160"/>
       <c r="E460" s="8" t="s">
         <v>584</v>
       </c>
@@ -15081,8 +15227,8 @@
       <c r="B461" s="7">
         <v>3</v>
       </c>
-      <c r="C461" s="160"/>
-      <c r="D461" s="156"/>
+      <c r="C461" s="139"/>
+      <c r="D461" s="160"/>
       <c r="E461" s="8" t="s">
         <v>585</v>
       </c>
@@ -15103,8 +15249,8 @@
       <c r="B462" s="7">
         <v>4</v>
       </c>
-      <c r="C462" s="160"/>
-      <c r="D462" s="156"/>
+      <c r="C462" s="139"/>
+      <c r="D462" s="160"/>
       <c r="E462" s="8" t="s">
         <v>586</v>
       </c>
@@ -15125,8 +15271,8 @@
       <c r="B463" s="7">
         <v>5</v>
       </c>
-      <c r="C463" s="160"/>
-      <c r="D463" s="156"/>
+      <c r="C463" s="139"/>
+      <c r="D463" s="160"/>
       <c r="E463" s="8" t="s">
         <v>587</v>
       </c>
@@ -15147,8 +15293,8 @@
       <c r="B464" s="7">
         <v>6</v>
       </c>
-      <c r="C464" s="160"/>
-      <c r="D464" s="156"/>
+      <c r="C464" s="139"/>
+      <c r="D464" s="160"/>
       <c r="E464" s="8" t="s">
         <v>588</v>
       </c>
@@ -15169,8 +15315,8 @@
       <c r="B465" s="7">
         <v>7</v>
       </c>
-      <c r="C465" s="160"/>
-      <c r="D465" s="156"/>
+      <c r="C465" s="139"/>
+      <c r="D465" s="160"/>
       <c r="E465" s="8" t="s">
         <v>589</v>
       </c>
@@ -15191,8 +15337,8 @@
       <c r="B466" s="7">
         <v>8</v>
       </c>
-      <c r="C466" s="160"/>
-      <c r="D466" s="157"/>
+      <c r="C466" s="139"/>
+      <c r="D466" s="161"/>
       <c r="E466" s="8" t="s">
         <v>590</v>
       </c>
@@ -15213,8 +15359,8 @@
       <c r="B467" s="7">
         <v>9</v>
       </c>
-      <c r="C467" s="160"/>
-      <c r="D467" s="135" t="s">
+      <c r="C467" s="139"/>
+      <c r="D467" s="159" t="s">
         <v>591</v>
       </c>
       <c r="E467" s="8" t="s">
@@ -15237,8 +15383,8 @@
       <c r="B468" s="7">
         <v>10</v>
       </c>
-      <c r="C468" s="160"/>
-      <c r="D468" s="156"/>
+      <c r="C468" s="139"/>
+      <c r="D468" s="160"/>
       <c r="E468" s="8" t="s">
         <v>593</v>
       </c>
@@ -15259,8 +15405,8 @@
       <c r="B469" s="7">
         <v>11</v>
       </c>
-      <c r="C469" s="160"/>
-      <c r="D469" s="156"/>
+      <c r="C469" s="139"/>
+      <c r="D469" s="160"/>
       <c r="E469" s="8" t="s">
         <v>594</v>
       </c>
@@ -15281,8 +15427,8 @@
       <c r="B470" s="7">
         <v>12</v>
       </c>
-      <c r="C470" s="160"/>
-      <c r="D470" s="156"/>
+      <c r="C470" s="139"/>
+      <c r="D470" s="160"/>
       <c r="E470" s="8" t="s">
         <v>595</v>
       </c>
@@ -15303,8 +15449,8 @@
       <c r="B471" s="7">
         <v>13</v>
       </c>
-      <c r="C471" s="160"/>
-      <c r="D471" s="156"/>
+      <c r="C471" s="139"/>
+      <c r="D471" s="160"/>
       <c r="E471" s="8" t="s">
         <v>596</v>
       </c>
@@ -15325,8 +15471,8 @@
       <c r="B472" s="7">
         <v>14</v>
       </c>
-      <c r="C472" s="160"/>
-      <c r="D472" s="156"/>
+      <c r="C472" s="139"/>
+      <c r="D472" s="160"/>
       <c r="E472" s="8" t="s">
         <v>597</v>
       </c>
@@ -15347,8 +15493,8 @@
       <c r="B473" s="7">
         <v>15</v>
       </c>
-      <c r="C473" s="160"/>
-      <c r="D473" s="157"/>
+      <c r="C473" s="139"/>
+      <c r="D473" s="161"/>
       <c r="E473" s="8" t="s">
         <v>598</v>
       </c>
@@ -15369,8 +15515,8 @@
       <c r="B474" s="7">
         <v>16</v>
       </c>
-      <c r="C474" s="160"/>
-      <c r="D474" s="135" t="s">
+      <c r="C474" s="139"/>
+      <c r="D474" s="159" t="s">
         <v>599</v>
       </c>
       <c r="E474" s="8" t="s">
@@ -15393,8 +15539,8 @@
       <c r="B475" s="7">
         <v>17</v>
       </c>
-      <c r="C475" s="160"/>
-      <c r="D475" s="156"/>
+      <c r="C475" s="139"/>
+      <c r="D475" s="160"/>
       <c r="E475" s="8" t="s">
         <v>601</v>
       </c>
@@ -15415,8 +15561,8 @@
       <c r="B476" s="7">
         <v>18</v>
       </c>
-      <c r="C476" s="160"/>
-      <c r="D476" s="156"/>
+      <c r="C476" s="139"/>
+      <c r="D476" s="160"/>
       <c r="E476" s="8" t="s">
         <v>602</v>
       </c>
@@ -15437,8 +15583,8 @@
       <c r="B477" s="7">
         <v>19</v>
       </c>
-      <c r="C477" s="160"/>
-      <c r="D477" s="156"/>
+      <c r="C477" s="139"/>
+      <c r="D477" s="160"/>
       <c r="E477" s="8" t="s">
         <v>603</v>
       </c>
@@ -15459,8 +15605,8 @@
       <c r="B478" s="7">
         <v>20</v>
       </c>
-      <c r="C478" s="160"/>
-      <c r="D478" s="156"/>
+      <c r="C478" s="139"/>
+      <c r="D478" s="160"/>
       <c r="E478" s="8" t="s">
         <v>604</v>
       </c>
@@ -15481,8 +15627,8 @@
       <c r="B479" s="7">
         <v>21</v>
       </c>
-      <c r="C479" s="160"/>
-      <c r="D479" s="156"/>
+      <c r="C479" s="139"/>
+      <c r="D479" s="160"/>
       <c r="E479" s="8" t="s">
         <v>605</v>
       </c>
@@ -15503,8 +15649,8 @@
       <c r="B480" s="7">
         <v>22</v>
       </c>
-      <c r="C480" s="160"/>
-      <c r="D480" s="156"/>
+      <c r="C480" s="139"/>
+      <c r="D480" s="160"/>
       <c r="E480" s="8" t="s">
         <v>606</v>
       </c>
@@ -15525,8 +15671,8 @@
       <c r="B481" s="7">
         <v>23</v>
       </c>
-      <c r="C481" s="160"/>
-      <c r="D481" s="157"/>
+      <c r="C481" s="139"/>
+      <c r="D481" s="161"/>
       <c r="E481" s="8" t="s">
         <v>607</v>
       </c>
@@ -15547,8 +15693,8 @@
       <c r="B482" s="7">
         <v>24</v>
       </c>
-      <c r="C482" s="160"/>
-      <c r="D482" s="135" t="s">
+      <c r="C482" s="139"/>
+      <c r="D482" s="159" t="s">
         <v>608</v>
       </c>
       <c r="E482" s="8" t="s">
@@ -15571,8 +15717,8 @@
       <c r="B483" s="7">
         <v>25</v>
       </c>
-      <c r="C483" s="160"/>
-      <c r="D483" s="156"/>
+      <c r="C483" s="139"/>
+      <c r="D483" s="160"/>
       <c r="E483" s="8" t="s">
         <v>610</v>
       </c>
@@ -15593,8 +15739,8 @@
       <c r="B484" s="7">
         <v>26</v>
       </c>
-      <c r="C484" s="160"/>
-      <c r="D484" s="156"/>
+      <c r="C484" s="139"/>
+      <c r="D484" s="160"/>
       <c r="E484" s="8" t="s">
         <v>611</v>
       </c>
@@ -15615,8 +15761,8 @@
       <c r="B485" s="7">
         <v>27</v>
       </c>
-      <c r="C485" s="160"/>
-      <c r="D485" s="157"/>
+      <c r="C485" s="139"/>
+      <c r="D485" s="161"/>
       <c r="E485" s="8" t="s">
         <v>612</v>
       </c>
@@ -15637,8 +15783,8 @@
       <c r="B486" s="7">
         <v>28</v>
       </c>
-      <c r="C486" s="160"/>
-      <c r="D486" s="135" t="s">
+      <c r="C486" s="139"/>
+      <c r="D486" s="159" t="s">
         <v>613</v>
       </c>
       <c r="E486" s="8" t="s">
@@ -15661,8 +15807,8 @@
       <c r="B487" s="7">
         <v>29</v>
       </c>
-      <c r="C487" s="160"/>
-      <c r="D487" s="156"/>
+      <c r="C487" s="139"/>
+      <c r="D487" s="160"/>
       <c r="E487" s="8" t="s">
         <v>615</v>
       </c>
@@ -15683,8 +15829,8 @@
       <c r="B488" s="7">
         <v>30</v>
       </c>
-      <c r="C488" s="160"/>
-      <c r="D488" s="156"/>
+      <c r="C488" s="139"/>
+      <c r="D488" s="160"/>
       <c r="E488" s="8" t="s">
         <v>616</v>
       </c>
@@ -15705,8 +15851,8 @@
       <c r="B489" s="7">
         <v>31</v>
       </c>
-      <c r="C489" s="160"/>
-      <c r="D489" s="156"/>
+      <c r="C489" s="139"/>
+      <c r="D489" s="160"/>
       <c r="E489" s="8" t="s">
         <v>617</v>
       </c>
@@ -15727,8 +15873,8 @@
       <c r="B490" s="7">
         <v>32</v>
       </c>
-      <c r="C490" s="160"/>
-      <c r="D490" s="156"/>
+      <c r="C490" s="139"/>
+      <c r="D490" s="160"/>
       <c r="E490" s="8" t="s">
         <v>618</v>
       </c>
@@ -15749,8 +15895,8 @@
       <c r="B491" s="7">
         <v>33</v>
       </c>
-      <c r="C491" s="160"/>
-      <c r="D491" s="156"/>
+      <c r="C491" s="139"/>
+      <c r="D491" s="160"/>
       <c r="E491" s="8" t="s">
         <v>619</v>
       </c>
@@ -15771,8 +15917,8 @@
       <c r="B492" s="7">
         <v>34</v>
       </c>
-      <c r="C492" s="160"/>
-      <c r="D492" s="156"/>
+      <c r="C492" s="139"/>
+      <c r="D492" s="160"/>
       <c r="E492" s="8" t="s">
         <v>620</v>
       </c>
@@ -15793,8 +15939,8 @@
       <c r="B493" s="7">
         <v>35</v>
       </c>
-      <c r="C493" s="160"/>
-      <c r="D493" s="156"/>
+      <c r="C493" s="139"/>
+      <c r="D493" s="160"/>
       <c r="E493" s="8" t="s">
         <v>621</v>
       </c>
@@ -15815,8 +15961,8 @@
       <c r="B494" s="7">
         <v>36</v>
       </c>
-      <c r="C494" s="160"/>
-      <c r="D494" s="156"/>
+      <c r="C494" s="139"/>
+      <c r="D494" s="160"/>
       <c r="E494" s="8" t="s">
         <v>622</v>
       </c>
@@ -15837,8 +15983,8 @@
       <c r="B495" s="7">
         <v>37</v>
       </c>
-      <c r="C495" s="160"/>
-      <c r="D495" s="156"/>
+      <c r="C495" s="139"/>
+      <c r="D495" s="160"/>
       <c r="E495" s="8" t="s">
         <v>623</v>
       </c>
@@ -15859,8 +16005,8 @@
       <c r="B496" s="7">
         <v>38</v>
       </c>
-      <c r="C496" s="160"/>
-      <c r="D496" s="157"/>
+      <c r="C496" s="139"/>
+      <c r="D496" s="161"/>
       <c r="E496" s="8" t="s">
         <v>624</v>
       </c>
@@ -15881,8 +16027,8 @@
       <c r="B497" s="7">
         <v>39</v>
       </c>
-      <c r="C497" s="160"/>
-      <c r="D497" s="135" t="s">
+      <c r="C497" s="139"/>
+      <c r="D497" s="159" t="s">
         <v>625</v>
       </c>
       <c r="E497" s="8" t="s">
@@ -15905,8 +16051,8 @@
       <c r="B498" s="7">
         <v>40</v>
       </c>
-      <c r="C498" s="160"/>
-      <c r="D498" s="156"/>
+      <c r="C498" s="139"/>
+      <c r="D498" s="160"/>
       <c r="E498" s="8" t="s">
         <v>626</v>
       </c>
@@ -15927,8 +16073,8 @@
       <c r="B499" s="7">
         <v>41</v>
       </c>
-      <c r="C499" s="160"/>
-      <c r="D499" s="156"/>
+      <c r="C499" s="139"/>
+      <c r="D499" s="160"/>
       <c r="E499" s="8" t="s">
         <v>627</v>
       </c>
@@ -15949,8 +16095,8 @@
       <c r="B500" s="7">
         <v>42</v>
       </c>
-      <c r="C500" s="160"/>
-      <c r="D500" s="156"/>
+      <c r="C500" s="139"/>
+      <c r="D500" s="160"/>
       <c r="E500" s="8" t="s">
         <v>628</v>
       </c>
@@ -15971,8 +16117,8 @@
       <c r="B501" s="7">
         <v>43</v>
       </c>
-      <c r="C501" s="160"/>
-      <c r="D501" s="156"/>
+      <c r="C501" s="139"/>
+      <c r="D501" s="160"/>
       <c r="E501" s="8" t="s">
         <v>629</v>
       </c>
@@ -15993,8 +16139,8 @@
       <c r="B502" s="7">
         <v>44</v>
       </c>
-      <c r="C502" s="160"/>
-      <c r="D502" s="157"/>
+      <c r="C502" s="139"/>
+      <c r="D502" s="161"/>
       <c r="E502" s="8" t="s">
         <v>630</v>
       </c>
@@ -16015,8 +16161,8 @@
       <c r="B503" s="7">
         <v>45</v>
       </c>
-      <c r="C503" s="160"/>
-      <c r="D503" s="135" t="s">
+      <c r="C503" s="139"/>
+      <c r="D503" s="159" t="s">
         <v>631</v>
       </c>
       <c r="E503" s="8" t="s">
@@ -16039,8 +16185,8 @@
       <c r="B504" s="7">
         <v>46</v>
       </c>
-      <c r="C504" s="160"/>
-      <c r="D504" s="156"/>
+      <c r="C504" s="139"/>
+      <c r="D504" s="160"/>
       <c r="E504" s="8" t="s">
         <v>633</v>
       </c>
@@ -16061,8 +16207,8 @@
       <c r="B505" s="7">
         <v>47</v>
       </c>
-      <c r="C505" s="160"/>
-      <c r="D505" s="156"/>
+      <c r="C505" s="139"/>
+      <c r="D505" s="160"/>
       <c r="E505" s="8" t="s">
         <v>634</v>
       </c>
@@ -16083,8 +16229,8 @@
       <c r="B506" s="7">
         <v>48</v>
       </c>
-      <c r="C506" s="160"/>
-      <c r="D506" s="156"/>
+      <c r="C506" s="139"/>
+      <c r="D506" s="160"/>
       <c r="E506" s="8" t="s">
         <v>635</v>
       </c>
@@ -16105,8 +16251,8 @@
       <c r="B507" s="7">
         <v>49</v>
       </c>
-      <c r="C507" s="160"/>
-      <c r="D507" s="156"/>
+      <c r="C507" s="139"/>
+      <c r="D507" s="160"/>
       <c r="E507" s="8" t="s">
         <v>636</v>
       </c>
@@ -16127,8 +16273,8 @@
       <c r="B508" s="7">
         <v>50</v>
       </c>
-      <c r="C508" s="160"/>
-      <c r="D508" s="156"/>
+      <c r="C508" s="139"/>
+      <c r="D508" s="160"/>
       <c r="E508" s="8" t="s">
         <v>637</v>
       </c>
@@ -16149,8 +16295,8 @@
       <c r="B509" s="7">
         <v>51</v>
       </c>
-      <c r="C509" s="160"/>
-      <c r="D509" s="157"/>
+      <c r="C509" s="139"/>
+      <c r="D509" s="161"/>
       <c r="E509" s="8" t="s">
         <v>638</v>
       </c>
@@ -16171,8 +16317,8 @@
       <c r="B510" s="7">
         <v>52</v>
       </c>
-      <c r="C510" s="160"/>
-      <c r="D510" s="135" t="s">
+      <c r="C510" s="139"/>
+      <c r="D510" s="159" t="s">
         <v>639</v>
       </c>
       <c r="E510" s="8" t="s">
@@ -16195,8 +16341,8 @@
       <c r="B511" s="7">
         <v>53</v>
       </c>
-      <c r="C511" s="160"/>
-      <c r="D511" s="156"/>
+      <c r="C511" s="139"/>
+      <c r="D511" s="160"/>
       <c r="E511" s="8" t="s">
         <v>641</v>
       </c>
@@ -16217,8 +16363,8 @@
       <c r="B512" s="7">
         <v>54</v>
       </c>
-      <c r="C512" s="160"/>
-      <c r="D512" s="156"/>
+      <c r="C512" s="139"/>
+      <c r="D512" s="160"/>
       <c r="E512" s="8" t="s">
         <v>642</v>
       </c>
@@ -16239,8 +16385,8 @@
       <c r="B513" s="24">
         <v>55</v>
       </c>
-      <c r="C513" s="161"/>
-      <c r="D513" s="157"/>
+      <c r="C513" s="140"/>
+      <c r="D513" s="161"/>
       <c r="E513" s="17" t="s">
         <v>643</v>
       </c>
@@ -23174,6 +23320,107 @@
     </row>
   </sheetData>
   <mergeCells count="125">
+    <mergeCell ref="D26:D32"/>
+    <mergeCell ref="D33:D36"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="C4:C32"/>
+    <mergeCell ref="D4:D9"/>
+    <mergeCell ref="D10:D18"/>
+    <mergeCell ref="D19:D25"/>
+    <mergeCell ref="C33:C44"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="D40:D44"/>
+    <mergeCell ref="C107:C116"/>
+    <mergeCell ref="C117:C125"/>
+    <mergeCell ref="C127:C132"/>
+    <mergeCell ref="C134:C176"/>
+    <mergeCell ref="C177:C204"/>
+    <mergeCell ref="C205:C214"/>
+    <mergeCell ref="A106:J106"/>
+    <mergeCell ref="D107:D111"/>
+    <mergeCell ref="D112:D115"/>
+    <mergeCell ref="D117:D120"/>
+    <mergeCell ref="D121:D122"/>
+    <mergeCell ref="D123:D125"/>
+    <mergeCell ref="A126:J126"/>
+    <mergeCell ref="D127:D130"/>
+    <mergeCell ref="D131:D132"/>
+    <mergeCell ref="A133:J133"/>
+    <mergeCell ref="D210:D211"/>
+    <mergeCell ref="D212:D214"/>
+    <mergeCell ref="C45:C50"/>
+    <mergeCell ref="D45:D50"/>
+    <mergeCell ref="D51:D57"/>
+    <mergeCell ref="D58:D63"/>
+    <mergeCell ref="D64:D67"/>
+    <mergeCell ref="D69:D78"/>
+    <mergeCell ref="D79:D84"/>
+    <mergeCell ref="D85:D90"/>
+    <mergeCell ref="D91:D105"/>
+    <mergeCell ref="A68:J68"/>
+    <mergeCell ref="C51:C67"/>
+    <mergeCell ref="C69:C105"/>
+    <mergeCell ref="A215:J215"/>
+    <mergeCell ref="A273:J273"/>
+    <mergeCell ref="A358:J358"/>
+    <mergeCell ref="D134:D136"/>
+    <mergeCell ref="D137:D143"/>
+    <mergeCell ref="D144:D150"/>
+    <mergeCell ref="D151:D156"/>
+    <mergeCell ref="D157:D159"/>
+    <mergeCell ref="D160:D165"/>
+    <mergeCell ref="D166:D172"/>
+    <mergeCell ref="D173:D176"/>
+    <mergeCell ref="D177:D178"/>
+    <mergeCell ref="D179:D184"/>
+    <mergeCell ref="D185:D186"/>
+    <mergeCell ref="D187:D190"/>
+    <mergeCell ref="D191:D198"/>
+    <mergeCell ref="D199:D202"/>
+    <mergeCell ref="D203:D204"/>
+    <mergeCell ref="D205:D209"/>
+    <mergeCell ref="D216:D225"/>
+    <mergeCell ref="D226:D233"/>
+    <mergeCell ref="D234:D240"/>
+    <mergeCell ref="D241:D243"/>
+    <mergeCell ref="D244:D249"/>
+    <mergeCell ref="D442:D445"/>
+    <mergeCell ref="D446:D448"/>
+    <mergeCell ref="D400:D404"/>
+    <mergeCell ref="D405:D416"/>
+    <mergeCell ref="A436:J436"/>
+    <mergeCell ref="D359:D363"/>
+    <mergeCell ref="D364:D371"/>
+    <mergeCell ref="D372:D375"/>
+    <mergeCell ref="D376:D380"/>
+    <mergeCell ref="D381:D386"/>
+    <mergeCell ref="D387:D396"/>
+    <mergeCell ref="D397:D399"/>
+    <mergeCell ref="D301:D303"/>
+    <mergeCell ref="D304:D307"/>
+    <mergeCell ref="D308:D314"/>
+    <mergeCell ref="D315:D317"/>
+    <mergeCell ref="C343:C357"/>
+    <mergeCell ref="C359:C380"/>
+    <mergeCell ref="C381:C435"/>
+    <mergeCell ref="C437:C458"/>
+    <mergeCell ref="D250:D257"/>
+    <mergeCell ref="D258:D259"/>
+    <mergeCell ref="D260:D265"/>
+    <mergeCell ref="D266:D270"/>
+    <mergeCell ref="D271:D272"/>
+    <mergeCell ref="D274:D281"/>
+    <mergeCell ref="D282:D288"/>
+    <mergeCell ref="D289:D292"/>
+    <mergeCell ref="D293:D295"/>
+    <mergeCell ref="D449:D452"/>
+    <mergeCell ref="D453:D458"/>
+    <mergeCell ref="D417:D419"/>
+    <mergeCell ref="D420:D426"/>
+    <mergeCell ref="D427:D430"/>
+    <mergeCell ref="D431:D435"/>
+    <mergeCell ref="D437:D441"/>
     <mergeCell ref="C459:C513"/>
     <mergeCell ref="C216:C249"/>
     <mergeCell ref="C250:C265"/>
@@ -23198,107 +23445,6 @@
     <mergeCell ref="D348:D353"/>
     <mergeCell ref="D354:D357"/>
     <mergeCell ref="D296:D300"/>
-    <mergeCell ref="D301:D303"/>
-    <mergeCell ref="D304:D307"/>
-    <mergeCell ref="D308:D314"/>
-    <mergeCell ref="D315:D317"/>
-    <mergeCell ref="C343:C357"/>
-    <mergeCell ref="C359:C380"/>
-    <mergeCell ref="C381:C435"/>
-    <mergeCell ref="C437:C458"/>
-    <mergeCell ref="D250:D257"/>
-    <mergeCell ref="D258:D259"/>
-    <mergeCell ref="D260:D265"/>
-    <mergeCell ref="D266:D270"/>
-    <mergeCell ref="D271:D272"/>
-    <mergeCell ref="D274:D281"/>
-    <mergeCell ref="D282:D288"/>
-    <mergeCell ref="D289:D292"/>
-    <mergeCell ref="D293:D295"/>
-    <mergeCell ref="D449:D452"/>
-    <mergeCell ref="D453:D458"/>
-    <mergeCell ref="D417:D419"/>
-    <mergeCell ref="D420:D426"/>
-    <mergeCell ref="D427:D430"/>
-    <mergeCell ref="D431:D435"/>
-    <mergeCell ref="D437:D441"/>
-    <mergeCell ref="D442:D445"/>
-    <mergeCell ref="D446:D448"/>
-    <mergeCell ref="D400:D404"/>
-    <mergeCell ref="D405:D416"/>
-    <mergeCell ref="A436:J436"/>
-    <mergeCell ref="D359:D363"/>
-    <mergeCell ref="D364:D371"/>
-    <mergeCell ref="D372:D375"/>
-    <mergeCell ref="D376:D380"/>
-    <mergeCell ref="D381:D386"/>
-    <mergeCell ref="D387:D396"/>
-    <mergeCell ref="D397:D399"/>
-    <mergeCell ref="A215:J215"/>
-    <mergeCell ref="A273:J273"/>
-    <mergeCell ref="A358:J358"/>
-    <mergeCell ref="D134:D136"/>
-    <mergeCell ref="D137:D143"/>
-    <mergeCell ref="D144:D150"/>
-    <mergeCell ref="D151:D156"/>
-    <mergeCell ref="D157:D159"/>
-    <mergeCell ref="D160:D165"/>
-    <mergeCell ref="D166:D172"/>
-    <mergeCell ref="D173:D176"/>
-    <mergeCell ref="D177:D178"/>
-    <mergeCell ref="D179:D184"/>
-    <mergeCell ref="D185:D186"/>
-    <mergeCell ref="D187:D190"/>
-    <mergeCell ref="D191:D198"/>
-    <mergeCell ref="D199:D202"/>
-    <mergeCell ref="D203:D204"/>
-    <mergeCell ref="D205:D209"/>
-    <mergeCell ref="D216:D225"/>
-    <mergeCell ref="D226:D233"/>
-    <mergeCell ref="D234:D240"/>
-    <mergeCell ref="D241:D243"/>
-    <mergeCell ref="D244:D249"/>
-    <mergeCell ref="C45:C50"/>
-    <mergeCell ref="D45:D50"/>
-    <mergeCell ref="D51:D57"/>
-    <mergeCell ref="D58:D63"/>
-    <mergeCell ref="D64:D67"/>
-    <mergeCell ref="D69:D78"/>
-    <mergeCell ref="D79:D84"/>
-    <mergeCell ref="D85:D90"/>
-    <mergeCell ref="D91:D105"/>
-    <mergeCell ref="A68:J68"/>
-    <mergeCell ref="C51:C67"/>
-    <mergeCell ref="C69:C105"/>
-    <mergeCell ref="C107:C116"/>
-    <mergeCell ref="C117:C125"/>
-    <mergeCell ref="C127:C132"/>
-    <mergeCell ref="C134:C176"/>
-    <mergeCell ref="C177:C204"/>
-    <mergeCell ref="C205:C214"/>
-    <mergeCell ref="A106:J106"/>
-    <mergeCell ref="D107:D111"/>
-    <mergeCell ref="D112:D115"/>
-    <mergeCell ref="D117:D120"/>
-    <mergeCell ref="D121:D122"/>
-    <mergeCell ref="D123:D125"/>
-    <mergeCell ref="A126:J126"/>
-    <mergeCell ref="D127:D130"/>
-    <mergeCell ref="D131:D132"/>
-    <mergeCell ref="A133:J133"/>
-    <mergeCell ref="D210:D211"/>
-    <mergeCell ref="D212:D214"/>
-    <mergeCell ref="D26:D32"/>
-    <mergeCell ref="D33:D36"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="C4:C32"/>
-    <mergeCell ref="D4:D9"/>
-    <mergeCell ref="D10:D18"/>
-    <mergeCell ref="D19:D25"/>
-    <mergeCell ref="C33:C44"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="D40:D44"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H67 H69:H105 H107:H125 H127:H132 H134:H214 H216:H272 H274:H357 H359:H435 H437:H513" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -23827,16 +23973,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="31.5" customHeight="1">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="189" t="s">
         <v>644</v>
       </c>
-      <c r="B1" s="152"/>
+      <c r="B1" s="190"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1">
-      <c r="A2" s="153" t="s">
+      <c r="A2" s="191" t="s">
         <v>645</v>
       </c>
-      <c r="B2" s="152"/>
+      <c r="B2" s="190"/>
     </row>
     <row r="3" spans="1:2" ht="18" customHeight="1">
       <c r="A3" s="46" t="s">
@@ -23883,10 +24029,10 @@
       <c r="B8" s="47"/>
     </row>
     <row r="9" spans="1:2" ht="18" customHeight="1">
-      <c r="A9" s="153" t="s">
+      <c r="A9" s="191" t="s">
         <v>656</v>
       </c>
-      <c r="B9" s="152"/>
+      <c r="B9" s="190"/>
     </row>
     <row r="10" spans="1:2" ht="18" customHeight="1">
       <c r="A10" s="52" t="s">
@@ -23965,10 +24111,10 @@
       <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:2" ht="18" customHeight="1">
-      <c r="A20" s="153" t="s">
+      <c r="A20" s="191" t="s">
         <v>675</v>
       </c>
-      <c r="B20" s="152"/>
+      <c r="B20" s="190"/>
     </row>
     <row r="21" spans="1:2" ht="18" customHeight="1">
       <c r="A21" s="52" t="s">
@@ -24965,15 +25111,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="154" t="s">
+      <c r="A1" s="192" t="s">
         <v>678</v>
       </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="152"/>
+      <c r="B1" s="193"/>
+      <c r="C1" s="193"/>
+      <c r="D1" s="193"/>
+      <c r="E1" s="193"/>
+      <c r="F1" s="193"/>
+      <c r="G1" s="190"/>
     </row>
     <row r="2" spans="1:8" ht="13.2">
       <c r="A2" s="53" t="s">

--- a/DSA Master Sheet.xlsx
+++ b/DSA Master Sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\OneDrive\Desktop\DSA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aamer\Desktop\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B7707A-2786-47BF-B3A4-7825A85D6518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4617297E-C261-4D43-81D8-616C18D54CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="724">
   <si>
     <t>DSA Master Sheet</t>
   </si>
@@ -2796,16 +2796,32 @@
         return sum;</t>
     </r>
   </si>
+  <si>
+    <t>Start checking palindrome from the center character.
+Assume every index is a center (i = 0 to n-1).
+Expand for odd palindrome → (i, i).
+Expand for even palindrome → (i-1, i).
+Expand left and right while characters are equal.
+Extract using substring(low + 1, high).
+Keep the longest palindrome and return it.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="98">
+  <fonts count="99">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3888,364 +3904,367 @@
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="86" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="87" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="87" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="196">
+  <cellXfs count="197">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="31" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="33" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="34" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="20" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="20" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="22" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="22" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="24" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="24" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="28" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="28" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="29" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="29" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="31" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="31" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="32" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="32" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="37" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="37" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="38" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="38" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="38" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="38" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="39" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="39" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="40" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="40" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="67" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="41" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="41" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="42" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="68" fillId="42" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="42" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="42" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="43" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="43" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="44" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="44" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="44" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="71" fillId="44" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="45" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="45" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="46" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="46" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="46" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="46" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="47" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="47" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="48" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="48" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="49" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="49" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="49" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="77" fillId="49" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="50" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="50" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="51" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="78" fillId="51" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="51" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="79" fillId="51" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="80" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="81" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="86" fillId="52" borderId="6" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="87" fillId="53" borderId="6" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="88" fillId="54" borderId="6" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="87" fillId="52" borderId="6" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="88" fillId="53" borderId="6" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="89" fillId="54" borderId="6" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4254,184 +4273,182 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="87" fillId="52" borderId="8" xfId="2" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
@@ -4669,18 +4686,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="30.75" customHeight="1">
-      <c r="A1" s="186" t="s">
+      <c r="A1" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="187"/>
-      <c r="C1" s="187"/>
-      <c r="D1" s="187"/>
-      <c r="E1" s="187"/>
-      <c r="F1" s="187"/>
-      <c r="G1" s="187"/>
-      <c r="H1" s="187"/>
-      <c r="I1" s="187"/>
-      <c r="J1" s="188"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="145"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -4735,18 +4752,18 @@
       <c r="T2" s="5"/>
     </row>
     <row r="3" spans="1:20" ht="13.8">
-      <c r="A3" s="183" t="s">
+      <c r="A3" s="146" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="184"/>
-      <c r="C3" s="184"/>
-      <c r="D3" s="184"/>
-      <c r="E3" s="184"/>
-      <c r="F3" s="184"/>
-      <c r="G3" s="184"/>
-      <c r="H3" s="184"/>
-      <c r="I3" s="184"/>
-      <c r="J3" s="185"/>
+      <c r="B3" s="147"/>
+      <c r="C3" s="147"/>
+      <c r="D3" s="147"/>
+      <c r="E3" s="147"/>
+      <c r="F3" s="147"/>
+      <c r="G3" s="147"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="148"/>
     </row>
     <row r="4" spans="1:20" ht="13.8">
       <c r="A4" s="6">
@@ -4755,10 +4772,10 @@
       <c r="B4" s="7">
         <v>1</v>
       </c>
-      <c r="C4" s="144" t="s">
+      <c r="C4" s="149" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="159" t="s">
+      <c r="D4" s="140" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -4788,8 +4805,8 @@
       <c r="B5" s="7">
         <v>2</v>
       </c>
-      <c r="C5" s="145"/>
-      <c r="D5" s="160"/>
+      <c r="C5" s="150"/>
+      <c r="D5" s="141"/>
       <c r="E5" s="8" t="s">
         <v>16</v>
       </c>
@@ -4817,8 +4834,8 @@
       <c r="B6" s="7">
         <v>3</v>
       </c>
-      <c r="C6" s="145"/>
-      <c r="D6" s="160"/>
+      <c r="C6" s="150"/>
+      <c r="D6" s="141"/>
       <c r="E6" s="8" t="s">
         <v>19</v>
       </c>
@@ -4846,8 +4863,8 @@
       <c r="B7" s="7">
         <v>4</v>
       </c>
-      <c r="C7" s="145"/>
-      <c r="D7" s="160"/>
+      <c r="C7" s="150"/>
+      <c r="D7" s="141"/>
       <c r="E7" s="8" t="s">
         <v>23</v>
       </c>
@@ -4875,8 +4892,8 @@
       <c r="B8" s="7">
         <v>5</v>
       </c>
-      <c r="C8" s="145"/>
-      <c r="D8" s="160"/>
+      <c r="C8" s="150"/>
+      <c r="D8" s="141"/>
       <c r="E8" s="8" t="s">
         <v>26</v>
       </c>
@@ -4904,8 +4921,8 @@
       <c r="B9" s="7">
         <v>6</v>
       </c>
-      <c r="C9" s="145"/>
-      <c r="D9" s="161"/>
+      <c r="C9" s="150"/>
+      <c r="D9" s="142"/>
       <c r="E9" s="8" t="s">
         <v>29</v>
       </c>
@@ -4930,8 +4947,8 @@
       <c r="B10" s="7">
         <v>7</v>
       </c>
-      <c r="C10" s="145"/>
-      <c r="D10" s="159" t="s">
+      <c r="C10" s="150"/>
+      <c r="D10" s="140" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="8" t="s">
@@ -4958,8 +4975,8 @@
       <c r="B11" s="7">
         <v>8</v>
       </c>
-      <c r="C11" s="145"/>
-      <c r="D11" s="160"/>
+      <c r="C11" s="150"/>
+      <c r="D11" s="141"/>
       <c r="E11" s="13" t="s">
         <v>32</v>
       </c>
@@ -4984,8 +5001,8 @@
       <c r="B12" s="7">
         <v>9</v>
       </c>
-      <c r="C12" s="145"/>
-      <c r="D12" s="160"/>
+      <c r="C12" s="150"/>
+      <c r="D12" s="141"/>
       <c r="E12" s="8" t="s">
         <v>33</v>
       </c>
@@ -5010,8 +5027,8 @@
       <c r="B13" s="7">
         <v>10</v>
       </c>
-      <c r="C13" s="145"/>
-      <c r="D13" s="160"/>
+      <c r="C13" s="150"/>
+      <c r="D13" s="141"/>
       <c r="E13" s="8" t="s">
         <v>34</v>
       </c>
@@ -5038,8 +5055,8 @@
       <c r="B14" s="7">
         <v>11</v>
       </c>
-      <c r="C14" s="145"/>
-      <c r="D14" s="160"/>
+      <c r="C14" s="150"/>
+      <c r="D14" s="141"/>
       <c r="E14" s="8" t="s">
         <v>35</v>
       </c>
@@ -5064,8 +5081,8 @@
       <c r="B15" s="7">
         <v>12</v>
       </c>
-      <c r="C15" s="145"/>
-      <c r="D15" s="160"/>
+      <c r="C15" s="150"/>
+      <c r="D15" s="141"/>
       <c r="E15" s="8" t="s">
         <v>36</v>
       </c>
@@ -5092,8 +5109,8 @@
       <c r="B16" s="7">
         <v>13</v>
       </c>
-      <c r="C16" s="145"/>
-      <c r="D16" s="160"/>
+      <c r="C16" s="150"/>
+      <c r="D16" s="141"/>
       <c r="E16" s="8" t="s">
         <v>37</v>
       </c>
@@ -5118,8 +5135,8 @@
       <c r="B17" s="7">
         <v>14</v>
       </c>
-      <c r="C17" s="145"/>
-      <c r="D17" s="160"/>
+      <c r="C17" s="150"/>
+      <c r="D17" s="141"/>
       <c r="E17" s="8" t="s">
         <v>38</v>
       </c>
@@ -5146,8 +5163,8 @@
       <c r="B18" s="7">
         <v>15</v>
       </c>
-      <c r="C18" s="145"/>
-      <c r="D18" s="161"/>
+      <c r="C18" s="150"/>
+      <c r="D18" s="142"/>
       <c r="E18" s="13" t="s">
         <v>39</v>
       </c>
@@ -5174,8 +5191,8 @@
       <c r="B19" s="7">
         <v>16</v>
       </c>
-      <c r="C19" s="145"/>
-      <c r="D19" s="159" t="s">
+      <c r="C19" s="150"/>
+      <c r="D19" s="140" t="s">
         <v>40</v>
       </c>
       <c r="E19" s="8" t="s">
@@ -5204,8 +5221,8 @@
       <c r="B20" s="7">
         <v>17</v>
       </c>
-      <c r="C20" s="145"/>
-      <c r="D20" s="160"/>
+      <c r="C20" s="150"/>
+      <c r="D20" s="141"/>
       <c r="E20" s="8" t="s">
         <v>42</v>
       </c>
@@ -5232,8 +5249,8 @@
       <c r="B21" s="7">
         <v>18</v>
       </c>
-      <c r="C21" s="145"/>
-      <c r="D21" s="160"/>
+      <c r="C21" s="150"/>
+      <c r="D21" s="141"/>
       <c r="E21" s="8" t="s">
         <v>43</v>
       </c>
@@ -5260,8 +5277,8 @@
       <c r="B22" s="7">
         <v>19</v>
       </c>
-      <c r="C22" s="145"/>
-      <c r="D22" s="160"/>
+      <c r="C22" s="150"/>
+      <c r="D22" s="141"/>
       <c r="E22" s="8" t="s">
         <v>44</v>
       </c>
@@ -5282,8 +5299,8 @@
       <c r="B23" s="7">
         <v>20</v>
       </c>
-      <c r="C23" s="145"/>
-      <c r="D23" s="160"/>
+      <c r="C23" s="150"/>
+      <c r="D23" s="141"/>
       <c r="E23" s="8" t="s">
         <v>45</v>
       </c>
@@ -5304,8 +5321,8 @@
       <c r="B24" s="7">
         <v>21</v>
       </c>
-      <c r="C24" s="145"/>
-      <c r="D24" s="160"/>
+      <c r="C24" s="150"/>
+      <c r="D24" s="141"/>
       <c r="E24" s="13" t="s">
         <v>46</v>
       </c>
@@ -5330,8 +5347,8 @@
       <c r="B25" s="7">
         <v>22</v>
       </c>
-      <c r="C25" s="145"/>
-      <c r="D25" s="161"/>
+      <c r="C25" s="150"/>
+      <c r="D25" s="142"/>
       <c r="E25" s="8" t="s">
         <v>47</v>
       </c>
@@ -5358,8 +5375,8 @@
       <c r="B26" s="7">
         <v>23</v>
       </c>
-      <c r="C26" s="145"/>
-      <c r="D26" s="159" t="s">
+      <c r="C26" s="150"/>
+      <c r="D26" s="140" t="s">
         <v>48</v>
       </c>
       <c r="E26" s="13" t="s">
@@ -5388,8 +5405,8 @@
       <c r="B27" s="7">
         <v>24</v>
       </c>
-      <c r="C27" s="145"/>
-      <c r="D27" s="160"/>
+      <c r="C27" s="150"/>
+      <c r="D27" s="141"/>
       <c r="E27" s="8" t="s">
         <v>50</v>
       </c>
@@ -5399,7 +5416,7 @@
       <c r="G27" s="10">
         <v>4</v>
       </c>
-      <c r="H27" s="194" t="s">
+      <c r="H27" s="138" t="s">
         <v>720</v>
       </c>
       <c r="I27" s="131"/>
@@ -5414,8 +5431,8 @@
       <c r="B28" s="7">
         <v>25</v>
       </c>
-      <c r="C28" s="145"/>
-      <c r="D28" s="160"/>
+      <c r="C28" s="150"/>
+      <c r="D28" s="141"/>
       <c r="E28" s="8" t="s">
         <v>51</v>
       </c>
@@ -5442,8 +5459,8 @@
       <c r="B29" s="7">
         <v>26</v>
       </c>
-      <c r="C29" s="145"/>
-      <c r="D29" s="160"/>
+      <c r="C29" s="150"/>
+      <c r="D29" s="141"/>
       <c r="E29" s="8" t="s">
         <v>52</v>
       </c>
@@ -5464,8 +5481,8 @@
       <c r="B30" s="7">
         <v>27</v>
       </c>
-      <c r="C30" s="145"/>
-      <c r="D30" s="160"/>
+      <c r="C30" s="150"/>
+      <c r="D30" s="141"/>
       <c r="E30" s="8" t="s">
         <v>53</v>
       </c>
@@ -5486,8 +5503,8 @@
       <c r="B31" s="7">
         <v>28</v>
       </c>
-      <c r="C31" s="145"/>
-      <c r="D31" s="160"/>
+      <c r="C31" s="150"/>
+      <c r="D31" s="141"/>
       <c r="E31" s="8" t="s">
         <v>54</v>
       </c>
@@ -5508,8 +5525,8 @@
       <c r="B32" s="7">
         <v>29</v>
       </c>
-      <c r="C32" s="146"/>
-      <c r="D32" s="161"/>
+      <c r="C32" s="151"/>
+      <c r="D32" s="142"/>
       <c r="E32" s="17" t="s">
         <v>55</v>
       </c>
@@ -5530,10 +5547,10 @@
       <c r="B33" s="22">
         <v>1</v>
       </c>
-      <c r="C33" s="147" t="s">
+      <c r="C33" s="152" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="159" t="s">
+      <c r="D33" s="140" t="s">
         <v>57</v>
       </c>
       <c r="E33" s="8" t="s">
@@ -5560,8 +5577,8 @@
       <c r="B34" s="7">
         <v>2</v>
       </c>
-      <c r="C34" s="148"/>
-      <c r="D34" s="160"/>
+      <c r="C34" s="153"/>
+      <c r="D34" s="141"/>
       <c r="E34" s="8" t="s">
         <v>59</v>
       </c>
@@ -5586,8 +5603,8 @@
       <c r="B35" s="7">
         <v>3</v>
       </c>
-      <c r="C35" s="148"/>
-      <c r="D35" s="160"/>
+      <c r="C35" s="153"/>
+      <c r="D35" s="141"/>
       <c r="E35" s="8" t="s">
         <v>60</v>
       </c>
@@ -5600,7 +5617,7 @@
       <c r="H35" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="I35" s="195" t="s">
+      <c r="I35" s="139" t="s">
         <v>721</v>
       </c>
       <c r="J35" s="126" t="s">
@@ -5614,8 +5631,8 @@
       <c r="B36" s="7">
         <v>4</v>
       </c>
-      <c r="C36" s="148"/>
-      <c r="D36" s="161"/>
+      <c r="C36" s="153"/>
+      <c r="D36" s="142"/>
       <c r="E36" s="8" t="s">
         <v>61</v>
       </c>
@@ -5628,7 +5645,7 @@
       <c r="H36" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I36" s="195" t="s">
+      <c r="I36" s="139" t="s">
         <v>722</v>
       </c>
       <c r="J36" s="126" t="s">
@@ -5642,8 +5659,8 @@
       <c r="B37" s="7">
         <v>5</v>
       </c>
-      <c r="C37" s="148"/>
-      <c r="D37" s="159" t="s">
+      <c r="C37" s="153"/>
+      <c r="D37" s="140" t="s">
         <v>62</v>
       </c>
       <c r="E37" s="8" t="s">
@@ -5670,8 +5687,8 @@
       <c r="B38" s="7">
         <v>6</v>
       </c>
-      <c r="C38" s="148"/>
-      <c r="D38" s="160"/>
+      <c r="C38" s="153"/>
+      <c r="D38" s="141"/>
       <c r="E38" s="8" t="s">
         <v>64</v>
       </c>
@@ -5681,9 +5698,13 @@
       <c r="G38" s="10">
         <v>3</v>
       </c>
-      <c r="H38" s="11"/>
+      <c r="H38" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
+      <c r="J38" s="11" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="39" spans="1:10" ht="13.8">
       <c r="A39" s="6">
@@ -5692,8 +5713,8 @@
       <c r="B39" s="7">
         <v>7</v>
       </c>
-      <c r="C39" s="148"/>
-      <c r="D39" s="161"/>
+      <c r="C39" s="153"/>
+      <c r="D39" s="142"/>
       <c r="E39" s="8" t="s">
         <v>65</v>
       </c>
@@ -5703,9 +5724,13 @@
       <c r="G39" s="10">
         <v>3</v>
       </c>
-      <c r="H39" s="11"/>
+      <c r="H39" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
+      <c r="J39" s="11" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="40" spans="1:10" ht="13.8">
       <c r="A40" s="6">
@@ -5714,8 +5739,8 @@
       <c r="B40" s="7">
         <v>8</v>
       </c>
-      <c r="C40" s="148"/>
-      <c r="D40" s="159" t="s">
+      <c r="C40" s="153"/>
+      <c r="D40" s="140" t="s">
         <v>66</v>
       </c>
       <c r="E40" s="8" t="s">
@@ -5727,9 +5752,13 @@
       <c r="G40" s="10">
         <v>4</v>
       </c>
-      <c r="H40" s="11"/>
+      <c r="H40" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="I40" s="11"/>
-      <c r="J40" s="11"/>
+      <c r="J40" s="11" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="41" spans="1:10" ht="13.8">
       <c r="A41" s="6">
@@ -5738,8 +5767,8 @@
       <c r="B41" s="7">
         <v>9</v>
       </c>
-      <c r="C41" s="148"/>
-      <c r="D41" s="160"/>
+      <c r="C41" s="153"/>
+      <c r="D41" s="141"/>
       <c r="E41" s="8" t="s">
         <v>68</v>
       </c>
@@ -5749,9 +5778,13 @@
       <c r="G41" s="10">
         <v>4</v>
       </c>
-      <c r="H41" s="11"/>
+      <c r="H41" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
+      <c r="J41" s="126" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="42" spans="1:10" ht="13.8">
       <c r="A42" s="6">
@@ -5760,8 +5793,8 @@
       <c r="B42" s="7">
         <v>10</v>
       </c>
-      <c r="C42" s="148"/>
-      <c r="D42" s="160"/>
+      <c r="C42" s="153"/>
+      <c r="D42" s="141"/>
       <c r="E42" s="8" t="s">
         <v>69</v>
       </c>
@@ -5771,9 +5804,13 @@
       <c r="G42" s="10">
         <v>4</v>
       </c>
-      <c r="H42" s="11"/>
+      <c r="H42" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="I42" s="11"/>
-      <c r="J42" s="11"/>
+      <c r="J42" s="126" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="43" spans="1:10" ht="13.8">
       <c r="A43" s="6">
@@ -5782,8 +5819,8 @@
       <c r="B43" s="7">
         <v>11</v>
       </c>
-      <c r="C43" s="148"/>
-      <c r="D43" s="160"/>
+      <c r="C43" s="153"/>
+      <c r="D43" s="141"/>
       <c r="E43" s="8" t="s">
         <v>70</v>
       </c>
@@ -5793,9 +5830,13 @@
       <c r="G43" s="10">
         <v>4</v>
       </c>
-      <c r="H43" s="11"/>
+      <c r="H43" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="I43" s="11"/>
-      <c r="J43" s="11"/>
+      <c r="J43" s="126" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="44" spans="1:10" ht="13.8">
       <c r="A44" s="23">
@@ -5804,8 +5845,8 @@
       <c r="B44" s="24">
         <v>12</v>
       </c>
-      <c r="C44" s="149"/>
-      <c r="D44" s="161"/>
+      <c r="C44" s="154"/>
+      <c r="D44" s="142"/>
       <c r="E44" s="17" t="s">
         <v>71</v>
       </c>
@@ -5815,9 +5856,13 @@
       <c r="G44" s="19">
         <v>5</v>
       </c>
-      <c r="H44" s="20"/>
+      <c r="H44" s="20" t="s">
+        <v>27</v>
+      </c>
       <c r="I44" s="20"/>
-      <c r="J44" s="20"/>
+      <c r="J44" s="196" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="45" spans="1:10" ht="13.8">
       <c r="A45" s="21">
@@ -5826,10 +5871,10 @@
       <c r="B45" s="22">
         <v>1</v>
       </c>
-      <c r="C45" s="150" t="s">
+      <c r="C45" s="167" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="162" t="s">
+      <c r="D45" s="170" t="s">
         <v>73</v>
       </c>
       <c r="E45" s="13" t="s">
@@ -5856,8 +5901,8 @@
       <c r="B46" s="7">
         <v>2</v>
       </c>
-      <c r="C46" s="151"/>
-      <c r="D46" s="163"/>
+      <c r="C46" s="168"/>
+      <c r="D46" s="171"/>
       <c r="E46" s="8" t="s">
         <v>75</v>
       </c>
@@ -5884,8 +5929,8 @@
       <c r="B47" s="7">
         <v>3</v>
       </c>
-      <c r="C47" s="151"/>
-      <c r="D47" s="163"/>
+      <c r="C47" s="168"/>
+      <c r="D47" s="171"/>
       <c r="E47" s="13" t="s">
         <v>76</v>
       </c>
@@ -5912,8 +5957,8 @@
       <c r="B48" s="7">
         <v>4</v>
       </c>
-      <c r="C48" s="151"/>
-      <c r="D48" s="163"/>
+      <c r="C48" s="168"/>
+      <c r="D48" s="171"/>
       <c r="E48" s="13" t="s">
         <v>77</v>
       </c>
@@ -5940,8 +5985,8 @@
       <c r="B49" s="7">
         <v>5</v>
       </c>
-      <c r="C49" s="151"/>
-      <c r="D49" s="163"/>
+      <c r="C49" s="168"/>
+      <c r="D49" s="171"/>
       <c r="E49" s="13" t="s">
         <v>78</v>
       </c>
@@ -5966,8 +6011,8 @@
       <c r="B50" s="24">
         <v>6</v>
       </c>
-      <c r="C50" s="152"/>
-      <c r="D50" s="164"/>
+      <c r="C50" s="169"/>
+      <c r="D50" s="172"/>
       <c r="E50" s="25" t="s">
         <v>79</v>
       </c>
@@ -5992,10 +6037,10 @@
       <c r="B51" s="7">
         <v>1</v>
       </c>
-      <c r="C51" s="141" t="s">
+      <c r="C51" s="158" t="s">
         <v>80</v>
       </c>
-      <c r="D51" s="159" t="s">
+      <c r="D51" s="140" t="s">
         <v>81</v>
       </c>
       <c r="E51" s="13" t="s">
@@ -6024,8 +6069,8 @@
       <c r="B52" s="7">
         <v>2</v>
       </c>
-      <c r="C52" s="142"/>
-      <c r="D52" s="160"/>
+      <c r="C52" s="159"/>
+      <c r="D52" s="141"/>
       <c r="E52" s="8" t="s">
         <v>83</v>
       </c>
@@ -6052,8 +6097,8 @@
       <c r="B53" s="7">
         <v>3</v>
       </c>
-      <c r="C53" s="142"/>
-      <c r="D53" s="160"/>
+      <c r="C53" s="159"/>
+      <c r="D53" s="141"/>
       <c r="E53" s="27" t="s">
         <v>84</v>
       </c>
@@ -6078,8 +6123,8 @@
       <c r="B54" s="7">
         <v>4</v>
       </c>
-      <c r="C54" s="142"/>
-      <c r="D54" s="160"/>
+      <c r="C54" s="159"/>
+      <c r="D54" s="141"/>
       <c r="E54" s="13" t="s">
         <v>85</v>
       </c>
@@ -6104,8 +6149,8 @@
       <c r="B55" s="7">
         <v>5</v>
       </c>
-      <c r="C55" s="142"/>
-      <c r="D55" s="160"/>
+      <c r="C55" s="159"/>
+      <c r="D55" s="141"/>
       <c r="E55" s="13" t="s">
         <v>86</v>
       </c>
@@ -6132,8 +6177,8 @@
       <c r="B56" s="7">
         <v>6</v>
       </c>
-      <c r="C56" s="142"/>
-      <c r="D56" s="160"/>
+      <c r="C56" s="159"/>
+      <c r="D56" s="141"/>
       <c r="E56" s="13" t="s">
         <v>87</v>
       </c>
@@ -6160,8 +6205,8 @@
       <c r="B57" s="7">
         <v>7</v>
       </c>
-      <c r="C57" s="142"/>
-      <c r="D57" s="161"/>
+      <c r="C57" s="159"/>
+      <c r="D57" s="142"/>
       <c r="E57" s="13" t="s">
         <v>88</v>
       </c>
@@ -6188,8 +6233,8 @@
       <c r="B58" s="7">
         <v>8</v>
       </c>
-      <c r="C58" s="142"/>
-      <c r="D58" s="159" t="s">
+      <c r="C58" s="159"/>
+      <c r="D58" s="140" t="s">
         <v>89</v>
       </c>
       <c r="E58" s="13" t="s">
@@ -6201,9 +6246,13 @@
       <c r="G58" s="10">
         <v>3</v>
       </c>
-      <c r="H58" s="11"/>
+      <c r="H58" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="I58" s="11"/>
-      <c r="J58" s="11"/>
+      <c r="J58" s="11" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="59" spans="1:10" ht="13.8">
       <c r="A59" s="6">
@@ -6212,8 +6261,8 @@
       <c r="B59" s="7">
         <v>9</v>
       </c>
-      <c r="C59" s="142"/>
-      <c r="D59" s="160"/>
+      <c r="C59" s="159"/>
+      <c r="D59" s="141"/>
       <c r="E59" s="8" t="s">
         <v>91</v>
       </c>
@@ -6223,9 +6272,13 @@
       <c r="G59" s="10">
         <v>3</v>
       </c>
-      <c r="H59" s="11"/>
+      <c r="H59" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="I59" s="11"/>
-      <c r="J59" s="11"/>
+      <c r="J59" s="11" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="60" spans="1:10" ht="13.8">
       <c r="A60" s="6">
@@ -6234,8 +6287,8 @@
       <c r="B60" s="7">
         <v>10</v>
       </c>
-      <c r="C60" s="142"/>
-      <c r="D60" s="160"/>
+      <c r="C60" s="159"/>
+      <c r="D60" s="141"/>
       <c r="E60" s="8" t="s">
         <v>92</v>
       </c>
@@ -6256,8 +6309,8 @@
       <c r="B61" s="7">
         <v>11</v>
       </c>
-      <c r="C61" s="142"/>
-      <c r="D61" s="160"/>
+      <c r="C61" s="159"/>
+      <c r="D61" s="141"/>
       <c r="E61" s="8" t="s">
         <v>93</v>
       </c>
@@ -6278,8 +6331,8 @@
       <c r="B62" s="7">
         <v>12</v>
       </c>
-      <c r="C62" s="142"/>
-      <c r="D62" s="160"/>
+      <c r="C62" s="159"/>
+      <c r="D62" s="141"/>
       <c r="E62" s="8" t="s">
         <v>94</v>
       </c>
@@ -6289,9 +6342,13 @@
       <c r="G62" s="10">
         <v>3</v>
       </c>
-      <c r="H62" s="11"/>
+      <c r="H62" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="I62" s="11"/>
-      <c r="J62" s="11"/>
+      <c r="J62" s="126" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="63" spans="1:10" ht="13.8">
       <c r="A63" s="6">
@@ -6300,8 +6357,8 @@
       <c r="B63" s="7">
         <v>13</v>
       </c>
-      <c r="C63" s="142"/>
-      <c r="D63" s="161"/>
+      <c r="C63" s="159"/>
+      <c r="D63" s="142"/>
       <c r="E63" s="8" t="s">
         <v>95</v>
       </c>
@@ -6311,19 +6368,23 @@
       <c r="G63" s="10">
         <v>3</v>
       </c>
-      <c r="H63" s="11"/>
+      <c r="H63" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="I63" s="11"/>
-      <c r="J63" s="11"/>
-    </row>
-    <row r="64" spans="1:10" ht="13.8">
+      <c r="J63" s="126" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="193.2">
       <c r="A64" s="6">
         <v>61</v>
       </c>
       <c r="B64" s="7">
         <v>14</v>
       </c>
-      <c r="C64" s="142"/>
-      <c r="D64" s="159" t="s">
+      <c r="C64" s="159"/>
+      <c r="D64" s="140" t="s">
         <v>48</v>
       </c>
       <c r="E64" s="8" t="s">
@@ -6335,9 +6396,15 @@
       <c r="G64" s="10">
         <v>4</v>
       </c>
-      <c r="H64" s="11"/>
-      <c r="I64" s="11"/>
-      <c r="J64" s="11"/>
+      <c r="H64" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I64" s="125" t="s">
+        <v>723</v>
+      </c>
+      <c r="J64" s="128" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="65" spans="1:10" ht="13.8">
       <c r="A65" s="6">
@@ -6346,8 +6413,8 @@
       <c r="B65" s="7">
         <v>15</v>
       </c>
-      <c r="C65" s="142"/>
-      <c r="D65" s="160"/>
+      <c r="C65" s="159"/>
+      <c r="D65" s="141"/>
       <c r="E65" s="8" t="s">
         <v>97</v>
       </c>
@@ -6368,8 +6435,8 @@
       <c r="B66" s="7">
         <v>16</v>
       </c>
-      <c r="C66" s="142"/>
-      <c r="D66" s="160"/>
+      <c r="C66" s="159"/>
+      <c r="D66" s="141"/>
       <c r="E66" s="8" t="s">
         <v>98</v>
       </c>
@@ -6379,7 +6446,6 @@
       <c r="G66" s="10">
         <v>4</v>
       </c>
-      <c r="H66" s="11"/>
       <c r="I66" s="11"/>
       <c r="J66" s="11"/>
     </row>
@@ -6390,8 +6456,8 @@
       <c r="B67" s="7">
         <v>17</v>
       </c>
-      <c r="C67" s="143"/>
-      <c r="D67" s="161"/>
+      <c r="C67" s="160"/>
+      <c r="D67" s="142"/>
       <c r="E67" s="8" t="s">
         <v>99</v>
       </c>
@@ -6406,18 +6472,18 @@
       <c r="J67" s="11"/>
     </row>
     <row r="68" spans="1:10" ht="13.8">
-      <c r="A68" s="171" t="s">
+      <c r="A68" s="173" t="s">
         <v>100</v>
       </c>
-      <c r="B68" s="172"/>
-      <c r="C68" s="172"/>
-      <c r="D68" s="172"/>
-      <c r="E68" s="172"/>
-      <c r="F68" s="172"/>
-      <c r="G68" s="172"/>
-      <c r="H68" s="172"/>
-      <c r="I68" s="172"/>
-      <c r="J68" s="173"/>
+      <c r="B68" s="174"/>
+      <c r="C68" s="174"/>
+      <c r="D68" s="174"/>
+      <c r="E68" s="174"/>
+      <c r="F68" s="174"/>
+      <c r="G68" s="174"/>
+      <c r="H68" s="174"/>
+      <c r="I68" s="174"/>
+      <c r="J68" s="175"/>
     </row>
     <row r="69" spans="1:10" ht="13.8">
       <c r="A69" s="6">
@@ -6426,10 +6492,10 @@
       <c r="B69" s="7">
         <v>1</v>
       </c>
-      <c r="C69" s="144" t="s">
+      <c r="C69" s="149" t="s">
         <v>101</v>
       </c>
-      <c r="D69" s="159" t="s">
+      <c r="D69" s="140" t="s">
         <v>102</v>
       </c>
       <c r="E69" s="8" t="s">
@@ -6452,8 +6518,8 @@
       <c r="B70" s="7">
         <v>2</v>
       </c>
-      <c r="C70" s="145"/>
-      <c r="D70" s="160"/>
+      <c r="C70" s="150"/>
+      <c r="D70" s="141"/>
       <c r="E70" s="28" t="s">
         <v>104</v>
       </c>
@@ -6474,8 +6540,8 @@
       <c r="B71" s="7">
         <v>3</v>
       </c>
-      <c r="C71" s="145"/>
-      <c r="D71" s="160"/>
+      <c r="C71" s="150"/>
+      <c r="D71" s="141"/>
       <c r="E71" s="8" t="s">
         <v>105</v>
       </c>
@@ -6496,8 +6562,8 @@
       <c r="B72" s="7">
         <v>4</v>
       </c>
-      <c r="C72" s="145"/>
-      <c r="D72" s="160"/>
+      <c r="C72" s="150"/>
+      <c r="D72" s="141"/>
       <c r="E72" s="8" t="s">
         <v>106</v>
       </c>
@@ -6518,8 +6584,8 @@
       <c r="B73" s="7">
         <v>5</v>
       </c>
-      <c r="C73" s="145"/>
-      <c r="D73" s="160"/>
+      <c r="C73" s="150"/>
+      <c r="D73" s="141"/>
       <c r="E73" s="28" t="s">
         <v>107</v>
       </c>
@@ -6540,8 +6606,8 @@
       <c r="B74" s="7">
         <v>6</v>
       </c>
-      <c r="C74" s="145"/>
-      <c r="D74" s="160"/>
+      <c r="C74" s="150"/>
+      <c r="D74" s="141"/>
       <c r="E74" s="28" t="s">
         <v>108</v>
       </c>
@@ -6562,8 +6628,8 @@
       <c r="B75" s="7">
         <v>7</v>
       </c>
-      <c r="C75" s="145"/>
-      <c r="D75" s="160"/>
+      <c r="C75" s="150"/>
+      <c r="D75" s="141"/>
       <c r="E75" s="28" t="s">
         <v>109</v>
       </c>
@@ -6584,8 +6650,8 @@
       <c r="B76" s="7">
         <v>8</v>
       </c>
-      <c r="C76" s="145"/>
-      <c r="D76" s="160"/>
+      <c r="C76" s="150"/>
+      <c r="D76" s="141"/>
       <c r="E76" s="8" t="s">
         <v>110</v>
       </c>
@@ -6606,8 +6672,8 @@
       <c r="B77" s="7">
         <v>9</v>
       </c>
-      <c r="C77" s="145"/>
-      <c r="D77" s="160"/>
+      <c r="C77" s="150"/>
+      <c r="D77" s="141"/>
       <c r="E77" s="8" t="s">
         <v>111</v>
       </c>
@@ -6628,8 +6694,8 @@
       <c r="B78" s="7">
         <v>10</v>
       </c>
-      <c r="C78" s="145"/>
-      <c r="D78" s="161"/>
+      <c r="C78" s="150"/>
+      <c r="D78" s="142"/>
       <c r="E78" s="8" t="s">
         <v>112</v>
       </c>
@@ -6650,8 +6716,8 @@
       <c r="B79" s="7">
         <v>11</v>
       </c>
-      <c r="C79" s="145"/>
-      <c r="D79" s="159" t="s">
+      <c r="C79" s="150"/>
+      <c r="D79" s="140" t="s">
         <v>113</v>
       </c>
       <c r="E79" s="8" t="s">
@@ -6674,8 +6740,8 @@
       <c r="B80" s="7">
         <v>12</v>
       </c>
-      <c r="C80" s="145"/>
-      <c r="D80" s="160"/>
+      <c r="C80" s="150"/>
+      <c r="D80" s="141"/>
       <c r="E80" s="8" t="s">
         <v>115</v>
       </c>
@@ -6696,8 +6762,8 @@
       <c r="B81" s="7">
         <v>13</v>
       </c>
-      <c r="C81" s="145"/>
-      <c r="D81" s="160"/>
+      <c r="C81" s="150"/>
+      <c r="D81" s="141"/>
       <c r="E81" s="8" t="s">
         <v>116</v>
       </c>
@@ -6718,8 +6784,8 @@
       <c r="B82" s="7">
         <v>14</v>
       </c>
-      <c r="C82" s="145"/>
-      <c r="D82" s="160"/>
+      <c r="C82" s="150"/>
+      <c r="D82" s="141"/>
       <c r="E82" s="8" t="s">
         <v>117</v>
       </c>
@@ -6740,8 +6806,8 @@
       <c r="B83" s="7">
         <v>15</v>
       </c>
-      <c r="C83" s="145"/>
-      <c r="D83" s="160"/>
+      <c r="C83" s="150"/>
+      <c r="D83" s="141"/>
       <c r="E83" s="8" t="s">
         <v>118</v>
       </c>
@@ -6762,8 +6828,8 @@
       <c r="B84" s="7">
         <v>16</v>
       </c>
-      <c r="C84" s="145"/>
-      <c r="D84" s="161"/>
+      <c r="C84" s="150"/>
+      <c r="D84" s="142"/>
       <c r="E84" s="8" t="s">
         <v>119</v>
       </c>
@@ -6784,8 +6850,8 @@
       <c r="B85" s="7">
         <v>17</v>
       </c>
-      <c r="C85" s="145"/>
-      <c r="D85" s="159" t="s">
+      <c r="C85" s="150"/>
+      <c r="D85" s="140" t="s">
         <v>120</v>
       </c>
       <c r="E85" s="8" t="s">
@@ -6808,8 +6874,8 @@
       <c r="B86" s="7">
         <v>18</v>
       </c>
-      <c r="C86" s="145"/>
-      <c r="D86" s="160"/>
+      <c r="C86" s="150"/>
+      <c r="D86" s="141"/>
       <c r="E86" s="8" t="s">
         <v>122</v>
       </c>
@@ -6830,8 +6896,8 @@
       <c r="B87" s="7">
         <v>19</v>
       </c>
-      <c r="C87" s="145"/>
-      <c r="D87" s="160"/>
+      <c r="C87" s="150"/>
+      <c r="D87" s="141"/>
       <c r="E87" s="29" t="s">
         <v>123</v>
       </c>
@@ -6852,8 +6918,8 @@
       <c r="B88" s="7">
         <v>20</v>
       </c>
-      <c r="C88" s="145"/>
-      <c r="D88" s="160"/>
+      <c r="C88" s="150"/>
+      <c r="D88" s="141"/>
       <c r="E88" s="8" t="s">
         <v>124</v>
       </c>
@@ -6874,8 +6940,8 @@
       <c r="B89" s="7">
         <v>21</v>
       </c>
-      <c r="C89" s="145"/>
-      <c r="D89" s="160"/>
+      <c r="C89" s="150"/>
+      <c r="D89" s="141"/>
       <c r="E89" s="8" t="s">
         <v>125</v>
       </c>
@@ -6896,8 +6962,8 @@
       <c r="B90" s="7">
         <v>22</v>
       </c>
-      <c r="C90" s="145"/>
-      <c r="D90" s="161"/>
+      <c r="C90" s="150"/>
+      <c r="D90" s="142"/>
       <c r="E90" s="8" t="s">
         <v>126</v>
       </c>
@@ -6918,8 +6984,8 @@
       <c r="B91" s="7">
         <v>23</v>
       </c>
-      <c r="C91" s="145"/>
-      <c r="D91" s="159" t="s">
+      <c r="C91" s="150"/>
+      <c r="D91" s="140" t="s">
         <v>127</v>
       </c>
       <c r="E91" s="8" t="s">
@@ -6942,8 +7008,8 @@
       <c r="B92" s="7">
         <v>24</v>
       </c>
-      <c r="C92" s="145"/>
-      <c r="D92" s="160"/>
+      <c r="C92" s="150"/>
+      <c r="D92" s="141"/>
       <c r="E92" s="8" t="s">
         <v>129</v>
       </c>
@@ -6964,8 +7030,8 @@
       <c r="B93" s="7">
         <v>25</v>
       </c>
-      <c r="C93" s="145"/>
-      <c r="D93" s="160"/>
+      <c r="C93" s="150"/>
+      <c r="D93" s="141"/>
       <c r="E93" s="8" t="s">
         <v>130</v>
       </c>
@@ -6986,8 +7052,8 @@
       <c r="B94" s="7">
         <v>26</v>
       </c>
-      <c r="C94" s="145"/>
-      <c r="D94" s="160"/>
+      <c r="C94" s="150"/>
+      <c r="D94" s="141"/>
       <c r="E94" s="8" t="s">
         <v>131</v>
       </c>
@@ -7008,8 +7074,8 @@
       <c r="B95" s="7">
         <v>27</v>
       </c>
-      <c r="C95" s="145"/>
-      <c r="D95" s="160"/>
+      <c r="C95" s="150"/>
+      <c r="D95" s="141"/>
       <c r="E95" s="8" t="s">
         <v>132</v>
       </c>
@@ -7030,8 +7096,8 @@
       <c r="B96" s="7">
         <v>28</v>
       </c>
-      <c r="C96" s="145"/>
-      <c r="D96" s="160"/>
+      <c r="C96" s="150"/>
+      <c r="D96" s="141"/>
       <c r="E96" s="8" t="s">
         <v>133</v>
       </c>
@@ -7052,8 +7118,8 @@
       <c r="B97" s="7">
         <v>29</v>
       </c>
-      <c r="C97" s="145"/>
-      <c r="D97" s="160"/>
+      <c r="C97" s="150"/>
+      <c r="D97" s="141"/>
       <c r="E97" s="8" t="s">
         <v>134</v>
       </c>
@@ -7074,8 +7140,8 @@
       <c r="B98" s="7">
         <v>30</v>
       </c>
-      <c r="C98" s="145"/>
-      <c r="D98" s="160"/>
+      <c r="C98" s="150"/>
+      <c r="D98" s="141"/>
       <c r="E98" s="8" t="s">
         <v>135</v>
       </c>
@@ -7096,8 +7162,8 @@
       <c r="B99" s="7">
         <v>31</v>
       </c>
-      <c r="C99" s="145"/>
-      <c r="D99" s="160"/>
+      <c r="C99" s="150"/>
+      <c r="D99" s="141"/>
       <c r="E99" s="30" t="s">
         <v>136</v>
       </c>
@@ -7118,8 +7184,8 @@
       <c r="B100" s="7">
         <v>32</v>
       </c>
-      <c r="C100" s="145"/>
-      <c r="D100" s="160"/>
+      <c r="C100" s="150"/>
+      <c r="D100" s="141"/>
       <c r="E100" s="8" t="s">
         <v>137</v>
       </c>
@@ -7140,8 +7206,8 @@
       <c r="B101" s="7">
         <v>33</v>
       </c>
-      <c r="C101" s="145"/>
-      <c r="D101" s="160"/>
+      <c r="C101" s="150"/>
+      <c r="D101" s="141"/>
       <c r="E101" s="8" t="s">
         <v>138</v>
       </c>
@@ -7162,8 +7228,8 @@
       <c r="B102" s="7">
         <v>34</v>
       </c>
-      <c r="C102" s="145"/>
-      <c r="D102" s="160"/>
+      <c r="C102" s="150"/>
+      <c r="D102" s="141"/>
       <c r="E102" s="8" t="s">
         <v>139</v>
       </c>
@@ -7184,8 +7250,8 @@
       <c r="B103" s="7">
         <v>35</v>
       </c>
-      <c r="C103" s="145"/>
-      <c r="D103" s="160"/>
+      <c r="C103" s="150"/>
+      <c r="D103" s="141"/>
       <c r="E103" s="8" t="s">
         <v>140</v>
       </c>
@@ -7206,8 +7272,8 @@
       <c r="B104" s="7">
         <v>36</v>
       </c>
-      <c r="C104" s="145"/>
-      <c r="D104" s="160"/>
+      <c r="C104" s="150"/>
+      <c r="D104" s="141"/>
       <c r="E104" s="8" t="s">
         <v>141</v>
       </c>
@@ -7228,8 +7294,8 @@
       <c r="B105" s="7">
         <v>37</v>
       </c>
-      <c r="C105" s="146"/>
-      <c r="D105" s="161"/>
+      <c r="C105" s="151"/>
+      <c r="D105" s="142"/>
       <c r="E105" s="8" t="s">
         <v>142</v>
       </c>
@@ -7244,18 +7310,18 @@
       <c r="J105" s="11"/>
     </row>
     <row r="106" spans="1:10" ht="13.8">
-      <c r="A106" s="177" t="s">
+      <c r="A106" s="161" t="s">
         <v>143</v>
       </c>
-      <c r="B106" s="178"/>
-      <c r="C106" s="178"/>
-      <c r="D106" s="178"/>
-      <c r="E106" s="178"/>
-      <c r="F106" s="178"/>
-      <c r="G106" s="178"/>
-      <c r="H106" s="178"/>
-      <c r="I106" s="178"/>
-      <c r="J106" s="179"/>
+      <c r="B106" s="162"/>
+      <c r="C106" s="162"/>
+      <c r="D106" s="162"/>
+      <c r="E106" s="162"/>
+      <c r="F106" s="162"/>
+      <c r="G106" s="162"/>
+      <c r="H106" s="162"/>
+      <c r="I106" s="162"/>
+      <c r="J106" s="163"/>
     </row>
     <row r="107" spans="1:10" ht="13.8">
       <c r="A107" s="6">
@@ -7264,10 +7330,10 @@
       <c r="B107" s="7">
         <v>1</v>
       </c>
-      <c r="C107" s="147" t="s">
+      <c r="C107" s="152" t="s">
         <v>144</v>
       </c>
-      <c r="D107" s="159" t="s">
+      <c r="D107" s="140" t="s">
         <v>145</v>
       </c>
       <c r="E107" s="8" t="s">
@@ -7290,8 +7356,8 @@
       <c r="B108" s="7">
         <v>2</v>
       </c>
-      <c r="C108" s="148"/>
-      <c r="D108" s="160"/>
+      <c r="C108" s="153"/>
+      <c r="D108" s="141"/>
       <c r="E108" s="8" t="s">
         <v>147</v>
       </c>
@@ -7312,8 +7378,8 @@
       <c r="B109" s="7">
         <v>3</v>
       </c>
-      <c r="C109" s="148"/>
-      <c r="D109" s="160"/>
+      <c r="C109" s="153"/>
+      <c r="D109" s="141"/>
       <c r="E109" s="8" t="s">
         <v>148</v>
       </c>
@@ -7334,8 +7400,8 @@
       <c r="B110" s="7">
         <v>4</v>
       </c>
-      <c r="C110" s="148"/>
-      <c r="D110" s="160"/>
+      <c r="C110" s="153"/>
+      <c r="D110" s="141"/>
       <c r="E110" s="8" t="s">
         <v>149</v>
       </c>
@@ -7356,8 +7422,8 @@
       <c r="B111" s="7">
         <v>5</v>
       </c>
-      <c r="C111" s="148"/>
-      <c r="D111" s="161"/>
+      <c r="C111" s="153"/>
+      <c r="D111" s="142"/>
       <c r="E111" s="8" t="s">
         <v>150</v>
       </c>
@@ -7378,8 +7444,8 @@
       <c r="B112" s="7">
         <v>6</v>
       </c>
-      <c r="C112" s="148"/>
-      <c r="D112" s="159" t="s">
+      <c r="C112" s="153"/>
+      <c r="D112" s="140" t="s">
         <v>151</v>
       </c>
       <c r="E112" s="8" t="s">
@@ -7402,8 +7468,8 @@
       <c r="B113" s="7">
         <v>7</v>
       </c>
-      <c r="C113" s="148"/>
-      <c r="D113" s="160"/>
+      <c r="C113" s="153"/>
+      <c r="D113" s="141"/>
       <c r="E113" s="8" t="s">
         <v>153</v>
       </c>
@@ -7424,8 +7490,8 @@
       <c r="B114" s="7">
         <v>8</v>
       </c>
-      <c r="C114" s="148"/>
-      <c r="D114" s="160"/>
+      <c r="C114" s="153"/>
+      <c r="D114" s="141"/>
       <c r="E114" s="8" t="s">
         <v>154</v>
       </c>
@@ -7446,8 +7512,8 @@
       <c r="B115" s="7">
         <v>9</v>
       </c>
-      <c r="C115" s="148"/>
-      <c r="D115" s="161"/>
+      <c r="C115" s="153"/>
+      <c r="D115" s="142"/>
       <c r="E115" s="8" t="s">
         <v>155</v>
       </c>
@@ -7468,7 +7534,7 @@
       <c r="B116" s="24">
         <v>10</v>
       </c>
-      <c r="C116" s="149"/>
+      <c r="C116" s="154"/>
       <c r="D116" s="31" t="s">
         <v>156</v>
       </c>
@@ -7492,10 +7558,10 @@
       <c r="B117" s="7">
         <v>1</v>
       </c>
-      <c r="C117" s="138" t="s">
+      <c r="C117" s="155" t="s">
         <v>158</v>
       </c>
-      <c r="D117" s="159" t="s">
+      <c r="D117" s="140" t="s">
         <v>159</v>
       </c>
       <c r="E117" s="8" t="s">
@@ -7518,8 +7584,8 @@
       <c r="B118" s="7">
         <v>2</v>
       </c>
-      <c r="C118" s="139"/>
-      <c r="D118" s="160"/>
+      <c r="C118" s="156"/>
+      <c r="D118" s="141"/>
       <c r="E118" s="8" t="s">
         <v>161</v>
       </c>
@@ -7540,8 +7606,8 @@
       <c r="B119" s="7">
         <v>3</v>
       </c>
-      <c r="C119" s="139"/>
-      <c r="D119" s="160"/>
+      <c r="C119" s="156"/>
+      <c r="D119" s="141"/>
       <c r="E119" s="8" t="s">
         <v>162</v>
       </c>
@@ -7562,8 +7628,8 @@
       <c r="B120" s="7">
         <v>4</v>
       </c>
-      <c r="C120" s="139"/>
-      <c r="D120" s="161"/>
+      <c r="C120" s="156"/>
+      <c r="D120" s="142"/>
       <c r="E120" s="8" t="s">
         <v>163</v>
       </c>
@@ -7584,8 +7650,8 @@
       <c r="B121" s="7">
         <v>5</v>
       </c>
-      <c r="C121" s="139"/>
-      <c r="D121" s="159" t="s">
+      <c r="C121" s="156"/>
+      <c r="D121" s="140" t="s">
         <v>164</v>
       </c>
       <c r="E121" s="8" t="s">
@@ -7608,8 +7674,8 @@
       <c r="B122" s="7">
         <v>6</v>
       </c>
-      <c r="C122" s="139"/>
-      <c r="D122" s="161"/>
+      <c r="C122" s="156"/>
+      <c r="D122" s="142"/>
       <c r="E122" s="8" t="s">
         <v>166</v>
       </c>
@@ -7630,8 +7696,8 @@
       <c r="B123" s="7">
         <v>7</v>
       </c>
-      <c r="C123" s="139"/>
-      <c r="D123" s="159" t="s">
+      <c r="C123" s="156"/>
+      <c r="D123" s="140" t="s">
         <v>167</v>
       </c>
       <c r="E123" s="8" t="s">
@@ -7654,8 +7720,8 @@
       <c r="B124" s="7">
         <v>8</v>
       </c>
-      <c r="C124" s="139"/>
-      <c r="D124" s="160"/>
+      <c r="C124" s="156"/>
+      <c r="D124" s="141"/>
       <c r="E124" s="28" t="s">
         <v>169</v>
       </c>
@@ -7676,8 +7742,8 @@
       <c r="B125" s="7">
         <v>9</v>
       </c>
-      <c r="C125" s="140"/>
-      <c r="D125" s="161"/>
+      <c r="C125" s="157"/>
+      <c r="D125" s="142"/>
       <c r="E125" s="8" t="s">
         <v>170</v>
       </c>
@@ -7692,18 +7758,18 @@
       <c r="J125" s="11"/>
     </row>
     <row r="126" spans="1:10" ht="13.8">
-      <c r="A126" s="180" t="s">
+      <c r="A126" s="164" t="s">
         <v>171</v>
       </c>
-      <c r="B126" s="181"/>
-      <c r="C126" s="181"/>
-      <c r="D126" s="181"/>
-      <c r="E126" s="181"/>
-      <c r="F126" s="181"/>
-      <c r="G126" s="181"/>
-      <c r="H126" s="181"/>
-      <c r="I126" s="181"/>
-      <c r="J126" s="182"/>
+      <c r="B126" s="165"/>
+      <c r="C126" s="165"/>
+      <c r="D126" s="165"/>
+      <c r="E126" s="165"/>
+      <c r="F126" s="165"/>
+      <c r="G126" s="165"/>
+      <c r="H126" s="165"/>
+      <c r="I126" s="165"/>
+      <c r="J126" s="166"/>
     </row>
     <row r="127" spans="1:10" ht="13.8">
       <c r="A127" s="6">
@@ -7712,10 +7778,10 @@
       <c r="B127" s="7">
         <v>1</v>
       </c>
-      <c r="C127" s="141" t="s">
+      <c r="C127" s="158" t="s">
         <v>172</v>
       </c>
-      <c r="D127" s="159" t="s">
+      <c r="D127" s="140" t="s">
         <v>173</v>
       </c>
       <c r="E127" s="32" t="s">
@@ -7736,8 +7802,8 @@
       <c r="B128" s="7">
         <v>2</v>
       </c>
-      <c r="C128" s="142"/>
-      <c r="D128" s="160"/>
+      <c r="C128" s="159"/>
+      <c r="D128" s="141"/>
       <c r="E128" s="32" t="s">
         <v>175</v>
       </c>
@@ -7756,8 +7822,8 @@
       <c r="B129" s="7">
         <v>3</v>
       </c>
-      <c r="C129" s="142"/>
-      <c r="D129" s="160"/>
+      <c r="C129" s="159"/>
+      <c r="D129" s="141"/>
       <c r="E129" s="32" t="s">
         <v>176</v>
       </c>
@@ -7776,8 +7842,8 @@
       <c r="B130" s="7">
         <v>4</v>
       </c>
-      <c r="C130" s="142"/>
-      <c r="D130" s="161"/>
+      <c r="C130" s="159"/>
+      <c r="D130" s="142"/>
       <c r="E130" s="32" t="s">
         <v>177</v>
       </c>
@@ -7796,8 +7862,8 @@
       <c r="B131" s="7">
         <v>5</v>
       </c>
-      <c r="C131" s="142"/>
-      <c r="D131" s="159" t="s">
+      <c r="C131" s="159"/>
+      <c r="D131" s="140" t="s">
         <v>178</v>
       </c>
       <c r="E131" s="32" t="s">
@@ -7818,8 +7884,8 @@
       <c r="B132" s="7">
         <v>6</v>
       </c>
-      <c r="C132" s="143"/>
-      <c r="D132" s="161"/>
+      <c r="C132" s="160"/>
+      <c r="D132" s="142"/>
       <c r="E132" s="32" t="s">
         <v>180</v>
       </c>
@@ -7832,18 +7898,18 @@
       <c r="J132" s="11"/>
     </row>
     <row r="133" spans="1:10" ht="13.8">
-      <c r="A133" s="183" t="s">
+      <c r="A133" s="146" t="s">
         <v>181</v>
       </c>
-      <c r="B133" s="184"/>
-      <c r="C133" s="184"/>
-      <c r="D133" s="184"/>
-      <c r="E133" s="184"/>
-      <c r="F133" s="184"/>
-      <c r="G133" s="184"/>
-      <c r="H133" s="184"/>
-      <c r="I133" s="184"/>
-      <c r="J133" s="185"/>
+      <c r="B133" s="147"/>
+      <c r="C133" s="147"/>
+      <c r="D133" s="147"/>
+      <c r="E133" s="147"/>
+      <c r="F133" s="147"/>
+      <c r="G133" s="147"/>
+      <c r="H133" s="147"/>
+      <c r="I133" s="147"/>
+      <c r="J133" s="148"/>
     </row>
     <row r="134" spans="1:10" ht="13.8">
       <c r="A134" s="6">
@@ -7852,10 +7918,10 @@
       <c r="B134" s="7">
         <v>1</v>
       </c>
-      <c r="C134" s="144" t="s">
+      <c r="C134" s="149" t="s">
         <v>182</v>
       </c>
-      <c r="D134" s="159" t="s">
+      <c r="D134" s="140" t="s">
         <v>183</v>
       </c>
       <c r="E134" s="8" t="s">
@@ -7878,8 +7944,8 @@
       <c r="B135" s="7">
         <v>2</v>
       </c>
-      <c r="C135" s="145"/>
-      <c r="D135" s="160"/>
+      <c r="C135" s="150"/>
+      <c r="D135" s="141"/>
       <c r="E135" s="8" t="s">
         <v>185</v>
       </c>
@@ -7900,8 +7966,8 @@
       <c r="B136" s="7">
         <v>3</v>
       </c>
-      <c r="C136" s="145"/>
-      <c r="D136" s="161"/>
+      <c r="C136" s="150"/>
+      <c r="D136" s="142"/>
       <c r="E136" s="8" t="s">
         <v>186</v>
       </c>
@@ -7922,8 +7988,8 @@
       <c r="B137" s="7">
         <v>4</v>
       </c>
-      <c r="C137" s="145"/>
-      <c r="D137" s="159" t="s">
+      <c r="C137" s="150"/>
+      <c r="D137" s="140" t="s">
         <v>187</v>
       </c>
       <c r="E137" s="8" t="s">
@@ -7946,8 +8012,8 @@
       <c r="B138" s="7">
         <v>5</v>
       </c>
-      <c r="C138" s="145"/>
-      <c r="D138" s="160"/>
+      <c r="C138" s="150"/>
+      <c r="D138" s="141"/>
       <c r="E138" s="8" t="s">
         <v>189</v>
       </c>
@@ -7968,8 +8034,8 @@
       <c r="B139" s="7">
         <v>6</v>
       </c>
-      <c r="C139" s="145"/>
-      <c r="D139" s="160"/>
+      <c r="C139" s="150"/>
+      <c r="D139" s="141"/>
       <c r="E139" s="8" t="s">
         <v>190</v>
       </c>
@@ -7990,8 +8056,8 @@
       <c r="B140" s="7">
         <v>7</v>
       </c>
-      <c r="C140" s="145"/>
-      <c r="D140" s="160"/>
+      <c r="C140" s="150"/>
+      <c r="D140" s="141"/>
       <c r="E140" s="8" t="s">
         <v>191</v>
       </c>
@@ -8012,8 +8078,8 @@
       <c r="B141" s="7">
         <v>8</v>
       </c>
-      <c r="C141" s="145"/>
-      <c r="D141" s="160"/>
+      <c r="C141" s="150"/>
+      <c r="D141" s="141"/>
       <c r="E141" s="8" t="s">
         <v>192</v>
       </c>
@@ -8034,8 +8100,8 @@
       <c r="B142" s="7">
         <v>9</v>
       </c>
-      <c r="C142" s="145"/>
-      <c r="D142" s="160"/>
+      <c r="C142" s="150"/>
+      <c r="D142" s="141"/>
       <c r="E142" s="8" t="s">
         <v>193</v>
       </c>
@@ -8056,8 +8122,8 @@
       <c r="B143" s="7">
         <v>10</v>
       </c>
-      <c r="C143" s="145"/>
-      <c r="D143" s="161"/>
+      <c r="C143" s="150"/>
+      <c r="D143" s="142"/>
       <c r="E143" s="8" t="s">
         <v>194</v>
       </c>
@@ -8078,8 +8144,8 @@
       <c r="B144" s="7">
         <v>11</v>
       </c>
-      <c r="C144" s="145"/>
-      <c r="D144" s="159" t="s">
+      <c r="C144" s="150"/>
+      <c r="D144" s="140" t="s">
         <v>195</v>
       </c>
       <c r="E144" s="8" t="s">
@@ -8102,8 +8168,8 @@
       <c r="B145" s="7">
         <v>12</v>
       </c>
-      <c r="C145" s="145"/>
-      <c r="D145" s="160"/>
+      <c r="C145" s="150"/>
+      <c r="D145" s="141"/>
       <c r="E145" s="8" t="s">
         <v>197</v>
       </c>
@@ -8124,8 +8190,8 @@
       <c r="B146" s="7">
         <v>13</v>
       </c>
-      <c r="C146" s="145"/>
-      <c r="D146" s="160"/>
+      <c r="C146" s="150"/>
+      <c r="D146" s="141"/>
       <c r="E146" s="8" t="s">
         <v>198</v>
       </c>
@@ -8146,8 +8212,8 @@
       <c r="B147" s="7">
         <v>14</v>
       </c>
-      <c r="C147" s="145"/>
-      <c r="D147" s="160"/>
+      <c r="C147" s="150"/>
+      <c r="D147" s="141"/>
       <c r="E147" s="8" t="s">
         <v>199</v>
       </c>
@@ -8168,8 +8234,8 @@
       <c r="B148" s="7">
         <v>15</v>
       </c>
-      <c r="C148" s="145"/>
-      <c r="D148" s="160"/>
+      <c r="C148" s="150"/>
+      <c r="D148" s="141"/>
       <c r="E148" s="8" t="s">
         <v>200</v>
       </c>
@@ -8190,8 +8256,8 @@
       <c r="B149" s="7">
         <v>16</v>
       </c>
-      <c r="C149" s="145"/>
-      <c r="D149" s="160"/>
+      <c r="C149" s="150"/>
+      <c r="D149" s="141"/>
       <c r="E149" s="8" t="s">
         <v>201</v>
       </c>
@@ -8212,8 +8278,8 @@
       <c r="B150" s="7">
         <v>17</v>
       </c>
-      <c r="C150" s="145"/>
-      <c r="D150" s="161"/>
+      <c r="C150" s="150"/>
+      <c r="D150" s="142"/>
       <c r="E150" s="8" t="s">
         <v>202</v>
       </c>
@@ -8234,8 +8300,8 @@
       <c r="B151" s="7">
         <v>18</v>
       </c>
-      <c r="C151" s="145"/>
-      <c r="D151" s="159" t="s">
+      <c r="C151" s="150"/>
+      <c r="D151" s="140" t="s">
         <v>203</v>
       </c>
       <c r="E151" s="8" t="s">
@@ -8258,8 +8324,8 @@
       <c r="B152" s="7">
         <v>19</v>
       </c>
-      <c r="C152" s="145"/>
-      <c r="D152" s="160"/>
+      <c r="C152" s="150"/>
+      <c r="D152" s="141"/>
       <c r="E152" s="8" t="s">
         <v>205</v>
       </c>
@@ -8280,8 +8346,8 @@
       <c r="B153" s="7">
         <v>20</v>
       </c>
-      <c r="C153" s="145"/>
-      <c r="D153" s="160"/>
+      <c r="C153" s="150"/>
+      <c r="D153" s="141"/>
       <c r="E153" s="8" t="s">
         <v>206</v>
       </c>
@@ -8302,8 +8368,8 @@
       <c r="B154" s="7">
         <v>21</v>
       </c>
-      <c r="C154" s="145"/>
-      <c r="D154" s="160"/>
+      <c r="C154" s="150"/>
+      <c r="D154" s="141"/>
       <c r="E154" s="8" t="s">
         <v>207</v>
       </c>
@@ -8324,8 +8390,8 @@
       <c r="B155" s="7">
         <v>22</v>
       </c>
-      <c r="C155" s="145"/>
-      <c r="D155" s="160"/>
+      <c r="C155" s="150"/>
+      <c r="D155" s="141"/>
       <c r="E155" s="8" t="s">
         <v>208</v>
       </c>
@@ -8346,8 +8412,8 @@
       <c r="B156" s="7">
         <v>23</v>
       </c>
-      <c r="C156" s="145"/>
-      <c r="D156" s="161"/>
+      <c r="C156" s="150"/>
+      <c r="D156" s="142"/>
       <c r="E156" s="8" t="s">
         <v>209</v>
       </c>
@@ -8368,8 +8434,8 @@
       <c r="B157" s="7">
         <v>24</v>
       </c>
-      <c r="C157" s="145"/>
-      <c r="D157" s="159" t="s">
+      <c r="C157" s="150"/>
+      <c r="D157" s="140" t="s">
         <v>210</v>
       </c>
       <c r="E157" s="8" t="s">
@@ -8392,8 +8458,8 @@
       <c r="B158" s="7">
         <v>25</v>
       </c>
-      <c r="C158" s="145"/>
-      <c r="D158" s="160"/>
+      <c r="C158" s="150"/>
+      <c r="D158" s="141"/>
       <c r="E158" s="8" t="s">
         <v>212</v>
       </c>
@@ -8414,8 +8480,8 @@
       <c r="B159" s="7">
         <v>26</v>
       </c>
-      <c r="C159" s="145"/>
-      <c r="D159" s="161"/>
+      <c r="C159" s="150"/>
+      <c r="D159" s="142"/>
       <c r="E159" s="8" t="s">
         <v>213</v>
       </c>
@@ -8436,8 +8502,8 @@
       <c r="B160" s="7">
         <v>27</v>
       </c>
-      <c r="C160" s="145"/>
-      <c r="D160" s="159" t="s">
+      <c r="C160" s="150"/>
+      <c r="D160" s="140" t="s">
         <v>214</v>
       </c>
       <c r="E160" s="8" t="s">
@@ -8460,8 +8526,8 @@
       <c r="B161" s="7">
         <v>28</v>
       </c>
-      <c r="C161" s="145"/>
-      <c r="D161" s="160"/>
+      <c r="C161" s="150"/>
+      <c r="D161" s="141"/>
       <c r="E161" s="8" t="s">
         <v>216</v>
       </c>
@@ -8482,8 +8548,8 @@
       <c r="B162" s="7">
         <v>29</v>
       </c>
-      <c r="C162" s="145"/>
-      <c r="D162" s="160"/>
+      <c r="C162" s="150"/>
+      <c r="D162" s="141"/>
       <c r="E162" s="8" t="s">
         <v>217</v>
       </c>
@@ -8504,8 +8570,8 @@
       <c r="B163" s="7">
         <v>30</v>
       </c>
-      <c r="C163" s="145"/>
-      <c r="D163" s="160"/>
+      <c r="C163" s="150"/>
+      <c r="D163" s="141"/>
       <c r="E163" s="8" t="s">
         <v>218</v>
       </c>
@@ -8526,8 +8592,8 @@
       <c r="B164" s="7">
         <v>31</v>
       </c>
-      <c r="C164" s="145"/>
-      <c r="D164" s="160"/>
+      <c r="C164" s="150"/>
+      <c r="D164" s="141"/>
       <c r="E164" s="8" t="s">
         <v>219</v>
       </c>
@@ -8548,8 +8614,8 @@
       <c r="B165" s="7">
         <v>32</v>
       </c>
-      <c r="C165" s="145"/>
-      <c r="D165" s="161"/>
+      <c r="C165" s="150"/>
+      <c r="D165" s="142"/>
       <c r="E165" s="8" t="s">
         <v>220</v>
       </c>
@@ -8570,8 +8636,8 @@
       <c r="B166" s="7">
         <v>33</v>
       </c>
-      <c r="C166" s="145"/>
-      <c r="D166" s="159" t="s">
+      <c r="C166" s="150"/>
+      <c r="D166" s="140" t="s">
         <v>221</v>
       </c>
       <c r="E166" s="8" t="s">
@@ -8594,8 +8660,8 @@
       <c r="B167" s="7">
         <v>34</v>
       </c>
-      <c r="C167" s="145"/>
-      <c r="D167" s="160"/>
+      <c r="C167" s="150"/>
+      <c r="D167" s="141"/>
       <c r="E167" s="8" t="s">
         <v>223</v>
       </c>
@@ -8614,8 +8680,8 @@
       <c r="B168" s="7">
         <v>35</v>
       </c>
-      <c r="C168" s="145"/>
-      <c r="D168" s="160"/>
+      <c r="C168" s="150"/>
+      <c r="D168" s="141"/>
       <c r="E168" s="8" t="s">
         <v>224</v>
       </c>
@@ -8636,8 +8702,8 @@
       <c r="B169" s="7">
         <v>36</v>
       </c>
-      <c r="C169" s="145"/>
-      <c r="D169" s="160"/>
+      <c r="C169" s="150"/>
+      <c r="D169" s="141"/>
       <c r="E169" s="8" t="s">
         <v>225</v>
       </c>
@@ -8658,8 +8724,8 @@
       <c r="B170" s="7">
         <v>37</v>
       </c>
-      <c r="C170" s="145"/>
-      <c r="D170" s="160"/>
+      <c r="C170" s="150"/>
+      <c r="D170" s="141"/>
       <c r="E170" s="8" t="s">
         <v>226</v>
       </c>
@@ -8680,8 +8746,8 @@
       <c r="B171" s="7">
         <v>38</v>
       </c>
-      <c r="C171" s="145"/>
-      <c r="D171" s="160"/>
+      <c r="C171" s="150"/>
+      <c r="D171" s="141"/>
       <c r="E171" s="8" t="s">
         <v>227</v>
       </c>
@@ -8702,8 +8768,8 @@
       <c r="B172" s="7">
         <v>39</v>
       </c>
-      <c r="C172" s="145"/>
-      <c r="D172" s="161"/>
+      <c r="C172" s="150"/>
+      <c r="D172" s="142"/>
       <c r="E172" s="8" t="s">
         <v>228</v>
       </c>
@@ -8724,8 +8790,8 @@
       <c r="B173" s="7">
         <v>40</v>
       </c>
-      <c r="C173" s="145"/>
-      <c r="D173" s="159" t="s">
+      <c r="C173" s="150"/>
+      <c r="D173" s="140" t="s">
         <v>48</v>
       </c>
       <c r="E173" s="11" t="s">
@@ -8748,8 +8814,8 @@
       <c r="B174" s="7">
         <v>41</v>
       </c>
-      <c r="C174" s="145"/>
-      <c r="D174" s="160"/>
+      <c r="C174" s="150"/>
+      <c r="D174" s="141"/>
       <c r="E174" s="8" t="s">
         <v>230</v>
       </c>
@@ -8770,8 +8836,8 @@
       <c r="B175" s="7">
         <v>42</v>
       </c>
-      <c r="C175" s="145"/>
-      <c r="D175" s="160"/>
+      <c r="C175" s="150"/>
+      <c r="D175" s="141"/>
       <c r="E175" s="8" t="s">
         <v>231</v>
       </c>
@@ -8792,8 +8858,8 @@
       <c r="B176" s="24">
         <v>43</v>
       </c>
-      <c r="C176" s="146"/>
-      <c r="D176" s="161"/>
+      <c r="C176" s="151"/>
+      <c r="D176" s="142"/>
       <c r="E176" s="17" t="s">
         <v>232</v>
       </c>
@@ -8814,10 +8880,10 @@
       <c r="B177" s="7">
         <v>1</v>
       </c>
-      <c r="C177" s="147" t="s">
+      <c r="C177" s="152" t="s">
         <v>233</v>
       </c>
-      <c r="D177" s="159" t="s">
+      <c r="D177" s="140" t="s">
         <v>234</v>
       </c>
       <c r="E177" s="8" t="s">
@@ -8840,8 +8906,8 @@
       <c r="B178" s="7">
         <v>2</v>
       </c>
-      <c r="C178" s="148"/>
-      <c r="D178" s="161"/>
+      <c r="C178" s="153"/>
+      <c r="D178" s="142"/>
       <c r="E178" s="8" t="s">
         <v>236</v>
       </c>
@@ -8862,8 +8928,8 @@
       <c r="B179" s="7">
         <v>3</v>
       </c>
-      <c r="C179" s="148"/>
-      <c r="D179" s="159" t="s">
+      <c r="C179" s="153"/>
+      <c r="D179" s="140" t="s">
         <v>237</v>
       </c>
       <c r="E179" s="8" t="s">
@@ -8886,8 +8952,8 @@
       <c r="B180" s="7">
         <v>4</v>
       </c>
-      <c r="C180" s="148"/>
-      <c r="D180" s="160"/>
+      <c r="C180" s="153"/>
+      <c r="D180" s="141"/>
       <c r="E180" s="8" t="s">
         <v>239</v>
       </c>
@@ -8908,8 +8974,8 @@
       <c r="B181" s="7">
         <v>5</v>
       </c>
-      <c r="C181" s="148"/>
-      <c r="D181" s="160"/>
+      <c r="C181" s="153"/>
+      <c r="D181" s="141"/>
       <c r="E181" s="8" t="s">
         <v>240</v>
       </c>
@@ -8930,8 +8996,8 @@
       <c r="B182" s="7">
         <v>6</v>
       </c>
-      <c r="C182" s="148"/>
-      <c r="D182" s="160"/>
+      <c r="C182" s="153"/>
+      <c r="D182" s="141"/>
       <c r="E182" s="8" t="s">
         <v>241</v>
       </c>
@@ -8952,8 +9018,8 @@
       <c r="B183" s="7">
         <v>7</v>
       </c>
-      <c r="C183" s="148"/>
-      <c r="D183" s="160"/>
+      <c r="C183" s="153"/>
+      <c r="D183" s="141"/>
       <c r="E183" s="8" t="s">
         <v>242</v>
       </c>
@@ -8974,8 +9040,8 @@
       <c r="B184" s="7">
         <v>8</v>
       </c>
-      <c r="C184" s="148"/>
-      <c r="D184" s="161"/>
+      <c r="C184" s="153"/>
+      <c r="D184" s="142"/>
       <c r="E184" s="8" t="s">
         <v>243</v>
       </c>
@@ -8996,8 +9062,8 @@
       <c r="B185" s="7">
         <v>9</v>
       </c>
-      <c r="C185" s="148"/>
-      <c r="D185" s="159" t="s">
+      <c r="C185" s="153"/>
+      <c r="D185" s="140" t="s">
         <v>244</v>
       </c>
       <c r="E185" s="8" t="s">
@@ -9020,8 +9086,8 @@
       <c r="B186" s="7">
         <v>10</v>
       </c>
-      <c r="C186" s="148"/>
-      <c r="D186" s="161"/>
+      <c r="C186" s="153"/>
+      <c r="D186" s="142"/>
       <c r="E186" s="8" t="s">
         <v>246</v>
       </c>
@@ -9042,8 +9108,8 @@
       <c r="B187" s="7">
         <v>11</v>
       </c>
-      <c r="C187" s="148"/>
-      <c r="D187" s="159" t="s">
+      <c r="C187" s="153"/>
+      <c r="D187" s="140" t="s">
         <v>247</v>
       </c>
       <c r="E187" s="8" t="s">
@@ -9066,8 +9132,8 @@
       <c r="B188" s="7">
         <v>12</v>
       </c>
-      <c r="C188" s="148"/>
-      <c r="D188" s="160"/>
+      <c r="C188" s="153"/>
+      <c r="D188" s="141"/>
       <c r="E188" s="8" t="s">
         <v>249</v>
       </c>
@@ -9088,8 +9154,8 @@
       <c r="B189" s="7">
         <v>13</v>
       </c>
-      <c r="C189" s="148"/>
-      <c r="D189" s="160"/>
+      <c r="C189" s="153"/>
+      <c r="D189" s="141"/>
       <c r="E189" s="11" t="s">
         <v>250</v>
       </c>
@@ -9110,8 +9176,8 @@
       <c r="B190" s="7">
         <v>14</v>
       </c>
-      <c r="C190" s="148"/>
-      <c r="D190" s="161"/>
+      <c r="C190" s="153"/>
+      <c r="D190" s="142"/>
       <c r="E190" s="8" t="s">
         <v>251</v>
       </c>
@@ -9132,8 +9198,8 @@
       <c r="B191" s="7">
         <v>15</v>
       </c>
-      <c r="C191" s="148"/>
-      <c r="D191" s="159" t="s">
+      <c r="C191" s="153"/>
+      <c r="D191" s="140" t="s">
         <v>252</v>
       </c>
       <c r="E191" s="8" t="s">
@@ -9156,8 +9222,8 @@
       <c r="B192" s="7">
         <v>16</v>
       </c>
-      <c r="C192" s="148"/>
-      <c r="D192" s="160"/>
+      <c r="C192" s="153"/>
+      <c r="D192" s="141"/>
       <c r="E192" s="8" t="s">
         <v>254</v>
       </c>
@@ -9178,8 +9244,8 @@
       <c r="B193" s="7">
         <v>17</v>
       </c>
-      <c r="C193" s="148"/>
-      <c r="D193" s="160"/>
+      <c r="C193" s="153"/>
+      <c r="D193" s="141"/>
       <c r="E193" s="8" t="s">
         <v>255</v>
       </c>
@@ -9200,8 +9266,8 @@
       <c r="B194" s="7">
         <v>18</v>
       </c>
-      <c r="C194" s="148"/>
-      <c r="D194" s="160"/>
+      <c r="C194" s="153"/>
+      <c r="D194" s="141"/>
       <c r="E194" s="8" t="s">
         <v>256</v>
       </c>
@@ -9222,8 +9288,8 @@
       <c r="B195" s="7">
         <v>19</v>
       </c>
-      <c r="C195" s="148"/>
-      <c r="D195" s="160"/>
+      <c r="C195" s="153"/>
+      <c r="D195" s="141"/>
       <c r="E195" s="8" t="s">
         <v>257</v>
       </c>
@@ -9244,8 +9310,8 @@
       <c r="B196" s="7">
         <v>20</v>
       </c>
-      <c r="C196" s="148"/>
-      <c r="D196" s="160"/>
+      <c r="C196" s="153"/>
+      <c r="D196" s="141"/>
       <c r="E196" s="8" t="s">
         <v>258</v>
       </c>
@@ -9266,8 +9332,8 @@
       <c r="B197" s="7">
         <v>21</v>
       </c>
-      <c r="C197" s="148"/>
-      <c r="D197" s="160"/>
+      <c r="C197" s="153"/>
+      <c r="D197" s="141"/>
       <c r="E197" s="8" t="s">
         <v>259</v>
       </c>
@@ -9288,8 +9354,8 @@
       <c r="B198" s="7">
         <v>22</v>
       </c>
-      <c r="C198" s="148"/>
-      <c r="D198" s="161"/>
+      <c r="C198" s="153"/>
+      <c r="D198" s="142"/>
       <c r="E198" s="8" t="s">
         <v>260</v>
       </c>
@@ -9310,8 +9376,8 @@
       <c r="B199" s="7">
         <v>23</v>
       </c>
-      <c r="C199" s="148"/>
-      <c r="D199" s="159" t="s">
+      <c r="C199" s="153"/>
+      <c r="D199" s="140" t="s">
         <v>261</v>
       </c>
       <c r="E199" s="8" t="s">
@@ -9334,8 +9400,8 @@
       <c r="B200" s="7">
         <v>24</v>
       </c>
-      <c r="C200" s="148"/>
-      <c r="D200" s="160"/>
+      <c r="C200" s="153"/>
+      <c r="D200" s="141"/>
       <c r="E200" s="8" t="s">
         <v>263</v>
       </c>
@@ -9356,8 +9422,8 @@
       <c r="B201" s="7">
         <v>25</v>
       </c>
-      <c r="C201" s="148"/>
-      <c r="D201" s="160"/>
+      <c r="C201" s="153"/>
+      <c r="D201" s="141"/>
       <c r="E201" s="8" t="s">
         <v>264</v>
       </c>
@@ -9378,8 +9444,8 @@
       <c r="B202" s="7">
         <v>26</v>
       </c>
-      <c r="C202" s="148"/>
-      <c r="D202" s="161"/>
+      <c r="C202" s="153"/>
+      <c r="D202" s="142"/>
       <c r="E202" s="8" t="s">
         <v>265</v>
       </c>
@@ -9400,8 +9466,8 @@
       <c r="B203" s="7">
         <v>27</v>
       </c>
-      <c r="C203" s="148"/>
-      <c r="D203" s="159" t="s">
+      <c r="C203" s="153"/>
+      <c r="D203" s="140" t="s">
         <v>266</v>
       </c>
       <c r="E203" s="8" t="s">
@@ -9424,8 +9490,8 @@
       <c r="B204" s="24">
         <v>28</v>
       </c>
-      <c r="C204" s="149"/>
-      <c r="D204" s="161"/>
+      <c r="C204" s="154"/>
+      <c r="D204" s="142"/>
       <c r="E204" s="17" t="s">
         <v>268</v>
       </c>
@@ -9446,10 +9512,10 @@
       <c r="B205" s="7">
         <v>1</v>
       </c>
-      <c r="C205" s="138" t="s">
+      <c r="C205" s="155" t="s">
         <v>269</v>
       </c>
-      <c r="D205" s="159" t="s">
+      <c r="D205" s="140" t="s">
         <v>270</v>
       </c>
       <c r="E205" s="8" t="s">
@@ -9472,8 +9538,8 @@
       <c r="B206" s="7">
         <v>2</v>
       </c>
-      <c r="C206" s="139"/>
-      <c r="D206" s="160"/>
+      <c r="C206" s="156"/>
+      <c r="D206" s="141"/>
       <c r="E206" s="8" t="s">
         <v>272</v>
       </c>
@@ -9494,8 +9560,8 @@
       <c r="B207" s="7">
         <v>3</v>
       </c>
-      <c r="C207" s="139"/>
-      <c r="D207" s="160"/>
+      <c r="C207" s="156"/>
+      <c r="D207" s="141"/>
       <c r="E207" s="8" t="s">
         <v>273</v>
       </c>
@@ -9516,8 +9582,8 @@
       <c r="B208" s="7">
         <v>4</v>
       </c>
-      <c r="C208" s="139"/>
-      <c r="D208" s="160"/>
+      <c r="C208" s="156"/>
+      <c r="D208" s="141"/>
       <c r="E208" s="8" t="s">
         <v>274</v>
       </c>
@@ -9538,8 +9604,8 @@
       <c r="B209" s="7">
         <v>5</v>
       </c>
-      <c r="C209" s="139"/>
-      <c r="D209" s="161"/>
+      <c r="C209" s="156"/>
+      <c r="D209" s="142"/>
       <c r="E209" s="8" t="s">
         <v>275</v>
       </c>
@@ -9560,8 +9626,8 @@
       <c r="B210" s="7">
         <v>6</v>
       </c>
-      <c r="C210" s="139"/>
-      <c r="D210" s="159" t="s">
+      <c r="C210" s="156"/>
+      <c r="D210" s="140" t="s">
         <v>276</v>
       </c>
       <c r="E210" s="8" t="s">
@@ -9584,8 +9650,8 @@
       <c r="B211" s="7">
         <v>7</v>
       </c>
-      <c r="C211" s="139"/>
-      <c r="D211" s="161"/>
+      <c r="C211" s="156"/>
+      <c r="D211" s="142"/>
       <c r="E211" s="8" t="s">
         <v>278</v>
       </c>
@@ -9606,8 +9672,8 @@
       <c r="B212" s="7">
         <v>8</v>
       </c>
-      <c r="C212" s="139"/>
-      <c r="D212" s="159" t="s">
+      <c r="C212" s="156"/>
+      <c r="D212" s="140" t="s">
         <v>279</v>
       </c>
       <c r="E212" s="8" t="s">
@@ -9630,8 +9696,8 @@
       <c r="B213" s="7">
         <v>9</v>
       </c>
-      <c r="C213" s="139"/>
-      <c r="D213" s="160"/>
+      <c r="C213" s="156"/>
+      <c r="D213" s="141"/>
       <c r="E213" s="8" t="s">
         <v>281</v>
       </c>
@@ -9652,8 +9718,8 @@
       <c r="B214" s="7">
         <v>10</v>
       </c>
-      <c r="C214" s="140"/>
-      <c r="D214" s="161"/>
+      <c r="C214" s="157"/>
+      <c r="D214" s="142"/>
       <c r="E214" s="8" t="s">
         <v>282</v>
       </c>
@@ -9668,18 +9734,18 @@
       <c r="J214" s="11"/>
     </row>
     <row r="215" spans="1:10" ht="13.8">
-      <c r="A215" s="168" t="s">
+      <c r="A215" s="176" t="s">
         <v>283</v>
       </c>
-      <c r="B215" s="169"/>
-      <c r="C215" s="169"/>
-      <c r="D215" s="169"/>
-      <c r="E215" s="169"/>
-      <c r="F215" s="169"/>
-      <c r="G215" s="169"/>
-      <c r="H215" s="169"/>
-      <c r="I215" s="169"/>
-      <c r="J215" s="170"/>
+      <c r="B215" s="177"/>
+      <c r="C215" s="177"/>
+      <c r="D215" s="177"/>
+      <c r="E215" s="177"/>
+      <c r="F215" s="177"/>
+      <c r="G215" s="177"/>
+      <c r="H215" s="177"/>
+      <c r="I215" s="177"/>
+      <c r="J215" s="178"/>
     </row>
     <row r="216" spans="1:10" ht="13.8">
       <c r="A216" s="6">
@@ -9688,10 +9754,10 @@
       <c r="B216" s="7">
         <v>1</v>
       </c>
-      <c r="C216" s="141" t="s">
+      <c r="C216" s="158" t="s">
         <v>284</v>
       </c>
-      <c r="D216" s="159" t="s">
+      <c r="D216" s="140" t="s">
         <v>285</v>
       </c>
       <c r="E216" s="8" t="s">
@@ -9714,8 +9780,8 @@
       <c r="B217" s="7">
         <v>2</v>
       </c>
-      <c r="C217" s="142"/>
-      <c r="D217" s="160"/>
+      <c r="C217" s="159"/>
+      <c r="D217" s="141"/>
       <c r="E217" s="8" t="s">
         <v>287</v>
       </c>
@@ -9736,8 +9802,8 @@
       <c r="B218" s="7">
         <v>3</v>
       </c>
-      <c r="C218" s="142"/>
-      <c r="D218" s="160"/>
+      <c r="C218" s="159"/>
+      <c r="D218" s="141"/>
       <c r="E218" s="8" t="s">
         <v>288</v>
       </c>
@@ -9758,8 +9824,8 @@
       <c r="B219" s="7">
         <v>4</v>
       </c>
-      <c r="C219" s="142"/>
-      <c r="D219" s="160"/>
+      <c r="C219" s="159"/>
+      <c r="D219" s="141"/>
       <c r="E219" s="8" t="s">
         <v>289</v>
       </c>
@@ -9780,8 +9846,8 @@
       <c r="B220" s="7">
         <v>5</v>
       </c>
-      <c r="C220" s="142"/>
-      <c r="D220" s="160"/>
+      <c r="C220" s="159"/>
+      <c r="D220" s="141"/>
       <c r="E220" s="8" t="s">
         <v>290</v>
       </c>
@@ -9802,8 +9868,8 @@
       <c r="B221" s="7">
         <v>6</v>
       </c>
-      <c r="C221" s="142"/>
-      <c r="D221" s="160"/>
+      <c r="C221" s="159"/>
+      <c r="D221" s="141"/>
       <c r="E221" s="8" t="s">
         <v>291</v>
       </c>
@@ -9824,8 +9890,8 @@
       <c r="B222" s="7">
         <v>7</v>
       </c>
-      <c r="C222" s="142"/>
-      <c r="D222" s="160"/>
+      <c r="C222" s="159"/>
+      <c r="D222" s="141"/>
       <c r="E222" s="8" t="s">
         <v>292</v>
       </c>
@@ -9846,8 +9912,8 @@
       <c r="B223" s="7">
         <v>8</v>
       </c>
-      <c r="C223" s="142"/>
-      <c r="D223" s="160"/>
+      <c r="C223" s="159"/>
+      <c r="D223" s="141"/>
       <c r="E223" s="8" t="s">
         <v>293</v>
       </c>
@@ -9868,8 +9934,8 @@
       <c r="B224" s="7">
         <v>9</v>
       </c>
-      <c r="C224" s="142"/>
-      <c r="D224" s="160"/>
+      <c r="C224" s="159"/>
+      <c r="D224" s="141"/>
       <c r="E224" s="8" t="s">
         <v>294</v>
       </c>
@@ -9890,8 +9956,8 @@
       <c r="B225" s="7">
         <v>10</v>
       </c>
-      <c r="C225" s="142"/>
-      <c r="D225" s="161"/>
+      <c r="C225" s="159"/>
+      <c r="D225" s="142"/>
       <c r="E225" s="8" t="s">
         <v>295</v>
       </c>
@@ -9912,8 +9978,8 @@
       <c r="B226" s="7">
         <v>11</v>
       </c>
-      <c r="C226" s="142"/>
-      <c r="D226" s="159" t="s">
+      <c r="C226" s="159"/>
+      <c r="D226" s="140" t="s">
         <v>296</v>
       </c>
       <c r="E226" s="8" t="s">
@@ -9936,8 +10002,8 @@
       <c r="B227" s="7">
         <v>12</v>
       </c>
-      <c r="C227" s="142"/>
-      <c r="D227" s="160"/>
+      <c r="C227" s="159"/>
+      <c r="D227" s="141"/>
       <c r="E227" s="8" t="s">
         <v>298</v>
       </c>
@@ -9958,8 +10024,8 @@
       <c r="B228" s="7">
         <v>13</v>
       </c>
-      <c r="C228" s="142"/>
-      <c r="D228" s="160"/>
+      <c r="C228" s="159"/>
+      <c r="D228" s="141"/>
       <c r="E228" s="8" t="s">
         <v>299</v>
       </c>
@@ -9980,8 +10046,8 @@
       <c r="B229" s="7">
         <v>14</v>
       </c>
-      <c r="C229" s="142"/>
-      <c r="D229" s="160"/>
+      <c r="C229" s="159"/>
+      <c r="D229" s="141"/>
       <c r="E229" s="8" t="s">
         <v>300</v>
       </c>
@@ -10002,8 +10068,8 @@
       <c r="B230" s="7">
         <v>15</v>
       </c>
-      <c r="C230" s="142"/>
-      <c r="D230" s="160"/>
+      <c r="C230" s="159"/>
+      <c r="D230" s="141"/>
       <c r="E230" s="8" t="s">
         <v>301</v>
       </c>
@@ -10024,8 +10090,8 @@
       <c r="B231" s="7">
         <v>16</v>
       </c>
-      <c r="C231" s="142"/>
-      <c r="D231" s="160"/>
+      <c r="C231" s="159"/>
+      <c r="D231" s="141"/>
       <c r="E231" s="8" t="s">
         <v>302</v>
       </c>
@@ -10046,8 +10112,8 @@
       <c r="B232" s="7">
         <v>17</v>
       </c>
-      <c r="C232" s="142"/>
-      <c r="D232" s="160"/>
+      <c r="C232" s="159"/>
+      <c r="D232" s="141"/>
       <c r="E232" s="8" t="s">
         <v>303</v>
       </c>
@@ -10068,8 +10134,8 @@
       <c r="B233" s="7">
         <v>18</v>
       </c>
-      <c r="C233" s="142"/>
-      <c r="D233" s="161"/>
+      <c r="C233" s="159"/>
+      <c r="D233" s="142"/>
       <c r="E233" s="8" t="s">
         <v>304</v>
       </c>
@@ -10090,8 +10156,8 @@
       <c r="B234" s="7">
         <v>19</v>
       </c>
-      <c r="C234" s="142"/>
-      <c r="D234" s="159" t="s">
+      <c r="C234" s="159"/>
+      <c r="D234" s="140" t="s">
         <v>305</v>
       </c>
       <c r="E234" s="8" t="s">
@@ -10114,8 +10180,8 @@
       <c r="B235" s="7">
         <v>20</v>
       </c>
-      <c r="C235" s="142"/>
-      <c r="D235" s="160"/>
+      <c r="C235" s="159"/>
+      <c r="D235" s="141"/>
       <c r="E235" s="8" t="s">
         <v>307</v>
       </c>
@@ -10136,8 +10202,8 @@
       <c r="B236" s="7">
         <v>21</v>
       </c>
-      <c r="C236" s="142"/>
-      <c r="D236" s="160"/>
+      <c r="C236" s="159"/>
+      <c r="D236" s="141"/>
       <c r="E236" s="8" t="s">
         <v>308</v>
       </c>
@@ -10158,8 +10224,8 @@
       <c r="B237" s="7">
         <v>22</v>
       </c>
-      <c r="C237" s="142"/>
-      <c r="D237" s="160"/>
+      <c r="C237" s="159"/>
+      <c r="D237" s="141"/>
       <c r="E237" s="8" t="s">
         <v>309</v>
       </c>
@@ -10180,8 +10246,8 @@
       <c r="B238" s="7">
         <v>23</v>
       </c>
-      <c r="C238" s="142"/>
-      <c r="D238" s="160"/>
+      <c r="C238" s="159"/>
+      <c r="D238" s="141"/>
       <c r="E238" s="8" t="s">
         <v>310</v>
       </c>
@@ -10202,8 +10268,8 @@
       <c r="B239" s="7">
         <v>24</v>
       </c>
-      <c r="C239" s="142"/>
-      <c r="D239" s="160"/>
+      <c r="C239" s="159"/>
+      <c r="D239" s="141"/>
       <c r="E239" s="8" t="s">
         <v>311</v>
       </c>
@@ -10224,8 +10290,8 @@
       <c r="B240" s="7">
         <v>25</v>
       </c>
-      <c r="C240" s="142"/>
-      <c r="D240" s="161"/>
+      <c r="C240" s="159"/>
+      <c r="D240" s="142"/>
       <c r="E240" s="8" t="s">
         <v>312</v>
       </c>
@@ -10246,8 +10312,8 @@
       <c r="B241" s="7">
         <v>26</v>
       </c>
-      <c r="C241" s="142"/>
-      <c r="D241" s="159" t="s">
+      <c r="C241" s="159"/>
+      <c r="D241" s="140" t="s">
         <v>313</v>
       </c>
       <c r="E241" s="8" t="s">
@@ -10270,8 +10336,8 @@
       <c r="B242" s="7">
         <v>27</v>
       </c>
-      <c r="C242" s="142"/>
-      <c r="D242" s="160"/>
+      <c r="C242" s="159"/>
+      <c r="D242" s="141"/>
       <c r="E242" s="8" t="s">
         <v>315</v>
       </c>
@@ -10292,8 +10358,8 @@
       <c r="B243" s="7">
         <v>28</v>
       </c>
-      <c r="C243" s="142"/>
-      <c r="D243" s="161"/>
+      <c r="C243" s="159"/>
+      <c r="D243" s="142"/>
       <c r="E243" s="8" t="s">
         <v>316</v>
       </c>
@@ -10314,8 +10380,8 @@
       <c r="B244" s="7">
         <v>29</v>
       </c>
-      <c r="C244" s="142"/>
-      <c r="D244" s="159" t="s">
+      <c r="C244" s="159"/>
+      <c r="D244" s="140" t="s">
         <v>317</v>
       </c>
       <c r="E244" s="8" t="s">
@@ -10338,8 +10404,8 @@
       <c r="B245" s="7">
         <v>30</v>
       </c>
-      <c r="C245" s="142"/>
-      <c r="D245" s="160"/>
+      <c r="C245" s="159"/>
+      <c r="D245" s="141"/>
       <c r="E245" s="8" t="s">
         <v>319</v>
       </c>
@@ -10360,8 +10426,8 @@
       <c r="B246" s="7">
         <v>31</v>
       </c>
-      <c r="C246" s="142"/>
-      <c r="D246" s="160"/>
+      <c r="C246" s="159"/>
+      <c r="D246" s="141"/>
       <c r="E246" s="8" t="s">
         <v>320</v>
       </c>
@@ -10382,8 +10448,8 @@
       <c r="B247" s="7">
         <v>32</v>
       </c>
-      <c r="C247" s="142"/>
-      <c r="D247" s="160"/>
+      <c r="C247" s="159"/>
+      <c r="D247" s="141"/>
       <c r="E247" s="8" t="s">
         <v>321</v>
       </c>
@@ -10404,8 +10470,8 @@
       <c r="B248" s="7">
         <v>33</v>
       </c>
-      <c r="C248" s="142"/>
-      <c r="D248" s="160"/>
+      <c r="C248" s="159"/>
+      <c r="D248" s="141"/>
       <c r="E248" s="8" t="s">
         <v>322</v>
       </c>
@@ -10426,8 +10492,8 @@
       <c r="B249" s="24">
         <v>34</v>
       </c>
-      <c r="C249" s="143"/>
-      <c r="D249" s="161"/>
+      <c r="C249" s="160"/>
+      <c r="D249" s="142"/>
       <c r="E249" s="17" t="s">
         <v>323</v>
       </c>
@@ -10448,10 +10514,10 @@
       <c r="B250" s="7">
         <v>1</v>
       </c>
-      <c r="C250" s="144" t="s">
+      <c r="C250" s="149" t="s">
         <v>324</v>
       </c>
-      <c r="D250" s="159" t="s">
+      <c r="D250" s="140" t="s">
         <v>325</v>
       </c>
       <c r="E250" s="8" t="s">
@@ -10474,8 +10540,8 @@
       <c r="B251" s="7">
         <v>2</v>
       </c>
-      <c r="C251" s="145"/>
-      <c r="D251" s="160"/>
+      <c r="C251" s="150"/>
+      <c r="D251" s="141"/>
       <c r="E251" s="8" t="s">
         <v>327</v>
       </c>
@@ -10496,8 +10562,8 @@
       <c r="B252" s="7">
         <v>3</v>
       </c>
-      <c r="C252" s="145"/>
-      <c r="D252" s="160"/>
+      <c r="C252" s="150"/>
+      <c r="D252" s="141"/>
       <c r="E252" s="8" t="s">
         <v>328</v>
       </c>
@@ -10518,8 +10584,8 @@
       <c r="B253" s="7">
         <v>4</v>
       </c>
-      <c r="C253" s="145"/>
-      <c r="D253" s="160"/>
+      <c r="C253" s="150"/>
+      <c r="D253" s="141"/>
       <c r="E253" s="8" t="s">
         <v>329</v>
       </c>
@@ -10540,8 +10606,8 @@
       <c r="B254" s="7">
         <v>5</v>
       </c>
-      <c r="C254" s="145"/>
-      <c r="D254" s="160"/>
+      <c r="C254" s="150"/>
+      <c r="D254" s="141"/>
       <c r="E254" s="8" t="s">
         <v>330</v>
       </c>
@@ -10562,8 +10628,8 @@
       <c r="B255" s="7">
         <v>6</v>
       </c>
-      <c r="C255" s="145"/>
-      <c r="D255" s="160"/>
+      <c r="C255" s="150"/>
+      <c r="D255" s="141"/>
       <c r="E255" s="8" t="s">
         <v>331</v>
       </c>
@@ -10584,8 +10650,8 @@
       <c r="B256" s="7">
         <v>7</v>
       </c>
-      <c r="C256" s="145"/>
-      <c r="D256" s="160"/>
+      <c r="C256" s="150"/>
+      <c r="D256" s="141"/>
       <c r="E256" s="8" t="s">
         <v>332</v>
       </c>
@@ -10606,8 +10672,8 @@
       <c r="B257" s="7">
         <v>8</v>
       </c>
-      <c r="C257" s="145"/>
-      <c r="D257" s="161"/>
+      <c r="C257" s="150"/>
+      <c r="D257" s="142"/>
       <c r="E257" s="8" t="s">
         <v>333</v>
       </c>
@@ -10628,8 +10694,8 @@
       <c r="B258" s="7">
         <v>9</v>
       </c>
-      <c r="C258" s="145"/>
-      <c r="D258" s="159" t="s">
+      <c r="C258" s="150"/>
+      <c r="D258" s="140" t="s">
         <v>334</v>
       </c>
       <c r="E258" s="8" t="s">
@@ -10652,8 +10718,8 @@
       <c r="B259" s="7">
         <v>10</v>
       </c>
-      <c r="C259" s="145"/>
-      <c r="D259" s="161"/>
+      <c r="C259" s="150"/>
+      <c r="D259" s="142"/>
       <c r="E259" s="8" t="s">
         <v>336</v>
       </c>
@@ -10674,8 +10740,8 @@
       <c r="B260" s="7">
         <v>11</v>
       </c>
-      <c r="C260" s="145"/>
-      <c r="D260" s="159" t="s">
+      <c r="C260" s="150"/>
+      <c r="D260" s="140" t="s">
         <v>337</v>
       </c>
       <c r="E260" s="8" t="s">
@@ -10698,8 +10764,8 @@
       <c r="B261" s="7">
         <v>12</v>
       </c>
-      <c r="C261" s="145"/>
-      <c r="D261" s="160"/>
+      <c r="C261" s="150"/>
+      <c r="D261" s="141"/>
       <c r="E261" s="8" t="s">
         <v>339</v>
       </c>
@@ -10720,8 +10786,8 @@
       <c r="B262" s="7">
         <v>13</v>
       </c>
-      <c r="C262" s="145"/>
-      <c r="D262" s="160"/>
+      <c r="C262" s="150"/>
+      <c r="D262" s="141"/>
       <c r="E262" s="8" t="s">
         <v>340</v>
       </c>
@@ -10742,8 +10808,8 @@
       <c r="B263" s="7">
         <v>14</v>
       </c>
-      <c r="C263" s="145"/>
-      <c r="D263" s="160"/>
+      <c r="C263" s="150"/>
+      <c r="D263" s="141"/>
       <c r="E263" s="8" t="s">
         <v>341</v>
       </c>
@@ -10764,8 +10830,8 @@
       <c r="B264" s="7">
         <v>15</v>
       </c>
-      <c r="C264" s="145"/>
-      <c r="D264" s="160"/>
+      <c r="C264" s="150"/>
+      <c r="D264" s="141"/>
       <c r="E264" s="8" t="s">
         <v>342</v>
       </c>
@@ -10786,8 +10852,8 @@
       <c r="B265" s="24">
         <v>16</v>
       </c>
-      <c r="C265" s="146"/>
-      <c r="D265" s="161"/>
+      <c r="C265" s="151"/>
+      <c r="D265" s="142"/>
       <c r="E265" s="17" t="s">
         <v>343</v>
       </c>
@@ -10808,10 +10874,10 @@
       <c r="B266" s="7">
         <v>1</v>
       </c>
-      <c r="C266" s="147" t="s">
+      <c r="C266" s="152" t="s">
         <v>344</v>
       </c>
-      <c r="D266" s="159" t="s">
+      <c r="D266" s="140" t="s">
         <v>345</v>
       </c>
       <c r="E266" s="8" t="s">
@@ -10834,8 +10900,8 @@
       <c r="B267" s="7">
         <v>2</v>
       </c>
-      <c r="C267" s="148"/>
-      <c r="D267" s="160"/>
+      <c r="C267" s="153"/>
+      <c r="D267" s="141"/>
       <c r="E267" s="8" t="s">
         <v>347</v>
       </c>
@@ -10856,8 +10922,8 @@
       <c r="B268" s="7">
         <v>3</v>
       </c>
-      <c r="C268" s="148"/>
-      <c r="D268" s="160"/>
+      <c r="C268" s="153"/>
+      <c r="D268" s="141"/>
       <c r="E268" s="8" t="s">
         <v>348</v>
       </c>
@@ -10878,8 +10944,8 @@
       <c r="B269" s="7">
         <v>4</v>
       </c>
-      <c r="C269" s="148"/>
-      <c r="D269" s="160"/>
+      <c r="C269" s="153"/>
+      <c r="D269" s="141"/>
       <c r="E269" s="8" t="s">
         <v>349</v>
       </c>
@@ -10900,8 +10966,8 @@
       <c r="B270" s="7">
         <v>5</v>
       </c>
-      <c r="C270" s="148"/>
-      <c r="D270" s="161"/>
+      <c r="C270" s="153"/>
+      <c r="D270" s="142"/>
       <c r="E270" s="8" t="s">
         <v>350</v>
       </c>
@@ -10922,8 +10988,8 @@
       <c r="B271" s="7">
         <v>6</v>
       </c>
-      <c r="C271" s="148"/>
-      <c r="D271" s="159" t="s">
+      <c r="C271" s="153"/>
+      <c r="D271" s="140" t="s">
         <v>351</v>
       </c>
       <c r="E271" s="8" t="s">
@@ -10946,8 +11012,8 @@
       <c r="B272" s="7">
         <v>7</v>
       </c>
-      <c r="C272" s="149"/>
-      <c r="D272" s="161"/>
+      <c r="C272" s="154"/>
+      <c r="D272" s="142"/>
       <c r="E272" s="8" t="s">
         <v>353</v>
       </c>
@@ -10962,18 +11028,18 @@
       <c r="J272" s="11"/>
     </row>
     <row r="273" spans="1:10" ht="13.8">
-      <c r="A273" s="171" t="s">
+      <c r="A273" s="173" t="s">
         <v>354</v>
       </c>
-      <c r="B273" s="172"/>
-      <c r="C273" s="172"/>
-      <c r="D273" s="172"/>
-      <c r="E273" s="172"/>
-      <c r="F273" s="172"/>
-      <c r="G273" s="172"/>
-      <c r="H273" s="172"/>
-      <c r="I273" s="172"/>
-      <c r="J273" s="173"/>
+      <c r="B273" s="174"/>
+      <c r="C273" s="174"/>
+      <c r="D273" s="174"/>
+      <c r="E273" s="174"/>
+      <c r="F273" s="174"/>
+      <c r="G273" s="174"/>
+      <c r="H273" s="174"/>
+      <c r="I273" s="174"/>
+      <c r="J273" s="175"/>
     </row>
     <row r="274" spans="1:10" ht="13.8">
       <c r="A274" s="33">
@@ -10982,10 +11048,10 @@
       <c r="B274" s="7">
         <v>1</v>
       </c>
-      <c r="C274" s="150" t="s">
+      <c r="C274" s="167" t="s">
         <v>355</v>
       </c>
-      <c r="D274" s="162" t="s">
+      <c r="D274" s="170" t="s">
         <v>356</v>
       </c>
       <c r="E274" s="13" t="s">
@@ -11008,8 +11074,8 @@
       <c r="B275" s="7">
         <v>2</v>
       </c>
-      <c r="C275" s="151"/>
-      <c r="D275" s="163"/>
+      <c r="C275" s="168"/>
+      <c r="D275" s="171"/>
       <c r="E275" s="13" t="s">
         <v>358</v>
       </c>
@@ -11030,8 +11096,8 @@
       <c r="B276" s="7">
         <v>3</v>
       </c>
-      <c r="C276" s="151"/>
-      <c r="D276" s="163"/>
+      <c r="C276" s="168"/>
+      <c r="D276" s="171"/>
       <c r="E276" s="8" t="s">
         <v>359</v>
       </c>
@@ -11052,8 +11118,8 @@
       <c r="B277" s="7">
         <v>4</v>
       </c>
-      <c r="C277" s="151"/>
-      <c r="D277" s="163"/>
+      <c r="C277" s="168"/>
+      <c r="D277" s="171"/>
       <c r="E277" s="8" t="s">
         <v>360</v>
       </c>
@@ -11074,8 +11140,8 @@
       <c r="B278" s="7">
         <v>5</v>
       </c>
-      <c r="C278" s="151"/>
-      <c r="D278" s="163"/>
+      <c r="C278" s="168"/>
+      <c r="D278" s="171"/>
       <c r="E278" s="8" t="s">
         <v>361</v>
       </c>
@@ -11096,8 +11162,8 @@
       <c r="B279" s="7">
         <v>6</v>
       </c>
-      <c r="C279" s="151"/>
-      <c r="D279" s="163"/>
+      <c r="C279" s="168"/>
+      <c r="D279" s="171"/>
       <c r="E279" s="8" t="s">
         <v>362</v>
       </c>
@@ -11118,8 +11184,8 @@
       <c r="B280" s="7">
         <v>7</v>
       </c>
-      <c r="C280" s="151"/>
-      <c r="D280" s="163"/>
+      <c r="C280" s="168"/>
+      <c r="D280" s="171"/>
       <c r="E280" s="8" t="s">
         <v>363</v>
       </c>
@@ -11140,8 +11206,8 @@
       <c r="B281" s="7">
         <v>8</v>
       </c>
-      <c r="C281" s="151"/>
-      <c r="D281" s="164"/>
+      <c r="C281" s="168"/>
+      <c r="D281" s="172"/>
       <c r="E281" s="13" t="s">
         <v>364</v>
       </c>
@@ -11162,8 +11228,8 @@
       <c r="B282" s="7">
         <v>9</v>
       </c>
-      <c r="C282" s="151"/>
-      <c r="D282" s="162" t="s">
+      <c r="C282" s="168"/>
+      <c r="D282" s="170" t="s">
         <v>365</v>
       </c>
       <c r="E282" s="8" t="s">
@@ -11186,8 +11252,8 @@
       <c r="B283" s="7">
         <v>10</v>
       </c>
-      <c r="C283" s="151"/>
-      <c r="D283" s="163"/>
+      <c r="C283" s="168"/>
+      <c r="D283" s="171"/>
       <c r="E283" s="13" t="s">
         <v>367</v>
       </c>
@@ -11208,8 +11274,8 @@
       <c r="B284" s="7">
         <v>11</v>
       </c>
-      <c r="C284" s="151"/>
-      <c r="D284" s="163"/>
+      <c r="C284" s="168"/>
+      <c r="D284" s="171"/>
       <c r="E284" s="13" t="s">
         <v>368</v>
       </c>
@@ -11230,8 +11296,8 @@
       <c r="B285" s="7">
         <v>12</v>
       </c>
-      <c r="C285" s="151"/>
-      <c r="D285" s="163"/>
+      <c r="C285" s="168"/>
+      <c r="D285" s="171"/>
       <c r="E285" s="13" t="s">
         <v>369</v>
       </c>
@@ -11252,8 +11318,8 @@
       <c r="B286" s="7">
         <v>13</v>
       </c>
-      <c r="C286" s="151"/>
-      <c r="D286" s="163"/>
+      <c r="C286" s="168"/>
+      <c r="D286" s="171"/>
       <c r="E286" s="13" t="s">
         <v>370</v>
       </c>
@@ -11274,8 +11340,8 @@
       <c r="B287" s="7">
         <v>14</v>
       </c>
-      <c r="C287" s="151"/>
-      <c r="D287" s="163"/>
+      <c r="C287" s="168"/>
+      <c r="D287" s="171"/>
       <c r="E287" s="13" t="s">
         <v>371</v>
       </c>
@@ -11296,8 +11362,8 @@
       <c r="B288" s="7">
         <v>15</v>
       </c>
-      <c r="C288" s="151"/>
-      <c r="D288" s="164"/>
+      <c r="C288" s="168"/>
+      <c r="D288" s="172"/>
       <c r="E288" s="13" t="s">
         <v>372</v>
       </c>
@@ -11318,8 +11384,8 @@
       <c r="B289" s="7">
         <v>16</v>
       </c>
-      <c r="C289" s="151"/>
-      <c r="D289" s="162" t="s">
+      <c r="C289" s="168"/>
+      <c r="D289" s="170" t="s">
         <v>373</v>
       </c>
       <c r="E289" s="13" t="s">
@@ -11342,8 +11408,8 @@
       <c r="B290" s="7">
         <v>17</v>
       </c>
-      <c r="C290" s="151"/>
-      <c r="D290" s="163"/>
+      <c r="C290" s="168"/>
+      <c r="D290" s="171"/>
       <c r="E290" s="8" t="s">
         <v>375</v>
       </c>
@@ -11364,8 +11430,8 @@
       <c r="B291" s="7">
         <v>18</v>
       </c>
-      <c r="C291" s="151"/>
-      <c r="D291" s="163"/>
+      <c r="C291" s="168"/>
+      <c r="D291" s="171"/>
       <c r="E291" s="11" t="s">
         <v>376</v>
       </c>
@@ -11386,8 +11452,8 @@
       <c r="B292" s="24">
         <v>19</v>
       </c>
-      <c r="C292" s="152"/>
-      <c r="D292" s="164"/>
+      <c r="C292" s="169"/>
+      <c r="D292" s="172"/>
       <c r="E292" s="20" t="s">
         <v>377</v>
       </c>
@@ -11408,10 +11474,10 @@
       <c r="B293" s="7">
         <v>1</v>
       </c>
-      <c r="C293" s="141" t="s">
+      <c r="C293" s="158" t="s">
         <v>378</v>
       </c>
-      <c r="D293" s="159" t="s">
+      <c r="D293" s="140" t="s">
         <v>379</v>
       </c>
       <c r="E293" s="8" t="s">
@@ -11434,8 +11500,8 @@
       <c r="B294" s="7">
         <v>2</v>
       </c>
-      <c r="C294" s="142"/>
-      <c r="D294" s="160"/>
+      <c r="C294" s="159"/>
+      <c r="D294" s="141"/>
       <c r="E294" s="8" t="s">
         <v>381</v>
       </c>
@@ -11456,8 +11522,8 @@
       <c r="B295" s="7">
         <v>3</v>
       </c>
-      <c r="C295" s="142"/>
-      <c r="D295" s="161"/>
+      <c r="C295" s="159"/>
+      <c r="D295" s="142"/>
       <c r="E295" s="8" t="s">
         <v>382</v>
       </c>
@@ -11476,8 +11542,8 @@
       <c r="B296" s="7">
         <v>4</v>
       </c>
-      <c r="C296" s="142"/>
-      <c r="D296" s="159" t="s">
+      <c r="C296" s="159"/>
+      <c r="D296" s="140" t="s">
         <v>383</v>
       </c>
       <c r="E296" s="37" t="s">
@@ -11500,8 +11566,8 @@
       <c r="B297" s="7">
         <v>5</v>
       </c>
-      <c r="C297" s="142"/>
-      <c r="D297" s="160"/>
+      <c r="C297" s="159"/>
+      <c r="D297" s="141"/>
       <c r="E297" s="8" t="s">
         <v>385</v>
       </c>
@@ -11522,8 +11588,8 @@
       <c r="B298" s="7">
         <v>6</v>
       </c>
-      <c r="C298" s="142"/>
-      <c r="D298" s="160"/>
+      <c r="C298" s="159"/>
+      <c r="D298" s="141"/>
       <c r="E298" s="8" t="s">
         <v>386</v>
       </c>
@@ -11544,8 +11610,8 @@
       <c r="B299" s="7">
         <v>7</v>
       </c>
-      <c r="C299" s="142"/>
-      <c r="D299" s="160"/>
+      <c r="C299" s="159"/>
+      <c r="D299" s="141"/>
       <c r="E299" s="8" t="s">
         <v>387</v>
       </c>
@@ -11566,8 +11632,8 @@
       <c r="B300" s="7">
         <v>8</v>
       </c>
-      <c r="C300" s="142"/>
-      <c r="D300" s="161"/>
+      <c r="C300" s="159"/>
+      <c r="D300" s="142"/>
       <c r="E300" s="8" t="s">
         <v>388</v>
       </c>
@@ -11588,8 +11654,8 @@
       <c r="B301" s="7">
         <v>9</v>
       </c>
-      <c r="C301" s="142"/>
-      <c r="D301" s="159" t="s">
+      <c r="C301" s="159"/>
+      <c r="D301" s="140" t="s">
         <v>389</v>
       </c>
       <c r="E301" s="8" t="s">
@@ -11612,8 +11678,8 @@
       <c r="B302" s="7">
         <v>10</v>
       </c>
-      <c r="C302" s="142"/>
-      <c r="D302" s="160"/>
+      <c r="C302" s="159"/>
+      <c r="D302" s="141"/>
       <c r="E302" s="8" t="s">
         <v>391</v>
       </c>
@@ -11634,8 +11700,8 @@
       <c r="B303" s="7">
         <v>11</v>
       </c>
-      <c r="C303" s="142"/>
-      <c r="D303" s="161"/>
+      <c r="C303" s="159"/>
+      <c r="D303" s="142"/>
       <c r="E303" s="8" t="s">
         <v>392</v>
       </c>
@@ -11656,8 +11722,8 @@
       <c r="B304" s="7">
         <v>12</v>
       </c>
-      <c r="C304" s="142"/>
-      <c r="D304" s="159" t="s">
+      <c r="C304" s="159"/>
+      <c r="D304" s="140" t="s">
         <v>393</v>
       </c>
       <c r="E304" s="8" t="s">
@@ -11680,8 +11746,8 @@
       <c r="B305" s="7">
         <v>13</v>
       </c>
-      <c r="C305" s="142"/>
-      <c r="D305" s="160"/>
+      <c r="C305" s="159"/>
+      <c r="D305" s="141"/>
       <c r="E305" s="8" t="s">
         <v>395</v>
       </c>
@@ -11702,8 +11768,8 @@
       <c r="B306" s="7">
         <v>14</v>
       </c>
-      <c r="C306" s="142"/>
-      <c r="D306" s="160"/>
+      <c r="C306" s="159"/>
+      <c r="D306" s="141"/>
       <c r="E306" s="8" t="s">
         <v>396</v>
       </c>
@@ -11724,8 +11790,8 @@
       <c r="B307" s="24">
         <v>15</v>
       </c>
-      <c r="C307" s="143"/>
-      <c r="D307" s="161"/>
+      <c r="C307" s="160"/>
+      <c r="D307" s="142"/>
       <c r="E307" s="17" t="s">
         <v>397</v>
       </c>
@@ -11746,10 +11812,10 @@
       <c r="B308" s="7">
         <v>1</v>
       </c>
-      <c r="C308" s="153" t="s">
+      <c r="C308" s="185" t="s">
         <v>398</v>
       </c>
-      <c r="D308" s="162" t="s">
+      <c r="D308" s="170" t="s">
         <v>399</v>
       </c>
       <c r="E308" s="13" t="s">
@@ -11772,8 +11838,8 @@
       <c r="B309" s="7">
         <v>2</v>
       </c>
-      <c r="C309" s="154"/>
-      <c r="D309" s="163"/>
+      <c r="C309" s="186"/>
+      <c r="D309" s="171"/>
       <c r="E309" s="8" t="s">
         <v>401</v>
       </c>
@@ -11794,8 +11860,8 @@
       <c r="B310" s="7">
         <v>3</v>
       </c>
-      <c r="C310" s="154"/>
-      <c r="D310" s="163"/>
+      <c r="C310" s="186"/>
+      <c r="D310" s="171"/>
       <c r="E310" s="13" t="s">
         <v>402</v>
       </c>
@@ -11816,8 +11882,8 @@
       <c r="B311" s="7">
         <v>4</v>
       </c>
-      <c r="C311" s="154"/>
-      <c r="D311" s="163"/>
+      <c r="C311" s="186"/>
+      <c r="D311" s="171"/>
       <c r="E311" s="8" t="s">
         <v>403</v>
       </c>
@@ -11838,8 +11904,8 @@
       <c r="B312" s="7">
         <v>5</v>
       </c>
-      <c r="C312" s="154"/>
-      <c r="D312" s="163"/>
+      <c r="C312" s="186"/>
+      <c r="D312" s="171"/>
       <c r="E312" s="13" t="s">
         <v>404</v>
       </c>
@@ -11860,8 +11926,8 @@
       <c r="B313" s="7">
         <v>6</v>
       </c>
-      <c r="C313" s="154"/>
-      <c r="D313" s="163"/>
+      <c r="C313" s="186"/>
+      <c r="D313" s="171"/>
       <c r="E313" s="13" t="s">
         <v>405</v>
       </c>
@@ -11882,8 +11948,8 @@
       <c r="B314" s="7">
         <v>7</v>
       </c>
-      <c r="C314" s="154"/>
-      <c r="D314" s="164"/>
+      <c r="C314" s="186"/>
+      <c r="D314" s="172"/>
       <c r="E314" s="8" t="s">
         <v>406</v>
       </c>
@@ -11904,8 +11970,8 @@
       <c r="B315" s="7">
         <v>8</v>
       </c>
-      <c r="C315" s="154"/>
-      <c r="D315" s="162" t="s">
+      <c r="C315" s="186"/>
+      <c r="D315" s="170" t="s">
         <v>407</v>
       </c>
       <c r="E315" s="13" t="s">
@@ -11928,8 +11994,8 @@
       <c r="B316" s="7">
         <v>9</v>
       </c>
-      <c r="C316" s="154"/>
-      <c r="D316" s="163"/>
+      <c r="C316" s="186"/>
+      <c r="D316" s="171"/>
       <c r="E316" s="8" t="s">
         <v>409</v>
       </c>
@@ -11950,8 +12016,8 @@
       <c r="B317" s="24">
         <v>10</v>
       </c>
-      <c r="C317" s="155"/>
-      <c r="D317" s="164"/>
+      <c r="C317" s="187"/>
+      <c r="D317" s="172"/>
       <c r="E317" s="17" t="s">
         <v>410</v>
       </c>
@@ -11972,10 +12038,10 @@
       <c r="B318" s="7">
         <v>1</v>
       </c>
-      <c r="C318" s="156" t="s">
+      <c r="C318" s="188" t="s">
         <v>411</v>
       </c>
-      <c r="D318" s="162" t="s">
+      <c r="D318" s="170" t="s">
         <v>412</v>
       </c>
       <c r="E318" s="8" t="s">
@@ -11998,8 +12064,8 @@
       <c r="B319" s="7">
         <v>2</v>
       </c>
-      <c r="C319" s="157"/>
-      <c r="D319" s="163"/>
+      <c r="C319" s="189"/>
+      <c r="D319" s="171"/>
       <c r="E319" s="13" t="s">
         <v>414</v>
       </c>
@@ -12020,8 +12086,8 @@
       <c r="B320" s="7">
         <v>3</v>
       </c>
-      <c r="C320" s="157"/>
-      <c r="D320" s="163"/>
+      <c r="C320" s="189"/>
+      <c r="D320" s="171"/>
       <c r="E320" s="8" t="s">
         <v>415</v>
       </c>
@@ -12042,8 +12108,8 @@
       <c r="B321" s="7">
         <v>4</v>
       </c>
-      <c r="C321" s="157"/>
-      <c r="D321" s="163"/>
+      <c r="C321" s="189"/>
+      <c r="D321" s="171"/>
       <c r="E321" s="8" t="s">
         <v>416</v>
       </c>
@@ -12064,8 +12130,8 @@
       <c r="B322" s="7">
         <v>5</v>
       </c>
-      <c r="C322" s="157"/>
-      <c r="D322" s="163"/>
+      <c r="C322" s="189"/>
+      <c r="D322" s="171"/>
       <c r="E322" s="8" t="s">
         <v>417</v>
       </c>
@@ -12086,8 +12152,8 @@
       <c r="B323" s="7">
         <v>6</v>
       </c>
-      <c r="C323" s="157"/>
-      <c r="D323" s="164"/>
+      <c r="C323" s="189"/>
+      <c r="D323" s="172"/>
       <c r="E323" s="29" t="s">
         <v>418</v>
       </c>
@@ -12108,8 +12174,8 @@
       <c r="B324" s="7">
         <v>7</v>
       </c>
-      <c r="C324" s="157"/>
-      <c r="D324" s="162" t="s">
+      <c r="C324" s="189"/>
+      <c r="D324" s="170" t="s">
         <v>419</v>
       </c>
       <c r="E324" s="13" t="s">
@@ -12132,8 +12198,8 @@
       <c r="B325" s="7">
         <v>8</v>
       </c>
-      <c r="C325" s="157"/>
-      <c r="D325" s="163"/>
+      <c r="C325" s="189"/>
+      <c r="D325" s="171"/>
       <c r="E325" s="8" t="s">
         <v>421</v>
       </c>
@@ -12154,8 +12220,8 @@
       <c r="B326" s="7">
         <v>9</v>
       </c>
-      <c r="C326" s="157"/>
-      <c r="D326" s="163"/>
+      <c r="C326" s="189"/>
+      <c r="D326" s="171"/>
       <c r="E326" s="8" t="s">
         <v>422</v>
       </c>
@@ -12176,8 +12242,8 @@
       <c r="B327" s="7">
         <v>10</v>
       </c>
-      <c r="C327" s="157"/>
-      <c r="D327" s="163"/>
+      <c r="C327" s="189"/>
+      <c r="D327" s="171"/>
       <c r="E327" s="8" t="s">
         <v>423</v>
       </c>
@@ -12198,8 +12264,8 @@
       <c r="B328" s="7">
         <v>11</v>
       </c>
-      <c r="C328" s="157"/>
-      <c r="D328" s="164"/>
+      <c r="C328" s="189"/>
+      <c r="D328" s="172"/>
       <c r="E328" s="13" t="s">
         <v>424</v>
       </c>
@@ -12220,8 +12286,8 @@
       <c r="B329" s="7">
         <v>12</v>
       </c>
-      <c r="C329" s="157"/>
-      <c r="D329" s="162" t="s">
+      <c r="C329" s="189"/>
+      <c r="D329" s="170" t="s">
         <v>425</v>
       </c>
       <c r="E329" s="8" t="s">
@@ -12244,8 +12310,8 @@
       <c r="B330" s="7">
         <v>13</v>
       </c>
-      <c r="C330" s="157"/>
-      <c r="D330" s="163"/>
+      <c r="C330" s="189"/>
+      <c r="D330" s="171"/>
       <c r="E330" s="8" t="s">
         <v>427</v>
       </c>
@@ -12266,8 +12332,8 @@
       <c r="B331" s="7">
         <v>14</v>
       </c>
-      <c r="C331" s="157"/>
-      <c r="D331" s="163"/>
+      <c r="C331" s="189"/>
+      <c r="D331" s="171"/>
       <c r="E331" s="8" t="s">
         <v>428</v>
       </c>
@@ -12288,8 +12354,8 @@
       <c r="B332" s="7">
         <v>15</v>
       </c>
-      <c r="C332" s="157"/>
-      <c r="D332" s="163"/>
+      <c r="C332" s="189"/>
+      <c r="D332" s="171"/>
       <c r="E332" s="8" t="s">
         <v>429</v>
       </c>
@@ -12310,8 +12376,8 @@
       <c r="B333" s="7">
         <v>16</v>
       </c>
-      <c r="C333" s="157"/>
-      <c r="D333" s="163"/>
+      <c r="C333" s="189"/>
+      <c r="D333" s="171"/>
       <c r="E333" s="8" t="s">
         <v>430</v>
       </c>
@@ -12332,8 +12398,8 @@
       <c r="B334" s="7">
         <v>17</v>
       </c>
-      <c r="C334" s="157"/>
-      <c r="D334" s="163"/>
+      <c r="C334" s="189"/>
+      <c r="D334" s="171"/>
       <c r="E334" s="8" t="s">
         <v>431</v>
       </c>
@@ -12354,8 +12420,8 @@
       <c r="B335" s="7">
         <v>18</v>
       </c>
-      <c r="C335" s="157"/>
-      <c r="D335" s="163"/>
+      <c r="C335" s="189"/>
+      <c r="D335" s="171"/>
       <c r="E335" s="8" t="s">
         <v>432</v>
       </c>
@@ -12376,8 +12442,8 @@
       <c r="B336" s="7">
         <v>19</v>
       </c>
-      <c r="C336" s="157"/>
-      <c r="D336" s="163"/>
+      <c r="C336" s="189"/>
+      <c r="D336" s="171"/>
       <c r="E336" s="8" t="s">
         <v>433</v>
       </c>
@@ -12398,8 +12464,8 @@
       <c r="B337" s="7">
         <v>20</v>
       </c>
-      <c r="C337" s="157"/>
-      <c r="D337" s="164"/>
+      <c r="C337" s="189"/>
+      <c r="D337" s="172"/>
       <c r="E337" s="13" t="s">
         <v>434</v>
       </c>
@@ -12420,8 +12486,8 @@
       <c r="B338" s="7">
         <v>21</v>
       </c>
-      <c r="C338" s="157"/>
-      <c r="D338" s="162" t="s">
+      <c r="C338" s="189"/>
+      <c r="D338" s="170" t="s">
         <v>435</v>
       </c>
       <c r="E338" s="13" t="s">
@@ -12444,8 +12510,8 @@
       <c r="B339" s="7">
         <v>22</v>
       </c>
-      <c r="C339" s="157"/>
-      <c r="D339" s="163"/>
+      <c r="C339" s="189"/>
+      <c r="D339" s="171"/>
       <c r="E339" s="13" t="s">
         <v>437</v>
       </c>
@@ -12466,8 +12532,8 @@
       <c r="B340" s="7">
         <v>23</v>
       </c>
-      <c r="C340" s="157"/>
-      <c r="D340" s="163"/>
+      <c r="C340" s="189"/>
+      <c r="D340" s="171"/>
       <c r="E340" s="13" t="s">
         <v>438</v>
       </c>
@@ -12488,8 +12554,8 @@
       <c r="B341" s="7">
         <v>24</v>
       </c>
-      <c r="C341" s="157"/>
-      <c r="D341" s="163"/>
+      <c r="C341" s="189"/>
+      <c r="D341" s="171"/>
       <c r="E341" s="13" t="s">
         <v>439</v>
       </c>
@@ -12510,8 +12576,8 @@
       <c r="B342" s="24">
         <v>25</v>
       </c>
-      <c r="C342" s="158"/>
-      <c r="D342" s="164"/>
+      <c r="C342" s="190"/>
+      <c r="D342" s="172"/>
       <c r="E342" s="25" t="s">
         <v>440</v>
       </c>
@@ -12532,10 +12598,10 @@
       <c r="B343" s="7">
         <v>1</v>
       </c>
-      <c r="C343" s="138" t="s">
+      <c r="C343" s="155" t="s">
         <v>441</v>
       </c>
-      <c r="D343" s="159" t="s">
+      <c r="D343" s="140" t="s">
         <v>442</v>
       </c>
       <c r="E343" s="8" t="s">
@@ -12564,8 +12630,8 @@
       <c r="B344" s="7">
         <v>2</v>
       </c>
-      <c r="C344" s="139"/>
-      <c r="D344" s="160"/>
+      <c r="C344" s="156"/>
+      <c r="D344" s="141"/>
       <c r="E344" s="8" t="s">
         <v>444</v>
       </c>
@@ -12592,8 +12658,8 @@
       <c r="B345" s="7">
         <v>3</v>
       </c>
-      <c r="C345" s="139"/>
-      <c r="D345" s="160"/>
+      <c r="C345" s="156"/>
+      <c r="D345" s="141"/>
       <c r="E345" s="8" t="s">
         <v>445</v>
       </c>
@@ -12620,8 +12686,8 @@
       <c r="B346" s="7">
         <v>4</v>
       </c>
-      <c r="C346" s="139"/>
-      <c r="D346" s="160"/>
+      <c r="C346" s="156"/>
+      <c r="D346" s="141"/>
       <c r="E346" s="8" t="s">
         <v>446</v>
       </c>
@@ -12648,8 +12714,8 @@
       <c r="B347" s="7">
         <v>5</v>
       </c>
-      <c r="C347" s="139"/>
-      <c r="D347" s="161"/>
+      <c r="C347" s="156"/>
+      <c r="D347" s="142"/>
       <c r="E347" s="8" t="s">
         <v>447</v>
       </c>
@@ -12676,8 +12742,8 @@
       <c r="B348" s="7">
         <v>6</v>
       </c>
-      <c r="C348" s="139"/>
-      <c r="D348" s="159" t="s">
+      <c r="C348" s="156"/>
+      <c r="D348" s="140" t="s">
         <v>448</v>
       </c>
       <c r="E348" s="8" t="s">
@@ -12704,8 +12770,8 @@
       <c r="B349" s="7">
         <v>7</v>
       </c>
-      <c r="C349" s="139"/>
-      <c r="D349" s="160"/>
+      <c r="C349" s="156"/>
+      <c r="D349" s="141"/>
       <c r="E349" s="8" t="s">
         <v>450</v>
       </c>
@@ -12732,8 +12798,8 @@
       <c r="B350" s="7">
         <v>8</v>
       </c>
-      <c r="C350" s="139"/>
-      <c r="D350" s="160"/>
+      <c r="C350" s="156"/>
+      <c r="D350" s="141"/>
       <c r="E350" s="8" t="s">
         <v>451</v>
       </c>
@@ -12760,8 +12826,8 @@
       <c r="B351" s="7">
         <v>9</v>
       </c>
-      <c r="C351" s="139"/>
-      <c r="D351" s="160"/>
+      <c r="C351" s="156"/>
+      <c r="D351" s="141"/>
       <c r="E351" s="8" t="s">
         <v>452</v>
       </c>
@@ -12784,8 +12850,8 @@
       <c r="B352" s="7">
         <v>10</v>
       </c>
-      <c r="C352" s="139"/>
-      <c r="D352" s="160"/>
+      <c r="C352" s="156"/>
+      <c r="D352" s="141"/>
       <c r="E352" s="8" t="s">
         <v>453</v>
       </c>
@@ -12812,8 +12878,8 @@
       <c r="B353" s="7">
         <v>11</v>
       </c>
-      <c r="C353" s="139"/>
-      <c r="D353" s="161"/>
+      <c r="C353" s="156"/>
+      <c r="D353" s="142"/>
       <c r="E353" s="8" t="s">
         <v>454</v>
       </c>
@@ -12834,8 +12900,8 @@
       <c r="B354" s="7">
         <v>12</v>
       </c>
-      <c r="C354" s="139"/>
-      <c r="D354" s="159" t="s">
+      <c r="C354" s="156"/>
+      <c r="D354" s="140" t="s">
         <v>455</v>
       </c>
       <c r="E354" s="8" t="s">
@@ -12862,8 +12928,8 @@
       <c r="B355" s="7">
         <v>13</v>
       </c>
-      <c r="C355" s="139"/>
-      <c r="D355" s="160"/>
+      <c r="C355" s="156"/>
+      <c r="D355" s="141"/>
       <c r="E355" s="8" t="s">
         <v>457</v>
       </c>
@@ -12890,8 +12956,8 @@
       <c r="B356" s="7">
         <v>14</v>
       </c>
-      <c r="C356" s="139"/>
-      <c r="D356" s="160"/>
+      <c r="C356" s="156"/>
+      <c r="D356" s="141"/>
       <c r="E356" s="8" t="s">
         <v>458</v>
       </c>
@@ -12912,8 +12978,8 @@
       <c r="B357" s="7">
         <v>15</v>
       </c>
-      <c r="C357" s="140"/>
-      <c r="D357" s="161"/>
+      <c r="C357" s="157"/>
+      <c r="D357" s="142"/>
       <c r="E357" s="8" t="s">
         <v>459</v>
       </c>
@@ -12928,18 +12994,18 @@
       <c r="J357" s="11"/>
     </row>
     <row r="358" spans="1:10" ht="13.8">
-      <c r="A358" s="174" t="s">
+      <c r="A358" s="179" t="s">
         <v>460</v>
       </c>
-      <c r="B358" s="175"/>
-      <c r="C358" s="175"/>
-      <c r="D358" s="175"/>
-      <c r="E358" s="175"/>
-      <c r="F358" s="175"/>
-      <c r="G358" s="175"/>
-      <c r="H358" s="175"/>
-      <c r="I358" s="175"/>
-      <c r="J358" s="176"/>
+      <c r="B358" s="180"/>
+      <c r="C358" s="180"/>
+      <c r="D358" s="180"/>
+      <c r="E358" s="180"/>
+      <c r="F358" s="180"/>
+      <c r="G358" s="180"/>
+      <c r="H358" s="180"/>
+      <c r="I358" s="180"/>
+      <c r="J358" s="181"/>
     </row>
     <row r="359" spans="1:10" ht="13.8">
       <c r="A359" s="6">
@@ -12948,10 +13014,10 @@
       <c r="B359" s="7">
         <v>1</v>
       </c>
-      <c r="C359" s="141" t="s">
+      <c r="C359" s="158" t="s">
         <v>461</v>
       </c>
-      <c r="D359" s="159" t="s">
+      <c r="D359" s="140" t="s">
         <v>462</v>
       </c>
       <c r="E359" s="8" t="s">
@@ -12974,8 +13040,8 @@
       <c r="B360" s="7">
         <v>2</v>
       </c>
-      <c r="C360" s="142"/>
-      <c r="D360" s="160"/>
+      <c r="C360" s="159"/>
+      <c r="D360" s="141"/>
       <c r="E360" s="8" t="s">
         <v>464</v>
       </c>
@@ -12996,8 +13062,8 @@
       <c r="B361" s="7">
         <v>3</v>
       </c>
-      <c r="C361" s="142"/>
-      <c r="D361" s="160"/>
+      <c r="C361" s="159"/>
+      <c r="D361" s="141"/>
       <c r="E361" s="8" t="s">
         <v>465</v>
       </c>
@@ -13018,8 +13084,8 @@
       <c r="B362" s="7">
         <v>4</v>
       </c>
-      <c r="C362" s="142"/>
-      <c r="D362" s="160"/>
+      <c r="C362" s="159"/>
+      <c r="D362" s="141"/>
       <c r="E362" s="8" t="s">
         <v>466</v>
       </c>
@@ -13040,8 +13106,8 @@
       <c r="B363" s="7">
         <v>5</v>
       </c>
-      <c r="C363" s="142"/>
-      <c r="D363" s="161"/>
+      <c r="C363" s="159"/>
+      <c r="D363" s="142"/>
       <c r="E363" s="8" t="s">
         <v>467</v>
       </c>
@@ -13062,8 +13128,8 @@
       <c r="B364" s="7">
         <v>6</v>
       </c>
-      <c r="C364" s="142"/>
-      <c r="D364" s="159" t="s">
+      <c r="C364" s="159"/>
+      <c r="D364" s="140" t="s">
         <v>468</v>
       </c>
       <c r="E364" s="8" t="s">
@@ -13086,8 +13152,8 @@
       <c r="B365" s="7">
         <v>7</v>
       </c>
-      <c r="C365" s="142"/>
-      <c r="D365" s="160"/>
+      <c r="C365" s="159"/>
+      <c r="D365" s="141"/>
       <c r="E365" s="8" t="s">
         <v>470</v>
       </c>
@@ -13108,8 +13174,8 @@
       <c r="B366" s="7">
         <v>8</v>
       </c>
-      <c r="C366" s="142"/>
-      <c r="D366" s="160"/>
+      <c r="C366" s="159"/>
+      <c r="D366" s="141"/>
       <c r="E366" s="8" t="s">
         <v>471</v>
       </c>
@@ -13130,8 +13196,8 @@
       <c r="B367" s="7">
         <v>9</v>
       </c>
-      <c r="C367" s="142"/>
-      <c r="D367" s="160"/>
+      <c r="C367" s="159"/>
+      <c r="D367" s="141"/>
       <c r="E367" s="8" t="s">
         <v>472</v>
       </c>
@@ -13152,8 +13218,8 @@
       <c r="B368" s="7">
         <v>10</v>
       </c>
-      <c r="C368" s="142"/>
-      <c r="D368" s="160"/>
+      <c r="C368" s="159"/>
+      <c r="D368" s="141"/>
       <c r="E368" s="8" t="s">
         <v>473</v>
       </c>
@@ -13174,8 +13240,8 @@
       <c r="B369" s="7">
         <v>11</v>
       </c>
-      <c r="C369" s="142"/>
-      <c r="D369" s="160"/>
+      <c r="C369" s="159"/>
+      <c r="D369" s="141"/>
       <c r="E369" s="8" t="s">
         <v>474</v>
       </c>
@@ -13196,8 +13262,8 @@
       <c r="B370" s="7">
         <v>12</v>
       </c>
-      <c r="C370" s="142"/>
-      <c r="D370" s="160"/>
+      <c r="C370" s="159"/>
+      <c r="D370" s="141"/>
       <c r="E370" s="8" t="s">
         <v>475</v>
       </c>
@@ -13218,8 +13284,8 @@
       <c r="B371" s="7">
         <v>13</v>
       </c>
-      <c r="C371" s="142"/>
-      <c r="D371" s="161"/>
+      <c r="C371" s="159"/>
+      <c r="D371" s="142"/>
       <c r="E371" s="8" t="s">
         <v>476</v>
       </c>
@@ -13240,8 +13306,8 @@
       <c r="B372" s="7">
         <v>14</v>
       </c>
-      <c r="C372" s="142"/>
-      <c r="D372" s="159" t="s">
+      <c r="C372" s="159"/>
+      <c r="D372" s="140" t="s">
         <v>477</v>
       </c>
       <c r="E372" s="8" t="s">
@@ -13264,8 +13330,8 @@
       <c r="B373" s="7">
         <v>15</v>
       </c>
-      <c r="C373" s="142"/>
-      <c r="D373" s="160"/>
+      <c r="C373" s="159"/>
+      <c r="D373" s="141"/>
       <c r="E373" s="11" t="s">
         <v>479</v>
       </c>
@@ -13286,8 +13352,8 @@
       <c r="B374" s="7">
         <v>16</v>
       </c>
-      <c r="C374" s="142"/>
-      <c r="D374" s="160"/>
+      <c r="C374" s="159"/>
+      <c r="D374" s="141"/>
       <c r="E374" s="8" t="s">
         <v>480</v>
       </c>
@@ -13308,8 +13374,8 @@
       <c r="B375" s="7">
         <v>17</v>
       </c>
-      <c r="C375" s="142"/>
-      <c r="D375" s="161"/>
+      <c r="C375" s="159"/>
+      <c r="D375" s="142"/>
       <c r="E375" s="8" t="s">
         <v>481</v>
       </c>
@@ -13330,8 +13396,8 @@
       <c r="B376" s="7">
         <v>18</v>
       </c>
-      <c r="C376" s="142"/>
-      <c r="D376" s="159" t="s">
+      <c r="C376" s="159"/>
+      <c r="D376" s="140" t="s">
         <v>482</v>
       </c>
       <c r="E376" s="8" t="s">
@@ -13354,8 +13420,8 @@
       <c r="B377" s="7">
         <v>19</v>
       </c>
-      <c r="C377" s="142"/>
-      <c r="D377" s="160"/>
+      <c r="C377" s="159"/>
+      <c r="D377" s="141"/>
       <c r="E377" s="8" t="s">
         <v>484</v>
       </c>
@@ -13376,8 +13442,8 @@
       <c r="B378" s="7">
         <v>20</v>
       </c>
-      <c r="C378" s="142"/>
-      <c r="D378" s="160"/>
+      <c r="C378" s="159"/>
+      <c r="D378" s="141"/>
       <c r="E378" s="8" t="s">
         <v>485</v>
       </c>
@@ -13398,8 +13464,8 @@
       <c r="B379" s="7">
         <v>21</v>
       </c>
-      <c r="C379" s="142"/>
-      <c r="D379" s="160"/>
+      <c r="C379" s="159"/>
+      <c r="D379" s="141"/>
       <c r="E379" s="8" t="s">
         <v>486</v>
       </c>
@@ -13420,8 +13486,8 @@
       <c r="B380" s="24">
         <v>22</v>
       </c>
-      <c r="C380" s="143"/>
-      <c r="D380" s="161"/>
+      <c r="C380" s="160"/>
+      <c r="D380" s="142"/>
       <c r="E380" s="17" t="s">
         <v>487</v>
       </c>
@@ -13442,10 +13508,10 @@
       <c r="B381" s="7">
         <v>1</v>
       </c>
-      <c r="C381" s="144" t="s">
+      <c r="C381" s="149" t="s">
         <v>488</v>
       </c>
-      <c r="D381" s="159" t="s">
+      <c r="D381" s="140" t="s">
         <v>489</v>
       </c>
       <c r="E381" s="8" t="s">
@@ -13468,8 +13534,8 @@
       <c r="B382" s="7">
         <v>2</v>
       </c>
-      <c r="C382" s="145"/>
-      <c r="D382" s="160"/>
+      <c r="C382" s="150"/>
+      <c r="D382" s="141"/>
       <c r="E382" s="8" t="s">
         <v>491</v>
       </c>
@@ -13490,8 +13556,8 @@
       <c r="B383" s="7">
         <v>3</v>
       </c>
-      <c r="C383" s="145"/>
-      <c r="D383" s="160"/>
+      <c r="C383" s="150"/>
+      <c r="D383" s="141"/>
       <c r="E383" s="8" t="s">
         <v>492</v>
       </c>
@@ -13512,8 +13578,8 @@
       <c r="B384" s="7">
         <v>4</v>
       </c>
-      <c r="C384" s="145"/>
-      <c r="D384" s="160"/>
+      <c r="C384" s="150"/>
+      <c r="D384" s="141"/>
       <c r="E384" s="8" t="s">
         <v>493</v>
       </c>
@@ -13534,8 +13600,8 @@
       <c r="B385" s="7">
         <v>5</v>
       </c>
-      <c r="C385" s="145"/>
-      <c r="D385" s="160"/>
+      <c r="C385" s="150"/>
+      <c r="D385" s="141"/>
       <c r="E385" s="8" t="s">
         <v>494</v>
       </c>
@@ -13556,8 +13622,8 @@
       <c r="B386" s="7">
         <v>6</v>
       </c>
-      <c r="C386" s="145"/>
-      <c r="D386" s="161"/>
+      <c r="C386" s="150"/>
+      <c r="D386" s="142"/>
       <c r="E386" s="8" t="s">
         <v>495</v>
       </c>
@@ -13578,8 +13644,8 @@
       <c r="B387" s="7">
         <v>7</v>
       </c>
-      <c r="C387" s="145"/>
-      <c r="D387" s="159" t="s">
+      <c r="C387" s="150"/>
+      <c r="D387" s="140" t="s">
         <v>496</v>
       </c>
       <c r="E387" s="8" t="s">
@@ -13602,8 +13668,8 @@
       <c r="B388" s="7">
         <v>8</v>
       </c>
-      <c r="C388" s="145"/>
-      <c r="D388" s="160"/>
+      <c r="C388" s="150"/>
+      <c r="D388" s="141"/>
       <c r="E388" s="8" t="s">
         <v>498</v>
       </c>
@@ -13624,8 +13690,8 @@
       <c r="B389" s="7">
         <v>9</v>
       </c>
-      <c r="C389" s="145"/>
-      <c r="D389" s="160"/>
+      <c r="C389" s="150"/>
+      <c r="D389" s="141"/>
       <c r="E389" s="8" t="s">
         <v>499</v>
       </c>
@@ -13646,8 +13712,8 @@
       <c r="B390" s="7">
         <v>10</v>
       </c>
-      <c r="C390" s="145"/>
-      <c r="D390" s="160"/>
+      <c r="C390" s="150"/>
+      <c r="D390" s="141"/>
       <c r="E390" s="8" t="s">
         <v>500</v>
       </c>
@@ -13668,8 +13734,8 @@
       <c r="B391" s="7">
         <v>11</v>
       </c>
-      <c r="C391" s="145"/>
-      <c r="D391" s="160"/>
+      <c r="C391" s="150"/>
+      <c r="D391" s="141"/>
       <c r="E391" s="8" t="s">
         <v>501</v>
       </c>
@@ -13690,8 +13756,8 @@
       <c r="B392" s="7">
         <v>12</v>
       </c>
-      <c r="C392" s="145"/>
-      <c r="D392" s="160"/>
+      <c r="C392" s="150"/>
+      <c r="D392" s="141"/>
       <c r="E392" s="8" t="s">
         <v>502</v>
       </c>
@@ -13712,8 +13778,8 @@
       <c r="B393" s="7">
         <v>13</v>
       </c>
-      <c r="C393" s="145"/>
-      <c r="D393" s="160"/>
+      <c r="C393" s="150"/>
+      <c r="D393" s="141"/>
       <c r="E393" s="8" t="s">
         <v>503</v>
       </c>
@@ -13734,8 +13800,8 @@
       <c r="B394" s="7">
         <v>14</v>
       </c>
-      <c r="C394" s="145"/>
-      <c r="D394" s="160"/>
+      <c r="C394" s="150"/>
+      <c r="D394" s="141"/>
       <c r="E394" s="8" t="s">
         <v>504</v>
       </c>
@@ -13756,8 +13822,8 @@
       <c r="B395" s="7">
         <v>15</v>
       </c>
-      <c r="C395" s="145"/>
-      <c r="D395" s="160"/>
+      <c r="C395" s="150"/>
+      <c r="D395" s="141"/>
       <c r="E395" s="8" t="s">
         <v>505</v>
       </c>
@@ -13778,8 +13844,8 @@
       <c r="B396" s="7">
         <v>16</v>
       </c>
-      <c r="C396" s="145"/>
-      <c r="D396" s="161"/>
+      <c r="C396" s="150"/>
+      <c r="D396" s="142"/>
       <c r="E396" s="8" t="s">
         <v>506</v>
       </c>
@@ -13800,8 +13866,8 @@
       <c r="B397" s="7">
         <v>17</v>
       </c>
-      <c r="C397" s="145"/>
-      <c r="D397" s="159" t="s">
+      <c r="C397" s="150"/>
+      <c r="D397" s="140" t="s">
         <v>507</v>
       </c>
       <c r="E397" s="8" t="s">
@@ -13824,8 +13890,8 @@
       <c r="B398" s="7">
         <v>18</v>
       </c>
-      <c r="C398" s="145"/>
-      <c r="D398" s="160"/>
+      <c r="C398" s="150"/>
+      <c r="D398" s="141"/>
       <c r="E398" s="8" t="s">
         <v>509</v>
       </c>
@@ -13846,8 +13912,8 @@
       <c r="B399" s="7">
         <v>19</v>
       </c>
-      <c r="C399" s="145"/>
-      <c r="D399" s="161"/>
+      <c r="C399" s="150"/>
+      <c r="D399" s="142"/>
       <c r="E399" s="8" t="s">
         <v>510</v>
       </c>
@@ -13868,8 +13934,8 @@
       <c r="B400" s="7">
         <v>20</v>
       </c>
-      <c r="C400" s="145"/>
-      <c r="D400" s="159" t="s">
+      <c r="C400" s="150"/>
+      <c r="D400" s="140" t="s">
         <v>511</v>
       </c>
       <c r="E400" s="8" t="s">
@@ -13892,8 +13958,8 @@
       <c r="B401" s="7">
         <v>21</v>
       </c>
-      <c r="C401" s="145"/>
-      <c r="D401" s="160"/>
+      <c r="C401" s="150"/>
+      <c r="D401" s="141"/>
       <c r="E401" s="8" t="s">
         <v>513</v>
       </c>
@@ -13914,8 +13980,8 @@
       <c r="B402" s="7">
         <v>22</v>
       </c>
-      <c r="C402" s="145"/>
-      <c r="D402" s="160"/>
+      <c r="C402" s="150"/>
+      <c r="D402" s="141"/>
       <c r="E402" s="8" t="s">
         <v>514</v>
       </c>
@@ -13936,8 +14002,8 @@
       <c r="B403" s="7">
         <v>23</v>
       </c>
-      <c r="C403" s="145"/>
-      <c r="D403" s="160"/>
+      <c r="C403" s="150"/>
+      <c r="D403" s="141"/>
       <c r="E403" s="8" t="s">
         <v>515</v>
       </c>
@@ -13958,8 +14024,8 @@
       <c r="B404" s="7">
         <v>24</v>
       </c>
-      <c r="C404" s="145"/>
-      <c r="D404" s="161"/>
+      <c r="C404" s="150"/>
+      <c r="D404" s="142"/>
       <c r="E404" s="8" t="s">
         <v>516</v>
       </c>
@@ -13980,8 +14046,8 @@
       <c r="B405" s="7">
         <v>25</v>
       </c>
-      <c r="C405" s="145"/>
-      <c r="D405" s="159" t="s">
+      <c r="C405" s="150"/>
+      <c r="D405" s="140" t="s">
         <v>517</v>
       </c>
       <c r="E405" s="8" t="s">
@@ -14004,8 +14070,8 @@
       <c r="B406" s="7">
         <v>26</v>
       </c>
-      <c r="C406" s="145"/>
-      <c r="D406" s="160"/>
+      <c r="C406" s="150"/>
+      <c r="D406" s="141"/>
       <c r="E406" s="8" t="s">
         <v>519</v>
       </c>
@@ -14026,8 +14092,8 @@
       <c r="B407" s="7">
         <v>27</v>
       </c>
-      <c r="C407" s="145"/>
-      <c r="D407" s="160"/>
+      <c r="C407" s="150"/>
+      <c r="D407" s="141"/>
       <c r="E407" s="8" t="s">
         <v>520</v>
       </c>
@@ -14048,8 +14114,8 @@
       <c r="B408" s="7">
         <v>28</v>
       </c>
-      <c r="C408" s="145"/>
-      <c r="D408" s="160"/>
+      <c r="C408" s="150"/>
+      <c r="D408" s="141"/>
       <c r="E408" s="8" t="s">
         <v>521</v>
       </c>
@@ -14070,8 +14136,8 @@
       <c r="B409" s="7">
         <v>29</v>
       </c>
-      <c r="C409" s="145"/>
-      <c r="D409" s="160"/>
+      <c r="C409" s="150"/>
+      <c r="D409" s="141"/>
       <c r="E409" s="8" t="s">
         <v>522</v>
       </c>
@@ -14092,8 +14158,8 @@
       <c r="B410" s="7">
         <v>30</v>
       </c>
-      <c r="C410" s="145"/>
-      <c r="D410" s="160"/>
+      <c r="C410" s="150"/>
+      <c r="D410" s="141"/>
       <c r="E410" s="8" t="s">
         <v>523</v>
       </c>
@@ -14114,8 +14180,8 @@
       <c r="B411" s="7">
         <v>31</v>
       </c>
-      <c r="C411" s="145"/>
-      <c r="D411" s="160"/>
+      <c r="C411" s="150"/>
+      <c r="D411" s="141"/>
       <c r="E411" s="8" t="s">
         <v>524</v>
       </c>
@@ -14136,8 +14202,8 @@
       <c r="B412" s="7">
         <v>32</v>
       </c>
-      <c r="C412" s="145"/>
-      <c r="D412" s="160"/>
+      <c r="C412" s="150"/>
+      <c r="D412" s="141"/>
       <c r="E412" s="8" t="s">
         <v>525</v>
       </c>
@@ -14158,8 +14224,8 @@
       <c r="B413" s="7">
         <v>33</v>
       </c>
-      <c r="C413" s="145"/>
-      <c r="D413" s="160"/>
+      <c r="C413" s="150"/>
+      <c r="D413" s="141"/>
       <c r="E413" s="8" t="s">
         <v>526</v>
       </c>
@@ -14180,8 +14246,8 @@
       <c r="B414" s="7">
         <v>34</v>
       </c>
-      <c r="C414" s="145"/>
-      <c r="D414" s="160"/>
+      <c r="C414" s="150"/>
+      <c r="D414" s="141"/>
       <c r="E414" s="8" t="s">
         <v>527</v>
       </c>
@@ -14202,8 +14268,8 @@
       <c r="B415" s="7">
         <v>35</v>
       </c>
-      <c r="C415" s="145"/>
-      <c r="D415" s="160"/>
+      <c r="C415" s="150"/>
+      <c r="D415" s="141"/>
       <c r="E415" s="8" t="s">
         <v>528</v>
       </c>
@@ -14224,8 +14290,8 @@
       <c r="B416" s="7">
         <v>36</v>
       </c>
-      <c r="C416" s="145"/>
-      <c r="D416" s="161"/>
+      <c r="C416" s="150"/>
+      <c r="D416" s="142"/>
       <c r="E416" s="8" t="s">
         <v>529</v>
       </c>
@@ -14246,8 +14312,8 @@
       <c r="B417" s="7">
         <v>37</v>
       </c>
-      <c r="C417" s="145"/>
-      <c r="D417" s="159" t="s">
+      <c r="C417" s="150"/>
+      <c r="D417" s="140" t="s">
         <v>530</v>
       </c>
       <c r="E417" s="8" t="s">
@@ -14270,8 +14336,8 @@
       <c r="B418" s="7">
         <v>38</v>
       </c>
-      <c r="C418" s="145"/>
-      <c r="D418" s="160"/>
+      <c r="C418" s="150"/>
+      <c r="D418" s="141"/>
       <c r="E418" s="8" t="s">
         <v>532</v>
       </c>
@@ -14292,8 +14358,8 @@
       <c r="B419" s="7">
         <v>39</v>
       </c>
-      <c r="C419" s="145"/>
-      <c r="D419" s="161"/>
+      <c r="C419" s="150"/>
+      <c r="D419" s="142"/>
       <c r="E419" s="8" t="s">
         <v>533</v>
       </c>
@@ -14314,8 +14380,8 @@
       <c r="B420" s="7">
         <v>40</v>
       </c>
-      <c r="C420" s="145"/>
-      <c r="D420" s="159" t="s">
+      <c r="C420" s="150"/>
+      <c r="D420" s="140" t="s">
         <v>534</v>
       </c>
       <c r="E420" s="8" t="s">
@@ -14338,8 +14404,8 @@
       <c r="B421" s="7">
         <v>41</v>
       </c>
-      <c r="C421" s="145"/>
-      <c r="D421" s="160"/>
+      <c r="C421" s="150"/>
+      <c r="D421" s="141"/>
       <c r="E421" s="8" t="s">
         <v>536</v>
       </c>
@@ -14360,8 +14426,8 @@
       <c r="B422" s="7">
         <v>42</v>
       </c>
-      <c r="C422" s="145"/>
-      <c r="D422" s="160"/>
+      <c r="C422" s="150"/>
+      <c r="D422" s="141"/>
       <c r="E422" s="8" t="s">
         <v>537</v>
       </c>
@@ -14382,8 +14448,8 @@
       <c r="B423" s="7">
         <v>43</v>
       </c>
-      <c r="C423" s="145"/>
-      <c r="D423" s="160"/>
+      <c r="C423" s="150"/>
+      <c r="D423" s="141"/>
       <c r="E423" s="8" t="s">
         <v>538</v>
       </c>
@@ -14404,8 +14470,8 @@
       <c r="B424" s="7">
         <v>44</v>
       </c>
-      <c r="C424" s="145"/>
-      <c r="D424" s="160"/>
+      <c r="C424" s="150"/>
+      <c r="D424" s="141"/>
       <c r="E424" s="8" t="s">
         <v>539</v>
       </c>
@@ -14426,8 +14492,8 @@
       <c r="B425" s="7">
         <v>45</v>
       </c>
-      <c r="C425" s="145"/>
-      <c r="D425" s="160"/>
+      <c r="C425" s="150"/>
+      <c r="D425" s="141"/>
       <c r="E425" s="8" t="s">
         <v>540</v>
       </c>
@@ -14448,8 +14514,8 @@
       <c r="B426" s="7">
         <v>46</v>
       </c>
-      <c r="C426" s="145"/>
-      <c r="D426" s="161"/>
+      <c r="C426" s="150"/>
+      <c r="D426" s="142"/>
       <c r="E426" s="8" t="s">
         <v>541</v>
       </c>
@@ -14470,8 +14536,8 @@
       <c r="B427" s="7">
         <v>47</v>
       </c>
-      <c r="C427" s="145"/>
-      <c r="D427" s="159" t="s">
+      <c r="C427" s="150"/>
+      <c r="D427" s="140" t="s">
         <v>542</v>
       </c>
       <c r="E427" s="8" t="s">
@@ -14492,8 +14558,8 @@
       <c r="B428" s="7">
         <v>48</v>
       </c>
-      <c r="C428" s="145"/>
-      <c r="D428" s="160"/>
+      <c r="C428" s="150"/>
+      <c r="D428" s="141"/>
       <c r="E428" s="8" t="s">
         <v>544</v>
       </c>
@@ -14514,8 +14580,8 @@
       <c r="B429" s="7">
         <v>49</v>
       </c>
-      <c r="C429" s="145"/>
-      <c r="D429" s="160"/>
+      <c r="C429" s="150"/>
+      <c r="D429" s="141"/>
       <c r="E429" s="8" t="s">
         <v>545</v>
       </c>
@@ -14536,8 +14602,8 @@
       <c r="B430" s="7">
         <v>50</v>
       </c>
-      <c r="C430" s="145"/>
-      <c r="D430" s="161"/>
+      <c r="C430" s="150"/>
+      <c r="D430" s="142"/>
       <c r="E430" s="8" t="s">
         <v>546</v>
       </c>
@@ -14558,8 +14624,8 @@
       <c r="B431" s="7">
         <v>51</v>
       </c>
-      <c r="C431" s="145"/>
-      <c r="D431" s="159" t="s">
+      <c r="C431" s="150"/>
+      <c r="D431" s="140" t="s">
         <v>547</v>
       </c>
       <c r="E431" s="8" t="s">
@@ -14582,8 +14648,8 @@
       <c r="B432" s="7">
         <v>52</v>
       </c>
-      <c r="C432" s="145"/>
-      <c r="D432" s="160"/>
+      <c r="C432" s="150"/>
+      <c r="D432" s="141"/>
       <c r="E432" s="8" t="s">
         <v>549</v>
       </c>
@@ -14604,8 +14670,8 @@
       <c r="B433" s="7">
         <v>53</v>
       </c>
-      <c r="C433" s="145"/>
-      <c r="D433" s="160"/>
+      <c r="C433" s="150"/>
+      <c r="D433" s="141"/>
       <c r="E433" s="8" t="s">
         <v>550</v>
       </c>
@@ -14626,8 +14692,8 @@
       <c r="B434" s="7">
         <v>54</v>
       </c>
-      <c r="C434" s="145"/>
-      <c r="D434" s="160"/>
+      <c r="C434" s="150"/>
+      <c r="D434" s="141"/>
       <c r="E434" s="8" t="s">
         <v>551</v>
       </c>
@@ -14648,8 +14714,8 @@
       <c r="B435" s="7">
         <v>55</v>
       </c>
-      <c r="C435" s="146"/>
-      <c r="D435" s="161"/>
+      <c r="C435" s="151"/>
+      <c r="D435" s="142"/>
       <c r="E435" s="8" t="s">
         <v>552</v>
       </c>
@@ -14664,18 +14730,18 @@
       <c r="J435" s="11"/>
     </row>
     <row r="436" spans="1:10" ht="13.8">
-      <c r="A436" s="165" t="s">
+      <c r="A436" s="182" t="s">
         <v>553</v>
       </c>
-      <c r="B436" s="166"/>
-      <c r="C436" s="166"/>
-      <c r="D436" s="166"/>
-      <c r="E436" s="166"/>
-      <c r="F436" s="166"/>
-      <c r="G436" s="166"/>
-      <c r="H436" s="166"/>
-      <c r="I436" s="166"/>
-      <c r="J436" s="167"/>
+      <c r="B436" s="183"/>
+      <c r="C436" s="183"/>
+      <c r="D436" s="183"/>
+      <c r="E436" s="183"/>
+      <c r="F436" s="183"/>
+      <c r="G436" s="183"/>
+      <c r="H436" s="183"/>
+      <c r="I436" s="183"/>
+      <c r="J436" s="184"/>
     </row>
     <row r="437" spans="1:10" ht="13.8">
       <c r="A437" s="6">
@@ -14684,10 +14750,10 @@
       <c r="B437" s="7">
         <v>1</v>
       </c>
-      <c r="C437" s="147" t="s">
+      <c r="C437" s="152" t="s">
         <v>554</v>
       </c>
-      <c r="D437" s="159" t="s">
+      <c r="D437" s="140" t="s">
         <v>555</v>
       </c>
       <c r="E437" s="29" t="s">
@@ -14710,8 +14776,8 @@
       <c r="B438" s="7">
         <v>2</v>
       </c>
-      <c r="C438" s="148"/>
-      <c r="D438" s="160"/>
+      <c r="C438" s="153"/>
+      <c r="D438" s="141"/>
       <c r="E438" s="8" t="s">
         <v>557</v>
       </c>
@@ -14730,8 +14796,8 @@
       <c r="B439" s="7">
         <v>3</v>
       </c>
-      <c r="C439" s="148"/>
-      <c r="D439" s="160"/>
+      <c r="C439" s="153"/>
+      <c r="D439" s="141"/>
       <c r="E439" s="8" t="s">
         <v>558</v>
       </c>
@@ -14752,8 +14818,8 @@
       <c r="B440" s="7">
         <v>4</v>
       </c>
-      <c r="C440" s="148"/>
-      <c r="D440" s="160"/>
+      <c r="C440" s="153"/>
+      <c r="D440" s="141"/>
       <c r="E440" s="29" t="s">
         <v>559</v>
       </c>
@@ -14774,8 +14840,8 @@
       <c r="B441" s="7">
         <v>5</v>
       </c>
-      <c r="C441" s="148"/>
-      <c r="D441" s="161"/>
+      <c r="C441" s="153"/>
+      <c r="D441" s="142"/>
       <c r="E441" s="8" t="s">
         <v>560</v>
       </c>
@@ -14796,8 +14862,8 @@
       <c r="B442" s="7">
         <v>6</v>
       </c>
-      <c r="C442" s="148"/>
-      <c r="D442" s="159" t="s">
+      <c r="C442" s="153"/>
+      <c r="D442" s="140" t="s">
         <v>561</v>
       </c>
       <c r="E442" s="29" t="s">
@@ -14820,8 +14886,8 @@
       <c r="B443" s="7">
         <v>7</v>
       </c>
-      <c r="C443" s="148"/>
-      <c r="D443" s="160"/>
+      <c r="C443" s="153"/>
+      <c r="D443" s="141"/>
       <c r="E443" s="8" t="s">
         <v>563</v>
       </c>
@@ -14842,8 +14908,8 @@
       <c r="B444" s="7">
         <v>8</v>
       </c>
-      <c r="C444" s="148"/>
-      <c r="D444" s="160"/>
+      <c r="C444" s="153"/>
+      <c r="D444" s="141"/>
       <c r="E444" s="29" t="s">
         <v>564</v>
       </c>
@@ -14864,8 +14930,8 @@
       <c r="B445" s="7">
         <v>9</v>
       </c>
-      <c r="C445" s="148"/>
-      <c r="D445" s="161"/>
+      <c r="C445" s="153"/>
+      <c r="D445" s="142"/>
       <c r="E445" s="8" t="s">
         <v>565</v>
       </c>
@@ -14886,8 +14952,8 @@
       <c r="B446" s="7">
         <v>10</v>
       </c>
-      <c r="C446" s="148"/>
-      <c r="D446" s="159" t="s">
+      <c r="C446" s="153"/>
+      <c r="D446" s="140" t="s">
         <v>566</v>
       </c>
       <c r="E446" s="8" t="s">
@@ -14910,8 +14976,8 @@
       <c r="B447" s="7">
         <v>11</v>
       </c>
-      <c r="C447" s="148"/>
-      <c r="D447" s="160"/>
+      <c r="C447" s="153"/>
+      <c r="D447" s="141"/>
       <c r="E447" s="8" t="s">
         <v>568</v>
       </c>
@@ -14932,8 +14998,8 @@
       <c r="B448" s="7">
         <v>12</v>
       </c>
-      <c r="C448" s="148"/>
-      <c r="D448" s="161"/>
+      <c r="C448" s="153"/>
+      <c r="D448" s="142"/>
       <c r="E448" s="8" t="s">
         <v>569</v>
       </c>
@@ -14954,8 +15020,8 @@
       <c r="B449" s="7">
         <v>13</v>
       </c>
-      <c r="C449" s="148"/>
-      <c r="D449" s="159" t="s">
+      <c r="C449" s="153"/>
+      <c r="D449" s="140" t="s">
         <v>570</v>
       </c>
       <c r="E449" s="8" t="s">
@@ -14978,8 +15044,8 @@
       <c r="B450" s="7">
         <v>14</v>
       </c>
-      <c r="C450" s="148"/>
-      <c r="D450" s="160"/>
+      <c r="C450" s="153"/>
+      <c r="D450" s="141"/>
       <c r="E450" s="29" t="s">
         <v>572</v>
       </c>
@@ -15000,8 +15066,8 @@
       <c r="B451" s="7">
         <v>15</v>
       </c>
-      <c r="C451" s="148"/>
-      <c r="D451" s="160"/>
+      <c r="C451" s="153"/>
+      <c r="D451" s="141"/>
       <c r="E451" s="8" t="s">
         <v>573</v>
       </c>
@@ -15022,8 +15088,8 @@
       <c r="B452" s="7">
         <v>16</v>
       </c>
-      <c r="C452" s="148"/>
-      <c r="D452" s="161"/>
+      <c r="C452" s="153"/>
+      <c r="D452" s="142"/>
       <c r="E452" s="8" t="s">
         <v>574</v>
       </c>
@@ -15044,8 +15110,8 @@
       <c r="B453" s="7">
         <v>17</v>
       </c>
-      <c r="C453" s="148"/>
-      <c r="D453" s="159" t="s">
+      <c r="C453" s="153"/>
+      <c r="D453" s="140" t="s">
         <v>575</v>
       </c>
       <c r="E453" s="8" t="s">
@@ -15068,8 +15134,8 @@
       <c r="B454" s="7">
         <v>18</v>
       </c>
-      <c r="C454" s="148"/>
-      <c r="D454" s="160"/>
+      <c r="C454" s="153"/>
+      <c r="D454" s="141"/>
       <c r="E454" s="8" t="s">
         <v>577</v>
       </c>
@@ -15090,8 +15156,8 @@
       <c r="B455" s="7">
         <v>19</v>
       </c>
-      <c r="C455" s="148"/>
-      <c r="D455" s="160"/>
+      <c r="C455" s="153"/>
+      <c r="D455" s="141"/>
       <c r="E455" s="8" t="s">
         <v>578</v>
       </c>
@@ -15112,8 +15178,8 @@
       <c r="B456" s="7">
         <v>20</v>
       </c>
-      <c r="C456" s="148"/>
-      <c r="D456" s="160"/>
+      <c r="C456" s="153"/>
+      <c r="D456" s="141"/>
       <c r="E456" s="39" t="s">
         <v>579</v>
       </c>
@@ -15134,8 +15200,8 @@
       <c r="B457" s="7">
         <v>21</v>
       </c>
-      <c r="C457" s="148"/>
-      <c r="D457" s="160"/>
+      <c r="C457" s="153"/>
+      <c r="D457" s="141"/>
       <c r="E457" s="8" t="s">
         <v>580</v>
       </c>
@@ -15156,8 +15222,8 @@
       <c r="B458" s="24">
         <v>22</v>
       </c>
-      <c r="C458" s="149"/>
-      <c r="D458" s="161"/>
+      <c r="C458" s="154"/>
+      <c r="D458" s="142"/>
       <c r="E458" s="17" t="s">
         <v>581</v>
       </c>
@@ -15179,10 +15245,10 @@
       <c r="B459" s="7">
         <v>1</v>
       </c>
-      <c r="C459" s="138" t="s">
+      <c r="C459" s="155" t="s">
         <v>582</v>
       </c>
-      <c r="D459" s="159" t="s">
+      <c r="D459" s="140" t="s">
         <v>583</v>
       </c>
       <c r="E459" s="8" t="s">
@@ -15205,8 +15271,8 @@
       <c r="B460" s="7">
         <v>2</v>
       </c>
-      <c r="C460" s="139"/>
-      <c r="D460" s="160"/>
+      <c r="C460" s="156"/>
+      <c r="D460" s="141"/>
       <c r="E460" s="8" t="s">
         <v>584</v>
       </c>
@@ -15227,8 +15293,8 @@
       <c r="B461" s="7">
         <v>3</v>
       </c>
-      <c r="C461" s="139"/>
-      <c r="D461" s="160"/>
+      <c r="C461" s="156"/>
+      <c r="D461" s="141"/>
       <c r="E461" s="8" t="s">
         <v>585</v>
       </c>
@@ -15249,8 +15315,8 @@
       <c r="B462" s="7">
         <v>4</v>
       </c>
-      <c r="C462" s="139"/>
-      <c r="D462" s="160"/>
+      <c r="C462" s="156"/>
+      <c r="D462" s="141"/>
       <c r="E462" s="8" t="s">
         <v>586</v>
       </c>
@@ -15271,8 +15337,8 @@
       <c r="B463" s="7">
         <v>5</v>
       </c>
-      <c r="C463" s="139"/>
-      <c r="D463" s="160"/>
+      <c r="C463" s="156"/>
+      <c r="D463" s="141"/>
       <c r="E463" s="8" t="s">
         <v>587</v>
       </c>
@@ -15293,8 +15359,8 @@
       <c r="B464" s="7">
         <v>6</v>
       </c>
-      <c r="C464" s="139"/>
-      <c r="D464" s="160"/>
+      <c r="C464" s="156"/>
+      <c r="D464" s="141"/>
       <c r="E464" s="8" t="s">
         <v>588</v>
       </c>
@@ -15315,8 +15381,8 @@
       <c r="B465" s="7">
         <v>7</v>
       </c>
-      <c r="C465" s="139"/>
-      <c r="D465" s="160"/>
+      <c r="C465" s="156"/>
+      <c r="D465" s="141"/>
       <c r="E465" s="8" t="s">
         <v>589</v>
       </c>
@@ -15337,8 +15403,8 @@
       <c r="B466" s="7">
         <v>8</v>
       </c>
-      <c r="C466" s="139"/>
-      <c r="D466" s="161"/>
+      <c r="C466" s="156"/>
+      <c r="D466" s="142"/>
       <c r="E466" s="8" t="s">
         <v>590</v>
       </c>
@@ -15359,8 +15425,8 @@
       <c r="B467" s="7">
         <v>9</v>
       </c>
-      <c r="C467" s="139"/>
-      <c r="D467" s="159" t="s">
+      <c r="C467" s="156"/>
+      <c r="D467" s="140" t="s">
         <v>591</v>
       </c>
       <c r="E467" s="8" t="s">
@@ -15383,8 +15449,8 @@
       <c r="B468" s="7">
         <v>10</v>
       </c>
-      <c r="C468" s="139"/>
-      <c r="D468" s="160"/>
+      <c r="C468" s="156"/>
+      <c r="D468" s="141"/>
       <c r="E468" s="8" t="s">
         <v>593</v>
       </c>
@@ -15405,8 +15471,8 @@
       <c r="B469" s="7">
         <v>11</v>
       </c>
-      <c r="C469" s="139"/>
-      <c r="D469" s="160"/>
+      <c r="C469" s="156"/>
+      <c r="D469" s="141"/>
       <c r="E469" s="8" t="s">
         <v>594</v>
       </c>
@@ -15427,8 +15493,8 @@
       <c r="B470" s="7">
         <v>12</v>
       </c>
-      <c r="C470" s="139"/>
-      <c r="D470" s="160"/>
+      <c r="C470" s="156"/>
+      <c r="D470" s="141"/>
       <c r="E470" s="8" t="s">
         <v>595</v>
       </c>
@@ -15449,8 +15515,8 @@
       <c r="B471" s="7">
         <v>13</v>
       </c>
-      <c r="C471" s="139"/>
-      <c r="D471" s="160"/>
+      <c r="C471" s="156"/>
+      <c r="D471" s="141"/>
       <c r="E471" s="8" t="s">
         <v>596</v>
       </c>
@@ -15471,8 +15537,8 @@
       <c r="B472" s="7">
         <v>14</v>
       </c>
-      <c r="C472" s="139"/>
-      <c r="D472" s="160"/>
+      <c r="C472" s="156"/>
+      <c r="D472" s="141"/>
       <c r="E472" s="8" t="s">
         <v>597</v>
       </c>
@@ -15493,8 +15559,8 @@
       <c r="B473" s="7">
         <v>15</v>
       </c>
-      <c r="C473" s="139"/>
-      <c r="D473" s="161"/>
+      <c r="C473" s="156"/>
+      <c r="D473" s="142"/>
       <c r="E473" s="8" t="s">
         <v>598</v>
       </c>
@@ -15515,8 +15581,8 @@
       <c r="B474" s="7">
         <v>16</v>
       </c>
-      <c r="C474" s="139"/>
-      <c r="D474" s="159" t="s">
+      <c r="C474" s="156"/>
+      <c r="D474" s="140" t="s">
         <v>599</v>
       </c>
       <c r="E474" s="8" t="s">
@@ -15539,8 +15605,8 @@
       <c r="B475" s="7">
         <v>17</v>
       </c>
-      <c r="C475" s="139"/>
-      <c r="D475" s="160"/>
+      <c r="C475" s="156"/>
+      <c r="D475" s="141"/>
       <c r="E475" s="8" t="s">
         <v>601</v>
       </c>
@@ -15561,8 +15627,8 @@
       <c r="B476" s="7">
         <v>18</v>
       </c>
-      <c r="C476" s="139"/>
-      <c r="D476" s="160"/>
+      <c r="C476" s="156"/>
+      <c r="D476" s="141"/>
       <c r="E476" s="8" t="s">
         <v>602</v>
       </c>
@@ -15583,8 +15649,8 @@
       <c r="B477" s="7">
         <v>19</v>
       </c>
-      <c r="C477" s="139"/>
-      <c r="D477" s="160"/>
+      <c r="C477" s="156"/>
+      <c r="D477" s="141"/>
       <c r="E477" s="8" t="s">
         <v>603</v>
       </c>
@@ -15605,8 +15671,8 @@
       <c r="B478" s="7">
         <v>20</v>
       </c>
-      <c r="C478" s="139"/>
-      <c r="D478" s="160"/>
+      <c r="C478" s="156"/>
+      <c r="D478" s="141"/>
       <c r="E478" s="8" t="s">
         <v>604</v>
       </c>
@@ -15627,8 +15693,8 @@
       <c r="B479" s="7">
         <v>21</v>
       </c>
-      <c r="C479" s="139"/>
-      <c r="D479" s="160"/>
+      <c r="C479" s="156"/>
+      <c r="D479" s="141"/>
       <c r="E479" s="8" t="s">
         <v>605</v>
       </c>
@@ -15649,8 +15715,8 @@
       <c r="B480" s="7">
         <v>22</v>
       </c>
-      <c r="C480" s="139"/>
-      <c r="D480" s="160"/>
+      <c r="C480" s="156"/>
+      <c r="D480" s="141"/>
       <c r="E480" s="8" t="s">
         <v>606</v>
       </c>
@@ -15671,8 +15737,8 @@
       <c r="B481" s="7">
         <v>23</v>
       </c>
-      <c r="C481" s="139"/>
-      <c r="D481" s="161"/>
+      <c r="C481" s="156"/>
+      <c r="D481" s="142"/>
       <c r="E481" s="8" t="s">
         <v>607</v>
       </c>
@@ -15693,8 +15759,8 @@
       <c r="B482" s="7">
         <v>24</v>
       </c>
-      <c r="C482" s="139"/>
-      <c r="D482" s="159" t="s">
+      <c r="C482" s="156"/>
+      <c r="D482" s="140" t="s">
         <v>608</v>
       </c>
       <c r="E482" s="8" t="s">
@@ -15717,8 +15783,8 @@
       <c r="B483" s="7">
         <v>25</v>
       </c>
-      <c r="C483" s="139"/>
-      <c r="D483" s="160"/>
+      <c r="C483" s="156"/>
+      <c r="D483" s="141"/>
       <c r="E483" s="8" t="s">
         <v>610</v>
       </c>
@@ -15739,8 +15805,8 @@
       <c r="B484" s="7">
         <v>26</v>
       </c>
-      <c r="C484" s="139"/>
-      <c r="D484" s="160"/>
+      <c r="C484" s="156"/>
+      <c r="D484" s="141"/>
       <c r="E484" s="8" t="s">
         <v>611</v>
       </c>
@@ -15761,8 +15827,8 @@
       <c r="B485" s="7">
         <v>27</v>
       </c>
-      <c r="C485" s="139"/>
-      <c r="D485" s="161"/>
+      <c r="C485" s="156"/>
+      <c r="D485" s="142"/>
       <c r="E485" s="8" t="s">
         <v>612</v>
       </c>
@@ -15783,8 +15849,8 @@
       <c r="B486" s="7">
         <v>28</v>
       </c>
-      <c r="C486" s="139"/>
-      <c r="D486" s="159" t="s">
+      <c r="C486" s="156"/>
+      <c r="D486" s="140" t="s">
         <v>613</v>
       </c>
       <c r="E486" s="8" t="s">
@@ -15807,8 +15873,8 @@
       <c r="B487" s="7">
         <v>29</v>
       </c>
-      <c r="C487" s="139"/>
-      <c r="D487" s="160"/>
+      <c r="C487" s="156"/>
+      <c r="D487" s="141"/>
       <c r="E487" s="8" t="s">
         <v>615</v>
       </c>
@@ -15829,8 +15895,8 @@
       <c r="B488" s="7">
         <v>30</v>
       </c>
-      <c r="C488" s="139"/>
-      <c r="D488" s="160"/>
+      <c r="C488" s="156"/>
+      <c r="D488" s="141"/>
       <c r="E488" s="8" t="s">
         <v>616</v>
       </c>
@@ -15851,8 +15917,8 @@
       <c r="B489" s="7">
         <v>31</v>
       </c>
-      <c r="C489" s="139"/>
-      <c r="D489" s="160"/>
+      <c r="C489" s="156"/>
+      <c r="D489" s="141"/>
       <c r="E489" s="8" t="s">
         <v>617</v>
       </c>
@@ -15873,8 +15939,8 @@
       <c r="B490" s="7">
         <v>32</v>
       </c>
-      <c r="C490" s="139"/>
-      <c r="D490" s="160"/>
+      <c r="C490" s="156"/>
+      <c r="D490" s="141"/>
       <c r="E490" s="8" t="s">
         <v>618</v>
       </c>
@@ -15895,8 +15961,8 @@
       <c r="B491" s="7">
         <v>33</v>
       </c>
-      <c r="C491" s="139"/>
-      <c r="D491" s="160"/>
+      <c r="C491" s="156"/>
+      <c r="D491" s="141"/>
       <c r="E491" s="8" t="s">
         <v>619</v>
       </c>
@@ -15917,8 +15983,8 @@
       <c r="B492" s="7">
         <v>34</v>
       </c>
-      <c r="C492" s="139"/>
-      <c r="D492" s="160"/>
+      <c r="C492" s="156"/>
+      <c r="D492" s="141"/>
       <c r="E492" s="8" t="s">
         <v>620</v>
       </c>
@@ -15939,8 +16005,8 @@
       <c r="B493" s="7">
         <v>35</v>
       </c>
-      <c r="C493" s="139"/>
-      <c r="D493" s="160"/>
+      <c r="C493" s="156"/>
+      <c r="D493" s="141"/>
       <c r="E493" s="8" t="s">
         <v>621</v>
       </c>
@@ -15961,8 +16027,8 @@
       <c r="B494" s="7">
         <v>36</v>
       </c>
-      <c r="C494" s="139"/>
-      <c r="D494" s="160"/>
+      <c r="C494" s="156"/>
+      <c r="D494" s="141"/>
       <c r="E494" s="8" t="s">
         <v>622</v>
       </c>
@@ -15983,8 +16049,8 @@
       <c r="B495" s="7">
         <v>37</v>
       </c>
-      <c r="C495" s="139"/>
-      <c r="D495" s="160"/>
+      <c r="C495" s="156"/>
+      <c r="D495" s="141"/>
       <c r="E495" s="8" t="s">
         <v>623</v>
       </c>
@@ -16005,8 +16071,8 @@
       <c r="B496" s="7">
         <v>38</v>
       </c>
-      <c r="C496" s="139"/>
-      <c r="D496" s="161"/>
+      <c r="C496" s="156"/>
+      <c r="D496" s="142"/>
       <c r="E496" s="8" t="s">
         <v>624</v>
       </c>
@@ -16027,8 +16093,8 @@
       <c r="B497" s="7">
         <v>39</v>
       </c>
-      <c r="C497" s="139"/>
-      <c r="D497" s="159" t="s">
+      <c r="C497" s="156"/>
+      <c r="D497" s="140" t="s">
         <v>625</v>
       </c>
       <c r="E497" s="8" t="s">
@@ -16051,8 +16117,8 @@
       <c r="B498" s="7">
         <v>40</v>
       </c>
-      <c r="C498" s="139"/>
-      <c r="D498" s="160"/>
+      <c r="C498" s="156"/>
+      <c r="D498" s="141"/>
       <c r="E498" s="8" t="s">
         <v>626</v>
       </c>
@@ -16073,8 +16139,8 @@
       <c r="B499" s="7">
         <v>41</v>
       </c>
-      <c r="C499" s="139"/>
-      <c r="D499" s="160"/>
+      <c r="C499" s="156"/>
+      <c r="D499" s="141"/>
       <c r="E499" s="8" t="s">
         <v>627</v>
       </c>
@@ -16095,8 +16161,8 @@
       <c r="B500" s="7">
         <v>42</v>
       </c>
-      <c r="C500" s="139"/>
-      <c r="D500" s="160"/>
+      <c r="C500" s="156"/>
+      <c r="D500" s="141"/>
       <c r="E500" s="8" t="s">
         <v>628</v>
       </c>
@@ -16117,8 +16183,8 @@
       <c r="B501" s="7">
         <v>43</v>
       </c>
-      <c r="C501" s="139"/>
-      <c r="D501" s="160"/>
+      <c r="C501" s="156"/>
+      <c r="D501" s="141"/>
       <c r="E501" s="8" t="s">
         <v>629</v>
       </c>
@@ -16139,8 +16205,8 @@
       <c r="B502" s="7">
         <v>44</v>
       </c>
-      <c r="C502" s="139"/>
-      <c r="D502" s="161"/>
+      <c r="C502" s="156"/>
+      <c r="D502" s="142"/>
       <c r="E502" s="8" t="s">
         <v>630</v>
       </c>
@@ -16161,8 +16227,8 @@
       <c r="B503" s="7">
         <v>45</v>
       </c>
-      <c r="C503" s="139"/>
-      <c r="D503" s="159" t="s">
+      <c r="C503" s="156"/>
+      <c r="D503" s="140" t="s">
         <v>631</v>
       </c>
       <c r="E503" s="8" t="s">
@@ -16185,8 +16251,8 @@
       <c r="B504" s="7">
         <v>46</v>
       </c>
-      <c r="C504" s="139"/>
-      <c r="D504" s="160"/>
+      <c r="C504" s="156"/>
+      <c r="D504" s="141"/>
       <c r="E504" s="8" t="s">
         <v>633</v>
       </c>
@@ -16207,8 +16273,8 @@
       <c r="B505" s="7">
         <v>47</v>
       </c>
-      <c r="C505" s="139"/>
-      <c r="D505" s="160"/>
+      <c r="C505" s="156"/>
+      <c r="D505" s="141"/>
       <c r="E505" s="8" t="s">
         <v>634</v>
       </c>
@@ -16229,8 +16295,8 @@
       <c r="B506" s="7">
         <v>48</v>
       </c>
-      <c r="C506" s="139"/>
-      <c r="D506" s="160"/>
+      <c r="C506" s="156"/>
+      <c r="D506" s="141"/>
       <c r="E506" s="8" t="s">
         <v>635</v>
       </c>
@@ -16251,8 +16317,8 @@
       <c r="B507" s="7">
         <v>49</v>
       </c>
-      <c r="C507" s="139"/>
-      <c r="D507" s="160"/>
+      <c r="C507" s="156"/>
+      <c r="D507" s="141"/>
       <c r="E507" s="8" t="s">
         <v>636</v>
       </c>
@@ -16273,8 +16339,8 @@
       <c r="B508" s="7">
         <v>50</v>
       </c>
-      <c r="C508" s="139"/>
-      <c r="D508" s="160"/>
+      <c r="C508" s="156"/>
+      <c r="D508" s="141"/>
       <c r="E508" s="8" t="s">
         <v>637</v>
       </c>
@@ -16295,8 +16361,8 @@
       <c r="B509" s="7">
         <v>51</v>
       </c>
-      <c r="C509" s="139"/>
-      <c r="D509" s="161"/>
+      <c r="C509" s="156"/>
+      <c r="D509" s="142"/>
       <c r="E509" s="8" t="s">
         <v>638</v>
       </c>
@@ -16317,8 +16383,8 @@
       <c r="B510" s="7">
         <v>52</v>
       </c>
-      <c r="C510" s="139"/>
-      <c r="D510" s="159" t="s">
+      <c r="C510" s="156"/>
+      <c r="D510" s="140" t="s">
         <v>639</v>
       </c>
       <c r="E510" s="8" t="s">
@@ -16341,8 +16407,8 @@
       <c r="B511" s="7">
         <v>53</v>
       </c>
-      <c r="C511" s="139"/>
-      <c r="D511" s="160"/>
+      <c r="C511" s="156"/>
+      <c r="D511" s="141"/>
       <c r="E511" s="8" t="s">
         <v>641</v>
       </c>
@@ -16363,8 +16429,8 @@
       <c r="B512" s="7">
         <v>54</v>
       </c>
-      <c r="C512" s="139"/>
-      <c r="D512" s="160"/>
+      <c r="C512" s="156"/>
+      <c r="D512" s="141"/>
       <c r="E512" s="8" t="s">
         <v>642</v>
       </c>
@@ -16385,8 +16451,8 @@
       <c r="B513" s="24">
         <v>55</v>
       </c>
-      <c r="C513" s="140"/>
-      <c r="D513" s="161"/>
+      <c r="C513" s="157"/>
+      <c r="D513" s="142"/>
       <c r="E513" s="17" t="s">
         <v>643</v>
       </c>
@@ -23320,47 +23386,66 @@
     </row>
   </sheetData>
   <mergeCells count="125">
-    <mergeCell ref="D26:D32"/>
-    <mergeCell ref="D33:D36"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="C4:C32"/>
-    <mergeCell ref="D4:D9"/>
-    <mergeCell ref="D10:D18"/>
-    <mergeCell ref="D19:D25"/>
-    <mergeCell ref="C33:C44"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="D40:D44"/>
-    <mergeCell ref="C107:C116"/>
-    <mergeCell ref="C117:C125"/>
-    <mergeCell ref="C127:C132"/>
-    <mergeCell ref="C134:C176"/>
-    <mergeCell ref="C177:C204"/>
-    <mergeCell ref="C205:C214"/>
-    <mergeCell ref="A106:J106"/>
-    <mergeCell ref="D107:D111"/>
-    <mergeCell ref="D112:D115"/>
-    <mergeCell ref="D117:D120"/>
-    <mergeCell ref="D121:D122"/>
-    <mergeCell ref="D123:D125"/>
-    <mergeCell ref="A126:J126"/>
-    <mergeCell ref="D127:D130"/>
-    <mergeCell ref="D131:D132"/>
-    <mergeCell ref="A133:J133"/>
-    <mergeCell ref="D210:D211"/>
-    <mergeCell ref="D212:D214"/>
-    <mergeCell ref="C45:C50"/>
-    <mergeCell ref="D45:D50"/>
-    <mergeCell ref="D51:D57"/>
-    <mergeCell ref="D58:D63"/>
-    <mergeCell ref="D64:D67"/>
-    <mergeCell ref="D69:D78"/>
-    <mergeCell ref="D79:D84"/>
-    <mergeCell ref="D85:D90"/>
-    <mergeCell ref="D91:D105"/>
-    <mergeCell ref="A68:J68"/>
-    <mergeCell ref="C51:C67"/>
-    <mergeCell ref="C69:C105"/>
+    <mergeCell ref="C459:C513"/>
+    <mergeCell ref="C216:C249"/>
+    <mergeCell ref="C250:C265"/>
+    <mergeCell ref="C266:C272"/>
+    <mergeCell ref="C274:C292"/>
+    <mergeCell ref="C293:C307"/>
+    <mergeCell ref="C308:C317"/>
+    <mergeCell ref="C318:C342"/>
+    <mergeCell ref="D459:D466"/>
+    <mergeCell ref="D467:D473"/>
+    <mergeCell ref="D474:D481"/>
+    <mergeCell ref="D482:D485"/>
+    <mergeCell ref="D486:D496"/>
+    <mergeCell ref="D497:D502"/>
+    <mergeCell ref="D503:D509"/>
+    <mergeCell ref="D510:D513"/>
+    <mergeCell ref="D318:D323"/>
+    <mergeCell ref="D324:D328"/>
+    <mergeCell ref="D329:D337"/>
+    <mergeCell ref="D338:D342"/>
+    <mergeCell ref="D343:D347"/>
+    <mergeCell ref="D348:D353"/>
+    <mergeCell ref="D354:D357"/>
+    <mergeCell ref="D296:D300"/>
+    <mergeCell ref="D301:D303"/>
+    <mergeCell ref="D304:D307"/>
+    <mergeCell ref="D308:D314"/>
+    <mergeCell ref="D315:D317"/>
+    <mergeCell ref="C343:C357"/>
+    <mergeCell ref="C359:C380"/>
+    <mergeCell ref="C381:C435"/>
+    <mergeCell ref="C437:C458"/>
+    <mergeCell ref="D250:D257"/>
+    <mergeCell ref="D258:D259"/>
+    <mergeCell ref="D260:D265"/>
+    <mergeCell ref="D266:D270"/>
+    <mergeCell ref="D271:D272"/>
+    <mergeCell ref="D274:D281"/>
+    <mergeCell ref="D282:D288"/>
+    <mergeCell ref="D289:D292"/>
+    <mergeCell ref="D293:D295"/>
+    <mergeCell ref="D449:D452"/>
+    <mergeCell ref="D453:D458"/>
+    <mergeCell ref="D417:D419"/>
+    <mergeCell ref="D420:D426"/>
+    <mergeCell ref="D427:D430"/>
+    <mergeCell ref="D431:D435"/>
+    <mergeCell ref="D437:D441"/>
+    <mergeCell ref="D442:D445"/>
+    <mergeCell ref="D446:D448"/>
+    <mergeCell ref="D400:D404"/>
+    <mergeCell ref="D405:D416"/>
+    <mergeCell ref="A436:J436"/>
+    <mergeCell ref="D359:D363"/>
+    <mergeCell ref="D364:D371"/>
+    <mergeCell ref="D372:D375"/>
+    <mergeCell ref="D376:D380"/>
+    <mergeCell ref="D381:D386"/>
+    <mergeCell ref="D387:D396"/>
+    <mergeCell ref="D397:D399"/>
     <mergeCell ref="A215:J215"/>
     <mergeCell ref="A273:J273"/>
     <mergeCell ref="A358:J358"/>
@@ -23385,69 +23470,50 @@
     <mergeCell ref="D234:D240"/>
     <mergeCell ref="D241:D243"/>
     <mergeCell ref="D244:D249"/>
-    <mergeCell ref="D442:D445"/>
-    <mergeCell ref="D446:D448"/>
-    <mergeCell ref="D400:D404"/>
-    <mergeCell ref="D405:D416"/>
-    <mergeCell ref="A436:J436"/>
-    <mergeCell ref="D359:D363"/>
-    <mergeCell ref="D364:D371"/>
-    <mergeCell ref="D372:D375"/>
-    <mergeCell ref="D376:D380"/>
-    <mergeCell ref="D381:D386"/>
-    <mergeCell ref="D387:D396"/>
-    <mergeCell ref="D397:D399"/>
-    <mergeCell ref="D301:D303"/>
-    <mergeCell ref="D304:D307"/>
-    <mergeCell ref="D308:D314"/>
-    <mergeCell ref="D315:D317"/>
-    <mergeCell ref="C343:C357"/>
-    <mergeCell ref="C359:C380"/>
-    <mergeCell ref="C381:C435"/>
-    <mergeCell ref="C437:C458"/>
-    <mergeCell ref="D250:D257"/>
-    <mergeCell ref="D258:D259"/>
-    <mergeCell ref="D260:D265"/>
-    <mergeCell ref="D266:D270"/>
-    <mergeCell ref="D271:D272"/>
-    <mergeCell ref="D274:D281"/>
-    <mergeCell ref="D282:D288"/>
-    <mergeCell ref="D289:D292"/>
-    <mergeCell ref="D293:D295"/>
-    <mergeCell ref="D449:D452"/>
-    <mergeCell ref="D453:D458"/>
-    <mergeCell ref="D417:D419"/>
-    <mergeCell ref="D420:D426"/>
-    <mergeCell ref="D427:D430"/>
-    <mergeCell ref="D431:D435"/>
-    <mergeCell ref="D437:D441"/>
-    <mergeCell ref="C459:C513"/>
-    <mergeCell ref="C216:C249"/>
-    <mergeCell ref="C250:C265"/>
-    <mergeCell ref="C266:C272"/>
-    <mergeCell ref="C274:C292"/>
-    <mergeCell ref="C293:C307"/>
-    <mergeCell ref="C308:C317"/>
-    <mergeCell ref="C318:C342"/>
-    <mergeCell ref="D459:D466"/>
-    <mergeCell ref="D467:D473"/>
-    <mergeCell ref="D474:D481"/>
-    <mergeCell ref="D482:D485"/>
-    <mergeCell ref="D486:D496"/>
-    <mergeCell ref="D497:D502"/>
-    <mergeCell ref="D503:D509"/>
-    <mergeCell ref="D510:D513"/>
-    <mergeCell ref="D318:D323"/>
-    <mergeCell ref="D324:D328"/>
-    <mergeCell ref="D329:D337"/>
-    <mergeCell ref="D338:D342"/>
-    <mergeCell ref="D343:D347"/>
-    <mergeCell ref="D348:D353"/>
-    <mergeCell ref="D354:D357"/>
-    <mergeCell ref="D296:D300"/>
+    <mergeCell ref="C45:C50"/>
+    <mergeCell ref="D45:D50"/>
+    <mergeCell ref="D51:D57"/>
+    <mergeCell ref="D58:D63"/>
+    <mergeCell ref="D64:D67"/>
+    <mergeCell ref="D69:D78"/>
+    <mergeCell ref="D79:D84"/>
+    <mergeCell ref="D85:D90"/>
+    <mergeCell ref="D91:D105"/>
+    <mergeCell ref="A68:J68"/>
+    <mergeCell ref="C51:C67"/>
+    <mergeCell ref="C69:C105"/>
+    <mergeCell ref="C107:C116"/>
+    <mergeCell ref="C117:C125"/>
+    <mergeCell ref="C127:C132"/>
+    <mergeCell ref="C134:C176"/>
+    <mergeCell ref="C177:C204"/>
+    <mergeCell ref="C205:C214"/>
+    <mergeCell ref="A106:J106"/>
+    <mergeCell ref="D107:D111"/>
+    <mergeCell ref="D112:D115"/>
+    <mergeCell ref="D117:D120"/>
+    <mergeCell ref="D121:D122"/>
+    <mergeCell ref="D123:D125"/>
+    <mergeCell ref="A126:J126"/>
+    <mergeCell ref="D127:D130"/>
+    <mergeCell ref="D131:D132"/>
+    <mergeCell ref="A133:J133"/>
+    <mergeCell ref="D210:D211"/>
+    <mergeCell ref="D212:D214"/>
+    <mergeCell ref="D26:D32"/>
+    <mergeCell ref="D33:D36"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="C4:C32"/>
+    <mergeCell ref="D4:D9"/>
+    <mergeCell ref="D10:D18"/>
+    <mergeCell ref="D19:D25"/>
+    <mergeCell ref="C33:C44"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="D40:D44"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H67 H69:H105 H107:H125 H127:H132 H134:H214 H216:H272 H274:H357 H359:H435 H437:H513" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H69:H105 H107:H125 H127:H132 H134:H214 H216:H272 H274:H357 H359:H435 H437:H513 H4:H65 H67" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Not Attempted,Tried (couldn't think of logic),Logic Done (couldn't code),Code Done (but has error),Done "</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G4:G67 G69:G105 G107:G125 G127:G132 G134:G214 G216:G272 G274:G357 G359:G435 G437:G513" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -23973,16 +24039,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="31.5" customHeight="1">
-      <c r="A1" s="189" t="s">
+      <c r="A1" s="191" t="s">
         <v>644</v>
       </c>
-      <c r="B1" s="190"/>
+      <c r="B1" s="192"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1">
-      <c r="A2" s="191" t="s">
+      <c r="A2" s="193" t="s">
         <v>645</v>
       </c>
-      <c r="B2" s="190"/>
+      <c r="B2" s="192"/>
     </row>
     <row r="3" spans="1:2" ht="18" customHeight="1">
       <c r="A3" s="46" t="s">
@@ -24029,10 +24095,10 @@
       <c r="B8" s="47"/>
     </row>
     <row r="9" spans="1:2" ht="18" customHeight="1">
-      <c r="A9" s="191" t="s">
+      <c r="A9" s="193" t="s">
         <v>656</v>
       </c>
-      <c r="B9" s="190"/>
+      <c r="B9" s="192"/>
     </row>
     <row r="10" spans="1:2" ht="18" customHeight="1">
       <c r="A10" s="52" t="s">
@@ -24111,10 +24177,10 @@
       <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:2" ht="18" customHeight="1">
-      <c r="A20" s="191" t="s">
+      <c r="A20" s="193" t="s">
         <v>675</v>
       </c>
-      <c r="B20" s="190"/>
+      <c r="B20" s="192"/>
     </row>
     <row r="21" spans="1:2" ht="18" customHeight="1">
       <c r="A21" s="52" t="s">
@@ -25111,15 +25177,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="192" t="s">
+      <c r="A1" s="194" t="s">
         <v>678</v>
       </c>
-      <c r="B1" s="193"/>
-      <c r="C1" s="193"/>
-      <c r="D1" s="193"/>
-      <c r="E1" s="193"/>
-      <c r="F1" s="193"/>
-      <c r="G1" s="190"/>
+      <c r="B1" s="195"/>
+      <c r="C1" s="195"/>
+      <c r="D1" s="195"/>
+      <c r="E1" s="195"/>
+      <c r="F1" s="195"/>
+      <c r="G1" s="192"/>
     </row>
     <row r="2" spans="1:8" ht="13.2">
       <c r="A2" s="53" t="s">

--- a/DSA Master Sheet.xlsx
+++ b/DSA Master Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aamer\Desktop\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4617297E-C261-4D43-81D8-616C18D54CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87EA8CA3-982B-4188-9FB6-B26EEBB1A549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="730">
   <si>
     <t>DSA Master Sheet</t>
   </si>
@@ -2804,6 +2804,90 @@
 Expand left and right while characters are equal.
 Extract using substring(low + 1, high).
 Keep the longest palindrome and return it.</t>
+  </si>
+  <si>
+    <t>Initialize → count = 0, max = 0
+Traverse → Read each character
+( → count++
+) → count--, update max
+Return → max</t>
+  </si>
+  <si>
+    <t>Beauty Sum of All Substrings — 5-Step Thinking Algorithm
+Fix the left index (i) → Start a new substring.
+Reset frequency array → int[] freq = new int[26].
+Expand the right index (j) → Add one character at a time.
+Update frequency &amp; find max and min → Ignore characters with frequency 0.
+Add beauty → ans += (max - min) and continue expanding.
+Memory Trick
+Fix Left → Expand Right → Update Frequency → Find Beauty → Add Answer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  int ans = arr.length;
+        while (low &lt;= high) {
+            int mid = low + (high - low) / 2;
+            if (arr[mid] &gt;= target) {
+                ans = mid;        // possible answer
+                high = mid - 1;   // search left half
+            } else {
+                low = mid + 1;    // search right half
+            }
+        }
+        return ans;</t>
+  </si>
+  <si>
+    <t>int ans = n;
+        while (low &lt;= high) {
+            int mid = low + (high - low) / 2;
+            if (arr[mid] &gt; target) {
+                ans = mid;          // possible answer
+                high = mid - 1;     // search left
+            } else {
+                low = mid + 1;      // search right
+            }
+        }
+        return ans;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        int ans = n;
+        if(nums[n-1]&lt;target)return n;
+        while(l&lt;=r){
+            int m = (l+r)/2;
+            if(nums[m]&gt;target){
+                r = m-1;
+                ans = m;
+            }
+            else if(nums[m]&lt;target){
+                l = m+1;
+            }
+            if(nums[m]==target)
+            return m;
+        }
+        return ans;</t>
+  </si>
+  <si>
+    <t>BINARY SEARCH CHEAT SHEET
+Lower Bound        → First index where element &gt;= x
+Store: arr[mid] &gt;= x
+Move : LEFT (high = mid - 1)
+Upper Bound        → First index where element &gt; x
+Store: arr[mid] &gt; x
+Move : LEFT (high = mid - 1)
+Search Insert      → Insert position of x
+Store: arr[mid] &gt;= x
+Move : LEFT (high = mid - 1)
+Ceil               → Smallest element &gt;= x
+Store: arr[mid] &gt;= x
+Move : LEFT (high = mid - 1)
+Floor              → Largest element &lt;= x
+Store: arr[mid] &lt;= x
+Move : RIGHT (low = mid + 1)
+First Occurrence   → Leftmost index of x
+Store: arr[mid] == x
+Move : LEFT (high = mid - 1)
+Last Occurrence    → Rightmost index of x
+Store: arr[mid] == x
+Move : RIGHT (low = mid + 1)</t>
   </si>
 </sst>
 </file>
@@ -3909,7 +3993,7 @@
     <xf numFmtId="0" fontId="88" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="89" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="197">
+  <cellXfs count="206">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4284,6 +4368,30 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="87" fillId="52" borderId="8" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="88" fillId="53" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="53" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="53" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="53" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="53" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="88" fillId="53" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="53" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="53" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="53" borderId="8" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4448,7 +4556,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="87" fillId="52" borderId="8" xfId="2" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
@@ -4468,6 +4575,566 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>434989</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>101441</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>437869</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123761</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="2" name="Ink 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E406247B-BDC8-09BC-B53D-3AFA8D84D51C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="7599213" y="65597834"/>
+            <a:ext cx="2880" cy="22320"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="2" name="Ink 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E406247B-BDC8-09BC-B53D-3AFA8D84D51C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7590213" y="65588834"/>
+              <a:ext cx="20520" cy="39960"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>411229</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>80089</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>484309</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>178729</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="8" name="Ink 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{929A29EC-E4B2-2588-B6C0-B6C853945B67}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="7575453" y="68204313"/>
+            <a:ext cx="73080" cy="98640"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="8" name="Ink 7">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{929A29EC-E4B2-2588-B6C0-B6C853945B67}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7569333" y="68198193"/>
+              <a:ext cx="85320" cy="110880"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>402589</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>147769</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>402949</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>150649</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="9" name="Ink 8">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9F9DC73-83FA-E5C6-7A23-FDE10927E561}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="7566813" y="68271993"/>
+            <a:ext cx="360" cy="2880"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="9" name="Ink 8">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9F9DC73-83FA-E5C6-7A23-FDE10927E561}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7560693" y="68265873"/>
+              <a:ext cx="12600" cy="15120"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>356149</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>131569</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>359749</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>133009</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="10" name="Ink 9">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31BA5D8C-89A8-877A-5562-99E7EE584EB8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="7520373" y="68255793"/>
+            <a:ext cx="3600" cy="1440"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="10" name="Ink 9">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31BA5D8C-89A8-877A-5562-99E7EE584EB8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7514253" y="68249673"/>
+              <a:ext cx="15840" cy="13680"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>365509</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>137689</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>368029</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>138049</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="11" name="Ink 10">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2130F9FF-7D9B-07DC-9E47-8A5248D79FFB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="7529733" y="68261913"/>
+            <a:ext cx="2520" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="11" name="Ink 10">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2130F9FF-7D9B-07DC-9E47-8A5248D79FFB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7523613" y="68255793"/>
+              <a:ext cx="14760" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>337429</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>107809</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>338509</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>120409</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="12" name="Ink 11">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F5581A5-AF6E-CBBB-28A6-529B33E25414}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="7501653" y="68232033"/>
+            <a:ext cx="1080" cy="12600"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="12" name="Ink 11">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F5581A5-AF6E-CBBB-28A6-529B33E25414}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7495533" y="68225913"/>
+              <a:ext cx="13320" cy="24840"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-04T10:02:13.279"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">8 61 132,'0'-5'1216,"0"0"-368,0 0-528,-2 0-244,2-2-120,0 4-72,-2-1-24,2-1-20,0 2-16,0 0-12,-2-1-16,2 1 0,0 1 0,0 0-24,0-1-32,-2 1-56</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink2.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-04T10:27:31.377"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">145 268 36,'0'1'59,"1"-1"1,0 1-1,0-1 1,0 1-1,0-1 1,0 1-1,0-1 1,0 0-1,0 1 1,0-1-1,0 0 1,0 0-1,0 0 1,0 0-1,0 0 1,0 0-1,0 0 1,0 0-1,0 0 1,0 0-1,0 0 1,0-1-1,0 1 1,0 0-1,0-1 1,1 0-1,-1 0-117,0 1-1,1-1 0,-1 1 1,0 0-1,0-1 0,0 1 0,1 0 1,-1 0-1,0-1 0,0 1 1,1 0-1,-1 0 0,0 1 1,0-1-1,1 0 0,-1 0 1,0 1-1,0-1 0,1 0 1,0 2-1,2-1-243</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="715.46">62 189 256,'-3'11'2062,"1"0"-3873</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1113.04">1 177 1020,'2'0'161,"0"0"0,-1-1 0,1 1-1,0-1 1,0 1 0,0-1 0,0 0 0,-1 0 0,1 0 0,0 0-1,-1 0 1,1 0 0,-1 0 0,1 0 0,-1-1 0,0 1 0,1-1-1,-1 1 1,0-1 0,1-1 0,10-11 271,-12 12-432</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1334.86">38 105 844,'6'-89'2242,"-1"73"-4979</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink3.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-04T10:27:39.191"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 1 124,'0'7'43</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink4.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-04T10:27:39.428"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 4 632,'2'0'508,"-2"-2"-252,2 0-44,0 2-164,0 0-12,0 0-220</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink5.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-04T10:27:39.585"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 0 136,'1'0'392,"1"0"-204,0 0-128</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink6.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-09-04T10:27:39.870"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">2 34 696,'-2'-8'324,"2"1"-264,0-1-180,0 3-116,0 0-76</inkml:trace>
+</inkml:ink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4686,18 +5353,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="30.75" customHeight="1">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="153" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="145"/>
+      <c r="B1" s="154"/>
+      <c r="C1" s="154"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="154"/>
+      <c r="F1" s="154"/>
+      <c r="G1" s="154"/>
+      <c r="H1" s="154"/>
+      <c r="I1" s="154"/>
+      <c r="J1" s="155"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -4752,18 +5419,18 @@
       <c r="T2" s="5"/>
     </row>
     <row r="3" spans="1:20" ht="13.8">
-      <c r="A3" s="146" t="s">
+      <c r="A3" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="147"/>
-      <c r="C3" s="147"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="147"/>
-      <c r="G3" s="147"/>
-      <c r="H3" s="147"/>
-      <c r="I3" s="147"/>
-      <c r="J3" s="148"/>
+      <c r="B3" s="157"/>
+      <c r="C3" s="157"/>
+      <c r="D3" s="157"/>
+      <c r="E3" s="157"/>
+      <c r="F3" s="157"/>
+      <c r="G3" s="157"/>
+      <c r="H3" s="157"/>
+      <c r="I3" s="157"/>
+      <c r="J3" s="158"/>
     </row>
     <row r="4" spans="1:20" ht="13.8">
       <c r="A4" s="6">
@@ -4772,10 +5439,10 @@
       <c r="B4" s="7">
         <v>1</v>
       </c>
-      <c r="C4" s="149" t="s">
+      <c r="C4" s="159" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="140" t="s">
+      <c r="D4" s="150" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -4805,8 +5472,8 @@
       <c r="B5" s="7">
         <v>2</v>
       </c>
-      <c r="C5" s="150"/>
-      <c r="D5" s="141"/>
+      <c r="C5" s="160"/>
+      <c r="D5" s="151"/>
       <c r="E5" s="8" t="s">
         <v>16</v>
       </c>
@@ -4834,8 +5501,8 @@
       <c r="B6" s="7">
         <v>3</v>
       </c>
-      <c r="C6" s="150"/>
-      <c r="D6" s="141"/>
+      <c r="C6" s="160"/>
+      <c r="D6" s="151"/>
       <c r="E6" s="8" t="s">
         <v>19</v>
       </c>
@@ -4863,8 +5530,8 @@
       <c r="B7" s="7">
         <v>4</v>
       </c>
-      <c r="C7" s="150"/>
-      <c r="D7" s="141"/>
+      <c r="C7" s="160"/>
+      <c r="D7" s="151"/>
       <c r="E7" s="8" t="s">
         <v>23</v>
       </c>
@@ -4892,8 +5559,8 @@
       <c r="B8" s="7">
         <v>5</v>
       </c>
-      <c r="C8" s="150"/>
-      <c r="D8" s="141"/>
+      <c r="C8" s="160"/>
+      <c r="D8" s="151"/>
       <c r="E8" s="8" t="s">
         <v>26</v>
       </c>
@@ -4921,8 +5588,8 @@
       <c r="B9" s="7">
         <v>6</v>
       </c>
-      <c r="C9" s="150"/>
-      <c r="D9" s="142"/>
+      <c r="C9" s="160"/>
+      <c r="D9" s="152"/>
       <c r="E9" s="8" t="s">
         <v>29</v>
       </c>
@@ -4947,8 +5614,8 @@
       <c r="B10" s="7">
         <v>7</v>
       </c>
-      <c r="C10" s="150"/>
-      <c r="D10" s="140" t="s">
+      <c r="C10" s="160"/>
+      <c r="D10" s="150" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="8" t="s">
@@ -4975,8 +5642,8 @@
       <c r="B11" s="7">
         <v>8</v>
       </c>
-      <c r="C11" s="150"/>
-      <c r="D11" s="141"/>
+      <c r="C11" s="160"/>
+      <c r="D11" s="151"/>
       <c r="E11" s="13" t="s">
         <v>32</v>
       </c>
@@ -5001,8 +5668,8 @@
       <c r="B12" s="7">
         <v>9</v>
       </c>
-      <c r="C12" s="150"/>
-      <c r="D12" s="141"/>
+      <c r="C12" s="160"/>
+      <c r="D12" s="151"/>
       <c r="E12" s="8" t="s">
         <v>33</v>
       </c>
@@ -5027,8 +5694,8 @@
       <c r="B13" s="7">
         <v>10</v>
       </c>
-      <c r="C13" s="150"/>
-      <c r="D13" s="141"/>
+      <c r="C13" s="160"/>
+      <c r="D13" s="151"/>
       <c r="E13" s="8" t="s">
         <v>34</v>
       </c>
@@ -5055,8 +5722,8 @@
       <c r="B14" s="7">
         <v>11</v>
       </c>
-      <c r="C14" s="150"/>
-      <c r="D14" s="141"/>
+      <c r="C14" s="160"/>
+      <c r="D14" s="151"/>
       <c r="E14" s="8" t="s">
         <v>35</v>
       </c>
@@ -5081,8 +5748,8 @@
       <c r="B15" s="7">
         <v>12</v>
       </c>
-      <c r="C15" s="150"/>
-      <c r="D15" s="141"/>
+      <c r="C15" s="160"/>
+      <c r="D15" s="151"/>
       <c r="E15" s="8" t="s">
         <v>36</v>
       </c>
@@ -5109,8 +5776,8 @@
       <c r="B16" s="7">
         <v>13</v>
       </c>
-      <c r="C16" s="150"/>
-      <c r="D16" s="141"/>
+      <c r="C16" s="160"/>
+      <c r="D16" s="151"/>
       <c r="E16" s="8" t="s">
         <v>37</v>
       </c>
@@ -5135,8 +5802,8 @@
       <c r="B17" s="7">
         <v>14</v>
       </c>
-      <c r="C17" s="150"/>
-      <c r="D17" s="141"/>
+      <c r="C17" s="160"/>
+      <c r="D17" s="151"/>
       <c r="E17" s="8" t="s">
         <v>38</v>
       </c>
@@ -5156,15 +5823,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="372.6">
+    <row r="18" spans="1:10" ht="386.4">
       <c r="A18" s="6">
         <v>15</v>
       </c>
       <c r="B18" s="7">
         <v>15</v>
       </c>
-      <c r="C18" s="150"/>
-      <c r="D18" s="142"/>
+      <c r="C18" s="160"/>
+      <c r="D18" s="152"/>
       <c r="E18" s="13" t="s">
         <v>39</v>
       </c>
@@ -5191,8 +5858,8 @@
       <c r="B19" s="7">
         <v>16</v>
       </c>
-      <c r="C19" s="150"/>
-      <c r="D19" s="140" t="s">
+      <c r="C19" s="160"/>
+      <c r="D19" s="150" t="s">
         <v>40</v>
       </c>
       <c r="E19" s="8" t="s">
@@ -5221,8 +5888,8 @@
       <c r="B20" s="7">
         <v>17</v>
       </c>
-      <c r="C20" s="150"/>
-      <c r="D20" s="141"/>
+      <c r="C20" s="160"/>
+      <c r="D20" s="151"/>
       <c r="E20" s="8" t="s">
         <v>42</v>
       </c>
@@ -5249,8 +5916,8 @@
       <c r="B21" s="7">
         <v>18</v>
       </c>
-      <c r="C21" s="150"/>
-      <c r="D21" s="141"/>
+      <c r="C21" s="160"/>
+      <c r="D21" s="151"/>
       <c r="E21" s="8" t="s">
         <v>43</v>
       </c>
@@ -5277,8 +5944,8 @@
       <c r="B22" s="7">
         <v>19</v>
       </c>
-      <c r="C22" s="150"/>
-      <c r="D22" s="141"/>
+      <c r="C22" s="160"/>
+      <c r="D22" s="151"/>
       <c r="E22" s="8" t="s">
         <v>44</v>
       </c>
@@ -5299,8 +5966,8 @@
       <c r="B23" s="7">
         <v>20</v>
       </c>
-      <c r="C23" s="150"/>
-      <c r="D23" s="141"/>
+      <c r="C23" s="160"/>
+      <c r="D23" s="151"/>
       <c r="E23" s="8" t="s">
         <v>45</v>
       </c>
@@ -5321,8 +5988,8 @@
       <c r="B24" s="7">
         <v>21</v>
       </c>
-      <c r="C24" s="150"/>
-      <c r="D24" s="141"/>
+      <c r="C24" s="160"/>
+      <c r="D24" s="151"/>
       <c r="E24" s="13" t="s">
         <v>46</v>
       </c>
@@ -5347,8 +6014,8 @@
       <c r="B25" s="7">
         <v>22</v>
       </c>
-      <c r="C25" s="150"/>
-      <c r="D25" s="142"/>
+      <c r="C25" s="160"/>
+      <c r="D25" s="152"/>
       <c r="E25" s="8" t="s">
         <v>47</v>
       </c>
@@ -5375,8 +6042,8 @@
       <c r="B26" s="7">
         <v>23</v>
       </c>
-      <c r="C26" s="150"/>
-      <c r="D26" s="140" t="s">
+      <c r="C26" s="160"/>
+      <c r="D26" s="150" t="s">
         <v>48</v>
       </c>
       <c r="E26" s="13" t="s">
@@ -5405,8 +6072,8 @@
       <c r="B27" s="7">
         <v>24</v>
       </c>
-      <c r="C27" s="150"/>
-      <c r="D27" s="141"/>
+      <c r="C27" s="160"/>
+      <c r="D27" s="151"/>
       <c r="E27" s="8" t="s">
         <v>50</v>
       </c>
@@ -5431,8 +6098,8 @@
       <c r="B28" s="7">
         <v>25</v>
       </c>
-      <c r="C28" s="150"/>
-      <c r="D28" s="141"/>
+      <c r="C28" s="160"/>
+      <c r="D28" s="151"/>
       <c r="E28" s="8" t="s">
         <v>51</v>
       </c>
@@ -5452,93 +6119,93 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="13.8">
-      <c r="A29" s="6">
+    <row r="29" spans="1:10" s="145" customFormat="1" ht="13.8">
+      <c r="A29" s="142">
         <v>26</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="143">
         <v>26</v>
       </c>
-      <c r="C29" s="150"/>
-      <c r="D29" s="141"/>
-      <c r="E29" s="8" t="s">
+      <c r="C29" s="160"/>
+      <c r="D29" s="151"/>
+      <c r="E29" s="144" t="s">
         <v>52</v>
       </c>
-      <c r="F29" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G29" s="10">
+      <c r="F29" s="142" t="s">
+        <v>6</v>
+      </c>
+      <c r="G29" s="141">
         <v>4</v>
       </c>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-    </row>
-    <row r="30" spans="1:10" ht="13.8">
-      <c r="A30" s="6">
+      <c r="H29" s="127"/>
+      <c r="I29" s="127"/>
+      <c r="J29" s="127"/>
+    </row>
+    <row r="30" spans="1:10" s="145" customFormat="1" ht="13.8">
+      <c r="A30" s="142">
         <v>27</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="143">
         <v>27</v>
       </c>
-      <c r="C30" s="150"/>
-      <c r="D30" s="141"/>
-      <c r="E30" s="8" t="s">
+      <c r="C30" s="160"/>
+      <c r="D30" s="151"/>
+      <c r="E30" s="144" t="s">
         <v>53</v>
       </c>
-      <c r="F30" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G30" s="10">
+      <c r="F30" s="142" t="s">
+        <v>6</v>
+      </c>
+      <c r="G30" s="141">
         <v>4</v>
       </c>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-    </row>
-    <row r="31" spans="1:10" ht="13.8">
-      <c r="A31" s="6">
+      <c r="H30" s="127"/>
+      <c r="I30" s="127"/>
+      <c r="J30" s="127"/>
+    </row>
+    <row r="31" spans="1:10" s="145" customFormat="1" ht="13.8">
+      <c r="A31" s="142">
         <v>28</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="143">
         <v>28</v>
       </c>
-      <c r="C31" s="150"/>
-      <c r="D31" s="141"/>
-      <c r="E31" s="8" t="s">
+      <c r="C31" s="160"/>
+      <c r="D31" s="151"/>
+      <c r="E31" s="144" t="s">
         <v>54</v>
       </c>
-      <c r="F31" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G31" s="10">
+      <c r="F31" s="142" t="s">
+        <v>6</v>
+      </c>
+      <c r="G31" s="141">
         <v>4</v>
       </c>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-    </row>
-    <row r="32" spans="1:10" ht="13.8">
-      <c r="A32" s="6">
+      <c r="H31" s="127"/>
+      <c r="I31" s="127"/>
+      <c r="J31" s="127"/>
+    </row>
+    <row r="32" spans="1:10" s="145" customFormat="1" ht="13.8">
+      <c r="A32" s="142">
         <v>29</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="143">
         <v>29</v>
       </c>
-      <c r="C32" s="151"/>
-      <c r="D32" s="142"/>
-      <c r="E32" s="17" t="s">
+      <c r="C32" s="161"/>
+      <c r="D32" s="152"/>
+      <c r="E32" s="146" t="s">
         <v>55</v>
       </c>
-      <c r="F32" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="G32" s="19">
+      <c r="F32" s="147" t="s">
+        <v>6</v>
+      </c>
+      <c r="G32" s="148">
         <v>5</v>
       </c>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
+      <c r="H32" s="149"/>
+      <c r="I32" s="149"/>
+      <c r="J32" s="149"/>
     </row>
     <row r="33" spans="1:10" ht="13.8">
       <c r="A33" s="21">
@@ -5547,10 +6214,10 @@
       <c r="B33" s="22">
         <v>1</v>
       </c>
-      <c r="C33" s="152" t="s">
+      <c r="C33" s="162" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="140" t="s">
+      <c r="D33" s="150" t="s">
         <v>57</v>
       </c>
       <c r="E33" s="8" t="s">
@@ -5577,8 +6244,8 @@
       <c r="B34" s="7">
         <v>2</v>
       </c>
-      <c r="C34" s="153"/>
-      <c r="D34" s="141"/>
+      <c r="C34" s="163"/>
+      <c r="D34" s="151"/>
       <c r="E34" s="8" t="s">
         <v>59</v>
       </c>
@@ -5603,8 +6270,8 @@
       <c r="B35" s="7">
         <v>3</v>
       </c>
-      <c r="C35" s="153"/>
-      <c r="D35" s="141"/>
+      <c r="C35" s="163"/>
+      <c r="D35" s="151"/>
       <c r="E35" s="8" t="s">
         <v>60</v>
       </c>
@@ -5631,8 +6298,8 @@
       <c r="B36" s="7">
         <v>4</v>
       </c>
-      <c r="C36" s="153"/>
-      <c r="D36" s="142"/>
+      <c r="C36" s="163"/>
+      <c r="D36" s="152"/>
       <c r="E36" s="8" t="s">
         <v>61</v>
       </c>
@@ -5659,8 +6326,8 @@
       <c r="B37" s="7">
         <v>5</v>
       </c>
-      <c r="C37" s="153"/>
-      <c r="D37" s="140" t="s">
+      <c r="C37" s="163"/>
+      <c r="D37" s="150" t="s">
         <v>62</v>
       </c>
       <c r="E37" s="8" t="s">
@@ -5687,8 +6354,8 @@
       <c r="B38" s="7">
         <v>6</v>
       </c>
-      <c r="C38" s="153"/>
-      <c r="D38" s="141"/>
+      <c r="C38" s="163"/>
+      <c r="D38" s="151"/>
       <c r="E38" s="8" t="s">
         <v>64</v>
       </c>
@@ -5713,8 +6380,8 @@
       <c r="B39" s="7">
         <v>7</v>
       </c>
-      <c r="C39" s="153"/>
-      <c r="D39" s="142"/>
+      <c r="C39" s="163"/>
+      <c r="D39" s="152"/>
       <c r="E39" s="8" t="s">
         <v>65</v>
       </c>
@@ -5739,8 +6406,8 @@
       <c r="B40" s="7">
         <v>8</v>
       </c>
-      <c r="C40" s="153"/>
-      <c r="D40" s="140" t="s">
+      <c r="C40" s="163"/>
+      <c r="D40" s="150" t="s">
         <v>66</v>
       </c>
       <c r="E40" s="8" t="s">
@@ -5767,8 +6434,8 @@
       <c r="B41" s="7">
         <v>9</v>
       </c>
-      <c r="C41" s="153"/>
-      <c r="D41" s="141"/>
+      <c r="C41" s="163"/>
+      <c r="D41" s="151"/>
       <c r="E41" s="8" t="s">
         <v>68</v>
       </c>
@@ -5793,8 +6460,8 @@
       <c r="B42" s="7">
         <v>10</v>
       </c>
-      <c r="C42" s="153"/>
-      <c r="D42" s="141"/>
+      <c r="C42" s="163"/>
+      <c r="D42" s="151"/>
       <c r="E42" s="8" t="s">
         <v>69</v>
       </c>
@@ -5819,8 +6486,8 @@
       <c r="B43" s="7">
         <v>11</v>
       </c>
-      <c r="C43" s="153"/>
-      <c r="D43" s="141"/>
+      <c r="C43" s="163"/>
+      <c r="D43" s="151"/>
       <c r="E43" s="8" t="s">
         <v>70</v>
       </c>
@@ -5845,8 +6512,8 @@
       <c r="B44" s="24">
         <v>12</v>
       </c>
-      <c r="C44" s="154"/>
-      <c r="D44" s="142"/>
+      <c r="C44" s="164"/>
+      <c r="D44" s="152"/>
       <c r="E44" s="17" t="s">
         <v>71</v>
       </c>
@@ -5860,7 +6527,7 @@
         <v>27</v>
       </c>
       <c r="I44" s="20"/>
-      <c r="J44" s="196" t="s">
+      <c r="J44" s="140" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5871,10 +6538,10 @@
       <c r="B45" s="22">
         <v>1</v>
       </c>
-      <c r="C45" s="167" t="s">
+      <c r="C45" s="177" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="170" t="s">
+      <c r="D45" s="180" t="s">
         <v>73</v>
       </c>
       <c r="E45" s="13" t="s">
@@ -5901,8 +6568,8 @@
       <c r="B46" s="7">
         <v>2</v>
       </c>
-      <c r="C46" s="168"/>
-      <c r="D46" s="171"/>
+      <c r="C46" s="178"/>
+      <c r="D46" s="181"/>
       <c r="E46" s="8" t="s">
         <v>75</v>
       </c>
@@ -5929,8 +6596,8 @@
       <c r="B47" s="7">
         <v>3</v>
       </c>
-      <c r="C47" s="168"/>
-      <c r="D47" s="171"/>
+      <c r="C47" s="178"/>
+      <c r="D47" s="181"/>
       <c r="E47" s="13" t="s">
         <v>76</v>
       </c>
@@ -5957,8 +6624,8 @@
       <c r="B48" s="7">
         <v>4</v>
       </c>
-      <c r="C48" s="168"/>
-      <c r="D48" s="171"/>
+      <c r="C48" s="178"/>
+      <c r="D48" s="181"/>
       <c r="E48" s="13" t="s">
         <v>77</v>
       </c>
@@ -5985,8 +6652,8 @@
       <c r="B49" s="7">
         <v>5</v>
       </c>
-      <c r="C49" s="168"/>
-      <c r="D49" s="171"/>
+      <c r="C49" s="178"/>
+      <c r="D49" s="181"/>
       <c r="E49" s="13" t="s">
         <v>78</v>
       </c>
@@ -6011,8 +6678,8 @@
       <c r="B50" s="24">
         <v>6</v>
       </c>
-      <c r="C50" s="169"/>
-      <c r="D50" s="172"/>
+      <c r="C50" s="179"/>
+      <c r="D50" s="182"/>
       <c r="E50" s="25" t="s">
         <v>79</v>
       </c>
@@ -6037,10 +6704,10 @@
       <c r="B51" s="7">
         <v>1</v>
       </c>
-      <c r="C51" s="158" t="s">
+      <c r="C51" s="168" t="s">
         <v>80</v>
       </c>
-      <c r="D51" s="140" t="s">
+      <c r="D51" s="150" t="s">
         <v>81</v>
       </c>
       <c r="E51" s="13" t="s">
@@ -6069,8 +6736,8 @@
       <c r="B52" s="7">
         <v>2</v>
       </c>
-      <c r="C52" s="159"/>
-      <c r="D52" s="141"/>
+      <c r="C52" s="169"/>
+      <c r="D52" s="151"/>
       <c r="E52" s="8" t="s">
         <v>83</v>
       </c>
@@ -6097,8 +6764,8 @@
       <c r="B53" s="7">
         <v>3</v>
       </c>
-      <c r="C53" s="159"/>
-      <c r="D53" s="141"/>
+      <c r="C53" s="169"/>
+      <c r="D53" s="151"/>
       <c r="E53" s="27" t="s">
         <v>84</v>
       </c>
@@ -6123,8 +6790,8 @@
       <c r="B54" s="7">
         <v>4</v>
       </c>
-      <c r="C54" s="159"/>
-      <c r="D54" s="141"/>
+      <c r="C54" s="169"/>
+      <c r="D54" s="151"/>
       <c r="E54" s="13" t="s">
         <v>85</v>
       </c>
@@ -6149,8 +6816,8 @@
       <c r="B55" s="7">
         <v>5</v>
       </c>
-      <c r="C55" s="159"/>
-      <c r="D55" s="141"/>
+      <c r="C55" s="169"/>
+      <c r="D55" s="151"/>
       <c r="E55" s="13" t="s">
         <v>86</v>
       </c>
@@ -6177,8 +6844,8 @@
       <c r="B56" s="7">
         <v>6</v>
       </c>
-      <c r="C56" s="159"/>
-      <c r="D56" s="141"/>
+      <c r="C56" s="169"/>
+      <c r="D56" s="151"/>
       <c r="E56" s="13" t="s">
         <v>87</v>
       </c>
@@ -6205,8 +6872,8 @@
       <c r="B57" s="7">
         <v>7</v>
       </c>
-      <c r="C57" s="159"/>
-      <c r="D57" s="142"/>
+      <c r="C57" s="169"/>
+      <c r="D57" s="152"/>
       <c r="E57" s="13" t="s">
         <v>88</v>
       </c>
@@ -6233,8 +6900,8 @@
       <c r="B58" s="7">
         <v>8</v>
       </c>
-      <c r="C58" s="159"/>
-      <c r="D58" s="140" t="s">
+      <c r="C58" s="169"/>
+      <c r="D58" s="150" t="s">
         <v>89</v>
       </c>
       <c r="E58" s="13" t="s">
@@ -6261,8 +6928,8 @@
       <c r="B59" s="7">
         <v>9</v>
       </c>
-      <c r="C59" s="159"/>
-      <c r="D59" s="141"/>
+      <c r="C59" s="169"/>
+      <c r="D59" s="151"/>
       <c r="E59" s="8" t="s">
         <v>91</v>
       </c>
@@ -6287,8 +6954,8 @@
       <c r="B60" s="7">
         <v>10</v>
       </c>
-      <c r="C60" s="159"/>
-      <c r="D60" s="141"/>
+      <c r="C60" s="169"/>
+      <c r="D60" s="151"/>
       <c r="E60" s="8" t="s">
         <v>92</v>
       </c>
@@ -6309,8 +6976,8 @@
       <c r="B61" s="7">
         <v>11</v>
       </c>
-      <c r="C61" s="159"/>
-      <c r="D61" s="141"/>
+      <c r="C61" s="169"/>
+      <c r="D61" s="151"/>
       <c r="E61" s="8" t="s">
         <v>93</v>
       </c>
@@ -6331,8 +6998,8 @@
       <c r="B62" s="7">
         <v>12</v>
       </c>
-      <c r="C62" s="159"/>
-      <c r="D62" s="141"/>
+      <c r="C62" s="169"/>
+      <c r="D62" s="151"/>
       <c r="E62" s="8" t="s">
         <v>94</v>
       </c>
@@ -6357,8 +7024,8 @@
       <c r="B63" s="7">
         <v>13</v>
       </c>
-      <c r="C63" s="159"/>
-      <c r="D63" s="142"/>
+      <c r="C63" s="169"/>
+      <c r="D63" s="152"/>
       <c r="E63" s="8" t="s">
         <v>95</v>
       </c>
@@ -6376,15 +7043,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="193.2">
+    <row r="64" spans="1:10" ht="207">
       <c r="A64" s="6">
         <v>61</v>
       </c>
       <c r="B64" s="7">
         <v>14</v>
       </c>
-      <c r="C64" s="159"/>
-      <c r="D64" s="140" t="s">
+      <c r="C64" s="169"/>
+      <c r="D64" s="150" t="s">
         <v>48</v>
       </c>
       <c r="E64" s="8" t="s">
@@ -6406,37 +7073,37 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="13.8">
-      <c r="A65" s="6">
+    <row r="65" spans="1:10" s="145" customFormat="1" ht="13.8">
+      <c r="A65" s="142">
         <v>62</v>
       </c>
-      <c r="B65" s="7">
+      <c r="B65" s="143">
         <v>15</v>
       </c>
-      <c r="C65" s="159"/>
-      <c r="D65" s="141"/>
-      <c r="E65" s="8" t="s">
+      <c r="C65" s="169"/>
+      <c r="D65" s="151"/>
+      <c r="E65" s="144" t="s">
         <v>97</v>
       </c>
-      <c r="F65" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G65" s="10">
+      <c r="F65" s="142" t="s">
+        <v>6</v>
+      </c>
+      <c r="G65" s="141">
         <v>4</v>
       </c>
-      <c r="H65" s="11"/>
-      <c r="I65" s="11"/>
-      <c r="J65" s="11"/>
-    </row>
-    <row r="66" spans="1:10" ht="13.8">
+      <c r="H65" s="127"/>
+      <c r="I65" s="127"/>
+      <c r="J65" s="127"/>
+    </row>
+    <row r="66" spans="1:10" ht="124.2">
       <c r="A66" s="6">
         <v>63</v>
       </c>
       <c r="B66" s="7">
         <v>16</v>
       </c>
-      <c r="C66" s="159"/>
-      <c r="D66" s="141"/>
+      <c r="C66" s="169"/>
+      <c r="D66" s="151"/>
       <c r="E66" s="8" t="s">
         <v>98</v>
       </c>
@@ -6446,18 +7113,25 @@
       <c r="G66" s="10">
         <v>4</v>
       </c>
-      <c r="I66" s="11"/>
-      <c r="J66" s="11"/>
-    </row>
-    <row r="67" spans="1:10" ht="13.8">
+      <c r="H66" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I66" s="125" t="s">
+        <v>724</v>
+      </c>
+      <c r="J66" s="11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="289.8">
       <c r="A67" s="6">
         <v>64</v>
       </c>
       <c r="B67" s="7">
         <v>17</v>
       </c>
-      <c r="C67" s="160"/>
-      <c r="D67" s="142"/>
+      <c r="C67" s="170"/>
+      <c r="D67" s="152"/>
       <c r="E67" s="8" t="s">
         <v>99</v>
       </c>
@@ -6467,23 +7141,29 @@
       <c r="G67" s="10">
         <v>4</v>
       </c>
-      <c r="H67" s="11"/>
-      <c r="I67" s="11"/>
-      <c r="J67" s="11"/>
+      <c r="H67" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I67" s="125" t="s">
+        <v>725</v>
+      </c>
+      <c r="J67" s="128" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="68" spans="1:10" ht="13.8">
-      <c r="A68" s="173" t="s">
+      <c r="A68" s="183" t="s">
         <v>100</v>
       </c>
-      <c r="B68" s="174"/>
-      <c r="C68" s="174"/>
-      <c r="D68" s="174"/>
-      <c r="E68" s="174"/>
-      <c r="F68" s="174"/>
-      <c r="G68" s="174"/>
-      <c r="H68" s="174"/>
-      <c r="I68" s="174"/>
-      <c r="J68" s="175"/>
+      <c r="B68" s="184"/>
+      <c r="C68" s="184"/>
+      <c r="D68" s="184"/>
+      <c r="E68" s="184"/>
+      <c r="F68" s="184"/>
+      <c r="G68" s="184"/>
+      <c r="H68" s="184"/>
+      <c r="I68" s="184"/>
+      <c r="J68" s="185"/>
     </row>
     <row r="69" spans="1:10" ht="13.8">
       <c r="A69" s="6">
@@ -6492,10 +7172,10 @@
       <c r="B69" s="7">
         <v>1</v>
       </c>
-      <c r="C69" s="149" t="s">
+      <c r="C69" s="159" t="s">
         <v>101</v>
       </c>
-      <c r="D69" s="140" t="s">
+      <c r="D69" s="150" t="s">
         <v>102</v>
       </c>
       <c r="E69" s="8" t="s">
@@ -6507,19 +7187,23 @@
       <c r="G69" s="10">
         <v>2</v>
       </c>
-      <c r="H69" s="11"/>
+      <c r="H69" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="I69" s="11"/>
-      <c r="J69" s="11"/>
-    </row>
-    <row r="70" spans="1:10" ht="13.8">
+      <c r="J69" s="11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="179.4">
       <c r="A70" s="6">
         <v>66</v>
       </c>
       <c r="B70" s="7">
         <v>2</v>
       </c>
-      <c r="C70" s="150"/>
-      <c r="D70" s="141"/>
+      <c r="C70" s="160"/>
+      <c r="D70" s="151"/>
       <c r="E70" s="28" t="s">
         <v>104</v>
       </c>
@@ -6529,19 +7213,25 @@
       <c r="G70" s="10">
         <v>2</v>
       </c>
-      <c r="H70" s="11"/>
-      <c r="I70" s="11"/>
-      <c r="J70" s="11"/>
-    </row>
-    <row r="71" spans="1:10" ht="13.8">
+      <c r="H70" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I70" s="125" t="s">
+        <v>726</v>
+      </c>
+      <c r="J70" s="126" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="207">
       <c r="A71" s="6">
         <v>67</v>
       </c>
       <c r="B71" s="7">
         <v>3</v>
       </c>
-      <c r="C71" s="150"/>
-      <c r="D71" s="141"/>
+      <c r="C71" s="160"/>
+      <c r="D71" s="151"/>
       <c r="E71" s="8" t="s">
         <v>105</v>
       </c>
@@ -6551,19 +7241,25 @@
       <c r="G71" s="10">
         <v>2</v>
       </c>
-      <c r="H71" s="11"/>
-      <c r="I71" s="11"/>
-      <c r="J71" s="11"/>
-    </row>
-    <row r="72" spans="1:10" ht="13.8">
+      <c r="H71" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I71" s="125" t="s">
+        <v>727</v>
+      </c>
+      <c r="J71" s="126" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="220.8">
       <c r="A72" s="6">
         <v>68</v>
       </c>
       <c r="B72" s="7">
         <v>4</v>
       </c>
-      <c r="C72" s="150"/>
-      <c r="D72" s="141"/>
+      <c r="C72" s="160"/>
+      <c r="D72" s="151"/>
       <c r="E72" s="8" t="s">
         <v>106</v>
       </c>
@@ -6573,19 +7269,25 @@
       <c r="G72" s="10">
         <v>2</v>
       </c>
-      <c r="H72" s="11"/>
-      <c r="I72" s="11"/>
-      <c r="J72" s="11"/>
-    </row>
-    <row r="73" spans="1:10" ht="13.8">
+      <c r="H72" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I72" s="125" t="s">
+        <v>728</v>
+      </c>
+      <c r="J72" s="126" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="409.6">
       <c r="A73" s="6">
         <v>69</v>
       </c>
       <c r="B73" s="7">
         <v>5</v>
       </c>
-      <c r="C73" s="150"/>
-      <c r="D73" s="141"/>
+      <c r="C73" s="160"/>
+      <c r="D73" s="151"/>
       <c r="E73" s="28" t="s">
         <v>107</v>
       </c>
@@ -6595,9 +7297,15 @@
       <c r="G73" s="10">
         <v>2</v>
       </c>
-      <c r="H73" s="11"/>
-      <c r="I73" s="11"/>
-      <c r="J73" s="11"/>
+      <c r="H73" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I73" s="125" t="s">
+        <v>729</v>
+      </c>
+      <c r="J73" s="126" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="74" spans="1:10" ht="13.8">
       <c r="A74" s="6">
@@ -6606,8 +7314,8 @@
       <c r="B74" s="7">
         <v>6</v>
       </c>
-      <c r="C74" s="150"/>
-      <c r="D74" s="141"/>
+      <c r="C74" s="160"/>
+      <c r="D74" s="151"/>
       <c r="E74" s="28" t="s">
         <v>108</v>
       </c>
@@ -6617,9 +7325,13 @@
       <c r="G74" s="10">
         <v>2</v>
       </c>
-      <c r="H74" s="11"/>
+      <c r="H74" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="I74" s="11"/>
-      <c r="J74" s="11"/>
+      <c r="J74" s="11" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="75" spans="1:10" ht="13.8">
       <c r="A75" s="6">
@@ -6628,8 +7340,8 @@
       <c r="B75" s="7">
         <v>7</v>
       </c>
-      <c r="C75" s="150"/>
-      <c r="D75" s="141"/>
+      <c r="C75" s="160"/>
+      <c r="D75" s="151"/>
       <c r="E75" s="28" t="s">
         <v>109</v>
       </c>
@@ -6650,8 +7362,8 @@
       <c r="B76" s="7">
         <v>8</v>
       </c>
-      <c r="C76" s="150"/>
-      <c r="D76" s="141"/>
+      <c r="C76" s="160"/>
+      <c r="D76" s="151"/>
       <c r="E76" s="8" t="s">
         <v>110</v>
       </c>
@@ -6672,8 +7384,8 @@
       <c r="B77" s="7">
         <v>9</v>
       </c>
-      <c r="C77" s="150"/>
-      <c r="D77" s="141"/>
+      <c r="C77" s="160"/>
+      <c r="D77" s="151"/>
       <c r="E77" s="8" t="s">
         <v>111</v>
       </c>
@@ -6694,8 +7406,8 @@
       <c r="B78" s="7">
         <v>10</v>
       </c>
-      <c r="C78" s="150"/>
-      <c r="D78" s="142"/>
+      <c r="C78" s="160"/>
+      <c r="D78" s="152"/>
       <c r="E78" s="8" t="s">
         <v>112</v>
       </c>
@@ -6716,8 +7428,8 @@
       <c r="B79" s="7">
         <v>11</v>
       </c>
-      <c r="C79" s="150"/>
-      <c r="D79" s="140" t="s">
+      <c r="C79" s="160"/>
+      <c r="D79" s="150" t="s">
         <v>113</v>
       </c>
       <c r="E79" s="8" t="s">
@@ -6740,8 +7452,8 @@
       <c r="B80" s="7">
         <v>12</v>
       </c>
-      <c r="C80" s="150"/>
-      <c r="D80" s="141"/>
+      <c r="C80" s="160"/>
+      <c r="D80" s="151"/>
       <c r="E80" s="8" t="s">
         <v>115</v>
       </c>
@@ -6762,8 +7474,8 @@
       <c r="B81" s="7">
         <v>13</v>
       </c>
-      <c r="C81" s="150"/>
-      <c r="D81" s="141"/>
+      <c r="C81" s="160"/>
+      <c r="D81" s="151"/>
       <c r="E81" s="8" t="s">
         <v>116</v>
       </c>
@@ -6784,8 +7496,8 @@
       <c r="B82" s="7">
         <v>14</v>
       </c>
-      <c r="C82" s="150"/>
-      <c r="D82" s="141"/>
+      <c r="C82" s="160"/>
+      <c r="D82" s="151"/>
       <c r="E82" s="8" t="s">
         <v>117</v>
       </c>
@@ -6806,8 +7518,8 @@
       <c r="B83" s="7">
         <v>15</v>
       </c>
-      <c r="C83" s="150"/>
-      <c r="D83" s="141"/>
+      <c r="C83" s="160"/>
+      <c r="D83" s="151"/>
       <c r="E83" s="8" t="s">
         <v>118</v>
       </c>
@@ -6828,8 +7540,8 @@
       <c r="B84" s="7">
         <v>16</v>
       </c>
-      <c r="C84" s="150"/>
-      <c r="D84" s="142"/>
+      <c r="C84" s="160"/>
+      <c r="D84" s="152"/>
       <c r="E84" s="8" t="s">
         <v>119</v>
       </c>
@@ -6850,8 +7562,8 @@
       <c r="B85" s="7">
         <v>17</v>
       </c>
-      <c r="C85" s="150"/>
-      <c r="D85" s="140" t="s">
+      <c r="C85" s="160"/>
+      <c r="D85" s="150" t="s">
         <v>120</v>
       </c>
       <c r="E85" s="8" t="s">
@@ -6874,8 +7586,8 @@
       <c r="B86" s="7">
         <v>18</v>
       </c>
-      <c r="C86" s="150"/>
-      <c r="D86" s="141"/>
+      <c r="C86" s="160"/>
+      <c r="D86" s="151"/>
       <c r="E86" s="8" t="s">
         <v>122</v>
       </c>
@@ -6896,8 +7608,8 @@
       <c r="B87" s="7">
         <v>19</v>
       </c>
-      <c r="C87" s="150"/>
-      <c r="D87" s="141"/>
+      <c r="C87" s="160"/>
+      <c r="D87" s="151"/>
       <c r="E87" s="29" t="s">
         <v>123</v>
       </c>
@@ -6918,8 +7630,8 @@
       <c r="B88" s="7">
         <v>20</v>
       </c>
-      <c r="C88" s="150"/>
-      <c r="D88" s="141"/>
+      <c r="C88" s="160"/>
+      <c r="D88" s="151"/>
       <c r="E88" s="8" t="s">
         <v>124</v>
       </c>
@@ -6940,8 +7652,8 @@
       <c r="B89" s="7">
         <v>21</v>
       </c>
-      <c r="C89" s="150"/>
-      <c r="D89" s="141"/>
+      <c r="C89" s="160"/>
+      <c r="D89" s="151"/>
       <c r="E89" s="8" t="s">
         <v>125</v>
       </c>
@@ -6962,8 +7674,8 @@
       <c r="B90" s="7">
         <v>22</v>
       </c>
-      <c r="C90" s="150"/>
-      <c r="D90" s="142"/>
+      <c r="C90" s="160"/>
+      <c r="D90" s="152"/>
       <c r="E90" s="8" t="s">
         <v>126</v>
       </c>
@@ -6984,8 +7696,8 @@
       <c r="B91" s="7">
         <v>23</v>
       </c>
-      <c r="C91" s="150"/>
-      <c r="D91" s="140" t="s">
+      <c r="C91" s="160"/>
+      <c r="D91" s="150" t="s">
         <v>127</v>
       </c>
       <c r="E91" s="8" t="s">
@@ -7008,8 +7720,8 @@
       <c r="B92" s="7">
         <v>24</v>
       </c>
-      <c r="C92" s="150"/>
-      <c r="D92" s="141"/>
+      <c r="C92" s="160"/>
+      <c r="D92" s="151"/>
       <c r="E92" s="8" t="s">
         <v>129</v>
       </c>
@@ -7030,8 +7742,8 @@
       <c r="B93" s="7">
         <v>25</v>
       </c>
-      <c r="C93" s="150"/>
-      <c r="D93" s="141"/>
+      <c r="C93" s="160"/>
+      <c r="D93" s="151"/>
       <c r="E93" s="8" t="s">
         <v>130</v>
       </c>
@@ -7052,8 +7764,8 @@
       <c r="B94" s="7">
         <v>26</v>
       </c>
-      <c r="C94" s="150"/>
-      <c r="D94" s="141"/>
+      <c r="C94" s="160"/>
+      <c r="D94" s="151"/>
       <c r="E94" s="8" t="s">
         <v>131</v>
       </c>
@@ -7074,8 +7786,8 @@
       <c r="B95" s="7">
         <v>27</v>
       </c>
-      <c r="C95" s="150"/>
-      <c r="D95" s="141"/>
+      <c r="C95" s="160"/>
+      <c r="D95" s="151"/>
       <c r="E95" s="8" t="s">
         <v>132</v>
       </c>
@@ -7096,8 +7808,8 @@
       <c r="B96" s="7">
         <v>28</v>
       </c>
-      <c r="C96" s="150"/>
-      <c r="D96" s="141"/>
+      <c r="C96" s="160"/>
+      <c r="D96" s="151"/>
       <c r="E96" s="8" t="s">
         <v>133</v>
       </c>
@@ -7118,8 +7830,8 @@
       <c r="B97" s="7">
         <v>29</v>
       </c>
-      <c r="C97" s="150"/>
-      <c r="D97" s="141"/>
+      <c r="C97" s="160"/>
+      <c r="D97" s="151"/>
       <c r="E97" s="8" t="s">
         <v>134</v>
       </c>
@@ -7140,8 +7852,8 @@
       <c r="B98" s="7">
         <v>30</v>
       </c>
-      <c r="C98" s="150"/>
-      <c r="D98" s="141"/>
+      <c r="C98" s="160"/>
+      <c r="D98" s="151"/>
       <c r="E98" s="8" t="s">
         <v>135</v>
       </c>
@@ -7162,8 +7874,8 @@
       <c r="B99" s="7">
         <v>31</v>
       </c>
-      <c r="C99" s="150"/>
-      <c r="D99" s="141"/>
+      <c r="C99" s="160"/>
+      <c r="D99" s="151"/>
       <c r="E99" s="30" t="s">
         <v>136</v>
       </c>
@@ -7184,8 +7896,8 @@
       <c r="B100" s="7">
         <v>32</v>
       </c>
-      <c r="C100" s="150"/>
-      <c r="D100" s="141"/>
+      <c r="C100" s="160"/>
+      <c r="D100" s="151"/>
       <c r="E100" s="8" t="s">
         <v>137</v>
       </c>
@@ -7206,8 +7918,8 @@
       <c r="B101" s="7">
         <v>33</v>
       </c>
-      <c r="C101" s="150"/>
-      <c r="D101" s="141"/>
+      <c r="C101" s="160"/>
+      <c r="D101" s="151"/>
       <c r="E101" s="8" t="s">
         <v>138</v>
       </c>
@@ -7228,8 +7940,8 @@
       <c r="B102" s="7">
         <v>34</v>
       </c>
-      <c r="C102" s="150"/>
-      <c r="D102" s="141"/>
+      <c r="C102" s="160"/>
+      <c r="D102" s="151"/>
       <c r="E102" s="8" t="s">
         <v>139</v>
       </c>
@@ -7250,8 +7962,8 @@
       <c r="B103" s="7">
         <v>35</v>
       </c>
-      <c r="C103" s="150"/>
-      <c r="D103" s="141"/>
+      <c r="C103" s="160"/>
+      <c r="D103" s="151"/>
       <c r="E103" s="8" t="s">
         <v>140</v>
       </c>
@@ -7272,8 +7984,8 @@
       <c r="B104" s="7">
         <v>36</v>
       </c>
-      <c r="C104" s="150"/>
-      <c r="D104" s="141"/>
+      <c r="C104" s="160"/>
+      <c r="D104" s="151"/>
       <c r="E104" s="8" t="s">
         <v>141</v>
       </c>
@@ -7294,8 +8006,8 @@
       <c r="B105" s="7">
         <v>37</v>
       </c>
-      <c r="C105" s="151"/>
-      <c r="D105" s="142"/>
+      <c r="C105" s="161"/>
+      <c r="D105" s="152"/>
       <c r="E105" s="8" t="s">
         <v>142</v>
       </c>
@@ -7310,18 +8022,18 @@
       <c r="J105" s="11"/>
     </row>
     <row r="106" spans="1:10" ht="13.8">
-      <c r="A106" s="161" t="s">
+      <c r="A106" s="171" t="s">
         <v>143</v>
       </c>
-      <c r="B106" s="162"/>
-      <c r="C106" s="162"/>
-      <c r="D106" s="162"/>
-      <c r="E106" s="162"/>
-      <c r="F106" s="162"/>
-      <c r="G106" s="162"/>
-      <c r="H106" s="162"/>
-      <c r="I106" s="162"/>
-      <c r="J106" s="163"/>
+      <c r="B106" s="172"/>
+      <c r="C106" s="172"/>
+      <c r="D106" s="172"/>
+      <c r="E106" s="172"/>
+      <c r="F106" s="172"/>
+      <c r="G106" s="172"/>
+      <c r="H106" s="172"/>
+      <c r="I106" s="172"/>
+      <c r="J106" s="173"/>
     </row>
     <row r="107" spans="1:10" ht="13.8">
       <c r="A107" s="6">
@@ -7330,10 +8042,10 @@
       <c r="B107" s="7">
         <v>1</v>
       </c>
-      <c r="C107" s="152" t="s">
+      <c r="C107" s="162" t="s">
         <v>144</v>
       </c>
-      <c r="D107" s="140" t="s">
+      <c r="D107" s="150" t="s">
         <v>145</v>
       </c>
       <c r="E107" s="8" t="s">
@@ -7356,8 +8068,8 @@
       <c r="B108" s="7">
         <v>2</v>
       </c>
-      <c r="C108" s="153"/>
-      <c r="D108" s="141"/>
+      <c r="C108" s="163"/>
+      <c r="D108" s="151"/>
       <c r="E108" s="8" t="s">
         <v>147</v>
       </c>
@@ -7378,8 +8090,8 @@
       <c r="B109" s="7">
         <v>3</v>
       </c>
-      <c r="C109" s="153"/>
-      <c r="D109" s="141"/>
+      <c r="C109" s="163"/>
+      <c r="D109" s="151"/>
       <c r="E109" s="8" t="s">
         <v>148</v>
       </c>
@@ -7400,8 +8112,8 @@
       <c r="B110" s="7">
         <v>4</v>
       </c>
-      <c r="C110" s="153"/>
-      <c r="D110" s="141"/>
+      <c r="C110" s="163"/>
+      <c r="D110" s="151"/>
       <c r="E110" s="8" t="s">
         <v>149</v>
       </c>
@@ -7422,8 +8134,8 @@
       <c r="B111" s="7">
         <v>5</v>
       </c>
-      <c r="C111" s="153"/>
-      <c r="D111" s="142"/>
+      <c r="C111" s="163"/>
+      <c r="D111" s="152"/>
       <c r="E111" s="8" t="s">
         <v>150</v>
       </c>
@@ -7444,8 +8156,8 @@
       <c r="B112" s="7">
         <v>6</v>
       </c>
-      <c r="C112" s="153"/>
-      <c r="D112" s="140" t="s">
+      <c r="C112" s="163"/>
+      <c r="D112" s="150" t="s">
         <v>151</v>
       </c>
       <c r="E112" s="8" t="s">
@@ -7468,8 +8180,8 @@
       <c r="B113" s="7">
         <v>7</v>
       </c>
-      <c r="C113" s="153"/>
-      <c r="D113" s="141"/>
+      <c r="C113" s="163"/>
+      <c r="D113" s="151"/>
       <c r="E113" s="8" t="s">
         <v>153</v>
       </c>
@@ -7490,8 +8202,8 @@
       <c r="B114" s="7">
         <v>8</v>
       </c>
-      <c r="C114" s="153"/>
-      <c r="D114" s="141"/>
+      <c r="C114" s="163"/>
+      <c r="D114" s="151"/>
       <c r="E114" s="8" t="s">
         <v>154</v>
       </c>
@@ -7512,8 +8224,8 @@
       <c r="B115" s="7">
         <v>9</v>
       </c>
-      <c r="C115" s="153"/>
-      <c r="D115" s="142"/>
+      <c r="C115" s="163"/>
+      <c r="D115" s="152"/>
       <c r="E115" s="8" t="s">
         <v>155</v>
       </c>
@@ -7534,7 +8246,7 @@
       <c r="B116" s="24">
         <v>10</v>
       </c>
-      <c r="C116" s="154"/>
+      <c r="C116" s="164"/>
       <c r="D116" s="31" t="s">
         <v>156</v>
       </c>
@@ -7558,10 +8270,10 @@
       <c r="B117" s="7">
         <v>1</v>
       </c>
-      <c r="C117" s="155" t="s">
+      <c r="C117" s="165" t="s">
         <v>158</v>
       </c>
-      <c r="D117" s="140" t="s">
+      <c r="D117" s="150" t="s">
         <v>159</v>
       </c>
       <c r="E117" s="8" t="s">
@@ -7584,8 +8296,8 @@
       <c r="B118" s="7">
         <v>2</v>
       </c>
-      <c r="C118" s="156"/>
-      <c r="D118" s="141"/>
+      <c r="C118" s="166"/>
+      <c r="D118" s="151"/>
       <c r="E118" s="8" t="s">
         <v>161</v>
       </c>
@@ -7606,8 +8318,8 @@
       <c r="B119" s="7">
         <v>3</v>
       </c>
-      <c r="C119" s="156"/>
-      <c r="D119" s="141"/>
+      <c r="C119" s="166"/>
+      <c r="D119" s="151"/>
       <c r="E119" s="8" t="s">
         <v>162</v>
       </c>
@@ -7628,8 +8340,8 @@
       <c r="B120" s="7">
         <v>4</v>
       </c>
-      <c r="C120" s="156"/>
-      <c r="D120" s="142"/>
+      <c r="C120" s="166"/>
+      <c r="D120" s="152"/>
       <c r="E120" s="8" t="s">
         <v>163</v>
       </c>
@@ -7650,8 +8362,8 @@
       <c r="B121" s="7">
         <v>5</v>
       </c>
-      <c r="C121" s="156"/>
-      <c r="D121" s="140" t="s">
+      <c r="C121" s="166"/>
+      <c r="D121" s="150" t="s">
         <v>164</v>
       </c>
       <c r="E121" s="8" t="s">
@@ -7674,8 +8386,8 @@
       <c r="B122" s="7">
         <v>6</v>
       </c>
-      <c r="C122" s="156"/>
-      <c r="D122" s="142"/>
+      <c r="C122" s="166"/>
+      <c r="D122" s="152"/>
       <c r="E122" s="8" t="s">
         <v>166</v>
       </c>
@@ -7696,8 +8408,8 @@
       <c r="B123" s="7">
         <v>7</v>
       </c>
-      <c r="C123" s="156"/>
-      <c r="D123" s="140" t="s">
+      <c r="C123" s="166"/>
+      <c r="D123" s="150" t="s">
         <v>167</v>
       </c>
       <c r="E123" s="8" t="s">
@@ -7720,8 +8432,8 @@
       <c r="B124" s="7">
         <v>8</v>
       </c>
-      <c r="C124" s="156"/>
-      <c r="D124" s="141"/>
+      <c r="C124" s="166"/>
+      <c r="D124" s="151"/>
       <c r="E124" s="28" t="s">
         <v>169</v>
       </c>
@@ -7742,8 +8454,8 @@
       <c r="B125" s="7">
         <v>9</v>
       </c>
-      <c r="C125" s="157"/>
-      <c r="D125" s="142"/>
+      <c r="C125" s="167"/>
+      <c r="D125" s="152"/>
       <c r="E125" s="8" t="s">
         <v>170</v>
       </c>
@@ -7758,18 +8470,18 @@
       <c r="J125" s="11"/>
     </row>
     <row r="126" spans="1:10" ht="13.8">
-      <c r="A126" s="164" t="s">
+      <c r="A126" s="174" t="s">
         <v>171</v>
       </c>
-      <c r="B126" s="165"/>
-      <c r="C126" s="165"/>
-      <c r="D126" s="165"/>
-      <c r="E126" s="165"/>
-      <c r="F126" s="165"/>
-      <c r="G126" s="165"/>
-      <c r="H126" s="165"/>
-      <c r="I126" s="165"/>
-      <c r="J126" s="166"/>
+      <c r="B126" s="175"/>
+      <c r="C126" s="175"/>
+      <c r="D126" s="175"/>
+      <c r="E126" s="175"/>
+      <c r="F126" s="175"/>
+      <c r="G126" s="175"/>
+      <c r="H126" s="175"/>
+      <c r="I126" s="175"/>
+      <c r="J126" s="176"/>
     </row>
     <row r="127" spans="1:10" ht="13.8">
       <c r="A127" s="6">
@@ -7778,10 +8490,10 @@
       <c r="B127" s="7">
         <v>1</v>
       </c>
-      <c r="C127" s="158" t="s">
+      <c r="C127" s="168" t="s">
         <v>172</v>
       </c>
-      <c r="D127" s="140" t="s">
+      <c r="D127" s="150" t="s">
         <v>173</v>
       </c>
       <c r="E127" s="32" t="s">
@@ -7802,8 +8514,8 @@
       <c r="B128" s="7">
         <v>2</v>
       </c>
-      <c r="C128" s="159"/>
-      <c r="D128" s="141"/>
+      <c r="C128" s="169"/>
+      <c r="D128" s="151"/>
       <c r="E128" s="32" t="s">
         <v>175</v>
       </c>
@@ -7822,8 +8534,8 @@
       <c r="B129" s="7">
         <v>3</v>
       </c>
-      <c r="C129" s="159"/>
-      <c r="D129" s="141"/>
+      <c r="C129" s="169"/>
+      <c r="D129" s="151"/>
       <c r="E129" s="32" t="s">
         <v>176</v>
       </c>
@@ -7842,8 +8554,8 @@
       <c r="B130" s="7">
         <v>4</v>
       </c>
-      <c r="C130" s="159"/>
-      <c r="D130" s="142"/>
+      <c r="C130" s="169"/>
+      <c r="D130" s="152"/>
       <c r="E130" s="32" t="s">
         <v>177</v>
       </c>
@@ -7862,8 +8574,8 @@
       <c r="B131" s="7">
         <v>5</v>
       </c>
-      <c r="C131" s="159"/>
-      <c r="D131" s="140" t="s">
+      <c r="C131" s="169"/>
+      <c r="D131" s="150" t="s">
         <v>178</v>
       </c>
       <c r="E131" s="32" t="s">
@@ -7884,8 +8596,8 @@
       <c r="B132" s="7">
         <v>6</v>
       </c>
-      <c r="C132" s="160"/>
-      <c r="D132" s="142"/>
+      <c r="C132" s="170"/>
+      <c r="D132" s="152"/>
       <c r="E132" s="32" t="s">
         <v>180</v>
       </c>
@@ -7898,18 +8610,18 @@
       <c r="J132" s="11"/>
     </row>
     <row r="133" spans="1:10" ht="13.8">
-      <c r="A133" s="146" t="s">
+      <c r="A133" s="156" t="s">
         <v>181</v>
       </c>
-      <c r="B133" s="147"/>
-      <c r="C133" s="147"/>
-      <c r="D133" s="147"/>
-      <c r="E133" s="147"/>
-      <c r="F133" s="147"/>
-      <c r="G133" s="147"/>
-      <c r="H133" s="147"/>
-      <c r="I133" s="147"/>
-      <c r="J133" s="148"/>
+      <c r="B133" s="157"/>
+      <c r="C133" s="157"/>
+      <c r="D133" s="157"/>
+      <c r="E133" s="157"/>
+      <c r="F133" s="157"/>
+      <c r="G133" s="157"/>
+      <c r="H133" s="157"/>
+      <c r="I133" s="157"/>
+      <c r="J133" s="158"/>
     </row>
     <row r="134" spans="1:10" ht="13.8">
       <c r="A134" s="6">
@@ -7918,10 +8630,10 @@
       <c r="B134" s="7">
         <v>1</v>
       </c>
-      <c r="C134" s="149" t="s">
+      <c r="C134" s="159" t="s">
         <v>182</v>
       </c>
-      <c r="D134" s="140" t="s">
+      <c r="D134" s="150" t="s">
         <v>183</v>
       </c>
       <c r="E134" s="8" t="s">
@@ -7944,8 +8656,8 @@
       <c r="B135" s="7">
         <v>2</v>
       </c>
-      <c r="C135" s="150"/>
-      <c r="D135" s="141"/>
+      <c r="C135" s="160"/>
+      <c r="D135" s="151"/>
       <c r="E135" s="8" t="s">
         <v>185</v>
       </c>
@@ -7966,8 +8678,8 @@
       <c r="B136" s="7">
         <v>3</v>
       </c>
-      <c r="C136" s="150"/>
-      <c r="D136" s="142"/>
+      <c r="C136" s="160"/>
+      <c r="D136" s="152"/>
       <c r="E136" s="8" t="s">
         <v>186</v>
       </c>
@@ -7988,8 +8700,8 @@
       <c r="B137" s="7">
         <v>4</v>
       </c>
-      <c r="C137" s="150"/>
-      <c r="D137" s="140" t="s">
+      <c r="C137" s="160"/>
+      <c r="D137" s="150" t="s">
         <v>187</v>
       </c>
       <c r="E137" s="8" t="s">
@@ -8012,8 +8724,8 @@
       <c r="B138" s="7">
         <v>5</v>
       </c>
-      <c r="C138" s="150"/>
-      <c r="D138" s="141"/>
+      <c r="C138" s="160"/>
+      <c r="D138" s="151"/>
       <c r="E138" s="8" t="s">
         <v>189</v>
       </c>
@@ -8034,8 +8746,8 @@
       <c r="B139" s="7">
         <v>6</v>
       </c>
-      <c r="C139" s="150"/>
-      <c r="D139" s="141"/>
+      <c r="C139" s="160"/>
+      <c r="D139" s="151"/>
       <c r="E139" s="8" t="s">
         <v>190</v>
       </c>
@@ -8056,8 +8768,8 @@
       <c r="B140" s="7">
         <v>7</v>
       </c>
-      <c r="C140" s="150"/>
-      <c r="D140" s="141"/>
+      <c r="C140" s="160"/>
+      <c r="D140" s="151"/>
       <c r="E140" s="8" t="s">
         <v>191</v>
       </c>
@@ -8078,8 +8790,8 @@
       <c r="B141" s="7">
         <v>8</v>
       </c>
-      <c r="C141" s="150"/>
-      <c r="D141" s="141"/>
+      <c r="C141" s="160"/>
+      <c r="D141" s="151"/>
       <c r="E141" s="8" t="s">
         <v>192</v>
       </c>
@@ -8100,8 +8812,8 @@
       <c r="B142" s="7">
         <v>9</v>
       </c>
-      <c r="C142" s="150"/>
-      <c r="D142" s="141"/>
+      <c r="C142" s="160"/>
+      <c r="D142" s="151"/>
       <c r="E142" s="8" t="s">
         <v>193</v>
       </c>
@@ -8122,8 +8834,8 @@
       <c r="B143" s="7">
         <v>10</v>
       </c>
-      <c r="C143" s="150"/>
-      <c r="D143" s="142"/>
+      <c r="C143" s="160"/>
+      <c r="D143" s="152"/>
       <c r="E143" s="8" t="s">
         <v>194</v>
       </c>
@@ -8144,8 +8856,8 @@
       <c r="B144" s="7">
         <v>11</v>
       </c>
-      <c r="C144" s="150"/>
-      <c r="D144" s="140" t="s">
+      <c r="C144" s="160"/>
+      <c r="D144" s="150" t="s">
         <v>195</v>
       </c>
       <c r="E144" s="8" t="s">
@@ -8168,8 +8880,8 @@
       <c r="B145" s="7">
         <v>12</v>
       </c>
-      <c r="C145" s="150"/>
-      <c r="D145" s="141"/>
+      <c r="C145" s="160"/>
+      <c r="D145" s="151"/>
       <c r="E145" s="8" t="s">
         <v>197</v>
       </c>
@@ -8190,8 +8902,8 @@
       <c r="B146" s="7">
         <v>13</v>
       </c>
-      <c r="C146" s="150"/>
-      <c r="D146" s="141"/>
+      <c r="C146" s="160"/>
+      <c r="D146" s="151"/>
       <c r="E146" s="8" t="s">
         <v>198</v>
       </c>
@@ -8212,8 +8924,8 @@
       <c r="B147" s="7">
         <v>14</v>
       </c>
-      <c r="C147" s="150"/>
-      <c r="D147" s="141"/>
+      <c r="C147" s="160"/>
+      <c r="D147" s="151"/>
       <c r="E147" s="8" t="s">
         <v>199</v>
       </c>
@@ -8234,8 +8946,8 @@
       <c r="B148" s="7">
         <v>15</v>
       </c>
-      <c r="C148" s="150"/>
-      <c r="D148" s="141"/>
+      <c r="C148" s="160"/>
+      <c r="D148" s="151"/>
       <c r="E148" s="8" t="s">
         <v>200</v>
       </c>
@@ -8256,8 +8968,8 @@
       <c r="B149" s="7">
         <v>16</v>
       </c>
-      <c r="C149" s="150"/>
-      <c r="D149" s="141"/>
+      <c r="C149" s="160"/>
+      <c r="D149" s="151"/>
       <c r="E149" s="8" t="s">
         <v>201</v>
       </c>
@@ -8278,8 +8990,8 @@
       <c r="B150" s="7">
         <v>17</v>
       </c>
-      <c r="C150" s="150"/>
-      <c r="D150" s="142"/>
+      <c r="C150" s="160"/>
+      <c r="D150" s="152"/>
       <c r="E150" s="8" t="s">
         <v>202</v>
       </c>
@@ -8300,8 +9012,8 @@
       <c r="B151" s="7">
         <v>18</v>
       </c>
-      <c r="C151" s="150"/>
-      <c r="D151" s="140" t="s">
+      <c r="C151" s="160"/>
+      <c r="D151" s="150" t="s">
         <v>203</v>
       </c>
       <c r="E151" s="8" t="s">
@@ -8324,8 +9036,8 @@
       <c r="B152" s="7">
         <v>19</v>
       </c>
-      <c r="C152" s="150"/>
-      <c r="D152" s="141"/>
+      <c r="C152" s="160"/>
+      <c r="D152" s="151"/>
       <c r="E152" s="8" t="s">
         <v>205</v>
       </c>
@@ -8346,8 +9058,8 @@
       <c r="B153" s="7">
         <v>20</v>
       </c>
-      <c r="C153" s="150"/>
-      <c r="D153" s="141"/>
+      <c r="C153" s="160"/>
+      <c r="D153" s="151"/>
       <c r="E153" s="8" t="s">
         <v>206</v>
       </c>
@@ -8368,8 +9080,8 @@
       <c r="B154" s="7">
         <v>21</v>
       </c>
-      <c r="C154" s="150"/>
-      <c r="D154" s="141"/>
+      <c r="C154" s="160"/>
+      <c r="D154" s="151"/>
       <c r="E154" s="8" t="s">
         <v>207</v>
       </c>
@@ -8390,8 +9102,8 @@
       <c r="B155" s="7">
         <v>22</v>
       </c>
-      <c r="C155" s="150"/>
-      <c r="D155" s="141"/>
+      <c r="C155" s="160"/>
+      <c r="D155" s="151"/>
       <c r="E155" s="8" t="s">
         <v>208</v>
       </c>
@@ -8412,8 +9124,8 @@
       <c r="B156" s="7">
         <v>23</v>
       </c>
-      <c r="C156" s="150"/>
-      <c r="D156" s="142"/>
+      <c r="C156" s="160"/>
+      <c r="D156" s="152"/>
       <c r="E156" s="8" t="s">
         <v>209</v>
       </c>
@@ -8434,8 +9146,8 @@
       <c r="B157" s="7">
         <v>24</v>
       </c>
-      <c r="C157" s="150"/>
-      <c r="D157" s="140" t="s">
+      <c r="C157" s="160"/>
+      <c r="D157" s="150" t="s">
         <v>210</v>
       </c>
       <c r="E157" s="8" t="s">
@@ -8458,8 +9170,8 @@
       <c r="B158" s="7">
         <v>25</v>
       </c>
-      <c r="C158" s="150"/>
-      <c r="D158" s="141"/>
+      <c r="C158" s="160"/>
+      <c r="D158" s="151"/>
       <c r="E158" s="8" t="s">
         <v>212</v>
       </c>
@@ -8480,8 +9192,8 @@
       <c r="B159" s="7">
         <v>26</v>
       </c>
-      <c r="C159" s="150"/>
-      <c r="D159" s="142"/>
+      <c r="C159" s="160"/>
+      <c r="D159" s="152"/>
       <c r="E159" s="8" t="s">
         <v>213</v>
       </c>
@@ -8502,8 +9214,8 @@
       <c r="B160" s="7">
         <v>27</v>
       </c>
-      <c r="C160" s="150"/>
-      <c r="D160" s="140" t="s">
+      <c r="C160" s="160"/>
+      <c r="D160" s="150" t="s">
         <v>214</v>
       </c>
       <c r="E160" s="8" t="s">
@@ -8526,8 +9238,8 @@
       <c r="B161" s="7">
         <v>28</v>
       </c>
-      <c r="C161" s="150"/>
-      <c r="D161" s="141"/>
+      <c r="C161" s="160"/>
+      <c r="D161" s="151"/>
       <c r="E161" s="8" t="s">
         <v>216</v>
       </c>
@@ -8548,8 +9260,8 @@
       <c r="B162" s="7">
         <v>29</v>
       </c>
-      <c r="C162" s="150"/>
-      <c r="D162" s="141"/>
+      <c r="C162" s="160"/>
+      <c r="D162" s="151"/>
       <c r="E162" s="8" t="s">
         <v>217</v>
       </c>
@@ -8570,8 +9282,8 @@
       <c r="B163" s="7">
         <v>30</v>
       </c>
-      <c r="C163" s="150"/>
-      <c r="D163" s="141"/>
+      <c r="C163" s="160"/>
+      <c r="D163" s="151"/>
       <c r="E163" s="8" t="s">
         <v>218</v>
       </c>
@@ -8592,8 +9304,8 @@
       <c r="B164" s="7">
         <v>31</v>
       </c>
-      <c r="C164" s="150"/>
-      <c r="D164" s="141"/>
+      <c r="C164" s="160"/>
+      <c r="D164" s="151"/>
       <c r="E164" s="8" t="s">
         <v>219</v>
       </c>
@@ -8614,8 +9326,8 @@
       <c r="B165" s="7">
         <v>32</v>
       </c>
-      <c r="C165" s="150"/>
-      <c r="D165" s="142"/>
+      <c r="C165" s="160"/>
+      <c r="D165" s="152"/>
       <c r="E165" s="8" t="s">
         <v>220</v>
       </c>
@@ -8636,8 +9348,8 @@
       <c r="B166" s="7">
         <v>33</v>
       </c>
-      <c r="C166" s="150"/>
-      <c r="D166" s="140" t="s">
+      <c r="C166" s="160"/>
+      <c r="D166" s="150" t="s">
         <v>221</v>
       </c>
       <c r="E166" s="8" t="s">
@@ -8660,8 +9372,8 @@
       <c r="B167" s="7">
         <v>34</v>
       </c>
-      <c r="C167" s="150"/>
-      <c r="D167" s="141"/>
+      <c r="C167" s="160"/>
+      <c r="D167" s="151"/>
       <c r="E167" s="8" t="s">
         <v>223</v>
       </c>
@@ -8680,8 +9392,8 @@
       <c r="B168" s="7">
         <v>35</v>
       </c>
-      <c r="C168" s="150"/>
-      <c r="D168" s="141"/>
+      <c r="C168" s="160"/>
+      <c r="D168" s="151"/>
       <c r="E168" s="8" t="s">
         <v>224</v>
       </c>
@@ -8702,8 +9414,8 @@
       <c r="B169" s="7">
         <v>36</v>
       </c>
-      <c r="C169" s="150"/>
-      <c r="D169" s="141"/>
+      <c r="C169" s="160"/>
+      <c r="D169" s="151"/>
       <c r="E169" s="8" t="s">
         <v>225</v>
       </c>
@@ -8724,8 +9436,8 @@
       <c r="B170" s="7">
         <v>37</v>
       </c>
-      <c r="C170" s="150"/>
-      <c r="D170" s="141"/>
+      <c r="C170" s="160"/>
+      <c r="D170" s="151"/>
       <c r="E170" s="8" t="s">
         <v>226</v>
       </c>
@@ -8746,8 +9458,8 @@
       <c r="B171" s="7">
         <v>38</v>
       </c>
-      <c r="C171" s="150"/>
-      <c r="D171" s="141"/>
+      <c r="C171" s="160"/>
+      <c r="D171" s="151"/>
       <c r="E171" s="8" t="s">
         <v>227</v>
       </c>
@@ -8768,8 +9480,8 @@
       <c r="B172" s="7">
         <v>39</v>
       </c>
-      <c r="C172" s="150"/>
-      <c r="D172" s="142"/>
+      <c r="C172" s="160"/>
+      <c r="D172" s="152"/>
       <c r="E172" s="8" t="s">
         <v>228</v>
       </c>
@@ -8790,8 +9502,8 @@
       <c r="B173" s="7">
         <v>40</v>
       </c>
-      <c r="C173" s="150"/>
-      <c r="D173" s="140" t="s">
+      <c r="C173" s="160"/>
+      <c r="D173" s="150" t="s">
         <v>48</v>
       </c>
       <c r="E173" s="11" t="s">
@@ -8814,8 +9526,8 @@
       <c r="B174" s="7">
         <v>41</v>
       </c>
-      <c r="C174" s="150"/>
-      <c r="D174" s="141"/>
+      <c r="C174" s="160"/>
+      <c r="D174" s="151"/>
       <c r="E174" s="8" t="s">
         <v>230</v>
       </c>
@@ -8836,8 +9548,8 @@
       <c r="B175" s="7">
         <v>42</v>
       </c>
-      <c r="C175" s="150"/>
-      <c r="D175" s="141"/>
+      <c r="C175" s="160"/>
+      <c r="D175" s="151"/>
       <c r="E175" s="8" t="s">
         <v>231</v>
       </c>
@@ -8858,8 +9570,8 @@
       <c r="B176" s="24">
         <v>43</v>
       </c>
-      <c r="C176" s="151"/>
-      <c r="D176" s="142"/>
+      <c r="C176" s="161"/>
+      <c r="D176" s="152"/>
       <c r="E176" s="17" t="s">
         <v>232</v>
       </c>
@@ -8880,10 +9592,10 @@
       <c r="B177" s="7">
         <v>1</v>
       </c>
-      <c r="C177" s="152" t="s">
+      <c r="C177" s="162" t="s">
         <v>233</v>
       </c>
-      <c r="D177" s="140" t="s">
+      <c r="D177" s="150" t="s">
         <v>234</v>
       </c>
       <c r="E177" s="8" t="s">
@@ -8906,8 +9618,8 @@
       <c r="B178" s="7">
         <v>2</v>
       </c>
-      <c r="C178" s="153"/>
-      <c r="D178" s="142"/>
+      <c r="C178" s="163"/>
+      <c r="D178" s="152"/>
       <c r="E178" s="8" t="s">
         <v>236</v>
       </c>
@@ -8928,8 +9640,8 @@
       <c r="B179" s="7">
         <v>3</v>
       </c>
-      <c r="C179" s="153"/>
-      <c r="D179" s="140" t="s">
+      <c r="C179" s="163"/>
+      <c r="D179" s="150" t="s">
         <v>237</v>
       </c>
       <c r="E179" s="8" t="s">
@@ -8952,8 +9664,8 @@
       <c r="B180" s="7">
         <v>4</v>
       </c>
-      <c r="C180" s="153"/>
-      <c r="D180" s="141"/>
+      <c r="C180" s="163"/>
+      <c r="D180" s="151"/>
       <c r="E180" s="8" t="s">
         <v>239</v>
       </c>
@@ -8974,8 +9686,8 @@
       <c r="B181" s="7">
         <v>5</v>
       </c>
-      <c r="C181" s="153"/>
-      <c r="D181" s="141"/>
+      <c r="C181" s="163"/>
+      <c r="D181" s="151"/>
       <c r="E181" s="8" t="s">
         <v>240</v>
       </c>
@@ -8996,8 +9708,8 @@
       <c r="B182" s="7">
         <v>6</v>
       </c>
-      <c r="C182" s="153"/>
-      <c r="D182" s="141"/>
+      <c r="C182" s="163"/>
+      <c r="D182" s="151"/>
       <c r="E182" s="8" t="s">
         <v>241</v>
       </c>
@@ -9018,8 +9730,8 @@
       <c r="B183" s="7">
         <v>7</v>
       </c>
-      <c r="C183" s="153"/>
-      <c r="D183" s="141"/>
+      <c r="C183" s="163"/>
+      <c r="D183" s="151"/>
       <c r="E183" s="8" t="s">
         <v>242</v>
       </c>
@@ -9040,8 +9752,8 @@
       <c r="B184" s="7">
         <v>8</v>
       </c>
-      <c r="C184" s="153"/>
-      <c r="D184" s="142"/>
+      <c r="C184" s="163"/>
+      <c r="D184" s="152"/>
       <c r="E184" s="8" t="s">
         <v>243</v>
       </c>
@@ -9062,8 +9774,8 @@
       <c r="B185" s="7">
         <v>9</v>
       </c>
-      <c r="C185" s="153"/>
-      <c r="D185" s="140" t="s">
+      <c r="C185" s="163"/>
+      <c r="D185" s="150" t="s">
         <v>244</v>
       </c>
       <c r="E185" s="8" t="s">
@@ -9086,8 +9798,8 @@
       <c r="B186" s="7">
         <v>10</v>
       </c>
-      <c r="C186" s="153"/>
-      <c r="D186" s="142"/>
+      <c r="C186" s="163"/>
+      <c r="D186" s="152"/>
       <c r="E186" s="8" t="s">
         <v>246</v>
       </c>
@@ -9108,8 +9820,8 @@
       <c r="B187" s="7">
         <v>11</v>
       </c>
-      <c r="C187" s="153"/>
-      <c r="D187" s="140" t="s">
+      <c r="C187" s="163"/>
+      <c r="D187" s="150" t="s">
         <v>247</v>
       </c>
       <c r="E187" s="8" t="s">
@@ -9132,8 +9844,8 @@
       <c r="B188" s="7">
         <v>12</v>
       </c>
-      <c r="C188" s="153"/>
-      <c r="D188" s="141"/>
+      <c r="C188" s="163"/>
+      <c r="D188" s="151"/>
       <c r="E188" s="8" t="s">
         <v>249</v>
       </c>
@@ -9154,8 +9866,8 @@
       <c r="B189" s="7">
         <v>13</v>
       </c>
-      <c r="C189" s="153"/>
-      <c r="D189" s="141"/>
+      <c r="C189" s="163"/>
+      <c r="D189" s="151"/>
       <c r="E189" s="11" t="s">
         <v>250</v>
       </c>
@@ -9176,8 +9888,8 @@
       <c r="B190" s="7">
         <v>14</v>
       </c>
-      <c r="C190" s="153"/>
-      <c r="D190" s="142"/>
+      <c r="C190" s="163"/>
+      <c r="D190" s="152"/>
       <c r="E190" s="8" t="s">
         <v>251</v>
       </c>
@@ -9198,8 +9910,8 @@
       <c r="B191" s="7">
         <v>15</v>
       </c>
-      <c r="C191" s="153"/>
-      <c r="D191" s="140" t="s">
+      <c r="C191" s="163"/>
+      <c r="D191" s="150" t="s">
         <v>252</v>
       </c>
       <c r="E191" s="8" t="s">
@@ -9222,8 +9934,8 @@
       <c r="B192" s="7">
         <v>16</v>
       </c>
-      <c r="C192" s="153"/>
-      <c r="D192" s="141"/>
+      <c r="C192" s="163"/>
+      <c r="D192" s="151"/>
       <c r="E192" s="8" t="s">
         <v>254</v>
       </c>
@@ -9244,8 +9956,8 @@
       <c r="B193" s="7">
         <v>17</v>
       </c>
-      <c r="C193" s="153"/>
-      <c r="D193" s="141"/>
+      <c r="C193" s="163"/>
+      <c r="D193" s="151"/>
       <c r="E193" s="8" t="s">
         <v>255</v>
       </c>
@@ -9266,8 +9978,8 @@
       <c r="B194" s="7">
         <v>18</v>
       </c>
-      <c r="C194" s="153"/>
-      <c r="D194" s="141"/>
+      <c r="C194" s="163"/>
+      <c r="D194" s="151"/>
       <c r="E194" s="8" t="s">
         <v>256</v>
       </c>
@@ -9288,8 +10000,8 @@
       <c r="B195" s="7">
         <v>19</v>
       </c>
-      <c r="C195" s="153"/>
-      <c r="D195" s="141"/>
+      <c r="C195" s="163"/>
+      <c r="D195" s="151"/>
       <c r="E195" s="8" t="s">
         <v>257</v>
       </c>
@@ -9310,8 +10022,8 @@
       <c r="B196" s="7">
         <v>20</v>
       </c>
-      <c r="C196" s="153"/>
-      <c r="D196" s="141"/>
+      <c r="C196" s="163"/>
+      <c r="D196" s="151"/>
       <c r="E196" s="8" t="s">
         <v>258</v>
       </c>
@@ -9332,8 +10044,8 @@
       <c r="B197" s="7">
         <v>21</v>
       </c>
-      <c r="C197" s="153"/>
-      <c r="D197" s="141"/>
+      <c r="C197" s="163"/>
+      <c r="D197" s="151"/>
       <c r="E197" s="8" t="s">
         <v>259</v>
       </c>
@@ -9354,8 +10066,8 @@
       <c r="B198" s="7">
         <v>22</v>
       </c>
-      <c r="C198" s="153"/>
-      <c r="D198" s="142"/>
+      <c r="C198" s="163"/>
+      <c r="D198" s="152"/>
       <c r="E198" s="8" t="s">
         <v>260</v>
       </c>
@@ -9376,8 +10088,8 @@
       <c r="B199" s="7">
         <v>23</v>
       </c>
-      <c r="C199" s="153"/>
-      <c r="D199" s="140" t="s">
+      <c r="C199" s="163"/>
+      <c r="D199" s="150" t="s">
         <v>261</v>
       </c>
       <c r="E199" s="8" t="s">
@@ -9400,8 +10112,8 @@
       <c r="B200" s="7">
         <v>24</v>
       </c>
-      <c r="C200" s="153"/>
-      <c r="D200" s="141"/>
+      <c r="C200" s="163"/>
+      <c r="D200" s="151"/>
       <c r="E200" s="8" t="s">
         <v>263</v>
       </c>
@@ -9422,8 +10134,8 @@
       <c r="B201" s="7">
         <v>25</v>
       </c>
-      <c r="C201" s="153"/>
-      <c r="D201" s="141"/>
+      <c r="C201" s="163"/>
+      <c r="D201" s="151"/>
       <c r="E201" s="8" t="s">
         <v>264</v>
       </c>
@@ -9444,8 +10156,8 @@
       <c r="B202" s="7">
         <v>26</v>
       </c>
-      <c r="C202" s="153"/>
-      <c r="D202" s="142"/>
+      <c r="C202" s="163"/>
+      <c r="D202" s="152"/>
       <c r="E202" s="8" t="s">
         <v>265</v>
       </c>
@@ -9466,8 +10178,8 @@
       <c r="B203" s="7">
         <v>27</v>
       </c>
-      <c r="C203" s="153"/>
-      <c r="D203" s="140" t="s">
+      <c r="C203" s="163"/>
+      <c r="D203" s="150" t="s">
         <v>266</v>
       </c>
       <c r="E203" s="8" t="s">
@@ -9490,8 +10202,8 @@
       <c r="B204" s="24">
         <v>28</v>
       </c>
-      <c r="C204" s="154"/>
-      <c r="D204" s="142"/>
+      <c r="C204" s="164"/>
+      <c r="D204" s="152"/>
       <c r="E204" s="17" t="s">
         <v>268</v>
       </c>
@@ -9512,10 +10224,10 @@
       <c r="B205" s="7">
         <v>1</v>
       </c>
-      <c r="C205" s="155" t="s">
+      <c r="C205" s="165" t="s">
         <v>269</v>
       </c>
-      <c r="D205" s="140" t="s">
+      <c r="D205" s="150" t="s">
         <v>270</v>
       </c>
       <c r="E205" s="8" t="s">
@@ -9538,8 +10250,8 @@
       <c r="B206" s="7">
         <v>2</v>
       </c>
-      <c r="C206" s="156"/>
-      <c r="D206" s="141"/>
+      <c r="C206" s="166"/>
+      <c r="D206" s="151"/>
       <c r="E206" s="8" t="s">
         <v>272</v>
       </c>
@@ -9560,8 +10272,8 @@
       <c r="B207" s="7">
         <v>3</v>
       </c>
-      <c r="C207" s="156"/>
-      <c r="D207" s="141"/>
+      <c r="C207" s="166"/>
+      <c r="D207" s="151"/>
       <c r="E207" s="8" t="s">
         <v>273</v>
       </c>
@@ -9582,8 +10294,8 @@
       <c r="B208" s="7">
         <v>4</v>
       </c>
-      <c r="C208" s="156"/>
-      <c r="D208" s="141"/>
+      <c r="C208" s="166"/>
+      <c r="D208" s="151"/>
       <c r="E208" s="8" t="s">
         <v>274</v>
       </c>
@@ -9604,8 +10316,8 @@
       <c r="B209" s="7">
         <v>5</v>
       </c>
-      <c r="C209" s="156"/>
-      <c r="D209" s="142"/>
+      <c r="C209" s="166"/>
+      <c r="D209" s="152"/>
       <c r="E209" s="8" t="s">
         <v>275</v>
       </c>
@@ -9626,8 +10338,8 @@
       <c r="B210" s="7">
         <v>6</v>
       </c>
-      <c r="C210" s="156"/>
-      <c r="D210" s="140" t="s">
+      <c r="C210" s="166"/>
+      <c r="D210" s="150" t="s">
         <v>276</v>
       </c>
       <c r="E210" s="8" t="s">
@@ -9650,8 +10362,8 @@
       <c r="B211" s="7">
         <v>7</v>
       </c>
-      <c r="C211" s="156"/>
-      <c r="D211" s="142"/>
+      <c r="C211" s="166"/>
+      <c r="D211" s="152"/>
       <c r="E211" s="8" t="s">
         <v>278</v>
       </c>
@@ -9672,8 +10384,8 @@
       <c r="B212" s="7">
         <v>8</v>
       </c>
-      <c r="C212" s="156"/>
-      <c r="D212" s="140" t="s">
+      <c r="C212" s="166"/>
+      <c r="D212" s="150" t="s">
         <v>279</v>
       </c>
       <c r="E212" s="8" t="s">
@@ -9696,8 +10408,8 @@
       <c r="B213" s="7">
         <v>9</v>
       </c>
-      <c r="C213" s="156"/>
-      <c r="D213" s="141"/>
+      <c r="C213" s="166"/>
+      <c r="D213" s="151"/>
       <c r="E213" s="8" t="s">
         <v>281</v>
       </c>
@@ -9718,8 +10430,8 @@
       <c r="B214" s="7">
         <v>10</v>
       </c>
-      <c r="C214" s="157"/>
-      <c r="D214" s="142"/>
+      <c r="C214" s="167"/>
+      <c r="D214" s="152"/>
       <c r="E214" s="8" t="s">
         <v>282</v>
       </c>
@@ -9734,18 +10446,18 @@
       <c r="J214" s="11"/>
     </row>
     <row r="215" spans="1:10" ht="13.8">
-      <c r="A215" s="176" t="s">
+      <c r="A215" s="186" t="s">
         <v>283</v>
       </c>
-      <c r="B215" s="177"/>
-      <c r="C215" s="177"/>
-      <c r="D215" s="177"/>
-      <c r="E215" s="177"/>
-      <c r="F215" s="177"/>
-      <c r="G215" s="177"/>
-      <c r="H215" s="177"/>
-      <c r="I215" s="177"/>
-      <c r="J215" s="178"/>
+      <c r="B215" s="187"/>
+      <c r="C215" s="187"/>
+      <c r="D215" s="187"/>
+      <c r="E215" s="187"/>
+      <c r="F215" s="187"/>
+      <c r="G215" s="187"/>
+      <c r="H215" s="187"/>
+      <c r="I215" s="187"/>
+      <c r="J215" s="188"/>
     </row>
     <row r="216" spans="1:10" ht="13.8">
       <c r="A216" s="6">
@@ -9754,10 +10466,10 @@
       <c r="B216" s="7">
         <v>1</v>
       </c>
-      <c r="C216" s="158" t="s">
+      <c r="C216" s="168" t="s">
         <v>284</v>
       </c>
-      <c r="D216" s="140" t="s">
+      <c r="D216" s="150" t="s">
         <v>285</v>
       </c>
       <c r="E216" s="8" t="s">
@@ -9780,8 +10492,8 @@
       <c r="B217" s="7">
         <v>2</v>
       </c>
-      <c r="C217" s="159"/>
-      <c r="D217" s="141"/>
+      <c r="C217" s="169"/>
+      <c r="D217" s="151"/>
       <c r="E217" s="8" t="s">
         <v>287</v>
       </c>
@@ -9802,8 +10514,8 @@
       <c r="B218" s="7">
         <v>3</v>
       </c>
-      <c r="C218" s="159"/>
-      <c r="D218" s="141"/>
+      <c r="C218" s="169"/>
+      <c r="D218" s="151"/>
       <c r="E218" s="8" t="s">
         <v>288</v>
       </c>
@@ -9824,8 +10536,8 @@
       <c r="B219" s="7">
         <v>4</v>
       </c>
-      <c r="C219" s="159"/>
-      <c r="D219" s="141"/>
+      <c r="C219" s="169"/>
+      <c r="D219" s="151"/>
       <c r="E219" s="8" t="s">
         <v>289</v>
       </c>
@@ -9846,8 +10558,8 @@
       <c r="B220" s="7">
         <v>5</v>
       </c>
-      <c r="C220" s="159"/>
-      <c r="D220" s="141"/>
+      <c r="C220" s="169"/>
+      <c r="D220" s="151"/>
       <c r="E220" s="8" t="s">
         <v>290</v>
       </c>
@@ -9868,8 +10580,8 @@
       <c r="B221" s="7">
         <v>6</v>
       </c>
-      <c r="C221" s="159"/>
-      <c r="D221" s="141"/>
+      <c r="C221" s="169"/>
+      <c r="D221" s="151"/>
       <c r="E221" s="8" t="s">
         <v>291</v>
       </c>
@@ -9890,8 +10602,8 @@
       <c r="B222" s="7">
         <v>7</v>
       </c>
-      <c r="C222" s="159"/>
-      <c r="D222" s="141"/>
+      <c r="C222" s="169"/>
+      <c r="D222" s="151"/>
       <c r="E222" s="8" t="s">
         <v>292</v>
       </c>
@@ -9912,8 +10624,8 @@
       <c r="B223" s="7">
         <v>8</v>
       </c>
-      <c r="C223" s="159"/>
-      <c r="D223" s="141"/>
+      <c r="C223" s="169"/>
+      <c r="D223" s="151"/>
       <c r="E223" s="8" t="s">
         <v>293</v>
       </c>
@@ -9934,8 +10646,8 @@
       <c r="B224" s="7">
         <v>9</v>
       </c>
-      <c r="C224" s="159"/>
-      <c r="D224" s="141"/>
+      <c r="C224" s="169"/>
+      <c r="D224" s="151"/>
       <c r="E224" s="8" t="s">
         <v>294</v>
       </c>
@@ -9956,8 +10668,8 @@
       <c r="B225" s="7">
         <v>10</v>
       </c>
-      <c r="C225" s="159"/>
-      <c r="D225" s="142"/>
+      <c r="C225" s="169"/>
+      <c r="D225" s="152"/>
       <c r="E225" s="8" t="s">
         <v>295</v>
       </c>
@@ -9978,8 +10690,8 @@
       <c r="B226" s="7">
         <v>11</v>
       </c>
-      <c r="C226" s="159"/>
-      <c r="D226" s="140" t="s">
+      <c r="C226" s="169"/>
+      <c r="D226" s="150" t="s">
         <v>296</v>
       </c>
       <c r="E226" s="8" t="s">
@@ -10002,8 +10714,8 @@
       <c r="B227" s="7">
         <v>12</v>
       </c>
-      <c r="C227" s="159"/>
-      <c r="D227" s="141"/>
+      <c r="C227" s="169"/>
+      <c r="D227" s="151"/>
       <c r="E227" s="8" t="s">
         <v>298</v>
       </c>
@@ -10024,8 +10736,8 @@
       <c r="B228" s="7">
         <v>13</v>
       </c>
-      <c r="C228" s="159"/>
-      <c r="D228" s="141"/>
+      <c r="C228" s="169"/>
+      <c r="D228" s="151"/>
       <c r="E228" s="8" t="s">
         <v>299</v>
       </c>
@@ -10046,8 +10758,8 @@
       <c r="B229" s="7">
         <v>14</v>
       </c>
-      <c r="C229" s="159"/>
-      <c r="D229" s="141"/>
+      <c r="C229" s="169"/>
+      <c r="D229" s="151"/>
       <c r="E229" s="8" t="s">
         <v>300</v>
       </c>
@@ -10068,8 +10780,8 @@
       <c r="B230" s="7">
         <v>15</v>
       </c>
-      <c r="C230" s="159"/>
-      <c r="D230" s="141"/>
+      <c r="C230" s="169"/>
+      <c r="D230" s="151"/>
       <c r="E230" s="8" t="s">
         <v>301</v>
       </c>
@@ -10090,8 +10802,8 @@
       <c r="B231" s="7">
         <v>16</v>
       </c>
-      <c r="C231" s="159"/>
-      <c r="D231" s="141"/>
+      <c r="C231" s="169"/>
+      <c r="D231" s="151"/>
       <c r="E231" s="8" t="s">
         <v>302</v>
       </c>
@@ -10112,8 +10824,8 @@
       <c r="B232" s="7">
         <v>17</v>
       </c>
-      <c r="C232" s="159"/>
-      <c r="D232" s="141"/>
+      <c r="C232" s="169"/>
+      <c r="D232" s="151"/>
       <c r="E232" s="8" t="s">
         <v>303</v>
       </c>
@@ -10134,8 +10846,8 @@
       <c r="B233" s="7">
         <v>18</v>
       </c>
-      <c r="C233" s="159"/>
-      <c r="D233" s="142"/>
+      <c r="C233" s="169"/>
+      <c r="D233" s="152"/>
       <c r="E233" s="8" t="s">
         <v>304</v>
       </c>
@@ -10156,8 +10868,8 @@
       <c r="B234" s="7">
         <v>19</v>
       </c>
-      <c r="C234" s="159"/>
-      <c r="D234" s="140" t="s">
+      <c r="C234" s="169"/>
+      <c r="D234" s="150" t="s">
         <v>305</v>
       </c>
       <c r="E234" s="8" t="s">
@@ -10180,8 +10892,8 @@
       <c r="B235" s="7">
         <v>20</v>
       </c>
-      <c r="C235" s="159"/>
-      <c r="D235" s="141"/>
+      <c r="C235" s="169"/>
+      <c r="D235" s="151"/>
       <c r="E235" s="8" t="s">
         <v>307</v>
       </c>
@@ -10202,8 +10914,8 @@
       <c r="B236" s="7">
         <v>21</v>
       </c>
-      <c r="C236" s="159"/>
-      <c r="D236" s="141"/>
+      <c r="C236" s="169"/>
+      <c r="D236" s="151"/>
       <c r="E236" s="8" t="s">
         <v>308</v>
       </c>
@@ -10224,8 +10936,8 @@
       <c r="B237" s="7">
         <v>22</v>
       </c>
-      <c r="C237" s="159"/>
-      <c r="D237" s="141"/>
+      <c r="C237" s="169"/>
+      <c r="D237" s="151"/>
       <c r="E237" s="8" t="s">
         <v>309</v>
       </c>
@@ -10246,8 +10958,8 @@
       <c r="B238" s="7">
         <v>23</v>
       </c>
-      <c r="C238" s="159"/>
-      <c r="D238" s="141"/>
+      <c r="C238" s="169"/>
+      <c r="D238" s="151"/>
       <c r="E238" s="8" t="s">
         <v>310</v>
       </c>
@@ -10268,8 +10980,8 @@
       <c r="B239" s="7">
         <v>24</v>
       </c>
-      <c r="C239" s="159"/>
-      <c r="D239" s="141"/>
+      <c r="C239" s="169"/>
+      <c r="D239" s="151"/>
       <c r="E239" s="8" t="s">
         <v>311</v>
       </c>
@@ -10290,8 +11002,8 @@
       <c r="B240" s="7">
         <v>25</v>
       </c>
-      <c r="C240" s="159"/>
-      <c r="D240" s="142"/>
+      <c r="C240" s="169"/>
+      <c r="D240" s="152"/>
       <c r="E240" s="8" t="s">
         <v>312</v>
       </c>
@@ -10312,8 +11024,8 @@
       <c r="B241" s="7">
         <v>26</v>
       </c>
-      <c r="C241" s="159"/>
-      <c r="D241" s="140" t="s">
+      <c r="C241" s="169"/>
+      <c r="D241" s="150" t="s">
         <v>313</v>
       </c>
       <c r="E241" s="8" t="s">
@@ -10336,8 +11048,8 @@
       <c r="B242" s="7">
         <v>27</v>
       </c>
-      <c r="C242" s="159"/>
-      <c r="D242" s="141"/>
+      <c r="C242" s="169"/>
+      <c r="D242" s="151"/>
       <c r="E242" s="8" t="s">
         <v>315</v>
       </c>
@@ -10358,8 +11070,8 @@
       <c r="B243" s="7">
         <v>28</v>
       </c>
-      <c r="C243" s="159"/>
-      <c r="D243" s="142"/>
+      <c r="C243" s="169"/>
+      <c r="D243" s="152"/>
       <c r="E243" s="8" t="s">
         <v>316</v>
       </c>
@@ -10380,8 +11092,8 @@
       <c r="B244" s="7">
         <v>29</v>
       </c>
-      <c r="C244" s="159"/>
-      <c r="D244" s="140" t="s">
+      <c r="C244" s="169"/>
+      <c r="D244" s="150" t="s">
         <v>317</v>
       </c>
       <c r="E244" s="8" t="s">
@@ -10404,8 +11116,8 @@
       <c r="B245" s="7">
         <v>30</v>
       </c>
-      <c r="C245" s="159"/>
-      <c r="D245" s="141"/>
+      <c r="C245" s="169"/>
+      <c r="D245" s="151"/>
       <c r="E245" s="8" t="s">
         <v>319</v>
       </c>
@@ -10426,8 +11138,8 @@
       <c r="B246" s="7">
         <v>31</v>
       </c>
-      <c r="C246" s="159"/>
-      <c r="D246" s="141"/>
+      <c r="C246" s="169"/>
+      <c r="D246" s="151"/>
       <c r="E246" s="8" t="s">
         <v>320</v>
       </c>
@@ -10448,8 +11160,8 @@
       <c r="B247" s="7">
         <v>32</v>
       </c>
-      <c r="C247" s="159"/>
-      <c r="D247" s="141"/>
+      <c r="C247" s="169"/>
+      <c r="D247" s="151"/>
       <c r="E247" s="8" t="s">
         <v>321</v>
       </c>
@@ -10470,8 +11182,8 @@
       <c r="B248" s="7">
         <v>33</v>
       </c>
-      <c r="C248" s="159"/>
-      <c r="D248" s="141"/>
+      <c r="C248" s="169"/>
+      <c r="D248" s="151"/>
       <c r="E248" s="8" t="s">
         <v>322</v>
       </c>
@@ -10492,8 +11204,8 @@
       <c r="B249" s="24">
         <v>34</v>
       </c>
-      <c r="C249" s="160"/>
-      <c r="D249" s="142"/>
+      <c r="C249" s="170"/>
+      <c r="D249" s="152"/>
       <c r="E249" s="17" t="s">
         <v>323</v>
       </c>
@@ -10514,10 +11226,10 @@
       <c r="B250" s="7">
         <v>1</v>
       </c>
-      <c r="C250" s="149" t="s">
+      <c r="C250" s="159" t="s">
         <v>324</v>
       </c>
-      <c r="D250" s="140" t="s">
+      <c r="D250" s="150" t="s">
         <v>325</v>
       </c>
       <c r="E250" s="8" t="s">
@@ -10540,8 +11252,8 @@
       <c r="B251" s="7">
         <v>2</v>
       </c>
-      <c r="C251" s="150"/>
-      <c r="D251" s="141"/>
+      <c r="C251" s="160"/>
+      <c r="D251" s="151"/>
       <c r="E251" s="8" t="s">
         <v>327</v>
       </c>
@@ -10562,8 +11274,8 @@
       <c r="B252" s="7">
         <v>3</v>
       </c>
-      <c r="C252" s="150"/>
-      <c r="D252" s="141"/>
+      <c r="C252" s="160"/>
+      <c r="D252" s="151"/>
       <c r="E252" s="8" t="s">
         <v>328</v>
       </c>
@@ -10584,8 +11296,8 @@
       <c r="B253" s="7">
         <v>4</v>
       </c>
-      <c r="C253" s="150"/>
-      <c r="D253" s="141"/>
+      <c r="C253" s="160"/>
+      <c r="D253" s="151"/>
       <c r="E253" s="8" t="s">
         <v>329</v>
       </c>
@@ -10606,8 +11318,8 @@
       <c r="B254" s="7">
         <v>5</v>
       </c>
-      <c r="C254" s="150"/>
-      <c r="D254" s="141"/>
+      <c r="C254" s="160"/>
+      <c r="D254" s="151"/>
       <c r="E254" s="8" t="s">
         <v>330</v>
       </c>
@@ -10628,8 +11340,8 @@
       <c r="B255" s="7">
         <v>6</v>
       </c>
-      <c r="C255" s="150"/>
-      <c r="D255" s="141"/>
+      <c r="C255" s="160"/>
+      <c r="D255" s="151"/>
       <c r="E255" s="8" t="s">
         <v>331</v>
       </c>
@@ -10650,8 +11362,8 @@
       <c r="B256" s="7">
         <v>7</v>
       </c>
-      <c r="C256" s="150"/>
-      <c r="D256" s="141"/>
+      <c r="C256" s="160"/>
+      <c r="D256" s="151"/>
       <c r="E256" s="8" t="s">
         <v>332</v>
       </c>
@@ -10672,8 +11384,8 @@
       <c r="B257" s="7">
         <v>8</v>
       </c>
-      <c r="C257" s="150"/>
-      <c r="D257" s="142"/>
+      <c r="C257" s="160"/>
+      <c r="D257" s="152"/>
       <c r="E257" s="8" t="s">
         <v>333</v>
       </c>
@@ -10694,8 +11406,8 @@
       <c r="B258" s="7">
         <v>9</v>
       </c>
-      <c r="C258" s="150"/>
-      <c r="D258" s="140" t="s">
+      <c r="C258" s="160"/>
+      <c r="D258" s="150" t="s">
         <v>334</v>
       </c>
       <c r="E258" s="8" t="s">
@@ -10718,8 +11430,8 @@
       <c r="B259" s="7">
         <v>10</v>
       </c>
-      <c r="C259" s="150"/>
-      <c r="D259" s="142"/>
+      <c r="C259" s="160"/>
+      <c r="D259" s="152"/>
       <c r="E259" s="8" t="s">
         <v>336</v>
       </c>
@@ -10740,8 +11452,8 @@
       <c r="B260" s="7">
         <v>11</v>
       </c>
-      <c r="C260" s="150"/>
-      <c r="D260" s="140" t="s">
+      <c r="C260" s="160"/>
+      <c r="D260" s="150" t="s">
         <v>337</v>
       </c>
       <c r="E260" s="8" t="s">
@@ -10764,8 +11476,8 @@
       <c r="B261" s="7">
         <v>12</v>
       </c>
-      <c r="C261" s="150"/>
-      <c r="D261" s="141"/>
+      <c r="C261" s="160"/>
+      <c r="D261" s="151"/>
       <c r="E261" s="8" t="s">
         <v>339</v>
       </c>
@@ -10786,8 +11498,8 @@
       <c r="B262" s="7">
         <v>13</v>
       </c>
-      <c r="C262" s="150"/>
-      <c r="D262" s="141"/>
+      <c r="C262" s="160"/>
+      <c r="D262" s="151"/>
       <c r="E262" s="8" t="s">
         <v>340</v>
       </c>
@@ -10808,8 +11520,8 @@
       <c r="B263" s="7">
         <v>14</v>
       </c>
-      <c r="C263" s="150"/>
-      <c r="D263" s="141"/>
+      <c r="C263" s="160"/>
+      <c r="D263" s="151"/>
       <c r="E263" s="8" t="s">
         <v>341</v>
       </c>
@@ -10830,8 +11542,8 @@
       <c r="B264" s="7">
         <v>15</v>
       </c>
-      <c r="C264" s="150"/>
-      <c r="D264" s="141"/>
+      <c r="C264" s="160"/>
+      <c r="D264" s="151"/>
       <c r="E264" s="8" t="s">
         <v>342</v>
       </c>
@@ -10852,8 +11564,8 @@
       <c r="B265" s="24">
         <v>16</v>
       </c>
-      <c r="C265" s="151"/>
-      <c r="D265" s="142"/>
+      <c r="C265" s="161"/>
+      <c r="D265" s="152"/>
       <c r="E265" s="17" t="s">
         <v>343</v>
       </c>
@@ -10874,10 +11586,10 @@
       <c r="B266" s="7">
         <v>1</v>
       </c>
-      <c r="C266" s="152" t="s">
+      <c r="C266" s="162" t="s">
         <v>344</v>
       </c>
-      <c r="D266" s="140" t="s">
+      <c r="D266" s="150" t="s">
         <v>345</v>
       </c>
       <c r="E266" s="8" t="s">
@@ -10900,8 +11612,8 @@
       <c r="B267" s="7">
         <v>2</v>
       </c>
-      <c r="C267" s="153"/>
-      <c r="D267" s="141"/>
+      <c r="C267" s="163"/>
+      <c r="D267" s="151"/>
       <c r="E267" s="8" t="s">
         <v>347</v>
       </c>
@@ -10922,8 +11634,8 @@
       <c r="B268" s="7">
         <v>3</v>
       </c>
-      <c r="C268" s="153"/>
-      <c r="D268" s="141"/>
+      <c r="C268" s="163"/>
+      <c r="D268" s="151"/>
       <c r="E268" s="8" t="s">
         <v>348</v>
       </c>
@@ -10944,8 +11656,8 @@
       <c r="B269" s="7">
         <v>4</v>
       </c>
-      <c r="C269" s="153"/>
-      <c r="D269" s="141"/>
+      <c r="C269" s="163"/>
+      <c r="D269" s="151"/>
       <c r="E269" s="8" t="s">
         <v>349</v>
       </c>
@@ -10966,8 +11678,8 @@
       <c r="B270" s="7">
         <v>5</v>
       </c>
-      <c r="C270" s="153"/>
-      <c r="D270" s="142"/>
+      <c r="C270" s="163"/>
+      <c r="D270" s="152"/>
       <c r="E270" s="8" t="s">
         <v>350</v>
       </c>
@@ -10988,8 +11700,8 @@
       <c r="B271" s="7">
         <v>6</v>
       </c>
-      <c r="C271" s="153"/>
-      <c r="D271" s="140" t="s">
+      <c r="C271" s="163"/>
+      <c r="D271" s="150" t="s">
         <v>351</v>
       </c>
       <c r="E271" s="8" t="s">
@@ -11012,8 +11724,8 @@
       <c r="B272" s="7">
         <v>7</v>
       </c>
-      <c r="C272" s="154"/>
-      <c r="D272" s="142"/>
+      <c r="C272" s="164"/>
+      <c r="D272" s="152"/>
       <c r="E272" s="8" t="s">
         <v>353</v>
       </c>
@@ -11028,18 +11740,18 @@
       <c r="J272" s="11"/>
     </row>
     <row r="273" spans="1:10" ht="13.8">
-      <c r="A273" s="173" t="s">
+      <c r="A273" s="183" t="s">
         <v>354</v>
       </c>
-      <c r="B273" s="174"/>
-      <c r="C273" s="174"/>
-      <c r="D273" s="174"/>
-      <c r="E273" s="174"/>
-      <c r="F273" s="174"/>
-      <c r="G273" s="174"/>
-      <c r="H273" s="174"/>
-      <c r="I273" s="174"/>
-      <c r="J273" s="175"/>
+      <c r="B273" s="184"/>
+      <c r="C273" s="184"/>
+      <c r="D273" s="184"/>
+      <c r="E273" s="184"/>
+      <c r="F273" s="184"/>
+      <c r="G273" s="184"/>
+      <c r="H273" s="184"/>
+      <c r="I273" s="184"/>
+      <c r="J273" s="185"/>
     </row>
     <row r="274" spans="1:10" ht="13.8">
       <c r="A274" s="33">
@@ -11048,10 +11760,10 @@
       <c r="B274" s="7">
         <v>1</v>
       </c>
-      <c r="C274" s="167" t="s">
+      <c r="C274" s="177" t="s">
         <v>355</v>
       </c>
-      <c r="D274" s="170" t="s">
+      <c r="D274" s="180" t="s">
         <v>356</v>
       </c>
       <c r="E274" s="13" t="s">
@@ -11074,8 +11786,8 @@
       <c r="B275" s="7">
         <v>2</v>
       </c>
-      <c r="C275" s="168"/>
-      <c r="D275" s="171"/>
+      <c r="C275" s="178"/>
+      <c r="D275" s="181"/>
       <c r="E275" s="13" t="s">
         <v>358</v>
       </c>
@@ -11096,8 +11808,8 @@
       <c r="B276" s="7">
         <v>3</v>
       </c>
-      <c r="C276" s="168"/>
-      <c r="D276" s="171"/>
+      <c r="C276" s="178"/>
+      <c r="D276" s="181"/>
       <c r="E276" s="8" t="s">
         <v>359</v>
       </c>
@@ -11118,8 +11830,8 @@
       <c r="B277" s="7">
         <v>4</v>
       </c>
-      <c r="C277" s="168"/>
-      <c r="D277" s="171"/>
+      <c r="C277" s="178"/>
+      <c r="D277" s="181"/>
       <c r="E277" s="8" t="s">
         <v>360</v>
       </c>
@@ -11140,8 +11852,8 @@
       <c r="B278" s="7">
         <v>5</v>
       </c>
-      <c r="C278" s="168"/>
-      <c r="D278" s="171"/>
+      <c r="C278" s="178"/>
+      <c r="D278" s="181"/>
       <c r="E278" s="8" t="s">
         <v>361</v>
       </c>
@@ -11162,8 +11874,8 @@
       <c r="B279" s="7">
         <v>6</v>
       </c>
-      <c r="C279" s="168"/>
-      <c r="D279" s="171"/>
+      <c r="C279" s="178"/>
+      <c r="D279" s="181"/>
       <c r="E279" s="8" t="s">
         <v>362</v>
       </c>
@@ -11184,8 +11896,8 @@
       <c r="B280" s="7">
         <v>7</v>
       </c>
-      <c r="C280" s="168"/>
-      <c r="D280" s="171"/>
+      <c r="C280" s="178"/>
+      <c r="D280" s="181"/>
       <c r="E280" s="8" t="s">
         <v>363</v>
       </c>
@@ -11206,8 +11918,8 @@
       <c r="B281" s="7">
         <v>8</v>
       </c>
-      <c r="C281" s="168"/>
-      <c r="D281" s="172"/>
+      <c r="C281" s="178"/>
+      <c r="D281" s="182"/>
       <c r="E281" s="13" t="s">
         <v>364</v>
       </c>
@@ -11228,8 +11940,8 @@
       <c r="B282" s="7">
         <v>9</v>
       </c>
-      <c r="C282" s="168"/>
-      <c r="D282" s="170" t="s">
+      <c r="C282" s="178"/>
+      <c r="D282" s="180" t="s">
         <v>365</v>
       </c>
       <c r="E282" s="8" t="s">
@@ -11252,8 +11964,8 @@
       <c r="B283" s="7">
         <v>10</v>
       </c>
-      <c r="C283" s="168"/>
-      <c r="D283" s="171"/>
+      <c r="C283" s="178"/>
+      <c r="D283" s="181"/>
       <c r="E283" s="13" t="s">
         <v>367</v>
       </c>
@@ -11274,8 +11986,8 @@
       <c r="B284" s="7">
         <v>11</v>
       </c>
-      <c r="C284" s="168"/>
-      <c r="D284" s="171"/>
+      <c r="C284" s="178"/>
+      <c r="D284" s="181"/>
       <c r="E284" s="13" t="s">
         <v>368</v>
       </c>
@@ -11296,8 +12008,8 @@
       <c r="B285" s="7">
         <v>12</v>
       </c>
-      <c r="C285" s="168"/>
-      <c r="D285" s="171"/>
+      <c r="C285" s="178"/>
+      <c r="D285" s="181"/>
       <c r="E285" s="13" t="s">
         <v>369</v>
       </c>
@@ -11318,8 +12030,8 @@
       <c r="B286" s="7">
         <v>13</v>
       </c>
-      <c r="C286" s="168"/>
-      <c r="D286" s="171"/>
+      <c r="C286" s="178"/>
+      <c r="D286" s="181"/>
       <c r="E286" s="13" t="s">
         <v>370</v>
       </c>
@@ -11340,8 +12052,8 @@
       <c r="B287" s="7">
         <v>14</v>
       </c>
-      <c r="C287" s="168"/>
-      <c r="D287" s="171"/>
+      <c r="C287" s="178"/>
+      <c r="D287" s="181"/>
       <c r="E287" s="13" t="s">
         <v>371</v>
       </c>
@@ -11362,8 +12074,8 @@
       <c r="B288" s="7">
         <v>15</v>
       </c>
-      <c r="C288" s="168"/>
-      <c r="D288" s="172"/>
+      <c r="C288" s="178"/>
+      <c r="D288" s="182"/>
       <c r="E288" s="13" t="s">
         <v>372</v>
       </c>
@@ -11384,8 +12096,8 @@
       <c r="B289" s="7">
         <v>16</v>
       </c>
-      <c r="C289" s="168"/>
-      <c r="D289" s="170" t="s">
+      <c r="C289" s="178"/>
+      <c r="D289" s="180" t="s">
         <v>373</v>
       </c>
       <c r="E289" s="13" t="s">
@@ -11408,8 +12120,8 @@
       <c r="B290" s="7">
         <v>17</v>
       </c>
-      <c r="C290" s="168"/>
-      <c r="D290" s="171"/>
+      <c r="C290" s="178"/>
+      <c r="D290" s="181"/>
       <c r="E290" s="8" t="s">
         <v>375</v>
       </c>
@@ -11430,8 +12142,8 @@
       <c r="B291" s="7">
         <v>18</v>
       </c>
-      <c r="C291" s="168"/>
-      <c r="D291" s="171"/>
+      <c r="C291" s="178"/>
+      <c r="D291" s="181"/>
       <c r="E291" s="11" t="s">
         <v>376</v>
       </c>
@@ -11452,8 +12164,8 @@
       <c r="B292" s="24">
         <v>19</v>
       </c>
-      <c r="C292" s="169"/>
-      <c r="D292" s="172"/>
+      <c r="C292" s="179"/>
+      <c r="D292" s="182"/>
       <c r="E292" s="20" t="s">
         <v>377</v>
       </c>
@@ -11474,10 +12186,10 @@
       <c r="B293" s="7">
         <v>1</v>
       </c>
-      <c r="C293" s="158" t="s">
+      <c r="C293" s="168" t="s">
         <v>378</v>
       </c>
-      <c r="D293" s="140" t="s">
+      <c r="D293" s="150" t="s">
         <v>379</v>
       </c>
       <c r="E293" s="8" t="s">
@@ -11500,8 +12212,8 @@
       <c r="B294" s="7">
         <v>2</v>
       </c>
-      <c r="C294" s="159"/>
-      <c r="D294" s="141"/>
+      <c r="C294" s="169"/>
+      <c r="D294" s="151"/>
       <c r="E294" s="8" t="s">
         <v>381</v>
       </c>
@@ -11522,8 +12234,8 @@
       <c r="B295" s="7">
         <v>3</v>
       </c>
-      <c r="C295" s="159"/>
-      <c r="D295" s="142"/>
+      <c r="C295" s="169"/>
+      <c r="D295" s="152"/>
       <c r="E295" s="8" t="s">
         <v>382</v>
       </c>
@@ -11542,8 +12254,8 @@
       <c r="B296" s="7">
         <v>4</v>
       </c>
-      <c r="C296" s="159"/>
-      <c r="D296" s="140" t="s">
+      <c r="C296" s="169"/>
+      <c r="D296" s="150" t="s">
         <v>383</v>
       </c>
       <c r="E296" s="37" t="s">
@@ -11566,8 +12278,8 @@
       <c r="B297" s="7">
         <v>5</v>
       </c>
-      <c r="C297" s="159"/>
-      <c r="D297" s="141"/>
+      <c r="C297" s="169"/>
+      <c r="D297" s="151"/>
       <c r="E297" s="8" t="s">
         <v>385</v>
       </c>
@@ -11588,8 +12300,8 @@
       <c r="B298" s="7">
         <v>6</v>
       </c>
-      <c r="C298" s="159"/>
-      <c r="D298" s="141"/>
+      <c r="C298" s="169"/>
+      <c r="D298" s="151"/>
       <c r="E298" s="8" t="s">
         <v>386</v>
       </c>
@@ -11610,8 +12322,8 @@
       <c r="B299" s="7">
         <v>7</v>
       </c>
-      <c r="C299" s="159"/>
-      <c r="D299" s="141"/>
+      <c r="C299" s="169"/>
+      <c r="D299" s="151"/>
       <c r="E299" s="8" t="s">
         <v>387</v>
       </c>
@@ -11632,8 +12344,8 @@
       <c r="B300" s="7">
         <v>8</v>
       </c>
-      <c r="C300" s="159"/>
-      <c r="D300" s="142"/>
+      <c r="C300" s="169"/>
+      <c r="D300" s="152"/>
       <c r="E300" s="8" t="s">
         <v>388</v>
       </c>
@@ -11654,8 +12366,8 @@
       <c r="B301" s="7">
         <v>9</v>
       </c>
-      <c r="C301" s="159"/>
-      <c r="D301" s="140" t="s">
+      <c r="C301" s="169"/>
+      <c r="D301" s="150" t="s">
         <v>389</v>
       </c>
       <c r="E301" s="8" t="s">
@@ -11678,8 +12390,8 @@
       <c r="B302" s="7">
         <v>10</v>
       </c>
-      <c r="C302" s="159"/>
-      <c r="D302" s="141"/>
+      <c r="C302" s="169"/>
+      <c r="D302" s="151"/>
       <c r="E302" s="8" t="s">
         <v>391</v>
       </c>
@@ -11700,8 +12412,8 @@
       <c r="B303" s="7">
         <v>11</v>
       </c>
-      <c r="C303" s="159"/>
-      <c r="D303" s="142"/>
+      <c r="C303" s="169"/>
+      <c r="D303" s="152"/>
       <c r="E303" s="8" t="s">
         <v>392</v>
       </c>
@@ -11722,8 +12434,8 @@
       <c r="B304" s="7">
         <v>12</v>
       </c>
-      <c r="C304" s="159"/>
-      <c r="D304" s="140" t="s">
+      <c r="C304" s="169"/>
+      <c r="D304" s="150" t="s">
         <v>393</v>
       </c>
       <c r="E304" s="8" t="s">
@@ -11746,8 +12458,8 @@
       <c r="B305" s="7">
         <v>13</v>
       </c>
-      <c r="C305" s="159"/>
-      <c r="D305" s="141"/>
+      <c r="C305" s="169"/>
+      <c r="D305" s="151"/>
       <c r="E305" s="8" t="s">
         <v>395</v>
       </c>
@@ -11768,8 +12480,8 @@
       <c r="B306" s="7">
         <v>14</v>
       </c>
-      <c r="C306" s="159"/>
-      <c r="D306" s="141"/>
+      <c r="C306" s="169"/>
+      <c r="D306" s="151"/>
       <c r="E306" s="8" t="s">
         <v>396</v>
       </c>
@@ -11790,8 +12502,8 @@
       <c r="B307" s="24">
         <v>15</v>
       </c>
-      <c r="C307" s="160"/>
-      <c r="D307" s="142"/>
+      <c r="C307" s="170"/>
+      <c r="D307" s="152"/>
       <c r="E307" s="17" t="s">
         <v>397</v>
       </c>
@@ -11812,10 +12524,10 @@
       <c r="B308" s="7">
         <v>1</v>
       </c>
-      <c r="C308" s="185" t="s">
+      <c r="C308" s="195" t="s">
         <v>398</v>
       </c>
-      <c r="D308" s="170" t="s">
+      <c r="D308" s="180" t="s">
         <v>399</v>
       </c>
       <c r="E308" s="13" t="s">
@@ -11838,8 +12550,8 @@
       <c r="B309" s="7">
         <v>2</v>
       </c>
-      <c r="C309" s="186"/>
-      <c r="D309" s="171"/>
+      <c r="C309" s="196"/>
+      <c r="D309" s="181"/>
       <c r="E309" s="8" t="s">
         <v>401</v>
       </c>
@@ -11860,8 +12572,8 @@
       <c r="B310" s="7">
         <v>3</v>
       </c>
-      <c r="C310" s="186"/>
-      <c r="D310" s="171"/>
+      <c r="C310" s="196"/>
+      <c r="D310" s="181"/>
       <c r="E310" s="13" t="s">
         <v>402</v>
       </c>
@@ -11882,8 +12594,8 @@
       <c r="B311" s="7">
         <v>4</v>
       </c>
-      <c r="C311" s="186"/>
-      <c r="D311" s="171"/>
+      <c r="C311" s="196"/>
+      <c r="D311" s="181"/>
       <c r="E311" s="8" t="s">
         <v>403</v>
       </c>
@@ -11904,8 +12616,8 @@
       <c r="B312" s="7">
         <v>5</v>
       </c>
-      <c r="C312" s="186"/>
-      <c r="D312" s="171"/>
+      <c r="C312" s="196"/>
+      <c r="D312" s="181"/>
       <c r="E312" s="13" t="s">
         <v>404</v>
       </c>
@@ -11926,8 +12638,8 @@
       <c r="B313" s="7">
         <v>6</v>
       </c>
-      <c r="C313" s="186"/>
-      <c r="D313" s="171"/>
+      <c r="C313" s="196"/>
+      <c r="D313" s="181"/>
       <c r="E313" s="13" t="s">
         <v>405</v>
       </c>
@@ -11948,8 +12660,8 @@
       <c r="B314" s="7">
         <v>7</v>
       </c>
-      <c r="C314" s="186"/>
-      <c r="D314" s="172"/>
+      <c r="C314" s="196"/>
+      <c r="D314" s="182"/>
       <c r="E314" s="8" t="s">
         <v>406</v>
       </c>
@@ -11970,8 +12682,8 @@
       <c r="B315" s="7">
         <v>8</v>
       </c>
-      <c r="C315" s="186"/>
-      <c r="D315" s="170" t="s">
+      <c r="C315" s="196"/>
+      <c r="D315" s="180" t="s">
         <v>407</v>
       </c>
       <c r="E315" s="13" t="s">
@@ -11994,8 +12706,8 @@
       <c r="B316" s="7">
         <v>9</v>
       </c>
-      <c r="C316" s="186"/>
-      <c r="D316" s="171"/>
+      <c r="C316" s="196"/>
+      <c r="D316" s="181"/>
       <c r="E316" s="8" t="s">
         <v>409</v>
       </c>
@@ -12016,8 +12728,8 @@
       <c r="B317" s="24">
         <v>10</v>
       </c>
-      <c r="C317" s="187"/>
-      <c r="D317" s="172"/>
+      <c r="C317" s="197"/>
+      <c r="D317" s="182"/>
       <c r="E317" s="17" t="s">
         <v>410</v>
       </c>
@@ -12038,10 +12750,10 @@
       <c r="B318" s="7">
         <v>1</v>
       </c>
-      <c r="C318" s="188" t="s">
+      <c r="C318" s="198" t="s">
         <v>411</v>
       </c>
-      <c r="D318" s="170" t="s">
+      <c r="D318" s="180" t="s">
         <v>412</v>
       </c>
       <c r="E318" s="8" t="s">
@@ -12064,8 +12776,8 @@
       <c r="B319" s="7">
         <v>2</v>
       </c>
-      <c r="C319" s="189"/>
-      <c r="D319" s="171"/>
+      <c r="C319" s="199"/>
+      <c r="D319" s="181"/>
       <c r="E319" s="13" t="s">
         <v>414</v>
       </c>
@@ -12086,8 +12798,8 @@
       <c r="B320" s="7">
         <v>3</v>
       </c>
-      <c r="C320" s="189"/>
-      <c r="D320" s="171"/>
+      <c r="C320" s="199"/>
+      <c r="D320" s="181"/>
       <c r="E320" s="8" t="s">
         <v>415</v>
       </c>
@@ -12108,8 +12820,8 @@
       <c r="B321" s="7">
         <v>4</v>
       </c>
-      <c r="C321" s="189"/>
-      <c r="D321" s="171"/>
+      <c r="C321" s="199"/>
+      <c r="D321" s="181"/>
       <c r="E321" s="8" t="s">
         <v>416</v>
       </c>
@@ -12130,8 +12842,8 @@
       <c r="B322" s="7">
         <v>5</v>
       </c>
-      <c r="C322" s="189"/>
-      <c r="D322" s="171"/>
+      <c r="C322" s="199"/>
+      <c r="D322" s="181"/>
       <c r="E322" s="8" t="s">
         <v>417</v>
       </c>
@@ -12152,8 +12864,8 @@
       <c r="B323" s="7">
         <v>6</v>
       </c>
-      <c r="C323" s="189"/>
-      <c r="D323" s="172"/>
+      <c r="C323" s="199"/>
+      <c r="D323" s="182"/>
       <c r="E323" s="29" t="s">
         <v>418</v>
       </c>
@@ -12174,8 +12886,8 @@
       <c r="B324" s="7">
         <v>7</v>
       </c>
-      <c r="C324" s="189"/>
-      <c r="D324" s="170" t="s">
+      <c r="C324" s="199"/>
+      <c r="D324" s="180" t="s">
         <v>419</v>
       </c>
       <c r="E324" s="13" t="s">
@@ -12198,8 +12910,8 @@
       <c r="B325" s="7">
         <v>8</v>
       </c>
-      <c r="C325" s="189"/>
-      <c r="D325" s="171"/>
+      <c r="C325" s="199"/>
+      <c r="D325" s="181"/>
       <c r="E325" s="8" t="s">
         <v>421</v>
       </c>
@@ -12220,8 +12932,8 @@
       <c r="B326" s="7">
         <v>9</v>
       </c>
-      <c r="C326" s="189"/>
-      <c r="D326" s="171"/>
+      <c r="C326" s="199"/>
+      <c r="D326" s="181"/>
       <c r="E326" s="8" t="s">
         <v>422</v>
       </c>
@@ -12242,8 +12954,8 @@
       <c r="B327" s="7">
         <v>10</v>
       </c>
-      <c r="C327" s="189"/>
-      <c r="D327" s="171"/>
+      <c r="C327" s="199"/>
+      <c r="D327" s="181"/>
       <c r="E327" s="8" t="s">
         <v>423</v>
       </c>
@@ -12264,8 +12976,8 @@
       <c r="B328" s="7">
         <v>11</v>
       </c>
-      <c r="C328" s="189"/>
-      <c r="D328" s="172"/>
+      <c r="C328" s="199"/>
+      <c r="D328" s="182"/>
       <c r="E328" s="13" t="s">
         <v>424</v>
       </c>
@@ -12286,8 +12998,8 @@
       <c r="B329" s="7">
         <v>12</v>
       </c>
-      <c r="C329" s="189"/>
-      <c r="D329" s="170" t="s">
+      <c r="C329" s="199"/>
+      <c r="D329" s="180" t="s">
         <v>425</v>
       </c>
       <c r="E329" s="8" t="s">
@@ -12310,8 +13022,8 @@
       <c r="B330" s="7">
         <v>13</v>
       </c>
-      <c r="C330" s="189"/>
-      <c r="D330" s="171"/>
+      <c r="C330" s="199"/>
+      <c r="D330" s="181"/>
       <c r="E330" s="8" t="s">
         <v>427</v>
       </c>
@@ -12332,8 +13044,8 @@
       <c r="B331" s="7">
         <v>14</v>
       </c>
-      <c r="C331" s="189"/>
-      <c r="D331" s="171"/>
+      <c r="C331" s="199"/>
+      <c r="D331" s="181"/>
       <c r="E331" s="8" t="s">
         <v>428</v>
       </c>
@@ -12354,8 +13066,8 @@
       <c r="B332" s="7">
         <v>15</v>
       </c>
-      <c r="C332" s="189"/>
-      <c r="D332" s="171"/>
+      <c r="C332" s="199"/>
+      <c r="D332" s="181"/>
       <c r="E332" s="8" t="s">
         <v>429</v>
       </c>
@@ -12376,8 +13088,8 @@
       <c r="B333" s="7">
         <v>16</v>
       </c>
-      <c r="C333" s="189"/>
-      <c r="D333" s="171"/>
+      <c r="C333" s="199"/>
+      <c r="D333" s="181"/>
       <c r="E333" s="8" t="s">
         <v>430</v>
       </c>
@@ -12398,8 +13110,8 @@
       <c r="B334" s="7">
         <v>17</v>
       </c>
-      <c r="C334" s="189"/>
-      <c r="D334" s="171"/>
+      <c r="C334" s="199"/>
+      <c r="D334" s="181"/>
       <c r="E334" s="8" t="s">
         <v>431</v>
       </c>
@@ -12420,8 +13132,8 @@
       <c r="B335" s="7">
         <v>18</v>
       </c>
-      <c r="C335" s="189"/>
-      <c r="D335" s="171"/>
+      <c r="C335" s="199"/>
+      <c r="D335" s="181"/>
       <c r="E335" s="8" t="s">
         <v>432</v>
       </c>
@@ -12442,8 +13154,8 @@
       <c r="B336" s="7">
         <v>19</v>
       </c>
-      <c r="C336" s="189"/>
-      <c r="D336" s="171"/>
+      <c r="C336" s="199"/>
+      <c r="D336" s="181"/>
       <c r="E336" s="8" t="s">
         <v>433</v>
       </c>
@@ -12464,8 +13176,8 @@
       <c r="B337" s="7">
         <v>20</v>
       </c>
-      <c r="C337" s="189"/>
-      <c r="D337" s="172"/>
+      <c r="C337" s="199"/>
+      <c r="D337" s="182"/>
       <c r="E337" s="13" t="s">
         <v>434</v>
       </c>
@@ -12486,8 +13198,8 @@
       <c r="B338" s="7">
         <v>21</v>
       </c>
-      <c r="C338" s="189"/>
-      <c r="D338" s="170" t="s">
+      <c r="C338" s="199"/>
+      <c r="D338" s="180" t="s">
         <v>435</v>
       </c>
       <c r="E338" s="13" t="s">
@@ -12510,8 +13222,8 @@
       <c r="B339" s="7">
         <v>22</v>
       </c>
-      <c r="C339" s="189"/>
-      <c r="D339" s="171"/>
+      <c r="C339" s="199"/>
+      <c r="D339" s="181"/>
       <c r="E339" s="13" t="s">
         <v>437</v>
       </c>
@@ -12532,8 +13244,8 @@
       <c r="B340" s="7">
         <v>23</v>
       </c>
-      <c r="C340" s="189"/>
-      <c r="D340" s="171"/>
+      <c r="C340" s="199"/>
+      <c r="D340" s="181"/>
       <c r="E340" s="13" t="s">
         <v>438</v>
       </c>
@@ -12554,8 +13266,8 @@
       <c r="B341" s="7">
         <v>24</v>
       </c>
-      <c r="C341" s="189"/>
-      <c r="D341" s="171"/>
+      <c r="C341" s="199"/>
+      <c r="D341" s="181"/>
       <c r="E341" s="13" t="s">
         <v>439</v>
       </c>
@@ -12576,8 +13288,8 @@
       <c r="B342" s="24">
         <v>25</v>
       </c>
-      <c r="C342" s="190"/>
-      <c r="D342" s="172"/>
+      <c r="C342" s="200"/>
+      <c r="D342" s="182"/>
       <c r="E342" s="25" t="s">
         <v>440</v>
       </c>
@@ -12598,10 +13310,10 @@
       <c r="B343" s="7">
         <v>1</v>
       </c>
-      <c r="C343" s="155" t="s">
+      <c r="C343" s="165" t="s">
         <v>441</v>
       </c>
-      <c r="D343" s="140" t="s">
+      <c r="D343" s="150" t="s">
         <v>442</v>
       </c>
       <c r="E343" s="8" t="s">
@@ -12630,8 +13342,8 @@
       <c r="B344" s="7">
         <v>2</v>
       </c>
-      <c r="C344" s="156"/>
-      <c r="D344" s="141"/>
+      <c r="C344" s="166"/>
+      <c r="D344" s="151"/>
       <c r="E344" s="8" t="s">
         <v>444</v>
       </c>
@@ -12658,8 +13370,8 @@
       <c r="B345" s="7">
         <v>3</v>
       </c>
-      <c r="C345" s="156"/>
-      <c r="D345" s="141"/>
+      <c r="C345" s="166"/>
+      <c r="D345" s="151"/>
       <c r="E345" s="8" t="s">
         <v>445</v>
       </c>
@@ -12686,8 +13398,8 @@
       <c r="B346" s="7">
         <v>4</v>
       </c>
-      <c r="C346" s="156"/>
-      <c r="D346" s="141"/>
+      <c r="C346" s="166"/>
+      <c r="D346" s="151"/>
       <c r="E346" s="8" t="s">
         <v>446</v>
       </c>
@@ -12714,8 +13426,8 @@
       <c r="B347" s="7">
         <v>5</v>
       </c>
-      <c r="C347" s="156"/>
-      <c r="D347" s="142"/>
+      <c r="C347" s="166"/>
+      <c r="D347" s="152"/>
       <c r="E347" s="8" t="s">
         <v>447</v>
       </c>
@@ -12742,8 +13454,8 @@
       <c r="B348" s="7">
         <v>6</v>
       </c>
-      <c r="C348" s="156"/>
-      <c r="D348" s="140" t="s">
+      <c r="C348" s="166"/>
+      <c r="D348" s="150" t="s">
         <v>448</v>
       </c>
       <c r="E348" s="8" t="s">
@@ -12770,8 +13482,8 @@
       <c r="B349" s="7">
         <v>7</v>
       </c>
-      <c r="C349" s="156"/>
-      <c r="D349" s="141"/>
+      <c r="C349" s="166"/>
+      <c r="D349" s="151"/>
       <c r="E349" s="8" t="s">
         <v>450</v>
       </c>
@@ -12798,8 +13510,8 @@
       <c r="B350" s="7">
         <v>8</v>
       </c>
-      <c r="C350" s="156"/>
-      <c r="D350" s="141"/>
+      <c r="C350" s="166"/>
+      <c r="D350" s="151"/>
       <c r="E350" s="8" t="s">
         <v>451</v>
       </c>
@@ -12826,8 +13538,8 @@
       <c r="B351" s="7">
         <v>9</v>
       </c>
-      <c r="C351" s="156"/>
-      <c r="D351" s="141"/>
+      <c r="C351" s="166"/>
+      <c r="D351" s="151"/>
       <c r="E351" s="8" t="s">
         <v>452</v>
       </c>
@@ -12850,8 +13562,8 @@
       <c r="B352" s="7">
         <v>10</v>
       </c>
-      <c r="C352" s="156"/>
-      <c r="D352" s="141"/>
+      <c r="C352" s="166"/>
+      <c r="D352" s="151"/>
       <c r="E352" s="8" t="s">
         <v>453</v>
       </c>
@@ -12878,8 +13590,8 @@
       <c r="B353" s="7">
         <v>11</v>
       </c>
-      <c r="C353" s="156"/>
-      <c r="D353" s="142"/>
+      <c r="C353" s="166"/>
+      <c r="D353" s="152"/>
       <c r="E353" s="8" t="s">
         <v>454</v>
       </c>
@@ -12900,8 +13612,8 @@
       <c r="B354" s="7">
         <v>12</v>
       </c>
-      <c r="C354" s="156"/>
-      <c r="D354" s="140" t="s">
+      <c r="C354" s="166"/>
+      <c r="D354" s="150" t="s">
         <v>455</v>
       </c>
       <c r="E354" s="8" t="s">
@@ -12928,8 +13640,8 @@
       <c r="B355" s="7">
         <v>13</v>
       </c>
-      <c r="C355" s="156"/>
-      <c r="D355" s="141"/>
+      <c r="C355" s="166"/>
+      <c r="D355" s="151"/>
       <c r="E355" s="8" t="s">
         <v>457</v>
       </c>
@@ -12956,8 +13668,8 @@
       <c r="B356" s="7">
         <v>14</v>
       </c>
-      <c r="C356" s="156"/>
-      <c r="D356" s="141"/>
+      <c r="C356" s="166"/>
+      <c r="D356" s="151"/>
       <c r="E356" s="8" t="s">
         <v>458</v>
       </c>
@@ -12978,8 +13690,8 @@
       <c r="B357" s="7">
         <v>15</v>
       </c>
-      <c r="C357" s="157"/>
-      <c r="D357" s="142"/>
+      <c r="C357" s="167"/>
+      <c r="D357" s="152"/>
       <c r="E357" s="8" t="s">
         <v>459</v>
       </c>
@@ -12994,18 +13706,18 @@
       <c r="J357" s="11"/>
     </row>
     <row r="358" spans="1:10" ht="13.8">
-      <c r="A358" s="179" t="s">
+      <c r="A358" s="189" t="s">
         <v>460</v>
       </c>
-      <c r="B358" s="180"/>
-      <c r="C358" s="180"/>
-      <c r="D358" s="180"/>
-      <c r="E358" s="180"/>
-      <c r="F358" s="180"/>
-      <c r="G358" s="180"/>
-      <c r="H358" s="180"/>
-      <c r="I358" s="180"/>
-      <c r="J358" s="181"/>
+      <c r="B358" s="190"/>
+      <c r="C358" s="190"/>
+      <c r="D358" s="190"/>
+      <c r="E358" s="190"/>
+      <c r="F358" s="190"/>
+      <c r="G358" s="190"/>
+      <c r="H358" s="190"/>
+      <c r="I358" s="190"/>
+      <c r="J358" s="191"/>
     </row>
     <row r="359" spans="1:10" ht="13.8">
       <c r="A359" s="6">
@@ -13014,10 +13726,10 @@
       <c r="B359" s="7">
         <v>1</v>
       </c>
-      <c r="C359" s="158" t="s">
+      <c r="C359" s="168" t="s">
         <v>461</v>
       </c>
-      <c r="D359" s="140" t="s">
+      <c r="D359" s="150" t="s">
         <v>462</v>
       </c>
       <c r="E359" s="8" t="s">
@@ -13040,8 +13752,8 @@
       <c r="B360" s="7">
         <v>2</v>
       </c>
-      <c r="C360" s="159"/>
-      <c r="D360" s="141"/>
+      <c r="C360" s="169"/>
+      <c r="D360" s="151"/>
       <c r="E360" s="8" t="s">
         <v>464</v>
       </c>
@@ -13062,8 +13774,8 @@
       <c r="B361" s="7">
         <v>3</v>
       </c>
-      <c r="C361" s="159"/>
-      <c r="D361" s="141"/>
+      <c r="C361" s="169"/>
+      <c r="D361" s="151"/>
       <c r="E361" s="8" t="s">
         <v>465</v>
       </c>
@@ -13084,8 +13796,8 @@
       <c r="B362" s="7">
         <v>4</v>
       </c>
-      <c r="C362" s="159"/>
-      <c r="D362" s="141"/>
+      <c r="C362" s="169"/>
+      <c r="D362" s="151"/>
       <c r="E362" s="8" t="s">
         <v>466</v>
       </c>
@@ -13106,8 +13818,8 @@
       <c r="B363" s="7">
         <v>5</v>
       </c>
-      <c r="C363" s="159"/>
-      <c r="D363" s="142"/>
+      <c r="C363" s="169"/>
+      <c r="D363" s="152"/>
       <c r="E363" s="8" t="s">
         <v>467</v>
       </c>
@@ -13128,8 +13840,8 @@
       <c r="B364" s="7">
         <v>6</v>
       </c>
-      <c r="C364" s="159"/>
-      <c r="D364" s="140" t="s">
+      <c r="C364" s="169"/>
+      <c r="D364" s="150" t="s">
         <v>468</v>
       </c>
       <c r="E364" s="8" t="s">
@@ -13152,8 +13864,8 @@
       <c r="B365" s="7">
         <v>7</v>
       </c>
-      <c r="C365" s="159"/>
-      <c r="D365" s="141"/>
+      <c r="C365" s="169"/>
+      <c r="D365" s="151"/>
       <c r="E365" s="8" t="s">
         <v>470</v>
       </c>
@@ -13174,8 +13886,8 @@
       <c r="B366" s="7">
         <v>8</v>
       </c>
-      <c r="C366" s="159"/>
-      <c r="D366" s="141"/>
+      <c r="C366" s="169"/>
+      <c r="D366" s="151"/>
       <c r="E366" s="8" t="s">
         <v>471</v>
       </c>
@@ -13196,8 +13908,8 @@
       <c r="B367" s="7">
         <v>9</v>
       </c>
-      <c r="C367" s="159"/>
-      <c r="D367" s="141"/>
+      <c r="C367" s="169"/>
+      <c r="D367" s="151"/>
       <c r="E367" s="8" t="s">
         <v>472</v>
       </c>
@@ -13218,8 +13930,8 @@
       <c r="B368" s="7">
         <v>10</v>
       </c>
-      <c r="C368" s="159"/>
-      <c r="D368" s="141"/>
+      <c r="C368" s="169"/>
+      <c r="D368" s="151"/>
       <c r="E368" s="8" t="s">
         <v>473</v>
       </c>
@@ -13240,8 +13952,8 @@
       <c r="B369" s="7">
         <v>11</v>
       </c>
-      <c r="C369" s="159"/>
-      <c r="D369" s="141"/>
+      <c r="C369" s="169"/>
+      <c r="D369" s="151"/>
       <c r="E369" s="8" t="s">
         <v>474</v>
       </c>
@@ -13262,8 +13974,8 @@
       <c r="B370" s="7">
         <v>12</v>
       </c>
-      <c r="C370" s="159"/>
-      <c r="D370" s="141"/>
+      <c r="C370" s="169"/>
+      <c r="D370" s="151"/>
       <c r="E370" s="8" t="s">
         <v>475</v>
       </c>
@@ -13284,8 +13996,8 @@
       <c r="B371" s="7">
         <v>13</v>
       </c>
-      <c r="C371" s="159"/>
-      <c r="D371" s="142"/>
+      <c r="C371" s="169"/>
+      <c r="D371" s="152"/>
       <c r="E371" s="8" t="s">
         <v>476</v>
       </c>
@@ -13306,8 +14018,8 @@
       <c r="B372" s="7">
         <v>14</v>
       </c>
-      <c r="C372" s="159"/>
-      <c r="D372" s="140" t="s">
+      <c r="C372" s="169"/>
+      <c r="D372" s="150" t="s">
         <v>477</v>
       </c>
       <c r="E372" s="8" t="s">
@@ -13330,8 +14042,8 @@
       <c r="B373" s="7">
         <v>15</v>
       </c>
-      <c r="C373" s="159"/>
-      <c r="D373" s="141"/>
+      <c r="C373" s="169"/>
+      <c r="D373" s="151"/>
       <c r="E373" s="11" t="s">
         <v>479</v>
       </c>
@@ -13352,8 +14064,8 @@
       <c r="B374" s="7">
         <v>16</v>
       </c>
-      <c r="C374" s="159"/>
-      <c r="D374" s="141"/>
+      <c r="C374" s="169"/>
+      <c r="D374" s="151"/>
       <c r="E374" s="8" t="s">
         <v>480</v>
       </c>
@@ -13374,8 +14086,8 @@
       <c r="B375" s="7">
         <v>17</v>
       </c>
-      <c r="C375" s="159"/>
-      <c r="D375" s="142"/>
+      <c r="C375" s="169"/>
+      <c r="D375" s="152"/>
       <c r="E375" s="8" t="s">
         <v>481</v>
       </c>
@@ -13396,8 +14108,8 @@
       <c r="B376" s="7">
         <v>18</v>
       </c>
-      <c r="C376" s="159"/>
-      <c r="D376" s="140" t="s">
+      <c r="C376" s="169"/>
+      <c r="D376" s="150" t="s">
         <v>482</v>
       </c>
       <c r="E376" s="8" t="s">
@@ -13420,8 +14132,8 @@
       <c r="B377" s="7">
         <v>19</v>
       </c>
-      <c r="C377" s="159"/>
-      <c r="D377" s="141"/>
+      <c r="C377" s="169"/>
+      <c r="D377" s="151"/>
       <c r="E377" s="8" t="s">
         <v>484</v>
       </c>
@@ -13442,8 +14154,8 @@
       <c r="B378" s="7">
         <v>20</v>
       </c>
-      <c r="C378" s="159"/>
-      <c r="D378" s="141"/>
+      <c r="C378" s="169"/>
+      <c r="D378" s="151"/>
       <c r="E378" s="8" t="s">
         <v>485</v>
       </c>
@@ -13464,8 +14176,8 @@
       <c r="B379" s="7">
         <v>21</v>
       </c>
-      <c r="C379" s="159"/>
-      <c r="D379" s="141"/>
+      <c r="C379" s="169"/>
+      <c r="D379" s="151"/>
       <c r="E379" s="8" t="s">
         <v>486</v>
       </c>
@@ -13486,8 +14198,8 @@
       <c r="B380" s="24">
         <v>22</v>
       </c>
-      <c r="C380" s="160"/>
-      <c r="D380" s="142"/>
+      <c r="C380" s="170"/>
+      <c r="D380" s="152"/>
       <c r="E380" s="17" t="s">
         <v>487</v>
       </c>
@@ -13508,10 +14220,10 @@
       <c r="B381" s="7">
         <v>1</v>
       </c>
-      <c r="C381" s="149" t="s">
+      <c r="C381" s="159" t="s">
         <v>488</v>
       </c>
-      <c r="D381" s="140" t="s">
+      <c r="D381" s="150" t="s">
         <v>489</v>
       </c>
       <c r="E381" s="8" t="s">
@@ -13534,8 +14246,8 @@
       <c r="B382" s="7">
         <v>2</v>
       </c>
-      <c r="C382" s="150"/>
-      <c r="D382" s="141"/>
+      <c r="C382" s="160"/>
+      <c r="D382" s="151"/>
       <c r="E382" s="8" t="s">
         <v>491</v>
       </c>
@@ -13556,8 +14268,8 @@
       <c r="B383" s="7">
         <v>3</v>
       </c>
-      <c r="C383" s="150"/>
-      <c r="D383" s="141"/>
+      <c r="C383" s="160"/>
+      <c r="D383" s="151"/>
       <c r="E383" s="8" t="s">
         <v>492</v>
       </c>
@@ -13578,8 +14290,8 @@
       <c r="B384" s="7">
         <v>4</v>
       </c>
-      <c r="C384" s="150"/>
-      <c r="D384" s="141"/>
+      <c r="C384" s="160"/>
+      <c r="D384" s="151"/>
       <c r="E384" s="8" t="s">
         <v>493</v>
       </c>
@@ -13600,8 +14312,8 @@
       <c r="B385" s="7">
         <v>5</v>
       </c>
-      <c r="C385" s="150"/>
-      <c r="D385" s="141"/>
+      <c r="C385" s="160"/>
+      <c r="D385" s="151"/>
       <c r="E385" s="8" t="s">
         <v>494</v>
       </c>
@@ -13622,8 +14334,8 @@
       <c r="B386" s="7">
         <v>6</v>
       </c>
-      <c r="C386" s="150"/>
-      <c r="D386" s="142"/>
+      <c r="C386" s="160"/>
+      <c r="D386" s="152"/>
       <c r="E386" s="8" t="s">
         <v>495</v>
       </c>
@@ -13644,8 +14356,8 @@
       <c r="B387" s="7">
         <v>7</v>
       </c>
-      <c r="C387" s="150"/>
-      <c r="D387" s="140" t="s">
+      <c r="C387" s="160"/>
+      <c r="D387" s="150" t="s">
         <v>496</v>
       </c>
       <c r="E387" s="8" t="s">
@@ -13668,8 +14380,8 @@
       <c r="B388" s="7">
         <v>8</v>
       </c>
-      <c r="C388" s="150"/>
-      <c r="D388" s="141"/>
+      <c r="C388" s="160"/>
+      <c r="D388" s="151"/>
       <c r="E388" s="8" t="s">
         <v>498</v>
       </c>
@@ -13690,8 +14402,8 @@
       <c r="B389" s="7">
         <v>9</v>
       </c>
-      <c r="C389" s="150"/>
-      <c r="D389" s="141"/>
+      <c r="C389" s="160"/>
+      <c r="D389" s="151"/>
       <c r="E389" s="8" t="s">
         <v>499</v>
       </c>
@@ -13712,8 +14424,8 @@
       <c r="B390" s="7">
         <v>10</v>
       </c>
-      <c r="C390" s="150"/>
-      <c r="D390" s="141"/>
+      <c r="C390" s="160"/>
+      <c r="D390" s="151"/>
       <c r="E390" s="8" t="s">
         <v>500</v>
       </c>
@@ -13734,8 +14446,8 @@
       <c r="B391" s="7">
         <v>11</v>
       </c>
-      <c r="C391" s="150"/>
-      <c r="D391" s="141"/>
+      <c r="C391" s="160"/>
+      <c r="D391" s="151"/>
       <c r="E391" s="8" t="s">
         <v>501</v>
       </c>
@@ -13756,8 +14468,8 @@
       <c r="B392" s="7">
         <v>12</v>
       </c>
-      <c r="C392" s="150"/>
-      <c r="D392" s="141"/>
+      <c r="C392" s="160"/>
+      <c r="D392" s="151"/>
       <c r="E392" s="8" t="s">
         <v>502</v>
       </c>
@@ -13778,8 +14490,8 @@
       <c r="B393" s="7">
         <v>13</v>
       </c>
-      <c r="C393" s="150"/>
-      <c r="D393" s="141"/>
+      <c r="C393" s="160"/>
+      <c r="D393" s="151"/>
       <c r="E393" s="8" t="s">
         <v>503</v>
       </c>
@@ -13800,8 +14512,8 @@
       <c r="B394" s="7">
         <v>14</v>
       </c>
-      <c r="C394" s="150"/>
-      <c r="D394" s="141"/>
+      <c r="C394" s="160"/>
+      <c r="D394" s="151"/>
       <c r="E394" s="8" t="s">
         <v>504</v>
       </c>
@@ -13822,8 +14534,8 @@
       <c r="B395" s="7">
         <v>15</v>
       </c>
-      <c r="C395" s="150"/>
-      <c r="D395" s="141"/>
+      <c r="C395" s="160"/>
+      <c r="D395" s="151"/>
       <c r="E395" s="8" t="s">
         <v>505</v>
       </c>
@@ -13844,8 +14556,8 @@
       <c r="B396" s="7">
         <v>16</v>
       </c>
-      <c r="C396" s="150"/>
-      <c r="D396" s="142"/>
+      <c r="C396" s="160"/>
+      <c r="D396" s="152"/>
       <c r="E396" s="8" t="s">
         <v>506</v>
       </c>
@@ -13866,8 +14578,8 @@
       <c r="B397" s="7">
         <v>17</v>
       </c>
-      <c r="C397" s="150"/>
-      <c r="D397" s="140" t="s">
+      <c r="C397" s="160"/>
+      <c r="D397" s="150" t="s">
         <v>507</v>
       </c>
       <c r="E397" s="8" t="s">
@@ -13890,8 +14602,8 @@
       <c r="B398" s="7">
         <v>18</v>
       </c>
-      <c r="C398" s="150"/>
-      <c r="D398" s="141"/>
+      <c r="C398" s="160"/>
+      <c r="D398" s="151"/>
       <c r="E398" s="8" t="s">
         <v>509</v>
       </c>
@@ -13912,8 +14624,8 @@
       <c r="B399" s="7">
         <v>19</v>
       </c>
-      <c r="C399" s="150"/>
-      <c r="D399" s="142"/>
+      <c r="C399" s="160"/>
+      <c r="D399" s="152"/>
       <c r="E399" s="8" t="s">
         <v>510</v>
       </c>
@@ -13934,8 +14646,8 @@
       <c r="B400" s="7">
         <v>20</v>
       </c>
-      <c r="C400" s="150"/>
-      <c r="D400" s="140" t="s">
+      <c r="C400" s="160"/>
+      <c r="D400" s="150" t="s">
         <v>511</v>
       </c>
       <c r="E400" s="8" t="s">
@@ -13958,8 +14670,8 @@
       <c r="B401" s="7">
         <v>21</v>
       </c>
-      <c r="C401" s="150"/>
-      <c r="D401" s="141"/>
+      <c r="C401" s="160"/>
+      <c r="D401" s="151"/>
       <c r="E401" s="8" t="s">
         <v>513</v>
       </c>
@@ -13980,8 +14692,8 @@
       <c r="B402" s="7">
         <v>22</v>
       </c>
-      <c r="C402" s="150"/>
-      <c r="D402" s="141"/>
+      <c r="C402" s="160"/>
+      <c r="D402" s="151"/>
       <c r="E402" s="8" t="s">
         <v>514</v>
       </c>
@@ -14002,8 +14714,8 @@
       <c r="B403" s="7">
         <v>23</v>
       </c>
-      <c r="C403" s="150"/>
-      <c r="D403" s="141"/>
+      <c r="C403" s="160"/>
+      <c r="D403" s="151"/>
       <c r="E403" s="8" t="s">
         <v>515</v>
       </c>
@@ -14024,8 +14736,8 @@
       <c r="B404" s="7">
         <v>24</v>
       </c>
-      <c r="C404" s="150"/>
-      <c r="D404" s="142"/>
+      <c r="C404" s="160"/>
+      <c r="D404" s="152"/>
       <c r="E404" s="8" t="s">
         <v>516</v>
       </c>
@@ -14046,8 +14758,8 @@
       <c r="B405" s="7">
         <v>25</v>
       </c>
-      <c r="C405" s="150"/>
-      <c r="D405" s="140" t="s">
+      <c r="C405" s="160"/>
+      <c r="D405" s="150" t="s">
         <v>517</v>
       </c>
       <c r="E405" s="8" t="s">
@@ -14070,8 +14782,8 @@
       <c r="B406" s="7">
         <v>26</v>
       </c>
-      <c r="C406" s="150"/>
-      <c r="D406" s="141"/>
+      <c r="C406" s="160"/>
+      <c r="D406" s="151"/>
       <c r="E406" s="8" t="s">
         <v>519</v>
       </c>
@@ -14092,8 +14804,8 @@
       <c r="B407" s="7">
         <v>27</v>
       </c>
-      <c r="C407" s="150"/>
-      <c r="D407" s="141"/>
+      <c r="C407" s="160"/>
+      <c r="D407" s="151"/>
       <c r="E407" s="8" t="s">
         <v>520</v>
       </c>
@@ -14114,8 +14826,8 @@
       <c r="B408" s="7">
         <v>28</v>
       </c>
-      <c r="C408" s="150"/>
-      <c r="D408" s="141"/>
+      <c r="C408" s="160"/>
+      <c r="D408" s="151"/>
       <c r="E408" s="8" t="s">
         <v>521</v>
       </c>
@@ -14136,8 +14848,8 @@
       <c r="B409" s="7">
         <v>29</v>
       </c>
-      <c r="C409" s="150"/>
-      <c r="D409" s="141"/>
+      <c r="C409" s="160"/>
+      <c r="D409" s="151"/>
       <c r="E409" s="8" t="s">
         <v>522</v>
       </c>
@@ -14158,8 +14870,8 @@
       <c r="B410" s="7">
         <v>30</v>
       </c>
-      <c r="C410" s="150"/>
-      <c r="D410" s="141"/>
+      <c r="C410" s="160"/>
+      <c r="D410" s="151"/>
       <c r="E410" s="8" t="s">
         <v>523</v>
       </c>
@@ -14180,8 +14892,8 @@
       <c r="B411" s="7">
         <v>31</v>
       </c>
-      <c r="C411" s="150"/>
-      <c r="D411" s="141"/>
+      <c r="C411" s="160"/>
+      <c r="D411" s="151"/>
       <c r="E411" s="8" t="s">
         <v>524</v>
       </c>
@@ -14202,8 +14914,8 @@
       <c r="B412" s="7">
         <v>32</v>
       </c>
-      <c r="C412" s="150"/>
-      <c r="D412" s="141"/>
+      <c r="C412" s="160"/>
+      <c r="D412" s="151"/>
       <c r="E412" s="8" t="s">
         <v>525</v>
       </c>
@@ -14224,8 +14936,8 @@
       <c r="B413" s="7">
         <v>33</v>
       </c>
-      <c r="C413" s="150"/>
-      <c r="D413" s="141"/>
+      <c r="C413" s="160"/>
+      <c r="D413" s="151"/>
       <c r="E413" s="8" t="s">
         <v>526</v>
       </c>
@@ -14246,8 +14958,8 @@
       <c r="B414" s="7">
         <v>34</v>
       </c>
-      <c r="C414" s="150"/>
-      <c r="D414" s="141"/>
+      <c r="C414" s="160"/>
+      <c r="D414" s="151"/>
       <c r="E414" s="8" t="s">
         <v>527</v>
       </c>
@@ -14268,8 +14980,8 @@
       <c r="B415" s="7">
         <v>35</v>
       </c>
-      <c r="C415" s="150"/>
-      <c r="D415" s="141"/>
+      <c r="C415" s="160"/>
+      <c r="D415" s="151"/>
       <c r="E415" s="8" t="s">
         <v>528</v>
       </c>
@@ -14290,8 +15002,8 @@
       <c r="B416" s="7">
         <v>36</v>
       </c>
-      <c r="C416" s="150"/>
-      <c r="D416" s="142"/>
+      <c r="C416" s="160"/>
+      <c r="D416" s="152"/>
       <c r="E416" s="8" t="s">
         <v>529</v>
       </c>
@@ -14312,8 +15024,8 @@
       <c r="B417" s="7">
         <v>37</v>
       </c>
-      <c r="C417" s="150"/>
-      <c r="D417" s="140" t="s">
+      <c r="C417" s="160"/>
+      <c r="D417" s="150" t="s">
         <v>530</v>
       </c>
       <c r="E417" s="8" t="s">
@@ -14336,8 +15048,8 @@
       <c r="B418" s="7">
         <v>38</v>
       </c>
-      <c r="C418" s="150"/>
-      <c r="D418" s="141"/>
+      <c r="C418" s="160"/>
+      <c r="D418" s="151"/>
       <c r="E418" s="8" t="s">
         <v>532</v>
       </c>
@@ -14358,8 +15070,8 @@
       <c r="B419" s="7">
         <v>39</v>
       </c>
-      <c r="C419" s="150"/>
-      <c r="D419" s="142"/>
+      <c r="C419" s="160"/>
+      <c r="D419" s="152"/>
       <c r="E419" s="8" t="s">
         <v>533</v>
       </c>
@@ -14380,8 +15092,8 @@
       <c r="B420" s="7">
         <v>40</v>
       </c>
-      <c r="C420" s="150"/>
-      <c r="D420" s="140" t="s">
+      <c r="C420" s="160"/>
+      <c r="D420" s="150" t="s">
         <v>534</v>
       </c>
       <c r="E420" s="8" t="s">
@@ -14404,8 +15116,8 @@
       <c r="B421" s="7">
         <v>41</v>
       </c>
-      <c r="C421" s="150"/>
-      <c r="D421" s="141"/>
+      <c r="C421" s="160"/>
+      <c r="D421" s="151"/>
       <c r="E421" s="8" t="s">
         <v>536</v>
       </c>
@@ -14426,8 +15138,8 @@
       <c r="B422" s="7">
         <v>42</v>
       </c>
-      <c r="C422" s="150"/>
-      <c r="D422" s="141"/>
+      <c r="C422" s="160"/>
+      <c r="D422" s="151"/>
       <c r="E422" s="8" t="s">
         <v>537</v>
       </c>
@@ -14448,8 +15160,8 @@
       <c r="B423" s="7">
         <v>43</v>
       </c>
-      <c r="C423" s="150"/>
-      <c r="D423" s="141"/>
+      <c r="C423" s="160"/>
+      <c r="D423" s="151"/>
       <c r="E423" s="8" t="s">
         <v>538</v>
       </c>
@@ -14470,8 +15182,8 @@
       <c r="B424" s="7">
         <v>44</v>
       </c>
-      <c r="C424" s="150"/>
-      <c r="D424" s="141"/>
+      <c r="C424" s="160"/>
+      <c r="D424" s="151"/>
       <c r="E424" s="8" t="s">
         <v>539</v>
       </c>
@@ -14492,8 +15204,8 @@
       <c r="B425" s="7">
         <v>45</v>
       </c>
-      <c r="C425" s="150"/>
-      <c r="D425" s="141"/>
+      <c r="C425" s="160"/>
+      <c r="D425" s="151"/>
       <c r="E425" s="8" t="s">
         <v>540</v>
       </c>
@@ -14514,8 +15226,8 @@
       <c r="B426" s="7">
         <v>46</v>
       </c>
-      <c r="C426" s="150"/>
-      <c r="D426" s="142"/>
+      <c r="C426" s="160"/>
+      <c r="D426" s="152"/>
       <c r="E426" s="8" t="s">
         <v>541</v>
       </c>
@@ -14536,8 +15248,8 @@
       <c r="B427" s="7">
         <v>47</v>
       </c>
-      <c r="C427" s="150"/>
-      <c r="D427" s="140" t="s">
+      <c r="C427" s="160"/>
+      <c r="D427" s="150" t="s">
         <v>542</v>
       </c>
       <c r="E427" s="8" t="s">
@@ -14558,8 +15270,8 @@
       <c r="B428" s="7">
         <v>48</v>
       </c>
-      <c r="C428" s="150"/>
-      <c r="D428" s="141"/>
+      <c r="C428" s="160"/>
+      <c r="D428" s="151"/>
       <c r="E428" s="8" t="s">
         <v>544</v>
       </c>
@@ -14580,8 +15292,8 @@
       <c r="B429" s="7">
         <v>49</v>
       </c>
-      <c r="C429" s="150"/>
-      <c r="D429" s="141"/>
+      <c r="C429" s="160"/>
+      <c r="D429" s="151"/>
       <c r="E429" s="8" t="s">
         <v>545</v>
       </c>
@@ -14602,8 +15314,8 @@
       <c r="B430" s="7">
         <v>50</v>
       </c>
-      <c r="C430" s="150"/>
-      <c r="D430" s="142"/>
+      <c r="C430" s="160"/>
+      <c r="D430" s="152"/>
       <c r="E430" s="8" t="s">
         <v>546</v>
       </c>
@@ -14624,8 +15336,8 @@
       <c r="B431" s="7">
         <v>51</v>
       </c>
-      <c r="C431" s="150"/>
-      <c r="D431" s="140" t="s">
+      <c r="C431" s="160"/>
+      <c r="D431" s="150" t="s">
         <v>547</v>
       </c>
       <c r="E431" s="8" t="s">
@@ -14648,8 +15360,8 @@
       <c r="B432" s="7">
         <v>52</v>
       </c>
-      <c r="C432" s="150"/>
-      <c r="D432" s="141"/>
+      <c r="C432" s="160"/>
+      <c r="D432" s="151"/>
       <c r="E432" s="8" t="s">
         <v>549</v>
       </c>
@@ -14670,8 +15382,8 @@
       <c r="B433" s="7">
         <v>53</v>
       </c>
-      <c r="C433" s="150"/>
-      <c r="D433" s="141"/>
+      <c r="C433" s="160"/>
+      <c r="D433" s="151"/>
       <c r="E433" s="8" t="s">
         <v>550</v>
       </c>
@@ -14692,8 +15404,8 @@
       <c r="B434" s="7">
         <v>54</v>
       </c>
-      <c r="C434" s="150"/>
-      <c r="D434" s="141"/>
+      <c r="C434" s="160"/>
+      <c r="D434" s="151"/>
       <c r="E434" s="8" t="s">
         <v>551</v>
       </c>
@@ -14714,8 +15426,8 @@
       <c r="B435" s="7">
         <v>55</v>
       </c>
-      <c r="C435" s="151"/>
-      <c r="D435" s="142"/>
+      <c r="C435" s="161"/>
+      <c r="D435" s="152"/>
       <c r="E435" s="8" t="s">
         <v>552</v>
       </c>
@@ -14730,18 +15442,18 @@
       <c r="J435" s="11"/>
     </row>
     <row r="436" spans="1:10" ht="13.8">
-      <c r="A436" s="182" t="s">
+      <c r="A436" s="192" t="s">
         <v>553</v>
       </c>
-      <c r="B436" s="183"/>
-      <c r="C436" s="183"/>
-      <c r="D436" s="183"/>
-      <c r="E436" s="183"/>
-      <c r="F436" s="183"/>
-      <c r="G436" s="183"/>
-      <c r="H436" s="183"/>
-      <c r="I436" s="183"/>
-      <c r="J436" s="184"/>
+      <c r="B436" s="193"/>
+      <c r="C436" s="193"/>
+      <c r="D436" s="193"/>
+      <c r="E436" s="193"/>
+      <c r="F436" s="193"/>
+      <c r="G436" s="193"/>
+      <c r="H436" s="193"/>
+      <c r="I436" s="193"/>
+      <c r="J436" s="194"/>
     </row>
     <row r="437" spans="1:10" ht="13.8">
       <c r="A437" s="6">
@@ -14750,10 +15462,10 @@
       <c r="B437" s="7">
         <v>1</v>
       </c>
-      <c r="C437" s="152" t="s">
+      <c r="C437" s="162" t="s">
         <v>554</v>
       </c>
-      <c r="D437" s="140" t="s">
+      <c r="D437" s="150" t="s">
         <v>555</v>
       </c>
       <c r="E437" s="29" t="s">
@@ -14776,8 +15488,8 @@
       <c r="B438" s="7">
         <v>2</v>
       </c>
-      <c r="C438" s="153"/>
-      <c r="D438" s="141"/>
+      <c r="C438" s="163"/>
+      <c r="D438" s="151"/>
       <c r="E438" s="8" t="s">
         <v>557</v>
       </c>
@@ -14796,8 +15508,8 @@
       <c r="B439" s="7">
         <v>3</v>
       </c>
-      <c r="C439" s="153"/>
-      <c r="D439" s="141"/>
+      <c r="C439" s="163"/>
+      <c r="D439" s="151"/>
       <c r="E439" s="8" t="s">
         <v>558</v>
       </c>
@@ -14818,8 +15530,8 @@
       <c r="B440" s="7">
         <v>4</v>
       </c>
-      <c r="C440" s="153"/>
-      <c r="D440" s="141"/>
+      <c r="C440" s="163"/>
+      <c r="D440" s="151"/>
       <c r="E440" s="29" t="s">
         <v>559</v>
       </c>
@@ -14840,8 +15552,8 @@
       <c r="B441" s="7">
         <v>5</v>
       </c>
-      <c r="C441" s="153"/>
-      <c r="D441" s="142"/>
+      <c r="C441" s="163"/>
+      <c r="D441" s="152"/>
       <c r="E441" s="8" t="s">
         <v>560</v>
       </c>
@@ -14862,8 +15574,8 @@
       <c r="B442" s="7">
         <v>6</v>
       </c>
-      <c r="C442" s="153"/>
-      <c r="D442" s="140" t="s">
+      <c r="C442" s="163"/>
+      <c r="D442" s="150" t="s">
         <v>561</v>
       </c>
       <c r="E442" s="29" t="s">
@@ -14886,8 +15598,8 @@
       <c r="B443" s="7">
         <v>7</v>
       </c>
-      <c r="C443" s="153"/>
-      <c r="D443" s="141"/>
+      <c r="C443" s="163"/>
+      <c r="D443" s="151"/>
       <c r="E443" s="8" t="s">
         <v>563</v>
       </c>
@@ -14908,8 +15620,8 @@
       <c r="B444" s="7">
         <v>8</v>
       </c>
-      <c r="C444" s="153"/>
-      <c r="D444" s="141"/>
+      <c r="C444" s="163"/>
+      <c r="D444" s="151"/>
       <c r="E444" s="29" t="s">
         <v>564</v>
       </c>
@@ -14930,8 +15642,8 @@
       <c r="B445" s="7">
         <v>9</v>
       </c>
-      <c r="C445" s="153"/>
-      <c r="D445" s="142"/>
+      <c r="C445" s="163"/>
+      <c r="D445" s="152"/>
       <c r="E445" s="8" t="s">
         <v>565</v>
       </c>
@@ -14952,8 +15664,8 @@
       <c r="B446" s="7">
         <v>10</v>
       </c>
-      <c r="C446" s="153"/>
-      <c r="D446" s="140" t="s">
+      <c r="C446" s="163"/>
+      <c r="D446" s="150" t="s">
         <v>566</v>
       </c>
       <c r="E446" s="8" t="s">
@@ -14976,8 +15688,8 @@
       <c r="B447" s="7">
         <v>11</v>
       </c>
-      <c r="C447" s="153"/>
-      <c r="D447" s="141"/>
+      <c r="C447" s="163"/>
+      <c r="D447" s="151"/>
       <c r="E447" s="8" t="s">
         <v>568</v>
       </c>
@@ -14998,8 +15710,8 @@
       <c r="B448" s="7">
         <v>12</v>
       </c>
-      <c r="C448" s="153"/>
-      <c r="D448" s="142"/>
+      <c r="C448" s="163"/>
+      <c r="D448" s="152"/>
       <c r="E448" s="8" t="s">
         <v>569</v>
       </c>
@@ -15020,8 +15732,8 @@
       <c r="B449" s="7">
         <v>13</v>
       </c>
-      <c r="C449" s="153"/>
-      <c r="D449" s="140" t="s">
+      <c r="C449" s="163"/>
+      <c r="D449" s="150" t="s">
         <v>570</v>
       </c>
       <c r="E449" s="8" t="s">
@@ -15044,8 +15756,8 @@
       <c r="B450" s="7">
         <v>14</v>
       </c>
-      <c r="C450" s="153"/>
-      <c r="D450" s="141"/>
+      <c r="C450" s="163"/>
+      <c r="D450" s="151"/>
       <c r="E450" s="29" t="s">
         <v>572</v>
       </c>
@@ -15066,8 +15778,8 @@
       <c r="B451" s="7">
         <v>15</v>
       </c>
-      <c r="C451" s="153"/>
-      <c r="D451" s="141"/>
+      <c r="C451" s="163"/>
+      <c r="D451" s="151"/>
       <c r="E451" s="8" t="s">
         <v>573</v>
       </c>
@@ -15088,8 +15800,8 @@
       <c r="B452" s="7">
         <v>16</v>
       </c>
-      <c r="C452" s="153"/>
-      <c r="D452" s="142"/>
+      <c r="C452" s="163"/>
+      <c r="D452" s="152"/>
       <c r="E452" s="8" t="s">
         <v>574</v>
       </c>
@@ -15110,8 +15822,8 @@
       <c r="B453" s="7">
         <v>17</v>
       </c>
-      <c r="C453" s="153"/>
-      <c r="D453" s="140" t="s">
+      <c r="C453" s="163"/>
+      <c r="D453" s="150" t="s">
         <v>575</v>
       </c>
       <c r="E453" s="8" t="s">
@@ -15134,8 +15846,8 @@
       <c r="B454" s="7">
         <v>18</v>
       </c>
-      <c r="C454" s="153"/>
-      <c r="D454" s="141"/>
+      <c r="C454" s="163"/>
+      <c r="D454" s="151"/>
       <c r="E454" s="8" t="s">
         <v>577</v>
       </c>
@@ -15156,8 +15868,8 @@
       <c r="B455" s="7">
         <v>19</v>
       </c>
-      <c r="C455" s="153"/>
-      <c r="D455" s="141"/>
+      <c r="C455" s="163"/>
+      <c r="D455" s="151"/>
       <c r="E455" s="8" t="s">
         <v>578</v>
       </c>
@@ -15178,8 +15890,8 @@
       <c r="B456" s="7">
         <v>20</v>
       </c>
-      <c r="C456" s="153"/>
-      <c r="D456" s="141"/>
+      <c r="C456" s="163"/>
+      <c r="D456" s="151"/>
       <c r="E456" s="39" t="s">
         <v>579</v>
       </c>
@@ -15200,8 +15912,8 @@
       <c r="B457" s="7">
         <v>21</v>
       </c>
-      <c r="C457" s="153"/>
-      <c r="D457" s="141"/>
+      <c r="C457" s="163"/>
+      <c r="D457" s="151"/>
       <c r="E457" s="8" t="s">
         <v>580</v>
       </c>
@@ -15222,8 +15934,8 @@
       <c r="B458" s="24">
         <v>22</v>
       </c>
-      <c r="C458" s="154"/>
-      <c r="D458" s="142"/>
+      <c r="C458" s="164"/>
+      <c r="D458" s="152"/>
       <c r="E458" s="17" t="s">
         <v>581</v>
       </c>
@@ -15245,10 +15957,10 @@
       <c r="B459" s="7">
         <v>1</v>
       </c>
-      <c r="C459" s="155" t="s">
+      <c r="C459" s="165" t="s">
         <v>582</v>
       </c>
-      <c r="D459" s="140" t="s">
+      <c r="D459" s="150" t="s">
         <v>583</v>
       </c>
       <c r="E459" s="8" t="s">
@@ -15271,8 +15983,8 @@
       <c r="B460" s="7">
         <v>2</v>
       </c>
-      <c r="C460" s="156"/>
-      <c r="D460" s="141"/>
+      <c r="C460" s="166"/>
+      <c r="D460" s="151"/>
       <c r="E460" s="8" t="s">
         <v>584</v>
       </c>
@@ -15293,8 +16005,8 @@
       <c r="B461" s="7">
         <v>3</v>
       </c>
-      <c r="C461" s="156"/>
-      <c r="D461" s="141"/>
+      <c r="C461" s="166"/>
+      <c r="D461" s="151"/>
       <c r="E461" s="8" t="s">
         <v>585</v>
       </c>
@@ -15315,8 +16027,8 @@
       <c r="B462" s="7">
         <v>4</v>
       </c>
-      <c r="C462" s="156"/>
-      <c r="D462" s="141"/>
+      <c r="C462" s="166"/>
+      <c r="D462" s="151"/>
       <c r="E462" s="8" t="s">
         <v>586</v>
       </c>
@@ -15337,8 +16049,8 @@
       <c r="B463" s="7">
         <v>5</v>
       </c>
-      <c r="C463" s="156"/>
-      <c r="D463" s="141"/>
+      <c r="C463" s="166"/>
+      <c r="D463" s="151"/>
       <c r="E463" s="8" t="s">
         <v>587</v>
       </c>
@@ -15359,8 +16071,8 @@
       <c r="B464" s="7">
         <v>6</v>
       </c>
-      <c r="C464" s="156"/>
-      <c r="D464" s="141"/>
+      <c r="C464" s="166"/>
+      <c r="D464" s="151"/>
       <c r="E464" s="8" t="s">
         <v>588</v>
       </c>
@@ -15381,8 +16093,8 @@
       <c r="B465" s="7">
         <v>7</v>
       </c>
-      <c r="C465" s="156"/>
-      <c r="D465" s="141"/>
+      <c r="C465" s="166"/>
+      <c r="D465" s="151"/>
       <c r="E465" s="8" t="s">
         <v>589</v>
       </c>
@@ -15403,8 +16115,8 @@
       <c r="B466" s="7">
         <v>8</v>
       </c>
-      <c r="C466" s="156"/>
-      <c r="D466" s="142"/>
+      <c r="C466" s="166"/>
+      <c r="D466" s="152"/>
       <c r="E466" s="8" t="s">
         <v>590</v>
       </c>
@@ -15425,8 +16137,8 @@
       <c r="B467" s="7">
         <v>9</v>
       </c>
-      <c r="C467" s="156"/>
-      <c r="D467" s="140" t="s">
+      <c r="C467" s="166"/>
+      <c r="D467" s="150" t="s">
         <v>591</v>
       </c>
       <c r="E467" s="8" t="s">
@@ -15449,8 +16161,8 @@
       <c r="B468" s="7">
         <v>10</v>
       </c>
-      <c r="C468" s="156"/>
-      <c r="D468" s="141"/>
+      <c r="C468" s="166"/>
+      <c r="D468" s="151"/>
       <c r="E468" s="8" t="s">
         <v>593</v>
       </c>
@@ -15471,8 +16183,8 @@
       <c r="B469" s="7">
         <v>11</v>
       </c>
-      <c r="C469" s="156"/>
-      <c r="D469" s="141"/>
+      <c r="C469" s="166"/>
+      <c r="D469" s="151"/>
       <c r="E469" s="8" t="s">
         <v>594</v>
       </c>
@@ -15493,8 +16205,8 @@
       <c r="B470" s="7">
         <v>12</v>
       </c>
-      <c r="C470" s="156"/>
-      <c r="D470" s="141"/>
+      <c r="C470" s="166"/>
+      <c r="D470" s="151"/>
       <c r="E470" s="8" t="s">
         <v>595</v>
       </c>
@@ -15515,8 +16227,8 @@
       <c r="B471" s="7">
         <v>13</v>
       </c>
-      <c r="C471" s="156"/>
-      <c r="D471" s="141"/>
+      <c r="C471" s="166"/>
+      <c r="D471" s="151"/>
       <c r="E471" s="8" t="s">
         <v>596</v>
       </c>
@@ -15537,8 +16249,8 @@
       <c r="B472" s="7">
         <v>14</v>
       </c>
-      <c r="C472" s="156"/>
-      <c r="D472" s="141"/>
+      <c r="C472" s="166"/>
+      <c r="D472" s="151"/>
       <c r="E472" s="8" t="s">
         <v>597</v>
       </c>
@@ -15559,8 +16271,8 @@
       <c r="B473" s="7">
         <v>15</v>
       </c>
-      <c r="C473" s="156"/>
-      <c r="D473" s="142"/>
+      <c r="C473" s="166"/>
+      <c r="D473" s="152"/>
       <c r="E473" s="8" t="s">
         <v>598</v>
       </c>
@@ -15581,8 +16293,8 @@
       <c r="B474" s="7">
         <v>16</v>
       </c>
-      <c r="C474" s="156"/>
-      <c r="D474" s="140" t="s">
+      <c r="C474" s="166"/>
+      <c r="D474" s="150" t="s">
         <v>599</v>
       </c>
       <c r="E474" s="8" t="s">
@@ -15605,8 +16317,8 @@
       <c r="B475" s="7">
         <v>17</v>
       </c>
-      <c r="C475" s="156"/>
-      <c r="D475" s="141"/>
+      <c r="C475" s="166"/>
+      <c r="D475" s="151"/>
       <c r="E475" s="8" t="s">
         <v>601</v>
       </c>
@@ -15627,8 +16339,8 @@
       <c r="B476" s="7">
         <v>18</v>
       </c>
-      <c r="C476" s="156"/>
-      <c r="D476" s="141"/>
+      <c r="C476" s="166"/>
+      <c r="D476" s="151"/>
       <c r="E476" s="8" t="s">
         <v>602</v>
       </c>
@@ -15649,8 +16361,8 @@
       <c r="B477" s="7">
         <v>19</v>
       </c>
-      <c r="C477" s="156"/>
-      <c r="D477" s="141"/>
+      <c r="C477" s="166"/>
+      <c r="D477" s="151"/>
       <c r="E477" s="8" t="s">
         <v>603</v>
       </c>
@@ -15671,8 +16383,8 @@
       <c r="B478" s="7">
         <v>20</v>
       </c>
-      <c r="C478" s="156"/>
-      <c r="D478" s="141"/>
+      <c r="C478" s="166"/>
+      <c r="D478" s="151"/>
       <c r="E478" s="8" t="s">
         <v>604</v>
       </c>
@@ -15693,8 +16405,8 @@
       <c r="B479" s="7">
         <v>21</v>
       </c>
-      <c r="C479" s="156"/>
-      <c r="D479" s="141"/>
+      <c r="C479" s="166"/>
+      <c r="D479" s="151"/>
       <c r="E479" s="8" t="s">
         <v>605</v>
       </c>
@@ -15715,8 +16427,8 @@
       <c r="B480" s="7">
         <v>22</v>
       </c>
-      <c r="C480" s="156"/>
-      <c r="D480" s="141"/>
+      <c r="C480" s="166"/>
+      <c r="D480" s="151"/>
       <c r="E480" s="8" t="s">
         <v>606</v>
       </c>
@@ -15737,8 +16449,8 @@
       <c r="B481" s="7">
         <v>23</v>
       </c>
-      <c r="C481" s="156"/>
-      <c r="D481" s="142"/>
+      <c r="C481" s="166"/>
+      <c r="D481" s="152"/>
       <c r="E481" s="8" t="s">
         <v>607</v>
       </c>
@@ -15759,8 +16471,8 @@
       <c r="B482" s="7">
         <v>24</v>
       </c>
-      <c r="C482" s="156"/>
-      <c r="D482" s="140" t="s">
+      <c r="C482" s="166"/>
+      <c r="D482" s="150" t="s">
         <v>608</v>
       </c>
       <c r="E482" s="8" t="s">
@@ -15783,8 +16495,8 @@
       <c r="B483" s="7">
         <v>25</v>
       </c>
-      <c r="C483" s="156"/>
-      <c r="D483" s="141"/>
+      <c r="C483" s="166"/>
+      <c r="D483" s="151"/>
       <c r="E483" s="8" t="s">
         <v>610</v>
       </c>
@@ -15805,8 +16517,8 @@
       <c r="B484" s="7">
         <v>26</v>
       </c>
-      <c r="C484" s="156"/>
-      <c r="D484" s="141"/>
+      <c r="C484" s="166"/>
+      <c r="D484" s="151"/>
       <c r="E484" s="8" t="s">
         <v>611</v>
       </c>
@@ -15827,8 +16539,8 @@
       <c r="B485" s="7">
         <v>27</v>
       </c>
-      <c r="C485" s="156"/>
-      <c r="D485" s="142"/>
+      <c r="C485" s="166"/>
+      <c r="D485" s="152"/>
       <c r="E485" s="8" t="s">
         <v>612</v>
       </c>
@@ -15849,8 +16561,8 @@
       <c r="B486" s="7">
         <v>28</v>
       </c>
-      <c r="C486" s="156"/>
-      <c r="D486" s="140" t="s">
+      <c r="C486" s="166"/>
+      <c r="D486" s="150" t="s">
         <v>613</v>
       </c>
       <c r="E486" s="8" t="s">
@@ -15873,8 +16585,8 @@
       <c r="B487" s="7">
         <v>29</v>
       </c>
-      <c r="C487" s="156"/>
-      <c r="D487" s="141"/>
+      <c r="C487" s="166"/>
+      <c r="D487" s="151"/>
       <c r="E487" s="8" t="s">
         <v>615</v>
       </c>
@@ -15895,8 +16607,8 @@
       <c r="B488" s="7">
         <v>30</v>
       </c>
-      <c r="C488" s="156"/>
-      <c r="D488" s="141"/>
+      <c r="C488" s="166"/>
+      <c r="D488" s="151"/>
       <c r="E488" s="8" t="s">
         <v>616</v>
       </c>
@@ -15917,8 +16629,8 @@
       <c r="B489" s="7">
         <v>31</v>
       </c>
-      <c r="C489" s="156"/>
-      <c r="D489" s="141"/>
+      <c r="C489" s="166"/>
+      <c r="D489" s="151"/>
       <c r="E489" s="8" t="s">
         <v>617</v>
       </c>
@@ -15939,8 +16651,8 @@
       <c r="B490" s="7">
         <v>32</v>
       </c>
-      <c r="C490" s="156"/>
-      <c r="D490" s="141"/>
+      <c r="C490" s="166"/>
+      <c r="D490" s="151"/>
       <c r="E490" s="8" t="s">
         <v>618</v>
       </c>
@@ -15961,8 +16673,8 @@
       <c r="B491" s="7">
         <v>33</v>
       </c>
-      <c r="C491" s="156"/>
-      <c r="D491" s="141"/>
+      <c r="C491" s="166"/>
+      <c r="D491" s="151"/>
       <c r="E491" s="8" t="s">
         <v>619</v>
       </c>
@@ -15983,8 +16695,8 @@
       <c r="B492" s="7">
         <v>34</v>
       </c>
-      <c r="C492" s="156"/>
-      <c r="D492" s="141"/>
+      <c r="C492" s="166"/>
+      <c r="D492" s="151"/>
       <c r="E492" s="8" t="s">
         <v>620</v>
       </c>
@@ -16005,8 +16717,8 @@
       <c r="B493" s="7">
         <v>35</v>
       </c>
-      <c r="C493" s="156"/>
-      <c r="D493" s="141"/>
+      <c r="C493" s="166"/>
+      <c r="D493" s="151"/>
       <c r="E493" s="8" t="s">
         <v>621</v>
       </c>
@@ -16027,8 +16739,8 @@
       <c r="B494" s="7">
         <v>36</v>
       </c>
-      <c r="C494" s="156"/>
-      <c r="D494" s="141"/>
+      <c r="C494" s="166"/>
+      <c r="D494" s="151"/>
       <c r="E494" s="8" t="s">
         <v>622</v>
       </c>
@@ -16049,8 +16761,8 @@
       <c r="B495" s="7">
         <v>37</v>
       </c>
-      <c r="C495" s="156"/>
-      <c r="D495" s="141"/>
+      <c r="C495" s="166"/>
+      <c r="D495" s="151"/>
       <c r="E495" s="8" t="s">
         <v>623</v>
       </c>
@@ -16071,8 +16783,8 @@
       <c r="B496" s="7">
         <v>38</v>
       </c>
-      <c r="C496" s="156"/>
-      <c r="D496" s="142"/>
+      <c r="C496" s="166"/>
+      <c r="D496" s="152"/>
       <c r="E496" s="8" t="s">
         <v>624</v>
       </c>
@@ -16093,8 +16805,8 @@
       <c r="B497" s="7">
         <v>39</v>
       </c>
-      <c r="C497" s="156"/>
-      <c r="D497" s="140" t="s">
+      <c r="C497" s="166"/>
+      <c r="D497" s="150" t="s">
         <v>625</v>
       </c>
       <c r="E497" s="8" t="s">
@@ -16117,8 +16829,8 @@
       <c r="B498" s="7">
         <v>40</v>
       </c>
-      <c r="C498" s="156"/>
-      <c r="D498" s="141"/>
+      <c r="C498" s="166"/>
+      <c r="D498" s="151"/>
       <c r="E498" s="8" t="s">
         <v>626</v>
       </c>
@@ -16139,8 +16851,8 @@
       <c r="B499" s="7">
         <v>41</v>
       </c>
-      <c r="C499" s="156"/>
-      <c r="D499" s="141"/>
+      <c r="C499" s="166"/>
+      <c r="D499" s="151"/>
       <c r="E499" s="8" t="s">
         <v>627</v>
       </c>
@@ -16161,8 +16873,8 @@
       <c r="B500" s="7">
         <v>42</v>
       </c>
-      <c r="C500" s="156"/>
-      <c r="D500" s="141"/>
+      <c r="C500" s="166"/>
+      <c r="D500" s="151"/>
       <c r="E500" s="8" t="s">
         <v>628</v>
       </c>
@@ -16183,8 +16895,8 @@
       <c r="B501" s="7">
         <v>43</v>
       </c>
-      <c r="C501" s="156"/>
-      <c r="D501" s="141"/>
+      <c r="C501" s="166"/>
+      <c r="D501" s="151"/>
       <c r="E501" s="8" t="s">
         <v>629</v>
       </c>
@@ -16205,8 +16917,8 @@
       <c r="B502" s="7">
         <v>44</v>
       </c>
-      <c r="C502" s="156"/>
-      <c r="D502" s="142"/>
+      <c r="C502" s="166"/>
+      <c r="D502" s="152"/>
       <c r="E502" s="8" t="s">
         <v>630</v>
       </c>
@@ -16227,8 +16939,8 @@
       <c r="B503" s="7">
         <v>45</v>
       </c>
-      <c r="C503" s="156"/>
-      <c r="D503" s="140" t="s">
+      <c r="C503" s="166"/>
+      <c r="D503" s="150" t="s">
         <v>631</v>
       </c>
       <c r="E503" s="8" t="s">
@@ -16251,8 +16963,8 @@
       <c r="B504" s="7">
         <v>46</v>
       </c>
-      <c r="C504" s="156"/>
-      <c r="D504" s="141"/>
+      <c r="C504" s="166"/>
+      <c r="D504" s="151"/>
       <c r="E504" s="8" t="s">
         <v>633</v>
       </c>
@@ -16273,8 +16985,8 @@
       <c r="B505" s="7">
         <v>47</v>
       </c>
-      <c r="C505" s="156"/>
-      <c r="D505" s="141"/>
+      <c r="C505" s="166"/>
+      <c r="D505" s="151"/>
       <c r="E505" s="8" t="s">
         <v>634</v>
       </c>
@@ -16295,8 +17007,8 @@
       <c r="B506" s="7">
         <v>48</v>
       </c>
-      <c r="C506" s="156"/>
-      <c r="D506" s="141"/>
+      <c r="C506" s="166"/>
+      <c r="D506" s="151"/>
       <c r="E506" s="8" t="s">
         <v>635</v>
       </c>
@@ -16317,8 +17029,8 @@
       <c r="B507" s="7">
         <v>49</v>
       </c>
-      <c r="C507" s="156"/>
-      <c r="D507" s="141"/>
+      <c r="C507" s="166"/>
+      <c r="D507" s="151"/>
       <c r="E507" s="8" t="s">
         <v>636</v>
       </c>
@@ -16339,8 +17051,8 @@
       <c r="B508" s="7">
         <v>50</v>
       </c>
-      <c r="C508" s="156"/>
-      <c r="D508" s="141"/>
+      <c r="C508" s="166"/>
+      <c r="D508" s="151"/>
       <c r="E508" s="8" t="s">
         <v>637</v>
       </c>
@@ -16361,8 +17073,8 @@
       <c r="B509" s="7">
         <v>51</v>
       </c>
-      <c r="C509" s="156"/>
-      <c r="D509" s="142"/>
+      <c r="C509" s="166"/>
+      <c r="D509" s="152"/>
       <c r="E509" s="8" t="s">
         <v>638</v>
       </c>
@@ -16383,8 +17095,8 @@
       <c r="B510" s="7">
         <v>52</v>
       </c>
-      <c r="C510" s="156"/>
-      <c r="D510" s="140" t="s">
+      <c r="C510" s="166"/>
+      <c r="D510" s="150" t="s">
         <v>639</v>
       </c>
       <c r="E510" s="8" t="s">
@@ -16407,8 +17119,8 @@
       <c r="B511" s="7">
         <v>53</v>
       </c>
-      <c r="C511" s="156"/>
-      <c r="D511" s="141"/>
+      <c r="C511" s="166"/>
+      <c r="D511" s="151"/>
       <c r="E511" s="8" t="s">
         <v>641</v>
       </c>
@@ -16429,8 +17141,8 @@
       <c r="B512" s="7">
         <v>54</v>
       </c>
-      <c r="C512" s="156"/>
-      <c r="D512" s="141"/>
+      <c r="C512" s="166"/>
+      <c r="D512" s="151"/>
       <c r="E512" s="8" t="s">
         <v>642</v>
       </c>
@@ -16451,8 +17163,8 @@
       <c r="B513" s="24">
         <v>55</v>
       </c>
-      <c r="C513" s="157"/>
-      <c r="D513" s="142"/>
+      <c r="C513" s="167"/>
+      <c r="D513" s="152"/>
       <c r="E513" s="17" t="s">
         <v>643</v>
       </c>
@@ -24025,6 +24737,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId495"/>
+  <drawing r:id="rId496"/>
 </worksheet>
 </file>
 
@@ -24039,16 +24752,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="31.5" customHeight="1">
-      <c r="A1" s="191" t="s">
+      <c r="A1" s="201" t="s">
         <v>644</v>
       </c>
-      <c r="B1" s="192"/>
+      <c r="B1" s="202"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1">
-      <c r="A2" s="193" t="s">
+      <c r="A2" s="203" t="s">
         <v>645</v>
       </c>
-      <c r="B2" s="192"/>
+      <c r="B2" s="202"/>
     </row>
     <row r="3" spans="1:2" ht="18" customHeight="1">
       <c r="A3" s="46" t="s">
@@ -24095,10 +24808,10 @@
       <c r="B8" s="47"/>
     </row>
     <row r="9" spans="1:2" ht="18" customHeight="1">
-      <c r="A9" s="193" t="s">
+      <c r="A9" s="203" t="s">
         <v>656</v>
       </c>
-      <c r="B9" s="192"/>
+      <c r="B9" s="202"/>
     </row>
     <row r="10" spans="1:2" ht="18" customHeight="1">
       <c r="A10" s="52" t="s">
@@ -24177,10 +24890,10 @@
       <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:2" ht="18" customHeight="1">
-      <c r="A20" s="193" t="s">
+      <c r="A20" s="203" t="s">
         <v>675</v>
       </c>
-      <c r="B20" s="192"/>
+      <c r="B20" s="202"/>
     </row>
     <row r="21" spans="1:2" ht="18" customHeight="1">
       <c r="A21" s="52" t="s">
@@ -25177,15 +25890,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="194" t="s">
+      <c r="A1" s="204" t="s">
         <v>678</v>
       </c>
-      <c r="B1" s="195"/>
-      <c r="C1" s="195"/>
-      <c r="D1" s="195"/>
-      <c r="E1" s="195"/>
-      <c r="F1" s="195"/>
-      <c r="G1" s="192"/>
+      <c r="B1" s="205"/>
+      <c r="C1" s="205"/>
+      <c r="D1" s="205"/>
+      <c r="E1" s="205"/>
+      <c r="F1" s="205"/>
+      <c r="G1" s="202"/>
     </row>
     <row r="2" spans="1:8" ht="13.2">
       <c r="A2" s="53" t="s">

--- a/DSA Master Sheet.xlsx
+++ b/DSA Master Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aamer\Desktop\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87EA8CA3-982B-4188-9FB6-B26EEBB1A549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C7E8F5-B658-471F-8B44-4895567CA17E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="731">
   <si>
     <t>DSA Master Sheet</t>
   </si>
@@ -2888,6 +2888,15 @@
 Last Occurrence    → Rightmost index of x
 Store: arr[mid] == x
 Move : RIGHT (low = mid + 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> while(low&lt;=high){
+             mid = low+(high-low)/2;
+            int sign = guess(mid);
+            if(sign==0)return mid; 
+            if(sign==1)low = mid+1;
+            else high = mid-1;
+        }</t>
   </si>
 </sst>
 </file>
@@ -3993,7 +4002,7 @@
     <xf numFmtId="0" fontId="88" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="89" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="206">
+  <cellXfs count="207">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4392,32 +4401,23 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="88" fillId="53" borderId="8" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4437,23 +4437,86 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4473,77 +4536,23 @@
     <xf numFmtId="0" fontId="11" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4556,6 +4565,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
@@ -4592,8 +4602,8 @@
       <xdr:row>70</xdr:row>
       <xdr:rowOff>123761</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="2" name="Ink 1">
@@ -4612,7 +4622,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="2" name="Ink 1">
@@ -4657,8 +4667,8 @@
       <xdr:row>71</xdr:row>
       <xdr:rowOff>178729</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="8" name="Ink 7">
@@ -4677,7 +4687,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="8" name="Ink 7">
@@ -4722,8 +4732,8 @@
       <xdr:row>71</xdr:row>
       <xdr:rowOff>150649</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="9" name="Ink 8">
@@ -4742,7 +4752,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="9" name="Ink 8">
@@ -4787,8 +4797,8 @@
       <xdr:row>71</xdr:row>
       <xdr:rowOff>133009</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="10" name="Ink 9">
@@ -4807,7 +4817,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="10" name="Ink 9">
@@ -4852,8 +4862,8 @@
       <xdr:row>71</xdr:row>
       <xdr:rowOff>138049</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="11" name="Ink 10">
@@ -4872,7 +4882,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="11" name="Ink 10">
@@ -4917,8 +4927,8 @@
       <xdr:row>71</xdr:row>
       <xdr:rowOff>120409</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="12" name="Ink 11">
@@ -4937,7 +4947,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="12" name="Ink 11">
@@ -5023,7 +5033,7 @@
     </inkml:brush>
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">145 268 36,'0'1'59,"1"-1"1,0 1-1,0-1 1,0 1-1,0-1 1,0 1-1,0-1 1,0 0-1,0 1 1,0-1-1,0 0 1,0 0-1,0 0 1,0 0-1,0 0 1,0 0-1,0 0 1,0 0-1,0 0 1,0 0-1,0 0 1,0-1-1,0 1 1,0 0-1,0-1 1,1 0-1,-1 0-117,0 1-1,1-1 0,-1 1 1,0 0-1,0-1 0,0 1 0,1 0 1,-1 0-1,0-1 0,0 1 1,1 0-1,-1 0 0,0 1 1,0-1-1,1 0 0,-1 0 1,0 1-1,0-1 0,1 0 1,0 2-1,2-1-243</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="715.46">62 189 256,'-3'11'2062,"1"0"-3873</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="715.45">62 189 256,'-3'11'2062,"1"0"-3873</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1113.04">1 177 1020,'2'0'161,"0"0"0,-1-1 0,1 1-1,0-1 1,0 1 0,0-1 0,0 0 0,-1 0 0,1 0 0,0 0-1,-1 0 1,1 0 0,-1 0 0,1 0 0,-1-1 0,0 1 0,1-1-1,-1 1 1,0-1 0,1-1 0,10-11 271,-12 12-432</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1334.86">38 105 844,'6'-89'2242,"-1"73"-4979</inkml:trace>
 </inkml:ink>
@@ -5353,18 +5363,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="30.75" customHeight="1">
-      <c r="A1" s="153" t="s">
+      <c r="A1" s="198" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="154"/>
-      <c r="C1" s="154"/>
-      <c r="D1" s="154"/>
-      <c r="E1" s="154"/>
-      <c r="F1" s="154"/>
-      <c r="G1" s="154"/>
-      <c r="H1" s="154"/>
-      <c r="I1" s="154"/>
-      <c r="J1" s="155"/>
+      <c r="B1" s="199"/>
+      <c r="C1" s="199"/>
+      <c r="D1" s="199"/>
+      <c r="E1" s="199"/>
+      <c r="F1" s="199"/>
+      <c r="G1" s="199"/>
+      <c r="H1" s="199"/>
+      <c r="I1" s="199"/>
+      <c r="J1" s="200"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -5419,18 +5429,18 @@
       <c r="T2" s="5"/>
     </row>
     <row r="3" spans="1:20" ht="13.8">
-      <c r="A3" s="156" t="s">
+      <c r="A3" s="195" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="157"/>
-      <c r="C3" s="157"/>
-      <c r="D3" s="157"/>
-      <c r="E3" s="157"/>
-      <c r="F3" s="157"/>
-      <c r="G3" s="157"/>
-      <c r="H3" s="157"/>
-      <c r="I3" s="157"/>
-      <c r="J3" s="158"/>
+      <c r="B3" s="196"/>
+      <c r="C3" s="196"/>
+      <c r="D3" s="196"/>
+      <c r="E3" s="196"/>
+      <c r="F3" s="196"/>
+      <c r="G3" s="196"/>
+      <c r="H3" s="196"/>
+      <c r="I3" s="196"/>
+      <c r="J3" s="197"/>
     </row>
     <row r="4" spans="1:20" ht="13.8">
       <c r="A4" s="6">
@@ -5439,10 +5449,10 @@
       <c r="B4" s="7">
         <v>1</v>
       </c>
-      <c r="C4" s="159" t="s">
+      <c r="C4" s="156" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="150" t="s">
+      <c r="D4" s="171" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -5472,8 +5482,8 @@
       <c r="B5" s="7">
         <v>2</v>
       </c>
-      <c r="C5" s="160"/>
-      <c r="D5" s="151"/>
+      <c r="C5" s="157"/>
+      <c r="D5" s="172"/>
       <c r="E5" s="8" t="s">
         <v>16</v>
       </c>
@@ -5501,8 +5511,8 @@
       <c r="B6" s="7">
         <v>3</v>
       </c>
-      <c r="C6" s="160"/>
-      <c r="D6" s="151"/>
+      <c r="C6" s="157"/>
+      <c r="D6" s="172"/>
       <c r="E6" s="8" t="s">
         <v>19</v>
       </c>
@@ -5530,8 +5540,8 @@
       <c r="B7" s="7">
         <v>4</v>
       </c>
-      <c r="C7" s="160"/>
-      <c r="D7" s="151"/>
+      <c r="C7" s="157"/>
+      <c r="D7" s="172"/>
       <c r="E7" s="8" t="s">
         <v>23</v>
       </c>
@@ -5559,8 +5569,8 @@
       <c r="B8" s="7">
         <v>5</v>
       </c>
-      <c r="C8" s="160"/>
-      <c r="D8" s="151"/>
+      <c r="C8" s="157"/>
+      <c r="D8" s="172"/>
       <c r="E8" s="8" t="s">
         <v>26</v>
       </c>
@@ -5588,8 +5598,8 @@
       <c r="B9" s="7">
         <v>6</v>
       </c>
-      <c r="C9" s="160"/>
-      <c r="D9" s="152"/>
+      <c r="C9" s="157"/>
+      <c r="D9" s="173"/>
       <c r="E9" s="8" t="s">
         <v>29</v>
       </c>
@@ -5614,8 +5624,8 @@
       <c r="B10" s="7">
         <v>7</v>
       </c>
-      <c r="C10" s="160"/>
-      <c r="D10" s="150" t="s">
+      <c r="C10" s="157"/>
+      <c r="D10" s="171" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="8" t="s">
@@ -5642,8 +5652,8 @@
       <c r="B11" s="7">
         <v>8</v>
       </c>
-      <c r="C11" s="160"/>
-      <c r="D11" s="151"/>
+      <c r="C11" s="157"/>
+      <c r="D11" s="172"/>
       <c r="E11" s="13" t="s">
         <v>32</v>
       </c>
@@ -5668,8 +5678,8 @@
       <c r="B12" s="7">
         <v>9</v>
       </c>
-      <c r="C12" s="160"/>
-      <c r="D12" s="151"/>
+      <c r="C12" s="157"/>
+      <c r="D12" s="172"/>
       <c r="E12" s="8" t="s">
         <v>33</v>
       </c>
@@ -5694,8 +5704,8 @@
       <c r="B13" s="7">
         <v>10</v>
       </c>
-      <c r="C13" s="160"/>
-      <c r="D13" s="151"/>
+      <c r="C13" s="157"/>
+      <c r="D13" s="172"/>
       <c r="E13" s="8" t="s">
         <v>34</v>
       </c>
@@ -5722,8 +5732,8 @@
       <c r="B14" s="7">
         <v>11</v>
       </c>
-      <c r="C14" s="160"/>
-      <c r="D14" s="151"/>
+      <c r="C14" s="157"/>
+      <c r="D14" s="172"/>
       <c r="E14" s="8" t="s">
         <v>35</v>
       </c>
@@ -5748,8 +5758,8 @@
       <c r="B15" s="7">
         <v>12</v>
       </c>
-      <c r="C15" s="160"/>
-      <c r="D15" s="151"/>
+      <c r="C15" s="157"/>
+      <c r="D15" s="172"/>
       <c r="E15" s="8" t="s">
         <v>36</v>
       </c>
@@ -5776,8 +5786,8 @@
       <c r="B16" s="7">
         <v>13</v>
       </c>
-      <c r="C16" s="160"/>
-      <c r="D16" s="151"/>
+      <c r="C16" s="157"/>
+      <c r="D16" s="172"/>
       <c r="E16" s="8" t="s">
         <v>37</v>
       </c>
@@ -5802,8 +5812,8 @@
       <c r="B17" s="7">
         <v>14</v>
       </c>
-      <c r="C17" s="160"/>
-      <c r="D17" s="151"/>
+      <c r="C17" s="157"/>
+      <c r="D17" s="172"/>
       <c r="E17" s="8" t="s">
         <v>38</v>
       </c>
@@ -5823,15 +5833,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="386.4">
+    <row r="18" spans="1:10" ht="372.6">
       <c r="A18" s="6">
         <v>15</v>
       </c>
       <c r="B18" s="7">
         <v>15</v>
       </c>
-      <c r="C18" s="160"/>
-      <c r="D18" s="152"/>
+      <c r="C18" s="157"/>
+      <c r="D18" s="173"/>
       <c r="E18" s="13" t="s">
         <v>39</v>
       </c>
@@ -5858,8 +5868,8 @@
       <c r="B19" s="7">
         <v>16</v>
       </c>
-      <c r="C19" s="160"/>
-      <c r="D19" s="150" t="s">
+      <c r="C19" s="157"/>
+      <c r="D19" s="171" t="s">
         <v>40</v>
       </c>
       <c r="E19" s="8" t="s">
@@ -5888,8 +5898,8 @@
       <c r="B20" s="7">
         <v>17</v>
       </c>
-      <c r="C20" s="160"/>
-      <c r="D20" s="151"/>
+      <c r="C20" s="157"/>
+      <c r="D20" s="172"/>
       <c r="E20" s="8" t="s">
         <v>42</v>
       </c>
@@ -5916,8 +5926,8 @@
       <c r="B21" s="7">
         <v>18</v>
       </c>
-      <c r="C21" s="160"/>
-      <c r="D21" s="151"/>
+      <c r="C21" s="157"/>
+      <c r="D21" s="172"/>
       <c r="E21" s="8" t="s">
         <v>43</v>
       </c>
@@ -5944,8 +5954,8 @@
       <c r="B22" s="7">
         <v>19</v>
       </c>
-      <c r="C22" s="160"/>
-      <c r="D22" s="151"/>
+      <c r="C22" s="157"/>
+      <c r="D22" s="172"/>
       <c r="E22" s="8" t="s">
         <v>44</v>
       </c>
@@ -5966,8 +5976,8 @@
       <c r="B23" s="7">
         <v>20</v>
       </c>
-      <c r="C23" s="160"/>
-      <c r="D23" s="151"/>
+      <c r="C23" s="157"/>
+      <c r="D23" s="172"/>
       <c r="E23" s="8" t="s">
         <v>45</v>
       </c>
@@ -5988,8 +5998,8 @@
       <c r="B24" s="7">
         <v>21</v>
       </c>
-      <c r="C24" s="160"/>
-      <c r="D24" s="151"/>
+      <c r="C24" s="157"/>
+      <c r="D24" s="172"/>
       <c r="E24" s="13" t="s">
         <v>46</v>
       </c>
@@ -6014,8 +6024,8 @@
       <c r="B25" s="7">
         <v>22</v>
       </c>
-      <c r="C25" s="160"/>
-      <c r="D25" s="152"/>
+      <c r="C25" s="157"/>
+      <c r="D25" s="173"/>
       <c r="E25" s="8" t="s">
         <v>47</v>
       </c>
@@ -6042,8 +6052,8 @@
       <c r="B26" s="7">
         <v>23</v>
       </c>
-      <c r="C26" s="160"/>
-      <c r="D26" s="150" t="s">
+      <c r="C26" s="157"/>
+      <c r="D26" s="171" t="s">
         <v>48</v>
       </c>
       <c r="E26" s="13" t="s">
@@ -6072,8 +6082,8 @@
       <c r="B27" s="7">
         <v>24</v>
       </c>
-      <c r="C27" s="160"/>
-      <c r="D27" s="151"/>
+      <c r="C27" s="157"/>
+      <c r="D27" s="172"/>
       <c r="E27" s="8" t="s">
         <v>50</v>
       </c>
@@ -6098,8 +6108,8 @@
       <c r="B28" s="7">
         <v>25</v>
       </c>
-      <c r="C28" s="160"/>
-      <c r="D28" s="151"/>
+      <c r="C28" s="157"/>
+      <c r="D28" s="172"/>
       <c r="E28" s="8" t="s">
         <v>51</v>
       </c>
@@ -6126,8 +6136,8 @@
       <c r="B29" s="143">
         <v>26</v>
       </c>
-      <c r="C29" s="160"/>
-      <c r="D29" s="151"/>
+      <c r="C29" s="157"/>
+      <c r="D29" s="172"/>
       <c r="E29" s="144" t="s">
         <v>52</v>
       </c>
@@ -6148,8 +6158,8 @@
       <c r="B30" s="143">
         <v>27</v>
       </c>
-      <c r="C30" s="160"/>
-      <c r="D30" s="151"/>
+      <c r="C30" s="157"/>
+      <c r="D30" s="172"/>
       <c r="E30" s="144" t="s">
         <v>53</v>
       </c>
@@ -6170,8 +6180,8 @@
       <c r="B31" s="143">
         <v>28</v>
       </c>
-      <c r="C31" s="160"/>
-      <c r="D31" s="151"/>
+      <c r="C31" s="157"/>
+      <c r="D31" s="172"/>
       <c r="E31" s="144" t="s">
         <v>54</v>
       </c>
@@ -6192,8 +6202,8 @@
       <c r="B32" s="143">
         <v>29</v>
       </c>
-      <c r="C32" s="161"/>
-      <c r="D32" s="152"/>
+      <c r="C32" s="158"/>
+      <c r="D32" s="173"/>
       <c r="E32" s="146" t="s">
         <v>55</v>
       </c>
@@ -6214,10 +6224,10 @@
       <c r="B33" s="22">
         <v>1</v>
       </c>
-      <c r="C33" s="162" t="s">
+      <c r="C33" s="159" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="150" t="s">
+      <c r="D33" s="171" t="s">
         <v>57</v>
       </c>
       <c r="E33" s="8" t="s">
@@ -6244,8 +6254,8 @@
       <c r="B34" s="7">
         <v>2</v>
       </c>
-      <c r="C34" s="163"/>
-      <c r="D34" s="151"/>
+      <c r="C34" s="160"/>
+      <c r="D34" s="172"/>
       <c r="E34" s="8" t="s">
         <v>59</v>
       </c>
@@ -6270,8 +6280,8 @@
       <c r="B35" s="7">
         <v>3</v>
       </c>
-      <c r="C35" s="163"/>
-      <c r="D35" s="151"/>
+      <c r="C35" s="160"/>
+      <c r="D35" s="172"/>
       <c r="E35" s="8" t="s">
         <v>60</v>
       </c>
@@ -6298,8 +6308,8 @@
       <c r="B36" s="7">
         <v>4</v>
       </c>
-      <c r="C36" s="163"/>
-      <c r="D36" s="152"/>
+      <c r="C36" s="160"/>
+      <c r="D36" s="173"/>
       <c r="E36" s="8" t="s">
         <v>61</v>
       </c>
@@ -6326,8 +6336,8 @@
       <c r="B37" s="7">
         <v>5</v>
       </c>
-      <c r="C37" s="163"/>
-      <c r="D37" s="150" t="s">
+      <c r="C37" s="160"/>
+      <c r="D37" s="171" t="s">
         <v>62</v>
       </c>
       <c r="E37" s="8" t="s">
@@ -6354,8 +6364,8 @@
       <c r="B38" s="7">
         <v>6</v>
       </c>
-      <c r="C38" s="163"/>
-      <c r="D38" s="151"/>
+      <c r="C38" s="160"/>
+      <c r="D38" s="172"/>
       <c r="E38" s="8" t="s">
         <v>64</v>
       </c>
@@ -6380,8 +6390,8 @@
       <c r="B39" s="7">
         <v>7</v>
       </c>
-      <c r="C39" s="163"/>
-      <c r="D39" s="152"/>
+      <c r="C39" s="160"/>
+      <c r="D39" s="173"/>
       <c r="E39" s="8" t="s">
         <v>65</v>
       </c>
@@ -6406,8 +6416,8 @@
       <c r="B40" s="7">
         <v>8</v>
       </c>
-      <c r="C40" s="163"/>
-      <c r="D40" s="150" t="s">
+      <c r="C40" s="160"/>
+      <c r="D40" s="171" t="s">
         <v>66</v>
       </c>
       <c r="E40" s="8" t="s">
@@ -6434,8 +6444,8 @@
       <c r="B41" s="7">
         <v>9</v>
       </c>
-      <c r="C41" s="163"/>
-      <c r="D41" s="151"/>
+      <c r="C41" s="160"/>
+      <c r="D41" s="172"/>
       <c r="E41" s="8" t="s">
         <v>68</v>
       </c>
@@ -6460,8 +6470,8 @@
       <c r="B42" s="7">
         <v>10</v>
       </c>
-      <c r="C42" s="163"/>
-      <c r="D42" s="151"/>
+      <c r="C42" s="160"/>
+      <c r="D42" s="172"/>
       <c r="E42" s="8" t="s">
         <v>69</v>
       </c>
@@ -6486,8 +6496,8 @@
       <c r="B43" s="7">
         <v>11</v>
       </c>
-      <c r="C43" s="163"/>
-      <c r="D43" s="151"/>
+      <c r="C43" s="160"/>
+      <c r="D43" s="172"/>
       <c r="E43" s="8" t="s">
         <v>70</v>
       </c>
@@ -6512,8 +6522,8 @@
       <c r="B44" s="24">
         <v>12</v>
       </c>
-      <c r="C44" s="164"/>
-      <c r="D44" s="152"/>
+      <c r="C44" s="161"/>
+      <c r="D44" s="173"/>
       <c r="E44" s="17" t="s">
         <v>71</v>
       </c>
@@ -6538,10 +6548,10 @@
       <c r="B45" s="22">
         <v>1</v>
       </c>
-      <c r="C45" s="177" t="s">
+      <c r="C45" s="162" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="180" t="s">
+      <c r="D45" s="174" t="s">
         <v>73</v>
       </c>
       <c r="E45" s="13" t="s">
@@ -6568,8 +6578,8 @@
       <c r="B46" s="7">
         <v>2</v>
       </c>
-      <c r="C46" s="178"/>
-      <c r="D46" s="181"/>
+      <c r="C46" s="163"/>
+      <c r="D46" s="175"/>
       <c r="E46" s="8" t="s">
         <v>75</v>
       </c>
@@ -6596,8 +6606,8 @@
       <c r="B47" s="7">
         <v>3</v>
       </c>
-      <c r="C47" s="178"/>
-      <c r="D47" s="181"/>
+      <c r="C47" s="163"/>
+      <c r="D47" s="175"/>
       <c r="E47" s="13" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6634,8 @@
       <c r="B48" s="7">
         <v>4</v>
       </c>
-      <c r="C48" s="178"/>
-      <c r="D48" s="181"/>
+      <c r="C48" s="163"/>
+      <c r="D48" s="175"/>
       <c r="E48" s="13" t="s">
         <v>77</v>
       </c>
@@ -6652,8 +6662,8 @@
       <c r="B49" s="7">
         <v>5</v>
       </c>
-      <c r="C49" s="178"/>
-      <c r="D49" s="181"/>
+      <c r="C49" s="163"/>
+      <c r="D49" s="175"/>
       <c r="E49" s="13" t="s">
         <v>78</v>
       </c>
@@ -6678,8 +6688,8 @@
       <c r="B50" s="24">
         <v>6</v>
       </c>
-      <c r="C50" s="179"/>
-      <c r="D50" s="182"/>
+      <c r="C50" s="164"/>
+      <c r="D50" s="176"/>
       <c r="E50" s="25" t="s">
         <v>79</v>
       </c>
@@ -6704,10 +6714,10 @@
       <c r="B51" s="7">
         <v>1</v>
       </c>
-      <c r="C51" s="168" t="s">
+      <c r="C51" s="153" t="s">
         <v>80</v>
       </c>
-      <c r="D51" s="150" t="s">
+      <c r="D51" s="171" t="s">
         <v>81</v>
       </c>
       <c r="E51" s="13" t="s">
@@ -6736,8 +6746,8 @@
       <c r="B52" s="7">
         <v>2</v>
       </c>
-      <c r="C52" s="169"/>
-      <c r="D52" s="151"/>
+      <c r="C52" s="154"/>
+      <c r="D52" s="172"/>
       <c r="E52" s="8" t="s">
         <v>83</v>
       </c>
@@ -6764,8 +6774,8 @@
       <c r="B53" s="7">
         <v>3</v>
       </c>
-      <c r="C53" s="169"/>
-      <c r="D53" s="151"/>
+      <c r="C53" s="154"/>
+      <c r="D53" s="172"/>
       <c r="E53" s="27" t="s">
         <v>84</v>
       </c>
@@ -6790,8 +6800,8 @@
       <c r="B54" s="7">
         <v>4</v>
       </c>
-      <c r="C54" s="169"/>
-      <c r="D54" s="151"/>
+      <c r="C54" s="154"/>
+      <c r="D54" s="172"/>
       <c r="E54" s="13" t="s">
         <v>85</v>
       </c>
@@ -6816,8 +6826,8 @@
       <c r="B55" s="7">
         <v>5</v>
       </c>
-      <c r="C55" s="169"/>
-      <c r="D55" s="151"/>
+      <c r="C55" s="154"/>
+      <c r="D55" s="172"/>
       <c r="E55" s="13" t="s">
         <v>86</v>
       </c>
@@ -6844,8 +6854,8 @@
       <c r="B56" s="7">
         <v>6</v>
       </c>
-      <c r="C56" s="169"/>
-      <c r="D56" s="151"/>
+      <c r="C56" s="154"/>
+      <c r="D56" s="172"/>
       <c r="E56" s="13" t="s">
         <v>87</v>
       </c>
@@ -6872,8 +6882,8 @@
       <c r="B57" s="7">
         <v>7</v>
       </c>
-      <c r="C57" s="169"/>
-      <c r="D57" s="152"/>
+      <c r="C57" s="154"/>
+      <c r="D57" s="173"/>
       <c r="E57" s="13" t="s">
         <v>88</v>
       </c>
@@ -6900,8 +6910,8 @@
       <c r="B58" s="7">
         <v>8</v>
       </c>
-      <c r="C58" s="169"/>
-      <c r="D58" s="150" t="s">
+      <c r="C58" s="154"/>
+      <c r="D58" s="171" t="s">
         <v>89</v>
       </c>
       <c r="E58" s="13" t="s">
@@ -6928,8 +6938,8 @@
       <c r="B59" s="7">
         <v>9</v>
       </c>
-      <c r="C59" s="169"/>
-      <c r="D59" s="151"/>
+      <c r="C59" s="154"/>
+      <c r="D59" s="172"/>
       <c r="E59" s="8" t="s">
         <v>91</v>
       </c>
@@ -6954,8 +6964,8 @@
       <c r="B60" s="7">
         <v>10</v>
       </c>
-      <c r="C60" s="169"/>
-      <c r="D60" s="151"/>
+      <c r="C60" s="154"/>
+      <c r="D60" s="172"/>
       <c r="E60" s="8" t="s">
         <v>92</v>
       </c>
@@ -6976,8 +6986,8 @@
       <c r="B61" s="7">
         <v>11</v>
       </c>
-      <c r="C61" s="169"/>
-      <c r="D61" s="151"/>
+      <c r="C61" s="154"/>
+      <c r="D61" s="172"/>
       <c r="E61" s="8" t="s">
         <v>93</v>
       </c>
@@ -6998,8 +7008,8 @@
       <c r="B62" s="7">
         <v>12</v>
       </c>
-      <c r="C62" s="169"/>
-      <c r="D62" s="151"/>
+      <c r="C62" s="154"/>
+      <c r="D62" s="172"/>
       <c r="E62" s="8" t="s">
         <v>94</v>
       </c>
@@ -7024,8 +7034,8 @@
       <c r="B63" s="7">
         <v>13</v>
       </c>
-      <c r="C63" s="169"/>
-      <c r="D63" s="152"/>
+      <c r="C63" s="154"/>
+      <c r="D63" s="173"/>
       <c r="E63" s="8" t="s">
         <v>95</v>
       </c>
@@ -7043,15 +7053,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="207">
+    <row r="64" spans="1:10" ht="193.2">
       <c r="A64" s="6">
         <v>61</v>
       </c>
       <c r="B64" s="7">
         <v>14</v>
       </c>
-      <c r="C64" s="169"/>
-      <c r="D64" s="150" t="s">
+      <c r="C64" s="154"/>
+      <c r="D64" s="171" t="s">
         <v>48</v>
       </c>
       <c r="E64" s="8" t="s">
@@ -7080,8 +7090,8 @@
       <c r="B65" s="143">
         <v>15</v>
       </c>
-      <c r="C65" s="169"/>
-      <c r="D65" s="151"/>
+      <c r="C65" s="154"/>
+      <c r="D65" s="172"/>
       <c r="E65" s="144" t="s">
         <v>97</v>
       </c>
@@ -7102,8 +7112,8 @@
       <c r="B66" s="7">
         <v>16</v>
       </c>
-      <c r="C66" s="169"/>
-      <c r="D66" s="151"/>
+      <c r="C66" s="154"/>
+      <c r="D66" s="172"/>
       <c r="E66" s="8" t="s">
         <v>98</v>
       </c>
@@ -7123,15 +7133,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="289.8">
+    <row r="67" spans="1:10" ht="276">
       <c r="A67" s="6">
         <v>64</v>
       </c>
       <c r="B67" s="7">
         <v>17</v>
       </c>
-      <c r="C67" s="170"/>
-      <c r="D67" s="152"/>
+      <c r="C67" s="155"/>
+      <c r="D67" s="173"/>
       <c r="E67" s="8" t="s">
         <v>99</v>
       </c>
@@ -7172,10 +7182,10 @@
       <c r="B69" s="7">
         <v>1</v>
       </c>
-      <c r="C69" s="159" t="s">
+      <c r="C69" s="156" t="s">
         <v>101</v>
       </c>
-      <c r="D69" s="150" t="s">
+      <c r="D69" s="171" t="s">
         <v>102</v>
       </c>
       <c r="E69" s="8" t="s">
@@ -7202,8 +7212,8 @@
       <c r="B70" s="7">
         <v>2</v>
       </c>
-      <c r="C70" s="160"/>
-      <c r="D70" s="151"/>
+      <c r="C70" s="157"/>
+      <c r="D70" s="172"/>
       <c r="E70" s="28" t="s">
         <v>104</v>
       </c>
@@ -7230,8 +7240,8 @@
       <c r="B71" s="7">
         <v>3</v>
       </c>
-      <c r="C71" s="160"/>
-      <c r="D71" s="151"/>
+      <c r="C71" s="157"/>
+      <c r="D71" s="172"/>
       <c r="E71" s="8" t="s">
         <v>105</v>
       </c>
@@ -7258,8 +7268,8 @@
       <c r="B72" s="7">
         <v>4</v>
       </c>
-      <c r="C72" s="160"/>
-      <c r="D72" s="151"/>
+      <c r="C72" s="157"/>
+      <c r="D72" s="172"/>
       <c r="E72" s="8" t="s">
         <v>106</v>
       </c>
@@ -7286,8 +7296,8 @@
       <c r="B73" s="7">
         <v>5</v>
       </c>
-      <c r="C73" s="160"/>
-      <c r="D73" s="151"/>
+      <c r="C73" s="157"/>
+      <c r="D73" s="172"/>
       <c r="E73" s="28" t="s">
         <v>107</v>
       </c>
@@ -7314,8 +7324,8 @@
       <c r="B74" s="7">
         <v>6</v>
       </c>
-      <c r="C74" s="160"/>
-      <c r="D74" s="151"/>
+      <c r="C74" s="157"/>
+      <c r="D74" s="172"/>
       <c r="E74" s="28" t="s">
         <v>108</v>
       </c>
@@ -7333,15 +7343,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="13.8">
+    <row r="75" spans="1:10" ht="124.2">
       <c r="A75" s="6">
         <v>71</v>
       </c>
       <c r="B75" s="7">
         <v>7</v>
       </c>
-      <c r="C75" s="160"/>
-      <c r="D75" s="151"/>
+      <c r="C75" s="157"/>
+      <c r="D75" s="172"/>
       <c r="E75" s="28" t="s">
         <v>109</v>
       </c>
@@ -7351,9 +7361,15 @@
       <c r="G75" s="10">
         <v>2</v>
       </c>
-      <c r="H75" s="11"/>
-      <c r="I75" s="11"/>
-      <c r="J75" s="11"/>
+      <c r="H75" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I75" s="125" t="s">
+        <v>730</v>
+      </c>
+      <c r="J75" s="126" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="76" spans="1:10" ht="13.8">
       <c r="A76" s="6">
@@ -7362,8 +7378,8 @@
       <c r="B76" s="7">
         <v>8</v>
       </c>
-      <c r="C76" s="160"/>
-      <c r="D76" s="151"/>
+      <c r="C76" s="157"/>
+      <c r="D76" s="172"/>
       <c r="E76" s="8" t="s">
         <v>110</v>
       </c>
@@ -7373,9 +7389,13 @@
       <c r="G76" s="10">
         <v>2</v>
       </c>
-      <c r="H76" s="11"/>
+      <c r="H76" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="I76" s="11"/>
-      <c r="J76" s="11"/>
+      <c r="J76" s="11" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="77" spans="1:10" ht="13.8">
       <c r="A77" s="6">
@@ -7384,8 +7404,8 @@
       <c r="B77" s="7">
         <v>9</v>
       </c>
-      <c r="C77" s="160"/>
-      <c r="D77" s="151"/>
+      <c r="C77" s="157"/>
+      <c r="D77" s="172"/>
       <c r="E77" s="8" t="s">
         <v>111</v>
       </c>
@@ -7397,7 +7417,9 @@
       </c>
       <c r="H77" s="11"/>
       <c r="I77" s="11"/>
-      <c r="J77" s="11"/>
+      <c r="J77" s="206" t="s">
+        <v>720</v>
+      </c>
     </row>
     <row r="78" spans="1:10" ht="13.8">
       <c r="A78" s="6">
@@ -7406,8 +7428,8 @@
       <c r="B78" s="7">
         <v>10</v>
       </c>
-      <c r="C78" s="160"/>
-      <c r="D78" s="152"/>
+      <c r="C78" s="157"/>
+      <c r="D78" s="173"/>
       <c r="E78" s="8" t="s">
         <v>112</v>
       </c>
@@ -7428,8 +7450,8 @@
       <c r="B79" s="7">
         <v>11</v>
       </c>
-      <c r="C79" s="160"/>
-      <c r="D79" s="150" t="s">
+      <c r="C79" s="157"/>
+      <c r="D79" s="171" t="s">
         <v>113</v>
       </c>
       <c r="E79" s="8" t="s">
@@ -7452,8 +7474,8 @@
       <c r="B80" s="7">
         <v>12</v>
       </c>
-      <c r="C80" s="160"/>
-      <c r="D80" s="151"/>
+      <c r="C80" s="157"/>
+      <c r="D80" s="172"/>
       <c r="E80" s="8" t="s">
         <v>115</v>
       </c>
@@ -7474,8 +7496,8 @@
       <c r="B81" s="7">
         <v>13</v>
       </c>
-      <c r="C81" s="160"/>
-      <c r="D81" s="151"/>
+      <c r="C81" s="157"/>
+      <c r="D81" s="172"/>
       <c r="E81" s="8" t="s">
         <v>116</v>
       </c>
@@ -7496,8 +7518,8 @@
       <c r="B82" s="7">
         <v>14</v>
       </c>
-      <c r="C82" s="160"/>
-      <c r="D82" s="151"/>
+      <c r="C82" s="157"/>
+      <c r="D82" s="172"/>
       <c r="E82" s="8" t="s">
         <v>117</v>
       </c>
@@ -7518,8 +7540,8 @@
       <c r="B83" s="7">
         <v>15</v>
       </c>
-      <c r="C83" s="160"/>
-      <c r="D83" s="151"/>
+      <c r="C83" s="157"/>
+      <c r="D83" s="172"/>
       <c r="E83" s="8" t="s">
         <v>118</v>
       </c>
@@ -7540,8 +7562,8 @@
       <c r="B84" s="7">
         <v>16</v>
       </c>
-      <c r="C84" s="160"/>
-      <c r="D84" s="152"/>
+      <c r="C84" s="157"/>
+      <c r="D84" s="173"/>
       <c r="E84" s="8" t="s">
         <v>119</v>
       </c>
@@ -7562,8 +7584,8 @@
       <c r="B85" s="7">
         <v>17</v>
       </c>
-      <c r="C85" s="160"/>
-      <c r="D85" s="150" t="s">
+      <c r="C85" s="157"/>
+      <c r="D85" s="171" t="s">
         <v>120</v>
       </c>
       <c r="E85" s="8" t="s">
@@ -7586,8 +7608,8 @@
       <c r="B86" s="7">
         <v>18</v>
       </c>
-      <c r="C86" s="160"/>
-      <c r="D86" s="151"/>
+      <c r="C86" s="157"/>
+      <c r="D86" s="172"/>
       <c r="E86" s="8" t="s">
         <v>122</v>
       </c>
@@ -7608,8 +7630,8 @@
       <c r="B87" s="7">
         <v>19</v>
       </c>
-      <c r="C87" s="160"/>
-      <c r="D87" s="151"/>
+      <c r="C87" s="157"/>
+      <c r="D87" s="172"/>
       <c r="E87" s="29" t="s">
         <v>123</v>
       </c>
@@ -7630,8 +7652,8 @@
       <c r="B88" s="7">
         <v>20</v>
       </c>
-      <c r="C88" s="160"/>
-      <c r="D88" s="151"/>
+      <c r="C88" s="157"/>
+      <c r="D88" s="172"/>
       <c r="E88" s="8" t="s">
         <v>124</v>
       </c>
@@ -7652,8 +7674,8 @@
       <c r="B89" s="7">
         <v>21</v>
       </c>
-      <c r="C89" s="160"/>
-      <c r="D89" s="151"/>
+      <c r="C89" s="157"/>
+      <c r="D89" s="172"/>
       <c r="E89" s="8" t="s">
         <v>125</v>
       </c>
@@ -7674,8 +7696,8 @@
       <c r="B90" s="7">
         <v>22</v>
       </c>
-      <c r="C90" s="160"/>
-      <c r="D90" s="152"/>
+      <c r="C90" s="157"/>
+      <c r="D90" s="173"/>
       <c r="E90" s="8" t="s">
         <v>126</v>
       </c>
@@ -7696,8 +7718,8 @@
       <c r="B91" s="7">
         <v>23</v>
       </c>
-      <c r="C91" s="160"/>
-      <c r="D91" s="150" t="s">
+      <c r="C91" s="157"/>
+      <c r="D91" s="171" t="s">
         <v>127</v>
       </c>
       <c r="E91" s="8" t="s">
@@ -7720,8 +7742,8 @@
       <c r="B92" s="7">
         <v>24</v>
       </c>
-      <c r="C92" s="160"/>
-      <c r="D92" s="151"/>
+      <c r="C92" s="157"/>
+      <c r="D92" s="172"/>
       <c r="E92" s="8" t="s">
         <v>129</v>
       </c>
@@ -7742,8 +7764,8 @@
       <c r="B93" s="7">
         <v>25</v>
       </c>
-      <c r="C93" s="160"/>
-      <c r="D93" s="151"/>
+      <c r="C93" s="157"/>
+      <c r="D93" s="172"/>
       <c r="E93" s="8" t="s">
         <v>130</v>
       </c>
@@ -7764,8 +7786,8 @@
       <c r="B94" s="7">
         <v>26</v>
       </c>
-      <c r="C94" s="160"/>
-      <c r="D94" s="151"/>
+      <c r="C94" s="157"/>
+      <c r="D94" s="172"/>
       <c r="E94" s="8" t="s">
         <v>131</v>
       </c>
@@ -7786,8 +7808,8 @@
       <c r="B95" s="7">
         <v>27</v>
       </c>
-      <c r="C95" s="160"/>
-      <c r="D95" s="151"/>
+      <c r="C95" s="157"/>
+      <c r="D95" s="172"/>
       <c r="E95" s="8" t="s">
         <v>132</v>
       </c>
@@ -7808,8 +7830,8 @@
       <c r="B96" s="7">
         <v>28</v>
       </c>
-      <c r="C96" s="160"/>
-      <c r="D96" s="151"/>
+      <c r="C96" s="157"/>
+      <c r="D96" s="172"/>
       <c r="E96" s="8" t="s">
         <v>133</v>
       </c>
@@ -7830,8 +7852,8 @@
       <c r="B97" s="7">
         <v>29</v>
       </c>
-      <c r="C97" s="160"/>
-      <c r="D97" s="151"/>
+      <c r="C97" s="157"/>
+      <c r="D97" s="172"/>
       <c r="E97" s="8" t="s">
         <v>134</v>
       </c>
@@ -7852,8 +7874,8 @@
       <c r="B98" s="7">
         <v>30</v>
       </c>
-      <c r="C98" s="160"/>
-      <c r="D98" s="151"/>
+      <c r="C98" s="157"/>
+      <c r="D98" s="172"/>
       <c r="E98" s="8" t="s">
         <v>135</v>
       </c>
@@ -7874,8 +7896,8 @@
       <c r="B99" s="7">
         <v>31</v>
       </c>
-      <c r="C99" s="160"/>
-      <c r="D99" s="151"/>
+      <c r="C99" s="157"/>
+      <c r="D99" s="172"/>
       <c r="E99" s="30" t="s">
         <v>136</v>
       </c>
@@ -7896,8 +7918,8 @@
       <c r="B100" s="7">
         <v>32</v>
       </c>
-      <c r="C100" s="160"/>
-      <c r="D100" s="151"/>
+      <c r="C100" s="157"/>
+      <c r="D100" s="172"/>
       <c r="E100" s="8" t="s">
         <v>137</v>
       </c>
@@ -7918,8 +7940,8 @@
       <c r="B101" s="7">
         <v>33</v>
       </c>
-      <c r="C101" s="160"/>
-      <c r="D101" s="151"/>
+      <c r="C101" s="157"/>
+      <c r="D101" s="172"/>
       <c r="E101" s="8" t="s">
         <v>138</v>
       </c>
@@ -7940,8 +7962,8 @@
       <c r="B102" s="7">
         <v>34</v>
       </c>
-      <c r="C102" s="160"/>
-      <c r="D102" s="151"/>
+      <c r="C102" s="157"/>
+      <c r="D102" s="172"/>
       <c r="E102" s="8" t="s">
         <v>139</v>
       </c>
@@ -7962,8 +7984,8 @@
       <c r="B103" s="7">
         <v>35</v>
       </c>
-      <c r="C103" s="160"/>
-      <c r="D103" s="151"/>
+      <c r="C103" s="157"/>
+      <c r="D103" s="172"/>
       <c r="E103" s="8" t="s">
         <v>140</v>
       </c>
@@ -7984,8 +8006,8 @@
       <c r="B104" s="7">
         <v>36</v>
       </c>
-      <c r="C104" s="160"/>
-      <c r="D104" s="151"/>
+      <c r="C104" s="157"/>
+      <c r="D104" s="172"/>
       <c r="E104" s="8" t="s">
         <v>141</v>
       </c>
@@ -8006,8 +8028,8 @@
       <c r="B105" s="7">
         <v>37</v>
       </c>
-      <c r="C105" s="161"/>
-      <c r="D105" s="152"/>
+      <c r="C105" s="158"/>
+      <c r="D105" s="173"/>
       <c r="E105" s="8" t="s">
         <v>142</v>
       </c>
@@ -8022,18 +8044,18 @@
       <c r="J105" s="11"/>
     </row>
     <row r="106" spans="1:10" ht="13.8">
-      <c r="A106" s="171" t="s">
+      <c r="A106" s="189" t="s">
         <v>143</v>
       </c>
-      <c r="B106" s="172"/>
-      <c r="C106" s="172"/>
-      <c r="D106" s="172"/>
-      <c r="E106" s="172"/>
-      <c r="F106" s="172"/>
-      <c r="G106" s="172"/>
-      <c r="H106" s="172"/>
-      <c r="I106" s="172"/>
-      <c r="J106" s="173"/>
+      <c r="B106" s="190"/>
+      <c r="C106" s="190"/>
+      <c r="D106" s="190"/>
+      <c r="E106" s="190"/>
+      <c r="F106" s="190"/>
+      <c r="G106" s="190"/>
+      <c r="H106" s="190"/>
+      <c r="I106" s="190"/>
+      <c r="J106" s="191"/>
     </row>
     <row r="107" spans="1:10" ht="13.8">
       <c r="A107" s="6">
@@ -8042,10 +8064,10 @@
       <c r="B107" s="7">
         <v>1</v>
       </c>
-      <c r="C107" s="162" t="s">
+      <c r="C107" s="159" t="s">
         <v>144</v>
       </c>
-      <c r="D107" s="150" t="s">
+      <c r="D107" s="171" t="s">
         <v>145</v>
       </c>
       <c r="E107" s="8" t="s">
@@ -8068,8 +8090,8 @@
       <c r="B108" s="7">
         <v>2</v>
       </c>
-      <c r="C108" s="163"/>
-      <c r="D108" s="151"/>
+      <c r="C108" s="160"/>
+      <c r="D108" s="172"/>
       <c r="E108" s="8" t="s">
         <v>147</v>
       </c>
@@ -8090,8 +8112,8 @@
       <c r="B109" s="7">
         <v>3</v>
       </c>
-      <c r="C109" s="163"/>
-      <c r="D109" s="151"/>
+      <c r="C109" s="160"/>
+      <c r="D109" s="172"/>
       <c r="E109" s="8" t="s">
         <v>148</v>
       </c>
@@ -8112,8 +8134,8 @@
       <c r="B110" s="7">
         <v>4</v>
       </c>
-      <c r="C110" s="163"/>
-      <c r="D110" s="151"/>
+      <c r="C110" s="160"/>
+      <c r="D110" s="172"/>
       <c r="E110" s="8" t="s">
         <v>149</v>
       </c>
@@ -8134,8 +8156,8 @@
       <c r="B111" s="7">
         <v>5</v>
       </c>
-      <c r="C111" s="163"/>
-      <c r="D111" s="152"/>
+      <c r="C111" s="160"/>
+      <c r="D111" s="173"/>
       <c r="E111" s="8" t="s">
         <v>150</v>
       </c>
@@ -8156,8 +8178,8 @@
       <c r="B112" s="7">
         <v>6</v>
       </c>
-      <c r="C112" s="163"/>
-      <c r="D112" s="150" t="s">
+      <c r="C112" s="160"/>
+      <c r="D112" s="171" t="s">
         <v>151</v>
       </c>
       <c r="E112" s="8" t="s">
@@ -8180,8 +8202,8 @@
       <c r="B113" s="7">
         <v>7</v>
       </c>
-      <c r="C113" s="163"/>
-      <c r="D113" s="151"/>
+      <c r="C113" s="160"/>
+      <c r="D113" s="172"/>
       <c r="E113" s="8" t="s">
         <v>153</v>
       </c>
@@ -8202,8 +8224,8 @@
       <c r="B114" s="7">
         <v>8</v>
       </c>
-      <c r="C114" s="163"/>
-      <c r="D114" s="151"/>
+      <c r="C114" s="160"/>
+      <c r="D114" s="172"/>
       <c r="E114" s="8" t="s">
         <v>154</v>
       </c>
@@ -8224,8 +8246,8 @@
       <c r="B115" s="7">
         <v>9</v>
       </c>
-      <c r="C115" s="163"/>
-      <c r="D115" s="152"/>
+      <c r="C115" s="160"/>
+      <c r="D115" s="173"/>
       <c r="E115" s="8" t="s">
         <v>155</v>
       </c>
@@ -8246,7 +8268,7 @@
       <c r="B116" s="24">
         <v>10</v>
       </c>
-      <c r="C116" s="164"/>
+      <c r="C116" s="161"/>
       <c r="D116" s="31" t="s">
         <v>156</v>
       </c>
@@ -8270,10 +8292,10 @@
       <c r="B117" s="7">
         <v>1</v>
       </c>
-      <c r="C117" s="165" t="s">
+      <c r="C117" s="150" t="s">
         <v>158</v>
       </c>
-      <c r="D117" s="150" t="s">
+      <c r="D117" s="171" t="s">
         <v>159</v>
       </c>
       <c r="E117" s="8" t="s">
@@ -8296,8 +8318,8 @@
       <c r="B118" s="7">
         <v>2</v>
       </c>
-      <c r="C118" s="166"/>
-      <c r="D118" s="151"/>
+      <c r="C118" s="151"/>
+      <c r="D118" s="172"/>
       <c r="E118" s="8" t="s">
         <v>161</v>
       </c>
@@ -8318,8 +8340,8 @@
       <c r="B119" s="7">
         <v>3</v>
       </c>
-      <c r="C119" s="166"/>
-      <c r="D119" s="151"/>
+      <c r="C119" s="151"/>
+      <c r="D119" s="172"/>
       <c r="E119" s="8" t="s">
         <v>162</v>
       </c>
@@ -8340,8 +8362,8 @@
       <c r="B120" s="7">
         <v>4</v>
       </c>
-      <c r="C120" s="166"/>
-      <c r="D120" s="152"/>
+      <c r="C120" s="151"/>
+      <c r="D120" s="173"/>
       <c r="E120" s="8" t="s">
         <v>163</v>
       </c>
@@ -8362,8 +8384,8 @@
       <c r="B121" s="7">
         <v>5</v>
       </c>
-      <c r="C121" s="166"/>
-      <c r="D121" s="150" t="s">
+      <c r="C121" s="151"/>
+      <c r="D121" s="171" t="s">
         <v>164</v>
       </c>
       <c r="E121" s="8" t="s">
@@ -8386,8 +8408,8 @@
       <c r="B122" s="7">
         <v>6</v>
       </c>
-      <c r="C122" s="166"/>
-      <c r="D122" s="152"/>
+      <c r="C122" s="151"/>
+      <c r="D122" s="173"/>
       <c r="E122" s="8" t="s">
         <v>166</v>
       </c>
@@ -8408,8 +8430,8 @@
       <c r="B123" s="7">
         <v>7</v>
       </c>
-      <c r="C123" s="166"/>
-      <c r="D123" s="150" t="s">
+      <c r="C123" s="151"/>
+      <c r="D123" s="171" t="s">
         <v>167</v>
       </c>
       <c r="E123" s="8" t="s">
@@ -8432,8 +8454,8 @@
       <c r="B124" s="7">
         <v>8</v>
       </c>
-      <c r="C124" s="166"/>
-      <c r="D124" s="151"/>
+      <c r="C124" s="151"/>
+      <c r="D124" s="172"/>
       <c r="E124" s="28" t="s">
         <v>169</v>
       </c>
@@ -8454,8 +8476,8 @@
       <c r="B125" s="7">
         <v>9</v>
       </c>
-      <c r="C125" s="167"/>
-      <c r="D125" s="152"/>
+      <c r="C125" s="152"/>
+      <c r="D125" s="173"/>
       <c r="E125" s="8" t="s">
         <v>170</v>
       </c>
@@ -8470,18 +8492,18 @@
       <c r="J125" s="11"/>
     </row>
     <row r="126" spans="1:10" ht="13.8">
-      <c r="A126" s="174" t="s">
+      <c r="A126" s="192" t="s">
         <v>171</v>
       </c>
-      <c r="B126" s="175"/>
-      <c r="C126" s="175"/>
-      <c r="D126" s="175"/>
-      <c r="E126" s="175"/>
-      <c r="F126" s="175"/>
-      <c r="G126" s="175"/>
-      <c r="H126" s="175"/>
-      <c r="I126" s="175"/>
-      <c r="J126" s="176"/>
+      <c r="B126" s="193"/>
+      <c r="C126" s="193"/>
+      <c r="D126" s="193"/>
+      <c r="E126" s="193"/>
+      <c r="F126" s="193"/>
+      <c r="G126" s="193"/>
+      <c r="H126" s="193"/>
+      <c r="I126" s="193"/>
+      <c r="J126" s="194"/>
     </row>
     <row r="127" spans="1:10" ht="13.8">
       <c r="A127" s="6">
@@ -8490,10 +8512,10 @@
       <c r="B127" s="7">
         <v>1</v>
       </c>
-      <c r="C127" s="168" t="s">
+      <c r="C127" s="153" t="s">
         <v>172</v>
       </c>
-      <c r="D127" s="150" t="s">
+      <c r="D127" s="171" t="s">
         <v>173</v>
       </c>
       <c r="E127" s="32" t="s">
@@ -8514,8 +8536,8 @@
       <c r="B128" s="7">
         <v>2</v>
       </c>
-      <c r="C128" s="169"/>
-      <c r="D128" s="151"/>
+      <c r="C128" s="154"/>
+      <c r="D128" s="172"/>
       <c r="E128" s="32" t="s">
         <v>175</v>
       </c>
@@ -8534,8 +8556,8 @@
       <c r="B129" s="7">
         <v>3</v>
       </c>
-      <c r="C129" s="169"/>
-      <c r="D129" s="151"/>
+      <c r="C129" s="154"/>
+      <c r="D129" s="172"/>
       <c r="E129" s="32" t="s">
         <v>176</v>
       </c>
@@ -8554,8 +8576,8 @@
       <c r="B130" s="7">
         <v>4</v>
       </c>
-      <c r="C130" s="169"/>
-      <c r="D130" s="152"/>
+      <c r="C130" s="154"/>
+      <c r="D130" s="173"/>
       <c r="E130" s="32" t="s">
         <v>177</v>
       </c>
@@ -8574,8 +8596,8 @@
       <c r="B131" s="7">
         <v>5</v>
       </c>
-      <c r="C131" s="169"/>
-      <c r="D131" s="150" t="s">
+      <c r="C131" s="154"/>
+      <c r="D131" s="171" t="s">
         <v>178</v>
       </c>
       <c r="E131" s="32" t="s">
@@ -8596,8 +8618,8 @@
       <c r="B132" s="7">
         <v>6</v>
       </c>
-      <c r="C132" s="170"/>
-      <c r="D132" s="152"/>
+      <c r="C132" s="155"/>
+      <c r="D132" s="173"/>
       <c r="E132" s="32" t="s">
         <v>180</v>
       </c>
@@ -8610,18 +8632,18 @@
       <c r="J132" s="11"/>
     </row>
     <row r="133" spans="1:10" ht="13.8">
-      <c r="A133" s="156" t="s">
+      <c r="A133" s="195" t="s">
         <v>181</v>
       </c>
-      <c r="B133" s="157"/>
-      <c r="C133" s="157"/>
-      <c r="D133" s="157"/>
-      <c r="E133" s="157"/>
-      <c r="F133" s="157"/>
-      <c r="G133" s="157"/>
-      <c r="H133" s="157"/>
-      <c r="I133" s="157"/>
-      <c r="J133" s="158"/>
+      <c r="B133" s="196"/>
+      <c r="C133" s="196"/>
+      <c r="D133" s="196"/>
+      <c r="E133" s="196"/>
+      <c r="F133" s="196"/>
+      <c r="G133" s="196"/>
+      <c r="H133" s="196"/>
+      <c r="I133" s="196"/>
+      <c r="J133" s="197"/>
     </row>
     <row r="134" spans="1:10" ht="13.8">
       <c r="A134" s="6">
@@ -8630,10 +8652,10 @@
       <c r="B134" s="7">
         <v>1</v>
       </c>
-      <c r="C134" s="159" t="s">
+      <c r="C134" s="156" t="s">
         <v>182</v>
       </c>
-      <c r="D134" s="150" t="s">
+      <c r="D134" s="171" t="s">
         <v>183</v>
       </c>
       <c r="E134" s="8" t="s">
@@ -8656,8 +8678,8 @@
       <c r="B135" s="7">
         <v>2</v>
       </c>
-      <c r="C135" s="160"/>
-      <c r="D135" s="151"/>
+      <c r="C135" s="157"/>
+      <c r="D135" s="172"/>
       <c r="E135" s="8" t="s">
         <v>185</v>
       </c>
@@ -8678,8 +8700,8 @@
       <c r="B136" s="7">
         <v>3</v>
       </c>
-      <c r="C136" s="160"/>
-      <c r="D136" s="152"/>
+      <c r="C136" s="157"/>
+      <c r="D136" s="173"/>
       <c r="E136" s="8" t="s">
         <v>186</v>
       </c>
@@ -8700,8 +8722,8 @@
       <c r="B137" s="7">
         <v>4</v>
       </c>
-      <c r="C137" s="160"/>
-      <c r="D137" s="150" t="s">
+      <c r="C137" s="157"/>
+      <c r="D137" s="171" t="s">
         <v>187</v>
       </c>
       <c r="E137" s="8" t="s">
@@ -8724,8 +8746,8 @@
       <c r="B138" s="7">
         <v>5</v>
       </c>
-      <c r="C138" s="160"/>
-      <c r="D138" s="151"/>
+      <c r="C138" s="157"/>
+      <c r="D138" s="172"/>
       <c r="E138" s="8" t="s">
         <v>189</v>
       </c>
@@ -8746,8 +8768,8 @@
       <c r="B139" s="7">
         <v>6</v>
       </c>
-      <c r="C139" s="160"/>
-      <c r="D139" s="151"/>
+      <c r="C139" s="157"/>
+      <c r="D139" s="172"/>
       <c r="E139" s="8" t="s">
         <v>190</v>
       </c>
@@ -8768,8 +8790,8 @@
       <c r="B140" s="7">
         <v>7</v>
       </c>
-      <c r="C140" s="160"/>
-      <c r="D140" s="151"/>
+      <c r="C140" s="157"/>
+      <c r="D140" s="172"/>
       <c r="E140" s="8" t="s">
         <v>191</v>
       </c>
@@ -8790,8 +8812,8 @@
       <c r="B141" s="7">
         <v>8</v>
       </c>
-      <c r="C141" s="160"/>
-      <c r="D141" s="151"/>
+      <c r="C141" s="157"/>
+      <c r="D141" s="172"/>
       <c r="E141" s="8" t="s">
         <v>192</v>
       </c>
@@ -8812,8 +8834,8 @@
       <c r="B142" s="7">
         <v>9</v>
       </c>
-      <c r="C142" s="160"/>
-      <c r="D142" s="151"/>
+      <c r="C142" s="157"/>
+      <c r="D142" s="172"/>
       <c r="E142" s="8" t="s">
         <v>193</v>
       </c>
@@ -8834,8 +8856,8 @@
       <c r="B143" s="7">
         <v>10</v>
       </c>
-      <c r="C143" s="160"/>
-      <c r="D143" s="152"/>
+      <c r="C143" s="157"/>
+      <c r="D143" s="173"/>
       <c r="E143" s="8" t="s">
         <v>194</v>
       </c>
@@ -8856,8 +8878,8 @@
       <c r="B144" s="7">
         <v>11</v>
       </c>
-      <c r="C144" s="160"/>
-      <c r="D144" s="150" t="s">
+      <c r="C144" s="157"/>
+      <c r="D144" s="171" t="s">
         <v>195</v>
       </c>
       <c r="E144" s="8" t="s">
@@ -8880,8 +8902,8 @@
       <c r="B145" s="7">
         <v>12</v>
       </c>
-      <c r="C145" s="160"/>
-      <c r="D145" s="151"/>
+      <c r="C145" s="157"/>
+      <c r="D145" s="172"/>
       <c r="E145" s="8" t="s">
         <v>197</v>
       </c>
@@ -8902,8 +8924,8 @@
       <c r="B146" s="7">
         <v>13</v>
       </c>
-      <c r="C146" s="160"/>
-      <c r="D146" s="151"/>
+      <c r="C146" s="157"/>
+      <c r="D146" s="172"/>
       <c r="E146" s="8" t="s">
         <v>198</v>
       </c>
@@ -8924,8 +8946,8 @@
       <c r="B147" s="7">
         <v>14</v>
       </c>
-      <c r="C147" s="160"/>
-      <c r="D147" s="151"/>
+      <c r="C147" s="157"/>
+      <c r="D147" s="172"/>
       <c r="E147" s="8" t="s">
         <v>199</v>
       </c>
@@ -8946,8 +8968,8 @@
       <c r="B148" s="7">
         <v>15</v>
       </c>
-      <c r="C148" s="160"/>
-      <c r="D148" s="151"/>
+      <c r="C148" s="157"/>
+      <c r="D148" s="172"/>
       <c r="E148" s="8" t="s">
         <v>200</v>
       </c>
@@ -8968,8 +8990,8 @@
       <c r="B149" s="7">
         <v>16</v>
       </c>
-      <c r="C149" s="160"/>
-      <c r="D149" s="151"/>
+      <c r="C149" s="157"/>
+      <c r="D149" s="172"/>
       <c r="E149" s="8" t="s">
         <v>201</v>
       </c>
@@ -8990,8 +9012,8 @@
       <c r="B150" s="7">
         <v>17</v>
       </c>
-      <c r="C150" s="160"/>
-      <c r="D150" s="152"/>
+      <c r="C150" s="157"/>
+      <c r="D150" s="173"/>
       <c r="E150" s="8" t="s">
         <v>202</v>
       </c>
@@ -9012,8 +9034,8 @@
       <c r="B151" s="7">
         <v>18</v>
       </c>
-      <c r="C151" s="160"/>
-      <c r="D151" s="150" t="s">
+      <c r="C151" s="157"/>
+      <c r="D151" s="171" t="s">
         <v>203</v>
       </c>
       <c r="E151" s="8" t="s">
@@ -9036,8 +9058,8 @@
       <c r="B152" s="7">
         <v>19</v>
       </c>
-      <c r="C152" s="160"/>
-      <c r="D152" s="151"/>
+      <c r="C152" s="157"/>
+      <c r="D152" s="172"/>
       <c r="E152" s="8" t="s">
         <v>205</v>
       </c>
@@ -9058,8 +9080,8 @@
       <c r="B153" s="7">
         <v>20</v>
       </c>
-      <c r="C153" s="160"/>
-      <c r="D153" s="151"/>
+      <c r="C153" s="157"/>
+      <c r="D153" s="172"/>
       <c r="E153" s="8" t="s">
         <v>206</v>
       </c>
@@ -9080,8 +9102,8 @@
       <c r="B154" s="7">
         <v>21</v>
       </c>
-      <c r="C154" s="160"/>
-      <c r="D154" s="151"/>
+      <c r="C154" s="157"/>
+      <c r="D154" s="172"/>
       <c r="E154" s="8" t="s">
         <v>207</v>
       </c>
@@ -9102,8 +9124,8 @@
       <c r="B155" s="7">
         <v>22</v>
       </c>
-      <c r="C155" s="160"/>
-      <c r="D155" s="151"/>
+      <c r="C155" s="157"/>
+      <c r="D155" s="172"/>
       <c r="E155" s="8" t="s">
         <v>208</v>
       </c>
@@ -9124,8 +9146,8 @@
       <c r="B156" s="7">
         <v>23</v>
       </c>
-      <c r="C156" s="160"/>
-      <c r="D156" s="152"/>
+      <c r="C156" s="157"/>
+      <c r="D156" s="173"/>
       <c r="E156" s="8" t="s">
         <v>209</v>
       </c>
@@ -9146,8 +9168,8 @@
       <c r="B157" s="7">
         <v>24</v>
       </c>
-      <c r="C157" s="160"/>
-      <c r="D157" s="150" t="s">
+      <c r="C157" s="157"/>
+      <c r="D157" s="171" t="s">
         <v>210</v>
       </c>
       <c r="E157" s="8" t="s">
@@ -9170,8 +9192,8 @@
       <c r="B158" s="7">
         <v>25</v>
       </c>
-      <c r="C158" s="160"/>
-      <c r="D158" s="151"/>
+      <c r="C158" s="157"/>
+      <c r="D158" s="172"/>
       <c r="E158" s="8" t="s">
         <v>212</v>
       </c>
@@ -9192,8 +9214,8 @@
       <c r="B159" s="7">
         <v>26</v>
       </c>
-      <c r="C159" s="160"/>
-      <c r="D159" s="152"/>
+      <c r="C159" s="157"/>
+      <c r="D159" s="173"/>
       <c r="E159" s="8" t="s">
         <v>213</v>
       </c>
@@ -9214,8 +9236,8 @@
       <c r="B160" s="7">
         <v>27</v>
       </c>
-      <c r="C160" s="160"/>
-      <c r="D160" s="150" t="s">
+      <c r="C160" s="157"/>
+      <c r="D160" s="171" t="s">
         <v>214</v>
       </c>
       <c r="E160" s="8" t="s">
@@ -9238,8 +9260,8 @@
       <c r="B161" s="7">
         <v>28</v>
       </c>
-      <c r="C161" s="160"/>
-      <c r="D161" s="151"/>
+      <c r="C161" s="157"/>
+      <c r="D161" s="172"/>
       <c r="E161" s="8" t="s">
         <v>216</v>
       </c>
@@ -9260,8 +9282,8 @@
       <c r="B162" s="7">
         <v>29</v>
       </c>
-      <c r="C162" s="160"/>
-      <c r="D162" s="151"/>
+      <c r="C162" s="157"/>
+      <c r="D162" s="172"/>
       <c r="E162" s="8" t="s">
         <v>217</v>
       </c>
@@ -9282,8 +9304,8 @@
       <c r="B163" s="7">
         <v>30</v>
       </c>
-      <c r="C163" s="160"/>
-      <c r="D163" s="151"/>
+      <c r="C163" s="157"/>
+      <c r="D163" s="172"/>
       <c r="E163" s="8" t="s">
         <v>218</v>
       </c>
@@ -9304,8 +9326,8 @@
       <c r="B164" s="7">
         <v>31</v>
       </c>
-      <c r="C164" s="160"/>
-      <c r="D164" s="151"/>
+      <c r="C164" s="157"/>
+      <c r="D164" s="172"/>
       <c r="E164" s="8" t="s">
         <v>219</v>
       </c>
@@ -9326,8 +9348,8 @@
       <c r="B165" s="7">
         <v>32</v>
       </c>
-      <c r="C165" s="160"/>
-      <c r="D165" s="152"/>
+      <c r="C165" s="157"/>
+      <c r="D165" s="173"/>
       <c r="E165" s="8" t="s">
         <v>220</v>
       </c>
@@ -9348,8 +9370,8 @@
       <c r="B166" s="7">
         <v>33</v>
       </c>
-      <c r="C166" s="160"/>
-      <c r="D166" s="150" t="s">
+      <c r="C166" s="157"/>
+      <c r="D166" s="171" t="s">
         <v>221</v>
       </c>
       <c r="E166" s="8" t="s">
@@ -9372,8 +9394,8 @@
       <c r="B167" s="7">
         <v>34</v>
       </c>
-      <c r="C167" s="160"/>
-      <c r="D167" s="151"/>
+      <c r="C167" s="157"/>
+      <c r="D167" s="172"/>
       <c r="E167" s="8" t="s">
         <v>223</v>
       </c>
@@ -9392,8 +9414,8 @@
       <c r="B168" s="7">
         <v>35</v>
       </c>
-      <c r="C168" s="160"/>
-      <c r="D168" s="151"/>
+      <c r="C168" s="157"/>
+      <c r="D168" s="172"/>
       <c r="E168" s="8" t="s">
         <v>224</v>
       </c>
@@ -9414,8 +9436,8 @@
       <c r="B169" s="7">
         <v>36</v>
       </c>
-      <c r="C169" s="160"/>
-      <c r="D169" s="151"/>
+      <c r="C169" s="157"/>
+      <c r="D169" s="172"/>
       <c r="E169" s="8" t="s">
         <v>225</v>
       </c>
@@ -9436,8 +9458,8 @@
       <c r="B170" s="7">
         <v>37</v>
       </c>
-      <c r="C170" s="160"/>
-      <c r="D170" s="151"/>
+      <c r="C170" s="157"/>
+      <c r="D170" s="172"/>
       <c r="E170" s="8" t="s">
         <v>226</v>
       </c>
@@ -9458,8 +9480,8 @@
       <c r="B171" s="7">
         <v>38</v>
       </c>
-      <c r="C171" s="160"/>
-      <c r="D171" s="151"/>
+      <c r="C171" s="157"/>
+      <c r="D171" s="172"/>
       <c r="E171" s="8" t="s">
         <v>227</v>
       </c>
@@ -9480,8 +9502,8 @@
       <c r="B172" s="7">
         <v>39</v>
       </c>
-      <c r="C172" s="160"/>
-      <c r="D172" s="152"/>
+      <c r="C172" s="157"/>
+      <c r="D172" s="173"/>
       <c r="E172" s="8" t="s">
         <v>228</v>
       </c>
@@ -9502,8 +9524,8 @@
       <c r="B173" s="7">
         <v>40</v>
       </c>
-      <c r="C173" s="160"/>
-      <c r="D173" s="150" t="s">
+      <c r="C173" s="157"/>
+      <c r="D173" s="171" t="s">
         <v>48</v>
       </c>
       <c r="E173" s="11" t="s">
@@ -9526,8 +9548,8 @@
       <c r="B174" s="7">
         <v>41</v>
       </c>
-      <c r="C174" s="160"/>
-      <c r="D174" s="151"/>
+      <c r="C174" s="157"/>
+      <c r="D174" s="172"/>
       <c r="E174" s="8" t="s">
         <v>230</v>
       </c>
@@ -9548,8 +9570,8 @@
       <c r="B175" s="7">
         <v>42</v>
       </c>
-      <c r="C175" s="160"/>
-      <c r="D175" s="151"/>
+      <c r="C175" s="157"/>
+      <c r="D175" s="172"/>
       <c r="E175" s="8" t="s">
         <v>231</v>
       </c>
@@ -9570,8 +9592,8 @@
       <c r="B176" s="24">
         <v>43</v>
       </c>
-      <c r="C176" s="161"/>
-      <c r="D176" s="152"/>
+      <c r="C176" s="158"/>
+      <c r="D176" s="173"/>
       <c r="E176" s="17" t="s">
         <v>232</v>
       </c>
@@ -9592,10 +9614,10 @@
       <c r="B177" s="7">
         <v>1</v>
       </c>
-      <c r="C177" s="162" t="s">
+      <c r="C177" s="159" t="s">
         <v>233</v>
       </c>
-      <c r="D177" s="150" t="s">
+      <c r="D177" s="171" t="s">
         <v>234</v>
       </c>
       <c r="E177" s="8" t="s">
@@ -9618,8 +9640,8 @@
       <c r="B178" s="7">
         <v>2</v>
       </c>
-      <c r="C178" s="163"/>
-      <c r="D178" s="152"/>
+      <c r="C178" s="160"/>
+      <c r="D178" s="173"/>
       <c r="E178" s="8" t="s">
         <v>236</v>
       </c>
@@ -9640,8 +9662,8 @@
       <c r="B179" s="7">
         <v>3</v>
       </c>
-      <c r="C179" s="163"/>
-      <c r="D179" s="150" t="s">
+      <c r="C179" s="160"/>
+      <c r="D179" s="171" t="s">
         <v>237</v>
       </c>
       <c r="E179" s="8" t="s">
@@ -9664,8 +9686,8 @@
       <c r="B180" s="7">
         <v>4</v>
       </c>
-      <c r="C180" s="163"/>
-      <c r="D180" s="151"/>
+      <c r="C180" s="160"/>
+      <c r="D180" s="172"/>
       <c r="E180" s="8" t="s">
         <v>239</v>
       </c>
@@ -9686,8 +9708,8 @@
       <c r="B181" s="7">
         <v>5</v>
       </c>
-      <c r="C181" s="163"/>
-      <c r="D181" s="151"/>
+      <c r="C181" s="160"/>
+      <c r="D181" s="172"/>
       <c r="E181" s="8" t="s">
         <v>240</v>
       </c>
@@ -9708,8 +9730,8 @@
       <c r="B182" s="7">
         <v>6</v>
       </c>
-      <c r="C182" s="163"/>
-      <c r="D182" s="151"/>
+      <c r="C182" s="160"/>
+      <c r="D182" s="172"/>
       <c r="E182" s="8" t="s">
         <v>241</v>
       </c>
@@ -9730,8 +9752,8 @@
       <c r="B183" s="7">
         <v>7</v>
       </c>
-      <c r="C183" s="163"/>
-      <c r="D183" s="151"/>
+      <c r="C183" s="160"/>
+      <c r="D183" s="172"/>
       <c r="E183" s="8" t="s">
         <v>242</v>
       </c>
@@ -9752,8 +9774,8 @@
       <c r="B184" s="7">
         <v>8</v>
       </c>
-      <c r="C184" s="163"/>
-      <c r="D184" s="152"/>
+      <c r="C184" s="160"/>
+      <c r="D184" s="173"/>
       <c r="E184" s="8" t="s">
         <v>243</v>
       </c>
@@ -9774,8 +9796,8 @@
       <c r="B185" s="7">
         <v>9</v>
       </c>
-      <c r="C185" s="163"/>
-      <c r="D185" s="150" t="s">
+      <c r="C185" s="160"/>
+      <c r="D185" s="171" t="s">
         <v>244</v>
       </c>
       <c r="E185" s="8" t="s">
@@ -9798,8 +9820,8 @@
       <c r="B186" s="7">
         <v>10</v>
       </c>
-      <c r="C186" s="163"/>
-      <c r="D186" s="152"/>
+      <c r="C186" s="160"/>
+      <c r="D186" s="173"/>
       <c r="E186" s="8" t="s">
         <v>246</v>
       </c>
@@ -9820,8 +9842,8 @@
       <c r="B187" s="7">
         <v>11</v>
       </c>
-      <c r="C187" s="163"/>
-      <c r="D187" s="150" t="s">
+      <c r="C187" s="160"/>
+      <c r="D187" s="171" t="s">
         <v>247</v>
       </c>
       <c r="E187" s="8" t="s">
@@ -9844,8 +9866,8 @@
       <c r="B188" s="7">
         <v>12</v>
       </c>
-      <c r="C188" s="163"/>
-      <c r="D188" s="151"/>
+      <c r="C188" s="160"/>
+      <c r="D188" s="172"/>
       <c r="E188" s="8" t="s">
         <v>249</v>
       </c>
@@ -9866,8 +9888,8 @@
       <c r="B189" s="7">
         <v>13</v>
       </c>
-      <c r="C189" s="163"/>
-      <c r="D189" s="151"/>
+      <c r="C189" s="160"/>
+      <c r="D189" s="172"/>
       <c r="E189" s="11" t="s">
         <v>250</v>
       </c>
@@ -9888,8 +9910,8 @@
       <c r="B190" s="7">
         <v>14</v>
       </c>
-      <c r="C190" s="163"/>
-      <c r="D190" s="152"/>
+      <c r="C190" s="160"/>
+      <c r="D190" s="173"/>
       <c r="E190" s="8" t="s">
         <v>251</v>
       </c>
@@ -9910,8 +9932,8 @@
       <c r="B191" s="7">
         <v>15</v>
       </c>
-      <c r="C191" s="163"/>
-      <c r="D191" s="150" t="s">
+      <c r="C191" s="160"/>
+      <c r="D191" s="171" t="s">
         <v>252</v>
       </c>
       <c r="E191" s="8" t="s">
@@ -9934,8 +9956,8 @@
       <c r="B192" s="7">
         <v>16</v>
       </c>
-      <c r="C192" s="163"/>
-      <c r="D192" s="151"/>
+      <c r="C192" s="160"/>
+      <c r="D192" s="172"/>
       <c r="E192" s="8" t="s">
         <v>254</v>
       </c>
@@ -9956,8 +9978,8 @@
       <c r="B193" s="7">
         <v>17</v>
       </c>
-      <c r="C193" s="163"/>
-      <c r="D193" s="151"/>
+      <c r="C193" s="160"/>
+      <c r="D193" s="172"/>
       <c r="E193" s="8" t="s">
         <v>255</v>
       </c>
@@ -9978,8 +10000,8 @@
       <c r="B194" s="7">
         <v>18</v>
       </c>
-      <c r="C194" s="163"/>
-      <c r="D194" s="151"/>
+      <c r="C194" s="160"/>
+      <c r="D194" s="172"/>
       <c r="E194" s="8" t="s">
         <v>256</v>
       </c>
@@ -10000,8 +10022,8 @@
       <c r="B195" s="7">
         <v>19</v>
       </c>
-      <c r="C195" s="163"/>
-      <c r="D195" s="151"/>
+      <c r="C195" s="160"/>
+      <c r="D195" s="172"/>
       <c r="E195" s="8" t="s">
         <v>257</v>
       </c>
@@ -10022,8 +10044,8 @@
       <c r="B196" s="7">
         <v>20</v>
       </c>
-      <c r="C196" s="163"/>
-      <c r="D196" s="151"/>
+      <c r="C196" s="160"/>
+      <c r="D196" s="172"/>
       <c r="E196" s="8" t="s">
         <v>258</v>
       </c>
@@ -10044,8 +10066,8 @@
       <c r="B197" s="7">
         <v>21</v>
       </c>
-      <c r="C197" s="163"/>
-      <c r="D197" s="151"/>
+      <c r="C197" s="160"/>
+      <c r="D197" s="172"/>
       <c r="E197" s="8" t="s">
         <v>259</v>
       </c>
@@ -10066,8 +10088,8 @@
       <c r="B198" s="7">
         <v>22</v>
       </c>
-      <c r="C198" s="163"/>
-      <c r="D198" s="152"/>
+      <c r="C198" s="160"/>
+      <c r="D198" s="173"/>
       <c r="E198" s="8" t="s">
         <v>260</v>
       </c>
@@ -10088,8 +10110,8 @@
       <c r="B199" s="7">
         <v>23</v>
       </c>
-      <c r="C199" s="163"/>
-      <c r="D199" s="150" t="s">
+      <c r="C199" s="160"/>
+      <c r="D199" s="171" t="s">
         <v>261</v>
       </c>
       <c r="E199" s="8" t="s">
@@ -10112,8 +10134,8 @@
       <c r="B200" s="7">
         <v>24</v>
       </c>
-      <c r="C200" s="163"/>
-      <c r="D200" s="151"/>
+      <c r="C200" s="160"/>
+      <c r="D200" s="172"/>
       <c r="E200" s="8" t="s">
         <v>263</v>
       </c>
@@ -10134,8 +10156,8 @@
       <c r="B201" s="7">
         <v>25</v>
       </c>
-      <c r="C201" s="163"/>
-      <c r="D201" s="151"/>
+      <c r="C201" s="160"/>
+      <c r="D201" s="172"/>
       <c r="E201" s="8" t="s">
         <v>264</v>
       </c>
@@ -10156,8 +10178,8 @@
       <c r="B202" s="7">
         <v>26</v>
       </c>
-      <c r="C202" s="163"/>
-      <c r="D202" s="152"/>
+      <c r="C202" s="160"/>
+      <c r="D202" s="173"/>
       <c r="E202" s="8" t="s">
         <v>265</v>
       </c>
@@ -10178,8 +10200,8 @@
       <c r="B203" s="7">
         <v>27</v>
       </c>
-      <c r="C203" s="163"/>
-      <c r="D203" s="150" t="s">
+      <c r="C203" s="160"/>
+      <c r="D203" s="171" t="s">
         <v>266</v>
       </c>
       <c r="E203" s="8" t="s">
@@ -10202,8 +10224,8 @@
       <c r="B204" s="24">
         <v>28</v>
       </c>
-      <c r="C204" s="164"/>
-      <c r="D204" s="152"/>
+      <c r="C204" s="161"/>
+      <c r="D204" s="173"/>
       <c r="E204" s="17" t="s">
         <v>268</v>
       </c>
@@ -10224,10 +10246,10 @@
       <c r="B205" s="7">
         <v>1</v>
       </c>
-      <c r="C205" s="165" t="s">
+      <c r="C205" s="150" t="s">
         <v>269</v>
       </c>
-      <c r="D205" s="150" t="s">
+      <c r="D205" s="171" t="s">
         <v>270</v>
       </c>
       <c r="E205" s="8" t="s">
@@ -10250,8 +10272,8 @@
       <c r="B206" s="7">
         <v>2</v>
       </c>
-      <c r="C206" s="166"/>
-      <c r="D206" s="151"/>
+      <c r="C206" s="151"/>
+      <c r="D206" s="172"/>
       <c r="E206" s="8" t="s">
         <v>272</v>
       </c>
@@ -10272,8 +10294,8 @@
       <c r="B207" s="7">
         <v>3</v>
       </c>
-      <c r="C207" s="166"/>
-      <c r="D207" s="151"/>
+      <c r="C207" s="151"/>
+      <c r="D207" s="172"/>
       <c r="E207" s="8" t="s">
         <v>273</v>
       </c>
@@ -10294,8 +10316,8 @@
       <c r="B208" s="7">
         <v>4</v>
       </c>
-      <c r="C208" s="166"/>
-      <c r="D208" s="151"/>
+      <c r="C208" s="151"/>
+      <c r="D208" s="172"/>
       <c r="E208" s="8" t="s">
         <v>274</v>
       </c>
@@ -10316,8 +10338,8 @@
       <c r="B209" s="7">
         <v>5</v>
       </c>
-      <c r="C209" s="166"/>
-      <c r="D209" s="152"/>
+      <c r="C209" s="151"/>
+      <c r="D209" s="173"/>
       <c r="E209" s="8" t="s">
         <v>275</v>
       </c>
@@ -10338,8 +10360,8 @@
       <c r="B210" s="7">
         <v>6</v>
       </c>
-      <c r="C210" s="166"/>
-      <c r="D210" s="150" t="s">
+      <c r="C210" s="151"/>
+      <c r="D210" s="171" t="s">
         <v>276</v>
       </c>
       <c r="E210" s="8" t="s">
@@ -10362,8 +10384,8 @@
       <c r="B211" s="7">
         <v>7</v>
       </c>
-      <c r="C211" s="166"/>
-      <c r="D211" s="152"/>
+      <c r="C211" s="151"/>
+      <c r="D211" s="173"/>
       <c r="E211" s="8" t="s">
         <v>278</v>
       </c>
@@ -10384,8 +10406,8 @@
       <c r="B212" s="7">
         <v>8</v>
       </c>
-      <c r="C212" s="166"/>
-      <c r="D212" s="150" t="s">
+      <c r="C212" s="151"/>
+      <c r="D212" s="171" t="s">
         <v>279</v>
       </c>
       <c r="E212" s="8" t="s">
@@ -10408,8 +10430,8 @@
       <c r="B213" s="7">
         <v>9</v>
       </c>
-      <c r="C213" s="166"/>
-      <c r="D213" s="151"/>
+      <c r="C213" s="151"/>
+      <c r="D213" s="172"/>
       <c r="E213" s="8" t="s">
         <v>281</v>
       </c>
@@ -10430,8 +10452,8 @@
       <c r="B214" s="7">
         <v>10</v>
       </c>
-      <c r="C214" s="167"/>
-      <c r="D214" s="152"/>
+      <c r="C214" s="152"/>
+      <c r="D214" s="173"/>
       <c r="E214" s="8" t="s">
         <v>282</v>
       </c>
@@ -10446,18 +10468,18 @@
       <c r="J214" s="11"/>
     </row>
     <row r="215" spans="1:10" ht="13.8">
-      <c r="A215" s="186" t="s">
+      <c r="A215" s="180" t="s">
         <v>283</v>
       </c>
-      <c r="B215" s="187"/>
-      <c r="C215" s="187"/>
-      <c r="D215" s="187"/>
-      <c r="E215" s="187"/>
-      <c r="F215" s="187"/>
-      <c r="G215" s="187"/>
-      <c r="H215" s="187"/>
-      <c r="I215" s="187"/>
-      <c r="J215" s="188"/>
+      <c r="B215" s="181"/>
+      <c r="C215" s="181"/>
+      <c r="D215" s="181"/>
+      <c r="E215" s="181"/>
+      <c r="F215" s="181"/>
+      <c r="G215" s="181"/>
+      <c r="H215" s="181"/>
+      <c r="I215" s="181"/>
+      <c r="J215" s="182"/>
     </row>
     <row r="216" spans="1:10" ht="13.8">
       <c r="A216" s="6">
@@ -10466,10 +10488,10 @@
       <c r="B216" s="7">
         <v>1</v>
       </c>
-      <c r="C216" s="168" t="s">
+      <c r="C216" s="153" t="s">
         <v>284</v>
       </c>
-      <c r="D216" s="150" t="s">
+      <c r="D216" s="171" t="s">
         <v>285</v>
       </c>
       <c r="E216" s="8" t="s">
@@ -10492,8 +10514,8 @@
       <c r="B217" s="7">
         <v>2</v>
       </c>
-      <c r="C217" s="169"/>
-      <c r="D217" s="151"/>
+      <c r="C217" s="154"/>
+      <c r="D217" s="172"/>
       <c r="E217" s="8" t="s">
         <v>287</v>
       </c>
@@ -10514,8 +10536,8 @@
       <c r="B218" s="7">
         <v>3</v>
       </c>
-      <c r="C218" s="169"/>
-      <c r="D218" s="151"/>
+      <c r="C218" s="154"/>
+      <c r="D218" s="172"/>
       <c r="E218" s="8" t="s">
         <v>288</v>
       </c>
@@ -10536,8 +10558,8 @@
       <c r="B219" s="7">
         <v>4</v>
       </c>
-      <c r="C219" s="169"/>
-      <c r="D219" s="151"/>
+      <c r="C219" s="154"/>
+      <c r="D219" s="172"/>
       <c r="E219" s="8" t="s">
         <v>289</v>
       </c>
@@ -10558,8 +10580,8 @@
       <c r="B220" s="7">
         <v>5</v>
       </c>
-      <c r="C220" s="169"/>
-      <c r="D220" s="151"/>
+      <c r="C220" s="154"/>
+      <c r="D220" s="172"/>
       <c r="E220" s="8" t="s">
         <v>290</v>
       </c>
@@ -10580,8 +10602,8 @@
       <c r="B221" s="7">
         <v>6</v>
       </c>
-      <c r="C221" s="169"/>
-      <c r="D221" s="151"/>
+      <c r="C221" s="154"/>
+      <c r="D221" s="172"/>
       <c r="E221" s="8" t="s">
         <v>291</v>
       </c>
@@ -10602,8 +10624,8 @@
       <c r="B222" s="7">
         <v>7</v>
       </c>
-      <c r="C222" s="169"/>
-      <c r="D222" s="151"/>
+      <c r="C222" s="154"/>
+      <c r="D222" s="172"/>
       <c r="E222" s="8" t="s">
         <v>292</v>
       </c>
@@ -10624,8 +10646,8 @@
       <c r="B223" s="7">
         <v>8</v>
       </c>
-      <c r="C223" s="169"/>
-      <c r="D223" s="151"/>
+      <c r="C223" s="154"/>
+      <c r="D223" s="172"/>
       <c r="E223" s="8" t="s">
         <v>293</v>
       </c>
@@ -10646,8 +10668,8 @@
       <c r="B224" s="7">
         <v>9</v>
       </c>
-      <c r="C224" s="169"/>
-      <c r="D224" s="151"/>
+      <c r="C224" s="154"/>
+      <c r="D224" s="172"/>
       <c r="E224" s="8" t="s">
         <v>294</v>
       </c>
@@ -10668,8 +10690,8 @@
       <c r="B225" s="7">
         <v>10</v>
       </c>
-      <c r="C225" s="169"/>
-      <c r="D225" s="152"/>
+      <c r="C225" s="154"/>
+      <c r="D225" s="173"/>
       <c r="E225" s="8" t="s">
         <v>295</v>
       </c>
@@ -10690,8 +10712,8 @@
       <c r="B226" s="7">
         <v>11</v>
       </c>
-      <c r="C226" s="169"/>
-      <c r="D226" s="150" t="s">
+      <c r="C226" s="154"/>
+      <c r="D226" s="171" t="s">
         <v>296</v>
       </c>
       <c r="E226" s="8" t="s">
@@ -10714,8 +10736,8 @@
       <c r="B227" s="7">
         <v>12</v>
       </c>
-      <c r="C227" s="169"/>
-      <c r="D227" s="151"/>
+      <c r="C227" s="154"/>
+      <c r="D227" s="172"/>
       <c r="E227" s="8" t="s">
         <v>298</v>
       </c>
@@ -10736,8 +10758,8 @@
       <c r="B228" s="7">
         <v>13</v>
       </c>
-      <c r="C228" s="169"/>
-      <c r="D228" s="151"/>
+      <c r="C228" s="154"/>
+      <c r="D228" s="172"/>
       <c r="E228" s="8" t="s">
         <v>299</v>
       </c>
@@ -10758,8 +10780,8 @@
       <c r="B229" s="7">
         <v>14</v>
       </c>
-      <c r="C229" s="169"/>
-      <c r="D229" s="151"/>
+      <c r="C229" s="154"/>
+      <c r="D229" s="172"/>
       <c r="E229" s="8" t="s">
         <v>300</v>
       </c>
@@ -10780,8 +10802,8 @@
       <c r="B230" s="7">
         <v>15</v>
       </c>
-      <c r="C230" s="169"/>
-      <c r="D230" s="151"/>
+      <c r="C230" s="154"/>
+      <c r="D230" s="172"/>
       <c r="E230" s="8" t="s">
         <v>301</v>
       </c>
@@ -10802,8 +10824,8 @@
       <c r="B231" s="7">
         <v>16</v>
       </c>
-      <c r="C231" s="169"/>
-      <c r="D231" s="151"/>
+      <c r="C231" s="154"/>
+      <c r="D231" s="172"/>
       <c r="E231" s="8" t="s">
         <v>302</v>
       </c>
@@ -10824,8 +10846,8 @@
       <c r="B232" s="7">
         <v>17</v>
       </c>
-      <c r="C232" s="169"/>
-      <c r="D232" s="151"/>
+      <c r="C232" s="154"/>
+      <c r="D232" s="172"/>
       <c r="E232" s="8" t="s">
         <v>303</v>
       </c>
@@ -10846,8 +10868,8 @@
       <c r="B233" s="7">
         <v>18</v>
       </c>
-      <c r="C233" s="169"/>
-      <c r="D233" s="152"/>
+      <c r="C233" s="154"/>
+      <c r="D233" s="173"/>
       <c r="E233" s="8" t="s">
         <v>304</v>
       </c>
@@ -10868,8 +10890,8 @@
       <c r="B234" s="7">
         <v>19</v>
       </c>
-      <c r="C234" s="169"/>
-      <c r="D234" s="150" t="s">
+      <c r="C234" s="154"/>
+      <c r="D234" s="171" t="s">
         <v>305</v>
       </c>
       <c r="E234" s="8" t="s">
@@ -10892,8 +10914,8 @@
       <c r="B235" s="7">
         <v>20</v>
       </c>
-      <c r="C235" s="169"/>
-      <c r="D235" s="151"/>
+      <c r="C235" s="154"/>
+      <c r="D235" s="172"/>
       <c r="E235" s="8" t="s">
         <v>307</v>
       </c>
@@ -10914,8 +10936,8 @@
       <c r="B236" s="7">
         <v>21</v>
       </c>
-      <c r="C236" s="169"/>
-      <c r="D236" s="151"/>
+      <c r="C236" s="154"/>
+      <c r="D236" s="172"/>
       <c r="E236" s="8" t="s">
         <v>308</v>
       </c>
@@ -10936,8 +10958,8 @@
       <c r="B237" s="7">
         <v>22</v>
       </c>
-      <c r="C237" s="169"/>
-      <c r="D237" s="151"/>
+      <c r="C237" s="154"/>
+      <c r="D237" s="172"/>
       <c r="E237" s="8" t="s">
         <v>309</v>
       </c>
@@ -10958,8 +10980,8 @@
       <c r="B238" s="7">
         <v>23</v>
       </c>
-      <c r="C238" s="169"/>
-      <c r="D238" s="151"/>
+      <c r="C238" s="154"/>
+      <c r="D238" s="172"/>
       <c r="E238" s="8" t="s">
         <v>310</v>
       </c>
@@ -10980,8 +11002,8 @@
       <c r="B239" s="7">
         <v>24</v>
       </c>
-      <c r="C239" s="169"/>
-      <c r="D239" s="151"/>
+      <c r="C239" s="154"/>
+      <c r="D239" s="172"/>
       <c r="E239" s="8" t="s">
         <v>311</v>
       </c>
@@ -11002,8 +11024,8 @@
       <c r="B240" s="7">
         <v>25</v>
       </c>
-      <c r="C240" s="169"/>
-      <c r="D240" s="152"/>
+      <c r="C240" s="154"/>
+      <c r="D240" s="173"/>
       <c r="E240" s="8" t="s">
         <v>312</v>
       </c>
@@ -11024,8 +11046,8 @@
       <c r="B241" s="7">
         <v>26</v>
       </c>
-      <c r="C241" s="169"/>
-      <c r="D241" s="150" t="s">
+      <c r="C241" s="154"/>
+      <c r="D241" s="171" t="s">
         <v>313</v>
       </c>
       <c r="E241" s="8" t="s">
@@ -11048,8 +11070,8 @@
       <c r="B242" s="7">
         <v>27</v>
       </c>
-      <c r="C242" s="169"/>
-      <c r="D242" s="151"/>
+      <c r="C242" s="154"/>
+      <c r="D242" s="172"/>
       <c r="E242" s="8" t="s">
         <v>315</v>
       </c>
@@ -11070,8 +11092,8 @@
       <c r="B243" s="7">
         <v>28</v>
       </c>
-      <c r="C243" s="169"/>
-      <c r="D243" s="152"/>
+      <c r="C243" s="154"/>
+      <c r="D243" s="173"/>
       <c r="E243" s="8" t="s">
         <v>316</v>
       </c>
@@ -11092,8 +11114,8 @@
       <c r="B244" s="7">
         <v>29</v>
       </c>
-      <c r="C244" s="169"/>
-      <c r="D244" s="150" t="s">
+      <c r="C244" s="154"/>
+      <c r="D244" s="171" t="s">
         <v>317</v>
       </c>
       <c r="E244" s="8" t="s">
@@ -11116,8 +11138,8 @@
       <c r="B245" s="7">
         <v>30</v>
       </c>
-      <c r="C245" s="169"/>
-      <c r="D245" s="151"/>
+      <c r="C245" s="154"/>
+      <c r="D245" s="172"/>
       <c r="E245" s="8" t="s">
         <v>319</v>
       </c>
@@ -11138,8 +11160,8 @@
       <c r="B246" s="7">
         <v>31</v>
       </c>
-      <c r="C246" s="169"/>
-      <c r="D246" s="151"/>
+      <c r="C246" s="154"/>
+      <c r="D246" s="172"/>
       <c r="E246" s="8" t="s">
         <v>320</v>
       </c>
@@ -11160,8 +11182,8 @@
       <c r="B247" s="7">
         <v>32</v>
       </c>
-      <c r="C247" s="169"/>
-      <c r="D247" s="151"/>
+      <c r="C247" s="154"/>
+      <c r="D247" s="172"/>
       <c r="E247" s="8" t="s">
         <v>321</v>
       </c>
@@ -11182,8 +11204,8 @@
       <c r="B248" s="7">
         <v>33</v>
       </c>
-      <c r="C248" s="169"/>
-      <c r="D248" s="151"/>
+      <c r="C248" s="154"/>
+      <c r="D248" s="172"/>
       <c r="E248" s="8" t="s">
         <v>322</v>
       </c>
@@ -11204,8 +11226,8 @@
       <c r="B249" s="24">
         <v>34</v>
       </c>
-      <c r="C249" s="170"/>
-      <c r="D249" s="152"/>
+      <c r="C249" s="155"/>
+      <c r="D249" s="173"/>
       <c r="E249" s="17" t="s">
         <v>323</v>
       </c>
@@ -11226,10 +11248,10 @@
       <c r="B250" s="7">
         <v>1</v>
       </c>
-      <c r="C250" s="159" t="s">
+      <c r="C250" s="156" t="s">
         <v>324</v>
       </c>
-      <c r="D250" s="150" t="s">
+      <c r="D250" s="171" t="s">
         <v>325</v>
       </c>
       <c r="E250" s="8" t="s">
@@ -11252,8 +11274,8 @@
       <c r="B251" s="7">
         <v>2</v>
       </c>
-      <c r="C251" s="160"/>
-      <c r="D251" s="151"/>
+      <c r="C251" s="157"/>
+      <c r="D251" s="172"/>
       <c r="E251" s="8" t="s">
         <v>327</v>
       </c>
@@ -11274,8 +11296,8 @@
       <c r="B252" s="7">
         <v>3</v>
       </c>
-      <c r="C252" s="160"/>
-      <c r="D252" s="151"/>
+      <c r="C252" s="157"/>
+      <c r="D252" s="172"/>
       <c r="E252" s="8" t="s">
         <v>328</v>
       </c>
@@ -11296,8 +11318,8 @@
       <c r="B253" s="7">
         <v>4</v>
       </c>
-      <c r="C253" s="160"/>
-      <c r="D253" s="151"/>
+      <c r="C253" s="157"/>
+      <c r="D253" s="172"/>
       <c r="E253" s="8" t="s">
         <v>329</v>
       </c>
@@ -11318,8 +11340,8 @@
       <c r="B254" s="7">
         <v>5</v>
       </c>
-      <c r="C254" s="160"/>
-      <c r="D254" s="151"/>
+      <c r="C254" s="157"/>
+      <c r="D254" s="172"/>
       <c r="E254" s="8" t="s">
         <v>330</v>
       </c>
@@ -11340,8 +11362,8 @@
       <c r="B255" s="7">
         <v>6</v>
       </c>
-      <c r="C255" s="160"/>
-      <c r="D255" s="151"/>
+      <c r="C255" s="157"/>
+      <c r="D255" s="172"/>
       <c r="E255" s="8" t="s">
         <v>331</v>
       </c>
@@ -11362,8 +11384,8 @@
       <c r="B256" s="7">
         <v>7</v>
       </c>
-      <c r="C256" s="160"/>
-      <c r="D256" s="151"/>
+      <c r="C256" s="157"/>
+      <c r="D256" s="172"/>
       <c r="E256" s="8" t="s">
         <v>332</v>
       </c>
@@ -11384,8 +11406,8 @@
       <c r="B257" s="7">
         <v>8</v>
       </c>
-      <c r="C257" s="160"/>
-      <c r="D257" s="152"/>
+      <c r="C257" s="157"/>
+      <c r="D257" s="173"/>
       <c r="E257" s="8" t="s">
         <v>333</v>
       </c>
@@ -11406,8 +11428,8 @@
       <c r="B258" s="7">
         <v>9</v>
       </c>
-      <c r="C258" s="160"/>
-      <c r="D258" s="150" t="s">
+      <c r="C258" s="157"/>
+      <c r="D258" s="171" t="s">
         <v>334</v>
       </c>
       <c r="E258" s="8" t="s">
@@ -11430,8 +11452,8 @@
       <c r="B259" s="7">
         <v>10</v>
       </c>
-      <c r="C259" s="160"/>
-      <c r="D259" s="152"/>
+      <c r="C259" s="157"/>
+      <c r="D259" s="173"/>
       <c r="E259" s="8" t="s">
         <v>336</v>
       </c>
@@ -11452,8 +11474,8 @@
       <c r="B260" s="7">
         <v>11</v>
       </c>
-      <c r="C260" s="160"/>
-      <c r="D260" s="150" t="s">
+      <c r="C260" s="157"/>
+      <c r="D260" s="171" t="s">
         <v>337</v>
       </c>
       <c r="E260" s="8" t="s">
@@ -11476,8 +11498,8 @@
       <c r="B261" s="7">
         <v>12</v>
       </c>
-      <c r="C261" s="160"/>
-      <c r="D261" s="151"/>
+      <c r="C261" s="157"/>
+      <c r="D261" s="172"/>
       <c r="E261" s="8" t="s">
         <v>339</v>
       </c>
@@ -11498,8 +11520,8 @@
       <c r="B262" s="7">
         <v>13</v>
       </c>
-      <c r="C262" s="160"/>
-      <c r="D262" s="151"/>
+      <c r="C262" s="157"/>
+      <c r="D262" s="172"/>
       <c r="E262" s="8" t="s">
         <v>340</v>
       </c>
@@ -11520,8 +11542,8 @@
       <c r="B263" s="7">
         <v>14</v>
       </c>
-      <c r="C263" s="160"/>
-      <c r="D263" s="151"/>
+      <c r="C263" s="157"/>
+      <c r="D263" s="172"/>
       <c r="E263" s="8" t="s">
         <v>341</v>
       </c>
@@ -11542,8 +11564,8 @@
       <c r="B264" s="7">
         <v>15</v>
       </c>
-      <c r="C264" s="160"/>
-      <c r="D264" s="151"/>
+      <c r="C264" s="157"/>
+      <c r="D264" s="172"/>
       <c r="E264" s="8" t="s">
         <v>342</v>
       </c>
@@ -11564,8 +11586,8 @@
       <c r="B265" s="24">
         <v>16</v>
       </c>
-      <c r="C265" s="161"/>
-      <c r="D265" s="152"/>
+      <c r="C265" s="158"/>
+      <c r="D265" s="173"/>
       <c r="E265" s="17" t="s">
         <v>343</v>
       </c>
@@ -11586,10 +11608,10 @@
       <c r="B266" s="7">
         <v>1</v>
       </c>
-      <c r="C266" s="162" t="s">
+      <c r="C266" s="159" t="s">
         <v>344</v>
       </c>
-      <c r="D266" s="150" t="s">
+      <c r="D266" s="171" t="s">
         <v>345</v>
       </c>
       <c r="E266" s="8" t="s">
@@ -11612,8 +11634,8 @@
       <c r="B267" s="7">
         <v>2</v>
       </c>
-      <c r="C267" s="163"/>
-      <c r="D267" s="151"/>
+      <c r="C267" s="160"/>
+      <c r="D267" s="172"/>
       <c r="E267" s="8" t="s">
         <v>347</v>
       </c>
@@ -11634,8 +11656,8 @@
       <c r="B268" s="7">
         <v>3</v>
       </c>
-      <c r="C268" s="163"/>
-      <c r="D268" s="151"/>
+      <c r="C268" s="160"/>
+      <c r="D268" s="172"/>
       <c r="E268" s="8" t="s">
         <v>348</v>
       </c>
@@ -11656,8 +11678,8 @@
       <c r="B269" s="7">
         <v>4</v>
       </c>
-      <c r="C269" s="163"/>
-      <c r="D269" s="151"/>
+      <c r="C269" s="160"/>
+      <c r="D269" s="172"/>
       <c r="E269" s="8" t="s">
         <v>349</v>
       </c>
@@ -11678,8 +11700,8 @@
       <c r="B270" s="7">
         <v>5</v>
       </c>
-      <c r="C270" s="163"/>
-      <c r="D270" s="152"/>
+      <c r="C270" s="160"/>
+      <c r="D270" s="173"/>
       <c r="E270" s="8" t="s">
         <v>350</v>
       </c>
@@ -11700,8 +11722,8 @@
       <c r="B271" s="7">
         <v>6</v>
       </c>
-      <c r="C271" s="163"/>
-      <c r="D271" s="150" t="s">
+      <c r="C271" s="160"/>
+      <c r="D271" s="171" t="s">
         <v>351</v>
       </c>
       <c r="E271" s="8" t="s">
@@ -11724,8 +11746,8 @@
       <c r="B272" s="7">
         <v>7</v>
       </c>
-      <c r="C272" s="164"/>
-      <c r="D272" s="152"/>
+      <c r="C272" s="161"/>
+      <c r="D272" s="173"/>
       <c r="E272" s="8" t="s">
         <v>353</v>
       </c>
@@ -11760,10 +11782,10 @@
       <c r="B274" s="7">
         <v>1</v>
       </c>
-      <c r="C274" s="177" t="s">
+      <c r="C274" s="162" t="s">
         <v>355</v>
       </c>
-      <c r="D274" s="180" t="s">
+      <c r="D274" s="174" t="s">
         <v>356</v>
       </c>
       <c r="E274" s="13" t="s">
@@ -11786,8 +11808,8 @@
       <c r="B275" s="7">
         <v>2</v>
       </c>
-      <c r="C275" s="178"/>
-      <c r="D275" s="181"/>
+      <c r="C275" s="163"/>
+      <c r="D275" s="175"/>
       <c r="E275" s="13" t="s">
         <v>358</v>
       </c>
@@ -11808,8 +11830,8 @@
       <c r="B276" s="7">
         <v>3</v>
       </c>
-      <c r="C276" s="178"/>
-      <c r="D276" s="181"/>
+      <c r="C276" s="163"/>
+      <c r="D276" s="175"/>
       <c r="E276" s="8" t="s">
         <v>359</v>
       </c>
@@ -11830,8 +11852,8 @@
       <c r="B277" s="7">
         <v>4</v>
       </c>
-      <c r="C277" s="178"/>
-      <c r="D277" s="181"/>
+      <c r="C277" s="163"/>
+      <c r="D277" s="175"/>
       <c r="E277" s="8" t="s">
         <v>360</v>
       </c>
@@ -11852,8 +11874,8 @@
       <c r="B278" s="7">
         <v>5</v>
       </c>
-      <c r="C278" s="178"/>
-      <c r="D278" s="181"/>
+      <c r="C278" s="163"/>
+      <c r="D278" s="175"/>
       <c r="E278" s="8" t="s">
         <v>361</v>
       </c>
@@ -11874,8 +11896,8 @@
       <c r="B279" s="7">
         <v>6</v>
       </c>
-      <c r="C279" s="178"/>
-      <c r="D279" s="181"/>
+      <c r="C279" s="163"/>
+      <c r="D279" s="175"/>
       <c r="E279" s="8" t="s">
         <v>362</v>
       </c>
@@ -11896,8 +11918,8 @@
       <c r="B280" s="7">
         <v>7</v>
       </c>
-      <c r="C280" s="178"/>
-      <c r="D280" s="181"/>
+      <c r="C280" s="163"/>
+      <c r="D280" s="175"/>
       <c r="E280" s="8" t="s">
         <v>363</v>
       </c>
@@ -11918,8 +11940,8 @@
       <c r="B281" s="7">
         <v>8</v>
       </c>
-      <c r="C281" s="178"/>
-      <c r="D281" s="182"/>
+      <c r="C281" s="163"/>
+      <c r="D281" s="176"/>
       <c r="E281" s="13" t="s">
         <v>364</v>
       </c>
@@ -11940,8 +11962,8 @@
       <c r="B282" s="7">
         <v>9</v>
       </c>
-      <c r="C282" s="178"/>
-      <c r="D282" s="180" t="s">
+      <c r="C282" s="163"/>
+      <c r="D282" s="174" t="s">
         <v>365</v>
       </c>
       <c r="E282" s="8" t="s">
@@ -11964,8 +11986,8 @@
       <c r="B283" s="7">
         <v>10</v>
       </c>
-      <c r="C283" s="178"/>
-      <c r="D283" s="181"/>
+      <c r="C283" s="163"/>
+      <c r="D283" s="175"/>
       <c r="E283" s="13" t="s">
         <v>367</v>
       </c>
@@ -11986,8 +12008,8 @@
       <c r="B284" s="7">
         <v>11</v>
       </c>
-      <c r="C284" s="178"/>
-      <c r="D284" s="181"/>
+      <c r="C284" s="163"/>
+      <c r="D284" s="175"/>
       <c r="E284" s="13" t="s">
         <v>368</v>
       </c>
@@ -12008,8 +12030,8 @@
       <c r="B285" s="7">
         <v>12</v>
       </c>
-      <c r="C285" s="178"/>
-      <c r="D285" s="181"/>
+      <c r="C285" s="163"/>
+      <c r="D285" s="175"/>
       <c r="E285" s="13" t="s">
         <v>369</v>
       </c>
@@ -12030,8 +12052,8 @@
       <c r="B286" s="7">
         <v>13</v>
       </c>
-      <c r="C286" s="178"/>
-      <c r="D286" s="181"/>
+      <c r="C286" s="163"/>
+      <c r="D286" s="175"/>
       <c r="E286" s="13" t="s">
         <v>370</v>
       </c>
@@ -12052,8 +12074,8 @@
       <c r="B287" s="7">
         <v>14</v>
       </c>
-      <c r="C287" s="178"/>
-      <c r="D287" s="181"/>
+      <c r="C287" s="163"/>
+      <c r="D287" s="175"/>
       <c r="E287" s="13" t="s">
         <v>371</v>
       </c>
@@ -12074,8 +12096,8 @@
       <c r="B288" s="7">
         <v>15</v>
       </c>
-      <c r="C288" s="178"/>
-      <c r="D288" s="182"/>
+      <c r="C288" s="163"/>
+      <c r="D288" s="176"/>
       <c r="E288" s="13" t="s">
         <v>372</v>
       </c>
@@ -12096,8 +12118,8 @@
       <c r="B289" s="7">
         <v>16</v>
       </c>
-      <c r="C289" s="178"/>
-      <c r="D289" s="180" t="s">
+      <c r="C289" s="163"/>
+      <c r="D289" s="174" t="s">
         <v>373</v>
       </c>
       <c r="E289" s="13" t="s">
@@ -12120,8 +12142,8 @@
       <c r="B290" s="7">
         <v>17</v>
       </c>
-      <c r="C290" s="178"/>
-      <c r="D290" s="181"/>
+      <c r="C290" s="163"/>
+      <c r="D290" s="175"/>
       <c r="E290" s="8" t="s">
         <v>375</v>
       </c>
@@ -12142,8 +12164,8 @@
       <c r="B291" s="7">
         <v>18</v>
       </c>
-      <c r="C291" s="178"/>
-      <c r="D291" s="181"/>
+      <c r="C291" s="163"/>
+      <c r="D291" s="175"/>
       <c r="E291" s="11" t="s">
         <v>376</v>
       </c>
@@ -12164,8 +12186,8 @@
       <c r="B292" s="24">
         <v>19</v>
       </c>
-      <c r="C292" s="179"/>
-      <c r="D292" s="182"/>
+      <c r="C292" s="164"/>
+      <c r="D292" s="176"/>
       <c r="E292" s="20" t="s">
         <v>377</v>
       </c>
@@ -12186,10 +12208,10 @@
       <c r="B293" s="7">
         <v>1</v>
       </c>
-      <c r="C293" s="168" t="s">
+      <c r="C293" s="153" t="s">
         <v>378</v>
       </c>
-      <c r="D293" s="150" t="s">
+      <c r="D293" s="171" t="s">
         <v>379</v>
       </c>
       <c r="E293" s="8" t="s">
@@ -12212,8 +12234,8 @@
       <c r="B294" s="7">
         <v>2</v>
       </c>
-      <c r="C294" s="169"/>
-      <c r="D294" s="151"/>
+      <c r="C294" s="154"/>
+      <c r="D294" s="172"/>
       <c r="E294" s="8" t="s">
         <v>381</v>
       </c>
@@ -12234,8 +12256,8 @@
       <c r="B295" s="7">
         <v>3</v>
       </c>
-      <c r="C295" s="169"/>
-      <c r="D295" s="152"/>
+      <c r="C295" s="154"/>
+      <c r="D295" s="173"/>
       <c r="E295" s="8" t="s">
         <v>382</v>
       </c>
@@ -12254,8 +12276,8 @@
       <c r="B296" s="7">
         <v>4</v>
       </c>
-      <c r="C296" s="169"/>
-      <c r="D296" s="150" t="s">
+      <c r="C296" s="154"/>
+      <c r="D296" s="171" t="s">
         <v>383</v>
       </c>
       <c r="E296" s="37" t="s">
@@ -12278,8 +12300,8 @@
       <c r="B297" s="7">
         <v>5</v>
       </c>
-      <c r="C297" s="169"/>
-      <c r="D297" s="151"/>
+      <c r="C297" s="154"/>
+      <c r="D297" s="172"/>
       <c r="E297" s="8" t="s">
         <v>385</v>
       </c>
@@ -12300,8 +12322,8 @@
       <c r="B298" s="7">
         <v>6</v>
       </c>
-      <c r="C298" s="169"/>
-      <c r="D298" s="151"/>
+      <c r="C298" s="154"/>
+      <c r="D298" s="172"/>
       <c r="E298" s="8" t="s">
         <v>386</v>
       </c>
@@ -12322,8 +12344,8 @@
       <c r="B299" s="7">
         <v>7</v>
       </c>
-      <c r="C299" s="169"/>
-      <c r="D299" s="151"/>
+      <c r="C299" s="154"/>
+      <c r="D299" s="172"/>
       <c r="E299" s="8" t="s">
         <v>387</v>
       </c>
@@ -12344,8 +12366,8 @@
       <c r="B300" s="7">
         <v>8</v>
       </c>
-      <c r="C300" s="169"/>
-      <c r="D300" s="152"/>
+      <c r="C300" s="154"/>
+      <c r="D300" s="173"/>
       <c r="E300" s="8" t="s">
         <v>388</v>
       </c>
@@ -12366,8 +12388,8 @@
       <c r="B301" s="7">
         <v>9</v>
       </c>
-      <c r="C301" s="169"/>
-      <c r="D301" s="150" t="s">
+      <c r="C301" s="154"/>
+      <c r="D301" s="171" t="s">
         <v>389</v>
       </c>
       <c r="E301" s="8" t="s">
@@ -12390,8 +12412,8 @@
       <c r="B302" s="7">
         <v>10</v>
       </c>
-      <c r="C302" s="169"/>
-      <c r="D302" s="151"/>
+      <c r="C302" s="154"/>
+      <c r="D302" s="172"/>
       <c r="E302" s="8" t="s">
         <v>391</v>
       </c>
@@ -12412,8 +12434,8 @@
       <c r="B303" s="7">
         <v>11</v>
       </c>
-      <c r="C303" s="169"/>
-      <c r="D303" s="152"/>
+      <c r="C303" s="154"/>
+      <c r="D303" s="173"/>
       <c r="E303" s="8" t="s">
         <v>392</v>
       </c>
@@ -12434,8 +12456,8 @@
       <c r="B304" s="7">
         <v>12</v>
       </c>
-      <c r="C304" s="169"/>
-      <c r="D304" s="150" t="s">
+      <c r="C304" s="154"/>
+      <c r="D304" s="171" t="s">
         <v>393</v>
       </c>
       <c r="E304" s="8" t="s">
@@ -12458,8 +12480,8 @@
       <c r="B305" s="7">
         <v>13</v>
       </c>
-      <c r="C305" s="169"/>
-      <c r="D305" s="151"/>
+      <c r="C305" s="154"/>
+      <c r="D305" s="172"/>
       <c r="E305" s="8" t="s">
         <v>395</v>
       </c>
@@ -12480,8 +12502,8 @@
       <c r="B306" s="7">
         <v>14</v>
       </c>
-      <c r="C306" s="169"/>
-      <c r="D306" s="151"/>
+      <c r="C306" s="154"/>
+      <c r="D306" s="172"/>
       <c r="E306" s="8" t="s">
         <v>396</v>
       </c>
@@ -12502,8 +12524,8 @@
       <c r="B307" s="24">
         <v>15</v>
       </c>
-      <c r="C307" s="170"/>
-      <c r="D307" s="152"/>
+      <c r="C307" s="155"/>
+      <c r="D307" s="173"/>
       <c r="E307" s="17" t="s">
         <v>397</v>
       </c>
@@ -12524,10 +12546,10 @@
       <c r="B308" s="7">
         <v>1</v>
       </c>
-      <c r="C308" s="195" t="s">
+      <c r="C308" s="165" t="s">
         <v>398</v>
       </c>
-      <c r="D308" s="180" t="s">
+      <c r="D308" s="174" t="s">
         <v>399</v>
       </c>
       <c r="E308" s="13" t="s">
@@ -12550,8 +12572,8 @@
       <c r="B309" s="7">
         <v>2</v>
       </c>
-      <c r="C309" s="196"/>
-      <c r="D309" s="181"/>
+      <c r="C309" s="166"/>
+      <c r="D309" s="175"/>
       <c r="E309" s="8" t="s">
         <v>401</v>
       </c>
@@ -12572,8 +12594,8 @@
       <c r="B310" s="7">
         <v>3</v>
       </c>
-      <c r="C310" s="196"/>
-      <c r="D310" s="181"/>
+      <c r="C310" s="166"/>
+      <c r="D310" s="175"/>
       <c r="E310" s="13" t="s">
         <v>402</v>
       </c>
@@ -12594,8 +12616,8 @@
       <c r="B311" s="7">
         <v>4</v>
       </c>
-      <c r="C311" s="196"/>
-      <c r="D311" s="181"/>
+      <c r="C311" s="166"/>
+      <c r="D311" s="175"/>
       <c r="E311" s="8" t="s">
         <v>403</v>
       </c>
@@ -12616,8 +12638,8 @@
       <c r="B312" s="7">
         <v>5</v>
       </c>
-      <c r="C312" s="196"/>
-      <c r="D312" s="181"/>
+      <c r="C312" s="166"/>
+      <c r="D312" s="175"/>
       <c r="E312" s="13" t="s">
         <v>404</v>
       </c>
@@ -12638,8 +12660,8 @@
       <c r="B313" s="7">
         <v>6</v>
       </c>
-      <c r="C313" s="196"/>
-      <c r="D313" s="181"/>
+      <c r="C313" s="166"/>
+      <c r="D313" s="175"/>
       <c r="E313" s="13" t="s">
         <v>405</v>
       </c>
@@ -12660,8 +12682,8 @@
       <c r="B314" s="7">
         <v>7</v>
       </c>
-      <c r="C314" s="196"/>
-      <c r="D314" s="182"/>
+      <c r="C314" s="166"/>
+      <c r="D314" s="176"/>
       <c r="E314" s="8" t="s">
         <v>406</v>
       </c>
@@ -12682,8 +12704,8 @@
       <c r="B315" s="7">
         <v>8</v>
       </c>
-      <c r="C315" s="196"/>
-      <c r="D315" s="180" t="s">
+      <c r="C315" s="166"/>
+      <c r="D315" s="174" t="s">
         <v>407</v>
       </c>
       <c r="E315" s="13" t="s">
@@ -12706,8 +12728,8 @@
       <c r="B316" s="7">
         <v>9</v>
       </c>
-      <c r="C316" s="196"/>
-      <c r="D316" s="181"/>
+      <c r="C316" s="166"/>
+      <c r="D316" s="175"/>
       <c r="E316" s="8" t="s">
         <v>409</v>
       </c>
@@ -12728,8 +12750,8 @@
       <c r="B317" s="24">
         <v>10</v>
       </c>
-      <c r="C317" s="197"/>
-      <c r="D317" s="182"/>
+      <c r="C317" s="167"/>
+      <c r="D317" s="176"/>
       <c r="E317" s="17" t="s">
         <v>410</v>
       </c>
@@ -12750,10 +12772,10 @@
       <c r="B318" s="7">
         <v>1</v>
       </c>
-      <c r="C318" s="198" t="s">
+      <c r="C318" s="168" t="s">
         <v>411</v>
       </c>
-      <c r="D318" s="180" t="s">
+      <c r="D318" s="174" t="s">
         <v>412</v>
       </c>
       <c r="E318" s="8" t="s">
@@ -12776,8 +12798,8 @@
       <c r="B319" s="7">
         <v>2</v>
       </c>
-      <c r="C319" s="199"/>
-      <c r="D319" s="181"/>
+      <c r="C319" s="169"/>
+      <c r="D319" s="175"/>
       <c r="E319" s="13" t="s">
         <v>414</v>
       </c>
@@ -12798,8 +12820,8 @@
       <c r="B320" s="7">
         <v>3</v>
       </c>
-      <c r="C320" s="199"/>
-      <c r="D320" s="181"/>
+      <c r="C320" s="169"/>
+      <c r="D320" s="175"/>
       <c r="E320" s="8" t="s">
         <v>415</v>
       </c>
@@ -12820,8 +12842,8 @@
       <c r="B321" s="7">
         <v>4</v>
       </c>
-      <c r="C321" s="199"/>
-      <c r="D321" s="181"/>
+      <c r="C321" s="169"/>
+      <c r="D321" s="175"/>
       <c r="E321" s="8" t="s">
         <v>416</v>
       </c>
@@ -12842,8 +12864,8 @@
       <c r="B322" s="7">
         <v>5</v>
       </c>
-      <c r="C322" s="199"/>
-      <c r="D322" s="181"/>
+      <c r="C322" s="169"/>
+      <c r="D322" s="175"/>
       <c r="E322" s="8" t="s">
         <v>417</v>
       </c>
@@ -12864,8 +12886,8 @@
       <c r="B323" s="7">
         <v>6</v>
       </c>
-      <c r="C323" s="199"/>
-      <c r="D323" s="182"/>
+      <c r="C323" s="169"/>
+      <c r="D323" s="176"/>
       <c r="E323" s="29" t="s">
         <v>418</v>
       </c>
@@ -12886,8 +12908,8 @@
       <c r="B324" s="7">
         <v>7</v>
       </c>
-      <c r="C324" s="199"/>
-      <c r="D324" s="180" t="s">
+      <c r="C324" s="169"/>
+      <c r="D324" s="174" t="s">
         <v>419</v>
       </c>
       <c r="E324" s="13" t="s">
@@ -12910,8 +12932,8 @@
       <c r="B325" s="7">
         <v>8</v>
       </c>
-      <c r="C325" s="199"/>
-      <c r="D325" s="181"/>
+      <c r="C325" s="169"/>
+      <c r="D325" s="175"/>
       <c r="E325" s="8" t="s">
         <v>421</v>
       </c>
@@ -12932,8 +12954,8 @@
       <c r="B326" s="7">
         <v>9</v>
       </c>
-      <c r="C326" s="199"/>
-      <c r="D326" s="181"/>
+      <c r="C326" s="169"/>
+      <c r="D326" s="175"/>
       <c r="E326" s="8" t="s">
         <v>422</v>
       </c>
@@ -12954,8 +12976,8 @@
       <c r="B327" s="7">
         <v>10</v>
       </c>
-      <c r="C327" s="199"/>
-      <c r="D327" s="181"/>
+      <c r="C327" s="169"/>
+      <c r="D327" s="175"/>
       <c r="E327" s="8" t="s">
         <v>423</v>
       </c>
@@ -12976,8 +12998,8 @@
       <c r="B328" s="7">
         <v>11</v>
       </c>
-      <c r="C328" s="199"/>
-      <c r="D328" s="182"/>
+      <c r="C328" s="169"/>
+      <c r="D328" s="176"/>
       <c r="E328" s="13" t="s">
         <v>424</v>
       </c>
@@ -12998,8 +13020,8 @@
       <c r="B329" s="7">
         <v>12</v>
       </c>
-      <c r="C329" s="199"/>
-      <c r="D329" s="180" t="s">
+      <c r="C329" s="169"/>
+      <c r="D329" s="174" t="s">
         <v>425</v>
       </c>
       <c r="E329" s="8" t="s">
@@ -13022,8 +13044,8 @@
       <c r="B330" s="7">
         <v>13</v>
       </c>
-      <c r="C330" s="199"/>
-      <c r="D330" s="181"/>
+      <c r="C330" s="169"/>
+      <c r="D330" s="175"/>
       <c r="E330" s="8" t="s">
         <v>427</v>
       </c>
@@ -13044,8 +13066,8 @@
       <c r="B331" s="7">
         <v>14</v>
       </c>
-      <c r="C331" s="199"/>
-      <c r="D331" s="181"/>
+      <c r="C331" s="169"/>
+      <c r="D331" s="175"/>
       <c r="E331" s="8" t="s">
         <v>428</v>
       </c>
@@ -13066,8 +13088,8 @@
       <c r="B332" s="7">
         <v>15</v>
       </c>
-      <c r="C332" s="199"/>
-      <c r="D332" s="181"/>
+      <c r="C332" s="169"/>
+      <c r="D332" s="175"/>
       <c r="E332" s="8" t="s">
         <v>429</v>
       </c>
@@ -13088,8 +13110,8 @@
       <c r="B333" s="7">
         <v>16</v>
       </c>
-      <c r="C333" s="199"/>
-      <c r="D333" s="181"/>
+      <c r="C333" s="169"/>
+      <c r="D333" s="175"/>
       <c r="E333" s="8" t="s">
         <v>430</v>
       </c>
@@ -13110,8 +13132,8 @@
       <c r="B334" s="7">
         <v>17</v>
       </c>
-      <c r="C334" s="199"/>
-      <c r="D334" s="181"/>
+      <c r="C334" s="169"/>
+      <c r="D334" s="175"/>
       <c r="E334" s="8" t="s">
         <v>431</v>
       </c>
@@ -13132,8 +13154,8 @@
       <c r="B335" s="7">
         <v>18</v>
       </c>
-      <c r="C335" s="199"/>
-      <c r="D335" s="181"/>
+      <c r="C335" s="169"/>
+      <c r="D335" s="175"/>
       <c r="E335" s="8" t="s">
         <v>432</v>
       </c>
@@ -13154,8 +13176,8 @@
       <c r="B336" s="7">
         <v>19</v>
       </c>
-      <c r="C336" s="199"/>
-      <c r="D336" s="181"/>
+      <c r="C336" s="169"/>
+      <c r="D336" s="175"/>
       <c r="E336" s="8" t="s">
         <v>433</v>
       </c>
@@ -13176,8 +13198,8 @@
       <c r="B337" s="7">
         <v>20</v>
       </c>
-      <c r="C337" s="199"/>
-      <c r="D337" s="182"/>
+      <c r="C337" s="169"/>
+      <c r="D337" s="176"/>
       <c r="E337" s="13" t="s">
         <v>434</v>
       </c>
@@ -13198,8 +13220,8 @@
       <c r="B338" s="7">
         <v>21</v>
       </c>
-      <c r="C338" s="199"/>
-      <c r="D338" s="180" t="s">
+      <c r="C338" s="169"/>
+      <c r="D338" s="174" t="s">
         <v>435</v>
       </c>
       <c r="E338" s="13" t="s">
@@ -13222,8 +13244,8 @@
       <c r="B339" s="7">
         <v>22</v>
       </c>
-      <c r="C339" s="199"/>
-      <c r="D339" s="181"/>
+      <c r="C339" s="169"/>
+      <c r="D339" s="175"/>
       <c r="E339" s="13" t="s">
         <v>437</v>
       </c>
@@ -13244,8 +13266,8 @@
       <c r="B340" s="7">
         <v>23</v>
       </c>
-      <c r="C340" s="199"/>
-      <c r="D340" s="181"/>
+      <c r="C340" s="169"/>
+      <c r="D340" s="175"/>
       <c r="E340" s="13" t="s">
         <v>438</v>
       </c>
@@ -13266,8 +13288,8 @@
       <c r="B341" s="7">
         <v>24</v>
       </c>
-      <c r="C341" s="199"/>
-      <c r="D341" s="181"/>
+      <c r="C341" s="169"/>
+      <c r="D341" s="175"/>
       <c r="E341" s="13" t="s">
         <v>439</v>
       </c>
@@ -13288,8 +13310,8 @@
       <c r="B342" s="24">
         <v>25</v>
       </c>
-      <c r="C342" s="200"/>
-      <c r="D342" s="182"/>
+      <c r="C342" s="170"/>
+      <c r="D342" s="176"/>
       <c r="E342" s="25" t="s">
         <v>440</v>
       </c>
@@ -13310,10 +13332,10 @@
       <c r="B343" s="7">
         <v>1</v>
       </c>
-      <c r="C343" s="165" t="s">
+      <c r="C343" s="150" t="s">
         <v>441</v>
       </c>
-      <c r="D343" s="150" t="s">
+      <c r="D343" s="171" t="s">
         <v>442</v>
       </c>
       <c r="E343" s="8" t="s">
@@ -13342,8 +13364,8 @@
       <c r="B344" s="7">
         <v>2</v>
       </c>
-      <c r="C344" s="166"/>
-      <c r="D344" s="151"/>
+      <c r="C344" s="151"/>
+      <c r="D344" s="172"/>
       <c r="E344" s="8" t="s">
         <v>444</v>
       </c>
@@ -13370,8 +13392,8 @@
       <c r="B345" s="7">
         <v>3</v>
       </c>
-      <c r="C345" s="166"/>
-      <c r="D345" s="151"/>
+      <c r="C345" s="151"/>
+      <c r="D345" s="172"/>
       <c r="E345" s="8" t="s">
         <v>445</v>
       </c>
@@ -13398,8 +13420,8 @@
       <c r="B346" s="7">
         <v>4</v>
       </c>
-      <c r="C346" s="166"/>
-      <c r="D346" s="151"/>
+      <c r="C346" s="151"/>
+      <c r="D346" s="172"/>
       <c r="E346" s="8" t="s">
         <v>446</v>
       </c>
@@ -13426,8 +13448,8 @@
       <c r="B347" s="7">
         <v>5</v>
       </c>
-      <c r="C347" s="166"/>
-      <c r="D347" s="152"/>
+      <c r="C347" s="151"/>
+      <c r="D347" s="173"/>
       <c r="E347" s="8" t="s">
         <v>447</v>
       </c>
@@ -13454,8 +13476,8 @@
       <c r="B348" s="7">
         <v>6</v>
       </c>
-      <c r="C348" s="166"/>
-      <c r="D348" s="150" t="s">
+      <c r="C348" s="151"/>
+      <c r="D348" s="171" t="s">
         <v>448</v>
       </c>
       <c r="E348" s="8" t="s">
@@ -13482,8 +13504,8 @@
       <c r="B349" s="7">
         <v>7</v>
       </c>
-      <c r="C349" s="166"/>
-      <c r="D349" s="151"/>
+      <c r="C349" s="151"/>
+      <c r="D349" s="172"/>
       <c r="E349" s="8" t="s">
         <v>450</v>
       </c>
@@ -13510,8 +13532,8 @@
       <c r="B350" s="7">
         <v>8</v>
       </c>
-      <c r="C350" s="166"/>
-      <c r="D350" s="151"/>
+      <c r="C350" s="151"/>
+      <c r="D350" s="172"/>
       <c r="E350" s="8" t="s">
         <v>451</v>
       </c>
@@ -13538,8 +13560,8 @@
       <c r="B351" s="7">
         <v>9</v>
       </c>
-      <c r="C351" s="166"/>
-      <c r="D351" s="151"/>
+      <c r="C351" s="151"/>
+      <c r="D351" s="172"/>
       <c r="E351" s="8" t="s">
         <v>452</v>
       </c>
@@ -13562,8 +13584,8 @@
       <c r="B352" s="7">
         <v>10</v>
       </c>
-      <c r="C352" s="166"/>
-      <c r="D352" s="151"/>
+      <c r="C352" s="151"/>
+      <c r="D352" s="172"/>
       <c r="E352" s="8" t="s">
         <v>453</v>
       </c>
@@ -13590,8 +13612,8 @@
       <c r="B353" s="7">
         <v>11</v>
       </c>
-      <c r="C353" s="166"/>
-      <c r="D353" s="152"/>
+      <c r="C353" s="151"/>
+      <c r="D353" s="173"/>
       <c r="E353" s="8" t="s">
         <v>454</v>
       </c>
@@ -13612,8 +13634,8 @@
       <c r="B354" s="7">
         <v>12</v>
       </c>
-      <c r="C354" s="166"/>
-      <c r="D354" s="150" t="s">
+      <c r="C354" s="151"/>
+      <c r="D354" s="171" t="s">
         <v>455</v>
       </c>
       <c r="E354" s="8" t="s">
@@ -13640,8 +13662,8 @@
       <c r="B355" s="7">
         <v>13</v>
       </c>
-      <c r="C355" s="166"/>
-      <c r="D355" s="151"/>
+      <c r="C355" s="151"/>
+      <c r="D355" s="172"/>
       <c r="E355" s="8" t="s">
         <v>457</v>
       </c>
@@ -13668,8 +13690,8 @@
       <c r="B356" s="7">
         <v>14</v>
       </c>
-      <c r="C356" s="166"/>
-      <c r="D356" s="151"/>
+      <c r="C356" s="151"/>
+      <c r="D356" s="172"/>
       <c r="E356" s="8" t="s">
         <v>458</v>
       </c>
@@ -13690,8 +13712,8 @@
       <c r="B357" s="7">
         <v>15</v>
       </c>
-      <c r="C357" s="167"/>
-      <c r="D357" s="152"/>
+      <c r="C357" s="152"/>
+      <c r="D357" s="173"/>
       <c r="E357" s="8" t="s">
         <v>459</v>
       </c>
@@ -13706,18 +13728,18 @@
       <c r="J357" s="11"/>
     </row>
     <row r="358" spans="1:10" ht="13.8">
-      <c r="A358" s="189" t="s">
+      <c r="A358" s="186" t="s">
         <v>460</v>
       </c>
-      <c r="B358" s="190"/>
-      <c r="C358" s="190"/>
-      <c r="D358" s="190"/>
-      <c r="E358" s="190"/>
-      <c r="F358" s="190"/>
-      <c r="G358" s="190"/>
-      <c r="H358" s="190"/>
-      <c r="I358" s="190"/>
-      <c r="J358" s="191"/>
+      <c r="B358" s="187"/>
+      <c r="C358" s="187"/>
+      <c r="D358" s="187"/>
+      <c r="E358" s="187"/>
+      <c r="F358" s="187"/>
+      <c r="G358" s="187"/>
+      <c r="H358" s="187"/>
+      <c r="I358" s="187"/>
+      <c r="J358" s="188"/>
     </row>
     <row r="359" spans="1:10" ht="13.8">
       <c r="A359" s="6">
@@ -13726,10 +13748,10 @@
       <c r="B359" s="7">
         <v>1</v>
       </c>
-      <c r="C359" s="168" t="s">
+      <c r="C359" s="153" t="s">
         <v>461</v>
       </c>
-      <c r="D359" s="150" t="s">
+      <c r="D359" s="171" t="s">
         <v>462</v>
       </c>
       <c r="E359" s="8" t="s">
@@ -13752,8 +13774,8 @@
       <c r="B360" s="7">
         <v>2</v>
       </c>
-      <c r="C360" s="169"/>
-      <c r="D360" s="151"/>
+      <c r="C360" s="154"/>
+      <c r="D360" s="172"/>
       <c r="E360" s="8" t="s">
         <v>464</v>
       </c>
@@ -13774,8 +13796,8 @@
       <c r="B361" s="7">
         <v>3</v>
       </c>
-      <c r="C361" s="169"/>
-      <c r="D361" s="151"/>
+      <c r="C361" s="154"/>
+      <c r="D361" s="172"/>
       <c r="E361" s="8" t="s">
         <v>465</v>
       </c>
@@ -13796,8 +13818,8 @@
       <c r="B362" s="7">
         <v>4</v>
       </c>
-      <c r="C362" s="169"/>
-      <c r="D362" s="151"/>
+      <c r="C362" s="154"/>
+      <c r="D362" s="172"/>
       <c r="E362" s="8" t="s">
         <v>466</v>
       </c>
@@ -13818,8 +13840,8 @@
       <c r="B363" s="7">
         <v>5</v>
       </c>
-      <c r="C363" s="169"/>
-      <c r="D363" s="152"/>
+      <c r="C363" s="154"/>
+      <c r="D363" s="173"/>
       <c r="E363" s="8" t="s">
         <v>467</v>
       </c>
@@ -13840,8 +13862,8 @@
       <c r="B364" s="7">
         <v>6</v>
       </c>
-      <c r="C364" s="169"/>
-      <c r="D364" s="150" t="s">
+      <c r="C364" s="154"/>
+      <c r="D364" s="171" t="s">
         <v>468</v>
       </c>
       <c r="E364" s="8" t="s">
@@ -13864,8 +13886,8 @@
       <c r="B365" s="7">
         <v>7</v>
       </c>
-      <c r="C365" s="169"/>
-      <c r="D365" s="151"/>
+      <c r="C365" s="154"/>
+      <c r="D365" s="172"/>
       <c r="E365" s="8" t="s">
         <v>470</v>
       </c>
@@ -13886,8 +13908,8 @@
       <c r="B366" s="7">
         <v>8</v>
       </c>
-      <c r="C366" s="169"/>
-      <c r="D366" s="151"/>
+      <c r="C366" s="154"/>
+      <c r="D366" s="172"/>
       <c r="E366" s="8" t="s">
         <v>471</v>
       </c>
@@ -13908,8 +13930,8 @@
       <c r="B367" s="7">
         <v>9</v>
       </c>
-      <c r="C367" s="169"/>
-      <c r="D367" s="151"/>
+      <c r="C367" s="154"/>
+      <c r="D367" s="172"/>
       <c r="E367" s="8" t="s">
         <v>472</v>
       </c>
@@ -13930,8 +13952,8 @@
       <c r="B368" s="7">
         <v>10</v>
       </c>
-      <c r="C368" s="169"/>
-      <c r="D368" s="151"/>
+      <c r="C368" s="154"/>
+      <c r="D368" s="172"/>
       <c r="E368" s="8" t="s">
         <v>473</v>
       </c>
@@ -13952,8 +13974,8 @@
       <c r="B369" s="7">
         <v>11</v>
       </c>
-      <c r="C369" s="169"/>
-      <c r="D369" s="151"/>
+      <c r="C369" s="154"/>
+      <c r="D369" s="172"/>
       <c r="E369" s="8" t="s">
         <v>474</v>
       </c>
@@ -13974,8 +13996,8 @@
       <c r="B370" s="7">
         <v>12</v>
       </c>
-      <c r="C370" s="169"/>
-      <c r="D370" s="151"/>
+      <c r="C370" s="154"/>
+      <c r="D370" s="172"/>
       <c r="E370" s="8" t="s">
         <v>475</v>
       </c>
@@ -13996,8 +14018,8 @@
       <c r="B371" s="7">
         <v>13</v>
       </c>
-      <c r="C371" s="169"/>
-      <c r="D371" s="152"/>
+      <c r="C371" s="154"/>
+      <c r="D371" s="173"/>
       <c r="E371" s="8" t="s">
         <v>476</v>
       </c>
@@ -14018,8 +14040,8 @@
       <c r="B372" s="7">
         <v>14</v>
       </c>
-      <c r="C372" s="169"/>
-      <c r="D372" s="150" t="s">
+      <c r="C372" s="154"/>
+      <c r="D372" s="171" t="s">
         <v>477</v>
       </c>
       <c r="E372" s="8" t="s">
@@ -14042,8 +14064,8 @@
       <c r="B373" s="7">
         <v>15</v>
       </c>
-      <c r="C373" s="169"/>
-      <c r="D373" s="151"/>
+      <c r="C373" s="154"/>
+      <c r="D373" s="172"/>
       <c r="E373" s="11" t="s">
         <v>479</v>
       </c>
@@ -14064,8 +14086,8 @@
       <c r="B374" s="7">
         <v>16</v>
       </c>
-      <c r="C374" s="169"/>
-      <c r="D374" s="151"/>
+      <c r="C374" s="154"/>
+      <c r="D374" s="172"/>
       <c r="E374" s="8" t="s">
         <v>480</v>
       </c>
@@ -14086,8 +14108,8 @@
       <c r="B375" s="7">
         <v>17</v>
       </c>
-      <c r="C375" s="169"/>
-      <c r="D375" s="152"/>
+      <c r="C375" s="154"/>
+      <c r="D375" s="173"/>
       <c r="E375" s="8" t="s">
         <v>481</v>
       </c>
@@ -14108,8 +14130,8 @@
       <c r="B376" s="7">
         <v>18</v>
       </c>
-      <c r="C376" s="169"/>
-      <c r="D376" s="150" t="s">
+      <c r="C376" s="154"/>
+      <c r="D376" s="171" t="s">
         <v>482</v>
       </c>
       <c r="E376" s="8" t="s">
@@ -14132,8 +14154,8 @@
       <c r="B377" s="7">
         <v>19</v>
       </c>
-      <c r="C377" s="169"/>
-      <c r="D377" s="151"/>
+      <c r="C377" s="154"/>
+      <c r="D377" s="172"/>
       <c r="E377" s="8" t="s">
         <v>484</v>
       </c>
@@ -14154,8 +14176,8 @@
       <c r="B378" s="7">
         <v>20</v>
       </c>
-      <c r="C378" s="169"/>
-      <c r="D378" s="151"/>
+      <c r="C378" s="154"/>
+      <c r="D378" s="172"/>
       <c r="E378" s="8" t="s">
         <v>485</v>
       </c>
@@ -14176,8 +14198,8 @@
       <c r="B379" s="7">
         <v>21</v>
       </c>
-      <c r="C379" s="169"/>
-      <c r="D379" s="151"/>
+      <c r="C379" s="154"/>
+      <c r="D379" s="172"/>
       <c r="E379" s="8" t="s">
         <v>486</v>
       </c>
@@ -14198,8 +14220,8 @@
       <c r="B380" s="24">
         <v>22</v>
       </c>
-      <c r="C380" s="170"/>
-      <c r="D380" s="152"/>
+      <c r="C380" s="155"/>
+      <c r="D380" s="173"/>
       <c r="E380" s="17" t="s">
         <v>487</v>
       </c>
@@ -14220,10 +14242,10 @@
       <c r="B381" s="7">
         <v>1</v>
       </c>
-      <c r="C381" s="159" t="s">
+      <c r="C381" s="156" t="s">
         <v>488</v>
       </c>
-      <c r="D381" s="150" t="s">
+      <c r="D381" s="171" t="s">
         <v>489</v>
       </c>
       <c r="E381" s="8" t="s">
@@ -14246,8 +14268,8 @@
       <c r="B382" s="7">
         <v>2</v>
       </c>
-      <c r="C382" s="160"/>
-      <c r="D382" s="151"/>
+      <c r="C382" s="157"/>
+      <c r="D382" s="172"/>
       <c r="E382" s="8" t="s">
         <v>491</v>
       </c>
@@ -14268,8 +14290,8 @@
       <c r="B383" s="7">
         <v>3</v>
       </c>
-      <c r="C383" s="160"/>
-      <c r="D383" s="151"/>
+      <c r="C383" s="157"/>
+      <c r="D383" s="172"/>
       <c r="E383" s="8" t="s">
         <v>492</v>
       </c>
@@ -14290,8 +14312,8 @@
       <c r="B384" s="7">
         <v>4</v>
       </c>
-      <c r="C384" s="160"/>
-      <c r="D384" s="151"/>
+      <c r="C384" s="157"/>
+      <c r="D384" s="172"/>
       <c r="E384" s="8" t="s">
         <v>493</v>
       </c>
@@ -14312,8 +14334,8 @@
       <c r="B385" s="7">
         <v>5</v>
       </c>
-      <c r="C385" s="160"/>
-      <c r="D385" s="151"/>
+      <c r="C385" s="157"/>
+      <c r="D385" s="172"/>
       <c r="E385" s="8" t="s">
         <v>494</v>
       </c>
@@ -14334,8 +14356,8 @@
       <c r="B386" s="7">
         <v>6</v>
       </c>
-      <c r="C386" s="160"/>
-      <c r="D386" s="152"/>
+      <c r="C386" s="157"/>
+      <c r="D386" s="173"/>
       <c r="E386" s="8" t="s">
         <v>495</v>
       </c>
@@ -14356,8 +14378,8 @@
       <c r="B387" s="7">
         <v>7</v>
       </c>
-      <c r="C387" s="160"/>
-      <c r="D387" s="150" t="s">
+      <c r="C387" s="157"/>
+      <c r="D387" s="171" t="s">
         <v>496</v>
       </c>
       <c r="E387" s="8" t="s">
@@ -14380,8 +14402,8 @@
       <c r="B388" s="7">
         <v>8</v>
       </c>
-      <c r="C388" s="160"/>
-      <c r="D388" s="151"/>
+      <c r="C388" s="157"/>
+      <c r="D388" s="172"/>
       <c r="E388" s="8" t="s">
         <v>498</v>
       </c>
@@ -14402,8 +14424,8 @@
       <c r="B389" s="7">
         <v>9</v>
       </c>
-      <c r="C389" s="160"/>
-      <c r="D389" s="151"/>
+      <c r="C389" s="157"/>
+      <c r="D389" s="172"/>
       <c r="E389" s="8" t="s">
         <v>499</v>
       </c>
@@ -14424,8 +14446,8 @@
       <c r="B390" s="7">
         <v>10</v>
       </c>
-      <c r="C390" s="160"/>
-      <c r="D390" s="151"/>
+      <c r="C390" s="157"/>
+      <c r="D390" s="172"/>
       <c r="E390" s="8" t="s">
         <v>500</v>
       </c>
@@ -14446,8 +14468,8 @@
       <c r="B391" s="7">
         <v>11</v>
       </c>
-      <c r="C391" s="160"/>
-      <c r="D391" s="151"/>
+      <c r="C391" s="157"/>
+      <c r="D391" s="172"/>
       <c r="E391" s="8" t="s">
         <v>501</v>
       </c>
@@ -14468,8 +14490,8 @@
       <c r="B392" s="7">
         <v>12</v>
       </c>
-      <c r="C392" s="160"/>
-      <c r="D392" s="151"/>
+      <c r="C392" s="157"/>
+      <c r="D392" s="172"/>
       <c r="E392" s="8" t="s">
         <v>502</v>
       </c>
@@ -14490,8 +14512,8 @@
       <c r="B393" s="7">
         <v>13</v>
       </c>
-      <c r="C393" s="160"/>
-      <c r="D393" s="151"/>
+      <c r="C393" s="157"/>
+      <c r="D393" s="172"/>
       <c r="E393" s="8" t="s">
         <v>503</v>
       </c>
@@ -14512,8 +14534,8 @@
       <c r="B394" s="7">
         <v>14</v>
       </c>
-      <c r="C394" s="160"/>
-      <c r="D394" s="151"/>
+      <c r="C394" s="157"/>
+      <c r="D394" s="172"/>
       <c r="E394" s="8" t="s">
         <v>504</v>
       </c>
@@ -14534,8 +14556,8 @@
       <c r="B395" s="7">
         <v>15</v>
       </c>
-      <c r="C395" s="160"/>
-      <c r="D395" s="151"/>
+      <c r="C395" s="157"/>
+      <c r="D395" s="172"/>
       <c r="E395" s="8" t="s">
         <v>505</v>
       </c>
@@ -14556,8 +14578,8 @@
       <c r="B396" s="7">
         <v>16</v>
       </c>
-      <c r="C396" s="160"/>
-      <c r="D396" s="152"/>
+      <c r="C396" s="157"/>
+      <c r="D396" s="173"/>
       <c r="E396" s="8" t="s">
         <v>506</v>
       </c>
@@ -14578,8 +14600,8 @@
       <c r="B397" s="7">
         <v>17</v>
       </c>
-      <c r="C397" s="160"/>
-      <c r="D397" s="150" t="s">
+      <c r="C397" s="157"/>
+      <c r="D397" s="171" t="s">
         <v>507</v>
       </c>
       <c r="E397" s="8" t="s">
@@ -14602,8 +14624,8 @@
       <c r="B398" s="7">
         <v>18</v>
       </c>
-      <c r="C398" s="160"/>
-      <c r="D398" s="151"/>
+      <c r="C398" s="157"/>
+      <c r="D398" s="172"/>
       <c r="E398" s="8" t="s">
         <v>509</v>
       </c>
@@ -14624,8 +14646,8 @@
       <c r="B399" s="7">
         <v>19</v>
       </c>
-      <c r="C399" s="160"/>
-      <c r="D399" s="152"/>
+      <c r="C399" s="157"/>
+      <c r="D399" s="173"/>
       <c r="E399" s="8" t="s">
         <v>510</v>
       </c>
@@ -14646,8 +14668,8 @@
       <c r="B400" s="7">
         <v>20</v>
       </c>
-      <c r="C400" s="160"/>
-      <c r="D400" s="150" t="s">
+      <c r="C400" s="157"/>
+      <c r="D400" s="171" t="s">
         <v>511</v>
       </c>
       <c r="E400" s="8" t="s">
@@ -14670,8 +14692,8 @@
       <c r="B401" s="7">
         <v>21</v>
       </c>
-      <c r="C401" s="160"/>
-      <c r="D401" s="151"/>
+      <c r="C401" s="157"/>
+      <c r="D401" s="172"/>
       <c r="E401" s="8" t="s">
         <v>513</v>
       </c>
@@ -14692,8 +14714,8 @@
       <c r="B402" s="7">
         <v>22</v>
       </c>
-      <c r="C402" s="160"/>
-      <c r="D402" s="151"/>
+      <c r="C402" s="157"/>
+      <c r="D402" s="172"/>
       <c r="E402" s="8" t="s">
         <v>514</v>
       </c>
@@ -14714,8 +14736,8 @@
       <c r="B403" s="7">
         <v>23</v>
       </c>
-      <c r="C403" s="160"/>
-      <c r="D403" s="151"/>
+      <c r="C403" s="157"/>
+      <c r="D403" s="172"/>
       <c r="E403" s="8" t="s">
         <v>515</v>
       </c>
@@ -14736,8 +14758,8 @@
       <c r="B404" s="7">
         <v>24</v>
       </c>
-      <c r="C404" s="160"/>
-      <c r="D404" s="152"/>
+      <c r="C404" s="157"/>
+      <c r="D404" s="173"/>
       <c r="E404" s="8" t="s">
         <v>516</v>
       </c>
@@ -14758,8 +14780,8 @@
       <c r="B405" s="7">
         <v>25</v>
       </c>
-      <c r="C405" s="160"/>
-      <c r="D405" s="150" t="s">
+      <c r="C405" s="157"/>
+      <c r="D405" s="171" t="s">
         <v>517</v>
       </c>
       <c r="E405" s="8" t="s">
@@ -14782,8 +14804,8 @@
       <c r="B406" s="7">
         <v>26</v>
       </c>
-      <c r="C406" s="160"/>
-      <c r="D406" s="151"/>
+      <c r="C406" s="157"/>
+      <c r="D406" s="172"/>
       <c r="E406" s="8" t="s">
         <v>519</v>
       </c>
@@ -14804,8 +14826,8 @@
       <c r="B407" s="7">
         <v>27</v>
       </c>
-      <c r="C407" s="160"/>
-      <c r="D407" s="151"/>
+      <c r="C407" s="157"/>
+      <c r="D407" s="172"/>
       <c r="E407" s="8" t="s">
         <v>520</v>
       </c>
@@ -14826,8 +14848,8 @@
       <c r="B408" s="7">
         <v>28</v>
       </c>
-      <c r="C408" s="160"/>
-      <c r="D408" s="151"/>
+      <c r="C408" s="157"/>
+      <c r="D408" s="172"/>
       <c r="E408" s="8" t="s">
         <v>521</v>
       </c>
@@ -14848,8 +14870,8 @@
       <c r="B409" s="7">
         <v>29</v>
       </c>
-      <c r="C409" s="160"/>
-      <c r="D409" s="151"/>
+      <c r="C409" s="157"/>
+      <c r="D409" s="172"/>
       <c r="E409" s="8" t="s">
         <v>522</v>
       </c>
@@ -14870,8 +14892,8 @@
       <c r="B410" s="7">
         <v>30</v>
       </c>
-      <c r="C410" s="160"/>
-      <c r="D410" s="151"/>
+      <c r="C410" s="157"/>
+      <c r="D410" s="172"/>
       <c r="E410" s="8" t="s">
         <v>523</v>
       </c>
@@ -14892,8 +14914,8 @@
       <c r="B411" s="7">
         <v>31</v>
       </c>
-      <c r="C411" s="160"/>
-      <c r="D411" s="151"/>
+      <c r="C411" s="157"/>
+      <c r="D411" s="172"/>
       <c r="E411" s="8" t="s">
         <v>524</v>
       </c>
@@ -14914,8 +14936,8 @@
       <c r="B412" s="7">
         <v>32</v>
       </c>
-      <c r="C412" s="160"/>
-      <c r="D412" s="151"/>
+      <c r="C412" s="157"/>
+      <c r="D412" s="172"/>
       <c r="E412" s="8" t="s">
         <v>525</v>
       </c>
@@ -14936,8 +14958,8 @@
       <c r="B413" s="7">
         <v>33</v>
       </c>
-      <c r="C413" s="160"/>
-      <c r="D413" s="151"/>
+      <c r="C413" s="157"/>
+      <c r="D413" s="172"/>
       <c r="E413" s="8" t="s">
         <v>526</v>
       </c>
@@ -14958,8 +14980,8 @@
       <c r="B414" s="7">
         <v>34</v>
       </c>
-      <c r="C414" s="160"/>
-      <c r="D414" s="151"/>
+      <c r="C414" s="157"/>
+      <c r="D414" s="172"/>
       <c r="E414" s="8" t="s">
         <v>527</v>
       </c>
@@ -14980,8 +15002,8 @@
       <c r="B415" s="7">
         <v>35</v>
       </c>
-      <c r="C415" s="160"/>
-      <c r="D415" s="151"/>
+      <c r="C415" s="157"/>
+      <c r="D415" s="172"/>
       <c r="E415" s="8" t="s">
         <v>528</v>
       </c>
@@ -15002,8 +15024,8 @@
       <c r="B416" s="7">
         <v>36</v>
       </c>
-      <c r="C416" s="160"/>
-      <c r="D416" s="152"/>
+      <c r="C416" s="157"/>
+      <c r="D416" s="173"/>
       <c r="E416" s="8" t="s">
         <v>529</v>
       </c>
@@ -15024,8 +15046,8 @@
       <c r="B417" s="7">
         <v>37</v>
       </c>
-      <c r="C417" s="160"/>
-      <c r="D417" s="150" t="s">
+      <c r="C417" s="157"/>
+      <c r="D417" s="171" t="s">
         <v>530</v>
       </c>
       <c r="E417" s="8" t="s">
@@ -15048,8 +15070,8 @@
       <c r="B418" s="7">
         <v>38</v>
       </c>
-      <c r="C418" s="160"/>
-      <c r="D418" s="151"/>
+      <c r="C418" s="157"/>
+      <c r="D418" s="172"/>
       <c r="E418" s="8" t="s">
         <v>532</v>
       </c>
@@ -15070,8 +15092,8 @@
       <c r="B419" s="7">
         <v>39</v>
       </c>
-      <c r="C419" s="160"/>
-      <c r="D419" s="152"/>
+      <c r="C419" s="157"/>
+      <c r="D419" s="173"/>
       <c r="E419" s="8" t="s">
         <v>533</v>
       </c>
@@ -15092,8 +15114,8 @@
       <c r="B420" s="7">
         <v>40</v>
       </c>
-      <c r="C420" s="160"/>
-      <c r="D420" s="150" t="s">
+      <c r="C420" s="157"/>
+      <c r="D420" s="171" t="s">
         <v>534</v>
       </c>
       <c r="E420" s="8" t="s">
@@ -15116,8 +15138,8 @@
       <c r="B421" s="7">
         <v>41</v>
       </c>
-      <c r="C421" s="160"/>
-      <c r="D421" s="151"/>
+      <c r="C421" s="157"/>
+      <c r="D421" s="172"/>
       <c r="E421" s="8" t="s">
         <v>536</v>
       </c>
@@ -15138,8 +15160,8 @@
       <c r="B422" s="7">
         <v>42</v>
       </c>
-      <c r="C422" s="160"/>
-      <c r="D422" s="151"/>
+      <c r="C422" s="157"/>
+      <c r="D422" s="172"/>
       <c r="E422" s="8" t="s">
         <v>537</v>
       </c>
@@ -15160,8 +15182,8 @@
       <c r="B423" s="7">
         <v>43</v>
       </c>
-      <c r="C423" s="160"/>
-      <c r="D423" s="151"/>
+      <c r="C423" s="157"/>
+      <c r="D423" s="172"/>
       <c r="E423" s="8" t="s">
         <v>538</v>
       </c>
@@ -15182,8 +15204,8 @@
       <c r="B424" s="7">
         <v>44</v>
       </c>
-      <c r="C424" s="160"/>
-      <c r="D424" s="151"/>
+      <c r="C424" s="157"/>
+      <c r="D424" s="172"/>
       <c r="E424" s="8" t="s">
         <v>539</v>
       </c>
@@ -15204,8 +15226,8 @@
       <c r="B425" s="7">
         <v>45</v>
       </c>
-      <c r="C425" s="160"/>
-      <c r="D425" s="151"/>
+      <c r="C425" s="157"/>
+      <c r="D425" s="172"/>
       <c r="E425" s="8" t="s">
         <v>540</v>
       </c>
@@ -15226,8 +15248,8 @@
       <c r="B426" s="7">
         <v>46</v>
       </c>
-      <c r="C426" s="160"/>
-      <c r="D426" s="152"/>
+      <c r="C426" s="157"/>
+      <c r="D426" s="173"/>
       <c r="E426" s="8" t="s">
         <v>541</v>
       </c>
@@ -15248,8 +15270,8 @@
       <c r="B427" s="7">
         <v>47</v>
       </c>
-      <c r="C427" s="160"/>
-      <c r="D427" s="150" t="s">
+      <c r="C427" s="157"/>
+      <c r="D427" s="171" t="s">
         <v>542</v>
       </c>
       <c r="E427" s="8" t="s">
@@ -15270,8 +15292,8 @@
       <c r="B428" s="7">
         <v>48</v>
       </c>
-      <c r="C428" s="160"/>
-      <c r="D428" s="151"/>
+      <c r="C428" s="157"/>
+      <c r="D428" s="172"/>
       <c r="E428" s="8" t="s">
         <v>544</v>
       </c>
@@ -15292,8 +15314,8 @@
       <c r="B429" s="7">
         <v>49</v>
       </c>
-      <c r="C429" s="160"/>
-      <c r="D429" s="151"/>
+      <c r="C429" s="157"/>
+      <c r="D429" s="172"/>
       <c r="E429" s="8" t="s">
         <v>545</v>
       </c>
@@ -15314,8 +15336,8 @@
       <c r="B430" s="7">
         <v>50</v>
       </c>
-      <c r="C430" s="160"/>
-      <c r="D430" s="152"/>
+      <c r="C430" s="157"/>
+      <c r="D430" s="173"/>
       <c r="E430" s="8" t="s">
         <v>546</v>
       </c>
@@ -15336,8 +15358,8 @@
       <c r="B431" s="7">
         <v>51</v>
       </c>
-      <c r="C431" s="160"/>
-      <c r="D431" s="150" t="s">
+      <c r="C431" s="157"/>
+      <c r="D431" s="171" t="s">
         <v>547</v>
       </c>
       <c r="E431" s="8" t="s">
@@ -15360,8 +15382,8 @@
       <c r="B432" s="7">
         <v>52</v>
       </c>
-      <c r="C432" s="160"/>
-      <c r="D432" s="151"/>
+      <c r="C432" s="157"/>
+      <c r="D432" s="172"/>
       <c r="E432" s="8" t="s">
         <v>549</v>
       </c>
@@ -15382,8 +15404,8 @@
       <c r="B433" s="7">
         <v>53</v>
       </c>
-      <c r="C433" s="160"/>
-      <c r="D433" s="151"/>
+      <c r="C433" s="157"/>
+      <c r="D433" s="172"/>
       <c r="E433" s="8" t="s">
         <v>550</v>
       </c>
@@ -15404,8 +15426,8 @@
       <c r="B434" s="7">
         <v>54</v>
       </c>
-      <c r="C434" s="160"/>
-      <c r="D434" s="151"/>
+      <c r="C434" s="157"/>
+      <c r="D434" s="172"/>
       <c r="E434" s="8" t="s">
         <v>551</v>
       </c>
@@ -15426,8 +15448,8 @@
       <c r="B435" s="7">
         <v>55</v>
       </c>
-      <c r="C435" s="161"/>
-      <c r="D435" s="152"/>
+      <c r="C435" s="158"/>
+      <c r="D435" s="173"/>
       <c r="E435" s="8" t="s">
         <v>552</v>
       </c>
@@ -15442,18 +15464,18 @@
       <c r="J435" s="11"/>
     </row>
     <row r="436" spans="1:10" ht="13.8">
-      <c r="A436" s="192" t="s">
+      <c r="A436" s="177" t="s">
         <v>553</v>
       </c>
-      <c r="B436" s="193"/>
-      <c r="C436" s="193"/>
-      <c r="D436" s="193"/>
-      <c r="E436" s="193"/>
-      <c r="F436" s="193"/>
-      <c r="G436" s="193"/>
-      <c r="H436" s="193"/>
-      <c r="I436" s="193"/>
-      <c r="J436" s="194"/>
+      <c r="B436" s="178"/>
+      <c r="C436" s="178"/>
+      <c r="D436" s="178"/>
+      <c r="E436" s="178"/>
+      <c r="F436" s="178"/>
+      <c r="G436" s="178"/>
+      <c r="H436" s="178"/>
+      <c r="I436" s="178"/>
+      <c r="J436" s="179"/>
     </row>
     <row r="437" spans="1:10" ht="13.8">
       <c r="A437" s="6">
@@ -15462,10 +15484,10 @@
       <c r="B437" s="7">
         <v>1</v>
       </c>
-      <c r="C437" s="162" t="s">
+      <c r="C437" s="159" t="s">
         <v>554</v>
       </c>
-      <c r="D437" s="150" t="s">
+      <c r="D437" s="171" t="s">
         <v>555</v>
       </c>
       <c r="E437" s="29" t="s">
@@ -15488,8 +15510,8 @@
       <c r="B438" s="7">
         <v>2</v>
       </c>
-      <c r="C438" s="163"/>
-      <c r="D438" s="151"/>
+      <c r="C438" s="160"/>
+      <c r="D438" s="172"/>
       <c r="E438" s="8" t="s">
         <v>557</v>
       </c>
@@ -15508,8 +15530,8 @@
       <c r="B439" s="7">
         <v>3</v>
       </c>
-      <c r="C439" s="163"/>
-      <c r="D439" s="151"/>
+      <c r="C439" s="160"/>
+      <c r="D439" s="172"/>
       <c r="E439" s="8" t="s">
         <v>558</v>
       </c>
@@ -15530,8 +15552,8 @@
       <c r="B440" s="7">
         <v>4</v>
       </c>
-      <c r="C440" s="163"/>
-      <c r="D440" s="151"/>
+      <c r="C440" s="160"/>
+      <c r="D440" s="172"/>
       <c r="E440" s="29" t="s">
         <v>559</v>
       </c>
@@ -15552,8 +15574,8 @@
       <c r="B441" s="7">
         <v>5</v>
       </c>
-      <c r="C441" s="163"/>
-      <c r="D441" s="152"/>
+      <c r="C441" s="160"/>
+      <c r="D441" s="173"/>
       <c r="E441" s="8" t="s">
         <v>560</v>
       </c>
@@ -15574,8 +15596,8 @@
       <c r="B442" s="7">
         <v>6</v>
       </c>
-      <c r="C442" s="163"/>
-      <c r="D442" s="150" t="s">
+      <c r="C442" s="160"/>
+      <c r="D442" s="171" t="s">
         <v>561</v>
       </c>
       <c r="E442" s="29" t="s">
@@ -15598,8 +15620,8 @@
       <c r="B443" s="7">
         <v>7</v>
       </c>
-      <c r="C443" s="163"/>
-      <c r="D443" s="151"/>
+      <c r="C443" s="160"/>
+      <c r="D443" s="172"/>
       <c r="E443" s="8" t="s">
         <v>563</v>
       </c>
@@ -15620,8 +15642,8 @@
       <c r="B444" s="7">
         <v>8</v>
       </c>
-      <c r="C444" s="163"/>
-      <c r="D444" s="151"/>
+      <c r="C444" s="160"/>
+      <c r="D444" s="172"/>
       <c r="E444" s="29" t="s">
         <v>564</v>
       </c>
@@ -15642,8 +15664,8 @@
       <c r="B445" s="7">
         <v>9</v>
       </c>
-      <c r="C445" s="163"/>
-      <c r="D445" s="152"/>
+      <c r="C445" s="160"/>
+      <c r="D445" s="173"/>
       <c r="E445" s="8" t="s">
         <v>565</v>
       </c>
@@ -15664,8 +15686,8 @@
       <c r="B446" s="7">
         <v>10</v>
       </c>
-      <c r="C446" s="163"/>
-      <c r="D446" s="150" t="s">
+      <c r="C446" s="160"/>
+      <c r="D446" s="171" t="s">
         <v>566</v>
       </c>
       <c r="E446" s="8" t="s">
@@ -15688,8 +15710,8 @@
       <c r="B447" s="7">
         <v>11</v>
       </c>
-      <c r="C447" s="163"/>
-      <c r="D447" s="151"/>
+      <c r="C447" s="160"/>
+      <c r="D447" s="172"/>
       <c r="E447" s="8" t="s">
         <v>568</v>
       </c>
@@ -15710,8 +15732,8 @@
       <c r="B448" s="7">
         <v>12</v>
       </c>
-      <c r="C448" s="163"/>
-      <c r="D448" s="152"/>
+      <c r="C448" s="160"/>
+      <c r="D448" s="173"/>
       <c r="E448" s="8" t="s">
         <v>569</v>
       </c>
@@ -15732,8 +15754,8 @@
       <c r="B449" s="7">
         <v>13</v>
       </c>
-      <c r="C449" s="163"/>
-      <c r="D449" s="150" t="s">
+      <c r="C449" s="160"/>
+      <c r="D449" s="171" t="s">
         <v>570</v>
       </c>
       <c r="E449" s="8" t="s">
@@ -15756,8 +15778,8 @@
       <c r="B450" s="7">
         <v>14</v>
       </c>
-      <c r="C450" s="163"/>
-      <c r="D450" s="151"/>
+      <c r="C450" s="160"/>
+      <c r="D450" s="172"/>
       <c r="E450" s="29" t="s">
         <v>572</v>
       </c>
@@ -15778,8 +15800,8 @@
       <c r="B451" s="7">
         <v>15</v>
       </c>
-      <c r="C451" s="163"/>
-      <c r="D451" s="151"/>
+      <c r="C451" s="160"/>
+      <c r="D451" s="172"/>
       <c r="E451" s="8" t="s">
         <v>573</v>
       </c>
@@ -15800,8 +15822,8 @@
       <c r="B452" s="7">
         <v>16</v>
       </c>
-      <c r="C452" s="163"/>
-      <c r="D452" s="152"/>
+      <c r="C452" s="160"/>
+      <c r="D452" s="173"/>
       <c r="E452" s="8" t="s">
         <v>574</v>
       </c>
@@ -15822,8 +15844,8 @@
       <c r="B453" s="7">
         <v>17</v>
       </c>
-      <c r="C453" s="163"/>
-      <c r="D453" s="150" t="s">
+      <c r="C453" s="160"/>
+      <c r="D453" s="171" t="s">
         <v>575</v>
       </c>
       <c r="E453" s="8" t="s">
@@ -15846,8 +15868,8 @@
       <c r="B454" s="7">
         <v>18</v>
       </c>
-      <c r="C454" s="163"/>
-      <c r="D454" s="151"/>
+      <c r="C454" s="160"/>
+      <c r="D454" s="172"/>
       <c r="E454" s="8" t="s">
         <v>577</v>
       </c>
@@ -15868,8 +15890,8 @@
       <c r="B455" s="7">
         <v>19</v>
       </c>
-      <c r="C455" s="163"/>
-      <c r="D455" s="151"/>
+      <c r="C455" s="160"/>
+      <c r="D455" s="172"/>
       <c r="E455" s="8" t="s">
         <v>578</v>
       </c>
@@ -15890,8 +15912,8 @@
       <c r="B456" s="7">
         <v>20</v>
       </c>
-      <c r="C456" s="163"/>
-      <c r="D456" s="151"/>
+      <c r="C456" s="160"/>
+      <c r="D456" s="172"/>
       <c r="E456" s="39" t="s">
         <v>579</v>
       </c>
@@ -15912,8 +15934,8 @@
       <c r="B457" s="7">
         <v>21</v>
       </c>
-      <c r="C457" s="163"/>
-      <c r="D457" s="151"/>
+      <c r="C457" s="160"/>
+      <c r="D457" s="172"/>
       <c r="E457" s="8" t="s">
         <v>580</v>
       </c>
@@ -15934,8 +15956,8 @@
       <c r="B458" s="24">
         <v>22</v>
       </c>
-      <c r="C458" s="164"/>
-      <c r="D458" s="152"/>
+      <c r="C458" s="161"/>
+      <c r="D458" s="173"/>
       <c r="E458" s="17" t="s">
         <v>581</v>
       </c>
@@ -15957,10 +15979,10 @@
       <c r="B459" s="7">
         <v>1</v>
       </c>
-      <c r="C459" s="165" t="s">
+      <c r="C459" s="150" t="s">
         <v>582</v>
       </c>
-      <c r="D459" s="150" t="s">
+      <c r="D459" s="171" t="s">
         <v>583</v>
       </c>
       <c r="E459" s="8" t="s">
@@ -15983,8 +16005,8 @@
       <c r="B460" s="7">
         <v>2</v>
       </c>
-      <c r="C460" s="166"/>
-      <c r="D460" s="151"/>
+      <c r="C460" s="151"/>
+      <c r="D460" s="172"/>
       <c r="E460" s="8" t="s">
         <v>584</v>
       </c>
@@ -16005,8 +16027,8 @@
       <c r="B461" s="7">
         <v>3</v>
       </c>
-      <c r="C461" s="166"/>
-      <c r="D461" s="151"/>
+      <c r="C461" s="151"/>
+      <c r="D461" s="172"/>
       <c r="E461" s="8" t="s">
         <v>585</v>
       </c>
@@ -16027,8 +16049,8 @@
       <c r="B462" s="7">
         <v>4</v>
       </c>
-      <c r="C462" s="166"/>
-      <c r="D462" s="151"/>
+      <c r="C462" s="151"/>
+      <c r="D462" s="172"/>
       <c r="E462" s="8" t="s">
         <v>586</v>
       </c>
@@ -16049,8 +16071,8 @@
       <c r="B463" s="7">
         <v>5</v>
       </c>
-      <c r="C463" s="166"/>
-      <c r="D463" s="151"/>
+      <c r="C463" s="151"/>
+      <c r="D463" s="172"/>
       <c r="E463" s="8" t="s">
         <v>587</v>
       </c>
@@ -16071,8 +16093,8 @@
       <c r="B464" s="7">
         <v>6</v>
       </c>
-      <c r="C464" s="166"/>
-      <c r="D464" s="151"/>
+      <c r="C464" s="151"/>
+      <c r="D464" s="172"/>
       <c r="E464" s="8" t="s">
         <v>588</v>
       </c>
@@ -16093,8 +16115,8 @@
       <c r="B465" s="7">
         <v>7</v>
       </c>
-      <c r="C465" s="166"/>
-      <c r="D465" s="151"/>
+      <c r="C465" s="151"/>
+      <c r="D465" s="172"/>
       <c r="E465" s="8" t="s">
         <v>589</v>
       </c>
@@ -16115,8 +16137,8 @@
       <c r="B466" s="7">
         <v>8</v>
       </c>
-      <c r="C466" s="166"/>
-      <c r="D466" s="152"/>
+      <c r="C466" s="151"/>
+      <c r="D466" s="173"/>
       <c r="E466" s="8" t="s">
         <v>590</v>
       </c>
@@ -16137,8 +16159,8 @@
       <c r="B467" s="7">
         <v>9</v>
       </c>
-      <c r="C467" s="166"/>
-      <c r="D467" s="150" t="s">
+      <c r="C467" s="151"/>
+      <c r="D467" s="171" t="s">
         <v>591</v>
       </c>
       <c r="E467" s="8" t="s">
@@ -16161,8 +16183,8 @@
       <c r="B468" s="7">
         <v>10</v>
       </c>
-      <c r="C468" s="166"/>
-      <c r="D468" s="151"/>
+      <c r="C468" s="151"/>
+      <c r="D468" s="172"/>
       <c r="E468" s="8" t="s">
         <v>593</v>
       </c>
@@ -16183,8 +16205,8 @@
       <c r="B469" s="7">
         <v>11</v>
       </c>
-      <c r="C469" s="166"/>
-      <c r="D469" s="151"/>
+      <c r="C469" s="151"/>
+      <c r="D469" s="172"/>
       <c r="E469" s="8" t="s">
         <v>594</v>
       </c>
@@ -16205,8 +16227,8 @@
       <c r="B470" s="7">
         <v>12</v>
       </c>
-      <c r="C470" s="166"/>
-      <c r="D470" s="151"/>
+      <c r="C470" s="151"/>
+      <c r="D470" s="172"/>
       <c r="E470" s="8" t="s">
         <v>595</v>
       </c>
@@ -16227,8 +16249,8 @@
       <c r="B471" s="7">
         <v>13</v>
       </c>
-      <c r="C471" s="166"/>
-      <c r="D471" s="151"/>
+      <c r="C471" s="151"/>
+      <c r="D471" s="172"/>
       <c r="E471" s="8" t="s">
         <v>596</v>
       </c>
@@ -16249,8 +16271,8 @@
       <c r="B472" s="7">
         <v>14</v>
       </c>
-      <c r="C472" s="166"/>
-      <c r="D472" s="151"/>
+      <c r="C472" s="151"/>
+      <c r="D472" s="172"/>
       <c r="E472" s="8" t="s">
         <v>597</v>
       </c>
@@ -16271,8 +16293,8 @@
       <c r="B473" s="7">
         <v>15</v>
       </c>
-      <c r="C473" s="166"/>
-      <c r="D473" s="152"/>
+      <c r="C473" s="151"/>
+      <c r="D473" s="173"/>
       <c r="E473" s="8" t="s">
         <v>598</v>
       </c>
@@ -16293,8 +16315,8 @@
       <c r="B474" s="7">
         <v>16</v>
       </c>
-      <c r="C474" s="166"/>
-      <c r="D474" s="150" t="s">
+      <c r="C474" s="151"/>
+      <c r="D474" s="171" t="s">
         <v>599</v>
       </c>
       <c r="E474" s="8" t="s">
@@ -16317,8 +16339,8 @@
       <c r="B475" s="7">
         <v>17</v>
       </c>
-      <c r="C475" s="166"/>
-      <c r="D475" s="151"/>
+      <c r="C475" s="151"/>
+      <c r="D475" s="172"/>
       <c r="E475" s="8" t="s">
         <v>601</v>
       </c>
@@ -16339,8 +16361,8 @@
       <c r="B476" s="7">
         <v>18</v>
       </c>
-      <c r="C476" s="166"/>
-      <c r="D476" s="151"/>
+      <c r="C476" s="151"/>
+      <c r="D476" s="172"/>
       <c r="E476" s="8" t="s">
         <v>602</v>
       </c>
@@ -16361,8 +16383,8 @@
       <c r="B477" s="7">
         <v>19</v>
       </c>
-      <c r="C477" s="166"/>
-      <c r="D477" s="151"/>
+      <c r="C477" s="151"/>
+      <c r="D477" s="172"/>
       <c r="E477" s="8" t="s">
         <v>603</v>
       </c>
@@ -16383,8 +16405,8 @@
       <c r="B478" s="7">
         <v>20</v>
       </c>
-      <c r="C478" s="166"/>
-      <c r="D478" s="151"/>
+      <c r="C478" s="151"/>
+      <c r="D478" s="172"/>
       <c r="E478" s="8" t="s">
         <v>604</v>
       </c>
@@ -16405,8 +16427,8 @@
       <c r="B479" s="7">
         <v>21</v>
       </c>
-      <c r="C479" s="166"/>
-      <c r="D479" s="151"/>
+      <c r="C479" s="151"/>
+      <c r="D479" s="172"/>
       <c r="E479" s="8" t="s">
         <v>605</v>
       </c>
@@ -16427,8 +16449,8 @@
       <c r="B480" s="7">
         <v>22</v>
       </c>
-      <c r="C480" s="166"/>
-      <c r="D480" s="151"/>
+      <c r="C480" s="151"/>
+      <c r="D480" s="172"/>
       <c r="E480" s="8" t="s">
         <v>606</v>
       </c>
@@ -16449,8 +16471,8 @@
       <c r="B481" s="7">
         <v>23</v>
       </c>
-      <c r="C481" s="166"/>
-      <c r="D481" s="152"/>
+      <c r="C481" s="151"/>
+      <c r="D481" s="173"/>
       <c r="E481" s="8" t="s">
         <v>607</v>
       </c>
@@ -16471,8 +16493,8 @@
       <c r="B482" s="7">
         <v>24</v>
       </c>
-      <c r="C482" s="166"/>
-      <c r="D482" s="150" t="s">
+      <c r="C482" s="151"/>
+      <c r="D482" s="171" t="s">
         <v>608</v>
       </c>
       <c r="E482" s="8" t="s">
@@ -16495,8 +16517,8 @@
       <c r="B483" s="7">
         <v>25</v>
       </c>
-      <c r="C483" s="166"/>
-      <c r="D483" s="151"/>
+      <c r="C483" s="151"/>
+      <c r="D483" s="172"/>
       <c r="E483" s="8" t="s">
         <v>610</v>
       </c>
@@ -16517,8 +16539,8 @@
       <c r="B484" s="7">
         <v>26</v>
       </c>
-      <c r="C484" s="166"/>
-      <c r="D484" s="151"/>
+      <c r="C484" s="151"/>
+      <c r="D484" s="172"/>
       <c r="E484" s="8" t="s">
         <v>611</v>
       </c>
@@ -16539,8 +16561,8 @@
       <c r="B485" s="7">
         <v>27</v>
       </c>
-      <c r="C485" s="166"/>
-      <c r="D485" s="152"/>
+      <c r="C485" s="151"/>
+      <c r="D485" s="173"/>
       <c r="E485" s="8" t="s">
         <v>612</v>
       </c>
@@ -16561,8 +16583,8 @@
       <c r="B486" s="7">
         <v>28</v>
       </c>
-      <c r="C486" s="166"/>
-      <c r="D486" s="150" t="s">
+      <c r="C486" s="151"/>
+      <c r="D486" s="171" t="s">
         <v>613</v>
       </c>
       <c r="E486" s="8" t="s">
@@ -16585,8 +16607,8 @@
       <c r="B487" s="7">
         <v>29</v>
       </c>
-      <c r="C487" s="166"/>
-      <c r="D487" s="151"/>
+      <c r="C487" s="151"/>
+      <c r="D487" s="172"/>
       <c r="E487" s="8" t="s">
         <v>615</v>
       </c>
@@ -16607,8 +16629,8 @@
       <c r="B488" s="7">
         <v>30</v>
       </c>
-      <c r="C488" s="166"/>
-      <c r="D488" s="151"/>
+      <c r="C488" s="151"/>
+      <c r="D488" s="172"/>
       <c r="E488" s="8" t="s">
         <v>616</v>
       </c>
@@ -16629,8 +16651,8 @@
       <c r="B489" s="7">
         <v>31</v>
       </c>
-      <c r="C489" s="166"/>
-      <c r="D489" s="151"/>
+      <c r="C489" s="151"/>
+      <c r="D489" s="172"/>
       <c r="E489" s="8" t="s">
         <v>617</v>
       </c>
@@ -16651,8 +16673,8 @@
       <c r="B490" s="7">
         <v>32</v>
       </c>
-      <c r="C490" s="166"/>
-      <c r="D490" s="151"/>
+      <c r="C490" s="151"/>
+      <c r="D490" s="172"/>
       <c r="E490" s="8" t="s">
         <v>618</v>
       </c>
@@ -16673,8 +16695,8 @@
       <c r="B491" s="7">
         <v>33</v>
       </c>
-      <c r="C491" s="166"/>
-      <c r="D491" s="151"/>
+      <c r="C491" s="151"/>
+      <c r="D491" s="172"/>
       <c r="E491" s="8" t="s">
         <v>619</v>
       </c>
@@ -16695,8 +16717,8 @@
       <c r="B492" s="7">
         <v>34</v>
       </c>
-      <c r="C492" s="166"/>
-      <c r="D492" s="151"/>
+      <c r="C492" s="151"/>
+      <c r="D492" s="172"/>
       <c r="E492" s="8" t="s">
         <v>620</v>
       </c>
@@ -16717,8 +16739,8 @@
       <c r="B493" s="7">
         <v>35</v>
       </c>
-      <c r="C493" s="166"/>
-      <c r="D493" s="151"/>
+      <c r="C493" s="151"/>
+      <c r="D493" s="172"/>
       <c r="E493" s="8" t="s">
         <v>621</v>
       </c>
@@ -16739,8 +16761,8 @@
       <c r="B494" s="7">
         <v>36</v>
       </c>
-      <c r="C494" s="166"/>
-      <c r="D494" s="151"/>
+      <c r="C494" s="151"/>
+      <c r="D494" s="172"/>
       <c r="E494" s="8" t="s">
         <v>622</v>
       </c>
@@ -16761,8 +16783,8 @@
       <c r="B495" s="7">
         <v>37</v>
       </c>
-      <c r="C495" s="166"/>
-      <c r="D495" s="151"/>
+      <c r="C495" s="151"/>
+      <c r="D495" s="172"/>
       <c r="E495" s="8" t="s">
         <v>623</v>
       </c>
@@ -16783,8 +16805,8 @@
       <c r="B496" s="7">
         <v>38</v>
       </c>
-      <c r="C496" s="166"/>
-      <c r="D496" s="152"/>
+      <c r="C496" s="151"/>
+      <c r="D496" s="173"/>
       <c r="E496" s="8" t="s">
         <v>624</v>
       </c>
@@ -16805,8 +16827,8 @@
       <c r="B497" s="7">
         <v>39</v>
       </c>
-      <c r="C497" s="166"/>
-      <c r="D497" s="150" t="s">
+      <c r="C497" s="151"/>
+      <c r="D497" s="171" t="s">
         <v>625</v>
       </c>
       <c r="E497" s="8" t="s">
@@ -16829,8 +16851,8 @@
       <c r="B498" s="7">
         <v>40</v>
       </c>
-      <c r="C498" s="166"/>
-      <c r="D498" s="151"/>
+      <c r="C498" s="151"/>
+      <c r="D498" s="172"/>
       <c r="E498" s="8" t="s">
         <v>626</v>
       </c>
@@ -16851,8 +16873,8 @@
       <c r="B499" s="7">
         <v>41</v>
       </c>
-      <c r="C499" s="166"/>
-      <c r="D499" s="151"/>
+      <c r="C499" s="151"/>
+      <c r="D499" s="172"/>
       <c r="E499" s="8" t="s">
         <v>627</v>
       </c>
@@ -16873,8 +16895,8 @@
       <c r="B500" s="7">
         <v>42</v>
       </c>
-      <c r="C500" s="166"/>
-      <c r="D500" s="151"/>
+      <c r="C500" s="151"/>
+      <c r="D500" s="172"/>
       <c r="E500" s="8" t="s">
         <v>628</v>
       </c>
@@ -16895,8 +16917,8 @@
       <c r="B501" s="7">
         <v>43</v>
       </c>
-      <c r="C501" s="166"/>
-      <c r="D501" s="151"/>
+      <c r="C501" s="151"/>
+      <c r="D501" s="172"/>
       <c r="E501" s="8" t="s">
         <v>629</v>
       </c>
@@ -16917,8 +16939,8 @@
       <c r="B502" s="7">
         <v>44</v>
       </c>
-      <c r="C502" s="166"/>
-      <c r="D502" s="152"/>
+      <c r="C502" s="151"/>
+      <c r="D502" s="173"/>
       <c r="E502" s="8" t="s">
         <v>630</v>
       </c>
@@ -16939,8 +16961,8 @@
       <c r="B503" s="7">
         <v>45</v>
       </c>
-      <c r="C503" s="166"/>
-      <c r="D503" s="150" t="s">
+      <c r="C503" s="151"/>
+      <c r="D503" s="171" t="s">
         <v>631</v>
       </c>
       <c r="E503" s="8" t="s">
@@ -16963,8 +16985,8 @@
       <c r="B504" s="7">
         <v>46</v>
       </c>
-      <c r="C504" s="166"/>
-      <c r="D504" s="151"/>
+      <c r="C504" s="151"/>
+      <c r="D504" s="172"/>
       <c r="E504" s="8" t="s">
         <v>633</v>
       </c>
@@ -16985,8 +17007,8 @@
       <c r="B505" s="7">
         <v>47</v>
       </c>
-      <c r="C505" s="166"/>
-      <c r="D505" s="151"/>
+      <c r="C505" s="151"/>
+      <c r="D505" s="172"/>
       <c r="E505" s="8" t="s">
         <v>634</v>
       </c>
@@ -17007,8 +17029,8 @@
       <c r="B506" s="7">
         <v>48</v>
       </c>
-      <c r="C506" s="166"/>
-      <c r="D506" s="151"/>
+      <c r="C506" s="151"/>
+      <c r="D506" s="172"/>
       <c r="E506" s="8" t="s">
         <v>635</v>
       </c>
@@ -17029,8 +17051,8 @@
       <c r="B507" s="7">
         <v>49</v>
       </c>
-      <c r="C507" s="166"/>
-      <c r="D507" s="151"/>
+      <c r="C507" s="151"/>
+      <c r="D507" s="172"/>
       <c r="E507" s="8" t="s">
         <v>636</v>
       </c>
@@ -17051,8 +17073,8 @@
       <c r="B508" s="7">
         <v>50</v>
       </c>
-      <c r="C508" s="166"/>
-      <c r="D508" s="151"/>
+      <c r="C508" s="151"/>
+      <c r="D508" s="172"/>
       <c r="E508" s="8" t="s">
         <v>637</v>
       </c>
@@ -17073,8 +17095,8 @@
       <c r="B509" s="7">
         <v>51</v>
       </c>
-      <c r="C509" s="166"/>
-      <c r="D509" s="152"/>
+      <c r="C509" s="151"/>
+      <c r="D509" s="173"/>
       <c r="E509" s="8" t="s">
         <v>638</v>
       </c>
@@ -17095,8 +17117,8 @@
       <c r="B510" s="7">
         <v>52</v>
       </c>
-      <c r="C510" s="166"/>
-      <c r="D510" s="150" t="s">
+      <c r="C510" s="151"/>
+      <c r="D510" s="171" t="s">
         <v>639</v>
       </c>
       <c r="E510" s="8" t="s">
@@ -17119,8 +17141,8 @@
       <c r="B511" s="7">
         <v>53</v>
       </c>
-      <c r="C511" s="166"/>
-      <c r="D511" s="151"/>
+      <c r="C511" s="151"/>
+      <c r="D511" s="172"/>
       <c r="E511" s="8" t="s">
         <v>641</v>
       </c>
@@ -17141,8 +17163,8 @@
       <c r="B512" s="7">
         <v>54</v>
       </c>
-      <c r="C512" s="166"/>
-      <c r="D512" s="151"/>
+      <c r="C512" s="151"/>
+      <c r="D512" s="172"/>
       <c r="E512" s="8" t="s">
         <v>642</v>
       </c>
@@ -17163,8 +17185,8 @@
       <c r="B513" s="24">
         <v>55</v>
       </c>
-      <c r="C513" s="167"/>
-      <c r="D513" s="152"/>
+      <c r="C513" s="152"/>
+      <c r="D513" s="173"/>
       <c r="E513" s="17" t="s">
         <v>643</v>
       </c>
@@ -24098,6 +24120,107 @@
     </row>
   </sheetData>
   <mergeCells count="125">
+    <mergeCell ref="D26:D32"/>
+    <mergeCell ref="D33:D36"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="C4:C32"/>
+    <mergeCell ref="D4:D9"/>
+    <mergeCell ref="D10:D18"/>
+    <mergeCell ref="D19:D25"/>
+    <mergeCell ref="C33:C44"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="D40:D44"/>
+    <mergeCell ref="C107:C116"/>
+    <mergeCell ref="C117:C125"/>
+    <mergeCell ref="C127:C132"/>
+    <mergeCell ref="C134:C176"/>
+    <mergeCell ref="C177:C204"/>
+    <mergeCell ref="C205:C214"/>
+    <mergeCell ref="A106:J106"/>
+    <mergeCell ref="D107:D111"/>
+    <mergeCell ref="D112:D115"/>
+    <mergeCell ref="D117:D120"/>
+    <mergeCell ref="D121:D122"/>
+    <mergeCell ref="D123:D125"/>
+    <mergeCell ref="A126:J126"/>
+    <mergeCell ref="D127:D130"/>
+    <mergeCell ref="D131:D132"/>
+    <mergeCell ref="A133:J133"/>
+    <mergeCell ref="D210:D211"/>
+    <mergeCell ref="D212:D214"/>
+    <mergeCell ref="C45:C50"/>
+    <mergeCell ref="D45:D50"/>
+    <mergeCell ref="D51:D57"/>
+    <mergeCell ref="D58:D63"/>
+    <mergeCell ref="D64:D67"/>
+    <mergeCell ref="D69:D78"/>
+    <mergeCell ref="D79:D84"/>
+    <mergeCell ref="D85:D90"/>
+    <mergeCell ref="D91:D105"/>
+    <mergeCell ref="A68:J68"/>
+    <mergeCell ref="C51:C67"/>
+    <mergeCell ref="C69:C105"/>
+    <mergeCell ref="A215:J215"/>
+    <mergeCell ref="A273:J273"/>
+    <mergeCell ref="A358:J358"/>
+    <mergeCell ref="D134:D136"/>
+    <mergeCell ref="D137:D143"/>
+    <mergeCell ref="D144:D150"/>
+    <mergeCell ref="D151:D156"/>
+    <mergeCell ref="D157:D159"/>
+    <mergeCell ref="D160:D165"/>
+    <mergeCell ref="D166:D172"/>
+    <mergeCell ref="D173:D176"/>
+    <mergeCell ref="D177:D178"/>
+    <mergeCell ref="D179:D184"/>
+    <mergeCell ref="D185:D186"/>
+    <mergeCell ref="D187:D190"/>
+    <mergeCell ref="D191:D198"/>
+    <mergeCell ref="D199:D202"/>
+    <mergeCell ref="D203:D204"/>
+    <mergeCell ref="D205:D209"/>
+    <mergeCell ref="D216:D225"/>
+    <mergeCell ref="D226:D233"/>
+    <mergeCell ref="D234:D240"/>
+    <mergeCell ref="D241:D243"/>
+    <mergeCell ref="D244:D249"/>
+    <mergeCell ref="D442:D445"/>
+    <mergeCell ref="D446:D448"/>
+    <mergeCell ref="D400:D404"/>
+    <mergeCell ref="D405:D416"/>
+    <mergeCell ref="A436:J436"/>
+    <mergeCell ref="D359:D363"/>
+    <mergeCell ref="D364:D371"/>
+    <mergeCell ref="D372:D375"/>
+    <mergeCell ref="D376:D380"/>
+    <mergeCell ref="D381:D386"/>
+    <mergeCell ref="D387:D396"/>
+    <mergeCell ref="D397:D399"/>
+    <mergeCell ref="D301:D303"/>
+    <mergeCell ref="D304:D307"/>
+    <mergeCell ref="D308:D314"/>
+    <mergeCell ref="D315:D317"/>
+    <mergeCell ref="C343:C357"/>
+    <mergeCell ref="C359:C380"/>
+    <mergeCell ref="C381:C435"/>
+    <mergeCell ref="C437:C458"/>
+    <mergeCell ref="D250:D257"/>
+    <mergeCell ref="D258:D259"/>
+    <mergeCell ref="D260:D265"/>
+    <mergeCell ref="D266:D270"/>
+    <mergeCell ref="D271:D272"/>
+    <mergeCell ref="D274:D281"/>
+    <mergeCell ref="D282:D288"/>
+    <mergeCell ref="D289:D292"/>
+    <mergeCell ref="D293:D295"/>
+    <mergeCell ref="D449:D452"/>
+    <mergeCell ref="D453:D458"/>
+    <mergeCell ref="D417:D419"/>
+    <mergeCell ref="D420:D426"/>
+    <mergeCell ref="D427:D430"/>
+    <mergeCell ref="D431:D435"/>
+    <mergeCell ref="D437:D441"/>
     <mergeCell ref="C459:C513"/>
     <mergeCell ref="C216:C249"/>
     <mergeCell ref="C250:C265"/>
@@ -24122,107 +24245,6 @@
     <mergeCell ref="D348:D353"/>
     <mergeCell ref="D354:D357"/>
     <mergeCell ref="D296:D300"/>
-    <mergeCell ref="D301:D303"/>
-    <mergeCell ref="D304:D307"/>
-    <mergeCell ref="D308:D314"/>
-    <mergeCell ref="D315:D317"/>
-    <mergeCell ref="C343:C357"/>
-    <mergeCell ref="C359:C380"/>
-    <mergeCell ref="C381:C435"/>
-    <mergeCell ref="C437:C458"/>
-    <mergeCell ref="D250:D257"/>
-    <mergeCell ref="D258:D259"/>
-    <mergeCell ref="D260:D265"/>
-    <mergeCell ref="D266:D270"/>
-    <mergeCell ref="D271:D272"/>
-    <mergeCell ref="D274:D281"/>
-    <mergeCell ref="D282:D288"/>
-    <mergeCell ref="D289:D292"/>
-    <mergeCell ref="D293:D295"/>
-    <mergeCell ref="D449:D452"/>
-    <mergeCell ref="D453:D458"/>
-    <mergeCell ref="D417:D419"/>
-    <mergeCell ref="D420:D426"/>
-    <mergeCell ref="D427:D430"/>
-    <mergeCell ref="D431:D435"/>
-    <mergeCell ref="D437:D441"/>
-    <mergeCell ref="D442:D445"/>
-    <mergeCell ref="D446:D448"/>
-    <mergeCell ref="D400:D404"/>
-    <mergeCell ref="D405:D416"/>
-    <mergeCell ref="A436:J436"/>
-    <mergeCell ref="D359:D363"/>
-    <mergeCell ref="D364:D371"/>
-    <mergeCell ref="D372:D375"/>
-    <mergeCell ref="D376:D380"/>
-    <mergeCell ref="D381:D386"/>
-    <mergeCell ref="D387:D396"/>
-    <mergeCell ref="D397:D399"/>
-    <mergeCell ref="A215:J215"/>
-    <mergeCell ref="A273:J273"/>
-    <mergeCell ref="A358:J358"/>
-    <mergeCell ref="D134:D136"/>
-    <mergeCell ref="D137:D143"/>
-    <mergeCell ref="D144:D150"/>
-    <mergeCell ref="D151:D156"/>
-    <mergeCell ref="D157:D159"/>
-    <mergeCell ref="D160:D165"/>
-    <mergeCell ref="D166:D172"/>
-    <mergeCell ref="D173:D176"/>
-    <mergeCell ref="D177:D178"/>
-    <mergeCell ref="D179:D184"/>
-    <mergeCell ref="D185:D186"/>
-    <mergeCell ref="D187:D190"/>
-    <mergeCell ref="D191:D198"/>
-    <mergeCell ref="D199:D202"/>
-    <mergeCell ref="D203:D204"/>
-    <mergeCell ref="D205:D209"/>
-    <mergeCell ref="D216:D225"/>
-    <mergeCell ref="D226:D233"/>
-    <mergeCell ref="D234:D240"/>
-    <mergeCell ref="D241:D243"/>
-    <mergeCell ref="D244:D249"/>
-    <mergeCell ref="C45:C50"/>
-    <mergeCell ref="D45:D50"/>
-    <mergeCell ref="D51:D57"/>
-    <mergeCell ref="D58:D63"/>
-    <mergeCell ref="D64:D67"/>
-    <mergeCell ref="D69:D78"/>
-    <mergeCell ref="D79:D84"/>
-    <mergeCell ref="D85:D90"/>
-    <mergeCell ref="D91:D105"/>
-    <mergeCell ref="A68:J68"/>
-    <mergeCell ref="C51:C67"/>
-    <mergeCell ref="C69:C105"/>
-    <mergeCell ref="C107:C116"/>
-    <mergeCell ref="C117:C125"/>
-    <mergeCell ref="C127:C132"/>
-    <mergeCell ref="C134:C176"/>
-    <mergeCell ref="C177:C204"/>
-    <mergeCell ref="C205:C214"/>
-    <mergeCell ref="A106:J106"/>
-    <mergeCell ref="D107:D111"/>
-    <mergeCell ref="D112:D115"/>
-    <mergeCell ref="D117:D120"/>
-    <mergeCell ref="D121:D122"/>
-    <mergeCell ref="D123:D125"/>
-    <mergeCell ref="A126:J126"/>
-    <mergeCell ref="D127:D130"/>
-    <mergeCell ref="D131:D132"/>
-    <mergeCell ref="A133:J133"/>
-    <mergeCell ref="D210:D211"/>
-    <mergeCell ref="D212:D214"/>
-    <mergeCell ref="D26:D32"/>
-    <mergeCell ref="D33:D36"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="C4:C32"/>
-    <mergeCell ref="D4:D9"/>
-    <mergeCell ref="D10:D18"/>
-    <mergeCell ref="D19:D25"/>
-    <mergeCell ref="C33:C44"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="D40:D44"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H69:H105 H107:H125 H127:H132 H134:H214 H216:H272 H274:H357 H359:H435 H437:H513 H4:H65 H67" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/DSA Master Sheet.xlsx
+++ b/DSA Master Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aamer\Desktop\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C7E8F5-B658-471F-8B44-4895567CA17E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBFCC81E-1F6B-40CA-BB38-F3B303976AF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="733">
   <si>
     <t>DSA Master Sheet</t>
   </si>
@@ -2897,6 +2897,21 @@
             if(sign==1)low = mid+1;
             else high = mid-1;
         }</t>
+  </si>
+  <si>
+    <t>We need the kth missing, not the kth existing.
+For every index, calculate missing numbers before it using:
+arr[i]−1−i
+The missing count is monotonically increasing → use Binary Search.
+Find the first index where missing ≥ k (Lower Bound).
+Return index + k</t>
+  </si>
+  <si>
+    <t>Algorithm (4 Steps)
+1. Initialize `l = 0`, `r = n-1` (search whole array).
+2. Find `mid` and compare `nums[mid]` with `nums[r]`.
+3. If `nums[mid] &gt; nums[r]` → `l = mid+1`; else → `r = mid` (keep minimum side).
+4. When `l == r`, return `nums[l]` (minimum found).</t>
   </si>
 </sst>
 </file>
@@ -4401,23 +4416,32 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="88" fillId="53" borderId="8" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4437,6 +4461,42 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4445,6 +4505,51 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4464,96 +4569,6 @@
     <xf numFmtId="0" fontId="15" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4565,7 +4580,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="88" fillId="53" borderId="13" xfId="3" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
@@ -5363,18 +5378,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="30.75" customHeight="1">
-      <c r="A1" s="198" t="s">
+      <c r="A1" s="153" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="199"/>
-      <c r="C1" s="199"/>
-      <c r="D1" s="199"/>
-      <c r="E1" s="199"/>
-      <c r="F1" s="199"/>
-      <c r="G1" s="199"/>
-      <c r="H1" s="199"/>
-      <c r="I1" s="199"/>
-      <c r="J1" s="200"/>
+      <c r="B1" s="154"/>
+      <c r="C1" s="154"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="154"/>
+      <c r="F1" s="154"/>
+      <c r="G1" s="154"/>
+      <c r="H1" s="154"/>
+      <c r="I1" s="154"/>
+      <c r="J1" s="155"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -5429,18 +5444,18 @@
       <c r="T2" s="5"/>
     </row>
     <row r="3" spans="1:20" ht="13.8">
-      <c r="A3" s="195" t="s">
+      <c r="A3" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="196"/>
-      <c r="C3" s="196"/>
-      <c r="D3" s="196"/>
-      <c r="E3" s="196"/>
-      <c r="F3" s="196"/>
-      <c r="G3" s="196"/>
-      <c r="H3" s="196"/>
-      <c r="I3" s="196"/>
-      <c r="J3" s="197"/>
+      <c r="B3" s="157"/>
+      <c r="C3" s="157"/>
+      <c r="D3" s="157"/>
+      <c r="E3" s="157"/>
+      <c r="F3" s="157"/>
+      <c r="G3" s="157"/>
+      <c r="H3" s="157"/>
+      <c r="I3" s="157"/>
+      <c r="J3" s="158"/>
     </row>
     <row r="4" spans="1:20" ht="13.8">
       <c r="A4" s="6">
@@ -5449,10 +5464,10 @@
       <c r="B4" s="7">
         <v>1</v>
       </c>
-      <c r="C4" s="156" t="s">
+      <c r="C4" s="159" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="171" t="s">
+      <c r="D4" s="150" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -5482,8 +5497,8 @@
       <c r="B5" s="7">
         <v>2</v>
       </c>
-      <c r="C5" s="157"/>
-      <c r="D5" s="172"/>
+      <c r="C5" s="160"/>
+      <c r="D5" s="151"/>
       <c r="E5" s="8" t="s">
         <v>16</v>
       </c>
@@ -5511,8 +5526,8 @@
       <c r="B6" s="7">
         <v>3</v>
       </c>
-      <c r="C6" s="157"/>
-      <c r="D6" s="172"/>
+      <c r="C6" s="160"/>
+      <c r="D6" s="151"/>
       <c r="E6" s="8" t="s">
         <v>19</v>
       </c>
@@ -5540,8 +5555,8 @@
       <c r="B7" s="7">
         <v>4</v>
       </c>
-      <c r="C7" s="157"/>
-      <c r="D7" s="172"/>
+      <c r="C7" s="160"/>
+      <c r="D7" s="151"/>
       <c r="E7" s="8" t="s">
         <v>23</v>
       </c>
@@ -5569,8 +5584,8 @@
       <c r="B8" s="7">
         <v>5</v>
       </c>
-      <c r="C8" s="157"/>
-      <c r="D8" s="172"/>
+      <c r="C8" s="160"/>
+      <c r="D8" s="151"/>
       <c r="E8" s="8" t="s">
         <v>26</v>
       </c>
@@ -5598,8 +5613,8 @@
       <c r="B9" s="7">
         <v>6</v>
       </c>
-      <c r="C9" s="157"/>
-      <c r="D9" s="173"/>
+      <c r="C9" s="160"/>
+      <c r="D9" s="152"/>
       <c r="E9" s="8" t="s">
         <v>29</v>
       </c>
@@ -5624,8 +5639,8 @@
       <c r="B10" s="7">
         <v>7</v>
       </c>
-      <c r="C10" s="157"/>
-      <c r="D10" s="171" t="s">
+      <c r="C10" s="160"/>
+      <c r="D10" s="150" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="8" t="s">
@@ -5652,8 +5667,8 @@
       <c r="B11" s="7">
         <v>8</v>
       </c>
-      <c r="C11" s="157"/>
-      <c r="D11" s="172"/>
+      <c r="C11" s="160"/>
+      <c r="D11" s="151"/>
       <c r="E11" s="13" t="s">
         <v>32</v>
       </c>
@@ -5678,8 +5693,8 @@
       <c r="B12" s="7">
         <v>9</v>
       </c>
-      <c r="C12" s="157"/>
-      <c r="D12" s="172"/>
+      <c r="C12" s="160"/>
+      <c r="D12" s="151"/>
       <c r="E12" s="8" t="s">
         <v>33</v>
       </c>
@@ -5704,8 +5719,8 @@
       <c r="B13" s="7">
         <v>10</v>
       </c>
-      <c r="C13" s="157"/>
-      <c r="D13" s="172"/>
+      <c r="C13" s="160"/>
+      <c r="D13" s="151"/>
       <c r="E13" s="8" t="s">
         <v>34</v>
       </c>
@@ -5732,8 +5747,8 @@
       <c r="B14" s="7">
         <v>11</v>
       </c>
-      <c r="C14" s="157"/>
-      <c r="D14" s="172"/>
+      <c r="C14" s="160"/>
+      <c r="D14" s="151"/>
       <c r="E14" s="8" t="s">
         <v>35</v>
       </c>
@@ -5758,8 +5773,8 @@
       <c r="B15" s="7">
         <v>12</v>
       </c>
-      <c r="C15" s="157"/>
-      <c r="D15" s="172"/>
+      <c r="C15" s="160"/>
+      <c r="D15" s="151"/>
       <c r="E15" s="8" t="s">
         <v>36</v>
       </c>
@@ -5786,8 +5801,8 @@
       <c r="B16" s="7">
         <v>13</v>
       </c>
-      <c r="C16" s="157"/>
-      <c r="D16" s="172"/>
+      <c r="C16" s="160"/>
+      <c r="D16" s="151"/>
       <c r="E16" s="8" t="s">
         <v>37</v>
       </c>
@@ -5812,8 +5827,8 @@
       <c r="B17" s="7">
         <v>14</v>
       </c>
-      <c r="C17" s="157"/>
-      <c r="D17" s="172"/>
+      <c r="C17" s="160"/>
+      <c r="D17" s="151"/>
       <c r="E17" s="8" t="s">
         <v>38</v>
       </c>
@@ -5840,8 +5855,8 @@
       <c r="B18" s="7">
         <v>15</v>
       </c>
-      <c r="C18" s="157"/>
-      <c r="D18" s="173"/>
+      <c r="C18" s="160"/>
+      <c r="D18" s="152"/>
       <c r="E18" s="13" t="s">
         <v>39</v>
       </c>
@@ -5868,8 +5883,8 @@
       <c r="B19" s="7">
         <v>16</v>
       </c>
-      <c r="C19" s="157"/>
-      <c r="D19" s="171" t="s">
+      <c r="C19" s="160"/>
+      <c r="D19" s="150" t="s">
         <v>40</v>
       </c>
       <c r="E19" s="8" t="s">
@@ -5898,8 +5913,8 @@
       <c r="B20" s="7">
         <v>17</v>
       </c>
-      <c r="C20" s="157"/>
-      <c r="D20" s="172"/>
+      <c r="C20" s="160"/>
+      <c r="D20" s="151"/>
       <c r="E20" s="8" t="s">
         <v>42</v>
       </c>
@@ -5926,8 +5941,8 @@
       <c r="B21" s="7">
         <v>18</v>
       </c>
-      <c r="C21" s="157"/>
-      <c r="D21" s="172"/>
+      <c r="C21" s="160"/>
+      <c r="D21" s="151"/>
       <c r="E21" s="8" t="s">
         <v>43</v>
       </c>
@@ -5954,8 +5969,8 @@
       <c r="B22" s="7">
         <v>19</v>
       </c>
-      <c r="C22" s="157"/>
-      <c r="D22" s="172"/>
+      <c r="C22" s="160"/>
+      <c r="D22" s="151"/>
       <c r="E22" s="8" t="s">
         <v>44</v>
       </c>
@@ -5976,8 +5991,8 @@
       <c r="B23" s="7">
         <v>20</v>
       </c>
-      <c r="C23" s="157"/>
-      <c r="D23" s="172"/>
+      <c r="C23" s="160"/>
+      <c r="D23" s="151"/>
       <c r="E23" s="8" t="s">
         <v>45</v>
       </c>
@@ -5998,8 +6013,8 @@
       <c r="B24" s="7">
         <v>21</v>
       </c>
-      <c r="C24" s="157"/>
-      <c r="D24" s="172"/>
+      <c r="C24" s="160"/>
+      <c r="D24" s="151"/>
       <c r="E24" s="13" t="s">
         <v>46</v>
       </c>
@@ -6024,8 +6039,8 @@
       <c r="B25" s="7">
         <v>22</v>
       </c>
-      <c r="C25" s="157"/>
-      <c r="D25" s="173"/>
+      <c r="C25" s="160"/>
+      <c r="D25" s="152"/>
       <c r="E25" s="8" t="s">
         <v>47</v>
       </c>
@@ -6052,8 +6067,8 @@
       <c r="B26" s="7">
         <v>23</v>
       </c>
-      <c r="C26" s="157"/>
-      <c r="D26" s="171" t="s">
+      <c r="C26" s="160"/>
+      <c r="D26" s="150" t="s">
         <v>48</v>
       </c>
       <c r="E26" s="13" t="s">
@@ -6082,8 +6097,8 @@
       <c r="B27" s="7">
         <v>24</v>
       </c>
-      <c r="C27" s="157"/>
-      <c r="D27" s="172"/>
+      <c r="C27" s="160"/>
+      <c r="D27" s="151"/>
       <c r="E27" s="8" t="s">
         <v>50</v>
       </c>
@@ -6108,8 +6123,8 @@
       <c r="B28" s="7">
         <v>25</v>
       </c>
-      <c r="C28" s="157"/>
-      <c r="D28" s="172"/>
+      <c r="C28" s="160"/>
+      <c r="D28" s="151"/>
       <c r="E28" s="8" t="s">
         <v>51</v>
       </c>
@@ -6136,8 +6151,8 @@
       <c r="B29" s="143">
         <v>26</v>
       </c>
-      <c r="C29" s="157"/>
-      <c r="D29" s="172"/>
+      <c r="C29" s="160"/>
+      <c r="D29" s="151"/>
       <c r="E29" s="144" t="s">
         <v>52</v>
       </c>
@@ -6158,8 +6173,8 @@
       <c r="B30" s="143">
         <v>27</v>
       </c>
-      <c r="C30" s="157"/>
-      <c r="D30" s="172"/>
+      <c r="C30" s="160"/>
+      <c r="D30" s="151"/>
       <c r="E30" s="144" t="s">
         <v>53</v>
       </c>
@@ -6180,8 +6195,8 @@
       <c r="B31" s="143">
         <v>28</v>
       </c>
-      <c r="C31" s="157"/>
-      <c r="D31" s="172"/>
+      <c r="C31" s="160"/>
+      <c r="D31" s="151"/>
       <c r="E31" s="144" t="s">
         <v>54</v>
       </c>
@@ -6202,8 +6217,8 @@
       <c r="B32" s="143">
         <v>29</v>
       </c>
-      <c r="C32" s="158"/>
-      <c r="D32" s="173"/>
+      <c r="C32" s="161"/>
+      <c r="D32" s="152"/>
       <c r="E32" s="146" t="s">
         <v>55</v>
       </c>
@@ -6224,10 +6239,10 @@
       <c r="B33" s="22">
         <v>1</v>
       </c>
-      <c r="C33" s="159" t="s">
+      <c r="C33" s="162" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="171" t="s">
+      <c r="D33" s="150" t="s">
         <v>57</v>
       </c>
       <c r="E33" s="8" t="s">
@@ -6254,8 +6269,8 @@
       <c r="B34" s="7">
         <v>2</v>
       </c>
-      <c r="C34" s="160"/>
-      <c r="D34" s="172"/>
+      <c r="C34" s="163"/>
+      <c r="D34" s="151"/>
       <c r="E34" s="8" t="s">
         <v>59</v>
       </c>
@@ -6280,8 +6295,8 @@
       <c r="B35" s="7">
         <v>3</v>
       </c>
-      <c r="C35" s="160"/>
-      <c r="D35" s="172"/>
+      <c r="C35" s="163"/>
+      <c r="D35" s="151"/>
       <c r="E35" s="8" t="s">
         <v>60</v>
       </c>
@@ -6308,8 +6323,8 @@
       <c r="B36" s="7">
         <v>4</v>
       </c>
-      <c r="C36" s="160"/>
-      <c r="D36" s="173"/>
+      <c r="C36" s="163"/>
+      <c r="D36" s="152"/>
       <c r="E36" s="8" t="s">
         <v>61</v>
       </c>
@@ -6336,8 +6351,8 @@
       <c r="B37" s="7">
         <v>5</v>
       </c>
-      <c r="C37" s="160"/>
-      <c r="D37" s="171" t="s">
+      <c r="C37" s="163"/>
+      <c r="D37" s="150" t="s">
         <v>62</v>
       </c>
       <c r="E37" s="8" t="s">
@@ -6364,8 +6379,8 @@
       <c r="B38" s="7">
         <v>6</v>
       </c>
-      <c r="C38" s="160"/>
-      <c r="D38" s="172"/>
+      <c r="C38" s="163"/>
+      <c r="D38" s="151"/>
       <c r="E38" s="8" t="s">
         <v>64</v>
       </c>
@@ -6390,8 +6405,8 @@
       <c r="B39" s="7">
         <v>7</v>
       </c>
-      <c r="C39" s="160"/>
-      <c r="D39" s="173"/>
+      <c r="C39" s="163"/>
+      <c r="D39" s="152"/>
       <c r="E39" s="8" t="s">
         <v>65</v>
       </c>
@@ -6416,8 +6431,8 @@
       <c r="B40" s="7">
         <v>8</v>
       </c>
-      <c r="C40" s="160"/>
-      <c r="D40" s="171" t="s">
+      <c r="C40" s="163"/>
+      <c r="D40" s="150" t="s">
         <v>66</v>
       </c>
       <c r="E40" s="8" t="s">
@@ -6444,8 +6459,8 @@
       <c r="B41" s="7">
         <v>9</v>
       </c>
-      <c r="C41" s="160"/>
-      <c r="D41" s="172"/>
+      <c r="C41" s="163"/>
+      <c r="D41" s="151"/>
       <c r="E41" s="8" t="s">
         <v>68</v>
       </c>
@@ -6470,8 +6485,8 @@
       <c r="B42" s="7">
         <v>10</v>
       </c>
-      <c r="C42" s="160"/>
-      <c r="D42" s="172"/>
+      <c r="C42" s="163"/>
+      <c r="D42" s="151"/>
       <c r="E42" s="8" t="s">
         <v>69</v>
       </c>
@@ -6496,8 +6511,8 @@
       <c r="B43" s="7">
         <v>11</v>
       </c>
-      <c r="C43" s="160"/>
-      <c r="D43" s="172"/>
+      <c r="C43" s="163"/>
+      <c r="D43" s="151"/>
       <c r="E43" s="8" t="s">
         <v>70</v>
       </c>
@@ -6522,8 +6537,8 @@
       <c r="B44" s="24">
         <v>12</v>
       </c>
-      <c r="C44" s="161"/>
-      <c r="D44" s="173"/>
+      <c r="C44" s="164"/>
+      <c r="D44" s="152"/>
       <c r="E44" s="17" t="s">
         <v>71</v>
       </c>
@@ -6548,10 +6563,10 @@
       <c r="B45" s="22">
         <v>1</v>
       </c>
-      <c r="C45" s="162" t="s">
+      <c r="C45" s="177" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="174" t="s">
+      <c r="D45" s="180" t="s">
         <v>73</v>
       </c>
       <c r="E45" s="13" t="s">
@@ -6578,8 +6593,8 @@
       <c r="B46" s="7">
         <v>2</v>
       </c>
-      <c r="C46" s="163"/>
-      <c r="D46" s="175"/>
+      <c r="C46" s="178"/>
+      <c r="D46" s="181"/>
       <c r="E46" s="8" t="s">
         <v>75</v>
       </c>
@@ -6606,8 +6621,8 @@
       <c r="B47" s="7">
         <v>3</v>
       </c>
-      <c r="C47" s="163"/>
-      <c r="D47" s="175"/>
+      <c r="C47" s="178"/>
+      <c r="D47" s="181"/>
       <c r="E47" s="13" t="s">
         <v>76</v>
       </c>
@@ -6634,8 +6649,8 @@
       <c r="B48" s="7">
         <v>4</v>
       </c>
-      <c r="C48" s="163"/>
-      <c r="D48" s="175"/>
+      <c r="C48" s="178"/>
+      <c r="D48" s="181"/>
       <c r="E48" s="13" t="s">
         <v>77</v>
       </c>
@@ -6662,8 +6677,8 @@
       <c r="B49" s="7">
         <v>5</v>
       </c>
-      <c r="C49" s="163"/>
-      <c r="D49" s="175"/>
+      <c r="C49" s="178"/>
+      <c r="D49" s="181"/>
       <c r="E49" s="13" t="s">
         <v>78</v>
       </c>
@@ -6688,8 +6703,8 @@
       <c r="B50" s="24">
         <v>6</v>
       </c>
-      <c r="C50" s="164"/>
-      <c r="D50" s="176"/>
+      <c r="C50" s="179"/>
+      <c r="D50" s="182"/>
       <c r="E50" s="25" t="s">
         <v>79</v>
       </c>
@@ -6714,10 +6729,10 @@
       <c r="B51" s="7">
         <v>1</v>
       </c>
-      <c r="C51" s="153" t="s">
+      <c r="C51" s="168" t="s">
         <v>80</v>
       </c>
-      <c r="D51" s="171" t="s">
+      <c r="D51" s="150" t="s">
         <v>81</v>
       </c>
       <c r="E51" s="13" t="s">
@@ -6746,8 +6761,8 @@
       <c r="B52" s="7">
         <v>2</v>
       </c>
-      <c r="C52" s="154"/>
-      <c r="D52" s="172"/>
+      <c r="C52" s="169"/>
+      <c r="D52" s="151"/>
       <c r="E52" s="8" t="s">
         <v>83</v>
       </c>
@@ -6774,8 +6789,8 @@
       <c r="B53" s="7">
         <v>3</v>
       </c>
-      <c r="C53" s="154"/>
-      <c r="D53" s="172"/>
+      <c r="C53" s="169"/>
+      <c r="D53" s="151"/>
       <c r="E53" s="27" t="s">
         <v>84</v>
       </c>
@@ -6800,8 +6815,8 @@
       <c r="B54" s="7">
         <v>4</v>
       </c>
-      <c r="C54" s="154"/>
-      <c r="D54" s="172"/>
+      <c r="C54" s="169"/>
+      <c r="D54" s="151"/>
       <c r="E54" s="13" t="s">
         <v>85</v>
       </c>
@@ -6826,8 +6841,8 @@
       <c r="B55" s="7">
         <v>5</v>
       </c>
-      <c r="C55" s="154"/>
-      <c r="D55" s="172"/>
+      <c r="C55" s="169"/>
+      <c r="D55" s="151"/>
       <c r="E55" s="13" t="s">
         <v>86</v>
       </c>
@@ -6854,8 +6869,8 @@
       <c r="B56" s="7">
         <v>6</v>
       </c>
-      <c r="C56" s="154"/>
-      <c r="D56" s="172"/>
+      <c r="C56" s="169"/>
+      <c r="D56" s="151"/>
       <c r="E56" s="13" t="s">
         <v>87</v>
       </c>
@@ -6882,8 +6897,8 @@
       <c r="B57" s="7">
         <v>7</v>
       </c>
-      <c r="C57" s="154"/>
-      <c r="D57" s="173"/>
+      <c r="C57" s="169"/>
+      <c r="D57" s="152"/>
       <c r="E57" s="13" t="s">
         <v>88</v>
       </c>
@@ -6910,8 +6925,8 @@
       <c r="B58" s="7">
         <v>8</v>
       </c>
-      <c r="C58" s="154"/>
-      <c r="D58" s="171" t="s">
+      <c r="C58" s="169"/>
+      <c r="D58" s="150" t="s">
         <v>89</v>
       </c>
       <c r="E58" s="13" t="s">
@@ -6938,8 +6953,8 @@
       <c r="B59" s="7">
         <v>9</v>
       </c>
-      <c r="C59" s="154"/>
-      <c r="D59" s="172"/>
+      <c r="C59" s="169"/>
+      <c r="D59" s="151"/>
       <c r="E59" s="8" t="s">
         <v>91</v>
       </c>
@@ -6964,8 +6979,8 @@
       <c r="B60" s="7">
         <v>10</v>
       </c>
-      <c r="C60" s="154"/>
-      <c r="D60" s="172"/>
+      <c r="C60" s="169"/>
+      <c r="D60" s="151"/>
       <c r="E60" s="8" t="s">
         <v>92</v>
       </c>
@@ -6986,8 +7001,8 @@
       <c r="B61" s="7">
         <v>11</v>
       </c>
-      <c r="C61" s="154"/>
-      <c r="D61" s="172"/>
+      <c r="C61" s="169"/>
+      <c r="D61" s="151"/>
       <c r="E61" s="8" t="s">
         <v>93</v>
       </c>
@@ -7008,8 +7023,8 @@
       <c r="B62" s="7">
         <v>12</v>
       </c>
-      <c r="C62" s="154"/>
-      <c r="D62" s="172"/>
+      <c r="C62" s="169"/>
+      <c r="D62" s="151"/>
       <c r="E62" s="8" t="s">
         <v>94</v>
       </c>
@@ -7034,8 +7049,8 @@
       <c r="B63" s="7">
         <v>13</v>
       </c>
-      <c r="C63" s="154"/>
-      <c r="D63" s="173"/>
+      <c r="C63" s="169"/>
+      <c r="D63" s="152"/>
       <c r="E63" s="8" t="s">
         <v>95</v>
       </c>
@@ -7060,8 +7075,8 @@
       <c r="B64" s="7">
         <v>14</v>
       </c>
-      <c r="C64" s="154"/>
-      <c r="D64" s="171" t="s">
+      <c r="C64" s="169"/>
+      <c r="D64" s="150" t="s">
         <v>48</v>
       </c>
       <c r="E64" s="8" t="s">
@@ -7090,8 +7105,8 @@
       <c r="B65" s="143">
         <v>15</v>
       </c>
-      <c r="C65" s="154"/>
-      <c r="D65" s="172"/>
+      <c r="C65" s="169"/>
+      <c r="D65" s="151"/>
       <c r="E65" s="144" t="s">
         <v>97</v>
       </c>
@@ -7112,8 +7127,8 @@
       <c r="B66" s="7">
         <v>16</v>
       </c>
-      <c r="C66" s="154"/>
-      <c r="D66" s="172"/>
+      <c r="C66" s="169"/>
+      <c r="D66" s="151"/>
       <c r="E66" s="8" t="s">
         <v>98</v>
       </c>
@@ -7140,8 +7155,8 @@
       <c r="B67" s="7">
         <v>17</v>
       </c>
-      <c r="C67" s="155"/>
-      <c r="D67" s="173"/>
+      <c r="C67" s="170"/>
+      <c r="D67" s="152"/>
       <c r="E67" s="8" t="s">
         <v>99</v>
       </c>
@@ -7182,10 +7197,10 @@
       <c r="B69" s="7">
         <v>1</v>
       </c>
-      <c r="C69" s="156" t="s">
+      <c r="C69" s="159" t="s">
         <v>101</v>
       </c>
-      <c r="D69" s="171" t="s">
+      <c r="D69" s="150" t="s">
         <v>102</v>
       </c>
       <c r="E69" s="8" t="s">
@@ -7212,8 +7227,8 @@
       <c r="B70" s="7">
         <v>2</v>
       </c>
-      <c r="C70" s="157"/>
-      <c r="D70" s="172"/>
+      <c r="C70" s="160"/>
+      <c r="D70" s="151"/>
       <c r="E70" s="28" t="s">
         <v>104</v>
       </c>
@@ -7240,8 +7255,8 @@
       <c r="B71" s="7">
         <v>3</v>
       </c>
-      <c r="C71" s="157"/>
-      <c r="D71" s="172"/>
+      <c r="C71" s="160"/>
+      <c r="D71" s="151"/>
       <c r="E71" s="8" t="s">
         <v>105</v>
       </c>
@@ -7268,8 +7283,8 @@
       <c r="B72" s="7">
         <v>4</v>
       </c>
-      <c r="C72" s="157"/>
-      <c r="D72" s="172"/>
+      <c r="C72" s="160"/>
+      <c r="D72" s="151"/>
       <c r="E72" s="8" t="s">
         <v>106</v>
       </c>
@@ -7296,8 +7311,8 @@
       <c r="B73" s="7">
         <v>5</v>
       </c>
-      <c r="C73" s="157"/>
-      <c r="D73" s="172"/>
+      <c r="C73" s="160"/>
+      <c r="D73" s="151"/>
       <c r="E73" s="28" t="s">
         <v>107</v>
       </c>
@@ -7324,8 +7339,8 @@
       <c r="B74" s="7">
         <v>6</v>
       </c>
-      <c r="C74" s="157"/>
-      <c r="D74" s="172"/>
+      <c r="C74" s="160"/>
+      <c r="D74" s="151"/>
       <c r="E74" s="28" t="s">
         <v>108</v>
       </c>
@@ -7350,8 +7365,8 @@
       <c r="B75" s="7">
         <v>7</v>
       </c>
-      <c r="C75" s="157"/>
-      <c r="D75" s="172"/>
+      <c r="C75" s="160"/>
+      <c r="D75" s="151"/>
       <c r="E75" s="28" t="s">
         <v>109</v>
       </c>
@@ -7378,8 +7393,8 @@
       <c r="B76" s="7">
         <v>8</v>
       </c>
-      <c r="C76" s="157"/>
-      <c r="D76" s="172"/>
+      <c r="C76" s="160"/>
+      <c r="D76" s="151"/>
       <c r="E76" s="8" t="s">
         <v>110</v>
       </c>
@@ -7397,15 +7412,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="13.8">
+    <row r="77" spans="1:10" ht="193.2">
       <c r="A77" s="6">
         <v>73</v>
       </c>
       <c r="B77" s="7">
         <v>9</v>
       </c>
-      <c r="C77" s="157"/>
-      <c r="D77" s="172"/>
+      <c r="C77" s="160"/>
+      <c r="D77" s="151"/>
       <c r="E77" s="8" t="s">
         <v>111</v>
       </c>
@@ -7415,21 +7430,25 @@
       <c r="G77" s="10">
         <v>2</v>
       </c>
-      <c r="H77" s="11"/>
-      <c r="I77" s="11"/>
+      <c r="H77" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I77" s="125" t="s">
+        <v>731</v>
+      </c>
       <c r="J77" s="206" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" ht="13.8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="165.6">
       <c r="A78" s="6">
         <v>74</v>
       </c>
       <c r="B78" s="7">
         <v>10</v>
       </c>
-      <c r="C78" s="157"/>
-      <c r="D78" s="173"/>
+      <c r="C78" s="160"/>
+      <c r="D78" s="152"/>
       <c r="E78" s="8" t="s">
         <v>112</v>
       </c>
@@ -7439,9 +7458,15 @@
       <c r="G78" s="10">
         <v>2</v>
       </c>
-      <c r="H78" s="11"/>
-      <c r="I78" s="11"/>
-      <c r="J78" s="11"/>
+      <c r="H78" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I78" s="125" t="s">
+        <v>732</v>
+      </c>
+      <c r="J78" s="126" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="79" spans="1:10" ht="13.8">
       <c r="A79" s="6">
@@ -7450,8 +7475,8 @@
       <c r="B79" s="7">
         <v>11</v>
       </c>
-      <c r="C79" s="157"/>
-      <c r="D79" s="171" t="s">
+      <c r="C79" s="160"/>
+      <c r="D79" s="150" t="s">
         <v>113</v>
       </c>
       <c r="E79" s="8" t="s">
@@ -7474,8 +7499,8 @@
       <c r="B80" s="7">
         <v>12</v>
       </c>
-      <c r="C80" s="157"/>
-      <c r="D80" s="172"/>
+      <c r="C80" s="160"/>
+      <c r="D80" s="151"/>
       <c r="E80" s="8" t="s">
         <v>115</v>
       </c>
@@ -7496,8 +7521,8 @@
       <c r="B81" s="7">
         <v>13</v>
       </c>
-      <c r="C81" s="157"/>
-      <c r="D81" s="172"/>
+      <c r="C81" s="160"/>
+      <c r="D81" s="151"/>
       <c r="E81" s="8" t="s">
         <v>116</v>
       </c>
@@ -7518,8 +7543,8 @@
       <c r="B82" s="7">
         <v>14</v>
       </c>
-      <c r="C82" s="157"/>
-      <c r="D82" s="172"/>
+      <c r="C82" s="160"/>
+      <c r="D82" s="151"/>
       <c r="E82" s="8" t="s">
         <v>117</v>
       </c>
@@ -7540,8 +7565,8 @@
       <c r="B83" s="7">
         <v>15</v>
       </c>
-      <c r="C83" s="157"/>
-      <c r="D83" s="172"/>
+      <c r="C83" s="160"/>
+      <c r="D83" s="151"/>
       <c r="E83" s="8" t="s">
         <v>118</v>
       </c>
@@ -7562,8 +7587,8 @@
       <c r="B84" s="7">
         <v>16</v>
       </c>
-      <c r="C84" s="157"/>
-      <c r="D84" s="173"/>
+      <c r="C84" s="160"/>
+      <c r="D84" s="152"/>
       <c r="E84" s="8" t="s">
         <v>119</v>
       </c>
@@ -7584,8 +7609,8 @@
       <c r="B85" s="7">
         <v>17</v>
       </c>
-      <c r="C85" s="157"/>
-      <c r="D85" s="171" t="s">
+      <c r="C85" s="160"/>
+      <c r="D85" s="150" t="s">
         <v>120</v>
       </c>
       <c r="E85" s="8" t="s">
@@ -7608,8 +7633,8 @@
       <c r="B86" s="7">
         <v>18</v>
       </c>
-      <c r="C86" s="157"/>
-      <c r="D86" s="172"/>
+      <c r="C86" s="160"/>
+      <c r="D86" s="151"/>
       <c r="E86" s="8" t="s">
         <v>122</v>
       </c>
@@ -7630,8 +7655,8 @@
       <c r="B87" s="7">
         <v>19</v>
       </c>
-      <c r="C87" s="157"/>
-      <c r="D87" s="172"/>
+      <c r="C87" s="160"/>
+      <c r="D87" s="151"/>
       <c r="E87" s="29" t="s">
         <v>123</v>
       </c>
@@ -7652,8 +7677,8 @@
       <c r="B88" s="7">
         <v>20</v>
       </c>
-      <c r="C88" s="157"/>
-      <c r="D88" s="172"/>
+      <c r="C88" s="160"/>
+      <c r="D88" s="151"/>
       <c r="E88" s="8" t="s">
         <v>124</v>
       </c>
@@ -7674,8 +7699,8 @@
       <c r="B89" s="7">
         <v>21</v>
       </c>
-      <c r="C89" s="157"/>
-      <c r="D89" s="172"/>
+      <c r="C89" s="160"/>
+      <c r="D89" s="151"/>
       <c r="E89" s="8" t="s">
         <v>125</v>
       </c>
@@ -7696,8 +7721,8 @@
       <c r="B90" s="7">
         <v>22</v>
       </c>
-      <c r="C90" s="157"/>
-      <c r="D90" s="173"/>
+      <c r="C90" s="160"/>
+      <c r="D90" s="152"/>
       <c r="E90" s="8" t="s">
         <v>126</v>
       </c>
@@ -7718,8 +7743,8 @@
       <c r="B91" s="7">
         <v>23</v>
       </c>
-      <c r="C91" s="157"/>
-      <c r="D91" s="171" t="s">
+      <c r="C91" s="160"/>
+      <c r="D91" s="150" t="s">
         <v>127</v>
       </c>
       <c r="E91" s="8" t="s">
@@ -7742,8 +7767,8 @@
       <c r="B92" s="7">
         <v>24</v>
       </c>
-      <c r="C92" s="157"/>
-      <c r="D92" s="172"/>
+      <c r="C92" s="160"/>
+      <c r="D92" s="151"/>
       <c r="E92" s="8" t="s">
         <v>129</v>
       </c>
@@ -7764,8 +7789,8 @@
       <c r="B93" s="7">
         <v>25</v>
       </c>
-      <c r="C93" s="157"/>
-      <c r="D93" s="172"/>
+      <c r="C93" s="160"/>
+      <c r="D93" s="151"/>
       <c r="E93" s="8" t="s">
         <v>130</v>
       </c>
@@ -7786,8 +7811,8 @@
       <c r="B94" s="7">
         <v>26</v>
       </c>
-      <c r="C94" s="157"/>
-      <c r="D94" s="172"/>
+      <c r="C94" s="160"/>
+      <c r="D94" s="151"/>
       <c r="E94" s="8" t="s">
         <v>131</v>
       </c>
@@ -7808,8 +7833,8 @@
       <c r="B95" s="7">
         <v>27</v>
       </c>
-      <c r="C95" s="157"/>
-      <c r="D95" s="172"/>
+      <c r="C95" s="160"/>
+      <c r="D95" s="151"/>
       <c r="E95" s="8" t="s">
         <v>132</v>
       </c>
@@ -7830,8 +7855,8 @@
       <c r="B96" s="7">
         <v>28</v>
       </c>
-      <c r="C96" s="157"/>
-      <c r="D96" s="172"/>
+      <c r="C96" s="160"/>
+      <c r="D96" s="151"/>
       <c r="E96" s="8" t="s">
         <v>133</v>
       </c>
@@ -7852,8 +7877,8 @@
       <c r="B97" s="7">
         <v>29</v>
       </c>
-      <c r="C97" s="157"/>
-      <c r="D97" s="172"/>
+      <c r="C97" s="160"/>
+      <c r="D97" s="151"/>
       <c r="E97" s="8" t="s">
         <v>134</v>
       </c>
@@ -7874,8 +7899,8 @@
       <c r="B98" s="7">
         <v>30</v>
       </c>
-      <c r="C98" s="157"/>
-      <c r="D98" s="172"/>
+      <c r="C98" s="160"/>
+      <c r="D98" s="151"/>
       <c r="E98" s="8" t="s">
         <v>135</v>
       </c>
@@ -7896,8 +7921,8 @@
       <c r="B99" s="7">
         <v>31</v>
       </c>
-      <c r="C99" s="157"/>
-      <c r="D99" s="172"/>
+      <c r="C99" s="160"/>
+      <c r="D99" s="151"/>
       <c r="E99" s="30" t="s">
         <v>136</v>
       </c>
@@ -7918,8 +7943,8 @@
       <c r="B100" s="7">
         <v>32</v>
       </c>
-      <c r="C100" s="157"/>
-      <c r="D100" s="172"/>
+      <c r="C100" s="160"/>
+      <c r="D100" s="151"/>
       <c r="E100" s="8" t="s">
         <v>137</v>
       </c>
@@ -7940,8 +7965,8 @@
       <c r="B101" s="7">
         <v>33</v>
       </c>
-      <c r="C101" s="157"/>
-      <c r="D101" s="172"/>
+      <c r="C101" s="160"/>
+      <c r="D101" s="151"/>
       <c r="E101" s="8" t="s">
         <v>138</v>
       </c>
@@ -7962,8 +7987,8 @@
       <c r="B102" s="7">
         <v>34</v>
       </c>
-      <c r="C102" s="157"/>
-      <c r="D102" s="172"/>
+      <c r="C102" s="160"/>
+      <c r="D102" s="151"/>
       <c r="E102" s="8" t="s">
         <v>139</v>
       </c>
@@ -7984,8 +8009,8 @@
       <c r="B103" s="7">
         <v>35</v>
       </c>
-      <c r="C103" s="157"/>
-      <c r="D103" s="172"/>
+      <c r="C103" s="160"/>
+      <c r="D103" s="151"/>
       <c r="E103" s="8" t="s">
         <v>140</v>
       </c>
@@ -8006,8 +8031,8 @@
       <c r="B104" s="7">
         <v>36</v>
       </c>
-      <c r="C104" s="157"/>
-      <c r="D104" s="172"/>
+      <c r="C104" s="160"/>
+      <c r="D104" s="151"/>
       <c r="E104" s="8" t="s">
         <v>141</v>
       </c>
@@ -8028,8 +8053,8 @@
       <c r="B105" s="7">
         <v>37</v>
       </c>
-      <c r="C105" s="158"/>
-      <c r="D105" s="173"/>
+      <c r="C105" s="161"/>
+      <c r="D105" s="152"/>
       <c r="E105" s="8" t="s">
         <v>142</v>
       </c>
@@ -8044,18 +8069,18 @@
       <c r="J105" s="11"/>
     </row>
     <row r="106" spans="1:10" ht="13.8">
-      <c r="A106" s="189" t="s">
+      <c r="A106" s="171" t="s">
         <v>143</v>
       </c>
-      <c r="B106" s="190"/>
-      <c r="C106" s="190"/>
-      <c r="D106" s="190"/>
-      <c r="E106" s="190"/>
-      <c r="F106" s="190"/>
-      <c r="G106" s="190"/>
-      <c r="H106" s="190"/>
-      <c r="I106" s="190"/>
-      <c r="J106" s="191"/>
+      <c r="B106" s="172"/>
+      <c r="C106" s="172"/>
+      <c r="D106" s="172"/>
+      <c r="E106" s="172"/>
+      <c r="F106" s="172"/>
+      <c r="G106" s="172"/>
+      <c r="H106" s="172"/>
+      <c r="I106" s="172"/>
+      <c r="J106" s="173"/>
     </row>
     <row r="107" spans="1:10" ht="13.8">
       <c r="A107" s="6">
@@ -8064,10 +8089,10 @@
       <c r="B107" s="7">
         <v>1</v>
       </c>
-      <c r="C107" s="159" t="s">
+      <c r="C107" s="162" t="s">
         <v>144</v>
       </c>
-      <c r="D107" s="171" t="s">
+      <c r="D107" s="150" t="s">
         <v>145</v>
       </c>
       <c r="E107" s="8" t="s">
@@ -8090,8 +8115,8 @@
       <c r="B108" s="7">
         <v>2</v>
       </c>
-      <c r="C108" s="160"/>
-      <c r="D108" s="172"/>
+      <c r="C108" s="163"/>
+      <c r="D108" s="151"/>
       <c r="E108" s="8" t="s">
         <v>147</v>
       </c>
@@ -8112,8 +8137,8 @@
       <c r="B109" s="7">
         <v>3</v>
       </c>
-      <c r="C109" s="160"/>
-      <c r="D109" s="172"/>
+      <c r="C109" s="163"/>
+      <c r="D109" s="151"/>
       <c r="E109" s="8" t="s">
         <v>148</v>
       </c>
@@ -8134,8 +8159,8 @@
       <c r="B110" s="7">
         <v>4</v>
       </c>
-      <c r="C110" s="160"/>
-      <c r="D110" s="172"/>
+      <c r="C110" s="163"/>
+      <c r="D110" s="151"/>
       <c r="E110" s="8" t="s">
         <v>149</v>
       </c>
@@ -8156,8 +8181,8 @@
       <c r="B111" s="7">
         <v>5</v>
       </c>
-      <c r="C111" s="160"/>
-      <c r="D111" s="173"/>
+      <c r="C111" s="163"/>
+      <c r="D111" s="152"/>
       <c r="E111" s="8" t="s">
         <v>150</v>
       </c>
@@ -8178,8 +8203,8 @@
       <c r="B112" s="7">
         <v>6</v>
       </c>
-      <c r="C112" s="160"/>
-      <c r="D112" s="171" t="s">
+      <c r="C112" s="163"/>
+      <c r="D112" s="150" t="s">
         <v>151</v>
       </c>
       <c r="E112" s="8" t="s">
@@ -8202,8 +8227,8 @@
       <c r="B113" s="7">
         <v>7</v>
       </c>
-      <c r="C113" s="160"/>
-      <c r="D113" s="172"/>
+      <c r="C113" s="163"/>
+      <c r="D113" s="151"/>
       <c r="E113" s="8" t="s">
         <v>153</v>
       </c>
@@ -8224,8 +8249,8 @@
       <c r="B114" s="7">
         <v>8</v>
       </c>
-      <c r="C114" s="160"/>
-      <c r="D114" s="172"/>
+      <c r="C114" s="163"/>
+      <c r="D114" s="151"/>
       <c r="E114" s="8" t="s">
         <v>154</v>
       </c>
@@ -8246,8 +8271,8 @@
       <c r="B115" s="7">
         <v>9</v>
       </c>
-      <c r="C115" s="160"/>
-      <c r="D115" s="173"/>
+      <c r="C115" s="163"/>
+      <c r="D115" s="152"/>
       <c r="E115" s="8" t="s">
         <v>155</v>
       </c>
@@ -8268,7 +8293,7 @@
       <c r="B116" s="24">
         <v>10</v>
       </c>
-      <c r="C116" s="161"/>
+      <c r="C116" s="164"/>
       <c r="D116" s="31" t="s">
         <v>156</v>
       </c>
@@ -8292,10 +8317,10 @@
       <c r="B117" s="7">
         <v>1</v>
       </c>
-      <c r="C117" s="150" t="s">
+      <c r="C117" s="165" t="s">
         <v>158</v>
       </c>
-      <c r="D117" s="171" t="s">
+      <c r="D117" s="150" t="s">
         <v>159</v>
       </c>
       <c r="E117" s="8" t="s">
@@ -8318,8 +8343,8 @@
       <c r="B118" s="7">
         <v>2</v>
       </c>
-      <c r="C118" s="151"/>
-      <c r="D118" s="172"/>
+      <c r="C118" s="166"/>
+      <c r="D118" s="151"/>
       <c r="E118" s="8" t="s">
         <v>161</v>
       </c>
@@ -8340,8 +8365,8 @@
       <c r="B119" s="7">
         <v>3</v>
       </c>
-      <c r="C119" s="151"/>
-      <c r="D119" s="172"/>
+      <c r="C119" s="166"/>
+      <c r="D119" s="151"/>
       <c r="E119" s="8" t="s">
         <v>162</v>
       </c>
@@ -8362,8 +8387,8 @@
       <c r="B120" s="7">
         <v>4</v>
       </c>
-      <c r="C120" s="151"/>
-      <c r="D120" s="173"/>
+      <c r="C120" s="166"/>
+      <c r="D120" s="152"/>
       <c r="E120" s="8" t="s">
         <v>163</v>
       </c>
@@ -8384,8 +8409,8 @@
       <c r="B121" s="7">
         <v>5</v>
       </c>
-      <c r="C121" s="151"/>
-      <c r="D121" s="171" t="s">
+      <c r="C121" s="166"/>
+      <c r="D121" s="150" t="s">
         <v>164</v>
       </c>
       <c r="E121" s="8" t="s">
@@ -8408,8 +8433,8 @@
       <c r="B122" s="7">
         <v>6</v>
       </c>
-      <c r="C122" s="151"/>
-      <c r="D122" s="173"/>
+      <c r="C122" s="166"/>
+      <c r="D122" s="152"/>
       <c r="E122" s="8" t="s">
         <v>166</v>
       </c>
@@ -8430,8 +8455,8 @@
       <c r="B123" s="7">
         <v>7</v>
       </c>
-      <c r="C123" s="151"/>
-      <c r="D123" s="171" t="s">
+      <c r="C123" s="166"/>
+      <c r="D123" s="150" t="s">
         <v>167</v>
       </c>
       <c r="E123" s="8" t="s">
@@ -8454,8 +8479,8 @@
       <c r="B124" s="7">
         <v>8</v>
       </c>
-      <c r="C124" s="151"/>
-      <c r="D124" s="172"/>
+      <c r="C124" s="166"/>
+      <c r="D124" s="151"/>
       <c r="E124" s="28" t="s">
         <v>169</v>
       </c>
@@ -8476,8 +8501,8 @@
       <c r="B125" s="7">
         <v>9</v>
       </c>
-      <c r="C125" s="152"/>
-      <c r="D125" s="173"/>
+      <c r="C125" s="167"/>
+      <c r="D125" s="152"/>
       <c r="E125" s="8" t="s">
         <v>170</v>
       </c>
@@ -8492,18 +8517,18 @@
       <c r="J125" s="11"/>
     </row>
     <row r="126" spans="1:10" ht="13.8">
-      <c r="A126" s="192" t="s">
+      <c r="A126" s="174" t="s">
         <v>171</v>
       </c>
-      <c r="B126" s="193"/>
-      <c r="C126" s="193"/>
-      <c r="D126" s="193"/>
-      <c r="E126" s="193"/>
-      <c r="F126" s="193"/>
-      <c r="G126" s="193"/>
-      <c r="H126" s="193"/>
-      <c r="I126" s="193"/>
-      <c r="J126" s="194"/>
+      <c r="B126" s="175"/>
+      <c r="C126" s="175"/>
+      <c r="D126" s="175"/>
+      <c r="E126" s="175"/>
+      <c r="F126" s="175"/>
+      <c r="G126" s="175"/>
+      <c r="H126" s="175"/>
+      <c r="I126" s="175"/>
+      <c r="J126" s="176"/>
     </row>
     <row r="127" spans="1:10" ht="13.8">
       <c r="A127" s="6">
@@ -8512,10 +8537,10 @@
       <c r="B127" s="7">
         <v>1</v>
       </c>
-      <c r="C127" s="153" t="s">
+      <c r="C127" s="168" t="s">
         <v>172</v>
       </c>
-      <c r="D127" s="171" t="s">
+      <c r="D127" s="150" t="s">
         <v>173</v>
       </c>
       <c r="E127" s="32" t="s">
@@ -8536,8 +8561,8 @@
       <c r="B128" s="7">
         <v>2</v>
       </c>
-      <c r="C128" s="154"/>
-      <c r="D128" s="172"/>
+      <c r="C128" s="169"/>
+      <c r="D128" s="151"/>
       <c r="E128" s="32" t="s">
         <v>175</v>
       </c>
@@ -8556,8 +8581,8 @@
       <c r="B129" s="7">
         <v>3</v>
       </c>
-      <c r="C129" s="154"/>
-      <c r="D129" s="172"/>
+      <c r="C129" s="169"/>
+      <c r="D129" s="151"/>
       <c r="E129" s="32" t="s">
         <v>176</v>
       </c>
@@ -8576,8 +8601,8 @@
       <c r="B130" s="7">
         <v>4</v>
       </c>
-      <c r="C130" s="154"/>
-      <c r="D130" s="173"/>
+      <c r="C130" s="169"/>
+      <c r="D130" s="152"/>
       <c r="E130" s="32" t="s">
         <v>177</v>
       </c>
@@ -8596,8 +8621,8 @@
       <c r="B131" s="7">
         <v>5</v>
       </c>
-      <c r="C131" s="154"/>
-      <c r="D131" s="171" t="s">
+      <c r="C131" s="169"/>
+      <c r="D131" s="150" t="s">
         <v>178</v>
       </c>
       <c r="E131" s="32" t="s">
@@ -8618,8 +8643,8 @@
       <c r="B132" s="7">
         <v>6</v>
       </c>
-      <c r="C132" s="155"/>
-      <c r="D132" s="173"/>
+      <c r="C132" s="170"/>
+      <c r="D132" s="152"/>
       <c r="E132" s="32" t="s">
         <v>180</v>
       </c>
@@ -8632,18 +8657,18 @@
       <c r="J132" s="11"/>
     </row>
     <row r="133" spans="1:10" ht="13.8">
-      <c r="A133" s="195" t="s">
+      <c r="A133" s="156" t="s">
         <v>181</v>
       </c>
-      <c r="B133" s="196"/>
-      <c r="C133" s="196"/>
-      <c r="D133" s="196"/>
-      <c r="E133" s="196"/>
-      <c r="F133" s="196"/>
-      <c r="G133" s="196"/>
-      <c r="H133" s="196"/>
-      <c r="I133" s="196"/>
-      <c r="J133" s="197"/>
+      <c r="B133" s="157"/>
+      <c r="C133" s="157"/>
+      <c r="D133" s="157"/>
+      <c r="E133" s="157"/>
+      <c r="F133" s="157"/>
+      <c r="G133" s="157"/>
+      <c r="H133" s="157"/>
+      <c r="I133" s="157"/>
+      <c r="J133" s="158"/>
     </row>
     <row r="134" spans="1:10" ht="13.8">
       <c r="A134" s="6">
@@ -8652,10 +8677,10 @@
       <c r="B134" s="7">
         <v>1</v>
       </c>
-      <c r="C134" s="156" t="s">
+      <c r="C134" s="159" t="s">
         <v>182</v>
       </c>
-      <c r="D134" s="171" t="s">
+      <c r="D134" s="150" t="s">
         <v>183</v>
       </c>
       <c r="E134" s="8" t="s">
@@ -8678,8 +8703,8 @@
       <c r="B135" s="7">
         <v>2</v>
       </c>
-      <c r="C135" s="157"/>
-      <c r="D135" s="172"/>
+      <c r="C135" s="160"/>
+      <c r="D135" s="151"/>
       <c r="E135" s="8" t="s">
         <v>185</v>
       </c>
@@ -8700,8 +8725,8 @@
       <c r="B136" s="7">
         <v>3</v>
       </c>
-      <c r="C136" s="157"/>
-      <c r="D136" s="173"/>
+      <c r="C136" s="160"/>
+      <c r="D136" s="152"/>
       <c r="E136" s="8" t="s">
         <v>186</v>
       </c>
@@ -8722,8 +8747,8 @@
       <c r="B137" s="7">
         <v>4</v>
       </c>
-      <c r="C137" s="157"/>
-      <c r="D137" s="171" t="s">
+      <c r="C137" s="160"/>
+      <c r="D137" s="150" t="s">
         <v>187</v>
       </c>
       <c r="E137" s="8" t="s">
@@ -8746,8 +8771,8 @@
       <c r="B138" s="7">
         <v>5</v>
       </c>
-      <c r="C138" s="157"/>
-      <c r="D138" s="172"/>
+      <c r="C138" s="160"/>
+      <c r="D138" s="151"/>
       <c r="E138" s="8" t="s">
         <v>189</v>
       </c>
@@ -8768,8 +8793,8 @@
       <c r="B139" s="7">
         <v>6</v>
       </c>
-      <c r="C139" s="157"/>
-      <c r="D139" s="172"/>
+      <c r="C139" s="160"/>
+      <c r="D139" s="151"/>
       <c r="E139" s="8" t="s">
         <v>190</v>
       </c>
@@ -8790,8 +8815,8 @@
       <c r="B140" s="7">
         <v>7</v>
       </c>
-      <c r="C140" s="157"/>
-      <c r="D140" s="172"/>
+      <c r="C140" s="160"/>
+      <c r="D140" s="151"/>
       <c r="E140" s="8" t="s">
         <v>191</v>
       </c>
@@ -8812,8 +8837,8 @@
       <c r="B141" s="7">
         <v>8</v>
       </c>
-      <c r="C141" s="157"/>
-      <c r="D141" s="172"/>
+      <c r="C141" s="160"/>
+      <c r="D141" s="151"/>
       <c r="E141" s="8" t="s">
         <v>192</v>
       </c>
@@ -8834,8 +8859,8 @@
       <c r="B142" s="7">
         <v>9</v>
       </c>
-      <c r="C142" s="157"/>
-      <c r="D142" s="172"/>
+      <c r="C142" s="160"/>
+      <c r="D142" s="151"/>
       <c r="E142" s="8" t="s">
         <v>193</v>
       </c>
@@ -8856,8 +8881,8 @@
       <c r="B143" s="7">
         <v>10</v>
       </c>
-      <c r="C143" s="157"/>
-      <c r="D143" s="173"/>
+      <c r="C143" s="160"/>
+      <c r="D143" s="152"/>
       <c r="E143" s="8" t="s">
         <v>194</v>
       </c>
@@ -8878,8 +8903,8 @@
       <c r="B144" s="7">
         <v>11</v>
       </c>
-      <c r="C144" s="157"/>
-      <c r="D144" s="171" t="s">
+      <c r="C144" s="160"/>
+      <c r="D144" s="150" t="s">
         <v>195</v>
       </c>
       <c r="E144" s="8" t="s">
@@ -8902,8 +8927,8 @@
       <c r="B145" s="7">
         <v>12</v>
       </c>
-      <c r="C145" s="157"/>
-      <c r="D145" s="172"/>
+      <c r="C145" s="160"/>
+      <c r="D145" s="151"/>
       <c r="E145" s="8" t="s">
         <v>197</v>
       </c>
@@ -8924,8 +8949,8 @@
       <c r="B146" s="7">
         <v>13</v>
       </c>
-      <c r="C146" s="157"/>
-      <c r="D146" s="172"/>
+      <c r="C146" s="160"/>
+      <c r="D146" s="151"/>
       <c r="E146" s="8" t="s">
         <v>198</v>
       </c>
@@ -8946,8 +8971,8 @@
       <c r="B147" s="7">
         <v>14</v>
       </c>
-      <c r="C147" s="157"/>
-      <c r="D147" s="172"/>
+      <c r="C147" s="160"/>
+      <c r="D147" s="151"/>
       <c r="E147" s="8" t="s">
         <v>199</v>
       </c>
@@ -8968,8 +8993,8 @@
       <c r="B148" s="7">
         <v>15</v>
       </c>
-      <c r="C148" s="157"/>
-      <c r="D148" s="172"/>
+      <c r="C148" s="160"/>
+      <c r="D148" s="151"/>
       <c r="E148" s="8" t="s">
         <v>200</v>
       </c>
@@ -8990,8 +9015,8 @@
       <c r="B149" s="7">
         <v>16</v>
       </c>
-      <c r="C149" s="157"/>
-      <c r="D149" s="172"/>
+      <c r="C149" s="160"/>
+      <c r="D149" s="151"/>
       <c r="E149" s="8" t="s">
         <v>201</v>
       </c>
@@ -9012,8 +9037,8 @@
       <c r="B150" s="7">
         <v>17</v>
       </c>
-      <c r="C150" s="157"/>
-      <c r="D150" s="173"/>
+      <c r="C150" s="160"/>
+      <c r="D150" s="152"/>
       <c r="E150" s="8" t="s">
         <v>202</v>
       </c>
@@ -9034,8 +9059,8 @@
       <c r="B151" s="7">
         <v>18</v>
       </c>
-      <c r="C151" s="157"/>
-      <c r="D151" s="171" t="s">
+      <c r="C151" s="160"/>
+      <c r="D151" s="150" t="s">
         <v>203</v>
       </c>
       <c r="E151" s="8" t="s">
@@ -9058,8 +9083,8 @@
       <c r="B152" s="7">
         <v>19</v>
       </c>
-      <c r="C152" s="157"/>
-      <c r="D152" s="172"/>
+      <c r="C152" s="160"/>
+      <c r="D152" s="151"/>
       <c r="E152" s="8" t="s">
         <v>205</v>
       </c>
@@ -9080,8 +9105,8 @@
       <c r="B153" s="7">
         <v>20</v>
       </c>
-      <c r="C153" s="157"/>
-      <c r="D153" s="172"/>
+      <c r="C153" s="160"/>
+      <c r="D153" s="151"/>
       <c r="E153" s="8" t="s">
         <v>206</v>
       </c>
@@ -9102,8 +9127,8 @@
       <c r="B154" s="7">
         <v>21</v>
       </c>
-      <c r="C154" s="157"/>
-      <c r="D154" s="172"/>
+      <c r="C154" s="160"/>
+      <c r="D154" s="151"/>
       <c r="E154" s="8" t="s">
         <v>207</v>
       </c>
@@ -9124,8 +9149,8 @@
       <c r="B155" s="7">
         <v>22</v>
       </c>
-      <c r="C155" s="157"/>
-      <c r="D155" s="172"/>
+      <c r="C155" s="160"/>
+      <c r="D155" s="151"/>
       <c r="E155" s="8" t="s">
         <v>208</v>
       </c>
@@ -9146,8 +9171,8 @@
       <c r="B156" s="7">
         <v>23</v>
       </c>
-      <c r="C156" s="157"/>
-      <c r="D156" s="173"/>
+      <c r="C156" s="160"/>
+      <c r="D156" s="152"/>
       <c r="E156" s="8" t="s">
         <v>209</v>
       </c>
@@ -9168,8 +9193,8 @@
       <c r="B157" s="7">
         <v>24</v>
       </c>
-      <c r="C157" s="157"/>
-      <c r="D157" s="171" t="s">
+      <c r="C157" s="160"/>
+      <c r="D157" s="150" t="s">
         <v>210</v>
       </c>
       <c r="E157" s="8" t="s">
@@ -9192,8 +9217,8 @@
       <c r="B158" s="7">
         <v>25</v>
       </c>
-      <c r="C158" s="157"/>
-      <c r="D158" s="172"/>
+      <c r="C158" s="160"/>
+      <c r="D158" s="151"/>
       <c r="E158" s="8" t="s">
         <v>212</v>
       </c>
@@ -9214,8 +9239,8 @@
       <c r="B159" s="7">
         <v>26</v>
       </c>
-      <c r="C159" s="157"/>
-      <c r="D159" s="173"/>
+      <c r="C159" s="160"/>
+      <c r="D159" s="152"/>
       <c r="E159" s="8" t="s">
         <v>213</v>
       </c>
@@ -9236,8 +9261,8 @@
       <c r="B160" s="7">
         <v>27</v>
       </c>
-      <c r="C160" s="157"/>
-      <c r="D160" s="171" t="s">
+      <c r="C160" s="160"/>
+      <c r="D160" s="150" t="s">
         <v>214</v>
       </c>
       <c r="E160" s="8" t="s">
@@ -9260,8 +9285,8 @@
       <c r="B161" s="7">
         <v>28</v>
       </c>
-      <c r="C161" s="157"/>
-      <c r="D161" s="172"/>
+      <c r="C161" s="160"/>
+      <c r="D161" s="151"/>
       <c r="E161" s="8" t="s">
         <v>216</v>
       </c>
@@ -9282,8 +9307,8 @@
       <c r="B162" s="7">
         <v>29</v>
       </c>
-      <c r="C162" s="157"/>
-      <c r="D162" s="172"/>
+      <c r="C162" s="160"/>
+      <c r="D162" s="151"/>
       <c r="E162" s="8" t="s">
         <v>217</v>
       </c>
@@ -9304,8 +9329,8 @@
       <c r="B163" s="7">
         <v>30</v>
       </c>
-      <c r="C163" s="157"/>
-      <c r="D163" s="172"/>
+      <c r="C163" s="160"/>
+      <c r="D163" s="151"/>
       <c r="E163" s="8" t="s">
         <v>218</v>
       </c>
@@ -9326,8 +9351,8 @@
       <c r="B164" s="7">
         <v>31</v>
       </c>
-      <c r="C164" s="157"/>
-      <c r="D164" s="172"/>
+      <c r="C164" s="160"/>
+      <c r="D164" s="151"/>
       <c r="E164" s="8" t="s">
         <v>219</v>
       </c>
@@ -9348,8 +9373,8 @@
       <c r="B165" s="7">
         <v>32</v>
       </c>
-      <c r="C165" s="157"/>
-      <c r="D165" s="173"/>
+      <c r="C165" s="160"/>
+      <c r="D165" s="152"/>
       <c r="E165" s="8" t="s">
         <v>220</v>
       </c>
@@ -9370,8 +9395,8 @@
       <c r="B166" s="7">
         <v>33</v>
       </c>
-      <c r="C166" s="157"/>
-      <c r="D166" s="171" t="s">
+      <c r="C166" s="160"/>
+      <c r="D166" s="150" t="s">
         <v>221</v>
       </c>
       <c r="E166" s="8" t="s">
@@ -9394,8 +9419,8 @@
       <c r="B167" s="7">
         <v>34</v>
       </c>
-      <c r="C167" s="157"/>
-      <c r="D167" s="172"/>
+      <c r="C167" s="160"/>
+      <c r="D167" s="151"/>
       <c r="E167" s="8" t="s">
         <v>223</v>
       </c>
@@ -9414,8 +9439,8 @@
       <c r="B168" s="7">
         <v>35</v>
       </c>
-      <c r="C168" s="157"/>
-      <c r="D168" s="172"/>
+      <c r="C168" s="160"/>
+      <c r="D168" s="151"/>
       <c r="E168" s="8" t="s">
         <v>224</v>
       </c>
@@ -9436,8 +9461,8 @@
       <c r="B169" s="7">
         <v>36</v>
       </c>
-      <c r="C169" s="157"/>
-      <c r="D169" s="172"/>
+      <c r="C169" s="160"/>
+      <c r="D169" s="151"/>
       <c r="E169" s="8" t="s">
         <v>225</v>
       </c>
@@ -9458,8 +9483,8 @@
       <c r="B170" s="7">
         <v>37</v>
       </c>
-      <c r="C170" s="157"/>
-      <c r="D170" s="172"/>
+      <c r="C170" s="160"/>
+      <c r="D170" s="151"/>
       <c r="E170" s="8" t="s">
         <v>226</v>
       </c>
@@ -9480,8 +9505,8 @@
       <c r="B171" s="7">
         <v>38</v>
       </c>
-      <c r="C171" s="157"/>
-      <c r="D171" s="172"/>
+      <c r="C171" s="160"/>
+      <c r="D171" s="151"/>
       <c r="E171" s="8" t="s">
         <v>227</v>
       </c>
@@ -9502,8 +9527,8 @@
       <c r="B172" s="7">
         <v>39</v>
       </c>
-      <c r="C172" s="157"/>
-      <c r="D172" s="173"/>
+      <c r="C172" s="160"/>
+      <c r="D172" s="152"/>
       <c r="E172" s="8" t="s">
         <v>228</v>
       </c>
@@ -9524,8 +9549,8 @@
       <c r="B173" s="7">
         <v>40</v>
       </c>
-      <c r="C173" s="157"/>
-      <c r="D173" s="171" t="s">
+      <c r="C173" s="160"/>
+      <c r="D173" s="150" t="s">
         <v>48</v>
       </c>
       <c r="E173" s="11" t="s">
@@ -9548,8 +9573,8 @@
       <c r="B174" s="7">
         <v>41</v>
       </c>
-      <c r="C174" s="157"/>
-      <c r="D174" s="172"/>
+      <c r="C174" s="160"/>
+      <c r="D174" s="151"/>
       <c r="E174" s="8" t="s">
         <v>230</v>
       </c>
@@ -9570,8 +9595,8 @@
       <c r="B175" s="7">
         <v>42</v>
       </c>
-      <c r="C175" s="157"/>
-      <c r="D175" s="172"/>
+      <c r="C175" s="160"/>
+      <c r="D175" s="151"/>
       <c r="E175" s="8" t="s">
         <v>231</v>
       </c>
@@ -9592,8 +9617,8 @@
       <c r="B176" s="24">
         <v>43</v>
       </c>
-      <c r="C176" s="158"/>
-      <c r="D176" s="173"/>
+      <c r="C176" s="161"/>
+      <c r="D176" s="152"/>
       <c r="E176" s="17" t="s">
         <v>232</v>
       </c>
@@ -9614,10 +9639,10 @@
       <c r="B177" s="7">
         <v>1</v>
       </c>
-      <c r="C177" s="159" t="s">
+      <c r="C177" s="162" t="s">
         <v>233</v>
       </c>
-      <c r="D177" s="171" t="s">
+      <c r="D177" s="150" t="s">
         <v>234</v>
       </c>
       <c r="E177" s="8" t="s">
@@ -9640,8 +9665,8 @@
       <c r="B178" s="7">
         <v>2</v>
       </c>
-      <c r="C178" s="160"/>
-      <c r="D178" s="173"/>
+      <c r="C178" s="163"/>
+      <c r="D178" s="152"/>
       <c r="E178" s="8" t="s">
         <v>236</v>
       </c>
@@ -9662,8 +9687,8 @@
       <c r="B179" s="7">
         <v>3</v>
       </c>
-      <c r="C179" s="160"/>
-      <c r="D179" s="171" t="s">
+      <c r="C179" s="163"/>
+      <c r="D179" s="150" t="s">
         <v>237</v>
       </c>
       <c r="E179" s="8" t="s">
@@ -9686,8 +9711,8 @@
       <c r="B180" s="7">
         <v>4</v>
       </c>
-      <c r="C180" s="160"/>
-      <c r="D180" s="172"/>
+      <c r="C180" s="163"/>
+      <c r="D180" s="151"/>
       <c r="E180" s="8" t="s">
         <v>239</v>
       </c>
@@ -9708,8 +9733,8 @@
       <c r="B181" s="7">
         <v>5</v>
       </c>
-      <c r="C181" s="160"/>
-      <c r="D181" s="172"/>
+      <c r="C181" s="163"/>
+      <c r="D181" s="151"/>
       <c r="E181" s="8" t="s">
         <v>240</v>
       </c>
@@ -9730,8 +9755,8 @@
       <c r="B182" s="7">
         <v>6</v>
       </c>
-      <c r="C182" s="160"/>
-      <c r="D182" s="172"/>
+      <c r="C182" s="163"/>
+      <c r="D182" s="151"/>
       <c r="E182" s="8" t="s">
         <v>241</v>
       </c>
@@ -9752,8 +9777,8 @@
       <c r="B183" s="7">
         <v>7</v>
       </c>
-      <c r="C183" s="160"/>
-      <c r="D183" s="172"/>
+      <c r="C183" s="163"/>
+      <c r="D183" s="151"/>
       <c r="E183" s="8" t="s">
         <v>242</v>
       </c>
@@ -9774,8 +9799,8 @@
       <c r="B184" s="7">
         <v>8</v>
       </c>
-      <c r="C184" s="160"/>
-      <c r="D184" s="173"/>
+      <c r="C184" s="163"/>
+      <c r="D184" s="152"/>
       <c r="E184" s="8" t="s">
         <v>243</v>
       </c>
@@ -9796,8 +9821,8 @@
       <c r="B185" s="7">
         <v>9</v>
       </c>
-      <c r="C185" s="160"/>
-      <c r="D185" s="171" t="s">
+      <c r="C185" s="163"/>
+      <c r="D185" s="150" t="s">
         <v>244</v>
       </c>
       <c r="E185" s="8" t="s">
@@ -9820,8 +9845,8 @@
       <c r="B186" s="7">
         <v>10</v>
       </c>
-      <c r="C186" s="160"/>
-      <c r="D186" s="173"/>
+      <c r="C186" s="163"/>
+      <c r="D186" s="152"/>
       <c r="E186" s="8" t="s">
         <v>246</v>
       </c>
@@ -9842,8 +9867,8 @@
       <c r="B187" s="7">
         <v>11</v>
       </c>
-      <c r="C187" s="160"/>
-      <c r="D187" s="171" t="s">
+      <c r="C187" s="163"/>
+      <c r="D187" s="150" t="s">
         <v>247</v>
       </c>
       <c r="E187" s="8" t="s">
@@ -9866,8 +9891,8 @@
       <c r="B188" s="7">
         <v>12</v>
       </c>
-      <c r="C188" s="160"/>
-      <c r="D188" s="172"/>
+      <c r="C188" s="163"/>
+      <c r="D188" s="151"/>
       <c r="E188" s="8" t="s">
         <v>249</v>
       </c>
@@ -9888,8 +9913,8 @@
       <c r="B189" s="7">
         <v>13</v>
       </c>
-      <c r="C189" s="160"/>
-      <c r="D189" s="172"/>
+      <c r="C189" s="163"/>
+      <c r="D189" s="151"/>
       <c r="E189" s="11" t="s">
         <v>250</v>
       </c>
@@ -9910,8 +9935,8 @@
       <c r="B190" s="7">
         <v>14</v>
       </c>
-      <c r="C190" s="160"/>
-      <c r="D190" s="173"/>
+      <c r="C190" s="163"/>
+      <c r="D190" s="152"/>
       <c r="E190" s="8" t="s">
         <v>251</v>
       </c>
@@ -9932,8 +9957,8 @@
       <c r="B191" s="7">
         <v>15</v>
       </c>
-      <c r="C191" s="160"/>
-      <c r="D191" s="171" t="s">
+      <c r="C191" s="163"/>
+      <c r="D191" s="150" t="s">
         <v>252</v>
       </c>
       <c r="E191" s="8" t="s">
@@ -9956,8 +9981,8 @@
       <c r="B192" s="7">
         <v>16</v>
       </c>
-      <c r="C192" s="160"/>
-      <c r="D192" s="172"/>
+      <c r="C192" s="163"/>
+      <c r="D192" s="151"/>
       <c r="E192" s="8" t="s">
         <v>254</v>
       </c>
@@ -9978,8 +10003,8 @@
       <c r="B193" s="7">
         <v>17</v>
       </c>
-      <c r="C193" s="160"/>
-      <c r="D193" s="172"/>
+      <c r="C193" s="163"/>
+      <c r="D193" s="151"/>
       <c r="E193" s="8" t="s">
         <v>255</v>
       </c>
@@ -10000,8 +10025,8 @@
       <c r="B194" s="7">
         <v>18</v>
       </c>
-      <c r="C194" s="160"/>
-      <c r="D194" s="172"/>
+      <c r="C194" s="163"/>
+      <c r="D194" s="151"/>
       <c r="E194" s="8" t="s">
         <v>256</v>
       </c>
@@ -10022,8 +10047,8 @@
       <c r="B195" s="7">
         <v>19</v>
       </c>
-      <c r="C195" s="160"/>
-      <c r="D195" s="172"/>
+      <c r="C195" s="163"/>
+      <c r="D195" s="151"/>
       <c r="E195" s="8" t="s">
         <v>257</v>
       </c>
@@ -10044,8 +10069,8 @@
       <c r="B196" s="7">
         <v>20</v>
       </c>
-      <c r="C196" s="160"/>
-      <c r="D196" s="172"/>
+      <c r="C196" s="163"/>
+      <c r="D196" s="151"/>
       <c r="E196" s="8" t="s">
         <v>258</v>
       </c>
@@ -10066,8 +10091,8 @@
       <c r="B197" s="7">
         <v>21</v>
       </c>
-      <c r="C197" s="160"/>
-      <c r="D197" s="172"/>
+      <c r="C197" s="163"/>
+      <c r="D197" s="151"/>
       <c r="E197" s="8" t="s">
         <v>259</v>
       </c>
@@ -10088,8 +10113,8 @@
       <c r="B198" s="7">
         <v>22</v>
       </c>
-      <c r="C198" s="160"/>
-      <c r="D198" s="173"/>
+      <c r="C198" s="163"/>
+      <c r="D198" s="152"/>
       <c r="E198" s="8" t="s">
         <v>260</v>
       </c>
@@ -10110,8 +10135,8 @@
       <c r="B199" s="7">
         <v>23</v>
       </c>
-      <c r="C199" s="160"/>
-      <c r="D199" s="171" t="s">
+      <c r="C199" s="163"/>
+      <c r="D199" s="150" t="s">
         <v>261</v>
       </c>
       <c r="E199" s="8" t="s">
@@ -10134,8 +10159,8 @@
       <c r="B200" s="7">
         <v>24</v>
       </c>
-      <c r="C200" s="160"/>
-      <c r="D200" s="172"/>
+      <c r="C200" s="163"/>
+      <c r="D200" s="151"/>
       <c r="E200" s="8" t="s">
         <v>263</v>
       </c>
@@ -10156,8 +10181,8 @@
       <c r="B201" s="7">
         <v>25</v>
       </c>
-      <c r="C201" s="160"/>
-      <c r="D201" s="172"/>
+      <c r="C201" s="163"/>
+      <c r="D201" s="151"/>
       <c r="E201" s="8" t="s">
         <v>264</v>
       </c>
@@ -10178,8 +10203,8 @@
       <c r="B202" s="7">
         <v>26</v>
       </c>
-      <c r="C202" s="160"/>
-      <c r="D202" s="173"/>
+      <c r="C202" s="163"/>
+      <c r="D202" s="152"/>
       <c r="E202" s="8" t="s">
         <v>265</v>
       </c>
@@ -10200,8 +10225,8 @@
       <c r="B203" s="7">
         <v>27</v>
       </c>
-      <c r="C203" s="160"/>
-      <c r="D203" s="171" t="s">
+      <c r="C203" s="163"/>
+      <c r="D203" s="150" t="s">
         <v>266</v>
       </c>
       <c r="E203" s="8" t="s">
@@ -10224,8 +10249,8 @@
       <c r="B204" s="24">
         <v>28</v>
       </c>
-      <c r="C204" s="161"/>
-      <c r="D204" s="173"/>
+      <c r="C204" s="164"/>
+      <c r="D204" s="152"/>
       <c r="E204" s="17" t="s">
         <v>268</v>
       </c>
@@ -10246,10 +10271,10 @@
       <c r="B205" s="7">
         <v>1</v>
       </c>
-      <c r="C205" s="150" t="s">
+      <c r="C205" s="165" t="s">
         <v>269</v>
       </c>
-      <c r="D205" s="171" t="s">
+      <c r="D205" s="150" t="s">
         <v>270</v>
       </c>
       <c r="E205" s="8" t="s">
@@ -10272,8 +10297,8 @@
       <c r="B206" s="7">
         <v>2</v>
       </c>
-      <c r="C206" s="151"/>
-      <c r="D206" s="172"/>
+      <c r="C206" s="166"/>
+      <c r="D206" s="151"/>
       <c r="E206" s="8" t="s">
         <v>272</v>
       </c>
@@ -10294,8 +10319,8 @@
       <c r="B207" s="7">
         <v>3</v>
       </c>
-      <c r="C207" s="151"/>
-      <c r="D207" s="172"/>
+      <c r="C207" s="166"/>
+      <c r="D207" s="151"/>
       <c r="E207" s="8" t="s">
         <v>273</v>
       </c>
@@ -10316,8 +10341,8 @@
       <c r="B208" s="7">
         <v>4</v>
       </c>
-      <c r="C208" s="151"/>
-      <c r="D208" s="172"/>
+      <c r="C208" s="166"/>
+      <c r="D208" s="151"/>
       <c r="E208" s="8" t="s">
         <v>274</v>
       </c>
@@ -10338,8 +10363,8 @@
       <c r="B209" s="7">
         <v>5</v>
       </c>
-      <c r="C209" s="151"/>
-      <c r="D209" s="173"/>
+      <c r="C209" s="166"/>
+      <c r="D209" s="152"/>
       <c r="E209" s="8" t="s">
         <v>275</v>
       </c>
@@ -10360,8 +10385,8 @@
       <c r="B210" s="7">
         <v>6</v>
       </c>
-      <c r="C210" s="151"/>
-      <c r="D210" s="171" t="s">
+      <c r="C210" s="166"/>
+      <c r="D210" s="150" t="s">
         <v>276</v>
       </c>
       <c r="E210" s="8" t="s">
@@ -10384,8 +10409,8 @@
       <c r="B211" s="7">
         <v>7</v>
       </c>
-      <c r="C211" s="151"/>
-      <c r="D211" s="173"/>
+      <c r="C211" s="166"/>
+      <c r="D211" s="152"/>
       <c r="E211" s="8" t="s">
         <v>278</v>
       </c>
@@ -10406,8 +10431,8 @@
       <c r="B212" s="7">
         <v>8</v>
       </c>
-      <c r="C212" s="151"/>
-      <c r="D212" s="171" t="s">
+      <c r="C212" s="166"/>
+      <c r="D212" s="150" t="s">
         <v>279</v>
       </c>
       <c r="E212" s="8" t="s">
@@ -10430,8 +10455,8 @@
       <c r="B213" s="7">
         <v>9</v>
       </c>
-      <c r="C213" s="151"/>
-      <c r="D213" s="172"/>
+      <c r="C213" s="166"/>
+      <c r="D213" s="151"/>
       <c r="E213" s="8" t="s">
         <v>281</v>
       </c>
@@ -10452,8 +10477,8 @@
       <c r="B214" s="7">
         <v>10</v>
       </c>
-      <c r="C214" s="152"/>
-      <c r="D214" s="173"/>
+      <c r="C214" s="167"/>
+      <c r="D214" s="152"/>
       <c r="E214" s="8" t="s">
         <v>282</v>
       </c>
@@ -10468,18 +10493,18 @@
       <c r="J214" s="11"/>
     </row>
     <row r="215" spans="1:10" ht="13.8">
-      <c r="A215" s="180" t="s">
+      <c r="A215" s="186" t="s">
         <v>283</v>
       </c>
-      <c r="B215" s="181"/>
-      <c r="C215" s="181"/>
-      <c r="D215" s="181"/>
-      <c r="E215" s="181"/>
-      <c r="F215" s="181"/>
-      <c r="G215" s="181"/>
-      <c r="H215" s="181"/>
-      <c r="I215" s="181"/>
-      <c r="J215" s="182"/>
+      <c r="B215" s="187"/>
+      <c r="C215" s="187"/>
+      <c r="D215" s="187"/>
+      <c r="E215" s="187"/>
+      <c r="F215" s="187"/>
+      <c r="G215" s="187"/>
+      <c r="H215" s="187"/>
+      <c r="I215" s="187"/>
+      <c r="J215" s="188"/>
     </row>
     <row r="216" spans="1:10" ht="13.8">
       <c r="A216" s="6">
@@ -10488,10 +10513,10 @@
       <c r="B216" s="7">
         <v>1</v>
       </c>
-      <c r="C216" s="153" t="s">
+      <c r="C216" s="168" t="s">
         <v>284</v>
       </c>
-      <c r="D216" s="171" t="s">
+      <c r="D216" s="150" t="s">
         <v>285</v>
       </c>
       <c r="E216" s="8" t="s">
@@ -10514,8 +10539,8 @@
       <c r="B217" s="7">
         <v>2</v>
       </c>
-      <c r="C217" s="154"/>
-      <c r="D217" s="172"/>
+      <c r="C217" s="169"/>
+      <c r="D217" s="151"/>
       <c r="E217" s="8" t="s">
         <v>287</v>
       </c>
@@ -10536,8 +10561,8 @@
       <c r="B218" s="7">
         <v>3</v>
       </c>
-      <c r="C218" s="154"/>
-      <c r="D218" s="172"/>
+      <c r="C218" s="169"/>
+      <c r="D218" s="151"/>
       <c r="E218" s="8" t="s">
         <v>288</v>
       </c>
@@ -10558,8 +10583,8 @@
       <c r="B219" s="7">
         <v>4</v>
       </c>
-      <c r="C219" s="154"/>
-      <c r="D219" s="172"/>
+      <c r="C219" s="169"/>
+      <c r="D219" s="151"/>
       <c r="E219" s="8" t="s">
         <v>289</v>
       </c>
@@ -10580,8 +10605,8 @@
       <c r="B220" s="7">
         <v>5</v>
       </c>
-      <c r="C220" s="154"/>
-      <c r="D220" s="172"/>
+      <c r="C220" s="169"/>
+      <c r="D220" s="151"/>
       <c r="E220" s="8" t="s">
         <v>290</v>
       </c>
@@ -10602,8 +10627,8 @@
       <c r="B221" s="7">
         <v>6</v>
       </c>
-      <c r="C221" s="154"/>
-      <c r="D221" s="172"/>
+      <c r="C221" s="169"/>
+      <c r="D221" s="151"/>
       <c r="E221" s="8" t="s">
         <v>291</v>
       </c>
@@ -10624,8 +10649,8 @@
       <c r="B222" s="7">
         <v>7</v>
       </c>
-      <c r="C222" s="154"/>
-      <c r="D222" s="172"/>
+      <c r="C222" s="169"/>
+      <c r="D222" s="151"/>
       <c r="E222" s="8" t="s">
         <v>292</v>
       </c>
@@ -10646,8 +10671,8 @@
       <c r="B223" s="7">
         <v>8</v>
       </c>
-      <c r="C223" s="154"/>
-      <c r="D223" s="172"/>
+      <c r="C223" s="169"/>
+      <c r="D223" s="151"/>
       <c r="E223" s="8" t="s">
         <v>293</v>
       </c>
@@ -10668,8 +10693,8 @@
       <c r="B224" s="7">
         <v>9</v>
       </c>
-      <c r="C224" s="154"/>
-      <c r="D224" s="172"/>
+      <c r="C224" s="169"/>
+      <c r="D224" s="151"/>
       <c r="E224" s="8" t="s">
         <v>294</v>
       </c>
@@ -10690,8 +10715,8 @@
       <c r="B225" s="7">
         <v>10</v>
       </c>
-      <c r="C225" s="154"/>
-      <c r="D225" s="173"/>
+      <c r="C225" s="169"/>
+      <c r="D225" s="152"/>
       <c r="E225" s="8" t="s">
         <v>295</v>
       </c>
@@ -10712,8 +10737,8 @@
       <c r="B226" s="7">
         <v>11</v>
       </c>
-      <c r="C226" s="154"/>
-      <c r="D226" s="171" t="s">
+      <c r="C226" s="169"/>
+      <c r="D226" s="150" t="s">
         <v>296</v>
       </c>
       <c r="E226" s="8" t="s">
@@ -10736,8 +10761,8 @@
       <c r="B227" s="7">
         <v>12</v>
       </c>
-      <c r="C227" s="154"/>
-      <c r="D227" s="172"/>
+      <c r="C227" s="169"/>
+      <c r="D227" s="151"/>
       <c r="E227" s="8" t="s">
         <v>298</v>
       </c>
@@ -10758,8 +10783,8 @@
       <c r="B228" s="7">
         <v>13</v>
       </c>
-      <c r="C228" s="154"/>
-      <c r="D228" s="172"/>
+      <c r="C228" s="169"/>
+      <c r="D228" s="151"/>
       <c r="E228" s="8" t="s">
         <v>299</v>
       </c>
@@ -10780,8 +10805,8 @@
       <c r="B229" s="7">
         <v>14</v>
       </c>
-      <c r="C229" s="154"/>
-      <c r="D229" s="172"/>
+      <c r="C229" s="169"/>
+      <c r="D229" s="151"/>
       <c r="E229" s="8" t="s">
         <v>300</v>
       </c>
@@ -10802,8 +10827,8 @@
       <c r="B230" s="7">
         <v>15</v>
       </c>
-      <c r="C230" s="154"/>
-      <c r="D230" s="172"/>
+      <c r="C230" s="169"/>
+      <c r="D230" s="151"/>
       <c r="E230" s="8" t="s">
         <v>301</v>
       </c>
@@ -10824,8 +10849,8 @@
       <c r="B231" s="7">
         <v>16</v>
       </c>
-      <c r="C231" s="154"/>
-      <c r="D231" s="172"/>
+      <c r="C231" s="169"/>
+      <c r="D231" s="151"/>
       <c r="E231" s="8" t="s">
         <v>302</v>
       </c>
@@ -10846,8 +10871,8 @@
       <c r="B232" s="7">
         <v>17</v>
       </c>
-      <c r="C232" s="154"/>
-      <c r="D232" s="172"/>
+      <c r="C232" s="169"/>
+      <c r="D232" s="151"/>
       <c r="E232" s="8" t="s">
         <v>303</v>
       </c>
@@ -10868,8 +10893,8 @@
       <c r="B233" s="7">
         <v>18</v>
       </c>
-      <c r="C233" s="154"/>
-      <c r="D233" s="173"/>
+      <c r="C233" s="169"/>
+      <c r="D233" s="152"/>
       <c r="E233" s="8" t="s">
         <v>304</v>
       </c>
@@ -10890,8 +10915,8 @@
       <c r="B234" s="7">
         <v>19</v>
       </c>
-      <c r="C234" s="154"/>
-      <c r="D234" s="171" t="s">
+      <c r="C234" s="169"/>
+      <c r="D234" s="150" t="s">
         <v>305</v>
       </c>
       <c r="E234" s="8" t="s">
@@ -10914,8 +10939,8 @@
       <c r="B235" s="7">
         <v>20</v>
       </c>
-      <c r="C235" s="154"/>
-      <c r="D235" s="172"/>
+      <c r="C235" s="169"/>
+      <c r="D235" s="151"/>
       <c r="E235" s="8" t="s">
         <v>307</v>
       </c>
@@ -10936,8 +10961,8 @@
       <c r="B236" s="7">
         <v>21</v>
       </c>
-      <c r="C236" s="154"/>
-      <c r="D236" s="172"/>
+      <c r="C236" s="169"/>
+      <c r="D236" s="151"/>
       <c r="E236" s="8" t="s">
         <v>308</v>
       </c>
@@ -10958,8 +10983,8 @@
       <c r="B237" s="7">
         <v>22</v>
       </c>
-      <c r="C237" s="154"/>
-      <c r="D237" s="172"/>
+      <c r="C237" s="169"/>
+      <c r="D237" s="151"/>
       <c r="E237" s="8" t="s">
         <v>309</v>
       </c>
@@ -10980,8 +11005,8 @@
       <c r="B238" s="7">
         <v>23</v>
       </c>
-      <c r="C238" s="154"/>
-      <c r="D238" s="172"/>
+      <c r="C238" s="169"/>
+      <c r="D238" s="151"/>
       <c r="E238" s="8" t="s">
         <v>310</v>
       </c>
@@ -11002,8 +11027,8 @@
       <c r="B239" s="7">
         <v>24</v>
       </c>
-      <c r="C239" s="154"/>
-      <c r="D239" s="172"/>
+      <c r="C239" s="169"/>
+      <c r="D239" s="151"/>
       <c r="E239" s="8" t="s">
         <v>311</v>
       </c>
@@ -11024,8 +11049,8 @@
       <c r="B240" s="7">
         <v>25</v>
       </c>
-      <c r="C240" s="154"/>
-      <c r="D240" s="173"/>
+      <c r="C240" s="169"/>
+      <c r="D240" s="152"/>
       <c r="E240" s="8" t="s">
         <v>312</v>
       </c>
@@ -11046,8 +11071,8 @@
       <c r="B241" s="7">
         <v>26</v>
       </c>
-      <c r="C241" s="154"/>
-      <c r="D241" s="171" t="s">
+      <c r="C241" s="169"/>
+      <c r="D241" s="150" t="s">
         <v>313</v>
       </c>
       <c r="E241" s="8" t="s">
@@ -11070,8 +11095,8 @@
       <c r="B242" s="7">
         <v>27</v>
       </c>
-      <c r="C242" s="154"/>
-      <c r="D242" s="172"/>
+      <c r="C242" s="169"/>
+      <c r="D242" s="151"/>
       <c r="E242" s="8" t="s">
         <v>315</v>
       </c>
@@ -11092,8 +11117,8 @@
       <c r="B243" s="7">
         <v>28</v>
       </c>
-      <c r="C243" s="154"/>
-      <c r="D243" s="173"/>
+      <c r="C243" s="169"/>
+      <c r="D243" s="152"/>
       <c r="E243" s="8" t="s">
         <v>316</v>
       </c>
@@ -11114,8 +11139,8 @@
       <c r="B244" s="7">
         <v>29</v>
       </c>
-      <c r="C244" s="154"/>
-      <c r="D244" s="171" t="s">
+      <c r="C244" s="169"/>
+      <c r="D244" s="150" t="s">
         <v>317</v>
       </c>
       <c r="E244" s="8" t="s">
@@ -11138,8 +11163,8 @@
       <c r="B245" s="7">
         <v>30</v>
       </c>
-      <c r="C245" s="154"/>
-      <c r="D245" s="172"/>
+      <c r="C245" s="169"/>
+      <c r="D245" s="151"/>
       <c r="E245" s="8" t="s">
         <v>319</v>
       </c>
@@ -11160,8 +11185,8 @@
       <c r="B246" s="7">
         <v>31</v>
       </c>
-      <c r="C246" s="154"/>
-      <c r="D246" s="172"/>
+      <c r="C246" s="169"/>
+      <c r="D246" s="151"/>
       <c r="E246" s="8" t="s">
         <v>320</v>
       </c>
@@ -11182,8 +11207,8 @@
       <c r="B247" s="7">
         <v>32</v>
       </c>
-      <c r="C247" s="154"/>
-      <c r="D247" s="172"/>
+      <c r="C247" s="169"/>
+      <c r="D247" s="151"/>
       <c r="E247" s="8" t="s">
         <v>321</v>
       </c>
@@ -11204,8 +11229,8 @@
       <c r="B248" s="7">
         <v>33</v>
       </c>
-      <c r="C248" s="154"/>
-      <c r="D248" s="172"/>
+      <c r="C248" s="169"/>
+      <c r="D248" s="151"/>
       <c r="E248" s="8" t="s">
         <v>322</v>
       </c>
@@ -11226,8 +11251,8 @@
       <c r="B249" s="24">
         <v>34</v>
       </c>
-      <c r="C249" s="155"/>
-      <c r="D249" s="173"/>
+      <c r="C249" s="170"/>
+      <c r="D249" s="152"/>
       <c r="E249" s="17" t="s">
         <v>323</v>
       </c>
@@ -11248,10 +11273,10 @@
       <c r="B250" s="7">
         <v>1</v>
       </c>
-      <c r="C250" s="156" t="s">
+      <c r="C250" s="159" t="s">
         <v>324</v>
       </c>
-      <c r="D250" s="171" t="s">
+      <c r="D250" s="150" t="s">
         <v>325</v>
       </c>
       <c r="E250" s="8" t="s">
@@ -11274,8 +11299,8 @@
       <c r="B251" s="7">
         <v>2</v>
       </c>
-      <c r="C251" s="157"/>
-      <c r="D251" s="172"/>
+      <c r="C251" s="160"/>
+      <c r="D251" s="151"/>
       <c r="E251" s="8" t="s">
         <v>327</v>
       </c>
@@ -11296,8 +11321,8 @@
       <c r="B252" s="7">
         <v>3</v>
       </c>
-      <c r="C252" s="157"/>
-      <c r="D252" s="172"/>
+      <c r="C252" s="160"/>
+      <c r="D252" s="151"/>
       <c r="E252" s="8" t="s">
         <v>328</v>
       </c>
@@ -11318,8 +11343,8 @@
       <c r="B253" s="7">
         <v>4</v>
       </c>
-      <c r="C253" s="157"/>
-      <c r="D253" s="172"/>
+      <c r="C253" s="160"/>
+      <c r="D253" s="151"/>
       <c r="E253" s="8" t="s">
         <v>329</v>
       </c>
@@ -11340,8 +11365,8 @@
       <c r="B254" s="7">
         <v>5</v>
       </c>
-      <c r="C254" s="157"/>
-      <c r="D254" s="172"/>
+      <c r="C254" s="160"/>
+      <c r="D254" s="151"/>
       <c r="E254" s="8" t="s">
         <v>330</v>
       </c>
@@ -11362,8 +11387,8 @@
       <c r="B255" s="7">
         <v>6</v>
       </c>
-      <c r="C255" s="157"/>
-      <c r="D255" s="172"/>
+      <c r="C255" s="160"/>
+      <c r="D255" s="151"/>
       <c r="E255" s="8" t="s">
         <v>331</v>
       </c>
@@ -11384,8 +11409,8 @@
       <c r="B256" s="7">
         <v>7</v>
       </c>
-      <c r="C256" s="157"/>
-      <c r="D256" s="172"/>
+      <c r="C256" s="160"/>
+      <c r="D256" s="151"/>
       <c r="E256" s="8" t="s">
         <v>332</v>
       </c>
@@ -11406,8 +11431,8 @@
       <c r="B257" s="7">
         <v>8</v>
       </c>
-      <c r="C257" s="157"/>
-      <c r="D257" s="173"/>
+      <c r="C257" s="160"/>
+      <c r="D257" s="152"/>
       <c r="E257" s="8" t="s">
         <v>333</v>
       </c>
@@ -11428,8 +11453,8 @@
       <c r="B258" s="7">
         <v>9</v>
       </c>
-      <c r="C258" s="157"/>
-      <c r="D258" s="171" t="s">
+      <c r="C258" s="160"/>
+      <c r="D258" s="150" t="s">
         <v>334</v>
       </c>
       <c r="E258" s="8" t="s">
@@ -11452,8 +11477,8 @@
       <c r="B259" s="7">
         <v>10</v>
       </c>
-      <c r="C259" s="157"/>
-      <c r="D259" s="173"/>
+      <c r="C259" s="160"/>
+      <c r="D259" s="152"/>
       <c r="E259" s="8" t="s">
         <v>336</v>
       </c>
@@ -11474,8 +11499,8 @@
       <c r="B260" s="7">
         <v>11</v>
       </c>
-      <c r="C260" s="157"/>
-      <c r="D260" s="171" t="s">
+      <c r="C260" s="160"/>
+      <c r="D260" s="150" t="s">
         <v>337</v>
       </c>
       <c r="E260" s="8" t="s">
@@ -11498,8 +11523,8 @@
       <c r="B261" s="7">
         <v>12</v>
       </c>
-      <c r="C261" s="157"/>
-      <c r="D261" s="172"/>
+      <c r="C261" s="160"/>
+      <c r="D261" s="151"/>
       <c r="E261" s="8" t="s">
         <v>339</v>
       </c>
@@ -11520,8 +11545,8 @@
       <c r="B262" s="7">
         <v>13</v>
       </c>
-      <c r="C262" s="157"/>
-      <c r="D262" s="172"/>
+      <c r="C262" s="160"/>
+      <c r="D262" s="151"/>
       <c r="E262" s="8" t="s">
         <v>340</v>
       </c>
@@ -11542,8 +11567,8 @@
       <c r="B263" s="7">
         <v>14</v>
       </c>
-      <c r="C263" s="157"/>
-      <c r="D263" s="172"/>
+      <c r="C263" s="160"/>
+      <c r="D263" s="151"/>
       <c r="E263" s="8" t="s">
         <v>341</v>
       </c>
@@ -11564,8 +11589,8 @@
       <c r="B264" s="7">
         <v>15</v>
       </c>
-      <c r="C264" s="157"/>
-      <c r="D264" s="172"/>
+      <c r="C264" s="160"/>
+      <c r="D264" s="151"/>
       <c r="E264" s="8" t="s">
         <v>342</v>
       </c>
@@ -11586,8 +11611,8 @@
       <c r="B265" s="24">
         <v>16</v>
       </c>
-      <c r="C265" s="158"/>
-      <c r="D265" s="173"/>
+      <c r="C265" s="161"/>
+      <c r="D265" s="152"/>
       <c r="E265" s="17" t="s">
         <v>343</v>
       </c>
@@ -11608,10 +11633,10 @@
       <c r="B266" s="7">
         <v>1</v>
       </c>
-      <c r="C266" s="159" t="s">
+      <c r="C266" s="162" t="s">
         <v>344</v>
       </c>
-      <c r="D266" s="171" t="s">
+      <c r="D266" s="150" t="s">
         <v>345</v>
       </c>
       <c r="E266" s="8" t="s">
@@ -11634,8 +11659,8 @@
       <c r="B267" s="7">
         <v>2</v>
       </c>
-      <c r="C267" s="160"/>
-      <c r="D267" s="172"/>
+      <c r="C267" s="163"/>
+      <c r="D267" s="151"/>
       <c r="E267" s="8" t="s">
         <v>347</v>
       </c>
@@ -11656,8 +11681,8 @@
       <c r="B268" s="7">
         <v>3</v>
       </c>
-      <c r="C268" s="160"/>
-      <c r="D268" s="172"/>
+      <c r="C268" s="163"/>
+      <c r="D268" s="151"/>
       <c r="E268" s="8" t="s">
         <v>348</v>
       </c>
@@ -11678,8 +11703,8 @@
       <c r="B269" s="7">
         <v>4</v>
       </c>
-      <c r="C269" s="160"/>
-      <c r="D269" s="172"/>
+      <c r="C269" s="163"/>
+      <c r="D269" s="151"/>
       <c r="E269" s="8" t="s">
         <v>349</v>
       </c>
@@ -11700,8 +11725,8 @@
       <c r="B270" s="7">
         <v>5</v>
       </c>
-      <c r="C270" s="160"/>
-      <c r="D270" s="173"/>
+      <c r="C270" s="163"/>
+      <c r="D270" s="152"/>
       <c r="E270" s="8" t="s">
         <v>350</v>
       </c>
@@ -11722,8 +11747,8 @@
       <c r="B271" s="7">
         <v>6</v>
       </c>
-      <c r="C271" s="160"/>
-      <c r="D271" s="171" t="s">
+      <c r="C271" s="163"/>
+      <c r="D271" s="150" t="s">
         <v>351</v>
       </c>
       <c r="E271" s="8" t="s">
@@ -11746,8 +11771,8 @@
       <c r="B272" s="7">
         <v>7</v>
       </c>
-      <c r="C272" s="161"/>
-      <c r="D272" s="173"/>
+      <c r="C272" s="164"/>
+      <c r="D272" s="152"/>
       <c r="E272" s="8" t="s">
         <v>353</v>
       </c>
@@ -11782,10 +11807,10 @@
       <c r="B274" s="7">
         <v>1</v>
       </c>
-      <c r="C274" s="162" t="s">
+      <c r="C274" s="177" t="s">
         <v>355</v>
       </c>
-      <c r="D274" s="174" t="s">
+      <c r="D274" s="180" t="s">
         <v>356</v>
       </c>
       <c r="E274" s="13" t="s">
@@ -11808,8 +11833,8 @@
       <c r="B275" s="7">
         <v>2</v>
       </c>
-      <c r="C275" s="163"/>
-      <c r="D275" s="175"/>
+      <c r="C275" s="178"/>
+      <c r="D275" s="181"/>
       <c r="E275" s="13" t="s">
         <v>358</v>
       </c>
@@ -11830,8 +11855,8 @@
       <c r="B276" s="7">
         <v>3</v>
       </c>
-      <c r="C276" s="163"/>
-      <c r="D276" s="175"/>
+      <c r="C276" s="178"/>
+      <c r="D276" s="181"/>
       <c r="E276" s="8" t="s">
         <v>359</v>
       </c>
@@ -11852,8 +11877,8 @@
       <c r="B277" s="7">
         <v>4</v>
       </c>
-      <c r="C277" s="163"/>
-      <c r="D277" s="175"/>
+      <c r="C277" s="178"/>
+      <c r="D277" s="181"/>
       <c r="E277" s="8" t="s">
         <v>360</v>
       </c>
@@ -11874,8 +11899,8 @@
       <c r="B278" s="7">
         <v>5</v>
       </c>
-      <c r="C278" s="163"/>
-      <c r="D278" s="175"/>
+      <c r="C278" s="178"/>
+      <c r="D278" s="181"/>
       <c r="E278" s="8" t="s">
         <v>361</v>
       </c>
@@ -11896,8 +11921,8 @@
       <c r="B279" s="7">
         <v>6</v>
       </c>
-      <c r="C279" s="163"/>
-      <c r="D279" s="175"/>
+      <c r="C279" s="178"/>
+      <c r="D279" s="181"/>
       <c r="E279" s="8" t="s">
         <v>362</v>
       </c>
@@ -11918,8 +11943,8 @@
       <c r="B280" s="7">
         <v>7</v>
       </c>
-      <c r="C280" s="163"/>
-      <c r="D280" s="175"/>
+      <c r="C280" s="178"/>
+      <c r="D280" s="181"/>
       <c r="E280" s="8" t="s">
         <v>363</v>
       </c>
@@ -11940,8 +11965,8 @@
       <c r="B281" s="7">
         <v>8</v>
       </c>
-      <c r="C281" s="163"/>
-      <c r="D281" s="176"/>
+      <c r="C281" s="178"/>
+      <c r="D281" s="182"/>
       <c r="E281" s="13" t="s">
         <v>364</v>
       </c>
@@ -11962,8 +11987,8 @@
       <c r="B282" s="7">
         <v>9</v>
       </c>
-      <c r="C282" s="163"/>
-      <c r="D282" s="174" t="s">
+      <c r="C282" s="178"/>
+      <c r="D282" s="180" t="s">
         <v>365</v>
       </c>
       <c r="E282" s="8" t="s">
@@ -11986,8 +12011,8 @@
       <c r="B283" s="7">
         <v>10</v>
       </c>
-      <c r="C283" s="163"/>
-      <c r="D283" s="175"/>
+      <c r="C283" s="178"/>
+      <c r="D283" s="181"/>
       <c r="E283" s="13" t="s">
         <v>367</v>
       </c>
@@ -12008,8 +12033,8 @@
       <c r="B284" s="7">
         <v>11</v>
       </c>
-      <c r="C284" s="163"/>
-      <c r="D284" s="175"/>
+      <c r="C284" s="178"/>
+      <c r="D284" s="181"/>
       <c r="E284" s="13" t="s">
         <v>368</v>
       </c>
@@ -12030,8 +12055,8 @@
       <c r="B285" s="7">
         <v>12</v>
       </c>
-      <c r="C285" s="163"/>
-      <c r="D285" s="175"/>
+      <c r="C285" s="178"/>
+      <c r="D285" s="181"/>
       <c r="E285" s="13" t="s">
         <v>369</v>
       </c>
@@ -12052,8 +12077,8 @@
       <c r="B286" s="7">
         <v>13</v>
       </c>
-      <c r="C286" s="163"/>
-      <c r="D286" s="175"/>
+      <c r="C286" s="178"/>
+      <c r="D286" s="181"/>
       <c r="E286" s="13" t="s">
         <v>370</v>
       </c>
@@ -12074,8 +12099,8 @@
       <c r="B287" s="7">
         <v>14</v>
       </c>
-      <c r="C287" s="163"/>
-      <c r="D287" s="175"/>
+      <c r="C287" s="178"/>
+      <c r="D287" s="181"/>
       <c r="E287" s="13" t="s">
         <v>371</v>
       </c>
@@ -12096,8 +12121,8 @@
       <c r="B288" s="7">
         <v>15</v>
       </c>
-      <c r="C288" s="163"/>
-      <c r="D288" s="176"/>
+      <c r="C288" s="178"/>
+      <c r="D288" s="182"/>
       <c r="E288" s="13" t="s">
         <v>372</v>
       </c>
@@ -12118,8 +12143,8 @@
       <c r="B289" s="7">
         <v>16</v>
       </c>
-      <c r="C289" s="163"/>
-      <c r="D289" s="174" t="s">
+      <c r="C289" s="178"/>
+      <c r="D289" s="180" t="s">
         <v>373</v>
       </c>
       <c r="E289" s="13" t="s">
@@ -12142,8 +12167,8 @@
       <c r="B290" s="7">
         <v>17</v>
       </c>
-      <c r="C290" s="163"/>
-      <c r="D290" s="175"/>
+      <c r="C290" s="178"/>
+      <c r="D290" s="181"/>
       <c r="E290" s="8" t="s">
         <v>375</v>
       </c>
@@ -12164,8 +12189,8 @@
       <c r="B291" s="7">
         <v>18</v>
       </c>
-      <c r="C291" s="163"/>
-      <c r="D291" s="175"/>
+      <c r="C291" s="178"/>
+      <c r="D291" s="181"/>
       <c r="E291" s="11" t="s">
         <v>376</v>
       </c>
@@ -12186,8 +12211,8 @@
       <c r="B292" s="24">
         <v>19</v>
       </c>
-      <c r="C292" s="164"/>
-      <c r="D292" s="176"/>
+      <c r="C292" s="179"/>
+      <c r="D292" s="182"/>
       <c r="E292" s="20" t="s">
         <v>377</v>
       </c>
@@ -12208,10 +12233,10 @@
       <c r="B293" s="7">
         <v>1</v>
       </c>
-      <c r="C293" s="153" t="s">
+      <c r="C293" s="168" t="s">
         <v>378</v>
       </c>
-      <c r="D293" s="171" t="s">
+      <c r="D293" s="150" t="s">
         <v>379</v>
       </c>
       <c r="E293" s="8" t="s">
@@ -12234,8 +12259,8 @@
       <c r="B294" s="7">
         <v>2</v>
       </c>
-      <c r="C294" s="154"/>
-      <c r="D294" s="172"/>
+      <c r="C294" s="169"/>
+      <c r="D294" s="151"/>
       <c r="E294" s="8" t="s">
         <v>381</v>
       </c>
@@ -12256,8 +12281,8 @@
       <c r="B295" s="7">
         <v>3</v>
       </c>
-      <c r="C295" s="154"/>
-      <c r="D295" s="173"/>
+      <c r="C295" s="169"/>
+      <c r="D295" s="152"/>
       <c r="E295" s="8" t="s">
         <v>382</v>
       </c>
@@ -12276,8 +12301,8 @@
       <c r="B296" s="7">
         <v>4</v>
       </c>
-      <c r="C296" s="154"/>
-      <c r="D296" s="171" t="s">
+      <c r="C296" s="169"/>
+      <c r="D296" s="150" t="s">
         <v>383</v>
       </c>
       <c r="E296" s="37" t="s">
@@ -12300,8 +12325,8 @@
       <c r="B297" s="7">
         <v>5</v>
       </c>
-      <c r="C297" s="154"/>
-      <c r="D297" s="172"/>
+      <c r="C297" s="169"/>
+      <c r="D297" s="151"/>
       <c r="E297" s="8" t="s">
         <v>385</v>
       </c>
@@ -12322,8 +12347,8 @@
       <c r="B298" s="7">
         <v>6</v>
       </c>
-      <c r="C298" s="154"/>
-      <c r="D298" s="172"/>
+      <c r="C298" s="169"/>
+      <c r="D298" s="151"/>
       <c r="E298" s="8" t="s">
         <v>386</v>
       </c>
@@ -12344,8 +12369,8 @@
       <c r="B299" s="7">
         <v>7</v>
       </c>
-      <c r="C299" s="154"/>
-      <c r="D299" s="172"/>
+      <c r="C299" s="169"/>
+      <c r="D299" s="151"/>
       <c r="E299" s="8" t="s">
         <v>387</v>
       </c>
@@ -12366,8 +12391,8 @@
       <c r="B300" s="7">
         <v>8</v>
       </c>
-      <c r="C300" s="154"/>
-      <c r="D300" s="173"/>
+      <c r="C300" s="169"/>
+      <c r="D300" s="152"/>
       <c r="E300" s="8" t="s">
         <v>388</v>
       </c>
@@ -12388,8 +12413,8 @@
       <c r="B301" s="7">
         <v>9</v>
       </c>
-      <c r="C301" s="154"/>
-      <c r="D301" s="171" t="s">
+      <c r="C301" s="169"/>
+      <c r="D301" s="150" t="s">
         <v>389</v>
       </c>
       <c r="E301" s="8" t="s">
@@ -12412,8 +12437,8 @@
       <c r="B302" s="7">
         <v>10</v>
       </c>
-      <c r="C302" s="154"/>
-      <c r="D302" s="172"/>
+      <c r="C302" s="169"/>
+      <c r="D302" s="151"/>
       <c r="E302" s="8" t="s">
         <v>391</v>
       </c>
@@ -12434,8 +12459,8 @@
       <c r="B303" s="7">
         <v>11</v>
       </c>
-      <c r="C303" s="154"/>
-      <c r="D303" s="173"/>
+      <c r="C303" s="169"/>
+      <c r="D303" s="152"/>
       <c r="E303" s="8" t="s">
         <v>392</v>
       </c>
@@ -12456,8 +12481,8 @@
       <c r="B304" s="7">
         <v>12</v>
       </c>
-      <c r="C304" s="154"/>
-      <c r="D304" s="171" t="s">
+      <c r="C304" s="169"/>
+      <c r="D304" s="150" t="s">
         <v>393</v>
       </c>
       <c r="E304" s="8" t="s">
@@ -12480,8 +12505,8 @@
       <c r="B305" s="7">
         <v>13</v>
       </c>
-      <c r="C305" s="154"/>
-      <c r="D305" s="172"/>
+      <c r="C305" s="169"/>
+      <c r="D305" s="151"/>
       <c r="E305" s="8" t="s">
         <v>395</v>
       </c>
@@ -12502,8 +12527,8 @@
       <c r="B306" s="7">
         <v>14</v>
       </c>
-      <c r="C306" s="154"/>
-      <c r="D306" s="172"/>
+      <c r="C306" s="169"/>
+      <c r="D306" s="151"/>
       <c r="E306" s="8" t="s">
         <v>396</v>
       </c>
@@ -12524,8 +12549,8 @@
       <c r="B307" s="24">
         <v>15</v>
       </c>
-      <c r="C307" s="155"/>
-      <c r="D307" s="173"/>
+      <c r="C307" s="170"/>
+      <c r="D307" s="152"/>
       <c r="E307" s="17" t="s">
         <v>397</v>
       </c>
@@ -12546,10 +12571,10 @@
       <c r="B308" s="7">
         <v>1</v>
       </c>
-      <c r="C308" s="165" t="s">
+      <c r="C308" s="195" t="s">
         <v>398</v>
       </c>
-      <c r="D308" s="174" t="s">
+      <c r="D308" s="180" t="s">
         <v>399</v>
       </c>
       <c r="E308" s="13" t="s">
@@ -12572,8 +12597,8 @@
       <c r="B309" s="7">
         <v>2</v>
       </c>
-      <c r="C309" s="166"/>
-      <c r="D309" s="175"/>
+      <c r="C309" s="196"/>
+      <c r="D309" s="181"/>
       <c r="E309" s="8" t="s">
         <v>401</v>
       </c>
@@ -12594,8 +12619,8 @@
       <c r="B310" s="7">
         <v>3</v>
       </c>
-      <c r="C310" s="166"/>
-      <c r="D310" s="175"/>
+      <c r="C310" s="196"/>
+      <c r="D310" s="181"/>
       <c r="E310" s="13" t="s">
         <v>402</v>
       </c>
@@ -12616,8 +12641,8 @@
       <c r="B311" s="7">
         <v>4</v>
       </c>
-      <c r="C311" s="166"/>
-      <c r="D311" s="175"/>
+      <c r="C311" s="196"/>
+      <c r="D311" s="181"/>
       <c r="E311" s="8" t="s">
         <v>403</v>
       </c>
@@ -12638,8 +12663,8 @@
       <c r="B312" s="7">
         <v>5</v>
       </c>
-      <c r="C312" s="166"/>
-      <c r="D312" s="175"/>
+      <c r="C312" s="196"/>
+      <c r="D312" s="181"/>
       <c r="E312" s="13" t="s">
         <v>404</v>
       </c>
@@ -12660,8 +12685,8 @@
       <c r="B313" s="7">
         <v>6</v>
       </c>
-      <c r="C313" s="166"/>
-      <c r="D313" s="175"/>
+      <c r="C313" s="196"/>
+      <c r="D313" s="181"/>
       <c r="E313" s="13" t="s">
         <v>405</v>
       </c>
@@ -12682,8 +12707,8 @@
       <c r="B314" s="7">
         <v>7</v>
       </c>
-      <c r="C314" s="166"/>
-      <c r="D314" s="176"/>
+      <c r="C314" s="196"/>
+      <c r="D314" s="182"/>
       <c r="E314" s="8" t="s">
         <v>406</v>
       </c>
@@ -12704,8 +12729,8 @@
       <c r="B315" s="7">
         <v>8</v>
       </c>
-      <c r="C315" s="166"/>
-      <c r="D315" s="174" t="s">
+      <c r="C315" s="196"/>
+      <c r="D315" s="180" t="s">
         <v>407</v>
       </c>
       <c r="E315" s="13" t="s">
@@ -12728,8 +12753,8 @@
       <c r="B316" s="7">
         <v>9</v>
       </c>
-      <c r="C316" s="166"/>
-      <c r="D316" s="175"/>
+      <c r="C316" s="196"/>
+      <c r="D316" s="181"/>
       <c r="E316" s="8" t="s">
         <v>409</v>
       </c>
@@ -12750,8 +12775,8 @@
       <c r="B317" s="24">
         <v>10</v>
       </c>
-      <c r="C317" s="167"/>
-      <c r="D317" s="176"/>
+      <c r="C317" s="197"/>
+      <c r="D317" s="182"/>
       <c r="E317" s="17" t="s">
         <v>410</v>
       </c>
@@ -12772,10 +12797,10 @@
       <c r="B318" s="7">
         <v>1</v>
       </c>
-      <c r="C318" s="168" t="s">
+      <c r="C318" s="198" t="s">
         <v>411</v>
       </c>
-      <c r="D318" s="174" t="s">
+      <c r="D318" s="180" t="s">
         <v>412</v>
       </c>
       <c r="E318" s="8" t="s">
@@ -12798,8 +12823,8 @@
       <c r="B319" s="7">
         <v>2</v>
       </c>
-      <c r="C319" s="169"/>
-      <c r="D319" s="175"/>
+      <c r="C319" s="199"/>
+      <c r="D319" s="181"/>
       <c r="E319" s="13" t="s">
         <v>414</v>
       </c>
@@ -12820,8 +12845,8 @@
       <c r="B320" s="7">
         <v>3</v>
       </c>
-      <c r="C320" s="169"/>
-      <c r="D320" s="175"/>
+      <c r="C320" s="199"/>
+      <c r="D320" s="181"/>
       <c r="E320" s="8" t="s">
         <v>415</v>
       </c>
@@ -12842,8 +12867,8 @@
       <c r="B321" s="7">
         <v>4</v>
       </c>
-      <c r="C321" s="169"/>
-      <c r="D321" s="175"/>
+      <c r="C321" s="199"/>
+      <c r="D321" s="181"/>
       <c r="E321" s="8" t="s">
         <v>416</v>
       </c>
@@ -12864,8 +12889,8 @@
       <c r="B322" s="7">
         <v>5</v>
       </c>
-      <c r="C322" s="169"/>
-      <c r="D322" s="175"/>
+      <c r="C322" s="199"/>
+      <c r="D322" s="181"/>
       <c r="E322" s="8" t="s">
         <v>417</v>
       </c>
@@ -12886,8 +12911,8 @@
       <c r="B323" s="7">
         <v>6</v>
       </c>
-      <c r="C323" s="169"/>
-      <c r="D323" s="176"/>
+      <c r="C323" s="199"/>
+      <c r="D323" s="182"/>
       <c r="E323" s="29" t="s">
         <v>418</v>
       </c>
@@ -12908,8 +12933,8 @@
       <c r="B324" s="7">
         <v>7</v>
       </c>
-      <c r="C324" s="169"/>
-      <c r="D324" s="174" t="s">
+      <c r="C324" s="199"/>
+      <c r="D324" s="180" t="s">
         <v>419</v>
       </c>
       <c r="E324" s="13" t="s">
@@ -12932,8 +12957,8 @@
       <c r="B325" s="7">
         <v>8</v>
       </c>
-      <c r="C325" s="169"/>
-      <c r="D325" s="175"/>
+      <c r="C325" s="199"/>
+      <c r="D325" s="181"/>
       <c r="E325" s="8" t="s">
         <v>421</v>
       </c>
@@ -12954,8 +12979,8 @@
       <c r="B326" s="7">
         <v>9</v>
       </c>
-      <c r="C326" s="169"/>
-      <c r="D326" s="175"/>
+      <c r="C326" s="199"/>
+      <c r="D326" s="181"/>
       <c r="E326" s="8" t="s">
         <v>422</v>
       </c>
@@ -12976,8 +13001,8 @@
       <c r="B327" s="7">
         <v>10</v>
       </c>
-      <c r="C327" s="169"/>
-      <c r="D327" s="175"/>
+      <c r="C327" s="199"/>
+      <c r="D327" s="181"/>
       <c r="E327" s="8" t="s">
         <v>423</v>
       </c>
@@ -12998,8 +13023,8 @@
       <c r="B328" s="7">
         <v>11</v>
       </c>
-      <c r="C328" s="169"/>
-      <c r="D328" s="176"/>
+      <c r="C328" s="199"/>
+      <c r="D328" s="182"/>
       <c r="E328" s="13" t="s">
         <v>424</v>
       </c>
@@ -13020,8 +13045,8 @@
       <c r="B329" s="7">
         <v>12</v>
       </c>
-      <c r="C329" s="169"/>
-      <c r="D329" s="174" t="s">
+      <c r="C329" s="199"/>
+      <c r="D329" s="180" t="s">
         <v>425</v>
       </c>
       <c r="E329" s="8" t="s">
@@ -13044,8 +13069,8 @@
       <c r="B330" s="7">
         <v>13</v>
       </c>
-      <c r="C330" s="169"/>
-      <c r="D330" s="175"/>
+      <c r="C330" s="199"/>
+      <c r="D330" s="181"/>
       <c r="E330" s="8" t="s">
         <v>427</v>
       </c>
@@ -13066,8 +13091,8 @@
       <c r="B331" s="7">
         <v>14</v>
       </c>
-      <c r="C331" s="169"/>
-      <c r="D331" s="175"/>
+      <c r="C331" s="199"/>
+      <c r="D331" s="181"/>
       <c r="E331" s="8" t="s">
         <v>428</v>
       </c>
@@ -13088,8 +13113,8 @@
       <c r="B332" s="7">
         <v>15</v>
       </c>
-      <c r="C332" s="169"/>
-      <c r="D332" s="175"/>
+      <c r="C332" s="199"/>
+      <c r="D332" s="181"/>
       <c r="E332" s="8" t="s">
         <v>429</v>
       </c>
@@ -13110,8 +13135,8 @@
       <c r="B333" s="7">
         <v>16</v>
       </c>
-      <c r="C333" s="169"/>
-      <c r="D333" s="175"/>
+      <c r="C333" s="199"/>
+      <c r="D333" s="181"/>
       <c r="E333" s="8" t="s">
         <v>430</v>
       </c>
@@ -13132,8 +13157,8 @@
       <c r="B334" s="7">
         <v>17</v>
       </c>
-      <c r="C334" s="169"/>
-      <c r="D334" s="175"/>
+      <c r="C334" s="199"/>
+      <c r="D334" s="181"/>
       <c r="E334" s="8" t="s">
         <v>431</v>
       </c>
@@ -13154,8 +13179,8 @@
       <c r="B335" s="7">
         <v>18</v>
       </c>
-      <c r="C335" s="169"/>
-      <c r="D335" s="175"/>
+      <c r="C335" s="199"/>
+      <c r="D335" s="181"/>
       <c r="E335" s="8" t="s">
         <v>432</v>
       </c>
@@ -13176,8 +13201,8 @@
       <c r="B336" s="7">
         <v>19</v>
       </c>
-      <c r="C336" s="169"/>
-      <c r="D336" s="175"/>
+      <c r="C336" s="199"/>
+      <c r="D336" s="181"/>
       <c r="E336" s="8" t="s">
         <v>433</v>
       </c>
@@ -13198,8 +13223,8 @@
       <c r="B337" s="7">
         <v>20</v>
       </c>
-      <c r="C337" s="169"/>
-      <c r="D337" s="176"/>
+      <c r="C337" s="199"/>
+      <c r="D337" s="182"/>
       <c r="E337" s="13" t="s">
         <v>434</v>
       </c>
@@ -13220,8 +13245,8 @@
       <c r="B338" s="7">
         <v>21</v>
       </c>
-      <c r="C338" s="169"/>
-      <c r="D338" s="174" t="s">
+      <c r="C338" s="199"/>
+      <c r="D338" s="180" t="s">
         <v>435</v>
       </c>
       <c r="E338" s="13" t="s">
@@ -13244,8 +13269,8 @@
       <c r="B339" s="7">
         <v>22</v>
       </c>
-      <c r="C339" s="169"/>
-      <c r="D339" s="175"/>
+      <c r="C339" s="199"/>
+      <c r="D339" s="181"/>
       <c r="E339" s="13" t="s">
         <v>437</v>
       </c>
@@ -13266,8 +13291,8 @@
       <c r="B340" s="7">
         <v>23</v>
       </c>
-      <c r="C340" s="169"/>
-      <c r="D340" s="175"/>
+      <c r="C340" s="199"/>
+      <c r="D340" s="181"/>
       <c r="E340" s="13" t="s">
         <v>438</v>
       </c>
@@ -13288,8 +13313,8 @@
       <c r="B341" s="7">
         <v>24</v>
       </c>
-      <c r="C341" s="169"/>
-      <c r="D341" s="175"/>
+      <c r="C341" s="199"/>
+      <c r="D341" s="181"/>
       <c r="E341" s="13" t="s">
         <v>439</v>
       </c>
@@ -13310,8 +13335,8 @@
       <c r="B342" s="24">
         <v>25</v>
       </c>
-      <c r="C342" s="170"/>
-      <c r="D342" s="176"/>
+      <c r="C342" s="200"/>
+      <c r="D342" s="182"/>
       <c r="E342" s="25" t="s">
         <v>440</v>
       </c>
@@ -13332,10 +13357,10 @@
       <c r="B343" s="7">
         <v>1</v>
       </c>
-      <c r="C343" s="150" t="s">
+      <c r="C343" s="165" t="s">
         <v>441</v>
       </c>
-      <c r="D343" s="171" t="s">
+      <c r="D343" s="150" t="s">
         <v>442</v>
       </c>
       <c r="E343" s="8" t="s">
@@ -13364,8 +13389,8 @@
       <c r="B344" s="7">
         <v>2</v>
       </c>
-      <c r="C344" s="151"/>
-      <c r="D344" s="172"/>
+      <c r="C344" s="166"/>
+      <c r="D344" s="151"/>
       <c r="E344" s="8" t="s">
         <v>444</v>
       </c>
@@ -13392,8 +13417,8 @@
       <c r="B345" s="7">
         <v>3</v>
       </c>
-      <c r="C345" s="151"/>
-      <c r="D345" s="172"/>
+      <c r="C345" s="166"/>
+      <c r="D345" s="151"/>
       <c r="E345" s="8" t="s">
         <v>445</v>
       </c>
@@ -13420,8 +13445,8 @@
       <c r="B346" s="7">
         <v>4</v>
       </c>
-      <c r="C346" s="151"/>
-      <c r="D346" s="172"/>
+      <c r="C346" s="166"/>
+      <c r="D346" s="151"/>
       <c r="E346" s="8" t="s">
         <v>446</v>
       </c>
@@ -13448,8 +13473,8 @@
       <c r="B347" s="7">
         <v>5</v>
       </c>
-      <c r="C347" s="151"/>
-      <c r="D347" s="173"/>
+      <c r="C347" s="166"/>
+      <c r="D347" s="152"/>
       <c r="E347" s="8" t="s">
         <v>447</v>
       </c>
@@ -13476,8 +13501,8 @@
       <c r="B348" s="7">
         <v>6</v>
       </c>
-      <c r="C348" s="151"/>
-      <c r="D348" s="171" t="s">
+      <c r="C348" s="166"/>
+      <c r="D348" s="150" t="s">
         <v>448</v>
       </c>
       <c r="E348" s="8" t="s">
@@ -13504,8 +13529,8 @@
       <c r="B349" s="7">
         <v>7</v>
       </c>
-      <c r="C349" s="151"/>
-      <c r="D349" s="172"/>
+      <c r="C349" s="166"/>
+      <c r="D349" s="151"/>
       <c r="E349" s="8" t="s">
         <v>450</v>
       </c>
@@ -13532,8 +13557,8 @@
       <c r="B350" s="7">
         <v>8</v>
       </c>
-      <c r="C350" s="151"/>
-      <c r="D350" s="172"/>
+      <c r="C350" s="166"/>
+      <c r="D350" s="151"/>
       <c r="E350" s="8" t="s">
         <v>451</v>
       </c>
@@ -13560,8 +13585,8 @@
       <c r="B351" s="7">
         <v>9</v>
       </c>
-      <c r="C351" s="151"/>
-      <c r="D351" s="172"/>
+      <c r="C351" s="166"/>
+      <c r="D351" s="151"/>
       <c r="E351" s="8" t="s">
         <v>452</v>
       </c>
@@ -13584,8 +13609,8 @@
       <c r="B352" s="7">
         <v>10</v>
       </c>
-      <c r="C352" s="151"/>
-      <c r="D352" s="172"/>
+      <c r="C352" s="166"/>
+      <c r="D352" s="151"/>
       <c r="E352" s="8" t="s">
         <v>453</v>
       </c>
@@ -13612,8 +13637,8 @@
       <c r="B353" s="7">
         <v>11</v>
       </c>
-      <c r="C353" s="151"/>
-      <c r="D353" s="173"/>
+      <c r="C353" s="166"/>
+      <c r="D353" s="152"/>
       <c r="E353" s="8" t="s">
         <v>454</v>
       </c>
@@ -13634,8 +13659,8 @@
       <c r="B354" s="7">
         <v>12</v>
       </c>
-      <c r="C354" s="151"/>
-      <c r="D354" s="171" t="s">
+      <c r="C354" s="166"/>
+      <c r="D354" s="150" t="s">
         <v>455</v>
       </c>
       <c r="E354" s="8" t="s">
@@ -13662,8 +13687,8 @@
       <c r="B355" s="7">
         <v>13</v>
       </c>
-      <c r="C355" s="151"/>
-      <c r="D355" s="172"/>
+      <c r="C355" s="166"/>
+      <c r="D355" s="151"/>
       <c r="E355" s="8" t="s">
         <v>457</v>
       </c>
@@ -13690,8 +13715,8 @@
       <c r="B356" s="7">
         <v>14</v>
       </c>
-      <c r="C356" s="151"/>
-      <c r="D356" s="172"/>
+      <c r="C356" s="166"/>
+      <c r="D356" s="151"/>
       <c r="E356" s="8" t="s">
         <v>458</v>
       </c>
@@ -13712,8 +13737,8 @@
       <c r="B357" s="7">
         <v>15</v>
       </c>
-      <c r="C357" s="152"/>
-      <c r="D357" s="173"/>
+      <c r="C357" s="167"/>
+      <c r="D357" s="152"/>
       <c r="E357" s="8" t="s">
         <v>459</v>
       </c>
@@ -13728,18 +13753,18 @@
       <c r="J357" s="11"/>
     </row>
     <row r="358" spans="1:10" ht="13.8">
-      <c r="A358" s="186" t="s">
+      <c r="A358" s="189" t="s">
         <v>460</v>
       </c>
-      <c r="B358" s="187"/>
-      <c r="C358" s="187"/>
-      <c r="D358" s="187"/>
-      <c r="E358" s="187"/>
-      <c r="F358" s="187"/>
-      <c r="G358" s="187"/>
-      <c r="H358" s="187"/>
-      <c r="I358" s="187"/>
-      <c r="J358" s="188"/>
+      <c r="B358" s="190"/>
+      <c r="C358" s="190"/>
+      <c r="D358" s="190"/>
+      <c r="E358" s="190"/>
+      <c r="F358" s="190"/>
+      <c r="G358" s="190"/>
+      <c r="H358" s="190"/>
+      <c r="I358" s="190"/>
+      <c r="J358" s="191"/>
     </row>
     <row r="359" spans="1:10" ht="13.8">
       <c r="A359" s="6">
@@ -13748,10 +13773,10 @@
       <c r="B359" s="7">
         <v>1</v>
       </c>
-      <c r="C359" s="153" t="s">
+      <c r="C359" s="168" t="s">
         <v>461</v>
       </c>
-      <c r="D359" s="171" t="s">
+      <c r="D359" s="150" t="s">
         <v>462</v>
       </c>
       <c r="E359" s="8" t="s">
@@ -13774,8 +13799,8 @@
       <c r="B360" s="7">
         <v>2</v>
       </c>
-      <c r="C360" s="154"/>
-      <c r="D360" s="172"/>
+      <c r="C360" s="169"/>
+      <c r="D360" s="151"/>
       <c r="E360" s="8" t="s">
         <v>464</v>
       </c>
@@ -13796,8 +13821,8 @@
       <c r="B361" s="7">
         <v>3</v>
       </c>
-      <c r="C361" s="154"/>
-      <c r="D361" s="172"/>
+      <c r="C361" s="169"/>
+      <c r="D361" s="151"/>
       <c r="E361" s="8" t="s">
         <v>465</v>
       </c>
@@ -13818,8 +13843,8 @@
       <c r="B362" s="7">
         <v>4</v>
       </c>
-      <c r="C362" s="154"/>
-      <c r="D362" s="172"/>
+      <c r="C362" s="169"/>
+      <c r="D362" s="151"/>
       <c r="E362" s="8" t="s">
         <v>466</v>
       </c>
@@ -13840,8 +13865,8 @@
       <c r="B363" s="7">
         <v>5</v>
       </c>
-      <c r="C363" s="154"/>
-      <c r="D363" s="173"/>
+      <c r="C363" s="169"/>
+      <c r="D363" s="152"/>
       <c r="E363" s="8" t="s">
         <v>467</v>
       </c>
@@ -13862,8 +13887,8 @@
       <c r="B364" s="7">
         <v>6</v>
       </c>
-      <c r="C364" s="154"/>
-      <c r="D364" s="171" t="s">
+      <c r="C364" s="169"/>
+      <c r="D364" s="150" t="s">
         <v>468</v>
       </c>
       <c r="E364" s="8" t="s">
@@ -13886,8 +13911,8 @@
       <c r="B365" s="7">
         <v>7</v>
       </c>
-      <c r="C365" s="154"/>
-      <c r="D365" s="172"/>
+      <c r="C365" s="169"/>
+      <c r="D365" s="151"/>
       <c r="E365" s="8" t="s">
         <v>470</v>
       </c>
@@ -13908,8 +13933,8 @@
       <c r="B366" s="7">
         <v>8</v>
       </c>
-      <c r="C366" s="154"/>
-      <c r="D366" s="172"/>
+      <c r="C366" s="169"/>
+      <c r="D366" s="151"/>
       <c r="E366" s="8" t="s">
         <v>471</v>
       </c>
@@ -13930,8 +13955,8 @@
       <c r="B367" s="7">
         <v>9</v>
       </c>
-      <c r="C367" s="154"/>
-      <c r="D367" s="172"/>
+      <c r="C367" s="169"/>
+      <c r="D367" s="151"/>
       <c r="E367" s="8" t="s">
         <v>472</v>
       </c>
@@ -13952,8 +13977,8 @@
       <c r="B368" s="7">
         <v>10</v>
       </c>
-      <c r="C368" s="154"/>
-      <c r="D368" s="172"/>
+      <c r="C368" s="169"/>
+      <c r="D368" s="151"/>
       <c r="E368" s="8" t="s">
         <v>473</v>
       </c>
@@ -13974,8 +13999,8 @@
       <c r="B369" s="7">
         <v>11</v>
       </c>
-      <c r="C369" s="154"/>
-      <c r="D369" s="172"/>
+      <c r="C369" s="169"/>
+      <c r="D369" s="151"/>
       <c r="E369" s="8" t="s">
         <v>474</v>
       </c>
@@ -13996,8 +14021,8 @@
       <c r="B370" s="7">
         <v>12</v>
       </c>
-      <c r="C370" s="154"/>
-      <c r="D370" s="172"/>
+      <c r="C370" s="169"/>
+      <c r="D370" s="151"/>
       <c r="E370" s="8" t="s">
         <v>475</v>
       </c>
@@ -14018,8 +14043,8 @@
       <c r="B371" s="7">
         <v>13</v>
       </c>
-      <c r="C371" s="154"/>
-      <c r="D371" s="173"/>
+      <c r="C371" s="169"/>
+      <c r="D371" s="152"/>
       <c r="E371" s="8" t="s">
         <v>476</v>
       </c>
@@ -14040,8 +14065,8 @@
       <c r="B372" s="7">
         <v>14</v>
       </c>
-      <c r="C372" s="154"/>
-      <c r="D372" s="171" t="s">
+      <c r="C372" s="169"/>
+      <c r="D372" s="150" t="s">
         <v>477</v>
       </c>
       <c r="E372" s="8" t="s">
@@ -14064,8 +14089,8 @@
       <c r="B373" s="7">
         <v>15</v>
       </c>
-      <c r="C373" s="154"/>
-      <c r="D373" s="172"/>
+      <c r="C373" s="169"/>
+      <c r="D373" s="151"/>
       <c r="E373" s="11" t="s">
         <v>479</v>
       </c>
@@ -14086,8 +14111,8 @@
       <c r="B374" s="7">
         <v>16</v>
       </c>
-      <c r="C374" s="154"/>
-      <c r="D374" s="172"/>
+      <c r="C374" s="169"/>
+      <c r="D374" s="151"/>
       <c r="E374" s="8" t="s">
         <v>480</v>
       </c>
@@ -14108,8 +14133,8 @@
       <c r="B375" s="7">
         <v>17</v>
       </c>
-      <c r="C375" s="154"/>
-      <c r="D375" s="173"/>
+      <c r="C375" s="169"/>
+      <c r="D375" s="152"/>
       <c r="E375" s="8" t="s">
         <v>481</v>
       </c>
@@ -14130,8 +14155,8 @@
       <c r="B376" s="7">
         <v>18</v>
       </c>
-      <c r="C376" s="154"/>
-      <c r="D376" s="171" t="s">
+      <c r="C376" s="169"/>
+      <c r="D376" s="150" t="s">
         <v>482</v>
       </c>
       <c r="E376" s="8" t="s">
@@ -14154,8 +14179,8 @@
       <c r="B377" s="7">
         <v>19</v>
       </c>
-      <c r="C377" s="154"/>
-      <c r="D377" s="172"/>
+      <c r="C377" s="169"/>
+      <c r="D377" s="151"/>
       <c r="E377" s="8" t="s">
         <v>484</v>
       </c>
@@ -14176,8 +14201,8 @@
       <c r="B378" s="7">
         <v>20</v>
       </c>
-      <c r="C378" s="154"/>
-      <c r="D378" s="172"/>
+      <c r="C378" s="169"/>
+      <c r="D378" s="151"/>
       <c r="E378" s="8" t="s">
         <v>485</v>
       </c>
@@ -14198,8 +14223,8 @@
       <c r="B379" s="7">
         <v>21</v>
       </c>
-      <c r="C379" s="154"/>
-      <c r="D379" s="172"/>
+      <c r="C379" s="169"/>
+      <c r="D379" s="151"/>
       <c r="E379" s="8" t="s">
         <v>486</v>
       </c>
@@ -14220,8 +14245,8 @@
       <c r="B380" s="24">
         <v>22</v>
       </c>
-      <c r="C380" s="155"/>
-      <c r="D380" s="173"/>
+      <c r="C380" s="170"/>
+      <c r="D380" s="152"/>
       <c r="E380" s="17" t="s">
         <v>487</v>
       </c>
@@ -14242,10 +14267,10 @@
       <c r="B381" s="7">
         <v>1</v>
       </c>
-      <c r="C381" s="156" t="s">
+      <c r="C381" s="159" t="s">
         <v>488</v>
       </c>
-      <c r="D381" s="171" t="s">
+      <c r="D381" s="150" t="s">
         <v>489</v>
       </c>
       <c r="E381" s="8" t="s">
@@ -14268,8 +14293,8 @@
       <c r="B382" s="7">
         <v>2</v>
       </c>
-      <c r="C382" s="157"/>
-      <c r="D382" s="172"/>
+      <c r="C382" s="160"/>
+      <c r="D382" s="151"/>
       <c r="E382" s="8" t="s">
         <v>491</v>
       </c>
@@ -14290,8 +14315,8 @@
       <c r="B383" s="7">
         <v>3</v>
       </c>
-      <c r="C383" s="157"/>
-      <c r="D383" s="172"/>
+      <c r="C383" s="160"/>
+      <c r="D383" s="151"/>
       <c r="E383" s="8" t="s">
         <v>492</v>
       </c>
@@ -14312,8 +14337,8 @@
       <c r="B384" s="7">
         <v>4</v>
       </c>
-      <c r="C384" s="157"/>
-      <c r="D384" s="172"/>
+      <c r="C384" s="160"/>
+      <c r="D384" s="151"/>
       <c r="E384" s="8" t="s">
         <v>493</v>
       </c>
@@ -14334,8 +14359,8 @@
       <c r="B385" s="7">
         <v>5</v>
       </c>
-      <c r="C385" s="157"/>
-      <c r="D385" s="172"/>
+      <c r="C385" s="160"/>
+      <c r="D385" s="151"/>
       <c r="E385" s="8" t="s">
         <v>494</v>
       </c>
@@ -14356,8 +14381,8 @@
       <c r="B386" s="7">
         <v>6</v>
       </c>
-      <c r="C386" s="157"/>
-      <c r="D386" s="173"/>
+      <c r="C386" s="160"/>
+      <c r="D386" s="152"/>
       <c r="E386" s="8" t="s">
         <v>495</v>
       </c>
@@ -14378,8 +14403,8 @@
       <c r="B387" s="7">
         <v>7</v>
       </c>
-      <c r="C387" s="157"/>
-      <c r="D387" s="171" t="s">
+      <c r="C387" s="160"/>
+      <c r="D387" s="150" t="s">
         <v>496</v>
       </c>
       <c r="E387" s="8" t="s">
@@ -14402,8 +14427,8 @@
       <c r="B388" s="7">
         <v>8</v>
       </c>
-      <c r="C388" s="157"/>
-      <c r="D388" s="172"/>
+      <c r="C388" s="160"/>
+      <c r="D388" s="151"/>
       <c r="E388" s="8" t="s">
         <v>498</v>
       </c>
@@ -14424,8 +14449,8 @@
       <c r="B389" s="7">
         <v>9</v>
       </c>
-      <c r="C389" s="157"/>
-      <c r="D389" s="172"/>
+      <c r="C389" s="160"/>
+      <c r="D389" s="151"/>
       <c r="E389" s="8" t="s">
         <v>499</v>
       </c>
@@ -14446,8 +14471,8 @@
       <c r="B390" s="7">
         <v>10</v>
       </c>
-      <c r="C390" s="157"/>
-      <c r="D390" s="172"/>
+      <c r="C390" s="160"/>
+      <c r="D390" s="151"/>
       <c r="E390" s="8" t="s">
         <v>500</v>
       </c>
@@ -14468,8 +14493,8 @@
       <c r="B391" s="7">
         <v>11</v>
       </c>
-      <c r="C391" s="157"/>
-      <c r="D391" s="172"/>
+      <c r="C391" s="160"/>
+      <c r="D391" s="151"/>
       <c r="E391" s="8" t="s">
         <v>501</v>
       </c>
@@ -14490,8 +14515,8 @@
       <c r="B392" s="7">
         <v>12</v>
       </c>
-      <c r="C392" s="157"/>
-      <c r="D392" s="172"/>
+      <c r="C392" s="160"/>
+      <c r="D392" s="151"/>
       <c r="E392" s="8" t="s">
         <v>502</v>
       </c>
@@ -14512,8 +14537,8 @@
       <c r="B393" s="7">
         <v>13</v>
       </c>
-      <c r="C393" s="157"/>
-      <c r="D393" s="172"/>
+      <c r="C393" s="160"/>
+      <c r="D393" s="151"/>
       <c r="E393" s="8" t="s">
         <v>503</v>
       </c>
@@ -14534,8 +14559,8 @@
       <c r="B394" s="7">
         <v>14</v>
       </c>
-      <c r="C394" s="157"/>
-      <c r="D394" s="172"/>
+      <c r="C394" s="160"/>
+      <c r="D394" s="151"/>
       <c r="E394" s="8" t="s">
         <v>504</v>
       </c>
@@ -14556,8 +14581,8 @@
       <c r="B395" s="7">
         <v>15</v>
       </c>
-      <c r="C395" s="157"/>
-      <c r="D395" s="172"/>
+      <c r="C395" s="160"/>
+      <c r="D395" s="151"/>
       <c r="E395" s="8" t="s">
         <v>505</v>
       </c>
@@ -14578,8 +14603,8 @@
       <c r="B396" s="7">
         <v>16</v>
       </c>
-      <c r="C396" s="157"/>
-      <c r="D396" s="173"/>
+      <c r="C396" s="160"/>
+      <c r="D396" s="152"/>
       <c r="E396" s="8" t="s">
         <v>506</v>
       </c>
@@ -14600,8 +14625,8 @@
       <c r="B397" s="7">
         <v>17</v>
       </c>
-      <c r="C397" s="157"/>
-      <c r="D397" s="171" t="s">
+      <c r="C397" s="160"/>
+      <c r="D397" s="150" t="s">
         <v>507</v>
       </c>
       <c r="E397" s="8" t="s">
@@ -14624,8 +14649,8 @@
       <c r="B398" s="7">
         <v>18</v>
       </c>
-      <c r="C398" s="157"/>
-      <c r="D398" s="172"/>
+      <c r="C398" s="160"/>
+      <c r="D398" s="151"/>
       <c r="E398" s="8" t="s">
         <v>509</v>
       </c>
@@ -14646,8 +14671,8 @@
       <c r="B399" s="7">
         <v>19</v>
       </c>
-      <c r="C399" s="157"/>
-      <c r="D399" s="173"/>
+      <c r="C399" s="160"/>
+      <c r="D399" s="152"/>
       <c r="E399" s="8" t="s">
         <v>510</v>
       </c>
@@ -14668,8 +14693,8 @@
       <c r="B400" s="7">
         <v>20</v>
       </c>
-      <c r="C400" s="157"/>
-      <c r="D400" s="171" t="s">
+      <c r="C400" s="160"/>
+      <c r="D400" s="150" t="s">
         <v>511</v>
       </c>
       <c r="E400" s="8" t="s">
@@ -14692,8 +14717,8 @@
       <c r="B401" s="7">
         <v>21</v>
       </c>
-      <c r="C401" s="157"/>
-      <c r="D401" s="172"/>
+      <c r="C401" s="160"/>
+      <c r="D401" s="151"/>
       <c r="E401" s="8" t="s">
         <v>513</v>
       </c>
@@ -14714,8 +14739,8 @@
       <c r="B402" s="7">
         <v>22</v>
       </c>
-      <c r="C402" s="157"/>
-      <c r="D402" s="172"/>
+      <c r="C402" s="160"/>
+      <c r="D402" s="151"/>
       <c r="E402" s="8" t="s">
         <v>514</v>
       </c>
@@ -14736,8 +14761,8 @@
       <c r="B403" s="7">
         <v>23</v>
       </c>
-      <c r="C403" s="157"/>
-      <c r="D403" s="172"/>
+      <c r="C403" s="160"/>
+      <c r="D403" s="151"/>
       <c r="E403" s="8" t="s">
         <v>515</v>
       </c>
@@ -14758,8 +14783,8 @@
       <c r="B404" s="7">
         <v>24</v>
       </c>
-      <c r="C404" s="157"/>
-      <c r="D404" s="173"/>
+      <c r="C404" s="160"/>
+      <c r="D404" s="152"/>
       <c r="E404" s="8" t="s">
         <v>516</v>
       </c>
@@ -14780,8 +14805,8 @@
       <c r="B405" s="7">
         <v>25</v>
       </c>
-      <c r="C405" s="157"/>
-      <c r="D405" s="171" t="s">
+      <c r="C405" s="160"/>
+      <c r="D405" s="150" t="s">
         <v>517</v>
       </c>
       <c r="E405" s="8" t="s">
@@ -14804,8 +14829,8 @@
       <c r="B406" s="7">
         <v>26</v>
       </c>
-      <c r="C406" s="157"/>
-      <c r="D406" s="172"/>
+      <c r="C406" s="160"/>
+      <c r="D406" s="151"/>
       <c r="E406" s="8" t="s">
         <v>519</v>
       </c>
@@ -14826,8 +14851,8 @@
       <c r="B407" s="7">
         <v>27</v>
       </c>
-      <c r="C407" s="157"/>
-      <c r="D407" s="172"/>
+      <c r="C407" s="160"/>
+      <c r="D407" s="151"/>
       <c r="E407" s="8" t="s">
         <v>520</v>
       </c>
@@ -14848,8 +14873,8 @@
       <c r="B408" s="7">
         <v>28</v>
       </c>
-      <c r="C408" s="157"/>
-      <c r="D408" s="172"/>
+      <c r="C408" s="160"/>
+      <c r="D408" s="151"/>
       <c r="E408" s="8" t="s">
         <v>521</v>
       </c>
@@ -14870,8 +14895,8 @@
       <c r="B409" s="7">
         <v>29</v>
       </c>
-      <c r="C409" s="157"/>
-      <c r="D409" s="172"/>
+      <c r="C409" s="160"/>
+      <c r="D409" s="151"/>
       <c r="E409" s="8" t="s">
         <v>522</v>
       </c>
@@ -14892,8 +14917,8 @@
       <c r="B410" s="7">
         <v>30</v>
       </c>
-      <c r="C410" s="157"/>
-      <c r="D410" s="172"/>
+      <c r="C410" s="160"/>
+      <c r="D410" s="151"/>
       <c r="E410" s="8" t="s">
         <v>523</v>
       </c>
@@ -14914,8 +14939,8 @@
       <c r="B411" s="7">
         <v>31</v>
       </c>
-      <c r="C411" s="157"/>
-      <c r="D411" s="172"/>
+      <c r="C411" s="160"/>
+      <c r="D411" s="151"/>
       <c r="E411" s="8" t="s">
         <v>524</v>
       </c>
@@ -14936,8 +14961,8 @@
       <c r="B412" s="7">
         <v>32</v>
       </c>
-      <c r="C412" s="157"/>
-      <c r="D412" s="172"/>
+      <c r="C412" s="160"/>
+      <c r="D412" s="151"/>
       <c r="E412" s="8" t="s">
         <v>525</v>
       </c>
@@ -14958,8 +14983,8 @@
       <c r="B413" s="7">
         <v>33</v>
       </c>
-      <c r="C413" s="157"/>
-      <c r="D413" s="172"/>
+      <c r="C413" s="160"/>
+      <c r="D413" s="151"/>
       <c r="E413" s="8" t="s">
         <v>526</v>
       </c>
@@ -14980,8 +15005,8 @@
       <c r="B414" s="7">
         <v>34</v>
       </c>
-      <c r="C414" s="157"/>
-      <c r="D414" s="172"/>
+      <c r="C414" s="160"/>
+      <c r="D414" s="151"/>
       <c r="E414" s="8" t="s">
         <v>527</v>
       </c>
@@ -15002,8 +15027,8 @@
       <c r="B415" s="7">
         <v>35</v>
       </c>
-      <c r="C415" s="157"/>
-      <c r="D415" s="172"/>
+      <c r="C415" s="160"/>
+      <c r="D415" s="151"/>
       <c r="E415" s="8" t="s">
         <v>528</v>
       </c>
@@ -15024,8 +15049,8 @@
       <c r="B416" s="7">
         <v>36</v>
       </c>
-      <c r="C416" s="157"/>
-      <c r="D416" s="173"/>
+      <c r="C416" s="160"/>
+      <c r="D416" s="152"/>
       <c r="E416" s="8" t="s">
         <v>529</v>
       </c>
@@ -15046,8 +15071,8 @@
       <c r="B417" s="7">
         <v>37</v>
       </c>
-      <c r="C417" s="157"/>
-      <c r="D417" s="171" t="s">
+      <c r="C417" s="160"/>
+      <c r="D417" s="150" t="s">
         <v>530</v>
       </c>
       <c r="E417" s="8" t="s">
@@ -15070,8 +15095,8 @@
       <c r="B418" s="7">
         <v>38</v>
       </c>
-      <c r="C418" s="157"/>
-      <c r="D418" s="172"/>
+      <c r="C418" s="160"/>
+      <c r="D418" s="151"/>
       <c r="E418" s="8" t="s">
         <v>532</v>
       </c>
@@ -15092,8 +15117,8 @@
       <c r="B419" s="7">
         <v>39</v>
       </c>
-      <c r="C419" s="157"/>
-      <c r="D419" s="173"/>
+      <c r="C419" s="160"/>
+      <c r="D419" s="152"/>
       <c r="E419" s="8" t="s">
         <v>533</v>
       </c>
@@ -15114,8 +15139,8 @@
       <c r="B420" s="7">
         <v>40</v>
       </c>
-      <c r="C420" s="157"/>
-      <c r="D420" s="171" t="s">
+      <c r="C420" s="160"/>
+      <c r="D420" s="150" t="s">
         <v>534</v>
       </c>
       <c r="E420" s="8" t="s">
@@ -15138,8 +15163,8 @@
       <c r="B421" s="7">
         <v>41</v>
       </c>
-      <c r="C421" s="157"/>
-      <c r="D421" s="172"/>
+      <c r="C421" s="160"/>
+      <c r="D421" s="151"/>
       <c r="E421" s="8" t="s">
         <v>536</v>
       </c>
@@ -15160,8 +15185,8 @@
       <c r="B422" s="7">
         <v>42</v>
       </c>
-      <c r="C422" s="157"/>
-      <c r="D422" s="172"/>
+      <c r="C422" s="160"/>
+      <c r="D422" s="151"/>
       <c r="E422" s="8" t="s">
         <v>537</v>
       </c>
@@ -15182,8 +15207,8 @@
       <c r="B423" s="7">
         <v>43</v>
       </c>
-      <c r="C423" s="157"/>
-      <c r="D423" s="172"/>
+      <c r="C423" s="160"/>
+      <c r="D423" s="151"/>
       <c r="E423" s="8" t="s">
         <v>538</v>
       </c>
@@ -15204,8 +15229,8 @@
       <c r="B424" s="7">
         <v>44</v>
       </c>
-      <c r="C424" s="157"/>
-      <c r="D424" s="172"/>
+      <c r="C424" s="160"/>
+      <c r="D424" s="151"/>
       <c r="E424" s="8" t="s">
         <v>539</v>
       </c>
@@ -15226,8 +15251,8 @@
       <c r="B425" s="7">
         <v>45</v>
       </c>
-      <c r="C425" s="157"/>
-      <c r="D425" s="172"/>
+      <c r="C425" s="160"/>
+      <c r="D425" s="151"/>
       <c r="E425" s="8" t="s">
         <v>540</v>
       </c>
@@ -15248,8 +15273,8 @@
       <c r="B426" s="7">
         <v>46</v>
       </c>
-      <c r="C426" s="157"/>
-      <c r="D426" s="173"/>
+      <c r="C426" s="160"/>
+      <c r="D426" s="152"/>
       <c r="E426" s="8" t="s">
         <v>541</v>
       </c>
@@ -15270,8 +15295,8 @@
       <c r="B427" s="7">
         <v>47</v>
       </c>
-      <c r="C427" s="157"/>
-      <c r="D427" s="171" t="s">
+      <c r="C427" s="160"/>
+      <c r="D427" s="150" t="s">
         <v>542</v>
       </c>
       <c r="E427" s="8" t="s">
@@ -15292,8 +15317,8 @@
       <c r="B428" s="7">
         <v>48</v>
       </c>
-      <c r="C428" s="157"/>
-      <c r="D428" s="172"/>
+      <c r="C428" s="160"/>
+      <c r="D428" s="151"/>
       <c r="E428" s="8" t="s">
         <v>544</v>
       </c>
@@ -15314,8 +15339,8 @@
       <c r="B429" s="7">
         <v>49</v>
       </c>
-      <c r="C429" s="157"/>
-      <c r="D429" s="172"/>
+      <c r="C429" s="160"/>
+      <c r="D429" s="151"/>
       <c r="E429" s="8" t="s">
         <v>545</v>
       </c>
@@ -15336,8 +15361,8 @@
       <c r="B430" s="7">
         <v>50</v>
       </c>
-      <c r="C430" s="157"/>
-      <c r="D430" s="173"/>
+      <c r="C430" s="160"/>
+      <c r="D430" s="152"/>
       <c r="E430" s="8" t="s">
         <v>546</v>
       </c>
@@ -15358,8 +15383,8 @@
       <c r="B431" s="7">
         <v>51</v>
       </c>
-      <c r="C431" s="157"/>
-      <c r="D431" s="171" t="s">
+      <c r="C431" s="160"/>
+      <c r="D431" s="150" t="s">
         <v>547</v>
       </c>
       <c r="E431" s="8" t="s">
@@ -15382,8 +15407,8 @@
       <c r="B432" s="7">
         <v>52</v>
       </c>
-      <c r="C432" s="157"/>
-      <c r="D432" s="172"/>
+      <c r="C432" s="160"/>
+      <c r="D432" s="151"/>
       <c r="E432" s="8" t="s">
         <v>549</v>
       </c>
@@ -15404,8 +15429,8 @@
       <c r="B433" s="7">
         <v>53</v>
       </c>
-      <c r="C433" s="157"/>
-      <c r="D433" s="172"/>
+      <c r="C433" s="160"/>
+      <c r="D433" s="151"/>
       <c r="E433" s="8" t="s">
         <v>550</v>
       </c>
@@ -15426,8 +15451,8 @@
       <c r="B434" s="7">
         <v>54</v>
       </c>
-      <c r="C434" s="157"/>
-      <c r="D434" s="172"/>
+      <c r="C434" s="160"/>
+      <c r="D434" s="151"/>
       <c r="E434" s="8" t="s">
         <v>551</v>
       </c>
@@ -15448,8 +15473,8 @@
       <c r="B435" s="7">
         <v>55</v>
       </c>
-      <c r="C435" s="158"/>
-      <c r="D435" s="173"/>
+      <c r="C435" s="161"/>
+      <c r="D435" s="152"/>
       <c r="E435" s="8" t="s">
         <v>552</v>
       </c>
@@ -15464,18 +15489,18 @@
       <c r="J435" s="11"/>
     </row>
     <row r="436" spans="1:10" ht="13.8">
-      <c r="A436" s="177" t="s">
+      <c r="A436" s="192" t="s">
         <v>553</v>
       </c>
-      <c r="B436" s="178"/>
-      <c r="C436" s="178"/>
-      <c r="D436" s="178"/>
-      <c r="E436" s="178"/>
-      <c r="F436" s="178"/>
-      <c r="G436" s="178"/>
-      <c r="H436" s="178"/>
-      <c r="I436" s="178"/>
-      <c r="J436" s="179"/>
+      <c r="B436" s="193"/>
+      <c r="C436" s="193"/>
+      <c r="D436" s="193"/>
+      <c r="E436" s="193"/>
+      <c r="F436" s="193"/>
+      <c r="G436" s="193"/>
+      <c r="H436" s="193"/>
+      <c r="I436" s="193"/>
+      <c r="J436" s="194"/>
     </row>
     <row r="437" spans="1:10" ht="13.8">
       <c r="A437" s="6">
@@ -15484,10 +15509,10 @@
       <c r="B437" s="7">
         <v>1</v>
       </c>
-      <c r="C437" s="159" t="s">
+      <c r="C437" s="162" t="s">
         <v>554</v>
       </c>
-      <c r="D437" s="171" t="s">
+      <c r="D437" s="150" t="s">
         <v>555</v>
       </c>
       <c r="E437" s="29" t="s">
@@ -15510,8 +15535,8 @@
       <c r="B438" s="7">
         <v>2</v>
       </c>
-      <c r="C438" s="160"/>
-      <c r="D438" s="172"/>
+      <c r="C438" s="163"/>
+      <c r="D438" s="151"/>
       <c r="E438" s="8" t="s">
         <v>557</v>
       </c>
@@ -15530,8 +15555,8 @@
       <c r="B439" s="7">
         <v>3</v>
       </c>
-      <c r="C439" s="160"/>
-      <c r="D439" s="172"/>
+      <c r="C439" s="163"/>
+      <c r="D439" s="151"/>
       <c r="E439" s="8" t="s">
         <v>558</v>
       </c>
@@ -15552,8 +15577,8 @@
       <c r="B440" s="7">
         <v>4</v>
       </c>
-      <c r="C440" s="160"/>
-      <c r="D440" s="172"/>
+      <c r="C440" s="163"/>
+      <c r="D440" s="151"/>
       <c r="E440" s="29" t="s">
         <v>559</v>
       </c>
@@ -15574,8 +15599,8 @@
       <c r="B441" s="7">
         <v>5</v>
       </c>
-      <c r="C441" s="160"/>
-      <c r="D441" s="173"/>
+      <c r="C441" s="163"/>
+      <c r="D441" s="152"/>
       <c r="E441" s="8" t="s">
         <v>560</v>
       </c>
@@ -15596,8 +15621,8 @@
       <c r="B442" s="7">
         <v>6</v>
       </c>
-      <c r="C442" s="160"/>
-      <c r="D442" s="171" t="s">
+      <c r="C442" s="163"/>
+      <c r="D442" s="150" t="s">
         <v>561</v>
       </c>
       <c r="E442" s="29" t="s">
@@ -15620,8 +15645,8 @@
       <c r="B443" s="7">
         <v>7</v>
       </c>
-      <c r="C443" s="160"/>
-      <c r="D443" s="172"/>
+      <c r="C443" s="163"/>
+      <c r="D443" s="151"/>
       <c r="E443" s="8" t="s">
         <v>563</v>
       </c>
@@ -15642,8 +15667,8 @@
       <c r="B444" s="7">
         <v>8</v>
       </c>
-      <c r="C444" s="160"/>
-      <c r="D444" s="172"/>
+      <c r="C444" s="163"/>
+      <c r="D444" s="151"/>
       <c r="E444" s="29" t="s">
         <v>564</v>
       </c>
@@ -15664,8 +15689,8 @@
       <c r="B445" s="7">
         <v>9</v>
       </c>
-      <c r="C445" s="160"/>
-      <c r="D445" s="173"/>
+      <c r="C445" s="163"/>
+      <c r="D445" s="152"/>
       <c r="E445" s="8" t="s">
         <v>565</v>
       </c>
@@ -15686,8 +15711,8 @@
       <c r="B446" s="7">
         <v>10</v>
       </c>
-      <c r="C446" s="160"/>
-      <c r="D446" s="171" t="s">
+      <c r="C446" s="163"/>
+      <c r="D446" s="150" t="s">
         <v>566</v>
       </c>
       <c r="E446" s="8" t="s">
@@ -15710,8 +15735,8 @@
       <c r="B447" s="7">
         <v>11</v>
       </c>
-      <c r="C447" s="160"/>
-      <c r="D447" s="172"/>
+      <c r="C447" s="163"/>
+      <c r="D447" s="151"/>
       <c r="E447" s="8" t="s">
         <v>568</v>
       </c>
@@ -15732,8 +15757,8 @@
       <c r="B448" s="7">
         <v>12</v>
       </c>
-      <c r="C448" s="160"/>
-      <c r="D448" s="173"/>
+      <c r="C448" s="163"/>
+      <c r="D448" s="152"/>
       <c r="E448" s="8" t="s">
         <v>569</v>
       </c>
@@ -15754,8 +15779,8 @@
       <c r="B449" s="7">
         <v>13</v>
       </c>
-      <c r="C449" s="160"/>
-      <c r="D449" s="171" t="s">
+      <c r="C449" s="163"/>
+      <c r="D449" s="150" t="s">
         <v>570</v>
       </c>
       <c r="E449" s="8" t="s">
@@ -15778,8 +15803,8 @@
       <c r="B450" s="7">
         <v>14</v>
       </c>
-      <c r="C450" s="160"/>
-      <c r="D450" s="172"/>
+      <c r="C450" s="163"/>
+      <c r="D450" s="151"/>
       <c r="E450" s="29" t="s">
         <v>572</v>
       </c>
@@ -15800,8 +15825,8 @@
       <c r="B451" s="7">
         <v>15</v>
       </c>
-      <c r="C451" s="160"/>
-      <c r="D451" s="172"/>
+      <c r="C451" s="163"/>
+      <c r="D451" s="151"/>
       <c r="E451" s="8" t="s">
         <v>573</v>
       </c>
@@ -15822,8 +15847,8 @@
       <c r="B452" s="7">
         <v>16</v>
       </c>
-      <c r="C452" s="160"/>
-      <c r="D452" s="173"/>
+      <c r="C452" s="163"/>
+      <c r="D452" s="152"/>
       <c r="E452" s="8" t="s">
         <v>574</v>
       </c>
@@ -15844,8 +15869,8 @@
       <c r="B453" s="7">
         <v>17</v>
       </c>
-      <c r="C453" s="160"/>
-      <c r="D453" s="171" t="s">
+      <c r="C453" s="163"/>
+      <c r="D453" s="150" t="s">
         <v>575</v>
       </c>
       <c r="E453" s="8" t="s">
@@ -15868,8 +15893,8 @@
       <c r="B454" s="7">
         <v>18</v>
       </c>
-      <c r="C454" s="160"/>
-      <c r="D454" s="172"/>
+      <c r="C454" s="163"/>
+      <c r="D454" s="151"/>
       <c r="E454" s="8" t="s">
         <v>577</v>
       </c>
@@ -15890,8 +15915,8 @@
       <c r="B455" s="7">
         <v>19</v>
       </c>
-      <c r="C455" s="160"/>
-      <c r="D455" s="172"/>
+      <c r="C455" s="163"/>
+      <c r="D455" s="151"/>
       <c r="E455" s="8" t="s">
         <v>578</v>
       </c>
@@ -15912,8 +15937,8 @@
       <c r="B456" s="7">
         <v>20</v>
       </c>
-      <c r="C456" s="160"/>
-      <c r="D456" s="172"/>
+      <c r="C456" s="163"/>
+      <c r="D456" s="151"/>
       <c r="E456" s="39" t="s">
         <v>579</v>
       </c>
@@ -15934,8 +15959,8 @@
       <c r="B457" s="7">
         <v>21</v>
       </c>
-      <c r="C457" s="160"/>
-      <c r="D457" s="172"/>
+      <c r="C457" s="163"/>
+      <c r="D457" s="151"/>
       <c r="E457" s="8" t="s">
         <v>580</v>
       </c>
@@ -15956,8 +15981,8 @@
       <c r="B458" s="24">
         <v>22</v>
       </c>
-      <c r="C458" s="161"/>
-      <c r="D458" s="173"/>
+      <c r="C458" s="164"/>
+      <c r="D458" s="152"/>
       <c r="E458" s="17" t="s">
         <v>581</v>
       </c>
@@ -15979,10 +16004,10 @@
       <c r="B459" s="7">
         <v>1</v>
       </c>
-      <c r="C459" s="150" t="s">
+      <c r="C459" s="165" t="s">
         <v>582</v>
       </c>
-      <c r="D459" s="171" t="s">
+      <c r="D459" s="150" t="s">
         <v>583</v>
       </c>
       <c r="E459" s="8" t="s">
@@ -16005,8 +16030,8 @@
       <c r="B460" s="7">
         <v>2</v>
       </c>
-      <c r="C460" s="151"/>
-      <c r="D460" s="172"/>
+      <c r="C460" s="166"/>
+      <c r="D460" s="151"/>
       <c r="E460" s="8" t="s">
         <v>584</v>
       </c>
@@ -16027,8 +16052,8 @@
       <c r="B461" s="7">
         <v>3</v>
       </c>
-      <c r="C461" s="151"/>
-      <c r="D461" s="172"/>
+      <c r="C461" s="166"/>
+      <c r="D461" s="151"/>
       <c r="E461" s="8" t="s">
         <v>585</v>
       </c>
@@ -16049,8 +16074,8 @@
       <c r="B462" s="7">
         <v>4</v>
       </c>
-      <c r="C462" s="151"/>
-      <c r="D462" s="172"/>
+      <c r="C462" s="166"/>
+      <c r="D462" s="151"/>
       <c r="E462" s="8" t="s">
         <v>586</v>
       </c>
@@ -16071,8 +16096,8 @@
       <c r="B463" s="7">
         <v>5</v>
       </c>
-      <c r="C463" s="151"/>
-      <c r="D463" s="172"/>
+      <c r="C463" s="166"/>
+      <c r="D463" s="151"/>
       <c r="E463" s="8" t="s">
         <v>587</v>
       </c>
@@ -16093,8 +16118,8 @@
       <c r="B464" s="7">
         <v>6</v>
       </c>
-      <c r="C464" s="151"/>
-      <c r="D464" s="172"/>
+      <c r="C464" s="166"/>
+      <c r="D464" s="151"/>
       <c r="E464" s="8" t="s">
         <v>588</v>
       </c>
@@ -16115,8 +16140,8 @@
       <c r="B465" s="7">
         <v>7</v>
       </c>
-      <c r="C465" s="151"/>
-      <c r="D465" s="172"/>
+      <c r="C465" s="166"/>
+      <c r="D465" s="151"/>
       <c r="E465" s="8" t="s">
         <v>589</v>
       </c>
@@ -16137,8 +16162,8 @@
       <c r="B466" s="7">
         <v>8</v>
       </c>
-      <c r="C466" s="151"/>
-      <c r="D466" s="173"/>
+      <c r="C466" s="166"/>
+      <c r="D466" s="152"/>
       <c r="E466" s="8" t="s">
         <v>590</v>
       </c>
@@ -16159,8 +16184,8 @@
       <c r="B467" s="7">
         <v>9</v>
       </c>
-      <c r="C467" s="151"/>
-      <c r="D467" s="171" t="s">
+      <c r="C467" s="166"/>
+      <c r="D467" s="150" t="s">
         <v>591</v>
       </c>
       <c r="E467" s="8" t="s">
@@ -16183,8 +16208,8 @@
       <c r="B468" s="7">
         <v>10</v>
       </c>
-      <c r="C468" s="151"/>
-      <c r="D468" s="172"/>
+      <c r="C468" s="166"/>
+      <c r="D468" s="151"/>
       <c r="E468" s="8" t="s">
         <v>593</v>
       </c>
@@ -16205,8 +16230,8 @@
       <c r="B469" s="7">
         <v>11</v>
       </c>
-      <c r="C469" s="151"/>
-      <c r="D469" s="172"/>
+      <c r="C469" s="166"/>
+      <c r="D469" s="151"/>
       <c r="E469" s="8" t="s">
         <v>594</v>
       </c>
@@ -16227,8 +16252,8 @@
       <c r="B470" s="7">
         <v>12</v>
       </c>
-      <c r="C470" s="151"/>
-      <c r="D470" s="172"/>
+      <c r="C470" s="166"/>
+      <c r="D470" s="151"/>
       <c r="E470" s="8" t="s">
         <v>595</v>
       </c>
@@ -16249,8 +16274,8 @@
       <c r="B471" s="7">
         <v>13</v>
       </c>
-      <c r="C471" s="151"/>
-      <c r="D471" s="172"/>
+      <c r="C471" s="166"/>
+      <c r="D471" s="151"/>
       <c r="E471" s="8" t="s">
         <v>596</v>
       </c>
@@ -16271,8 +16296,8 @@
       <c r="B472" s="7">
         <v>14</v>
       </c>
-      <c r="C472" s="151"/>
-      <c r="D472" s="172"/>
+      <c r="C472" s="166"/>
+      <c r="D472" s="151"/>
       <c r="E472" s="8" t="s">
         <v>597</v>
       </c>
@@ -16293,8 +16318,8 @@
       <c r="B473" s="7">
         <v>15</v>
       </c>
-      <c r="C473" s="151"/>
-      <c r="D473" s="173"/>
+      <c r="C473" s="166"/>
+      <c r="D473" s="152"/>
       <c r="E473" s="8" t="s">
         <v>598</v>
       </c>
@@ -16315,8 +16340,8 @@
       <c r="B474" s="7">
         <v>16</v>
       </c>
-      <c r="C474" s="151"/>
-      <c r="D474" s="171" t="s">
+      <c r="C474" s="166"/>
+      <c r="D474" s="150" t="s">
         <v>599</v>
       </c>
       <c r="E474" s="8" t="s">
@@ -16339,8 +16364,8 @@
       <c r="B475" s="7">
         <v>17</v>
       </c>
-      <c r="C475" s="151"/>
-      <c r="D475" s="172"/>
+      <c r="C475" s="166"/>
+      <c r="D475" s="151"/>
       <c r="E475" s="8" t="s">
         <v>601</v>
       </c>
@@ -16361,8 +16386,8 @@
       <c r="B476" s="7">
         <v>18</v>
       </c>
-      <c r="C476" s="151"/>
-      <c r="D476" s="172"/>
+      <c r="C476" s="166"/>
+      <c r="D476" s="151"/>
       <c r="E476" s="8" t="s">
         <v>602</v>
       </c>
@@ -16383,8 +16408,8 @@
       <c r="B477" s="7">
         <v>19</v>
       </c>
-      <c r="C477" s="151"/>
-      <c r="D477" s="172"/>
+      <c r="C477" s="166"/>
+      <c r="D477" s="151"/>
       <c r="E477" s="8" t="s">
         <v>603</v>
       </c>
@@ -16405,8 +16430,8 @@
       <c r="B478" s="7">
         <v>20</v>
       </c>
-      <c r="C478" s="151"/>
-      <c r="D478" s="172"/>
+      <c r="C478" s="166"/>
+      <c r="D478" s="151"/>
       <c r="E478" s="8" t="s">
         <v>604</v>
       </c>
@@ -16427,8 +16452,8 @@
       <c r="B479" s="7">
         <v>21</v>
       </c>
-      <c r="C479" s="151"/>
-      <c r="D479" s="172"/>
+      <c r="C479" s="166"/>
+      <c r="D479" s="151"/>
       <c r="E479" s="8" t="s">
         <v>605</v>
       </c>
@@ -16449,8 +16474,8 @@
       <c r="B480" s="7">
         <v>22</v>
       </c>
-      <c r="C480" s="151"/>
-      <c r="D480" s="172"/>
+      <c r="C480" s="166"/>
+      <c r="D480" s="151"/>
       <c r="E480" s="8" t="s">
         <v>606</v>
       </c>
@@ -16471,8 +16496,8 @@
       <c r="B481" s="7">
         <v>23</v>
       </c>
-      <c r="C481" s="151"/>
-      <c r="D481" s="173"/>
+      <c r="C481" s="166"/>
+      <c r="D481" s="152"/>
       <c r="E481" s="8" t="s">
         <v>607</v>
       </c>
@@ -16493,8 +16518,8 @@
       <c r="B482" s="7">
         <v>24</v>
       </c>
-      <c r="C482" s="151"/>
-      <c r="D482" s="171" t="s">
+      <c r="C482" s="166"/>
+      <c r="D482" s="150" t="s">
         <v>608</v>
       </c>
       <c r="E482" s="8" t="s">
@@ -16517,8 +16542,8 @@
       <c r="B483" s="7">
         <v>25</v>
       </c>
-      <c r="C483" s="151"/>
-      <c r="D483" s="172"/>
+      <c r="C483" s="166"/>
+      <c r="D483" s="151"/>
       <c r="E483" s="8" t="s">
         <v>610</v>
       </c>
@@ -16539,8 +16564,8 @@
       <c r="B484" s="7">
         <v>26</v>
       </c>
-      <c r="C484" s="151"/>
-      <c r="D484" s="172"/>
+      <c r="C484" s="166"/>
+      <c r="D484" s="151"/>
       <c r="E484" s="8" t="s">
         <v>611</v>
       </c>
@@ -16561,8 +16586,8 @@
       <c r="B485" s="7">
         <v>27</v>
       </c>
-      <c r="C485" s="151"/>
-      <c r="D485" s="173"/>
+      <c r="C485" s="166"/>
+      <c r="D485" s="152"/>
       <c r="E485" s="8" t="s">
         <v>612</v>
       </c>
@@ -16583,8 +16608,8 @@
       <c r="B486" s="7">
         <v>28</v>
       </c>
-      <c r="C486" s="151"/>
-      <c r="D486" s="171" t="s">
+      <c r="C486" s="166"/>
+      <c r="D486" s="150" t="s">
         <v>613</v>
       </c>
       <c r="E486" s="8" t="s">
@@ -16607,8 +16632,8 @@
       <c r="B487" s="7">
         <v>29</v>
       </c>
-      <c r="C487" s="151"/>
-      <c r="D487" s="172"/>
+      <c r="C487" s="166"/>
+      <c r="D487" s="151"/>
       <c r="E487" s="8" t="s">
         <v>615</v>
       </c>
@@ -16629,8 +16654,8 @@
       <c r="B488" s="7">
         <v>30</v>
       </c>
-      <c r="C488" s="151"/>
-      <c r="D488" s="172"/>
+      <c r="C488" s="166"/>
+      <c r="D488" s="151"/>
       <c r="E488" s="8" t="s">
         <v>616</v>
       </c>
@@ -16651,8 +16676,8 @@
       <c r="B489" s="7">
         <v>31</v>
       </c>
-      <c r="C489" s="151"/>
-      <c r="D489" s="172"/>
+      <c r="C489" s="166"/>
+      <c r="D489" s="151"/>
       <c r="E489" s="8" t="s">
         <v>617</v>
       </c>
@@ -16673,8 +16698,8 @@
       <c r="B490" s="7">
         <v>32</v>
       </c>
-      <c r="C490" s="151"/>
-      <c r="D490" s="172"/>
+      <c r="C490" s="166"/>
+      <c r="D490" s="151"/>
       <c r="E490" s="8" t="s">
         <v>618</v>
       </c>
@@ -16695,8 +16720,8 @@
       <c r="B491" s="7">
         <v>33</v>
       </c>
-      <c r="C491" s="151"/>
-      <c r="D491" s="172"/>
+      <c r="C491" s="166"/>
+      <c r="D491" s="151"/>
       <c r="E491" s="8" t="s">
         <v>619</v>
       </c>
@@ -16717,8 +16742,8 @@
       <c r="B492" s="7">
         <v>34</v>
       </c>
-      <c r="C492" s="151"/>
-      <c r="D492" s="172"/>
+      <c r="C492" s="166"/>
+      <c r="D492" s="151"/>
       <c r="E492" s="8" t="s">
         <v>620</v>
       </c>
@@ -16739,8 +16764,8 @@
       <c r="B493" s="7">
         <v>35</v>
       </c>
-      <c r="C493" s="151"/>
-      <c r="D493" s="172"/>
+      <c r="C493" s="166"/>
+      <c r="D493" s="151"/>
       <c r="E493" s="8" t="s">
         <v>621</v>
       </c>
@@ -16761,8 +16786,8 @@
       <c r="B494" s="7">
         <v>36</v>
       </c>
-      <c r="C494" s="151"/>
-      <c r="D494" s="172"/>
+      <c r="C494" s="166"/>
+      <c r="D494" s="151"/>
       <c r="E494" s="8" t="s">
         <v>622</v>
       </c>
@@ -16783,8 +16808,8 @@
       <c r="B495" s="7">
         <v>37</v>
       </c>
-      <c r="C495" s="151"/>
-      <c r="D495" s="172"/>
+      <c r="C495" s="166"/>
+      <c r="D495" s="151"/>
       <c r="E495" s="8" t="s">
         <v>623</v>
       </c>
@@ -16805,8 +16830,8 @@
       <c r="B496" s="7">
         <v>38</v>
       </c>
-      <c r="C496" s="151"/>
-      <c r="D496" s="173"/>
+      <c r="C496" s="166"/>
+      <c r="D496" s="152"/>
       <c r="E496" s="8" t="s">
         <v>624</v>
       </c>
@@ -16827,8 +16852,8 @@
       <c r="B497" s="7">
         <v>39</v>
       </c>
-      <c r="C497" s="151"/>
-      <c r="D497" s="171" t="s">
+      <c r="C497" s="166"/>
+      <c r="D497" s="150" t="s">
         <v>625</v>
       </c>
       <c r="E497" s="8" t="s">
@@ -16851,8 +16876,8 @@
       <c r="B498" s="7">
         <v>40</v>
       </c>
-      <c r="C498" s="151"/>
-      <c r="D498" s="172"/>
+      <c r="C498" s="166"/>
+      <c r="D498" s="151"/>
       <c r="E498" s="8" t="s">
         <v>626</v>
       </c>
@@ -16873,8 +16898,8 @@
       <c r="B499" s="7">
         <v>41</v>
       </c>
-      <c r="C499" s="151"/>
-      <c r="D499" s="172"/>
+      <c r="C499" s="166"/>
+      <c r="D499" s="151"/>
       <c r="E499" s="8" t="s">
         <v>627</v>
       </c>
@@ -16895,8 +16920,8 @@
       <c r="B500" s="7">
         <v>42</v>
       </c>
-      <c r="C500" s="151"/>
-      <c r="D500" s="172"/>
+      <c r="C500" s="166"/>
+      <c r="D500" s="151"/>
       <c r="E500" s="8" t="s">
         <v>628</v>
       </c>
@@ -16917,8 +16942,8 @@
       <c r="B501" s="7">
         <v>43</v>
       </c>
-      <c r="C501" s="151"/>
-      <c r="D501" s="172"/>
+      <c r="C501" s="166"/>
+      <c r="D501" s="151"/>
       <c r="E501" s="8" t="s">
         <v>629</v>
       </c>
@@ -16939,8 +16964,8 @@
       <c r="B502" s="7">
         <v>44</v>
       </c>
-      <c r="C502" s="151"/>
-      <c r="D502" s="173"/>
+      <c r="C502" s="166"/>
+      <c r="D502" s="152"/>
       <c r="E502" s="8" t="s">
         <v>630</v>
       </c>
@@ -16961,8 +16986,8 @@
       <c r="B503" s="7">
         <v>45</v>
       </c>
-      <c r="C503" s="151"/>
-      <c r="D503" s="171" t="s">
+      <c r="C503" s="166"/>
+      <c r="D503" s="150" t="s">
         <v>631</v>
       </c>
       <c r="E503" s="8" t="s">
@@ -16985,8 +17010,8 @@
       <c r="B504" s="7">
         <v>46</v>
       </c>
-      <c r="C504" s="151"/>
-      <c r="D504" s="172"/>
+      <c r="C504" s="166"/>
+      <c r="D504" s="151"/>
       <c r="E504" s="8" t="s">
         <v>633</v>
       </c>
@@ -17007,8 +17032,8 @@
       <c r="B505" s="7">
         <v>47</v>
       </c>
-      <c r="C505" s="151"/>
-      <c r="D505" s="172"/>
+      <c r="C505" s="166"/>
+      <c r="D505" s="151"/>
       <c r="E505" s="8" t="s">
         <v>634</v>
       </c>
@@ -17029,8 +17054,8 @@
       <c r="B506" s="7">
         <v>48</v>
       </c>
-      <c r="C506" s="151"/>
-      <c r="D506" s="172"/>
+      <c r="C506" s="166"/>
+      <c r="D506" s="151"/>
       <c r="E506" s="8" t="s">
         <v>635</v>
       </c>
@@ -17051,8 +17076,8 @@
       <c r="B507" s="7">
         <v>49</v>
       </c>
-      <c r="C507" s="151"/>
-      <c r="D507" s="172"/>
+      <c r="C507" s="166"/>
+      <c r="D507" s="151"/>
       <c r="E507" s="8" t="s">
         <v>636</v>
       </c>
@@ -17073,8 +17098,8 @@
       <c r="B508" s="7">
         <v>50</v>
       </c>
-      <c r="C508" s="151"/>
-      <c r="D508" s="172"/>
+      <c r="C508" s="166"/>
+      <c r="D508" s="151"/>
       <c r="E508" s="8" t="s">
         <v>637</v>
       </c>
@@ -17095,8 +17120,8 @@
       <c r="B509" s="7">
         <v>51</v>
       </c>
-      <c r="C509" s="151"/>
-      <c r="D509" s="173"/>
+      <c r="C509" s="166"/>
+      <c r="D509" s="152"/>
       <c r="E509" s="8" t="s">
         <v>638</v>
       </c>
@@ -17117,8 +17142,8 @@
       <c r="B510" s="7">
         <v>52</v>
       </c>
-      <c r="C510" s="151"/>
-      <c r="D510" s="171" t="s">
+      <c r="C510" s="166"/>
+      <c r="D510" s="150" t="s">
         <v>639</v>
       </c>
       <c r="E510" s="8" t="s">
@@ -17141,8 +17166,8 @@
       <c r="B511" s="7">
         <v>53</v>
       </c>
-      <c r="C511" s="151"/>
-      <c r="D511" s="172"/>
+      <c r="C511" s="166"/>
+      <c r="D511" s="151"/>
       <c r="E511" s="8" t="s">
         <v>641</v>
       </c>
@@ -17163,8 +17188,8 @@
       <c r="B512" s="7">
         <v>54</v>
       </c>
-      <c r="C512" s="151"/>
-      <c r="D512" s="172"/>
+      <c r="C512" s="166"/>
+      <c r="D512" s="151"/>
       <c r="E512" s="8" t="s">
         <v>642</v>
       </c>
@@ -17185,8 +17210,8 @@
       <c r="B513" s="24">
         <v>55</v>
       </c>
-      <c r="C513" s="152"/>
-      <c r="D513" s="173"/>
+      <c r="C513" s="167"/>
+      <c r="D513" s="152"/>
       <c r="E513" s="17" t="s">
         <v>643</v>
       </c>
@@ -24120,47 +24145,66 @@
     </row>
   </sheetData>
   <mergeCells count="125">
-    <mergeCell ref="D26:D32"/>
-    <mergeCell ref="D33:D36"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="C4:C32"/>
-    <mergeCell ref="D4:D9"/>
-    <mergeCell ref="D10:D18"/>
-    <mergeCell ref="D19:D25"/>
-    <mergeCell ref="C33:C44"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="D40:D44"/>
-    <mergeCell ref="C107:C116"/>
-    <mergeCell ref="C117:C125"/>
-    <mergeCell ref="C127:C132"/>
-    <mergeCell ref="C134:C176"/>
-    <mergeCell ref="C177:C204"/>
-    <mergeCell ref="C205:C214"/>
-    <mergeCell ref="A106:J106"/>
-    <mergeCell ref="D107:D111"/>
-    <mergeCell ref="D112:D115"/>
-    <mergeCell ref="D117:D120"/>
-    <mergeCell ref="D121:D122"/>
-    <mergeCell ref="D123:D125"/>
-    <mergeCell ref="A126:J126"/>
-    <mergeCell ref="D127:D130"/>
-    <mergeCell ref="D131:D132"/>
-    <mergeCell ref="A133:J133"/>
-    <mergeCell ref="D210:D211"/>
-    <mergeCell ref="D212:D214"/>
-    <mergeCell ref="C45:C50"/>
-    <mergeCell ref="D45:D50"/>
-    <mergeCell ref="D51:D57"/>
-    <mergeCell ref="D58:D63"/>
-    <mergeCell ref="D64:D67"/>
-    <mergeCell ref="D69:D78"/>
-    <mergeCell ref="D79:D84"/>
-    <mergeCell ref="D85:D90"/>
-    <mergeCell ref="D91:D105"/>
-    <mergeCell ref="A68:J68"/>
-    <mergeCell ref="C51:C67"/>
-    <mergeCell ref="C69:C105"/>
+    <mergeCell ref="C459:C513"/>
+    <mergeCell ref="C216:C249"/>
+    <mergeCell ref="C250:C265"/>
+    <mergeCell ref="C266:C272"/>
+    <mergeCell ref="C274:C292"/>
+    <mergeCell ref="C293:C307"/>
+    <mergeCell ref="C308:C317"/>
+    <mergeCell ref="C318:C342"/>
+    <mergeCell ref="D459:D466"/>
+    <mergeCell ref="D467:D473"/>
+    <mergeCell ref="D474:D481"/>
+    <mergeCell ref="D482:D485"/>
+    <mergeCell ref="D486:D496"/>
+    <mergeCell ref="D497:D502"/>
+    <mergeCell ref="D503:D509"/>
+    <mergeCell ref="D510:D513"/>
+    <mergeCell ref="D318:D323"/>
+    <mergeCell ref="D324:D328"/>
+    <mergeCell ref="D329:D337"/>
+    <mergeCell ref="D338:D342"/>
+    <mergeCell ref="D343:D347"/>
+    <mergeCell ref="D348:D353"/>
+    <mergeCell ref="D354:D357"/>
+    <mergeCell ref="D296:D300"/>
+    <mergeCell ref="D301:D303"/>
+    <mergeCell ref="D304:D307"/>
+    <mergeCell ref="D308:D314"/>
+    <mergeCell ref="D315:D317"/>
+    <mergeCell ref="C343:C357"/>
+    <mergeCell ref="C359:C380"/>
+    <mergeCell ref="C381:C435"/>
+    <mergeCell ref="C437:C458"/>
+    <mergeCell ref="D250:D257"/>
+    <mergeCell ref="D258:D259"/>
+    <mergeCell ref="D260:D265"/>
+    <mergeCell ref="D266:D270"/>
+    <mergeCell ref="D271:D272"/>
+    <mergeCell ref="D274:D281"/>
+    <mergeCell ref="D282:D288"/>
+    <mergeCell ref="D289:D292"/>
+    <mergeCell ref="D293:D295"/>
+    <mergeCell ref="D449:D452"/>
+    <mergeCell ref="D453:D458"/>
+    <mergeCell ref="D417:D419"/>
+    <mergeCell ref="D420:D426"/>
+    <mergeCell ref="D427:D430"/>
+    <mergeCell ref="D431:D435"/>
+    <mergeCell ref="D437:D441"/>
+    <mergeCell ref="D442:D445"/>
+    <mergeCell ref="D446:D448"/>
+    <mergeCell ref="D400:D404"/>
+    <mergeCell ref="D405:D416"/>
+    <mergeCell ref="A436:J436"/>
+    <mergeCell ref="D359:D363"/>
+    <mergeCell ref="D364:D371"/>
+    <mergeCell ref="D372:D375"/>
+    <mergeCell ref="D376:D380"/>
+    <mergeCell ref="D381:D386"/>
+    <mergeCell ref="D387:D396"/>
+    <mergeCell ref="D397:D399"/>
     <mergeCell ref="A215:J215"/>
     <mergeCell ref="A273:J273"/>
     <mergeCell ref="A358:J358"/>
@@ -24185,66 +24229,47 @@
     <mergeCell ref="D234:D240"/>
     <mergeCell ref="D241:D243"/>
     <mergeCell ref="D244:D249"/>
-    <mergeCell ref="D442:D445"/>
-    <mergeCell ref="D446:D448"/>
-    <mergeCell ref="D400:D404"/>
-    <mergeCell ref="D405:D416"/>
-    <mergeCell ref="A436:J436"/>
-    <mergeCell ref="D359:D363"/>
-    <mergeCell ref="D364:D371"/>
-    <mergeCell ref="D372:D375"/>
-    <mergeCell ref="D376:D380"/>
-    <mergeCell ref="D381:D386"/>
-    <mergeCell ref="D387:D396"/>
-    <mergeCell ref="D397:D399"/>
-    <mergeCell ref="D301:D303"/>
-    <mergeCell ref="D304:D307"/>
-    <mergeCell ref="D308:D314"/>
-    <mergeCell ref="D315:D317"/>
-    <mergeCell ref="C343:C357"/>
-    <mergeCell ref="C359:C380"/>
-    <mergeCell ref="C381:C435"/>
-    <mergeCell ref="C437:C458"/>
-    <mergeCell ref="D250:D257"/>
-    <mergeCell ref="D258:D259"/>
-    <mergeCell ref="D260:D265"/>
-    <mergeCell ref="D266:D270"/>
-    <mergeCell ref="D271:D272"/>
-    <mergeCell ref="D274:D281"/>
-    <mergeCell ref="D282:D288"/>
-    <mergeCell ref="D289:D292"/>
-    <mergeCell ref="D293:D295"/>
-    <mergeCell ref="D449:D452"/>
-    <mergeCell ref="D453:D458"/>
-    <mergeCell ref="D417:D419"/>
-    <mergeCell ref="D420:D426"/>
-    <mergeCell ref="D427:D430"/>
-    <mergeCell ref="D431:D435"/>
-    <mergeCell ref="D437:D441"/>
-    <mergeCell ref="C459:C513"/>
-    <mergeCell ref="C216:C249"/>
-    <mergeCell ref="C250:C265"/>
-    <mergeCell ref="C266:C272"/>
-    <mergeCell ref="C274:C292"/>
-    <mergeCell ref="C293:C307"/>
-    <mergeCell ref="C308:C317"/>
-    <mergeCell ref="C318:C342"/>
-    <mergeCell ref="D459:D466"/>
-    <mergeCell ref="D467:D473"/>
-    <mergeCell ref="D474:D481"/>
-    <mergeCell ref="D482:D485"/>
-    <mergeCell ref="D486:D496"/>
-    <mergeCell ref="D497:D502"/>
-    <mergeCell ref="D503:D509"/>
-    <mergeCell ref="D510:D513"/>
-    <mergeCell ref="D318:D323"/>
-    <mergeCell ref="D324:D328"/>
-    <mergeCell ref="D329:D337"/>
-    <mergeCell ref="D338:D342"/>
-    <mergeCell ref="D343:D347"/>
-    <mergeCell ref="D348:D353"/>
-    <mergeCell ref="D354:D357"/>
-    <mergeCell ref="D296:D300"/>
+    <mergeCell ref="C45:C50"/>
+    <mergeCell ref="D45:D50"/>
+    <mergeCell ref="D51:D57"/>
+    <mergeCell ref="D58:D63"/>
+    <mergeCell ref="D64:D67"/>
+    <mergeCell ref="D69:D78"/>
+    <mergeCell ref="D79:D84"/>
+    <mergeCell ref="D85:D90"/>
+    <mergeCell ref="D91:D105"/>
+    <mergeCell ref="A68:J68"/>
+    <mergeCell ref="C51:C67"/>
+    <mergeCell ref="C69:C105"/>
+    <mergeCell ref="C107:C116"/>
+    <mergeCell ref="C117:C125"/>
+    <mergeCell ref="C127:C132"/>
+    <mergeCell ref="C134:C176"/>
+    <mergeCell ref="C177:C204"/>
+    <mergeCell ref="C205:C214"/>
+    <mergeCell ref="A106:J106"/>
+    <mergeCell ref="D107:D111"/>
+    <mergeCell ref="D112:D115"/>
+    <mergeCell ref="D117:D120"/>
+    <mergeCell ref="D121:D122"/>
+    <mergeCell ref="D123:D125"/>
+    <mergeCell ref="A126:J126"/>
+    <mergeCell ref="D127:D130"/>
+    <mergeCell ref="D131:D132"/>
+    <mergeCell ref="A133:J133"/>
+    <mergeCell ref="D210:D211"/>
+    <mergeCell ref="D212:D214"/>
+    <mergeCell ref="D26:D32"/>
+    <mergeCell ref="D33:D36"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="C4:C32"/>
+    <mergeCell ref="D4:D9"/>
+    <mergeCell ref="D10:D18"/>
+    <mergeCell ref="D19:D25"/>
+    <mergeCell ref="C33:C44"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="D40:D44"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H69:H105 H107:H125 H127:H132 H134:H214 H216:H272 H274:H357 H359:H435 H437:H513 H4:H65 H67" xr:uid="{00000000-0002-0000-0000-000000000000}">

--- a/DSA Master Sheet.xlsx
+++ b/DSA Master Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aamer\Desktop\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBFCC81E-1F6B-40CA-BB38-F3B303976AF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F3F839-BE7B-4C00-8658-EAD648CFB65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="736">
   <si>
     <t>DSA Master Sheet</t>
   </si>
@@ -2912,6 +2912,39 @@
 2. Find `mid` and compare `nums[mid]` with `nums[r]`.
 3. If `nums[mid] &gt; nums[r]` → `l = mid+1`; else → `r = mid` (keep minimum side).
 4. When `l == r`, return `nums[l]` (minimum found).</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Apply binary search and find the first occurrence of target.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Store the firstIndex = mid, then move left (r = mid - 1) to search for an earlier match.(lower position)
+Reset l and r, then apply binary search again for the last occurrence.
+Store the lastIndex = mid, then move right (l = mid + 1) to search for a later match.(higher position)
+Return firstIndex, lastIndex.</t>
+    </r>
+  </si>
+  <si>
+    <t>Find mid using binary search.
+If nums[mid] == target, return mid.
+Check which half is sorted: nums[l] &lt;= nums[mid] → left sorted, else right sorted.
+If target lies in the sorted half, search there; otherwise search the other half.
+Repeat until found; otherwise return -1</t>
+  </si>
+  <si>
+    <t>If nums[mid] == target, return true.
+If nums[low] == nums[mid] == nums[high], duplicates make it impossible to identify the sorted half, so increment low and decrement high.
+Otherwise, check which half is sorted: nums[low] &lt;= nums[mid] → left sorted, else right sorted.
+If the target lies in the sorted half, search there; otherwise search the other half.
+Repeat until found; otherwise return false.</t>
   </si>
 </sst>
 </file>
@@ -4017,7 +4050,7 @@
     <xf numFmtId="0" fontId="88" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="89" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="207">
+  <cellXfs count="208">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4416,32 +4449,24 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="88" fillId="53" borderId="8" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="88" fillId="53" borderId="13" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4461,23 +4486,86 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4497,77 +4585,23 @@
     <xf numFmtId="0" fontId="11" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4580,7 +4614,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="88" fillId="53" borderId="13" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
@@ -5378,18 +5414,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="30.75" customHeight="1">
-      <c r="A1" s="153" t="s">
+      <c r="A1" s="199" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="154"/>
-      <c r="C1" s="154"/>
-      <c r="D1" s="154"/>
-      <c r="E1" s="154"/>
-      <c r="F1" s="154"/>
-      <c r="G1" s="154"/>
-      <c r="H1" s="154"/>
-      <c r="I1" s="154"/>
-      <c r="J1" s="155"/>
+      <c r="B1" s="200"/>
+      <c r="C1" s="200"/>
+      <c r="D1" s="200"/>
+      <c r="E1" s="200"/>
+      <c r="F1" s="200"/>
+      <c r="G1" s="200"/>
+      <c r="H1" s="200"/>
+      <c r="I1" s="200"/>
+      <c r="J1" s="201"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -5444,18 +5480,18 @@
       <c r="T2" s="5"/>
     </row>
     <row r="3" spans="1:20" ht="13.8">
-      <c r="A3" s="156" t="s">
+      <c r="A3" s="196" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="157"/>
-      <c r="C3" s="157"/>
-      <c r="D3" s="157"/>
-      <c r="E3" s="157"/>
-      <c r="F3" s="157"/>
-      <c r="G3" s="157"/>
-      <c r="H3" s="157"/>
-      <c r="I3" s="157"/>
-      <c r="J3" s="158"/>
+      <c r="B3" s="197"/>
+      <c r="C3" s="197"/>
+      <c r="D3" s="197"/>
+      <c r="E3" s="197"/>
+      <c r="F3" s="197"/>
+      <c r="G3" s="197"/>
+      <c r="H3" s="197"/>
+      <c r="I3" s="197"/>
+      <c r="J3" s="198"/>
     </row>
     <row r="4" spans="1:20" ht="13.8">
       <c r="A4" s="6">
@@ -5464,10 +5500,10 @@
       <c r="B4" s="7">
         <v>1</v>
       </c>
-      <c r="C4" s="159" t="s">
+      <c r="C4" s="157" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="150" t="s">
+      <c r="D4" s="172" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -5497,8 +5533,8 @@
       <c r="B5" s="7">
         <v>2</v>
       </c>
-      <c r="C5" s="160"/>
-      <c r="D5" s="151"/>
+      <c r="C5" s="158"/>
+      <c r="D5" s="173"/>
       <c r="E5" s="8" t="s">
         <v>16</v>
       </c>
@@ -5526,8 +5562,8 @@
       <c r="B6" s="7">
         <v>3</v>
       </c>
-      <c r="C6" s="160"/>
-      <c r="D6" s="151"/>
+      <c r="C6" s="158"/>
+      <c r="D6" s="173"/>
       <c r="E6" s="8" t="s">
         <v>19</v>
       </c>
@@ -5555,8 +5591,8 @@
       <c r="B7" s="7">
         <v>4</v>
       </c>
-      <c r="C7" s="160"/>
-      <c r="D7" s="151"/>
+      <c r="C7" s="158"/>
+      <c r="D7" s="173"/>
       <c r="E7" s="8" t="s">
         <v>23</v>
       </c>
@@ -5584,8 +5620,8 @@
       <c r="B8" s="7">
         <v>5</v>
       </c>
-      <c r="C8" s="160"/>
-      <c r="D8" s="151"/>
+      <c r="C8" s="158"/>
+      <c r="D8" s="173"/>
       <c r="E8" s="8" t="s">
         <v>26</v>
       </c>
@@ -5613,8 +5649,8 @@
       <c r="B9" s="7">
         <v>6</v>
       </c>
-      <c r="C9" s="160"/>
-      <c r="D9" s="152"/>
+      <c r="C9" s="158"/>
+      <c r="D9" s="174"/>
       <c r="E9" s="8" t="s">
         <v>29</v>
       </c>
@@ -5639,8 +5675,8 @@
       <c r="B10" s="7">
         <v>7</v>
       </c>
-      <c r="C10" s="160"/>
-      <c r="D10" s="150" t="s">
+      <c r="C10" s="158"/>
+      <c r="D10" s="172" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="8" t="s">
@@ -5667,8 +5703,8 @@
       <c r="B11" s="7">
         <v>8</v>
       </c>
-      <c r="C11" s="160"/>
-      <c r="D11" s="151"/>
+      <c r="C11" s="158"/>
+      <c r="D11" s="173"/>
       <c r="E11" s="13" t="s">
         <v>32</v>
       </c>
@@ -5693,8 +5729,8 @@
       <c r="B12" s="7">
         <v>9</v>
       </c>
-      <c r="C12" s="160"/>
-      <c r="D12" s="151"/>
+      <c r="C12" s="158"/>
+      <c r="D12" s="173"/>
       <c r="E12" s="8" t="s">
         <v>33</v>
       </c>
@@ -5719,8 +5755,8 @@
       <c r="B13" s="7">
         <v>10</v>
       </c>
-      <c r="C13" s="160"/>
-      <c r="D13" s="151"/>
+      <c r="C13" s="158"/>
+      <c r="D13" s="173"/>
       <c r="E13" s="8" t="s">
         <v>34</v>
       </c>
@@ -5747,8 +5783,8 @@
       <c r="B14" s="7">
         <v>11</v>
       </c>
-      <c r="C14" s="160"/>
-      <c r="D14" s="151"/>
+      <c r="C14" s="158"/>
+      <c r="D14" s="173"/>
       <c r="E14" s="8" t="s">
         <v>35</v>
       </c>
@@ -5773,8 +5809,8 @@
       <c r="B15" s="7">
         <v>12</v>
       </c>
-      <c r="C15" s="160"/>
-      <c r="D15" s="151"/>
+      <c r="C15" s="158"/>
+      <c r="D15" s="173"/>
       <c r="E15" s="8" t="s">
         <v>36</v>
       </c>
@@ -5801,8 +5837,8 @@
       <c r="B16" s="7">
         <v>13</v>
       </c>
-      <c r="C16" s="160"/>
-      <c r="D16" s="151"/>
+      <c r="C16" s="158"/>
+      <c r="D16" s="173"/>
       <c r="E16" s="8" t="s">
         <v>37</v>
       </c>
@@ -5827,8 +5863,8 @@
       <c r="B17" s="7">
         <v>14</v>
       </c>
-      <c r="C17" s="160"/>
-      <c r="D17" s="151"/>
+      <c r="C17" s="158"/>
+      <c r="D17" s="173"/>
       <c r="E17" s="8" t="s">
         <v>38</v>
       </c>
@@ -5855,8 +5891,8 @@
       <c r="B18" s="7">
         <v>15</v>
       </c>
-      <c r="C18" s="160"/>
-      <c r="D18" s="152"/>
+      <c r="C18" s="158"/>
+      <c r="D18" s="174"/>
       <c r="E18" s="13" t="s">
         <v>39</v>
       </c>
@@ -5883,8 +5919,8 @@
       <c r="B19" s="7">
         <v>16</v>
       </c>
-      <c r="C19" s="160"/>
-      <c r="D19" s="150" t="s">
+      <c r="C19" s="158"/>
+      <c r="D19" s="172" t="s">
         <v>40</v>
       </c>
       <c r="E19" s="8" t="s">
@@ -5913,8 +5949,8 @@
       <c r="B20" s="7">
         <v>17</v>
       </c>
-      <c r="C20" s="160"/>
-      <c r="D20" s="151"/>
+      <c r="C20" s="158"/>
+      <c r="D20" s="173"/>
       <c r="E20" s="8" t="s">
         <v>42</v>
       </c>
@@ -5941,8 +5977,8 @@
       <c r="B21" s="7">
         <v>18</v>
       </c>
-      <c r="C21" s="160"/>
-      <c r="D21" s="151"/>
+      <c r="C21" s="158"/>
+      <c r="D21" s="173"/>
       <c r="E21" s="8" t="s">
         <v>43</v>
       </c>
@@ -5969,8 +6005,8 @@
       <c r="B22" s="7">
         <v>19</v>
       </c>
-      <c r="C22" s="160"/>
-      <c r="D22" s="151"/>
+      <c r="C22" s="158"/>
+      <c r="D22" s="173"/>
       <c r="E22" s="8" t="s">
         <v>44</v>
       </c>
@@ -5991,8 +6027,8 @@
       <c r="B23" s="7">
         <v>20</v>
       </c>
-      <c r="C23" s="160"/>
-      <c r="D23" s="151"/>
+      <c r="C23" s="158"/>
+      <c r="D23" s="173"/>
       <c r="E23" s="8" t="s">
         <v>45</v>
       </c>
@@ -6013,8 +6049,8 @@
       <c r="B24" s="7">
         <v>21</v>
       </c>
-      <c r="C24" s="160"/>
-      <c r="D24" s="151"/>
+      <c r="C24" s="158"/>
+      <c r="D24" s="173"/>
       <c r="E24" s="13" t="s">
         <v>46</v>
       </c>
@@ -6039,8 +6075,8 @@
       <c r="B25" s="7">
         <v>22</v>
       </c>
-      <c r="C25" s="160"/>
-      <c r="D25" s="152"/>
+      <c r="C25" s="158"/>
+      <c r="D25" s="174"/>
       <c r="E25" s="8" t="s">
         <v>47</v>
       </c>
@@ -6067,8 +6103,8 @@
       <c r="B26" s="7">
         <v>23</v>
       </c>
-      <c r="C26" s="160"/>
-      <c r="D26" s="150" t="s">
+      <c r="C26" s="158"/>
+      <c r="D26" s="172" t="s">
         <v>48</v>
       </c>
       <c r="E26" s="13" t="s">
@@ -6097,8 +6133,8 @@
       <c r="B27" s="7">
         <v>24</v>
       </c>
-      <c r="C27" s="160"/>
-      <c r="D27" s="151"/>
+      <c r="C27" s="158"/>
+      <c r="D27" s="173"/>
       <c r="E27" s="8" t="s">
         <v>50</v>
       </c>
@@ -6123,8 +6159,8 @@
       <c r="B28" s="7">
         <v>25</v>
       </c>
-      <c r="C28" s="160"/>
-      <c r="D28" s="151"/>
+      <c r="C28" s="158"/>
+      <c r="D28" s="173"/>
       <c r="E28" s="8" t="s">
         <v>51</v>
       </c>
@@ -6151,8 +6187,8 @@
       <c r="B29" s="143">
         <v>26</v>
       </c>
-      <c r="C29" s="160"/>
-      <c r="D29" s="151"/>
+      <c r="C29" s="158"/>
+      <c r="D29" s="173"/>
       <c r="E29" s="144" t="s">
         <v>52</v>
       </c>
@@ -6173,8 +6209,8 @@
       <c r="B30" s="143">
         <v>27</v>
       </c>
-      <c r="C30" s="160"/>
-      <c r="D30" s="151"/>
+      <c r="C30" s="158"/>
+      <c r="D30" s="173"/>
       <c r="E30" s="144" t="s">
         <v>53</v>
       </c>
@@ -6195,8 +6231,8 @@
       <c r="B31" s="143">
         <v>28</v>
       </c>
-      <c r="C31" s="160"/>
-      <c r="D31" s="151"/>
+      <c r="C31" s="158"/>
+      <c r="D31" s="173"/>
       <c r="E31" s="144" t="s">
         <v>54</v>
       </c>
@@ -6217,8 +6253,8 @@
       <c r="B32" s="143">
         <v>29</v>
       </c>
-      <c r="C32" s="161"/>
-      <c r="D32" s="152"/>
+      <c r="C32" s="159"/>
+      <c r="D32" s="174"/>
       <c r="E32" s="146" t="s">
         <v>55</v>
       </c>
@@ -6239,10 +6275,10 @@
       <c r="B33" s="22">
         <v>1</v>
       </c>
-      <c r="C33" s="162" t="s">
+      <c r="C33" s="160" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="150" t="s">
+      <c r="D33" s="172" t="s">
         <v>57</v>
       </c>
       <c r="E33" s="8" t="s">
@@ -6269,8 +6305,8 @@
       <c r="B34" s="7">
         <v>2</v>
       </c>
-      <c r="C34" s="163"/>
-      <c r="D34" s="151"/>
+      <c r="C34" s="161"/>
+      <c r="D34" s="173"/>
       <c r="E34" s="8" t="s">
         <v>59</v>
       </c>
@@ -6295,8 +6331,8 @@
       <c r="B35" s="7">
         <v>3</v>
       </c>
-      <c r="C35" s="163"/>
-      <c r="D35" s="151"/>
+      <c r="C35" s="161"/>
+      <c r="D35" s="173"/>
       <c r="E35" s="8" t="s">
         <v>60</v>
       </c>
@@ -6323,8 +6359,8 @@
       <c r="B36" s="7">
         <v>4</v>
       </c>
-      <c r="C36" s="163"/>
-      <c r="D36" s="152"/>
+      <c r="C36" s="161"/>
+      <c r="D36" s="174"/>
       <c r="E36" s="8" t="s">
         <v>61</v>
       </c>
@@ -6351,8 +6387,8 @@
       <c r="B37" s="7">
         <v>5</v>
       </c>
-      <c r="C37" s="163"/>
-      <c r="D37" s="150" t="s">
+      <c r="C37" s="161"/>
+      <c r="D37" s="172" t="s">
         <v>62</v>
       </c>
       <c r="E37" s="8" t="s">
@@ -6379,8 +6415,8 @@
       <c r="B38" s="7">
         <v>6</v>
       </c>
-      <c r="C38" s="163"/>
-      <c r="D38" s="151"/>
+      <c r="C38" s="161"/>
+      <c r="D38" s="173"/>
       <c r="E38" s="8" t="s">
         <v>64</v>
       </c>
@@ -6405,8 +6441,8 @@
       <c r="B39" s="7">
         <v>7</v>
       </c>
-      <c r="C39" s="163"/>
-      <c r="D39" s="152"/>
+      <c r="C39" s="161"/>
+      <c r="D39" s="174"/>
       <c r="E39" s="8" t="s">
         <v>65</v>
       </c>
@@ -6431,8 +6467,8 @@
       <c r="B40" s="7">
         <v>8</v>
       </c>
-      <c r="C40" s="163"/>
-      <c r="D40" s="150" t="s">
+      <c r="C40" s="161"/>
+      <c r="D40" s="172" t="s">
         <v>66</v>
       </c>
       <c r="E40" s="8" t="s">
@@ -6459,8 +6495,8 @@
       <c r="B41" s="7">
         <v>9</v>
       </c>
-      <c r="C41" s="163"/>
-      <c r="D41" s="151"/>
+      <c r="C41" s="161"/>
+      <c r="D41" s="173"/>
       <c r="E41" s="8" t="s">
         <v>68</v>
       </c>
@@ -6485,8 +6521,8 @@
       <c r="B42" s="7">
         <v>10</v>
       </c>
-      <c r="C42" s="163"/>
-      <c r="D42" s="151"/>
+      <c r="C42" s="161"/>
+      <c r="D42" s="173"/>
       <c r="E42" s="8" t="s">
         <v>69</v>
       </c>
@@ -6511,8 +6547,8 @@
       <c r="B43" s="7">
         <v>11</v>
       </c>
-      <c r="C43" s="163"/>
-      <c r="D43" s="151"/>
+      <c r="C43" s="161"/>
+      <c r="D43" s="173"/>
       <c r="E43" s="8" t="s">
         <v>70</v>
       </c>
@@ -6537,8 +6573,8 @@
       <c r="B44" s="24">
         <v>12</v>
       </c>
-      <c r="C44" s="164"/>
-      <c r="D44" s="152"/>
+      <c r="C44" s="162"/>
+      <c r="D44" s="174"/>
       <c r="E44" s="17" t="s">
         <v>71</v>
       </c>
@@ -6563,10 +6599,10 @@
       <c r="B45" s="22">
         <v>1</v>
       </c>
-      <c r="C45" s="177" t="s">
+      <c r="C45" s="163" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="180" t="s">
+      <c r="D45" s="175" t="s">
         <v>73</v>
       </c>
       <c r="E45" s="13" t="s">
@@ -6593,8 +6629,8 @@
       <c r="B46" s="7">
         <v>2</v>
       </c>
-      <c r="C46" s="178"/>
-      <c r="D46" s="181"/>
+      <c r="C46" s="164"/>
+      <c r="D46" s="176"/>
       <c r="E46" s="8" t="s">
         <v>75</v>
       </c>
@@ -6621,8 +6657,8 @@
       <c r="B47" s="7">
         <v>3</v>
       </c>
-      <c r="C47" s="178"/>
-      <c r="D47" s="181"/>
+      <c r="C47" s="164"/>
+      <c r="D47" s="176"/>
       <c r="E47" s="13" t="s">
         <v>76</v>
       </c>
@@ -6649,8 +6685,8 @@
       <c r="B48" s="7">
         <v>4</v>
       </c>
-      <c r="C48" s="178"/>
-      <c r="D48" s="181"/>
+      <c r="C48" s="164"/>
+      <c r="D48" s="176"/>
       <c r="E48" s="13" t="s">
         <v>77</v>
       </c>
@@ -6677,8 +6713,8 @@
       <c r="B49" s="7">
         <v>5</v>
       </c>
-      <c r="C49" s="178"/>
-      <c r="D49" s="181"/>
+      <c r="C49" s="164"/>
+      <c r="D49" s="176"/>
       <c r="E49" s="13" t="s">
         <v>78</v>
       </c>
@@ -6703,8 +6739,8 @@
       <c r="B50" s="24">
         <v>6</v>
       </c>
-      <c r="C50" s="179"/>
-      <c r="D50" s="182"/>
+      <c r="C50" s="165"/>
+      <c r="D50" s="177"/>
       <c r="E50" s="25" t="s">
         <v>79</v>
       </c>
@@ -6729,10 +6765,10 @@
       <c r="B51" s="7">
         <v>1</v>
       </c>
-      <c r="C51" s="168" t="s">
+      <c r="C51" s="154" t="s">
         <v>80</v>
       </c>
-      <c r="D51" s="150" t="s">
+      <c r="D51" s="172" t="s">
         <v>81</v>
       </c>
       <c r="E51" s="13" t="s">
@@ -6761,8 +6797,8 @@
       <c r="B52" s="7">
         <v>2</v>
       </c>
-      <c r="C52" s="169"/>
-      <c r="D52" s="151"/>
+      <c r="C52" s="155"/>
+      <c r="D52" s="173"/>
       <c r="E52" s="8" t="s">
         <v>83</v>
       </c>
@@ -6789,8 +6825,8 @@
       <c r="B53" s="7">
         <v>3</v>
       </c>
-      <c r="C53" s="169"/>
-      <c r="D53" s="151"/>
+      <c r="C53" s="155"/>
+      <c r="D53" s="173"/>
       <c r="E53" s="27" t="s">
         <v>84</v>
       </c>
@@ -6815,8 +6851,8 @@
       <c r="B54" s="7">
         <v>4</v>
       </c>
-      <c r="C54" s="169"/>
-      <c r="D54" s="151"/>
+      <c r="C54" s="155"/>
+      <c r="D54" s="173"/>
       <c r="E54" s="13" t="s">
         <v>85</v>
       </c>
@@ -6841,8 +6877,8 @@
       <c r="B55" s="7">
         <v>5</v>
       </c>
-      <c r="C55" s="169"/>
-      <c r="D55" s="151"/>
+      <c r="C55" s="155"/>
+      <c r="D55" s="173"/>
       <c r="E55" s="13" t="s">
         <v>86</v>
       </c>
@@ -6869,8 +6905,8 @@
       <c r="B56" s="7">
         <v>6</v>
       </c>
-      <c r="C56" s="169"/>
-      <c r="D56" s="151"/>
+      <c r="C56" s="155"/>
+      <c r="D56" s="173"/>
       <c r="E56" s="13" t="s">
         <v>87</v>
       </c>
@@ -6897,8 +6933,8 @@
       <c r="B57" s="7">
         <v>7</v>
       </c>
-      <c r="C57" s="169"/>
-      <c r="D57" s="152"/>
+      <c r="C57" s="155"/>
+      <c r="D57" s="174"/>
       <c r="E57" s="13" t="s">
         <v>88</v>
       </c>
@@ -6925,8 +6961,8 @@
       <c r="B58" s="7">
         <v>8</v>
       </c>
-      <c r="C58" s="169"/>
-      <c r="D58" s="150" t="s">
+      <c r="C58" s="155"/>
+      <c r="D58" s="172" t="s">
         <v>89</v>
       </c>
       <c r="E58" s="13" t="s">
@@ -6953,8 +6989,8 @@
       <c r="B59" s="7">
         <v>9</v>
       </c>
-      <c r="C59" s="169"/>
-      <c r="D59" s="151"/>
+      <c r="C59" s="155"/>
+      <c r="D59" s="173"/>
       <c r="E59" s="8" t="s">
         <v>91</v>
       </c>
@@ -6979,8 +7015,8 @@
       <c r="B60" s="7">
         <v>10</v>
       </c>
-      <c r="C60" s="169"/>
-      <c r="D60" s="151"/>
+      <c r="C60" s="155"/>
+      <c r="D60" s="173"/>
       <c r="E60" s="8" t="s">
         <v>92</v>
       </c>
@@ -7001,8 +7037,8 @@
       <c r="B61" s="7">
         <v>11</v>
       </c>
-      <c r="C61" s="169"/>
-      <c r="D61" s="151"/>
+      <c r="C61" s="155"/>
+      <c r="D61" s="173"/>
       <c r="E61" s="8" t="s">
         <v>93</v>
       </c>
@@ -7023,8 +7059,8 @@
       <c r="B62" s="7">
         <v>12</v>
       </c>
-      <c r="C62" s="169"/>
-      <c r="D62" s="151"/>
+      <c r="C62" s="155"/>
+      <c r="D62" s="173"/>
       <c r="E62" s="8" t="s">
         <v>94</v>
       </c>
@@ -7049,8 +7085,8 @@
       <c r="B63" s="7">
         <v>13</v>
       </c>
-      <c r="C63" s="169"/>
-      <c r="D63" s="152"/>
+      <c r="C63" s="155"/>
+      <c r="D63" s="174"/>
       <c r="E63" s="8" t="s">
         <v>95</v>
       </c>
@@ -7075,8 +7111,8 @@
       <c r="B64" s="7">
         <v>14</v>
       </c>
-      <c r="C64" s="169"/>
-      <c r="D64" s="150" t="s">
+      <c r="C64" s="155"/>
+      <c r="D64" s="172" t="s">
         <v>48</v>
       </c>
       <c r="E64" s="8" t="s">
@@ -7105,8 +7141,8 @@
       <c r="B65" s="143">
         <v>15</v>
       </c>
-      <c r="C65" s="169"/>
-      <c r="D65" s="151"/>
+      <c r="C65" s="155"/>
+      <c r="D65" s="173"/>
       <c r="E65" s="144" t="s">
         <v>97</v>
       </c>
@@ -7127,8 +7163,8 @@
       <c r="B66" s="7">
         <v>16</v>
       </c>
-      <c r="C66" s="169"/>
-      <c r="D66" s="151"/>
+      <c r="C66" s="155"/>
+      <c r="D66" s="173"/>
       <c r="E66" s="8" t="s">
         <v>98</v>
       </c>
@@ -7155,8 +7191,8 @@
       <c r="B67" s="7">
         <v>17</v>
       </c>
-      <c r="C67" s="170"/>
-      <c r="D67" s="152"/>
+      <c r="C67" s="156"/>
+      <c r="D67" s="174"/>
       <c r="E67" s="8" t="s">
         <v>99</v>
       </c>
@@ -7177,18 +7213,18 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="13.8">
-      <c r="A68" s="183" t="s">
+      <c r="A68" s="184" t="s">
         <v>100</v>
       </c>
-      <c r="B68" s="184"/>
-      <c r="C68" s="184"/>
-      <c r="D68" s="184"/>
-      <c r="E68" s="184"/>
-      <c r="F68" s="184"/>
-      <c r="G68" s="184"/>
-      <c r="H68" s="184"/>
-      <c r="I68" s="184"/>
-      <c r="J68" s="185"/>
+      <c r="B68" s="185"/>
+      <c r="C68" s="185"/>
+      <c r="D68" s="185"/>
+      <c r="E68" s="185"/>
+      <c r="F68" s="185"/>
+      <c r="G68" s="185"/>
+      <c r="H68" s="185"/>
+      <c r="I68" s="185"/>
+      <c r="J68" s="186"/>
     </row>
     <row r="69" spans="1:10" ht="13.8">
       <c r="A69" s="6">
@@ -7197,10 +7233,10 @@
       <c r="B69" s="7">
         <v>1</v>
       </c>
-      <c r="C69" s="159" t="s">
+      <c r="C69" s="157" t="s">
         <v>101</v>
       </c>
-      <c r="D69" s="150" t="s">
+      <c r="D69" s="172" t="s">
         <v>102</v>
       </c>
       <c r="E69" s="8" t="s">
@@ -7227,8 +7263,8 @@
       <c r="B70" s="7">
         <v>2</v>
       </c>
-      <c r="C70" s="160"/>
-      <c r="D70" s="151"/>
+      <c r="C70" s="158"/>
+      <c r="D70" s="173"/>
       <c r="E70" s="28" t="s">
         <v>104</v>
       </c>
@@ -7255,8 +7291,8 @@
       <c r="B71" s="7">
         <v>3</v>
       </c>
-      <c r="C71" s="160"/>
-      <c r="D71" s="151"/>
+      <c r="C71" s="158"/>
+      <c r="D71" s="173"/>
       <c r="E71" s="8" t="s">
         <v>105</v>
       </c>
@@ -7283,8 +7319,8 @@
       <c r="B72" s="7">
         <v>4</v>
       </c>
-      <c r="C72" s="160"/>
-      <c r="D72" s="151"/>
+      <c r="C72" s="158"/>
+      <c r="D72" s="173"/>
       <c r="E72" s="8" t="s">
         <v>106</v>
       </c>
@@ -7311,8 +7347,8 @@
       <c r="B73" s="7">
         <v>5</v>
       </c>
-      <c r="C73" s="160"/>
-      <c r="D73" s="151"/>
+      <c r="C73" s="158"/>
+      <c r="D73" s="173"/>
       <c r="E73" s="28" t="s">
         <v>107</v>
       </c>
@@ -7339,8 +7375,8 @@
       <c r="B74" s="7">
         <v>6</v>
       </c>
-      <c r="C74" s="160"/>
-      <c r="D74" s="151"/>
+      <c r="C74" s="158"/>
+      <c r="D74" s="173"/>
       <c r="E74" s="28" t="s">
         <v>108</v>
       </c>
@@ -7365,8 +7401,8 @@
       <c r="B75" s="7">
         <v>7</v>
       </c>
-      <c r="C75" s="160"/>
-      <c r="D75" s="151"/>
+      <c r="C75" s="158"/>
+      <c r="D75" s="173"/>
       <c r="E75" s="28" t="s">
         <v>109</v>
       </c>
@@ -7393,8 +7429,8 @@
       <c r="B76" s="7">
         <v>8</v>
       </c>
-      <c r="C76" s="160"/>
-      <c r="D76" s="151"/>
+      <c r="C76" s="158"/>
+      <c r="D76" s="173"/>
       <c r="E76" s="8" t="s">
         <v>110</v>
       </c>
@@ -7419,8 +7455,8 @@
       <c r="B77" s="7">
         <v>9</v>
       </c>
-      <c r="C77" s="160"/>
-      <c r="D77" s="151"/>
+      <c r="C77" s="158"/>
+      <c r="D77" s="173"/>
       <c r="E77" s="8" t="s">
         <v>111</v>
       </c>
@@ -7436,7 +7472,7 @@
       <c r="I77" s="125" t="s">
         <v>731</v>
       </c>
-      <c r="J77" s="206" t="s">
+      <c r="J77" s="150" t="s">
         <v>10</v>
       </c>
     </row>
@@ -7447,8 +7483,8 @@
       <c r="B78" s="7">
         <v>10</v>
       </c>
-      <c r="C78" s="160"/>
-      <c r="D78" s="152"/>
+      <c r="C78" s="158"/>
+      <c r="D78" s="174"/>
       <c r="E78" s="8" t="s">
         <v>112</v>
       </c>
@@ -7468,15 +7504,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="13.8">
+    <row r="79" spans="1:10" ht="193.2">
       <c r="A79" s="6">
         <v>75</v>
       </c>
       <c r="B79" s="7">
         <v>11</v>
       </c>
-      <c r="C79" s="160"/>
-      <c r="D79" s="150" t="s">
+      <c r="C79" s="158"/>
+      <c r="D79" s="172" t="s">
         <v>113</v>
       </c>
       <c r="E79" s="8" t="s">
@@ -7488,19 +7524,25 @@
       <c r="G79" s="10">
         <v>3</v>
       </c>
-      <c r="H79" s="11"/>
-      <c r="I79" s="11"/>
-      <c r="J79" s="11"/>
-    </row>
-    <row r="80" spans="1:10" ht="13.8">
+      <c r="H79" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I79" s="207" t="s">
+        <v>733</v>
+      </c>
+      <c r="J79" s="126" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="151.80000000000001">
       <c r="A80" s="6">
         <v>76</v>
       </c>
       <c r="B80" s="7">
         <v>12</v>
       </c>
-      <c r="C80" s="160"/>
-      <c r="D80" s="151"/>
+      <c r="C80" s="158"/>
+      <c r="D80" s="173"/>
       <c r="E80" s="8" t="s">
         <v>115</v>
       </c>
@@ -7510,19 +7552,25 @@
       <c r="G80" s="10">
         <v>3</v>
       </c>
-      <c r="H80" s="11"/>
-      <c r="I80" s="11"/>
-      <c r="J80" s="11"/>
-    </row>
-    <row r="81" spans="1:10" ht="13.8">
+      <c r="H80" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I80" s="125" t="s">
+        <v>734</v>
+      </c>
+      <c r="J80" s="126" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="207">
       <c r="A81" s="6">
         <v>77</v>
       </c>
       <c r="B81" s="7">
         <v>13</v>
       </c>
-      <c r="C81" s="160"/>
-      <c r="D81" s="151"/>
+      <c r="C81" s="158"/>
+      <c r="D81" s="173"/>
       <c r="E81" s="8" t="s">
         <v>116</v>
       </c>
@@ -7532,9 +7580,15 @@
       <c r="G81" s="10">
         <v>3</v>
       </c>
-      <c r="H81" s="11"/>
-      <c r="I81" s="11"/>
-      <c r="J81" s="11"/>
+      <c r="H81" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I81" s="125" t="s">
+        <v>735</v>
+      </c>
+      <c r="J81" s="126" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="82" spans="1:10" ht="13.8">
       <c r="A82" s="6">
@@ -7543,8 +7597,8 @@
       <c r="B82" s="7">
         <v>14</v>
       </c>
-      <c r="C82" s="160"/>
-      <c r="D82" s="151"/>
+      <c r="C82" s="158"/>
+      <c r="D82" s="173"/>
       <c r="E82" s="8" t="s">
         <v>117</v>
       </c>
@@ -7565,8 +7619,8 @@
       <c r="B83" s="7">
         <v>15</v>
       </c>
-      <c r="C83" s="160"/>
-      <c r="D83" s="151"/>
+      <c r="C83" s="158"/>
+      <c r="D83" s="173"/>
       <c r="E83" s="8" t="s">
         <v>118</v>
       </c>
@@ -7587,8 +7641,8 @@
       <c r="B84" s="7">
         <v>16</v>
       </c>
-      <c r="C84" s="160"/>
-      <c r="D84" s="152"/>
+      <c r="C84" s="158"/>
+      <c r="D84" s="174"/>
       <c r="E84" s="8" t="s">
         <v>119</v>
       </c>
@@ -7609,8 +7663,8 @@
       <c r="B85" s="7">
         <v>17</v>
       </c>
-      <c r="C85" s="160"/>
-      <c r="D85" s="150" t="s">
+      <c r="C85" s="158"/>
+      <c r="D85" s="172" t="s">
         <v>120</v>
       </c>
       <c r="E85" s="8" t="s">
@@ -7633,8 +7687,8 @@
       <c r="B86" s="7">
         <v>18</v>
       </c>
-      <c r="C86" s="160"/>
-      <c r="D86" s="151"/>
+      <c r="C86" s="158"/>
+      <c r="D86" s="173"/>
       <c r="E86" s="8" t="s">
         <v>122</v>
       </c>
@@ -7655,8 +7709,8 @@
       <c r="B87" s="7">
         <v>19</v>
       </c>
-      <c r="C87" s="160"/>
-      <c r="D87" s="151"/>
+      <c r="C87" s="158"/>
+      <c r="D87" s="173"/>
       <c r="E87" s="29" t="s">
         <v>123</v>
       </c>
@@ -7677,8 +7731,8 @@
       <c r="B88" s="7">
         <v>20</v>
       </c>
-      <c r="C88" s="160"/>
-      <c r="D88" s="151"/>
+      <c r="C88" s="158"/>
+      <c r="D88" s="173"/>
       <c r="E88" s="8" t="s">
         <v>124</v>
       </c>
@@ -7699,8 +7753,8 @@
       <c r="B89" s="7">
         <v>21</v>
       </c>
-      <c r="C89" s="160"/>
-      <c r="D89" s="151"/>
+      <c r="C89" s="158"/>
+      <c r="D89" s="173"/>
       <c r="E89" s="8" t="s">
         <v>125</v>
       </c>
@@ -7721,8 +7775,8 @@
       <c r="B90" s="7">
         <v>22</v>
       </c>
-      <c r="C90" s="160"/>
-      <c r="D90" s="152"/>
+      <c r="C90" s="158"/>
+      <c r="D90" s="174"/>
       <c r="E90" s="8" t="s">
         <v>126</v>
       </c>
@@ -7743,8 +7797,8 @@
       <c r="B91" s="7">
         <v>23</v>
       </c>
-      <c r="C91" s="160"/>
-      <c r="D91" s="150" t="s">
+      <c r="C91" s="158"/>
+      <c r="D91" s="172" t="s">
         <v>127</v>
       </c>
       <c r="E91" s="8" t="s">
@@ -7767,8 +7821,8 @@
       <c r="B92" s="7">
         <v>24</v>
       </c>
-      <c r="C92" s="160"/>
-      <c r="D92" s="151"/>
+      <c r="C92" s="158"/>
+      <c r="D92" s="173"/>
       <c r="E92" s="8" t="s">
         <v>129</v>
       </c>
@@ -7789,8 +7843,8 @@
       <c r="B93" s="7">
         <v>25</v>
       </c>
-      <c r="C93" s="160"/>
-      <c r="D93" s="151"/>
+      <c r="C93" s="158"/>
+      <c r="D93" s="173"/>
       <c r="E93" s="8" t="s">
         <v>130</v>
       </c>
@@ -7811,8 +7865,8 @@
       <c r="B94" s="7">
         <v>26</v>
       </c>
-      <c r="C94" s="160"/>
-      <c r="D94" s="151"/>
+      <c r="C94" s="158"/>
+      <c r="D94" s="173"/>
       <c r="E94" s="8" t="s">
         <v>131</v>
       </c>
@@ -7833,8 +7887,8 @@
       <c r="B95" s="7">
         <v>27</v>
       </c>
-      <c r="C95" s="160"/>
-      <c r="D95" s="151"/>
+      <c r="C95" s="158"/>
+      <c r="D95" s="173"/>
       <c r="E95" s="8" t="s">
         <v>132</v>
       </c>
@@ -7855,8 +7909,8 @@
       <c r="B96" s="7">
         <v>28</v>
       </c>
-      <c r="C96" s="160"/>
-      <c r="D96" s="151"/>
+      <c r="C96" s="158"/>
+      <c r="D96" s="173"/>
       <c r="E96" s="8" t="s">
         <v>133</v>
       </c>
@@ -7877,8 +7931,8 @@
       <c r="B97" s="7">
         <v>29</v>
       </c>
-      <c r="C97" s="160"/>
-      <c r="D97" s="151"/>
+      <c r="C97" s="158"/>
+      <c r="D97" s="173"/>
       <c r="E97" s="8" t="s">
         <v>134</v>
       </c>
@@ -7899,8 +7953,8 @@
       <c r="B98" s="7">
         <v>30</v>
       </c>
-      <c r="C98" s="160"/>
-      <c r="D98" s="151"/>
+      <c r="C98" s="158"/>
+      <c r="D98" s="173"/>
       <c r="E98" s="8" t="s">
         <v>135</v>
       </c>
@@ -7921,8 +7975,8 @@
       <c r="B99" s="7">
         <v>31</v>
       </c>
-      <c r="C99" s="160"/>
-      <c r="D99" s="151"/>
+      <c r="C99" s="158"/>
+      <c r="D99" s="173"/>
       <c r="E99" s="30" t="s">
         <v>136</v>
       </c>
@@ -7943,8 +7997,8 @@
       <c r="B100" s="7">
         <v>32</v>
       </c>
-      <c r="C100" s="160"/>
-      <c r="D100" s="151"/>
+      <c r="C100" s="158"/>
+      <c r="D100" s="173"/>
       <c r="E100" s="8" t="s">
         <v>137</v>
       </c>
@@ -7965,8 +8019,8 @@
       <c r="B101" s="7">
         <v>33</v>
       </c>
-      <c r="C101" s="160"/>
-      <c r="D101" s="151"/>
+      <c r="C101" s="158"/>
+      <c r="D101" s="173"/>
       <c r="E101" s="8" t="s">
         <v>138</v>
       </c>
@@ -7987,8 +8041,8 @@
       <c r="B102" s="7">
         <v>34</v>
       </c>
-      <c r="C102" s="160"/>
-      <c r="D102" s="151"/>
+      <c r="C102" s="158"/>
+      <c r="D102" s="173"/>
       <c r="E102" s="8" t="s">
         <v>139</v>
       </c>
@@ -8009,8 +8063,8 @@
       <c r="B103" s="7">
         <v>35</v>
       </c>
-      <c r="C103" s="160"/>
-      <c r="D103" s="151"/>
+      <c r="C103" s="158"/>
+      <c r="D103" s="173"/>
       <c r="E103" s="8" t="s">
         <v>140</v>
       </c>
@@ -8031,8 +8085,8 @@
       <c r="B104" s="7">
         <v>36</v>
       </c>
-      <c r="C104" s="160"/>
-      <c r="D104" s="151"/>
+      <c r="C104" s="158"/>
+      <c r="D104" s="173"/>
       <c r="E104" s="8" t="s">
         <v>141</v>
       </c>
@@ -8053,8 +8107,8 @@
       <c r="B105" s="7">
         <v>37</v>
       </c>
-      <c r="C105" s="161"/>
-      <c r="D105" s="152"/>
+      <c r="C105" s="159"/>
+      <c r="D105" s="174"/>
       <c r="E105" s="8" t="s">
         <v>142</v>
       </c>
@@ -8069,18 +8123,18 @@
       <c r="J105" s="11"/>
     </row>
     <row r="106" spans="1:10" ht="13.8">
-      <c r="A106" s="171" t="s">
+      <c r="A106" s="190" t="s">
         <v>143</v>
       </c>
-      <c r="B106" s="172"/>
-      <c r="C106" s="172"/>
-      <c r="D106" s="172"/>
-      <c r="E106" s="172"/>
-      <c r="F106" s="172"/>
-      <c r="G106" s="172"/>
-      <c r="H106" s="172"/>
-      <c r="I106" s="172"/>
-      <c r="J106" s="173"/>
+      <c r="B106" s="191"/>
+      <c r="C106" s="191"/>
+      <c r="D106" s="191"/>
+      <c r="E106" s="191"/>
+      <c r="F106" s="191"/>
+      <c r="G106" s="191"/>
+      <c r="H106" s="191"/>
+      <c r="I106" s="191"/>
+      <c r="J106" s="192"/>
     </row>
     <row r="107" spans="1:10" ht="13.8">
       <c r="A107" s="6">
@@ -8089,10 +8143,10 @@
       <c r="B107" s="7">
         <v>1</v>
       </c>
-      <c r="C107" s="162" t="s">
+      <c r="C107" s="160" t="s">
         <v>144</v>
       </c>
-      <c r="D107" s="150" t="s">
+      <c r="D107" s="172" t="s">
         <v>145</v>
       </c>
       <c r="E107" s="8" t="s">
@@ -8115,8 +8169,8 @@
       <c r="B108" s="7">
         <v>2</v>
       </c>
-      <c r="C108" s="163"/>
-      <c r="D108" s="151"/>
+      <c r="C108" s="161"/>
+      <c r="D108" s="173"/>
       <c r="E108" s="8" t="s">
         <v>147</v>
       </c>
@@ -8137,8 +8191,8 @@
       <c r="B109" s="7">
         <v>3</v>
       </c>
-      <c r="C109" s="163"/>
-      <c r="D109" s="151"/>
+      <c r="C109" s="161"/>
+      <c r="D109" s="173"/>
       <c r="E109" s="8" t="s">
         <v>148</v>
       </c>
@@ -8159,8 +8213,8 @@
       <c r="B110" s="7">
         <v>4</v>
       </c>
-      <c r="C110" s="163"/>
-      <c r="D110" s="151"/>
+      <c r="C110" s="161"/>
+      <c r="D110" s="173"/>
       <c r="E110" s="8" t="s">
         <v>149</v>
       </c>
@@ -8181,8 +8235,8 @@
       <c r="B111" s="7">
         <v>5</v>
       </c>
-      <c r="C111" s="163"/>
-      <c r="D111" s="152"/>
+      <c r="C111" s="161"/>
+      <c r="D111" s="174"/>
       <c r="E111" s="8" t="s">
         <v>150</v>
       </c>
@@ -8203,8 +8257,8 @@
       <c r="B112" s="7">
         <v>6</v>
       </c>
-      <c r="C112" s="163"/>
-      <c r="D112" s="150" t="s">
+      <c r="C112" s="161"/>
+      <c r="D112" s="172" t="s">
         <v>151</v>
       </c>
       <c r="E112" s="8" t="s">
@@ -8227,8 +8281,8 @@
       <c r="B113" s="7">
         <v>7</v>
       </c>
-      <c r="C113" s="163"/>
-      <c r="D113" s="151"/>
+      <c r="C113" s="161"/>
+      <c r="D113" s="173"/>
       <c r="E113" s="8" t="s">
         <v>153</v>
       </c>
@@ -8249,8 +8303,8 @@
       <c r="B114" s="7">
         <v>8</v>
       </c>
-      <c r="C114" s="163"/>
-      <c r="D114" s="151"/>
+      <c r="C114" s="161"/>
+      <c r="D114" s="173"/>
       <c r="E114" s="8" t="s">
         <v>154</v>
       </c>
@@ -8271,8 +8325,8 @@
       <c r="B115" s="7">
         <v>9</v>
       </c>
-      <c r="C115" s="163"/>
-      <c r="D115" s="152"/>
+      <c r="C115" s="161"/>
+      <c r="D115" s="174"/>
       <c r="E115" s="8" t="s">
         <v>155</v>
       </c>
@@ -8293,7 +8347,7 @@
       <c r="B116" s="24">
         <v>10</v>
       </c>
-      <c r="C116" s="164"/>
+      <c r="C116" s="162"/>
       <c r="D116" s="31" t="s">
         <v>156</v>
       </c>
@@ -8317,10 +8371,10 @@
       <c r="B117" s="7">
         <v>1</v>
       </c>
-      <c r="C117" s="165" t="s">
+      <c r="C117" s="151" t="s">
         <v>158</v>
       </c>
-      <c r="D117" s="150" t="s">
+      <c r="D117" s="172" t="s">
         <v>159</v>
       </c>
       <c r="E117" s="8" t="s">
@@ -8343,8 +8397,8 @@
       <c r="B118" s="7">
         <v>2</v>
       </c>
-      <c r="C118" s="166"/>
-      <c r="D118" s="151"/>
+      <c r="C118" s="152"/>
+      <c r="D118" s="173"/>
       <c r="E118" s="8" t="s">
         <v>161</v>
       </c>
@@ -8365,8 +8419,8 @@
       <c r="B119" s="7">
         <v>3</v>
       </c>
-      <c r="C119" s="166"/>
-      <c r="D119" s="151"/>
+      <c r="C119" s="152"/>
+      <c r="D119" s="173"/>
       <c r="E119" s="8" t="s">
         <v>162</v>
       </c>
@@ -8387,8 +8441,8 @@
       <c r="B120" s="7">
         <v>4</v>
       </c>
-      <c r="C120" s="166"/>
-      <c r="D120" s="152"/>
+      <c r="C120" s="152"/>
+      <c r="D120" s="174"/>
       <c r="E120" s="8" t="s">
         <v>163</v>
       </c>
@@ -8409,8 +8463,8 @@
       <c r="B121" s="7">
         <v>5</v>
       </c>
-      <c r="C121" s="166"/>
-      <c r="D121" s="150" t="s">
+      <c r="C121" s="152"/>
+      <c r="D121" s="172" t="s">
         <v>164</v>
       </c>
       <c r="E121" s="8" t="s">
@@ -8433,8 +8487,8 @@
       <c r="B122" s="7">
         <v>6</v>
       </c>
-      <c r="C122" s="166"/>
-      <c r="D122" s="152"/>
+      <c r="C122" s="152"/>
+      <c r="D122" s="174"/>
       <c r="E122" s="8" t="s">
         <v>166</v>
       </c>
@@ -8455,8 +8509,8 @@
       <c r="B123" s="7">
         <v>7</v>
       </c>
-      <c r="C123" s="166"/>
-      <c r="D123" s="150" t="s">
+      <c r="C123" s="152"/>
+      <c r="D123" s="172" t="s">
         <v>167</v>
       </c>
       <c r="E123" s="8" t="s">
@@ -8479,8 +8533,8 @@
       <c r="B124" s="7">
         <v>8</v>
       </c>
-      <c r="C124" s="166"/>
-      <c r="D124" s="151"/>
+      <c r="C124" s="152"/>
+      <c r="D124" s="173"/>
       <c r="E124" s="28" t="s">
         <v>169</v>
       </c>
@@ -8501,8 +8555,8 @@
       <c r="B125" s="7">
         <v>9</v>
       </c>
-      <c r="C125" s="167"/>
-      <c r="D125" s="152"/>
+      <c r="C125" s="153"/>
+      <c r="D125" s="174"/>
       <c r="E125" s="8" t="s">
         <v>170</v>
       </c>
@@ -8517,18 +8571,18 @@
       <c r="J125" s="11"/>
     </row>
     <row r="126" spans="1:10" ht="13.8">
-      <c r="A126" s="174" t="s">
+      <c r="A126" s="193" t="s">
         <v>171</v>
       </c>
-      <c r="B126" s="175"/>
-      <c r="C126" s="175"/>
-      <c r="D126" s="175"/>
-      <c r="E126" s="175"/>
-      <c r="F126" s="175"/>
-      <c r="G126" s="175"/>
-      <c r="H126" s="175"/>
-      <c r="I126" s="175"/>
-      <c r="J126" s="176"/>
+      <c r="B126" s="194"/>
+      <c r="C126" s="194"/>
+      <c r="D126" s="194"/>
+      <c r="E126" s="194"/>
+      <c r="F126" s="194"/>
+      <c r="G126" s="194"/>
+      <c r="H126" s="194"/>
+      <c r="I126" s="194"/>
+      <c r="J126" s="195"/>
     </row>
     <row r="127" spans="1:10" ht="13.8">
       <c r="A127" s="6">
@@ -8537,10 +8591,10 @@
       <c r="B127" s="7">
         <v>1</v>
       </c>
-      <c r="C127" s="168" t="s">
+      <c r="C127" s="154" t="s">
         <v>172</v>
       </c>
-      <c r="D127" s="150" t="s">
+      <c r="D127" s="172" t="s">
         <v>173</v>
       </c>
       <c r="E127" s="32" t="s">
@@ -8561,8 +8615,8 @@
       <c r="B128" s="7">
         <v>2</v>
       </c>
-      <c r="C128" s="169"/>
-      <c r="D128" s="151"/>
+      <c r="C128" s="155"/>
+      <c r="D128" s="173"/>
       <c r="E128" s="32" t="s">
         <v>175</v>
       </c>
@@ -8581,8 +8635,8 @@
       <c r="B129" s="7">
         <v>3</v>
       </c>
-      <c r="C129" s="169"/>
-      <c r="D129" s="151"/>
+      <c r="C129" s="155"/>
+      <c r="D129" s="173"/>
       <c r="E129" s="32" t="s">
         <v>176</v>
       </c>
@@ -8601,8 +8655,8 @@
       <c r="B130" s="7">
         <v>4</v>
       </c>
-      <c r="C130" s="169"/>
-      <c r="D130" s="152"/>
+      <c r="C130" s="155"/>
+      <c r="D130" s="174"/>
       <c r="E130" s="32" t="s">
         <v>177</v>
       </c>
@@ -8621,8 +8675,8 @@
       <c r="B131" s="7">
         <v>5</v>
       </c>
-      <c r="C131" s="169"/>
-      <c r="D131" s="150" t="s">
+      <c r="C131" s="155"/>
+      <c r="D131" s="172" t="s">
         <v>178</v>
       </c>
       <c r="E131" s="32" t="s">
@@ -8643,8 +8697,8 @@
       <c r="B132" s="7">
         <v>6</v>
       </c>
-      <c r="C132" s="170"/>
-      <c r="D132" s="152"/>
+      <c r="C132" s="156"/>
+      <c r="D132" s="174"/>
       <c r="E132" s="32" t="s">
         <v>180</v>
       </c>
@@ -8657,18 +8711,18 @@
       <c r="J132" s="11"/>
     </row>
     <row r="133" spans="1:10" ht="13.8">
-      <c r="A133" s="156" t="s">
+      <c r="A133" s="196" t="s">
         <v>181</v>
       </c>
-      <c r="B133" s="157"/>
-      <c r="C133" s="157"/>
-      <c r="D133" s="157"/>
-      <c r="E133" s="157"/>
-      <c r="F133" s="157"/>
-      <c r="G133" s="157"/>
-      <c r="H133" s="157"/>
-      <c r="I133" s="157"/>
-      <c r="J133" s="158"/>
+      <c r="B133" s="197"/>
+      <c r="C133" s="197"/>
+      <c r="D133" s="197"/>
+      <c r="E133" s="197"/>
+      <c r="F133" s="197"/>
+      <c r="G133" s="197"/>
+      <c r="H133" s="197"/>
+      <c r="I133" s="197"/>
+      <c r="J133" s="198"/>
     </row>
     <row r="134" spans="1:10" ht="13.8">
       <c r="A134" s="6">
@@ -8677,10 +8731,10 @@
       <c r="B134" s="7">
         <v>1</v>
       </c>
-      <c r="C134" s="159" t="s">
+      <c r="C134" s="157" t="s">
         <v>182</v>
       </c>
-      <c r="D134" s="150" t="s">
+      <c r="D134" s="172" t="s">
         <v>183</v>
       </c>
       <c r="E134" s="8" t="s">
@@ -8703,8 +8757,8 @@
       <c r="B135" s="7">
         <v>2</v>
       </c>
-      <c r="C135" s="160"/>
-      <c r="D135" s="151"/>
+      <c r="C135" s="158"/>
+      <c r="D135" s="173"/>
       <c r="E135" s="8" t="s">
         <v>185</v>
       </c>
@@ -8725,8 +8779,8 @@
       <c r="B136" s="7">
         <v>3</v>
       </c>
-      <c r="C136" s="160"/>
-      <c r="D136" s="152"/>
+      <c r="C136" s="158"/>
+      <c r="D136" s="174"/>
       <c r="E136" s="8" t="s">
         <v>186</v>
       </c>
@@ -8747,8 +8801,8 @@
       <c r="B137" s="7">
         <v>4</v>
       </c>
-      <c r="C137" s="160"/>
-      <c r="D137" s="150" t="s">
+      <c r="C137" s="158"/>
+      <c r="D137" s="172" t="s">
         <v>187</v>
       </c>
       <c r="E137" s="8" t="s">
@@ -8771,8 +8825,8 @@
       <c r="B138" s="7">
         <v>5</v>
       </c>
-      <c r="C138" s="160"/>
-      <c r="D138" s="151"/>
+      <c r="C138" s="158"/>
+      <c r="D138" s="173"/>
       <c r="E138" s="8" t="s">
         <v>189</v>
       </c>
@@ -8793,8 +8847,8 @@
       <c r="B139" s="7">
         <v>6</v>
       </c>
-      <c r="C139" s="160"/>
-      <c r="D139" s="151"/>
+      <c r="C139" s="158"/>
+      <c r="D139" s="173"/>
       <c r="E139" s="8" t="s">
         <v>190</v>
       </c>
@@ -8815,8 +8869,8 @@
       <c r="B140" s="7">
         <v>7</v>
       </c>
-      <c r="C140" s="160"/>
-      <c r="D140" s="151"/>
+      <c r="C140" s="158"/>
+      <c r="D140" s="173"/>
       <c r="E140" s="8" t="s">
         <v>191</v>
       </c>
@@ -8837,8 +8891,8 @@
       <c r="B141" s="7">
         <v>8</v>
       </c>
-      <c r="C141" s="160"/>
-      <c r="D141" s="151"/>
+      <c r="C141" s="158"/>
+      <c r="D141" s="173"/>
       <c r="E141" s="8" t="s">
         <v>192</v>
       </c>
@@ -8859,8 +8913,8 @@
       <c r="B142" s="7">
         <v>9</v>
       </c>
-      <c r="C142" s="160"/>
-      <c r="D142" s="151"/>
+      <c r="C142" s="158"/>
+      <c r="D142" s="173"/>
       <c r="E142" s="8" t="s">
         <v>193</v>
       </c>
@@ -8881,8 +8935,8 @@
       <c r="B143" s="7">
         <v>10</v>
       </c>
-      <c r="C143" s="160"/>
-      <c r="D143" s="152"/>
+      <c r="C143" s="158"/>
+      <c r="D143" s="174"/>
       <c r="E143" s="8" t="s">
         <v>194</v>
       </c>
@@ -8903,8 +8957,8 @@
       <c r="B144" s="7">
         <v>11</v>
       </c>
-      <c r="C144" s="160"/>
-      <c r="D144" s="150" t="s">
+      <c r="C144" s="158"/>
+      <c r="D144" s="172" t="s">
         <v>195</v>
       </c>
       <c r="E144" s="8" t="s">
@@ -8927,8 +8981,8 @@
       <c r="B145" s="7">
         <v>12</v>
       </c>
-      <c r="C145" s="160"/>
-      <c r="D145" s="151"/>
+      <c r="C145" s="158"/>
+      <c r="D145" s="173"/>
       <c r="E145" s="8" t="s">
         <v>197</v>
       </c>
@@ -8949,8 +9003,8 @@
       <c r="B146" s="7">
         <v>13</v>
       </c>
-      <c r="C146" s="160"/>
-      <c r="D146" s="151"/>
+      <c r="C146" s="158"/>
+      <c r="D146" s="173"/>
       <c r="E146" s="8" t="s">
         <v>198</v>
       </c>
@@ -8971,8 +9025,8 @@
       <c r="B147" s="7">
         <v>14</v>
       </c>
-      <c r="C147" s="160"/>
-      <c r="D147" s="151"/>
+      <c r="C147" s="158"/>
+      <c r="D147" s="173"/>
       <c r="E147" s="8" t="s">
         <v>199</v>
       </c>
@@ -8993,8 +9047,8 @@
       <c r="B148" s="7">
         <v>15</v>
       </c>
-      <c r="C148" s="160"/>
-      <c r="D148" s="151"/>
+      <c r="C148" s="158"/>
+      <c r="D148" s="173"/>
       <c r="E148" s="8" t="s">
         <v>200</v>
       </c>
@@ -9015,8 +9069,8 @@
       <c r="B149" s="7">
         <v>16</v>
       </c>
-      <c r="C149" s="160"/>
-      <c r="D149" s="151"/>
+      <c r="C149" s="158"/>
+      <c r="D149" s="173"/>
       <c r="E149" s="8" t="s">
         <v>201</v>
       </c>
@@ -9037,8 +9091,8 @@
       <c r="B150" s="7">
         <v>17</v>
       </c>
-      <c r="C150" s="160"/>
-      <c r="D150" s="152"/>
+      <c r="C150" s="158"/>
+      <c r="D150" s="174"/>
       <c r="E150" s="8" t="s">
         <v>202</v>
       </c>
@@ -9059,8 +9113,8 @@
       <c r="B151" s="7">
         <v>18</v>
       </c>
-      <c r="C151" s="160"/>
-      <c r="D151" s="150" t="s">
+      <c r="C151" s="158"/>
+      <c r="D151" s="172" t="s">
         <v>203</v>
       </c>
       <c r="E151" s="8" t="s">
@@ -9083,8 +9137,8 @@
       <c r="B152" s="7">
         <v>19</v>
       </c>
-      <c r="C152" s="160"/>
-      <c r="D152" s="151"/>
+      <c r="C152" s="158"/>
+      <c r="D152" s="173"/>
       <c r="E152" s="8" t="s">
         <v>205</v>
       </c>
@@ -9105,8 +9159,8 @@
       <c r="B153" s="7">
         <v>20</v>
       </c>
-      <c r="C153" s="160"/>
-      <c r="D153" s="151"/>
+      <c r="C153" s="158"/>
+      <c r="D153" s="173"/>
       <c r="E153" s="8" t="s">
         <v>206</v>
       </c>
@@ -9127,8 +9181,8 @@
       <c r="B154" s="7">
         <v>21</v>
       </c>
-      <c r="C154" s="160"/>
-      <c r="D154" s="151"/>
+      <c r="C154" s="158"/>
+      <c r="D154" s="173"/>
       <c r="E154" s="8" t="s">
         <v>207</v>
       </c>
@@ -9149,8 +9203,8 @@
       <c r="B155" s="7">
         <v>22</v>
       </c>
-      <c r="C155" s="160"/>
-      <c r="D155" s="151"/>
+      <c r="C155" s="158"/>
+      <c r="D155" s="173"/>
       <c r="E155" s="8" t="s">
         <v>208</v>
       </c>
@@ -9171,8 +9225,8 @@
       <c r="B156" s="7">
         <v>23</v>
       </c>
-      <c r="C156" s="160"/>
-      <c r="D156" s="152"/>
+      <c r="C156" s="158"/>
+      <c r="D156" s="174"/>
       <c r="E156" s="8" t="s">
         <v>209</v>
       </c>
@@ -9193,8 +9247,8 @@
       <c r="B157" s="7">
         <v>24</v>
       </c>
-      <c r="C157" s="160"/>
-      <c r="D157" s="150" t="s">
+      <c r="C157" s="158"/>
+      <c r="D157" s="172" t="s">
         <v>210</v>
       </c>
       <c r="E157" s="8" t="s">
@@ -9217,8 +9271,8 @@
       <c r="B158" s="7">
         <v>25</v>
       </c>
-      <c r="C158" s="160"/>
-      <c r="D158" s="151"/>
+      <c r="C158" s="158"/>
+      <c r="D158" s="173"/>
       <c r="E158" s="8" t="s">
         <v>212</v>
       </c>
@@ -9239,8 +9293,8 @@
       <c r="B159" s="7">
         <v>26</v>
       </c>
-      <c r="C159" s="160"/>
-      <c r="D159" s="152"/>
+      <c r="C159" s="158"/>
+      <c r="D159" s="174"/>
       <c r="E159" s="8" t="s">
         <v>213</v>
       </c>
@@ -9261,8 +9315,8 @@
       <c r="B160" s="7">
         <v>27</v>
       </c>
-      <c r="C160" s="160"/>
-      <c r="D160" s="150" t="s">
+      <c r="C160" s="158"/>
+      <c r="D160" s="172" t="s">
         <v>214</v>
       </c>
       <c r="E160" s="8" t="s">
@@ -9285,8 +9339,8 @@
       <c r="B161" s="7">
         <v>28</v>
       </c>
-      <c r="C161" s="160"/>
-      <c r="D161" s="151"/>
+      <c r="C161" s="158"/>
+      <c r="D161" s="173"/>
       <c r="E161" s="8" t="s">
         <v>216</v>
       </c>
@@ -9307,8 +9361,8 @@
       <c r="B162" s="7">
         <v>29</v>
       </c>
-      <c r="C162" s="160"/>
-      <c r="D162" s="151"/>
+      <c r="C162" s="158"/>
+      <c r="D162" s="173"/>
       <c r="E162" s="8" t="s">
         <v>217</v>
       </c>
@@ -9329,8 +9383,8 @@
       <c r="B163" s="7">
         <v>30</v>
       </c>
-      <c r="C163" s="160"/>
-      <c r="D163" s="151"/>
+      <c r="C163" s="158"/>
+      <c r="D163" s="173"/>
       <c r="E163" s="8" t="s">
         <v>218</v>
       </c>
@@ -9351,8 +9405,8 @@
       <c r="B164" s="7">
         <v>31</v>
       </c>
-      <c r="C164" s="160"/>
-      <c r="D164" s="151"/>
+      <c r="C164" s="158"/>
+      <c r="D164" s="173"/>
       <c r="E164" s="8" t="s">
         <v>219</v>
       </c>
@@ -9373,8 +9427,8 @@
       <c r="B165" s="7">
         <v>32</v>
       </c>
-      <c r="C165" s="160"/>
-      <c r="D165" s="152"/>
+      <c r="C165" s="158"/>
+      <c r="D165" s="174"/>
       <c r="E165" s="8" t="s">
         <v>220</v>
       </c>
@@ -9395,8 +9449,8 @@
       <c r="B166" s="7">
         <v>33</v>
       </c>
-      <c r="C166" s="160"/>
-      <c r="D166" s="150" t="s">
+      <c r="C166" s="158"/>
+      <c r="D166" s="172" t="s">
         <v>221</v>
       </c>
       <c r="E166" s="8" t="s">
@@ -9419,8 +9473,8 @@
       <c r="B167" s="7">
         <v>34</v>
       </c>
-      <c r="C167" s="160"/>
-      <c r="D167" s="151"/>
+      <c r="C167" s="158"/>
+      <c r="D167" s="173"/>
       <c r="E167" s="8" t="s">
         <v>223</v>
       </c>
@@ -9439,8 +9493,8 @@
       <c r="B168" s="7">
         <v>35</v>
       </c>
-      <c r="C168" s="160"/>
-      <c r="D168" s="151"/>
+      <c r="C168" s="158"/>
+      <c r="D168" s="173"/>
       <c r="E168" s="8" t="s">
         <v>224</v>
       </c>
@@ -9461,8 +9515,8 @@
       <c r="B169" s="7">
         <v>36</v>
       </c>
-      <c r="C169" s="160"/>
-      <c r="D169" s="151"/>
+      <c r="C169" s="158"/>
+      <c r="D169" s="173"/>
       <c r="E169" s="8" t="s">
         <v>225</v>
       </c>
@@ -9483,8 +9537,8 @@
       <c r="B170" s="7">
         <v>37</v>
       </c>
-      <c r="C170" s="160"/>
-      <c r="D170" s="151"/>
+      <c r="C170" s="158"/>
+      <c r="D170" s="173"/>
       <c r="E170" s="8" t="s">
         <v>226</v>
       </c>
@@ -9505,8 +9559,8 @@
       <c r="B171" s="7">
         <v>38</v>
       </c>
-      <c r="C171" s="160"/>
-      <c r="D171" s="151"/>
+      <c r="C171" s="158"/>
+      <c r="D171" s="173"/>
       <c r="E171" s="8" t="s">
         <v>227</v>
       </c>
@@ -9527,8 +9581,8 @@
       <c r="B172" s="7">
         <v>39</v>
       </c>
-      <c r="C172" s="160"/>
-      <c r="D172" s="152"/>
+      <c r="C172" s="158"/>
+      <c r="D172" s="174"/>
       <c r="E172" s="8" t="s">
         <v>228</v>
       </c>
@@ -9549,8 +9603,8 @@
       <c r="B173" s="7">
         <v>40</v>
       </c>
-      <c r="C173" s="160"/>
-      <c r="D173" s="150" t="s">
+      <c r="C173" s="158"/>
+      <c r="D173" s="172" t="s">
         <v>48</v>
       </c>
       <c r="E173" s="11" t="s">
@@ -9573,8 +9627,8 @@
       <c r="B174" s="7">
         <v>41</v>
       </c>
-      <c r="C174" s="160"/>
-      <c r="D174" s="151"/>
+      <c r="C174" s="158"/>
+      <c r="D174" s="173"/>
       <c r="E174" s="8" t="s">
         <v>230</v>
       </c>
@@ -9595,8 +9649,8 @@
       <c r="B175" s="7">
         <v>42</v>
       </c>
-      <c r="C175" s="160"/>
-      <c r="D175" s="151"/>
+      <c r="C175" s="158"/>
+      <c r="D175" s="173"/>
       <c r="E175" s="8" t="s">
         <v>231</v>
       </c>
@@ -9617,8 +9671,8 @@
       <c r="B176" s="24">
         <v>43</v>
       </c>
-      <c r="C176" s="161"/>
-      <c r="D176" s="152"/>
+      <c r="C176" s="159"/>
+      <c r="D176" s="174"/>
       <c r="E176" s="17" t="s">
         <v>232</v>
       </c>
@@ -9639,10 +9693,10 @@
       <c r="B177" s="7">
         <v>1</v>
       </c>
-      <c r="C177" s="162" t="s">
+      <c r="C177" s="160" t="s">
         <v>233</v>
       </c>
-      <c r="D177" s="150" t="s">
+      <c r="D177" s="172" t="s">
         <v>234</v>
       </c>
       <c r="E177" s="8" t="s">
@@ -9665,8 +9719,8 @@
       <c r="B178" s="7">
         <v>2</v>
       </c>
-      <c r="C178" s="163"/>
-      <c r="D178" s="152"/>
+      <c r="C178" s="161"/>
+      <c r="D178" s="174"/>
       <c r="E178" s="8" t="s">
         <v>236</v>
       </c>
@@ -9687,8 +9741,8 @@
       <c r="B179" s="7">
         <v>3</v>
       </c>
-      <c r="C179" s="163"/>
-      <c r="D179" s="150" t="s">
+      <c r="C179" s="161"/>
+      <c r="D179" s="172" t="s">
         <v>237</v>
       </c>
       <c r="E179" s="8" t="s">
@@ -9711,8 +9765,8 @@
       <c r="B180" s="7">
         <v>4</v>
       </c>
-      <c r="C180" s="163"/>
-      <c r="D180" s="151"/>
+      <c r="C180" s="161"/>
+      <c r="D180" s="173"/>
       <c r="E180" s="8" t="s">
         <v>239</v>
       </c>
@@ -9733,8 +9787,8 @@
       <c r="B181" s="7">
         <v>5</v>
       </c>
-      <c r="C181" s="163"/>
-      <c r="D181" s="151"/>
+      <c r="C181" s="161"/>
+      <c r="D181" s="173"/>
       <c r="E181" s="8" t="s">
         <v>240</v>
       </c>
@@ -9755,8 +9809,8 @@
       <c r="B182" s="7">
         <v>6</v>
       </c>
-      <c r="C182" s="163"/>
-      <c r="D182" s="151"/>
+      <c r="C182" s="161"/>
+      <c r="D182" s="173"/>
       <c r="E182" s="8" t="s">
         <v>241</v>
       </c>
@@ -9777,8 +9831,8 @@
       <c r="B183" s="7">
         <v>7</v>
       </c>
-      <c r="C183" s="163"/>
-      <c r="D183" s="151"/>
+      <c r="C183" s="161"/>
+      <c r="D183" s="173"/>
       <c r="E183" s="8" t="s">
         <v>242</v>
       </c>
@@ -9799,8 +9853,8 @@
       <c r="B184" s="7">
         <v>8</v>
       </c>
-      <c r="C184" s="163"/>
-      <c r="D184" s="152"/>
+      <c r="C184" s="161"/>
+      <c r="D184" s="174"/>
       <c r="E184" s="8" t="s">
         <v>243</v>
       </c>
@@ -9821,8 +9875,8 @@
       <c r="B185" s="7">
         <v>9</v>
       </c>
-      <c r="C185" s="163"/>
-      <c r="D185" s="150" t="s">
+      <c r="C185" s="161"/>
+      <c r="D185" s="172" t="s">
         <v>244</v>
       </c>
       <c r="E185" s="8" t="s">
@@ -9845,8 +9899,8 @@
       <c r="B186" s="7">
         <v>10</v>
       </c>
-      <c r="C186" s="163"/>
-      <c r="D186" s="152"/>
+      <c r="C186" s="161"/>
+      <c r="D186" s="174"/>
       <c r="E186" s="8" t="s">
         <v>246</v>
       </c>
@@ -9867,8 +9921,8 @@
       <c r="B187" s="7">
         <v>11</v>
       </c>
-      <c r="C187" s="163"/>
-      <c r="D187" s="150" t="s">
+      <c r="C187" s="161"/>
+      <c r="D187" s="172" t="s">
         <v>247</v>
       </c>
       <c r="E187" s="8" t="s">
@@ -9891,8 +9945,8 @@
       <c r="B188" s="7">
         <v>12</v>
       </c>
-      <c r="C188" s="163"/>
-      <c r="D188" s="151"/>
+      <c r="C188" s="161"/>
+      <c r="D188" s="173"/>
       <c r="E188" s="8" t="s">
         <v>249</v>
       </c>
@@ -9913,8 +9967,8 @@
       <c r="B189" s="7">
         <v>13</v>
       </c>
-      <c r="C189" s="163"/>
-      <c r="D189" s="151"/>
+      <c r="C189" s="161"/>
+      <c r="D189" s="173"/>
       <c r="E189" s="11" t="s">
         <v>250</v>
       </c>
@@ -9935,8 +9989,8 @@
       <c r="B190" s="7">
         <v>14</v>
       </c>
-      <c r="C190" s="163"/>
-      <c r="D190" s="152"/>
+      <c r="C190" s="161"/>
+      <c r="D190" s="174"/>
       <c r="E190" s="8" t="s">
         <v>251</v>
       </c>
@@ -9957,8 +10011,8 @@
       <c r="B191" s="7">
         <v>15</v>
       </c>
-      <c r="C191" s="163"/>
-      <c r="D191" s="150" t="s">
+      <c r="C191" s="161"/>
+      <c r="D191" s="172" t="s">
         <v>252</v>
       </c>
       <c r="E191" s="8" t="s">
@@ -9981,8 +10035,8 @@
       <c r="B192" s="7">
         <v>16</v>
       </c>
-      <c r="C192" s="163"/>
-      <c r="D192" s="151"/>
+      <c r="C192" s="161"/>
+      <c r="D192" s="173"/>
       <c r="E192" s="8" t="s">
         <v>254</v>
       </c>
@@ -10003,8 +10057,8 @@
       <c r="B193" s="7">
         <v>17</v>
       </c>
-      <c r="C193" s="163"/>
-      <c r="D193" s="151"/>
+      <c r="C193" s="161"/>
+      <c r="D193" s="173"/>
       <c r="E193" s="8" t="s">
         <v>255</v>
       </c>
@@ -10025,8 +10079,8 @@
       <c r="B194" s="7">
         <v>18</v>
       </c>
-      <c r="C194" s="163"/>
-      <c r="D194" s="151"/>
+      <c r="C194" s="161"/>
+      <c r="D194" s="173"/>
       <c r="E194" s="8" t="s">
         <v>256</v>
       </c>
@@ -10047,8 +10101,8 @@
       <c r="B195" s="7">
         <v>19</v>
       </c>
-      <c r="C195" s="163"/>
-      <c r="D195" s="151"/>
+      <c r="C195" s="161"/>
+      <c r="D195" s="173"/>
       <c r="E195" s="8" t="s">
         <v>257</v>
       </c>
@@ -10069,8 +10123,8 @@
       <c r="B196" s="7">
         <v>20</v>
       </c>
-      <c r="C196" s="163"/>
-      <c r="D196" s="151"/>
+      <c r="C196" s="161"/>
+      <c r="D196" s="173"/>
       <c r="E196" s="8" t="s">
         <v>258</v>
       </c>
@@ -10091,8 +10145,8 @@
       <c r="B197" s="7">
         <v>21</v>
       </c>
-      <c r="C197" s="163"/>
-      <c r="D197" s="151"/>
+      <c r="C197" s="161"/>
+      <c r="D197" s="173"/>
       <c r="E197" s="8" t="s">
         <v>259</v>
       </c>
@@ -10113,8 +10167,8 @@
       <c r="B198" s="7">
         <v>22</v>
       </c>
-      <c r="C198" s="163"/>
-      <c r="D198" s="152"/>
+      <c r="C198" s="161"/>
+      <c r="D198" s="174"/>
       <c r="E198" s="8" t="s">
         <v>260</v>
       </c>
@@ -10135,8 +10189,8 @@
       <c r="B199" s="7">
         <v>23</v>
       </c>
-      <c r="C199" s="163"/>
-      <c r="D199" s="150" t="s">
+      <c r="C199" s="161"/>
+      <c r="D199" s="172" t="s">
         <v>261</v>
       </c>
       <c r="E199" s="8" t="s">
@@ -10159,8 +10213,8 @@
       <c r="B200" s="7">
         <v>24</v>
       </c>
-      <c r="C200" s="163"/>
-      <c r="D200" s="151"/>
+      <c r="C200" s="161"/>
+      <c r="D200" s="173"/>
       <c r="E200" s="8" t="s">
         <v>263</v>
       </c>
@@ -10181,8 +10235,8 @@
       <c r="B201" s="7">
         <v>25</v>
       </c>
-      <c r="C201" s="163"/>
-      <c r="D201" s="151"/>
+      <c r="C201" s="161"/>
+      <c r="D201" s="173"/>
       <c r="E201" s="8" t="s">
         <v>264</v>
       </c>
@@ -10203,8 +10257,8 @@
       <c r="B202" s="7">
         <v>26</v>
       </c>
-      <c r="C202" s="163"/>
-      <c r="D202" s="152"/>
+      <c r="C202" s="161"/>
+      <c r="D202" s="174"/>
       <c r="E202" s="8" t="s">
         <v>265</v>
       </c>
@@ -10225,8 +10279,8 @@
       <c r="B203" s="7">
         <v>27</v>
       </c>
-      <c r="C203" s="163"/>
-      <c r="D203" s="150" t="s">
+      <c r="C203" s="161"/>
+      <c r="D203" s="172" t="s">
         <v>266</v>
       </c>
       <c r="E203" s="8" t="s">
@@ -10249,8 +10303,8 @@
       <c r="B204" s="24">
         <v>28</v>
       </c>
-      <c r="C204" s="164"/>
-      <c r="D204" s="152"/>
+      <c r="C204" s="162"/>
+      <c r="D204" s="174"/>
       <c r="E204" s="17" t="s">
         <v>268</v>
       </c>
@@ -10271,10 +10325,10 @@
       <c r="B205" s="7">
         <v>1</v>
       </c>
-      <c r="C205" s="165" t="s">
+      <c r="C205" s="151" t="s">
         <v>269</v>
       </c>
-      <c r="D205" s="150" t="s">
+      <c r="D205" s="172" t="s">
         <v>270</v>
       </c>
       <c r="E205" s="8" t="s">
@@ -10297,8 +10351,8 @@
       <c r="B206" s="7">
         <v>2</v>
       </c>
-      <c r="C206" s="166"/>
-      <c r="D206" s="151"/>
+      <c r="C206" s="152"/>
+      <c r="D206" s="173"/>
       <c r="E206" s="8" t="s">
         <v>272</v>
       </c>
@@ -10319,8 +10373,8 @@
       <c r="B207" s="7">
         <v>3</v>
       </c>
-      <c r="C207" s="166"/>
-      <c r="D207" s="151"/>
+      <c r="C207" s="152"/>
+      <c r="D207" s="173"/>
       <c r="E207" s="8" t="s">
         <v>273</v>
       </c>
@@ -10341,8 +10395,8 @@
       <c r="B208" s="7">
         <v>4</v>
       </c>
-      <c r="C208" s="166"/>
-      <c r="D208" s="151"/>
+      <c r="C208" s="152"/>
+      <c r="D208" s="173"/>
       <c r="E208" s="8" t="s">
         <v>274</v>
       </c>
@@ -10363,8 +10417,8 @@
       <c r="B209" s="7">
         <v>5</v>
       </c>
-      <c r="C209" s="166"/>
-      <c r="D209" s="152"/>
+      <c r="C209" s="152"/>
+      <c r="D209" s="174"/>
       <c r="E209" s="8" t="s">
         <v>275</v>
       </c>
@@ -10385,8 +10439,8 @@
       <c r="B210" s="7">
         <v>6</v>
       </c>
-      <c r="C210" s="166"/>
-      <c r="D210" s="150" t="s">
+      <c r="C210" s="152"/>
+      <c r="D210" s="172" t="s">
         <v>276</v>
       </c>
       <c r="E210" s="8" t="s">
@@ -10409,8 +10463,8 @@
       <c r="B211" s="7">
         <v>7</v>
       </c>
-      <c r="C211" s="166"/>
-      <c r="D211" s="152"/>
+      <c r="C211" s="152"/>
+      <c r="D211" s="174"/>
       <c r="E211" s="8" t="s">
         <v>278</v>
       </c>
@@ -10431,8 +10485,8 @@
       <c r="B212" s="7">
         <v>8</v>
       </c>
-      <c r="C212" s="166"/>
-      <c r="D212" s="150" t="s">
+      <c r="C212" s="152"/>
+      <c r="D212" s="172" t="s">
         <v>279</v>
       </c>
       <c r="E212" s="8" t="s">
@@ -10455,8 +10509,8 @@
       <c r="B213" s="7">
         <v>9</v>
       </c>
-      <c r="C213" s="166"/>
-      <c r="D213" s="151"/>
+      <c r="C213" s="152"/>
+      <c r="D213" s="173"/>
       <c r="E213" s="8" t="s">
         <v>281</v>
       </c>
@@ -10477,8 +10531,8 @@
       <c r="B214" s="7">
         <v>10</v>
       </c>
-      <c r="C214" s="167"/>
-      <c r="D214" s="152"/>
+      <c r="C214" s="153"/>
+      <c r="D214" s="174"/>
       <c r="E214" s="8" t="s">
         <v>282</v>
       </c>
@@ -10493,18 +10547,18 @@
       <c r="J214" s="11"/>
     </row>
     <row r="215" spans="1:10" ht="13.8">
-      <c r="A215" s="186" t="s">
+      <c r="A215" s="181" t="s">
         <v>283</v>
       </c>
-      <c r="B215" s="187"/>
-      <c r="C215" s="187"/>
-      <c r="D215" s="187"/>
-      <c r="E215" s="187"/>
-      <c r="F215" s="187"/>
-      <c r="G215" s="187"/>
-      <c r="H215" s="187"/>
-      <c r="I215" s="187"/>
-      <c r="J215" s="188"/>
+      <c r="B215" s="182"/>
+      <c r="C215" s="182"/>
+      <c r="D215" s="182"/>
+      <c r="E215" s="182"/>
+      <c r="F215" s="182"/>
+      <c r="G215" s="182"/>
+      <c r="H215" s="182"/>
+      <c r="I215" s="182"/>
+      <c r="J215" s="183"/>
     </row>
     <row r="216" spans="1:10" ht="13.8">
       <c r="A216" s="6">
@@ -10513,10 +10567,10 @@
       <c r="B216" s="7">
         <v>1</v>
       </c>
-      <c r="C216" s="168" t="s">
+      <c r="C216" s="154" t="s">
         <v>284</v>
       </c>
-      <c r="D216" s="150" t="s">
+      <c r="D216" s="172" t="s">
         <v>285</v>
       </c>
       <c r="E216" s="8" t="s">
@@ -10539,8 +10593,8 @@
       <c r="B217" s="7">
         <v>2</v>
       </c>
-      <c r="C217" s="169"/>
-      <c r="D217" s="151"/>
+      <c r="C217" s="155"/>
+      <c r="D217" s="173"/>
       <c r="E217" s="8" t="s">
         <v>287</v>
       </c>
@@ -10561,8 +10615,8 @@
       <c r="B218" s="7">
         <v>3</v>
       </c>
-      <c r="C218" s="169"/>
-      <c r="D218" s="151"/>
+      <c r="C218" s="155"/>
+      <c r="D218" s="173"/>
       <c r="E218" s="8" t="s">
         <v>288</v>
       </c>
@@ -10583,8 +10637,8 @@
       <c r="B219" s="7">
         <v>4</v>
       </c>
-      <c r="C219" s="169"/>
-      <c r="D219" s="151"/>
+      <c r="C219" s="155"/>
+      <c r="D219" s="173"/>
       <c r="E219" s="8" t="s">
         <v>289</v>
       </c>
@@ -10605,8 +10659,8 @@
       <c r="B220" s="7">
         <v>5</v>
       </c>
-      <c r="C220" s="169"/>
-      <c r="D220" s="151"/>
+      <c r="C220" s="155"/>
+      <c r="D220" s="173"/>
       <c r="E220" s="8" t="s">
         <v>290</v>
       </c>
@@ -10627,8 +10681,8 @@
       <c r="B221" s="7">
         <v>6</v>
       </c>
-      <c r="C221" s="169"/>
-      <c r="D221" s="151"/>
+      <c r="C221" s="155"/>
+      <c r="D221" s="173"/>
       <c r="E221" s="8" t="s">
         <v>291</v>
       </c>
@@ -10649,8 +10703,8 @@
       <c r="B222" s="7">
         <v>7</v>
       </c>
-      <c r="C222" s="169"/>
-      <c r="D222" s="151"/>
+      <c r="C222" s="155"/>
+      <c r="D222" s="173"/>
       <c r="E222" s="8" t="s">
         <v>292</v>
       </c>
@@ -10671,8 +10725,8 @@
       <c r="B223" s="7">
         <v>8</v>
       </c>
-      <c r="C223" s="169"/>
-      <c r="D223" s="151"/>
+      <c r="C223" s="155"/>
+      <c r="D223" s="173"/>
       <c r="E223" s="8" t="s">
         <v>293</v>
       </c>
@@ -10693,8 +10747,8 @@
       <c r="B224" s="7">
         <v>9</v>
       </c>
-      <c r="C224" s="169"/>
-      <c r="D224" s="151"/>
+      <c r="C224" s="155"/>
+      <c r="D224" s="173"/>
       <c r="E224" s="8" t="s">
         <v>294</v>
       </c>
@@ -10715,8 +10769,8 @@
       <c r="B225" s="7">
         <v>10</v>
       </c>
-      <c r="C225" s="169"/>
-      <c r="D225" s="152"/>
+      <c r="C225" s="155"/>
+      <c r="D225" s="174"/>
       <c r="E225" s="8" t="s">
         <v>295</v>
       </c>
@@ -10737,8 +10791,8 @@
       <c r="B226" s="7">
         <v>11</v>
       </c>
-      <c r="C226" s="169"/>
-      <c r="D226" s="150" t="s">
+      <c r="C226" s="155"/>
+      <c r="D226" s="172" t="s">
         <v>296</v>
       </c>
       <c r="E226" s="8" t="s">
@@ -10761,8 +10815,8 @@
       <c r="B227" s="7">
         <v>12</v>
       </c>
-      <c r="C227" s="169"/>
-      <c r="D227" s="151"/>
+      <c r="C227" s="155"/>
+      <c r="D227" s="173"/>
       <c r="E227" s="8" t="s">
         <v>298</v>
       </c>
@@ -10783,8 +10837,8 @@
       <c r="B228" s="7">
         <v>13</v>
       </c>
-      <c r="C228" s="169"/>
-      <c r="D228" s="151"/>
+      <c r="C228" s="155"/>
+      <c r="D228" s="173"/>
       <c r="E228" s="8" t="s">
         <v>299</v>
       </c>
@@ -10805,8 +10859,8 @@
       <c r="B229" s="7">
         <v>14</v>
       </c>
-      <c r="C229" s="169"/>
-      <c r="D229" s="151"/>
+      <c r="C229" s="155"/>
+      <c r="D229" s="173"/>
       <c r="E229" s="8" t="s">
         <v>300</v>
       </c>
@@ -10827,8 +10881,8 @@
       <c r="B230" s="7">
         <v>15</v>
       </c>
-      <c r="C230" s="169"/>
-      <c r="D230" s="151"/>
+      <c r="C230" s="155"/>
+      <c r="D230" s="173"/>
       <c r="E230" s="8" t="s">
         <v>301</v>
       </c>
@@ -10849,8 +10903,8 @@
       <c r="B231" s="7">
         <v>16</v>
       </c>
-      <c r="C231" s="169"/>
-      <c r="D231" s="151"/>
+      <c r="C231" s="155"/>
+      <c r="D231" s="173"/>
       <c r="E231" s="8" t="s">
         <v>302</v>
       </c>
@@ -10871,8 +10925,8 @@
       <c r="B232" s="7">
         <v>17</v>
       </c>
-      <c r="C232" s="169"/>
-      <c r="D232" s="151"/>
+      <c r="C232" s="155"/>
+      <c r="D232" s="173"/>
       <c r="E232" s="8" t="s">
         <v>303</v>
       </c>
@@ -10893,8 +10947,8 @@
       <c r="B233" s="7">
         <v>18</v>
       </c>
-      <c r="C233" s="169"/>
-      <c r="D233" s="152"/>
+      <c r="C233" s="155"/>
+      <c r="D233" s="174"/>
       <c r="E233" s="8" t="s">
         <v>304</v>
       </c>
@@ -10915,8 +10969,8 @@
       <c r="B234" s="7">
         <v>19</v>
       </c>
-      <c r="C234" s="169"/>
-      <c r="D234" s="150" t="s">
+      <c r="C234" s="155"/>
+      <c r="D234" s="172" t="s">
         <v>305</v>
       </c>
       <c r="E234" s="8" t="s">
@@ -10939,8 +10993,8 @@
       <c r="B235" s="7">
         <v>20</v>
       </c>
-      <c r="C235" s="169"/>
-      <c r="D235" s="151"/>
+      <c r="C235" s="155"/>
+      <c r="D235" s="173"/>
       <c r="E235" s="8" t="s">
         <v>307</v>
       </c>
@@ -10961,8 +11015,8 @@
       <c r="B236" s="7">
         <v>21</v>
       </c>
-      <c r="C236" s="169"/>
-      <c r="D236" s="151"/>
+      <c r="C236" s="155"/>
+      <c r="D236" s="173"/>
       <c r="E236" s="8" t="s">
         <v>308</v>
       </c>
@@ -10983,8 +11037,8 @@
       <c r="B237" s="7">
         <v>22</v>
       </c>
-      <c r="C237" s="169"/>
-      <c r="D237" s="151"/>
+      <c r="C237" s="155"/>
+      <c r="D237" s="173"/>
       <c r="E237" s="8" t="s">
         <v>309</v>
       </c>
@@ -11005,8 +11059,8 @@
       <c r="B238" s="7">
         <v>23</v>
       </c>
-      <c r="C238" s="169"/>
-      <c r="D238" s="151"/>
+      <c r="C238" s="155"/>
+      <c r="D238" s="173"/>
       <c r="E238" s="8" t="s">
         <v>310</v>
       </c>
@@ -11027,8 +11081,8 @@
       <c r="B239" s="7">
         <v>24</v>
       </c>
-      <c r="C239" s="169"/>
-      <c r="D239" s="151"/>
+      <c r="C239" s="155"/>
+      <c r="D239" s="173"/>
       <c r="E239" s="8" t="s">
         <v>311</v>
       </c>
@@ -11049,8 +11103,8 @@
       <c r="B240" s="7">
         <v>25</v>
       </c>
-      <c r="C240" s="169"/>
-      <c r="D240" s="152"/>
+      <c r="C240" s="155"/>
+      <c r="D240" s="174"/>
       <c r="E240" s="8" t="s">
         <v>312</v>
       </c>
@@ -11071,8 +11125,8 @@
       <c r="B241" s="7">
         <v>26</v>
       </c>
-      <c r="C241" s="169"/>
-      <c r="D241" s="150" t="s">
+      <c r="C241" s="155"/>
+      <c r="D241" s="172" t="s">
         <v>313</v>
       </c>
       <c r="E241" s="8" t="s">
@@ -11095,8 +11149,8 @@
       <c r="B242" s="7">
         <v>27</v>
       </c>
-      <c r="C242" s="169"/>
-      <c r="D242" s="151"/>
+      <c r="C242" s="155"/>
+      <c r="D242" s="173"/>
       <c r="E242" s="8" t="s">
         <v>315</v>
       </c>
@@ -11117,8 +11171,8 @@
       <c r="B243" s="7">
         <v>28</v>
       </c>
-      <c r="C243" s="169"/>
-      <c r="D243" s="152"/>
+      <c r="C243" s="155"/>
+      <c r="D243" s="174"/>
       <c r="E243" s="8" t="s">
         <v>316</v>
       </c>
@@ -11139,8 +11193,8 @@
       <c r="B244" s="7">
         <v>29</v>
       </c>
-      <c r="C244" s="169"/>
-      <c r="D244" s="150" t="s">
+      <c r="C244" s="155"/>
+      <c r="D244" s="172" t="s">
         <v>317</v>
       </c>
       <c r="E244" s="8" t="s">
@@ -11163,8 +11217,8 @@
       <c r="B245" s="7">
         <v>30</v>
       </c>
-      <c r="C245" s="169"/>
-      <c r="D245" s="151"/>
+      <c r="C245" s="155"/>
+      <c r="D245" s="173"/>
       <c r="E245" s="8" t="s">
         <v>319</v>
       </c>
@@ -11185,8 +11239,8 @@
       <c r="B246" s="7">
         <v>31</v>
       </c>
-      <c r="C246" s="169"/>
-      <c r="D246" s="151"/>
+      <c r="C246" s="155"/>
+      <c r="D246" s="173"/>
       <c r="E246" s="8" t="s">
         <v>320</v>
       </c>
@@ -11207,8 +11261,8 @@
       <c r="B247" s="7">
         <v>32</v>
       </c>
-      <c r="C247" s="169"/>
-      <c r="D247" s="151"/>
+      <c r="C247" s="155"/>
+      <c r="D247" s="173"/>
       <c r="E247" s="8" t="s">
         <v>321</v>
       </c>
@@ -11229,8 +11283,8 @@
       <c r="B248" s="7">
         <v>33</v>
       </c>
-      <c r="C248" s="169"/>
-      <c r="D248" s="151"/>
+      <c r="C248" s="155"/>
+      <c r="D248" s="173"/>
       <c r="E248" s="8" t="s">
         <v>322</v>
       </c>
@@ -11251,8 +11305,8 @@
       <c r="B249" s="24">
         <v>34</v>
       </c>
-      <c r="C249" s="170"/>
-      <c r="D249" s="152"/>
+      <c r="C249" s="156"/>
+      <c r="D249" s="174"/>
       <c r="E249" s="17" t="s">
         <v>323</v>
       </c>
@@ -11273,10 +11327,10 @@
       <c r="B250" s="7">
         <v>1</v>
       </c>
-      <c r="C250" s="159" t="s">
+      <c r="C250" s="157" t="s">
         <v>324</v>
       </c>
-      <c r="D250" s="150" t="s">
+      <c r="D250" s="172" t="s">
         <v>325</v>
       </c>
       <c r="E250" s="8" t="s">
@@ -11299,8 +11353,8 @@
       <c r="B251" s="7">
         <v>2</v>
       </c>
-      <c r="C251" s="160"/>
-      <c r="D251" s="151"/>
+      <c r="C251" s="158"/>
+      <c r="D251" s="173"/>
       <c r="E251" s="8" t="s">
         <v>327</v>
       </c>
@@ -11321,8 +11375,8 @@
       <c r="B252" s="7">
         <v>3</v>
       </c>
-      <c r="C252" s="160"/>
-      <c r="D252" s="151"/>
+      <c r="C252" s="158"/>
+      <c r="D252" s="173"/>
       <c r="E252" s="8" t="s">
         <v>328</v>
       </c>
@@ -11343,8 +11397,8 @@
       <c r="B253" s="7">
         <v>4</v>
       </c>
-      <c r="C253" s="160"/>
-      <c r="D253" s="151"/>
+      <c r="C253" s="158"/>
+      <c r="D253" s="173"/>
       <c r="E253" s="8" t="s">
         <v>329</v>
       </c>
@@ -11365,8 +11419,8 @@
       <c r="B254" s="7">
         <v>5</v>
       </c>
-      <c r="C254" s="160"/>
-      <c r="D254" s="151"/>
+      <c r="C254" s="158"/>
+      <c r="D254" s="173"/>
       <c r="E254" s="8" t="s">
         <v>330</v>
       </c>
@@ -11387,8 +11441,8 @@
       <c r="B255" s="7">
         <v>6</v>
       </c>
-      <c r="C255" s="160"/>
-      <c r="D255" s="151"/>
+      <c r="C255" s="158"/>
+      <c r="D255" s="173"/>
       <c r="E255" s="8" t="s">
         <v>331</v>
       </c>
@@ -11409,8 +11463,8 @@
       <c r="B256" s="7">
         <v>7</v>
       </c>
-      <c r="C256" s="160"/>
-      <c r="D256" s="151"/>
+      <c r="C256" s="158"/>
+      <c r="D256" s="173"/>
       <c r="E256" s="8" t="s">
         <v>332</v>
       </c>
@@ -11431,8 +11485,8 @@
       <c r="B257" s="7">
         <v>8</v>
       </c>
-      <c r="C257" s="160"/>
-      <c r="D257" s="152"/>
+      <c r="C257" s="158"/>
+      <c r="D257" s="174"/>
       <c r="E257" s="8" t="s">
         <v>333</v>
       </c>
@@ -11453,8 +11507,8 @@
       <c r="B258" s="7">
         <v>9</v>
       </c>
-      <c r="C258" s="160"/>
-      <c r="D258" s="150" t="s">
+      <c r="C258" s="158"/>
+      <c r="D258" s="172" t="s">
         <v>334</v>
       </c>
       <c r="E258" s="8" t="s">
@@ -11477,8 +11531,8 @@
       <c r="B259" s="7">
         <v>10</v>
       </c>
-      <c r="C259" s="160"/>
-      <c r="D259" s="152"/>
+      <c r="C259" s="158"/>
+      <c r="D259" s="174"/>
       <c r="E259" s="8" t="s">
         <v>336</v>
       </c>
@@ -11499,8 +11553,8 @@
       <c r="B260" s="7">
         <v>11</v>
       </c>
-      <c r="C260" s="160"/>
-      <c r="D260" s="150" t="s">
+      <c r="C260" s="158"/>
+      <c r="D260" s="172" t="s">
         <v>337</v>
       </c>
       <c r="E260" s="8" t="s">
@@ -11523,8 +11577,8 @@
       <c r="B261" s="7">
         <v>12</v>
       </c>
-      <c r="C261" s="160"/>
-      <c r="D261" s="151"/>
+      <c r="C261" s="158"/>
+      <c r="D261" s="173"/>
       <c r="E261" s="8" t="s">
         <v>339</v>
       </c>
@@ -11545,8 +11599,8 @@
       <c r="B262" s="7">
         <v>13</v>
       </c>
-      <c r="C262" s="160"/>
-      <c r="D262" s="151"/>
+      <c r="C262" s="158"/>
+      <c r="D262" s="173"/>
       <c r="E262" s="8" t="s">
         <v>340</v>
       </c>
@@ -11567,8 +11621,8 @@
       <c r="B263" s="7">
         <v>14</v>
       </c>
-      <c r="C263" s="160"/>
-      <c r="D263" s="151"/>
+      <c r="C263" s="158"/>
+      <c r="D263" s="173"/>
       <c r="E263" s="8" t="s">
         <v>341</v>
       </c>
@@ -11589,8 +11643,8 @@
       <c r="B264" s="7">
         <v>15</v>
       </c>
-      <c r="C264" s="160"/>
-      <c r="D264" s="151"/>
+      <c r="C264" s="158"/>
+      <c r="D264" s="173"/>
       <c r="E264" s="8" t="s">
         <v>342</v>
       </c>
@@ -11611,8 +11665,8 @@
       <c r="B265" s="24">
         <v>16</v>
       </c>
-      <c r="C265" s="161"/>
-      <c r="D265" s="152"/>
+      <c r="C265" s="159"/>
+      <c r="D265" s="174"/>
       <c r="E265" s="17" t="s">
         <v>343</v>
       </c>
@@ -11633,10 +11687,10 @@
       <c r="B266" s="7">
         <v>1</v>
       </c>
-      <c r="C266" s="162" t="s">
+      <c r="C266" s="160" t="s">
         <v>344</v>
       </c>
-      <c r="D266" s="150" t="s">
+      <c r="D266" s="172" t="s">
         <v>345</v>
       </c>
       <c r="E266" s="8" t="s">
@@ -11659,8 +11713,8 @@
       <c r="B267" s="7">
         <v>2</v>
       </c>
-      <c r="C267" s="163"/>
-      <c r="D267" s="151"/>
+      <c r="C267" s="161"/>
+      <c r="D267" s="173"/>
       <c r="E267" s="8" t="s">
         <v>347</v>
       </c>
@@ -11681,8 +11735,8 @@
       <c r="B268" s="7">
         <v>3</v>
       </c>
-      <c r="C268" s="163"/>
-      <c r="D268" s="151"/>
+      <c r="C268" s="161"/>
+      <c r="D268" s="173"/>
       <c r="E268" s="8" t="s">
         <v>348</v>
       </c>
@@ -11703,8 +11757,8 @@
       <c r="B269" s="7">
         <v>4</v>
       </c>
-      <c r="C269" s="163"/>
-      <c r="D269" s="151"/>
+      <c r="C269" s="161"/>
+      <c r="D269" s="173"/>
       <c r="E269" s="8" t="s">
         <v>349</v>
       </c>
@@ -11725,8 +11779,8 @@
       <c r="B270" s="7">
         <v>5</v>
       </c>
-      <c r="C270" s="163"/>
-      <c r="D270" s="152"/>
+      <c r="C270" s="161"/>
+      <c r="D270" s="174"/>
       <c r="E270" s="8" t="s">
         <v>350</v>
       </c>
@@ -11747,8 +11801,8 @@
       <c r="B271" s="7">
         <v>6</v>
       </c>
-      <c r="C271" s="163"/>
-      <c r="D271" s="150" t="s">
+      <c r="C271" s="161"/>
+      <c r="D271" s="172" t="s">
         <v>351</v>
       </c>
       <c r="E271" s="8" t="s">
@@ -11771,8 +11825,8 @@
       <c r="B272" s="7">
         <v>7</v>
       </c>
-      <c r="C272" s="164"/>
-      <c r="D272" s="152"/>
+      <c r="C272" s="162"/>
+      <c r="D272" s="174"/>
       <c r="E272" s="8" t="s">
         <v>353</v>
       </c>
@@ -11787,18 +11841,18 @@
       <c r="J272" s="11"/>
     </row>
     <row r="273" spans="1:10" ht="13.8">
-      <c r="A273" s="183" t="s">
+      <c r="A273" s="184" t="s">
         <v>354</v>
       </c>
-      <c r="B273" s="184"/>
-      <c r="C273" s="184"/>
-      <c r="D273" s="184"/>
-      <c r="E273" s="184"/>
-      <c r="F273" s="184"/>
-      <c r="G273" s="184"/>
-      <c r="H273" s="184"/>
-      <c r="I273" s="184"/>
-      <c r="J273" s="185"/>
+      <c r="B273" s="185"/>
+      <c r="C273" s="185"/>
+      <c r="D273" s="185"/>
+      <c r="E273" s="185"/>
+      <c r="F273" s="185"/>
+      <c r="G273" s="185"/>
+      <c r="H273" s="185"/>
+      <c r="I273" s="185"/>
+      <c r="J273" s="186"/>
     </row>
     <row r="274" spans="1:10" ht="13.8">
       <c r="A274" s="33">
@@ -11807,10 +11861,10 @@
       <c r="B274" s="7">
         <v>1</v>
       </c>
-      <c r="C274" s="177" t="s">
+      <c r="C274" s="163" t="s">
         <v>355</v>
       </c>
-      <c r="D274" s="180" t="s">
+      <c r="D274" s="175" t="s">
         <v>356</v>
       </c>
       <c r="E274" s="13" t="s">
@@ -11833,8 +11887,8 @@
       <c r="B275" s="7">
         <v>2</v>
       </c>
-      <c r="C275" s="178"/>
-      <c r="D275" s="181"/>
+      <c r="C275" s="164"/>
+      <c r="D275" s="176"/>
       <c r="E275" s="13" t="s">
         <v>358</v>
       </c>
@@ -11855,8 +11909,8 @@
       <c r="B276" s="7">
         <v>3</v>
       </c>
-      <c r="C276" s="178"/>
-      <c r="D276" s="181"/>
+      <c r="C276" s="164"/>
+      <c r="D276" s="176"/>
       <c r="E276" s="8" t="s">
         <v>359</v>
       </c>
@@ -11877,8 +11931,8 @@
       <c r="B277" s="7">
         <v>4</v>
       </c>
-      <c r="C277" s="178"/>
-      <c r="D277" s="181"/>
+      <c r="C277" s="164"/>
+      <c r="D277" s="176"/>
       <c r="E277" s="8" t="s">
         <v>360</v>
       </c>
@@ -11899,8 +11953,8 @@
       <c r="B278" s="7">
         <v>5</v>
       </c>
-      <c r="C278" s="178"/>
-      <c r="D278" s="181"/>
+      <c r="C278" s="164"/>
+      <c r="D278" s="176"/>
       <c r="E278" s="8" t="s">
         <v>361</v>
       </c>
@@ -11921,8 +11975,8 @@
       <c r="B279" s="7">
         <v>6</v>
       </c>
-      <c r="C279" s="178"/>
-      <c r="D279" s="181"/>
+      <c r="C279" s="164"/>
+      <c r="D279" s="176"/>
       <c r="E279" s="8" t="s">
         <v>362</v>
       </c>
@@ -11943,8 +11997,8 @@
       <c r="B280" s="7">
         <v>7</v>
       </c>
-      <c r="C280" s="178"/>
-      <c r="D280" s="181"/>
+      <c r="C280" s="164"/>
+      <c r="D280" s="176"/>
       <c r="E280" s="8" t="s">
         <v>363</v>
       </c>
@@ -11965,8 +12019,8 @@
       <c r="B281" s="7">
         <v>8</v>
       </c>
-      <c r="C281" s="178"/>
-      <c r="D281" s="182"/>
+      <c r="C281" s="164"/>
+      <c r="D281" s="177"/>
       <c r="E281" s="13" t="s">
         <v>364</v>
       </c>
@@ -11987,8 +12041,8 @@
       <c r="B282" s="7">
         <v>9</v>
       </c>
-      <c r="C282" s="178"/>
-      <c r="D282" s="180" t="s">
+      <c r="C282" s="164"/>
+      <c r="D282" s="175" t="s">
         <v>365</v>
       </c>
       <c r="E282" s="8" t="s">
@@ -12011,8 +12065,8 @@
       <c r="B283" s="7">
         <v>10</v>
       </c>
-      <c r="C283" s="178"/>
-      <c r="D283" s="181"/>
+      <c r="C283" s="164"/>
+      <c r="D283" s="176"/>
       <c r="E283" s="13" t="s">
         <v>367</v>
       </c>
@@ -12033,8 +12087,8 @@
       <c r="B284" s="7">
         <v>11</v>
       </c>
-      <c r="C284" s="178"/>
-      <c r="D284" s="181"/>
+      <c r="C284" s="164"/>
+      <c r="D284" s="176"/>
       <c r="E284" s="13" t="s">
         <v>368</v>
       </c>
@@ -12055,8 +12109,8 @@
       <c r="B285" s="7">
         <v>12</v>
       </c>
-      <c r="C285" s="178"/>
-      <c r="D285" s="181"/>
+      <c r="C285" s="164"/>
+      <c r="D285" s="176"/>
       <c r="E285" s="13" t="s">
         <v>369</v>
       </c>
@@ -12077,8 +12131,8 @@
       <c r="B286" s="7">
         <v>13</v>
       </c>
-      <c r="C286" s="178"/>
-      <c r="D286" s="181"/>
+      <c r="C286" s="164"/>
+      <c r="D286" s="176"/>
       <c r="E286" s="13" t="s">
         <v>370</v>
       </c>
@@ -12099,8 +12153,8 @@
       <c r="B287" s="7">
         <v>14</v>
       </c>
-      <c r="C287" s="178"/>
-      <c r="D287" s="181"/>
+      <c r="C287" s="164"/>
+      <c r="D287" s="176"/>
       <c r="E287" s="13" t="s">
         <v>371</v>
       </c>
@@ -12121,8 +12175,8 @@
       <c r="B288" s="7">
         <v>15</v>
       </c>
-      <c r="C288" s="178"/>
-      <c r="D288" s="182"/>
+      <c r="C288" s="164"/>
+      <c r="D288" s="177"/>
       <c r="E288" s="13" t="s">
         <v>372</v>
       </c>
@@ -12143,8 +12197,8 @@
       <c r="B289" s="7">
         <v>16</v>
       </c>
-      <c r="C289" s="178"/>
-      <c r="D289" s="180" t="s">
+      <c r="C289" s="164"/>
+      <c r="D289" s="175" t="s">
         <v>373</v>
       </c>
       <c r="E289" s="13" t="s">
@@ -12167,8 +12221,8 @@
       <c r="B290" s="7">
         <v>17</v>
       </c>
-      <c r="C290" s="178"/>
-      <c r="D290" s="181"/>
+      <c r="C290" s="164"/>
+      <c r="D290" s="176"/>
       <c r="E290" s="8" t="s">
         <v>375</v>
       </c>
@@ -12189,8 +12243,8 @@
       <c r="B291" s="7">
         <v>18</v>
       </c>
-      <c r="C291" s="178"/>
-      <c r="D291" s="181"/>
+      <c r="C291" s="164"/>
+      <c r="D291" s="176"/>
       <c r="E291" s="11" t="s">
         <v>376</v>
       </c>
@@ -12211,8 +12265,8 @@
       <c r="B292" s="24">
         <v>19</v>
       </c>
-      <c r="C292" s="179"/>
-      <c r="D292" s="182"/>
+      <c r="C292" s="165"/>
+      <c r="D292" s="177"/>
       <c r="E292" s="20" t="s">
         <v>377</v>
       </c>
@@ -12233,10 +12287,10 @@
       <c r="B293" s="7">
         <v>1</v>
       </c>
-      <c r="C293" s="168" t="s">
+      <c r="C293" s="154" t="s">
         <v>378</v>
       </c>
-      <c r="D293" s="150" t="s">
+      <c r="D293" s="172" t="s">
         <v>379</v>
       </c>
       <c r="E293" s="8" t="s">
@@ -12259,8 +12313,8 @@
       <c r="B294" s="7">
         <v>2</v>
       </c>
-      <c r="C294" s="169"/>
-      <c r="D294" s="151"/>
+      <c r="C294" s="155"/>
+      <c r="D294" s="173"/>
       <c r="E294" s="8" t="s">
         <v>381</v>
       </c>
@@ -12281,8 +12335,8 @@
       <c r="B295" s="7">
         <v>3</v>
       </c>
-      <c r="C295" s="169"/>
-      <c r="D295" s="152"/>
+      <c r="C295" s="155"/>
+      <c r="D295" s="174"/>
       <c r="E295" s="8" t="s">
         <v>382</v>
       </c>
@@ -12301,8 +12355,8 @@
       <c r="B296" s="7">
         <v>4</v>
       </c>
-      <c r="C296" s="169"/>
-      <c r="D296" s="150" t="s">
+      <c r="C296" s="155"/>
+      <c r="D296" s="172" t="s">
         <v>383</v>
       </c>
       <c r="E296" s="37" t="s">
@@ -12325,8 +12379,8 @@
       <c r="B297" s="7">
         <v>5</v>
       </c>
-      <c r="C297" s="169"/>
-      <c r="D297" s="151"/>
+      <c r="C297" s="155"/>
+      <c r="D297" s="173"/>
       <c r="E297" s="8" t="s">
         <v>385</v>
       </c>
@@ -12347,8 +12401,8 @@
       <c r="B298" s="7">
         <v>6</v>
       </c>
-      <c r="C298" s="169"/>
-      <c r="D298" s="151"/>
+      <c r="C298" s="155"/>
+      <c r="D298" s="173"/>
       <c r="E298" s="8" t="s">
         <v>386</v>
       </c>
@@ -12369,8 +12423,8 @@
       <c r="B299" s="7">
         <v>7</v>
       </c>
-      <c r="C299" s="169"/>
-      <c r="D299" s="151"/>
+      <c r="C299" s="155"/>
+      <c r="D299" s="173"/>
       <c r="E299" s="8" t="s">
         <v>387</v>
       </c>
@@ -12391,8 +12445,8 @@
       <c r="B300" s="7">
         <v>8</v>
       </c>
-      <c r="C300" s="169"/>
-      <c r="D300" s="152"/>
+      <c r="C300" s="155"/>
+      <c r="D300" s="174"/>
       <c r="E300" s="8" t="s">
         <v>388</v>
       </c>
@@ -12413,8 +12467,8 @@
       <c r="B301" s="7">
         <v>9</v>
       </c>
-      <c r="C301" s="169"/>
-      <c r="D301" s="150" t="s">
+      <c r="C301" s="155"/>
+      <c r="D301" s="172" t="s">
         <v>389</v>
       </c>
       <c r="E301" s="8" t="s">
@@ -12437,8 +12491,8 @@
       <c r="B302" s="7">
         <v>10</v>
       </c>
-      <c r="C302" s="169"/>
-      <c r="D302" s="151"/>
+      <c r="C302" s="155"/>
+      <c r="D302" s="173"/>
       <c r="E302" s="8" t="s">
         <v>391</v>
       </c>
@@ -12459,8 +12513,8 @@
       <c r="B303" s="7">
         <v>11</v>
       </c>
-      <c r="C303" s="169"/>
-      <c r="D303" s="152"/>
+      <c r="C303" s="155"/>
+      <c r="D303" s="174"/>
       <c r="E303" s="8" t="s">
         <v>392</v>
       </c>
@@ -12481,8 +12535,8 @@
       <c r="B304" s="7">
         <v>12</v>
       </c>
-      <c r="C304" s="169"/>
-      <c r="D304" s="150" t="s">
+      <c r="C304" s="155"/>
+      <c r="D304" s="172" t="s">
         <v>393</v>
       </c>
       <c r="E304" s="8" t="s">
@@ -12505,8 +12559,8 @@
       <c r="B305" s="7">
         <v>13</v>
       </c>
-      <c r="C305" s="169"/>
-      <c r="D305" s="151"/>
+      <c r="C305" s="155"/>
+      <c r="D305" s="173"/>
       <c r="E305" s="8" t="s">
         <v>395</v>
       </c>
@@ -12527,8 +12581,8 @@
       <c r="B306" s="7">
         <v>14</v>
       </c>
-      <c r="C306" s="169"/>
-      <c r="D306" s="151"/>
+      <c r="C306" s="155"/>
+      <c r="D306" s="173"/>
       <c r="E306" s="8" t="s">
         <v>396</v>
       </c>
@@ -12549,8 +12603,8 @@
       <c r="B307" s="24">
         <v>15</v>
       </c>
-      <c r="C307" s="170"/>
-      <c r="D307" s="152"/>
+      <c r="C307" s="156"/>
+      <c r="D307" s="174"/>
       <c r="E307" s="17" t="s">
         <v>397</v>
       </c>
@@ -12571,10 +12625,10 @@
       <c r="B308" s="7">
         <v>1</v>
       </c>
-      <c r="C308" s="195" t="s">
+      <c r="C308" s="166" t="s">
         <v>398</v>
       </c>
-      <c r="D308" s="180" t="s">
+      <c r="D308" s="175" t="s">
         <v>399</v>
       </c>
       <c r="E308" s="13" t="s">
@@ -12597,8 +12651,8 @@
       <c r="B309" s="7">
         <v>2</v>
       </c>
-      <c r="C309" s="196"/>
-      <c r="D309" s="181"/>
+      <c r="C309" s="167"/>
+      <c r="D309" s="176"/>
       <c r="E309" s="8" t="s">
         <v>401</v>
       </c>
@@ -12619,8 +12673,8 @@
       <c r="B310" s="7">
         <v>3</v>
       </c>
-      <c r="C310" s="196"/>
-      <c r="D310" s="181"/>
+      <c r="C310" s="167"/>
+      <c r="D310" s="176"/>
       <c r="E310" s="13" t="s">
         <v>402</v>
       </c>
@@ -12641,8 +12695,8 @@
       <c r="B311" s="7">
         <v>4</v>
       </c>
-      <c r="C311" s="196"/>
-      <c r="D311" s="181"/>
+      <c r="C311" s="167"/>
+      <c r="D311" s="176"/>
       <c r="E311" s="8" t="s">
         <v>403</v>
       </c>
@@ -12663,8 +12717,8 @@
       <c r="B312" s="7">
         <v>5</v>
       </c>
-      <c r="C312" s="196"/>
-      <c r="D312" s="181"/>
+      <c r="C312" s="167"/>
+      <c r="D312" s="176"/>
       <c r="E312" s="13" t="s">
         <v>404</v>
       </c>
@@ -12685,8 +12739,8 @@
       <c r="B313" s="7">
         <v>6</v>
       </c>
-      <c r="C313" s="196"/>
-      <c r="D313" s="181"/>
+      <c r="C313" s="167"/>
+      <c r="D313" s="176"/>
       <c r="E313" s="13" t="s">
         <v>405</v>
       </c>
@@ -12707,8 +12761,8 @@
       <c r="B314" s="7">
         <v>7</v>
       </c>
-      <c r="C314" s="196"/>
-      <c r="D314" s="182"/>
+      <c r="C314" s="167"/>
+      <c r="D314" s="177"/>
       <c r="E314" s="8" t="s">
         <v>406</v>
       </c>
@@ -12729,8 +12783,8 @@
       <c r="B315" s="7">
         <v>8</v>
       </c>
-      <c r="C315" s="196"/>
-      <c r="D315" s="180" t="s">
+      <c r="C315" s="167"/>
+      <c r="D315" s="175" t="s">
         <v>407</v>
       </c>
       <c r="E315" s="13" t="s">
@@ -12753,8 +12807,8 @@
       <c r="B316" s="7">
         <v>9</v>
       </c>
-      <c r="C316" s="196"/>
-      <c r="D316" s="181"/>
+      <c r="C316" s="167"/>
+      <c r="D316" s="176"/>
       <c r="E316" s="8" t="s">
         <v>409</v>
       </c>
@@ -12775,8 +12829,8 @@
       <c r="B317" s="24">
         <v>10</v>
       </c>
-      <c r="C317" s="197"/>
-      <c r="D317" s="182"/>
+      <c r="C317" s="168"/>
+      <c r="D317" s="177"/>
       <c r="E317" s="17" t="s">
         <v>410</v>
       </c>
@@ -12797,10 +12851,10 @@
       <c r="B318" s="7">
         <v>1</v>
       </c>
-      <c r="C318" s="198" t="s">
+      <c r="C318" s="169" t="s">
         <v>411</v>
       </c>
-      <c r="D318" s="180" t="s">
+      <c r="D318" s="175" t="s">
         <v>412</v>
       </c>
       <c r="E318" s="8" t="s">
@@ -12823,8 +12877,8 @@
       <c r="B319" s="7">
         <v>2</v>
       </c>
-      <c r="C319" s="199"/>
-      <c r="D319" s="181"/>
+      <c r="C319" s="170"/>
+      <c r="D319" s="176"/>
       <c r="E319" s="13" t="s">
         <v>414</v>
       </c>
@@ -12845,8 +12899,8 @@
       <c r="B320" s="7">
         <v>3</v>
       </c>
-      <c r="C320" s="199"/>
-      <c r="D320" s="181"/>
+      <c r="C320" s="170"/>
+      <c r="D320" s="176"/>
       <c r="E320" s="8" t="s">
         <v>415</v>
       </c>
@@ -12867,8 +12921,8 @@
       <c r="B321" s="7">
         <v>4</v>
       </c>
-      <c r="C321" s="199"/>
-      <c r="D321" s="181"/>
+      <c r="C321" s="170"/>
+      <c r="D321" s="176"/>
       <c r="E321" s="8" t="s">
         <v>416</v>
       </c>
@@ -12889,8 +12943,8 @@
       <c r="B322" s="7">
         <v>5</v>
       </c>
-      <c r="C322" s="199"/>
-      <c r="D322" s="181"/>
+      <c r="C322" s="170"/>
+      <c r="D322" s="176"/>
       <c r="E322" s="8" t="s">
         <v>417</v>
       </c>
@@ -12911,8 +12965,8 @@
       <c r="B323" s="7">
         <v>6</v>
       </c>
-      <c r="C323" s="199"/>
-      <c r="D323" s="182"/>
+      <c r="C323" s="170"/>
+      <c r="D323" s="177"/>
       <c r="E323" s="29" t="s">
         <v>418</v>
       </c>
@@ -12933,8 +12987,8 @@
       <c r="B324" s="7">
         <v>7</v>
       </c>
-      <c r="C324" s="199"/>
-      <c r="D324" s="180" t="s">
+      <c r="C324" s="170"/>
+      <c r="D324" s="175" t="s">
         <v>419</v>
       </c>
       <c r="E324" s="13" t="s">
@@ -12957,8 +13011,8 @@
       <c r="B325" s="7">
         <v>8</v>
       </c>
-      <c r="C325" s="199"/>
-      <c r="D325" s="181"/>
+      <c r="C325" s="170"/>
+      <c r="D325" s="176"/>
       <c r="E325" s="8" t="s">
         <v>421</v>
       </c>
@@ -12979,8 +13033,8 @@
       <c r="B326" s="7">
         <v>9</v>
       </c>
-      <c r="C326" s="199"/>
-      <c r="D326" s="181"/>
+      <c r="C326" s="170"/>
+      <c r="D326" s="176"/>
       <c r="E326" s="8" t="s">
         <v>422</v>
       </c>
@@ -13001,8 +13055,8 @@
       <c r="B327" s="7">
         <v>10</v>
       </c>
-      <c r="C327" s="199"/>
-      <c r="D327" s="181"/>
+      <c r="C327" s="170"/>
+      <c r="D327" s="176"/>
       <c r="E327" s="8" t="s">
         <v>423</v>
       </c>
@@ -13023,8 +13077,8 @@
       <c r="B328" s="7">
         <v>11</v>
       </c>
-      <c r="C328" s="199"/>
-      <c r="D328" s="182"/>
+      <c r="C328" s="170"/>
+      <c r="D328" s="177"/>
       <c r="E328" s="13" t="s">
         <v>424</v>
       </c>
@@ -13045,8 +13099,8 @@
       <c r="B329" s="7">
         <v>12</v>
       </c>
-      <c r="C329" s="199"/>
-      <c r="D329" s="180" t="s">
+      <c r="C329" s="170"/>
+      <c r="D329" s="175" t="s">
         <v>425</v>
       </c>
       <c r="E329" s="8" t="s">
@@ -13069,8 +13123,8 @@
       <c r="B330" s="7">
         <v>13</v>
       </c>
-      <c r="C330" s="199"/>
-      <c r="D330" s="181"/>
+      <c r="C330" s="170"/>
+      <c r="D330" s="176"/>
       <c r="E330" s="8" t="s">
         <v>427</v>
       </c>
@@ -13091,8 +13145,8 @@
       <c r="B331" s="7">
         <v>14</v>
       </c>
-      <c r="C331" s="199"/>
-      <c r="D331" s="181"/>
+      <c r="C331" s="170"/>
+      <c r="D331" s="176"/>
       <c r="E331" s="8" t="s">
         <v>428</v>
       </c>
@@ -13113,8 +13167,8 @@
       <c r="B332" s="7">
         <v>15</v>
       </c>
-      <c r="C332" s="199"/>
-      <c r="D332" s="181"/>
+      <c r="C332" s="170"/>
+      <c r="D332" s="176"/>
       <c r="E332" s="8" t="s">
         <v>429</v>
       </c>
@@ -13135,8 +13189,8 @@
       <c r="B333" s="7">
         <v>16</v>
       </c>
-      <c r="C333" s="199"/>
-      <c r="D333" s="181"/>
+      <c r="C333" s="170"/>
+      <c r="D333" s="176"/>
       <c r="E333" s="8" t="s">
         <v>430</v>
       </c>
@@ -13157,8 +13211,8 @@
       <c r="B334" s="7">
         <v>17</v>
       </c>
-      <c r="C334" s="199"/>
-      <c r="D334" s="181"/>
+      <c r="C334" s="170"/>
+      <c r="D334" s="176"/>
       <c r="E334" s="8" t="s">
         <v>431</v>
       </c>
@@ -13179,8 +13233,8 @@
       <c r="B335" s="7">
         <v>18</v>
       </c>
-      <c r="C335" s="199"/>
-      <c r="D335" s="181"/>
+      <c r="C335" s="170"/>
+      <c r="D335" s="176"/>
       <c r="E335" s="8" t="s">
         <v>432</v>
       </c>
@@ -13201,8 +13255,8 @@
       <c r="B336" s="7">
         <v>19</v>
       </c>
-      <c r="C336" s="199"/>
-      <c r="D336" s="181"/>
+      <c r="C336" s="170"/>
+      <c r="D336" s="176"/>
       <c r="E336" s="8" t="s">
         <v>433</v>
       </c>
@@ -13223,8 +13277,8 @@
       <c r="B337" s="7">
         <v>20</v>
       </c>
-      <c r="C337" s="199"/>
-      <c r="D337" s="182"/>
+      <c r="C337" s="170"/>
+      <c r="D337" s="177"/>
       <c r="E337" s="13" t="s">
         <v>434</v>
       </c>
@@ -13245,8 +13299,8 @@
       <c r="B338" s="7">
         <v>21</v>
       </c>
-      <c r="C338" s="199"/>
-      <c r="D338" s="180" t="s">
+      <c r="C338" s="170"/>
+      <c r="D338" s="175" t="s">
         <v>435</v>
       </c>
       <c r="E338" s="13" t="s">
@@ -13269,8 +13323,8 @@
       <c r="B339" s="7">
         <v>22</v>
       </c>
-      <c r="C339" s="199"/>
-      <c r="D339" s="181"/>
+      <c r="C339" s="170"/>
+      <c r="D339" s="176"/>
       <c r="E339" s="13" t="s">
         <v>437</v>
       </c>
@@ -13291,8 +13345,8 @@
       <c r="B340" s="7">
         <v>23</v>
       </c>
-      <c r="C340" s="199"/>
-      <c r="D340" s="181"/>
+      <c r="C340" s="170"/>
+      <c r="D340" s="176"/>
       <c r="E340" s="13" t="s">
         <v>438</v>
       </c>
@@ -13313,8 +13367,8 @@
       <c r="B341" s="7">
         <v>24</v>
       </c>
-      <c r="C341" s="199"/>
-      <c r="D341" s="181"/>
+      <c r="C341" s="170"/>
+      <c r="D341" s="176"/>
       <c r="E341" s="13" t="s">
         <v>439</v>
       </c>
@@ -13335,8 +13389,8 @@
       <c r="B342" s="24">
         <v>25</v>
       </c>
-      <c r="C342" s="200"/>
-      <c r="D342" s="182"/>
+      <c r="C342" s="171"/>
+      <c r="D342" s="177"/>
       <c r="E342" s="25" t="s">
         <v>440</v>
       </c>
@@ -13357,10 +13411,10 @@
       <c r="B343" s="7">
         <v>1</v>
       </c>
-      <c r="C343" s="165" t="s">
+      <c r="C343" s="151" t="s">
         <v>441</v>
       </c>
-      <c r="D343" s="150" t="s">
+      <c r="D343" s="172" t="s">
         <v>442</v>
       </c>
       <c r="E343" s="8" t="s">
@@ -13389,8 +13443,8 @@
       <c r="B344" s="7">
         <v>2</v>
       </c>
-      <c r="C344" s="166"/>
-      <c r="D344" s="151"/>
+      <c r="C344" s="152"/>
+      <c r="D344" s="173"/>
       <c r="E344" s="8" t="s">
         <v>444</v>
       </c>
@@ -13417,8 +13471,8 @@
       <c r="B345" s="7">
         <v>3</v>
       </c>
-      <c r="C345" s="166"/>
-      <c r="D345" s="151"/>
+      <c r="C345" s="152"/>
+      <c r="D345" s="173"/>
       <c r="E345" s="8" t="s">
         <v>445</v>
       </c>
@@ -13445,8 +13499,8 @@
       <c r="B346" s="7">
         <v>4</v>
       </c>
-      <c r="C346" s="166"/>
-      <c r="D346" s="151"/>
+      <c r="C346" s="152"/>
+      <c r="D346" s="173"/>
       <c r="E346" s="8" t="s">
         <v>446</v>
       </c>
@@ -13473,8 +13527,8 @@
       <c r="B347" s="7">
         <v>5</v>
       </c>
-      <c r="C347" s="166"/>
-      <c r="D347" s="152"/>
+      <c r="C347" s="152"/>
+      <c r="D347" s="174"/>
       <c r="E347" s="8" t="s">
         <v>447</v>
       </c>
@@ -13501,8 +13555,8 @@
       <c r="B348" s="7">
         <v>6</v>
       </c>
-      <c r="C348" s="166"/>
-      <c r="D348" s="150" t="s">
+      <c r="C348" s="152"/>
+      <c r="D348" s="172" t="s">
         <v>448</v>
       </c>
       <c r="E348" s="8" t="s">
@@ -13529,8 +13583,8 @@
       <c r="B349" s="7">
         <v>7</v>
       </c>
-      <c r="C349" s="166"/>
-      <c r="D349" s="151"/>
+      <c r="C349" s="152"/>
+      <c r="D349" s="173"/>
       <c r="E349" s="8" t="s">
         <v>450</v>
       </c>
@@ -13557,8 +13611,8 @@
       <c r="B350" s="7">
         <v>8</v>
       </c>
-      <c r="C350" s="166"/>
-      <c r="D350" s="151"/>
+      <c r="C350" s="152"/>
+      <c r="D350" s="173"/>
       <c r="E350" s="8" t="s">
         <v>451</v>
       </c>
@@ -13585,8 +13639,8 @@
       <c r="B351" s="7">
         <v>9</v>
       </c>
-      <c r="C351" s="166"/>
-      <c r="D351" s="151"/>
+      <c r="C351" s="152"/>
+      <c r="D351" s="173"/>
       <c r="E351" s="8" t="s">
         <v>452</v>
       </c>
@@ -13609,8 +13663,8 @@
       <c r="B352" s="7">
         <v>10</v>
       </c>
-      <c r="C352" s="166"/>
-      <c r="D352" s="151"/>
+      <c r="C352" s="152"/>
+      <c r="D352" s="173"/>
       <c r="E352" s="8" t="s">
         <v>453</v>
       </c>
@@ -13637,8 +13691,8 @@
       <c r="B353" s="7">
         <v>11</v>
       </c>
-      <c r="C353" s="166"/>
-      <c r="D353" s="152"/>
+      <c r="C353" s="152"/>
+      <c r="D353" s="174"/>
       <c r="E353" s="8" t="s">
         <v>454</v>
       </c>
@@ -13659,8 +13713,8 @@
       <c r="B354" s="7">
         <v>12</v>
       </c>
-      <c r="C354" s="166"/>
-      <c r="D354" s="150" t="s">
+      <c r="C354" s="152"/>
+      <c r="D354" s="172" t="s">
         <v>455</v>
       </c>
       <c r="E354" s="8" t="s">
@@ -13687,8 +13741,8 @@
       <c r="B355" s="7">
         <v>13</v>
       </c>
-      <c r="C355" s="166"/>
-      <c r="D355" s="151"/>
+      <c r="C355" s="152"/>
+      <c r="D355" s="173"/>
       <c r="E355" s="8" t="s">
         <v>457</v>
       </c>
@@ -13715,8 +13769,8 @@
       <c r="B356" s="7">
         <v>14</v>
       </c>
-      <c r="C356" s="166"/>
-      <c r="D356" s="151"/>
+      <c r="C356" s="152"/>
+      <c r="D356" s="173"/>
       <c r="E356" s="8" t="s">
         <v>458</v>
       </c>
@@ -13737,8 +13791,8 @@
       <c r="B357" s="7">
         <v>15</v>
       </c>
-      <c r="C357" s="167"/>
-      <c r="D357" s="152"/>
+      <c r="C357" s="153"/>
+      <c r="D357" s="174"/>
       <c r="E357" s="8" t="s">
         <v>459</v>
       </c>
@@ -13753,18 +13807,18 @@
       <c r="J357" s="11"/>
     </row>
     <row r="358" spans="1:10" ht="13.8">
-      <c r="A358" s="189" t="s">
+      <c r="A358" s="187" t="s">
         <v>460</v>
       </c>
-      <c r="B358" s="190"/>
-      <c r="C358" s="190"/>
-      <c r="D358" s="190"/>
-      <c r="E358" s="190"/>
-      <c r="F358" s="190"/>
-      <c r="G358" s="190"/>
-      <c r="H358" s="190"/>
-      <c r="I358" s="190"/>
-      <c r="J358" s="191"/>
+      <c r="B358" s="188"/>
+      <c r="C358" s="188"/>
+      <c r="D358" s="188"/>
+      <c r="E358" s="188"/>
+      <c r="F358" s="188"/>
+      <c r="G358" s="188"/>
+      <c r="H358" s="188"/>
+      <c r="I358" s="188"/>
+      <c r="J358" s="189"/>
     </row>
     <row r="359" spans="1:10" ht="13.8">
       <c r="A359" s="6">
@@ -13773,10 +13827,10 @@
       <c r="B359" s="7">
         <v>1</v>
       </c>
-      <c r="C359" s="168" t="s">
+      <c r="C359" s="154" t="s">
         <v>461</v>
       </c>
-      <c r="D359" s="150" t="s">
+      <c r="D359" s="172" t="s">
         <v>462</v>
       </c>
       <c r="E359" s="8" t="s">
@@ -13799,8 +13853,8 @@
       <c r="B360" s="7">
         <v>2</v>
       </c>
-      <c r="C360" s="169"/>
-      <c r="D360" s="151"/>
+      <c r="C360" s="155"/>
+      <c r="D360" s="173"/>
       <c r="E360" s="8" t="s">
         <v>464</v>
       </c>
@@ -13821,8 +13875,8 @@
       <c r="B361" s="7">
         <v>3</v>
       </c>
-      <c r="C361" s="169"/>
-      <c r="D361" s="151"/>
+      <c r="C361" s="155"/>
+      <c r="D361" s="173"/>
       <c r="E361" s="8" t="s">
         <v>465</v>
       </c>
@@ -13843,8 +13897,8 @@
       <c r="B362" s="7">
         <v>4</v>
       </c>
-      <c r="C362" s="169"/>
-      <c r="D362" s="151"/>
+      <c r="C362" s="155"/>
+      <c r="D362" s="173"/>
       <c r="E362" s="8" t="s">
         <v>466</v>
       </c>
@@ -13865,8 +13919,8 @@
       <c r="B363" s="7">
         <v>5</v>
       </c>
-      <c r="C363" s="169"/>
-      <c r="D363" s="152"/>
+      <c r="C363" s="155"/>
+      <c r="D363" s="174"/>
       <c r="E363" s="8" t="s">
         <v>467</v>
       </c>
@@ -13887,8 +13941,8 @@
       <c r="B364" s="7">
         <v>6</v>
       </c>
-      <c r="C364" s="169"/>
-      <c r="D364" s="150" t="s">
+      <c r="C364" s="155"/>
+      <c r="D364" s="172" t="s">
         <v>468</v>
       </c>
       <c r="E364" s="8" t="s">
@@ -13911,8 +13965,8 @@
       <c r="B365" s="7">
         <v>7</v>
       </c>
-      <c r="C365" s="169"/>
-      <c r="D365" s="151"/>
+      <c r="C365" s="155"/>
+      <c r="D365" s="173"/>
       <c r="E365" s="8" t="s">
         <v>470</v>
       </c>
@@ -13933,8 +13987,8 @@
       <c r="B366" s="7">
         <v>8</v>
       </c>
-      <c r="C366" s="169"/>
-      <c r="D366" s="151"/>
+      <c r="C366" s="155"/>
+      <c r="D366" s="173"/>
       <c r="E366" s="8" t="s">
         <v>471</v>
       </c>
@@ -13955,8 +14009,8 @@
       <c r="B367" s="7">
         <v>9</v>
       </c>
-      <c r="C367" s="169"/>
-      <c r="D367" s="151"/>
+      <c r="C367" s="155"/>
+      <c r="D367" s="173"/>
       <c r="E367" s="8" t="s">
         <v>472</v>
       </c>
@@ -13977,8 +14031,8 @@
       <c r="B368" s="7">
         <v>10</v>
       </c>
-      <c r="C368" s="169"/>
-      <c r="D368" s="151"/>
+      <c r="C368" s="155"/>
+      <c r="D368" s="173"/>
       <c r="E368" s="8" t="s">
         <v>473</v>
       </c>
@@ -13999,8 +14053,8 @@
       <c r="B369" s="7">
         <v>11</v>
       </c>
-      <c r="C369" s="169"/>
-      <c r="D369" s="151"/>
+      <c r="C369" s="155"/>
+      <c r="D369" s="173"/>
       <c r="E369" s="8" t="s">
         <v>474</v>
       </c>
@@ -14021,8 +14075,8 @@
       <c r="B370" s="7">
         <v>12</v>
       </c>
-      <c r="C370" s="169"/>
-      <c r="D370" s="151"/>
+      <c r="C370" s="155"/>
+      <c r="D370" s="173"/>
       <c r="E370" s="8" t="s">
         <v>475</v>
       </c>
@@ -14043,8 +14097,8 @@
       <c r="B371" s="7">
         <v>13</v>
       </c>
-      <c r="C371" s="169"/>
-      <c r="D371" s="152"/>
+      <c r="C371" s="155"/>
+      <c r="D371" s="174"/>
       <c r="E371" s="8" t="s">
         <v>476</v>
       </c>
@@ -14065,8 +14119,8 @@
       <c r="B372" s="7">
         <v>14</v>
       </c>
-      <c r="C372" s="169"/>
-      <c r="D372" s="150" t="s">
+      <c r="C372" s="155"/>
+      <c r="D372" s="172" t="s">
         <v>477</v>
       </c>
       <c r="E372" s="8" t="s">
@@ -14089,8 +14143,8 @@
       <c r="B373" s="7">
         <v>15</v>
       </c>
-      <c r="C373" s="169"/>
-      <c r="D373" s="151"/>
+      <c r="C373" s="155"/>
+      <c r="D373" s="173"/>
       <c r="E373" s="11" t="s">
         <v>479</v>
       </c>
@@ -14111,8 +14165,8 @@
       <c r="B374" s="7">
         <v>16</v>
       </c>
-      <c r="C374" s="169"/>
-      <c r="D374" s="151"/>
+      <c r="C374" s="155"/>
+      <c r="D374" s="173"/>
       <c r="E374" s="8" t="s">
         <v>480</v>
       </c>
@@ -14133,8 +14187,8 @@
       <c r="B375" s="7">
         <v>17</v>
       </c>
-      <c r="C375" s="169"/>
-      <c r="D375" s="152"/>
+      <c r="C375" s="155"/>
+      <c r="D375" s="174"/>
       <c r="E375" s="8" t="s">
         <v>481</v>
       </c>
@@ -14155,8 +14209,8 @@
       <c r="B376" s="7">
         <v>18</v>
       </c>
-      <c r="C376" s="169"/>
-      <c r="D376" s="150" t="s">
+      <c r="C376" s="155"/>
+      <c r="D376" s="172" t="s">
         <v>482</v>
       </c>
       <c r="E376" s="8" t="s">
@@ -14179,8 +14233,8 @@
       <c r="B377" s="7">
         <v>19</v>
       </c>
-      <c r="C377" s="169"/>
-      <c r="D377" s="151"/>
+      <c r="C377" s="155"/>
+      <c r="D377" s="173"/>
       <c r="E377" s="8" t="s">
         <v>484</v>
       </c>
@@ -14201,8 +14255,8 @@
       <c r="B378" s="7">
         <v>20</v>
       </c>
-      <c r="C378" s="169"/>
-      <c r="D378" s="151"/>
+      <c r="C378" s="155"/>
+      <c r="D378" s="173"/>
       <c r="E378" s="8" t="s">
         <v>485</v>
       </c>
@@ -14223,8 +14277,8 @@
       <c r="B379" s="7">
         <v>21</v>
       </c>
-      <c r="C379" s="169"/>
-      <c r="D379" s="151"/>
+      <c r="C379" s="155"/>
+      <c r="D379" s="173"/>
       <c r="E379" s="8" t="s">
         <v>486</v>
       </c>
@@ -14245,8 +14299,8 @@
       <c r="B380" s="24">
         <v>22</v>
       </c>
-      <c r="C380" s="170"/>
-      <c r="D380" s="152"/>
+      <c r="C380" s="156"/>
+      <c r="D380" s="174"/>
       <c r="E380" s="17" t="s">
         <v>487</v>
       </c>
@@ -14267,10 +14321,10 @@
       <c r="B381" s="7">
         <v>1</v>
       </c>
-      <c r="C381" s="159" t="s">
+      <c r="C381" s="157" t="s">
         <v>488</v>
       </c>
-      <c r="D381" s="150" t="s">
+      <c r="D381" s="172" t="s">
         <v>489</v>
       </c>
       <c r="E381" s="8" t="s">
@@ -14293,8 +14347,8 @@
       <c r="B382" s="7">
         <v>2</v>
       </c>
-      <c r="C382" s="160"/>
-      <c r="D382" s="151"/>
+      <c r="C382" s="158"/>
+      <c r="D382" s="173"/>
       <c r="E382" s="8" t="s">
         <v>491</v>
       </c>
@@ -14315,8 +14369,8 @@
       <c r="B383" s="7">
         <v>3</v>
       </c>
-      <c r="C383" s="160"/>
-      <c r="D383" s="151"/>
+      <c r="C383" s="158"/>
+      <c r="D383" s="173"/>
       <c r="E383" s="8" t="s">
         <v>492</v>
       </c>
@@ -14337,8 +14391,8 @@
       <c r="B384" s="7">
         <v>4</v>
       </c>
-      <c r="C384" s="160"/>
-      <c r="D384" s="151"/>
+      <c r="C384" s="158"/>
+      <c r="D384" s="173"/>
       <c r="E384" s="8" t="s">
         <v>493</v>
       </c>
@@ -14359,8 +14413,8 @@
       <c r="B385" s="7">
         <v>5</v>
       </c>
-      <c r="C385" s="160"/>
-      <c r="D385" s="151"/>
+      <c r="C385" s="158"/>
+      <c r="D385" s="173"/>
       <c r="E385" s="8" t="s">
         <v>494</v>
       </c>
@@ -14381,8 +14435,8 @@
       <c r="B386" s="7">
         <v>6</v>
       </c>
-      <c r="C386" s="160"/>
-      <c r="D386" s="152"/>
+      <c r="C386" s="158"/>
+      <c r="D386" s="174"/>
       <c r="E386" s="8" t="s">
         <v>495</v>
       </c>
@@ -14403,8 +14457,8 @@
       <c r="B387" s="7">
         <v>7</v>
       </c>
-      <c r="C387" s="160"/>
-      <c r="D387" s="150" t="s">
+      <c r="C387" s="158"/>
+      <c r="D387" s="172" t="s">
         <v>496</v>
       </c>
       <c r="E387" s="8" t="s">
@@ -14427,8 +14481,8 @@
       <c r="B388" s="7">
         <v>8</v>
       </c>
-      <c r="C388" s="160"/>
-      <c r="D388" s="151"/>
+      <c r="C388" s="158"/>
+      <c r="D388" s="173"/>
       <c r="E388" s="8" t="s">
         <v>498</v>
       </c>
@@ -14449,8 +14503,8 @@
       <c r="B389" s="7">
         <v>9</v>
       </c>
-      <c r="C389" s="160"/>
-      <c r="D389" s="151"/>
+      <c r="C389" s="158"/>
+      <c r="D389" s="173"/>
       <c r="E389" s="8" t="s">
         <v>499</v>
       </c>
@@ -14471,8 +14525,8 @@
       <c r="B390" s="7">
         <v>10</v>
       </c>
-      <c r="C390" s="160"/>
-      <c r="D390" s="151"/>
+      <c r="C390" s="158"/>
+      <c r="D390" s="173"/>
       <c r="E390" s="8" t="s">
         <v>500</v>
       </c>
@@ -14493,8 +14547,8 @@
       <c r="B391" s="7">
         <v>11</v>
       </c>
-      <c r="C391" s="160"/>
-      <c r="D391" s="151"/>
+      <c r="C391" s="158"/>
+      <c r="D391" s="173"/>
       <c r="E391" s="8" t="s">
         <v>501</v>
       </c>
@@ -14515,8 +14569,8 @@
       <c r="B392" s="7">
         <v>12</v>
       </c>
-      <c r="C392" s="160"/>
-      <c r="D392" s="151"/>
+      <c r="C392" s="158"/>
+      <c r="D392" s="173"/>
       <c r="E392" s="8" t="s">
         <v>502</v>
       </c>
@@ -14537,8 +14591,8 @@
       <c r="B393" s="7">
         <v>13</v>
       </c>
-      <c r="C393" s="160"/>
-      <c r="D393" s="151"/>
+      <c r="C393" s="158"/>
+      <c r="D393" s="173"/>
       <c r="E393" s="8" t="s">
         <v>503</v>
       </c>
@@ -14559,8 +14613,8 @@
       <c r="B394" s="7">
         <v>14</v>
       </c>
-      <c r="C394" s="160"/>
-      <c r="D394" s="151"/>
+      <c r="C394" s="158"/>
+      <c r="D394" s="173"/>
       <c r="E394" s="8" t="s">
         <v>504</v>
       </c>
@@ -14581,8 +14635,8 @@
       <c r="B395" s="7">
         <v>15</v>
       </c>
-      <c r="C395" s="160"/>
-      <c r="D395" s="151"/>
+      <c r="C395" s="158"/>
+      <c r="D395" s="173"/>
       <c r="E395" s="8" t="s">
         <v>505</v>
       </c>
@@ -14603,8 +14657,8 @@
       <c r="B396" s="7">
         <v>16</v>
       </c>
-      <c r="C396" s="160"/>
-      <c r="D396" s="152"/>
+      <c r="C396" s="158"/>
+      <c r="D396" s="174"/>
       <c r="E396" s="8" t="s">
         <v>506</v>
       </c>
@@ -14625,8 +14679,8 @@
       <c r="B397" s="7">
         <v>17</v>
       </c>
-      <c r="C397" s="160"/>
-      <c r="D397" s="150" t="s">
+      <c r="C397" s="158"/>
+      <c r="D397" s="172" t="s">
         <v>507</v>
       </c>
       <c r="E397" s="8" t="s">
@@ -14649,8 +14703,8 @@
       <c r="B398" s="7">
         <v>18</v>
       </c>
-      <c r="C398" s="160"/>
-      <c r="D398" s="151"/>
+      <c r="C398" s="158"/>
+      <c r="D398" s="173"/>
       <c r="E398" s="8" t="s">
         <v>509</v>
       </c>
@@ -14671,8 +14725,8 @@
       <c r="B399" s="7">
         <v>19</v>
       </c>
-      <c r="C399" s="160"/>
-      <c r="D399" s="152"/>
+      <c r="C399" s="158"/>
+      <c r="D399" s="174"/>
       <c r="E399" s="8" t="s">
         <v>510</v>
       </c>
@@ -14693,8 +14747,8 @@
       <c r="B400" s="7">
         <v>20</v>
       </c>
-      <c r="C400" s="160"/>
-      <c r="D400" s="150" t="s">
+      <c r="C400" s="158"/>
+      <c r="D400" s="172" t="s">
         <v>511</v>
       </c>
       <c r="E400" s="8" t="s">
@@ -14717,8 +14771,8 @@
       <c r="B401" s="7">
         <v>21</v>
       </c>
-      <c r="C401" s="160"/>
-      <c r="D401" s="151"/>
+      <c r="C401" s="158"/>
+      <c r="D401" s="173"/>
       <c r="E401" s="8" t="s">
         <v>513</v>
       </c>
@@ -14739,8 +14793,8 @@
       <c r="B402" s="7">
         <v>22</v>
       </c>
-      <c r="C402" s="160"/>
-      <c r="D402" s="151"/>
+      <c r="C402" s="158"/>
+      <c r="D402" s="173"/>
       <c r="E402" s="8" t="s">
         <v>514</v>
       </c>
@@ -14761,8 +14815,8 @@
       <c r="B403" s="7">
         <v>23</v>
       </c>
-      <c r="C403" s="160"/>
-      <c r="D403" s="151"/>
+      <c r="C403" s="158"/>
+      <c r="D403" s="173"/>
       <c r="E403" s="8" t="s">
         <v>515</v>
       </c>
@@ -14783,8 +14837,8 @@
       <c r="B404" s="7">
         <v>24</v>
       </c>
-      <c r="C404" s="160"/>
-      <c r="D404" s="152"/>
+      <c r="C404" s="158"/>
+      <c r="D404" s="174"/>
       <c r="E404" s="8" t="s">
         <v>516</v>
       </c>
@@ -14805,8 +14859,8 @@
       <c r="B405" s="7">
         <v>25</v>
       </c>
-      <c r="C405" s="160"/>
-      <c r="D405" s="150" t="s">
+      <c r="C405" s="158"/>
+      <c r="D405" s="172" t="s">
         <v>517</v>
       </c>
       <c r="E405" s="8" t="s">
@@ -14829,8 +14883,8 @@
       <c r="B406" s="7">
         <v>26</v>
       </c>
-      <c r="C406" s="160"/>
-      <c r="D406" s="151"/>
+      <c r="C406" s="158"/>
+      <c r="D406" s="173"/>
       <c r="E406" s="8" t="s">
         <v>519</v>
       </c>
@@ -14851,8 +14905,8 @@
       <c r="B407" s="7">
         <v>27</v>
       </c>
-      <c r="C407" s="160"/>
-      <c r="D407" s="151"/>
+      <c r="C407" s="158"/>
+      <c r="D407" s="173"/>
       <c r="E407" s="8" t="s">
         <v>520</v>
       </c>
@@ -14873,8 +14927,8 @@
       <c r="B408" s="7">
         <v>28</v>
       </c>
-      <c r="C408" s="160"/>
-      <c r="D408" s="151"/>
+      <c r="C408" s="158"/>
+      <c r="D408" s="173"/>
       <c r="E408" s="8" t="s">
         <v>521</v>
       </c>
@@ -14895,8 +14949,8 @@
       <c r="B409" s="7">
         <v>29</v>
       </c>
-      <c r="C409" s="160"/>
-      <c r="D409" s="151"/>
+      <c r="C409" s="158"/>
+      <c r="D409" s="173"/>
       <c r="E409" s="8" t="s">
         <v>522</v>
       </c>
@@ -14917,8 +14971,8 @@
       <c r="B410" s="7">
         <v>30</v>
       </c>
-      <c r="C410" s="160"/>
-      <c r="D410" s="151"/>
+      <c r="C410" s="158"/>
+      <c r="D410" s="173"/>
       <c r="E410" s="8" t="s">
         <v>523</v>
       </c>
@@ -14939,8 +14993,8 @@
       <c r="B411" s="7">
         <v>31</v>
       </c>
-      <c r="C411" s="160"/>
-      <c r="D411" s="151"/>
+      <c r="C411" s="158"/>
+      <c r="D411" s="173"/>
       <c r="E411" s="8" t="s">
         <v>524</v>
       </c>
@@ -14961,8 +15015,8 @@
       <c r="B412" s="7">
         <v>32</v>
       </c>
-      <c r="C412" s="160"/>
-      <c r="D412" s="151"/>
+      <c r="C412" s="158"/>
+      <c r="D412" s="173"/>
       <c r="E412" s="8" t="s">
         <v>525</v>
       </c>
@@ -14983,8 +15037,8 @@
       <c r="B413" s="7">
         <v>33</v>
       </c>
-      <c r="C413" s="160"/>
-      <c r="D413" s="151"/>
+      <c r="C413" s="158"/>
+      <c r="D413" s="173"/>
       <c r="E413" s="8" t="s">
         <v>526</v>
       </c>
@@ -15005,8 +15059,8 @@
       <c r="B414" s="7">
         <v>34</v>
       </c>
-      <c r="C414" s="160"/>
-      <c r="D414" s="151"/>
+      <c r="C414" s="158"/>
+      <c r="D414" s="173"/>
       <c r="E414" s="8" t="s">
         <v>527</v>
       </c>
@@ -15027,8 +15081,8 @@
       <c r="B415" s="7">
         <v>35</v>
       </c>
-      <c r="C415" s="160"/>
-      <c r="D415" s="151"/>
+      <c r="C415" s="158"/>
+      <c r="D415" s="173"/>
       <c r="E415" s="8" t="s">
         <v>528</v>
       </c>
@@ -15049,8 +15103,8 @@
       <c r="B416" s="7">
         <v>36</v>
       </c>
-      <c r="C416" s="160"/>
-      <c r="D416" s="152"/>
+      <c r="C416" s="158"/>
+      <c r="D416" s="174"/>
       <c r="E416" s="8" t="s">
         <v>529</v>
       </c>
@@ -15071,8 +15125,8 @@
       <c r="B417" s="7">
         <v>37</v>
       </c>
-      <c r="C417" s="160"/>
-      <c r="D417" s="150" t="s">
+      <c r="C417" s="158"/>
+      <c r="D417" s="172" t="s">
         <v>530</v>
       </c>
       <c r="E417" s="8" t="s">
@@ -15095,8 +15149,8 @@
       <c r="B418" s="7">
         <v>38</v>
       </c>
-      <c r="C418" s="160"/>
-      <c r="D418" s="151"/>
+      <c r="C418" s="158"/>
+      <c r="D418" s="173"/>
       <c r="E418" s="8" t="s">
         <v>532</v>
       </c>
@@ -15117,8 +15171,8 @@
       <c r="B419" s="7">
         <v>39</v>
       </c>
-      <c r="C419" s="160"/>
-      <c r="D419" s="152"/>
+      <c r="C419" s="158"/>
+      <c r="D419" s="174"/>
       <c r="E419" s="8" t="s">
         <v>533</v>
       </c>
@@ -15139,8 +15193,8 @@
       <c r="B420" s="7">
         <v>40</v>
       </c>
-      <c r="C420" s="160"/>
-      <c r="D420" s="150" t="s">
+      <c r="C420" s="158"/>
+      <c r="D420" s="172" t="s">
         <v>534</v>
       </c>
       <c r="E420" s="8" t="s">
@@ -15163,8 +15217,8 @@
       <c r="B421" s="7">
         <v>41</v>
       </c>
-      <c r="C421" s="160"/>
-      <c r="D421" s="151"/>
+      <c r="C421" s="158"/>
+      <c r="D421" s="173"/>
       <c r="E421" s="8" t="s">
         <v>536</v>
       </c>
@@ -15185,8 +15239,8 @@
       <c r="B422" s="7">
         <v>42</v>
       </c>
-      <c r="C422" s="160"/>
-      <c r="D422" s="151"/>
+      <c r="C422" s="158"/>
+      <c r="D422" s="173"/>
       <c r="E422" s="8" t="s">
         <v>537</v>
       </c>
@@ -15207,8 +15261,8 @@
       <c r="B423" s="7">
         <v>43</v>
       </c>
-      <c r="C423" s="160"/>
-      <c r="D423" s="151"/>
+      <c r="C423" s="158"/>
+      <c r="D423" s="173"/>
       <c r="E423" s="8" t="s">
         <v>538</v>
       </c>
@@ -15229,8 +15283,8 @@
       <c r="B424" s="7">
         <v>44</v>
       </c>
-      <c r="C424" s="160"/>
-      <c r="D424" s="151"/>
+      <c r="C424" s="158"/>
+      <c r="D424" s="173"/>
       <c r="E424" s="8" t="s">
         <v>539</v>
       </c>
@@ -15251,8 +15305,8 @@
       <c r="B425" s="7">
         <v>45</v>
       </c>
-      <c r="C425" s="160"/>
-      <c r="D425" s="151"/>
+      <c r="C425" s="158"/>
+      <c r="D425" s="173"/>
       <c r="E425" s="8" t="s">
         <v>540</v>
       </c>
@@ -15273,8 +15327,8 @@
       <c r="B426" s="7">
         <v>46</v>
       </c>
-      <c r="C426" s="160"/>
-      <c r="D426" s="152"/>
+      <c r="C426" s="158"/>
+      <c r="D426" s="174"/>
       <c r="E426" s="8" t="s">
         <v>541</v>
       </c>
@@ -15295,8 +15349,8 @@
       <c r="B427" s="7">
         <v>47</v>
       </c>
-      <c r="C427" s="160"/>
-      <c r="D427" s="150" t="s">
+      <c r="C427" s="158"/>
+      <c r="D427" s="172" t="s">
         <v>542</v>
       </c>
       <c r="E427" s="8" t="s">
@@ -15317,8 +15371,8 @@
       <c r="B428" s="7">
         <v>48</v>
       </c>
-      <c r="C428" s="160"/>
-      <c r="D428" s="151"/>
+      <c r="C428" s="158"/>
+      <c r="D428" s="173"/>
       <c r="E428" s="8" t="s">
         <v>544</v>
       </c>
@@ -15339,8 +15393,8 @@
       <c r="B429" s="7">
         <v>49</v>
       </c>
-      <c r="C429" s="160"/>
-      <c r="D429" s="151"/>
+      <c r="C429" s="158"/>
+      <c r="D429" s="173"/>
       <c r="E429" s="8" t="s">
         <v>545</v>
       </c>
@@ -15361,8 +15415,8 @@
       <c r="B430" s="7">
         <v>50</v>
       </c>
-      <c r="C430" s="160"/>
-      <c r="D430" s="152"/>
+      <c r="C430" s="158"/>
+      <c r="D430" s="174"/>
       <c r="E430" s="8" t="s">
         <v>546</v>
       </c>
@@ -15383,8 +15437,8 @@
       <c r="B431" s="7">
         <v>51</v>
       </c>
-      <c r="C431" s="160"/>
-      <c r="D431" s="150" t="s">
+      <c r="C431" s="158"/>
+      <c r="D431" s="172" t="s">
         <v>547</v>
       </c>
       <c r="E431" s="8" t="s">
@@ -15407,8 +15461,8 @@
       <c r="B432" s="7">
         <v>52</v>
       </c>
-      <c r="C432" s="160"/>
-      <c r="D432" s="151"/>
+      <c r="C432" s="158"/>
+      <c r="D432" s="173"/>
       <c r="E432" s="8" t="s">
         <v>549</v>
       </c>
@@ -15429,8 +15483,8 @@
       <c r="B433" s="7">
         <v>53</v>
       </c>
-      <c r="C433" s="160"/>
-      <c r="D433" s="151"/>
+      <c r="C433" s="158"/>
+      <c r="D433" s="173"/>
       <c r="E433" s="8" t="s">
         <v>550</v>
       </c>
@@ -15451,8 +15505,8 @@
       <c r="B434" s="7">
         <v>54</v>
       </c>
-      <c r="C434" s="160"/>
-      <c r="D434" s="151"/>
+      <c r="C434" s="158"/>
+      <c r="D434" s="173"/>
       <c r="E434" s="8" t="s">
         <v>551</v>
       </c>
@@ -15473,8 +15527,8 @@
       <c r="B435" s="7">
         <v>55</v>
       </c>
-      <c r="C435" s="161"/>
-      <c r="D435" s="152"/>
+      <c r="C435" s="159"/>
+      <c r="D435" s="174"/>
       <c r="E435" s="8" t="s">
         <v>552</v>
       </c>
@@ -15489,18 +15543,18 @@
       <c r="J435" s="11"/>
     </row>
     <row r="436" spans="1:10" ht="13.8">
-      <c r="A436" s="192" t="s">
+      <c r="A436" s="178" t="s">
         <v>553</v>
       </c>
-      <c r="B436" s="193"/>
-      <c r="C436" s="193"/>
-      <c r="D436" s="193"/>
-      <c r="E436" s="193"/>
-      <c r="F436" s="193"/>
-      <c r="G436" s="193"/>
-      <c r="H436" s="193"/>
-      <c r="I436" s="193"/>
-      <c r="J436" s="194"/>
+      <c r="B436" s="179"/>
+      <c r="C436" s="179"/>
+      <c r="D436" s="179"/>
+      <c r="E436" s="179"/>
+      <c r="F436" s="179"/>
+      <c r="G436" s="179"/>
+      <c r="H436" s="179"/>
+      <c r="I436" s="179"/>
+      <c r="J436" s="180"/>
     </row>
     <row r="437" spans="1:10" ht="13.8">
       <c r="A437" s="6">
@@ -15509,10 +15563,10 @@
       <c r="B437" s="7">
         <v>1</v>
       </c>
-      <c r="C437" s="162" t="s">
+      <c r="C437" s="160" t="s">
         <v>554</v>
       </c>
-      <c r="D437" s="150" t="s">
+      <c r="D437" s="172" t="s">
         <v>555</v>
       </c>
       <c r="E437" s="29" t="s">
@@ -15535,8 +15589,8 @@
       <c r="B438" s="7">
         <v>2</v>
       </c>
-      <c r="C438" s="163"/>
-      <c r="D438" s="151"/>
+      <c r="C438" s="161"/>
+      <c r="D438" s="173"/>
       <c r="E438" s="8" t="s">
         <v>557</v>
       </c>
@@ -15555,8 +15609,8 @@
       <c r="B439" s="7">
         <v>3</v>
       </c>
-      <c r="C439" s="163"/>
-      <c r="D439" s="151"/>
+      <c r="C439" s="161"/>
+      <c r="D439" s="173"/>
       <c r="E439" s="8" t="s">
         <v>558</v>
       </c>
@@ -15577,8 +15631,8 @@
       <c r="B440" s="7">
         <v>4</v>
       </c>
-      <c r="C440" s="163"/>
-      <c r="D440" s="151"/>
+      <c r="C440" s="161"/>
+      <c r="D440" s="173"/>
       <c r="E440" s="29" t="s">
         <v>559</v>
       </c>
@@ -15599,8 +15653,8 @@
       <c r="B441" s="7">
         <v>5</v>
       </c>
-      <c r="C441" s="163"/>
-      <c r="D441" s="152"/>
+      <c r="C441" s="161"/>
+      <c r="D441" s="174"/>
       <c r="E441" s="8" t="s">
         <v>560</v>
       </c>
@@ -15621,8 +15675,8 @@
       <c r="B442" s="7">
         <v>6</v>
       </c>
-      <c r="C442" s="163"/>
-      <c r="D442" s="150" t="s">
+      <c r="C442" s="161"/>
+      <c r="D442" s="172" t="s">
         <v>561</v>
       </c>
       <c r="E442" s="29" t="s">
@@ -15645,8 +15699,8 @@
       <c r="B443" s="7">
         <v>7</v>
       </c>
-      <c r="C443" s="163"/>
-      <c r="D443" s="151"/>
+      <c r="C443" s="161"/>
+      <c r="D443" s="173"/>
       <c r="E443" s="8" t="s">
         <v>563</v>
       </c>
@@ -15667,8 +15721,8 @@
       <c r="B444" s="7">
         <v>8</v>
       </c>
-      <c r="C444" s="163"/>
-      <c r="D444" s="151"/>
+      <c r="C444" s="161"/>
+      <c r="D444" s="173"/>
       <c r="E444" s="29" t="s">
         <v>564</v>
       </c>
@@ -15689,8 +15743,8 @@
       <c r="B445" s="7">
         <v>9</v>
       </c>
-      <c r="C445" s="163"/>
-      <c r="D445" s="152"/>
+      <c r="C445" s="161"/>
+      <c r="D445" s="174"/>
       <c r="E445" s="8" t="s">
         <v>565</v>
       </c>
@@ -15711,8 +15765,8 @@
       <c r="B446" s="7">
         <v>10</v>
       </c>
-      <c r="C446" s="163"/>
-      <c r="D446" s="150" t="s">
+      <c r="C446" s="161"/>
+      <c r="D446" s="172" t="s">
         <v>566</v>
       </c>
       <c r="E446" s="8" t="s">
@@ -15735,8 +15789,8 @@
       <c r="B447" s="7">
         <v>11</v>
       </c>
-      <c r="C447" s="163"/>
-      <c r="D447" s="151"/>
+      <c r="C447" s="161"/>
+      <c r="D447" s="173"/>
       <c r="E447" s="8" t="s">
         <v>568</v>
       </c>
@@ -15757,8 +15811,8 @@
       <c r="B448" s="7">
         <v>12</v>
       </c>
-      <c r="C448" s="163"/>
-      <c r="D448" s="152"/>
+      <c r="C448" s="161"/>
+      <c r="D448" s="174"/>
       <c r="E448" s="8" t="s">
         <v>569</v>
       </c>
@@ -15779,8 +15833,8 @@
       <c r="B449" s="7">
         <v>13</v>
       </c>
-      <c r="C449" s="163"/>
-      <c r="D449" s="150" t="s">
+      <c r="C449" s="161"/>
+      <c r="D449" s="172" t="s">
         <v>570</v>
       </c>
       <c r="E449" s="8" t="s">
@@ -15803,8 +15857,8 @@
       <c r="B450" s="7">
         <v>14</v>
       </c>
-      <c r="C450" s="163"/>
-      <c r="D450" s="151"/>
+      <c r="C450" s="161"/>
+      <c r="D450" s="173"/>
       <c r="E450" s="29" t="s">
         <v>572</v>
       </c>
@@ -15825,8 +15879,8 @@
       <c r="B451" s="7">
         <v>15</v>
       </c>
-      <c r="C451" s="163"/>
-      <c r="D451" s="151"/>
+      <c r="C451" s="161"/>
+      <c r="D451" s="173"/>
       <c r="E451" s="8" t="s">
         <v>573</v>
       </c>
@@ -15847,8 +15901,8 @@
       <c r="B452" s="7">
         <v>16</v>
       </c>
-      <c r="C452" s="163"/>
-      <c r="D452" s="152"/>
+      <c r="C452" s="161"/>
+      <c r="D452" s="174"/>
       <c r="E452" s="8" t="s">
         <v>574</v>
       </c>
@@ -15869,8 +15923,8 @@
       <c r="B453" s="7">
         <v>17</v>
       </c>
-      <c r="C453" s="163"/>
-      <c r="D453" s="150" t="s">
+      <c r="C453" s="161"/>
+      <c r="D453" s="172" t="s">
         <v>575</v>
       </c>
       <c r="E453" s="8" t="s">
@@ -15893,8 +15947,8 @@
       <c r="B454" s="7">
         <v>18</v>
       </c>
-      <c r="C454" s="163"/>
-      <c r="D454" s="151"/>
+      <c r="C454" s="161"/>
+      <c r="D454" s="173"/>
       <c r="E454" s="8" t="s">
         <v>577</v>
       </c>
@@ -15915,8 +15969,8 @@
       <c r="B455" s="7">
         <v>19</v>
       </c>
-      <c r="C455" s="163"/>
-      <c r="D455" s="151"/>
+      <c r="C455" s="161"/>
+      <c r="D455" s="173"/>
       <c r="E455" s="8" t="s">
         <v>578</v>
       </c>
@@ -15937,8 +15991,8 @@
       <c r="B456" s="7">
         <v>20</v>
       </c>
-      <c r="C456" s="163"/>
-      <c r="D456" s="151"/>
+      <c r="C456" s="161"/>
+      <c r="D456" s="173"/>
       <c r="E456" s="39" t="s">
         <v>579</v>
       </c>
@@ -15959,8 +16013,8 @@
       <c r="B457" s="7">
         <v>21</v>
       </c>
-      <c r="C457" s="163"/>
-      <c r="D457" s="151"/>
+      <c r="C457" s="161"/>
+      <c r="D457" s="173"/>
       <c r="E457" s="8" t="s">
         <v>580</v>
       </c>
@@ -15981,8 +16035,8 @@
       <c r="B458" s="24">
         <v>22</v>
       </c>
-      <c r="C458" s="164"/>
-      <c r="D458" s="152"/>
+      <c r="C458" s="162"/>
+      <c r="D458" s="174"/>
       <c r="E458" s="17" t="s">
         <v>581</v>
       </c>
@@ -16004,10 +16058,10 @@
       <c r="B459" s="7">
         <v>1</v>
       </c>
-      <c r="C459" s="165" t="s">
+      <c r="C459" s="151" t="s">
         <v>582</v>
       </c>
-      <c r="D459" s="150" t="s">
+      <c r="D459" s="172" t="s">
         <v>583</v>
       </c>
       <c r="E459" s="8" t="s">
@@ -16030,8 +16084,8 @@
       <c r="B460" s="7">
         <v>2</v>
       </c>
-      <c r="C460" s="166"/>
-      <c r="D460" s="151"/>
+      <c r="C460" s="152"/>
+      <c r="D460" s="173"/>
       <c r="E460" s="8" t="s">
         <v>584</v>
       </c>
@@ -16052,8 +16106,8 @@
       <c r="B461" s="7">
         <v>3</v>
       </c>
-      <c r="C461" s="166"/>
-      <c r="D461" s="151"/>
+      <c r="C461" s="152"/>
+      <c r="D461" s="173"/>
       <c r="E461" s="8" t="s">
         <v>585</v>
       </c>
@@ -16074,8 +16128,8 @@
       <c r="B462" s="7">
         <v>4</v>
       </c>
-      <c r="C462" s="166"/>
-      <c r="D462" s="151"/>
+      <c r="C462" s="152"/>
+      <c r="D462" s="173"/>
       <c r="E462" s="8" t="s">
         <v>586</v>
       </c>
@@ -16096,8 +16150,8 @@
       <c r="B463" s="7">
         <v>5</v>
       </c>
-      <c r="C463" s="166"/>
-      <c r="D463" s="151"/>
+      <c r="C463" s="152"/>
+      <c r="D463" s="173"/>
       <c r="E463" s="8" t="s">
         <v>587</v>
       </c>
@@ -16118,8 +16172,8 @@
       <c r="B464" s="7">
         <v>6</v>
       </c>
-      <c r="C464" s="166"/>
-      <c r="D464" s="151"/>
+      <c r="C464" s="152"/>
+      <c r="D464" s="173"/>
       <c r="E464" s="8" t="s">
         <v>588</v>
       </c>
@@ -16140,8 +16194,8 @@
       <c r="B465" s="7">
         <v>7</v>
       </c>
-      <c r="C465" s="166"/>
-      <c r="D465" s="151"/>
+      <c r="C465" s="152"/>
+      <c r="D465" s="173"/>
       <c r="E465" s="8" t="s">
         <v>589</v>
       </c>
@@ -16162,8 +16216,8 @@
       <c r="B466" s="7">
         <v>8</v>
       </c>
-      <c r="C466" s="166"/>
-      <c r="D466" s="152"/>
+      <c r="C466" s="152"/>
+      <c r="D466" s="174"/>
       <c r="E466" s="8" t="s">
         <v>590</v>
       </c>
@@ -16184,8 +16238,8 @@
       <c r="B467" s="7">
         <v>9</v>
       </c>
-      <c r="C467" s="166"/>
-      <c r="D467" s="150" t="s">
+      <c r="C467" s="152"/>
+      <c r="D467" s="172" t="s">
         <v>591</v>
       </c>
       <c r="E467" s="8" t="s">
@@ -16208,8 +16262,8 @@
       <c r="B468" s="7">
         <v>10</v>
       </c>
-      <c r="C468" s="166"/>
-      <c r="D468" s="151"/>
+      <c r="C468" s="152"/>
+      <c r="D468" s="173"/>
       <c r="E468" s="8" t="s">
         <v>593</v>
       </c>
@@ -16230,8 +16284,8 @@
       <c r="B469" s="7">
         <v>11</v>
       </c>
-      <c r="C469" s="166"/>
-      <c r="D469" s="151"/>
+      <c r="C469" s="152"/>
+      <c r="D469" s="173"/>
       <c r="E469" s="8" t="s">
         <v>594</v>
       </c>
@@ -16252,8 +16306,8 @@
       <c r="B470" s="7">
         <v>12</v>
       </c>
-      <c r="C470" s="166"/>
-      <c r="D470" s="151"/>
+      <c r="C470" s="152"/>
+      <c r="D470" s="173"/>
       <c r="E470" s="8" t="s">
         <v>595</v>
       </c>
@@ -16274,8 +16328,8 @@
       <c r="B471" s="7">
         <v>13</v>
       </c>
-      <c r="C471" s="166"/>
-      <c r="D471" s="151"/>
+      <c r="C471" s="152"/>
+      <c r="D471" s="173"/>
       <c r="E471" s="8" t="s">
         <v>596</v>
       </c>
@@ -16296,8 +16350,8 @@
       <c r="B472" s="7">
         <v>14</v>
       </c>
-      <c r="C472" s="166"/>
-      <c r="D472" s="151"/>
+      <c r="C472" s="152"/>
+      <c r="D472" s="173"/>
       <c r="E472" s="8" t="s">
         <v>597</v>
       </c>
@@ -16318,8 +16372,8 @@
       <c r="B473" s="7">
         <v>15</v>
       </c>
-      <c r="C473" s="166"/>
-      <c r="D473" s="152"/>
+      <c r="C473" s="152"/>
+      <c r="D473" s="174"/>
       <c r="E473" s="8" t="s">
         <v>598</v>
       </c>
@@ -16340,8 +16394,8 @@
       <c r="B474" s="7">
         <v>16</v>
       </c>
-      <c r="C474" s="166"/>
-      <c r="D474" s="150" t="s">
+      <c r="C474" s="152"/>
+      <c r="D474" s="172" t="s">
         <v>599</v>
       </c>
       <c r="E474" s="8" t="s">
@@ -16364,8 +16418,8 @@
       <c r="B475" s="7">
         <v>17</v>
       </c>
-      <c r="C475" s="166"/>
-      <c r="D475" s="151"/>
+      <c r="C475" s="152"/>
+      <c r="D475" s="173"/>
       <c r="E475" s="8" t="s">
         <v>601</v>
       </c>
@@ -16386,8 +16440,8 @@
       <c r="B476" s="7">
         <v>18</v>
       </c>
-      <c r="C476" s="166"/>
-      <c r="D476" s="151"/>
+      <c r="C476" s="152"/>
+      <c r="D476" s="173"/>
       <c r="E476" s="8" t="s">
         <v>602</v>
       </c>
@@ -16408,8 +16462,8 @@
       <c r="B477" s="7">
         <v>19</v>
       </c>
-      <c r="C477" s="166"/>
-      <c r="D477" s="151"/>
+      <c r="C477" s="152"/>
+      <c r="D477" s="173"/>
       <c r="E477" s="8" t="s">
         <v>603</v>
       </c>
@@ -16430,8 +16484,8 @@
       <c r="B478" s="7">
         <v>20</v>
       </c>
-      <c r="C478" s="166"/>
-      <c r="D478" s="151"/>
+      <c r="C478" s="152"/>
+      <c r="D478" s="173"/>
       <c r="E478" s="8" t="s">
         <v>604</v>
       </c>
@@ -16452,8 +16506,8 @@
       <c r="B479" s="7">
         <v>21</v>
       </c>
-      <c r="C479" s="166"/>
-      <c r="D479" s="151"/>
+      <c r="C479" s="152"/>
+      <c r="D479" s="173"/>
       <c r="E479" s="8" t="s">
         <v>605</v>
       </c>
@@ -16474,8 +16528,8 @@
       <c r="B480" s="7">
         <v>22</v>
       </c>
-      <c r="C480" s="166"/>
-      <c r="D480" s="151"/>
+      <c r="C480" s="152"/>
+      <c r="D480" s="173"/>
       <c r="E480" s="8" t="s">
         <v>606</v>
       </c>
@@ -16496,8 +16550,8 @@
       <c r="B481" s="7">
         <v>23</v>
       </c>
-      <c r="C481" s="166"/>
-      <c r="D481" s="152"/>
+      <c r="C481" s="152"/>
+      <c r="D481" s="174"/>
       <c r="E481" s="8" t="s">
         <v>607</v>
       </c>
@@ -16518,8 +16572,8 @@
       <c r="B482" s="7">
         <v>24</v>
       </c>
-      <c r="C482" s="166"/>
-      <c r="D482" s="150" t="s">
+      <c r="C482" s="152"/>
+      <c r="D482" s="172" t="s">
         <v>608</v>
       </c>
       <c r="E482" s="8" t="s">
@@ -16542,8 +16596,8 @@
       <c r="B483" s="7">
         <v>25</v>
       </c>
-      <c r="C483" s="166"/>
-      <c r="D483" s="151"/>
+      <c r="C483" s="152"/>
+      <c r="D483" s="173"/>
       <c r="E483" s="8" t="s">
         <v>610</v>
       </c>
@@ -16564,8 +16618,8 @@
       <c r="B484" s="7">
         <v>26</v>
       </c>
-      <c r="C484" s="166"/>
-      <c r="D484" s="151"/>
+      <c r="C484" s="152"/>
+      <c r="D484" s="173"/>
       <c r="E484" s="8" t="s">
         <v>611</v>
       </c>
@@ -16586,8 +16640,8 @@
       <c r="B485" s="7">
         <v>27</v>
       </c>
-      <c r="C485" s="166"/>
-      <c r="D485" s="152"/>
+      <c r="C485" s="152"/>
+      <c r="D485" s="174"/>
       <c r="E485" s="8" t="s">
         <v>612</v>
       </c>
@@ -16608,8 +16662,8 @@
       <c r="B486" s="7">
         <v>28</v>
       </c>
-      <c r="C486" s="166"/>
-      <c r="D486" s="150" t="s">
+      <c r="C486" s="152"/>
+      <c r="D486" s="172" t="s">
         <v>613</v>
       </c>
       <c r="E486" s="8" t="s">
@@ -16632,8 +16686,8 @@
       <c r="B487" s="7">
         <v>29</v>
       </c>
-      <c r="C487" s="166"/>
-      <c r="D487" s="151"/>
+      <c r="C487" s="152"/>
+      <c r="D487" s="173"/>
       <c r="E487" s="8" t="s">
         <v>615</v>
       </c>
@@ -16654,8 +16708,8 @@
       <c r="B488" s="7">
         <v>30</v>
       </c>
-      <c r="C488" s="166"/>
-      <c r="D488" s="151"/>
+      <c r="C488" s="152"/>
+      <c r="D488" s="173"/>
       <c r="E488" s="8" t="s">
         <v>616</v>
       </c>
@@ -16676,8 +16730,8 @@
       <c r="B489" s="7">
         <v>31</v>
       </c>
-      <c r="C489" s="166"/>
-      <c r="D489" s="151"/>
+      <c r="C489" s="152"/>
+      <c r="D489" s="173"/>
       <c r="E489" s="8" t="s">
         <v>617</v>
       </c>
@@ -16698,8 +16752,8 @@
       <c r="B490" s="7">
         <v>32</v>
       </c>
-      <c r="C490" s="166"/>
-      <c r="D490" s="151"/>
+      <c r="C490" s="152"/>
+      <c r="D490" s="173"/>
       <c r="E490" s="8" t="s">
         <v>618</v>
       </c>
@@ -16720,8 +16774,8 @@
       <c r="B491" s="7">
         <v>33</v>
       </c>
-      <c r="C491" s="166"/>
-      <c r="D491" s="151"/>
+      <c r="C491" s="152"/>
+      <c r="D491" s="173"/>
       <c r="E491" s="8" t="s">
         <v>619</v>
       </c>
@@ -16742,8 +16796,8 @@
       <c r="B492" s="7">
         <v>34</v>
       </c>
-      <c r="C492" s="166"/>
-      <c r="D492" s="151"/>
+      <c r="C492" s="152"/>
+      <c r="D492" s="173"/>
       <c r="E492" s="8" t="s">
         <v>620</v>
       </c>
@@ -16764,8 +16818,8 @@
       <c r="B493" s="7">
         <v>35</v>
       </c>
-      <c r="C493" s="166"/>
-      <c r="D493" s="151"/>
+      <c r="C493" s="152"/>
+      <c r="D493" s="173"/>
       <c r="E493" s="8" t="s">
         <v>621</v>
       </c>
@@ -16786,8 +16840,8 @@
       <c r="B494" s="7">
         <v>36</v>
       </c>
-      <c r="C494" s="166"/>
-      <c r="D494" s="151"/>
+      <c r="C494" s="152"/>
+      <c r="D494" s="173"/>
       <c r="E494" s="8" t="s">
         <v>622</v>
       </c>
@@ -16808,8 +16862,8 @@
       <c r="B495" s="7">
         <v>37</v>
       </c>
-      <c r="C495" s="166"/>
-      <c r="D495" s="151"/>
+      <c r="C495" s="152"/>
+      <c r="D495" s="173"/>
       <c r="E495" s="8" t="s">
         <v>623</v>
       </c>
@@ -16830,8 +16884,8 @@
       <c r="B496" s="7">
         <v>38</v>
       </c>
-      <c r="C496" s="166"/>
-      <c r="D496" s="152"/>
+      <c r="C496" s="152"/>
+      <c r="D496" s="174"/>
       <c r="E496" s="8" t="s">
         <v>624</v>
       </c>
@@ -16852,8 +16906,8 @@
       <c r="B497" s="7">
         <v>39</v>
       </c>
-      <c r="C497" s="166"/>
-      <c r="D497" s="150" t="s">
+      <c r="C497" s="152"/>
+      <c r="D497" s="172" t="s">
         <v>625</v>
       </c>
       <c r="E497" s="8" t="s">
@@ -16876,8 +16930,8 @@
       <c r="B498" s="7">
         <v>40</v>
       </c>
-      <c r="C498" s="166"/>
-      <c r="D498" s="151"/>
+      <c r="C498" s="152"/>
+      <c r="D498" s="173"/>
       <c r="E498" s="8" t="s">
         <v>626</v>
       </c>
@@ -16898,8 +16952,8 @@
       <c r="B499" s="7">
         <v>41</v>
       </c>
-      <c r="C499" s="166"/>
-      <c r="D499" s="151"/>
+      <c r="C499" s="152"/>
+      <c r="D499" s="173"/>
       <c r="E499" s="8" t="s">
         <v>627</v>
       </c>
@@ -16920,8 +16974,8 @@
       <c r="B500" s="7">
         <v>42</v>
       </c>
-      <c r="C500" s="166"/>
-      <c r="D500" s="151"/>
+      <c r="C500" s="152"/>
+      <c r="D500" s="173"/>
       <c r="E500" s="8" t="s">
         <v>628</v>
       </c>
@@ -16942,8 +16996,8 @@
       <c r="B501" s="7">
         <v>43</v>
       </c>
-      <c r="C501" s="166"/>
-      <c r="D501" s="151"/>
+      <c r="C501" s="152"/>
+      <c r="D501" s="173"/>
       <c r="E501" s="8" t="s">
         <v>629</v>
       </c>
@@ -16964,8 +17018,8 @@
       <c r="B502" s="7">
         <v>44</v>
       </c>
-      <c r="C502" s="166"/>
-      <c r="D502" s="152"/>
+      <c r="C502" s="152"/>
+      <c r="D502" s="174"/>
       <c r="E502" s="8" t="s">
         <v>630</v>
       </c>
@@ -16986,8 +17040,8 @@
       <c r="B503" s="7">
         <v>45</v>
       </c>
-      <c r="C503" s="166"/>
-      <c r="D503" s="150" t="s">
+      <c r="C503" s="152"/>
+      <c r="D503" s="172" t="s">
         <v>631</v>
       </c>
       <c r="E503" s="8" t="s">
@@ -17010,8 +17064,8 @@
       <c r="B504" s="7">
         <v>46</v>
       </c>
-      <c r="C504" s="166"/>
-      <c r="D504" s="151"/>
+      <c r="C504" s="152"/>
+      <c r="D504" s="173"/>
       <c r="E504" s="8" t="s">
         <v>633</v>
       </c>
@@ -17032,8 +17086,8 @@
       <c r="B505" s="7">
         <v>47</v>
       </c>
-      <c r="C505" s="166"/>
-      <c r="D505" s="151"/>
+      <c r="C505" s="152"/>
+      <c r="D505" s="173"/>
       <c r="E505" s="8" t="s">
         <v>634</v>
       </c>
@@ -17054,8 +17108,8 @@
       <c r="B506" s="7">
         <v>48</v>
       </c>
-      <c r="C506" s="166"/>
-      <c r="D506" s="151"/>
+      <c r="C506" s="152"/>
+      <c r="D506" s="173"/>
       <c r="E506" s="8" t="s">
         <v>635</v>
       </c>
@@ -17076,8 +17130,8 @@
       <c r="B507" s="7">
         <v>49</v>
       </c>
-      <c r="C507" s="166"/>
-      <c r="D507" s="151"/>
+      <c r="C507" s="152"/>
+      <c r="D507" s="173"/>
       <c r="E507" s="8" t="s">
         <v>636</v>
       </c>
@@ -17098,8 +17152,8 @@
       <c r="B508" s="7">
         <v>50</v>
       </c>
-      <c r="C508" s="166"/>
-      <c r="D508" s="151"/>
+      <c r="C508" s="152"/>
+      <c r="D508" s="173"/>
       <c r="E508" s="8" t="s">
         <v>637</v>
       </c>
@@ -17120,8 +17174,8 @@
       <c r="B509" s="7">
         <v>51</v>
       </c>
-      <c r="C509" s="166"/>
-      <c r="D509" s="152"/>
+      <c r="C509" s="152"/>
+      <c r="D509" s="174"/>
       <c r="E509" s="8" t="s">
         <v>638</v>
       </c>
@@ -17142,8 +17196,8 @@
       <c r="B510" s="7">
         <v>52</v>
       </c>
-      <c r="C510" s="166"/>
-      <c r="D510" s="150" t="s">
+      <c r="C510" s="152"/>
+      <c r="D510" s="172" t="s">
         <v>639</v>
       </c>
       <c r="E510" s="8" t="s">
@@ -17166,8 +17220,8 @@
       <c r="B511" s="7">
         <v>53</v>
       </c>
-      <c r="C511" s="166"/>
-      <c r="D511" s="151"/>
+      <c r="C511" s="152"/>
+      <c r="D511" s="173"/>
       <c r="E511" s="8" t="s">
         <v>641</v>
       </c>
@@ -17188,8 +17242,8 @@
       <c r="B512" s="7">
         <v>54</v>
       </c>
-      <c r="C512" s="166"/>
-      <c r="D512" s="151"/>
+      <c r="C512" s="152"/>
+      <c r="D512" s="173"/>
       <c r="E512" s="8" t="s">
         <v>642</v>
       </c>
@@ -17210,8 +17264,8 @@
       <c r="B513" s="24">
         <v>55</v>
       </c>
-      <c r="C513" s="167"/>
-      <c r="D513" s="152"/>
+      <c r="C513" s="153"/>
+      <c r="D513" s="174"/>
       <c r="E513" s="17" t="s">
         <v>643</v>
       </c>
@@ -24145,6 +24199,107 @@
     </row>
   </sheetData>
   <mergeCells count="125">
+    <mergeCell ref="D26:D32"/>
+    <mergeCell ref="D33:D36"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="C4:C32"/>
+    <mergeCell ref="D4:D9"/>
+    <mergeCell ref="D10:D18"/>
+    <mergeCell ref="D19:D25"/>
+    <mergeCell ref="C33:C44"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="D40:D44"/>
+    <mergeCell ref="C107:C116"/>
+    <mergeCell ref="C117:C125"/>
+    <mergeCell ref="C127:C132"/>
+    <mergeCell ref="C134:C176"/>
+    <mergeCell ref="C177:C204"/>
+    <mergeCell ref="C205:C214"/>
+    <mergeCell ref="A106:J106"/>
+    <mergeCell ref="D107:D111"/>
+    <mergeCell ref="D112:D115"/>
+    <mergeCell ref="D117:D120"/>
+    <mergeCell ref="D121:D122"/>
+    <mergeCell ref="D123:D125"/>
+    <mergeCell ref="A126:J126"/>
+    <mergeCell ref="D127:D130"/>
+    <mergeCell ref="D131:D132"/>
+    <mergeCell ref="A133:J133"/>
+    <mergeCell ref="D210:D211"/>
+    <mergeCell ref="D212:D214"/>
+    <mergeCell ref="C45:C50"/>
+    <mergeCell ref="D45:D50"/>
+    <mergeCell ref="D51:D57"/>
+    <mergeCell ref="D58:D63"/>
+    <mergeCell ref="D64:D67"/>
+    <mergeCell ref="D69:D78"/>
+    <mergeCell ref="D79:D84"/>
+    <mergeCell ref="D85:D90"/>
+    <mergeCell ref="D91:D105"/>
+    <mergeCell ref="A68:J68"/>
+    <mergeCell ref="C51:C67"/>
+    <mergeCell ref="C69:C105"/>
+    <mergeCell ref="A215:J215"/>
+    <mergeCell ref="A273:J273"/>
+    <mergeCell ref="A358:J358"/>
+    <mergeCell ref="D134:D136"/>
+    <mergeCell ref="D137:D143"/>
+    <mergeCell ref="D144:D150"/>
+    <mergeCell ref="D151:D156"/>
+    <mergeCell ref="D157:D159"/>
+    <mergeCell ref="D160:D165"/>
+    <mergeCell ref="D166:D172"/>
+    <mergeCell ref="D173:D176"/>
+    <mergeCell ref="D177:D178"/>
+    <mergeCell ref="D179:D184"/>
+    <mergeCell ref="D185:D186"/>
+    <mergeCell ref="D187:D190"/>
+    <mergeCell ref="D191:D198"/>
+    <mergeCell ref="D199:D202"/>
+    <mergeCell ref="D203:D204"/>
+    <mergeCell ref="D205:D209"/>
+    <mergeCell ref="D216:D225"/>
+    <mergeCell ref="D226:D233"/>
+    <mergeCell ref="D234:D240"/>
+    <mergeCell ref="D241:D243"/>
+    <mergeCell ref="D244:D249"/>
+    <mergeCell ref="D442:D445"/>
+    <mergeCell ref="D446:D448"/>
+    <mergeCell ref="D400:D404"/>
+    <mergeCell ref="D405:D416"/>
+    <mergeCell ref="A436:J436"/>
+    <mergeCell ref="D359:D363"/>
+    <mergeCell ref="D364:D371"/>
+    <mergeCell ref="D372:D375"/>
+    <mergeCell ref="D376:D380"/>
+    <mergeCell ref="D381:D386"/>
+    <mergeCell ref="D387:D396"/>
+    <mergeCell ref="D397:D399"/>
+    <mergeCell ref="D301:D303"/>
+    <mergeCell ref="D304:D307"/>
+    <mergeCell ref="D308:D314"/>
+    <mergeCell ref="D315:D317"/>
+    <mergeCell ref="C343:C357"/>
+    <mergeCell ref="C359:C380"/>
+    <mergeCell ref="C381:C435"/>
+    <mergeCell ref="C437:C458"/>
+    <mergeCell ref="D250:D257"/>
+    <mergeCell ref="D258:D259"/>
+    <mergeCell ref="D260:D265"/>
+    <mergeCell ref="D266:D270"/>
+    <mergeCell ref="D271:D272"/>
+    <mergeCell ref="D274:D281"/>
+    <mergeCell ref="D282:D288"/>
+    <mergeCell ref="D289:D292"/>
+    <mergeCell ref="D293:D295"/>
+    <mergeCell ref="D449:D452"/>
+    <mergeCell ref="D453:D458"/>
+    <mergeCell ref="D417:D419"/>
+    <mergeCell ref="D420:D426"/>
+    <mergeCell ref="D427:D430"/>
+    <mergeCell ref="D431:D435"/>
+    <mergeCell ref="D437:D441"/>
     <mergeCell ref="C459:C513"/>
     <mergeCell ref="C216:C249"/>
     <mergeCell ref="C250:C265"/>
@@ -24169,107 +24324,6 @@
     <mergeCell ref="D348:D353"/>
     <mergeCell ref="D354:D357"/>
     <mergeCell ref="D296:D300"/>
-    <mergeCell ref="D301:D303"/>
-    <mergeCell ref="D304:D307"/>
-    <mergeCell ref="D308:D314"/>
-    <mergeCell ref="D315:D317"/>
-    <mergeCell ref="C343:C357"/>
-    <mergeCell ref="C359:C380"/>
-    <mergeCell ref="C381:C435"/>
-    <mergeCell ref="C437:C458"/>
-    <mergeCell ref="D250:D257"/>
-    <mergeCell ref="D258:D259"/>
-    <mergeCell ref="D260:D265"/>
-    <mergeCell ref="D266:D270"/>
-    <mergeCell ref="D271:D272"/>
-    <mergeCell ref="D274:D281"/>
-    <mergeCell ref="D282:D288"/>
-    <mergeCell ref="D289:D292"/>
-    <mergeCell ref="D293:D295"/>
-    <mergeCell ref="D449:D452"/>
-    <mergeCell ref="D453:D458"/>
-    <mergeCell ref="D417:D419"/>
-    <mergeCell ref="D420:D426"/>
-    <mergeCell ref="D427:D430"/>
-    <mergeCell ref="D431:D435"/>
-    <mergeCell ref="D437:D441"/>
-    <mergeCell ref="D442:D445"/>
-    <mergeCell ref="D446:D448"/>
-    <mergeCell ref="D400:D404"/>
-    <mergeCell ref="D405:D416"/>
-    <mergeCell ref="A436:J436"/>
-    <mergeCell ref="D359:D363"/>
-    <mergeCell ref="D364:D371"/>
-    <mergeCell ref="D372:D375"/>
-    <mergeCell ref="D376:D380"/>
-    <mergeCell ref="D381:D386"/>
-    <mergeCell ref="D387:D396"/>
-    <mergeCell ref="D397:D399"/>
-    <mergeCell ref="A215:J215"/>
-    <mergeCell ref="A273:J273"/>
-    <mergeCell ref="A358:J358"/>
-    <mergeCell ref="D134:D136"/>
-    <mergeCell ref="D137:D143"/>
-    <mergeCell ref="D144:D150"/>
-    <mergeCell ref="D151:D156"/>
-    <mergeCell ref="D157:D159"/>
-    <mergeCell ref="D160:D165"/>
-    <mergeCell ref="D166:D172"/>
-    <mergeCell ref="D173:D176"/>
-    <mergeCell ref="D177:D178"/>
-    <mergeCell ref="D179:D184"/>
-    <mergeCell ref="D185:D186"/>
-    <mergeCell ref="D187:D190"/>
-    <mergeCell ref="D191:D198"/>
-    <mergeCell ref="D199:D202"/>
-    <mergeCell ref="D203:D204"/>
-    <mergeCell ref="D205:D209"/>
-    <mergeCell ref="D216:D225"/>
-    <mergeCell ref="D226:D233"/>
-    <mergeCell ref="D234:D240"/>
-    <mergeCell ref="D241:D243"/>
-    <mergeCell ref="D244:D249"/>
-    <mergeCell ref="C45:C50"/>
-    <mergeCell ref="D45:D50"/>
-    <mergeCell ref="D51:D57"/>
-    <mergeCell ref="D58:D63"/>
-    <mergeCell ref="D64:D67"/>
-    <mergeCell ref="D69:D78"/>
-    <mergeCell ref="D79:D84"/>
-    <mergeCell ref="D85:D90"/>
-    <mergeCell ref="D91:D105"/>
-    <mergeCell ref="A68:J68"/>
-    <mergeCell ref="C51:C67"/>
-    <mergeCell ref="C69:C105"/>
-    <mergeCell ref="C107:C116"/>
-    <mergeCell ref="C117:C125"/>
-    <mergeCell ref="C127:C132"/>
-    <mergeCell ref="C134:C176"/>
-    <mergeCell ref="C177:C204"/>
-    <mergeCell ref="C205:C214"/>
-    <mergeCell ref="A106:J106"/>
-    <mergeCell ref="D107:D111"/>
-    <mergeCell ref="D112:D115"/>
-    <mergeCell ref="D117:D120"/>
-    <mergeCell ref="D121:D122"/>
-    <mergeCell ref="D123:D125"/>
-    <mergeCell ref="A126:J126"/>
-    <mergeCell ref="D127:D130"/>
-    <mergeCell ref="D131:D132"/>
-    <mergeCell ref="A133:J133"/>
-    <mergeCell ref="D210:D211"/>
-    <mergeCell ref="D212:D214"/>
-    <mergeCell ref="D26:D32"/>
-    <mergeCell ref="D33:D36"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="C4:C32"/>
-    <mergeCell ref="D4:D9"/>
-    <mergeCell ref="D10:D18"/>
-    <mergeCell ref="D19:D25"/>
-    <mergeCell ref="C33:C44"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="D40:D44"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H69:H105 H107:H125 H127:H132 H134:H214 H216:H272 H274:H357 H359:H435 H437:H513 H4:H65 H67" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -24799,16 +24853,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="31.5" customHeight="1">
-      <c r="A1" s="201" t="s">
+      <c r="A1" s="202" t="s">
         <v>644</v>
       </c>
-      <c r="B1" s="202"/>
+      <c r="B1" s="203"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1">
-      <c r="A2" s="203" t="s">
+      <c r="A2" s="204" t="s">
         <v>645</v>
       </c>
-      <c r="B2" s="202"/>
+      <c r="B2" s="203"/>
     </row>
     <row r="3" spans="1:2" ht="18" customHeight="1">
       <c r="A3" s="46" t="s">
@@ -24855,10 +24909,10 @@
       <c r="B8" s="47"/>
     </row>
     <row r="9" spans="1:2" ht="18" customHeight="1">
-      <c r="A9" s="203" t="s">
+      <c r="A9" s="204" t="s">
         <v>656</v>
       </c>
-      <c r="B9" s="202"/>
+      <c r="B9" s="203"/>
     </row>
     <row r="10" spans="1:2" ht="18" customHeight="1">
       <c r="A10" s="52" t="s">
@@ -24937,10 +24991,10 @@
       <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:2" ht="18" customHeight="1">
-      <c r="A20" s="203" t="s">
+      <c r="A20" s="204" t="s">
         <v>675</v>
       </c>
-      <c r="B20" s="202"/>
+      <c r="B20" s="203"/>
     </row>
     <row r="21" spans="1:2" ht="18" customHeight="1">
       <c r="A21" s="52" t="s">
@@ -25937,15 +25991,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="204" t="s">
+      <c r="A1" s="205" t="s">
         <v>678</v>
       </c>
-      <c r="B1" s="205"/>
-      <c r="C1" s="205"/>
-      <c r="D1" s="205"/>
-      <c r="E1" s="205"/>
-      <c r="F1" s="205"/>
-      <c r="G1" s="202"/>
+      <c r="B1" s="206"/>
+      <c r="C1" s="206"/>
+      <c r="D1" s="206"/>
+      <c r="E1" s="206"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="203"/>
     </row>
     <row r="2" spans="1:8" ht="13.2">
       <c r="A2" s="53" t="s">

--- a/DSA Master Sheet.xlsx
+++ b/DSA Master Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aamer\Desktop\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F3F839-BE7B-4C00-8658-EAD648CFB65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD7EDFA3-1A67-4830-9296-459400BDA85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1411" uniqueCount="739">
   <si>
     <t>DSA Master Sheet</t>
   </si>
@@ -2946,16 +2946,51 @@
 If the target lies in the sorted half, search there; otherwise search the other half.
 Repeat until found; otherwise return false.</t>
   </si>
+  <si>
+    <t>1. Find mid
+2. Make mid even
+3. Compare nums[mid] and nums[mid + 1]
+Equal → answer is on the right
+        low = mid + 2
+Not equal → answer is on the left
+            high = mid</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> while (low &lt;high) {
+            mid = (low + high) / 2;
+            if(arr[mid]&gt;arr[high])
+            low = mid+1;
+            else
+            high = mid;
+        }
+        return low;</t>
+  </si>
+  <si>
+    <t>Check first element → if peak, return 0
+Check last element → if peak, return n-1
+Search only middle: low=1, high=n-2
+Find mid
+If mid &gt; left AND mid &gt; right → peak found → return mid
+If mid &lt; left → going downhill → search LEFT
+If mid &lt; right → going uphill → search RIGHT</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="99">
+  <fonts count="100">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4045,364 +4080,367 @@
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="87" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="88" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="89" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="88" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="90" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="208">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="31" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="33" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="34" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="35" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="20" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="20" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="22" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="22" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="24" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="24" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="26" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="28" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="29" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="29" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="31" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="31" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="32" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="32" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="27" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="37" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="37" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="38" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="38" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="38" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="38" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="39" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="39" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="40" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="40" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="67" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="68" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="41" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="41" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="42" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="42" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="42" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="42" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="43" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="43" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="44" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="71" fillId="44" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="44" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="44" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="45" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="45" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="46" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="46" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="46" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="46" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="47" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="47" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="48" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="48" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="49" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="77" fillId="49" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="49" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="78" fillId="49" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="50" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="50" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="51" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="79" fillId="51" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="51" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="80" fillId="51" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="81" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="81" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="82" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="87" fillId="52" borderId="6" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="88" fillId="53" borderId="6" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="89" fillId="54" borderId="6" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="88" fillId="52" borderId="6" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="89" fillId="53" borderId="6" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="90" fillId="54" borderId="6" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4411,212 +4449,209 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="88" fillId="52" borderId="8" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="89" fillId="53" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="53" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="53" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="53" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="53" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="89" fillId="53" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="53" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="53" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="53" borderId="8" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="89" fillId="53" borderId="13" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="87" fillId="52" borderId="8" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="88" fillId="53" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="88" fillId="53" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="88" fillId="53" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="88" fillId="53" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="53" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="88" fillId="53" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="53" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="88" fillId="53" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="88" fillId="53" borderId="8" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="88" fillId="53" borderId="13" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
@@ -5414,18 +5449,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="30.75" customHeight="1">
-      <c r="A1" s="199" t="s">
+      <c r="A1" s="155" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="200"/>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
-      <c r="G1" s="200"/>
-      <c r="H1" s="200"/>
-      <c r="I1" s="200"/>
-      <c r="J1" s="201"/>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="157"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -5480,18 +5515,18 @@
       <c r="T2" s="5"/>
     </row>
     <row r="3" spans="1:20" ht="13.8">
-      <c r="A3" s="196" t="s">
+      <c r="A3" s="158" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
-      <c r="D3" s="197"/>
-      <c r="E3" s="197"/>
-      <c r="F3" s="197"/>
-      <c r="G3" s="197"/>
-      <c r="H3" s="197"/>
-      <c r="I3" s="197"/>
-      <c r="J3" s="198"/>
+      <c r="B3" s="159"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="159"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="160"/>
     </row>
     <row r="4" spans="1:20" ht="13.8">
       <c r="A4" s="6">
@@ -5500,10 +5535,10 @@
       <c r="B4" s="7">
         <v>1</v>
       </c>
-      <c r="C4" s="157" t="s">
+      <c r="C4" s="161" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="172" t="s">
+      <c r="D4" s="152" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -5533,8 +5568,8 @@
       <c r="B5" s="7">
         <v>2</v>
       </c>
-      <c r="C5" s="158"/>
-      <c r="D5" s="173"/>
+      <c r="C5" s="162"/>
+      <c r="D5" s="153"/>
       <c r="E5" s="8" t="s">
         <v>16</v>
       </c>
@@ -5562,8 +5597,8 @@
       <c r="B6" s="7">
         <v>3</v>
       </c>
-      <c r="C6" s="158"/>
-      <c r="D6" s="173"/>
+      <c r="C6" s="162"/>
+      <c r="D6" s="153"/>
       <c r="E6" s="8" t="s">
         <v>19</v>
       </c>
@@ -5591,8 +5626,8 @@
       <c r="B7" s="7">
         <v>4</v>
       </c>
-      <c r="C7" s="158"/>
-      <c r="D7" s="173"/>
+      <c r="C7" s="162"/>
+      <c r="D7" s="153"/>
       <c r="E7" s="8" t="s">
         <v>23</v>
       </c>
@@ -5620,8 +5655,8 @@
       <c r="B8" s="7">
         <v>5</v>
       </c>
-      <c r="C8" s="158"/>
-      <c r="D8" s="173"/>
+      <c r="C8" s="162"/>
+      <c r="D8" s="153"/>
       <c r="E8" s="8" t="s">
         <v>26</v>
       </c>
@@ -5649,8 +5684,8 @@
       <c r="B9" s="7">
         <v>6</v>
       </c>
-      <c r="C9" s="158"/>
-      <c r="D9" s="174"/>
+      <c r="C9" s="162"/>
+      <c r="D9" s="154"/>
       <c r="E9" s="8" t="s">
         <v>29</v>
       </c>
@@ -5675,8 +5710,8 @@
       <c r="B10" s="7">
         <v>7</v>
       </c>
-      <c r="C10" s="158"/>
-      <c r="D10" s="172" t="s">
+      <c r="C10" s="162"/>
+      <c r="D10" s="152" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="8" t="s">
@@ -5703,8 +5738,8 @@
       <c r="B11" s="7">
         <v>8</v>
       </c>
-      <c r="C11" s="158"/>
-      <c r="D11" s="173"/>
+      <c r="C11" s="162"/>
+      <c r="D11" s="153"/>
       <c r="E11" s="13" t="s">
         <v>32</v>
       </c>
@@ -5729,8 +5764,8 @@
       <c r="B12" s="7">
         <v>9</v>
       </c>
-      <c r="C12" s="158"/>
-      <c r="D12" s="173"/>
+      <c r="C12" s="162"/>
+      <c r="D12" s="153"/>
       <c r="E12" s="8" t="s">
         <v>33</v>
       </c>
@@ -5755,8 +5790,8 @@
       <c r="B13" s="7">
         <v>10</v>
       </c>
-      <c r="C13" s="158"/>
-      <c r="D13" s="173"/>
+      <c r="C13" s="162"/>
+      <c r="D13" s="153"/>
       <c r="E13" s="8" t="s">
         <v>34</v>
       </c>
@@ -5783,8 +5818,8 @@
       <c r="B14" s="7">
         <v>11</v>
       </c>
-      <c r="C14" s="158"/>
-      <c r="D14" s="173"/>
+      <c r="C14" s="162"/>
+      <c r="D14" s="153"/>
       <c r="E14" s="8" t="s">
         <v>35</v>
       </c>
@@ -5809,8 +5844,8 @@
       <c r="B15" s="7">
         <v>12</v>
       </c>
-      <c r="C15" s="158"/>
-      <c r="D15" s="173"/>
+      <c r="C15" s="162"/>
+      <c r="D15" s="153"/>
       <c r="E15" s="8" t="s">
         <v>36</v>
       </c>
@@ -5837,8 +5872,8 @@
       <c r="B16" s="7">
         <v>13</v>
       </c>
-      <c r="C16" s="158"/>
-      <c r="D16" s="173"/>
+      <c r="C16" s="162"/>
+      <c r="D16" s="153"/>
       <c r="E16" s="8" t="s">
         <v>37</v>
       </c>
@@ -5863,8 +5898,8 @@
       <c r="B17" s="7">
         <v>14</v>
       </c>
-      <c r="C17" s="158"/>
-      <c r="D17" s="173"/>
+      <c r="C17" s="162"/>
+      <c r="D17" s="153"/>
       <c r="E17" s="8" t="s">
         <v>38</v>
       </c>
@@ -5891,8 +5926,8 @@
       <c r="B18" s="7">
         <v>15</v>
       </c>
-      <c r="C18" s="158"/>
-      <c r="D18" s="174"/>
+      <c r="C18" s="162"/>
+      <c r="D18" s="154"/>
       <c r="E18" s="13" t="s">
         <v>39</v>
       </c>
@@ -5919,8 +5954,8 @@
       <c r="B19" s="7">
         <v>16</v>
       </c>
-      <c r="C19" s="158"/>
-      <c r="D19" s="172" t="s">
+      <c r="C19" s="162"/>
+      <c r="D19" s="152" t="s">
         <v>40</v>
       </c>
       <c r="E19" s="8" t="s">
@@ -5949,8 +5984,8 @@
       <c r="B20" s="7">
         <v>17</v>
       </c>
-      <c r="C20" s="158"/>
-      <c r="D20" s="173"/>
+      <c r="C20" s="162"/>
+      <c r="D20" s="153"/>
       <c r="E20" s="8" t="s">
         <v>42</v>
       </c>
@@ -5977,8 +6012,8 @@
       <c r="B21" s="7">
         <v>18</v>
       </c>
-      <c r="C21" s="158"/>
-      <c r="D21" s="173"/>
+      <c r="C21" s="162"/>
+      <c r="D21" s="153"/>
       <c r="E21" s="8" t="s">
         <v>43</v>
       </c>
@@ -6005,8 +6040,8 @@
       <c r="B22" s="7">
         <v>19</v>
       </c>
-      <c r="C22" s="158"/>
-      <c r="D22" s="173"/>
+      <c r="C22" s="162"/>
+      <c r="D22" s="153"/>
       <c r="E22" s="8" t="s">
         <v>44</v>
       </c>
@@ -6027,8 +6062,8 @@
       <c r="B23" s="7">
         <v>20</v>
       </c>
-      <c r="C23" s="158"/>
-      <c r="D23" s="173"/>
+      <c r="C23" s="162"/>
+      <c r="D23" s="153"/>
       <c r="E23" s="8" t="s">
         <v>45</v>
       </c>
@@ -6049,8 +6084,8 @@
       <c r="B24" s="7">
         <v>21</v>
       </c>
-      <c r="C24" s="158"/>
-      <c r="D24" s="173"/>
+      <c r="C24" s="162"/>
+      <c r="D24" s="153"/>
       <c r="E24" s="13" t="s">
         <v>46</v>
       </c>
@@ -6075,8 +6110,8 @@
       <c r="B25" s="7">
         <v>22</v>
       </c>
-      <c r="C25" s="158"/>
-      <c r="D25" s="174"/>
+      <c r="C25" s="162"/>
+      <c r="D25" s="154"/>
       <c r="E25" s="8" t="s">
         <v>47</v>
       </c>
@@ -6103,8 +6138,8 @@
       <c r="B26" s="7">
         <v>23</v>
       </c>
-      <c r="C26" s="158"/>
-      <c r="D26" s="172" t="s">
+      <c r="C26" s="162"/>
+      <c r="D26" s="152" t="s">
         <v>48</v>
       </c>
       <c r="E26" s="13" t="s">
@@ -6133,8 +6168,8 @@
       <c r="B27" s="7">
         <v>24</v>
       </c>
-      <c r="C27" s="158"/>
-      <c r="D27" s="173"/>
+      <c r="C27" s="162"/>
+      <c r="D27" s="153"/>
       <c r="E27" s="8" t="s">
         <v>50</v>
       </c>
@@ -6159,8 +6194,8 @@
       <c r="B28" s="7">
         <v>25</v>
       </c>
-      <c r="C28" s="158"/>
-      <c r="D28" s="173"/>
+      <c r="C28" s="162"/>
+      <c r="D28" s="153"/>
       <c r="E28" s="8" t="s">
         <v>51</v>
       </c>
@@ -6187,8 +6222,8 @@
       <c r="B29" s="143">
         <v>26</v>
       </c>
-      <c r="C29" s="158"/>
-      <c r="D29" s="173"/>
+      <c r="C29" s="162"/>
+      <c r="D29" s="153"/>
       <c r="E29" s="144" t="s">
         <v>52</v>
       </c>
@@ -6209,8 +6244,8 @@
       <c r="B30" s="143">
         <v>27</v>
       </c>
-      <c r="C30" s="158"/>
-      <c r="D30" s="173"/>
+      <c r="C30" s="162"/>
+      <c r="D30" s="153"/>
       <c r="E30" s="144" t="s">
         <v>53</v>
       </c>
@@ -6231,8 +6266,8 @@
       <c r="B31" s="143">
         <v>28</v>
       </c>
-      <c r="C31" s="158"/>
-      <c r="D31" s="173"/>
+      <c r="C31" s="162"/>
+      <c r="D31" s="153"/>
       <c r="E31" s="144" t="s">
         <v>54</v>
       </c>
@@ -6253,8 +6288,8 @@
       <c r="B32" s="143">
         <v>29</v>
       </c>
-      <c r="C32" s="159"/>
-      <c r="D32" s="174"/>
+      <c r="C32" s="163"/>
+      <c r="D32" s="154"/>
       <c r="E32" s="146" t="s">
         <v>55</v>
       </c>
@@ -6275,10 +6310,10 @@
       <c r="B33" s="22">
         <v>1</v>
       </c>
-      <c r="C33" s="160" t="s">
+      <c r="C33" s="164" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="172" t="s">
+      <c r="D33" s="152" t="s">
         <v>57</v>
       </c>
       <c r="E33" s="8" t="s">
@@ -6305,8 +6340,8 @@
       <c r="B34" s="7">
         <v>2</v>
       </c>
-      <c r="C34" s="161"/>
-      <c r="D34" s="173"/>
+      <c r="C34" s="165"/>
+      <c r="D34" s="153"/>
       <c r="E34" s="8" t="s">
         <v>59</v>
       </c>
@@ -6331,8 +6366,8 @@
       <c r="B35" s="7">
         <v>3</v>
       </c>
-      <c r="C35" s="161"/>
-      <c r="D35" s="173"/>
+      <c r="C35" s="165"/>
+      <c r="D35" s="153"/>
       <c r="E35" s="8" t="s">
         <v>60</v>
       </c>
@@ -6359,8 +6394,8 @@
       <c r="B36" s="7">
         <v>4</v>
       </c>
-      <c r="C36" s="161"/>
-      <c r="D36" s="174"/>
+      <c r="C36" s="165"/>
+      <c r="D36" s="154"/>
       <c r="E36" s="8" t="s">
         <v>61</v>
       </c>
@@ -6387,8 +6422,8 @@
       <c r="B37" s="7">
         <v>5</v>
       </c>
-      <c r="C37" s="161"/>
-      <c r="D37" s="172" t="s">
+      <c r="C37" s="165"/>
+      <c r="D37" s="152" t="s">
         <v>62</v>
       </c>
       <c r="E37" s="8" t="s">
@@ -6415,8 +6450,8 @@
       <c r="B38" s="7">
         <v>6</v>
       </c>
-      <c r="C38" s="161"/>
-      <c r="D38" s="173"/>
+      <c r="C38" s="165"/>
+      <c r="D38" s="153"/>
       <c r="E38" s="8" t="s">
         <v>64</v>
       </c>
@@ -6441,8 +6476,8 @@
       <c r="B39" s="7">
         <v>7</v>
       </c>
-      <c r="C39" s="161"/>
-      <c r="D39" s="174"/>
+      <c r="C39" s="165"/>
+      <c r="D39" s="154"/>
       <c r="E39" s="8" t="s">
         <v>65</v>
       </c>
@@ -6467,8 +6502,8 @@
       <c r="B40" s="7">
         <v>8</v>
       </c>
-      <c r="C40" s="161"/>
-      <c r="D40" s="172" t="s">
+      <c r="C40" s="165"/>
+      <c r="D40" s="152" t="s">
         <v>66</v>
       </c>
       <c r="E40" s="8" t="s">
@@ -6495,8 +6530,8 @@
       <c r="B41" s="7">
         <v>9</v>
       </c>
-      <c r="C41" s="161"/>
-      <c r="D41" s="173"/>
+      <c r="C41" s="165"/>
+      <c r="D41" s="153"/>
       <c r="E41" s="8" t="s">
         <v>68</v>
       </c>
@@ -6521,8 +6556,8 @@
       <c r="B42" s="7">
         <v>10</v>
       </c>
-      <c r="C42" s="161"/>
-      <c r="D42" s="173"/>
+      <c r="C42" s="165"/>
+      <c r="D42" s="153"/>
       <c r="E42" s="8" t="s">
         <v>69</v>
       </c>
@@ -6547,8 +6582,8 @@
       <c r="B43" s="7">
         <v>11</v>
       </c>
-      <c r="C43" s="161"/>
-      <c r="D43" s="173"/>
+      <c r="C43" s="165"/>
+      <c r="D43" s="153"/>
       <c r="E43" s="8" t="s">
         <v>70</v>
       </c>
@@ -6573,8 +6608,8 @@
       <c r="B44" s="24">
         <v>12</v>
       </c>
-      <c r="C44" s="162"/>
-      <c r="D44" s="174"/>
+      <c r="C44" s="166"/>
+      <c r="D44" s="154"/>
       <c r="E44" s="17" t="s">
         <v>71</v>
       </c>
@@ -6599,10 +6634,10 @@
       <c r="B45" s="22">
         <v>1</v>
       </c>
-      <c r="C45" s="163" t="s">
+      <c r="C45" s="179" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="175" t="s">
+      <c r="D45" s="182" t="s">
         <v>73</v>
       </c>
       <c r="E45" s="13" t="s">
@@ -6629,8 +6664,8 @@
       <c r="B46" s="7">
         <v>2</v>
       </c>
-      <c r="C46" s="164"/>
-      <c r="D46" s="176"/>
+      <c r="C46" s="180"/>
+      <c r="D46" s="183"/>
       <c r="E46" s="8" t="s">
         <v>75</v>
       </c>
@@ -6657,8 +6692,8 @@
       <c r="B47" s="7">
         <v>3</v>
       </c>
-      <c r="C47" s="164"/>
-      <c r="D47" s="176"/>
+      <c r="C47" s="180"/>
+      <c r="D47" s="183"/>
       <c r="E47" s="13" t="s">
         <v>76</v>
       </c>
@@ -6685,8 +6720,8 @@
       <c r="B48" s="7">
         <v>4</v>
       </c>
-      <c r="C48" s="164"/>
-      <c r="D48" s="176"/>
+      <c r="C48" s="180"/>
+      <c r="D48" s="183"/>
       <c r="E48" s="13" t="s">
         <v>77</v>
       </c>
@@ -6713,8 +6748,8 @@
       <c r="B49" s="7">
         <v>5</v>
       </c>
-      <c r="C49" s="164"/>
-      <c r="D49" s="176"/>
+      <c r="C49" s="180"/>
+      <c r="D49" s="183"/>
       <c r="E49" s="13" t="s">
         <v>78</v>
       </c>
@@ -6739,8 +6774,8 @@
       <c r="B50" s="24">
         <v>6</v>
       </c>
-      <c r="C50" s="165"/>
-      <c r="D50" s="177"/>
+      <c r="C50" s="181"/>
+      <c r="D50" s="184"/>
       <c r="E50" s="25" t="s">
         <v>79</v>
       </c>
@@ -6765,10 +6800,10 @@
       <c r="B51" s="7">
         <v>1</v>
       </c>
-      <c r="C51" s="154" t="s">
+      <c r="C51" s="170" t="s">
         <v>80</v>
       </c>
-      <c r="D51" s="172" t="s">
+      <c r="D51" s="152" t="s">
         <v>81</v>
       </c>
       <c r="E51" s="13" t="s">
@@ -6797,8 +6832,8 @@
       <c r="B52" s="7">
         <v>2</v>
       </c>
-      <c r="C52" s="155"/>
-      <c r="D52" s="173"/>
+      <c r="C52" s="171"/>
+      <c r="D52" s="153"/>
       <c r="E52" s="8" t="s">
         <v>83</v>
       </c>
@@ -6825,8 +6860,8 @@
       <c r="B53" s="7">
         <v>3</v>
       </c>
-      <c r="C53" s="155"/>
-      <c r="D53" s="173"/>
+      <c r="C53" s="171"/>
+      <c r="D53" s="153"/>
       <c r="E53" s="27" t="s">
         <v>84</v>
       </c>
@@ -6851,8 +6886,8 @@
       <c r="B54" s="7">
         <v>4</v>
       </c>
-      <c r="C54" s="155"/>
-      <c r="D54" s="173"/>
+      <c r="C54" s="171"/>
+      <c r="D54" s="153"/>
       <c r="E54" s="13" t="s">
         <v>85</v>
       </c>
@@ -6877,8 +6912,8 @@
       <c r="B55" s="7">
         <v>5</v>
       </c>
-      <c r="C55" s="155"/>
-      <c r="D55" s="173"/>
+      <c r="C55" s="171"/>
+      <c r="D55" s="153"/>
       <c r="E55" s="13" t="s">
         <v>86</v>
       </c>
@@ -6905,8 +6940,8 @@
       <c r="B56" s="7">
         <v>6</v>
       </c>
-      <c r="C56" s="155"/>
-      <c r="D56" s="173"/>
+      <c r="C56" s="171"/>
+      <c r="D56" s="153"/>
       <c r="E56" s="13" t="s">
         <v>87</v>
       </c>
@@ -6933,8 +6968,8 @@
       <c r="B57" s="7">
         <v>7</v>
       </c>
-      <c r="C57" s="155"/>
-      <c r="D57" s="174"/>
+      <c r="C57" s="171"/>
+      <c r="D57" s="154"/>
       <c r="E57" s="13" t="s">
         <v>88</v>
       </c>
@@ -6961,8 +6996,8 @@
       <c r="B58" s="7">
         <v>8</v>
       </c>
-      <c r="C58" s="155"/>
-      <c r="D58" s="172" t="s">
+      <c r="C58" s="171"/>
+      <c r="D58" s="152" t="s">
         <v>89</v>
       </c>
       <c r="E58" s="13" t="s">
@@ -6989,8 +7024,8 @@
       <c r="B59" s="7">
         <v>9</v>
       </c>
-      <c r="C59" s="155"/>
-      <c r="D59" s="173"/>
+      <c r="C59" s="171"/>
+      <c r="D59" s="153"/>
       <c r="E59" s="8" t="s">
         <v>91</v>
       </c>
@@ -7015,8 +7050,8 @@
       <c r="B60" s="7">
         <v>10</v>
       </c>
-      <c r="C60" s="155"/>
-      <c r="D60" s="173"/>
+      <c r="C60" s="171"/>
+      <c r="D60" s="153"/>
       <c r="E60" s="8" t="s">
         <v>92</v>
       </c>
@@ -7037,8 +7072,8 @@
       <c r="B61" s="7">
         <v>11</v>
       </c>
-      <c r="C61" s="155"/>
-      <c r="D61" s="173"/>
+      <c r="C61" s="171"/>
+      <c r="D61" s="153"/>
       <c r="E61" s="8" t="s">
         <v>93</v>
       </c>
@@ -7059,8 +7094,8 @@
       <c r="B62" s="7">
         <v>12</v>
       </c>
-      <c r="C62" s="155"/>
-      <c r="D62" s="173"/>
+      <c r="C62" s="171"/>
+      <c r="D62" s="153"/>
       <c r="E62" s="8" t="s">
         <v>94</v>
       </c>
@@ -7085,8 +7120,8 @@
       <c r="B63" s="7">
         <v>13</v>
       </c>
-      <c r="C63" s="155"/>
-      <c r="D63" s="174"/>
+      <c r="C63" s="171"/>
+      <c r="D63" s="154"/>
       <c r="E63" s="8" t="s">
         <v>95</v>
       </c>
@@ -7111,8 +7146,8 @@
       <c r="B64" s="7">
         <v>14</v>
       </c>
-      <c r="C64" s="155"/>
-      <c r="D64" s="172" t="s">
+      <c r="C64" s="171"/>
+      <c r="D64" s="152" t="s">
         <v>48</v>
       </c>
       <c r="E64" s="8" t="s">
@@ -7141,8 +7176,8 @@
       <c r="B65" s="143">
         <v>15</v>
       </c>
-      <c r="C65" s="155"/>
-      <c r="D65" s="173"/>
+      <c r="C65" s="171"/>
+      <c r="D65" s="153"/>
       <c r="E65" s="144" t="s">
         <v>97</v>
       </c>
@@ -7163,8 +7198,8 @@
       <c r="B66" s="7">
         <v>16</v>
       </c>
-      <c r="C66" s="155"/>
-      <c r="D66" s="173"/>
+      <c r="C66" s="171"/>
+      <c r="D66" s="153"/>
       <c r="E66" s="8" t="s">
         <v>98</v>
       </c>
@@ -7191,8 +7226,8 @@
       <c r="B67" s="7">
         <v>17</v>
       </c>
-      <c r="C67" s="156"/>
-      <c r="D67" s="174"/>
+      <c r="C67" s="172"/>
+      <c r="D67" s="154"/>
       <c r="E67" s="8" t="s">
         <v>99</v>
       </c>
@@ -7213,18 +7248,18 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="13.8">
-      <c r="A68" s="184" t="s">
+      <c r="A68" s="185" t="s">
         <v>100</v>
       </c>
-      <c r="B68" s="185"/>
-      <c r="C68" s="185"/>
-      <c r="D68" s="185"/>
-      <c r="E68" s="185"/>
-      <c r="F68" s="185"/>
-      <c r="G68" s="185"/>
-      <c r="H68" s="185"/>
-      <c r="I68" s="185"/>
-      <c r="J68" s="186"/>
+      <c r="B68" s="186"/>
+      <c r="C68" s="186"/>
+      <c r="D68" s="186"/>
+      <c r="E68" s="186"/>
+      <c r="F68" s="186"/>
+      <c r="G68" s="186"/>
+      <c r="H68" s="186"/>
+      <c r="I68" s="186"/>
+      <c r="J68" s="187"/>
     </row>
     <row r="69" spans="1:10" ht="13.8">
       <c r="A69" s="6">
@@ -7233,10 +7268,10 @@
       <c r="B69" s="7">
         <v>1</v>
       </c>
-      <c r="C69" s="157" t="s">
+      <c r="C69" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="D69" s="172" t="s">
+      <c r="D69" s="152" t="s">
         <v>102</v>
       </c>
       <c r="E69" s="8" t="s">
@@ -7263,8 +7298,8 @@
       <c r="B70" s="7">
         <v>2</v>
       </c>
-      <c r="C70" s="158"/>
-      <c r="D70" s="173"/>
+      <c r="C70" s="162"/>
+      <c r="D70" s="153"/>
       <c r="E70" s="28" t="s">
         <v>104</v>
       </c>
@@ -7291,8 +7326,8 @@
       <c r="B71" s="7">
         <v>3</v>
       </c>
-      <c r="C71" s="158"/>
-      <c r="D71" s="173"/>
+      <c r="C71" s="162"/>
+      <c r="D71" s="153"/>
       <c r="E71" s="8" t="s">
         <v>105</v>
       </c>
@@ -7319,8 +7354,8 @@
       <c r="B72" s="7">
         <v>4</v>
       </c>
-      <c r="C72" s="158"/>
-      <c r="D72" s="173"/>
+      <c r="C72" s="162"/>
+      <c r="D72" s="153"/>
       <c r="E72" s="8" t="s">
         <v>106</v>
       </c>
@@ -7347,8 +7382,8 @@
       <c r="B73" s="7">
         <v>5</v>
       </c>
-      <c r="C73" s="158"/>
-      <c r="D73" s="173"/>
+      <c r="C73" s="162"/>
+      <c r="D73" s="153"/>
       <c r="E73" s="28" t="s">
         <v>107</v>
       </c>
@@ -7375,8 +7410,8 @@
       <c r="B74" s="7">
         <v>6</v>
       </c>
-      <c r="C74" s="158"/>
-      <c r="D74" s="173"/>
+      <c r="C74" s="162"/>
+      <c r="D74" s="153"/>
       <c r="E74" s="28" t="s">
         <v>108</v>
       </c>
@@ -7401,8 +7436,8 @@
       <c r="B75" s="7">
         <v>7</v>
       </c>
-      <c r="C75" s="158"/>
-      <c r="D75" s="173"/>
+      <c r="C75" s="162"/>
+      <c r="D75" s="153"/>
       <c r="E75" s="28" t="s">
         <v>109</v>
       </c>
@@ -7429,8 +7464,8 @@
       <c r="B76" s="7">
         <v>8</v>
       </c>
-      <c r="C76" s="158"/>
-      <c r="D76" s="173"/>
+      <c r="C76" s="162"/>
+      <c r="D76" s="153"/>
       <c r="E76" s="8" t="s">
         <v>110</v>
       </c>
@@ -7455,8 +7490,8 @@
       <c r="B77" s="7">
         <v>9</v>
       </c>
-      <c r="C77" s="158"/>
-      <c r="D77" s="173"/>
+      <c r="C77" s="162"/>
+      <c r="D77" s="153"/>
       <c r="E77" s="8" t="s">
         <v>111</v>
       </c>
@@ -7466,7 +7501,7 @@
       <c r="G77" s="10">
         <v>2</v>
       </c>
-      <c r="H77" s="11" t="s">
+      <c r="H77" s="127" t="s">
         <v>17</v>
       </c>
       <c r="I77" s="125" t="s">
@@ -7483,8 +7518,8 @@
       <c r="B78" s="7">
         <v>10</v>
       </c>
-      <c r="C78" s="158"/>
-      <c r="D78" s="174"/>
+      <c r="C78" s="162"/>
+      <c r="D78" s="154"/>
       <c r="E78" s="8" t="s">
         <v>112</v>
       </c>
@@ -7511,8 +7546,8 @@
       <c r="B79" s="7">
         <v>11</v>
       </c>
-      <c r="C79" s="158"/>
-      <c r="D79" s="172" t="s">
+      <c r="C79" s="162"/>
+      <c r="D79" s="152" t="s">
         <v>113</v>
       </c>
       <c r="E79" s="8" t="s">
@@ -7527,7 +7562,7 @@
       <c r="H79" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I79" s="207" t="s">
+      <c r="I79" s="151" t="s">
         <v>733</v>
       </c>
       <c r="J79" s="126" t="s">
@@ -7541,8 +7576,8 @@
       <c r="B80" s="7">
         <v>12</v>
       </c>
-      <c r="C80" s="158"/>
-      <c r="D80" s="173"/>
+      <c r="C80" s="162"/>
+      <c r="D80" s="153"/>
       <c r="E80" s="8" t="s">
         <v>115</v>
       </c>
@@ -7569,8 +7604,8 @@
       <c r="B81" s="7">
         <v>13</v>
       </c>
-      <c r="C81" s="158"/>
-      <c r="D81" s="173"/>
+      <c r="C81" s="162"/>
+      <c r="D81" s="153"/>
       <c r="E81" s="8" t="s">
         <v>116</v>
       </c>
@@ -7580,7 +7615,7 @@
       <c r="G81" s="10">
         <v>3</v>
       </c>
-      <c r="H81" s="11" t="s">
+      <c r="H81" s="127" t="s">
         <v>20</v>
       </c>
       <c r="I81" s="125" t="s">
@@ -7590,15 +7625,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="13.8">
+    <row r="82" spans="1:10" ht="124.2">
       <c r="A82" s="6">
         <v>78</v>
       </c>
       <c r="B82" s="7">
         <v>14</v>
       </c>
-      <c r="C82" s="158"/>
-      <c r="D82" s="173"/>
+      <c r="C82" s="162"/>
+      <c r="D82" s="153"/>
       <c r="E82" s="8" t="s">
         <v>117</v>
       </c>
@@ -7608,19 +7643,25 @@
       <c r="G82" s="10">
         <v>3</v>
       </c>
-      <c r="H82" s="11"/>
-      <c r="I82" s="11"/>
-      <c r="J82" s="11"/>
-    </row>
-    <row r="83" spans="1:10" ht="13.8">
+      <c r="H82" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I82" s="125" t="s">
+        <v>736</v>
+      </c>
+      <c r="J82" s="126" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="151.80000000000001">
       <c r="A83" s="6">
         <v>79</v>
       </c>
       <c r="B83" s="7">
         <v>15</v>
       </c>
-      <c r="C83" s="158"/>
-      <c r="D83" s="173"/>
+      <c r="C83" s="162"/>
+      <c r="D83" s="153"/>
       <c r="E83" s="8" t="s">
         <v>118</v>
       </c>
@@ -7630,19 +7671,25 @@
       <c r="G83" s="10">
         <v>3</v>
       </c>
-      <c r="H83" s="11"/>
-      <c r="I83" s="11"/>
-      <c r="J83" s="11"/>
-    </row>
-    <row r="84" spans="1:10" ht="13.8">
+      <c r="H83" s="127" t="s">
+        <v>17</v>
+      </c>
+      <c r="I83" s="125" t="s">
+        <v>737</v>
+      </c>
+      <c r="J83" s="126" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="110.4">
       <c r="A84" s="6">
         <v>80</v>
       </c>
       <c r="B84" s="7">
         <v>16</v>
       </c>
-      <c r="C84" s="158"/>
-      <c r="D84" s="174"/>
+      <c r="C84" s="162"/>
+      <c r="D84" s="154"/>
       <c r="E84" s="8" t="s">
         <v>119</v>
       </c>
@@ -7652,9 +7699,15 @@
       <c r="G84" s="10">
         <v>3</v>
       </c>
-      <c r="H84" s="11"/>
-      <c r="I84" s="11"/>
-      <c r="J84" s="11"/>
+      <c r="H84" s="127" t="s">
+        <v>17</v>
+      </c>
+      <c r="I84" s="125" t="s">
+        <v>738</v>
+      </c>
+      <c r="J84" s="126" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="85" spans="1:10" ht="13.8">
       <c r="A85" s="6">
@@ -7663,8 +7716,8 @@
       <c r="B85" s="7">
         <v>17</v>
       </c>
-      <c r="C85" s="158"/>
-      <c r="D85" s="172" t="s">
+      <c r="C85" s="162"/>
+      <c r="D85" s="152" t="s">
         <v>120</v>
       </c>
       <c r="E85" s="8" t="s">
@@ -7687,8 +7740,8 @@
       <c r="B86" s="7">
         <v>18</v>
       </c>
-      <c r="C86" s="158"/>
-      <c r="D86" s="173"/>
+      <c r="C86" s="162"/>
+      <c r="D86" s="153"/>
       <c r="E86" s="8" t="s">
         <v>122</v>
       </c>
@@ -7709,8 +7762,8 @@
       <c r="B87" s="7">
         <v>19</v>
       </c>
-      <c r="C87" s="158"/>
-      <c r="D87" s="173"/>
+      <c r="C87" s="162"/>
+      <c r="D87" s="153"/>
       <c r="E87" s="29" t="s">
         <v>123</v>
       </c>
@@ -7731,8 +7784,8 @@
       <c r="B88" s="7">
         <v>20</v>
       </c>
-      <c r="C88" s="158"/>
-      <c r="D88" s="173"/>
+      <c r="C88" s="162"/>
+      <c r="D88" s="153"/>
       <c r="E88" s="8" t="s">
         <v>124</v>
       </c>
@@ -7753,8 +7806,8 @@
       <c r="B89" s="7">
         <v>21</v>
       </c>
-      <c r="C89" s="158"/>
-      <c r="D89" s="173"/>
+      <c r="C89" s="162"/>
+      <c r="D89" s="153"/>
       <c r="E89" s="8" t="s">
         <v>125</v>
       </c>
@@ -7775,8 +7828,8 @@
       <c r="B90" s="7">
         <v>22</v>
       </c>
-      <c r="C90" s="158"/>
-      <c r="D90" s="174"/>
+      <c r="C90" s="162"/>
+      <c r="D90" s="154"/>
       <c r="E90" s="8" t="s">
         <v>126</v>
       </c>
@@ -7797,8 +7850,8 @@
       <c r="B91" s="7">
         <v>23</v>
       </c>
-      <c r="C91" s="158"/>
-      <c r="D91" s="172" t="s">
+      <c r="C91" s="162"/>
+      <c r="D91" s="152" t="s">
         <v>127</v>
       </c>
       <c r="E91" s="8" t="s">
@@ -7821,8 +7874,8 @@
       <c r="B92" s="7">
         <v>24</v>
       </c>
-      <c r="C92" s="158"/>
-      <c r="D92" s="173"/>
+      <c r="C92" s="162"/>
+      <c r="D92" s="153"/>
       <c r="E92" s="8" t="s">
         <v>129</v>
       </c>
@@ -7843,8 +7896,8 @@
       <c r="B93" s="7">
         <v>25</v>
       </c>
-      <c r="C93" s="158"/>
-      <c r="D93" s="173"/>
+      <c r="C93" s="162"/>
+      <c r="D93" s="153"/>
       <c r="E93" s="8" t="s">
         <v>130</v>
       </c>
@@ -7865,8 +7918,8 @@
       <c r="B94" s="7">
         <v>26</v>
       </c>
-      <c r="C94" s="158"/>
-      <c r="D94" s="173"/>
+      <c r="C94" s="162"/>
+      <c r="D94" s="153"/>
       <c r="E94" s="8" t="s">
         <v>131</v>
       </c>
@@ -7887,8 +7940,8 @@
       <c r="B95" s="7">
         <v>27</v>
       </c>
-      <c r="C95" s="158"/>
-      <c r="D95" s="173"/>
+      <c r="C95" s="162"/>
+      <c r="D95" s="153"/>
       <c r="E95" s="8" t="s">
         <v>132</v>
       </c>
@@ -7909,8 +7962,8 @@
       <c r="B96" s="7">
         <v>28</v>
       </c>
-      <c r="C96" s="158"/>
-      <c r="D96" s="173"/>
+      <c r="C96" s="162"/>
+      <c r="D96" s="153"/>
       <c r="E96" s="8" t="s">
         <v>133</v>
       </c>
@@ -7931,8 +7984,8 @@
       <c r="B97" s="7">
         <v>29</v>
       </c>
-      <c r="C97" s="158"/>
-      <c r="D97" s="173"/>
+      <c r="C97" s="162"/>
+      <c r="D97" s="153"/>
       <c r="E97" s="8" t="s">
         <v>134</v>
       </c>
@@ -7953,8 +8006,8 @@
       <c r="B98" s="7">
         <v>30</v>
       </c>
-      <c r="C98" s="158"/>
-      <c r="D98" s="173"/>
+      <c r="C98" s="162"/>
+      <c r="D98" s="153"/>
       <c r="E98" s="8" t="s">
         <v>135</v>
       </c>
@@ -7975,8 +8028,8 @@
       <c r="B99" s="7">
         <v>31</v>
       </c>
-      <c r="C99" s="158"/>
-      <c r="D99" s="173"/>
+      <c r="C99" s="162"/>
+      <c r="D99" s="153"/>
       <c r="E99" s="30" t="s">
         <v>136</v>
       </c>
@@ -7997,8 +8050,8 @@
       <c r="B100" s="7">
         <v>32</v>
       </c>
-      <c r="C100" s="158"/>
-      <c r="D100" s="173"/>
+      <c r="C100" s="162"/>
+      <c r="D100" s="153"/>
       <c r="E100" s="8" t="s">
         <v>137</v>
       </c>
@@ -8019,8 +8072,8 @@
       <c r="B101" s="7">
         <v>33</v>
       </c>
-      <c r="C101" s="158"/>
-      <c r="D101" s="173"/>
+      <c r="C101" s="162"/>
+      <c r="D101" s="153"/>
       <c r="E101" s="8" t="s">
         <v>138</v>
       </c>
@@ -8041,8 +8094,8 @@
       <c r="B102" s="7">
         <v>34</v>
       </c>
-      <c r="C102" s="158"/>
-      <c r="D102" s="173"/>
+      <c r="C102" s="162"/>
+      <c r="D102" s="153"/>
       <c r="E102" s="8" t="s">
         <v>139</v>
       </c>
@@ -8063,8 +8116,8 @@
       <c r="B103" s="7">
         <v>35</v>
       </c>
-      <c r="C103" s="158"/>
-      <c r="D103" s="173"/>
+      <c r="C103" s="162"/>
+      <c r="D103" s="153"/>
       <c r="E103" s="8" t="s">
         <v>140</v>
       </c>
@@ -8085,8 +8138,8 @@
       <c r="B104" s="7">
         <v>36</v>
       </c>
-      <c r="C104" s="158"/>
-      <c r="D104" s="173"/>
+      <c r="C104" s="162"/>
+      <c r="D104" s="153"/>
       <c r="E104" s="8" t="s">
         <v>141</v>
       </c>
@@ -8107,8 +8160,8 @@
       <c r="B105" s="7">
         <v>37</v>
       </c>
-      <c r="C105" s="159"/>
-      <c r="D105" s="174"/>
+      <c r="C105" s="163"/>
+      <c r="D105" s="154"/>
       <c r="E105" s="8" t="s">
         <v>142</v>
       </c>
@@ -8123,18 +8176,18 @@
       <c r="J105" s="11"/>
     </row>
     <row r="106" spans="1:10" ht="13.8">
-      <c r="A106" s="190" t="s">
+      <c r="A106" s="173" t="s">
         <v>143</v>
       </c>
-      <c r="B106" s="191"/>
-      <c r="C106" s="191"/>
-      <c r="D106" s="191"/>
-      <c r="E106" s="191"/>
-      <c r="F106" s="191"/>
-      <c r="G106" s="191"/>
-      <c r="H106" s="191"/>
-      <c r="I106" s="191"/>
-      <c r="J106" s="192"/>
+      <c r="B106" s="174"/>
+      <c r="C106" s="174"/>
+      <c r="D106" s="174"/>
+      <c r="E106" s="174"/>
+      <c r="F106" s="174"/>
+      <c r="G106" s="174"/>
+      <c r="H106" s="174"/>
+      <c r="I106" s="174"/>
+      <c r="J106" s="175"/>
     </row>
     <row r="107" spans="1:10" ht="13.8">
       <c r="A107" s="6">
@@ -8143,10 +8196,10 @@
       <c r="B107" s="7">
         <v>1</v>
       </c>
-      <c r="C107" s="160" t="s">
+      <c r="C107" s="164" t="s">
         <v>144</v>
       </c>
-      <c r="D107" s="172" t="s">
+      <c r="D107" s="152" t="s">
         <v>145</v>
       </c>
       <c r="E107" s="8" t="s">
@@ -8169,8 +8222,8 @@
       <c r="B108" s="7">
         <v>2</v>
       </c>
-      <c r="C108" s="161"/>
-      <c r="D108" s="173"/>
+      <c r="C108" s="165"/>
+      <c r="D108" s="153"/>
       <c r="E108" s="8" t="s">
         <v>147</v>
       </c>
@@ -8191,8 +8244,8 @@
       <c r="B109" s="7">
         <v>3</v>
       </c>
-      <c r="C109" s="161"/>
-      <c r="D109" s="173"/>
+      <c r="C109" s="165"/>
+      <c r="D109" s="153"/>
       <c r="E109" s="8" t="s">
         <v>148</v>
       </c>
@@ -8213,8 +8266,8 @@
       <c r="B110" s="7">
         <v>4</v>
       </c>
-      <c r="C110" s="161"/>
-      <c r="D110" s="173"/>
+      <c r="C110" s="165"/>
+      <c r="D110" s="153"/>
       <c r="E110" s="8" t="s">
         <v>149</v>
       </c>
@@ -8235,8 +8288,8 @@
       <c r="B111" s="7">
         <v>5</v>
       </c>
-      <c r="C111" s="161"/>
-      <c r="D111" s="174"/>
+      <c r="C111" s="165"/>
+      <c r="D111" s="154"/>
       <c r="E111" s="8" t="s">
         <v>150</v>
       </c>
@@ -8257,8 +8310,8 @@
       <c r="B112" s="7">
         <v>6</v>
       </c>
-      <c r="C112" s="161"/>
-      <c r="D112" s="172" t="s">
+      <c r="C112" s="165"/>
+      <c r="D112" s="152" t="s">
         <v>151</v>
       </c>
       <c r="E112" s="8" t="s">
@@ -8281,8 +8334,8 @@
       <c r="B113" s="7">
         <v>7</v>
       </c>
-      <c r="C113" s="161"/>
-      <c r="D113" s="173"/>
+      <c r="C113" s="165"/>
+      <c r="D113" s="153"/>
       <c r="E113" s="8" t="s">
         <v>153</v>
       </c>
@@ -8303,8 +8356,8 @@
       <c r="B114" s="7">
         <v>8</v>
       </c>
-      <c r="C114" s="161"/>
-      <c r="D114" s="173"/>
+      <c r="C114" s="165"/>
+      <c r="D114" s="153"/>
       <c r="E114" s="8" t="s">
         <v>154</v>
       </c>
@@ -8325,8 +8378,8 @@
       <c r="B115" s="7">
         <v>9</v>
       </c>
-      <c r="C115" s="161"/>
-      <c r="D115" s="174"/>
+      <c r="C115" s="165"/>
+      <c r="D115" s="154"/>
       <c r="E115" s="8" t="s">
         <v>155</v>
       </c>
@@ -8347,7 +8400,7 @@
       <c r="B116" s="24">
         <v>10</v>
       </c>
-      <c r="C116" s="162"/>
+      <c r="C116" s="166"/>
       <c r="D116" s="31" t="s">
         <v>156</v>
       </c>
@@ -8371,10 +8424,10 @@
       <c r="B117" s="7">
         <v>1</v>
       </c>
-      <c r="C117" s="151" t="s">
+      <c r="C117" s="167" t="s">
         <v>158</v>
       </c>
-      <c r="D117" s="172" t="s">
+      <c r="D117" s="152" t="s">
         <v>159</v>
       </c>
       <c r="E117" s="8" t="s">
@@ -8397,8 +8450,8 @@
       <c r="B118" s="7">
         <v>2</v>
       </c>
-      <c r="C118" s="152"/>
-      <c r="D118" s="173"/>
+      <c r="C118" s="168"/>
+      <c r="D118" s="153"/>
       <c r="E118" s="8" t="s">
         <v>161</v>
       </c>
@@ -8419,8 +8472,8 @@
       <c r="B119" s="7">
         <v>3</v>
       </c>
-      <c r="C119" s="152"/>
-      <c r="D119" s="173"/>
+      <c r="C119" s="168"/>
+      <c r="D119" s="153"/>
       <c r="E119" s="8" t="s">
         <v>162</v>
       </c>
@@ -8441,8 +8494,8 @@
       <c r="B120" s="7">
         <v>4</v>
       </c>
-      <c r="C120" s="152"/>
-      <c r="D120" s="174"/>
+      <c r="C120" s="168"/>
+      <c r="D120" s="154"/>
       <c r="E120" s="8" t="s">
         <v>163</v>
       </c>
@@ -8463,8 +8516,8 @@
       <c r="B121" s="7">
         <v>5</v>
       </c>
-      <c r="C121" s="152"/>
-      <c r="D121" s="172" t="s">
+      <c r="C121" s="168"/>
+      <c r="D121" s="152" t="s">
         <v>164</v>
       </c>
       <c r="E121" s="8" t="s">
@@ -8487,8 +8540,8 @@
       <c r="B122" s="7">
         <v>6</v>
       </c>
-      <c r="C122" s="152"/>
-      <c r="D122" s="174"/>
+      <c r="C122" s="168"/>
+      <c r="D122" s="154"/>
       <c r="E122" s="8" t="s">
         <v>166</v>
       </c>
@@ -8509,8 +8562,8 @@
       <c r="B123" s="7">
         <v>7</v>
       </c>
-      <c r="C123" s="152"/>
-      <c r="D123" s="172" t="s">
+      <c r="C123" s="168"/>
+      <c r="D123" s="152" t="s">
         <v>167</v>
       </c>
       <c r="E123" s="8" t="s">
@@ -8533,8 +8586,8 @@
       <c r="B124" s="7">
         <v>8</v>
       </c>
-      <c r="C124" s="152"/>
-      <c r="D124" s="173"/>
+      <c r="C124" s="168"/>
+      <c r="D124" s="153"/>
       <c r="E124" s="28" t="s">
         <v>169</v>
       </c>
@@ -8555,8 +8608,8 @@
       <c r="B125" s="7">
         <v>9</v>
       </c>
-      <c r="C125" s="153"/>
-      <c r="D125" s="174"/>
+      <c r="C125" s="169"/>
+      <c r="D125" s="154"/>
       <c r="E125" s="8" t="s">
         <v>170</v>
       </c>
@@ -8571,18 +8624,18 @@
       <c r="J125" s="11"/>
     </row>
     <row r="126" spans="1:10" ht="13.8">
-      <c r="A126" s="193" t="s">
+      <c r="A126" s="176" t="s">
         <v>171</v>
       </c>
-      <c r="B126" s="194"/>
-      <c r="C126" s="194"/>
-      <c r="D126" s="194"/>
-      <c r="E126" s="194"/>
-      <c r="F126" s="194"/>
-      <c r="G126" s="194"/>
-      <c r="H126" s="194"/>
-      <c r="I126" s="194"/>
-      <c r="J126" s="195"/>
+      <c r="B126" s="177"/>
+      <c r="C126" s="177"/>
+      <c r="D126" s="177"/>
+      <c r="E126" s="177"/>
+      <c r="F126" s="177"/>
+      <c r="G126" s="177"/>
+      <c r="H126" s="177"/>
+      <c r="I126" s="177"/>
+      <c r="J126" s="178"/>
     </row>
     <row r="127" spans="1:10" ht="13.8">
       <c r="A127" s="6">
@@ -8591,10 +8644,10 @@
       <c r="B127" s="7">
         <v>1</v>
       </c>
-      <c r="C127" s="154" t="s">
+      <c r="C127" s="170" t="s">
         <v>172</v>
       </c>
-      <c r="D127" s="172" t="s">
+      <c r="D127" s="152" t="s">
         <v>173</v>
       </c>
       <c r="E127" s="32" t="s">
@@ -8615,8 +8668,8 @@
       <c r="B128" s="7">
         <v>2</v>
       </c>
-      <c r="C128" s="155"/>
-      <c r="D128" s="173"/>
+      <c r="C128" s="171"/>
+      <c r="D128" s="153"/>
       <c r="E128" s="32" t="s">
         <v>175</v>
       </c>
@@ -8635,8 +8688,8 @@
       <c r="B129" s="7">
         <v>3</v>
       </c>
-      <c r="C129" s="155"/>
-      <c r="D129" s="173"/>
+      <c r="C129" s="171"/>
+      <c r="D129" s="153"/>
       <c r="E129" s="32" t="s">
         <v>176</v>
       </c>
@@ -8655,8 +8708,8 @@
       <c r="B130" s="7">
         <v>4</v>
       </c>
-      <c r="C130" s="155"/>
-      <c r="D130" s="174"/>
+      <c r="C130" s="171"/>
+      <c r="D130" s="154"/>
       <c r="E130" s="32" t="s">
         <v>177</v>
       </c>
@@ -8675,8 +8728,8 @@
       <c r="B131" s="7">
         <v>5</v>
       </c>
-      <c r="C131" s="155"/>
-      <c r="D131" s="172" t="s">
+      <c r="C131" s="171"/>
+      <c r="D131" s="152" t="s">
         <v>178</v>
       </c>
       <c r="E131" s="32" t="s">
@@ -8697,8 +8750,8 @@
       <c r="B132" s="7">
         <v>6</v>
       </c>
-      <c r="C132" s="156"/>
-      <c r="D132" s="174"/>
+      <c r="C132" s="172"/>
+      <c r="D132" s="154"/>
       <c r="E132" s="32" t="s">
         <v>180</v>
       </c>
@@ -8711,18 +8764,18 @@
       <c r="J132" s="11"/>
     </row>
     <row r="133" spans="1:10" ht="13.8">
-      <c r="A133" s="196" t="s">
+      <c r="A133" s="158" t="s">
         <v>181</v>
       </c>
-      <c r="B133" s="197"/>
-      <c r="C133" s="197"/>
-      <c r="D133" s="197"/>
-      <c r="E133" s="197"/>
-      <c r="F133" s="197"/>
-      <c r="G133" s="197"/>
-      <c r="H133" s="197"/>
-      <c r="I133" s="197"/>
-      <c r="J133" s="198"/>
+      <c r="B133" s="159"/>
+      <c r="C133" s="159"/>
+      <c r="D133" s="159"/>
+      <c r="E133" s="159"/>
+      <c r="F133" s="159"/>
+      <c r="G133" s="159"/>
+      <c r="H133" s="159"/>
+      <c r="I133" s="159"/>
+      <c r="J133" s="160"/>
     </row>
     <row r="134" spans="1:10" ht="13.8">
       <c r="A134" s="6">
@@ -8731,10 +8784,10 @@
       <c r="B134" s="7">
         <v>1</v>
       </c>
-      <c r="C134" s="157" t="s">
+      <c r="C134" s="161" t="s">
         <v>182</v>
       </c>
-      <c r="D134" s="172" t="s">
+      <c r="D134" s="152" t="s">
         <v>183</v>
       </c>
       <c r="E134" s="8" t="s">
@@ -8757,8 +8810,8 @@
       <c r="B135" s="7">
         <v>2</v>
       </c>
-      <c r="C135" s="158"/>
-      <c r="D135" s="173"/>
+      <c r="C135" s="162"/>
+      <c r="D135" s="153"/>
       <c r="E135" s="8" t="s">
         <v>185</v>
       </c>
@@ -8779,8 +8832,8 @@
       <c r="B136" s="7">
         <v>3</v>
       </c>
-      <c r="C136" s="158"/>
-      <c r="D136" s="174"/>
+      <c r="C136" s="162"/>
+      <c r="D136" s="154"/>
       <c r="E136" s="8" t="s">
         <v>186</v>
       </c>
@@ -8801,8 +8854,8 @@
       <c r="B137" s="7">
         <v>4</v>
       </c>
-      <c r="C137" s="158"/>
-      <c r="D137" s="172" t="s">
+      <c r="C137" s="162"/>
+      <c r="D137" s="152" t="s">
         <v>187</v>
       </c>
       <c r="E137" s="8" t="s">
@@ -8825,8 +8878,8 @@
       <c r="B138" s="7">
         <v>5</v>
       </c>
-      <c r="C138" s="158"/>
-      <c r="D138" s="173"/>
+      <c r="C138" s="162"/>
+      <c r="D138" s="153"/>
       <c r="E138" s="8" t="s">
         <v>189</v>
       </c>
@@ -8847,8 +8900,8 @@
       <c r="B139" s="7">
         <v>6</v>
       </c>
-      <c r="C139" s="158"/>
-      <c r="D139" s="173"/>
+      <c r="C139" s="162"/>
+      <c r="D139" s="153"/>
       <c r="E139" s="8" t="s">
         <v>190</v>
       </c>
@@ -8869,8 +8922,8 @@
       <c r="B140" s="7">
         <v>7</v>
       </c>
-      <c r="C140" s="158"/>
-      <c r="D140" s="173"/>
+      <c r="C140" s="162"/>
+      <c r="D140" s="153"/>
       <c r="E140" s="8" t="s">
         <v>191</v>
       </c>
@@ -8891,8 +8944,8 @@
       <c r="B141" s="7">
         <v>8</v>
       </c>
-      <c r="C141" s="158"/>
-      <c r="D141" s="173"/>
+      <c r="C141" s="162"/>
+      <c r="D141" s="153"/>
       <c r="E141" s="8" t="s">
         <v>192</v>
       </c>
@@ -8913,8 +8966,8 @@
       <c r="B142" s="7">
         <v>9</v>
       </c>
-      <c r="C142" s="158"/>
-      <c r="D142" s="173"/>
+      <c r="C142" s="162"/>
+      <c r="D142" s="153"/>
       <c r="E142" s="8" t="s">
         <v>193</v>
       </c>
@@ -8935,8 +8988,8 @@
       <c r="B143" s="7">
         <v>10</v>
       </c>
-      <c r="C143" s="158"/>
-      <c r="D143" s="174"/>
+      <c r="C143" s="162"/>
+      <c r="D143" s="154"/>
       <c r="E143" s="8" t="s">
         <v>194</v>
       </c>
@@ -8957,8 +9010,8 @@
       <c r="B144" s="7">
         <v>11</v>
       </c>
-      <c r="C144" s="158"/>
-      <c r="D144" s="172" t="s">
+      <c r="C144" s="162"/>
+      <c r="D144" s="152" t="s">
         <v>195</v>
       </c>
       <c r="E144" s="8" t="s">
@@ -8981,8 +9034,8 @@
       <c r="B145" s="7">
         <v>12</v>
       </c>
-      <c r="C145" s="158"/>
-      <c r="D145" s="173"/>
+      <c r="C145" s="162"/>
+      <c r="D145" s="153"/>
       <c r="E145" s="8" t="s">
         <v>197</v>
       </c>
@@ -9003,8 +9056,8 @@
       <c r="B146" s="7">
         <v>13</v>
       </c>
-      <c r="C146" s="158"/>
-      <c r="D146" s="173"/>
+      <c r="C146" s="162"/>
+      <c r="D146" s="153"/>
       <c r="E146" s="8" t="s">
         <v>198</v>
       </c>
@@ -9025,8 +9078,8 @@
       <c r="B147" s="7">
         <v>14</v>
       </c>
-      <c r="C147" s="158"/>
-      <c r="D147" s="173"/>
+      <c r="C147" s="162"/>
+      <c r="D147" s="153"/>
       <c r="E147" s="8" t="s">
         <v>199</v>
       </c>
@@ -9047,8 +9100,8 @@
       <c r="B148" s="7">
         <v>15</v>
       </c>
-      <c r="C148" s="158"/>
-      <c r="D148" s="173"/>
+      <c r="C148" s="162"/>
+      <c r="D148" s="153"/>
       <c r="E148" s="8" t="s">
         <v>200</v>
       </c>
@@ -9069,8 +9122,8 @@
       <c r="B149" s="7">
         <v>16</v>
       </c>
-      <c r="C149" s="158"/>
-      <c r="D149" s="173"/>
+      <c r="C149" s="162"/>
+      <c r="D149" s="153"/>
       <c r="E149" s="8" t="s">
         <v>201</v>
       </c>
@@ -9091,8 +9144,8 @@
       <c r="B150" s="7">
         <v>17</v>
       </c>
-      <c r="C150" s="158"/>
-      <c r="D150" s="174"/>
+      <c r="C150" s="162"/>
+      <c r="D150" s="154"/>
       <c r="E150" s="8" t="s">
         <v>202</v>
       </c>
@@ -9113,8 +9166,8 @@
       <c r="B151" s="7">
         <v>18</v>
       </c>
-      <c r="C151" s="158"/>
-      <c r="D151" s="172" t="s">
+      <c r="C151" s="162"/>
+      <c r="D151" s="152" t="s">
         <v>203</v>
       </c>
       <c r="E151" s="8" t="s">
@@ -9137,8 +9190,8 @@
       <c r="B152" s="7">
         <v>19</v>
       </c>
-      <c r="C152" s="158"/>
-      <c r="D152" s="173"/>
+      <c r="C152" s="162"/>
+      <c r="D152" s="153"/>
       <c r="E152" s="8" t="s">
         <v>205</v>
       </c>
@@ -9159,8 +9212,8 @@
       <c r="B153" s="7">
         <v>20</v>
       </c>
-      <c r="C153" s="158"/>
-      <c r="D153" s="173"/>
+      <c r="C153" s="162"/>
+      <c r="D153" s="153"/>
       <c r="E153" s="8" t="s">
         <v>206</v>
       </c>
@@ -9181,8 +9234,8 @@
       <c r="B154" s="7">
         <v>21</v>
       </c>
-      <c r="C154" s="158"/>
-      <c r="D154" s="173"/>
+      <c r="C154" s="162"/>
+      <c r="D154" s="153"/>
       <c r="E154" s="8" t="s">
         <v>207</v>
       </c>
@@ -9203,8 +9256,8 @@
       <c r="B155" s="7">
         <v>22</v>
       </c>
-      <c r="C155" s="158"/>
-      <c r="D155" s="173"/>
+      <c r="C155" s="162"/>
+      <c r="D155" s="153"/>
       <c r="E155" s="8" t="s">
         <v>208</v>
       </c>
@@ -9225,8 +9278,8 @@
       <c r="B156" s="7">
         <v>23</v>
       </c>
-      <c r="C156" s="158"/>
-      <c r="D156" s="174"/>
+      <c r="C156" s="162"/>
+      <c r="D156" s="154"/>
       <c r="E156" s="8" t="s">
         <v>209</v>
       </c>
@@ -9247,8 +9300,8 @@
       <c r="B157" s="7">
         <v>24</v>
       </c>
-      <c r="C157" s="158"/>
-      <c r="D157" s="172" t="s">
+      <c r="C157" s="162"/>
+      <c r="D157" s="152" t="s">
         <v>210</v>
       </c>
       <c r="E157" s="8" t="s">
@@ -9271,8 +9324,8 @@
       <c r="B158" s="7">
         <v>25</v>
       </c>
-      <c r="C158" s="158"/>
-      <c r="D158" s="173"/>
+      <c r="C158" s="162"/>
+      <c r="D158" s="153"/>
       <c r="E158" s="8" t="s">
         <v>212</v>
       </c>
@@ -9293,8 +9346,8 @@
       <c r="B159" s="7">
         <v>26</v>
       </c>
-      <c r="C159" s="158"/>
-      <c r="D159" s="174"/>
+      <c r="C159" s="162"/>
+      <c r="D159" s="154"/>
       <c r="E159" s="8" t="s">
         <v>213</v>
       </c>
@@ -9315,8 +9368,8 @@
       <c r="B160" s="7">
         <v>27</v>
       </c>
-      <c r="C160" s="158"/>
-      <c r="D160" s="172" t="s">
+      <c r="C160" s="162"/>
+      <c r="D160" s="152" t="s">
         <v>214</v>
       </c>
       <c r="E160" s="8" t="s">
@@ -9339,8 +9392,8 @@
       <c r="B161" s="7">
         <v>28</v>
       </c>
-      <c r="C161" s="158"/>
-      <c r="D161" s="173"/>
+      <c r="C161" s="162"/>
+      <c r="D161" s="153"/>
       <c r="E161" s="8" t="s">
         <v>216</v>
       </c>
@@ -9361,8 +9414,8 @@
       <c r="B162" s="7">
         <v>29</v>
       </c>
-      <c r="C162" s="158"/>
-      <c r="D162" s="173"/>
+      <c r="C162" s="162"/>
+      <c r="D162" s="153"/>
       <c r="E162" s="8" t="s">
         <v>217</v>
       </c>
@@ -9383,8 +9436,8 @@
       <c r="B163" s="7">
         <v>30</v>
       </c>
-      <c r="C163" s="158"/>
-      <c r="D163" s="173"/>
+      <c r="C163" s="162"/>
+      <c r="D163" s="153"/>
       <c r="E163" s="8" t="s">
         <v>218</v>
       </c>
@@ -9405,8 +9458,8 @@
       <c r="B164" s="7">
         <v>31</v>
       </c>
-      <c r="C164" s="158"/>
-      <c r="D164" s="173"/>
+      <c r="C164" s="162"/>
+      <c r="D164" s="153"/>
       <c r="E164" s="8" t="s">
         <v>219</v>
       </c>
@@ -9427,8 +9480,8 @@
       <c r="B165" s="7">
         <v>32</v>
       </c>
-      <c r="C165" s="158"/>
-      <c r="D165" s="174"/>
+      <c r="C165" s="162"/>
+      <c r="D165" s="154"/>
       <c r="E165" s="8" t="s">
         <v>220</v>
       </c>
@@ -9449,8 +9502,8 @@
       <c r="B166" s="7">
         <v>33</v>
       </c>
-      <c r="C166" s="158"/>
-      <c r="D166" s="172" t="s">
+      <c r="C166" s="162"/>
+      <c r="D166" s="152" t="s">
         <v>221</v>
       </c>
       <c r="E166" s="8" t="s">
@@ -9473,8 +9526,8 @@
       <c r="B167" s="7">
         <v>34</v>
       </c>
-      <c r="C167" s="158"/>
-      <c r="D167" s="173"/>
+      <c r="C167" s="162"/>
+      <c r="D167" s="153"/>
       <c r="E167" s="8" t="s">
         <v>223</v>
       </c>
@@ -9493,8 +9546,8 @@
       <c r="B168" s="7">
         <v>35</v>
       </c>
-      <c r="C168" s="158"/>
-      <c r="D168" s="173"/>
+      <c r="C168" s="162"/>
+      <c r="D168" s="153"/>
       <c r="E168" s="8" t="s">
         <v>224</v>
       </c>
@@ -9515,8 +9568,8 @@
       <c r="B169" s="7">
         <v>36</v>
       </c>
-      <c r="C169" s="158"/>
-      <c r="D169" s="173"/>
+      <c r="C169" s="162"/>
+      <c r="D169" s="153"/>
       <c r="E169" s="8" t="s">
         <v>225</v>
       </c>
@@ -9537,8 +9590,8 @@
       <c r="B170" s="7">
         <v>37</v>
       </c>
-      <c r="C170" s="158"/>
-      <c r="D170" s="173"/>
+      <c r="C170" s="162"/>
+      <c r="D170" s="153"/>
       <c r="E170" s="8" t="s">
         <v>226</v>
       </c>
@@ -9559,8 +9612,8 @@
       <c r="B171" s="7">
         <v>38</v>
       </c>
-      <c r="C171" s="158"/>
-      <c r="D171" s="173"/>
+      <c r="C171" s="162"/>
+      <c r="D171" s="153"/>
       <c r="E171" s="8" t="s">
         <v>227</v>
       </c>
@@ -9581,8 +9634,8 @@
       <c r="B172" s="7">
         <v>39</v>
       </c>
-      <c r="C172" s="158"/>
-      <c r="D172" s="174"/>
+      <c r="C172" s="162"/>
+      <c r="D172" s="154"/>
       <c r="E172" s="8" t="s">
         <v>228</v>
       </c>
@@ -9603,8 +9656,8 @@
       <c r="B173" s="7">
         <v>40</v>
       </c>
-      <c r="C173" s="158"/>
-      <c r="D173" s="172" t="s">
+      <c r="C173" s="162"/>
+      <c r="D173" s="152" t="s">
         <v>48</v>
       </c>
       <c r="E173" s="11" t="s">
@@ -9627,8 +9680,8 @@
       <c r="B174" s="7">
         <v>41</v>
       </c>
-      <c r="C174" s="158"/>
-      <c r="D174" s="173"/>
+      <c r="C174" s="162"/>
+      <c r="D174" s="153"/>
       <c r="E174" s="8" t="s">
         <v>230</v>
       </c>
@@ -9649,8 +9702,8 @@
       <c r="B175" s="7">
         <v>42</v>
       </c>
-      <c r="C175" s="158"/>
-      <c r="D175" s="173"/>
+      <c r="C175" s="162"/>
+      <c r="D175" s="153"/>
       <c r="E175" s="8" t="s">
         <v>231</v>
       </c>
@@ -9671,8 +9724,8 @@
       <c r="B176" s="24">
         <v>43</v>
       </c>
-      <c r="C176" s="159"/>
-      <c r="D176" s="174"/>
+      <c r="C176" s="163"/>
+      <c r="D176" s="154"/>
       <c r="E176" s="17" t="s">
         <v>232</v>
       </c>
@@ -9693,10 +9746,10 @@
       <c r="B177" s="7">
         <v>1</v>
       </c>
-      <c r="C177" s="160" t="s">
+      <c r="C177" s="164" t="s">
         <v>233</v>
       </c>
-      <c r="D177" s="172" t="s">
+      <c r="D177" s="152" t="s">
         <v>234</v>
       </c>
       <c r="E177" s="8" t="s">
@@ -9719,8 +9772,8 @@
       <c r="B178" s="7">
         <v>2</v>
       </c>
-      <c r="C178" s="161"/>
-      <c r="D178" s="174"/>
+      <c r="C178" s="165"/>
+      <c r="D178" s="154"/>
       <c r="E178" s="8" t="s">
         <v>236</v>
       </c>
@@ -9741,8 +9794,8 @@
       <c r="B179" s="7">
         <v>3</v>
       </c>
-      <c r="C179" s="161"/>
-      <c r="D179" s="172" t="s">
+      <c r="C179" s="165"/>
+      <c r="D179" s="152" t="s">
         <v>237</v>
       </c>
       <c r="E179" s="8" t="s">
@@ -9765,8 +9818,8 @@
       <c r="B180" s="7">
         <v>4</v>
       </c>
-      <c r="C180" s="161"/>
-      <c r="D180" s="173"/>
+      <c r="C180" s="165"/>
+      <c r="D180" s="153"/>
       <c r="E180" s="8" t="s">
         <v>239</v>
       </c>
@@ -9787,8 +9840,8 @@
       <c r="B181" s="7">
         <v>5</v>
       </c>
-      <c r="C181" s="161"/>
-      <c r="D181" s="173"/>
+      <c r="C181" s="165"/>
+      <c r="D181" s="153"/>
       <c r="E181" s="8" t="s">
         <v>240</v>
       </c>
@@ -9809,8 +9862,8 @@
       <c r="B182" s="7">
         <v>6</v>
       </c>
-      <c r="C182" s="161"/>
-      <c r="D182" s="173"/>
+      <c r="C182" s="165"/>
+      <c r="D182" s="153"/>
       <c r="E182" s="8" t="s">
         <v>241</v>
       </c>
@@ -9831,8 +9884,8 @@
       <c r="B183" s="7">
         <v>7</v>
       </c>
-      <c r="C183" s="161"/>
-      <c r="D183" s="173"/>
+      <c r="C183" s="165"/>
+      <c r="D183" s="153"/>
       <c r="E183" s="8" t="s">
         <v>242</v>
       </c>
@@ -9853,8 +9906,8 @@
       <c r="B184" s="7">
         <v>8</v>
       </c>
-      <c r="C184" s="161"/>
-      <c r="D184" s="174"/>
+      <c r="C184" s="165"/>
+      <c r="D184" s="154"/>
       <c r="E184" s="8" t="s">
         <v>243</v>
       </c>
@@ -9875,8 +9928,8 @@
       <c r="B185" s="7">
         <v>9</v>
       </c>
-      <c r="C185" s="161"/>
-      <c r="D185" s="172" t="s">
+      <c r="C185" s="165"/>
+      <c r="D185" s="152" t="s">
         <v>244</v>
       </c>
       <c r="E185" s="8" t="s">
@@ -9899,8 +9952,8 @@
       <c r="B186" s="7">
         <v>10</v>
       </c>
-      <c r="C186" s="161"/>
-      <c r="D186" s="174"/>
+      <c r="C186" s="165"/>
+      <c r="D186" s="154"/>
       <c r="E186" s="8" t="s">
         <v>246</v>
       </c>
@@ -9921,8 +9974,8 @@
       <c r="B187" s="7">
         <v>11</v>
       </c>
-      <c r="C187" s="161"/>
-      <c r="D187" s="172" t="s">
+      <c r="C187" s="165"/>
+      <c r="D187" s="152" t="s">
         <v>247</v>
       </c>
       <c r="E187" s="8" t="s">
@@ -9945,8 +9998,8 @@
       <c r="B188" s="7">
         <v>12</v>
       </c>
-      <c r="C188" s="161"/>
-      <c r="D188" s="173"/>
+      <c r="C188" s="165"/>
+      <c r="D188" s="153"/>
       <c r="E188" s="8" t="s">
         <v>249</v>
       </c>
@@ -9967,8 +10020,8 @@
       <c r="B189" s="7">
         <v>13</v>
       </c>
-      <c r="C189" s="161"/>
-      <c r="D189" s="173"/>
+      <c r="C189" s="165"/>
+      <c r="D189" s="153"/>
       <c r="E189" s="11" t="s">
         <v>250</v>
       </c>
@@ -9989,8 +10042,8 @@
       <c r="B190" s="7">
         <v>14</v>
       </c>
-      <c r="C190" s="161"/>
-      <c r="D190" s="174"/>
+      <c r="C190" s="165"/>
+      <c r="D190" s="154"/>
       <c r="E190" s="8" t="s">
         <v>251</v>
       </c>
@@ -10011,8 +10064,8 @@
       <c r="B191" s="7">
         <v>15</v>
       </c>
-      <c r="C191" s="161"/>
-      <c r="D191" s="172" t="s">
+      <c r="C191" s="165"/>
+      <c r="D191" s="152" t="s">
         <v>252</v>
       </c>
       <c r="E191" s="8" t="s">
@@ -10035,8 +10088,8 @@
       <c r="B192" s="7">
         <v>16</v>
       </c>
-      <c r="C192" s="161"/>
-      <c r="D192" s="173"/>
+      <c r="C192" s="165"/>
+      <c r="D192" s="153"/>
       <c r="E192" s="8" t="s">
         <v>254</v>
       </c>
@@ -10057,8 +10110,8 @@
       <c r="B193" s="7">
         <v>17</v>
       </c>
-      <c r="C193" s="161"/>
-      <c r="D193" s="173"/>
+      <c r="C193" s="165"/>
+      <c r="D193" s="153"/>
       <c r="E193" s="8" t="s">
         <v>255</v>
       </c>
@@ -10079,8 +10132,8 @@
       <c r="B194" s="7">
         <v>18</v>
       </c>
-      <c r="C194" s="161"/>
-      <c r="D194" s="173"/>
+      <c r="C194" s="165"/>
+      <c r="D194" s="153"/>
       <c r="E194" s="8" t="s">
         <v>256</v>
       </c>
@@ -10101,8 +10154,8 @@
       <c r="B195" s="7">
         <v>19</v>
       </c>
-      <c r="C195" s="161"/>
-      <c r="D195" s="173"/>
+      <c r="C195" s="165"/>
+      <c r="D195" s="153"/>
       <c r="E195" s="8" t="s">
         <v>257</v>
       </c>
@@ -10123,8 +10176,8 @@
       <c r="B196" s="7">
         <v>20</v>
       </c>
-      <c r="C196" s="161"/>
-      <c r="D196" s="173"/>
+      <c r="C196" s="165"/>
+      <c r="D196" s="153"/>
       <c r="E196" s="8" t="s">
         <v>258</v>
       </c>
@@ -10145,8 +10198,8 @@
       <c r="B197" s="7">
         <v>21</v>
       </c>
-      <c r="C197" s="161"/>
-      <c r="D197" s="173"/>
+      <c r="C197" s="165"/>
+      <c r="D197" s="153"/>
       <c r="E197" s="8" t="s">
         <v>259</v>
       </c>
@@ -10167,8 +10220,8 @@
       <c r="B198" s="7">
         <v>22</v>
       </c>
-      <c r="C198" s="161"/>
-      <c r="D198" s="174"/>
+      <c r="C198" s="165"/>
+      <c r="D198" s="154"/>
       <c r="E198" s="8" t="s">
         <v>260</v>
       </c>
@@ -10189,8 +10242,8 @@
       <c r="B199" s="7">
         <v>23</v>
       </c>
-      <c r="C199" s="161"/>
-      <c r="D199" s="172" t="s">
+      <c r="C199" s="165"/>
+      <c r="D199" s="152" t="s">
         <v>261</v>
       </c>
       <c r="E199" s="8" t="s">
@@ -10213,8 +10266,8 @@
       <c r="B200" s="7">
         <v>24</v>
       </c>
-      <c r="C200" s="161"/>
-      <c r="D200" s="173"/>
+      <c r="C200" s="165"/>
+      <c r="D200" s="153"/>
       <c r="E200" s="8" t="s">
         <v>263</v>
       </c>
@@ -10235,8 +10288,8 @@
       <c r="B201" s="7">
         <v>25</v>
       </c>
-      <c r="C201" s="161"/>
-      <c r="D201" s="173"/>
+      <c r="C201" s="165"/>
+      <c r="D201" s="153"/>
       <c r="E201" s="8" t="s">
         <v>264</v>
       </c>
@@ -10257,8 +10310,8 @@
       <c r="B202" s="7">
         <v>26</v>
       </c>
-      <c r="C202" s="161"/>
-      <c r="D202" s="174"/>
+      <c r="C202" s="165"/>
+      <c r="D202" s="154"/>
       <c r="E202" s="8" t="s">
         <v>265</v>
       </c>
@@ -10279,8 +10332,8 @@
       <c r="B203" s="7">
         <v>27</v>
       </c>
-      <c r="C203" s="161"/>
-      <c r="D203" s="172" t="s">
+      <c r="C203" s="165"/>
+      <c r="D203" s="152" t="s">
         <v>266</v>
       </c>
       <c r="E203" s="8" t="s">
@@ -10303,8 +10356,8 @@
       <c r="B204" s="24">
         <v>28</v>
       </c>
-      <c r="C204" s="162"/>
-      <c r="D204" s="174"/>
+      <c r="C204" s="166"/>
+      <c r="D204" s="154"/>
       <c r="E204" s="17" t="s">
         <v>268</v>
       </c>
@@ -10325,10 +10378,10 @@
       <c r="B205" s="7">
         <v>1</v>
       </c>
-      <c r="C205" s="151" t="s">
+      <c r="C205" s="167" t="s">
         <v>269</v>
       </c>
-      <c r="D205" s="172" t="s">
+      <c r="D205" s="152" t="s">
         <v>270</v>
       </c>
       <c r="E205" s="8" t="s">
@@ -10351,8 +10404,8 @@
       <c r="B206" s="7">
         <v>2</v>
       </c>
-      <c r="C206" s="152"/>
-      <c r="D206" s="173"/>
+      <c r="C206" s="168"/>
+      <c r="D206" s="153"/>
       <c r="E206" s="8" t="s">
         <v>272</v>
       </c>
@@ -10373,8 +10426,8 @@
       <c r="B207" s="7">
         <v>3</v>
       </c>
-      <c r="C207" s="152"/>
-      <c r="D207" s="173"/>
+      <c r="C207" s="168"/>
+      <c r="D207" s="153"/>
       <c r="E207" s="8" t="s">
         <v>273</v>
       </c>
@@ -10395,8 +10448,8 @@
       <c r="B208" s="7">
         <v>4</v>
       </c>
-      <c r="C208" s="152"/>
-      <c r="D208" s="173"/>
+      <c r="C208" s="168"/>
+      <c r="D208" s="153"/>
       <c r="E208" s="8" t="s">
         <v>274</v>
       </c>
@@ -10417,8 +10470,8 @@
       <c r="B209" s="7">
         <v>5</v>
       </c>
-      <c r="C209" s="152"/>
-      <c r="D209" s="174"/>
+      <c r="C209" s="168"/>
+      <c r="D209" s="154"/>
       <c r="E209" s="8" t="s">
         <v>275</v>
       </c>
@@ -10439,8 +10492,8 @@
       <c r="B210" s="7">
         <v>6</v>
       </c>
-      <c r="C210" s="152"/>
-      <c r="D210" s="172" t="s">
+      <c r="C210" s="168"/>
+      <c r="D210" s="152" t="s">
         <v>276</v>
       </c>
       <c r="E210" s="8" t="s">
@@ -10463,8 +10516,8 @@
       <c r="B211" s="7">
         <v>7</v>
       </c>
-      <c r="C211" s="152"/>
-      <c r="D211" s="174"/>
+      <c r="C211" s="168"/>
+      <c r="D211" s="154"/>
       <c r="E211" s="8" t="s">
         <v>278</v>
       </c>
@@ -10485,8 +10538,8 @@
       <c r="B212" s="7">
         <v>8</v>
       </c>
-      <c r="C212" s="152"/>
-      <c r="D212" s="172" t="s">
+      <c r="C212" s="168"/>
+      <c r="D212" s="152" t="s">
         <v>279</v>
       </c>
       <c r="E212" s="8" t="s">
@@ -10509,8 +10562,8 @@
       <c r="B213" s="7">
         <v>9</v>
       </c>
-      <c r="C213" s="152"/>
-      <c r="D213" s="173"/>
+      <c r="C213" s="168"/>
+      <c r="D213" s="153"/>
       <c r="E213" s="8" t="s">
         <v>281</v>
       </c>
@@ -10531,8 +10584,8 @@
       <c r="B214" s="7">
         <v>10</v>
       </c>
-      <c r="C214" s="153"/>
-      <c r="D214" s="174"/>
+      <c r="C214" s="169"/>
+      <c r="D214" s="154"/>
       <c r="E214" s="8" t="s">
         <v>282</v>
       </c>
@@ -10547,18 +10600,18 @@
       <c r="J214" s="11"/>
     </row>
     <row r="215" spans="1:10" ht="13.8">
-      <c r="A215" s="181" t="s">
+      <c r="A215" s="188" t="s">
         <v>283</v>
       </c>
-      <c r="B215" s="182"/>
-      <c r="C215" s="182"/>
-      <c r="D215" s="182"/>
-      <c r="E215" s="182"/>
-      <c r="F215" s="182"/>
-      <c r="G215" s="182"/>
-      <c r="H215" s="182"/>
-      <c r="I215" s="182"/>
-      <c r="J215" s="183"/>
+      <c r="B215" s="189"/>
+      <c r="C215" s="189"/>
+      <c r="D215" s="189"/>
+      <c r="E215" s="189"/>
+      <c r="F215" s="189"/>
+      <c r="G215" s="189"/>
+      <c r="H215" s="189"/>
+      <c r="I215" s="189"/>
+      <c r="J215" s="190"/>
     </row>
     <row r="216" spans="1:10" ht="13.8">
       <c r="A216" s="6">
@@ -10567,10 +10620,10 @@
       <c r="B216" s="7">
         <v>1</v>
       </c>
-      <c r="C216" s="154" t="s">
+      <c r="C216" s="170" t="s">
         <v>284</v>
       </c>
-      <c r="D216" s="172" t="s">
+      <c r="D216" s="152" t="s">
         <v>285</v>
       </c>
       <c r="E216" s="8" t="s">
@@ -10593,8 +10646,8 @@
       <c r="B217" s="7">
         <v>2</v>
       </c>
-      <c r="C217" s="155"/>
-      <c r="D217" s="173"/>
+      <c r="C217" s="171"/>
+      <c r="D217" s="153"/>
       <c r="E217" s="8" t="s">
         <v>287</v>
       </c>
@@ -10615,8 +10668,8 @@
       <c r="B218" s="7">
         <v>3</v>
       </c>
-      <c r="C218" s="155"/>
-      <c r="D218" s="173"/>
+      <c r="C218" s="171"/>
+      <c r="D218" s="153"/>
       <c r="E218" s="8" t="s">
         <v>288</v>
       </c>
@@ -10637,8 +10690,8 @@
       <c r="B219" s="7">
         <v>4</v>
       </c>
-      <c r="C219" s="155"/>
-      <c r="D219" s="173"/>
+      <c r="C219" s="171"/>
+      <c r="D219" s="153"/>
       <c r="E219" s="8" t="s">
         <v>289</v>
       </c>
@@ -10659,8 +10712,8 @@
       <c r="B220" s="7">
         <v>5</v>
       </c>
-      <c r="C220" s="155"/>
-      <c r="D220" s="173"/>
+      <c r="C220" s="171"/>
+      <c r="D220" s="153"/>
       <c r="E220" s="8" t="s">
         <v>290</v>
       </c>
@@ -10681,8 +10734,8 @@
       <c r="B221" s="7">
         <v>6</v>
       </c>
-      <c r="C221" s="155"/>
-      <c r="D221" s="173"/>
+      <c r="C221" s="171"/>
+      <c r="D221" s="153"/>
       <c r="E221" s="8" t="s">
         <v>291</v>
       </c>
@@ -10703,8 +10756,8 @@
       <c r="B222" s="7">
         <v>7</v>
       </c>
-      <c r="C222" s="155"/>
-      <c r="D222" s="173"/>
+      <c r="C222" s="171"/>
+      <c r="D222" s="153"/>
       <c r="E222" s="8" t="s">
         <v>292</v>
       </c>
@@ -10725,8 +10778,8 @@
       <c r="B223" s="7">
         <v>8</v>
       </c>
-      <c r="C223" s="155"/>
-      <c r="D223" s="173"/>
+      <c r="C223" s="171"/>
+      <c r="D223" s="153"/>
       <c r="E223" s="8" t="s">
         <v>293</v>
       </c>
@@ -10747,8 +10800,8 @@
       <c r="B224" s="7">
         <v>9</v>
       </c>
-      <c r="C224" s="155"/>
-      <c r="D224" s="173"/>
+      <c r="C224" s="171"/>
+      <c r="D224" s="153"/>
       <c r="E224" s="8" t="s">
         <v>294</v>
       </c>
@@ -10769,8 +10822,8 @@
       <c r="B225" s="7">
         <v>10</v>
       </c>
-      <c r="C225" s="155"/>
-      <c r="D225" s="174"/>
+      <c r="C225" s="171"/>
+      <c r="D225" s="154"/>
       <c r="E225" s="8" t="s">
         <v>295</v>
       </c>
@@ -10791,8 +10844,8 @@
       <c r="B226" s="7">
         <v>11</v>
       </c>
-      <c r="C226" s="155"/>
-      <c r="D226" s="172" t="s">
+      <c r="C226" s="171"/>
+      <c r="D226" s="152" t="s">
         <v>296</v>
       </c>
       <c r="E226" s="8" t="s">
@@ -10815,8 +10868,8 @@
       <c r="B227" s="7">
         <v>12</v>
       </c>
-      <c r="C227" s="155"/>
-      <c r="D227" s="173"/>
+      <c r="C227" s="171"/>
+      <c r="D227" s="153"/>
       <c r="E227" s="8" t="s">
         <v>298</v>
       </c>
@@ -10837,8 +10890,8 @@
       <c r="B228" s="7">
         <v>13</v>
       </c>
-      <c r="C228" s="155"/>
-      <c r="D228" s="173"/>
+      <c r="C228" s="171"/>
+      <c r="D228" s="153"/>
       <c r="E228" s="8" t="s">
         <v>299</v>
       </c>
@@ -10859,8 +10912,8 @@
       <c r="B229" s="7">
         <v>14</v>
       </c>
-      <c r="C229" s="155"/>
-      <c r="D229" s="173"/>
+      <c r="C229" s="171"/>
+      <c r="D229" s="153"/>
       <c r="E229" s="8" t="s">
         <v>300</v>
       </c>
@@ -10881,8 +10934,8 @@
       <c r="B230" s="7">
         <v>15</v>
       </c>
-      <c r="C230" s="155"/>
-      <c r="D230" s="173"/>
+      <c r="C230" s="171"/>
+      <c r="D230" s="153"/>
       <c r="E230" s="8" t="s">
         <v>301</v>
       </c>
@@ -10903,8 +10956,8 @@
       <c r="B231" s="7">
         <v>16</v>
       </c>
-      <c r="C231" s="155"/>
-      <c r="D231" s="173"/>
+      <c r="C231" s="171"/>
+      <c r="D231" s="153"/>
       <c r="E231" s="8" t="s">
         <v>302</v>
       </c>
@@ -10925,8 +10978,8 @@
       <c r="B232" s="7">
         <v>17</v>
       </c>
-      <c r="C232" s="155"/>
-      <c r="D232" s="173"/>
+      <c r="C232" s="171"/>
+      <c r="D232" s="153"/>
       <c r="E232" s="8" t="s">
         <v>303</v>
       </c>
@@ -10947,8 +11000,8 @@
       <c r="B233" s="7">
         <v>18</v>
       </c>
-      <c r="C233" s="155"/>
-      <c r="D233" s="174"/>
+      <c r="C233" s="171"/>
+      <c r="D233" s="154"/>
       <c r="E233" s="8" t="s">
         <v>304</v>
       </c>
@@ -10969,8 +11022,8 @@
       <c r="B234" s="7">
         <v>19</v>
       </c>
-      <c r="C234" s="155"/>
-      <c r="D234" s="172" t="s">
+      <c r="C234" s="171"/>
+      <c r="D234" s="152" t="s">
         <v>305</v>
       </c>
       <c r="E234" s="8" t="s">
@@ -10993,8 +11046,8 @@
       <c r="B235" s="7">
         <v>20</v>
       </c>
-      <c r="C235" s="155"/>
-      <c r="D235" s="173"/>
+      <c r="C235" s="171"/>
+      <c r="D235" s="153"/>
       <c r="E235" s="8" t="s">
         <v>307</v>
       </c>
@@ -11015,8 +11068,8 @@
       <c r="B236" s="7">
         <v>21</v>
       </c>
-      <c r="C236" s="155"/>
-      <c r="D236" s="173"/>
+      <c r="C236" s="171"/>
+      <c r="D236" s="153"/>
       <c r="E236" s="8" t="s">
         <v>308</v>
       </c>
@@ -11037,8 +11090,8 @@
       <c r="B237" s="7">
         <v>22</v>
       </c>
-      <c r="C237" s="155"/>
-      <c r="D237" s="173"/>
+      <c r="C237" s="171"/>
+      <c r="D237" s="153"/>
       <c r="E237" s="8" t="s">
         <v>309</v>
       </c>
@@ -11059,8 +11112,8 @@
       <c r="B238" s="7">
         <v>23</v>
       </c>
-      <c r="C238" s="155"/>
-      <c r="D238" s="173"/>
+      <c r="C238" s="171"/>
+      <c r="D238" s="153"/>
       <c r="E238" s="8" t="s">
         <v>310</v>
       </c>
@@ -11081,8 +11134,8 @@
       <c r="B239" s="7">
         <v>24</v>
       </c>
-      <c r="C239" s="155"/>
-      <c r="D239" s="173"/>
+      <c r="C239" s="171"/>
+      <c r="D239" s="153"/>
       <c r="E239" s="8" t="s">
         <v>311</v>
       </c>
@@ -11103,8 +11156,8 @@
       <c r="B240" s="7">
         <v>25</v>
       </c>
-      <c r="C240" s="155"/>
-      <c r="D240" s="174"/>
+      <c r="C240" s="171"/>
+      <c r="D240" s="154"/>
       <c r="E240" s="8" t="s">
         <v>312</v>
       </c>
@@ -11125,8 +11178,8 @@
       <c r="B241" s="7">
         <v>26</v>
       </c>
-      <c r="C241" s="155"/>
-      <c r="D241" s="172" t="s">
+      <c r="C241" s="171"/>
+      <c r="D241" s="152" t="s">
         <v>313</v>
       </c>
       <c r="E241" s="8" t="s">
@@ -11149,8 +11202,8 @@
       <c r="B242" s="7">
         <v>27</v>
       </c>
-      <c r="C242" s="155"/>
-      <c r="D242" s="173"/>
+      <c r="C242" s="171"/>
+      <c r="D242" s="153"/>
       <c r="E242" s="8" t="s">
         <v>315</v>
       </c>
@@ -11171,8 +11224,8 @@
       <c r="B243" s="7">
         <v>28</v>
       </c>
-      <c r="C243" s="155"/>
-      <c r="D243" s="174"/>
+      <c r="C243" s="171"/>
+      <c r="D243" s="154"/>
       <c r="E243" s="8" t="s">
         <v>316</v>
       </c>
@@ -11193,8 +11246,8 @@
       <c r="B244" s="7">
         <v>29</v>
       </c>
-      <c r="C244" s="155"/>
-      <c r="D244" s="172" t="s">
+      <c r="C244" s="171"/>
+      <c r="D244" s="152" t="s">
         <v>317</v>
       </c>
       <c r="E244" s="8" t="s">
@@ -11217,8 +11270,8 @@
       <c r="B245" s="7">
         <v>30</v>
       </c>
-      <c r="C245" s="155"/>
-      <c r="D245" s="173"/>
+      <c r="C245" s="171"/>
+      <c r="D245" s="153"/>
       <c r="E245" s="8" t="s">
         <v>319</v>
       </c>
@@ -11239,8 +11292,8 @@
       <c r="B246" s="7">
         <v>31</v>
       </c>
-      <c r="C246" s="155"/>
-      <c r="D246" s="173"/>
+      <c r="C246" s="171"/>
+      <c r="D246" s="153"/>
       <c r="E246" s="8" t="s">
         <v>320</v>
       </c>
@@ -11261,8 +11314,8 @@
       <c r="B247" s="7">
         <v>32</v>
       </c>
-      <c r="C247" s="155"/>
-      <c r="D247" s="173"/>
+      <c r="C247" s="171"/>
+      <c r="D247" s="153"/>
       <c r="E247" s="8" t="s">
         <v>321</v>
       </c>
@@ -11283,8 +11336,8 @@
       <c r="B248" s="7">
         <v>33</v>
       </c>
-      <c r="C248" s="155"/>
-      <c r="D248" s="173"/>
+      <c r="C248" s="171"/>
+      <c r="D248" s="153"/>
       <c r="E248" s="8" t="s">
         <v>322</v>
       </c>
@@ -11305,8 +11358,8 @@
       <c r="B249" s="24">
         <v>34</v>
       </c>
-      <c r="C249" s="156"/>
-      <c r="D249" s="174"/>
+      <c r="C249" s="172"/>
+      <c r="D249" s="154"/>
       <c r="E249" s="17" t="s">
         <v>323</v>
       </c>
@@ -11327,10 +11380,10 @@
       <c r="B250" s="7">
         <v>1</v>
       </c>
-      <c r="C250" s="157" t="s">
+      <c r="C250" s="161" t="s">
         <v>324</v>
       </c>
-      <c r="D250" s="172" t="s">
+      <c r="D250" s="152" t="s">
         <v>325</v>
       </c>
       <c r="E250" s="8" t="s">
@@ -11353,8 +11406,8 @@
       <c r="B251" s="7">
         <v>2</v>
       </c>
-      <c r="C251" s="158"/>
-      <c r="D251" s="173"/>
+      <c r="C251" s="162"/>
+      <c r="D251" s="153"/>
       <c r="E251" s="8" t="s">
         <v>327</v>
       </c>
@@ -11375,8 +11428,8 @@
       <c r="B252" s="7">
         <v>3</v>
       </c>
-      <c r="C252" s="158"/>
-      <c r="D252" s="173"/>
+      <c r="C252" s="162"/>
+      <c r="D252" s="153"/>
       <c r="E252" s="8" t="s">
         <v>328</v>
       </c>
@@ -11397,8 +11450,8 @@
       <c r="B253" s="7">
         <v>4</v>
       </c>
-      <c r="C253" s="158"/>
-      <c r="D253" s="173"/>
+      <c r="C253" s="162"/>
+      <c r="D253" s="153"/>
       <c r="E253" s="8" t="s">
         <v>329</v>
       </c>
@@ -11419,8 +11472,8 @@
       <c r="B254" s="7">
         <v>5</v>
       </c>
-      <c r="C254" s="158"/>
-      <c r="D254" s="173"/>
+      <c r="C254" s="162"/>
+      <c r="D254" s="153"/>
       <c r="E254" s="8" t="s">
         <v>330</v>
       </c>
@@ -11441,8 +11494,8 @@
       <c r="B255" s="7">
         <v>6</v>
       </c>
-      <c r="C255" s="158"/>
-      <c r="D255" s="173"/>
+      <c r="C255" s="162"/>
+      <c r="D255" s="153"/>
       <c r="E255" s="8" t="s">
         <v>331</v>
       </c>
@@ -11463,8 +11516,8 @@
       <c r="B256" s="7">
         <v>7</v>
       </c>
-      <c r="C256" s="158"/>
-      <c r="D256" s="173"/>
+      <c r="C256" s="162"/>
+      <c r="D256" s="153"/>
       <c r="E256" s="8" t="s">
         <v>332</v>
       </c>
@@ -11485,8 +11538,8 @@
       <c r="B257" s="7">
         <v>8</v>
       </c>
-      <c r="C257" s="158"/>
-      <c r="D257" s="174"/>
+      <c r="C257" s="162"/>
+      <c r="D257" s="154"/>
       <c r="E257" s="8" t="s">
         <v>333</v>
       </c>
@@ -11507,8 +11560,8 @@
       <c r="B258" s="7">
         <v>9</v>
       </c>
-      <c r="C258" s="158"/>
-      <c r="D258" s="172" t="s">
+      <c r="C258" s="162"/>
+      <c r="D258" s="152" t="s">
         <v>334</v>
       </c>
       <c r="E258" s="8" t="s">
@@ -11531,8 +11584,8 @@
       <c r="B259" s="7">
         <v>10</v>
       </c>
-      <c r="C259" s="158"/>
-      <c r="D259" s="174"/>
+      <c r="C259" s="162"/>
+      <c r="D259" s="154"/>
       <c r="E259" s="8" t="s">
         <v>336</v>
       </c>
@@ -11553,8 +11606,8 @@
       <c r="B260" s="7">
         <v>11</v>
       </c>
-      <c r="C260" s="158"/>
-      <c r="D260" s="172" t="s">
+      <c r="C260" s="162"/>
+      <c r="D260" s="152" t="s">
         <v>337</v>
       </c>
       <c r="E260" s="8" t="s">
@@ -11577,8 +11630,8 @@
       <c r="B261" s="7">
         <v>12</v>
       </c>
-      <c r="C261" s="158"/>
-      <c r="D261" s="173"/>
+      <c r="C261" s="162"/>
+      <c r="D261" s="153"/>
       <c r="E261" s="8" t="s">
         <v>339</v>
       </c>
@@ -11599,8 +11652,8 @@
       <c r="B262" s="7">
         <v>13</v>
       </c>
-      <c r="C262" s="158"/>
-      <c r="D262" s="173"/>
+      <c r="C262" s="162"/>
+      <c r="D262" s="153"/>
       <c r="E262" s="8" t="s">
         <v>340</v>
       </c>
@@ -11621,8 +11674,8 @@
       <c r="B263" s="7">
         <v>14</v>
       </c>
-      <c r="C263" s="158"/>
-      <c r="D263" s="173"/>
+      <c r="C263" s="162"/>
+      <c r="D263" s="153"/>
       <c r="E263" s="8" t="s">
         <v>341</v>
       </c>
@@ -11643,8 +11696,8 @@
       <c r="B264" s="7">
         <v>15</v>
       </c>
-      <c r="C264" s="158"/>
-      <c r="D264" s="173"/>
+      <c r="C264" s="162"/>
+      <c r="D264" s="153"/>
       <c r="E264" s="8" t="s">
         <v>342</v>
       </c>
@@ -11665,8 +11718,8 @@
       <c r="B265" s="24">
         <v>16</v>
       </c>
-      <c r="C265" s="159"/>
-      <c r="D265" s="174"/>
+      <c r="C265" s="163"/>
+      <c r="D265" s="154"/>
       <c r="E265" s="17" t="s">
         <v>343</v>
       </c>
@@ -11687,10 +11740,10 @@
       <c r="B266" s="7">
         <v>1</v>
       </c>
-      <c r="C266" s="160" t="s">
+      <c r="C266" s="164" t="s">
         <v>344</v>
       </c>
-      <c r="D266" s="172" t="s">
+      <c r="D266" s="152" t="s">
         <v>345</v>
       </c>
       <c r="E266" s="8" t="s">
@@ -11713,8 +11766,8 @@
       <c r="B267" s="7">
         <v>2</v>
       </c>
-      <c r="C267" s="161"/>
-      <c r="D267" s="173"/>
+      <c r="C267" s="165"/>
+      <c r="D267" s="153"/>
       <c r="E267" s="8" t="s">
         <v>347</v>
       </c>
@@ -11735,8 +11788,8 @@
       <c r="B268" s="7">
         <v>3</v>
       </c>
-      <c r="C268" s="161"/>
-      <c r="D268" s="173"/>
+      <c r="C268" s="165"/>
+      <c r="D268" s="153"/>
       <c r="E268" s="8" t="s">
         <v>348</v>
       </c>
@@ -11757,8 +11810,8 @@
       <c r="B269" s="7">
         <v>4</v>
       </c>
-      <c r="C269" s="161"/>
-      <c r="D269" s="173"/>
+      <c r="C269" s="165"/>
+      <c r="D269" s="153"/>
       <c r="E269" s="8" t="s">
         <v>349</v>
       </c>
@@ -11779,8 +11832,8 @@
       <c r="B270" s="7">
         <v>5</v>
       </c>
-      <c r="C270" s="161"/>
-      <c r="D270" s="174"/>
+      <c r="C270" s="165"/>
+      <c r="D270" s="154"/>
       <c r="E270" s="8" t="s">
         <v>350</v>
       </c>
@@ -11801,8 +11854,8 @@
       <c r="B271" s="7">
         <v>6</v>
       </c>
-      <c r="C271" s="161"/>
-      <c r="D271" s="172" t="s">
+      <c r="C271" s="165"/>
+      <c r="D271" s="152" t="s">
         <v>351</v>
       </c>
       <c r="E271" s="8" t="s">
@@ -11825,8 +11878,8 @@
       <c r="B272" s="7">
         <v>7</v>
       </c>
-      <c r="C272" s="162"/>
-      <c r="D272" s="174"/>
+      <c r="C272" s="166"/>
+      <c r="D272" s="154"/>
       <c r="E272" s="8" t="s">
         <v>353</v>
       </c>
@@ -11841,18 +11894,18 @@
       <c r="J272" s="11"/>
     </row>
     <row r="273" spans="1:10" ht="13.8">
-      <c r="A273" s="184" t="s">
+      <c r="A273" s="185" t="s">
         <v>354</v>
       </c>
-      <c r="B273" s="185"/>
-      <c r="C273" s="185"/>
-      <c r="D273" s="185"/>
-      <c r="E273" s="185"/>
-      <c r="F273" s="185"/>
-      <c r="G273" s="185"/>
-      <c r="H273" s="185"/>
-      <c r="I273" s="185"/>
-      <c r="J273" s="186"/>
+      <c r="B273" s="186"/>
+      <c r="C273" s="186"/>
+      <c r="D273" s="186"/>
+      <c r="E273" s="186"/>
+      <c r="F273" s="186"/>
+      <c r="G273" s="186"/>
+      <c r="H273" s="186"/>
+      <c r="I273" s="186"/>
+      <c r="J273" s="187"/>
     </row>
     <row r="274" spans="1:10" ht="13.8">
       <c r="A274" s="33">
@@ -11861,10 +11914,10 @@
       <c r="B274" s="7">
         <v>1</v>
       </c>
-      <c r="C274" s="163" t="s">
+      <c r="C274" s="179" t="s">
         <v>355</v>
       </c>
-      <c r="D274" s="175" t="s">
+      <c r="D274" s="182" t="s">
         <v>356</v>
       </c>
       <c r="E274" s="13" t="s">
@@ -11887,8 +11940,8 @@
       <c r="B275" s="7">
         <v>2</v>
       </c>
-      <c r="C275" s="164"/>
-      <c r="D275" s="176"/>
+      <c r="C275" s="180"/>
+      <c r="D275" s="183"/>
       <c r="E275" s="13" t="s">
         <v>358</v>
       </c>
@@ -11909,8 +11962,8 @@
       <c r="B276" s="7">
         <v>3</v>
       </c>
-      <c r="C276" s="164"/>
-      <c r="D276" s="176"/>
+      <c r="C276" s="180"/>
+      <c r="D276" s="183"/>
       <c r="E276" s="8" t="s">
         <v>359</v>
       </c>
@@ -11931,8 +11984,8 @@
       <c r="B277" s="7">
         <v>4</v>
       </c>
-      <c r="C277" s="164"/>
-      <c r="D277" s="176"/>
+      <c r="C277" s="180"/>
+      <c r="D277" s="183"/>
       <c r="E277" s="8" t="s">
         <v>360</v>
       </c>
@@ -11953,8 +12006,8 @@
       <c r="B278" s="7">
         <v>5</v>
       </c>
-      <c r="C278" s="164"/>
-      <c r="D278" s="176"/>
+      <c r="C278" s="180"/>
+      <c r="D278" s="183"/>
       <c r="E278" s="8" t="s">
         <v>361</v>
       </c>
@@ -11975,8 +12028,8 @@
       <c r="B279" s="7">
         <v>6</v>
       </c>
-      <c r="C279" s="164"/>
-      <c r="D279" s="176"/>
+      <c r="C279" s="180"/>
+      <c r="D279" s="183"/>
       <c r="E279" s="8" t="s">
         <v>362</v>
       </c>
@@ -11997,8 +12050,8 @@
       <c r="B280" s="7">
         <v>7</v>
       </c>
-      <c r="C280" s="164"/>
-      <c r="D280" s="176"/>
+      <c r="C280" s="180"/>
+      <c r="D280" s="183"/>
       <c r="E280" s="8" t="s">
         <v>363</v>
       </c>
@@ -12019,8 +12072,8 @@
       <c r="B281" s="7">
         <v>8</v>
       </c>
-      <c r="C281" s="164"/>
-      <c r="D281" s="177"/>
+      <c r="C281" s="180"/>
+      <c r="D281" s="184"/>
       <c r="E281" s="13" t="s">
         <v>364</v>
       </c>
@@ -12041,8 +12094,8 @@
       <c r="B282" s="7">
         <v>9</v>
       </c>
-      <c r="C282" s="164"/>
-      <c r="D282" s="175" t="s">
+      <c r="C282" s="180"/>
+      <c r="D282" s="182" t="s">
         <v>365</v>
       </c>
       <c r="E282" s="8" t="s">
@@ -12065,8 +12118,8 @@
       <c r="B283" s="7">
         <v>10</v>
       </c>
-      <c r="C283" s="164"/>
-      <c r="D283" s="176"/>
+      <c r="C283" s="180"/>
+      <c r="D283" s="183"/>
       <c r="E283" s="13" t="s">
         <v>367</v>
       </c>
@@ -12087,8 +12140,8 @@
       <c r="B284" s="7">
         <v>11</v>
       </c>
-      <c r="C284" s="164"/>
-      <c r="D284" s="176"/>
+      <c r="C284" s="180"/>
+      <c r="D284" s="183"/>
       <c r="E284" s="13" t="s">
         <v>368</v>
       </c>
@@ -12109,8 +12162,8 @@
       <c r="B285" s="7">
         <v>12</v>
       </c>
-      <c r="C285" s="164"/>
-      <c r="D285" s="176"/>
+      <c r="C285" s="180"/>
+      <c r="D285" s="183"/>
       <c r="E285" s="13" t="s">
         <v>369</v>
       </c>
@@ -12131,8 +12184,8 @@
       <c r="B286" s="7">
         <v>13</v>
       </c>
-      <c r="C286" s="164"/>
-      <c r="D286" s="176"/>
+      <c r="C286" s="180"/>
+      <c r="D286" s="183"/>
       <c r="E286" s="13" t="s">
         <v>370</v>
       </c>
@@ -12153,8 +12206,8 @@
       <c r="B287" s="7">
         <v>14</v>
       </c>
-      <c r="C287" s="164"/>
-      <c r="D287" s="176"/>
+      <c r="C287" s="180"/>
+      <c r="D287" s="183"/>
       <c r="E287" s="13" t="s">
         <v>371</v>
       </c>
@@ -12175,8 +12228,8 @@
       <c r="B288" s="7">
         <v>15</v>
       </c>
-      <c r="C288" s="164"/>
-      <c r="D288" s="177"/>
+      <c r="C288" s="180"/>
+      <c r="D288" s="184"/>
       <c r="E288" s="13" t="s">
         <v>372</v>
       </c>
@@ -12197,8 +12250,8 @@
       <c r="B289" s="7">
         <v>16</v>
       </c>
-      <c r="C289" s="164"/>
-      <c r="D289" s="175" t="s">
+      <c r="C289" s="180"/>
+      <c r="D289" s="182" t="s">
         <v>373</v>
       </c>
       <c r="E289" s="13" t="s">
@@ -12221,8 +12274,8 @@
       <c r="B290" s="7">
         <v>17</v>
       </c>
-      <c r="C290" s="164"/>
-      <c r="D290" s="176"/>
+      <c r="C290" s="180"/>
+      <c r="D290" s="183"/>
       <c r="E290" s="8" t="s">
         <v>375</v>
       </c>
@@ -12243,8 +12296,8 @@
       <c r="B291" s="7">
         <v>18</v>
       </c>
-      <c r="C291" s="164"/>
-      <c r="D291" s="176"/>
+      <c r="C291" s="180"/>
+      <c r="D291" s="183"/>
       <c r="E291" s="11" t="s">
         <v>376</v>
       </c>
@@ -12265,8 +12318,8 @@
       <c r="B292" s="24">
         <v>19</v>
       </c>
-      <c r="C292" s="165"/>
-      <c r="D292" s="177"/>
+      <c r="C292" s="181"/>
+      <c r="D292" s="184"/>
       <c r="E292" s="20" t="s">
         <v>377</v>
       </c>
@@ -12287,10 +12340,10 @@
       <c r="B293" s="7">
         <v>1</v>
       </c>
-      <c r="C293" s="154" t="s">
+      <c r="C293" s="170" t="s">
         <v>378</v>
       </c>
-      <c r="D293" s="172" t="s">
+      <c r="D293" s="152" t="s">
         <v>379</v>
       </c>
       <c r="E293" s="8" t="s">
@@ -12313,8 +12366,8 @@
       <c r="B294" s="7">
         <v>2</v>
       </c>
-      <c r="C294" s="155"/>
-      <c r="D294" s="173"/>
+      <c r="C294" s="171"/>
+      <c r="D294" s="153"/>
       <c r="E294" s="8" t="s">
         <v>381</v>
       </c>
@@ -12335,8 +12388,8 @@
       <c r="B295" s="7">
         <v>3</v>
       </c>
-      <c r="C295" s="155"/>
-      <c r="D295" s="174"/>
+      <c r="C295" s="171"/>
+      <c r="D295" s="154"/>
       <c r="E295" s="8" t="s">
         <v>382</v>
       </c>
@@ -12355,8 +12408,8 @@
       <c r="B296" s="7">
         <v>4</v>
       </c>
-      <c r="C296" s="155"/>
-      <c r="D296" s="172" t="s">
+      <c r="C296" s="171"/>
+      <c r="D296" s="152" t="s">
         <v>383</v>
       </c>
       <c r="E296" s="37" t="s">
@@ -12379,8 +12432,8 @@
       <c r="B297" s="7">
         <v>5</v>
       </c>
-      <c r="C297" s="155"/>
-      <c r="D297" s="173"/>
+      <c r="C297" s="171"/>
+      <c r="D297" s="153"/>
       <c r="E297" s="8" t="s">
         <v>385</v>
       </c>
@@ -12401,8 +12454,8 @@
       <c r="B298" s="7">
         <v>6</v>
       </c>
-      <c r="C298" s="155"/>
-      <c r="D298" s="173"/>
+      <c r="C298" s="171"/>
+      <c r="D298" s="153"/>
       <c r="E298" s="8" t="s">
         <v>386</v>
       </c>
@@ -12423,8 +12476,8 @@
       <c r="B299" s="7">
         <v>7</v>
       </c>
-      <c r="C299" s="155"/>
-      <c r="D299" s="173"/>
+      <c r="C299" s="171"/>
+      <c r="D299" s="153"/>
       <c r="E299" s="8" t="s">
         <v>387</v>
       </c>
@@ -12445,8 +12498,8 @@
       <c r="B300" s="7">
         <v>8</v>
       </c>
-      <c r="C300" s="155"/>
-      <c r="D300" s="174"/>
+      <c r="C300" s="171"/>
+      <c r="D300" s="154"/>
       <c r="E300" s="8" t="s">
         <v>388</v>
       </c>
@@ -12467,8 +12520,8 @@
       <c r="B301" s="7">
         <v>9</v>
       </c>
-      <c r="C301" s="155"/>
-      <c r="D301" s="172" t="s">
+      <c r="C301" s="171"/>
+      <c r="D301" s="152" t="s">
         <v>389</v>
       </c>
       <c r="E301" s="8" t="s">
@@ -12491,8 +12544,8 @@
       <c r="B302" s="7">
         <v>10</v>
       </c>
-      <c r="C302" s="155"/>
-      <c r="D302" s="173"/>
+      <c r="C302" s="171"/>
+      <c r="D302" s="153"/>
       <c r="E302" s="8" t="s">
         <v>391</v>
       </c>
@@ -12513,8 +12566,8 @@
       <c r="B303" s="7">
         <v>11</v>
       </c>
-      <c r="C303" s="155"/>
-      <c r="D303" s="174"/>
+      <c r="C303" s="171"/>
+      <c r="D303" s="154"/>
       <c r="E303" s="8" t="s">
         <v>392</v>
       </c>
@@ -12535,8 +12588,8 @@
       <c r="B304" s="7">
         <v>12</v>
       </c>
-      <c r="C304" s="155"/>
-      <c r="D304" s="172" t="s">
+      <c r="C304" s="171"/>
+      <c r="D304" s="152" t="s">
         <v>393</v>
       </c>
       <c r="E304" s="8" t="s">
@@ -12559,8 +12612,8 @@
       <c r="B305" s="7">
         <v>13</v>
       </c>
-      <c r="C305" s="155"/>
-      <c r="D305" s="173"/>
+      <c r="C305" s="171"/>
+      <c r="D305" s="153"/>
       <c r="E305" s="8" t="s">
         <v>395</v>
       </c>
@@ -12581,8 +12634,8 @@
       <c r="B306" s="7">
         <v>14</v>
       </c>
-      <c r="C306" s="155"/>
-      <c r="D306" s="173"/>
+      <c r="C306" s="171"/>
+      <c r="D306" s="153"/>
       <c r="E306" s="8" t="s">
         <v>396</v>
       </c>
@@ -12603,8 +12656,8 @@
       <c r="B307" s="24">
         <v>15</v>
       </c>
-      <c r="C307" s="156"/>
-      <c r="D307" s="174"/>
+      <c r="C307" s="172"/>
+      <c r="D307" s="154"/>
       <c r="E307" s="17" t="s">
         <v>397</v>
       </c>
@@ -12625,10 +12678,10 @@
       <c r="B308" s="7">
         <v>1</v>
       </c>
-      <c r="C308" s="166" t="s">
+      <c r="C308" s="197" t="s">
         <v>398</v>
       </c>
-      <c r="D308" s="175" t="s">
+      <c r="D308" s="182" t="s">
         <v>399</v>
       </c>
       <c r="E308" s="13" t="s">
@@ -12651,8 +12704,8 @@
       <c r="B309" s="7">
         <v>2</v>
       </c>
-      <c r="C309" s="167"/>
-      <c r="D309" s="176"/>
+      <c r="C309" s="198"/>
+      <c r="D309" s="183"/>
       <c r="E309" s="8" t="s">
         <v>401</v>
       </c>
@@ -12673,8 +12726,8 @@
       <c r="B310" s="7">
         <v>3</v>
       </c>
-      <c r="C310" s="167"/>
-      <c r="D310" s="176"/>
+      <c r="C310" s="198"/>
+      <c r="D310" s="183"/>
       <c r="E310" s="13" t="s">
         <v>402</v>
       </c>
@@ -12695,8 +12748,8 @@
       <c r="B311" s="7">
         <v>4</v>
       </c>
-      <c r="C311" s="167"/>
-      <c r="D311" s="176"/>
+      <c r="C311" s="198"/>
+      <c r="D311" s="183"/>
       <c r="E311" s="8" t="s">
         <v>403</v>
       </c>
@@ -12717,8 +12770,8 @@
       <c r="B312" s="7">
         <v>5</v>
       </c>
-      <c r="C312" s="167"/>
-      <c r="D312" s="176"/>
+      <c r="C312" s="198"/>
+      <c r="D312" s="183"/>
       <c r="E312" s="13" t="s">
         <v>404</v>
       </c>
@@ -12739,8 +12792,8 @@
       <c r="B313" s="7">
         <v>6</v>
       </c>
-      <c r="C313" s="167"/>
-      <c r="D313" s="176"/>
+      <c r="C313" s="198"/>
+      <c r="D313" s="183"/>
       <c r="E313" s="13" t="s">
         <v>405</v>
       </c>
@@ -12761,8 +12814,8 @@
       <c r="B314" s="7">
         <v>7</v>
       </c>
-      <c r="C314" s="167"/>
-      <c r="D314" s="177"/>
+      <c r="C314" s="198"/>
+      <c r="D314" s="184"/>
       <c r="E314" s="8" t="s">
         <v>406</v>
       </c>
@@ -12783,8 +12836,8 @@
       <c r="B315" s="7">
         <v>8</v>
       </c>
-      <c r="C315" s="167"/>
-      <c r="D315" s="175" t="s">
+      <c r="C315" s="198"/>
+      <c r="D315" s="182" t="s">
         <v>407</v>
       </c>
       <c r="E315" s="13" t="s">
@@ -12807,8 +12860,8 @@
       <c r="B316" s="7">
         <v>9</v>
       </c>
-      <c r="C316" s="167"/>
-      <c r="D316" s="176"/>
+      <c r="C316" s="198"/>
+      <c r="D316" s="183"/>
       <c r="E316" s="8" t="s">
         <v>409</v>
       </c>
@@ -12829,8 +12882,8 @@
       <c r="B317" s="24">
         <v>10</v>
       </c>
-      <c r="C317" s="168"/>
-      <c r="D317" s="177"/>
+      <c r="C317" s="199"/>
+      <c r="D317" s="184"/>
       <c r="E317" s="17" t="s">
         <v>410</v>
       </c>
@@ -12851,10 +12904,10 @@
       <c r="B318" s="7">
         <v>1</v>
       </c>
-      <c r="C318" s="169" t="s">
+      <c r="C318" s="200" t="s">
         <v>411</v>
       </c>
-      <c r="D318" s="175" t="s">
+      <c r="D318" s="182" t="s">
         <v>412</v>
       </c>
       <c r="E318" s="8" t="s">
@@ -12877,8 +12930,8 @@
       <c r="B319" s="7">
         <v>2</v>
       </c>
-      <c r="C319" s="170"/>
-      <c r="D319" s="176"/>
+      <c r="C319" s="201"/>
+      <c r="D319" s="183"/>
       <c r="E319" s="13" t="s">
         <v>414</v>
       </c>
@@ -12899,8 +12952,8 @@
       <c r="B320" s="7">
         <v>3</v>
       </c>
-      <c r="C320" s="170"/>
-      <c r="D320" s="176"/>
+      <c r="C320" s="201"/>
+      <c r="D320" s="183"/>
       <c r="E320" s="8" t="s">
         <v>415</v>
       </c>
@@ -12921,8 +12974,8 @@
       <c r="B321" s="7">
         <v>4</v>
       </c>
-      <c r="C321" s="170"/>
-      <c r="D321" s="176"/>
+      <c r="C321" s="201"/>
+      <c r="D321" s="183"/>
       <c r="E321" s="8" t="s">
         <v>416</v>
       </c>
@@ -12943,8 +12996,8 @@
       <c r="B322" s="7">
         <v>5</v>
       </c>
-      <c r="C322" s="170"/>
-      <c r="D322" s="176"/>
+      <c r="C322" s="201"/>
+      <c r="D322" s="183"/>
       <c r="E322" s="8" t="s">
         <v>417</v>
       </c>
@@ -12965,8 +13018,8 @@
       <c r="B323" s="7">
         <v>6</v>
       </c>
-      <c r="C323" s="170"/>
-      <c r="D323" s="177"/>
+      <c r="C323" s="201"/>
+      <c r="D323" s="184"/>
       <c r="E323" s="29" t="s">
         <v>418</v>
       </c>
@@ -12987,8 +13040,8 @@
       <c r="B324" s="7">
         <v>7</v>
       </c>
-      <c r="C324" s="170"/>
-      <c r="D324" s="175" t="s">
+      <c r="C324" s="201"/>
+      <c r="D324" s="182" t="s">
         <v>419</v>
       </c>
       <c r="E324" s="13" t="s">
@@ -13011,8 +13064,8 @@
       <c r="B325" s="7">
         <v>8</v>
       </c>
-      <c r="C325" s="170"/>
-      <c r="D325" s="176"/>
+      <c r="C325" s="201"/>
+      <c r="D325" s="183"/>
       <c r="E325" s="8" t="s">
         <v>421</v>
       </c>
@@ -13033,8 +13086,8 @@
       <c r="B326" s="7">
         <v>9</v>
       </c>
-      <c r="C326" s="170"/>
-      <c r="D326" s="176"/>
+      <c r="C326" s="201"/>
+      <c r="D326" s="183"/>
       <c r="E326" s="8" t="s">
         <v>422</v>
       </c>
@@ -13055,8 +13108,8 @@
       <c r="B327" s="7">
         <v>10</v>
       </c>
-      <c r="C327" s="170"/>
-      <c r="D327" s="176"/>
+      <c r="C327" s="201"/>
+      <c r="D327" s="183"/>
       <c r="E327" s="8" t="s">
         <v>423</v>
       </c>
@@ -13077,8 +13130,8 @@
       <c r="B328" s="7">
         <v>11</v>
       </c>
-      <c r="C328" s="170"/>
-      <c r="D328" s="177"/>
+      <c r="C328" s="201"/>
+      <c r="D328" s="184"/>
       <c r="E328" s="13" t="s">
         <v>424</v>
       </c>
@@ -13099,8 +13152,8 @@
       <c r="B329" s="7">
         <v>12</v>
       </c>
-      <c r="C329" s="170"/>
-      <c r="D329" s="175" t="s">
+      <c r="C329" s="201"/>
+      <c r="D329" s="182" t="s">
         <v>425</v>
       </c>
       <c r="E329" s="8" t="s">
@@ -13123,8 +13176,8 @@
       <c r="B330" s="7">
         <v>13</v>
       </c>
-      <c r="C330" s="170"/>
-      <c r="D330" s="176"/>
+      <c r="C330" s="201"/>
+      <c r="D330" s="183"/>
       <c r="E330" s="8" t="s">
         <v>427</v>
       </c>
@@ -13145,8 +13198,8 @@
       <c r="B331" s="7">
         <v>14</v>
       </c>
-      <c r="C331" s="170"/>
-      <c r="D331" s="176"/>
+      <c r="C331" s="201"/>
+      <c r="D331" s="183"/>
       <c r="E331" s="8" t="s">
         <v>428</v>
       </c>
@@ -13167,8 +13220,8 @@
       <c r="B332" s="7">
         <v>15</v>
       </c>
-      <c r="C332" s="170"/>
-      <c r="D332" s="176"/>
+      <c r="C332" s="201"/>
+      <c r="D332" s="183"/>
       <c r="E332" s="8" t="s">
         <v>429</v>
       </c>
@@ -13189,8 +13242,8 @@
       <c r="B333" s="7">
         <v>16</v>
       </c>
-      <c r="C333" s="170"/>
-      <c r="D333" s="176"/>
+      <c r="C333" s="201"/>
+      <c r="D333" s="183"/>
       <c r="E333" s="8" t="s">
         <v>430</v>
       </c>
@@ -13211,8 +13264,8 @@
       <c r="B334" s="7">
         <v>17</v>
       </c>
-      <c r="C334" s="170"/>
-      <c r="D334" s="176"/>
+      <c r="C334" s="201"/>
+      <c r="D334" s="183"/>
       <c r="E334" s="8" t="s">
         <v>431</v>
       </c>
@@ -13233,8 +13286,8 @@
       <c r="B335" s="7">
         <v>18</v>
       </c>
-      <c r="C335" s="170"/>
-      <c r="D335" s="176"/>
+      <c r="C335" s="201"/>
+      <c r="D335" s="183"/>
       <c r="E335" s="8" t="s">
         <v>432</v>
       </c>
@@ -13255,8 +13308,8 @@
       <c r="B336" s="7">
         <v>19</v>
       </c>
-      <c r="C336" s="170"/>
-      <c r="D336" s="176"/>
+      <c r="C336" s="201"/>
+      <c r="D336" s="183"/>
       <c r="E336" s="8" t="s">
         <v>433</v>
       </c>
@@ -13277,8 +13330,8 @@
       <c r="B337" s="7">
         <v>20</v>
       </c>
-      <c r="C337" s="170"/>
-      <c r="D337" s="177"/>
+      <c r="C337" s="201"/>
+      <c r="D337" s="184"/>
       <c r="E337" s="13" t="s">
         <v>434</v>
       </c>
@@ -13299,8 +13352,8 @@
       <c r="B338" s="7">
         <v>21</v>
       </c>
-      <c r="C338" s="170"/>
-      <c r="D338" s="175" t="s">
+      <c r="C338" s="201"/>
+      <c r="D338" s="182" t="s">
         <v>435</v>
       </c>
       <c r="E338" s="13" t="s">
@@ -13323,8 +13376,8 @@
       <c r="B339" s="7">
         <v>22</v>
       </c>
-      <c r="C339" s="170"/>
-      <c r="D339" s="176"/>
+      <c r="C339" s="201"/>
+      <c r="D339" s="183"/>
       <c r="E339" s="13" t="s">
         <v>437</v>
       </c>
@@ -13345,8 +13398,8 @@
       <c r="B340" s="7">
         <v>23</v>
       </c>
-      <c r="C340" s="170"/>
-      <c r="D340" s="176"/>
+      <c r="C340" s="201"/>
+      <c r="D340" s="183"/>
       <c r="E340" s="13" t="s">
         <v>438</v>
       </c>
@@ -13367,8 +13420,8 @@
       <c r="B341" s="7">
         <v>24</v>
       </c>
-      <c r="C341" s="170"/>
-      <c r="D341" s="176"/>
+      <c r="C341" s="201"/>
+      <c r="D341" s="183"/>
       <c r="E341" s="13" t="s">
         <v>439</v>
       </c>
@@ -13389,8 +13442,8 @@
       <c r="B342" s="24">
         <v>25</v>
       </c>
-      <c r="C342" s="171"/>
-      <c r="D342" s="177"/>
+      <c r="C342" s="202"/>
+      <c r="D342" s="184"/>
       <c r="E342" s="25" t="s">
         <v>440</v>
       </c>
@@ -13411,10 +13464,10 @@
       <c r="B343" s="7">
         <v>1</v>
       </c>
-      <c r="C343" s="151" t="s">
+      <c r="C343" s="167" t="s">
         <v>441</v>
       </c>
-      <c r="D343" s="172" t="s">
+      <c r="D343" s="152" t="s">
         <v>442</v>
       </c>
       <c r="E343" s="8" t="s">
@@ -13443,8 +13496,8 @@
       <c r="B344" s="7">
         <v>2</v>
       </c>
-      <c r="C344" s="152"/>
-      <c r="D344" s="173"/>
+      <c r="C344" s="168"/>
+      <c r="D344" s="153"/>
       <c r="E344" s="8" t="s">
         <v>444</v>
       </c>
@@ -13471,8 +13524,8 @@
       <c r="B345" s="7">
         <v>3</v>
       </c>
-      <c r="C345" s="152"/>
-      <c r="D345" s="173"/>
+      <c r="C345" s="168"/>
+      <c r="D345" s="153"/>
       <c r="E345" s="8" t="s">
         <v>445</v>
       </c>
@@ -13499,8 +13552,8 @@
       <c r="B346" s="7">
         <v>4</v>
       </c>
-      <c r="C346" s="152"/>
-      <c r="D346" s="173"/>
+      <c r="C346" s="168"/>
+      <c r="D346" s="153"/>
       <c r="E346" s="8" t="s">
         <v>446</v>
       </c>
@@ -13527,8 +13580,8 @@
       <c r="B347" s="7">
         <v>5</v>
       </c>
-      <c r="C347" s="152"/>
-      <c r="D347" s="174"/>
+      <c r="C347" s="168"/>
+      <c r="D347" s="154"/>
       <c r="E347" s="8" t="s">
         <v>447</v>
       </c>
@@ -13555,8 +13608,8 @@
       <c r="B348" s="7">
         <v>6</v>
       </c>
-      <c r="C348" s="152"/>
-      <c r="D348" s="172" t="s">
+      <c r="C348" s="168"/>
+      <c r="D348" s="152" t="s">
         <v>448</v>
       </c>
       <c r="E348" s="8" t="s">
@@ -13583,8 +13636,8 @@
       <c r="B349" s="7">
         <v>7</v>
       </c>
-      <c r="C349" s="152"/>
-      <c r="D349" s="173"/>
+      <c r="C349" s="168"/>
+      <c r="D349" s="153"/>
       <c r="E349" s="8" t="s">
         <v>450</v>
       </c>
@@ -13611,8 +13664,8 @@
       <c r="B350" s="7">
         <v>8</v>
       </c>
-      <c r="C350" s="152"/>
-      <c r="D350" s="173"/>
+      <c r="C350" s="168"/>
+      <c r="D350" s="153"/>
       <c r="E350" s="8" t="s">
         <v>451</v>
       </c>
@@ -13639,8 +13692,8 @@
       <c r="B351" s="7">
         <v>9</v>
       </c>
-      <c r="C351" s="152"/>
-      <c r="D351" s="173"/>
+      <c r="C351" s="168"/>
+      <c r="D351" s="153"/>
       <c r="E351" s="8" t="s">
         <v>452</v>
       </c>
@@ -13663,8 +13716,8 @@
       <c r="B352" s="7">
         <v>10</v>
       </c>
-      <c r="C352" s="152"/>
-      <c r="D352" s="173"/>
+      <c r="C352" s="168"/>
+      <c r="D352" s="153"/>
       <c r="E352" s="8" t="s">
         <v>453</v>
       </c>
@@ -13691,8 +13744,8 @@
       <c r="B353" s="7">
         <v>11</v>
       </c>
-      <c r="C353" s="152"/>
-      <c r="D353" s="174"/>
+      <c r="C353" s="168"/>
+      <c r="D353" s="154"/>
       <c r="E353" s="8" t="s">
         <v>454</v>
       </c>
@@ -13713,8 +13766,8 @@
       <c r="B354" s="7">
         <v>12</v>
       </c>
-      <c r="C354" s="152"/>
-      <c r="D354" s="172" t="s">
+      <c r="C354" s="168"/>
+      <c r="D354" s="152" t="s">
         <v>455</v>
       </c>
       <c r="E354" s="8" t="s">
@@ -13741,8 +13794,8 @@
       <c r="B355" s="7">
         <v>13</v>
       </c>
-      <c r="C355" s="152"/>
-      <c r="D355" s="173"/>
+      <c r="C355" s="168"/>
+      <c r="D355" s="153"/>
       <c r="E355" s="8" t="s">
         <v>457</v>
       </c>
@@ -13769,8 +13822,8 @@
       <c r="B356" s="7">
         <v>14</v>
       </c>
-      <c r="C356" s="152"/>
-      <c r="D356" s="173"/>
+      <c r="C356" s="168"/>
+      <c r="D356" s="153"/>
       <c r="E356" s="8" t="s">
         <v>458</v>
       </c>
@@ -13791,8 +13844,8 @@
       <c r="B357" s="7">
         <v>15</v>
       </c>
-      <c r="C357" s="153"/>
-      <c r="D357" s="174"/>
+      <c r="C357" s="169"/>
+      <c r="D357" s="154"/>
       <c r="E357" s="8" t="s">
         <v>459</v>
       </c>
@@ -13807,18 +13860,18 @@
       <c r="J357" s="11"/>
     </row>
     <row r="358" spans="1:10" ht="13.8">
-      <c r="A358" s="187" t="s">
+      <c r="A358" s="191" t="s">
         <v>460</v>
       </c>
-      <c r="B358" s="188"/>
-      <c r="C358" s="188"/>
-      <c r="D358" s="188"/>
-      <c r="E358" s="188"/>
-      <c r="F358" s="188"/>
-      <c r="G358" s="188"/>
-      <c r="H358" s="188"/>
-      <c r="I358" s="188"/>
-      <c r="J358" s="189"/>
+      <c r="B358" s="192"/>
+      <c r="C358" s="192"/>
+      <c r="D358" s="192"/>
+      <c r="E358" s="192"/>
+      <c r="F358" s="192"/>
+      <c r="G358" s="192"/>
+      <c r="H358" s="192"/>
+      <c r="I358" s="192"/>
+      <c r="J358" s="193"/>
     </row>
     <row r="359" spans="1:10" ht="13.8">
       <c r="A359" s="6">
@@ -13827,10 +13880,10 @@
       <c r="B359" s="7">
         <v>1</v>
       </c>
-      <c r="C359" s="154" t="s">
+      <c r="C359" s="170" t="s">
         <v>461</v>
       </c>
-      <c r="D359" s="172" t="s">
+      <c r="D359" s="152" t="s">
         <v>462</v>
       </c>
       <c r="E359" s="8" t="s">
@@ -13853,8 +13906,8 @@
       <c r="B360" s="7">
         <v>2</v>
       </c>
-      <c r="C360" s="155"/>
-      <c r="D360" s="173"/>
+      <c r="C360" s="171"/>
+      <c r="D360" s="153"/>
       <c r="E360" s="8" t="s">
         <v>464</v>
       </c>
@@ -13875,8 +13928,8 @@
       <c r="B361" s="7">
         <v>3</v>
       </c>
-      <c r="C361" s="155"/>
-      <c r="D361" s="173"/>
+      <c r="C361" s="171"/>
+      <c r="D361" s="153"/>
       <c r="E361" s="8" t="s">
         <v>465</v>
       </c>
@@ -13897,8 +13950,8 @@
       <c r="B362" s="7">
         <v>4</v>
       </c>
-      <c r="C362" s="155"/>
-      <c r="D362" s="173"/>
+      <c r="C362" s="171"/>
+      <c r="D362" s="153"/>
       <c r="E362" s="8" t="s">
         <v>466</v>
       </c>
@@ -13919,8 +13972,8 @@
       <c r="B363" s="7">
         <v>5</v>
       </c>
-      <c r="C363" s="155"/>
-      <c r="D363" s="174"/>
+      <c r="C363" s="171"/>
+      <c r="D363" s="154"/>
       <c r="E363" s="8" t="s">
         <v>467</v>
       </c>
@@ -13941,8 +13994,8 @@
       <c r="B364" s="7">
         <v>6</v>
       </c>
-      <c r="C364" s="155"/>
-      <c r="D364" s="172" t="s">
+      <c r="C364" s="171"/>
+      <c r="D364" s="152" t="s">
         <v>468</v>
       </c>
       <c r="E364" s="8" t="s">
@@ -13965,8 +14018,8 @@
       <c r="B365" s="7">
         <v>7</v>
       </c>
-      <c r="C365" s="155"/>
-      <c r="D365" s="173"/>
+      <c r="C365" s="171"/>
+      <c r="D365" s="153"/>
       <c r="E365" s="8" t="s">
         <v>470</v>
       </c>
@@ -13987,8 +14040,8 @@
       <c r="B366" s="7">
         <v>8</v>
       </c>
-      <c r="C366" s="155"/>
-      <c r="D366" s="173"/>
+      <c r="C366" s="171"/>
+      <c r="D366" s="153"/>
       <c r="E366" s="8" t="s">
         <v>471</v>
       </c>
@@ -14009,8 +14062,8 @@
       <c r="B367" s="7">
         <v>9</v>
       </c>
-      <c r="C367" s="155"/>
-      <c r="D367" s="173"/>
+      <c r="C367" s="171"/>
+      <c r="D367" s="153"/>
       <c r="E367" s="8" t="s">
         <v>472</v>
       </c>
@@ -14031,8 +14084,8 @@
       <c r="B368" s="7">
         <v>10</v>
       </c>
-      <c r="C368" s="155"/>
-      <c r="D368" s="173"/>
+      <c r="C368" s="171"/>
+      <c r="D368" s="153"/>
       <c r="E368" s="8" t="s">
         <v>473</v>
       </c>
@@ -14053,8 +14106,8 @@
       <c r="B369" s="7">
         <v>11</v>
       </c>
-      <c r="C369" s="155"/>
-      <c r="D369" s="173"/>
+      <c r="C369" s="171"/>
+      <c r="D369" s="153"/>
       <c r="E369" s="8" t="s">
         <v>474</v>
       </c>
@@ -14075,8 +14128,8 @@
       <c r="B370" s="7">
         <v>12</v>
       </c>
-      <c r="C370" s="155"/>
-      <c r="D370" s="173"/>
+      <c r="C370" s="171"/>
+      <c r="D370" s="153"/>
       <c r="E370" s="8" t="s">
         <v>475</v>
       </c>
@@ -14097,8 +14150,8 @@
       <c r="B371" s="7">
         <v>13</v>
       </c>
-      <c r="C371" s="155"/>
-      <c r="D371" s="174"/>
+      <c r="C371" s="171"/>
+      <c r="D371" s="154"/>
       <c r="E371" s="8" t="s">
         <v>476</v>
       </c>
@@ -14119,8 +14172,8 @@
       <c r="B372" s="7">
         <v>14</v>
       </c>
-      <c r="C372" s="155"/>
-      <c r="D372" s="172" t="s">
+      <c r="C372" s="171"/>
+      <c r="D372" s="152" t="s">
         <v>477</v>
       </c>
       <c r="E372" s="8" t="s">
@@ -14143,8 +14196,8 @@
       <c r="B373" s="7">
         <v>15</v>
       </c>
-      <c r="C373" s="155"/>
-      <c r="D373" s="173"/>
+      <c r="C373" s="171"/>
+      <c r="D373" s="153"/>
       <c r="E373" s="11" t="s">
         <v>479</v>
       </c>
@@ -14165,8 +14218,8 @@
       <c r="B374" s="7">
         <v>16</v>
       </c>
-      <c r="C374" s="155"/>
-      <c r="D374" s="173"/>
+      <c r="C374" s="171"/>
+      <c r="D374" s="153"/>
       <c r="E374" s="8" t="s">
         <v>480</v>
       </c>
@@ -14187,8 +14240,8 @@
       <c r="B375" s="7">
         <v>17</v>
       </c>
-      <c r="C375" s="155"/>
-      <c r="D375" s="174"/>
+      <c r="C375" s="171"/>
+      <c r="D375" s="154"/>
       <c r="E375" s="8" t="s">
         <v>481</v>
       </c>
@@ -14209,8 +14262,8 @@
       <c r="B376" s="7">
         <v>18</v>
       </c>
-      <c r="C376" s="155"/>
-      <c r="D376" s="172" t="s">
+      <c r="C376" s="171"/>
+      <c r="D376" s="152" t="s">
         <v>482</v>
       </c>
       <c r="E376" s="8" t="s">
@@ -14233,8 +14286,8 @@
       <c r="B377" s="7">
         <v>19</v>
       </c>
-      <c r="C377" s="155"/>
-      <c r="D377" s="173"/>
+      <c r="C377" s="171"/>
+      <c r="D377" s="153"/>
       <c r="E377" s="8" t="s">
         <v>484</v>
       </c>
@@ -14255,8 +14308,8 @@
       <c r="B378" s="7">
         <v>20</v>
       </c>
-      <c r="C378" s="155"/>
-      <c r="D378" s="173"/>
+      <c r="C378" s="171"/>
+      <c r="D378" s="153"/>
       <c r="E378" s="8" t="s">
         <v>485</v>
       </c>
@@ -14277,8 +14330,8 @@
       <c r="B379" s="7">
         <v>21</v>
       </c>
-      <c r="C379" s="155"/>
-      <c r="D379" s="173"/>
+      <c r="C379" s="171"/>
+      <c r="D379" s="153"/>
       <c r="E379" s="8" t="s">
         <v>486</v>
       </c>
@@ -14299,8 +14352,8 @@
       <c r="B380" s="24">
         <v>22</v>
       </c>
-      <c r="C380" s="156"/>
-      <c r="D380" s="174"/>
+      <c r="C380" s="172"/>
+      <c r="D380" s="154"/>
       <c r="E380" s="17" t="s">
         <v>487</v>
       </c>
@@ -14321,10 +14374,10 @@
       <c r="B381" s="7">
         <v>1</v>
       </c>
-      <c r="C381" s="157" t="s">
+      <c r="C381" s="161" t="s">
         <v>488</v>
       </c>
-      <c r="D381" s="172" t="s">
+      <c r="D381" s="152" t="s">
         <v>489</v>
       </c>
       <c r="E381" s="8" t="s">
@@ -14347,8 +14400,8 @@
       <c r="B382" s="7">
         <v>2</v>
       </c>
-      <c r="C382" s="158"/>
-      <c r="D382" s="173"/>
+      <c r="C382" s="162"/>
+      <c r="D382" s="153"/>
       <c r="E382" s="8" t="s">
         <v>491</v>
       </c>
@@ -14369,8 +14422,8 @@
       <c r="B383" s="7">
         <v>3</v>
       </c>
-      <c r="C383" s="158"/>
-      <c r="D383" s="173"/>
+      <c r="C383" s="162"/>
+      <c r="D383" s="153"/>
       <c r="E383" s="8" t="s">
         <v>492</v>
       </c>
@@ -14391,8 +14444,8 @@
       <c r="B384" s="7">
         <v>4</v>
       </c>
-      <c r="C384" s="158"/>
-      <c r="D384" s="173"/>
+      <c r="C384" s="162"/>
+      <c r="D384" s="153"/>
       <c r="E384" s="8" t="s">
         <v>493</v>
       </c>
@@ -14413,8 +14466,8 @@
       <c r="B385" s="7">
         <v>5</v>
       </c>
-      <c r="C385" s="158"/>
-      <c r="D385" s="173"/>
+      <c r="C385" s="162"/>
+      <c r="D385" s="153"/>
       <c r="E385" s="8" t="s">
         <v>494</v>
       </c>
@@ -14435,8 +14488,8 @@
       <c r="B386" s="7">
         <v>6</v>
       </c>
-      <c r="C386" s="158"/>
-      <c r="D386" s="174"/>
+      <c r="C386" s="162"/>
+      <c r="D386" s="154"/>
       <c r="E386" s="8" t="s">
         <v>495</v>
       </c>
@@ -14457,8 +14510,8 @@
       <c r="B387" s="7">
         <v>7</v>
       </c>
-      <c r="C387" s="158"/>
-      <c r="D387" s="172" t="s">
+      <c r="C387" s="162"/>
+      <c r="D387" s="152" t="s">
         <v>496</v>
       </c>
       <c r="E387" s="8" t="s">
@@ -14481,8 +14534,8 @@
       <c r="B388" s="7">
         <v>8</v>
       </c>
-      <c r="C388" s="158"/>
-      <c r="D388" s="173"/>
+      <c r="C388" s="162"/>
+      <c r="D388" s="153"/>
       <c r="E388" s="8" t="s">
         <v>498</v>
       </c>
@@ -14503,8 +14556,8 @@
       <c r="B389" s="7">
         <v>9</v>
       </c>
-      <c r="C389" s="158"/>
-      <c r="D389" s="173"/>
+      <c r="C389" s="162"/>
+      <c r="D389" s="153"/>
       <c r="E389" s="8" t="s">
         <v>499</v>
       </c>
@@ -14525,8 +14578,8 @@
       <c r="B390" s="7">
         <v>10</v>
       </c>
-      <c r="C390" s="158"/>
-      <c r="D390" s="173"/>
+      <c r="C390" s="162"/>
+      <c r="D390" s="153"/>
       <c r="E390" s="8" t="s">
         <v>500</v>
       </c>
@@ -14547,8 +14600,8 @@
       <c r="B391" s="7">
         <v>11</v>
       </c>
-      <c r="C391" s="158"/>
-      <c r="D391" s="173"/>
+      <c r="C391" s="162"/>
+      <c r="D391" s="153"/>
       <c r="E391" s="8" t="s">
         <v>501</v>
       </c>
@@ -14569,8 +14622,8 @@
       <c r="B392" s="7">
         <v>12</v>
       </c>
-      <c r="C392" s="158"/>
-      <c r="D392" s="173"/>
+      <c r="C392" s="162"/>
+      <c r="D392" s="153"/>
       <c r="E392" s="8" t="s">
         <v>502</v>
       </c>
@@ -14591,8 +14644,8 @@
       <c r="B393" s="7">
         <v>13</v>
       </c>
-      <c r="C393" s="158"/>
-      <c r="D393" s="173"/>
+      <c r="C393" s="162"/>
+      <c r="D393" s="153"/>
       <c r="E393" s="8" t="s">
         <v>503</v>
       </c>
@@ -14613,8 +14666,8 @@
       <c r="B394" s="7">
         <v>14</v>
       </c>
-      <c r="C394" s="158"/>
-      <c r="D394" s="173"/>
+      <c r="C394" s="162"/>
+      <c r="D394" s="153"/>
       <c r="E394" s="8" t="s">
         <v>504</v>
       </c>
@@ -14635,8 +14688,8 @@
       <c r="B395" s="7">
         <v>15</v>
       </c>
-      <c r="C395" s="158"/>
-      <c r="D395" s="173"/>
+      <c r="C395" s="162"/>
+      <c r="D395" s="153"/>
       <c r="E395" s="8" t="s">
         <v>505</v>
       </c>
@@ -14657,8 +14710,8 @@
       <c r="B396" s="7">
         <v>16</v>
       </c>
-      <c r="C396" s="158"/>
-      <c r="D396" s="174"/>
+      <c r="C396" s="162"/>
+      <c r="D396" s="154"/>
       <c r="E396" s="8" t="s">
         <v>506</v>
       </c>
@@ -14679,8 +14732,8 @@
       <c r="B397" s="7">
         <v>17</v>
       </c>
-      <c r="C397" s="158"/>
-      <c r="D397" s="172" t="s">
+      <c r="C397" s="162"/>
+      <c r="D397" s="152" t="s">
         <v>507</v>
       </c>
       <c r="E397" s="8" t="s">
@@ -14703,8 +14756,8 @@
       <c r="B398" s="7">
         <v>18</v>
       </c>
-      <c r="C398" s="158"/>
-      <c r="D398" s="173"/>
+      <c r="C398" s="162"/>
+      <c r="D398" s="153"/>
       <c r="E398" s="8" t="s">
         <v>509</v>
       </c>
@@ -14725,8 +14778,8 @@
       <c r="B399" s="7">
         <v>19</v>
       </c>
-      <c r="C399" s="158"/>
-      <c r="D399" s="174"/>
+      <c r="C399" s="162"/>
+      <c r="D399" s="154"/>
       <c r="E399" s="8" t="s">
         <v>510</v>
       </c>
@@ -14747,8 +14800,8 @@
       <c r="B400" s="7">
         <v>20</v>
       </c>
-      <c r="C400" s="158"/>
-      <c r="D400" s="172" t="s">
+      <c r="C400" s="162"/>
+      <c r="D400" s="152" t="s">
         <v>511</v>
       </c>
       <c r="E400" s="8" t="s">
@@ -14771,8 +14824,8 @@
       <c r="B401" s="7">
         <v>21</v>
       </c>
-      <c r="C401" s="158"/>
-      <c r="D401" s="173"/>
+      <c r="C401" s="162"/>
+      <c r="D401" s="153"/>
       <c r="E401" s="8" t="s">
         <v>513</v>
       </c>
@@ -14793,8 +14846,8 @@
       <c r="B402" s="7">
         <v>22</v>
       </c>
-      <c r="C402" s="158"/>
-      <c r="D402" s="173"/>
+      <c r="C402" s="162"/>
+      <c r="D402" s="153"/>
       <c r="E402" s="8" t="s">
         <v>514</v>
       </c>
@@ -14815,8 +14868,8 @@
       <c r="B403" s="7">
         <v>23</v>
       </c>
-      <c r="C403" s="158"/>
-      <c r="D403" s="173"/>
+      <c r="C403" s="162"/>
+      <c r="D403" s="153"/>
       <c r="E403" s="8" t="s">
         <v>515</v>
       </c>
@@ -14837,8 +14890,8 @@
       <c r="B404" s="7">
         <v>24</v>
       </c>
-      <c r="C404" s="158"/>
-      <c r="D404" s="174"/>
+      <c r="C404" s="162"/>
+      <c r="D404" s="154"/>
       <c r="E404" s="8" t="s">
         <v>516</v>
       </c>
@@ -14859,8 +14912,8 @@
       <c r="B405" s="7">
         <v>25</v>
       </c>
-      <c r="C405" s="158"/>
-      <c r="D405" s="172" t="s">
+      <c r="C405" s="162"/>
+      <c r="D405" s="152" t="s">
         <v>517</v>
       </c>
       <c r="E405" s="8" t="s">
@@ -14883,8 +14936,8 @@
       <c r="B406" s="7">
         <v>26</v>
       </c>
-      <c r="C406" s="158"/>
-      <c r="D406" s="173"/>
+      <c r="C406" s="162"/>
+      <c r="D406" s="153"/>
       <c r="E406" s="8" t="s">
         <v>519</v>
       </c>
@@ -14905,8 +14958,8 @@
       <c r="B407" s="7">
         <v>27</v>
       </c>
-      <c r="C407" s="158"/>
-      <c r="D407" s="173"/>
+      <c r="C407" s="162"/>
+      <c r="D407" s="153"/>
       <c r="E407" s="8" t="s">
         <v>520</v>
       </c>
@@ -14927,8 +14980,8 @@
       <c r="B408" s="7">
         <v>28</v>
       </c>
-      <c r="C408" s="158"/>
-      <c r="D408" s="173"/>
+      <c r="C408" s="162"/>
+      <c r="D408" s="153"/>
       <c r="E408" s="8" t="s">
         <v>521</v>
       </c>
@@ -14949,8 +15002,8 @@
       <c r="B409" s="7">
         <v>29</v>
       </c>
-      <c r="C409" s="158"/>
-      <c r="D409" s="173"/>
+      <c r="C409" s="162"/>
+      <c r="D409" s="153"/>
       <c r="E409" s="8" t="s">
         <v>522</v>
       </c>
@@ -14971,8 +15024,8 @@
       <c r="B410" s="7">
         <v>30</v>
       </c>
-      <c r="C410" s="158"/>
-      <c r="D410" s="173"/>
+      <c r="C410" s="162"/>
+      <c r="D410" s="153"/>
       <c r="E410" s="8" t="s">
         <v>523</v>
       </c>
@@ -14993,8 +15046,8 @@
       <c r="B411" s="7">
         <v>31</v>
       </c>
-      <c r="C411" s="158"/>
-      <c r="D411" s="173"/>
+      <c r="C411" s="162"/>
+      <c r="D411" s="153"/>
       <c r="E411" s="8" t="s">
         <v>524</v>
       </c>
@@ -15015,8 +15068,8 @@
       <c r="B412" s="7">
         <v>32</v>
       </c>
-      <c r="C412" s="158"/>
-      <c r="D412" s="173"/>
+      <c r="C412" s="162"/>
+      <c r="D412" s="153"/>
       <c r="E412" s="8" t="s">
         <v>525</v>
       </c>
@@ -15037,8 +15090,8 @@
       <c r="B413" s="7">
         <v>33</v>
       </c>
-      <c r="C413" s="158"/>
-      <c r="D413" s="173"/>
+      <c r="C413" s="162"/>
+      <c r="D413" s="153"/>
       <c r="E413" s="8" t="s">
         <v>526</v>
       </c>
@@ -15059,8 +15112,8 @@
       <c r="B414" s="7">
         <v>34</v>
       </c>
-      <c r="C414" s="158"/>
-      <c r="D414" s="173"/>
+      <c r="C414" s="162"/>
+      <c r="D414" s="153"/>
       <c r="E414" s="8" t="s">
         <v>527</v>
       </c>
@@ -15081,8 +15134,8 @@
       <c r="B415" s="7">
         <v>35</v>
       </c>
-      <c r="C415" s="158"/>
-      <c r="D415" s="173"/>
+      <c r="C415" s="162"/>
+      <c r="D415" s="153"/>
       <c r="E415" s="8" t="s">
         <v>528</v>
       </c>
@@ -15103,8 +15156,8 @@
       <c r="B416" s="7">
         <v>36</v>
       </c>
-      <c r="C416" s="158"/>
-      <c r="D416" s="174"/>
+      <c r="C416" s="162"/>
+      <c r="D416" s="154"/>
       <c r="E416" s="8" t="s">
         <v>529</v>
       </c>
@@ -15125,8 +15178,8 @@
       <c r="B417" s="7">
         <v>37</v>
       </c>
-      <c r="C417" s="158"/>
-      <c r="D417" s="172" t="s">
+      <c r="C417" s="162"/>
+      <c r="D417" s="152" t="s">
         <v>530</v>
       </c>
       <c r="E417" s="8" t="s">
@@ -15149,8 +15202,8 @@
       <c r="B418" s="7">
         <v>38</v>
       </c>
-      <c r="C418" s="158"/>
-      <c r="D418" s="173"/>
+      <c r="C418" s="162"/>
+      <c r="D418" s="153"/>
       <c r="E418" s="8" t="s">
         <v>532</v>
       </c>
@@ -15171,8 +15224,8 @@
       <c r="B419" s="7">
         <v>39</v>
       </c>
-      <c r="C419" s="158"/>
-      <c r="D419" s="174"/>
+      <c r="C419" s="162"/>
+      <c r="D419" s="154"/>
       <c r="E419" s="8" t="s">
         <v>533</v>
       </c>
@@ -15193,8 +15246,8 @@
       <c r="B420" s="7">
         <v>40</v>
       </c>
-      <c r="C420" s="158"/>
-      <c r="D420" s="172" t="s">
+      <c r="C420" s="162"/>
+      <c r="D420" s="152" t="s">
         <v>534</v>
       </c>
       <c r="E420" s="8" t="s">
@@ -15217,8 +15270,8 @@
       <c r="B421" s="7">
         <v>41</v>
       </c>
-      <c r="C421" s="158"/>
-      <c r="D421" s="173"/>
+      <c r="C421" s="162"/>
+      <c r="D421" s="153"/>
       <c r="E421" s="8" t="s">
         <v>536</v>
       </c>
@@ -15239,8 +15292,8 @@
       <c r="B422" s="7">
         <v>42</v>
       </c>
-      <c r="C422" s="158"/>
-      <c r="D422" s="173"/>
+      <c r="C422" s="162"/>
+      <c r="D422" s="153"/>
       <c r="E422" s="8" t="s">
         <v>537</v>
       </c>
@@ -15261,8 +15314,8 @@
       <c r="B423" s="7">
         <v>43</v>
       </c>
-      <c r="C423" s="158"/>
-      <c r="D423" s="173"/>
+      <c r="C423" s="162"/>
+      <c r="D423" s="153"/>
       <c r="E423" s="8" t="s">
         <v>538</v>
       </c>
@@ -15283,8 +15336,8 @@
       <c r="B424" s="7">
         <v>44</v>
       </c>
-      <c r="C424" s="158"/>
-      <c r="D424" s="173"/>
+      <c r="C424" s="162"/>
+      <c r="D424" s="153"/>
       <c r="E424" s="8" t="s">
         <v>539</v>
       </c>
@@ -15305,8 +15358,8 @@
       <c r="B425" s="7">
         <v>45</v>
       </c>
-      <c r="C425" s="158"/>
-      <c r="D425" s="173"/>
+      <c r="C425" s="162"/>
+      <c r="D425" s="153"/>
       <c r="E425" s="8" t="s">
         <v>540</v>
       </c>
@@ -15327,8 +15380,8 @@
       <c r="B426" s="7">
         <v>46</v>
       </c>
-      <c r="C426" s="158"/>
-      <c r="D426" s="174"/>
+      <c r="C426" s="162"/>
+      <c r="D426" s="154"/>
       <c r="E426" s="8" t="s">
         <v>541</v>
       </c>
@@ -15349,8 +15402,8 @@
       <c r="B427" s="7">
         <v>47</v>
       </c>
-      <c r="C427" s="158"/>
-      <c r="D427" s="172" t="s">
+      <c r="C427" s="162"/>
+      <c r="D427" s="152" t="s">
         <v>542</v>
       </c>
       <c r="E427" s="8" t="s">
@@ -15371,8 +15424,8 @@
       <c r="B428" s="7">
         <v>48</v>
       </c>
-      <c r="C428" s="158"/>
-      <c r="D428" s="173"/>
+      <c r="C428" s="162"/>
+      <c r="D428" s="153"/>
       <c r="E428" s="8" t="s">
         <v>544</v>
       </c>
@@ -15393,8 +15446,8 @@
       <c r="B429" s="7">
         <v>49</v>
       </c>
-      <c r="C429" s="158"/>
-      <c r="D429" s="173"/>
+      <c r="C429" s="162"/>
+      <c r="D429" s="153"/>
       <c r="E429" s="8" t="s">
         <v>545</v>
       </c>
@@ -15415,8 +15468,8 @@
       <c r="B430" s="7">
         <v>50</v>
       </c>
-      <c r="C430" s="158"/>
-      <c r="D430" s="174"/>
+      <c r="C430" s="162"/>
+      <c r="D430" s="154"/>
       <c r="E430" s="8" t="s">
         <v>546</v>
       </c>
@@ -15437,8 +15490,8 @@
       <c r="B431" s="7">
         <v>51</v>
       </c>
-      <c r="C431" s="158"/>
-      <c r="D431" s="172" t="s">
+      <c r="C431" s="162"/>
+      <c r="D431" s="152" t="s">
         <v>547</v>
       </c>
       <c r="E431" s="8" t="s">
@@ -15461,8 +15514,8 @@
       <c r="B432" s="7">
         <v>52</v>
       </c>
-      <c r="C432" s="158"/>
-      <c r="D432" s="173"/>
+      <c r="C432" s="162"/>
+      <c r="D432" s="153"/>
       <c r="E432" s="8" t="s">
         <v>549</v>
       </c>
@@ -15483,8 +15536,8 @@
       <c r="B433" s="7">
         <v>53</v>
       </c>
-      <c r="C433" s="158"/>
-      <c r="D433" s="173"/>
+      <c r="C433" s="162"/>
+      <c r="D433" s="153"/>
       <c r="E433" s="8" t="s">
         <v>550</v>
       </c>
@@ -15505,8 +15558,8 @@
       <c r="B434" s="7">
         <v>54</v>
       </c>
-      <c r="C434" s="158"/>
-      <c r="D434" s="173"/>
+      <c r="C434" s="162"/>
+      <c r="D434" s="153"/>
       <c r="E434" s="8" t="s">
         <v>551</v>
       </c>
@@ -15527,8 +15580,8 @@
       <c r="B435" s="7">
         <v>55</v>
       </c>
-      <c r="C435" s="159"/>
-      <c r="D435" s="174"/>
+      <c r="C435" s="163"/>
+      <c r="D435" s="154"/>
       <c r="E435" s="8" t="s">
         <v>552</v>
       </c>
@@ -15543,18 +15596,18 @@
       <c r="J435" s="11"/>
     </row>
     <row r="436" spans="1:10" ht="13.8">
-      <c r="A436" s="178" t="s">
+      <c r="A436" s="194" t="s">
         <v>553</v>
       </c>
-      <c r="B436" s="179"/>
-      <c r="C436" s="179"/>
-      <c r="D436" s="179"/>
-      <c r="E436" s="179"/>
-      <c r="F436" s="179"/>
-      <c r="G436" s="179"/>
-      <c r="H436" s="179"/>
-      <c r="I436" s="179"/>
-      <c r="J436" s="180"/>
+      <c r="B436" s="195"/>
+      <c r="C436" s="195"/>
+      <c r="D436" s="195"/>
+      <c r="E436" s="195"/>
+      <c r="F436" s="195"/>
+      <c r="G436" s="195"/>
+      <c r="H436" s="195"/>
+      <c r="I436" s="195"/>
+      <c r="J436" s="196"/>
     </row>
     <row r="437" spans="1:10" ht="13.8">
       <c r="A437" s="6">
@@ -15563,10 +15616,10 @@
       <c r="B437" s="7">
         <v>1</v>
       </c>
-      <c r="C437" s="160" t="s">
+      <c r="C437" s="164" t="s">
         <v>554</v>
       </c>
-      <c r="D437" s="172" t="s">
+      <c r="D437" s="152" t="s">
         <v>555</v>
       </c>
       <c r="E437" s="29" t="s">
@@ -15589,8 +15642,8 @@
       <c r="B438" s="7">
         <v>2</v>
       </c>
-      <c r="C438" s="161"/>
-      <c r="D438" s="173"/>
+      <c r="C438" s="165"/>
+      <c r="D438" s="153"/>
       <c r="E438" s="8" t="s">
         <v>557</v>
       </c>
@@ -15609,8 +15662,8 @@
       <c r="B439" s="7">
         <v>3</v>
       </c>
-      <c r="C439" s="161"/>
-      <c r="D439" s="173"/>
+      <c r="C439" s="165"/>
+      <c r="D439" s="153"/>
       <c r="E439" s="8" t="s">
         <v>558</v>
       </c>
@@ -15631,8 +15684,8 @@
       <c r="B440" s="7">
         <v>4</v>
       </c>
-      <c r="C440" s="161"/>
-      <c r="D440" s="173"/>
+      <c r="C440" s="165"/>
+      <c r="D440" s="153"/>
       <c r="E440" s="29" t="s">
         <v>559</v>
       </c>
@@ -15653,8 +15706,8 @@
       <c r="B441" s="7">
         <v>5</v>
       </c>
-      <c r="C441" s="161"/>
-      <c r="D441" s="174"/>
+      <c r="C441" s="165"/>
+      <c r="D441" s="154"/>
       <c r="E441" s="8" t="s">
         <v>560</v>
       </c>
@@ -15675,8 +15728,8 @@
       <c r="B442" s="7">
         <v>6</v>
       </c>
-      <c r="C442" s="161"/>
-      <c r="D442" s="172" t="s">
+      <c r="C442" s="165"/>
+      <c r="D442" s="152" t="s">
         <v>561</v>
       </c>
       <c r="E442" s="29" t="s">
@@ -15699,8 +15752,8 @@
       <c r="B443" s="7">
         <v>7</v>
       </c>
-      <c r="C443" s="161"/>
-      <c r="D443" s="173"/>
+      <c r="C443" s="165"/>
+      <c r="D443" s="153"/>
       <c r="E443" s="8" t="s">
         <v>563</v>
       </c>
@@ -15721,8 +15774,8 @@
       <c r="B444" s="7">
         <v>8</v>
       </c>
-      <c r="C444" s="161"/>
-      <c r="D444" s="173"/>
+      <c r="C444" s="165"/>
+      <c r="D444" s="153"/>
       <c r="E444" s="29" t="s">
         <v>564</v>
       </c>
@@ -15743,8 +15796,8 @@
       <c r="B445" s="7">
         <v>9</v>
       </c>
-      <c r="C445" s="161"/>
-      <c r="D445" s="174"/>
+      <c r="C445" s="165"/>
+      <c r="D445" s="154"/>
       <c r="E445" s="8" t="s">
         <v>565</v>
       </c>
@@ -15765,8 +15818,8 @@
       <c r="B446" s="7">
         <v>10</v>
       </c>
-      <c r="C446" s="161"/>
-      <c r="D446" s="172" t="s">
+      <c r="C446" s="165"/>
+      <c r="D446" s="152" t="s">
         <v>566</v>
       </c>
       <c r="E446" s="8" t="s">
@@ -15789,8 +15842,8 @@
       <c r="B447" s="7">
         <v>11</v>
       </c>
-      <c r="C447" s="161"/>
-      <c r="D447" s="173"/>
+      <c r="C447" s="165"/>
+      <c r="D447" s="153"/>
       <c r="E447" s="8" t="s">
         <v>568</v>
       </c>
@@ -15811,8 +15864,8 @@
       <c r="B448" s="7">
         <v>12</v>
       </c>
-      <c r="C448" s="161"/>
-      <c r="D448" s="174"/>
+      <c r="C448" s="165"/>
+      <c r="D448" s="154"/>
       <c r="E448" s="8" t="s">
         <v>569</v>
       </c>
@@ -15833,8 +15886,8 @@
       <c r="B449" s="7">
         <v>13</v>
       </c>
-      <c r="C449" s="161"/>
-      <c r="D449" s="172" t="s">
+      <c r="C449" s="165"/>
+      <c r="D449" s="152" t="s">
         <v>570</v>
       </c>
       <c r="E449" s="8" t="s">
@@ -15857,8 +15910,8 @@
       <c r="B450" s="7">
         <v>14</v>
       </c>
-      <c r="C450" s="161"/>
-      <c r="D450" s="173"/>
+      <c r="C450" s="165"/>
+      <c r="D450" s="153"/>
       <c r="E450" s="29" t="s">
         <v>572</v>
       </c>
@@ -15879,8 +15932,8 @@
       <c r="B451" s="7">
         <v>15</v>
       </c>
-      <c r="C451" s="161"/>
-      <c r="D451" s="173"/>
+      <c r="C451" s="165"/>
+      <c r="D451" s="153"/>
       <c r="E451" s="8" t="s">
         <v>573</v>
       </c>
@@ -15901,8 +15954,8 @@
       <c r="B452" s="7">
         <v>16</v>
       </c>
-      <c r="C452" s="161"/>
-      <c r="D452" s="174"/>
+      <c r="C452" s="165"/>
+      <c r="D452" s="154"/>
       <c r="E452" s="8" t="s">
         <v>574</v>
       </c>
@@ -15923,8 +15976,8 @@
       <c r="B453" s="7">
         <v>17</v>
       </c>
-      <c r="C453" s="161"/>
-      <c r="D453" s="172" t="s">
+      <c r="C453" s="165"/>
+      <c r="D453" s="152" t="s">
         <v>575</v>
       </c>
       <c r="E453" s="8" t="s">
@@ -15947,8 +16000,8 @@
       <c r="B454" s="7">
         <v>18</v>
       </c>
-      <c r="C454" s="161"/>
-      <c r="D454" s="173"/>
+      <c r="C454" s="165"/>
+      <c r="D454" s="153"/>
       <c r="E454" s="8" t="s">
         <v>577</v>
       </c>
@@ -15969,8 +16022,8 @@
       <c r="B455" s="7">
         <v>19</v>
       </c>
-      <c r="C455" s="161"/>
-      <c r="D455" s="173"/>
+      <c r="C455" s="165"/>
+      <c r="D455" s="153"/>
       <c r="E455" s="8" t="s">
         <v>578</v>
       </c>
@@ -15991,8 +16044,8 @@
       <c r="B456" s="7">
         <v>20</v>
       </c>
-      <c r="C456" s="161"/>
-      <c r="D456" s="173"/>
+      <c r="C456" s="165"/>
+      <c r="D456" s="153"/>
       <c r="E456" s="39" t="s">
         <v>579</v>
       </c>
@@ -16013,8 +16066,8 @@
       <c r="B457" s="7">
         <v>21</v>
       </c>
-      <c r="C457" s="161"/>
-      <c r="D457" s="173"/>
+      <c r="C457" s="165"/>
+      <c r="D457" s="153"/>
       <c r="E457" s="8" t="s">
         <v>580</v>
       </c>
@@ -16035,8 +16088,8 @@
       <c r="B458" s="24">
         <v>22</v>
       </c>
-      <c r="C458" s="162"/>
-      <c r="D458" s="174"/>
+      <c r="C458" s="166"/>
+      <c r="D458" s="154"/>
       <c r="E458" s="17" t="s">
         <v>581</v>
       </c>
@@ -16058,10 +16111,10 @@
       <c r="B459" s="7">
         <v>1</v>
       </c>
-      <c r="C459" s="151" t="s">
+      <c r="C459" s="167" t="s">
         <v>582</v>
       </c>
-      <c r="D459" s="172" t="s">
+      <c r="D459" s="152" t="s">
         <v>583</v>
       </c>
       <c r="E459" s="8" t="s">
@@ -16084,8 +16137,8 @@
       <c r="B460" s="7">
         <v>2</v>
       </c>
-      <c r="C460" s="152"/>
-      <c r="D460" s="173"/>
+      <c r="C460" s="168"/>
+      <c r="D460" s="153"/>
       <c r="E460" s="8" t="s">
         <v>584</v>
       </c>
@@ -16106,8 +16159,8 @@
       <c r="B461" s="7">
         <v>3</v>
       </c>
-      <c r="C461" s="152"/>
-      <c r="D461" s="173"/>
+      <c r="C461" s="168"/>
+      <c r="D461" s="153"/>
       <c r="E461" s="8" t="s">
         <v>585</v>
       </c>
@@ -16128,8 +16181,8 @@
       <c r="B462" s="7">
         <v>4</v>
       </c>
-      <c r="C462" s="152"/>
-      <c r="D462" s="173"/>
+      <c r="C462" s="168"/>
+      <c r="D462" s="153"/>
       <c r="E462" s="8" t="s">
         <v>586</v>
       </c>
@@ -16150,8 +16203,8 @@
       <c r="B463" s="7">
         <v>5</v>
       </c>
-      <c r="C463" s="152"/>
-      <c r="D463" s="173"/>
+      <c r="C463" s="168"/>
+      <c r="D463" s="153"/>
       <c r="E463" s="8" t="s">
         <v>587</v>
       </c>
@@ -16172,8 +16225,8 @@
       <c r="B464" s="7">
         <v>6</v>
       </c>
-      <c r="C464" s="152"/>
-      <c r="D464" s="173"/>
+      <c r="C464" s="168"/>
+      <c r="D464" s="153"/>
       <c r="E464" s="8" t="s">
         <v>588</v>
       </c>
@@ -16194,8 +16247,8 @@
       <c r="B465" s="7">
         <v>7</v>
       </c>
-      <c r="C465" s="152"/>
-      <c r="D465" s="173"/>
+      <c r="C465" s="168"/>
+      <c r="D465" s="153"/>
       <c r="E465" s="8" t="s">
         <v>589</v>
       </c>
@@ -16216,8 +16269,8 @@
       <c r="B466" s="7">
         <v>8</v>
       </c>
-      <c r="C466" s="152"/>
-      <c r="D466" s="174"/>
+      <c r="C466" s="168"/>
+      <c r="D466" s="154"/>
       <c r="E466" s="8" t="s">
         <v>590</v>
       </c>
@@ -16238,8 +16291,8 @@
       <c r="B467" s="7">
         <v>9</v>
       </c>
-      <c r="C467" s="152"/>
-      <c r="D467" s="172" t="s">
+      <c r="C467" s="168"/>
+      <c r="D467" s="152" t="s">
         <v>591</v>
       </c>
       <c r="E467" s="8" t="s">
@@ -16262,8 +16315,8 @@
       <c r="B468" s="7">
         <v>10</v>
       </c>
-      <c r="C468" s="152"/>
-      <c r="D468" s="173"/>
+      <c r="C468" s="168"/>
+      <c r="D468" s="153"/>
       <c r="E468" s="8" t="s">
         <v>593</v>
       </c>
@@ -16284,8 +16337,8 @@
       <c r="B469" s="7">
         <v>11</v>
       </c>
-      <c r="C469" s="152"/>
-      <c r="D469" s="173"/>
+      <c r="C469" s="168"/>
+      <c r="D469" s="153"/>
       <c r="E469" s="8" t="s">
         <v>594</v>
       </c>
@@ -16306,8 +16359,8 @@
       <c r="B470" s="7">
         <v>12</v>
       </c>
-      <c r="C470" s="152"/>
-      <c r="D470" s="173"/>
+      <c r="C470" s="168"/>
+      <c r="D470" s="153"/>
       <c r="E470" s="8" t="s">
         <v>595</v>
       </c>
@@ -16328,8 +16381,8 @@
       <c r="B471" s="7">
         <v>13</v>
       </c>
-      <c r="C471" s="152"/>
-      <c r="D471" s="173"/>
+      <c r="C471" s="168"/>
+      <c r="D471" s="153"/>
       <c r="E471" s="8" t="s">
         <v>596</v>
       </c>
@@ -16350,8 +16403,8 @@
       <c r="B472" s="7">
         <v>14</v>
       </c>
-      <c r="C472" s="152"/>
-      <c r="D472" s="173"/>
+      <c r="C472" s="168"/>
+      <c r="D472" s="153"/>
       <c r="E472" s="8" t="s">
         <v>597</v>
       </c>
@@ -16372,8 +16425,8 @@
       <c r="B473" s="7">
         <v>15</v>
       </c>
-      <c r="C473" s="152"/>
-      <c r="D473" s="174"/>
+      <c r="C473" s="168"/>
+      <c r="D473" s="154"/>
       <c r="E473" s="8" t="s">
         <v>598</v>
       </c>
@@ -16394,8 +16447,8 @@
       <c r="B474" s="7">
         <v>16</v>
       </c>
-      <c r="C474" s="152"/>
-      <c r="D474" s="172" t="s">
+      <c r="C474" s="168"/>
+      <c r="D474" s="152" t="s">
         <v>599</v>
       </c>
       <c r="E474" s="8" t="s">
@@ -16418,8 +16471,8 @@
       <c r="B475" s="7">
         <v>17</v>
       </c>
-      <c r="C475" s="152"/>
-      <c r="D475" s="173"/>
+      <c r="C475" s="168"/>
+      <c r="D475" s="153"/>
       <c r="E475" s="8" t="s">
         <v>601</v>
       </c>
@@ -16440,8 +16493,8 @@
       <c r="B476" s="7">
         <v>18</v>
       </c>
-      <c r="C476" s="152"/>
-      <c r="D476" s="173"/>
+      <c r="C476" s="168"/>
+      <c r="D476" s="153"/>
       <c r="E476" s="8" t="s">
         <v>602</v>
       </c>
@@ -16462,8 +16515,8 @@
       <c r="B477" s="7">
         <v>19</v>
       </c>
-      <c r="C477" s="152"/>
-      <c r="D477" s="173"/>
+      <c r="C477" s="168"/>
+      <c r="D477" s="153"/>
       <c r="E477" s="8" t="s">
         <v>603</v>
       </c>
@@ -16484,8 +16537,8 @@
       <c r="B478" s="7">
         <v>20</v>
       </c>
-      <c r="C478" s="152"/>
-      <c r="D478" s="173"/>
+      <c r="C478" s="168"/>
+      <c r="D478" s="153"/>
       <c r="E478" s="8" t="s">
         <v>604</v>
       </c>
@@ -16506,8 +16559,8 @@
       <c r="B479" s="7">
         <v>21</v>
       </c>
-      <c r="C479" s="152"/>
-      <c r="D479" s="173"/>
+      <c r="C479" s="168"/>
+      <c r="D479" s="153"/>
       <c r="E479" s="8" t="s">
         <v>605</v>
       </c>
@@ -16528,8 +16581,8 @@
       <c r="B480" s="7">
         <v>22</v>
       </c>
-      <c r="C480" s="152"/>
-      <c r="D480" s="173"/>
+      <c r="C480" s="168"/>
+      <c r="D480" s="153"/>
       <c r="E480" s="8" t="s">
         <v>606</v>
       </c>
@@ -16550,8 +16603,8 @@
       <c r="B481" s="7">
         <v>23</v>
       </c>
-      <c r="C481" s="152"/>
-      <c r="D481" s="174"/>
+      <c r="C481" s="168"/>
+      <c r="D481" s="154"/>
       <c r="E481" s="8" t="s">
         <v>607</v>
       </c>
@@ -16572,8 +16625,8 @@
       <c r="B482" s="7">
         <v>24</v>
       </c>
-      <c r="C482" s="152"/>
-      <c r="D482" s="172" t="s">
+      <c r="C482" s="168"/>
+      <c r="D482" s="152" t="s">
         <v>608</v>
       </c>
       <c r="E482" s="8" t="s">
@@ -16596,8 +16649,8 @@
       <c r="B483" s="7">
         <v>25</v>
       </c>
-      <c r="C483" s="152"/>
-      <c r="D483" s="173"/>
+      <c r="C483" s="168"/>
+      <c r="D483" s="153"/>
       <c r="E483" s="8" t="s">
         <v>610</v>
       </c>
@@ -16618,8 +16671,8 @@
       <c r="B484" s="7">
         <v>26</v>
       </c>
-      <c r="C484" s="152"/>
-      <c r="D484" s="173"/>
+      <c r="C484" s="168"/>
+      <c r="D484" s="153"/>
       <c r="E484" s="8" t="s">
         <v>611</v>
       </c>
@@ -16640,8 +16693,8 @@
       <c r="B485" s="7">
         <v>27</v>
       </c>
-      <c r="C485" s="152"/>
-      <c r="D485" s="174"/>
+      <c r="C485" s="168"/>
+      <c r="D485" s="154"/>
       <c r="E485" s="8" t="s">
         <v>612</v>
       </c>
@@ -16662,8 +16715,8 @@
       <c r="B486" s="7">
         <v>28</v>
       </c>
-      <c r="C486" s="152"/>
-      <c r="D486" s="172" t="s">
+      <c r="C486" s="168"/>
+      <c r="D486" s="152" t="s">
         <v>613</v>
       </c>
       <c r="E486" s="8" t="s">
@@ -16686,8 +16739,8 @@
       <c r="B487" s="7">
         <v>29</v>
       </c>
-      <c r="C487" s="152"/>
-      <c r="D487" s="173"/>
+      <c r="C487" s="168"/>
+      <c r="D487" s="153"/>
       <c r="E487" s="8" t="s">
         <v>615</v>
       </c>
@@ -16708,8 +16761,8 @@
       <c r="B488" s="7">
         <v>30</v>
       </c>
-      <c r="C488" s="152"/>
-      <c r="D488" s="173"/>
+      <c r="C488" s="168"/>
+      <c r="D488" s="153"/>
       <c r="E488" s="8" t="s">
         <v>616</v>
       </c>
@@ -16730,8 +16783,8 @@
       <c r="B489" s="7">
         <v>31</v>
       </c>
-      <c r="C489" s="152"/>
-      <c r="D489" s="173"/>
+      <c r="C489" s="168"/>
+      <c r="D489" s="153"/>
       <c r="E489" s="8" t="s">
         <v>617</v>
       </c>
@@ -16752,8 +16805,8 @@
       <c r="B490" s="7">
         <v>32</v>
       </c>
-      <c r="C490" s="152"/>
-      <c r="D490" s="173"/>
+      <c r="C490" s="168"/>
+      <c r="D490" s="153"/>
       <c r="E490" s="8" t="s">
         <v>618</v>
       </c>
@@ -16774,8 +16827,8 @@
       <c r="B491" s="7">
         <v>33</v>
       </c>
-      <c r="C491" s="152"/>
-      <c r="D491" s="173"/>
+      <c r="C491" s="168"/>
+      <c r="D491" s="153"/>
       <c r="E491" s="8" t="s">
         <v>619</v>
       </c>
@@ -16796,8 +16849,8 @@
       <c r="B492" s="7">
         <v>34</v>
       </c>
-      <c r="C492" s="152"/>
-      <c r="D492" s="173"/>
+      <c r="C492" s="168"/>
+      <c r="D492" s="153"/>
       <c r="E492" s="8" t="s">
         <v>620</v>
       </c>
@@ -16818,8 +16871,8 @@
       <c r="B493" s="7">
         <v>35</v>
       </c>
-      <c r="C493" s="152"/>
-      <c r="D493" s="173"/>
+      <c r="C493" s="168"/>
+      <c r="D493" s="153"/>
       <c r="E493" s="8" t="s">
         <v>621</v>
       </c>
@@ -16840,8 +16893,8 @@
       <c r="B494" s="7">
         <v>36</v>
       </c>
-      <c r="C494" s="152"/>
-      <c r="D494" s="173"/>
+      <c r="C494" s="168"/>
+      <c r="D494" s="153"/>
       <c r="E494" s="8" t="s">
         <v>622</v>
       </c>
@@ -16862,8 +16915,8 @@
       <c r="B495" s="7">
         <v>37</v>
       </c>
-      <c r="C495" s="152"/>
-      <c r="D495" s="173"/>
+      <c r="C495" s="168"/>
+      <c r="D495" s="153"/>
       <c r="E495" s="8" t="s">
         <v>623</v>
       </c>
@@ -16884,8 +16937,8 @@
       <c r="B496" s="7">
         <v>38</v>
       </c>
-      <c r="C496" s="152"/>
-      <c r="D496" s="174"/>
+      <c r="C496" s="168"/>
+      <c r="D496" s="154"/>
       <c r="E496" s="8" t="s">
         <v>624</v>
       </c>
@@ -16906,8 +16959,8 @@
       <c r="B497" s="7">
         <v>39</v>
       </c>
-      <c r="C497" s="152"/>
-      <c r="D497" s="172" t="s">
+      <c r="C497" s="168"/>
+      <c r="D497" s="152" t="s">
         <v>625</v>
       </c>
       <c r="E497" s="8" t="s">
@@ -16930,8 +16983,8 @@
       <c r="B498" s="7">
         <v>40</v>
       </c>
-      <c r="C498" s="152"/>
-      <c r="D498" s="173"/>
+      <c r="C498" s="168"/>
+      <c r="D498" s="153"/>
       <c r="E498" s="8" t="s">
         <v>626</v>
       </c>
@@ -16952,8 +17005,8 @@
       <c r="B499" s="7">
         <v>41</v>
       </c>
-      <c r="C499" s="152"/>
-      <c r="D499" s="173"/>
+      <c r="C499" s="168"/>
+      <c r="D499" s="153"/>
       <c r="E499" s="8" t="s">
         <v>627</v>
       </c>
@@ -16974,8 +17027,8 @@
       <c r="B500" s="7">
         <v>42</v>
       </c>
-      <c r="C500" s="152"/>
-      <c r="D500" s="173"/>
+      <c r="C500" s="168"/>
+      <c r="D500" s="153"/>
       <c r="E500" s="8" t="s">
         <v>628</v>
       </c>
@@ -16996,8 +17049,8 @@
       <c r="B501" s="7">
         <v>43</v>
       </c>
-      <c r="C501" s="152"/>
-      <c r="D501" s="173"/>
+      <c r="C501" s="168"/>
+      <c r="D501" s="153"/>
       <c r="E501" s="8" t="s">
         <v>629</v>
       </c>
@@ -17018,8 +17071,8 @@
       <c r="B502" s="7">
         <v>44</v>
       </c>
-      <c r="C502" s="152"/>
-      <c r="D502" s="174"/>
+      <c r="C502" s="168"/>
+      <c r="D502" s="154"/>
       <c r="E502" s="8" t="s">
         <v>630</v>
       </c>
@@ -17040,8 +17093,8 @@
       <c r="B503" s="7">
         <v>45</v>
       </c>
-      <c r="C503" s="152"/>
-      <c r="D503" s="172" t="s">
+      <c r="C503" s="168"/>
+      <c r="D503" s="152" t="s">
         <v>631</v>
       </c>
       <c r="E503" s="8" t="s">
@@ -17064,8 +17117,8 @@
       <c r="B504" s="7">
         <v>46</v>
       </c>
-      <c r="C504" s="152"/>
-      <c r="D504" s="173"/>
+      <c r="C504" s="168"/>
+      <c r="D504" s="153"/>
       <c r="E504" s="8" t="s">
         <v>633</v>
       </c>
@@ -17086,8 +17139,8 @@
       <c r="B505" s="7">
         <v>47</v>
       </c>
-      <c r="C505" s="152"/>
-      <c r="D505" s="173"/>
+      <c r="C505" s="168"/>
+      <c r="D505" s="153"/>
       <c r="E505" s="8" t="s">
         <v>634</v>
       </c>
@@ -17108,8 +17161,8 @@
       <c r="B506" s="7">
         <v>48</v>
       </c>
-      <c r="C506" s="152"/>
-      <c r="D506" s="173"/>
+      <c r="C506" s="168"/>
+      <c r="D506" s="153"/>
       <c r="E506" s="8" t="s">
         <v>635</v>
       </c>
@@ -17130,8 +17183,8 @@
       <c r="B507" s="7">
         <v>49</v>
       </c>
-      <c r="C507" s="152"/>
-      <c r="D507" s="173"/>
+      <c r="C507" s="168"/>
+      <c r="D507" s="153"/>
       <c r="E507" s="8" t="s">
         <v>636</v>
       </c>
@@ -17152,8 +17205,8 @@
       <c r="B508" s="7">
         <v>50</v>
       </c>
-      <c r="C508" s="152"/>
-      <c r="D508" s="173"/>
+      <c r="C508" s="168"/>
+      <c r="D508" s="153"/>
       <c r="E508" s="8" t="s">
         <v>637</v>
       </c>
@@ -17174,8 +17227,8 @@
       <c r="B509" s="7">
         <v>51</v>
       </c>
-      <c r="C509" s="152"/>
-      <c r="D509" s="174"/>
+      <c r="C509" s="168"/>
+      <c r="D509" s="154"/>
       <c r="E509" s="8" t="s">
         <v>638</v>
       </c>
@@ -17196,8 +17249,8 @@
       <c r="B510" s="7">
         <v>52</v>
       </c>
-      <c r="C510" s="152"/>
-      <c r="D510" s="172" t="s">
+      <c r="C510" s="168"/>
+      <c r="D510" s="152" t="s">
         <v>639</v>
       </c>
       <c r="E510" s="8" t="s">
@@ -17220,8 +17273,8 @@
       <c r="B511" s="7">
         <v>53</v>
       </c>
-      <c r="C511" s="152"/>
-      <c r="D511" s="173"/>
+      <c r="C511" s="168"/>
+      <c r="D511" s="153"/>
       <c r="E511" s="8" t="s">
         <v>641</v>
       </c>
@@ -17242,8 +17295,8 @@
       <c r="B512" s="7">
         <v>54</v>
       </c>
-      <c r="C512" s="152"/>
-      <c r="D512" s="173"/>
+      <c r="C512" s="168"/>
+      <c r="D512" s="153"/>
       <c r="E512" s="8" t="s">
         <v>642</v>
       </c>
@@ -17264,8 +17317,8 @@
       <c r="B513" s="24">
         <v>55</v>
       </c>
-      <c r="C513" s="153"/>
-      <c r="D513" s="174"/>
+      <c r="C513" s="169"/>
+      <c r="D513" s="154"/>
       <c r="E513" s="17" t="s">
         <v>643</v>
       </c>
@@ -24199,47 +24252,66 @@
     </row>
   </sheetData>
   <mergeCells count="125">
-    <mergeCell ref="D26:D32"/>
-    <mergeCell ref="D33:D36"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="C4:C32"/>
-    <mergeCell ref="D4:D9"/>
-    <mergeCell ref="D10:D18"/>
-    <mergeCell ref="D19:D25"/>
-    <mergeCell ref="C33:C44"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="D40:D44"/>
-    <mergeCell ref="C107:C116"/>
-    <mergeCell ref="C117:C125"/>
-    <mergeCell ref="C127:C132"/>
-    <mergeCell ref="C134:C176"/>
-    <mergeCell ref="C177:C204"/>
-    <mergeCell ref="C205:C214"/>
-    <mergeCell ref="A106:J106"/>
-    <mergeCell ref="D107:D111"/>
-    <mergeCell ref="D112:D115"/>
-    <mergeCell ref="D117:D120"/>
-    <mergeCell ref="D121:D122"/>
-    <mergeCell ref="D123:D125"/>
-    <mergeCell ref="A126:J126"/>
-    <mergeCell ref="D127:D130"/>
-    <mergeCell ref="D131:D132"/>
-    <mergeCell ref="A133:J133"/>
-    <mergeCell ref="D210:D211"/>
-    <mergeCell ref="D212:D214"/>
-    <mergeCell ref="C45:C50"/>
-    <mergeCell ref="D45:D50"/>
-    <mergeCell ref="D51:D57"/>
-    <mergeCell ref="D58:D63"/>
-    <mergeCell ref="D64:D67"/>
-    <mergeCell ref="D69:D78"/>
-    <mergeCell ref="D79:D84"/>
-    <mergeCell ref="D85:D90"/>
-    <mergeCell ref="D91:D105"/>
-    <mergeCell ref="A68:J68"/>
-    <mergeCell ref="C51:C67"/>
-    <mergeCell ref="C69:C105"/>
+    <mergeCell ref="C459:C513"/>
+    <mergeCell ref="C216:C249"/>
+    <mergeCell ref="C250:C265"/>
+    <mergeCell ref="C266:C272"/>
+    <mergeCell ref="C274:C292"/>
+    <mergeCell ref="C293:C307"/>
+    <mergeCell ref="C308:C317"/>
+    <mergeCell ref="C318:C342"/>
+    <mergeCell ref="D459:D466"/>
+    <mergeCell ref="D467:D473"/>
+    <mergeCell ref="D474:D481"/>
+    <mergeCell ref="D482:D485"/>
+    <mergeCell ref="D486:D496"/>
+    <mergeCell ref="D497:D502"/>
+    <mergeCell ref="D503:D509"/>
+    <mergeCell ref="D510:D513"/>
+    <mergeCell ref="D318:D323"/>
+    <mergeCell ref="D324:D328"/>
+    <mergeCell ref="D329:D337"/>
+    <mergeCell ref="D338:D342"/>
+    <mergeCell ref="D343:D347"/>
+    <mergeCell ref="D348:D353"/>
+    <mergeCell ref="D354:D357"/>
+    <mergeCell ref="D296:D300"/>
+    <mergeCell ref="D301:D303"/>
+    <mergeCell ref="D304:D307"/>
+    <mergeCell ref="D308:D314"/>
+    <mergeCell ref="D315:D317"/>
+    <mergeCell ref="C343:C357"/>
+    <mergeCell ref="C359:C380"/>
+    <mergeCell ref="C381:C435"/>
+    <mergeCell ref="C437:C458"/>
+    <mergeCell ref="D250:D257"/>
+    <mergeCell ref="D258:D259"/>
+    <mergeCell ref="D260:D265"/>
+    <mergeCell ref="D266:D270"/>
+    <mergeCell ref="D271:D272"/>
+    <mergeCell ref="D274:D281"/>
+    <mergeCell ref="D282:D288"/>
+    <mergeCell ref="D289:D292"/>
+    <mergeCell ref="D293:D295"/>
+    <mergeCell ref="D449:D452"/>
+    <mergeCell ref="D453:D458"/>
+    <mergeCell ref="D417:D419"/>
+    <mergeCell ref="D420:D426"/>
+    <mergeCell ref="D427:D430"/>
+    <mergeCell ref="D431:D435"/>
+    <mergeCell ref="D437:D441"/>
+    <mergeCell ref="D442:D445"/>
+    <mergeCell ref="D446:D448"/>
+    <mergeCell ref="D400:D404"/>
+    <mergeCell ref="D405:D416"/>
+    <mergeCell ref="A436:J436"/>
+    <mergeCell ref="D359:D363"/>
+    <mergeCell ref="D364:D371"/>
+    <mergeCell ref="D372:D375"/>
+    <mergeCell ref="D376:D380"/>
+    <mergeCell ref="D381:D386"/>
+    <mergeCell ref="D387:D396"/>
+    <mergeCell ref="D397:D399"/>
     <mergeCell ref="A215:J215"/>
     <mergeCell ref="A273:J273"/>
     <mergeCell ref="A358:J358"/>
@@ -24264,66 +24336,47 @@
     <mergeCell ref="D234:D240"/>
     <mergeCell ref="D241:D243"/>
     <mergeCell ref="D244:D249"/>
-    <mergeCell ref="D442:D445"/>
-    <mergeCell ref="D446:D448"/>
-    <mergeCell ref="D400:D404"/>
-    <mergeCell ref="D405:D416"/>
-    <mergeCell ref="A436:J436"/>
-    <mergeCell ref="D359:D363"/>
-    <mergeCell ref="D364:D371"/>
-    <mergeCell ref="D372:D375"/>
-    <mergeCell ref="D376:D380"/>
-    <mergeCell ref="D381:D386"/>
-    <mergeCell ref="D387:D396"/>
-    <mergeCell ref="D397:D399"/>
-    <mergeCell ref="D301:D303"/>
-    <mergeCell ref="D304:D307"/>
-    <mergeCell ref="D308:D314"/>
-    <mergeCell ref="D315:D317"/>
-    <mergeCell ref="C343:C357"/>
-    <mergeCell ref="C359:C380"/>
-    <mergeCell ref="C381:C435"/>
-    <mergeCell ref="C437:C458"/>
-    <mergeCell ref="D250:D257"/>
-    <mergeCell ref="D258:D259"/>
-    <mergeCell ref="D260:D265"/>
-    <mergeCell ref="D266:D270"/>
-    <mergeCell ref="D271:D272"/>
-    <mergeCell ref="D274:D281"/>
-    <mergeCell ref="D282:D288"/>
-    <mergeCell ref="D289:D292"/>
-    <mergeCell ref="D293:D295"/>
-    <mergeCell ref="D449:D452"/>
-    <mergeCell ref="D453:D458"/>
-    <mergeCell ref="D417:D419"/>
-    <mergeCell ref="D420:D426"/>
-    <mergeCell ref="D427:D430"/>
-    <mergeCell ref="D431:D435"/>
-    <mergeCell ref="D437:D441"/>
-    <mergeCell ref="C459:C513"/>
-    <mergeCell ref="C216:C249"/>
-    <mergeCell ref="C250:C265"/>
-    <mergeCell ref="C266:C272"/>
-    <mergeCell ref="C274:C292"/>
-    <mergeCell ref="C293:C307"/>
-    <mergeCell ref="C308:C317"/>
-    <mergeCell ref="C318:C342"/>
-    <mergeCell ref="D459:D466"/>
-    <mergeCell ref="D467:D473"/>
-    <mergeCell ref="D474:D481"/>
-    <mergeCell ref="D482:D485"/>
-    <mergeCell ref="D486:D496"/>
-    <mergeCell ref="D497:D502"/>
-    <mergeCell ref="D503:D509"/>
-    <mergeCell ref="D510:D513"/>
-    <mergeCell ref="D318:D323"/>
-    <mergeCell ref="D324:D328"/>
-    <mergeCell ref="D329:D337"/>
-    <mergeCell ref="D338:D342"/>
-    <mergeCell ref="D343:D347"/>
-    <mergeCell ref="D348:D353"/>
-    <mergeCell ref="D354:D357"/>
-    <mergeCell ref="D296:D300"/>
+    <mergeCell ref="C45:C50"/>
+    <mergeCell ref="D45:D50"/>
+    <mergeCell ref="D51:D57"/>
+    <mergeCell ref="D58:D63"/>
+    <mergeCell ref="D64:D67"/>
+    <mergeCell ref="D69:D78"/>
+    <mergeCell ref="D79:D84"/>
+    <mergeCell ref="D85:D90"/>
+    <mergeCell ref="D91:D105"/>
+    <mergeCell ref="A68:J68"/>
+    <mergeCell ref="C51:C67"/>
+    <mergeCell ref="C69:C105"/>
+    <mergeCell ref="C107:C116"/>
+    <mergeCell ref="C117:C125"/>
+    <mergeCell ref="C127:C132"/>
+    <mergeCell ref="C134:C176"/>
+    <mergeCell ref="C177:C204"/>
+    <mergeCell ref="C205:C214"/>
+    <mergeCell ref="A106:J106"/>
+    <mergeCell ref="D107:D111"/>
+    <mergeCell ref="D112:D115"/>
+    <mergeCell ref="D117:D120"/>
+    <mergeCell ref="D121:D122"/>
+    <mergeCell ref="D123:D125"/>
+    <mergeCell ref="A126:J126"/>
+    <mergeCell ref="D127:D130"/>
+    <mergeCell ref="D131:D132"/>
+    <mergeCell ref="A133:J133"/>
+    <mergeCell ref="D210:D211"/>
+    <mergeCell ref="D212:D214"/>
+    <mergeCell ref="D26:D32"/>
+    <mergeCell ref="D33:D36"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="C4:C32"/>
+    <mergeCell ref="D4:D9"/>
+    <mergeCell ref="D10:D18"/>
+    <mergeCell ref="D19:D25"/>
+    <mergeCell ref="C33:C44"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="D40:D44"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H69:H105 H107:H125 H127:H132 H134:H214 H216:H272 H274:H357 H359:H435 H437:H513 H4:H65 H67" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -24853,16 +24906,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="31.5" customHeight="1">
-      <c r="A1" s="202" t="s">
+      <c r="A1" s="203" t="s">
         <v>644</v>
       </c>
-      <c r="B1" s="203"/>
+      <c r="B1" s="204"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1">
-      <c r="A2" s="204" t="s">
+      <c r="A2" s="205" t="s">
         <v>645</v>
       </c>
-      <c r="B2" s="203"/>
+      <c r="B2" s="204"/>
     </row>
     <row r="3" spans="1:2" ht="18" customHeight="1">
       <c r="A3" s="46" t="s">
@@ -24909,10 +24962,10 @@
       <c r="B8" s="47"/>
     </row>
     <row r="9" spans="1:2" ht="18" customHeight="1">
-      <c r="A9" s="204" t="s">
+      <c r="A9" s="205" t="s">
         <v>656</v>
       </c>
-      <c r="B9" s="203"/>
+      <c r="B9" s="204"/>
     </row>
     <row r="10" spans="1:2" ht="18" customHeight="1">
       <c r="A10" s="52" t="s">
@@ -24991,10 +25044,10 @@
       <c r="B19" s="47"/>
     </row>
     <row r="20" spans="1:2" ht="18" customHeight="1">
-      <c r="A20" s="204" t="s">
+      <c r="A20" s="205" t="s">
         <v>675</v>
       </c>
-      <c r="B20" s="203"/>
+      <c r="B20" s="204"/>
     </row>
     <row r="21" spans="1:2" ht="18" customHeight="1">
       <c r="A21" s="52" t="s">
@@ -25991,15 +26044,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="205" t="s">
+      <c r="A1" s="206" t="s">
         <v>678</v>
       </c>
-      <c r="B1" s="206"/>
-      <c r="C1" s="206"/>
-      <c r="D1" s="206"/>
-      <c r="E1" s="206"/>
-      <c r="F1" s="206"/>
-      <c r="G1" s="203"/>
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="204"/>
     </row>
     <row r="2" spans="1:8" ht="13.2">
       <c r="A2" s="53" t="s">

--- a/DSA Master Sheet.xlsx
+++ b/DSA Master Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aamer\Desktop\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD7EDFA3-1A67-4830-9296-459400BDA85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A028AE-97D1-448F-944D-E593724E0A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1411" uniqueCount="739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="743">
   <si>
     <t>DSA Master Sheet</t>
   </si>
@@ -2973,6 +2973,61 @@
 If mid &gt; left AND mid &gt; right → peak found → return mid
 If mid &lt; left → going downhill → search LEFT
 If mid &lt; right → going uphill → search RIGHT</t>
+  </si>
+  <si>
+    <t>Start from bottom-left → 
+If negative, count all right elements and move up
+→ Else move right → Repeat → Return count.</t>
+  </si>
+  <si>
+    <t>Addition is faster rather than using if.</t>
+  </si>
+  <si>
+    <t>1. Binary search for the row:
+mid = (low + high) / 2
+If matrix[mid][0] &gt; target → high = mid - 1
+Else if matrix[mid][0] &lt;= target &amp;&amp; matrix[mid][n-1] &gt;= target → row found
+Else → low = mid + 1
+2. Binary search inside selected row:
+If matrix[row][mid] &lt; target → low = mid + 1
+Else if matrix[row][mid] == target → return true
+Else → high = mid - 1
+3. If not found → return false.</t>
+  </si>
+  <si>
+    <r>
+      <t>Start from bottom-left.
+If target is greater → move right; if target is smaller → move up; if equal → found.
+Continue until found or matrix ends.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Start from bottom-left →
+1. If `matrix[i][j] == target` → return true
+2. If `matrix[i][j] &lt; target` → move right (j++)
+3. Else (`matrix[i][j] &gt; target`) → move up (i--)
+4. Repeat while `i &gt;= 0 &amp;&amp; j &lt;= col`
+5. If loop ends → return false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+TC: `O(m + n)` 
+SC:`O(1)` </t>
+    </r>
   </si>
 </sst>
 </file>
@@ -4488,32 +4543,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4533,23 +4579,86 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4569,77 +4678,23 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5449,18 +5504,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="30.75" customHeight="1">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="200" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="157"/>
+      <c r="B1" s="201"/>
+      <c r="C1" s="201"/>
+      <c r="D1" s="201"/>
+      <c r="E1" s="201"/>
+      <c r="F1" s="201"/>
+      <c r="G1" s="201"/>
+      <c r="H1" s="201"/>
+      <c r="I1" s="201"/>
+      <c r="J1" s="202"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -5515,18 +5570,18 @@
       <c r="T2" s="5"/>
     </row>
     <row r="3" spans="1:20" ht="13.8">
-      <c r="A3" s="158" t="s">
+      <c r="A3" s="197" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="159"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="159"/>
-      <c r="G3" s="159"/>
-      <c r="H3" s="159"/>
-      <c r="I3" s="159"/>
-      <c r="J3" s="160"/>
+      <c r="B3" s="198"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="199"/>
     </row>
     <row r="4" spans="1:20" ht="13.8">
       <c r="A4" s="6">
@@ -5535,10 +5590,10 @@
       <c r="B4" s="7">
         <v>1</v>
       </c>
-      <c r="C4" s="161" t="s">
+      <c r="C4" s="158" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="152" t="s">
+      <c r="D4" s="173" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -5568,8 +5623,8 @@
       <c r="B5" s="7">
         <v>2</v>
       </c>
-      <c r="C5" s="162"/>
-      <c r="D5" s="153"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="174"/>
       <c r="E5" s="8" t="s">
         <v>16</v>
       </c>
@@ -5597,8 +5652,8 @@
       <c r="B6" s="7">
         <v>3</v>
       </c>
-      <c r="C6" s="162"/>
-      <c r="D6" s="153"/>
+      <c r="C6" s="159"/>
+      <c r="D6" s="174"/>
       <c r="E6" s="8" t="s">
         <v>19</v>
       </c>
@@ -5626,8 +5681,8 @@
       <c r="B7" s="7">
         <v>4</v>
       </c>
-      <c r="C7" s="162"/>
-      <c r="D7" s="153"/>
+      <c r="C7" s="159"/>
+      <c r="D7" s="174"/>
       <c r="E7" s="8" t="s">
         <v>23</v>
       </c>
@@ -5655,8 +5710,8 @@
       <c r="B8" s="7">
         <v>5</v>
       </c>
-      <c r="C8" s="162"/>
-      <c r="D8" s="153"/>
+      <c r="C8" s="159"/>
+      <c r="D8" s="174"/>
       <c r="E8" s="8" t="s">
         <v>26</v>
       </c>
@@ -5684,8 +5739,8 @@
       <c r="B9" s="7">
         <v>6</v>
       </c>
-      <c r="C9" s="162"/>
-      <c r="D9" s="154"/>
+      <c r="C9" s="159"/>
+      <c r="D9" s="175"/>
       <c r="E9" s="8" t="s">
         <v>29</v>
       </c>
@@ -5710,8 +5765,8 @@
       <c r="B10" s="7">
         <v>7</v>
       </c>
-      <c r="C10" s="162"/>
-      <c r="D10" s="152" t="s">
+      <c r="C10" s="159"/>
+      <c r="D10" s="173" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="8" t="s">
@@ -5738,8 +5793,8 @@
       <c r="B11" s="7">
         <v>8</v>
       </c>
-      <c r="C11" s="162"/>
-      <c r="D11" s="153"/>
+      <c r="C11" s="159"/>
+      <c r="D11" s="174"/>
       <c r="E11" s="13" t="s">
         <v>32</v>
       </c>
@@ -5764,8 +5819,8 @@
       <c r="B12" s="7">
         <v>9</v>
       </c>
-      <c r="C12" s="162"/>
-      <c r="D12" s="153"/>
+      <c r="C12" s="159"/>
+      <c r="D12" s="174"/>
       <c r="E12" s="8" t="s">
         <v>33</v>
       </c>
@@ -5790,8 +5845,8 @@
       <c r="B13" s="7">
         <v>10</v>
       </c>
-      <c r="C13" s="162"/>
-      <c r="D13" s="153"/>
+      <c r="C13" s="159"/>
+      <c r="D13" s="174"/>
       <c r="E13" s="8" t="s">
         <v>34</v>
       </c>
@@ -5818,8 +5873,8 @@
       <c r="B14" s="7">
         <v>11</v>
       </c>
-      <c r="C14" s="162"/>
-      <c r="D14" s="153"/>
+      <c r="C14" s="159"/>
+      <c r="D14" s="174"/>
       <c r="E14" s="8" t="s">
         <v>35</v>
       </c>
@@ -5844,8 +5899,8 @@
       <c r="B15" s="7">
         <v>12</v>
       </c>
-      <c r="C15" s="162"/>
-      <c r="D15" s="153"/>
+      <c r="C15" s="159"/>
+      <c r="D15" s="174"/>
       <c r="E15" s="8" t="s">
         <v>36</v>
       </c>
@@ -5872,8 +5927,8 @@
       <c r="B16" s="7">
         <v>13</v>
       </c>
-      <c r="C16" s="162"/>
-      <c r="D16" s="153"/>
+      <c r="C16" s="159"/>
+      <c r="D16" s="174"/>
       <c r="E16" s="8" t="s">
         <v>37</v>
       </c>
@@ -5898,8 +5953,8 @@
       <c r="B17" s="7">
         <v>14</v>
       </c>
-      <c r="C17" s="162"/>
-      <c r="D17" s="153"/>
+      <c r="C17" s="159"/>
+      <c r="D17" s="174"/>
       <c r="E17" s="8" t="s">
         <v>38</v>
       </c>
@@ -5926,8 +5981,8 @@
       <c r="B18" s="7">
         <v>15</v>
       </c>
-      <c r="C18" s="162"/>
-      <c r="D18" s="154"/>
+      <c r="C18" s="159"/>
+      <c r="D18" s="175"/>
       <c r="E18" s="13" t="s">
         <v>39</v>
       </c>
@@ -5954,8 +6009,8 @@
       <c r="B19" s="7">
         <v>16</v>
       </c>
-      <c r="C19" s="162"/>
-      <c r="D19" s="152" t="s">
+      <c r="C19" s="159"/>
+      <c r="D19" s="173" t="s">
         <v>40</v>
       </c>
       <c r="E19" s="8" t="s">
@@ -5984,8 +6039,8 @@
       <c r="B20" s="7">
         <v>17</v>
       </c>
-      <c r="C20" s="162"/>
-      <c r="D20" s="153"/>
+      <c r="C20" s="159"/>
+      <c r="D20" s="174"/>
       <c r="E20" s="8" t="s">
         <v>42</v>
       </c>
@@ -6012,8 +6067,8 @@
       <c r="B21" s="7">
         <v>18</v>
       </c>
-      <c r="C21" s="162"/>
-      <c r="D21" s="153"/>
+      <c r="C21" s="159"/>
+      <c r="D21" s="174"/>
       <c r="E21" s="8" t="s">
         <v>43</v>
       </c>
@@ -6040,8 +6095,8 @@
       <c r="B22" s="7">
         <v>19</v>
       </c>
-      <c r="C22" s="162"/>
-      <c r="D22" s="153"/>
+      <c r="C22" s="159"/>
+      <c r="D22" s="174"/>
       <c r="E22" s="8" t="s">
         <v>44</v>
       </c>
@@ -6062,8 +6117,8 @@
       <c r="B23" s="7">
         <v>20</v>
       </c>
-      <c r="C23" s="162"/>
-      <c r="D23" s="153"/>
+      <c r="C23" s="159"/>
+      <c r="D23" s="174"/>
       <c r="E23" s="8" t="s">
         <v>45</v>
       </c>
@@ -6084,8 +6139,8 @@
       <c r="B24" s="7">
         <v>21</v>
       </c>
-      <c r="C24" s="162"/>
-      <c r="D24" s="153"/>
+      <c r="C24" s="159"/>
+      <c r="D24" s="174"/>
       <c r="E24" s="13" t="s">
         <v>46</v>
       </c>
@@ -6110,8 +6165,8 @@
       <c r="B25" s="7">
         <v>22</v>
       </c>
-      <c r="C25" s="162"/>
-      <c r="D25" s="154"/>
+      <c r="C25" s="159"/>
+      <c r="D25" s="175"/>
       <c r="E25" s="8" t="s">
         <v>47</v>
       </c>
@@ -6138,8 +6193,8 @@
       <c r="B26" s="7">
         <v>23</v>
       </c>
-      <c r="C26" s="162"/>
-      <c r="D26" s="152" t="s">
+      <c r="C26" s="159"/>
+      <c r="D26" s="173" t="s">
         <v>48</v>
       </c>
       <c r="E26" s="13" t="s">
@@ -6168,8 +6223,8 @@
       <c r="B27" s="7">
         <v>24</v>
       </c>
-      <c r="C27" s="162"/>
-      <c r="D27" s="153"/>
+      <c r="C27" s="159"/>
+      <c r="D27" s="174"/>
       <c r="E27" s="8" t="s">
         <v>50</v>
       </c>
@@ -6194,8 +6249,8 @@
       <c r="B28" s="7">
         <v>25</v>
       </c>
-      <c r="C28" s="162"/>
-      <c r="D28" s="153"/>
+      <c r="C28" s="159"/>
+      <c r="D28" s="174"/>
       <c r="E28" s="8" t="s">
         <v>51</v>
       </c>
@@ -6222,8 +6277,8 @@
       <c r="B29" s="143">
         <v>26</v>
       </c>
-      <c r="C29" s="162"/>
-      <c r="D29" s="153"/>
+      <c r="C29" s="159"/>
+      <c r="D29" s="174"/>
       <c r="E29" s="144" t="s">
         <v>52</v>
       </c>
@@ -6244,8 +6299,8 @@
       <c r="B30" s="143">
         <v>27</v>
       </c>
-      <c r="C30" s="162"/>
-      <c r="D30" s="153"/>
+      <c r="C30" s="159"/>
+      <c r="D30" s="174"/>
       <c r="E30" s="144" t="s">
         <v>53</v>
       </c>
@@ -6266,8 +6321,8 @@
       <c r="B31" s="143">
         <v>28</v>
       </c>
-      <c r="C31" s="162"/>
-      <c r="D31" s="153"/>
+      <c r="C31" s="159"/>
+      <c r="D31" s="174"/>
       <c r="E31" s="144" t="s">
         <v>54</v>
       </c>
@@ -6288,8 +6343,8 @@
       <c r="B32" s="143">
         <v>29</v>
       </c>
-      <c r="C32" s="163"/>
-      <c r="D32" s="154"/>
+      <c r="C32" s="160"/>
+      <c r="D32" s="175"/>
       <c r="E32" s="146" t="s">
         <v>55</v>
       </c>
@@ -6310,10 +6365,10 @@
       <c r="B33" s="22">
         <v>1</v>
       </c>
-      <c r="C33" s="164" t="s">
+      <c r="C33" s="161" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="152" t="s">
+      <c r="D33" s="173" t="s">
         <v>57</v>
       </c>
       <c r="E33" s="8" t="s">
@@ -6340,8 +6395,8 @@
       <c r="B34" s="7">
         <v>2</v>
       </c>
-      <c r="C34" s="165"/>
-      <c r="D34" s="153"/>
+      <c r="C34" s="162"/>
+      <c r="D34" s="174"/>
       <c r="E34" s="8" t="s">
         <v>59</v>
       </c>
@@ -6366,8 +6421,8 @@
       <c r="B35" s="7">
         <v>3</v>
       </c>
-      <c r="C35" s="165"/>
-      <c r="D35" s="153"/>
+      <c r="C35" s="162"/>
+      <c r="D35" s="174"/>
       <c r="E35" s="8" t="s">
         <v>60</v>
       </c>
@@ -6394,8 +6449,8 @@
       <c r="B36" s="7">
         <v>4</v>
       </c>
-      <c r="C36" s="165"/>
-      <c r="D36" s="154"/>
+      <c r="C36" s="162"/>
+      <c r="D36" s="175"/>
       <c r="E36" s="8" t="s">
         <v>61</v>
       </c>
@@ -6422,8 +6477,8 @@
       <c r="B37" s="7">
         <v>5</v>
       </c>
-      <c r="C37" s="165"/>
-      <c r="D37" s="152" t="s">
+      <c r="C37" s="162"/>
+      <c r="D37" s="173" t="s">
         <v>62</v>
       </c>
       <c r="E37" s="8" t="s">
@@ -6450,8 +6505,8 @@
       <c r="B38" s="7">
         <v>6</v>
       </c>
-      <c r="C38" s="165"/>
-      <c r="D38" s="153"/>
+      <c r="C38" s="162"/>
+      <c r="D38" s="174"/>
       <c r="E38" s="8" t="s">
         <v>64</v>
       </c>
@@ -6476,8 +6531,8 @@
       <c r="B39" s="7">
         <v>7</v>
       </c>
-      <c r="C39" s="165"/>
-      <c r="D39" s="154"/>
+      <c r="C39" s="162"/>
+      <c r="D39" s="175"/>
       <c r="E39" s="8" t="s">
         <v>65</v>
       </c>
@@ -6502,8 +6557,8 @@
       <c r="B40" s="7">
         <v>8</v>
       </c>
-      <c r="C40" s="165"/>
-      <c r="D40" s="152" t="s">
+      <c r="C40" s="162"/>
+      <c r="D40" s="173" t="s">
         <v>66</v>
       </c>
       <c r="E40" s="8" t="s">
@@ -6530,8 +6585,8 @@
       <c r="B41" s="7">
         <v>9</v>
       </c>
-      <c r="C41" s="165"/>
-      <c r="D41" s="153"/>
+      <c r="C41" s="162"/>
+      <c r="D41" s="174"/>
       <c r="E41" s="8" t="s">
         <v>68</v>
       </c>
@@ -6556,8 +6611,8 @@
       <c r="B42" s="7">
         <v>10</v>
       </c>
-      <c r="C42" s="165"/>
-      <c r="D42" s="153"/>
+      <c r="C42" s="162"/>
+      <c r="D42" s="174"/>
       <c r="E42" s="8" t="s">
         <v>69</v>
       </c>
@@ -6582,8 +6637,8 @@
       <c r="B43" s="7">
         <v>11</v>
       </c>
-      <c r="C43" s="165"/>
-      <c r="D43" s="153"/>
+      <c r="C43" s="162"/>
+      <c r="D43" s="174"/>
       <c r="E43" s="8" t="s">
         <v>70</v>
       </c>
@@ -6608,8 +6663,8 @@
       <c r="B44" s="24">
         <v>12</v>
       </c>
-      <c r="C44" s="166"/>
-      <c r="D44" s="154"/>
+      <c r="C44" s="163"/>
+      <c r="D44" s="175"/>
       <c r="E44" s="17" t="s">
         <v>71</v>
       </c>
@@ -6634,10 +6689,10 @@
       <c r="B45" s="22">
         <v>1</v>
       </c>
-      <c r="C45" s="179" t="s">
+      <c r="C45" s="164" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="182" t="s">
+      <c r="D45" s="176" t="s">
         <v>73</v>
       </c>
       <c r="E45" s="13" t="s">
@@ -6664,8 +6719,8 @@
       <c r="B46" s="7">
         <v>2</v>
       </c>
-      <c r="C46" s="180"/>
-      <c r="D46" s="183"/>
+      <c r="C46" s="165"/>
+      <c r="D46" s="177"/>
       <c r="E46" s="8" t="s">
         <v>75</v>
       </c>
@@ -6692,8 +6747,8 @@
       <c r="B47" s="7">
         <v>3</v>
       </c>
-      <c r="C47" s="180"/>
-      <c r="D47" s="183"/>
+      <c r="C47" s="165"/>
+      <c r="D47" s="177"/>
       <c r="E47" s="13" t="s">
         <v>76</v>
       </c>
@@ -6720,8 +6775,8 @@
       <c r="B48" s="7">
         <v>4</v>
       </c>
-      <c r="C48" s="180"/>
-      <c r="D48" s="183"/>
+      <c r="C48" s="165"/>
+      <c r="D48" s="177"/>
       <c r="E48" s="13" t="s">
         <v>77</v>
       </c>
@@ -6748,8 +6803,8 @@
       <c r="B49" s="7">
         <v>5</v>
       </c>
-      <c r="C49" s="180"/>
-      <c r="D49" s="183"/>
+      <c r="C49" s="165"/>
+      <c r="D49" s="177"/>
       <c r="E49" s="13" t="s">
         <v>78</v>
       </c>
@@ -6774,8 +6829,8 @@
       <c r="B50" s="24">
         <v>6</v>
       </c>
-      <c r="C50" s="181"/>
-      <c r="D50" s="184"/>
+      <c r="C50" s="166"/>
+      <c r="D50" s="178"/>
       <c r="E50" s="25" t="s">
         <v>79</v>
       </c>
@@ -6800,10 +6855,10 @@
       <c r="B51" s="7">
         <v>1</v>
       </c>
-      <c r="C51" s="170" t="s">
+      <c r="C51" s="155" t="s">
         <v>80</v>
       </c>
-      <c r="D51" s="152" t="s">
+      <c r="D51" s="173" t="s">
         <v>81</v>
       </c>
       <c r="E51" s="13" t="s">
@@ -6832,8 +6887,8 @@
       <c r="B52" s="7">
         <v>2</v>
       </c>
-      <c r="C52" s="171"/>
-      <c r="D52" s="153"/>
+      <c r="C52" s="156"/>
+      <c r="D52" s="174"/>
       <c r="E52" s="8" t="s">
         <v>83</v>
       </c>
@@ -6860,8 +6915,8 @@
       <c r="B53" s="7">
         <v>3</v>
       </c>
-      <c r="C53" s="171"/>
-      <c r="D53" s="153"/>
+      <c r="C53" s="156"/>
+      <c r="D53" s="174"/>
       <c r="E53" s="27" t="s">
         <v>84</v>
       </c>
@@ -6886,8 +6941,8 @@
       <c r="B54" s="7">
         <v>4</v>
       </c>
-      <c r="C54" s="171"/>
-      <c r="D54" s="153"/>
+      <c r="C54" s="156"/>
+      <c r="D54" s="174"/>
       <c r="E54" s="13" t="s">
         <v>85</v>
       </c>
@@ -6912,8 +6967,8 @@
       <c r="B55" s="7">
         <v>5</v>
       </c>
-      <c r="C55" s="171"/>
-      <c r="D55" s="153"/>
+      <c r="C55" s="156"/>
+      <c r="D55" s="174"/>
       <c r="E55" s="13" t="s">
         <v>86</v>
       </c>
@@ -6940,8 +6995,8 @@
       <c r="B56" s="7">
         <v>6</v>
       </c>
-      <c r="C56" s="171"/>
-      <c r="D56" s="153"/>
+      <c r="C56" s="156"/>
+      <c r="D56" s="174"/>
       <c r="E56" s="13" t="s">
         <v>87</v>
       </c>
@@ -6968,8 +7023,8 @@
       <c r="B57" s="7">
         <v>7</v>
       </c>
-      <c r="C57" s="171"/>
-      <c r="D57" s="154"/>
+      <c r="C57" s="156"/>
+      <c r="D57" s="175"/>
       <c r="E57" s="13" t="s">
         <v>88</v>
       </c>
@@ -6996,8 +7051,8 @@
       <c r="B58" s="7">
         <v>8</v>
       </c>
-      <c r="C58" s="171"/>
-      <c r="D58" s="152" t="s">
+      <c r="C58" s="156"/>
+      <c r="D58" s="173" t="s">
         <v>89</v>
       </c>
       <c r="E58" s="13" t="s">
@@ -7024,8 +7079,8 @@
       <c r="B59" s="7">
         <v>9</v>
       </c>
-      <c r="C59" s="171"/>
-      <c r="D59" s="153"/>
+      <c r="C59" s="156"/>
+      <c r="D59" s="174"/>
       <c r="E59" s="8" t="s">
         <v>91</v>
       </c>
@@ -7050,8 +7105,8 @@
       <c r="B60" s="7">
         <v>10</v>
       </c>
-      <c r="C60" s="171"/>
-      <c r="D60" s="153"/>
+      <c r="C60" s="156"/>
+      <c r="D60" s="174"/>
       <c r="E60" s="8" t="s">
         <v>92</v>
       </c>
@@ -7072,8 +7127,8 @@
       <c r="B61" s="7">
         <v>11</v>
       </c>
-      <c r="C61" s="171"/>
-      <c r="D61" s="153"/>
+      <c r="C61" s="156"/>
+      <c r="D61" s="174"/>
       <c r="E61" s="8" t="s">
         <v>93</v>
       </c>
@@ -7094,8 +7149,8 @@
       <c r="B62" s="7">
         <v>12</v>
       </c>
-      <c r="C62" s="171"/>
-      <c r="D62" s="153"/>
+      <c r="C62" s="156"/>
+      <c r="D62" s="174"/>
       <c r="E62" s="8" t="s">
         <v>94</v>
       </c>
@@ -7120,8 +7175,8 @@
       <c r="B63" s="7">
         <v>13</v>
       </c>
-      <c r="C63" s="171"/>
-      <c r="D63" s="154"/>
+      <c r="C63" s="156"/>
+      <c r="D63" s="175"/>
       <c r="E63" s="8" t="s">
         <v>95</v>
       </c>
@@ -7146,8 +7201,8 @@
       <c r="B64" s="7">
         <v>14</v>
       </c>
-      <c r="C64" s="171"/>
-      <c r="D64" s="152" t="s">
+      <c r="C64" s="156"/>
+      <c r="D64" s="173" t="s">
         <v>48</v>
       </c>
       <c r="E64" s="8" t="s">
@@ -7176,8 +7231,8 @@
       <c r="B65" s="143">
         <v>15</v>
       </c>
-      <c r="C65" s="171"/>
-      <c r="D65" s="153"/>
+      <c r="C65" s="156"/>
+      <c r="D65" s="174"/>
       <c r="E65" s="144" t="s">
         <v>97</v>
       </c>
@@ -7198,8 +7253,8 @@
       <c r="B66" s="7">
         <v>16</v>
       </c>
-      <c r="C66" s="171"/>
-      <c r="D66" s="153"/>
+      <c r="C66" s="156"/>
+      <c r="D66" s="174"/>
       <c r="E66" s="8" t="s">
         <v>98</v>
       </c>
@@ -7226,8 +7281,8 @@
       <c r="B67" s="7">
         <v>17</v>
       </c>
-      <c r="C67" s="172"/>
-      <c r="D67" s="154"/>
+      <c r="C67" s="157"/>
+      <c r="D67" s="175"/>
       <c r="E67" s="8" t="s">
         <v>99</v>
       </c>
@@ -7268,10 +7323,10 @@
       <c r="B69" s="7">
         <v>1</v>
       </c>
-      <c r="C69" s="161" t="s">
+      <c r="C69" s="158" t="s">
         <v>101</v>
       </c>
-      <c r="D69" s="152" t="s">
+      <c r="D69" s="173" t="s">
         <v>102</v>
       </c>
       <c r="E69" s="8" t="s">
@@ -7298,8 +7353,8 @@
       <c r="B70" s="7">
         <v>2</v>
       </c>
-      <c r="C70" s="162"/>
-      <c r="D70" s="153"/>
+      <c r="C70" s="159"/>
+      <c r="D70" s="174"/>
       <c r="E70" s="28" t="s">
         <v>104</v>
       </c>
@@ -7326,8 +7381,8 @@
       <c r="B71" s="7">
         <v>3</v>
       </c>
-      <c r="C71" s="162"/>
-      <c r="D71" s="153"/>
+      <c r="C71" s="159"/>
+      <c r="D71" s="174"/>
       <c r="E71" s="8" t="s">
         <v>105</v>
       </c>
@@ -7354,8 +7409,8 @@
       <c r="B72" s="7">
         <v>4</v>
       </c>
-      <c r="C72" s="162"/>
-      <c r="D72" s="153"/>
+      <c r="C72" s="159"/>
+      <c r="D72" s="174"/>
       <c r="E72" s="8" t="s">
         <v>106</v>
       </c>
@@ -7382,8 +7437,8 @@
       <c r="B73" s="7">
         <v>5</v>
       </c>
-      <c r="C73" s="162"/>
-      <c r="D73" s="153"/>
+      <c r="C73" s="159"/>
+      <c r="D73" s="174"/>
       <c r="E73" s="28" t="s">
         <v>107</v>
       </c>
@@ -7410,8 +7465,8 @@
       <c r="B74" s="7">
         <v>6</v>
       </c>
-      <c r="C74" s="162"/>
-      <c r="D74" s="153"/>
+      <c r="C74" s="159"/>
+      <c r="D74" s="174"/>
       <c r="E74" s="28" t="s">
         <v>108</v>
       </c>
@@ -7436,8 +7491,8 @@
       <c r="B75" s="7">
         <v>7</v>
       </c>
-      <c r="C75" s="162"/>
-      <c r="D75" s="153"/>
+      <c r="C75" s="159"/>
+      <c r="D75" s="174"/>
       <c r="E75" s="28" t="s">
         <v>109</v>
       </c>
@@ -7464,8 +7519,8 @@
       <c r="B76" s="7">
         <v>8</v>
       </c>
-      <c r="C76" s="162"/>
-      <c r="D76" s="153"/>
+      <c r="C76" s="159"/>
+      <c r="D76" s="174"/>
       <c r="E76" s="8" t="s">
         <v>110</v>
       </c>
@@ -7490,8 +7545,8 @@
       <c r="B77" s="7">
         <v>9</v>
       </c>
-      <c r="C77" s="162"/>
-      <c r="D77" s="153"/>
+      <c r="C77" s="159"/>
+      <c r="D77" s="174"/>
       <c r="E77" s="8" t="s">
         <v>111</v>
       </c>
@@ -7518,8 +7573,8 @@
       <c r="B78" s="7">
         <v>10</v>
       </c>
-      <c r="C78" s="162"/>
-      <c r="D78" s="154"/>
+      <c r="C78" s="159"/>
+      <c r="D78" s="175"/>
       <c r="E78" s="8" t="s">
         <v>112</v>
       </c>
@@ -7546,8 +7601,8 @@
       <c r="B79" s="7">
         <v>11</v>
       </c>
-      <c r="C79" s="162"/>
-      <c r="D79" s="152" t="s">
+      <c r="C79" s="159"/>
+      <c r="D79" s="173" t="s">
         <v>113</v>
       </c>
       <c r="E79" s="8" t="s">
@@ -7576,8 +7631,8 @@
       <c r="B80" s="7">
         <v>12</v>
       </c>
-      <c r="C80" s="162"/>
-      <c r="D80" s="153"/>
+      <c r="C80" s="159"/>
+      <c r="D80" s="174"/>
       <c r="E80" s="8" t="s">
         <v>115</v>
       </c>
@@ -7604,8 +7659,8 @@
       <c r="B81" s="7">
         <v>13</v>
       </c>
-      <c r="C81" s="162"/>
-      <c r="D81" s="153"/>
+      <c r="C81" s="159"/>
+      <c r="D81" s="174"/>
       <c r="E81" s="8" t="s">
         <v>116</v>
       </c>
@@ -7632,8 +7687,8 @@
       <c r="B82" s="7">
         <v>14</v>
       </c>
-      <c r="C82" s="162"/>
-      <c r="D82" s="153"/>
+      <c r="C82" s="159"/>
+      <c r="D82" s="174"/>
       <c r="E82" s="8" t="s">
         <v>117</v>
       </c>
@@ -7660,8 +7715,8 @@
       <c r="B83" s="7">
         <v>15</v>
       </c>
-      <c r="C83" s="162"/>
-      <c r="D83" s="153"/>
+      <c r="C83" s="159"/>
+      <c r="D83" s="174"/>
       <c r="E83" s="8" t="s">
         <v>118</v>
       </c>
@@ -7688,8 +7743,8 @@
       <c r="B84" s="7">
         <v>16</v>
       </c>
-      <c r="C84" s="162"/>
-      <c r="D84" s="154"/>
+      <c r="C84" s="159"/>
+      <c r="D84" s="175"/>
       <c r="E84" s="8" t="s">
         <v>119</v>
       </c>
@@ -7709,15 +7764,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="13.8">
+    <row r="85" spans="1:10" ht="55.2">
       <c r="A85" s="6">
         <v>81</v>
       </c>
       <c r="B85" s="7">
         <v>17</v>
       </c>
-      <c r="C85" s="162"/>
-      <c r="D85" s="152" t="s">
+      <c r="C85" s="159"/>
+      <c r="D85" s="173" t="s">
         <v>120</v>
       </c>
       <c r="E85" s="8" t="s">
@@ -7729,9 +7784,15 @@
       <c r="G85" s="10">
         <v>2</v>
       </c>
-      <c r="H85" s="11"/>
-      <c r="I85" s="11"/>
-      <c r="J85" s="11"/>
+      <c r="H85" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I85" s="125" t="s">
+        <v>739</v>
+      </c>
+      <c r="J85" s="126" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="86" spans="1:10" ht="13.8">
       <c r="A86" s="6">
@@ -7740,8 +7801,8 @@
       <c r="B86" s="7">
         <v>18</v>
       </c>
-      <c r="C86" s="162"/>
-      <c r="D86" s="153"/>
+      <c r="C86" s="159"/>
+      <c r="D86" s="174"/>
       <c r="E86" s="8" t="s">
         <v>122</v>
       </c>
@@ -7751,19 +7812,25 @@
       <c r="G86" s="10">
         <v>2</v>
       </c>
-      <c r="H86" s="11"/>
-      <c r="I86" s="11"/>
-      <c r="J86" s="11"/>
-    </row>
-    <row r="87" spans="1:10" ht="13.8">
+      <c r="H86" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I86" s="126" t="s">
+        <v>740</v>
+      </c>
+      <c r="J86" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="207">
       <c r="A87" s="6">
         <v>83</v>
       </c>
       <c r="B87" s="7">
         <v>19</v>
       </c>
-      <c r="C87" s="162"/>
-      <c r="D87" s="153"/>
+      <c r="C87" s="159"/>
+      <c r="D87" s="174"/>
       <c r="E87" s="29" t="s">
         <v>123</v>
       </c>
@@ -7773,19 +7840,25 @@
       <c r="G87" s="10">
         <v>2</v>
       </c>
-      <c r="H87" s="11"/>
-      <c r="I87" s="11"/>
-      <c r="J87" s="11"/>
-    </row>
-    <row r="88" spans="1:10" ht="13.8">
+      <c r="H87" s="128" t="s">
+        <v>17</v>
+      </c>
+      <c r="I87" s="125" t="s">
+        <v>741</v>
+      </c>
+      <c r="J87" s="126" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="248.4">
       <c r="A88" s="6">
         <v>84</v>
       </c>
       <c r="B88" s="7">
         <v>20</v>
       </c>
-      <c r="C88" s="162"/>
-      <c r="D88" s="153"/>
+      <c r="C88" s="159"/>
+      <c r="D88" s="174"/>
       <c r="E88" s="8" t="s">
         <v>124</v>
       </c>
@@ -7795,9 +7868,15 @@
       <c r="G88" s="10">
         <v>3</v>
       </c>
-      <c r="H88" s="11"/>
-      <c r="I88" s="11"/>
-      <c r="J88" s="11"/>
+      <c r="H88" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I88" s="131" t="s">
+        <v>742</v>
+      </c>
+      <c r="J88" s="126" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="89" spans="1:10" ht="13.8">
       <c r="A89" s="6">
@@ -7806,8 +7885,8 @@
       <c r="B89" s="7">
         <v>21</v>
       </c>
-      <c r="C89" s="162"/>
-      <c r="D89" s="153"/>
+      <c r="C89" s="159"/>
+      <c r="D89" s="174"/>
       <c r="E89" s="8" t="s">
         <v>125</v>
       </c>
@@ -7828,8 +7907,8 @@
       <c r="B90" s="7">
         <v>22</v>
       </c>
-      <c r="C90" s="162"/>
-      <c r="D90" s="154"/>
+      <c r="C90" s="159"/>
+      <c r="D90" s="175"/>
       <c r="E90" s="8" t="s">
         <v>126</v>
       </c>
@@ -7850,8 +7929,8 @@
       <c r="B91" s="7">
         <v>23</v>
       </c>
-      <c r="C91" s="162"/>
-      <c r="D91" s="152" t="s">
+      <c r="C91" s="159"/>
+      <c r="D91" s="173" t="s">
         <v>127</v>
       </c>
       <c r="E91" s="8" t="s">
@@ -7874,8 +7953,8 @@
       <c r="B92" s="7">
         <v>24</v>
       </c>
-      <c r="C92" s="162"/>
-      <c r="D92" s="153"/>
+      <c r="C92" s="159"/>
+      <c r="D92" s="174"/>
       <c r="E92" s="8" t="s">
         <v>129</v>
       </c>
@@ -7896,8 +7975,8 @@
       <c r="B93" s="7">
         <v>25</v>
       </c>
-      <c r="C93" s="162"/>
-      <c r="D93" s="153"/>
+      <c r="C93" s="159"/>
+      <c r="D93" s="174"/>
       <c r="E93" s="8" t="s">
         <v>130</v>
       </c>
@@ -7918,8 +7997,8 @@
       <c r="B94" s="7">
         <v>26</v>
       </c>
-      <c r="C94" s="162"/>
-      <c r="D94" s="153"/>
+      <c r="C94" s="159"/>
+      <c r="D94" s="174"/>
       <c r="E94" s="8" t="s">
         <v>131</v>
       </c>
@@ -7940,8 +8019,8 @@
       <c r="B95" s="7">
         <v>27</v>
       </c>
-      <c r="C95" s="162"/>
-      <c r="D95" s="153"/>
+      <c r="C95" s="159"/>
+      <c r="D95" s="174"/>
       <c r="E95" s="8" t="s">
         <v>132</v>
       </c>
@@ -7962,8 +8041,8 @@
       <c r="B96" s="7">
         <v>28</v>
       </c>
-      <c r="C96" s="162"/>
-      <c r="D96" s="153"/>
+      <c r="C96" s="159"/>
+      <c r="D96" s="174"/>
       <c r="E96" s="8" t="s">
         <v>133</v>
       </c>
@@ -7984,8 +8063,8 @@
       <c r="B97" s="7">
         <v>29</v>
       </c>
-      <c r="C97" s="162"/>
-      <c r="D97" s="153"/>
+      <c r="C97" s="159"/>
+      <c r="D97" s="174"/>
       <c r="E97" s="8" t="s">
         <v>134</v>
       </c>
@@ -8006,8 +8085,8 @@
       <c r="B98" s="7">
         <v>30</v>
       </c>
-      <c r="C98" s="162"/>
-      <c r="D98" s="153"/>
+      <c r="C98" s="159"/>
+      <c r="D98" s="174"/>
       <c r="E98" s="8" t="s">
         <v>135</v>
       </c>
@@ -8028,8 +8107,8 @@
       <c r="B99" s="7">
         <v>31</v>
       </c>
-      <c r="C99" s="162"/>
-      <c r="D99" s="153"/>
+      <c r="C99" s="159"/>
+      <c r="D99" s="174"/>
       <c r="E99" s="30" t="s">
         <v>136</v>
       </c>
@@ -8050,8 +8129,8 @@
       <c r="B100" s="7">
         <v>32</v>
       </c>
-      <c r="C100" s="162"/>
-      <c r="D100" s="153"/>
+      <c r="C100" s="159"/>
+      <c r="D100" s="174"/>
       <c r="E100" s="8" t="s">
         <v>137</v>
       </c>
@@ -8072,8 +8151,8 @@
       <c r="B101" s="7">
         <v>33</v>
       </c>
-      <c r="C101" s="162"/>
-      <c r="D101" s="153"/>
+      <c r="C101" s="159"/>
+      <c r="D101" s="174"/>
       <c r="E101" s="8" t="s">
         <v>138</v>
       </c>
@@ -8094,8 +8173,8 @@
       <c r="B102" s="7">
         <v>34</v>
       </c>
-      <c r="C102" s="162"/>
-      <c r="D102" s="153"/>
+      <c r="C102" s="159"/>
+      <c r="D102" s="174"/>
       <c r="E102" s="8" t="s">
         <v>139</v>
       </c>
@@ -8116,8 +8195,8 @@
       <c r="B103" s="7">
         <v>35</v>
       </c>
-      <c r="C103" s="162"/>
-      <c r="D103" s="153"/>
+      <c r="C103" s="159"/>
+      <c r="D103" s="174"/>
       <c r="E103" s="8" t="s">
         <v>140</v>
       </c>
@@ -8138,8 +8217,8 @@
       <c r="B104" s="7">
         <v>36</v>
       </c>
-      <c r="C104" s="162"/>
-      <c r="D104" s="153"/>
+      <c r="C104" s="159"/>
+      <c r="D104" s="174"/>
       <c r="E104" s="8" t="s">
         <v>141</v>
       </c>
@@ -8160,8 +8239,8 @@
       <c r="B105" s="7">
         <v>37</v>
       </c>
-      <c r="C105" s="163"/>
-      <c r="D105" s="154"/>
+      <c r="C105" s="160"/>
+      <c r="D105" s="175"/>
       <c r="E105" s="8" t="s">
         <v>142</v>
       </c>
@@ -8176,18 +8255,18 @@
       <c r="J105" s="11"/>
     </row>
     <row r="106" spans="1:10" ht="13.8">
-      <c r="A106" s="173" t="s">
+      <c r="A106" s="191" t="s">
         <v>143</v>
       </c>
-      <c r="B106" s="174"/>
-      <c r="C106" s="174"/>
-      <c r="D106" s="174"/>
-      <c r="E106" s="174"/>
-      <c r="F106" s="174"/>
-      <c r="G106" s="174"/>
-      <c r="H106" s="174"/>
-      <c r="I106" s="174"/>
-      <c r="J106" s="175"/>
+      <c r="B106" s="192"/>
+      <c r="C106" s="192"/>
+      <c r="D106" s="192"/>
+      <c r="E106" s="192"/>
+      <c r="F106" s="192"/>
+      <c r="G106" s="192"/>
+      <c r="H106" s="192"/>
+      <c r="I106" s="192"/>
+      <c r="J106" s="193"/>
     </row>
     <row r="107" spans="1:10" ht="13.8">
       <c r="A107" s="6">
@@ -8196,10 +8275,10 @@
       <c r="B107" s="7">
         <v>1</v>
       </c>
-      <c r="C107" s="164" t="s">
+      <c r="C107" s="161" t="s">
         <v>144</v>
       </c>
-      <c r="D107" s="152" t="s">
+      <c r="D107" s="173" t="s">
         <v>145</v>
       </c>
       <c r="E107" s="8" t="s">
@@ -8222,8 +8301,8 @@
       <c r="B108" s="7">
         <v>2</v>
       </c>
-      <c r="C108" s="165"/>
-      <c r="D108" s="153"/>
+      <c r="C108" s="162"/>
+      <c r="D108" s="174"/>
       <c r="E108" s="8" t="s">
         <v>147</v>
       </c>
@@ -8244,8 +8323,8 @@
       <c r="B109" s="7">
         <v>3</v>
       </c>
-      <c r="C109" s="165"/>
-      <c r="D109" s="153"/>
+      <c r="C109" s="162"/>
+      <c r="D109" s="174"/>
       <c r="E109" s="8" t="s">
         <v>148</v>
       </c>
@@ -8266,8 +8345,8 @@
       <c r="B110" s="7">
         <v>4</v>
       </c>
-      <c r="C110" s="165"/>
-      <c r="D110" s="153"/>
+      <c r="C110" s="162"/>
+      <c r="D110" s="174"/>
       <c r="E110" s="8" t="s">
         <v>149</v>
       </c>
@@ -8288,8 +8367,8 @@
       <c r="B111" s="7">
         <v>5</v>
       </c>
-      <c r="C111" s="165"/>
-      <c r="D111" s="154"/>
+      <c r="C111" s="162"/>
+      <c r="D111" s="175"/>
       <c r="E111" s="8" t="s">
         <v>150</v>
       </c>
@@ -8310,8 +8389,8 @@
       <c r="B112" s="7">
         <v>6</v>
       </c>
-      <c r="C112" s="165"/>
-      <c r="D112" s="152" t="s">
+      <c r="C112" s="162"/>
+      <c r="D112" s="173" t="s">
         <v>151</v>
       </c>
       <c r="E112" s="8" t="s">
@@ -8334,8 +8413,8 @@
       <c r="B113" s="7">
         <v>7</v>
       </c>
-      <c r="C113" s="165"/>
-      <c r="D113" s="153"/>
+      <c r="C113" s="162"/>
+      <c r="D113" s="174"/>
       <c r="E113" s="8" t="s">
         <v>153</v>
       </c>
@@ -8356,8 +8435,8 @@
       <c r="B114" s="7">
         <v>8</v>
       </c>
-      <c r="C114" s="165"/>
-      <c r="D114" s="153"/>
+      <c r="C114" s="162"/>
+      <c r="D114" s="174"/>
       <c r="E114" s="8" t="s">
         <v>154</v>
       </c>
@@ -8378,8 +8457,8 @@
       <c r="B115" s="7">
         <v>9</v>
       </c>
-      <c r="C115" s="165"/>
-      <c r="D115" s="154"/>
+      <c r="C115" s="162"/>
+      <c r="D115" s="175"/>
       <c r="E115" s="8" t="s">
         <v>155</v>
       </c>
@@ -8400,7 +8479,7 @@
       <c r="B116" s="24">
         <v>10</v>
       </c>
-      <c r="C116" s="166"/>
+      <c r="C116" s="163"/>
       <c r="D116" s="31" t="s">
         <v>156</v>
       </c>
@@ -8424,10 +8503,10 @@
       <c r="B117" s="7">
         <v>1</v>
       </c>
-      <c r="C117" s="167" t="s">
+      <c r="C117" s="152" t="s">
         <v>158</v>
       </c>
-      <c r="D117" s="152" t="s">
+      <c r="D117" s="173" t="s">
         <v>159</v>
       </c>
       <c r="E117" s="8" t="s">
@@ -8450,8 +8529,8 @@
       <c r="B118" s="7">
         <v>2</v>
       </c>
-      <c r="C118" s="168"/>
-      <c r="D118" s="153"/>
+      <c r="C118" s="153"/>
+      <c r="D118" s="174"/>
       <c r="E118" s="8" t="s">
         <v>161</v>
       </c>
@@ -8472,8 +8551,8 @@
       <c r="B119" s="7">
         <v>3</v>
       </c>
-      <c r="C119" s="168"/>
-      <c r="D119" s="153"/>
+      <c r="C119" s="153"/>
+      <c r="D119" s="174"/>
       <c r="E119" s="8" t="s">
         <v>162</v>
       </c>
@@ -8494,8 +8573,8 @@
       <c r="B120" s="7">
         <v>4</v>
       </c>
-      <c r="C120" s="168"/>
-      <c r="D120" s="154"/>
+      <c r="C120" s="153"/>
+      <c r="D120" s="175"/>
       <c r="E120" s="8" t="s">
         <v>163</v>
       </c>
@@ -8516,8 +8595,8 @@
       <c r="B121" s="7">
         <v>5</v>
       </c>
-      <c r="C121" s="168"/>
-      <c r="D121" s="152" t="s">
+      <c r="C121" s="153"/>
+      <c r="D121" s="173" t="s">
         <v>164</v>
       </c>
       <c r="E121" s="8" t="s">
@@ -8540,8 +8619,8 @@
       <c r="B122" s="7">
         <v>6</v>
       </c>
-      <c r="C122" s="168"/>
-      <c r="D122" s="154"/>
+      <c r="C122" s="153"/>
+      <c r="D122" s="175"/>
       <c r="E122" s="8" t="s">
         <v>166</v>
       </c>
@@ -8562,8 +8641,8 @@
       <c r="B123" s="7">
         <v>7</v>
       </c>
-      <c r="C123" s="168"/>
-      <c r="D123" s="152" t="s">
+      <c r="C123" s="153"/>
+      <c r="D123" s="173" t="s">
         <v>167</v>
       </c>
       <c r="E123" s="8" t="s">
@@ -8586,8 +8665,8 @@
       <c r="B124" s="7">
         <v>8</v>
       </c>
-      <c r="C124" s="168"/>
-      <c r="D124" s="153"/>
+      <c r="C124" s="153"/>
+      <c r="D124" s="174"/>
       <c r="E124" s="28" t="s">
         <v>169</v>
       </c>
@@ -8608,8 +8687,8 @@
       <c r="B125" s="7">
         <v>9</v>
       </c>
-      <c r="C125" s="169"/>
-      <c r="D125" s="154"/>
+      <c r="C125" s="154"/>
+      <c r="D125" s="175"/>
       <c r="E125" s="8" t="s">
         <v>170</v>
       </c>
@@ -8624,18 +8703,18 @@
       <c r="J125" s="11"/>
     </row>
     <row r="126" spans="1:10" ht="13.8">
-      <c r="A126" s="176" t="s">
+      <c r="A126" s="194" t="s">
         <v>171</v>
       </c>
-      <c r="B126" s="177"/>
-      <c r="C126" s="177"/>
-      <c r="D126" s="177"/>
-      <c r="E126" s="177"/>
-      <c r="F126" s="177"/>
-      <c r="G126" s="177"/>
-      <c r="H126" s="177"/>
-      <c r="I126" s="177"/>
-      <c r="J126" s="178"/>
+      <c r="B126" s="195"/>
+      <c r="C126" s="195"/>
+      <c r="D126" s="195"/>
+      <c r="E126" s="195"/>
+      <c r="F126" s="195"/>
+      <c r="G126" s="195"/>
+      <c r="H126" s="195"/>
+      <c r="I126" s="195"/>
+      <c r="J126" s="196"/>
     </row>
     <row r="127" spans="1:10" ht="13.8">
       <c r="A127" s="6">
@@ -8644,10 +8723,10 @@
       <c r="B127" s="7">
         <v>1</v>
       </c>
-      <c r="C127" s="170" t="s">
+      <c r="C127" s="155" t="s">
         <v>172</v>
       </c>
-      <c r="D127" s="152" t="s">
+      <c r="D127" s="173" t="s">
         <v>173</v>
       </c>
       <c r="E127" s="32" t="s">
@@ -8668,8 +8747,8 @@
       <c r="B128" s="7">
         <v>2</v>
       </c>
-      <c r="C128" s="171"/>
-      <c r="D128" s="153"/>
+      <c r="C128" s="156"/>
+      <c r="D128" s="174"/>
       <c r="E128" s="32" t="s">
         <v>175</v>
       </c>
@@ -8688,8 +8767,8 @@
       <c r="B129" s="7">
         <v>3</v>
       </c>
-      <c r="C129" s="171"/>
-      <c r="D129" s="153"/>
+      <c r="C129" s="156"/>
+      <c r="D129" s="174"/>
       <c r="E129" s="32" t="s">
         <v>176</v>
       </c>
@@ -8708,8 +8787,8 @@
       <c r="B130" s="7">
         <v>4</v>
       </c>
-      <c r="C130" s="171"/>
-      <c r="D130" s="154"/>
+      <c r="C130" s="156"/>
+      <c r="D130" s="175"/>
       <c r="E130" s="32" t="s">
         <v>177</v>
       </c>
@@ -8728,8 +8807,8 @@
       <c r="B131" s="7">
         <v>5</v>
       </c>
-      <c r="C131" s="171"/>
-      <c r="D131" s="152" t="s">
+      <c r="C131" s="156"/>
+      <c r="D131" s="173" t="s">
         <v>178</v>
       </c>
       <c r="E131" s="32" t="s">
@@ -8750,8 +8829,8 @@
       <c r="B132" s="7">
         <v>6</v>
       </c>
-      <c r="C132" s="172"/>
-      <c r="D132" s="154"/>
+      <c r="C132" s="157"/>
+      <c r="D132" s="175"/>
       <c r="E132" s="32" t="s">
         <v>180</v>
       </c>
@@ -8764,18 +8843,18 @@
       <c r="J132" s="11"/>
     </row>
     <row r="133" spans="1:10" ht="13.8">
-      <c r="A133" s="158" t="s">
+      <c r="A133" s="197" t="s">
         <v>181</v>
       </c>
-      <c r="B133" s="159"/>
-      <c r="C133" s="159"/>
-      <c r="D133" s="159"/>
-      <c r="E133" s="159"/>
-      <c r="F133" s="159"/>
-      <c r="G133" s="159"/>
-      <c r="H133" s="159"/>
-      <c r="I133" s="159"/>
-      <c r="J133" s="160"/>
+      <c r="B133" s="198"/>
+      <c r="C133" s="198"/>
+      <c r="D133" s="198"/>
+      <c r="E133" s="198"/>
+      <c r="F133" s="198"/>
+      <c r="G133" s="198"/>
+      <c r="H133" s="198"/>
+      <c r="I133" s="198"/>
+      <c r="J133" s="199"/>
     </row>
     <row r="134" spans="1:10" ht="13.8">
       <c r="A134" s="6">
@@ -8784,10 +8863,10 @@
       <c r="B134" s="7">
         <v>1</v>
       </c>
-      <c r="C134" s="161" t="s">
+      <c r="C134" s="158" t="s">
         <v>182</v>
       </c>
-      <c r="D134" s="152" t="s">
+      <c r="D134" s="173" t="s">
         <v>183</v>
       </c>
       <c r="E134" s="8" t="s">
@@ -8810,8 +8889,8 @@
       <c r="B135" s="7">
         <v>2</v>
       </c>
-      <c r="C135" s="162"/>
-      <c r="D135" s="153"/>
+      <c r="C135" s="159"/>
+      <c r="D135" s="174"/>
       <c r="E135" s="8" t="s">
         <v>185</v>
       </c>
@@ -8832,8 +8911,8 @@
       <c r="B136" s="7">
         <v>3</v>
       </c>
-      <c r="C136" s="162"/>
-      <c r="D136" s="154"/>
+      <c r="C136" s="159"/>
+      <c r="D136" s="175"/>
       <c r="E136" s="8" t="s">
         <v>186</v>
       </c>
@@ -8854,8 +8933,8 @@
       <c r="B137" s="7">
         <v>4</v>
       </c>
-      <c r="C137" s="162"/>
-      <c r="D137" s="152" t="s">
+      <c r="C137" s="159"/>
+      <c r="D137" s="173" t="s">
         <v>187</v>
       </c>
       <c r="E137" s="8" t="s">
@@ -8878,8 +8957,8 @@
       <c r="B138" s="7">
         <v>5</v>
       </c>
-      <c r="C138" s="162"/>
-      <c r="D138" s="153"/>
+      <c r="C138" s="159"/>
+      <c r="D138" s="174"/>
       <c r="E138" s="8" t="s">
         <v>189</v>
       </c>
@@ -8900,8 +8979,8 @@
       <c r="B139" s="7">
         <v>6</v>
       </c>
-      <c r="C139" s="162"/>
-      <c r="D139" s="153"/>
+      <c r="C139" s="159"/>
+      <c r="D139" s="174"/>
       <c r="E139" s="8" t="s">
         <v>190</v>
       </c>
@@ -8922,8 +9001,8 @@
       <c r="B140" s="7">
         <v>7</v>
       </c>
-      <c r="C140" s="162"/>
-      <c r="D140" s="153"/>
+      <c r="C140" s="159"/>
+      <c r="D140" s="174"/>
       <c r="E140" s="8" t="s">
         <v>191</v>
       </c>
@@ -8944,8 +9023,8 @@
       <c r="B141" s="7">
         <v>8</v>
       </c>
-      <c r="C141" s="162"/>
-      <c r="D141" s="153"/>
+      <c r="C141" s="159"/>
+      <c r="D141" s="174"/>
       <c r="E141" s="8" t="s">
         <v>192</v>
       </c>
@@ -8966,8 +9045,8 @@
       <c r="B142" s="7">
         <v>9</v>
       </c>
-      <c r="C142" s="162"/>
-      <c r="D142" s="153"/>
+      <c r="C142" s="159"/>
+      <c r="D142" s="174"/>
       <c r="E142" s="8" t="s">
         <v>193</v>
       </c>
@@ -8988,8 +9067,8 @@
       <c r="B143" s="7">
         <v>10</v>
       </c>
-      <c r="C143" s="162"/>
-      <c r="D143" s="154"/>
+      <c r="C143" s="159"/>
+      <c r="D143" s="175"/>
       <c r="E143" s="8" t="s">
         <v>194</v>
       </c>
@@ -9010,8 +9089,8 @@
       <c r="B144" s="7">
         <v>11</v>
       </c>
-      <c r="C144" s="162"/>
-      <c r="D144" s="152" t="s">
+      <c r="C144" s="159"/>
+      <c r="D144" s="173" t="s">
         <v>195</v>
       </c>
       <c r="E144" s="8" t="s">
@@ -9034,8 +9113,8 @@
       <c r="B145" s="7">
         <v>12</v>
       </c>
-      <c r="C145" s="162"/>
-      <c r="D145" s="153"/>
+      <c r="C145" s="159"/>
+      <c r="D145" s="174"/>
       <c r="E145" s="8" t="s">
         <v>197</v>
       </c>
@@ -9056,8 +9135,8 @@
       <c r="B146" s="7">
         <v>13</v>
       </c>
-      <c r="C146" s="162"/>
-      <c r="D146" s="153"/>
+      <c r="C146" s="159"/>
+      <c r="D146" s="174"/>
       <c r="E146" s="8" t="s">
         <v>198</v>
       </c>
@@ -9078,8 +9157,8 @@
       <c r="B147" s="7">
         <v>14</v>
       </c>
-      <c r="C147" s="162"/>
-      <c r="D147" s="153"/>
+      <c r="C147" s="159"/>
+      <c r="D147" s="174"/>
       <c r="E147" s="8" t="s">
         <v>199</v>
       </c>
@@ -9100,8 +9179,8 @@
       <c r="B148" s="7">
         <v>15</v>
       </c>
-      <c r="C148" s="162"/>
-      <c r="D148" s="153"/>
+      <c r="C148" s="159"/>
+      <c r="D148" s="174"/>
       <c r="E148" s="8" t="s">
         <v>200</v>
       </c>
@@ -9122,8 +9201,8 @@
       <c r="B149" s="7">
         <v>16</v>
       </c>
-      <c r="C149" s="162"/>
-      <c r="D149" s="153"/>
+      <c r="C149" s="159"/>
+      <c r="D149" s="174"/>
       <c r="E149" s="8" t="s">
         <v>201</v>
       </c>
@@ -9144,8 +9223,8 @@
       <c r="B150" s="7">
         <v>17</v>
       </c>
-      <c r="C150" s="162"/>
-      <c r="D150" s="154"/>
+      <c r="C150" s="159"/>
+      <c r="D150" s="175"/>
       <c r="E150" s="8" t="s">
         <v>202</v>
       </c>
@@ -9166,8 +9245,8 @@
       <c r="B151" s="7">
         <v>18</v>
       </c>
-      <c r="C151" s="162"/>
-      <c r="D151" s="152" t="s">
+      <c r="C151" s="159"/>
+      <c r="D151" s="173" t="s">
         <v>203</v>
       </c>
       <c r="E151" s="8" t="s">
@@ -9190,8 +9269,8 @@
       <c r="B152" s="7">
         <v>19</v>
       </c>
-      <c r="C152" s="162"/>
-      <c r="D152" s="153"/>
+      <c r="C152" s="159"/>
+      <c r="D152" s="174"/>
       <c r="E152" s="8" t="s">
         <v>205</v>
       </c>
@@ -9212,8 +9291,8 @@
       <c r="B153" s="7">
         <v>20</v>
       </c>
-      <c r="C153" s="162"/>
-      <c r="D153" s="153"/>
+      <c r="C153" s="159"/>
+      <c r="D153" s="174"/>
       <c r="E153" s="8" t="s">
         <v>206</v>
       </c>
@@ -9234,8 +9313,8 @@
       <c r="B154" s="7">
         <v>21</v>
       </c>
-      <c r="C154" s="162"/>
-      <c r="D154" s="153"/>
+      <c r="C154" s="159"/>
+      <c r="D154" s="174"/>
       <c r="E154" s="8" t="s">
         <v>207</v>
       </c>
@@ -9256,8 +9335,8 @@
       <c r="B155" s="7">
         <v>22</v>
       </c>
-      <c r="C155" s="162"/>
-      <c r="D155" s="153"/>
+      <c r="C155" s="159"/>
+      <c r="D155" s="174"/>
       <c r="E155" s="8" t="s">
         <v>208</v>
       </c>
@@ -9278,8 +9357,8 @@
       <c r="B156" s="7">
         <v>23</v>
       </c>
-      <c r="C156" s="162"/>
-      <c r="D156" s="154"/>
+      <c r="C156" s="159"/>
+      <c r="D156" s="175"/>
       <c r="E156" s="8" t="s">
         <v>209</v>
       </c>
@@ -9300,8 +9379,8 @@
       <c r="B157" s="7">
         <v>24</v>
       </c>
-      <c r="C157" s="162"/>
-      <c r="D157" s="152" t="s">
+      <c r="C157" s="159"/>
+      <c r="D157" s="173" t="s">
         <v>210</v>
       </c>
       <c r="E157" s="8" t="s">
@@ -9324,8 +9403,8 @@
       <c r="B158" s="7">
         <v>25</v>
       </c>
-      <c r="C158" s="162"/>
-      <c r="D158" s="153"/>
+      <c r="C158" s="159"/>
+      <c r="D158" s="174"/>
       <c r="E158" s="8" t="s">
         <v>212</v>
       </c>
@@ -9346,8 +9425,8 @@
       <c r="B159" s="7">
         <v>26</v>
       </c>
-      <c r="C159" s="162"/>
-      <c r="D159" s="154"/>
+      <c r="C159" s="159"/>
+      <c r="D159" s="175"/>
       <c r="E159" s="8" t="s">
         <v>213</v>
       </c>
@@ -9368,8 +9447,8 @@
       <c r="B160" s="7">
         <v>27</v>
       </c>
-      <c r="C160" s="162"/>
-      <c r="D160" s="152" t="s">
+      <c r="C160" s="159"/>
+      <c r="D160" s="173" t="s">
         <v>214</v>
       </c>
       <c r="E160" s="8" t="s">
@@ -9392,8 +9471,8 @@
       <c r="B161" s="7">
         <v>28</v>
       </c>
-      <c r="C161" s="162"/>
-      <c r="D161" s="153"/>
+      <c r="C161" s="159"/>
+      <c r="D161" s="174"/>
       <c r="E161" s="8" t="s">
         <v>216</v>
       </c>
@@ -9414,8 +9493,8 @@
       <c r="B162" s="7">
         <v>29</v>
       </c>
-      <c r="C162" s="162"/>
-      <c r="D162" s="153"/>
+      <c r="C162" s="159"/>
+      <c r="D162" s="174"/>
       <c r="E162" s="8" t="s">
         <v>217</v>
       </c>
@@ -9436,8 +9515,8 @@
       <c r="B163" s="7">
         <v>30</v>
       </c>
-      <c r="C163" s="162"/>
-      <c r="D163" s="153"/>
+      <c r="C163" s="159"/>
+      <c r="D163" s="174"/>
       <c r="E163" s="8" t="s">
         <v>218</v>
       </c>
@@ -9458,8 +9537,8 @@
       <c r="B164" s="7">
         <v>31</v>
       </c>
-      <c r="C164" s="162"/>
-      <c r="D164" s="153"/>
+      <c r="C164" s="159"/>
+      <c r="D164" s="174"/>
       <c r="E164" s="8" t="s">
         <v>219</v>
       </c>
@@ -9480,8 +9559,8 @@
       <c r="B165" s="7">
         <v>32</v>
       </c>
-      <c r="C165" s="162"/>
-      <c r="D165" s="154"/>
+      <c r="C165" s="159"/>
+      <c r="D165" s="175"/>
       <c r="E165" s="8" t="s">
         <v>220</v>
       </c>
@@ -9502,8 +9581,8 @@
       <c r="B166" s="7">
         <v>33</v>
       </c>
-      <c r="C166" s="162"/>
-      <c r="D166" s="152" t="s">
+      <c r="C166" s="159"/>
+      <c r="D166" s="173" t="s">
         <v>221</v>
       </c>
       <c r="E166" s="8" t="s">
@@ -9526,8 +9605,8 @@
       <c r="B167" s="7">
         <v>34</v>
       </c>
-      <c r="C167" s="162"/>
-      <c r="D167" s="153"/>
+      <c r="C167" s="159"/>
+      <c r="D167" s="174"/>
       <c r="E167" s="8" t="s">
         <v>223</v>
       </c>
@@ -9546,8 +9625,8 @@
       <c r="B168" s="7">
         <v>35</v>
       </c>
-      <c r="C168" s="162"/>
-      <c r="D168" s="153"/>
+      <c r="C168" s="159"/>
+      <c r="D168" s="174"/>
       <c r="E168" s="8" t="s">
         <v>224</v>
       </c>
@@ -9568,8 +9647,8 @@
       <c r="B169" s="7">
         <v>36</v>
       </c>
-      <c r="C169" s="162"/>
-      <c r="D169" s="153"/>
+      <c r="C169" s="159"/>
+      <c r="D169" s="174"/>
       <c r="E169" s="8" t="s">
         <v>225</v>
       </c>
@@ -9590,8 +9669,8 @@
       <c r="B170" s="7">
         <v>37</v>
       </c>
-      <c r="C170" s="162"/>
-      <c r="D170" s="153"/>
+      <c r="C170" s="159"/>
+      <c r="D170" s="174"/>
       <c r="E170" s="8" t="s">
         <v>226</v>
       </c>
@@ -9612,8 +9691,8 @@
       <c r="B171" s="7">
         <v>38</v>
       </c>
-      <c r="C171" s="162"/>
-      <c r="D171" s="153"/>
+      <c r="C171" s="159"/>
+      <c r="D171" s="174"/>
       <c r="E171" s="8" t="s">
         <v>227</v>
       </c>
@@ -9634,8 +9713,8 @@
       <c r="B172" s="7">
         <v>39</v>
       </c>
-      <c r="C172" s="162"/>
-      <c r="D172" s="154"/>
+      <c r="C172" s="159"/>
+      <c r="D172" s="175"/>
       <c r="E172" s="8" t="s">
         <v>228</v>
       </c>
@@ -9656,8 +9735,8 @@
       <c r="B173" s="7">
         <v>40</v>
       </c>
-      <c r="C173" s="162"/>
-      <c r="D173" s="152" t="s">
+      <c r="C173" s="159"/>
+      <c r="D173" s="173" t="s">
         <v>48</v>
       </c>
       <c r="E173" s="11" t="s">
@@ -9680,8 +9759,8 @@
       <c r="B174" s="7">
         <v>41</v>
       </c>
-      <c r="C174" s="162"/>
-      <c r="D174" s="153"/>
+      <c r="C174" s="159"/>
+      <c r="D174" s="174"/>
       <c r="E174" s="8" t="s">
         <v>230</v>
       </c>
@@ -9702,8 +9781,8 @@
       <c r="B175" s="7">
         <v>42</v>
       </c>
-      <c r="C175" s="162"/>
-      <c r="D175" s="153"/>
+      <c r="C175" s="159"/>
+      <c r="D175" s="174"/>
       <c r="E175" s="8" t="s">
         <v>231</v>
       </c>
@@ -9724,8 +9803,8 @@
       <c r="B176" s="24">
         <v>43</v>
       </c>
-      <c r="C176" s="163"/>
-      <c r="D176" s="154"/>
+      <c r="C176" s="160"/>
+      <c r="D176" s="175"/>
       <c r="E176" s="17" t="s">
         <v>232</v>
       </c>
@@ -9746,10 +9825,10 @@
       <c r="B177" s="7">
         <v>1</v>
       </c>
-      <c r="C177" s="164" t="s">
+      <c r="C177" s="161" t="s">
         <v>233</v>
       </c>
-      <c r="D177" s="152" t="s">
+      <c r="D177" s="173" t="s">
         <v>234</v>
       </c>
       <c r="E177" s="8" t="s">
@@ -9772,8 +9851,8 @@
       <c r="B178" s="7">
         <v>2</v>
       </c>
-      <c r="C178" s="165"/>
-      <c r="D178" s="154"/>
+      <c r="C178" s="162"/>
+      <c r="D178" s="175"/>
       <c r="E178" s="8" t="s">
         <v>236</v>
       </c>
@@ -9794,8 +9873,8 @@
       <c r="B179" s="7">
         <v>3</v>
       </c>
-      <c r="C179" s="165"/>
-      <c r="D179" s="152" t="s">
+      <c r="C179" s="162"/>
+      <c r="D179" s="173" t="s">
         <v>237</v>
       </c>
       <c r="E179" s="8" t="s">
@@ -9818,8 +9897,8 @@
       <c r="B180" s="7">
         <v>4</v>
       </c>
-      <c r="C180" s="165"/>
-      <c r="D180" s="153"/>
+      <c r="C180" s="162"/>
+      <c r="D180" s="174"/>
       <c r="E180" s="8" t="s">
         <v>239</v>
       </c>
@@ -9840,8 +9919,8 @@
       <c r="B181" s="7">
         <v>5</v>
       </c>
-      <c r="C181" s="165"/>
-      <c r="D181" s="153"/>
+      <c r="C181" s="162"/>
+      <c r="D181" s="174"/>
       <c r="E181" s="8" t="s">
         <v>240</v>
       </c>
@@ -9862,8 +9941,8 @@
       <c r="B182" s="7">
         <v>6</v>
       </c>
-      <c r="C182" s="165"/>
-      <c r="D182" s="153"/>
+      <c r="C182" s="162"/>
+      <c r="D182" s="174"/>
       <c r="E182" s="8" t="s">
         <v>241</v>
       </c>
@@ -9884,8 +9963,8 @@
       <c r="B183" s="7">
         <v>7</v>
       </c>
-      <c r="C183" s="165"/>
-      <c r="D183" s="153"/>
+      <c r="C183" s="162"/>
+      <c r="D183" s="174"/>
       <c r="E183" s="8" t="s">
         <v>242</v>
       </c>
@@ -9906,8 +9985,8 @@
       <c r="B184" s="7">
         <v>8</v>
       </c>
-      <c r="C184" s="165"/>
-      <c r="D184" s="154"/>
+      <c r="C184" s="162"/>
+      <c r="D184" s="175"/>
       <c r="E184" s="8" t="s">
         <v>243</v>
       </c>
@@ -9928,8 +10007,8 @@
       <c r="B185" s="7">
         <v>9</v>
       </c>
-      <c r="C185" s="165"/>
-      <c r="D185" s="152" t="s">
+      <c r="C185" s="162"/>
+      <c r="D185" s="173" t="s">
         <v>244</v>
       </c>
       <c r="E185" s="8" t="s">
@@ -9952,8 +10031,8 @@
       <c r="B186" s="7">
         <v>10</v>
       </c>
-      <c r="C186" s="165"/>
-      <c r="D186" s="154"/>
+      <c r="C186" s="162"/>
+      <c r="D186" s="175"/>
       <c r="E186" s="8" t="s">
         <v>246</v>
       </c>
@@ -9974,8 +10053,8 @@
       <c r="B187" s="7">
         <v>11</v>
       </c>
-      <c r="C187" s="165"/>
-      <c r="D187" s="152" t="s">
+      <c r="C187" s="162"/>
+      <c r="D187" s="173" t="s">
         <v>247</v>
       </c>
       <c r="E187" s="8" t="s">
@@ -9998,8 +10077,8 @@
       <c r="B188" s="7">
         <v>12</v>
       </c>
-      <c r="C188" s="165"/>
-      <c r="D188" s="153"/>
+      <c r="C188" s="162"/>
+      <c r="D188" s="174"/>
       <c r="E188" s="8" t="s">
         <v>249</v>
       </c>
@@ -10020,8 +10099,8 @@
       <c r="B189" s="7">
         <v>13</v>
       </c>
-      <c r="C189" s="165"/>
-      <c r="D189" s="153"/>
+      <c r="C189" s="162"/>
+      <c r="D189" s="174"/>
       <c r="E189" s="11" t="s">
         <v>250</v>
       </c>
@@ -10042,8 +10121,8 @@
       <c r="B190" s="7">
         <v>14</v>
       </c>
-      <c r="C190" s="165"/>
-      <c r="D190" s="154"/>
+      <c r="C190" s="162"/>
+      <c r="D190" s="175"/>
       <c r="E190" s="8" t="s">
         <v>251</v>
       </c>
@@ -10064,8 +10143,8 @@
       <c r="B191" s="7">
         <v>15</v>
       </c>
-      <c r="C191" s="165"/>
-      <c r="D191" s="152" t="s">
+      <c r="C191" s="162"/>
+      <c r="D191" s="173" t="s">
         <v>252</v>
       </c>
       <c r="E191" s="8" t="s">
@@ -10088,8 +10167,8 @@
       <c r="B192" s="7">
         <v>16</v>
       </c>
-      <c r="C192" s="165"/>
-      <c r="D192" s="153"/>
+      <c r="C192" s="162"/>
+      <c r="D192" s="174"/>
       <c r="E192" s="8" t="s">
         <v>254</v>
       </c>
@@ -10110,8 +10189,8 @@
       <c r="B193" s="7">
         <v>17</v>
       </c>
-      <c r="C193" s="165"/>
-      <c r="D193" s="153"/>
+      <c r="C193" s="162"/>
+      <c r="D193" s="174"/>
       <c r="E193" s="8" t="s">
         <v>255</v>
       </c>
@@ -10132,8 +10211,8 @@
       <c r="B194" s="7">
         <v>18</v>
       </c>
-      <c r="C194" s="165"/>
-      <c r="D194" s="153"/>
+      <c r="C194" s="162"/>
+      <c r="D194" s="174"/>
       <c r="E194" s="8" t="s">
         <v>256</v>
       </c>
@@ -10154,8 +10233,8 @@
       <c r="B195" s="7">
         <v>19</v>
       </c>
-      <c r="C195" s="165"/>
-      <c r="D195" s="153"/>
+      <c r="C195" s="162"/>
+      <c r="D195" s="174"/>
       <c r="E195" s="8" t="s">
         <v>257</v>
       </c>
@@ -10176,8 +10255,8 @@
       <c r="B196" s="7">
         <v>20</v>
       </c>
-      <c r="C196" s="165"/>
-      <c r="D196" s="153"/>
+      <c r="C196" s="162"/>
+      <c r="D196" s="174"/>
       <c r="E196" s="8" t="s">
         <v>258</v>
       </c>
@@ -10198,8 +10277,8 @@
       <c r="B197" s="7">
         <v>21</v>
       </c>
-      <c r="C197" s="165"/>
-      <c r="D197" s="153"/>
+      <c r="C197" s="162"/>
+      <c r="D197" s="174"/>
       <c r="E197" s="8" t="s">
         <v>259</v>
       </c>
@@ -10220,8 +10299,8 @@
       <c r="B198" s="7">
         <v>22</v>
       </c>
-      <c r="C198" s="165"/>
-      <c r="D198" s="154"/>
+      <c r="C198" s="162"/>
+      <c r="D198" s="175"/>
       <c r="E198" s="8" t="s">
         <v>260</v>
       </c>
@@ -10242,8 +10321,8 @@
       <c r="B199" s="7">
         <v>23</v>
       </c>
-      <c r="C199" s="165"/>
-      <c r="D199" s="152" t="s">
+      <c r="C199" s="162"/>
+      <c r="D199" s="173" t="s">
         <v>261</v>
       </c>
       <c r="E199" s="8" t="s">
@@ -10266,8 +10345,8 @@
       <c r="B200" s="7">
         <v>24</v>
       </c>
-      <c r="C200" s="165"/>
-      <c r="D200" s="153"/>
+      <c r="C200" s="162"/>
+      <c r="D200" s="174"/>
       <c r="E200" s="8" t="s">
         <v>263</v>
       </c>
@@ -10288,8 +10367,8 @@
       <c r="B201" s="7">
         <v>25</v>
       </c>
-      <c r="C201" s="165"/>
-      <c r="D201" s="153"/>
+      <c r="C201" s="162"/>
+      <c r="D201" s="174"/>
       <c r="E201" s="8" t="s">
         <v>264</v>
       </c>
@@ -10310,8 +10389,8 @@
       <c r="B202" s="7">
         <v>26</v>
       </c>
-      <c r="C202" s="165"/>
-      <c r="D202" s="154"/>
+      <c r="C202" s="162"/>
+      <c r="D202" s="175"/>
       <c r="E202" s="8" t="s">
         <v>265</v>
       </c>
@@ -10332,8 +10411,8 @@
       <c r="B203" s="7">
         <v>27</v>
       </c>
-      <c r="C203" s="165"/>
-      <c r="D203" s="152" t="s">
+      <c r="C203" s="162"/>
+      <c r="D203" s="173" t="s">
         <v>266</v>
       </c>
       <c r="E203" s="8" t="s">
@@ -10356,8 +10435,8 @@
       <c r="B204" s="24">
         <v>28</v>
       </c>
-      <c r="C204" s="166"/>
-      <c r="D204" s="154"/>
+      <c r="C204" s="163"/>
+      <c r="D204" s="175"/>
       <c r="E204" s="17" t="s">
         <v>268</v>
       </c>
@@ -10378,10 +10457,10 @@
       <c r="B205" s="7">
         <v>1</v>
       </c>
-      <c r="C205" s="167" t="s">
+      <c r="C205" s="152" t="s">
         <v>269</v>
       </c>
-      <c r="D205" s="152" t="s">
+      <c r="D205" s="173" t="s">
         <v>270</v>
       </c>
       <c r="E205" s="8" t="s">
@@ -10404,8 +10483,8 @@
       <c r="B206" s="7">
         <v>2</v>
       </c>
-      <c r="C206" s="168"/>
-      <c r="D206" s="153"/>
+      <c r="C206" s="153"/>
+      <c r="D206" s="174"/>
       <c r="E206" s="8" t="s">
         <v>272</v>
       </c>
@@ -10426,8 +10505,8 @@
       <c r="B207" s="7">
         <v>3</v>
       </c>
-      <c r="C207" s="168"/>
-      <c r="D207" s="153"/>
+      <c r="C207" s="153"/>
+      <c r="D207" s="174"/>
       <c r="E207" s="8" t="s">
         <v>273</v>
       </c>
@@ -10448,8 +10527,8 @@
       <c r="B208" s="7">
         <v>4</v>
       </c>
-      <c r="C208" s="168"/>
-      <c r="D208" s="153"/>
+      <c r="C208" s="153"/>
+      <c r="D208" s="174"/>
       <c r="E208" s="8" t="s">
         <v>274</v>
       </c>
@@ -10470,8 +10549,8 @@
       <c r="B209" s="7">
         <v>5</v>
       </c>
-      <c r="C209" s="168"/>
-      <c r="D209" s="154"/>
+      <c r="C209" s="153"/>
+      <c r="D209" s="175"/>
       <c r="E209" s="8" t="s">
         <v>275</v>
       </c>
@@ -10492,8 +10571,8 @@
       <c r="B210" s="7">
         <v>6</v>
       </c>
-      <c r="C210" s="168"/>
-      <c r="D210" s="152" t="s">
+      <c r="C210" s="153"/>
+      <c r="D210" s="173" t="s">
         <v>276</v>
       </c>
       <c r="E210" s="8" t="s">
@@ -10516,8 +10595,8 @@
       <c r="B211" s="7">
         <v>7</v>
       </c>
-      <c r="C211" s="168"/>
-      <c r="D211" s="154"/>
+      <c r="C211" s="153"/>
+      <c r="D211" s="175"/>
       <c r="E211" s="8" t="s">
         <v>278</v>
       </c>
@@ -10538,8 +10617,8 @@
       <c r="B212" s="7">
         <v>8</v>
       </c>
-      <c r="C212" s="168"/>
-      <c r="D212" s="152" t="s">
+      <c r="C212" s="153"/>
+      <c r="D212" s="173" t="s">
         <v>279</v>
       </c>
       <c r="E212" s="8" t="s">
@@ -10562,8 +10641,8 @@
       <c r="B213" s="7">
         <v>9</v>
       </c>
-      <c r="C213" s="168"/>
-      <c r="D213" s="153"/>
+      <c r="C213" s="153"/>
+      <c r="D213" s="174"/>
       <c r="E213" s="8" t="s">
         <v>281</v>
       </c>
@@ -10584,8 +10663,8 @@
       <c r="B214" s="7">
         <v>10</v>
       </c>
-      <c r="C214" s="169"/>
-      <c r="D214" s="154"/>
+      <c r="C214" s="154"/>
+      <c r="D214" s="175"/>
       <c r="E214" s="8" t="s">
         <v>282</v>
       </c>
@@ -10600,18 +10679,18 @@
       <c r="J214" s="11"/>
     </row>
     <row r="215" spans="1:10" ht="13.8">
-      <c r="A215" s="188" t="s">
+      <c r="A215" s="182" t="s">
         <v>283</v>
       </c>
-      <c r="B215" s="189"/>
-      <c r="C215" s="189"/>
-      <c r="D215" s="189"/>
-      <c r="E215" s="189"/>
-      <c r="F215" s="189"/>
-      <c r="G215" s="189"/>
-      <c r="H215" s="189"/>
-      <c r="I215" s="189"/>
-      <c r="J215" s="190"/>
+      <c r="B215" s="183"/>
+      <c r="C215" s="183"/>
+      <c r="D215" s="183"/>
+      <c r="E215" s="183"/>
+      <c r="F215" s="183"/>
+      <c r="G215" s="183"/>
+      <c r="H215" s="183"/>
+      <c r="I215" s="183"/>
+      <c r="J215" s="184"/>
     </row>
     <row r="216" spans="1:10" ht="13.8">
       <c r="A216" s="6">
@@ -10620,10 +10699,10 @@
       <c r="B216" s="7">
         <v>1</v>
       </c>
-      <c r="C216" s="170" t="s">
+      <c r="C216" s="155" t="s">
         <v>284</v>
       </c>
-      <c r="D216" s="152" t="s">
+      <c r="D216" s="173" t="s">
         <v>285</v>
       </c>
       <c r="E216" s="8" t="s">
@@ -10646,8 +10725,8 @@
       <c r="B217" s="7">
         <v>2</v>
       </c>
-      <c r="C217" s="171"/>
-      <c r="D217" s="153"/>
+      <c r="C217" s="156"/>
+      <c r="D217" s="174"/>
       <c r="E217" s="8" t="s">
         <v>287</v>
       </c>
@@ -10668,8 +10747,8 @@
       <c r="B218" s="7">
         <v>3</v>
       </c>
-      <c r="C218" s="171"/>
-      <c r="D218" s="153"/>
+      <c r="C218" s="156"/>
+      <c r="D218" s="174"/>
       <c r="E218" s="8" t="s">
         <v>288</v>
       </c>
@@ -10690,8 +10769,8 @@
       <c r="B219" s="7">
         <v>4</v>
       </c>
-      <c r="C219" s="171"/>
-      <c r="D219" s="153"/>
+      <c r="C219" s="156"/>
+      <c r="D219" s="174"/>
       <c r="E219" s="8" t="s">
         <v>289</v>
       </c>
@@ -10712,8 +10791,8 @@
       <c r="B220" s="7">
         <v>5</v>
       </c>
-      <c r="C220" s="171"/>
-      <c r="D220" s="153"/>
+      <c r="C220" s="156"/>
+      <c r="D220" s="174"/>
       <c r="E220" s="8" t="s">
         <v>290</v>
       </c>
@@ -10734,8 +10813,8 @@
       <c r="B221" s="7">
         <v>6</v>
       </c>
-      <c r="C221" s="171"/>
-      <c r="D221" s="153"/>
+      <c r="C221" s="156"/>
+      <c r="D221" s="174"/>
       <c r="E221" s="8" t="s">
         <v>291</v>
       </c>
@@ -10756,8 +10835,8 @@
       <c r="B222" s="7">
         <v>7</v>
       </c>
-      <c r="C222" s="171"/>
-      <c r="D222" s="153"/>
+      <c r="C222" s="156"/>
+      <c r="D222" s="174"/>
       <c r="E222" s="8" t="s">
         <v>292</v>
       </c>
@@ -10778,8 +10857,8 @@
       <c r="B223" s="7">
         <v>8</v>
       </c>
-      <c r="C223" s="171"/>
-      <c r="D223" s="153"/>
+      <c r="C223" s="156"/>
+      <c r="D223" s="174"/>
       <c r="E223" s="8" t="s">
         <v>293</v>
       </c>
@@ -10800,8 +10879,8 @@
       <c r="B224" s="7">
         <v>9</v>
       </c>
-      <c r="C224" s="171"/>
-      <c r="D224" s="153"/>
+      <c r="C224" s="156"/>
+      <c r="D224" s="174"/>
       <c r="E224" s="8" t="s">
         <v>294</v>
       </c>
@@ -10822,8 +10901,8 @@
       <c r="B225" s="7">
         <v>10</v>
       </c>
-      <c r="C225" s="171"/>
-      <c r="D225" s="154"/>
+      <c r="C225" s="156"/>
+      <c r="D225" s="175"/>
       <c r="E225" s="8" t="s">
         <v>295</v>
       </c>
@@ -10844,8 +10923,8 @@
       <c r="B226" s="7">
         <v>11</v>
       </c>
-      <c r="C226" s="171"/>
-      <c r="D226" s="152" t="s">
+      <c r="C226" s="156"/>
+      <c r="D226" s="173" t="s">
         <v>296</v>
       </c>
       <c r="E226" s="8" t="s">
@@ -10868,8 +10947,8 @@
       <c r="B227" s="7">
         <v>12</v>
       </c>
-      <c r="C227" s="171"/>
-      <c r="D227" s="153"/>
+      <c r="C227" s="156"/>
+      <c r="D227" s="174"/>
       <c r="E227" s="8" t="s">
         <v>298</v>
       </c>
@@ -10890,8 +10969,8 @@
       <c r="B228" s="7">
         <v>13</v>
       </c>
-      <c r="C228" s="171"/>
-      <c r="D228" s="153"/>
+      <c r="C228" s="156"/>
+      <c r="D228" s="174"/>
       <c r="E228" s="8" t="s">
         <v>299</v>
       </c>
@@ -10912,8 +10991,8 @@
       <c r="B229" s="7">
         <v>14</v>
       </c>
-      <c r="C229" s="171"/>
-      <c r="D229" s="153"/>
+      <c r="C229" s="156"/>
+      <c r="D229" s="174"/>
       <c r="E229" s="8" t="s">
         <v>300</v>
       </c>
@@ -10934,8 +11013,8 @@
       <c r="B230" s="7">
         <v>15</v>
       </c>
-      <c r="C230" s="171"/>
-      <c r="D230" s="153"/>
+      <c r="C230" s="156"/>
+      <c r="D230" s="174"/>
       <c r="E230" s="8" t="s">
         <v>301</v>
       </c>
@@ -10956,8 +11035,8 @@
       <c r="B231" s="7">
         <v>16</v>
       </c>
-      <c r="C231" s="171"/>
-      <c r="D231" s="153"/>
+      <c r="C231" s="156"/>
+      <c r="D231" s="174"/>
       <c r="E231" s="8" t="s">
         <v>302</v>
       </c>
@@ -10978,8 +11057,8 @@
       <c r="B232" s="7">
         <v>17</v>
       </c>
-      <c r="C232" s="171"/>
-      <c r="D232" s="153"/>
+      <c r="C232" s="156"/>
+      <c r="D232" s="174"/>
       <c r="E232" s="8" t="s">
         <v>303</v>
       </c>
@@ -11000,8 +11079,8 @@
       <c r="B233" s="7">
         <v>18</v>
       </c>
-      <c r="C233" s="171"/>
-      <c r="D233" s="154"/>
+      <c r="C233" s="156"/>
+      <c r="D233" s="175"/>
       <c r="E233" s="8" t="s">
         <v>304</v>
       </c>
@@ -11022,8 +11101,8 @@
       <c r="B234" s="7">
         <v>19</v>
       </c>
-      <c r="C234" s="171"/>
-      <c r="D234" s="152" t="s">
+      <c r="C234" s="156"/>
+      <c r="D234" s="173" t="s">
         <v>305</v>
       </c>
       <c r="E234" s="8" t="s">
@@ -11046,8 +11125,8 @@
       <c r="B235" s="7">
         <v>20</v>
       </c>
-      <c r="C235" s="171"/>
-      <c r="D235" s="153"/>
+      <c r="C235" s="156"/>
+      <c r="D235" s="174"/>
       <c r="E235" s="8" t="s">
         <v>307</v>
       </c>
@@ -11068,8 +11147,8 @@
       <c r="B236" s="7">
         <v>21</v>
       </c>
-      <c r="C236" s="171"/>
-      <c r="D236" s="153"/>
+      <c r="C236" s="156"/>
+      <c r="D236" s="174"/>
       <c r="E236" s="8" t="s">
         <v>308</v>
       </c>
@@ -11090,8 +11169,8 @@
       <c r="B237" s="7">
         <v>22</v>
       </c>
-      <c r="C237" s="171"/>
-      <c r="D237" s="153"/>
+      <c r="C237" s="156"/>
+      <c r="D237" s="174"/>
       <c r="E237" s="8" t="s">
         <v>309</v>
       </c>
@@ -11112,8 +11191,8 @@
       <c r="B238" s="7">
         <v>23</v>
       </c>
-      <c r="C238" s="171"/>
-      <c r="D238" s="153"/>
+      <c r="C238" s="156"/>
+      <c r="D238" s="174"/>
       <c r="E238" s="8" t="s">
         <v>310</v>
       </c>
@@ -11134,8 +11213,8 @@
       <c r="B239" s="7">
         <v>24</v>
       </c>
-      <c r="C239" s="171"/>
-      <c r="D239" s="153"/>
+      <c r="C239" s="156"/>
+      <c r="D239" s="174"/>
       <c r="E239" s="8" t="s">
         <v>311</v>
       </c>
@@ -11156,8 +11235,8 @@
       <c r="B240" s="7">
         <v>25</v>
       </c>
-      <c r="C240" s="171"/>
-      <c r="D240" s="154"/>
+      <c r="C240" s="156"/>
+      <c r="D240" s="175"/>
       <c r="E240" s="8" t="s">
         <v>312</v>
       </c>
@@ -11178,8 +11257,8 @@
       <c r="B241" s="7">
         <v>26</v>
       </c>
-      <c r="C241" s="171"/>
-      <c r="D241" s="152" t="s">
+      <c r="C241" s="156"/>
+      <c r="D241" s="173" t="s">
         <v>313</v>
       </c>
       <c r="E241" s="8" t="s">
@@ -11202,8 +11281,8 @@
       <c r="B242" s="7">
         <v>27</v>
       </c>
-      <c r="C242" s="171"/>
-      <c r="D242" s="153"/>
+      <c r="C242" s="156"/>
+      <c r="D242" s="174"/>
       <c r="E242" s="8" t="s">
         <v>315</v>
       </c>
@@ -11224,8 +11303,8 @@
       <c r="B243" s="7">
         <v>28</v>
       </c>
-      <c r="C243" s="171"/>
-      <c r="D243" s="154"/>
+      <c r="C243" s="156"/>
+      <c r="D243" s="175"/>
       <c r="E243" s="8" t="s">
         <v>316</v>
       </c>
@@ -11246,8 +11325,8 @@
       <c r="B244" s="7">
         <v>29</v>
       </c>
-      <c r="C244" s="171"/>
-      <c r="D244" s="152" t="s">
+      <c r="C244" s="156"/>
+      <c r="D244" s="173" t="s">
         <v>317</v>
       </c>
       <c r="E244" s="8" t="s">
@@ -11270,8 +11349,8 @@
       <c r="B245" s="7">
         <v>30</v>
       </c>
-      <c r="C245" s="171"/>
-      <c r="D245" s="153"/>
+      <c r="C245" s="156"/>
+      <c r="D245" s="174"/>
       <c r="E245" s="8" t="s">
         <v>319</v>
       </c>
@@ -11292,8 +11371,8 @@
       <c r="B246" s="7">
         <v>31</v>
       </c>
-      <c r="C246" s="171"/>
-      <c r="D246" s="153"/>
+      <c r="C246" s="156"/>
+      <c r="D246" s="174"/>
       <c r="E246" s="8" t="s">
         <v>320</v>
       </c>
@@ -11314,8 +11393,8 @@
       <c r="B247" s="7">
         <v>32</v>
       </c>
-      <c r="C247" s="171"/>
-      <c r="D247" s="153"/>
+      <c r="C247" s="156"/>
+      <c r="D247" s="174"/>
       <c r="E247" s="8" t="s">
         <v>321</v>
       </c>
@@ -11336,8 +11415,8 @@
       <c r="B248" s="7">
         <v>33</v>
       </c>
-      <c r="C248" s="171"/>
-      <c r="D248" s="153"/>
+      <c r="C248" s="156"/>
+      <c r="D248" s="174"/>
       <c r="E248" s="8" t="s">
         <v>322</v>
       </c>
@@ -11358,8 +11437,8 @@
       <c r="B249" s="24">
         <v>34</v>
       </c>
-      <c r="C249" s="172"/>
-      <c r="D249" s="154"/>
+      <c r="C249" s="157"/>
+      <c r="D249" s="175"/>
       <c r="E249" s="17" t="s">
         <v>323</v>
       </c>
@@ -11380,10 +11459,10 @@
       <c r="B250" s="7">
         <v>1</v>
       </c>
-      <c r="C250" s="161" t="s">
+      <c r="C250" s="158" t="s">
         <v>324</v>
       </c>
-      <c r="D250" s="152" t="s">
+      <c r="D250" s="173" t="s">
         <v>325</v>
       </c>
       <c r="E250" s="8" t="s">
@@ -11406,8 +11485,8 @@
       <c r="B251" s="7">
         <v>2</v>
       </c>
-      <c r="C251" s="162"/>
-      <c r="D251" s="153"/>
+      <c r="C251" s="159"/>
+      <c r="D251" s="174"/>
       <c r="E251" s="8" t="s">
         <v>327</v>
       </c>
@@ -11428,8 +11507,8 @@
       <c r="B252" s="7">
         <v>3</v>
       </c>
-      <c r="C252" s="162"/>
-      <c r="D252" s="153"/>
+      <c r="C252" s="159"/>
+      <c r="D252" s="174"/>
       <c r="E252" s="8" t="s">
         <v>328</v>
       </c>
@@ -11450,8 +11529,8 @@
       <c r="B253" s="7">
         <v>4</v>
       </c>
-      <c r="C253" s="162"/>
-      <c r="D253" s="153"/>
+      <c r="C253" s="159"/>
+      <c r="D253" s="174"/>
       <c r="E253" s="8" t="s">
         <v>329</v>
       </c>
@@ -11472,8 +11551,8 @@
       <c r="B254" s="7">
         <v>5</v>
       </c>
-      <c r="C254" s="162"/>
-      <c r="D254" s="153"/>
+      <c r="C254" s="159"/>
+      <c r="D254" s="174"/>
       <c r="E254" s="8" t="s">
         <v>330</v>
       </c>
@@ -11494,8 +11573,8 @@
       <c r="B255" s="7">
         <v>6</v>
       </c>
-      <c r="C255" s="162"/>
-      <c r="D255" s="153"/>
+      <c r="C255" s="159"/>
+      <c r="D255" s="174"/>
       <c r="E255" s="8" t="s">
         <v>331</v>
       </c>
@@ -11516,8 +11595,8 @@
       <c r="B256" s="7">
         <v>7</v>
       </c>
-      <c r="C256" s="162"/>
-      <c r="D256" s="153"/>
+      <c r="C256" s="159"/>
+      <c r="D256" s="174"/>
       <c r="E256" s="8" t="s">
         <v>332</v>
       </c>
@@ -11538,8 +11617,8 @@
       <c r="B257" s="7">
         <v>8</v>
       </c>
-      <c r="C257" s="162"/>
-      <c r="D257" s="154"/>
+      <c r="C257" s="159"/>
+      <c r="D257" s="175"/>
       <c r="E257" s="8" t="s">
         <v>333</v>
       </c>
@@ -11560,8 +11639,8 @@
       <c r="B258" s="7">
         <v>9</v>
       </c>
-      <c r="C258" s="162"/>
-      <c r="D258" s="152" t="s">
+      <c r="C258" s="159"/>
+      <c r="D258" s="173" t="s">
         <v>334</v>
       </c>
       <c r="E258" s="8" t="s">
@@ -11584,8 +11663,8 @@
       <c r="B259" s="7">
         <v>10</v>
       </c>
-      <c r="C259" s="162"/>
-      <c r="D259" s="154"/>
+      <c r="C259" s="159"/>
+      <c r="D259" s="175"/>
       <c r="E259" s="8" t="s">
         <v>336</v>
       </c>
@@ -11606,8 +11685,8 @@
       <c r="B260" s="7">
         <v>11</v>
       </c>
-      <c r="C260" s="162"/>
-      <c r="D260" s="152" t="s">
+      <c r="C260" s="159"/>
+      <c r="D260" s="173" t="s">
         <v>337</v>
       </c>
       <c r="E260" s="8" t="s">
@@ -11630,8 +11709,8 @@
       <c r="B261" s="7">
         <v>12</v>
       </c>
-      <c r="C261" s="162"/>
-      <c r="D261" s="153"/>
+      <c r="C261" s="159"/>
+      <c r="D261" s="174"/>
       <c r="E261" s="8" t="s">
         <v>339</v>
       </c>
@@ -11652,8 +11731,8 @@
       <c r="B262" s="7">
         <v>13</v>
       </c>
-      <c r="C262" s="162"/>
-      <c r="D262" s="153"/>
+      <c r="C262" s="159"/>
+      <c r="D262" s="174"/>
       <c r="E262" s="8" t="s">
         <v>340</v>
       </c>
@@ -11674,8 +11753,8 @@
       <c r="B263" s="7">
         <v>14</v>
       </c>
-      <c r="C263" s="162"/>
-      <c r="D263" s="153"/>
+      <c r="C263" s="159"/>
+      <c r="D263" s="174"/>
       <c r="E263" s="8" t="s">
         <v>341</v>
       </c>
@@ -11696,8 +11775,8 @@
       <c r="B264" s="7">
         <v>15</v>
       </c>
-      <c r="C264" s="162"/>
-      <c r="D264" s="153"/>
+      <c r="C264" s="159"/>
+      <c r="D264" s="174"/>
       <c r="E264" s="8" t="s">
         <v>342</v>
       </c>
@@ -11718,8 +11797,8 @@
       <c r="B265" s="24">
         <v>16</v>
       </c>
-      <c r="C265" s="163"/>
-      <c r="D265" s="154"/>
+      <c r="C265" s="160"/>
+      <c r="D265" s="175"/>
       <c r="E265" s="17" t="s">
         <v>343</v>
       </c>
@@ -11740,10 +11819,10 @@
       <c r="B266" s="7">
         <v>1</v>
       </c>
-      <c r="C266" s="164" t="s">
+      <c r="C266" s="161" t="s">
         <v>344</v>
       </c>
-      <c r="D266" s="152" t="s">
+      <c r="D266" s="173" t="s">
         <v>345</v>
       </c>
       <c r="E266" s="8" t="s">
@@ -11766,8 +11845,8 @@
       <c r="B267" s="7">
         <v>2</v>
       </c>
-      <c r="C267" s="165"/>
-      <c r="D267" s="153"/>
+      <c r="C267" s="162"/>
+      <c r="D267" s="174"/>
       <c r="E267" s="8" t="s">
         <v>347</v>
       </c>
@@ -11788,8 +11867,8 @@
       <c r="B268" s="7">
         <v>3</v>
       </c>
-      <c r="C268" s="165"/>
-      <c r="D268" s="153"/>
+      <c r="C268" s="162"/>
+      <c r="D268" s="174"/>
       <c r="E268" s="8" t="s">
         <v>348</v>
       </c>
@@ -11810,8 +11889,8 @@
       <c r="B269" s="7">
         <v>4</v>
       </c>
-      <c r="C269" s="165"/>
-      <c r="D269" s="153"/>
+      <c r="C269" s="162"/>
+      <c r="D269" s="174"/>
       <c r="E269" s="8" t="s">
         <v>349</v>
       </c>
@@ -11832,8 +11911,8 @@
       <c r="B270" s="7">
         <v>5</v>
       </c>
-      <c r="C270" s="165"/>
-      <c r="D270" s="154"/>
+      <c r="C270" s="162"/>
+      <c r="D270" s="175"/>
       <c r="E270" s="8" t="s">
         <v>350</v>
       </c>
@@ -11854,8 +11933,8 @@
       <c r="B271" s="7">
         <v>6</v>
       </c>
-      <c r="C271" s="165"/>
-      <c r="D271" s="152" t="s">
+      <c r="C271" s="162"/>
+      <c r="D271" s="173" t="s">
         <v>351</v>
       </c>
       <c r="E271" s="8" t="s">
@@ -11878,8 +11957,8 @@
       <c r="B272" s="7">
         <v>7</v>
       </c>
-      <c r="C272" s="166"/>
-      <c r="D272" s="154"/>
+      <c r="C272" s="163"/>
+      <c r="D272" s="175"/>
       <c r="E272" s="8" t="s">
         <v>353</v>
       </c>
@@ -11914,10 +11993,10 @@
       <c r="B274" s="7">
         <v>1</v>
       </c>
-      <c r="C274" s="179" t="s">
+      <c r="C274" s="164" t="s">
         <v>355</v>
       </c>
-      <c r="D274" s="182" t="s">
+      <c r="D274" s="176" t="s">
         <v>356</v>
       </c>
       <c r="E274" s="13" t="s">
@@ -11940,8 +12019,8 @@
       <c r="B275" s="7">
         <v>2</v>
       </c>
-      <c r="C275" s="180"/>
-      <c r="D275" s="183"/>
+      <c r="C275" s="165"/>
+      <c r="D275" s="177"/>
       <c r="E275" s="13" t="s">
         <v>358</v>
       </c>
@@ -11962,8 +12041,8 @@
       <c r="B276" s="7">
         <v>3</v>
       </c>
-      <c r="C276" s="180"/>
-      <c r="D276" s="183"/>
+      <c r="C276" s="165"/>
+      <c r="D276" s="177"/>
       <c r="E276" s="8" t="s">
         <v>359</v>
       </c>
@@ -11984,8 +12063,8 @@
       <c r="B277" s="7">
         <v>4</v>
       </c>
-      <c r="C277" s="180"/>
-      <c r="D277" s="183"/>
+      <c r="C277" s="165"/>
+      <c r="D277" s="177"/>
       <c r="E277" s="8" t="s">
         <v>360</v>
       </c>
@@ -12006,8 +12085,8 @@
       <c r="B278" s="7">
         <v>5</v>
       </c>
-      <c r="C278" s="180"/>
-      <c r="D278" s="183"/>
+      <c r="C278" s="165"/>
+      <c r="D278" s="177"/>
       <c r="E278" s="8" t="s">
         <v>361</v>
       </c>
@@ -12028,8 +12107,8 @@
       <c r="B279" s="7">
         <v>6</v>
       </c>
-      <c r="C279" s="180"/>
-      <c r="D279" s="183"/>
+      <c r="C279" s="165"/>
+      <c r="D279" s="177"/>
       <c r="E279" s="8" t="s">
         <v>362</v>
       </c>
@@ -12050,8 +12129,8 @@
       <c r="B280" s="7">
         <v>7</v>
       </c>
-      <c r="C280" s="180"/>
-      <c r="D280" s="183"/>
+      <c r="C280" s="165"/>
+      <c r="D280" s="177"/>
       <c r="E280" s="8" t="s">
         <v>363</v>
       </c>
@@ -12072,8 +12151,8 @@
       <c r="B281" s="7">
         <v>8</v>
       </c>
-      <c r="C281" s="180"/>
-      <c r="D281" s="184"/>
+      <c r="C281" s="165"/>
+      <c r="D281" s="178"/>
       <c r="E281" s="13" t="s">
         <v>364</v>
       </c>
@@ -12094,8 +12173,8 @@
       <c r="B282" s="7">
         <v>9</v>
       </c>
-      <c r="C282" s="180"/>
-      <c r="D282" s="182" t="s">
+      <c r="C282" s="165"/>
+      <c r="D282" s="176" t="s">
         <v>365</v>
       </c>
       <c r="E282" s="8" t="s">
@@ -12118,8 +12197,8 @@
       <c r="B283" s="7">
         <v>10</v>
       </c>
-      <c r="C283" s="180"/>
-      <c r="D283" s="183"/>
+      <c r="C283" s="165"/>
+      <c r="D283" s="177"/>
       <c r="E283" s="13" t="s">
         <v>367</v>
       </c>
@@ -12140,8 +12219,8 @@
       <c r="B284" s="7">
         <v>11</v>
       </c>
-      <c r="C284" s="180"/>
-      <c r="D284" s="183"/>
+      <c r="C284" s="165"/>
+      <c r="D284" s="177"/>
       <c r="E284" s="13" t="s">
         <v>368</v>
       </c>
@@ -12162,8 +12241,8 @@
       <c r="B285" s="7">
         <v>12</v>
       </c>
-      <c r="C285" s="180"/>
-      <c r="D285" s="183"/>
+      <c r="C285" s="165"/>
+      <c r="D285" s="177"/>
       <c r="E285" s="13" t="s">
         <v>369</v>
       </c>
@@ -12184,8 +12263,8 @@
       <c r="B286" s="7">
         <v>13</v>
       </c>
-      <c r="C286" s="180"/>
-      <c r="D286" s="183"/>
+      <c r="C286" s="165"/>
+      <c r="D286" s="177"/>
       <c r="E286" s="13" t="s">
         <v>370</v>
       </c>
@@ -12206,8 +12285,8 @@
       <c r="B287" s="7">
         <v>14</v>
       </c>
-      <c r="C287" s="180"/>
-      <c r="D287" s="183"/>
+      <c r="C287" s="165"/>
+      <c r="D287" s="177"/>
       <c r="E287" s="13" t="s">
         <v>371</v>
       </c>
@@ -12228,8 +12307,8 @@
       <c r="B288" s="7">
         <v>15</v>
       </c>
-      <c r="C288" s="180"/>
-      <c r="D288" s="184"/>
+      <c r="C288" s="165"/>
+      <c r="D288" s="178"/>
       <c r="E288" s="13" t="s">
         <v>372</v>
       </c>
@@ -12250,8 +12329,8 @@
       <c r="B289" s="7">
         <v>16</v>
       </c>
-      <c r="C289" s="180"/>
-      <c r="D289" s="182" t="s">
+      <c r="C289" s="165"/>
+      <c r="D289" s="176" t="s">
         <v>373</v>
       </c>
       <c r="E289" s="13" t="s">
@@ -12274,8 +12353,8 @@
       <c r="B290" s="7">
         <v>17</v>
       </c>
-      <c r="C290" s="180"/>
-      <c r="D290" s="183"/>
+      <c r="C290" s="165"/>
+      <c r="D290" s="177"/>
       <c r="E290" s="8" t="s">
         <v>375</v>
       </c>
@@ -12296,8 +12375,8 @@
       <c r="B291" s="7">
         <v>18</v>
       </c>
-      <c r="C291" s="180"/>
-      <c r="D291" s="183"/>
+      <c r="C291" s="165"/>
+      <c r="D291" s="177"/>
       <c r="E291" s="11" t="s">
         <v>376</v>
       </c>
@@ -12318,8 +12397,8 @@
       <c r="B292" s="24">
         <v>19</v>
       </c>
-      <c r="C292" s="181"/>
-      <c r="D292" s="184"/>
+      <c r="C292" s="166"/>
+      <c r="D292" s="178"/>
       <c r="E292" s="20" t="s">
         <v>377</v>
       </c>
@@ -12340,10 +12419,10 @@
       <c r="B293" s="7">
         <v>1</v>
       </c>
-      <c r="C293" s="170" t="s">
+      <c r="C293" s="155" t="s">
         <v>378</v>
       </c>
-      <c r="D293" s="152" t="s">
+      <c r="D293" s="173" t="s">
         <v>379</v>
       </c>
       <c r="E293" s="8" t="s">
@@ -12366,8 +12445,8 @@
       <c r="B294" s="7">
         <v>2</v>
       </c>
-      <c r="C294" s="171"/>
-      <c r="D294" s="153"/>
+      <c r="C294" s="156"/>
+      <c r="D294" s="174"/>
       <c r="E294" s="8" t="s">
         <v>381</v>
       </c>
@@ -12388,8 +12467,8 @@
       <c r="B295" s="7">
         <v>3</v>
       </c>
-      <c r="C295" s="171"/>
-      <c r="D295" s="154"/>
+      <c r="C295" s="156"/>
+      <c r="D295" s="175"/>
       <c r="E295" s="8" t="s">
         <v>382</v>
       </c>
@@ -12408,8 +12487,8 @@
       <c r="B296" s="7">
         <v>4</v>
       </c>
-      <c r="C296" s="171"/>
-      <c r="D296" s="152" t="s">
+      <c r="C296" s="156"/>
+      <c r="D296" s="173" t="s">
         <v>383</v>
       </c>
       <c r="E296" s="37" t="s">
@@ -12432,8 +12511,8 @@
       <c r="B297" s="7">
         <v>5</v>
       </c>
-      <c r="C297" s="171"/>
-      <c r="D297" s="153"/>
+      <c r="C297" s="156"/>
+      <c r="D297" s="174"/>
       <c r="E297" s="8" t="s">
         <v>385</v>
       </c>
@@ -12454,8 +12533,8 @@
       <c r="B298" s="7">
         <v>6</v>
       </c>
-      <c r="C298" s="171"/>
-      <c r="D298" s="153"/>
+      <c r="C298" s="156"/>
+      <c r="D298" s="174"/>
       <c r="E298" s="8" t="s">
         <v>386</v>
       </c>
@@ -12476,8 +12555,8 @@
       <c r="B299" s="7">
         <v>7</v>
       </c>
-      <c r="C299" s="171"/>
-      <c r="D299" s="153"/>
+      <c r="C299" s="156"/>
+      <c r="D299" s="174"/>
       <c r="E299" s="8" t="s">
         <v>387</v>
       </c>
@@ -12498,8 +12577,8 @@
       <c r="B300" s="7">
         <v>8</v>
       </c>
-      <c r="C300" s="171"/>
-      <c r="D300" s="154"/>
+      <c r="C300" s="156"/>
+      <c r="D300" s="175"/>
       <c r="E300" s="8" t="s">
         <v>388</v>
       </c>
@@ -12520,8 +12599,8 @@
       <c r="B301" s="7">
         <v>9</v>
       </c>
-      <c r="C301" s="171"/>
-      <c r="D301" s="152" t="s">
+      <c r="C301" s="156"/>
+      <c r="D301" s="173" t="s">
         <v>389</v>
       </c>
       <c r="E301" s="8" t="s">
@@ -12544,8 +12623,8 @@
       <c r="B302" s="7">
         <v>10</v>
       </c>
-      <c r="C302" s="171"/>
-      <c r="D302" s="153"/>
+      <c r="C302" s="156"/>
+      <c r="D302" s="174"/>
       <c r="E302" s="8" t="s">
         <v>391</v>
       </c>
@@ -12566,8 +12645,8 @@
       <c r="B303" s="7">
         <v>11</v>
       </c>
-      <c r="C303" s="171"/>
-      <c r="D303" s="154"/>
+      <c r="C303" s="156"/>
+      <c r="D303" s="175"/>
       <c r="E303" s="8" t="s">
         <v>392</v>
       </c>
@@ -12588,8 +12667,8 @@
       <c r="B304" s="7">
         <v>12</v>
       </c>
-      <c r="C304" s="171"/>
-      <c r="D304" s="152" t="s">
+      <c r="C304" s="156"/>
+      <c r="D304" s="173" t="s">
         <v>393</v>
       </c>
       <c r="E304" s="8" t="s">
@@ -12612,8 +12691,8 @@
       <c r="B305" s="7">
         <v>13</v>
       </c>
-      <c r="C305" s="171"/>
-      <c r="D305" s="153"/>
+      <c r="C305" s="156"/>
+      <c r="D305" s="174"/>
       <c r="E305" s="8" t="s">
         <v>395</v>
       </c>
@@ -12634,8 +12713,8 @@
       <c r="B306" s="7">
         <v>14</v>
       </c>
-      <c r="C306" s="171"/>
-      <c r="D306" s="153"/>
+      <c r="C306" s="156"/>
+      <c r="D306" s="174"/>
       <c r="E306" s="8" t="s">
         <v>396</v>
       </c>
@@ -12656,8 +12735,8 @@
       <c r="B307" s="24">
         <v>15</v>
       </c>
-      <c r="C307" s="172"/>
-      <c r="D307" s="154"/>
+      <c r="C307" s="157"/>
+      <c r="D307" s="175"/>
       <c r="E307" s="17" t="s">
         <v>397</v>
       </c>
@@ -12678,10 +12757,10 @@
       <c r="B308" s="7">
         <v>1</v>
       </c>
-      <c r="C308" s="197" t="s">
+      <c r="C308" s="167" t="s">
         <v>398</v>
       </c>
-      <c r="D308" s="182" t="s">
+      <c r="D308" s="176" t="s">
         <v>399</v>
       </c>
       <c r="E308" s="13" t="s">
@@ -12704,8 +12783,8 @@
       <c r="B309" s="7">
         <v>2</v>
       </c>
-      <c r="C309" s="198"/>
-      <c r="D309" s="183"/>
+      <c r="C309" s="168"/>
+      <c r="D309" s="177"/>
       <c r="E309" s="8" t="s">
         <v>401</v>
       </c>
@@ -12726,8 +12805,8 @@
       <c r="B310" s="7">
         <v>3</v>
       </c>
-      <c r="C310" s="198"/>
-      <c r="D310" s="183"/>
+      <c r="C310" s="168"/>
+      <c r="D310" s="177"/>
       <c r="E310" s="13" t="s">
         <v>402</v>
       </c>
@@ -12748,8 +12827,8 @@
       <c r="B311" s="7">
         <v>4</v>
       </c>
-      <c r="C311" s="198"/>
-      <c r="D311" s="183"/>
+      <c r="C311" s="168"/>
+      <c r="D311" s="177"/>
       <c r="E311" s="8" t="s">
         <v>403</v>
       </c>
@@ -12770,8 +12849,8 @@
       <c r="B312" s="7">
         <v>5</v>
       </c>
-      <c r="C312" s="198"/>
-      <c r="D312" s="183"/>
+      <c r="C312" s="168"/>
+      <c r="D312" s="177"/>
       <c r="E312" s="13" t="s">
         <v>404</v>
       </c>
@@ -12792,8 +12871,8 @@
       <c r="B313" s="7">
         <v>6</v>
       </c>
-      <c r="C313" s="198"/>
-      <c r="D313" s="183"/>
+      <c r="C313" s="168"/>
+      <c r="D313" s="177"/>
       <c r="E313" s="13" t="s">
         <v>405</v>
       </c>
@@ -12814,8 +12893,8 @@
       <c r="B314" s="7">
         <v>7</v>
       </c>
-      <c r="C314" s="198"/>
-      <c r="D314" s="184"/>
+      <c r="C314" s="168"/>
+      <c r="D314" s="178"/>
       <c r="E314" s="8" t="s">
         <v>406</v>
       </c>
@@ -12836,8 +12915,8 @@
       <c r="B315" s="7">
         <v>8</v>
       </c>
-      <c r="C315" s="198"/>
-      <c r="D315" s="182" t="s">
+      <c r="C315" s="168"/>
+      <c r="D315" s="176" t="s">
         <v>407</v>
       </c>
       <c r="E315" s="13" t="s">
@@ -12860,8 +12939,8 @@
       <c r="B316" s="7">
         <v>9</v>
       </c>
-      <c r="C316" s="198"/>
-      <c r="D316" s="183"/>
+      <c r="C316" s="168"/>
+      <c r="D316" s="177"/>
       <c r="E316" s="8" t="s">
         <v>409</v>
       </c>
@@ -12882,8 +12961,8 @@
       <c r="B317" s="24">
         <v>10</v>
       </c>
-      <c r="C317" s="199"/>
-      <c r="D317" s="184"/>
+      <c r="C317" s="169"/>
+      <c r="D317" s="178"/>
       <c r="E317" s="17" t="s">
         <v>410</v>
       </c>
@@ -12904,10 +12983,10 @@
       <c r="B318" s="7">
         <v>1</v>
       </c>
-      <c r="C318" s="200" t="s">
+      <c r="C318" s="170" t="s">
         <v>411</v>
       </c>
-      <c r="D318" s="182" t="s">
+      <c r="D318" s="176" t="s">
         <v>412</v>
       </c>
       <c r="E318" s="8" t="s">
@@ -12930,8 +13009,8 @@
       <c r="B319" s="7">
         <v>2</v>
       </c>
-      <c r="C319" s="201"/>
-      <c r="D319" s="183"/>
+      <c r="C319" s="171"/>
+      <c r="D319" s="177"/>
       <c r="E319" s="13" t="s">
         <v>414</v>
       </c>
@@ -12952,8 +13031,8 @@
       <c r="B320" s="7">
         <v>3</v>
       </c>
-      <c r="C320" s="201"/>
-      <c r="D320" s="183"/>
+      <c r="C320" s="171"/>
+      <c r="D320" s="177"/>
       <c r="E320" s="8" t="s">
         <v>415</v>
       </c>
@@ -12974,8 +13053,8 @@
       <c r="B321" s="7">
         <v>4</v>
       </c>
-      <c r="C321" s="201"/>
-      <c r="D321" s="183"/>
+      <c r="C321" s="171"/>
+      <c r="D321" s="177"/>
       <c r="E321" s="8" t="s">
         <v>416</v>
       </c>
@@ -12996,8 +13075,8 @@
       <c r="B322" s="7">
         <v>5</v>
       </c>
-      <c r="C322" s="201"/>
-      <c r="D322" s="183"/>
+      <c r="C322" s="171"/>
+      <c r="D322" s="177"/>
       <c r="E322" s="8" t="s">
         <v>417</v>
       </c>
@@ -13018,8 +13097,8 @@
       <c r="B323" s="7">
         <v>6</v>
       </c>
-      <c r="C323" s="201"/>
-      <c r="D323" s="184"/>
+      <c r="C323" s="171"/>
+      <c r="D323" s="178"/>
       <c r="E323" s="29" t="s">
         <v>418</v>
       </c>
@@ -13040,8 +13119,8 @@
       <c r="B324" s="7">
         <v>7</v>
       </c>
-      <c r="C324" s="201"/>
-      <c r="D324" s="182" t="s">
+      <c r="C324" s="171"/>
+      <c r="D324" s="176" t="s">
         <v>419</v>
       </c>
       <c r="E324" s="13" t="s">
@@ -13064,8 +13143,8 @@
       <c r="B325" s="7">
         <v>8</v>
       </c>
-      <c r="C325" s="201"/>
-      <c r="D325" s="183"/>
+      <c r="C325" s="171"/>
+      <c r="D325" s="177"/>
       <c r="E325" s="8" t="s">
         <v>421</v>
       </c>
@@ -13086,8 +13165,8 @@
       <c r="B326" s="7">
         <v>9</v>
       </c>
-      <c r="C326" s="201"/>
-      <c r="D326" s="183"/>
+      <c r="C326" s="171"/>
+      <c r="D326" s="177"/>
       <c r="E326" s="8" t="s">
         <v>422</v>
       </c>
@@ -13108,8 +13187,8 @@
       <c r="B327" s="7">
         <v>10</v>
       </c>
-      <c r="C327" s="201"/>
-      <c r="D327" s="183"/>
+      <c r="C327" s="171"/>
+      <c r="D327" s="177"/>
       <c r="E327" s="8" t="s">
         <v>423</v>
       </c>
@@ -13130,8 +13209,8 @@
       <c r="B328" s="7">
         <v>11</v>
       </c>
-      <c r="C328" s="201"/>
-      <c r="D328" s="184"/>
+      <c r="C328" s="171"/>
+      <c r="D328" s="178"/>
       <c r="E328" s="13" t="s">
         <v>424</v>
       </c>
@@ -13152,8 +13231,8 @@
       <c r="B329" s="7">
         <v>12</v>
       </c>
-      <c r="C329" s="201"/>
-      <c r="D329" s="182" t="s">
+      <c r="C329" s="171"/>
+      <c r="D329" s="176" t="s">
         <v>425</v>
       </c>
       <c r="E329" s="8" t="s">
@@ -13176,8 +13255,8 @@
       <c r="B330" s="7">
         <v>13</v>
       </c>
-      <c r="C330" s="201"/>
-      <c r="D330" s="183"/>
+      <c r="C330" s="171"/>
+      <c r="D330" s="177"/>
       <c r="E330" s="8" t="s">
         <v>427</v>
       </c>
@@ -13198,8 +13277,8 @@
       <c r="B331" s="7">
         <v>14</v>
       </c>
-      <c r="C331" s="201"/>
-      <c r="D331" s="183"/>
+      <c r="C331" s="171"/>
+      <c r="D331" s="177"/>
       <c r="E331" s="8" t="s">
         <v>428</v>
       </c>
@@ -13220,8 +13299,8 @@
       <c r="B332" s="7">
         <v>15</v>
       </c>
-      <c r="C332" s="201"/>
-      <c r="D332" s="183"/>
+      <c r="C332" s="171"/>
+      <c r="D332" s="177"/>
       <c r="E332" s="8" t="s">
         <v>429</v>
       </c>
@@ -13242,8 +13321,8 @@
       <c r="B333" s="7">
         <v>16</v>
       </c>
-      <c r="C333" s="201"/>
-      <c r="D333" s="183"/>
+      <c r="C333" s="171"/>
+      <c r="D333" s="177"/>
       <c r="E333" s="8" t="s">
         <v>430</v>
       </c>
@@ -13264,8 +13343,8 @@
       <c r="B334" s="7">
         <v>17</v>
       </c>
-      <c r="C334" s="201"/>
-      <c r="D334" s="183"/>
+      <c r="C334" s="171"/>
+      <c r="D334" s="177"/>
       <c r="E334" s="8" t="s">
         <v>431</v>
       </c>
@@ -13286,8 +13365,8 @@
       <c r="B335" s="7">
         <v>18</v>
       </c>
-      <c r="C335" s="201"/>
-      <c r="D335" s="183"/>
+      <c r="C335" s="171"/>
+      <c r="D335" s="177"/>
       <c r="E335" s="8" t="s">
         <v>432</v>
       </c>
@@ -13308,8 +13387,8 @@
       <c r="B336" s="7">
         <v>19</v>
       </c>
-      <c r="C336" s="201"/>
-      <c r="D336" s="183"/>
+      <c r="C336" s="171"/>
+      <c r="D336" s="177"/>
       <c r="E336" s="8" t="s">
         <v>433</v>
       </c>
@@ -13330,8 +13409,8 @@
       <c r="B337" s="7">
         <v>20</v>
       </c>
-      <c r="C337" s="201"/>
-      <c r="D337" s="184"/>
+      <c r="C337" s="171"/>
+      <c r="D337" s="178"/>
       <c r="E337" s="13" t="s">
         <v>434</v>
       </c>
@@ -13352,8 +13431,8 @@
       <c r="B338" s="7">
         <v>21</v>
       </c>
-      <c r="C338" s="201"/>
-      <c r="D338" s="182" t="s">
+      <c r="C338" s="171"/>
+      <c r="D338" s="176" t="s">
         <v>435</v>
       </c>
       <c r="E338" s="13" t="s">
@@ -13376,8 +13455,8 @@
       <c r="B339" s="7">
         <v>22</v>
       </c>
-      <c r="C339" s="201"/>
-      <c r="D339" s="183"/>
+      <c r="C339" s="171"/>
+      <c r="D339" s="177"/>
       <c r="E339" s="13" t="s">
         <v>437</v>
       </c>
@@ -13398,8 +13477,8 @@
       <c r="B340" s="7">
         <v>23</v>
       </c>
-      <c r="C340" s="201"/>
-      <c r="D340" s="183"/>
+      <c r="C340" s="171"/>
+      <c r="D340" s="177"/>
       <c r="E340" s="13" t="s">
         <v>438</v>
       </c>
@@ -13420,8 +13499,8 @@
       <c r="B341" s="7">
         <v>24</v>
       </c>
-      <c r="C341" s="201"/>
-      <c r="D341" s="183"/>
+      <c r="C341" s="171"/>
+      <c r="D341" s="177"/>
       <c r="E341" s="13" t="s">
         <v>439</v>
       </c>
@@ -13442,8 +13521,8 @@
       <c r="B342" s="24">
         <v>25</v>
       </c>
-      <c r="C342" s="202"/>
-      <c r="D342" s="184"/>
+      <c r="C342" s="172"/>
+      <c r="D342" s="178"/>
       <c r="E342" s="25" t="s">
         <v>440</v>
       </c>
@@ -13464,10 +13543,10 @@
       <c r="B343" s="7">
         <v>1</v>
       </c>
-      <c r="C343" s="167" t="s">
+      <c r="C343" s="152" t="s">
         <v>441</v>
       </c>
-      <c r="D343" s="152" t="s">
+      <c r="D343" s="173" t="s">
         <v>442</v>
       </c>
       <c r="E343" s="8" t="s">
@@ -13496,8 +13575,8 @@
       <c r="B344" s="7">
         <v>2</v>
       </c>
-      <c r="C344" s="168"/>
-      <c r="D344" s="153"/>
+      <c r="C344" s="153"/>
+      <c r="D344" s="174"/>
       <c r="E344" s="8" t="s">
         <v>444</v>
       </c>
@@ -13524,8 +13603,8 @@
       <c r="B345" s="7">
         <v>3</v>
       </c>
-      <c r="C345" s="168"/>
-      <c r="D345" s="153"/>
+      <c r="C345" s="153"/>
+      <c r="D345" s="174"/>
       <c r="E345" s="8" t="s">
         <v>445</v>
       </c>
@@ -13552,8 +13631,8 @@
       <c r="B346" s="7">
         <v>4</v>
       </c>
-      <c r="C346" s="168"/>
-      <c r="D346" s="153"/>
+      <c r="C346" s="153"/>
+      <c r="D346" s="174"/>
       <c r="E346" s="8" t="s">
         <v>446</v>
       </c>
@@ -13580,8 +13659,8 @@
       <c r="B347" s="7">
         <v>5</v>
       </c>
-      <c r="C347" s="168"/>
-      <c r="D347" s="154"/>
+      <c r="C347" s="153"/>
+      <c r="D347" s="175"/>
       <c r="E347" s="8" t="s">
         <v>447</v>
       </c>
@@ -13608,8 +13687,8 @@
       <c r="B348" s="7">
         <v>6</v>
       </c>
-      <c r="C348" s="168"/>
-      <c r="D348" s="152" t="s">
+      <c r="C348" s="153"/>
+      <c r="D348" s="173" t="s">
         <v>448</v>
       </c>
       <c r="E348" s="8" t="s">
@@ -13636,8 +13715,8 @@
       <c r="B349" s="7">
         <v>7</v>
       </c>
-      <c r="C349" s="168"/>
-      <c r="D349" s="153"/>
+      <c r="C349" s="153"/>
+      <c r="D349" s="174"/>
       <c r="E349" s="8" t="s">
         <v>450</v>
       </c>
@@ -13664,8 +13743,8 @@
       <c r="B350" s="7">
         <v>8</v>
       </c>
-      <c r="C350" s="168"/>
-      <c r="D350" s="153"/>
+      <c r="C350" s="153"/>
+      <c r="D350" s="174"/>
       <c r="E350" s="8" t="s">
         <v>451</v>
       </c>
@@ -13692,8 +13771,8 @@
       <c r="B351" s="7">
         <v>9</v>
       </c>
-      <c r="C351" s="168"/>
-      <c r="D351" s="153"/>
+      <c r="C351" s="153"/>
+      <c r="D351" s="174"/>
       <c r="E351" s="8" t="s">
         <v>452</v>
       </c>
@@ -13716,8 +13795,8 @@
       <c r="B352" s="7">
         <v>10</v>
       </c>
-      <c r="C352" s="168"/>
-      <c r="D352" s="153"/>
+      <c r="C352" s="153"/>
+      <c r="D352" s="174"/>
       <c r="E352" s="8" t="s">
         <v>453</v>
       </c>
@@ -13744,8 +13823,8 @@
       <c r="B353" s="7">
         <v>11</v>
       </c>
-      <c r="C353" s="168"/>
-      <c r="D353" s="154"/>
+      <c r="C353" s="153"/>
+      <c r="D353" s="175"/>
       <c r="E353" s="8" t="s">
         <v>454</v>
       </c>
@@ -13766,8 +13845,8 @@
       <c r="B354" s="7">
         <v>12</v>
       </c>
-      <c r="C354" s="168"/>
-      <c r="D354" s="152" t="s">
+      <c r="C354" s="153"/>
+      <c r="D354" s="173" t="s">
         <v>455</v>
       </c>
       <c r="E354" s="8" t="s">
@@ -13794,8 +13873,8 @@
       <c r="B355" s="7">
         <v>13</v>
       </c>
-      <c r="C355" s="168"/>
-      <c r="D355" s="153"/>
+      <c r="C355" s="153"/>
+      <c r="D355" s="174"/>
       <c r="E355" s="8" t="s">
         <v>457</v>
       </c>
@@ -13822,8 +13901,8 @@
       <c r="B356" s="7">
         <v>14</v>
       </c>
-      <c r="C356" s="168"/>
-      <c r="D356" s="153"/>
+      <c r="C356" s="153"/>
+      <c r="D356" s="174"/>
       <c r="E356" s="8" t="s">
         <v>458</v>
       </c>
@@ -13844,8 +13923,8 @@
       <c r="B357" s="7">
         <v>15</v>
       </c>
-      <c r="C357" s="169"/>
-      <c r="D357" s="154"/>
+      <c r="C357" s="154"/>
+      <c r="D357" s="175"/>
       <c r="E357" s="8" t="s">
         <v>459</v>
       </c>
@@ -13860,18 +13939,18 @@
       <c r="J357" s="11"/>
     </row>
     <row r="358" spans="1:10" ht="13.8">
-      <c r="A358" s="191" t="s">
+      <c r="A358" s="188" t="s">
         <v>460</v>
       </c>
-      <c r="B358" s="192"/>
-      <c r="C358" s="192"/>
-      <c r="D358" s="192"/>
-      <c r="E358" s="192"/>
-      <c r="F358" s="192"/>
-      <c r="G358" s="192"/>
-      <c r="H358" s="192"/>
-      <c r="I358" s="192"/>
-      <c r="J358" s="193"/>
+      <c r="B358" s="189"/>
+      <c r="C358" s="189"/>
+      <c r="D358" s="189"/>
+      <c r="E358" s="189"/>
+      <c r="F358" s="189"/>
+      <c r="G358" s="189"/>
+      <c r="H358" s="189"/>
+      <c r="I358" s="189"/>
+      <c r="J358" s="190"/>
     </row>
     <row r="359" spans="1:10" ht="13.8">
       <c r="A359" s="6">
@@ -13880,10 +13959,10 @@
       <c r="B359" s="7">
         <v>1</v>
       </c>
-      <c r="C359" s="170" t="s">
+      <c r="C359" s="155" t="s">
         <v>461</v>
       </c>
-      <c r="D359" s="152" t="s">
+      <c r="D359" s="173" t="s">
         <v>462</v>
       </c>
       <c r="E359" s="8" t="s">
@@ -13906,8 +13985,8 @@
       <c r="B360" s="7">
         <v>2</v>
       </c>
-      <c r="C360" s="171"/>
-      <c r="D360" s="153"/>
+      <c r="C360" s="156"/>
+      <c r="D360" s="174"/>
       <c r="E360" s="8" t="s">
         <v>464</v>
       </c>
@@ -13928,8 +14007,8 @@
       <c r="B361" s="7">
         <v>3</v>
       </c>
-      <c r="C361" s="171"/>
-      <c r="D361" s="153"/>
+      <c r="C361" s="156"/>
+      <c r="D361" s="174"/>
       <c r="E361" s="8" t="s">
         <v>465</v>
       </c>
@@ -13950,8 +14029,8 @@
       <c r="B362" s="7">
         <v>4</v>
       </c>
-      <c r="C362" s="171"/>
-      <c r="D362" s="153"/>
+      <c r="C362" s="156"/>
+      <c r="D362" s="174"/>
       <c r="E362" s="8" t="s">
         <v>466</v>
       </c>
@@ -13972,8 +14051,8 @@
       <c r="B363" s="7">
         <v>5</v>
       </c>
-      <c r="C363" s="171"/>
-      <c r="D363" s="154"/>
+      <c r="C363" s="156"/>
+      <c r="D363" s="175"/>
       <c r="E363" s="8" t="s">
         <v>467</v>
       </c>
@@ -13994,8 +14073,8 @@
       <c r="B364" s="7">
         <v>6</v>
       </c>
-      <c r="C364" s="171"/>
-      <c r="D364" s="152" t="s">
+      <c r="C364" s="156"/>
+      <c r="D364" s="173" t="s">
         <v>468</v>
       </c>
       <c r="E364" s="8" t="s">
@@ -14018,8 +14097,8 @@
       <c r="B365" s="7">
         <v>7</v>
       </c>
-      <c r="C365" s="171"/>
-      <c r="D365" s="153"/>
+      <c r="C365" s="156"/>
+      <c r="D365" s="174"/>
       <c r="E365" s="8" t="s">
         <v>470</v>
       </c>
@@ -14040,8 +14119,8 @@
       <c r="B366" s="7">
         <v>8</v>
       </c>
-      <c r="C366" s="171"/>
-      <c r="D366" s="153"/>
+      <c r="C366" s="156"/>
+      <c r="D366" s="174"/>
       <c r="E366" s="8" t="s">
         <v>471</v>
       </c>
@@ -14062,8 +14141,8 @@
       <c r="B367" s="7">
         <v>9</v>
       </c>
-      <c r="C367" s="171"/>
-      <c r="D367" s="153"/>
+      <c r="C367" s="156"/>
+      <c r="D367" s="174"/>
       <c r="E367" s="8" t="s">
         <v>472</v>
       </c>
@@ -14084,8 +14163,8 @@
       <c r="B368" s="7">
         <v>10</v>
       </c>
-      <c r="C368" s="171"/>
-      <c r="D368" s="153"/>
+      <c r="C368" s="156"/>
+      <c r="D368" s="174"/>
       <c r="E368" s="8" t="s">
         <v>473</v>
       </c>
@@ -14106,8 +14185,8 @@
       <c r="B369" s="7">
         <v>11</v>
       </c>
-      <c r="C369" s="171"/>
-      <c r="D369" s="153"/>
+      <c r="C369" s="156"/>
+      <c r="D369" s="174"/>
       <c r="E369" s="8" t="s">
         <v>474</v>
       </c>
@@ -14128,8 +14207,8 @@
       <c r="B370" s="7">
         <v>12</v>
       </c>
-      <c r="C370" s="171"/>
-      <c r="D370" s="153"/>
+      <c r="C370" s="156"/>
+      <c r="D370" s="174"/>
       <c r="E370" s="8" t="s">
         <v>475</v>
       </c>
@@ -14150,8 +14229,8 @@
       <c r="B371" s="7">
         <v>13</v>
       </c>
-      <c r="C371" s="171"/>
-      <c r="D371" s="154"/>
+      <c r="C371" s="156"/>
+      <c r="D371" s="175"/>
       <c r="E371" s="8" t="s">
         <v>476</v>
       </c>
@@ -14172,8 +14251,8 @@
       <c r="B372" s="7">
         <v>14</v>
       </c>
-      <c r="C372" s="171"/>
-      <c r="D372" s="152" t="s">
+      <c r="C372" s="156"/>
+      <c r="D372" s="173" t="s">
         <v>477</v>
       </c>
       <c r="E372" s="8" t="s">
@@ -14196,8 +14275,8 @@
       <c r="B373" s="7">
         <v>15</v>
       </c>
-      <c r="C373" s="171"/>
-      <c r="D373" s="153"/>
+      <c r="C373" s="156"/>
+      <c r="D373" s="174"/>
       <c r="E373" s="11" t="s">
         <v>479</v>
       </c>
@@ -14218,8 +14297,8 @@
       <c r="B374" s="7">
         <v>16</v>
       </c>
-      <c r="C374" s="171"/>
-      <c r="D374" s="153"/>
+      <c r="C374" s="156"/>
+      <c r="D374" s="174"/>
       <c r="E374" s="8" t="s">
         <v>480</v>
       </c>
@@ -14240,8 +14319,8 @@
       <c r="B375" s="7">
         <v>17</v>
       </c>
-      <c r="C375" s="171"/>
-      <c r="D375" s="154"/>
+      <c r="C375" s="156"/>
+      <c r="D375" s="175"/>
       <c r="E375" s="8" t="s">
         <v>481</v>
       </c>
@@ -14262,8 +14341,8 @@
       <c r="B376" s="7">
         <v>18</v>
       </c>
-      <c r="C376" s="171"/>
-      <c r="D376" s="152" t="s">
+      <c r="C376" s="156"/>
+      <c r="D376" s="173" t="s">
         <v>482</v>
       </c>
       <c r="E376" s="8" t="s">
@@ -14286,8 +14365,8 @@
       <c r="B377" s="7">
         <v>19</v>
       </c>
-      <c r="C377" s="171"/>
-      <c r="D377" s="153"/>
+      <c r="C377" s="156"/>
+      <c r="D377" s="174"/>
       <c r="E377" s="8" t="s">
         <v>484</v>
       </c>
@@ -14308,8 +14387,8 @@
       <c r="B378" s="7">
         <v>20</v>
       </c>
-      <c r="C378" s="171"/>
-      <c r="D378" s="153"/>
+      <c r="C378" s="156"/>
+      <c r="D378" s="174"/>
       <c r="E378" s="8" t="s">
         <v>485</v>
       </c>
@@ -14330,8 +14409,8 @@
       <c r="B379" s="7">
         <v>21</v>
       </c>
-      <c r="C379" s="171"/>
-      <c r="D379" s="153"/>
+      <c r="C379" s="156"/>
+      <c r="D379" s="174"/>
       <c r="E379" s="8" t="s">
         <v>486</v>
       </c>
@@ -14352,8 +14431,8 @@
       <c r="B380" s="24">
         <v>22</v>
       </c>
-      <c r="C380" s="172"/>
-      <c r="D380" s="154"/>
+      <c r="C380" s="157"/>
+      <c r="D380" s="175"/>
       <c r="E380" s="17" t="s">
         <v>487</v>
       </c>
@@ -14374,10 +14453,10 @@
       <c r="B381" s="7">
         <v>1</v>
       </c>
-      <c r="C381" s="161" t="s">
+      <c r="C381" s="158" t="s">
         <v>488</v>
       </c>
-      <c r="D381" s="152" t="s">
+      <c r="D381" s="173" t="s">
         <v>489</v>
       </c>
       <c r="E381" s="8" t="s">
@@ -14400,8 +14479,8 @@
       <c r="B382" s="7">
         <v>2</v>
       </c>
-      <c r="C382" s="162"/>
-      <c r="D382" s="153"/>
+      <c r="C382" s="159"/>
+      <c r="D382" s="174"/>
       <c r="E382" s="8" t="s">
         <v>491</v>
       </c>
@@ -14422,8 +14501,8 @@
       <c r="B383" s="7">
         <v>3</v>
       </c>
-      <c r="C383" s="162"/>
-      <c r="D383" s="153"/>
+      <c r="C383" s="159"/>
+      <c r="D383" s="174"/>
       <c r="E383" s="8" t="s">
         <v>492</v>
       </c>
@@ -14444,8 +14523,8 @@
       <c r="B384" s="7">
         <v>4</v>
       </c>
-      <c r="C384" s="162"/>
-      <c r="D384" s="153"/>
+      <c r="C384" s="159"/>
+      <c r="D384" s="174"/>
       <c r="E384" s="8" t="s">
         <v>493</v>
       </c>
@@ -14466,8 +14545,8 @@
       <c r="B385" s="7">
         <v>5</v>
       </c>
-      <c r="C385" s="162"/>
-      <c r="D385" s="153"/>
+      <c r="C385" s="159"/>
+      <c r="D385" s="174"/>
       <c r="E385" s="8" t="s">
         <v>494</v>
       </c>
@@ -14488,8 +14567,8 @@
       <c r="B386" s="7">
         <v>6</v>
       </c>
-      <c r="C386" s="162"/>
-      <c r="D386" s="154"/>
+      <c r="C386" s="159"/>
+      <c r="D386" s="175"/>
       <c r="E386" s="8" t="s">
         <v>495</v>
       </c>
@@ -14510,8 +14589,8 @@
       <c r="B387" s="7">
         <v>7</v>
       </c>
-      <c r="C387" s="162"/>
-      <c r="D387" s="152" t="s">
+      <c r="C387" s="159"/>
+      <c r="D387" s="173" t="s">
         <v>496</v>
       </c>
       <c r="E387" s="8" t="s">
@@ -14534,8 +14613,8 @@
       <c r="B388" s="7">
         <v>8</v>
       </c>
-      <c r="C388" s="162"/>
-      <c r="D388" s="153"/>
+      <c r="C388" s="159"/>
+      <c r="D388" s="174"/>
       <c r="E388" s="8" t="s">
         <v>498</v>
       </c>
@@ -14556,8 +14635,8 @@
       <c r="B389" s="7">
         <v>9</v>
       </c>
-      <c r="C389" s="162"/>
-      <c r="D389" s="153"/>
+      <c r="C389" s="159"/>
+      <c r="D389" s="174"/>
       <c r="E389" s="8" t="s">
         <v>499</v>
       </c>
@@ -14578,8 +14657,8 @@
       <c r="B390" s="7">
         <v>10</v>
       </c>
-      <c r="C390" s="162"/>
-      <c r="D390" s="153"/>
+      <c r="C390" s="159"/>
+      <c r="D390" s="174"/>
       <c r="E390" s="8" t="s">
         <v>500</v>
       </c>
@@ -14600,8 +14679,8 @@
       <c r="B391" s="7">
         <v>11</v>
       </c>
-      <c r="C391" s="162"/>
-      <c r="D391" s="153"/>
+      <c r="C391" s="159"/>
+      <c r="D391" s="174"/>
       <c r="E391" s="8" t="s">
         <v>501</v>
       </c>
@@ -14622,8 +14701,8 @@
       <c r="B392" s="7">
         <v>12</v>
       </c>
-      <c r="C392" s="162"/>
-      <c r="D392" s="153"/>
+      <c r="C392" s="159"/>
+      <c r="D392" s="174"/>
       <c r="E392" s="8" t="s">
         <v>502</v>
       </c>
@@ -14644,8 +14723,8 @@
       <c r="B393" s="7">
         <v>13</v>
       </c>
-      <c r="C393" s="162"/>
-      <c r="D393" s="153"/>
+      <c r="C393" s="159"/>
+      <c r="D393" s="174"/>
       <c r="E393" s="8" t="s">
         <v>503</v>
       </c>
@@ -14666,8 +14745,8 @@
       <c r="B394" s="7">
         <v>14</v>
       </c>
-      <c r="C394" s="162"/>
-      <c r="D394" s="153"/>
+      <c r="C394" s="159"/>
+      <c r="D394" s="174"/>
       <c r="E394" s="8" t="s">
         <v>504</v>
       </c>
@@ -14688,8 +14767,8 @@
       <c r="B395" s="7">
         <v>15</v>
       </c>
-      <c r="C395" s="162"/>
-      <c r="D395" s="153"/>
+      <c r="C395" s="159"/>
+      <c r="D395" s="174"/>
       <c r="E395" s="8" t="s">
         <v>505</v>
       </c>
@@ -14710,8 +14789,8 @@
       <c r="B396" s="7">
         <v>16</v>
       </c>
-      <c r="C396" s="162"/>
-      <c r="D396" s="154"/>
+      <c r="C396" s="159"/>
+      <c r="D396" s="175"/>
       <c r="E396" s="8" t="s">
         <v>506</v>
       </c>
@@ -14732,8 +14811,8 @@
       <c r="B397" s="7">
         <v>17</v>
       </c>
-      <c r="C397" s="162"/>
-      <c r="D397" s="152" t="s">
+      <c r="C397" s="159"/>
+      <c r="D397" s="173" t="s">
         <v>507</v>
       </c>
       <c r="E397" s="8" t="s">
@@ -14756,8 +14835,8 @@
       <c r="B398" s="7">
         <v>18</v>
       </c>
-      <c r="C398" s="162"/>
-      <c r="D398" s="153"/>
+      <c r="C398" s="159"/>
+      <c r="D398" s="174"/>
       <c r="E398" s="8" t="s">
         <v>509</v>
       </c>
@@ -14778,8 +14857,8 @@
       <